--- a/book.xlsx
+++ b/book.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>chapter</t>
   </si>
@@ -94,6 +94,34 @@
   <si>
     <t>这一章的核心就在“冲”字，冲是一个组合字，大家把它两点放平，这个冲就得到了正确的理解，冲就是二中。二就是阴和阳。道是一阴一阳之为道。冲的本义的形象在讲什么？两股水。这个水冲到那个里边，两个水就掺到一块了。这是讲它是两种力量的作用，是讲它是一个动态的。所以现在我们来理解这个冲字，然后这一章就变得容易理解了。道冲，道就是阴阳两者的相互中和，二中，阴和阳的相互中和。
 第三章第四章，都在强调道是万物的本源，老子一开始第一章第二章讲完了，还是觉得有点不放心，还在补充，还在添砖加瓦。就这个事情，拿一个具体的例证，不尚贤、不贵难得之货、不见可欲，具体的事物，因为这个是大家常做的，然后得出结论，然后告诉大家，我讲这个道，确实是重要的一种思维的智慧。阴阳两者，道冲。了解这个，那我们的思想水平，我们的境界，我们对事情问题的认知，就会有非常明显的提高。阴阳两者的相互综合，相互作用，相互转化，在动态中形成的像我们的太极图，始终你怎么转，它都是那个样子。既然是阴阳两者相互作用产生的万事万物，所以万物负阴而抱阳。万事万物都承载着阴，环抱着阳，都有阴阳两个方面。万物负阴而抱阳，冲气以为和，这个气就是阴阳二气，两者参与到一起，形成这个和谐的世界。</t>
+  </si>
+  <si>
+    <t>第五章</t>
+  </si>
+  <si>
+    <t>天地不仁，以万物为刍（chú）狗；圣人不仁，以百姓为刍狗。天地之间，其犹橐籥（tuó yuè）乎？虚而不屈（qū），动而愈出。多言数（shuò）穷，不如守中。</t>
+  </si>
+  <si>
+    <t>天地无所偏爱，将万物像刍狗（草扎的狗）一样平等看待；圣人没有偏私，对百姓像刍狗一样平等看待。天地这个大空间，不就像一个大风箱吗？因其中间虚静才能鼓出风，越动鼓出的风越多。政令繁多会招致败亡，不如保持虚静才能恰如其分。</t>
+  </si>
+  <si>
+    <t>第五章讲“天地不仁，以万物为刍狗”，然后告诉一个好的领导者，应该是这样，圣人不仁，以百姓为刍狗。你就应该有这样的一种公平，无偏私，制定这个规则，制定法令谁都不要例外。所以这个地方讲的道理是天地对万事万物都是平等的。他对万事万物是没有关心的。然后就讲，就问题里引起最大争议的就圣人不仁。如果有人说圣人对人世间的很多罪过也应该忍心，就像有人说什么叫哲学家，你在我门口杀人我都无动于衷，那就已经练成哲学家了，这完全是一种错误。有人就把它解释成这样，这是不对的，圣人对万事万物也应该是平等的。你让他们自己去奋斗，让他们自己去努力。不要你认为弱，你就一定要想去帮他，你这就叫有偏私。万事万物都是一样的，一律公平，没有偏私。所以道家讲的不仁是“大仁”。
+天地根本不关心人世间的事。什么意思？你别老去麻烦他。你别老以为是有事，天会罩着你。要靠你自己。你别老以为天会关照你，别老去麻烦他，很多是天道酬勤靠自己。这个地方讲的就是这样的一个道理。天地对人世间的事情不关心，万事万物在他的眼里都是平等的。万事万物在他眼里，无所爱惜。就像草扎的狗，草扎的狗原来用来干吗的 —— 是用来祭祀的。祭祀之前大家对它很尊重。祭祀之后就扔在那没人管。万事万物在我眼里，就是叫无所爱惜。然后告诉一个好的领导者，应该是这样，圣人不仁，以百姓为刍狗。你就应该有这样的一种公平，无偏私，制定这个规则，制定法令谁都不要例外。第二个部分。“天地之间，其犹橐籥乎。”像风箱一样。风箱不能乱动，乱动，你在那地方那就麻烦了。它本身是静的，中间是空的，虚静，所以你动的时候前边有虚静为前提，动的时候才能够不断鼓出风来，这鼓出是讲应用。所以下边就讲政令也应该如此，像风箱一样，不要变来变去动来动去，位置挪来挪去，换来换去。讲究虚静，这样政令简要大道至简，这样才能够恰如其分，不如守中，恰如其分。</t>
+  </si>
+  <si>
+    <t>第六章</t>
+  </si>
+  <si>
+    <t>谷神不死，是谓玄牝（pìn）。玄牝之门，是谓天地根。绵绵若存，用之不勤。</t>
+  </si>
+  <si>
+    <t>道虚无莫测 永存不灭，称为“玄牝”，“玄牝”之门，是天地万物的根源。连绵不绝地永存，取之不尽用之不竭。</t>
+  </si>
+  <si>
+    <t>这一章讲了一个非常重要的道理，对母亲的尊重。很多章，特别是道教，把这一章解释得简直就玄而又玄。大家知道这一章讲的是一个什么事呢？谷神，把它断开，谷神，谷神不死，是谓玄牝。牝就是女性的生殖器，指代母亲。而前边这个谷恰恰也是对它这个形象的描述。所以这一章在讲什么，谷神不死，是谓玄牝，玄牝之门，是谓天地根。
+你看人生命的产生，虽然是男女结合才产生生命，但大家都知道这生命它是女性，从牝、谷产生的。
+所以老子认为把这个事情扩大了，天地也是一样。道生万物就跟人的生命产生的道理是一样的。老子将“道”比作孕育一切的母体，强调其柔韧、生生不息的特性。你在一种文化里边，如果没有对母亲的敬畏和尊重，这文化其他方面都会崩塌。
+你看人生命的产生，虽然是男女结合才产生生命，但大家都知道这生命它是女性，从牝、谷产生的。所以老子认为把这个事情扩大了，天地也是一样。道生万物就跟人的生命产生的道理是一样的。</t>
   </si>
 </sst>
 </file>
@@ -1331,16 +1359,32 @@
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:4">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="7" customHeight="1" spans="1:4">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/book.xlsx
+++ b/book.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$9</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>chapter</t>
   </si>
@@ -39,6 +42,27 @@
   </si>
   <si>
     <t>summary</t>
+  </si>
+  <si>
+    <t>总述</t>
+  </si>
+  <si>
+    <t>学习道德经之前，先了解《道德经》的背景（其人，其书，其道）
+1、其人：老子这个人，我们要讲两个内容：一个是老子的职业背景；另一个是这本书的写作背景。
+老子的职业：先他掌管天下的图书，别人看不到的很多的著作他都能读得到，知识渊博。
+写作的背景：尹喜在函谷关对老子说，如果不写“道”的思想，就不让其过关。
+2、其书：经过考古验证发现，老子亲手撰写的版本为帛书版，为了便后人理解，前人进行了优化。
+版本的迭代：道德经被历史名人修改后很多版，后人多以魏晋王弼的经典版进行学习和传诵。
+书名的由来：因为“道”和“德”出现的频率最高，故汉朝时期又名《老子》。
+形象的体现：《道德经》落实到现实中包含的内容——目标、方向、规则、境界、边界、底线。
+3、其道：老子所写的《道德经》的受众对象主要是针对三类人而写的。
+第一类人 - 士：基层的领导者和管理者（推十为一，把自己放在最后的位置）。
+第二类人 - 王：主要的领导者（善用人者为之下，姿态谦卑尊重对方）。
+第三类人 - 圣：品德修养高，通情达理的领导者（圣人之道为而不争，为大家谋福利）。
+—— 摘自：韩鹏杰《道德经说什么》</t>
+  </si>
+  <si>
+    <t>以下内容摘自：韩鹏杰《道德经说什么》</t>
   </si>
   <si>
     <t>第一章</t>
@@ -122,6 +146,34 @@
 你看人生命的产生，虽然是男女结合才产生生命，但大家都知道这生命它是女性，从牝、谷产生的。
 所以老子认为把这个事情扩大了，天地也是一样。道生万物就跟人的生命产生的道理是一样的。老子将“道”比作孕育一切的母体，强调其柔韧、生生不息的特性。你在一种文化里边，如果没有对母亲的敬畏和尊重，这文化其他方面都会崩塌。
 你看人生命的产生，虽然是男女结合才产生生命，但大家都知道这生命它是女性，从牝、谷产生的。所以老子认为把这个事情扩大了，天地也是一样。道生万物就跟人的生命产生的道理是一样的。</t>
+  </si>
+  <si>
+    <t>第七章</t>
+  </si>
+  <si>
+    <t>天长地久。天地所以能长且久者，以其不自生，故能长生。是以圣人后其身而身先，外其身而身存。非以其无私邪？故能成其私。</t>
+  </si>
+  <si>
+    <t>天地长长久久啊。天地之所以能长长久久，就是因为天地不自私、不只是只为了自己的生存，所以能长久啊。所以有智慧的领导者总是把自己的利益放在后面，这样才被大家乐推而不厌 乐于接受他们的领导，不贪身外之物 才让自己有更好的存在状态。天地和效法天地的圣人 不就是因为他们没有私心嘛，所以才更好地成就了他们的被人尊敬、平安无事的私心吗！</t>
+  </si>
+  <si>
+    <t>其实从第七章开始，第七章第八章第九章都在讲一个道理，我们经常讲知进退，但是有的人知进而不知退，知争而不知让。作为老子这样的一个思想家，他认为其实争和这个不争，进和退，强和弱，它们都是阴阳的两个方面，都具有相等的力量。所以大家经常看到的那个部分争强进，在《道德经》里很少讲，可是被大家忽略的部分，不争，退和弱，是《道德经》里最为强调的。在这三章里边，把这个意思讲得非常明晰。
+第七章分两个部分，一个部分是讲天道，也就是讲以天地为形象，告诉大家这样的一个道理。你看我们心里为什么觉得对天地有一种敬畏，认为天长地久，这是我们经常的一个祝愿的词，大家为什么要这样想？为什么这样认为？因为天地并不以自己的私利为其目标，而是为我们万事万物提供条件，阳光雨露土壤，任万事万物自由生长，我们对天地有什么回报啊？几乎没有。所以这就拿天地说事告诉大家一个道理，这天地做事情正因为其不自私，不以自己自我的生存为唯一的目的，所以才得到了大家的敬畏、敬仰。
+第二部分就讲人道，我们人做事也应该有这样的境界，也应该后其身而身先，外其身而身存。这句话点睛之笔就是最后一句话。他说你看天地是这样，这个世界里面我们敬仰的一些人物也是如此。为什么呢？他们无私！他们肯帮助别人，正因为他这样无私反而成就了自己的私心。你说让大家长久地纪念，让大家敬畏，这不也是大家都具有的一种潜意识里边的私心私念吗？这世界上谁无私？都有私心。可是一个人如果只是强调考虑自己的私心，他最后连自己的私心都不能很好地满足，这是这段话的整个大概的意思。</t>
+  </si>
+  <si>
+    <t>第八章</t>
+  </si>
+  <si>
+    <t>上善若水，水善利万物而不争，处众人之所恶（wù），故几于道，居善地；心善渊；与善仁；言善信；正善治；事善能；动善时。夫唯不争，故无尤。</t>
+  </si>
+  <si>
+    <t>最高的智慧和品德就像水一样，水善于利万物而不争，水处于众人最不愿去的地方，这是它最接近道的品性，它处于的是行善之地；人心也要像深水一样静水流深、要宁静致远、要善于沉淀；与人相处时、给人东西时、对人有恩德时要像水一样平等仁爱 要“生而不有，为而不恃，长而不宰”；说话也要像潮水一样“潮信” 讲信用、要言善信；政治清明像水一样公平公正清廉 要政善治 政清如水 为人做事要像水一样有多种多样的本事却又做事专一 奔流向海；处事智慧也像水一样 懂得寻找时机 该动则动 该静则静 该隐则隐 该绕行则绕行。所以像水一样有善利不争的品性，也就没有忧愁烦恼。</t>
+  </si>
+  <si>
+    <t>本章“上善若水”是一则非常著名的命题。水具有处下不争、施恩而不求回报等特性，因此应该成为人们效法的对象。自然界的很多植物都能开花结果，水又不能开花结果，可是没有水，这有生命的东西，它都是不成立的，无法生存的。言外之意就是说在我们中国人的眼里最高的智慧和品德就像水一样，我们中华民族是一个温和的热爱和平的民族，善于成就别人，同时也成就自己！这不就是双赢的含义吗？
+水善利万物而不争，这不就是双赢的含义吗？所以我们现在来解释，先要给大家说明。我们虽然在解释第八章，但是我们要告诉大家，在《道德经》里总共讲了十条关于水的智慧和品德。我们现在要解释的第八章就有八条。
+各位千万不要以为这个老子是趴在水边悟出来的道理，他只是借助水的形象，把他要传达给我们的智慧，借助这个形象告诉给我们大家，你要想让这个东西得到一个广泛的传播，被大家记得住，能够得以领悟和运用，那就得用这种形象的表达的方式，后边我们讲的很多的事情也是如此。所以老子借助水的形象，把他从战争、政治、人生中领悟的这种智慧与品德传达给我们。上善若水。</t>
   </si>
 </sst>
 </file>
@@ -134,7 +186,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,6 +201,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -615,145 +673,154 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1280,15 +1347,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="23.75" defaultRowHeight="27" customHeight="1" outlineLevelRow="6" outlineLevelCol="3"/>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultColWidth="23.75" defaultRowHeight="30" customHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="23.75" customWidth="1"/>
-    <col min="2" max="4" width="54.25" customWidth="1"/>
-    <col min="5" max="16384" width="23.75" customWidth="1"/>
+    <col min="1" max="1" width="23.75" style="3" customWidth="1"/>
+    <col min="2" max="4" width="54.25" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="23.75" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="20" customHeight="1" spans="1:4">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1302,7 +1369,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:4">
+    <row r="2" s="2" customFormat="1" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1313,80 +1380,125 @@
         <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:4">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:4">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:4">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:4">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="2" t="s">
+    </row>
+    <row r="8" customHeight="1" spans="1:4">
+      <c r="A8" s="4" t="s">
         <v>27</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:4">
+      <c r="A9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:4">
+      <c r="A10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D9" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/book.xlsx
+++ b/book.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$42</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="335">
   <si>
     <t>chapter</t>
   </si>
@@ -42,6 +42,9 @@
   </si>
   <si>
     <t>summary</t>
+  </si>
+  <si>
+    <t>type</t>
   </si>
   <si>
     <t>总述</t>
@@ -49,20 +52,26 @@
   <si>
     <t>学习道德经之前，先了解《道德经》的背景（其人，其书，其道）
 1、其人：老子这个人，我们要讲两个内容：一个是老子的职业背景；另一个是这本书的写作背景。
-老子的职业：先他掌管天下的图书，别人看不到的很多的著作他都能读得到，知识渊博。
-写作的背景：尹喜在函谷关对老子说，如果不写“道”的思想，就不让其过关。
+(1)老子的职业：先他掌管天下的图书，别人看不到的很多的著作他都能读得到，知识渊博。
+(2)写作的背景：尹喜在函谷关对老子说，如果不写“道”的思想，就不让其过关。
 2、其书：经过考古验证发现，老子亲手撰写的版本为帛书版，为了便后人理解，前人进行了优化。
-版本的迭代：道德经被历史名人修改后很多版，后人多以魏晋王弼的经典版进行学习和传诵。
-书名的由来：因为“道”和“德”出现的频率最高，故汉朝时期又名《老子》。
-形象的体现：《道德经》落实到现实中包含的内容——目标、方向、规则、境界、边界、底线。
+(1)版本的迭代：道德经被历史名人修改后很多版，后人多以魏晋王弼的经典版进行学习和传诵。
+(2)书名的由来：因为“道”和“德”出现的频率最高，故汉朝时期又名《老子》。
+(3)形象的体现：《道德经》落实到现实中包含的内容——目标、方向、规则、境界、边界、底线。
 3、其道：老子所写的《道德经》的受众对象主要是针对三类人而写的。
-第一类人 - 士：基层的领导者和管理者（推十为一，把自己放在最后的位置）。
-第二类人 - 王：主要的领导者（善用人者为之下，姿态谦卑尊重对方）。
-第三类人 - 圣：品德修养高，通情达理的领导者（圣人之道为而不争，为大家谋福利）。
-—— 摘自：韩鹏杰《道德经说什么》</t>
-  </si>
-  <si>
-    <t>以下内容摘自：韩鹏杰《道德经说什么》</t>
+(1)第一类人 - 士：基层的领导者和管理者（推十为一，把自己放在最后的位置）。
+(2)第二类人 - 王：主要的领导者（善用人者为之下，姿态谦卑尊重对方）。
+(3)第三类人 - 圣：品德修养高，通情达理的领导者（圣人之道为而不争，为大家谋福利）。</t>
+  </si>
+  <si>
+    <t>摘自：韩鹏杰《道德经说什么》</t>
+  </si>
+  <si>
+    <t>本章是全书导读，回答为什么读《道德经》、这本书讲什么、写给谁三个问题。为什么要学经典：经典是一个民族文化传承的途径与道路，认真读透一本经典胜过泛读百书，也是在为往圣继绝学、为万世开太平。其人：老子曾任周朝守藏史，掌管天下图书，能读到别人看不到的著作，知识渊博；因尹喜在函谷关要求他写下“道”的思想，才留下这部经典。
+其书：经考古验证，帛书版最接近老子亲笔原貌，后人为了便于理解不断优化，后世多沿用魏晋王弼的经典本；书名因“道”“德”出现频率最高而得名；道落实到现实生活，包含目标、方向、规则、境界、边界、底线六个方面。其道：本书主要写给三类人——士（基层领导者，推十为一、把自己放在最后）、王（主要领导者，善用人者为之下）、圣（品德修养高、通情达理的领导者，为而不争、为大家谋福利）。书中讲的是治国之道、为官之道与人生之道，为逐章解读打下基础。</t>
+  </si>
+  <si>
+    <t>道经</t>
   </si>
   <si>
     <t>第一章</t>
@@ -74,8 +83,8 @@
     <t>可以言说的道，就不是永恒的道；能够用来称呼的具体名称，就不是永恒的名称。天地开始的时候，把它叫做“无”；万物的母亲，把它叫做“有”。所以常处于无，从无的角度来观察它的妙处；常处于有，从有的角度来观察它的边界。有和无是任何事物都具有的两个方面，来源相同但名称不同，都可以称之为“玄妙深远”，玄而又玄，是一切奥妙的源头。</t>
   </si>
   <si>
-    <t>本章为《道德经》的主旨所在，强调的是“有”和“无”两个方面，从天地开始说起，天地的起源——我们叫做“无”；万物产生——我们叫做“有”。所以任何一个事物都不能脱离开有和无两个方面，我们从有的方面观察的是它的边界，从无的方面观察的是它的妙处，因为大家都看不到，观察它的妙处，这两者合到一块来理解，那就叫做“玄”。
-水平已经蛮高了，把有去掉，更多地关注这个无的作用，因为它是经常被大家所忽略的，看到这个无的作用就是“玄而又玄”，这是理解这本书重要的途径和门户。有形的东西大家都知道，老子重点强调了无形的被大家忽略的东西，道这个东西是最高的，你把它讲出来就低了，因为名可名，非常名（语言和逻辑是有局限的，讲出来后道就变成了有局限的道了），任何一件事物都有两面，没有无就不知道什么是有，所以观察一个事物，要从无的角度观察它的妙处，从有的角度观察它的边界，所以老子就告诉大家，如果有和无两个方面你都看到了，水平已经够高了（叫做玄），如果在这个基础上，再看到这无形东西的无比巨大的作用，精神力量的作用，这就叫众妙之门。</t>
+    <t>本章是《道德经》的门户，核心是“有”和“无”，特别强调常被忽略的“无”。道可道，非常道；名可名，非常名：道是最高、最全面的存在，用语言和逻辑讲出来就变成有局限的道，所以要借形象来领悟。无，名天地之始；有，名万物之母：天地起源时混沌无形，称为无；天地成形、万物出现，称为有。任何事物都有有和无两个方面，观察事物既要从“有”的角度看它的边界，也要从“无”的角度看它的妙处。
+此两者同出而异名，同谓之玄：能把有和无合起来理解，已是高级的思维水平，叫做玄；再进一步看到无形力量（精神、信仰、家风、作风等）的巨大作用，就是玄之又玄、众妙之门。韩鹏杰以“风”为形象：风无形却力量无尽，正如人的精神世界。老子提醒人们不要只看到金钱、财富等有形的东西，更要看到精神、思想、理想信念这些无形的力量；只重有形，物质越发达，精神家园就越花果飘零。</t>
   </si>
   <si>
     <t>第二章</t>
@@ -87,10 +96,8 @@
     <t>天下都知道美是什么，丑自然就存在了；都知道什么是善，不善自然也就出现了。所以有和无相待而生，难和易相待而成，长和短相待而显，高和下相待而倾倚，音和声相待而和谐，前和后相待而顺序相随。所以圣人行事 顺乎自然 崇尚无为，实行不言的教诲，顺应万物自然的生长而不加干预，创造万物而不占有，施泽万物而不将这当成是倚仗、凭借的手段，有了功劳而不居功自傲。正因为他不居功自傲，所以他的功德永存不灭。</t>
   </si>
   <si>
-    <t>第一章我们解读了世界的本源，根据这个世界的开端、本源，强调了认识事物的这种方法，提出一对重要的范畴“有和无”。沿着这样一个思路；
-第二章也讲的是世界运动的规律，以及我们按照这个规律来认识事物的方式方法，用哲学的语言概括这一章的内容，两句话——叫“相比较而存在，相对立而发展”。
-世界上很多的事物有正必有反，在它们的对立之中，才能形成一个运动变化与发展。通过读第二章，这《道德经》里面很多的东西你把它解释完了，很多东西就能够理解了，因为这是思维方式，他把考虑问题的思维方式告诉了我们。
-“天下皆知美之为美，斯恶（è）已；皆知善之为善，斯不善已。”这两句话是本章的总纲。有智慧有修养的人做事、好的这些领导者做事，应该怎么做？处无为之事。正因为让你有为，所以你应该从反面来理解，因为事情都是相反相成的。你说有为就是天天忙吗？天天折腾吗？你得了解哪些是该无为该舍掉的，处无为之事，才能达到更好的有为的效果。大家千万不要认为道家讲的无为是一个消极的，他反而是一种无比积极的智慧与想法，你要想做好有为的事，你得从反面才能把这个事情认识得更清楚，哪些是我们该无为的，这样才能够达到更好有为的效果。</t>
+    <t>本章讲世界运动的规律和认识世界的方法，是理解《道德经》的另一扇门。用哲学的语言概括：相比较而存在，相对立而发展。天下皆知美之为美，斯恶已；皆知善之为善，斯不善已：知道美就知道丑，知道善就知道不善，对立双方互相规定、互相依存。老子随后列出有无相生、难易相成、长短相较、高下相倾、音声相和、前后相随，指出这些对立面并非固定不变，而是在对立中运动、转化。
+因此圣人处无为之事，行不言之教：越是懂得有为，越要知道哪些该无为、该舍掉，从反面认识事情，才能达到更好的有为效果，千万不要把无为理解成消极。万物作焉而不辞，生而不有，为而不恃，功成而弗居：顺应万物自然生长而不干预，创造而不占有，做事而不依仗，有功而不居功，正因不居功，功德才不离去。本章还像目录一样，把后文许多重要内容提前概括出来，读熟这一章，后面很多章节都能以经解经。</t>
   </si>
   <si>
     <t>第三章</t>
@@ -102,9 +109,8 @@
     <t>不崇尚标榜贤才，使民众不起争心；不炒作炫耀难得的物品，使民众不去做盗贼；不展现能引起人私欲的东西，使民众心不受惑乱。所以圣人的治理，使民众虚心、饱腹；减弱民众的欲望，强壮民众的身体。使民众常保持无知无欲的自然淳朴状态，那些诡计多端的人就不敢耍诈。以顺应自然、不强行干预、不违背规律的方式来治世，则没有治理不好的。</t>
   </si>
   <si>
-    <t>第一章告诉我们，这本著作里边讲的一个最核心的内容是“有”和“无”，特别强调“无”的意义和作用。
-第二章和第三章是紧密连在一块的，要结合起来读。是说我们看问题，它不能只看到一个方面，不能一点论，而应该两点论。正反两个方面，包括他们这个动态中转化的方面。很好的一件事，很多事情是不是好事？是好事，但是它可以向相反的方面转化，就像我们很多人经常讲，我是为了你好，是为你好，但是你做的这件事情可能会产生巨大伤害。你是好心，但是它可能办成另外的坏事情。“尚贤”本来是很好的一件事，重视人才，可是这个事情发展到一定程度就走到了它另一个方面，真正的人才反而被过滤掉了。投机取巧的人，反而被披上了这种贤的外衣，挂上贤的名声。所以老子对当时这件事是有警醒作用的，是提醒这些。
-因为老子的话对面都是有人的。老子提出警告，任何一件事情它是有尺度的，这个度把握不好就会转化到相反的方面。</t>
+    <t>本章与第二章紧密相连，讲看问题不能一点论，要两点论：好事发展到一定程度会向反面转化。不尚贤，使民不争：尚贤本是重视人才的好事，但一旦立了标准，就有人按标准投机取巧、自我包装，真正有才能的人不屑于此，反而被过滤掉，贤名被投机者占据，所以尚贤过了头反而害了人才选拔。不贵难得之货，使民不为盗；不见可欲，使民心不乱：不炒作珍贵物品、不显露引发欲望的东西，民心才不会乱。
+圣人之治，虚其心，实其腹，弱其志，强其骨：使民心虚静、生活温饱、欲望减弱、身体强健。常使民无知无欲，使夫智者不敢为也：少用智巧套路，投机者才不敢妄为。为无为，则无不治：治理者不妄为、不折腾，按规律和规则办事，天下自然治理得好。韩鹏杰强调，老子的话对面坐着的是领导者，这些话是对治理者提出的警醒：任何事都有尺度，把握不好度，好事也会变成坏事。</t>
   </si>
   <si>
     <t>第四章</t>
@@ -116,8 +122,8 @@
     <t>道是阴阳两者相互中和，其作用无穷无尽，其渊深、渊博好像万物的宗主。它锋芒不外露，解除纷扰，在光明之处便与光融合，在尘垢之处便与尘垢同一。其深远幽暗好像无处不在。我不知它是从何而来，只知道在象帝之前便已存在。</t>
   </si>
   <si>
-    <t>这一章的核心就在“冲”字，冲是一个组合字，大家把它两点放平，这个冲就得到了正确的理解，冲就是二中。二就是阴和阳。道是一阴一阳之为道。冲的本义的形象在讲什么？两股水。这个水冲到那个里边，两个水就掺到一块了。这是讲它是两种力量的作用，是讲它是一个动态的。所以现在我们来理解这个冲字，然后这一章就变得容易理解了。道冲，道就是阴阳两者的相互中和，二中，阴和阳的相互中和。
-第三章第四章，都在强调道是万物的本源，老子一开始第一章第二章讲完了，还是觉得有点不放心，还在补充，还在添砖加瓦。就这个事情，拿一个具体的例证，不尚贤、不贵难得之货、不见可欲，具体的事物，因为这个是大家常做的，然后得出结论，然后告诉大家，我讲这个道，确实是重要的一种思维的智慧。阴阳两者，道冲。了解这个，那我们的思想水平，我们的境界，我们对事情问题的认知，就会有非常明显的提高。阴阳两者的相互综合，相互作用，相互转化，在动态中形成的像我们的太极图，始终你怎么转，它都是那个样子。既然是阴阳两者相互作用产生的万事万物，所以万物负阴而抱阳。万事万物都承载着阴，环抱着阳，都有阴阳两个方面。万物负阴而抱阳，冲气以为和，这个气就是阴阳二气，两者参与到一起，形成这个和谐的世界。</t>
+    <t>本章强调道是万物的本源，理解的关键在“冲”字。冲是组合字，把两点放平就是“二中”，二指阴阳；冲的本义是两股水冲到一块，象征阴阳两种力量相互中和、相互作用、动态转化。道冲，而用之或不盈：阴阳中和而成道，作用无穷无尽。渊兮似万物之宗：道渊深博厚，像万物的宗主。挫其锐，解其纷，和其光，同其尘：道收敛锋芒、化解纷争，与光明融合、与尘垢同一，深远幽暗却无处不在。吾不知谁之子，象帝之先：道先于天帝而存在，是万事万物的本源。
+韩鹏杰用第四十二章“道生一，一生二，二生三，三生万物；万物负阴而抱阳，冲气以为和”来印证：三即参，阴阳参与到一起而生万物，万事万物都同时具有阴阳两面，无论怎么转都像太极图一样保持和谐。了解道冲，就掌握了一种重要思维：任何事物都是两种相反力量在动态中达成的和谐，看问题、做决策都不能只偏执一方。</t>
   </si>
   <si>
     <t>第五章</t>
@@ -129,8 +135,8 @@
     <t>天地无所偏爱，将万物像刍狗（草扎的狗）一样平等看待；圣人没有偏私，对百姓像刍狗一样平等看待。天地这个大空间，不就像一个大风箱吗？因其中间虚静才能鼓出风，越动鼓出的风越多。政令繁多会招致败亡，不如保持虚静才能恰如其分。</t>
   </si>
   <si>
-    <t>第五章讲“天地不仁，以万物为刍狗”，然后告诉一个好的领导者，应该是这样，圣人不仁，以百姓为刍狗。你就应该有这样的一种公平，无偏私，制定这个规则，制定法令谁都不要例外。所以这个地方讲的道理是天地对万事万物都是平等的。他对万事万物是没有关心的。然后就讲，就问题里引起最大争议的就圣人不仁。如果有人说圣人对人世间的很多罪过也应该忍心，就像有人说什么叫哲学家，你在我门口杀人我都无动于衷，那就已经练成哲学家了，这完全是一种错误。有人就把它解释成这样，这是不对的，圣人对万事万物也应该是平等的。你让他们自己去奋斗，让他们自己去努力。不要你认为弱，你就一定要想去帮他，你这就叫有偏私。万事万物都是一样的，一律公平，没有偏私。所以道家讲的不仁是“大仁”。
-天地根本不关心人世间的事。什么意思？你别老去麻烦他。你别老以为是有事，天会罩着你。要靠你自己。你别老以为天会关照你，别老去麻烦他，很多是天道酬勤靠自己。这个地方讲的就是这样的一个道理。天地对人世间的事情不关心，万事万物在他的眼里都是平等的。万事万物在他眼里，无所爱惜。就像草扎的狗，草扎的狗原来用来干吗的 —— 是用来祭祀的。祭祀之前大家对它很尊重。祭祀之后就扔在那没人管。万事万物在我眼里，就是叫无所爱惜。然后告诉一个好的领导者，应该是这样，圣人不仁，以百姓为刍狗。你就应该有这样的一种公平，无偏私，制定这个规则，制定法令谁都不要例外。第二个部分。“天地之间，其犹橐籥乎。”像风箱一样。风箱不能乱动，乱动，你在那地方那就麻烦了。它本身是静的，中间是空的，虚静，所以你动的时候前边有虚静为前提，动的时候才能够不断鼓出风来，这鼓出是讲应用。所以下边就讲政令也应该如此，像风箱一样，不要变来变去动来动去，位置挪来挪去，换来换去。讲究虚静，这样政令简要大道至简，这样才能够恰如其分，不如守中，恰如其分。</t>
+    <t>本章讲天地对万物的平等和治理者的虚静。天地不仁，以万物为刍狗：不仁不是残忍，而是不偏爱、不干预；天地看待万物一视同仁，像草扎的祭狗，祭祀前被尊重，祭祀后被丢弃，无所爱惜。圣人不仁，以百姓为刍狗：好的领导者对百姓也应一律公平，制定规则法令，谁都不能例外；不要因为谁弱就特殊照顾，那反而是一种偏私，让被照顾者失去自立。道家讲的不仁是“大仁”，天地不偏私地让万物自己去奋斗、去努力。
+天地之间，其犹橐籥乎：天地像风箱，中间虚静，一拉动就能鼓出风来；政令也应如此，保持虚静、简要稳定，不能今天一变明天一变。多言数穷，不如守中：政令繁多、变动频繁会把自己逼入困境，不如恰到好处、大道至简。韩鹏杰提醒，这些话都是讲给领导者听的：治理要公平无私，政令要少而稳定，靠规则而不是靠折腾。</t>
   </si>
   <si>
     <t>第六章</t>
@@ -142,10 +148,8 @@
     <t>道虚无莫测 永存不灭，称为“玄牝”，“玄牝”之门，是天地万物的根源。连绵不绝地永存，取之不尽用之不竭。</t>
   </si>
   <si>
-    <t>这一章讲了一个非常重要的道理，对母亲的尊重。很多章，特别是道教，把这一章解释得简直就玄而又玄。大家知道这一章讲的是一个什么事呢？谷神，把它断开，谷神，谷神不死，是谓玄牝。牝就是女性的生殖器，指代母亲。而前边这个谷恰恰也是对它这个形象的描述。所以这一章在讲什么，谷神不死，是谓玄牝，玄牝之门，是谓天地根。
-你看人生命的产生，虽然是男女结合才产生生命，但大家都知道这生命它是女性，从牝、谷产生的。
-所以老子认为把这个事情扩大了，天地也是一样。道生万物就跟人的生命产生的道理是一样的。老子将“道”比作孕育一切的母体，强调其柔韧、生生不息的特性。你在一种文化里边，如果没有对母亲的敬畏和尊重，这文化其他方面都会崩塌。
-你看人生命的产生，虽然是男女结合才产生生命，但大家都知道这生命它是女性，从牝、谷产生的。所以老子认为把这个事情扩大了，天地也是一样。道生万物就跟人的生命产生的道理是一样的。</t>
+    <t>本章以谷与牝为喻，把道比作孕育万物的母体，根本精神是对母亲的尊重、对生命的敬畏。谷神不死，是谓玄牝：谷指空虚的山谷，神指精神、生机；牝指女性生殖器，代表母亲。谷神不死，即这种孕育生命的力量绵延不绝，称为玄牝。玄牝之门，是谓天地根：玄牝之门是天地万物的根源，道生万物与母亲生育生命是同一个道理。绵绵若存，用之不勤：它连绵不断地存在，取之不尽、用之不竭。
+韩鹏杰强调，老子用神、玄这些最高字眼来称呼谷与牝，绝不允许亵渎；一个文化里若失去对母亲的尊重、对生命的敬畏，其他方面都会崩塌。读这一章不要陷入玄虚，要读出其中朴素而伟大的情感：尊重母亲、敬畏生命，是文化延续的根基。</t>
   </si>
   <si>
     <t>第七章</t>
@@ -157,9 +161,8 @@
     <t>天地长长久久啊。天地之所以能长长久久，就是因为天地不自私、不只是只为了自己的生存，所以能长久啊。所以有智慧的领导者总是把自己的利益放在后面，这样才被大家乐推而不厌 乐于接受他们的领导，不贪身外之物 才让自己有更好的存在状态。天地和效法天地的圣人 不就是因为他们没有私心嘛，所以才更好地成就了他们的被人尊敬、平安无事的私心吗！</t>
   </si>
   <si>
-    <t>其实从第七章开始，第七章第八章第九章都在讲一个道理，我们经常讲知进退，但是有的人知进而不知退，知争而不知让。作为老子这样的一个思想家，他认为其实争和这个不争，进和退，强和弱，它们都是阴阳的两个方面，都具有相等的力量。所以大家经常看到的那个部分争强进，在《道德经》里很少讲，可是被大家忽略的部分，不争，退和弱，是《道德经》里最为强调的。在这三章里边，把这个意思讲得非常明晰。
-第七章分两个部分，一个部分是讲天道，也就是讲以天地为形象，告诉大家这样的一个道理。你看我们心里为什么觉得对天地有一种敬畏，认为天长地久，这是我们经常的一个祝愿的词，大家为什么要这样想？为什么这样认为？因为天地并不以自己的私利为其目标，而是为我们万事万物提供条件，阳光雨露土壤，任万事万物自由生长，我们对天地有什么回报啊？几乎没有。所以这就拿天地说事告诉大家一个道理，这天地做事情正因为其不自私，不以自己自我的生存为唯一的目的，所以才得到了大家的敬畏、敬仰。
-第二部分就讲人道，我们人做事也应该有这样的境界，也应该后其身而身先，外其身而身存。这句话点睛之笔就是最后一句话。他说你看天地是这样，这个世界里面我们敬仰的一些人物也是如此。为什么呢？他们无私！他们肯帮助别人，正因为他这样无私反而成就了自己的私心。你说让大家长久地纪念，让大家敬畏，这不也是大家都具有的一种潜意识里边的私心私念吗？这世界上谁无私？都有私心。可是一个人如果只是强调考虑自己的私心，他最后连自己的私心都不能很好地满足，这是这段话的整个大概的意思。</t>
+    <t>本章与第八、九章共同讲进退、争让、强弱：人们习惯强调争、进、强，老子偏要讲被忽略的不争、退、弱，因为它们与争、进、强是阴阳的两个方面，具有同等力量。天长地久：天地之所以长久，是因为天地不自私，不以自己的生存为唯一目的，而是为万物提供阳光雨露土壤，任万物自由生长，因此赢得人们长久的敬畏。后其身而身先，外其身而身存：圣人把自身利益放在后面，反而被众人推举到前面；把自身安危置之度外，反而安然长存。非以其无私邪，故能成其私：正因无私，才更好地成就了自己的长久与被人敬仰，这是人人都有的潜意识私心。
+本章是典型的“天道人道”两段论：先讲天道，再讲人道，人道效法天道。韩鹏杰用“公仪休不受鱼”的故事说明：懂得从长远看问题、不贪眼前不该得的利益，才能长久地满足自己的愿望；只盯着私利的人，最后连私利也保不住。</t>
   </si>
   <si>
     <t>第八章</t>
@@ -171,9 +174,925 @@
     <t>最高的智慧和品德就像水一样，水善于利万物而不争，水处于众人最不愿去的地方，这是它最接近道的品性，它处于的是行善之地；人心也要像深水一样静水流深、要宁静致远、要善于沉淀；与人相处时、给人东西时、对人有恩德时要像水一样平等仁爱 要“生而不有，为而不恃，长而不宰”；说话也要像潮水一样“潮信” 讲信用、要言善信；政治清明像水一样公平公正清廉 要政善治 政清如水 为人做事要像水一样有多种多样的本事却又做事专一 奔流向海；处事智慧也像水一样 懂得寻找时机 该动则动 该静则静 该隐则隐 该绕行则绕行。所以像水一样有善利不争的品性，也就没有忧愁烦恼。</t>
   </si>
   <si>
-    <t>本章“上善若水”是一则非常著名的命题。水具有处下不争、施恩而不求回报等特性，因此应该成为人们效法的对象。自然界的很多植物都能开花结果，水又不能开花结果，可是没有水，这有生命的东西，它都是不成立的，无法生存的。言外之意就是说在我们中国人的眼里最高的智慧和品德就像水一样，我们中华民族是一个温和的热爱和平的民族，善于成就别人，同时也成就自己！这不就是双赢的含义吗？
-水善利万物而不争，这不就是双赢的含义吗？所以我们现在来解释，先要给大家说明。我们虽然在解释第八章，但是我们要告诉大家，在《道德经》里总共讲了十条关于水的智慧和品德。我们现在要解释的第八章就有八条。
-各位千万不要以为这个老子是趴在水边悟出来的道理，他只是借助水的形象，把他要传达给我们的智慧，借助这个形象告诉给我们大家，你要想让这个东西得到一个广泛的传播，被大家记得住，能够得以领悟和运用，那就得用这种形象的表达的方式，后边我们讲的很多的事情也是如此。所以老子借助水的形象，把他从战争、政治、人生中领悟的这种智慧与品德传达给我们。上善若水。</t>
+    <t>本章“上善若水”是《道德经》最著名的命题，也是中华民族精神的重要代表。上善若水，水善利万物而不争：最高的智慧与品德像水一样，滋润万物、成就他人而不争功，甘处众人不愿去的低处，所以最接近道。老子借水讲了善下、善渊、善仁、善信、善治、善能、善时等品质：居善地，甘居下位；心善渊，静水深流、宁静致远；与善仁，平等仁爱地给予；言善信，说话像潮信一样讲信用；政善治，政治清正公平如水；事善能，有多种本事又专一向前；动善时，该动则动、该静则静、该绕行则绕行。
+水的“不争”有丰富含义：有边界不争（湖有湖畔、河有河堤、海有海岸），有秩序不争（前后相随、循序渐进），有牺牲不争（成就万物而默默无闻）。夫唯不争，故无尤：不争就不会招来怨恨和过错。韩鹏杰指出，老子不是趴在河边悟道，而是借水的形象传达从战争、政治、人生中领悟的智慧：善于成就别人，同时也成就自己，这正是双赢。</t>
+  </si>
+  <si>
+    <t>第九章</t>
+  </si>
+  <si>
+    <t>持而盈之，不如其已（yǐ）。揣（zhuī）而锐之，不可长保。金玉满堂，莫之能守。富贵而骄，自遗其咎。功遂身退，天之道也。</t>
+  </si>
+  <si>
+    <t>如果做事一定要做到盈满，还不如停止不做。刀刃捶锻得尖锐锋利，其锋刃就不能长期保持锋利。家中充满财富和珍宝，没有人能够守住。因富贵而骄傲自满，是自取灾难。功成而懂得不居功自傲的道理，才真正符合天道天理。</t>
+  </si>
+  <si>
+    <t>本章讲“不盈”：凡事勿求满，适可而止。持而盈之，不如其已：端着一盘盛满的水走路，战战兢兢还不断洒出，不如少装一点，走得更轻松。揣而锐之，不可长保：把锥子磨得极锋利，一碰就断；削铅笔削到只剩笔头，再尖也保不住。金玉满堂，莫之能守：家中满是财富珍宝，反而守不住。富贵而骄，自遗其咎：因富贵而骄傲自满，是自取灾难。功遂身退，天之道也：功成而不居功、懂得退让，才符合天道。
+韩鹏杰用民间故事讲这个道理：弟弟只拿一点金子平安回家，哥哥贪心装满全身，被太阳晒化。第七章讲先后，第八章讲不争，第九章讲不盈，都提醒人知进退、懂谦让。中国文化的“中”就是恰到好处，不走到极端：物极必反、乐极生悲、泰极否来，好事到了极端容易向坏处转化，所以要战战兢兢、如履薄冰地把握分寸。</t>
+  </si>
+  <si>
+    <t>第十章</t>
+  </si>
+  <si>
+    <t>载（zài）营魄抱一，能无离乎？专气致柔，能如婴儿乎？涤除玄览，能无疵（cī）乎？爱民治国，能无为乎？天门开阖，能为雌乎？明白四达，能无知乎？生之畜（xù）之，生而不有，为而不恃，长（zhǎng）而不宰，是谓玄德。</t>
+  </si>
+  <si>
+    <t>身体像车一样载着魂魄，它们能不能不要分离？聚结精气以致柔和温顺，能不能像婴儿那样的纯粹呢？像玄镜照心一样清除杂念而深入观察心灵，能不能让心灵没有瑕疵呢？爱民治国能不能遵行自然无为的规律呢？感官与外界的对立变化相接触，能不能守住雌柔宁静呢？明白四达，能不能不用心机诈术呢？万物生长繁殖，产生万物、养育万物而不占为己有，作万物之长而不主宰它们，这就叫做“玄德”。</t>
+  </si>
+  <si>
+    <t>本章与十一、十二章共讲“虚静”：心里放空才能宁静，宁静才能看清事物本质，抵抗外在诱惑。载营魄抱一，能无离乎：身体像车载着魂魄，灵魂与肉体能否合一不分离？不要做丢了灵魂的行尸走肉。专气致柔，能如婴儿乎：聚结精气、身心柔软，能否像婴儿一样纯粹？涤除玄览，能无疵乎：清除内心杂念，能否像明镜一样无瑕疵？爱民治国，能无为乎：治理能否顺其自然、不妄为？天门开阖，能为雌乎：面对外界纷扰，能否守住柔静？明白四达，能无知乎：通达事理之后，能否不用机巧套路？
+一连串反问都在讲修养路径：魂魄不离、身心合一、少欲守静、厚道不用智巧。最后点出玄德：生之畜之，生而不有，为而不恃，长而不宰——生养万物而不占有、不倚仗、不主宰，这是最高深的德。韩鹏杰认为这一章是后面九章的总纲，虚静既是个人修养，也是治国的基础。</t>
+  </si>
+  <si>
+    <t>第十一章</t>
+  </si>
+  <si>
+    <t>三十辐（fú）共一毂（gǔ），当其无，有车之用。埏（shān）埴（zhí）以为器，当其无，有器之用。凿户牖（yǒu）以为室，当其无，有室之用。故有之以为利，无之以为用。</t>
+  </si>
+  <si>
+    <t>三十根辐条集中在一个车毂上，正是因为有了车厢中的空间，才有了车子的作用。用水和着黏土制造各种陶器，正是因为有了陶器里的空间，才有了陶器的作用。开凿门窗修建房屋，正是因为有了房屋中的空间，才有了房屋的作用。所以说各种器物的物质部分（实有部分）给人带来了利益，而器物里的空间（空虚部分）才使这些器物能够发挥自己的作用。</t>
+  </si>
+  <si>
+    <t>本章讲“无”的作用，用三个日常形象说明虚空的巨大价值。三十辐共一毂，当其无，有车之用：车轮有三十根辐条，车毂中间是空的，车轮才能转动，才有车的功用。埏埴以为器，当其无，有器之用：黏土烧成器皿，中间是空的，才能盛水装物。凿户牖以为室，当其无，有室之用：开凿门窗建成房屋，中间是空的，人才能居住。有之以为利，无之以为用：实体提供便利条件，虚空成就实际功用，有与无相互成全。
+韩鹏杰指出，“利用”这个词就来自本章。第十章讲虚静，本章讲怎样虚静——心里放空，去掉杂念，才能听得进别人的意见、看得见别人的长处、学得到别人的优点，虚怀若谷、满招损谦受益。中国文化的悟道方式是“给一个形象，自己领悟”，本章就是最好的示范：通过车、器、室三个形象，让人领悟空与用的道理。</t>
+  </si>
+  <si>
+    <t>第十二章</t>
+  </si>
+  <si>
+    <t>五色令人目盲；五音令人耳聋；五味令人口爽；驰骋畋（tián）猎，令人心发狂；难得之货，令人行妨。是以圣人为腹不为目，故去彼取此。</t>
+  </si>
+  <si>
+    <t>艳丽的色彩看多了会伤害人的视力；美妙的音乐听多了会伤害人的听力；味美的食物吃多了会伤害人的味觉；沉溺于驰马打猎，会使人心神狂乱；珍贵的金银财宝，会使人的行为受到妨碍。所以圣人只求吃饱肚子而不求感官享受，因此要舍弃感官享受（过度的欲望）而选择简单朴素的生活。</t>
+  </si>
+  <si>
+    <t>本章讲外在诱惑对心灵的扰乱，以及如何以内心的虚静守住根本。五色令人目盲：颜色太多太杂，反而区分不出好坏，视觉被迷乱；五音令人耳聋：高音快节奏听多了，好音乐也分辨不出来；五味令人口爽：厚食重味吃多了，味觉被破坏（爽是错乱）；驰骋畋猎令人心发狂：声色犬马让人心静不下来；难得之货令人行妨：被炒作的珍奇之物让人行为失当。老子并不要求消灭这些享受，而是说要以内心的虚静合理把握，适可而止。
+是以圣人为腹不为目，故去彼取此：圣人重实质内容，不重外在浮华；取舍的标准是看什么最重要——健康、营养、真实比外表颜色更重要。韩鹏杰把本章与第十章、十一章连起来读：虚静的心才能看清本质，处其厚不居其薄，掌握生命中真正重要的东西，返璞归真。</t>
+  </si>
+  <si>
+    <t>第十三章</t>
+  </si>
+  <si>
+    <t>宠辱若惊，贵大患若身。何谓宠辱若惊？宠为下，得之若惊，失之若惊，是谓宠辱若惊。何谓贵大患若身？吾所以有大患者，为吾有身，及吾无身，吾有何患！故贵以身为天下，若可寄天下；爱以身为天下，若可托天下。</t>
+  </si>
+  <si>
+    <t>受到宠爱和受到侮辱都好像受到惊恐，把荣辱这样的大患看得与自身生命一样珍贵。那么为什么会得宠和受辱都感到惊慌失措呢？受宠者是卑下的，得到宠爱又怕失去会感觉惊恐，失去宠爱则更令人惊慌不安；受辱时惊恐，失去时又害怕辱再来也会惊恐，这就叫做得宠和受辱都感到惊恐。什么叫做重视大患像重视自身生命一样？我之所以有大患，是因为我有身体；如果我没有身体，我还会有什么祸患呢？所以，珍贵、爱惜自己的身体，而为了天下这个更重要的价值可以奉献生命，这样的人可以把天下寄托给他了。</t>
+  </si>
+  <si>
+    <t>本章讲宠辱与生命，核心是如何看待得失、珍视生命，什么样的人才可托付天下。宠辱若惊：得到宠幸和失去宠幸都会惊恐。为什么？宠为下：被宠的人在下面，宠我们的人在上面，所以得之若惊（怕失去），失之若惊（更恐惧），这叫宠辱若惊。能做到宠辱不惊、淡然处之，是难得的人生境界。贵大患若身：有身体就有祸患，身体代表利益，也带来疾病与麻烦；但身体是摆脱不掉的，所以更要珍视它。
+吾所以有大患者，为吾有身，及吾无身，吾有何患——不把身体和生命当回事的人，坐到重要位置上是很可怕的；声色犬马、厚食重味正是戕害生命。贵以身为天下，若可寄天下；爱以身为天下，若可托天下：真正把自身生命看得与天下一样贵重、肯为天下担当牺牲的人，才值得把天下托付给他。韩鹏杰区分两种勇敢：无赖式的勇敢不把命当回事，有责任的勇敢珍视生命又肯担当，后者才值得托付。</t>
+  </si>
+  <si>
+    <t>第十四章</t>
+  </si>
+  <si>
+    <t>视之不见名曰夷（yí），听之不闻名曰希，搏之不得名曰微。此三者不可致诘（jié），故混而为一。其上不皦（jiǎo），其下不昧，绳（mǐn）绳（mǐn）不可名，复归于无物。是谓无状之状，无物之象，是谓惚恍。迎之不见其首，随之不见其后。执古之道，以御今之有。能知古始，是谓道纪。</t>
+  </si>
+  <si>
+    <t>察看大道又看不见，这叫作无形；聆听大道又听不到，这叫作无声；触摸大道又摸不着，这叫作无体。这三种特性都是无法进一步追究考察的，它们混合于一体。
+大道的上面不会显得明亮，它的下面也不会显得昏暗，它无形无象难以描述，可以说它不是一个物质性的实体。可以说大道是没有形状的形状，没有形体的形象，它可以说是迷离恍惚、无法捉摸的。站在它前面却看不见它的头部，尾随着它也看不见它的尾部。
+掌握了自古以来就存在的大道，就能够凭借它来驾驭、支配现在的万物，就能够了解远古时代的情况。以上所讲的就是关于大道的大致情况。</t>
+  </si>
+  <si>
+    <t>本章形容道大象无形却无处不在，并指出知古通今的方法。视之不见名曰夷，听之不闻名曰希，搏之不得名曰微：道太细微，看不见、听不到、摸不着，三个词都说明道不可用感官把握。此三者不可致诘，故混而为一：不能用语言追问道在哪里，它混然一体。其上不皦，其下不昧，绳绳不可名：道不明不暗、不上不下，绵延存在却无法命名。无状之状，无物之象，是谓惚恍：道没有具体形状和物象，似有若无。迎之不见其首，随之不见其后：寻不到它的首尾。
+执古之道，以御今之有：了解古往今来的大道，才能把握今天、做好今天的事；能知古始，是谓道纪：知道万物开始的道理，就是把握了道的纲领。韩鹏杰用庄子的“道在瓦片、稗草、大小便中”来说明道无在无不在，越往下越有；用风的形象说明道无形却左右万物。学习本章要记住：道看不见摸不着，但真实存在、无处不在，了解它才能做好今天的事。</t>
+  </si>
+  <si>
+    <t>第十五章</t>
+  </si>
+  <si>
+    <t>古之善为士者，微妙玄通，深不可识。夫唯不可识，故强为之容。豫焉若冬涉川，犹兮若畏四邻，俨（yǎn）兮其若客，涣兮若冰之将释，敦兮其若朴，旷兮其若谷，混兮其若浊。孰能浊以止？静之徐清。孰能安以久？动之徐生。保此道者不欲盈，夫唯不盈，故能蔽而新成。</t>
+  </si>
+  <si>
+    <t>古代那些掌握大道的人，其思想微妙通达，深刻得难以理解。正因为他们难以被理解，所以要勉强对他们的言行加以描述：
+他们做事反复考虑，就好像寒冬要徒步过河一样；谨慎小心，就好像畏惧四邻的围攻一般；恭敬庄重，就好像一位做客的人；通达而不固执，就好像将要融化的冰块；朴实敦厚，就好像未经雕饰的原木；胸怀空阔宽广，就好像那深山的幽谷；能够包容一切，就好像那混浊的大水。
+谁能够持久地像混浊的大水那样去包容一切呢？世人总是要让浊水安静下来，慢慢加以澄清；但是谁又能够永远坚持这种安定清静的状态呢？世人又总是搅动这种清静状态，慢慢产生各种追名逐利的活动。
+掌握大道的人，办事不求盈满。正因为不求盈满，所以能够安于有缺陷的旧状态而不去创造新的事物。</t>
+  </si>
+  <si>
+    <t>本章讲基层领导者“士”应有的修养。古之善为士者，微妙玄通，深不可识：善于做士的人，智慧微妙、通达深远，难以被了解，所以要强为之容（勉强形容）。豫兮若冬涉川：像冬天过河一样谨慎，一步一探；犹兮若畏四邻：像敬畏四邻一样不敢妄动；俨兮其若客：庄重像做客；涣兮若冰之将释：温和像冰雪消融；敦兮其若朴：敦厚像未经雕琢的木头；旷兮其若谷：胸怀开阔像山谷；混兮其若浊：包容混同像浊水。
+孰能浊以静之徐清？孰能安以久动之徐生：浊水静下来才能慢慢澄清，安定的状态动起来才能慢慢焕发生机，这是“静中求清、动中求生”的修养。保此道者不欲盈，夫唯不盈，故能蔽而新成：守道者不求满，留出空间，舍弃旧的东西才能革故鼎新。韩鹏杰强调，书中的话多针对具体的人讲，本章针对带领十几人做事的小组长等“士”阶层，说明基层领导者也需要很高的素质：谨慎、敬畏、质朴、虚怀、不盈。</t>
+  </si>
+  <si>
+    <t>第十六章</t>
+  </si>
+  <si>
+    <t>致虚极，守静笃，万物并作，吾以观复。夫物芸芸，各复归其根。归根曰静，是谓复命。复命曰常，知常曰明。不知常，妄作，凶。知常容，容乃公，公乃王（wàng），王乃天，天乃道，道乃久。没身不殆。</t>
+  </si>
+  <si>
+    <t>尽力使心灵的谦虚达到极点，使生活清静坚守不变。万物都一齐蓬勃生长，有道之人在纷繁中考察其往复的道理。万事万物纷纷芸芸，各自返回它的本根。返回到它的本根就是清静，清静就能使生命复归而再次续命；复命续命就是自然，认识了自然规律就叫做明智，不认识自然规律的轻妄举止，往往会出乱子和灾凶。认识自然规律的人是宽容的，宽容才会坦然公正，公正才能内圣外王，内圣外王才能符合自然的“道”，符合自然的道才能长久，终身不会遭到危险。</t>
+  </si>
+  <si>
+    <t>本章承第十五章，进一步讲虚静观复、知常守根。致虚极，守静笃：把心放到极度虚空、极度宁静的状态，不是枯木死灰，而是心灵安稳、不受杂念干扰。万物并作，吾以观复：万物纷繁生长，观察它的根本规律就是一个“复”字，反复循环、复归本根。夫物芸芸，各复归其根：万物虽然纷纭，最终都要回归自己的根本。归根曰静，静曰复命，复命曰常：归根就是静，静就是复归本性，复归本性就是恒常之道。
+知常容，容乃公，公乃王，王乃天，天乃道，道乃久，没身不殆：懂得恒常之道就能包容，包容就公正，公正就周全，周全就合天，合天就合道，合道就长久，终身不会遇到危险。韩鹏杰说，从草的枯荣到人的生死，都体现“复”的规律；观察规律是为了认识自己、掌控自己：知道哪些因素会带来负面状态，就主动避免；知道哪些条件带来积极状态，就主动创造，让好的状态恢复。</t>
+  </si>
+  <si>
+    <t>第十七章</t>
+  </si>
+  <si>
+    <t>太上，不知有之；其次，亲而誉之；其次，畏之；其次，侮之。信不足焉，有不信焉。悠兮其贵言。功成事遂，百姓皆谓我自然。</t>
+  </si>
+  <si>
+    <t>最高层次的统治者，百姓感觉不到他们的存在；低一层次的统治者，百姓亲近他们、赞美他们；更低层次的统治者，百姓害怕他们；最低层次的统治者，百姓轻视、羞辱他们。正是因为统治者本身的诚信不足，所以才出现不被百姓信任的情况。最好的统治者清静无为 很少发号施令。国家治理得美满祥和，而百姓都认为“我们本来就是这个样子”。</t>
+  </si>
+  <si>
+    <t>本章讲领导者的层次与境界。太上，下知有之：最高明的领导者，百姓只隐隐知道有他这个人，因为他不过多干预、不越边界，该管的事管好，不该管的放手。其次，亲而誉之：次一等的领导者被百姓亲近、赞誉。其次，畏之：再次一等的，百姓畏惧他。其次，侮之：最差的，百姓轻侮他。信不足焉，有不信焉：领导者自身诚信不足，百姓自然不会信任他。悠兮其贵言：最高境界是少言、贵言，不唠里唠叨，把话讲得有分量。功成事遂，百姓皆谓我自然：事情办成了，百姓都觉得是我们自己自然而然做成的，而不是领导者的功劳和主宰。
+韩鹏杰用“太上”的拆字讲：大上加一点才是太，点放下才成太，放到上面就成犬，寓意善于处下才能真正居上，太太、处长等词都蕴含此理。最好的教育和管理也是如此：不越俎代庖，让孩子、下属自己把事情做成，他们才有自信和成长，功成事遂皆谓我自然。</t>
+  </si>
+  <si>
+    <t>第十八章</t>
+  </si>
+  <si>
+    <t>大道废，有仁义；慧智出，有大伪；六亲不和，有孝慈；国家昏乱，有忠臣。</t>
+  </si>
+  <si>
+    <t>大道被废弃之后，人们开始提倡仁义；智慧出现之后，就产生了严重的虚伪；亲人之间关系不和睦，才会强调孝顺和慈爱；国家动乱时，才会出现忠臣。</t>
+  </si>
+  <si>
+    <t>本章与第十九章原为一章，讲“越缺什么越提倡什么”的历史递降逻辑。大道废，有仁义：大道被废弃了，才需要提倡仁义；六亲不和，有孝慈：家庭不和睦了，才强调孝慈；国家昏乱，有忠臣：国家混乱了，才显出忠臣。智慧出，有大伪：智巧盛行，反而产生大伪诈。韩鹏杰指出，这是老子的历史观：有道的时候不需要讲德，失道才讲德，失德才讲仁，失仁才讲义，失义才讲礼，一层一层往下掉。
+一个社会天天提倡道德，正说明道德已经滑坡；什么时候妇女节、教师节不再成为问题，才说明相关地位真正提高了。这不是否定仁义孝慈，而是提醒人们不要靠表面提倡来补救，要从根本上回到道。把第十八、十九章连起来读：与其用仁义、智巧等外在名目补救，不如回归素朴本心，做个好人、存点好心、行些好事。</t>
+  </si>
+  <si>
+    <t>第十九章</t>
+  </si>
+  <si>
+    <t>绝圣弃智，民利百倍；绝仁弃义，民复孝慈；绝巧弃利，盗贼无有。此三者以为文，不足。故令有所属：见（xiàn）素抱朴，少私寡欲，绝学无忧。</t>
+  </si>
+  <si>
+    <t>抛弃圣贤和智慧，百姓反而会得到百倍的利益；不去提倡仁义，百姓反而能够做到孝慈；清除技巧和利益，盗贼就不会产生。以上三条原则仅仅作为理论谈谈，是不够的。所以要为它们分别落实一些施行的具体措施：行为单纯 内心淳朴，减少私心 降低欲望，抛弃学问 没有忧虑。</t>
+  </si>
+  <si>
+    <t>本章主张绝弃外在名目，回归素朴本心。绝圣弃智，民利百倍：抛弃圣贤名号和智巧机心，百姓反而得到百倍利益；绝仁弃义，民复孝慈：不刻意提倡仁义，百姓反而自然做到孝慈；绝巧弃利，盗贼无有：清除技巧和利益诱惑，盗贼就不会产生。此三者以为文不足：仅仅在理论上讲这三条还不够，要落实为具体方向——见素抱朴，少私寡欲，绝学无忧：行为单纯、内心淳朴，减少私心、降低欲望，不为纷繁的学问和机巧所惑，就没有忧虑。
+韩鹏杰说，道家认为人的本心就是真心，真心就是朴素之心，朴素之心就是少私寡欲；外在花花绿绿的学问看多了，反而把人搞乱。读经典要由博返约，最后陪我们一生的可能只是一两本书、一两句话，真传一句话，假传万卷书。绝学无忧不是不要学习，而是学真正的大道，不被浮华知识蒙蔽。</t>
+  </si>
+  <si>
+    <t>第二十章</t>
+  </si>
+  <si>
+    <t>唯之与阿（hē），相去几何？善之与恶，相去若何？人之所畏，不可不畏。荒兮，其未央哉！众人熙熙，如享太牢，如春登台。我独泊兮，其未兆，如婴儿之未孩。儽（léi）儽兮，若无所归。众人皆有余，而我独若遗。我愚人之心也哉，沌（dùn）沌兮！俗人昭昭，我独昏昏；俗人察察，我独闷闷。澹（dàn）兮其若海； 飂（liù）兮若无止 。众人皆有以，而我独顽似鄙。我独异于人，而贵食母。</t>
+  </si>
+  <si>
+    <t>赞成与反对，相差有多远？善良与丑恶，相差又有多远？然而别人所害怕的，我不能不怕。前面的道路多么漫长啊，就像没有尽头！众人是那样的快乐，就好像参加盛大宴会，春日登台赏景一样。而只有我淡泊处之，无动于衷，就如同一个还不会笑的婴儿一般。我是如此狼狈不堪，就像个无家可归的人一样。众人都过着富裕幸福的生活，只有我却像被遗弃了一样。因为我有一副愚人的心肠，太笨拙了！世人是那样的明白，只有我是如此的糊涂；世人是那样的聪慧，只有我是这样的宽厚。我的生活是那样的坎坷多难 就好像那动荡不安的大海一样；我如同那飘忽不定的长风 不知何处才是归宿。众人活得都是那样的有用，只有我如此冥顽无能。虽然我和世人格格不入，但我还要继续以大道为依归。</t>
+  </si>
+  <si>
+    <t>本章是得道者的自画像。唯之与阿，相去几何？善之与恶，相去若何：恭敬的应答与呵斥相差多远？善与恶又相差多少？老子提醒，是非善恶的界限并非表面看起来那么分明，好事也可能带来坏结果。人之所畏，不可不畏：但众人共同敬畏的规则，也要敬守，不要为了标新立异而违背公认的规范。众人熙熙，如享太牢，如春登台：众人都热热闹闹，像参加盛宴、春日登台；我独泊兮，其未兆，如婴儿之未孩：得道者独自淡泊、无动于衷，像还不会笑的婴儿。
+众人皆有余，而我独若遗：众人都显得富足有余，得道者却像有所遗失。我愚人之心也哉，沌沌兮：一副愚人心肠，混沌淳朴。俗人昭昭，我独昏昏；俗人察察，我独闷闷：世人精明，得道者看似糊涂宽厚。澹兮其若海，飂兮若无止：他像大海一样淡泊深沉，像长风一样自由无羁。众人皆有以，而我独顽似鄙：世人都有用处，他看似冥顽无能。我独异于人，而贵食母：与众人不同，因为他以大道为归依。本章刻画了不随波逐流、独立守道的精神境界。</t>
+  </si>
+  <si>
+    <t>第二十一章</t>
+  </si>
+  <si>
+    <t>孔德之容，惟道是从。道之为物，惟恍惟惚。惚兮恍兮，其中有象；恍兮惚兮，其中有物。窈（yǎo）兮冥兮，其中有精；其精甚真，其中有信。自古及今，其名不去，以阅众甫。吾何以知众甫之状哉？以此。</t>
+  </si>
+  <si>
+    <t>高尚品德的内容，与大道是一致的。大道这种事物，是恍恍惚惚而没有形体的。它虽然是那样的恍惚迷离，但其中确实有一定内容；它虽然是那样的迷离恍惚，但其中确实有自己的内涵。大道是那样的深邃而难以认识，但它却有着自己的内容；它的内容是那样的真实无妄，充满了诚信。从古至今，大道都是无法被废弃的，凭借着它就可以知道万物开始时的情况。我凭什么知道万物开始时的情况呢？就是凭借大道。</t>
+  </si>
+  <si>
+    <t>本章讲大德与道的关系，证明道真实存在、可以验证。孔德之容，惟道是从：大德之人的样子，就是坚定地依道而行，“孔”是大，高僧大德即此意。道之为物，惟恍惟惚：道这个东西恍恍惚惚、没有固定形体；恍惚不是迷糊，而是心中忽然有光、有所领悟的顿悟状态。惚兮恍兮，其中有象；恍兮惚兮，其中有物：恍惚之中有境界、有内容。窈兮冥兮，其中有精：深远幽暗之中有精神；其精甚真，其中有信：这精神真实不虚，其中包含可信、可验证的规律。
+自古及今，其名不去，以阅众甫：从古至今，道的名字不曾消失，凭借它可以认识万物起始。吾何以知众甫之状哉？以此：我就是凭借道来认识圣人得道的状态。韩鹏杰强调，道不仅是万物的本源和规律，也是人生的境界；离开了道，人就变成无源之水、无本之木。这一章让人对道建立确信：它看不见摸不着，但真实存在，是精神世界的根基。</t>
+  </si>
+  <si>
+    <t>第二十二章</t>
+  </si>
+  <si>
+    <t>曲则全，枉则直，洼则盈，敝则新，少则得，多则惑。是以圣人抱一为天下式。不自见，故明；不自是，故彰；不自伐，故有功；不自矜，故长。夫唯不争，故天下莫能与之争。古之所谓“曲则全”者，岂虚言哉？诚全而归之。</t>
+  </si>
+  <si>
+    <t>忍受委屈则能保全自我，先弯曲反而能够伸直，低洼反而能够变得充盈，守旧反而能够创新，少取一些则有所收获，贪得无厌反而会变得迷惑。因此圣人能够同以上原则保持一致（持守道作为天下的法则）。他们不仅仅依靠自己的眼睛去观察，所以才能够看得清楚；从不自以为是，所以才能够彰显名声；从不自我夸耀，所以才能够保有功劳；从不自高自大，所以才能够成为领导者。正因为他们从不与别人争夺，所以天下没有任何人能够争得赢他们。古人所说的“委屈则能求全”这句话，难道是句空话吗？确实应该把保全自我的功劳归于这一原则（回归道）。</t>
+  </si>
+  <si>
+    <t>本章开头即主旨：曲则全，枉则直——懂得委婉迂回，才有更圆满的结果，像水一样绕开障碍、曲折流淌，才能到达目标；洼则盈——低洼处先被水灌满，善于处下才能获得更多；敝则新——破旧才有更新，世界有生有灭才生生不息；少则得，多则惑——知道自己懂得少才会努力学习，贪多反而迷惑。是以圣人抱一为天下式：圣人持守“一”作为天下范式，“一”就是阴阳两者的统一，看问题不能偏颇，要把对立两面合起来理解，就像同是数字6，对面看是9，各有立场。
+不自见故明，不自是故彰，不自伐故有功，不自矜故长：不固执己见才看得清，不自以为是才声名彰显，不自我夸耀才保有功劳，不自高自大才长久。夫唯不争，故天下莫能与之争：因为不与别人争夺，天下没有人能争得过他。古之所谓曲则全者，岂虚言哉，诚全而归之：古人说的曲则全，确实能把圆满的结果带回来。本章教人以迂回、谦下、统一的思维处理问题。</t>
+  </si>
+  <si>
+    <t>第二十三章</t>
+  </si>
+  <si>
+    <t>希言自然。故飘风不终朝（zhāo），骤雨不终日。孰为此者？天地。天地尚不能久，而况于人乎？故从事于道者，同于道；德者，同于德；失者，同于失。同于道者，道亦乐得之；同于德者，德亦乐得之；同于失者，失亦乐得之。信不足焉，有不信焉。</t>
+  </si>
+  <si>
+    <t>君主要很少发号施令而让百姓自由发展。所以说狂风刮不了整整一个早晨，暴雨下不了整整一天。谁制造了这些狂风暴雨？是天地。天地尚且不能长久维持这种剧烈动荡的局面，更何况人呢？因此那些寻求大道的人，言行就会符合大道；修养美德的人，就会具备美德；坚持错误的人，就会永远犯错误。愿意同大道在一起的人，大道也乐于同他在一起；愿意同美德在一起的人，美德也乐于同他在一起；愿意同错误在一起的人，错误也乐于同他在一起。由于自己的诚信不足，才会不被信任。</t>
+  </si>
+  <si>
+    <t>本章讲少言自然、同气相求。希言自然：珍惜言语、少发号施令，顺其自然才是规律。飘风不终朝，骤雨不终日：狂风刮不过一个早晨，暴雨下不了一整天，天地发的“脾气”尚且不能长久，何况人呢？人不应长期处于急躁、暴躁、浮躁的情绪状态。从事于道者，同于道；德者，同于德；失者，同于失：追求道的人与道相合，修养德的人与德相合，放任过失的人与过失相合。
+同于道者，道亦乐得之；同于德者，德亦乐得之；同于失者，失亦乐得之：你喜欢什么、亲近什么，就会被什么吸引和成就，人身边聚集什么样的人，往往取决于你自己是什么样的人。信不足焉，有不信焉：自己诚信不足，别人自然不会信任你。韩鹏杰指出，本章看似同语反复，其实在反复劝告：要让自己的境界不断提高，就要亲近有道有德的人和事，勇于发现并改正缺点，路是自己走出来的。</t>
+  </si>
+  <si>
+    <t>第二十四章</t>
+  </si>
+  <si>
+    <t>企者不立；跨者不行；自见者不明；自是者不彰；自伐者无功；自矜者不长。其在道也，曰余食赘（zhuì）行。物或恶（wù）之，故有道者不处。</t>
+  </si>
+  <si>
+    <t>踮起脚跟想站得高一些的人反而站不稳；跨着大步想走得快一些的人反而走不远；仅仅依靠自己的眼睛去观察反而看不清楚；自以为是反而名声不高；自我夸功反而会把功劳夸没了；自高自大反而做不了领导者。站在大道的立场上去衡量这些行为，可以说这些行为都像剩饭肉瘤一样多余无用。人们大概都很讨厌这些行为，所以懂得大道的人不去做这样的事情。</t>
+  </si>
+  <si>
+    <t>本章列举自见、自是、自伐、自矜四种毛病，提醒人们平稳谦逊。企者不立：踮起脚尖想站得高，反而站不稳；跨者不行：跨着大步想走得快，反而走不远，稳定才能致远。自见者不明：固执己见的人看不清，兼听则明、偏听则暗；自是者不彰：自以为是，德行和功绩反不能彰显；自伐者无功：自我夸耀、攻击别人，反而把功劳送掉；自矜者不长：自高自大、放不下虚荣，反而失去成长机会。
+其在道也，曰余食赘行：这些行为在道看来，就像吃饱了再吃、身上长赘瘤，多余无用；物或恶之，故有道者不处：人们厌恶它们，有道的人不做这些事。韩鹏杰用项羽举例：力拔山兮气盖世，却因骄傲自大、听不进意见，落得自刎乌江的下场。孔子讲毋意、毋必、毋固、毋我，佛家讲无我相，与老子相通。做事要稳扎稳打，收敛自见、自是、自伐、自矜，才能不断进步。</t>
+  </si>
+  <si>
+    <t>第二十五章</t>
+  </si>
+  <si>
+    <t>有物混成，先天地生。寂兮寥兮，独立不改，周行而不殆，可以为天下母。吾不知其名，字之曰“道”，强为之名曰“大”。大曰逝，逝曰远，远曰反。故道大，天大，地大，王（wàng）亦大。域中有四大，而王居其一焉。人法地，地法天，天法道，道法自然。</t>
+  </si>
+  <si>
+    <t>有一个事物混然而成，它出现在天地之先。它无声无形，独立存在永不改变，它支配万物循环运动永不停止，可以把它看作是天地万物产生的根源。我不知道这个事物的名字，就给它起个字叫“道”，再勉强给它起个名叫“大”。“大”使万物向前发展，发展下去就会走向极盛，走向极盛后又要返回到起点。所以说道有道的规律，天有天的规律，地有地的规律，治国也有治国的规律。天地间有四种主要规律，而治国的规律只占其中之一。人要效法地，地要效法天，天要效法大道，大道就效法它自身的样子。</t>
+  </si>
+  <si>
+    <t>本章是《道德经》极重要的一章，把道确立为宇宙本源，并提出全书最高法则道法自然。有物混成，先天地生：有一个混然一体的东西，先于天地而存在；寂兮寥兮：它无声无形；独立不改，周行而不殆：独立存在、永不改变，循环运行、永不停止，可以为天下母：可以看作天地万物的母亲。吾不知其名，字之曰道，强为之名曰大：不知它叫什么名字，勉强称它为道，再勉强称它为大。大曰逝，逝曰远，远曰反：大则向前运行，运行则越走越远，远到极点又返回本根，这是道的运动轨迹——周而复始。
+道大，天大，地大，王亦大，域中有四大，而王居其一焉：道、天、地、人（王）都是大的，人只是四大之一，不能自大。人法地，地法天，天法道，道法自然：人效法地，地效法天，天效法道，道效法它本来的样子，自然就是本该如此。韩鹏杰强调，道法自然是全书信仰和规则的源头，人要敬畏天道，与天地和谐相处。</t>
+  </si>
+  <si>
+    <t>第二十六章</t>
+  </si>
+  <si>
+    <t>重为轻根，静为躁君。是以圣人终日行不离辎（zī）重。虽有荣观，燕处超然。奈何万乘（shèng）之主，而以身轻天下？轻则失本，躁则失君。</t>
+  </si>
+  <si>
+    <t>重是轻的基础，静是动的根本。因此圣人整天在外旅行而从不离开自己的衣食行李。即使有奇观美景，也安处超然。为什么一个大国君主，却为了个人享乐而不重视自己的国家呢？不重视国家就会丧失自己的生存基础，轻举妄动就会丢掉自己的生存根本。</t>
+  </si>
+  <si>
+    <t>本章讲重与轻、静与躁的关系。重为轻根：稳重是轻率的根本，要拿稳重控制住轻率，不让它表露、掌控自己；静为躁君：宁静是急躁的主宰，用安静、宁静、冷静控制浮躁、急躁、暴躁。是以圣人终日行不离辎重：有修养的人像行军不离粮草辎重一样，始终持守稳重这个根本。虽有荣观，燕处超然：面对华美堂皇的外在诱惑，依然安处超然，不为其所动。奈何万乘之主，而以身轻天下：为什么掌握大权的君主，却为了个人享乐而轻率地对待天下大事？
+轻则失根：轻率轻浮就失去根本，像飘蓬浮萍没有根基；躁则失君：浮躁急躁就失去对自己的掌控，冲动之下常常酿成大祸。韩鹏杰用“路怒”举例：开车偶有小摩擦就粗口相向甚至拔刀，动手前问自己要不要动手、后果如何、有无别的办法，几秒钟的冷静可能改变结果。开头八字“重为轻根，静为躁君”与结尾“轻则失根，躁则失君”都是至理名言。</t>
+  </si>
+  <si>
+    <t>第二十七章</t>
+  </si>
+  <si>
+    <t>善行，无辙迹；善言，无瑕谪（zhé）；善数，不用筹策；善闭，无关楗（jiàn）而不可开；善结，无绳约而不可解。是以圣人常善救人，故无弃人；常善救物，故无弃物。是谓袭明。故善人者，不善人之师；不善人者，善人之资。不贵其师，不爱其资，虽智大迷，是谓要妙。</t>
+  </si>
+  <si>
+    <t>善于行走的人，不会留下车辙痕迹；善于讲话的人，不会出现语言瑕疵；善于计算的人，不必使用筹策；善于关门的人，不用关楗却固不可开；善于打结的人，不用绳索却牢不可解。因此圣人总是善于感化、以道救人，所以没有被遗弃的人。这是承袭道的智慧。善良的人，是不善人的老师；不善良的人，是善人的借鉴。不善人如果不尊重他们的老师，善人如果不爱惜他们的借鉴，即使是明智的人也会变得十分糊涂，善人与不善人之间的关系是非常重要而微妙的。</t>
+  </si>
+  <si>
+    <t>本章讲善行无迹、善救无弃。善行无辙迹：真正的善行不留下痕迹，做了好事为了留名、作秀，就走到反面；善言无瑕谪：会说话的人语言没有瑕疵，与其多言被挑毛病，不如大音希声、无言胜有声；善数不用筹策：真正会计算的人不用算盘筹码，很多事情越算计越被算计，厚道才是最高的聪明；善闭无关楗而不可开：真正会关闭的人不用门闩门锁，心门上锁就找不到锁在哪里；善结无绳约而不可解：真正会捆绑的人不用绳索，情丝情网看似无形却解不开。
+是以圣人常善救人，故无弃人；常善救物，故无弃物：圣人善于救人救物，天下没有可抛弃的人、没有可抛弃之物，你没发现用处不等于无用，无用方为大用。善人者，不善人之师；不善人者，善人之资：善人是恶人的老师，恶人是善人的借鉴，“师资”一词正源于此。不贵其师，不爱其资，虽智大迷：不尊重老师、不爱惜借鉴，再聪明也是大迷惑，这是道的枢要。做人要善行不留痕迹，看人看物发现其用处，并善于从正反两方面学习。</t>
+  </si>
+  <si>
+    <t>第二十八章</t>
+  </si>
+  <si>
+    <t>知其雄，守其雌，为天下谿（xi1）。为天下谿，常德不离，复归于婴儿。知其白，守其黑，为天下式。为天下式，常德不忒（te4），复归于无极。知其荣，守其辱，为天下谷。为天下谷，常德乃足，复归于朴（pu3）。朴散则为器，圣人用之则为官长，故大制不割。</t>
+  </si>
+  <si>
+    <t>知道什么是刚健，却要安于柔顺的地位，甘愿做天下的沟谿（溪谷）。甘愿做天下的沟谿（溪谷），高尚的品德就永远不会丧失，就能恢复到婴儿的纯真状态。知道什么是显赫地位，却要安于低下的地位，做天下人的榜样。做天下人的榜样，高尚的品德就永远不会出差错，就能具有无穷的力量。知道什么是荣耀，却要安于屈辱的地位，甘愿做天下的虚谷。甘愿做天下的虚谷，高尚品德就会永远保持圆满，就能够同大道保持一致。大道会分散显现为万物各自的本性，圣人就顺应着万物各自的本性去进行管理，所以说最完美的治理是不去伤害万物的本性。</t>
+  </si>
+  <si>
+    <t>本章是“抱一为天下式”的例证，讲刚柔、黑白、荣辱的辩证统一。知其雄，守其雌，为天下谿：知道自己强大，却不恃强，安守柔雌，甘做天下的溪谷，水都汇到低处来，反而源远流长，复归于婴儿：回归婴儿般纯真柔软。知其白，守其黑，为天下式：知道明亮，却安守暗黑，做天下范式，常德不忒，复归于无极：德行不出差错，回归无穷的境界。知其荣，守其辱，为天下谷：知道荣耀，却安守屈辱，甘做天下的虚谷，常德乃足，复归于朴：德行充足，回归素朴。
+朴散则为器，圣人用之则为官长，故大制不割：素朴分散为万物之器，圣人顺应本性管理，最好的制度不伤害本性。韩鹏杰强调，守雌、守黑、守辱不是没有经历过强、白、荣就假装谦卑，而是先有实力和成就，再有资格谈守，比如书法先经历精巧，才能返璞归真。记住十八个字：知其雄守其雌，知其白守其黑，知其荣守其辱，就是这一章的核心智慧。</t>
+  </si>
+  <si>
+    <t>第二十九章</t>
+  </si>
+  <si>
+    <t>将欲取天下而为之，吾见其不得已。天下神器，不可为也，不可执也。为者败之，执者失之。是以圣人无为，故无败；无执，故无失。故物或行或随；或歔（xū）或吹；或强或羸（léi）；或载（zài）或隳（huī）。
+是以圣人去甚，去奢，去泰。</t>
+  </si>
+  <si>
+    <t>君主想要治理好天下却又按照个人意志去采取行动，我将会看到他达不到自己的目的（断定必然会失败）。天下这个神圣的器物，是不可以按照个人意志强行干预，强行把持。随心所欲地去治理天下的君主，一定会搞乱天下。想把天下据为己有的君主，一定会失去天下。因此圣人顺应自然 不妄为，故无失败；不强行把持，故无损失。（所以事情往往如此）本意也许是想走在前面 结果可能反而落在后面；本意也许是想轻轻哈气为物取暖 结果可能因为吹气太快而使物变凉；本意也许是想强壮 结果可能反而变得瘦弱；本意也许是想稍微减损一点儿 结果可能是全部毁掉了。因此圣人去掉那些极端的，奢侈的，过分的言行和欲望。</t>
+  </si>
+  <si>
+    <t>本章讲天下不可强为、强取。将欲取天下而为之，吾见其不得已：想用强力、武力夺取天下并按个人意志治理，注定达不到目的。天下神器，不可为也，不可执也：天下是神圣之物，不可强行干预，不可强行把持；为者败之，执者失之：强行去做的必失败，死死抓住的必失去。是以圣人无为，故无败；无执，故无失：圣人顺其自然、不妄为，所以不会失败；不强行把持，所以不会失去。
+故物或行或随，或嘘或吹，或强或羸，或载或隳：万物本性各不相同，有前行有跟随，有轻嘘有急吹，有强壮有羸弱，有安稳有毁坏，不能用一个标准、一种方式强求。是以圣人去甚，去奢，去泰：圣人去掉极端的、奢侈的、过分的言行和欲望。韩鹏杰指出，这一章要结合时代背景理解：春秋末期诸侯争霸、生灵涂炭，老子提出小国寡民设想，反对强为；读这一章要体会其中的沉痛感，任何事有生必有灭、有成必有败，强求和把持都违背天道。</t>
+  </si>
+  <si>
+    <t>第三十章</t>
+  </si>
+  <si>
+    <t>以道佐人主者，不以兵强天下。其事好还（huán）。师之所处，荆棘生焉。大军之后，必有凶年。善有果而已，不敢以取强。果而勿矜，果而勿伐，果而勿骄。果而不得已，果而勿强。物壮则老，是谓不道，不道早已。</t>
+  </si>
+  <si>
+    <t>遵循大道去辅佐君主的人，是不会凭借武力去逞强于天下的。用兵打仗的事很快就会得到报应。战争发生过的地区，荆棘丛生。大战之后，必有一个灾荒年。只要很好地取得胜利就罢手，不敢依仗武力称王称霸。胜利了而不自大，胜利了而不夸耀，胜利了而不骄傲。胜利之后还要感到自己是出于不得已才打的这次胜仗，胜利了而不逞强。事物强盛了就会走向衰败，求强求壮的做法是不符合大道的，不符合大道就会很快灭亡。</t>
+  </si>
+  <si>
+    <t>本章与三十一章表达中国人对战争的痛恨与对和平的热爱。以道佐人主者，不以兵强天下：用道辅佐君主的人，不靠武力逞强天下。其事好还：用兵之事很快有报应，你打人多重，反作用力就多重。师之所处，荆棘生焉：军队到过的地方，荆棘丛生、断壁残垣；大军之后，必有凶年：大战之后必有灾荒凶年。善有果而已，不敢以取强：不得已打仗，达到保卫目的就停手，不敢逞强。
+果而勿矜，果而勿伐，果而勿骄：胜利了不自大、不夸耀、不骄傲；果而不得已，果而勿强：胜利是出于不得已，胜了也不逞强。物壮则老，是谓不道，不道早已：事物强盛到极点就走向衰败，逞强求壮不合道，不合道就很快灭亡。韩鹏杰说，这章最后三句话值得牢记：师之所处荆棘生焉，大军之后必有凶年，物壮则老。战争不可轻易发动，对待战争的态度就是对待同胞生命的态度；中华民族热爱和平，不惹事也不怕事。</t>
+  </si>
+  <si>
+    <t>第三十一章</t>
+  </si>
+  <si>
+    <t>夫兵者，不祥之器，物或恶（wù）之，故有道者不处。君子居则贵左，用兵则贵右。兵者不祥之器，非君子之器，不得已而用之，恬淡为上。胜而不美，而美之者，是乐杀人。夫乐杀人者，则不可以得志于天下矣。吉事尚左，凶事尚右。偏将军居左，上将军居右，言以丧礼处之。杀人之众，以悲哀泣之，战胜以丧礼处之。</t>
+  </si>
+  <si>
+    <t>战争，是一种不吉祥的东西，人们大概都很讨厌它，所以掌握大道的人不去使用它。君子平时以左边为高贵，作战时却以右边为高贵。战争是不吉祥的东西，不是君子应该使用的，迫不得已时才使用它，最好漠然处之。即使战胜了也不应该赞美胜利，如果赞美战争的胜利，这就是以杀人为快乐。以杀人为快乐的人，不可能实现统一天下的志向。吉庆之事以左边为高贵，凶丧之事以右边为高贵。打仗时副将居于左边，主将居于右边，这是说要用办理丧事的礼节去处理战争的事情。战争杀人众多，要带着悲哀的心情参与战争，战胜了也要用办理丧事的礼节去处理它。</t>
+  </si>
+  <si>
+    <t>本章继续讲对待战争的态度，主张以丧礼对待战争。夫兵者，不祥之器：兵器是不祥之物，人们都厌恶它，所以有道的人不使用它。君子居则贵左，用兵则贵右：平时以左为尊，作战时以右为尊，用兵属于凶事。兵者不祥之器，非君子之器，不得已而用之，恬淡为上：战争不是君子常用的东西，万不得已才用，还要淡然处之。胜而不美，而美之者，是乐杀人：打了胜仗不应赞美庆祝，赞美胜利就是以杀人为乐；以杀人为乐的人，不可能得志于天下。
+吉事尚左，凶事尚右：吉庆之事尚左，凶丧之事尚右；偏将军居左，上将军居右，就是用办理丧事的礼节来对待战争。杀人之众，以悲哀泣之，战胜以丧礼处之：战争杀人众多，要带着悲哀的心情参与，战胜了也要用丧礼的仪式对待。韩鹏杰强调，这两章应该进小学课本，让和平的种子从小种下；战争胜利后第一件事不是放肆庆祝，而是祭奠双方的死者，因为他们都是生命。</t>
+  </si>
+  <si>
+    <t>第三十二章</t>
+  </si>
+  <si>
+    <t>道常无名，朴虽小，天下莫能臣也。侯王若能守之，万物将自宾。天地相合，以降甘露，民莫之令而自均。始制有名，名亦既有，夫亦将知止。知止可以不殆。譬道之在天下，犹川谷之于江海。</t>
+  </si>
+  <si>
+    <t>大道永远处于一种看不见、摸不着的虚无状态，它好像未加工过的原木一样，虽然微不足道 但是天下没有人能够改变它。王侯如果能够遵循大道，万物将会自然而然地宾服于他。天之气和地之气就会相互交融，降下甘露一类的美好事物，没有人指使人们该如何做而自然均平安定。人们开始制作各种各样有名称的器物和制度，各种器物和制度出现以后，也应该知道适可而止。知道适可而止就能避免危险。打个比方 大道与天下万物的关系，就好像江海与河川的关系一样。</t>
+  </si>
+  <si>
+    <t>本章讲道的特点和知止的智慧。道常无名，朴虽小，天下莫能臣：道恒常无名，它的重要属性是朴实厚道；朴像原木，看似微小，却没有任何东西能让它臣服。侯王若能守之，万物将自宾：领导者若能守住朴实厚道，万物自然宾服归附。天地相合，以降甘露，民莫之令而自均：天地阴阳相合降下甘露，没有人命令，雨露自然均匀，治理也应如此自然而然。
+始制有名，名亦既有，夫亦将知止，知止可以不殆：人类社会开始有制度、名分是合理的，但有了名分制度要懂得边界，不能制度崇拜、名分崇拜，做过了头就走向反面；知道适可而止，才能避免危险。譬道之在天下，犹川谷之于江海：道在天下，就像川谷流向江海，是自然归附的过程，不是强迫。韩鹏杰强调，老子反复用重复和强调来突出重要思想，本章的核心就是朴与知止：做事朴实厚道，对制度名分保持克制，知道边界和限度，物极必反，知止不殆。</t>
+  </si>
+  <si>
+    <t>第三十三章</t>
+  </si>
+  <si>
+    <t>知人者智，自知者明。胜人者有力，自胜者强。知足者富，强行者有志。不失其所者久，死而不亡者寿。</t>
+  </si>
+  <si>
+    <t>能够认识别人的人是聪明的，能够认识自我的人则更为睿智。能够战胜别人的人是有力量的，能够战胜自我的人则更为强大。知道满足的人是富有的，遵循大道坚持力行的人是有志的。不违背大道的人就能长久生存，死而精神永存的人是真正的长寿之人。</t>
+  </si>
+  <si>
+    <t>本章像一首哲理诗，讲认识自己、战胜自己。知人者智，自知者明：了解别人是智慧，了解自己才是高明，人贵有自知之明，眼睛能看远方却看不见自己的眉毛。胜人者有力，自胜者强：战胜别人只是有力，能战胜自己的欲望、弱点才是真正的强大，西方强国强调强加于人，只是胜人者有力。知足者富：知道满足才是真正的富有，贪得无厌永远觉得匮乏；强行者有志：坚持按道去做、知难而进的人才有志向。
+不失其所者久：不离开自己的归宿才能长久，“所”就是精神家园，物质再发达也不能让精神家园花果飘零。死而不亡者寿：身死而精神不亡，才是真正的长寿，那些思想家的光芒像群星，在黑暗时指引方向。韩鹏杰说，这一章既写给领导者也写给普通人：自知、自胜、知足、强行、守所、精神不亡，六层递进，是中国文化中极高的人生境界。</t>
+  </si>
+  <si>
+    <t>第三十四章</t>
+  </si>
+  <si>
+    <t>大道泛兮，其可左右。万物恃之而生而不辞，功成而不名有。衣养万物而不为主，常无欲，可名于小。万物归焉而不为主，可名为大。以其终不自为大，故能成其大。</t>
+  </si>
+  <si>
+    <t>大道的作用是那样的广大而普遍，可以说无处不在。万物依靠它才能生存 而它从不限制万物，大功告成也不去求名、不去占有。护养了万物而不做万物的主宰者，永远没有什么欲望，可以把道看作是卑微的。因为虽然万物归附于它 而它却不当万物的主宰者，也可以把它看作是伟大的。因为它始终不追求成为伟大者，所以才能成为伟大者。</t>
+  </si>
+  <si>
+    <t>本章讲道无处不在、成就万物而不主宰，因不自大而成其大。大道泛兮，其可左右：道如水、如风，无处不在，左右逢源。万物恃之而生而不辞：万物依赖道生长，道从不推辞；功成而不名有：成就万物却不居功留名。衣养万物而不为主：护养万物却不做主宰，不要求感恩戴德。常无欲，可名于小：道无欲谦下，可以说它渺小；万物归焉而不为主，可名为大：万物归附它却不自居为主，又可以说它伟大。以其终不自为大，故能成其大：正因为它始终不自以为大，才真正成就了伟大。
+韩鹏杰强调，这一章讲量变质变、从小到大的道理：合抱之木生于毫末，九层之台起于累土，千里之行始于足下；天下难事必作于易，天下大事必作于细。做人做事不要自高自大、好高骛远，要虚怀若谷、脚踏实地，把容易的事当难事做，把小事做好，一步一步成就伟大。</t>
+  </si>
+  <si>
+    <t>第三十五章</t>
+  </si>
+  <si>
+    <t>执大象，天下往。往而不害，安平泰。乐与饵，过客止。道之出口，淡乎其无味。视之不足见，听之不足闻，用之不足既。</t>
+  </si>
+  <si>
+    <t>如果君主掌握了大道，天下人都会归附于他。归附他不会有任何害处，都能过上太平安乐的好生活。然而由于贪图诸如音乐美食等各种安逸的事物，往往会使那些皈依大道的人半途而废。大道这种事物说出来，淡淡的没有任何味道。看它又看不见，听它又听不到，用它却用不完。</t>
+  </si>
+  <si>
+    <t>本章讲守道则天下归往，平淡才是真。执大象，天下往：掌握大道（大象即道），天下人都会归附；往而不害，安平太：归附而不受伤害，安详、平稳、太平。乐与饵，过客止：音乐与美食能让人停下脚步，这些外在享受有吸引力，但也容易让人半途而废，不能沉溺其中。道之出口，淡乎其无味：道说出来淡而无味，不像美食音乐那样刺激；视之不足见，听之不足闻，用之不足既：看不见、听不到，却取之不尽、用之不竭。
+韩鹏杰说，我们日常所用而不知，天天都在用道却不自知；饮食清淡有益健康，人格返璞归真才接近道，清水出芙蓉、天然去雕饰是艺术的高境界。年轻人都觉得自己会成为伟大人物，最后发现伟大来自平凡，把自己看得平凡，才能重归于朴、重归于真、重归于道。真正的力量不是热闹炫耀，而是平淡之中无穷无尽。</t>
+  </si>
+  <si>
+    <t>第三十六章</t>
+  </si>
+  <si>
+    <t>将欲歙之，必固张之；将欲弱之，必固强之；将欲废之，必固兴之；将欲夺之，必固与之。是谓微明。柔弱胜刚强。鱼不可脱于渊，国之利器不可以示人。</t>
+  </si>
+  <si>
+    <t>要想收缩自己的对手，必须暂时让对手扩张开来；要想削弱自己的对手，必须暂时加强自己的对手；要想废除自己的对手，必须暂时让对手振兴起来；要想夺取对手的东西，必须暂时先赠予一些东西给对手。这就叫作含而不露的聪明。也即以柔弱的手段战胜刚强之人的策略。使用这些策略时要像鱼不可离开水那样不能脱离一定的客观条件，也像国家的优良武器一样 不能让别人知道。</t>
+  </si>
+  <si>
+    <t>本章把相反相成的思维讲得最直白，并提醒含藏的力量与边界。将欲歙之，必固张之：想收敛它，先让它张开；将欲弱之，必固强之：想削弱它，先让它强大（捧杀）；将欲废之，必固兴之：想废弃它，先让它兴盛，举得越高摔得越重；将欲夺之，必固与之：想夺取它，先给予它，钓鱼先下鱼饵。是谓微明：这种微妙而明确的智慧叫微明。柔弱胜刚强：柔弱可以战胜刚强。鱼不可脱于渊：鱼不能离开水，策略不能脱离客观条件；国之利器不可以示人：国家的利器不能轻易示人，时时亮剑威胁别人，别人就想折断你的剑。
+韩鹏杰用捧杀典故解释：杀君马者道旁儿，过分夸奖、吹捧使人骄傲自满、退步失败，关羽过不了奉承关而败走麦城；两军对垒时老弱残兵挑衅、敌人弃辎重诱敌，都是将欲夺之必固与之。本章不是说用阴谋，而是讲事物转化的规律：看清对立面的运动，力量与边界都要含藏，不能张扬炫耀。</t>
+  </si>
+  <si>
+    <t>第三十七章</t>
+  </si>
+  <si>
+    <t>道常无为而无不为。侯王若能守之，万物将自化。化而欲作，吾将镇之以无名之朴。无名之朴，亦将无欲。不欲以静，天下将自定。</t>
+  </si>
+  <si>
+    <t>大道永远是清静无为的 然而却又成就了万事万物。王侯如果能够遵循着它，百姓将会自然而然地发展生产。生产发展繁荣之后如有欲望产生，我将用无形无象的大道使他们安定下来。这种无名的质朴状态，本身也不会产生欲望。如果人们没有欲望就能保持平静，天下将自然会太平安定。</t>
+  </si>
+  <si>
+    <t>本章是《道经》的收束，讲无为而无不为。道常无为而无不为：道恒常无为，不妄为、不干预，却成就万事万物。侯王若能守之，万物将自化：领导者若能守住道，万物自然化育成长。化而欲作，吾将镇之以无名之朴：万物生长中欲望萌动时，用无名的素朴去镇服安定。无名之朴，亦将无欲：素朴本身没有欲望。不欲以静，天下将自定：没有欲望就能安静，天下自然安定。
+韩鹏杰把无为理解为：不违背规律、不妄为、不折腾，而不是消极不作为；治理的最高境界是让事物按自己的本性生长，让百姓自然发展生产、自然安定。从第一章到第三十七章是《道经》，讲道本身；后三十八章起是《德经》，讲道落实到人。把这两部分合起来读，“道在前而德在后”，做一切事才能顺理成章。</t>
+  </si>
+  <si>
+    <t>第三十八章</t>
+  </si>
+  <si>
+    <t>上德不德，是以有德；下德不失德，是以无德。上德无为而无以为；下德为之而有以为；上仁为之而无以为；上义为之而有以为；上礼为之而莫之应，则攘（rǎng）臂而扔之。故失道而后德，失德而后仁，失仁而后义，失义而后礼。夫礼者，忠信之薄而乱之首。前识者，道之华而愚之始。是以大丈夫处其厚，不居其薄；处其实，不居其华。故去彼取此。</t>
+  </si>
+  <si>
+    <t>真正崇尚美德的人并不去有意表现自己的美德，所以他才真正具有美德；不是真正崇尚美德的人却处处要表现自己的美德，所以他并不具有美德。真正崇尚美德的人清静无为 是因为他们没有个人功利目的需要多为；不是真正崇尚美德的人碌碌多为 多为是为了达到个人的功利目的；真正崇尚仁的人去做好事 做好事不是为了满足个人私欲；那些非常重视义的人去制定各种规则 制定规则是为了满足个人私心；那些非常重视礼的人去推行礼仪，如果没有人响应 他就会卷起袖子。因此说失去了道而后才去提倡德，失去了德而后才去提倡仁，失去了仁而后才去提倡义，失去了义而后才去提倡礼。礼仪，是忠信不足的标志 是祸乱的开始。那些超越时代的思想主张，站在道的角度来看 属于华而不实的东西，是愚昧的开始。因此大丈夫要笃守忠信，排除虚礼；要遵循规律，不要提倡超越时代的思想主张。所以要舍弃虚礼和超越时代的思想主张 笃守大道。</t>
+  </si>
+  <si>
+    <t>本章开启《德经》，讲真正的德是自然无心的。上德不德，是以有德：真正有德的人不把德行当回事，做了好事自然忘掉，反而真有德；下德不失德，是以无德：境界不高的人总怕德行失去，处处表现、宣扬，反而无德。上德无为而无以为：有德者自然作为，没有功利目的；下德为之而有以为：无德者做事带着目的。上仁为之而无以为：仁者做好事不为私欲；上义为之而有以为：讲义的人制定规则，多少带着私心；上礼为之而莫之应，则攘臂而扔之：讲礼的人若没人响应，就卷起袖子强推。
+失道而后德，失德而后仁，失仁而后义，失义而后礼：道、德、仁、义、礼逐层下降。夫礼者，忠信之薄而乱之首：礼是忠信稀薄、祸乱开始的标志。前识者，道之华而愚之始：自诩能预知未来的人，只是道的浮华外表，是愚昧的开始。是以大丈夫处其厚，不居其薄；处其实，不居其华：大丈夫要居厚实、弃浮华，去彼取此。韩鹏杰说，上德不德也是相反相成思维：越在意形式越失去内容。</t>
+  </si>
+  <si>
+    <t>德经</t>
+  </si>
+  <si>
+    <t>第三十九章</t>
+  </si>
+  <si>
+    <t>昔之得一者：天得一以清；地得一以宁；神得一以灵；谷得一以盈；万物得一以生；侯王得一以为天下正。其致之也，天无以清，将恐裂；地无以宁，将恐发；神无以灵，将恐歇；谷无以盈，将恐竭；万物无以生，将恐灭；侯王无以贵高，将恐蹶（jué）。故贵以贱为本，高以下为基。是以侯王自谓孤、寡、不穀（gǔ）。此非以贱为本邪（yé）？非乎？故致数舆无舆。是故不欲琭（lù）琭如玉，珞（luò）珞如石。</t>
+  </si>
+  <si>
+    <t>从前所有能够同大道保持一致的事物：天与大道保持一致 因而能够清明；地与大道保持一致 因而能够安宁；神与大道保持一致 因而能够有灵；河谷与大道保持一致 因而能够充盈；万物与大道保持一致 因而能够滋生；侯王与大道保持一致 因而能够做天下人的首领。如果放弃了大道，天无法清明，恐怕要破裂；地无法安宁，恐怕要废掉；神无法有灵，恐怕要绝灭；河谷无法充盈，恐怕要枯竭；万物无法滋生，恐怕要灭绝；侯王无法保持高贵的地位，恐怕要亡国。因此贵要以贱为根本，高要以下为基础。所以侯王自称孤、寡、不穀。这不正是以低贱为根本的表现吗？难道不是吗？想要获取过多的荣誉反而会失去荣誉。因此不要把自己看作是高贵的美玉，而应定位为一块丑陋的石头。</t>
+  </si>
+  <si>
+    <t>本章讲“得一”的力量和贵以贱为本。昔之得一者：天得一以清，地得一以宁，神得一以灵，谷得一以盈，万物得一以生，侯王得一以为天下正：天得道而清明，地得道而安宁，神得道而有灵，河谷得道而充盈，万物得道而生长，侯王得道而成为天下首领。“一”就是阴阳两者的统一，也就是道。其致之也：若失去道，天将裂、地将废、神将歇、谷将竭、万物将灭、侯王将蹶。故贵以贱为本，高以下为基：贵以贱为根本，高以下为基础。
+是以侯王自谓孤、寡、不穀：侯王自称孤、寡、不穀，正是以贱为本、以下为基。致数舆无舆：刻意追求众多荣誉反而失去荣誉。是故不欲琭琭如玉，珞珞如石：不要像华美的玉，要像坚硬的石头，石头能铺路济人，华美的玉看似高贵却少有用处。韩鹏杰强调两个重点：一是“一”即道，是阴阳统一；二是“贵以贱为本，高以下为基”，位置越高越要善于处下，把根基打牢，做人要处实不居华。</t>
+  </si>
+  <si>
+    <t>第四十章</t>
+  </si>
+  <si>
+    <t>反者道之动。弱者道之用。天下万物生于有，有生于无。</t>
+  </si>
+  <si>
+    <t>万物在大道的支配下向相反的方向发展，大道的作用就在于它能够提醒万物保持柔弱的状态。天下万物产生于某种物质，而物质产生于空间。</t>
+  </si>
+  <si>
+    <t>本章只有三句话，却是全书思维总纲。反者道之动：道向相反的方向运动，事物发展到极点就走向反面，又终而复返，回到更高层次的本根。所以看问题不能只站在自己的角度，要换位思考、正反合地看：正面看、反面看、合起来看，才能全面。弱者道之用：道的作用体现在柔弱一面，大家都逞强，柔弱反被强调，这是阴阳统一的思维方式。天下万物生于有，有生于无：万物产生于有，有产生于无；任何事物都有有和无两个方面，有让我们观察边界，无让我们观察妙处。
+韩鹏杰强调，如果只看到有形东西的作用，忽略无形东西的作用，物质世界越发达，精神家园就越花果飘零；既要看到物质财富，更要看到精神、信仰、理论这些无形力量。前三章讲道，第四十章用三句话总结全书思维方式，后边各章都是它的展开和例证。</t>
+  </si>
+  <si>
+    <t>第四十一章</t>
+  </si>
+  <si>
+    <t>上士闻道，勤而行之；中士闻道，若存若亡；下士闻道，大笑之，不笑不足以为道。故建言有之﹕明道若昧，进道若退，夷道若颣。上德若谷，大白若辱，广德若不足，建德若偷，质真若渝。大方无隅，大器晚成，大音希声，大象无形。道隐无名，夫唯道善贷且成。</t>
+  </si>
+  <si>
+    <t>上等的士听到道，就会努力去实行；中等的士听到道，将信将疑；下等的士听到道，大声嘲笑。不被嘲笑，就不足以成为道了。所以古时候立言的人说过这样的话：光明的道路好像是昏暗不明的；前进的道路好像是后退的；平坦的道路好像是不平的。最高的德好像是山谷，最光明纯洁的内心好像是蒙受屈辱，广大的德好像不足的样子，刚健的德好像是软弱的样子，质性真的东西仿佛都是有缺点一样。最大的方没有棱角，最大的器件最晚做成，大音平时少讲话，关键时刻掷地有声，最大的形象没有形状。道隐藏于事物背后，没有名字。道善于帮助万物并成就万物。</t>
+  </si>
+  <si>
+    <t>前边《德经》的部分我们讲了第三十八章，“上德不德，是以有德，下德不失德，是以无德。”讲了第三十九章，第三十九章第一个重要的概念是“一”。我再重申一遍，是阴阳两者的统一，也就是道。第三十九章里边的重点词，我们要不断地重申、重复，以求达到大家的记忆。“贵以贱为本，高以下为基。”第四十章我们极为看重。因为这一章开头五个字，是整个这一本书里思维的总纲：“反者，道之动”，下边是它的具体的体现，“弱者，道之用。天下万物生于有，生于无。”现在我们具体来讲第四十一章，这一章内容也非常丰富。首先我们在前边就强调过，《道德经》是对面有人问问题，老子给予的回答。现在对面有人问关于“士”的问题了。“士”这个阶层，把它理解为做官的阶层也可以，“士”这个概念，它的原意就是做事。延伸意指的是一个领导阶层。推十为一嘛，十个人里边推举出来一个领导大家，服务大家，管理大家。所以有人问老子，你看这些士，怎么来判断他们境界的高低呢？水平的高低呢？老子也是拿道来评价的。所以在这一章里边，一开始老子就讲“上士闻道，勤而行之”，境界高的、水平高的士这个阶层这些人，听到了道，比如说他的领导者讲的话，他觉得有道，有道理，“勤而行之”，就是执行力最强，坚定不移地按照它去做。有问题呢？自己勤勉、勤奋地把它解决，“勤而行之”，知行合一了嘛。知道了就按照道去做。中等境界的是什么呢？“中士闻道，若存若亡”，将信将疑。也想去按照道去做，但是一遇到事了就怀疑了。“若存若亡”，将信将疑，迟迟疑疑，犹犹豫豫，执行力不够。“下士闻道，大笑之”。境界最低的、最差的是干吗呢？嘲笑。人家说什么，制定什么样的制度规则，他都嘲笑，讲什么他都觉得不对，但是又提不出建设性意见，什么叫建设性意见？你觉得人家这个不好，你有没有更好的方案？觉得有问题，客观地指出来、提出来怎么改进，不是为了嘲笑而嘲笑，不是为了讽刺而讽刺。我觉得现在很多语言类的节目只是为了讽刺别人，讲话的时候只是为了打击别人，没有其他什么善良的目的。所以这就属于“大笑之”。别人给他讲道理，他还在那嘲笑，甚至羞辱人家。当然对这个事老子是想得开的。告诉坐在对面问他问题的人，怎么接待这些人，对待这些问题。别当回事，不笑不足以为道。这个世界现在已经没有哪件事是大家都赞成的了，所以有人嘲笑这是正常的。你要跟这些人计较，那就把自己的生命全都浪费了。说到这儿我就得插一句话，我觉得这个境界的差别，格局的差别，心胸的差别在什么地方呢？就在对待攻击者的身上。你看孟子也是我们文化里非常不得了的一个人，但是你看孟子的书里，会有一个什么感觉呢？年轻人，气势太盛。孟子对待当时的一些学术大咖，比如说墨子，比如说杨朱，当时杨墨是显学，名气很大。孟子怎么来评价他们呢？孟子就说墨子这个人讲“兼爱，是无父也”。兼爱嘛，你都平等，没有差别嘛，你置于你父亲于何地？没有把你父亲凸显出来，没有把对父亲的爱突出出来，无父也。杨朱不是讲，“拔一毛而利天下，吾不为也”。大家不要误解这句话，它的原意是你拿天下来换我的身体，让我损害自己的生命去换天下，我不干。它是强调自己的生命的重要。“拔一毛而利天下，吾不为也”。杨朱讲“为我”，所以孟子骂他是无君。你老为自己，你把君置于何地？“无父无君是禽兽也”——他骂杨朱和墨子两个人是禽兽。反过来看老子对待这些人的态度是——“不笑不足以为道”，淡然一笑，过了——很值得人佩服的一种态度。这就叫“明月清风”。对待别人的嘲讽，对待别人的攻击，有这样一个态度，也是很不得了的一种智慧与境界。这一段是本章里边的核心。因为我觉得他上中下的这种区分非常明了，很实用。“上士闻道，勤而行之”。坐而论道，不如起来行嘛。大家看道字的写法，首是头脑、思维、想。“走”之旁是行。所以这个道本身就是一个知行统一的概念。“上士闻道，勤而行之。中士闻道，若存若亡。”犹犹豫豫，不坚定，不能够坚定坚持的按照道去做。“下士闻道，大笑之。”我们千万不要做这种老是嘲笑别人，讽刺别人的，否则就会落于下乘，不笑不足以为道，太好了。明月清风一般地对待这种嘲讽辱骂的这种态度。下面这一段开头这句话非常有意思，叫“建言有之”，“建言”就是我们说的常言。常言说得好，这是我们经常用的，所以下面这句话大家注意，不是他本人的话。就是告诉大家了，明确下边讲的很多都是常言，在当时就是一句俗语。他讲的这些道理都是什么呢？都是前边我们讲的“反者，道之动”的例证。所以我在前面给大家说，第四十章是全书的总纲，可以举的例证会无限多，下边都是。“明道若昧”，光明的道路好像是昏暗不明的。为什么？有些给你指出的光明大道说得多么多么得好，指出光明大道简直就是美得不得了，你要小心了，前面有陷阱。真正的大道，反而像是昏暗不明的，就是把路上的艰险，遇到的阻碍，遇到的问题，都给你说清楚，让你看得清楚，这才是明道。给你说这条路没问题，太直了，平坦了，你沿着这条路走，肯定光明无限；沿着这条路走，肯定兴旺发达，一点阻碍都不会有，这个事绝对没问题。坏事了，这个时候你就得小心了。要知道“明道若昧”。再举个关于“朋友”的例子说明这个问题。朋友有三类，友直，友谅，友多闻。第一类的朋友直率，你有问题给你直接指出来。你走的道有问题的时候直接告诉你，跟你讲，怕你犯错误，怕你在这个地方出现问题。不是你的朋友呢？你走在道上遇到什么问题与他有什么关系啊，你问他这条道怎么样？他就告诉你，好好好，走走走，这条路没有任何问题。你给我提点建议，没什么建议，走就是了。你掉到坑里边他管你呀！所以我们说这“明道若昧”，暗昧，昏暗不明。“进道若退”。我们有的时候自己老觉得自己进步太小，人有时候都不免太着急，老觉得“一万年太久，只争朝夕”。只争朝夕，我每天都得进步，我都得看到自己的进步，一感觉到自己没有进步，就着急了。其实你别忘了，人呢，走在路上没有直线的，“进道若退”，有时候我们感觉是退步的时候，其实我们是在进步。比如说练书法，大家都有这个感觉，刚练这几天觉得进步很大，我以后每天按照这个速度会很快成为书法大家，过一段时间感觉怎么回事？怎么我这字越写越差了，还不如开始呢。好多事情开始都是这样。其实这就是我们前进中的一个必然的现象。懂得以退为进，懂得退就是进，有时候退不就是进嘛。“进道若退”，这不就是相反相成嘛。所以我在想，在老子那个时代，你说这些常言都在。这得说中国古代的这些人的哲学的思维水平竟然达到这样一个高度。所以有的时候我们做的事情感觉退步的时候不要着急，退是前进中的必须经历的。就像我们经常讲一个词叫“能屈能伸”，想要伸不得先屈回来吗？这是不是退？退之后才更加有力量，进道若退。“夷道若颣”，颣就是不平，夷就是平，夷道就是平坦的路。真正平坦的路像什么？它是不平的，高低起伏的。为什么？开车人都有一个体会，你说开车的路太平坦了，这就很容易放松警惕了，感觉无聊疲惫了，就很容易出事。假如前边一会儿出现一点坡，则高度警惕，有的不是故意把道做得有坡嘛，这才是平坦的道。所以我们经常讲的一句话叫“曲折是一种常态”，平坦的大道里边有这样的一些坡，不平的地方，这才是真正的大道。它告诉我们的道理就是，其实我们走在路上不会是绝对平坦的。对路上遇到的这些，我们要有高度的戒备和警惕，这样才属于真正的夷道，也就是平坦的大道。“夷道若颣”，又是一个“反者，道之动”，相反相成。“上德若谷”，谷就是无穷无尽。我们经常讲不是虚怀若谷嘛，真正有“上德”的这些表现是什么？就像虚怀若谷。比如说谦虚，听得进别人的意见，比如说做了好的事情，自己把它像山谷里的风一样，过而无形，“上德若谷”，就是讲它“满招损，谦受益”，不自满，做了事情不居功自傲，“上德若谷”。“大白若辱”，“白”，我们在第二十八章讲过，知白守黑，那个时候给大家说过白，白就是内心的光明信念与远大的抱负，内心有光明、信念和远大的抱负，那他就能忍受很多的屈辱。为什么？能屈能伸嘛，有远大的抱负，那么这些羞辱也就不必被自己挂在心中了。知白守黑，内心有光明、信念和远大的抱负，才能守得住这个黑。不管是别人黑，还是有时候的这种自黑，这就是“大白若辱”。说一事，有一次我在云南楚雄给医生讲课。我说你们穿着白大褂，大家把你们叫“白衣天使”，那对病人偶尔几句话不合适的话，也应该不那么太在意了。因为“知其白，守其黑”，忍得屈辱、羞辱，吞得下委屈，也就扩大了格局。“广德若不足”，“广”当然是大的意思。越是有广博的、大的德的人，反而好像自己有缺陷，不足就是不满，满招损，谦受益嘛。知道自己有不足，大成若缺，才能不断地进步，不断地学习，不断地努力，提高自己的境界，让自己的德行更伟大、更广博，“广德若不足”。下面这四个字理解起来不太容易，叫“建德若偷”。这个“偷”字是大家不喜欢的，怎么能跟德并列到一块呢？说到一起呢？首先我们说这个“建德”是什么意思？刚健。刚健的德好像是软弱的样子。这不就又符合“反者，道之动”了吗？偷，懒惰、懈怠、疲软，有着刚健的德的人，他反而正好有的时候表现为他的反面，而不是说我认为自己有这种刚健的德，谁要惹到我了，我一定跟他较量到底，我一定坚咬不放。这其实反而不是刚健的德，也不是强的真正的表现。刚健的德往往表现出宽容，忍让，甚至软、弱、懈怠等，“建德若偷”。当然有人也把这个“偷”解释为偷偷摸摸，意思就是不去表现。这个也说得过去。“质真若渝”，这个“渝”和我们讲的“瑕不掩瑜”意思相似，真的东西不会是完美无缺的。“大方无隅”，最大的方是没有棱角的，没有棱角那不就成了圆了吗？所以我们经常讲“外圆而内方”。“大方无隅”，没有角落，不留死角，这才是真正的大方。其实再说一遍，大家仔细想，这大方已经变成圆了，因为咱们中国人对这个圆的印象非常好。所以老用圆满这样的词来形容一个好的事情。进而言之，人有了这个原则是对的，但是这个原则不是老去像割伤别人，外面是圆的，可以和外界相衔接。而内部方的，坚守自己的原则，所以这叫大方无隅。“大器晚成”，最大的器件最晚做成。这个很好，提醒我们不用着急。想终成大器吗？那就要踏踏实实，不断地努力，不断地学习，机会总是留给有准备的人。心智不成熟的时候，早出名并没有什么太大的好处。因为人早出名，心智不成熟，他一定就气锐，盛气凌人，盛气凌人则敛怨。就会得到很多来自各方很多的这种怨言，而这个就形成自己未来的一种发展的阻碍。所以古人讲，松柏必经岁寒之后，可从栋梁之任。你看松树、柏树经历一次又一次的寒暑的磨练，最后才可成为栋梁之材。人类历史上大器晚成的例子比比皆是，比如，姜子牙八十岁为相。历史上记载了很多人，都是在有准备的情况下遇到机会，把以前自己积累的经验、智慧，充分地发扬出来，终成大器，人生最坏的结局也不过是大器晚成，又有什么可着急，可焦虑的呢？“大音希声”，“希”不是没有。这个“希”大家可以从两个角度来理解，一个“希”是前面有声，而中间出现的停顿，比如，白居易的《琵琶行》，“别有幽愁暗恨生，此时无声胜有声。”前面有声，可是这个地方的停顿，它反而蕴含了更加丰富的内容，用有声表达不出来的这种情感，这是一个希声。“希声”还有一个表现是乐曲结束，声音之后的余响。苏轼的《前赤壁赋》里边叫“余音袅袅，不绝如缕”。这一个也是“大音希声”。《道德经》里面讲的“大音希声”的道理，其实它是有延伸的。一个是说我们的语言。第五章里边讲“多言数穷，不如守中。”发号施令多了，话多了，声多了，唠叨多了，就不起作用了。真正的大音呢，一定是平常少讲，关键时候掷地有声，说得恰到好处——大音希声。一个是说我们的制度。制度太繁琐了，反而它走向了负面，恰到好处就好。“大象无形”，这个在我们前边讲的时候也经常引用。“大象”本来就很大了，反正中国人一开始指的这个“象”，也是拿这个“大象”说事，本来就很大的。当然这个“象”是一个延伸。最大的形象是没有形状的。天有形状吗？风有形状吗？精神有形状吗？理论有形状吗？都没有，“大象无形”。虽然无形却力量巨大。所以我们拿风来说大象无形是最恰当的。没有人看见过风，风是没有形状的，我们只能够通过水面的波纹，麦浪的翻滚，柳梢的摇曳，我们知道风是存在的。虽然无形，但是它客观存在的，并且力量无比巨大。所以我们写文章才经常用这样的词，“民风”“党风”“作风”“家风”。风没有形状，但是力量巨大，“大象无形”，就像道一样。拿什么东西来比方这个道最为恰当？那就是风。道就像风一样，你看不见但它无处不在？“大象无形”。前边这些其实都是一些相反相成的例证，尤其是“大白若辱，大器晚成，大音希声，大象无形”，都已经成了我们生活中常用的成语了。就这一章里边的成语，你算算就有多少！咱们也不说这本书别的方面的价值。单说它在让我们了解中国文化中的成语的角度，它的作用就有这么大，而且这些成语直到今天，我们还经常使用，发挥着巨大的作用。所以，我们说文化，“文”就在这儿。你把它变成自己的，化入自己的内心，化入自己的精神世界，就叫“文化”。大象无形，却力量无尽，永远存在。道隐无名，道是没有名的。你没办法定义它的。第二十五章的时候我们就讲“有物混成，先天地生，寂兮寥兮”，“寂”就是无声，“寥”就是无形。它是无形无声的，你没有办法去定义它。道隐无名，它就隐到事物的背后，但是它却是事物的本质。道隐无名，就像风一样，在万事万物的背后你看不见，但它能吹绿万物，它能够摧枯拉朽，作用无比巨大。下边这句话就好理解了，“夫唯道”，也只有道啊，“善贷且成”，“贷”就是帮助，意思是资助万物，贷款给你，不就是资助你嘛？善于帮助万事万物成长、成功。“道”有多伟大，你看不见。“道”也不求回报，但它帮助万事万物成为现在这个样子。本章内容非常深刻。首先，有一个恒定的标准“道”来衡量事物。“士”可以分出上中下：“上士闻道，勤而行之；中士闻道，若存若亡；下士闻道，大笑之。”胸怀宽广的人对待这事情，如清风掠过，淡然一笑。你笑你的我笑我的，你不笑不足以为道。没有哪一件事情非得是全部大家都认可的。做事情按照“道”去走，被人嘲笑，被人嘲讽，这是正常的。内心应该有这样的宽容，有这样的接纳，有这样的态度。所以下边告诉大家，那个时代的一些常言、俗语，作为第四十章“反者，道之动”的例证：“明道若昧，进道若退，夷道若颣，上德若谷，广德若不足”。我把这两个排列在一块，然后再说“大白若辱”“知白守黑”。是说什么羞辱都受不了的人，受到一点羞辱就暴跳如雷的人，甚至只是自以为受到了羞辱就拔拳相向的人，其实就是自以为刚健而事实上是匹夫之勇，往往会“勇于敢则杀”，所以真正刚健的德反而像软弱的一样。真的完美的东西是有瑕疵的一样，即大成若缺。所以要懂得“知白守黑”，“知荣守辱”。这几个成语前边带过了之后，重点强调“大器晚成”——不着急，有准备终成大器，机会终究会有的。“大音希声”，真正的大音不是絮絮叨叨，而要掌握尺度，“多言数穷，不如守中”，“无声胜有声”，所以要懂得无言之教，大音希声。接着，“大象无形。道隐无名，夫唯道善贷且成”。只有“道”才能善贷且成，资助万物，帮助万物成长，帮助万物成功。这一章给人很多的启发，很多的回味。每个人读，都会有不同的感受。随着年龄的增长，我们也会不断获得新的体会。</t>
+  </si>
+  <si>
+    <t>第四十二章</t>
+  </si>
+  <si>
+    <t>道生一，一生二，二生三，三生万物。万物负阴而抱阳，冲气以为和。人之所恶，唯孤寡不穀，而王公以为称。故物或损之而益，或益之而损。人之所教，我亦教之。强梁者不得其死，吾将以为教父。</t>
+  </si>
+  <si>
+    <t>“道”即阴阳二者的统一，“一”中蕴含着阴阳两个方面，阴阳二者参与到一起相互作用形成万事万物。万物背阴而向阳，阴阳二者相互中和形成和谐状态。人人都厌恶的是孤、寡、不穀，但王侯却以此自称。所以有的东西减损它反而得到增加，有的东西增加它反而得到减损。别人教给我的，我也教给别人。喜欢强大暴力的人不得好死，我把它当作座右铭。</t>
+  </si>
+  <si>
+    <t>《德经》部分我们今天讲四十二章。老规矩，把以前的这几章我们再顺一下。《德经》从第三十八章开始，第三十八章讲“上德不德，是以有德；下德不失德，是以无德。”第三十九章我们讲了两个重要的部分，一个就是这个“一”，因为第四十二章又出现了这个“一”，就是阴阳两者的相互平衡，形成的统一体。在第三十九章里边有两句话每一次我都要重申一下，以求让大家牢牢地记忆，“贵以贱为本，高以下为基”。第四十章有一个全部这本书思维的总纲，“反者，道之动”。下边举的这些都是“反者，道之动”的一些例证。比如说“弱者，道之用，天下万物生于有，生于无”。第四十一章的时候，我们是花了比较多的时间来说，为什么呢？因为这一章里边有非常多的“反者，道之动”的例证。比如说“大音希声，大象无形，大器晚成……”这些都是我们平时经常讲的成语。上次讲完了大家应该知道了它的出处。那么今天我们讲第四十二章，这一章并不难理解，但是非常的重要。因为这一章开头这段话，大家经常在很多地方看到，比如北京故宫是建筑的典范，故宫的太和、保和、中和三大殿都是三层台基，也就是建在三层高台之上，为什么选择“三”这个数字呢？再比如我所在的学校叫做西安交通大学，在交大的管理学院，我的一个朋友也在那做了一面墙的雕塑：太极，大家有机会到交大管理学院的时候就会看到，就在一楼。这两个地方的解释，用的都是这段话：“道生一，一生二，二生三，三生万物。”我们来解释这段话，原文大家都看到了：“道生一，一生二，二生三，三生万物。万物负阴而抱阳，冲气以为和。”这个“冲”字，读成中，一下就理解了。下面这段话其实大家也耳熟，起码意思在前边已经说过。“人之所恶，为孤寡不穀，而王公以为称。”大家讨厌的孤、寡、不榖，王公却用来称呼自己，这不是我们前面第三十九章的时候已经说过的这个意思嘛。“故物或损之而益，或益之而损。人之所教，我亦教之，强梁者不得其死，吾将以为教父。”这是第四十二章原文。我们一段一段来解释。先说第一段，“道生一”。“一”我们俗称叫太极。其实“一”就是道的具体的特点，强调道就是“一”，是说道的最重要的一个特点，就是它强调阴阳两者的统一，“一”里边蕴含着阴和阳两种力量，两个方面。“道生一，一生二”，这个“一”里边蕴含着“二”，也就是道里边蕴含着阴阳两种力量，两个方面，两种状态。中国人讲，事物都是相互对立而存在的，万事万物归结到最后，它也不会是一个单一的元素。你看咱们中国历史上的《易经》，落到最后就是两个符号，阴和阳。那已经到了事物的极致了，极点了。把阴和阳统一起来叫太极，但是这两个元素是最基本的。所以“一生二”，是说太极道里边蕴涵着阴阳两个方面，两种力量。“二生三”，很多人对这个“二生三”解释得太费劲。“三”是什么？很简单，就是繁体字那个“叁”，就是参。阴阳两者参与到一起，相互作用，形成了万事万物，多简单的事情。它们两者孤阴不生，孤阳不长，两者相互作用，形成万事万物，“三生万物”。所以我们用的那个《中庸》的名言叫“参天地，赞化育”。人能参与到天地之间的运动发展，天地人三才嘛。三才你看人不也参与其中嘛。这个赞可不是赞扬的意思，也是参与的意思。两者参与到一起，产生万事万物，这是从正面。然后再反过来推，既然是三生万物，那么万事万物里边都包含着这两种力量，两个方面，阴阳两个方面，所以叫“万物负阴而抱阳”。随便找，哪一个事物内部都有阴有阳，都包含着阴阳两种状态、两种力量。“万物负阴而抱阳，冲气以为和”。为什么要把这个“冲”念成“中”呢？大家看“冲”的写法，前边这两点其实就代表着阴和阳，那个中就是中和的意思，就是参的意思。阴阳两种力量，中国人把它叫做气，阴气、阳气嘛。通天下一气，形成和谐的、动态的、运动的世界，这就是冲气以为和。这一段讲了我们中国哲学中的宇宙生成模式，也讲了这个世界存在的状态，以及这个状态的原因。这种状态都是阴阳两者运动所形成的，动态的、和谐的状态。冲气以为和。再重复一遍。“道生一，一生二，二生三，三生万物。”所以万事万物都有阴阳两个方面，“万物负阴而抱阳，冲气以为和。”下边就开始讲。用这种思维方式你来理解世界，你就不能只站在一个方面了，明确地告诉你了。事物都是统一的，两个方面不可偏颇，不可偏废。所以对侯王讲，“人之所恶，唯孤寡不穀。”你说大家最讨厌的就是这些词，孤家、寡人、吃不上饭、饿死。可是你看这些王公大人，包括后来的皇帝，他们都拿这个来称呼自己。干嘛呢？“故物，或损之而益，或益之而损。”这个“物”大家不要解释成物质，就是我们中国人常讲的那个“东西”。中国人这个“东西”太奥妙了，什么都可以称之为东西，不管是物质的、精神的都可以称之为东西。所以老子就说你看说到万事万物存在的这些各类各样的东西，“或损之而益”，你以为它受损了，其实它得到了益处。有的时候我们受到一点挫折，我们觉得自己受了多大的这种屈辱一样，可是你知道人都是在不断地受的这种损中逐渐地成长起来的，你认为它是祸，其实它是福，“损之而益”。有的时候你认为自己是得到了，其实反而是一种损失。比如偷了东西的，得到了，其实把人格给损失掉了。有的人用不光彩的手段，不择手段得到的，其实他们损失的反而更大，“或益之而损”。所以老子讲的是相反相成的道理。我们中国人常用什么事情来说这个事？叫破财免灾，叫大难不死必有后福，叫祸福相依，叫塞翁失马焉知非福，你看这讲的都是“损之而益，益之而损”。刚才举的例子不就是这样吗？这侯王王公们不都在损自己吗？把自己叫做“孤寡不穀”。其实有这个提醒之后，反而避免了自己变成孤寡不穀。以前中国人也有这个习惯，给小孩起名起个贱名，好养活。当然现在这种习俗很少再看到了，它讲究的就是“损之而益，益之而损”。民间很多的道理大家也得认真对待，别以为我们上了学之后自己水平就高了，其实真正的高手在民间。很多老人讲的话，到最后你一生体会，反而你发现真的是有道理。“人之所教，我亦教之，强梁者不得其死”。老子也说这些东西，也都是别人教给我的，给我讲的。我再把这些写出来教给大家。这一句我们可得好好地来给大家说道说道。为什么呢？因为这涉及老子的思想的来源，老子的思想来源当然有很多方面，主要的两条，两条道路。一条道路自然就是《易经》。因为你看，《易经》它把这个叫易以道阴阳，老子也讲阴阳，而且这里边的损和益，这不就是《易经》里边的损卦和益卦嘛，损和益这也是《易经》里边经常强调的。另外一个，我觉得这一章里边非常奥妙，一个是讲这阴阳的事情，让我们知道他的思想里边《易经》是中国文化之源，众经之首，损之而益，益之而损。另外一个也表现出他的思想的来源，就是“强梁者不得其死”，这句话也不是老子自己的，它出自《金人铭》。传说黄帝写了六篇铭文，叫《黄帝六铭》。其中有一个是刻在周朝台阶右面立着的金人背后，金人就是青铜做的，这金人的背后有铭文。经过汉朝的刘向《说苑》的考证对比，发现《金人铭》里边的这句话：“强梁者不得其死”。“强梁”就是处处逞强。喜欢暴力的人，最后不会有好的结果。我们讲死得其所，叫得其死，得好死，不得好死，不得其死。强梁者不得其死。说到“强梁”这个词，我想读过《水浒传》的人一定记得，在《水浒传》里边用到“强梁”这个词的时候，是用在了矮脚虎王英的身上。矮脚虎王英，这个是梁山泊里边大家都瞧不上的那么一个人。原来是个车夫，后来抢劫，后来落草。所以用这个词来形容他，“强梁者”。“强梁者不得其死”，老子非常反对强暴，而强调和平、守弱，认为“强梁者不得其死”，“木强则折，兵强则灭”，这是他后边关于这个问题的一个延伸。“吾将以为教父”，这个“教父”就是说，这是别人教给我的，我也把它拿来作为座右铭，来指导我自己。总结一下，大家看这一章，第一段话是我们大家都耳熟能详的，“道生一，一生二，三生万物，万物负阴而抱阳，冲气以为和。”第二段是我们前边讲过的内容，在这个里边又重申了一遍，注意这些重申可不是排版排错了。因为《道德经》里边它讲的几条重要的原则，遇到机会的时候，它就会反复，用重复的方式来强调。“人之所恶，唯孤寡不穀，而王公以为称。”所以对于万事万物而言，对这个世界存在的东西而言，“或损之而益，或益之而损”。有的你觉得是损失了，结果反而是得到了。有的你认为自己得到了，反而是损失掉了。因此不可一概而论。遇到了乐事的时候，不要过于高兴，以免乐极生悲。遇到不好的事，祸事的时候，也不要丧气，因为这些可以成为我们的经验，塞翁失马，焉知非福！这是别人教给我的，我也把它来教给别人。然后下边这句话是老子也非常强调的，“强梁者不得其死”，还是要和平，还是要守弱，处处逞强，总和别人结梁子，最后不会有好的结果。国家也一样，“国虽大，好战必亡”。老子说我也要把这个当作座右铭，这就明显地透露出他思想的来源，一源于《易经》，阴阳之学，损益之论，谦卑之礼。二源于《金人铭》，尤其是《金人铭》里这句话对老子影响是非常大的，所以他把它叫做“教父”，座右铭。</t>
+  </si>
+  <si>
+    <t>第四十三章</t>
+  </si>
+  <si>
+    <t>天下之至柔，驰骋天下之至坚，无有入无间，吾是以知无为之有益。不言之教，无为之益，天下希及之。</t>
+  </si>
+  <si>
+    <t>天下最柔弱的东西，可以攻克天下最坚强的东西，无形的东西能够穿过没有缝隙的地方，我因此知道了“无为”的益处。不言的教导，无为的益处，天下很少有人能做到。</t>
+  </si>
+  <si>
+    <t>我们说“反者，道之动”是整个这本书思维的总纲，也就是说它是一种思维模式、思维方法。第四十章一开头就讲“反者，道之动，弱者，道之用。天下万物生于有，生于无。”这里边出现了两个在《道德经》里边非常重要的字，一个是“弱”，也可以称其为“柔”，另一个就是“无”。第四十三章是对这些内容进一步的引申和展开。第一句“天下之至柔，驰骋于天下之至坚，无有入无间”。最柔弱的东西，反而能够攻克最坚硬的东西。那些没有间隙的地方，无形的东西却能够进入，能攻克。就像风，没有什么地方它进不去的。这些就是“道”，道讲完了。老子开始讲“德”。“吾是以知无为之有益”。我从“至柔驰骋于至坚”，“无有入无间”中知道：人类也是一样，有些事情，无为比有为效果更好——“无为之有益”。可是话说回来，“不言之教，无为之益，天下希及之”按照无为的道理去做事，所获得的好处、益处，天下的人却很少能够知道，很少能够达到。这些话该怎样进一步理解呢？老子在第七十章讲过，“吾言甚易知，甚易行，天下莫能知，莫能行”。什么意思？其实，我讲的道理都是非常简单的、平常。但是大家为什么不知道呢？做不到呢？因为这里边就隔了一个东西——欲望。有些事情大家明知道是这么回事，但是很多东西被欲望牵引就变得难做了。就像我们说“不贪为宝”，但为什么还有那么多人上当？有些人上当了还不好意思说出来。因为自己心里清楚，自己是因为贪心才是上当受骗了嘛。没有这个贪心，很多事情理解起来就太容易，太简单了。但一个骗局，往往能骗很多很多人！再说回来，“天下之至柔，驰骋天下之至坚，无有入无间”。天下的“至柔”是什么？无形是风，有形是水。第七十八章就说，”天下莫柔弱于水，而攻坚强者莫之能胜”。这不是正是“天下之至柔，驰骋天下之至坚”吗？天下什么东西最坚硬，石头？水滴石穿；金属？水刀切可以割金属。有什么坚硬的东西是水它克服不了的呢？风更是弥漫天下，摧枯拉朽，无所不在，力量无尽。你说这个东西没有间隙，但是无形的东西，它反而能够穿透它。现在，科学发现有一些微小的东西，比如说中子、粒子、量子……他们是无形的，你看不见，但没间隙的地方，它们都能够进入。我们眼里没有间隙的地方，对于它们来讲，缝隙简直太大了。“无有入无间”，在强调无的东西的作用。道家的“无为”相当一部分内容在讲“无之为”——这些无形的东西、无用的东西的作为。所以，不要把“无”理解为“没有”，把“无为”理解为“不做事”。“吾不言之教”，第二章讲过“行不言之教”，为什么？身教重于言教，话太多了，老去教化，训导别人，反而会起负面的作用。老师也罢，家长也罢，国家的领导也罢，做一个好的榜样，上行下效。孔子也讲了一句话，叫“君子之德风，小人之德草”。这里小人不是道德上的低下，而是指人民、平民、一般人。榜样的“不言之教”就像风一样，一般人就像草一样。风向哪个方向吹，他们跟随着风而倒。无之为所带来的益处，天下却很少有人能够达到——“希及之”！在讲第三十七章的时候我们说，“道常无为而无不为”，道的规律、规则就是“无为”，而“无为”的效果却是“无不为”——覆盖面更广，效果更好。这不就是“无为之益”吗？一开始讲第一章的时候，我就给大家说过，道家讲的“無”和舞蹈的“舞”字形极为相近。因为对于原始人来讲，舞蹈起到的作用实在太大了。有形的几个姿势，产生出的力量却是巨大的。既然是“无”是“无之为”，那么“无用”，也就是“无用之用”。你认为没用的东西，其实不是它没用，只是你没有看见它的用处。书法有什么用，绘画有什么用？不能当吃，不能当穿，可是如果大家否定了这些，那不就进入了一种狭隘的功利主义的境地了吗？人生最没用的事是什么？睡觉。睡着了什么都做不成。小孩最讨厌睡觉了，可是大家都知道现在有多少人被失眠所折磨，为睡不着觉而痛苦。这些“没用”的事你做不成，那么有用的事你也做不来。最后一句，“无为之益，天下希及之”是老子的感慨。大家老看不到这一点，老觉得无为的事情没用。殊不知你不做这些无为的事，就不能真正的有为。不了解这些无用东西的作用，你也就不知道什么才算是真正的有用。从“反者，道之动”，一直到现在，都在讲述一个道理。</t>
+  </si>
+  <si>
+    <t>第四十四章</t>
+  </si>
+  <si>
+    <t>名与身孰亲？身与货孰多？得与亡孰病？是故甚爱必大费，多藏必厚亡。知足不辱，知止不殆，可以长久。</t>
+  </si>
+  <si>
+    <t>名声与身体哪一个更亲近？生命和财货哪一个更重要？得到和失去哪一个更有害？过于爱惜必定会有大的耗费，过多的藏货必然会导致惨重的损失。所以知道满足就不会遭受屈辱，知道停止就不会遭到危险失败，这样才能长久。</t>
+  </si>
+  <si>
+    <t>前面我们说了第四十三章，最后说“不言之教，无为之益，天下希及之”。然后说这都是前面“反者，道之动”这种思维方式的进一步的延伸和具体的例证。这种方法我们大家已经习惯了，在哲学上叫做“二分法”，叫做“对立的统一”。第四十四章讲的也是这个。一开始先列出来三个对立的事物——名与身、身与货、得与亡，进行比较。“名与身孰亲？”“名”和“身”哪一个更重要？哪一个是对大家来讲是更亲的东西？“身与货孰多？”我们的生命和外在的物质相，财富哪一个更重要？“亲”也罢，“多”也罢，意思都在说哪一个更重要。我们常说“身外之物”，常说名和利生不带来，死不带去。你看，这一章就在解读这个问题了。第三个，“得与亡孰病？”这个好理解，参照我们前面讲的“或损之而益，或益之而损”，是得到的好还是失去的好？哪一个危害更大呢？“病”当然不是什么好词了，“得与亡孰病？”其实在问的时候这个答案已经有了。这就是一种反问的语气，表示强调。因为有的人在名和自己生命的选择之中选择了殉名；有的人，“人为财死，鸟为食亡”——因为财富的事，把自己的生命搭上去了。真的是得到就好，失去就不好吗？比如，我们读像《道德经》这样的书，我们会得到什么？也许什么都没得到，但是我们失去了焦虑，失去了急躁，失去了自高自大，这些东西失去了，那不就是一种得到吗？不是说得到就好，失去就不好。有的东西失去，反而是获得；有些东西得到，反而是真正地失去。三个反问句，答案其实都在里边。下面这几句话，讲得就更深刻了。“甚爱必大费，多藏必厚亡”，对一个东西太珍爱了，最后一定会付出大的代价。比如，有的人他有这种癖好，他喜欢古玩，别人送的别的东西他不要，你拿着古玩一贿赂他就收下来，最后就因为这个自己犯了事儿——“甚爱必大费”。有的人把减肥当作唯一的事业，尝试各种各样靠谱不靠谱的方法，把身体折腾得一塌糊涂，那不就得付出大的代价吗？很多事情都是这样的结果。“甚爱”，太过分了，不是说不好，但是过分了，这就走向了它的反面，物极必反嘛！“多藏必厚亡”，很多东西收敛、搜刮到了，自己把它藏起来，能藏得住吗？最后这个搜刮来的东西一定都成为自己的污点和罪证。多藏必厚亡，“厚”也是大的意思。下边这两句话大家都熟：“知足不辱”。我们知道满足有边界，这样才不会受屈辱。这事我知足，我不卑躬屈膝求别人，我觉得我这个已经很好了，这是我自己奋斗来的，额外的，不择手段得来的东西，我不需要，“知足不辱”。“知止不殆”。这个地方，我得给大家多说几句。老子这个人真的是不得了，他只用一个“走道”的形象，就说清楚了很多问题。我们走在道上，应该注意什么呢？有几个最重要的内容：方向、目标、规则、境界、边界、底线。我们要去什么地方？方向、目标。我们什么时候该停下来呢？只要是道就有边界，道外边往往就是深沟，就是深渊，就是歧路。我们了解边界底线，不贸然地前闯，有“底线思维”，“红线思维”，给我们的欲望划出边界，就是“知足”。知足才能不辱。“知止不殆”，“殆”就是危险失败。知道边界、底线不闯，我们才能没有危险，没有失败。当年杨虎城在陕西把他办公的行园就改名叫“止园”。出处就是这四个字，“知止不殆”。“知足不辱，知止不殆”的意义在哪儿呢？——“可以长久”。其实这些事情不用举太多的例证，为什么？因为例证太多了，不了解边界、底线，冒进、冒险，肯定会导致大的，糟糕的后果。这一章没有什么难以理解的，但是内容也非常深刻，尤其是前边这三个提问或者叫反问，都是我们应该深深思考，并做出回答的。拿我们的生命和名声去交换名利，到底划得来划不来？到底哪个更重要？哪个对我们更亲？身与货和这些财富进行比较的时候，到底哪个更重要？我们拿生命去换财富，回头再拿财富来换健康——有时候，甚至换不回来。“得与亡孰病？”不要认为得到就高兴，失去就不高兴，其实得失就是这样的相反相成。很多事情反而是损之而益，有的是益之而损。祸福相依，相互转化，物极必反。既然物极必反，下面这几句话就好理解了，“甚爱必大费，多藏必厚亡”，因此应该“知足不辱，知止不殆”——知足可以不辱，知止可以不殆。知足、知止，我们才能长久。不管是对于生命，还是对于事业而言，才能稳定致远，长久地发展。这是第四十四章的内容，内容不多，但是我们应该熟记，尤其是几个对偶的句子：“甚爱必大费，多藏必厚亡”；“知足不辱，知止不殆”。</t>
+  </si>
+  <si>
+    <t>第四十五章</t>
+  </si>
+  <si>
+    <t>大成若缺，其用不弊；大盈若冲，其用不穷。大直若屈，大巧若拙，大辩若讷。躁胜寒，静胜热，清静为天下正。</t>
+  </si>
+  <si>
+    <t>最完满的东西好像有欠缺，但它的作用不会衰竭；最充盈的东西好像是空虚的，但它的作用没有穷尽。最直的东西好像是弯曲的，最精巧的东西好像是笨拙的，真正辩才高的人出语谨慎。运动可以克服寒冷，静可以战胜热，（治天下的人）保持内心清静才能将天下领上正道。</t>
+  </si>
+  <si>
+    <t>我们先来看一下原文，有几个词我们要注意先区分一下。比如说大辩若讷，这个讷呢，我们知道一个词叫做木讷，也就是说，说话不是那么样的流利，不是那么样的辩才无碍。但实际上在这章里，它所要表达的是谨慎，说话严谨、谨慎。为什么要给大家说“讷”这个字呢？大家知道，毛泽东两个女儿，一个叫李敏，一个叫李讷。可是包括中央电视台的广播员都把这个念成nà，其实这个讷，只有一个读音，应该读作nè（讷）。毛泽东两个女儿的名字出自《论语》，“讷于言而敏于行”。先把这个事情给大家说一下，然后我们从头一句一句来解释。“大成若缺，其用不弊。”这个是在讲，完满的东西都仿佛有缺陷。我们平常讲一句话叫完美诚不易。其实这个世界上没有真正完美的东西，任何事物都是有缺点的。了解到这一点，引申到道家的思想，那么这句话想要表达的真正的含义就是，一个越是有大成就的人，他越了解自己的缺点，越觉得自己有缺点，有缺憾。所以，他就不断学习，不断努力，这样的一种动力，它发挥的作用，那么是无穷无尽的。认识到自己有缺点，这样他才能够很好地避免自己的弊端，很好地使自己的缺点得以改正和进步。这个道理在《道德经》里边多处谈到，比如说第七十一章就在讲，“知不知，上；不知知，病”。你知道自己不知道，这个才是水平高的。你不知道自己不知道，这就出问题了，出弊端了。所以大成若缺，其用不弊。一个越是有大成就的人，越懂得应该不断学习，不断进步，不断努力，不断充电。反而是一些有一点小小成就的人，喜欢到处吹嘘，不把旁边人吹得感觉到活不下去，他都不松口。其实遇到这种人，我们根本不用去揭穿他，淡然一笑就可以了。一个越是喜欢自我吹嘘的人，其实越不会有什么大的成就。反之，大成若缺，其用不弊。其实这个道理不止局限于此，我们还可以把这个道理向更深处延展一下。比如说中国人从月圆月缺，领悟出一个道理，其实任何事物发展到到它的极点的时候，它就会向相反的方面转化。人生的最美的境界，花未全开月未圆。花全开了，就往凋零的方向走了，月圆了就往缺的方向走了。所以在临近全圆和全开那时候，才是最美的境界。其实大家注意，我们在生活中经常喜欢用一个词，来对人表示一种赞赏，叫如日中天。其实这个不是一个好的事情。你说人如日中天，不是马上就说他要走下坡路了吗？用道家的这种思想我们来理解。明白在我们生活中讲的很多事情，和这个道理的吻合。大成若缺，其用不弊。“大盈若冲，其用不穷。”“盈”就是满，“大盈”就是大满。“大盈若冲”，“冲”就是冲虚。我们经常讲，用这个冲虚来代表着谦逊谦虚，就像大家看《笑傲江湖》里边的武当的掌门，冲虚道长，大盈若冲。一个越是智慧高的人，智慧聪明的人，他越谦虚，越谦逊。在前面我们曾经说过，“满招损，谦受益”，这话出自《尚书》——中国第一部历史总集。在《尚书》里边有一篇讲到了君臣之间探讨治国的谋略，大禹手下的第二号人物叫伯益。就给他的领导讲了这样的一句话，“满招损，谦受益”，并且伯益还制作了一件警戒器，叫欹器。这个东西非常奥妙，水装满了就颠倒了，倾覆了。装得不满的时候，它稳稳当当。提醒告诫我们这个道理，“满招损，谦受益。”孔子的后半生这个警戒器也一直放在身旁，这么大的一个学问家，还经常提醒自己，“满招损，谦受益”的道理，何况我们。所以“大盈若冲”！一个越是知识充盈的人，知识多的人，越表现得外在的谦逊谦虚，感觉到自己的不足，不断学习，不断努力。“其用不穷”，这样他的知识才能够更好地发挥作用，它的作用无穷无尽，不会出现上边所说的那些弊端，其用不穷。这都是相反相成的道理，按照这个道理我们再解释下边的内容，就比较容易了。“大直若屈，大巧若拙。”一个越是正直的人，越是有正直的、高尚的境界的人，反而外在表现得都比较随和，对很多的事情不那么喜欢争锋，对很多的事情都能够宽容。若屈并不是真的屈枉，他只是懂得外圆而内方，用这种方式和外面的人相处、相衔接，“大直若屈”。关于“大巧若拙，”这个我们得多说几句，在第二十五章里我们讲过，“大曰逝，逝曰远，远曰反”，这是一个逐步发展的过程。就像中国的艺术品一样，一开始没有技巧，后来学到了很多技巧。真正达到一个更高的境界的时候，反而把这些技巧忘掉了，返璞归真。中国雕塑的最高的境界是什么呢？有机会大家到汉武帝的陵墓——茂陵看一看，就会有所体会。那儿被认为是中国雕塑的顶峰。可是大家进去一看却发现非常奇怪，汉代的雕塑几乎一件精巧的东西都没有，都是那样的笨拙、朴拙。特别是霍去病墓前的《马踏匈奴》，那简直笨拙到了极点。团块、圆雕。可是那是中国象征雕塑的顶峰，正因为它这个拙，反而体现出大气势、大气象、大境界，“大巧若拙。”中国诗歌的最高境界是什么呢？清水出芙蓉，天然去雕饰，自然而然，返璞归真。中国书法的最高境界是什么呢？大的书法家最后写得越来越笨拙，越来越稚拙，反而开拓出一片新的气象。我读过一本书法书，是凌云超先生的《中国五千年书法史》。凌云超先生讲到这样一件事，他说中国的书法到后来写得越来越精巧，越来越美，但是像小家碧玉。而中国早期的书法，比如说石鼓文、金文，如旷野风月，给人一种大开大合的气象，这当然是我们在欣赏过程中感觉到的。越是这种稚拙、朴拙、笨拙，反而给人带来更强烈的一种审美的气势和感觉，崇高的一种味道。所以“大巧若拙”。其实《道德经》里边主要讲的并不只是这些，主要说的是人格。一个人格发展到一种高点的时候，他就达到了一种自然而然，返璞归真，忘记了那些小的技巧，心眼、套路，回归到一种真正的高尚的人格的境界。“大巧若拙”，返璞归真，自然而然，明月清风。这是我们说“大巧若拙”。“大辩若讷”。“讷”字我们前面解释过了，这个意思也就非常清楚。真正辩才高的人，他出语反而非常谨慎，让人感觉到仿佛他语言不是那么样的流畅，辩才无碍。其实他不只是为了用语言和人争锋，用语言和人争辩，出语谨慎，这也是我们讲的道家思想里边的一个重要的方面，这样的人才是真正有大的这种辩才的人，“大辩若讷”。下边这几句话原文上就有争论了。我们按照原文先解释一下。“躁胜寒，静胜热”。这个“躁”，表面上意思是急躁，燥热，实际上在讲的是运动。运动可以战胜寒冷。“静胜热”是说冷静可以战胜昏热。因为比如说我们夏天的时候用冰镇，这个方式可以解暑，战胜暑热，但这个地方要讲的实际上是内心的这样的一种冷静，可以战胜我们头脑发热，“静胜热”。但有的人也认为，其实这句话应该是静胜躁，寒胜热。这样和原文连接起来就更顺了，我倒是同意这样的一种说法。因为比如说我们夏天的时候用冰镇，这个方式可以解暑，战胜暑热，所比喻的也是冷静下来时才能战胜头脑发热，而且句式更为对称。现在很多本子也这样做了这样的一种改动。我觉得这个说法更为成立。总之都是讲，内心冷静、宁静、安静，它可以战胜我们的急躁。如果我们能够保持内心的宁静、安静、冷静，这样就可以战胜我们的浮躁、急躁、暴躁、狂躁，宁静以致远，这个和原文意思比较吻合。寒胜热，也是这样一个意思的表现，就像我们刚才说的，一个人冷静下来，可以战胜头脑发热，万物静观犹自得，我们冷静下来才能看清事物的本来面貌，冷静下来才能找到解决问题的正确方法。所以这六个字，大家不妨把它理解为静胜躁，寒胜热。这样后边这句话就自然而然地引申出来了，“清静为天下正”。我们保持内心的清静，一个王者、统治者、领导者保持内心的清静，这样才能够引导天下走上正道。“我好静而民自正”，“清静为天下正”，让内心的清静、冷静、宁静，又具备这样的一种修养。这才能够引导天下走向正道。这个是天下最正的一种领导的方式方法，也是我们修养的由内圣而外王的一种正确的修养的方式方法。</t>
+  </si>
+  <si>
+    <t>第四十六章</t>
+  </si>
+  <si>
+    <t>天下有道，却走马以粪；天下无道，戎马生于郊。祸莫大于不知足，咎莫大于欲得。故知足之足，常足矣。</t>
+  </si>
+  <si>
+    <t>天下有道，善跑的马退还给农夫用来耕田；天下无道，所有的马用来征战甚至母马都要在疆场生小马。祸患没有大于不知足的了，罪过没有大于什么都想占有的了。所以知足的满足，才是长久的满足。</t>
+  </si>
+  <si>
+    <t>“天下有道，却走马以粪；天下无道，戎马生于郊，祸莫大于不知足，咎莫大于欲得，故知足之足，常足矣。”这段话也是《道德经》里边非常精彩的一章。因为它体现了我们中国人对待战争的态度，对待和平的热爱。前面我们讲的第三十章的内容，不知道大家是否还有印象，“师之所处，荆棘生焉。”军队打过仗的地方，一片衰草枯杨，断壁残垣，“大军之后，必有凶年。”打过仗以后，灾荒瘟疫都来了。第三十一章，老子讲得更为沉痛，说中国人把战争当作丧礼一样来对待，“以悲哀泣之，以丧礼处之，胜而不美，胜而美者是乐于杀人。”我以前讲过，通过“四大名著”让国外了解我们的文化，效果恐怕不尽如人意，应该让他们看什么呢？让他们看《道德经》，这部能真正代表中国人思想理念、境界和智慧的经典，像我们讲过的三十章、三十一章和现在要讲的第四十六章，就是如此。“天下有道”，普天下清明有道，这个“天下”包括各个诸侯国了。“天下有道，却走马以粪”，“却”就是推却，“走马”就是跑马，也就是好马。这好马不用来打仗，离开战场，推却战争，干吗呢？回来耕田。当然，古人耕田是要上肥的，撒上粪肥，马耕着田，把地耕好，也就是我们经常讲的，卸甲归田，“卸马归田”，把马从战场上拉回来，干它的本务工作。“天下无道，戎马生于郊”，普天下无道的时候，混乱不堪不清明的时候，是什么情况呢？战马把小马驹生到了战场之上，“郊”就是郊野，此处指疆场，战马把小马驹生到了疆场之上。打仗公马不够用了，母马也上去了，最后出现这种情况——“戎马生于郊”，说得非常形象。我要重点强调一下，这四句是以马喻道，马之却为有道，戎马生于郊为无道，也就是以马的“却”与“生”，比拟天下之有道与无道：以“粪马”与“戎马”，象征国家之治与不治。比喻巧妙，寓意深远。纵观《道德经》的治国之道，当以无为自然以养民，以无欲之事而安民。好像马匹一样，虽是有用之物，用之于疆场可以卫国，用之于战阵可以御敌，用之于农事可以耕田。道行天下之时，国泰民安，上下祥和，无兵甲之患，天下太平安然，百姓安居乐业，故用走马耕田种地，积粪肥田。所以说：“天下有道，却走马以粪。天下无道，戎马生于郊。”太精辟了。“祸莫大于不知足，咎莫大于欲得。”这个大家清楚，老子生活在春秋，春秋无义战——没有什么正义的战争。大家都为了争夺财富、城池、人口，相互混战，战火频仍，烽火四起。面对这种情况，老子在当时总结出这两句话：“祸莫大于不知足，咎莫大于欲得。”惹祸最大的原因在哪呢？在于内心的贪念，贪心不足，得到了还想更多，只会做加法，不会做减法。“人心不足蛇吞象”，其实这句话，不单只对当时的现实概括，对我们现在也有这种启发的意义。生活中这种情况也比比皆是：有了还想更有，多了还想更多，衣架里边永远缺一件衣服，房子永远少一间，总是处在不知足的这种状态。“祸莫大于不知足，咎莫大于欲得”，“咎”罪过，过错，动辄得咎，过往不咎。这个“欲得”，就是别人的东西，自己也想要，把别人东西尽量弄到自己手上——这就成了一种罪过了。前面讲“不知足”是一种“祸”，祸患，而“欲得”就是一种罪过了，甚至可以是一种罪恶。别人的城，想要；别人的人民，想要，什么都想占有，用占有的态度对待这个世界，天下是我的。他说古代封建时代皇帝是什么样子呢？“离散天下人之儿女，屠毒天下人之肝脑，以博我一人之产业。”是说皇帝他觉得天下都是自己的，什么东西想拿就拿，想要就要，想占有就占有。这不就是“欲得”吗，这不就是一种大的过错、罪过吗？“咎莫大于欲得。”这个事情该怎么样来处理呢？该我们得的，我们应该得，不该我们的，“虽一毫而莫取也”。这段话大家也知道，东坡先生的《前赤壁赋》，“物各有主，苟非吾之所有，虽一毫而莫取。”划清边界，该得的得，不该得的不要老去强占，不要老是欲得。我们有了边界、底线、标准，那么就知道知足，知足的满足才是长久的满足。知足者富，所以如果永远处在不知足的状态，人也就永远不会有心灵的安宁。我们把这段话和第四十四章联系起来理解就更加明确了。第四十四章最后的三句话讲，“知足不辱，知止不殆，可以长久。”这一章说，“祸莫大于不知足，咎莫大于欲得。故知足之足，常足矣。”</t>
+  </si>
+  <si>
+    <t>第四十七章</t>
+  </si>
+  <si>
+    <t>不出户，知天下；不窥牖，见天道。其出弥远，其知弥少。是以圣人不行而知，不见而名，不为而成。</t>
+  </si>
+  <si>
+    <t>不用出家门，便能知天下之事；不用通过窗户去看，就能知道自然的规律法则。越是向外寻找求索，对道的认识就越少。所以圣人不用出行却能知事理，不观察却能明白道理，无为却能成功。</t>
+  </si>
+  <si>
+    <t>由于这两章的内容非常相吻合、相近，所以我们合到一起作为一章来讲解。四十七章讲的是一个什么事儿呢？是说人的感性认识，从哲学上说就是我们的感官接触客观世界，有时候接触得多了，它反而会造成一种迷乱和混乱，要通过人的智慧、理性认识，这样我们才能了解事物的规律，也就是这一章里边所说的“天道”。在这个基础上，我们一句句来解释。“不出户，知天下。”“户”就是门户，也就是大门。我不用走出家门，不用去外边到处跑，也能了解天下的大事。为什么？因为道家认为，天下大道归根到底，融于人的内心。内心里边有道，也就了解了天下的正道，了解了天下的大事。“不窥牖，见天道。”“窥”，从小孔里看；“牖”，就是窗户。我不用通过窗户去看，也知道天地之间日月星辰运行的规律。所以你看这个地方，“出户”是行走，出行，行万里路；“窥牖”是眼睛看，用感官接触客观世界，我不用这样。所以这个地方大家就感觉到，直观的一开始看，就觉得老子这个人有点轻视感性认识，人得通过实践嘛，人得通过感官接触客观世界，才能产生对客观世界的认识。是不是老子把这些东西全部都否认了呢？不是的。因为大家从书里已经看得非常的清楚，《道德经》举了很多生活中的例子，比如说“治大国若烹小鲜”，比如说“凿户牖以为室”，比如“说三十辐共一毂”，前面讲过的，这不都是生活中的例证吗？他对这个东西也很熟悉，怎么知道的呢？通过接触、了解。为什么在这一章里一开始他就讲这个事呢？要落到下面这八个字上。“其出弥远，其知弥少。”“弥”就是越来越，有的人走的地方越多，见得越多，不懂得甄别，不懂得筛选，不懂得提炼概括，“乱花渐欲迷人眼”，出得越远，反而了解到的真知越少，进步越少，为什么？不懂得反观自省，不懂得人心像一面镜子，如果你这个镜子是被灰尘蒙蔽的，你见得越多，其实反而获得的真知越少。这八个字在强调什么？我们要反观自省，要自我修行，自我修养，从哲学上说，从那些感性认识要上升到一种理性认识，达到对事物本质和规律的认识。所以你看，天下、天道代表着对事物全面的、本质的、规律性的认识，这个规律性的认识，需要我们安静地学习，在家里边读古往今来的著作，这不也是“不出户”嘛，也是“不窥牖”！我们了解这些间接的经验，从前人那里得到根本性的、全面的、通过理论阐释的这些知识，我们才能更了解事物的本质，更了解事物的规律。所以不要只把希望寄托在我们出去跑一跑，看一看，以为这样我们的知识就会越来越深刻，很多事情其实要通过理性的思维，这样我们才能进入到对事物本质和规律的认识，“其出弥远，其知弥少”。如果从中国的文化的角度来进一步理解的话，它还探讨一个什么问题、强调一个什么问题呢？就是人的品德。“大道之行，以心之知。”就是我们的心，我们的自我的内在的精神世界，这是道的重要的方面。所以很多人认为知识就是智慧，知识就是品德。不是的，很多人知识很多，不一定有智慧，知识多也不一定有境界、有品德。所以《道德经》强调的根本的“知”，从前面的比较中，相对于我们的感官而言，是人的理性的思维，理性认识、智慧，相对于外面的世界而言，它又是人的道德品德、人的品德。明朝的时候，关学的代表人物冯从吾先生讲过的一句话，我觉得冯从吾先生的这句话就非常能够解释这个道理，冯先生认为，古往今来的大学问都不出乎三句话：“做个好人，存点好心，行些好事。”做个好人，心正，身安，魂梦稳；行些好事，天知，地鉴，鬼神钦。所以一个人内心的品德、境界，通过自我的反省，自我的修养，达到了一个更高的水平，返璞归真，“归根曰静”，这些也是通过内在的自我修养来达到的。所以《道德经》认为人的理性认识，人这样的内心、这样的根本，它可以通过“不出户”、“不窥牖”，也可以自我修养，自我认知，不断地进步以达到。“是以圣人不行而知，不见而明，不为而成。”“是以圣人不行而知”，“是以”，“是”就是这样，“以”就是用，“是”可以解释为所以。“圣人”，好的统治者、领导者，在《道德经》称其为圣人。这些圣人，好的领导者、统治者要经常反躬自省，要经常内心关照，提高自己对大道和规律的认知水平。“不行而知”，不用到处跑，这一点也是可以得到的。“不见而明”，不用亲自去看，也能够明了道理，明了了这个道理，那就内心清净、无欲。“不为而成”，“不为”就是无为，就是按照大道的方式自然而然地去做，而不去妄为，这样一切都会顺理成章。这是我们第四十七章里边讲的内容，字虽然不多，但道理需要我们认真体会，“不出户，知天下；不窥牖，见天道。其出弥远，其知弥少。是以圣人不行而知，不见而明，不为而成。”当然对这一章的更进一步的理解需要我们和第四十八章，也就是我后面要讲的这一章相互参照，我们对这个理解才会更深刻、更准确。一开始就给大家说第四十七章、第四十八章我们要合起来，相互参照，为什么？这两章的内容讲的是非常吻合的，事实上也应该是一章的内容。第四十七章里边讲，“其出弥远，其知弥少”，第四十八章一开头就讲：“为学日益，为道日损。损之又损，以至于无为，无为而无不为。”这八个字一下子和上边的内容就衔接起来，为什么跑得越远反而知道的越少，这是站在道的角度来讲的。“为学”，在学知识，学到的知识内容越来越多。当然从学知识的角度来讲，这是非常有益的，不断地增多，可是我们获得很多的东西，见到了很多的东西，其实对我们了解根本性的规律和本质，了解大道并没有好处。站在一个更高的层次理解，就是说我们“为学”，讲究的是越多越好，见得多，看得多，见多识广。但是“为道”讲究的是什么呢？讲究的是内心的修行，讲究的是减少，用我们前面讲的话来讲，为学做的是加法，为道做的是减法，减少我们内心的欲念，减少我们的贪念，减少我们对很多问题的一种受了外界的影响而导致的内心的纷扰、困惑、迷乱，把这些东西损之又损，一点一点地把它减少，就像那镜子的灰尘一点点擦掉一样，“损之又损，以至于无为。”“无为”就是自然而为，把欲望减少，减少再减少，就达到了一种“无为”的境界，没那么多的贪念，没那么多的纷扰。我们用镜子来照这个天下，来照事物，万物进入到镜子里边，呈现出它本来的面貌。我们了解了事物的本质规律，了解了大道按照它来做，“无为而无不为”达到的是“无不为”的效果。所以在这儿借着这个机会，我再说一下道家自然无为的具体的含义：第一，不妄为；第十六章里边就讲，“不知常，妄作，凶。”你不了解事物的规律、规则，瞎折腾、胡折腾，那结果是非常糟糕的。我们“损之又损”，减少了这些遮挡着我们的认识，遮挡了我们的心窍的这些外在的事物、灰尘、迷乱，我们就照见了事物的本质和规律，我们就“不妄为”。第二，不多为；抓住关键，举重若轻，静观，看到事物的本质，找到解决问题的正确的方法，抓住关键，举重若轻。第三，有所不为；人要想有所为，必须有所不为，要想有所得，必须有所舍。我们舍弃了那些阻碍了我们正确行动、阻碍我们沿着大道行走的那些纷纷扰扰，这样能达到一个无不为的效果，也就是覆盖面广，效果更好，“无为而无不为”。下面这一段就讲，按照“无为”的方式来理解天下万事万物。“取天下常以无事，及其有事，不足以取天下。”“取天下”的规则是什么呢？“无事”。“无事”就是不多事，不干涉，不扰民，这样一切就自然而然顺理成章。所以第五十七章里边讲的这个事情就比较明确，“我无事而民自富，我无为而民自化”。“及其有事”，如果老是多事，老是妄为，不懂得事物的规律、规则，瞎折腾、胡折腾，这就是“及其有事”。则“不足以取天下”，那就不能够获得天下。得到的天下也得失去，因为它违背了大道。</t>
+  </si>
+  <si>
+    <t>第四十八章</t>
+  </si>
+  <si>
+    <t>为学日益，为道日损。损之又损，以至于无为，无为而无不为。取天下常以无事，及其有事，不足以取天下。</t>
+  </si>
+  <si>
+    <t>为学是一天一天地增加知识，为道是一天一天地减少私欲。减少又减少，以致达到无为的境界。“无为”就能达到“无不为”的效果。取得天下要常常不多事不扰民，如果妄为滋扰，就不配取得天下。</t>
+  </si>
+  <si>
+    <t>由于四十七、四十八这两章的内容非常相吻合、相近，所以我们合到一起作为一章来讲解。四十七章讲的是一个什么事儿呢？是说人的感性认识，从哲学上说就是我们的感官接触客观世界，有时候接触得多了，它反而会造成一种迷乱和混乱，要通过人的智慧、理性认识，这样我们才能了解事物的规律，也就是这一章里边所说的“天道”。在这个基础上，我们一句句来解释。“不出户，知天下。”“户”就是门户，也就是大门。我不用走出家门，不用去外边到处跑，也能了解天下的大事。为什么？因为道家认为，天下大道归根到底，融于人的内心。内心里边有道，也就了解了天下的正道，了解了天下的大事。“不窥牖，见天道。”“窥”，从小孔里看；“牖”，就是窗户。我不用通过窗户去看，也知道天地之间日月星辰运行的规律。所以你看这个地方，“出户”是行走，出行，行万里路；“窥牖”是眼睛看，用感官接触客观世界，我不用这样。所以这个地方大家就感觉到，直观的一开始看，就觉得老子这个人有点轻视感性认识，人得通过实践嘛，人得通过感官接触客观世界，才能产生对客观世界的认识。是不是老子把这些东西全部都否认了呢？不是的。因为大家从书里已经看得非常的清楚，《道德经》举了很多生活中的例子，比如说“治大国若烹小鲜”，比如说“凿户牖以为室”，比如“说三十辐共一毂”，前面讲过的，这不都是生活中的例证吗？他对这个东西也很熟悉，怎么知道的呢？通过接触、了解。为什么在这一章里一开始他就讲这个事呢？要落到下面这八个字上。“其出弥远，其知弥少。”“弥”就是越来越，有的人走的地方越多，见得越多，不懂得甄别，不懂得筛选，不懂得提炼概括，“乱花渐欲迷人眼”，出得越远，反而了解到的真知越少，进步越少，为什么？不懂得反观自省，不懂得人心像一面镜子，如果你这个镜子是被灰尘蒙蔽的，你见得越多，其实反而获得的真知越少。这八个字在强调什么？我们要反观自省，要自我修行，自我修养，从哲学上说，从那些感性认识要上升到一种理性认识，达到对事物本质和规律的认识。所以你看，天下、天道代表着对事物全面的、本质的、规律性的认识，这个规律性的认识，需要我们安静地学习，在家里边读古往今来的著作，这不也是“不出户”嘛，也是“不窥牖”！我们了解这些间接的经验，从前人那里得到根本性的、全面的、通过理论阐释的这些知识，我们才能更了解事物的本质，更了解事物的规律。所以不要只把希望寄托在我们出去跑一跑，看一看，以为这样我们的知识就会越来越深刻，很多事情其实要通过理性的思维，这样我们才能进入到对事物本质和规律的认识，“其出弥远，其知弥少”。如果从中国的文化的角度来进一步理解的话，它还探讨一个什么问题、强调一个什么问题呢？就是人的品德。“大道之行，以心之知。”就是我们的心，我们的自我的内在的精神世界，这是道的重要的方面。所以很多人认为知识就是智慧，知识就是品德。不是的，很多人知识很多，不一定有智慧，知识多也不一定有境界、有品德。所以《道德经》强调的根本的“知”，从前面的比较中，相对于我们的感官而言，是人的理性的思维，理性认识、智慧，相对于外面的世界而言，它又是人的道德品德、人的品德。明朝的时候，关学的代表人物冯从吾先生讲过的一句话，我觉得冯从吾先生的这句话就非常能够解释这个道理，冯先生认为，古往今来的大学问都不出乎三句话：“做个好人，存点好心，行些好事。”做个好人，心正，身安，魂梦稳；行些好事，天知，地鉴，鬼神钦。所以一个人内心的品德、境界，通过自我的反省，自我的修养，达到了一个更高的水平，返璞归真，“归根曰静”，这些也是通过内在的自我修养来达到的。所以《道德经》认为人的理性认识，人这样的内心、这样的根本，它可以通过“不出户”、“不窥牖”，也可以自我修养，自我认知，不断地进步以达到。“是以圣人不行而知，不见而明，不为而成。”“是以圣人不行而知”，“是以”，“是”就是这样，“以”就是用，“是”可以解释为所以。“圣人”，好的统治者、领导者，在《道德经》称其为圣人。这些圣人，好的领导者、统治者要经常反躬自省，要经常内心关照，提高自己对大道和规律的认知水平。“不行而知”，不用到处跑，这一点也是可以得到的。“不见而明”，不用亲自去看，也能够明了道理，明了了这个道理，那就内心清净、无欲。“不为而成”，“不为”就是无为，就是按照大道的方式自然而然地去做，而不去妄为，这样一切都会顺理成章。这是我们第四十七章里边讲的内容，字虽然不多，但道理需要我们认真体会，“不出户，知天下；不窥牖，见天道。其出弥远，其知弥少。是以圣人不行而知，不见而明，不为而成。”当然对这一章的更进一步的理解需要我们和第四十八章，也就是我后面要讲的这一章相互参照，我们对这个理解才会更深刻、更准确。一开始就给大家说第四十七章、第四十八章我们要合起来，相互参照，为什么？这两章的内容讲的是非常吻合的，事实上也应该是一章的内容。第四十七章里边讲，“其出弥远，其知弥少”，第四十八章一开头就讲：“为学日益，为道日损。损之又损，以至于无为，无为而无不为。”这八个字一下子和上边的内容就衔接起来，为什么跑得越远反而知道的越少，这是站在道的角度来讲的。“为学”，在学知识，学到的知识内容越来越多。当然从学知识的角度来讲，这是非常有益的，不断地增多，可是我们获得很多的东西，见到了很多的东西，其实对我们了解根本性的规律和本质，了解大道并没有好处。站在一个更高的层次理解，就是说我们“为学”，讲究的是越多越好，见得多，看得多，见多识广。但是“为道”讲究的是什么呢？讲究的是内心的修行，讲究的是减少，用我们前面讲的话来讲，为学做的是加法，为道做的是减法，减少我们内心的欲念，减少我们的贪念，减少我们对很多问题的一种受了外界的影响而导致的内心的纷扰、困惑、迷乱，把这些东西损之又损，一点一点地把它减少，就像那镜子的灰尘一点点擦掉一样，“损之又损，以至于无为。”“无为”就是自然而为，把欲望减少，减少再减少，就达到了一种“无为”的境界，没那么多的贪念，没那么多的纷扰。我们用镜子来照这个天下，来照事物，万物进入到镜子里边，呈现出它本来的面貌。我们了解了事物的本质规律，了解了大道按照它来做，“无为而无不为”达到的是“无不为”的效果。所以在这儿借着这个机会，我再说一下道家自然无为的具体的含义：第一，不妄为；第十六章里边就讲，“不知常，妄作，凶。”你不了解事物的规律、规则，瞎折腾、胡折腾，那结果是非常糟糕的。我们“损之又损”，减少了这些遮挡着我们的认识，遮挡了我们的心窍的这些外在的事物、灰尘、迷乱，我们就照见了事物的本质和规律，我们就“不妄为”。第二，不多为；抓住关键，举重若轻，静观，看到事物的本质，找到解决问题的正确的方法，抓住关键，举重若轻。第三，有所不为；人要想有所为，必须有所不为，要想有所得，必须有所舍。我们舍弃了那些阻碍了我们正确行动、阻碍我们沿着大道行走的那些纷纷扰扰，这样能达到一个无不为的效果，也就是覆盖面广，效果更好，“无为而无不为”。下面这一段就讲，按照“无为”的方式来理解天下万事万物。“取天下常以无事，及其有事，不足以取天下。”“取天下”的规则是什么呢？“无事”。“无事”就是不多事，不干涉，不扰民，这样一切就自然而然顺理成章。所以第五十七章里边讲的这个事情就比较明确，“我无事而民自富，我无为而民自化”。“及其有事”，如果老是多事，老是妄为，不懂得事物的规律、规则，瞎折腾、胡折腾，这就是“及其有事”。则“不足以取天下”，那就不能够获得天下。得到的天下也得失去，因为它违背了大道。</t>
+  </si>
+  <si>
+    <t>第四十九章</t>
+  </si>
+  <si>
+    <t>圣人无常心，以百姓心为心。善者，吾善之；不善者，吾亦善之，德善。信者，吾信之；不信者，吾亦信之，德信。圣人在天下歙歙，为天下浑其心。百姓皆注其耳目，圣人皆孩之。</t>
+  </si>
+  <si>
+    <t>圣人没有成心，以百姓之心为心。善良的百姓我善待他们，不善良的百姓我也善待他们，这样使人向善；讲诚信的人我以诚信对待他们，不讲诚信的人我也以诚信对待他们，这样使人诚信。圣人领导天下，收敛自己的私欲，使天下百姓的心灵都变得淳朴。百姓都只关注耳听眼见的事，圣人将百姓像孩童一样对待。</t>
+  </si>
+  <si>
+    <t>第四十九章是《道德经》里边比较重要的一章，因为这里边有一句话大家都很熟悉，我们领导者讲话的时候也经常引用，就是以“百姓心为心”。从前面讲的内容，大家会知道这是一个通过换位思考，得出来这样的一种结论。这一章开头这句话我们先说一下。“圣人无常心，以百姓心为心。”是说一个好的领导者、统治者，不要老固执己见。“常心”就是固定的心思，自我的执着，不要老固执己见，不要老把自己的意志强加给别人，乃至强加给人民。应该怎么样呢？换位思考，将心比心，“以百姓心为心”，倾听民众的呼声，关注民众的利益，吸取民众的智慧，这都是“以百姓心为心”的表现。我们先体会一下这一章的宗旨在讲什么？其实这个道理就是讲了，换位思考，将心比心。百姓善良，我也对他善良；不善良，我也对他善良；信任我的，我信任他；不信任我的，我也信任他。干吗呢？这样我就能让人向善，让大家讲诚信。最后这一段就说一个好的领导者、统治者，让百姓都回归到他本来的这种生活，关注的是自己的生活中的事情。不要想那么多，不要心思混乱，不要烦乱，这样才能够形成一种良好的和谐的状态。这是老子的想法。我们一句一句来解释。“圣人无常心”，我再重申一遍，“圣”的繁体字，上面是个耳和口——聖，这两个字并列就代表着通达事理，下面是个王，也就是说一个好的领导者、领导人称其为“圣”。在这一章里体现得最为明显。“圣人无常心”，有的本子也叫“常无心”，意思都是一样的，就是不固执己见，没有自己僵化固定的思维，懂得换位思考。其实关于这个意思，我们通过前面讲过的第二十二章参照着理解，就比较容易了。我在前面多次说过，读《道德经》最好的方法就是不看注解，以经解经，相互参照，明白它要讲的真正的含义，谁的解读也不如他本人对这个东西的解释更符合他的本意。第二十二章里边就讲“不自是”“不自见”“不自矜”“不自伐”这“四不”。“不自是，故彰。不自伐，故有功。不自矜，故长。”这样我们才能不断成长，不断进步。一个好的领导人也是这样的，领导者、统治者，也应该“四不”，也就是“无常心”。你没有这样的智慧，老是固执己见，老是自我吹嘘，老是自我夸耀，老是觉得自己了不起，那你就没办法换位思考，将心比心了。所以“无常心”才能以百姓之心为心，倾听民众的呼声，吸取民众的智慧，关注民众的利益。沿着这个思路下面也好理解了。“善者，吾善之；不善者，吾亦善之，德善。”善良的人我用善良去对待他，不善良的人，我也用善良的方式去对待他，干嘛呀？教化、感化，这样我就得到了真正的善良。为什么呢？你这样做，起代表带头作用，大家也就人心向善了。大家注意这个“德”，王弼的解释非常明确，“德者，得也”，这样做就得到了这个天下、这个社会，这个国家就会人心向善。“信者，吾信之；不信者，吾亦信之，德信。”信我的人，我相信他，我跟他讲诚信；不相信我的人，我也相信他，跟他讲诚信。干嘛呀？这样天下人就会觉得诚信可贵，也就往诚信的方向去努力去发展了——“德信”。“圣人在天下歙歙”，“歙”就是合，就是收敛。你说圣人怎么样领导、管理这个天下呢？先要收敛自己的欲望，要想领导好别人，你先领导好自己，要想领导好自己，你先领导好自己的情绪，领导好自己的欲念，上梁不正则下梁歪嘛。“歙歙”，收敛自己的欲望，减少自己的欲念。“为天下浑其心”，让这个天下都怎么样呢？大家都没那么精明。不总是为了什么事都去争，“浑其心”，都那么样地浑厚、淳朴、厚道，关心自己的现实生活，而不是那么多纷乱的思维，那么多胡乱的想法，那么多的技巧、智谋、套路、心眼，用这种方式让大家和谐相处。“圣人皆孩之”，一个好的领导者把天下人都当作儿童，当作自己的孩子，一方面对他们非常关爱，另一方面也不要让百姓人心混乱，都像孩童一样纯净、淳朴。当然了，后边这一段大家也看得出来，这也是老子的一厢情愿。他希望统治者减少自己的欲望，天下人跟着也减少自己的欲望，关注自己的现实的生活，没有那么多的争斗、心眼、套路、技巧、欺骗、欺诈。这是老子生活的理想状态，也是他认为是和谐世界的前景，我们权当这也是他的一种理念和希望，毕竟这个社会的和谐也是我们的一种希望。只是他这种方法大家要辩证对待，大概用这种方法实现天下的太平，也只能是一种理想和理念，很难真正得以实现。但这一章里边大家要注意，开头这句话，我们要熟记，因为在我们国家的领导人的很多讲话里边都能看到这句话的出现，“以百姓心为心”，这是道家思想里边非常重要的一句话，让我们感觉到老子这个人在他冷静的、甚至有点冷酷的外表之下，内心涌动的热流，对于天下人的关注，对于天下人的关爱。这一章的原文我们解释完了，再强调一下这章的逻辑和重点，这章里边的关键在哪呢？这一章里边的关键是讲“圣人”和“百姓”，他们是国家不同层面的人，这一章讲究什么呢？讲究各安其位，各循其理。老子对这些做统治者的讲，你们要“以百姓之心为心”，善良的人呢你要好好地对待，不善良的人呢你也要好好对待，这样你才能得到这个国家人心向善的风气。信你的人你要讲诚信，不信你的人你也要讲诚信，这样才能得到天下诚信的风气。“圣人在天下”，圣人在上，领导天下。应该怎么样呢？怎么样叫循理循道呢？应该清静，无为，少折腾，少多事儿，这是上边的理，给他们讲的，你应该这样做，收敛自己的欲望，减少自己的奢靡、奢华，“清静为天下正”，这是对他们。对下边怎么讲呢？你这个在上边的人应该让下边遵循一个什么样的道理呢？“为天下浑其心”，让这个百姓浑厚，淳朴，宁静，没有那么多纷乱的想法，那么多技巧、心眼、套路、欺诈、欺骗，按照这个方向，百姓都关注自己现实的生活，把自己的日子过好，少管别的事儿，你让百姓能够做到这一点，上边的管上边的事，循上边之理，下边的循下边之理，这天下不就和谐了嘛。大家看出来了吧，“圣人皆孩之”，好的领导，一个国家的领导者，让这国家的百姓都像小孩一样，纯净、淳朴，没有那么多的欺瞒欺诈。上按上边的道理，下按下边的道理，这不就形成了一个和谐的状态了嘛。我们知道，真正的和谐是有差别的统一，大家都应该有表达自己的意见的机会，表达自己观点的机会，“各美其美，美人之美”，有差别的统一。但是老子这个地方讲的道理不是这样的，他讲的是“圣人无常心”，你要考虑到百姓，百姓在圣人的领导下应该怎么做呢？应该浑厚淳朴，没有那么多的智谋、欺诈、心眼，关注自己的现实生活，干好自己的事情，像儿童一样，纯净、干净、宁静，形成这个社会的和谐状态。所以我们只能说，老子这个想法呀追求一种和谐的目标，但是这个所用的方法在我们看来，这还是有很多地方值得检讨的，因为真的把百姓都变成小孩，还是不免有一点愚民政策的感觉。这一点大家还是要正确地理解。</t>
+  </si>
+  <si>
+    <t>第五十章</t>
+  </si>
+  <si>
+    <t>出生入死。生之徒十有三，死之徒十有三。人之生，动之死地，亦十有三。夫何故？以其生生之厚。盖闻善摄生者，陆行不遇兕虎，入军不被甲兵。兕无所投其角，虎无所措其爪，兵无所容其刃。夫何故？以其无死地。</t>
+  </si>
+  <si>
+    <t>人生就是从出生到死亡的历程。长寿的人占十分之三，短命的人占十分之三，本可以长寿但妄为把自己置于死地的人也占十分之三。为什么？因为他们过分地追求奉养自己以求生。听说善于养生的人，在陆地上行走不会遇到兕、虎，在战场上不会被兵器所伤。兕的角无处可用，虎的爪也没了用处，兵器的刃也用不上。为什么？因为他不把自己置于死地。</t>
+  </si>
+  <si>
+    <t>我们来讲第五十章，这一章表面上在讲养生之道，也就是文章所说的“摄生”，实际上表达的是更为深刻的道理。我们看书、看电视剧的时候，会发现有那么一些大师、大医生，一些位重权高的人向他们请教养生之道，“我怎么样能活得更加长寿？”这些医生、养生大师啊，大都是告诉他们要清心寡欲，不要奢靡奢华，不要胡吃海塞，其实这就是道家对于养生这事儿往更高的一个层次所要修养的内容，我们也可以把它概括为道家的生死观。道家认为养生跟生死密切关联。养生要顺应自然，要自然而然，要掌握规律、规则。你看我们读《庄子·养生主》里边的“庖丁解牛”，讲的不就是这个道理吗？目无全牛，游刃有余！这牛解得跟跳舞一样，跟音乐一样。所以文惠君最后就对这个庖丁讲：“吾闻庖丁之言，得养生焉。”养生要顺应自然规律，自然而然，自然而为。“生之徒十有三，死之徒十有三。”然后老子做分析，如果把天下的人分做十成，那么有十分之三的人是“生之徒”，也就是长寿的，还有十分之三的人是“死之徒”，是短命的。还有十分之三的人是怎么样的呢？“人之生，动之死地，亦十有三。”这些人本来可以长寿，最后由于自己的胡为、妄为、折腾，就把自己置于死地了。所以你看它的分类很有趣，十成的人中，三分之一的人应该是长寿的，三分之一的人本身体质各方面就是短寿的，还有三分之一的人本来可以长寿，但是妄动、胡为而置于死地。为什么会这样？《道德经》给了我们这样一句话：“以其生生之厚。”生，养生，或者可以解释得更明确，叫“求生”。太着急了，太迫切了，老想延长自己的性命，老害怕自己的营养不够，最后营养过剩了，反而把自己置于一个另外的相反的方向。当下一些有智慧的医生就提醒，我们现在不是营养不良，而是营养过剩，“生生之厚”。当然《道德经》讲的这句话只针对当时的统治者、位高权重的人而言，老是生活得这样奢靡奢华，“五色令人目盲，五音令人耳聋，五味令人口爽，驰骋畋猎，令人心发狂……”老是这样，还以为是让自己生命不亏，活得不亏。求生之厚，太急、太迫切，营养过剩，自己本来可以长寿，反而被置于成“死之徒”了，到短寿的那一拨去了。所以下面老子就讲了：“盖闻善摄生者”，听说这善于养生的人是什么样子呢？他们用了下边一段形容：“陆行不遇兕虎，入军不被甲兵。兕无所投其角，虎无所措其爪，兵无所容其刃。”习惯上我们以为“兕”是犀牛，或者有的叫母犀牛，其实这两种动物还不一样。这个“兕”是古代的一种瑞兽，比较凶猛，所以在古代的文字中，经常用这个“兕虎熊”比喻凶险之地。懂得养生的人，懂得正确对待自己生命的人，不去冒这个险。陆行的时候，尽量不碰这些凶猛的动物，如果你碰上它了，那你就没办法了，谁让你冒那个险呢？明知道野生动物园人家不让下车，你非得下车，遇到老虎了吧。有些地方人家告诉这个规则，这里边有危险，你偏不听，明知山有虎，偏向虎山行，明知山有狼，偏要做狼餐，这不就是“人之生，动之死地”吗？“入军不被甲兵”，上阵打仗的时候不为兵器所伤。为什么呢？“兕无所投其角”，你不遇到这个兕，那当然它那个凶猛的角就没有办法发挥它的作用了，没有办法针对你。一般我们画“兕”的时候都习惯把它画成独角兽。“兕”最有名的代表就是太上老君骑的那个板角青牛了，角非常锋利，尖锐，杀伤力强，你不遇到它，尽量别碰到，别把自己置于危险的境地，它的角当然就无所用了。“虎无所措其爪”，你不往虎山行，不遇到它，提前准备好避免这种凶险，老虎爪子再尖利，牙齿再锋利，它也无法对你发挥作用。“兵无所容其刃”，上阵不为甲兵所伤，尖锐的兵器，也没有办法发挥它的作用。“夫何故？”为什么会这样？“以其无死地”，不把自己置于死地，这样也就不会让自己的生命受到戕害。这是就是五十章。这一章体现了道家的养生之道：简单地说就是不要“作死”，自己不要找死，本来可以长寿的，自己作死把自己置于死地。很多人非得触犯法律的界限，甚至因此送掉了自己的生命，这不就是把自己置于死地嘛！所以我们说“NoZuoNoDie”，不作不死。从养生的角度来讲，你看道家讲的顺应自然，不单只是生活中的清心寡欲，而且还指不触犯边界底线，不触犯红线，知足不辱，知止不殆，不置身于死地，不让自己冒这种凶险，这也是道家养生之道里边的一个重要的内容，而且是更接近于哲学层面的、更有智慧的内容。那么这一段我们讲完了之后，我还要跟大家强调一下，道家的养生观，其实也是道家的生命观。道家对于生命的看法讲究的是自然而然，意思是什么呢？过于求生，过于厌恶死，这都不是一种自然而然的智慧，因为死亡本身就是生命的一部分，人自然而生，自然而死，真的到了生命结束的时候，那也应该开朗地、乐观地对待。这一点在道家的继承者那里，也就是道家的第二号人物庄子那里，讲得非常的明确——“之所以善吾生者，乃所以善吾死”。我们很好地对待自己的生命，不把自己的生命主动地置于死地，不求生之厚，真的面临死亡的时候，也应该把它好好地对待。自然而生，自然而亡，这是生命的自然而然的规律，谁也阻挡不了。第五十章，老子借养生之道讲了一个更重要的道理：有的人求生太急迫，太厌恶死亡，太害怕死亡，越是求生之厚，服了大量的药，用各种各样的营养的方式，推开死亡，想要避免，没想到越想避免的反而来得越快。所以，道家讲究自然而然的思想，这有着重要、杰出的意义。我们做个小小的梳理。第五十章，我们从开始讲的时候就给大家讲过，这一章可以分成两段，一段是讲有的人本来可以长寿，却进入了短命的行列，是因为“求生之厚”，太急迫、营养过剩导致的，另外一个是由于妄为、“作”，把自己置于死地的。怎样才能避免这两点呢？还是道家的这种思想，顺其自然，清心寡欲，清静为天下正。正确地对待生命和死亡，不把死亡当作是完全可以避免的事情，真的面临死亡的时候，也能够开朗地、乐观地对待。</t>
+  </si>
+  <si>
+    <t>第五十一章</t>
+  </si>
+  <si>
+    <t>道生之，德畜之，物形之，势成之。是以万物莫不尊道而贵德。道之尊，德之贵，夫莫之命而常自然。故道生之，德畜之：长之、育之、亭之、毒之、养之、覆之。生而不有，为而不恃，长而不宰，是谓玄德。</t>
+  </si>
+  <si>
+    <t>道生成万物，德蓄养万物，万物有了具体的形状，周围的环境使万物得以成长。道受尊崇，德被珍贵，不妄加干涉而使万物顺应自然。所以道生成万物，德蓄养万物：使万物成长作育，使万物成长成熟，使万物得到养覆保护。生成万物而不占有，化作万物却不把这当成是凭借、倚仗，长养万物却不主宰，这就叫“玄德”。</t>
+  </si>
+  <si>
+    <t>第五十一章逐句地来解释一下。“道生之”，“生”，创造，生养。道创造了万事万物。“德畜之”，德畜养了万事万物。“物形之”，万事万物有了具体的形状。“势成之”，周围的环境使它得以成长。正因为如此，所以“万物莫不尊道而贵德”，以道为尊，以德为贵。“道之尊，德之贵，夫莫之命而常自然。”尊道贵德，那自然会得到一个良好的结局和结果，这不是命，这就是自然而然的规律、规则。“故道生之，德畜之。”所以道生养万物，德蓄养万事万物。“长之、育之”，使它成长，使它不断地培育长大。“亭之、毒之”，这个“亭”呢，其实也好理解，我们常说亭亭玉立，这个“亭”就是成长的意思。这个“毒”就是成熟的意思，使万事万物成长，使其成熟。“养之、覆之”，“养”和“覆”都是保护的意思。养育万物，保护万物。“生而不有，为而不恃，长而不宰。”生养了万事万物，却不把它当作私有的产品，对万事万物有作为，却不把这个当作一种倚仗、凭借，甚至勒索的手段，对万事万物有这么大的功德，却不是以主宰者的身份出现。这个就是“玄德”，这就是最高深的、最深刻的智慧与品德。这是我们对这一段的直观的解释。其实，这一段的深意远不止于此。因为中国人讲哲学讲究“知行合一”，讲道的品性，其实也是为了人向道的品性去学习，按照道去做，这个也就是“德”。所以第五十一章里边讲道养育万物，德蓄养万物，也是人应该效法学习的。在这个层面上，我们深入地理解这一段话。“道生之，德畜之”，道创造了万事万物，但是它不把万事万物作为一种私有产品，并不是以一种主宰者的身份，以求其回报。由此我们可以看到，老子给我们提供了想要做成一件事的四个核心的要素和条件，也就是一种应有的程序和原则。第一个，要有道，因为道是创造万事万物的本源，所以我们要坚守大道，按大道的方式来创造。第二个，“德畜之”，“畜”就是积累的意思。在有道的基础上，我们要不断地、坚定地按照道去做，也就是“积德”。德就像水一样，我们就像一条船一样，我们积累的水越多，我们这条船在水上才能够航行得更自由。所以朱熹有一首诗说：“昨夜江边春水生，艨艟巨舰一毛轻。向来枉费推移力，此日中流自在行。”昨天江边涨水了，平常推也推不动的大船，现在根本不用推了，水多了，自然而然地就航行更加自由。他讲的是读书的积累达到一种自由的境界，其实人生又何尝不是如此呢？我们积累的德多了，按照道做事，更坚定、坚持、持久，那也就给我们人生提供了更广阔的空间与平台，不断地积德，我们的行为也就更加自由，我们的行为也就更加能够符合大道。庄子在《逍遥游》里面也讲了这样一句话，“且夫水之积也不厚，则其负大舟也无力”。水积累不多的时候，大船是浮不起来的，只要积累得多了，结果就是自然而然的事情，和朱熹所讲的道理不谋而合。第三个，“物形之”。人有道有德，是不是就可以把事情做成了呢？不够的，还需要一定的物质条件和手段，巧妇也难为无米之炊。有条件要上，没有条件我们创造条件，这样才能把事情向更成功的方向去发展。道、德、物三个条件总够了吧？不够的。要想把事情真正做成，还有一个很重要的条件，就是“势”，“势成之”。道家讲的无为，更强调的是顺势而为，掌握这个形势，了解大势，这样才能把事情做成。《淮南子》中举过这样的一个例子，大禹为什么能把水治成呢？顺水势而为。商汤周武为什么能夺得天下呢？顺民心而为。民心所向，就是历史发展的大势与潮流。所以大家在第二个层面把这四个字提炼出来，它是一个很好的成功学的例证，我觉得比现在讲的一些所谓的零零散散的成功学，不知道要深刻多少倍。道、德、物、势，“道生之，德畜之，物形之，势成之”。既然这四个要素，道和德是排在最前面的，“是以万物莫不尊道贵德”，所以万事万物没有不尊道而贵德的。人更是如此，有道有德，后边的事情才能继续发展，所以“道之尊，德之贵，夫莫之命而常自然”，这不是命，这就是一个永恒的自然而然的规律、规则。你按照道，按照德，尊道而贵德，会得到一个自然而然的良好的结局和结果，这是自然而然的事情。这不是命，这就是自然而然的规律和规则。所以大家注意，我们中国的这些经典，比如说《易经》，比如说《道德经》，都不是用来算卦占卜的，它就讲一个重要的内容：按照规律、规则来做，结果水到渠成、自然而然。下面这一段是对上面做的一个延伸。“道生之，德畜之”，道和德，生养万物，为万物提供条件，让它生长发展。“长之、育之”，培育万事万物使其生长、发展。“亭之、毒之”，使它成长、成熟。“养之、覆之”，不仅如此，还要养护万物，覆盖万物。道和德让万物长大，培育万物的成长，使它成熟又予以保护，功德可谓无量。孔子有一段名言：子曰：“予欲无言。”子贡曰：“子如不言，则小子何述焉？”子曰：“天何言哉？四时行焉，百物生焉，天何言哉？”这段话的直译是：孔子说：“我现在只想沉默。”子贡说：“如果你不说出心里想什么，那么我们这些学生还拿什么去记述呢？”孔子说：“自然说过些什么？不过放纵四季周而复始，任由百物蓬勃生长。自然你又何曾告诉别人什么啊？”很多人把这段话中的“天”翻译成神灵，这是不对的。其实这个“天”指的是大自然，也就是《道德经》里的天地，天地无语而泽被苍生万物，确又无语不居功自傲，不把自己当做万物主宰。这不也是《道德经》第五十一章的核心吗？培育万物的成长，使它成熟又予以保护，功德可谓无量。其实，在这样的智慧层面，孔子和老子的见解都是一样，“生而不有，为而不恃，长而不宰，是谓玄德”。关于这段重要的话，我们在第十章已经详细说过，不再重复。</t>
+  </si>
+  <si>
+    <t>第五十二章</t>
+  </si>
+  <si>
+    <t>天下有始，以为天下母。既得其母，以知其子；既知其子，复守其母，没身不殆。塞其兑，闭其门，终身不勤。开其兑，济其事，终身不救。见小曰明，守柔曰强。用其光，复归其明，无遗身殃，是为习常。</t>
+  </si>
+  <si>
+    <t>天下万物都有本原（即道），作为万物的母亲。认识了作为万物之母的道，就能认知万物；认知了万物，就能坚守作为万物之母的道。这样终身都没有危险。塞上欲望的孔穴，闭上欲望的门户，终身都没有忧劳；打开感官欲望的门户，增添纷繁的事件，终身都不可挽救。察见细微的事物叫“明”，坚守柔弱叫“强”。用道的光芒来了解具体事物中的规律、规则，复归到事物的光明的状态，不会给自己留下那么多的祸殃，这就叫普遍永恒的规律。</t>
+  </si>
+  <si>
+    <t>一开始我们就说过，《道德经》里边有一个非常好的“正能量”，就是每当说到高大上的、特别伟大的事情，都喜欢用母亲的“母”字来作为代替和概括，或者说用“母”来做一个形象的比喻。如果我们的孩子读这样的文字，潜意识里就会有对母亲有一种敬畏与尊重。我们在第一章里边就说到，“无，名天地之始；有，名万物之母”。在这一章里边，又出现了母亲的这个“母”的概念。“天下有始，以为天下母。”就像动物、人类都是由母亲生养的一样，万事万物也都是由道创造的。老子用“母”来比喻大道，生动形象且让人充满对道的敬畏，意思就是说，天地一开始的时候，其实大道已经就在了。“既得其母，以知其子。”我们了解了大道，就是“既得其母”。知晓了大道，那我们就“以知其子”，也就了解了儿女。这个意思是什么呢？道是万事万物的普遍规律，它永恒存在，具体的事物都拥有具体的道，也就是具体的规律。你了解了大道，就可以以此来了解万事万物的具体规律。茶有茶道，花有花道，练武有武道，下棋有棋道……了解了普遍的道，也就更能够了解这些具体事物间的规律与规则。反过来也一样，“既知其子，复守其母。”我们从具体的事物之间，比如棋道、花道、茶道，从这具体的事物之间，我们了解了大道，感知了大道，那也就能更好地坚定地坚守大道。“没身不殆”，这样地做事情永远没有危险，没有失败，为什么？以道佑之，以道护之，这样我们做事情才能没有危险，没有失败。下面就说了解大道的方式方法。大道的了解，不是靠感性来体验到的，就像我们前边说的，“为学日增，为道日损。”“不出户，知天下；不窥牖，见天道。”所以如果是跟着感觉走的话，你是了解不了真正的大道的。因此“塞其兑，闭其门，终身不勤”，不要依赖感觉，不要把我们所见所知的就当作大道，重要的要用心，也就是哲学上讲的，用理性的思维，来了解认知大道。反过来讲，“开其兑，济其事，终身不救”，如果跟着感觉走，打开我们的感官的门户，感官这个东西，它是有很大的局限的。第十二章里面就讲，“五色令人目盲，五音令人耳聋，五味令人口爽”。你只靠这个是了解不了大道的。“见小曰明，守柔曰强。”什么叫“见小”啊？“小”就是具体的事物，具体的事物里面也蕴含着规律、规则。你能够从具体事物里了解具体的道、具体的规律，这也是一种明智。“守柔曰强”，道家是讲“柔弱胜刚强”的，道家是讲“知其雄，守其雌”的，“柔”就是雌柔，不管我们多么强大，我们也懂得坚守这个柔弱，因为柔弱更能长久。力量不够的时候，我们懂得用守柔的方式、韬晦的方式，来使自己的力量不断增大、不断增强，这样才能成为真正的强大。“用其光，复归其明”，用道的光芒，“复归其明”，来了解具体事物中的规律、规则，复归到事物光明的、明智的状态，我们才能走在光明的大道上。“无遗身殃”，不会给自己留下那么多的祸殃。“是为习常”，这个“习”，不同的本子有不同的写法。习，就是普遍、永恒的意思，就是普遍的永恒的规律、规则。也有的本子用的是沿袭的“袭”，也就是遮盖的意思。《道德经》里边用这个“袭”字的意思就是说，这是被大家认识不到的、被遮盖的规律规则，了解了这一点，我们也就对事物的了解更加深入。这两个意思都通，我们这里边用的是复习的“习”，学习的“习”，也就是经常的、普遍的、永恒的意思。“是为习常”，这就是一个经常的、普遍的、永恒的规律、规则。这一章核心的内容是说，道是一个普遍的规律，它存在于天地之间，所以叫“大道”。我们了解了大道，掌握了普遍的规律、规则，再来认识具体事物中的规律、规则，这是非常有帮助的，也是非常重要的。反过来也是一样，了解了具体事物中的规律、规则，也能够让我们更加坚信大道的存在，更加了解大道的伟大。这一章以母和子为喻，大和小对照，就讲述了这样的一个哲学的道理。这样的智慧能让我们用到大道的光芒，走在光明的大道上。</t>
+  </si>
+  <si>
+    <t>第五十三章</t>
+  </si>
+  <si>
+    <t>使我介然有知，行于大道，唯施是畏。大道甚夷，而民好径。朝甚除，田甚芜，仓甚虚。服文彩，带利剑，厌饮食，财货有余，是为盗夸。非道也哉！</t>
+  </si>
+  <si>
+    <t>假如让我稍微有些认知，行走在大道上，最害怕走到斜路上去。大道非常平坦，但一般人喜欢走捷径。（无道之君）朝政非常混乱，田园非常荒芜，仓库非常空虚。穿着华美的衣服，佩带锋利的宝剑，吃饱喝足，积存财货有余，这是夸耀自己的强盗途径。无道啊！</t>
+  </si>
+  <si>
+    <t>讲到这里大家已经非常清楚了，老子衡量事情的最高原则就是大道。“使我介然有知”，“芥”就是小的、稍微的意思。假如让我稍微有知识、有智慧，“行于大道”，走在大道上。我最怕的是什么呢？“唯施是畏”，“施”，就是逶迤、曲折，在这里指的是邪路、歧路。走在大道上最可怕的是什么呢？就是害怕歧路太多，害怕走到邪路上去。“大道甚夷，而民好径。”其实大道是非常平坦的，但是一般人都喜欢走捷径，老想抄近道。“朝甚除”，朝政非常得混乱。“田甚芜”，田园都已经荒芜了。“仓甚虚”，仓廪实才好嘛，现在仓库里边都是空虚的。可是那些统治者在干吗呢？“服文采，带利剑。”穿着漂亮的、非常昂贵的衣服，带着珍珠宝石装饰的利剑。“厌饮食”，什么东西都吃腻了，对什么好吃的东西都已经感觉到厌烦了。“财货有余”，家里的财宝有那么多的富余。这叫什么？“是为盗夸。”《道德经》认为这个就叫“盗夸”，强盗，还夸耀自己的强盗行为。《道德经》在第七十七章里边就讲，“天之道，损有余而补不足”。现在这些人做的是什么呢？“损不足，以奉有余”。“非道也哉”，这完全不符合道的规律、规则，完全不是按照道的方式来做嘛。这一章表现了老子的平民的思想、公平的思想，指责在“朝甚除，田甚芜，仓甚虚”的情况下，那些人“服文彩，带利剑，厌饮食，财货有余”夸耀自己的强盗行为。这一章有一些字，我们还得具体地、细致地解释一下。“唯施是畏”，凭什么把这个“施”念成“迤”，解释成歧路呢？因为道弯弯曲曲的时候，歧路众多。在《列子•说符篇》里边讲的一件事——歧路亡羊。杨朱他们家的邻居羊丢了，很多人都出去找，杨朱就觉得很奇怪就问，就一只羊怎么这么多人去找啊？邻居就告诉他，歧路多，岔路太多了。找羊的人回来了，杨朱问找到了吗？邻居说没找到。又派更多的人去找，还没有找到。歧路中又有歧路，岔路中又有岔路，所以常常使人丧失了大道，迷失了大道，所以杨朱听了之后几天都不说话。古人有“歧路亡羊”，也有遇穷途而哭，走道遇到没有路了，痛哭而返，其实都是感觉到了人生道路上的一些很值得人害怕的事情。行于大道，最害怕的就是歧路、岔路，一旦走错路，方向一错，后边的一切麻烦就都来了。所以老子说“大道甚夷”，“夷”就是平坦的意思，大道其实极为平坦。“而民好径”，人却老喜欢去走这个捷径，走了捷径之后，最后发现回到正确的大道上是非常困难的。其实，很多的所谓捷径就是歧路，就是邪路，人要脚踏实地，这样才能够行走在正确的大道上。通过努力获得成功，而不要投机取巧，更不要把投机取巧里边得到的东西当作一种炫耀夸耀，这个叫什么？“盗夸，非道也哉。”</t>
+  </si>
+  <si>
+    <t>第五十四章</t>
+  </si>
+  <si>
+    <t>善建者不拔，善抱者不脱，子孙以祭祀不辍。修之于身，其德乃真；修之于家，其德乃余；修之于乡，其德乃长；修之于国，其德乃丰；修之于天下，其德乃普。故以身观身，以家观家，以乡观乡，以国观国，以天下观天下。吾何以知天下然哉？以此。</t>
+  </si>
+  <si>
+    <t>善于进行精神上的建设这是不可拔除的，善于掌握道的人不会脱离道，子孙世世代代不断尊敬、学习这个原则。用这个道理来修身，他的德会是真实的；将这个道理贯彻到修家，这样他的德才能有余；用这个道理来治乡，他的德才能不断丰富成长；用这个道理来治国，他的德才会丰盛；用这个道理来治理天下，他的德才会是普遍的。所以按照修身的原则来观察个人，按照齐家的原则来观察家庭，按照治乡的原则来观照乡，按照治国的原则来观照国，按照治天下的原则来观照天下。我怎么知道天下是这样的呢？就是因为这个道理。</t>
+  </si>
+  <si>
+    <t>第五十四章由三段构成。第一段：“善建者不拔，善抱者不脱，子孙以祭祀不辍。”这一段在讲按照大道来建设，没有人能够攻击倒它，把它拔除掉。大家想，人类建设的很多的东西，有成必有毁，都是会被拔除掉的，而大自然呢，比如说山川，这是大自然建筑的东西，有的或许可以被拔除掉，但这一章讲的不是这个意思。“善建者”指的是人精神方面的建设，大道方面的建设，这个伟大的思想是不会被攻击倒、被拔除掉的。比如我们现在学的《道德经》，历经两千多年，很多人都在攻击，在否定，在嘲笑，可是这无碍于它伟大的思想，现在学的人越来越多，大家越来越从里边得到一种智慧的启迪。另外像佛祖释迦牟尼，像孔子，历史上一些伟大人物的思想，他们的思想像什么？就像夜幕中的星光，给我们在黑暗中指引方向，有的甚至像光明普照的太阳。这些思想属于“善建者”，是没有办法把它攻击倒、拔除掉的。“善抱者”是什么意思呢？直观的理解就是善于把你抱住的人，你是脱离不开他的掌控的，其实这只是望文生义的理解。在《道德经》里边多次提到“抱”字，比如说第二十二章，“抱一为天下式”；比如说第四十二章，“万物负阴而抱阳，冲气以为和”。抱的是什么？“负阴抱阳”。所以这个“善抱者”就是掌握阴阳之不测，掌握阴阳相互作用、相互变化的规律规则，而“一阴一阳之谓道”，所谓“善抱者”，也就是了解大道的人。“不脱”，脱离不开大道的掌控，脱离了大道就走到了一个危险的境界。“子孙以祭祀不辍”，一代一代，千秋万代，按照“善建者”、“善抱者”这些伟大的思想来做，对他们表示一种尊重、敬仰，不断地学习。“修之于身，其德乃真。”按照这个伟大的思想来做事、来修身，这样所得到的德，才是真实的、纯净的。“修之于家，其德乃余。”按照大道来修家，一家人遵循大道，这样获得的家的品德才是丰盈有余的，积德之家必有余庆嘛。“修之于乡，其德乃长。”拿大道来传达给一个乡，按照这个方式形成一种良好的乡风。“长”就是领导的意思。你把这个方式在乡里边普及，让大家坚定地按照道的方式来做，你才能成为这个乡的好的领导者。我们知道，在宋朝的时候，陕西“蓝田四吕”首先制定了乡约，它对我们中国良好的乡风的培育起了非常大的作用，这不就是“修之于乡，其德乃长”的具体表现嘛。“修之于国，其德乃丰。”按照这样的一个方式来治理国家，让国家按照大道去做，所收获的德才是丰盛的、伟大的。同样的道理，“修之于天下，其德乃普。”天下是天下人的天下，不是一人之天下，所以大道之行，天下为公。按照善建、善抱的大道来做，修之于天下，这样大家得到的才是普遍的，如光明之普照。这是第二段，老子在讲按照“善建”、“善抱”的原则来做，所获得的伟大的结果。“以身观身”，“观”就是观察。我们按照修身的要求，大道修身的方式来观察这个人，他修身方面是不是善建、善抱，是不是没有脱离大道。“以家观家”，按照家庭的修养的要求来观察家庭的品德、家风。当然这个“观”的时候就自然有对比的意思，和其他的家里边进行对比，相互比较，看哪一个是更能按照“善建”、“善抱”的这种符合大道的原则方式来修身、来齐家。下边也是同样的道理，“以乡观乡”，乡自有乡的要求，和家是不一样的，范围扩展了，有很多家庭。但是如果这个大道一以贯穿，都是按照对“善建”的、“善抱”的原则祭祀不辍、尊敬，敬仰，以按照这样的一种规则来作为荣耀，都为良好的家风、乡风做出贡献，这不就是道一以贯之吗？同样的道理，“以国观国”，一个国家有这个国家的精神、思想、风貌，按照大道要求来做，在和其他国家比较中，取长补短。同样的道理，“以天下观天下”。大道一以贯之，一条主线，一切顺理成章，自然而然，无往而不胜。所以最后老子说，我怎么知道天下也会是这个样子？“以此”。大道所向无往而不胜，虽然人世间有那么多的枝枝蔓蔓，但是核心“善建”、“善抱”之大道，不要脱离开大道，坚定地、坚持地按照它去做，按照道去做就是“有德”。修身得到的是“真”，修家得到的是“余”，修乡得到的是“长”，修国得到的是“丰”，修天下得到的是“普”。所以，从修身开始，最后落到天下，不就是这样一个简单的道理吗？其实读这一章的时候，大家会有一个非常深刻的感受，中国先秦时代是中国的轴心时代，各个思想流派之间的思想，虽然有差别，但是也有相同的地方。所以我们看这和儒家的思想，修身、齐家、治国、平天下一样，都是从修身开始，最后才能够成为国家的好的领导者，才能把这种思想普及到天下。“天下难事必做于易，天下大事必做于细。”从自身做起，要求自己按照大道的这种修养、修为，按照“善建”、“善抱”的原则，坚持地、坚定地去做，我们才能真正地有德。</t>
+  </si>
+  <si>
+    <t>第五十五章</t>
+  </si>
+  <si>
+    <t>含德之厚，比于赤子。蜂虿虺蛇不螫，猛兽不据，攫鸟不搏。骨弱筋柔而握固，未知牝牡之合而全作，精之至也。终日号而不嗄，和之至也。知和曰常，知常曰明，益生曰祥，心使气曰强。物壮则老，谓之不道，不道早已。</t>
+  </si>
+  <si>
+    <t>含德深厚的人，可比于刚出生的小孩。蜂蝎毒蛇等都不会刺咬他，猛兽不抓他，猛禽不攫取他。筋骨柔弱但小拳头握得很牢固，不知道男女交合之事但生殖器会举起，这是因为他精气充足。整天嚎哭但嗓子不会哭哑，这是因为他元气醇和。知道醇和、平和就是了解了道的规律、规则，了解这个事物规律、规则的人才是明智，让我们的生命有益才是一个吉祥，纵心任气，是强暴、强蛮的表现。强壮会趋于衰老，这叫做不合于道，不合于道便会早早灭亡。</t>
+  </si>
+  <si>
+    <t>这章开头讲了一个非常有意思的概念，就是“赤子”，这是因为婴儿刚出生的时候浑身是红色的，但这个词更重要的作用是比喻心地的纯净、纯洁。“含德之厚，比于赤子。”按照道的标准来衡量，赤子心地纯净，无恃无为。这是含德浑厚的一种表现。其实，不只老子，孔子也对婴儿的状态充满了景仰，认为这是一种有道的含德之厚的表现。孟子也说，“大人者不失其赤子心”。老子更是把婴儿作为一个范本与榜样，第十章就说“专气致柔，能如婴儿乎？”人精神集中，气息平和，那不就是像婴儿的样子吗？下边这些都是从经验的角度来讲获得的感受。小孩的他精神状态很安稳，蜂子、毒虫、蛇也不蜇他，也不咬他，为什么呢？因为小孩没有危险，没有对这些动物造成威胁的举动。其实有时候蜂子落到我们脸上，也许只是为了得一滴汗液，没有汗液，它采的蜜也不能凝固，可是我们一打它，它当作危险的时候，就要用它的毒针来蜇我们。很多动物也是这样，人没有危险动作的时候，其实也不会攻击人，但人见到它就害怕，就有一种防范甚至攻击性的动作，这也是难免的。老子说你看，这婴儿啊，“毒虫不螫”，毒虫不蜇他。“猛兽不据”，虎啊、狼啊这些猛兽，也不把它叼走，不用爪子把他抓走。我们经常会听到这样的一些事，很多动物还喂养、抚育这些落在田野里边的荒野上的小孩，当然这也不是全部的情况，我估计老子也是拿这个做一个说明而已。“攫鸟不搏”，攫，攫取。有的时候，人手上拿着一个什么东西，比如说拿着肉，在一些荒远的地方，老鹰就飞下来把这肉抢走了，但是对小孩它却不这样做，除非是尸体。“骨弱筋柔而握固”，这小孩其实身体是最柔软的，但是你看他这小拳头却握得很紧固。这人生啊，深究起来是有点意思。小孩刚出生的时候，都是握着拳头，似乎想抓住点什么，但人最后离开这个世界的时候，却是放手了，知道什么也抓不住。“未知牝牡之合而全作”，“牝牡”本来指的是雄性和雌性的动物，但是这个地方指的是男女。小孩刚出生不知道什么男女的事情，但是你看他的小生殖器却非常坚挺。老子用这样的一个方式来做形容，说婴儿精气很纯、很多、很壮，“精之至也”，达到了一个最好的状态，老子是这样认为。下边这个描述确实挺有意思，叫“终日号而不嗄”，小孩终日啼哭，但是嗓子却不哑，那不是精气足的表现吗？我现在讲课，讲一段时间喉咙就哑了，我们现在为什么会这样？老子可能认为，这人长大了，欲望多了，精气耗费得多了，所以就不像小孩那样精气充足。这一段把婴儿作为一个得道者的良好状态的表现讲完了，下边老子该阐述自己的观点了。“知和曰常”，“常”就是规律、规则。了解了这个“和”，通过婴儿引出来的“和之至”，谁能够像婴儿一样，让我们气息平和，让我们的欲望平和，不那么欲壑难填，就了解大道的规律、规则。“知常曰明”，了解这个事物规律、规则的人，那才是明智。“益生曰祥”，让我们的生命有益，这个才是一个吉祥的表现。这是正面，那负面呢？“心使气曰强”，老是盛气凌人，体现的是这种强横、强暴，这个是道家所反对的。气息不平和，纵心任气、任性，这个是强暴、强蛮的表现。在前面第二十三章讲过，“飘风不终朝，骤雨不终日，孰为此者？天地。天地尚不能久，而况于人乎？”暴风骤雨它不会持久，天地的使强也不过只是持续一阵子，它告诉我们这个道理，强不能持久。“心使气曰强”，这不是一种好现象。“物壮则老”，事物发展到顶峰的时候，就开始走下坡路了，人到了壮年之后，就逐渐向衰老的方向发展了。“谓之不道”，这已经使气，老是以强壮来作为目标、作为处理问题的方式，这是不符合大道的。“不道早已”，既然不符合大道，那这个事情就不能持久，很快就会结束了。你看这婴儿的状态，其实应该能存活得更长久、寿命更长，为什么后来很多人变得短寿了呢？那就是让自己脱离了大道，没有像婴儿那样，“精之至”，“和之至”。所以人应该“知和，知常，益生”，而不应该使气，不应该“物壮”，如日中天的时候就走下坡路了。人生最美的境界是什么？花未全开月未圆。所以，按照大道的方式来处事、认知事物，这样我们才能够明，才能够益，否则的话就会“不道早已”。</t>
+  </si>
+  <si>
+    <t>第五十六章</t>
+  </si>
+  <si>
+    <t>知者不言，言者不知。塞其兑，闭其门，挫其锐，解其分，和其光，同其尘，是谓玄同。故不可得而亲，不可得而疏；不可得而利，不可得而害；不可得而贵，不可得而贱，故为天下贵。</t>
+  </si>
+  <si>
+    <t>有智慧的人不多言，多说话的人不是有智慧的。塞上欲望的孔穴，闭上欲望的门户，收敛锋芒，解除纷扰，在光明之处便与光融合，在尘垢之处便与尘垢同一，这就叫“玄同”。这样就没有了亲疏之别、利害之分、贵贱之差。所以为天下所尊贵。</t>
+  </si>
+  <si>
+    <t>这一章还是比较容易理解的。“知者不言，言者不知。”开头的第一句话就讲，有智慧的人是不多言的，所谓“行不言之教”，还有“悠兮其贵言”，都在讲这个道理，有智慧的人是不会多嘴多舌的，不会去乱说的。“知者不言，言者不知”，老是认为自己无所不知、以为自己有智慧的人，其实是不具备真正的智慧的。“塞其兑，闭其门。”我们前边解释过，“兑”指的就是耳、目、鼻、舌这些感官，所以它强调的是感性对事物的认识，是不可信的。“塞其兑，闭其门”，这样才能对事物本质的根本的内容有真正的理解。下面讲处理问题的方式方法，做人的思想与智慧，要“挫其锐，解其分，和其光，同其尘”，不要锋芒外露，这样才能长久。要解除那些纷纷扰扰，不要让纷纷扰扰在心里打成结——心有千千结。真正了解道的含义的人，按照道去做事的人，是很容易摆脱这些纷纷扰扰的。“和光同尘”，也就是讲同流而不合污，所谓外圆而内方，所谓与世推移。那么这个叫什么呢？就叫做“玄同”。“玄”本来是天的颜色，意味着深远，这样的同是深远的、深刻的，同流而不合污，当然里边就非常有玄妙了。下面的内容讲得也非常清楚，就是说道并不是为人谋利益的，得道的人他怎么样来和万事万物打交道呢？就像道一样，“不可得而亲，不可得而疏”，道并不是对谁更亲近，或者对谁更疏远。有亲就必有疏，有疏就必有亲，这个就不平等了，这就不“玄同”了。所以，按照道的、“玄同”的方式来做，没有亲疏之别，无差别。“不可得而利，不可得而害”，有利必有害，有害也必有利。所以你并不能凭借道而获利，也不能用这个道来危害别人，无差别，无利无害。“不可得而贵，不可得而贱”，道对谁也没有贵贱之分，还是依然玄同、平等，一旦有贵贱之别，便也就丧失了道的本质的属性。所以庄子讲，“以物观之，自贵而相贱。以俗观之，贵贱不在己。”从物的角度来看，都认为自己是珍贵的、宝贵的，其他的东西比不上自己的尊贵。用世俗的观点来看，贵和贱不在于自己，而在于别人的评价，在于外在的标准。而“以道观之，物无贵贱”，从道的角度来看，这万事万物并没有什么贵贱之分，所谓公正、平等、无差别、无贵贱之分。正是因为这样，所以它成为天下最尊贵的，“故为天下贵”。所以这章的内容啊，道表现为玄同，按照这样的深远的玄同的道理来理解事物，就是从道的角度来观察问题。道没有亲疏之别，没有利害之分，没有贵贱之差，所以用这样的一个角度来观察世界，这个才使它成为天下最令人敬重尊仰的，“故为天下贵”。</t>
+  </si>
+  <si>
+    <t>第五十七章</t>
+  </si>
+  <si>
+    <t>以正治国，以奇用兵，以无事取天下。吾何以知其然哉？以此。天下多忌讳，而民弥贫；民多利器，国家滋昏；人多伎巧，奇物滋起；法令滋彰，盗贼多有。故圣人云：我无为而民自化，我好静而民自正，我无事而民自富，我无欲而民自朴。</t>
+  </si>
+  <si>
+    <t>以清静无为之正道治国，以奇巧诡计用兵，以不多事滋扰来取得天下。我怎么知道是这样呢？因为上述。天下的忌讳太多，人民就越来越贫穷；百姓拥有很多锋利武器，国家就会越来越混乱；人民拥有很多奇技淫巧，奇怪甚至邪恶之事就会越来越多；法律条文越严苛，盗贼反而会越来越多。所以圣人说：我无为，人民便自我化育成长；我喜好清静，人民就会自己走上正道；我不多事不扰民，人民自己就会富起来；我没有私欲，人民自然就会淳朴。</t>
+  </si>
+  <si>
+    <t>第五十七章的这段话非常有智慧，因为这段话一开始就指出来了，事物之间的不同，有本质的区别，所以处理问题、解决问题的方式方法也不一样。“以正治国，以奇用兵”，治国讲究的是堂堂正道。道家讲的“正”当然就是清静无为，不多事，不扰民，这就是道家讲的正道，是治国的大道理。可是用兵讲究的是“以奇用兵”，“兵者诡道也”，兵不厌诈。所以不能把用兵的方式、战争的方式用到治国的上面来，这两者不同，解决的方式也不一样。“以无事取天下”，无事就是不多事、不扰民、不刁难，这样才能够得到天下，并且坐得了江山。道家“无事”是“无为”的一个重要的方面，不多事、不扰民、不刁难，而“有为”讲的是妄为，多事、扰民、刁难，我们在前边这一点已经非常明确了。“吾何以知其然哉”，我怎么知道是这个样子呢？所谓“以此”就是依据上边“以正治国，以奇用兵”它们之间的本质不一样，所以解决的方式方法也不同而得出的结论。下面，老子开始谈他对治理天下的重要的看法。违背了大道，违背了道家的以“清静无为”为根本来治理国家的方式，会出现什么问题呢？“天下多忌讳，而民弥贫”，治理天下、领导国家忌讳太多，这个也不能动，那个也不能动，这个人的职务比较高，法令涉及不到他，当然出现了忌讳，不敢动，这个地方一定会形成一个空场，形成一个腐败的群体。百姓当然越来越穷了，财富都集中在少数人的手上。“民多利器，国家滋昏”，“滋”就是越来越。如果民间利器众多，武器众多，民与民之间械斗、抗法，那国家当然越来越混乱。“人多伎巧，奇物滋起”，“伎巧”就是各种各样的奇技淫巧，越来越多，大家对这些越来越感兴趣，这个技巧能够给他们带来利益，那么各种各样的奇奇怪怪的东西，甚至包括那些妖孽的东西，就不断兴起。“法令滋彰，盗贼多有”，既然这样，要用法律来管，法条定得越来越多，越来越严苛，反而盗贼越来越多。在前面这一段讲完之后，《道德经》说“故圣人云”，很明显，这是引用以往的通达事理的王们的话，老子用自己心中有智慧的人的语言来作为结尾。“我无为而民自化”，道家讲的无为，第一，“不妄为”。第十六章里边说“不知常，妄作，凶”，不了解事物的规律、规则，瞎折腾、胡折腾，这个结果是非常糟糕的。第二是“不多为”。抓住关键，举重若轻，多言数穷，不如守中，适可而止，恰到好处。第三讲究的是“有所不为”。人要想有所为，必须有所不为。一个政府也罢，一个领导者也罢，所有的事情都抓在自己手上，那底下的人怎么得到锻炼呢？不把担子压给他，他怎么练出独当一面的能力呢？什么事都控制在自己手上，那众人怎么样自我化育自我成长呢？所以无为才能让国家的人民、才能让自己的属下自我化育自我成长。事情成了应该怎么样呢？第十七章“功成事遂，百姓皆谓‘我自然’”，事情做成了，百姓都说这是我们的努力把这事情做成的，这就叫“民自化”。“我好静而民自正”，前面我们讲过，道家讲的静，内心的清净，静下来才能找到解决事物的正确的方法。我清静，走正道，不那么浮躁、急躁、暴躁、狂躁，做一个好的表率，上梁而正，百姓当然也就正了，百姓当然也就好静而走正道了。“我无事而民自富”，不多事、不扰民、不刁难，那百姓自然就富起来了。“我无欲而民自朴”，“朴”就是原木，《道德经》里用原木喻指做事敦厚、朴实、厚道，没那么多欲望，不是老想抢夺别人、占有别人的。就像黄宗羲在《明夷待访录》里边讲的，古代的那些皇帝都是什么样的？“离散天下人之儿女，荼毒天下人之肝脑，以供一人之淫乐。”这是我的，普天之下都是我的。所以欲望无止境，你让百姓能够朴实厚道，这也不可能。所以不要欲壑难填，不要什么东西都看作是自己的，可以任意掠夺，这样百姓自然就朴实、厚道，民心淳朴。这里边的两句话，我们国家的领导者讲话的时候也经常引用：“我无为而民自化，我无事而民自富。”所以，第五十七章讲了两个重要的道理，第一个不能把打仗的这一套用到治国之上。治国讲究的是堂堂大道，讲究的是清静无为，所以以无事取天下。第二个就讲站在领导者的角度，站在统治者的角度，应该怎么做呢？无为、好静、无事、无欲，这样自然一切顺理成章，百姓就会自化、自正、自富、自朴，事成了也会“功遂身退，百姓皆谓我自然”。这是一个好的领导者、好的政府做事的道理之所在，反之越多事儿，越是用那种严苛的法令，导致的结果适得其反。忌讳多了，百姓就越来越穷，民间的利器多了，国家就越来越混乱，大家都倾向于奇技淫巧，把这个当作一种喜欢的甚至不停地去追求的目标，那这个国家就越来越怪，各种奇葩的事情都纷至沓来。越觉得法令不够，越制定得严格、细致，以为单靠着法令就可以解决所有问题，反而适得其反，盗贼多有。所以，这一章里边讲的，也是我们经常说的——这本书的总纲：“反者，道之动”。我们考虑问题，不要只考虑它一面，要相反相成，用一个更高的观察事物的角度来理解。</t>
+  </si>
+  <si>
+    <t>第五十八章</t>
+  </si>
+  <si>
+    <t>其政闷闷，其民淳淳；其政察察，其民缺缺。祸兮福之所倚，福兮祸之所伏。孰知其极？其无正。正复为奇，善复为妖。人之迷，其日固久。是以圣人方而不割，廉而不刿，直而不肆，光而不耀。</t>
+  </si>
+  <si>
+    <t>（治国者）为政宽容，人民就会淳厚；为政苛察，人民就会因感觉不足而欺上。祸啊，福倚靠着它；福啊，祸就藏伏其中。谁知它们的极点在哪呢？没有确定的标准。正转变为邪，善转变为恶。人们的迷惑，已经有很长的时间了。所以圣人方正而不割伤别人，有棱角但不刺伤别人，直率但不会放肆，有光芒但内敛，不刺眼炫耀。</t>
+  </si>
+  <si>
+    <t>第五十八章有两个我们非常熟悉的成语，一个叫“祸福相依”，一个叫“光而不耀”，也是这一章核心的内容。祸福相依，福和祸是相互转化的，两者也是相辅相成的，分不开的。“光而不耀”在讲什么呢？我们大家看到过月亮，月光是明亮的，在黑暗中给我们指引以方向；同时月光也是不张扬的、不炫耀的、不刺眼的。中国人喜欢拿月亮来比喻君子的形象，做君子得先有光，但是不管我们有什么，都不要老想着去张扬、炫耀，让别人感觉到刺眼。所以《道德经》很多章节，都向我们揭示了这样一个道理：有才华、有知识、有道德的人，不要老想着去张扬、炫耀。以这两个成语为切入点，我们会对这一章的内容有个直观的感觉。我们来逐字逐句地解释一下。“其政闷闷”，“闷”就是淳厚。就说政治比较淳厚宽容，那么这个国家的百姓也就是敦朴淳厚，不耍心眼。“其政察察，其民缺缺”，假如这个政治非常苛察，对一切都监控得到位，那老百姓就会感觉到有很多的缺陷与不足，就要耍心眼。所谓上有政策，下有对策，也就失去了原本的淳朴。“祸兮福之所倚，福兮祸之所伏。”福和祸是相辅相成的，在一定条件下是相互转化的。民间的很多说法，大家都能够体会到这意思的延伸和运用，比如，我们经常说“大难不死必有后福”、“好事多磨”……福和祸是相伴而行的，有时候我们认为是福的事情，它可以转化为祸，反过来也是一样，所以这就叫“祸福相依”。怎么样来理解这个事情呢？给大家举个例子，大家就清楚了。其实各民族的智慧到达高点的时候，往往是相互重合的，印度有一本佛经叫《大般涅槃经》，在这里面讲了这样一个故事。有一天早晨，一家主人一开门，门口站着一个衣着光鲜、非常漂亮的女子，主人就问你是谁，女子说我是“功德大天”，我到谁家谁家就一切兴旺。主人高兴地请进来，焚香供拜。刚一关门又有人敲门，开门一看，门口站着一个衣衫褴褛，非常丑陋的、黑瘦的女子，主人就没好气了，主人就问你是谁呀，那女子说我是“黑暗”，我到谁家，谁家就一切破败！主人当然不让她进来，拿着刀驱赶。结果这女孩说你太笨了，刚进去的是我姐姐，我们俩从出生这天起就没有分开过，你把我赶走了，她也留不下。主人不信，进去一问果然是这样。福跟祸是相伴而行的，所以它就提醒我们，遇到福事的时候就要小心谨慎，避免乐极生悲；遇到祸事的时候，也不要感觉到沮丧，因为我们对灾祸有所警惕，它可以避免后面更大的灾难。韩非子讲过“千里之堤，溃于蚁穴”，我们发现了这个蚂蚁窝，知道它是一个祸患，很早的把它堵上，那就避免了以后更大祸事的发生。这就是“祸福相依”的道理，在我们文化中影响是非常深刻的。讲完这一段后，《道德经》就说“孰知其极？”这个事物到达极点的时候，向它相反的方面转化，所谓两极相通，所谓物极必反，但是这个极在哪里呢？这个是需要我们认真去体会把握的。“其无正”，其实并没有确定的标准，所以并没有说我们到了一个什么程度，一定会向它相反的方面转化，这是要根据不同的时间、地点、条件，需要我们认真去领会把握的、体悟的一种智慧。“正复为奇，善复为妖。”“正”，你把它弄到极点它就偏了，“善”到达极点的时候，它就转化为它相反的方面。有些人老想寻找一个固定的标准，《道德经》就说：“人之迷，其日固久。”在这个方面的迷惑，时间已经由来已久。所以我们总是要寻找一个固定的标准，总是觉得做事情有一个固定的程序，固定的套路，这个就不圆融。下面就讲，“是以圣人方而不割”，“方”就是方正，“割”就是生硬。有原则但是不生硬，人要懂得去碰硬，但是不要去硬碰。方正而不生硬，这样才能圆融，我们把它叫做“外圆而内方”。“廉而不刿”，“廉”就是棱角，“刿”就是锐利。有棱角但是不要老用锐利之处去刺伤人。“直而不肆”，有人经常就说，我说这话你别在意，我这人很直。其实有的时候不是直而是自私，是放肆、过分。所以我们说直率，它是一种心态，但是你讲话的方式得懂得圆融，直率而不放肆。“光而不耀”，有光芒，但是不要老去张扬、炫耀，让别人感觉到刺眼。咱们中国人喜欢讲君子，什么样的人是君子呢？中国人除了用月亮来代表君子“光而不耀”的特点之外，另外，也喜欢用玉来代表君子的形象，所谓“谦谦君子，温润如玉”。“谦谦君子”出自《易经·谦卦》，原话叫“谦谦君子，用涉大川”，一个人保持这种内敛的、谦逊的风度，这样才能走好人生长远的坎坷的道路。另外一个是出自《诗经》的“温润如玉”，谁都知道闪着贼光的肯定不是什么好玉，真正的好玉都是光芒内敛，给人一种温润感。我认为“光而不耀”是中国文化里，对君子形象用得最好的一个比喻。我们有知识，不要老想着去张扬、炫耀，大家聚到一块的时候，一个人老去炫耀自己的知识，对别人的说法都嗤之以鼻，认为自己什么都懂，百事通，时间长了，大家就不喜欢跟这人打交道了。有道德，道德是约束我们内心的，不是老是向别人去张扬炫耀。《道德经》第三十八章开头这句话，大家都知道——“上德不德”，最有道德的人从来不去张扬、炫耀自己的道德。当然，至于炫官、炫富，这不仅不是一种君子的形象，还会给自己惹来无尽的祸殃。是否还记得第九章里“金玉满堂，莫之能守；富贵而骄，自遗其咎”，炫富炫贵，会给自己惹来无尽的祸殃。在第二章里“功成而弗居”，哪怕我们有功劳，不管是对家庭、对单位、对国家有功劳，也不要老想着去张扬、炫耀，越是不张扬、不炫耀，这个才能在人心里长久地存在。第九章里面也说“功遂身退，天之道”，这是符合自然的道理。第五十八章讲完之后，我再做一下梳理和强调。这一章有两点需要注意，一个是“祸福相依”的道理，一个是“光而不耀”的形象，怎么样能做到这一点？我们要明白“物极必反，两极相通”。了解这样的智慧与道理，我们做事情才能够圆融。所以一个有智慧的人，有智慧的领导者，为人处事应该方正而不生硬，要圆融，有棱角，但不要老去割伤人，要懂得委婉迂回地处理问题的方式。直率，但又不越界进入到了放肆、无所顾忌的程度，光芒内敛而不要老去张扬、炫耀，要给人留下一种谦谦君子、温润如玉的形象。这是我们和别人、和这个社会打交道的一个重要的思想与智慧。</t>
+  </si>
+  <si>
+    <t>第五十九章</t>
+  </si>
+  <si>
+    <t>治人事天莫若啬。夫唯啬，是谓早服，早服谓之重积德。重积德则无不克，无不克则莫知其极。莫知其极，可以有国。有国之母，可以长久。是谓深根固柢，长生久视之道。</t>
+  </si>
+  <si>
+    <t>治理人民要顺应天理，莫过于节俭节制。只有节俭节制，才能早得道。早得道就是不断地积德。不断地积德就没有什么是克服不了的，没有什么克服不了就不知道它的力量有多强大。不知道其力量有多强大，就可以掌管国家。掌握了治国的根本，就可以长久存在。这是可以把根本扎深、扎牢固，长久存在的道。</t>
+  </si>
+  <si>
+    <t>这一章讲了两种生活的态度：一种是做“加法”，不断地叠加，不断地累积，有了还想更有，多了还想更多；另外一种是要懂得做减法，要节俭节制，有的时候我们的欲望减少一分，其实我们的幸福也就多一分。这两种人生态度也是相辅相成的，可是大家更注重的是第一种，所以一章就强调我们这种做减法的态度的重要性。其实这一章核心就讲四个字：节俭节制，讲节俭节制对一个国家、对社会的重要意义。“治人事天莫若啬。”一开始就讲“治人事天”，领导这个国家的人民要顺应天理。“莫若啬”，什么事情最顺应天理呢？节俭节制。我们现在用的这个词叫“吝啬”，这个词有点负面的含义，在《道德经》中这个“啬”，我们把它译成节俭节制，这样更符合于我们的接受习惯。“夫唯啬，是谓早服”，“夫唯”是个语气助词，“啬”是节俭节制。“是谓早服”，“早服”就是早得道。懂得节俭节制的道理，就是可以早得道的人。“早服谓之重积德”，“重”就是不断。懂得节俭节制就是在不断地积累自己的品德，积累自己的德行。因为我们说《道德经》道和德要分开理解，按照道去做，就是有德，不断地按照道去做，就是不断地积德。重积德就是不断地积德，所以你看“早服谓之重积德”，早得道，一直坚定地坚持按照这个去做，就是不断地积累自己的德性，积累自己的品德，积德。我们就像一条船，我们积的德就像水，水积累得越多，我们船才能自由地航行，不管你船多大，如果没有水，在那儿搁浅，它也发挥不了船的这种作用。“重积德则无不克”，“克”就是克服，按照这个“啬”的方式，也就是节俭节制的方式去做事情，那就没有什么困难克服不了的。因为在节俭节制里边磨练的就是人的思想品德，磨练的就是人的意志，磨练的就是人面对困难无所畏惧的态度。“无不克则莫知其极”，你说这个东西力量这么强大，没有什么东西它克服不了，所以它的力量“莫知其极”，你不知道它的力量有多么强大，对一个人是这样，对一个国家更是如此。“莫知其极，可以有国。”你看这话是给谁讲的？给统治者、领导者讲的。一个领导者领导团队，领导这个国家的人民培养出一种节俭节制之风，你这样才能让你的国家长久地存在，长久地发展。毛泽东主席在中华人民共和国成立的时候就指出，“贪污和浪费是极大的犯罪”，自己也以身作则。你领导团队，领导全国人民培养出一种节俭节制之风，这样面临什么样的困难的时候，大家都有信心去克服。“有国之母，可以长久。”“母”就是根本。节俭节制是立国，是国家长久发展的根本。我们现在叫“八项规定”“反四风”，领导国家的人民培养出节俭节制之风，国家才能长久持续地发展。有一件事儿大家都知道，电视经常打出一个公益广告，说现在每年中国人浪费的粮食就是世界上两亿人的口粮。你说世界上现在每天都有人在饿死，可我们中国人这么浪费，能符合天道，能符合天理吗？如果因为这种浪费有什么惩罚落到我们头上，那么我们也无话可讲。你从这一章里面就可以感觉到，一个人浪费，糟蹋的是自己的福分；一个国家浪费，糟蹋的是国家的福分，对国家的根本有所损伤。“是谓深根固柢，长生久视之道。”国家培养出节俭节制之风，才能长久发展，这样做叫什么？叫“深根固柢”。我们讲叫根深蒂固，你让这个根本、让根扎得深，扎得稳固，深根固柢。“长生久视之道”，于人来讲是如此，可以让我们的生命更为长久，因为一个人的节制节俭，不去放纵自己的欲望，这也是一种养生之道。得以长久地存在，长久地发展，得以长寿，对国家来讲也是如此。所以“长生久视”，长久地存在，大家能够长久地看到它。《道德经》强调“做减法”的这个方面，在世界哲学界，有着非常重要的影响。我们中国人有一个优良的文化传统，讲勤俭持家，讲勤俭治国，所以这个是我们文化中非常重要的方面，但是很少在哪一本著作里面把它强调到这样的一个高度。“治人事天莫若啬。夫唯啬，是谓早服。”这就是早得道，坚定地按照这个道去做，就叫积德。不断地积德，那就使我们能够根深蒂固，长久存在，长久发展。人如此，国家亦如此，道理是相同的。第五十九章，希望大家认真地品味体会老先生给我们讲的“根深蒂固”的道理。</t>
+  </si>
+  <si>
+    <t>第六十章</t>
+  </si>
+  <si>
+    <t>治大国若烹小鲜。以道莅天下，其鬼不神。非其鬼不神，其神不伤人；非其神不伤人，圣人亦不伤人。夫两不相伤，故德交归焉。</t>
+  </si>
+  <si>
+    <t>治理大国就像烹调小鱼一样。用道来领导、指引天下，鬼也就没有神秘莫测的力量。不是说鬼不神秘莫测了，是它的神秘莫测伤害不了得道的人。不但鬼的神秘力量伤不了人，圣人也不伤害人。鬼和圣人都不伤人，所以德不断地积累交汇，形成有道有德的世界。</t>
+  </si>
+  <si>
+    <t>这一章有一句话，大家都非常熟，叫“治大国若烹小鲜”，这句话也是这一章的核心。一九八七年，美国前总统里根在发表国情咨文的时候也引过这句话。二〇一三年，“金砖各国”开会，在一个联合的采访中，有一位巴西记者问过习近平这样的一个问题：你担任这么大的一个国家的这么重要的职位是一种什么心态？你用什么样的态度来对待自己的职位？习近平答记者问，先引的是《诗经》，来回答第一个问题：“战战兢兢，如临深渊，如履薄冰。”这话出自《诗经·小雅·小旻》。治理国家要小心谨慎，就像行走在结着薄冰的冰面上一样，就像站在悬崖边一样，要小心谨慎，因为稍不谨慎就会出大的问题、大的危险。然后引用这句话来回答第二个问题，我要以“治大国若烹小鲜”的态度来对待我的职位。“治大国若烹小鲜”是什么意思呢？大家如果上网去搜对这句话的解释，类型就有二十多种，每一种解释都不一样，有的甚至把它直接翻译为“治理一个大的国家就像烹一碟小菜那么简单”，这是完全没有理解这句话的真正的含义。“小鲜”就是小鱼儿，鱼肉很细很嫩，拿它的时候就得小心谨慎，尤其是在高温里烹炒它的时候，都要小心谨慎，要有耐心。火候不到的时候你老折腾，甚至锅铲飞舞，翻腾，鱼不就成了碎片了吗？汉朝的毛亨，喜欢《诗经》的人都知道，这个人写过《毛诗传》的，他就用两句话来解读这句话，其实最符合它的本意。第一句话叫“烹鱼烦则碎”，环节太多老折腾它，那鱼就成了碎片了。第二句话“治民烦则乱”，治理一个国家也是一样，讲究的是制度的稳定，不能今天一个制度，明天一个制度，朝令夕改；你不能今天一个运动，明天一个运动来回折腾，国家不就被折腾散架了嘛。“治大国若烹小鲜”和“战战兢兢，如履薄冰”的道理是相同的，讲究的是小心谨慎，有耐心，掌握火候。“以道莅天下，其鬼不神。”“莅”就是莅临。用道来领导天下，指引天下。大家注意，这个“神”字很多的理解有问题，其实并不是神鬼的神，不是说我们后来的人格神、神化了的神。这个“神”在《易传》里面的解释是非常明确的，“阴阳之不测之谓神”，也就是神秘莫测。用道来领导天下、指引天下，鬼也没有什么神秘莫测的力量，因为你走的是正道，你走的是堂堂大道，鬼也没有办法去伤害到你，所以“以道莅天下，其鬼不神”。《道德经》里用它的道，把大家所恐惧的鬼的位置给取代了，你堂堂大道，鬼也近不了你的身，“其鬼不神；非其鬼不神”，不是鬼不神秘莫测，是因为你走大道，它的神秘、莫测、玄妙、诡秘已经没有办法伤害到你。所以把下一句话作为上一句话“其鬼不神”的注解，就很容易理解了。“非其鬼不神”，不是说这鬼不神秘莫测了，神秘莫测是它的本性。“其神不伤人”，但是它的神秘莫测已经伤害不了这种走在大道上的人、得道的人。“非其神不伤人，圣人亦不伤人”，不单是指鬼的力量伤害不了人了，反过来说，圣人他智慧高，但圣人智慧高也得返璞归真。圣人不会因为自己的智慧高，心眼多套路深，就使用这种“技巧”，这个东西不是正道。所以，鬼的神秘莫测伤不了人，圣人的智慧在领导大家的时候也会“善利万物而不争”，对人民没有伤害，“夫两不相伤”，你看鬼的神秘莫测也伤不了人，圣人领导也伤不了人。“夫两不相伤，故德交归焉。”所以有德的事情，积德的事情，两者交汇到一起，两不相伤。因为你按照道来做事情的话，鬼伤不了你，圣人也是按照道来做的，彼此也不相伤。这样大家就走在正确的道上，按照道去做，不断地积德，所以叫“德交归焉”，交汇，归到一块。“治大国若烹小鲜。以道莅天下，其鬼不神。非其鬼不神，其神不伤人；非其神不伤人，圣人亦不伤人。”如果这样两不相伤的，那就是“德交归焉”，这样就形成了一个和谐的、有道的、有德的世界。</t>
+  </si>
+  <si>
+    <t>第六十一章</t>
+  </si>
+  <si>
+    <t>大国者下流。天下之交，天下之牝。牝常以静胜牡，以静为下。故大国以下小国，则取小国；小国以下大国，则取大国。故或下以取，或下而取。大国不过欲兼畜人，小国不过欲入事人。夫两者各得其所欲，大者宜为下。</t>
+  </si>
+  <si>
+    <t>大国要善于处下，就像处在江河的下游。处在天下交汇的地方，处在天下最雌柔的地方。雌性常以柔静胜过雄性，是因为柔静又善于处下。所以大国以谦下的态度对待小国，就可以争取到小国的支持；小国以谦下的态度对待大国，就可以得到大国的庇护。所以有的“取”是从上面抓取，有的“取”是从下面托起。大国所希望的不过是得到小国的支持，小国所希望的不过是得到大国的庇护。大国小国都达成了各自的愿望，越是大国越要懂得善于处下。</t>
+  </si>
+  <si>
+    <t>《道德经》从头至尾有一个非常重要的智慧与理念：善于处下。在第八章里面就说，“处众人之所恶，故几于道”，水去的是又低又脏的地方，把那里的污浊洗净，在那个地方滋润万物，跟道最接近的。做人要做“上善若水”的人，才能称其为“大人”，这个“大”代表的是品德。国家要成为一个大的国家，该怎么样做呢？它的处事的态度是什么呢？第六十一章里边开头这句话说得简要、明确、深刻：“大国者下流。”所以，这一章的核心我们看一下，开头“大国者下流”；结尾“大者宜为下”。越是大的国家越懂得善于处下，和小的国家打交道的时候谦逊谦和，和谐相处，你就把小的国家争取了。人也如此，位置越高，越要善于处下，这样才能真正居上。这是这一章的开头、结尾，也是这一章的核心。我们在解读“大国者下流”之前，我们需要采用以经解经的方式，拿第六十六章开头这句话，用这个形象先来让大家直观地感知一下，这个直观的形象我们了解了，再来看这一章就容易了。第六十六章开头这句话：“江海所以能为百谷王者，以其善下之，故能为百谷王。”大江大海为什么能成其大呢？它地势低，善于处下，其他的水系就都汇到它这来了，用我们习惯的话讲，就叫“善于团结一切可以团结的力量”。不辞细流，所以成为大江大海。然后我们再来看第六十一章开头这个五个字就很容易理解了。“大国者下流。”所谓“下流”，就是善于处下、处在水的下游，最好是处在大海的入海口，涓涓细流慢慢地汇成大江大海。那么善于处下《道德经》拿什么来比喻它呢？这个地方是什么？是天下的水交汇的地方，所以叫“天下之交”。拿什么来比喻“天下之交”的呢？《道德经》把它叫“天下之牝”，“牝”代表母性、女性，本来这个“牝”是指母性的生殖部分。因为在《道德经》里边母性、女性代表着慈，代表着柔，代表着静，“牝常以静胜牡”，“牡”是雄性，“牝”是雌性。这世界上的事情便是如此，这雌性善于柔，善于静，所以她的力量更长久。拿这个道理来说明什么呢？以静为下，什么叫善于处下？就是以静为下。别那么急躁、暴躁、浮躁、狂躁，善于处下，这样才能具有更大的力量、更长久的力量。这段讲完了，下边又接着“大国者下流”的道理。上面那一段是在论述它力量产生的源泉。一个大国老去动武，喜欢好战，好战者必亡，看着很强大，其实这都不是长生久视之道。所以下面就讲，“故大国以下小国，则取小国。”不是以静为下吗？善于处下吗？一个大的国家在跟小的国家打交道的时候，态度谦逊谦和，善于处下，不是居高临下、盛气凌人、不可一世的处事的方式方法，把这个小的国家就争取了。你和它平等相待，它觉得你这个大国可以倚靠，它喜欢跟你交往，遇到事情的时候喜欢支持你，帮助你，为你出力。“小国以下大国，则取大国。”为什么小国会这样做呢？因为小的国家也得找倚靠。小的国家在和大的国家打交道的时候，也善于处下，也把自己的位置放低，那么它就成了大国的朋友，有事的时候，大国才能给予支持，用我们现在习惯的话叫“罩着你”。大国也罢小国也罢，都得善于处下，这样才能形成一种和谐的关系。下面这两句话是比较难以理解的。“故或下以取，或下而取。”什么叫“以取”呢？争取有两种方式，一种是从上边抓起来，还有一种方式是更为有智慧的从下面轻轻地托起来。别小看这两个虚字、连词，“以”和“而”，这表示不同的动作。“或下以取”，要抓住你掌控你，“执者失之”，越想抓住越想掌控，失去得越快。“或下而取”，其实我们在帮助别人的时候，也就获得了别人的这样一种真心的敬佩，遇到事情的时候才能够得到人家帮助。“大国不过欲兼畜人”，大国想要更强大，就得需要更强大地支持，大国就得团结更多的小的国家，形成一个相互支持、相互帮助的局面。我给大家举一个例子，大家对这个问题就理解更深刻一点。我们中国文化的图腾——龙，大家都熟悉，我们叫“龙的传人”。可是，龙在自然界里面是没有的，它是怎么形成的呢？原来这些氏族部落，我们也可以把它看作是一个一个小的国家，那个时候他们互相征战、合并。龙的主体的部分就是蛇图腾，源自中原地区一个力量非常强大的部落，后来这个部落把很多小的部落合并到自己大的部落里边，它们收归一个部落就加上一个部落的图腾，这样，逐渐形成了龙的样子：蛇的身，马的头，鬣的尾……这不就是“兼畜人”吗？其实落到国家的层面也是一样，形成了一个团结的阵营，当然最好是正义的，遇到事情力量不就强大了吗？“大国不过欲兼畜人，小国不过欲入事人。”小国不过也想加入这个里面，大家一起做事，遇到事情的时候，大国还可以帮助、支持，这不是挺好的事儿吗？各得其所，所以叫“夫两者各得其所欲”，都得到自己所想要的。话讲完了，下边这句话又来了，“大者宜为下”，越是大的国家，越是位置高的人，越要懂得善于处下。</t>
+  </si>
+  <si>
+    <t>第六十二章</t>
+  </si>
+  <si>
+    <t>道者万物之奥，善人之宝，不善人之所保。美言可以市尊，美行可以加人。人之不善，何弃之有？故立天子，置三公，虽有拱璧以先驷马，不如坐进此道。古之所以贵此道者何？不曰以求得，有罪以免邪？故为天下贵。</t>
+  </si>
+  <si>
+    <t>道是万事万物的奥妙所在，是善良的人珍贵的宝贝，是不善的人得以拯救的保障。说好的话、正确的话可以得到人们的尊重，美好的品行可以增加人的尊贵。品行不善的人，为什么就要把他抛弃掉？所以设立天子，设置三公，用珍贵的玉璧在前、驷马在后的礼仪来进奉，都不如静坐修道。为什么自古至今都把道看得这么珍贵呢？不就是说，按照道去做，我们所希望的就能得到，我们的过错就能改正免除吗？所以被天下人所珍视。</t>
+  </si>
+  <si>
+    <t>这一章比较难理解，先说一下这一章的断句，有很多不一样的版本。现在大家基本上能够认可的是“美言可以市尊，美行可以加人”，有的本子是“美言可以市，尊行可以加人”，断句的差别就在这两句上。这一章讲什么呢？这一章是讲“道”的重要性，“善人之宝”，善人要不停地按照道去做，是善人的宝贝。但是，不善人也不会被道所抛弃，道可以来拯救他，所以叫“不善人之所保”。现在我们从头来解释。“道者万物之奥，善人之宝，不善人之所保。”这个道是万事万物的奥妙之所在，所以它是“善人之宝”，是善良人的珍贵的宝贝，也是“不善人之所保”，是不善人得以被拯救的保障，道可以拯救这些走错路的人，让他回到正道上来。“美言可以市尊”，美言，好的话。说好的话、正确的话，它可以得到人们的尊重。“美行可以加人”，好的品行，可以增加人的尊贵，团结更多的人。其实这个道理也比较容易理解，我们熟悉的三个人——魏徵、李世民和长孙皇后。魏徵是美言，他劝李世民，你要做一个好皇帝，有些事你不能做。李世民很愤怒，回来之后在家里边发火，说要把魏徵给杀掉。长孙皇后反而衣服穿得很整齐，给他道喜，说你遇到了一个好的臣子，我应该向你贺喜。李世民后来领悟到这一点，他说镜子可以正衣冠，魏徵就像一面镜子可以正我的品行。历史上，三个人留下的都是美言，都得到了人们的尊重，所以叫“美言可以市尊”。既然道是“善人之宝，不善人之所保”，那么“人之不善，何弃之有”。有的人走错路了，你为什么就觉得要把他抛弃掉？让他回到正道上来，用道去教化、去拯救。这是从正面来说它的作用。下面就讲的这个事就有针对性了。“故立天子，置三公。”国家的制度慢慢地有了天子，作为最高的领导者，还有三公——辅佐天子的最重要的职位。“虽有拱璧以先驷马”，古代敬献礼的时候，拱璧，捧着玉璧，捧璧的人在前边，乘着高头大马进献。珍贵吧？不如“道”珍贵！这里面有两个意思：一个就讲国家的制度，有天子，有三公，很重要，但这也只是形式。还有呢，用高头大马进献珍贵的玉璧，这也是很珍贵。但是“不如坐进此道”，这些都不如按照道来做，大道才是“万物之奥”，“万物之宝”。“古之所以贵此道者何？不曰以求得，有罪以免邪？故为天下贵。”意犹未尽，讲到这地方，《道德经》还觉得这个话就应该再强调一下，说古往今来，为什么都要把这个道看得这样珍贵呢？“古之所以贵此道者何？”不就是说你按照道去做，你才能得到自己真正想要得到的吗？“以求得”，你要的那个东西才能真正得到。这里的“以求得”并不是像我们烧香拜佛求得发财。“有罪以免邪”，因为前面讲过，“不善人之所保”，就算走错路了，但是我们重归正道，浪子回头金不换，原来的这个罪，也能得以补偿。这个并不像有的宗教里边说你犯了什么罪去忏悔一下，这个罪就免除了，它是让你按照大道来做，回到正道。我们来分分类，人不就是这两类：“善人”、“不善人”，对那些不善良的人，走错路的人，你为什么要抛弃他呢？“坐进此道”，回归此道就可以啊。弄了那么多的官职，天子、三公，有那么多珍贵的财宝，拱璧、驷马，还不如“坐进此道”。既然如此，“道”就是天下人最珍贵、最宝贵的，“故为天下贵”。</t>
+  </si>
+  <si>
+    <t>第六十三章</t>
+  </si>
+  <si>
+    <t>为无为，事无事，味无味。大小、多少，报怨以德。图难于其易，为大于其细。天下难事必作于易，天下大事必作于细。是以圣人终不为大，故能成其大。夫轻诺必寡信，多易必多难。是以圣人犹难之，故终无难矣。</t>
+  </si>
+  <si>
+    <t>用无为的态度、方式来作为，用不找事、不多事的方式来做事，最好的味道反而是没有味道。大其小，因为大事都从小事做起；多其少，因为积少才能成多。用德来对待别人的怨。计划做难的事情要先从容易的做起，想做大的事情要先从小事做起。天下所有的难事都是从容易的做起，天下所有的大事都是从小事做起。所以圣人不自以为大，不说大话空话，所以最后能成就大事。没有把握的事轻易许诺别人一定会失去别人的信任，把事情看得太容易一定会遇到更多的困难。所以圣人把所有事情都看得很难，反而没有什么难事。</t>
+  </si>
+  <si>
+    <t>第六十三章的内容，我们在前边已经有所接触。之前我们说，第二章就是《道德经》的“目录”，第二章列出来了后边讲的六个重要内容，有无相生、难易相成等等，这一章的核心就是“难”和“易”。这一章的核心意思就说，要想做大事，先从小事做起，想要以后攻坚克难，你得从容易的事情做起。还有一个重要的问题、重要的智慧：你要把容易的事情当作难的事情来做，要有充分的、认真的准备，提前思考它的步骤、程序、会遇到的问题，这样再出什么问题的时候，你就能从容应对。有这样的态度，天下也没什么难事。天下无难事，但天下都是难事，看你怎么对待。开头这九个字非常有趣：“为无为，事无事，味无味。”“为无为”——想要有为吗？你得先懂得无为的道理。为什么？因为有些事你越有为，越强求，什么事都管，反而最后结果非常不好。道家讲的无为，就是按照道的方式来作为，想要有为，先要懂得无为的道理，不要妄为，要抓住关键，举重若轻，有所舍才能有所得，所以为无为。其实也就是第三十七章里边讲的“道常无为而无不为”，道的规律、规则是什么？用无为的方式达到无不为的效果，更好的效果。我再强调一下，《道德经》里出现得最多的一个词是“天下”。《道德经》针对的是天下，千万不要把道家当作一种消极的被动的思想，它是“想为”，但是强调要通过正确的道路和手段，懂得无为的正确的道路和手段，才能达到真正的有效的为，也就是用无为的方式，达到无不为的这种效果。下边再落一层，“事无事”。大家都想做事，可是大家有没有注意到，有些人他是“找事”，他是捣乱，是阻碍、多事，天下本无事，庸人自扰之。所以我们做事的时候要懂得无事的道理，不要多事，不要找事，不要刁难。尤其是做领导者，没事找事，权力就是刁难，你这不就麻烦了吗？“事无事”，想做事，得懂得无事的道理，不要多事，不要扰民。再落一层，“味无味”。我们经常讲一个词叫“真水无香”，真正好的饮料，就像那白开水一样，没有味道。我们饮食讲究清淡，寡味，少油少盐。最高的味道，反而是没有味道，无味。当然，这三个词核心还是“为无为”，让大家能够更明白一点。老子展开来讲，“事无事”，不要多事，不要扰民，不要刁难，就像“味无味”的道理一样。按照这样的一个逻辑推下来，下面四个字大家就能明白了，“大小、多少”，千万不要把它念成“大小多少”，这个东西就没意义了。这是告诉大家要“大其小”、要“多其少”，要把小事看得很重要，细节决定成败，千万不要忽略这个细节。为什么要“大其小”呢？因为天下的大事，都是从小事做起，为什么要“多其少”呢？因为积少才能成多。想要多，你得从少的一点一点积累，积少成多。就像我们学习《道德经》，一章一章讲，一章一章学，不要着急，最后达到一个整体的理解。我们经常讲“聚沙成塔”、“集腋成裘”，这不都是“多其少”的道理吗？“报怨以德”，按照这种相反相成的道理，对别人的埋怨、恩怨，也应该站在一个“德”的角度，因为德是符合道，用道的东西里面去感化。第六十二章不是讲了吗？“人之不善，何弃之有？”人家有这个埋怨，怎么正确地对待呢？“报怨以德”。用这种智慧和层次，让大家一起能回归到正途，回归到正道。“图难于其易，为大于其细。天下难事必作于易，天下大事必作于细。”这几句话，在我们文化里边名气非常大，因为讲的是哲学上的量的积累达到质的变化的道理。“图难于其易”，“图”就是图谋、计划。你计划想要做难的事情，要从容易的事情做起。“为大于其细”，想要做大的事情，得从小的事情一步一步来。我们大家都知道要脚踏实地，循序渐进，有条不紊，一屋不扫，何以扫天下？“天下难事必作于易”，天下所有的难事，都要从容易的事情做起。就像小孩的培养，让他们在处理小的事情中就形成良好的习惯，把小的事情、容易的事当成培养良好习惯的重要途径，将来，小孩在遇到大事、难事都能从容应对。现在很多人都有一个致命的弱点，大概是人的通病，就是好高骛远，老觉得自己应该是做大事的人，对小的事情不屑一顾。《道德经》就告诉我们这个智慧：想要做难的事情，从容易的事情做起；想要做大的事情，从小的事情做起，“天下大事必作于细”。“是以圣人终不为大，故能成其大。”“是以”，“是”就是这样，“以”就是所以。所以有智慧的领导者就是这样：“终不为大”，不是老说大话，不是老给大家画饼充饥，而是脚踏实地，一步一步地做起，“故能成其大”。一步一步把这个事情完成了，一步一步地完成计划，最后实现一个大的蓝图，好的结果，水到渠成。所以一个有智慧的人，不是老用那些虚幻的东西来画饼充饥，老是给大家讲大话、空话。“终不为大，故能成其大”，最后反而成就了大事，这话讲得非常好。我建议大家学习《道德经》，有一种重要的学习方法，就是反复看。有的人看《道德经》，也许一年就看一章，反复地看，反复地体会，“少则得，多则惑”，“终不为大，故能成其大”。以管窥天，以锥扎地，我们视力更集中，这样把这个事情才能做得更踏实，扎得更透。我们每一次的进步，虽然看起来好像只是一点点，但是这一点点积累起来就不得了了，“终不为大，故能成其大”。“轻诺必寡信”，大家还记得我们在讲《道德经》第八章的时候，就讲过“言善信”，我们中国人喜欢拿潮水作为讲信用的代表和象征，所以，有一个词就叫“潮信”。你看那钱塘潮每到农历八月十八前后就来了，人也应该如此，说话要讲信用，要有诚信，能给别人做成的事我们再去允诺，没把握做成的事，不要轻易去答应，不管我们有多热情。如果我们答应人家的很多事最后都做不成，时间长了，人家一定认为我们是食言而肥，不讲信用。《道德经》讲话是比较宽缓的，但这句话用的就是强逻辑判断，“轻诺必寡信”，这不是对我们委婉的劝告，这简直就是对我们严厉的警告。所以要讲诚信，君子重一诺，一诺千金嘛，所以“轻诺必寡信”，要避免这种结果出现。“多易必多难”，你把这个事情看得很容易，做什么事情，最后一定出问题。世界上哪有容易的事情，吃个饭喝个水，这都需要功夫，需要本事，小事情我们都要认真对待。我们经常讲“小河沟里翻船”，把一个事情看得太容易了，太简单了，往往会在这个事情上出问题。面对很多难的事情，大家战战兢兢，小心谨慎，反而没事，反而就是在一些认为最容易的事情出问题。很多学生做题、考试也是一样，难题没事，在容易的题上，出了问题，回去捶胸顿足，懊悔无比。所以，我们平常要形成一种把容易的事情当作难的事情来做的习惯，你要懂得“多易必多难”，凡事太容易，后面一定会出现很多的困难，出现很多的问题。所以，下边这句话就讲：“是以圣人犹难之”，所以有智慧的人，把这容易的事情都看作很难。天下的事情都当作难的事情来做，反而结果没有什么难的事情，“故终无难矣”。这个道理非常有趣，其实就是相反相成的道理，这个叫“难易相成”。世界上有没有难事呢？有，也没有。你把这个难的事情当作难的事情，看作是无法克服的，它就是难的事情；你把容易的事情当作容易的事情，没有认真对待，最后也会变成难的事情。我们把容易的事情当作难的事情来做，最后那个难的事也就做成了；真正难的事情，我们认真准备，有充分的信心，最后这难的事情也就克服了。“故终无难矣！”世上无难事，这就是“难易相成”的智慧。很多事情，决定于我们的想法、态度，态度不同，难易之间就会相互转化。</t>
+  </si>
+  <si>
+    <t>第六十四章</t>
+  </si>
+  <si>
+    <t>其安易持，其未兆易谋，其脆易泮，其微易散。为之于未有，治之于未乱。合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。为者败之，执者失之。是以圣人无为，故无败；无执，故无失。民之从事，常于几成而败之。慎终如始，则无败事。是以圣人欲不欲，不贵难得之货；学不学，复众人之所过。以辅万物之自然，而不敢为。</t>
+  </si>
+  <si>
+    <t>局面稳定的时候容易掌控，事情没有征兆的时候容易去谋划，脆弱的东西容易分开，微小的东西容易解散。在事情还没有开始的时候就要作为，在还没有出现乱象时就处理好。合抱的大树，都是从细小的萌芽一点一点长起来的。九层的高台，也是一层一层的土积累起来的。想要走千里的路，就要从脚下一步一步走起。强为、妄为就会失败，执意把控就会失去。所以圣人不强为、不妄为，所以不会失败；不强执、不固执，所以不会失去。众人做事常常在快要接近成功的时候惨遭失败。在事情快要做完的时候还像一开始时候那样谨慎、慎重，就不会有失败。所以圣人所想的都是别人不愿意去想的，不以难得的货物为珍贵；学别人不愿意学的，对别人的错误引以为鉴。只是按照道的规律自然而然地去做，而不敢妄为。</t>
+  </si>
+  <si>
+    <t>第六十三章、第六十四章讲的道理，就是大家熟悉的量变和质变的道理，量的积累达到质的变化。但是大家注意，这个量的积累，有向好的方面，也有向不好的方面。前面讲了“为大于其细”，要做大事，从小的事情做起，这样才能最后达到想要的结果，假如积累的是一个不好的量，最后就积重难返。第六十四章一开始就要把两个方面，都给大家做了说明，有的事情在它刚出现向坏的方面发展苗头的时候，我们在这个阶段就把它解决了。这一章里有两个非常重要的内容，一个是大家都熟悉的一段话：“合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。”第二个就告诉我们，做事情要“慎终如始，则无败事”。这两个重要内容，我们先有一个直观的认识，再来读就好理解了。我们一句一句来解释。“其安易持”，“安”就是稳定，局面稳定的时候，容易掌控，就像一个东西，它稳定的时候，你容易把它把握住；它活蹦乱跳的时候，你把握起来就困难了。“其未兆易谋”，“未兆”，没有征兆的时候，苗头还没有开始的时候，容易去谋划。“其脆易泮”，脆的时候一打就打散了。“其微易散”，很微小的时候，很容易把它解散。比如说一件事情，很小的时候，人数很少的时候，你把它处理起来很容易。众怒难犯，一大群人轰起来、闹起来的时候，这事情解决起来就困难。前面告诉大家这些现象，然后告诉大家处理的方法。什么方法呢？“为之于未有”——在事情没有出现的时候，没有开始的时候，要有预见性，就要有作为，凡事预则立，不预则废。“治之于未乱”，还没有出现这种乱象的时候，就把它治理了、解决了。这也是习近平讲话时经常引用的两句话。怎么来理解呢？先给大家说第一个例证。有一次晏子出巡，齐国发大水，把一座石桥给冲毁了，晏子就把自己的船让给了灾民，大家都赞誉晏子爱民如子。然而一位有智慧的高人就批评晏子，就说你做这个国家的宰相，齐国发大水能把一座桥梁冲毁，你都没有预见到，没有提前做出预防，你失职。所以应该是怎么样？“为之于未有”，你别等这个事情都已经成为这个样子，再去处理它，不管你处理的方式多么巧妙，多么有智慧，但是不如让这件事情没有发生。另外一个例证更能说明这个道理。有一次，扁鹊的国王问扁鹊：扁鹊你名气太大了，你是不是国家医术最高的？扁鹊说不是，别人我不知道，起码我大哥、我二哥都比我的医术高。所以这个国王就很奇怪，你大哥、你二哥是谁？他们医术那么高，怎么大家都不知道他们呀？扁鹊就说，我大哥怎么治病的呢？人家还没有病，他告诉人家怎么预防、怎么不得病。这不是“为之于未有”吗？提前就有作为了，预防得病。我二哥怎么治病的呢？人家刚有一点小病，他就把人治好了，不让他酿成大病，“治之于未乱”。所以我们经常讲，凡事预则立，不预则废，要有远见，要有预见，要未雨绸缪。这是讲负面，因为有些事情量的积累是向不好的方面发展的，所以要提前把这个问题给处理掉。下面讲的这个事，非常重要。我们做大事情都要从容易的事情、小的事情，一步一步积累才能达到这种质的变化，要脚踏实地，循序渐进。因为什么呢？“合抱之木，生于毫末”，合抱之木，它是一点一点长起来的。“九层之台，起于累土”，中国文化中，三六九都代表着高、多。那么高的高台也是一层一层土积累起来的。“千里之行，始于足下”，走这么远的路，要脚踏实地一步一步地做起。说到这里，我得加一句，有人老认为道家思想是消极的、被动的、无为的。“合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。”这不就是自强不息吗？所以有些事我们不能人云亦云，我们得看原文，以原典作为证据。“为者败之，执者失之。”“为”就是强为、妄为。因为《道德经》讲的真正的为叫“无为”，就是按照道的方式来作为，不按照道的方式来作为就是强为、妄为。越是强为，最后的结果越糟糕，因为量的积累还不到，你老想强行地发生质变，这不是急躁冒进吗？“执者失之”，就像我们抓沙子一样，你握得越紧，流出来越多，越想用力地把它抓住，反而失去得越来越快。所以一个有智慧的领导者，“无为”，按照道的方式来作为，不妄为，不强为，不多为，有所不为，所以也不会有急躁冒进的失败。“无执故无失”，没有这样的强执，最后也不会失去。“民之从事”，平常人做事，或者说领着大家做事，在什么时候最容易把事情给做砸了呢？“常于几成而败之”，经常在快要接近成功的时候，把事情给做砸了。那应该怎么办？“慎终如始，则无败事。”什么叫慎终如始呢？我先给大家打一个比方，大家走在结着冰的冰面上的时候，刚一下到冰面上都是小心谨慎，战战兢兢。走一会儿，觉得自己走熟了，就放松警惕了，有的干脆最后开始跑了，有的甚至在冰面上炫耀，危险往往就在这个时候发生了。所以我们中国人经常讲一句话叫“行百里者半九十”，一百里的路，走到九十里路的时候，还要当才走了一半，越是剩下那一段的时候越紧要，民间讲“编筐编篓，全在收口”，即最后这个结尾。“慎终如始”，走到最后那几步，还像开始下到冰面上一样小心谨慎，一步都不放松，那就没什么败事，没什么事情做不成。“慎终如始，则无败事”，就是我们现在经常讲的不忘初心，善始善终，那就没有什么事情做不成的。“是以圣人欲不欲”，一个有智慧的人，特别是一个有智慧的领导者，想要的东西是什么呢？是别人都不关心的，都不想要的。因为“天下熙熙，皆为利来；天下攘攘，皆为利往”，大家关心的是获取利益的方式方法，而一个有智慧的人，有智慧的领导者，应该有这种无功利之心。“欲不欲”，别人都不想这样的，反而是你应该考虑的。大家都针对“有”的东西，这有智慧的人、好的领导者得针对这无形的东西：人的精神财富，人的精神世界，人的修养。既然“欲不欲”，你跟一般人的欲望不一样，他们认为那个东西是珍贵的、难得的，反而在你的眼里是不重要的，不把它看作是难得的。领导国家的时候也是如此，第三章讲的，“不贵难得之货，使民不为盗”，形成一种淳朴的风气。“学不学，复众人之所过。”《道德经》讲的道理，叫“绝学”，一般人不愿意学，学这个东西能带来什么样的好处、利益吗？人的境界高的时候，学的很多的东西不就是和一般人不一样的嘛。一般人不愿意学的东西，又花功夫，又不能带来什么实际的利益，可是“学”这些东西代表了真正的智慧与学问。学这些东西干吗呢？“复众人之所过”，这个“复”不是重复，我们下围棋的人都知道有个词叫“复盘”，通过不断的重复模拟来检视，哪个地方下得好，哪个地方下得不好。别人犯的过错像复盘一样历历在目，以此为鉴，别再犯大家都经常犯的错误。“以辅万物之自然，而不敢为。”“以辅万物之自然”，就是按照自然的规律去做，追求的是一种水到渠成、自然而然的结果。“辅自然”就是无为。“而不敢为”，就是不敢妄为。因为我们违背了道，违背了自然规律，哪怕是短时间取得成功，其实也会受到更大的一种惩罚。这章告诉我们，一是我们做事情要“为之于未有，治之于未乱”，懂得预防，懂得不好的事情在苗头出现的时候就把它解决掉；二是我们做事情要脚踏实地，循序渐进；三是我们要“慎终如始”，不忘初心，善始善终，因为我们做事情经常在快要成功的时候，结果功亏一篑，所以要懂得这样一个道理。</t>
+  </si>
+  <si>
+    <t>第六十五章</t>
+  </si>
+  <si>
+    <t>古之善为道者，非以明民，将以愚之。民之难治，以其智多。故以智治国，国之贼；不以智治国，国之福。知此两者，亦稽式。常知稽式，是谓玄德。玄德深矣，远矣，与物反矣，然后乃至大顺。</t>
+  </si>
+  <si>
+    <t>以前那些善于按照道来治理国家的人，不教百姓有心眼、技巧，而是使人民敦厚淳朴。百姓之所以难以治理，是因为他们奇技淫巧太多。所以用技巧来治理国家，是国家的灾难。不用技巧治理国家，是国家的福分。知道这两者的差别，这就是治国的法则。按照规律了解这个法则，就是“玄德”。玄德深啊，远啊，最后又返回了宁静朴实的根本，这样就符合自然，达到了最大的和顺。</t>
+  </si>
+  <si>
+    <t>这一章所涉及的，也是我们现在哲学里面经常讲的一个道理，叫“否定之否定”规律，讲事物的发展分为三个阶段，第一个阶段是肯定，第二个阶段是否定，第三个阶段是否定之否定。比如说麦粒长出麦苗，最后结出更多的麦粒，这就是一个否定之否定的阶段。第三个阶段常常重复第一个阶段的某些特征，却是在更高的程度上重复第一阶段的某些特征。这一章和第四十章讲的“反者，道之动”，所运用的哲学的智慧和道理是一样的，既然这样，把这个道理运用到治国上，应该如何呢？这就用到了一个我们大家熟悉的词，叫“返璞归真”，《道德经》认为治民最关键的是要使民风纯朴，不要那么多的技巧，不要那么多的套路。了解了这一点，我们再来看这一章，就明白了老先生的良苦用心。“古之善为道者”，以前的那些善于按照道来治理国家的人。“非以明民，将以愚之”，不是让百姓有那么多的心眼技巧。这个“愚”，不是愚民，而是敦厚、厚道，让人民的民风纯朴。“民之难治，以其智多。”百姓为什么难以治理？因为他心眼多、技巧多。“智”就是技巧、心眼、套路。“故以智治国，国之贼”，用技巧来治国，经常用骗术谎言，这是国家的灾难。“不以智治国，国之福”，不用这些技巧，让民风纯朴、敦厚，这个才是国家的福祉、国家的福分。“知此两者，亦稽式。”“稽式”就是法则。知道这两个的差别，这就是一个法则，治国的一个法则。“常知稽式”，“常”就是规律。按照规律，我们来了解这个法则。这叫什么？“是谓玄德”，“玄”就是深远的意思，这个就是深远的智慧与品德。下面这句话就是我一开头讲的，这个品德“深矣，远矣，与物反矣”，“与物反矣”不就是“反者，道之动”吗？我们都能看到事物的正向的发展，所以《道德经》经常提醒我们，“反者，道之动”，道是向它相反的方向运动，所以你理解问题也不能只看一面。“与物反矣”怎么解释呢？第二十五章，“大曰逝，逝曰远，远曰反”，最后又回到了它的根本。根本是什么？“归根曰静”。民心没那么多的躁动，变得清静宁静、敦厚朴实，这不就符合大道了嘛。“然后乃至大顺”，这样慢慢地就回归到了正确的道路，符合自然之道。所以，这一章讲的就一个问题：你用什么方式治国呢？要让民心变得纯朴、敦厚，返璞归真，没那么多的技巧，没那么多的套路，没那么多骗人的把戏，这样才是符合大道。</t>
+  </si>
+  <si>
+    <t>第六十六章</t>
+  </si>
+  <si>
+    <t>江海所以能为百谷王者，以其善下之，故能为百谷王。是以欲上民，必以言下之；欲先民，必以身后之。是以圣人处上而民不重，处前而民不害。是以天下乐推而不厌。以其不争，故天下莫能与之争。</t>
+  </si>
+  <si>
+    <t>江海之所以能成为百川之王，是因为善于处下，所以能成为百川之王。所以要想站在上面领导好人民，必须在言语上懂得谦逊；要想站在前面领导好人民，必须要把自己的利益放在后面。所以圣人在上面领导大家而大家没有感到沉重的负担，在前面领导大家而大家没有感觉受到伤害。所以天下人都乐于拥戴他而不会感觉厌倦。因为他不争，所以天下没有人能与他争。</t>
+  </si>
+  <si>
+    <t>这一章所讲的这个道理是《道德经》从头至尾所强调的“善于处下”，只有善于处下，才能真正居上。我们在一开始说过，《道德经》的很多话是针对那些领导者、统治者讲的，所以老先生认为越是位置高的领导者、统治者，越要善于处下，为什么呢？首先从处下的结果上来看，“江海所以能为百谷王者，以其善下之，故能为百谷王。”这句话我在前面也多次引用过。大江大海之所以能成为大江大海，是因为善于处下，不辞细流，能团结一切可以团结的力量，故能为“百谷王”。老子先拿“百川归海”的形象讲了这个道理，让大家有一个感知。下面就开始讲具体的做法和内容。“是以欲上民，必以言下之。”所以你要想站在上面领导好下面这些人，在语言上要懂得谦逊、谦让。领导者，尤其国君、皇帝这一类的，讲话的时候不能够居高临下，盛气凌人，自尊自大，不可一世。第三十九章说过“贵以贱为本，高以下为基。是以侯王自称孤寡不穀”，所以在语言上要谦逊。“欲先民，必以身后之。”想要站在前面当好领导、当好领头的，要懂得把自己的利益放在后面，想要领导别人就得给别人利益。一个人既要领导别人，又想什么好处、利益、功名都抢在自己手上，这个人下场不是不言而喻的吗？范仲淹的《岳阳楼记》里说“先天下之忧而忧，后天下之乐而乐”，做官、做领导不得如此吗？钱钟书先生认为范仲淹这两句话就是出自《道德经》的。但是人家学得比较好，不也成了大家都熟悉的名句了吗？“是以圣人处上而民不重”，所以一个好的领导者，你在上面领导大家，大家没有感觉到沉重的压力。“处前而民不害”，你在前面领导大家，大家没有感觉到你对他的危害。因为你要想领导别人，得让别人得到利益。西汉史学家司马迁在《史记·循吏列传》说：“公仪休者，鲁博士也。以高弟为鲁相。奉法循理，无所变更，百官自正。使食禄者不得与下民争利，受大者不得取小。”这里的食禄者不与民争利，意思是做官的人不许和百姓争夺利益。“是以天下乐推而不厌”，所以天下的人民都往高举你，往前推你，不感觉到厌倦、厌烦。如果统治者穷奢极欲，危害百姓，草菅人命，下面的人就会感觉到“害”、感觉到“重”，这样的人百姓会“乐推”吗？当然不会。“以其不争，故天下莫能与之争。”一个领导者，能得到了大家的拥护、拥戴，正因为你不争，不与民争利，不与其他人争名，“利而不害，为而不争”，结果是“以其不争，故天下莫能与之争”。越是争的人，最后往往失败得越惨，因为你的位置已经规定了你应有的担当、使命和责任。陈毅元帅讲过“手莫伸，伸手必被捉”，形象而深刻，那么，反过来用这个道理讲，就得以更加明确了。“以其不争，故天下莫能与之争”，所谓“不争”，并不是消极被动，“不争”，当然要了解边界，不争边界之外的东西，这样的话才能“天下乐推而不厌”。</t>
+  </si>
+  <si>
+    <t>第六十七章</t>
+  </si>
+  <si>
+    <t>天下皆谓我道大，似不肖。夫唯大，故似不肖。若肖，久矣其细也夫。我有三宝，持而保之。一曰慈，二曰俭，三曰不敢为天下先。慈，故能勇；俭，故能广；不敢为天下先，故能成器长。今舍慈且勇，舍俭且广，舍后且先，死矣！夫慈，以战则胜，以守则固。天将救之，以慈卫之。</t>
+  </si>
+  <si>
+    <t>天下都说我的道大，似乎不像任何具体的东西。正是因为道大，所以不像。如果像，就早已归为具体事物了。我有三件最珍贵的宝物，值得永久保持。一个是“慈”，一个是“俭”，一个是“不敢为天下先”。有了慈母的情怀，才能真正的勇敢；节俭才能长久持续地发展；遇到利益不争先，懂得先人后己，才能成器、成长。现在的人舍弃慈母的情怀而炫耀勇武，舍弃节俭还奢求长久持续的发展，遇到利益争先恐后、一点都不退让，这是自寻死路！拥有慈母的情怀，自然是攻无不克，守无不固。如果天要拯救谁的话，一定是以慈母的情怀来守卫。</t>
+  </si>
+  <si>
+    <t>老子、孔子、释迦牟尼、柏拉图，这都是同时代人，在他们那个时代，书其实只有一种题材，就是对话体。《论语》是孔子弟子记的，记得非常清楚，坐在对面的是什么人，提了什么问题，老师怎么回答，所以大家读起来一目了然。佛经呢？很多的佛经也都是释迦牟尼对弟子问题的回答，大家看《金刚经》，是回答须菩提的，《心经》是回答舍利子的，都是针对他们的问题的回答。古希腊哲学家苏格拉底的学生叫柏拉图，写了一本《对话录》，就是记载当时苏格拉底跟学生之间的互动，对各种问题的解答。其实《道德经》的最早的形成也是这种形式，也是对面坐的人问的问题，老先生给予回答，也是对话体，所以我们读这本书，始终要感觉到这是在回答对方的问题，是有针对性的解释和回答，这样很多问题我们才能够得以正确地理解。那么这一章是在回答什么问题呢？对面坐的人，问老子关于道和德的事，老先生给他讲半天，他没听懂，于是提出要求：能不能把你的思想概括得简单点？你让我也能听得明白。大家自然会有疑问，我怎么知道是这样的？是不是我自己在杜撰？让我们回到原文，大家看一下这一章的开头就清楚了。“天下皆谓我道大，似不肖。”老子这个意思就是说，不仅是你，天下人都认为我把道讲得太大、太宽泛了，听不懂。你听不懂，我得给你打比方，类比虽然不能够说明问题，但是它可以让人理解问题。我说道就像风一样，大象无形，你们说不像；我说道就像水一样，大道汜兮，其可左右，你们还说不像……“夫唯大，故似不肖。”正因为把道讲得这么大，拿什么给他打比方，他都说不肖，所以老子就感慨，假如真的像的话，“久矣其细也夫”。意思是假如真的像，那早就归到小道了。比如，说道像一条大河，你拿这个比方，要像的话，就像支流了。道就像一条大道，你要说比方像的话，就像小道。其实意思就说，拿道打比方，要是真的像的话，就是把道说得太小、太细了。那怎么办？不跟你讲那么多了，把我的思想概括到简单得不能再简单。只剩下三个方面，“我有三宝，持而保之。”把我的思想概括到最后，简单得不能再简单了，就剩下三个方面拿出去，按照去做就行。那这“三宝”是什么呢？“一曰慈，二曰俭，三曰不敢为天下先。”大家解读这三组词的时候，不可以单独先解释几个字词，一定要把“三宝”里边的字词和后面的语句连接来解读：“一曰慈，慈故能勇；二曰俭，俭故能广；三曰不敢为天下先，故能成器长。”否则，会失之宽泛。“一曰慈，慈故能勇。”“慈”是指什么？指的是慈母的情怀。做领导、做家长，有了慈母的情怀，才能有真正的担当、勇敢。如果你单独解释这个“慈”就麻烦了，慈母有时候也唠里唠叨，有时也无原则地爱，不是经常说“慈母多败儿”吗？可是《道德经》为什么把“慈”放到第一位呢？这是针对坐在对面的提问者的。作为领导、作为诸侯王，你在这个位置，就要有慈母的情怀，才能有真正的担当、勇敢。如果没有慈母的情怀，一出事就会出卖国家和人民，一出事就把自己的部下当做替罪羊推到前边。“二曰俭，俭故能广。”我还是觉得这位老先生对咱们中国人了解得非常深刻，我们中国人致命的弱点是什么？好面子，好虚荣，好攀比。所以一旦是公开的场合，一旦是监督不力，往往就奢靡之风盛行，浪费之风盛行。没有节俭节制，而是有奢靡之风浪费之风，那就没办法“广”，“广”就是长久持续。家庭没有培养出节俭、节制之风，家庭就没有办法长久持续地发展，所以要勤俭持家。国家人民没有培养出节俭节制之风，而是奢靡浪费，这个国家也没有办法长久持续地发展。“三曰不敢为天下先，故能成器长。”先理解“成器长”，咱们中国很多的词是组合性的，所以大家理解的时候，也要把它组合的东西拆开，“成器长”拆成四个字“成器成长”。我们怎么样才能不断地成长，终成大器呢？“不敢为天下先”，现在咱们天天讲叫“敢为天下先”，这又来一个“不敢为天下先”，这两句话不就怼上了吗？其实这两句话根本不矛盾，讲的不是一回事儿。我们现在强调的“敢为天下先”，是敢闯敢创新，这是一种很好的品质，创新是一个民族的灵魂。《道德经》讲的“不敢为天下先”是什么意思呢？做领导，领着大家做事，要懂得把自己的利益放在后面，要懂得先人后己，不要私欲膨胀，不要什么事情只关注自己，这样才能够不断地进步，不断地成长，终成大器。各位是否还记得我在前面给大家说过，其实读这本书的时候，不用别人给你画出重点，你自己都能感觉到，因为老子在书里不断地强调自己的重点，一种强调的方法是重复，第二种强调的方法是头尾，第三种强调的方式就叫正反，也就是他正面讲完了，觉得是还言犹未尽，要从相反方面给大家再论证一下，你看这一章不就是这样吗？现在的人是什么样的，本来应该按照道的方式来做，要慈、俭、不敢为天下先，我们把这“不敢为天下先”也可以概括成两个字叫“谦让”，或者概括一个字叫“让”。我有三宝，慈、俭、让。可是老子对当时的人不满意，这些人都怎么做的？“舍慈且勇”，根本没有这种情怀，还到处炫耀自己的勇敢。我们现在不也经常看到这种情况？酒驾了，还拍个视频给警察发过去，我醉驾，警察你来抓我呀，炫耀自己无赖似的勇敢。“舍俭且广”，没有这种节俭、节制，还奢求长久持续地发展，不可能。“舍后且先”，遇到好处、利益，争先恐后，一点都不肯让，甚至不该自己的也抢，这样做的结果是什么呢？“死矣！”这样做的最终结果，就把自己弄到死路上去了。“夫慈，以战则胜，以守则固。天将救之，以慈卫之。”这些讲完了，又把他讲的第一个“慈”再说一遍。有这种慈母情怀的人，那么面临事情的时候就会“以战则胜”。他勇于担当，真正遇到困难的时候，领着这个大家当然攻无不克，战无不胜。“以守则固”，国家遇到侵犯的时候，领导者的这种情怀，力量无尽，守无不固。“天将救之，以慈卫之”，如果天真的有情感的话，他要拯救国家的人民，拯救团队团体，一定是“以慈卫之”，你一定有这种慈母的情怀才值得，因为它本身就拥有无穷无尽的力量。第六十七章，核心的就是“我有三宝，持而保之”，要坚定、坚持地按照去做。</t>
+  </si>
+  <si>
+    <t>第六十八章</t>
+  </si>
+  <si>
+    <t>善为士者不武，善战者不怒，善胜敌者不与，善用人者为之下。是谓不争之德，是谓用人之力，是谓配天古之极。</t>
+  </si>
+  <si>
+    <t>善于做基层领导的人，不耀武扬威、盛气凌人；善于作战的人，懂得制怒而不会被激怒；善于战胜敌人的人，不和敌人发生正面冲突；善于用人的人，善于处下。这就叫不争的品德，这就叫善于集中大家的力量，这就叫符合天道，这是自古以来的最高准则。</t>
+  </si>
+  <si>
+    <t>这一章讲什么呢？我们中国人有一个习惯，喜欢拿战争的术语来打比方，比如说我们现在吃个饭，也可以说“打个冲锋”，来个“歼灭战”，平常我们也经常讲“占领制高点”。这一章既是在讲战争，又通过战争延伸开来，讲普遍性的制度。“善为士者不武”，“武”的意思就是耀武扬威。善于做基层领导者的人，或者说指挥打仗的士官，不耀武扬威。不要有了这样的一个位置，就耀武扬威，趾高气扬，盛气凌人，不可一世。“善为士者不武”，保持一种谦逊的、平和的、冷静的心态。“善战者不怒”，善于指挥作战的人，不是动不动就暴跳如雷。“不怒”，懂得制怒。任何一个人不管他位置多高，在急躁、浮躁、暴躁、狂躁的心理状态下都谈不上智慧。我们看一下“怒”的写法，上面是个“奴隶”的“奴”，下面是个“心”，当我们控制不了自己的情绪，心成了情绪的奴隶，没有办法保持清醒、冷静、理智的心理状态，才会发怒。所以真正善于作战的人，善于做事的人，要保持这种清醒、冷静、理智的心理状态。“善胜敌者不与”，“不与”，就是不和他发生正面的冲突。从字面的意义上来讲，善于制胜的人，懂得用委婉迂回的方式获得胜利。我们把这个“战争术语”延伸一下，其实在家里也一样，两个人情绪都到达高点、发生剧烈的冲突，这时候解决起来就比较困难。所以，越是到这个时候，越要懂得以退为进，懂得用委婉迂回的方式来解决问题、处理问题，这样才能很好地战胜对方，说服对方。“善用人者为之下”，我在前面多次说过，这是《道德经》从头至尾强调的一个最普遍的原则，善于处下者方能真正居上。一个领导者也是如此，朋友之间相处也是如此，保持自己这种谦逊处下的态度，这样才能够跟人和谐相处，才能“用人之力”。这个叫什么？“是谓不争之德”。“善为士者不武，善战者不怒，善胜敌者不与”，尤其是“善用人者为之下”，都是《道德经》里边从头至尾强调的“不争之德”。说到“不争之德”，我们的思路又回到第八章，“上善若水，水善利万物而不争”，后边讲了“不争”的七种品德：去大家不愿意去的地方——“居善地”；我们要保持内心的宁静，静水流深——“心善渊”；和别人相处，要懂得关爱，一视同仁——“与善仁”；讲话要讲诚信——“言善信”；公平、公正、清廉，所谓政清如水——“政善治”；做事情的时候要尽其所能，像水一样有多种多样的这种本领——“事善能”；善于把握时机，掌握机会——“动善时”。所以，这里的“不武”、“不怒”、“不与”、“为之下”，也是对这个“不争之德”的进一步说明。这个就叫“用人之力”，我们熟悉的一个词叫“借力打力”，熟悉的一句话叫“孤举者不起，众行者易趋”。一个人举重物举不起来，大家同心协力，形成这种趋势，这样才能把事情做成。既然如此，就要懂得用人之力，而不是孤军奋斗，这样做才能够很好地和别人和谐团结。再往高了说“是谓配天古之极”，“古”就是古往今来，所谓“配天”就是符合天道，这些是古往今来的大智慧。第六十八章没有什么难的地方。大家要明白一点，我们中国人习惯用战争的术语来讲生活中的事情，所以我们的理解不能停留在字面上。</t>
+  </si>
+  <si>
+    <t>第六十九章</t>
+  </si>
+  <si>
+    <t>用兵有言：吾不敢为主而为客，不敢进寸而退尺。是谓行无行，攘无臂，扔无敌，执无兵。祸莫大于轻敌，轻敌几丧吾宝。故抗兵相加，哀者胜矣。</t>
+  </si>
+  <si>
+    <t>懂得用兵的人曾说：我不敢主动发动战争进犯别人，而只在被进犯时不得已而应战；作战时不敢盲目进军哪怕一寸，而要后退一尺，以退为进。（在入侵国家的领土上）虽然人民没有排成行列阵势，没有面对人民奋臂作怒，虽然好像没有面对敌人，虽然人民手中没有兵器，但四处都是侵略者的敌人。没有比轻敌更大的祸患，轻敌就几乎丧失了我的“三宝”。所以两军相持时，被同情、被支持的一方会获胜。</t>
+  </si>
+  <si>
+    <t>第六十八章是用战争的术语来做比方，讲的道理当然比仅局限于战争更为广泛。第六十九章我们也当作如是观，他讲的是战争的事情，但是这个道理我们也可以做延伸、做扩展，成为我们生活中的、工作中的普遍的思想与智慧。我们知道《道德经》里边很多的内容并不是老子本人的话语，他也是一个“集大成者”。他经常在回答坐在对面的圣、王、士这些领导者的问题的时候，引用当时或者以前那些智者的语言。第一句话，“用兵者言”，懂得用兵的人怎么做谋划？怎么来认识问题呢？“吾不敢为主而为客”，我才不去老是发动战争去侵略别人，“国虽大，好战必亡。”“我不敢进寸而退尺”，打不过的时候，对手力量太强大的时候，就要懂得以退为进，这个叫什么呢？这个就叫“行无行，攘无臂，扔无敌，执无兵”，这十二个字怎么理解？我先换一个角度给大家来认知这个问题。抗日战争胜利之后，有很多日本人就对这场战争表示不是很服气，因为他们有的认为，是因为东条英机改变了战略，才导致这场战争在中国的战场上的失利；有的人认为，日本战败是因为美军的加入，所以他们也想专门研究战败的原因。有一位日本学者专程来到了中国，他也是通过一本经典来了解我们中国人在这方面的思想与智慧，这本经典就是毛泽东的《论持久战》。各位知道，一九三七年七月七日卢沟桥事变，抗日战争全面爆发，同年的八月二十二日到二十五日，就在陕北洛川召开了洛川会议。在这次会议上，毛泽东就已经开始讲持久战的思想，一九三八年的时候这本书就面世，这不是战后的马后炮，是战前的预测。他把整个战争的进程就概括为六个字，而历史就是沿着这六个字发展：退却，相持，反攻。一开始当然日本侵略者锋芒外露，我们没有办法直接跟他们对抗，因为日本是一个统一的国家，而当时我们的中国四分五裂，军阀混战，政令不统一。日本军队装备精良，又蓄谋已久，所以一开始没有可能把他们赶出去，他们肯定会占领我们很多地方。所以这个时候我们就要懂得退却，以退为进。但是日本的军队又不多，占领我们的地方多了，双方就进入了一种相持的阶段。因为武汉和鄂西会战之后，双方就进入相持阶段，咬牙坚持。我们中国是站在正义的一方，况且我们是一个统一的世界反法西斯战场的一部分，为整个世界反法西斯战场拖住了那么多的日本军队，自然要得到国际舆论的支持、国际力量的援助，最后获得胜利。那么日本为什么会陷在中国的战场上？因为原本按照日本人的想法，中国战场很快就能拿下来，以此为基地，北面是针对苏联，南面是针对南洋的那些国家，很多是英国的殖民地，所以它的主要的目标并不是在中国。可是没想到中国的战场，几乎拖住了它绝大部分的力量，为什么会这样？我们来看一下下面这几句话，“行无行，攘无臂，扔无敌，执无兵”。侵略者进入了另外一个国家，虽然这个国家的人民没有站成军队的样子，“行无行”，但是他们不都是你的敌人吗？“攘无臂”，打击你非得用拳头吗？有各种各样的方式，坚壁清野可不可以？游击战可不可以？全民皆兵，所以叫“扔无敌”。“执无兵”，虽然他们手中没有兵器，但他们用多种多样的方式和侵略者对抗，到处都是敌人。所以为什么说“国虽大，好战必亡”？因为你侵略者是不得人心的，进入到别的国家的军队会遭到别的国家人民的反抗，到处都是你的敌人，“扔无敌，执无兵”。所以对于战争而言，你不要认为一个小的国家就好侵略，“祸莫大于轻敌”，对双方皆是如此。战略上藐视敌人，战术上要重视敌人。“祸莫大于轻敌，轻敌几丧吾宝”，轻敌，就把最宝贵的东西也就是“道”丢掉。所以在战争中要冷静理智，要对对方予以重视，在战略上藐视敌人，但是在战术上要重视敌人，不要轻敌。下面这句话基于上面的这个意思就好理解，“故抗兵相加，哀者胜矣。”就是站在正义一方的抵抗的军队、防御的军队，对抗侵略者，处在相持的阶段，双方相持不下、在那较劲的时候，旁边只要有人帮一下，都会起大的作用。可是大家知道问题的决定性作用并不在旁人，没有形成相持的状态谁帮也没用。所以我们说这句话让我们领悟到一个重要的问题，中国人获得这场抗日战争的胜利，根本的原因在于我们中国人自身，而不在于外面力量的援助。斯大林曾经说过，拉开窗帘天是亮，你不拉开窗帘，天也是亮，反正中国人会获胜，应该帮一下。所以这决定的作用不在外部，而在于我们中国自身。讲得最妙的是最后一句话，最后谁获胜呢？“哀者胜矣”，“哀”可不是哀伤的意思。鲁迅先生写的《阿Q正传》中有一句话叫“哀其不幸，怒其不争”，“哀”就是同情。我们中国人从古汉语里面延续了一个习惯，讲话的时候这种使动用法，通俗地说就是被动型用法。比如我们说老头晒太阳，其实是老头被太阳晒。比如大家到陕西来吃的肉夹馍，那是肉夹馍吗？那是肉被馍夹住了。所以这种使动的用法，用这个来理解，这句话就很清楚了，“哀者胜矣”，谁是被同情、被支持的一方，最后获得胜利。“退却，相持，反攻”——惊人的一致。毛泽东从十几岁就开始读《道德经》，我觉得他从这本书里得到的最大的启发就是这种格局上的、战略上的。人站得高了才能看得远，对未来才能有一个正确的这种预测。所以我说第六十九章，大家不要只局限在战争的一个方面，它也可以把我们的智慧得以扩展和延伸，成为一个普遍性的思想与智慧，成为一个普遍性的原则。</t>
+  </si>
+  <si>
+    <t>第七十章</t>
+  </si>
+  <si>
+    <t>吾言甚易知，甚易行。天下莫能知，莫能行。言有宗，事有君。夫唯无知，是以不我知。知我者希，则我者贵。是以圣人被褐怀玉。</t>
+  </si>
+  <si>
+    <t>我的话很容易被了解，很容易去实行。然而天下之人都不了解，也不按照这个去做。说话得有核心宗旨，做事得掌握事情的关键。正是因为不知道这个道理，所以不了解我。了解我的人很少，按我说的道理去做的人更是难得。所以圣人穿着粗布衣服而怀抱美玉。</t>
+  </si>
+  <si>
+    <t>从第七十章开始，老子强调的重点又发生了改变，他在强调什么呢？他说，我们看问题要“以道观物”，可是有道的人往往为人所误解。老子在书里经常用“吾”这个字，“吾”是人格化的我。“吾”作为一个有道者的代表，一个人格化的有道者的身份，并不一定是指老子本人。第七十章开始就讲人认知的重要性。“吾言甚易知，甚易行。”得道者讲的话，其实很容易被了解，很容易去实行。“天下莫能知，莫能行。”可是结果是什么？这天下的人都是没办法了解，或者说不去了解，也不去按照这个去做。这是一种沉重而深刻的感慨。我们常说道很玄妙，很难把握，而老子在这一章讲，按照道去行事并不难知，不难行，那为什么“莫能知，莫能行”呢？是因为大家根本不愿意去相信它，也不愿意按照它去做，是因为大家认识不到这个事情的重要的意义，认识不到“道”在我们生活中的重要的作用。老子这段话主要是针对领导者、统治者来讲的，老子在对他们讲了很多次之后，发现“万言不值一杯水，犹如东风射马耳”，那些话语仿佛随风而去，并没改变什么。所以，他有此感慨：“莫能知，莫能行”。“言有宗，事有君。”“宗”就是宗旨，说话你得有宗旨，得有核心。“君”是领导控制，做事情也得掌握这个事情的关键。言外之意就是讲，你看我讲的这些话，它是有核心宗旨的。他告诉大家做事怎么样掌握事物的关键，了解事物的本质，把事情做好。“夫唯无知，是以不我知。”可是正因为这些人无知、不了解、不想知道，所以他对我们得道的这些人也就不了解。“知我者希，则我者贵。”了解我的人太少了，懂我的人太少了。我们现在经常有这种感慨，有没有人懂我？其实我们真的了解一个人的精神世界，尤其是了解这些富有大智慧的人的精神世界，不是一件容易的事情。我们中国人经常说一个词叫“知道”，现在大家再说一下这个词，它的分量就不一样，并不是你听到了就叫“知道”，“知”还得去“行”。所以了解我的人太少了，按照我这个去做的人那就更为珍贵了。“是以圣人被褐怀玉”，“褐”，褐色，粗布衣服的颜色。所以得道的人，就像穿着粗布衣服可是身上却怀着珍宝的人一样。得道者讲了很多道理，可是很多人，因为“以貌取人”就是不信。所以，我们经常要透过现象来认识事物的本质，不要以貌取人，不要认为《道德经》里的语言不是那么华丽，就否定其思想与智慧。《道德经》的很多章节都在讲人贵有自知之明。第三十三章“知人者智”，我们真正能够去了解别人，这是一种非常有智慧的表现，可是比这个了解别人更重要的，是我们要了解自己，“自知者明”。人认识最少，却自认为认识最多的知识就是关于自己的知识。因为我们自我的认知，经常被一些假象所迷惑，被情绪所左右，所以“知人者智，自知者明”。其实，老子不仅是感叹“吾言甚易知，甚易行。天下莫能知，莫能行”，他对当时的领导者这种认知的不足及其原因，是有深刻认识的。一千多年后，王阳明提出“知是行之始，行是知之成”，也是这个话题的延伸。</t>
+  </si>
+  <si>
+    <t>第七十一章</t>
+  </si>
+  <si>
+    <t>知不知，上；不知知，病。夫唯病病，是以不病。圣人不病，以其病病，是以不病。</t>
+  </si>
+  <si>
+    <t>知道自己有所不知，这是有智慧的；不知道却自以为知道，这就是思想上出了问题。把缺点当作缺点，这样才能没有缺点。得道圣人没有缺点，正是因为他把缺点当作缺点，所以才能没有缺点。</t>
+  </si>
+  <si>
+    <t>第七十章讲“夫唯无知，是以不我知”，由于我们的认识上出了偏差，出了问题，所以没有办法了解有高超智慧的人、得道的，很多的时候，我们也没有办法真正地去了解自己，那么问题出在什么地方呢？这一章在分析问题的原因。我经常开玩笑说，这一章是我见过的中国历史上最有智慧的一段绕口令，比那些相声演员用来练贯口的绕口令更富有思想与智慧。“知不知，上”，我们知道自己不知道，我们知道自己的认识有局限，我们知道自己有缺点需要弥补，这是最有智慧的。后来庄子在《秋水》篇里面把这个意思给大家演绎得非常清楚，而且富有哲理。秋天发大水的时候，河伯就以为自己这个地方就是天下最大的，“以天下之美为尽在己”。后来流到了大海，见到了北海若，发现自己太渺小了。北海若又说，其实我在天下所占的位置，也就是像一粒米那样……这就叫“知不知”，知道自己不知道，那才能够不断地进步。“不知知，病”，不知道，却把它当作知道，也就是不懂装懂，这就是一个思想上的大病。怎么样来让我们病得以痊愈？“夫唯病病，是以不病”，我们知道自己有很多的东西不知道，我们知道这是我们的缺点，我们向别人学习，取长补短，谦逊努力。知道自己“有病”，却不讳疾忌医，这反而是没有病。大家熟悉的是《论语》里边的一句话：“由，诲汝知之乎？知之为知之，不知为不知，是知也。”知道就是知道，不知道就是不知道，坦率承认，不要不懂装懂，这个达到的结果“是知也”。这不是一样的意思吗？“夫唯病病，是以不病。”所以对一个有智慧的人，特别是对于领导者、统治者来讲，周边的人都在说好话，阿谀奉承，这样就经常让自己飘飘然，如果这个时候还能保持清醒的头脑，那就是一个有智慧的好的领导者和统治者。他在这个认知上的表现是什么呢？“圣人不病”，一个有智慧的人在这个方面没有病，没有缺点。为什么说它没有缺点？“以其病病”，因为他知道自己的问题在什么地方，知道哪个地方是自己所不擅长的。就像刘邦一样，虽然不能说刘邦为一位圣人，但是他讲的这段话却可以给很多领导者、统治者以启发：“夫运筹策帷帐之中，决胜于千里之外，吾不如子房。镇国家，抚百姓，给馈饷，不绝粮道，吾不如萧何。连百万之军，战必胜，攻必取，吾不如韩信。此三者，皆人杰也，吾能用之，此吾所以取天下也。”刘邦知道自己的短处，借人之力得以弥补，因为有这种清醒的认识，反而成了一个长项。有人总认为自己什么都可以，哪个地方都是自己水平最高，比如说诸葛亮从来也不听别人的意见，打仗的时候都自己谋划，要不就弄个锦囊远程指挥，像这样的人，很难成为一个优秀的领导者。我们经常讲一个人浑身是铁，能打多少钉，要懂得用人之力，懂得借别人的智慧。现在不是有很多的智库、智囊吗？历史上很多杰出的人，比如像曾国藩，手下有多少谋士啊！很多的问题不是他一个人想出来的，得集众人之力，一个优秀的领导者得知道自己弱项、短板在哪儿。对我们个人来讲，一定要知道，其实我们的认知视野都是非常狭窄的，了解了这一点，我们也就不会把自己当作是一个完人，当作什么都知道，不懂装懂。人有什么不懂的，坦率承认没有什么可丢脸的，即便是圣贤，也有自己认知的局限，可是他们的做法和平常人的不同在哪儿呢？“圣人不病，以其病病，是以不病。”知道自己这方面有弱点、有问题，因此不断学习，不断进步，不断成长。这一章虽然很短，但是意蕴深长，道理深刻。这段绕口令大家既可以当作练表达能力、练嘴皮子的体操，也可以当作思想上的体操，一举而双得，何乐而不为？</t>
+  </si>
+  <si>
+    <t>第七十二章</t>
+  </si>
+  <si>
+    <t>民不畏威，则大威至。无狎其所居，无厌其所生。夫唯不厌，是以不厌。是以圣人自知，不自见；自爱，不自贵。故去彼取此。</t>
+  </si>
+  <si>
+    <t>人民不畏惧统治者的威严，就会发生大的麻烦。不要让人民住的地方越来越狭小，不让他们的生存受到压迫。不去压迫人民，他们才不会对统治者的行为感到厌烦。所以圣人有自知之明，不自我表现；珍爱自己的生命但不自认为高贵。所以舍弃后者而取前者。</t>
+  </si>
+  <si>
+    <t>七十二章到七十五章，这一部分都出现了一个核心的概念——“民”。在中国历史上有“民本”的思想，我们大家熟悉孟子讲的“民为贵，社稷次之，君为轻”，大家觉得讲得好。但是，在孟子之前，《道德经》已经从哲学的层面把民本思想发展到非常高的程度，而且讲得更为具体。这一章最后一句话讲得非常明白，这两条路摆在这儿了，你应该走哪条路？“故去彼取此。”有哪些路可以选择呢？走哪条路是符合道的呢？我们从头来看。“民不畏威，则大威至。”如果一个国家的人民不害怕统治者、领导者的威严，那么对统治者、领导者来讲，大的麻烦就来了。什么大的麻烦呢？“民无信不立”，领导者在民众中丧失了诚信，就没法统治领导他们了，这不是一种大威吗？所以“无狎其所居”，“狎”通“狭”，也是使动用法。领导者，不要让百姓住的地方越来越狭小，最后都流离失所。因为“无恒产者无恒心”，一个国家如果到处都是流民，它能稳定才怪。“无厌其所生”，“厌”通“压”。不要让他们感觉到生存受到了压迫，不要去压迫他们，不要让他们感觉到厌倦生活，因为哪里有压迫，哪里就有反抗。所以这个“厌”，大家可以把它理解为两个意思，一个就是压迫，一个就是导致的结果感觉到生不如死，厌倦自己的生活。“夫唯不厌，是以不厌。”你不去压迫他们，不让他们感觉到生活的局迫、窘迫、生不如死，他们才不会对你的统治行为、领导行为感觉到厌烦。第六十六章说“处上而民不重，处前而民不害”，处上又重，处前而害，他当然会感觉到这种受压迫的厌烦的感觉。那么，真正有智慧的领导者、统治者应该是什么样呢？“自知，不自见”，自己有自知之明，不是有一点功劳，有一点什么就去自我表现。“自爱，不自贵”，很珍爱自己的生命，珍爱自己名声，自爱自重，但是不自以为高贵。第三十九章最重要的两句话，第一句话就是“贵以贱为本”，不要认为自己身份高贵，没有这个国家的人民，也就是很多人眼中的贱民，哪来你高贵的身份？自爱是对的，因为一个人不爱惜自己的生命，也就不会珍惜别人的生命。第十三章讲过，什么样的人才能把天下寄托给他呢？“贵以身为天下”、“爱以身为天下”。所以好的领导者对自己的生命非常珍视，但是为了天下的使命，可以奉献自己的生命，这样的人我们才能把天下寄托给他。“故去彼取此”，取的是什么呢？取的是自知自爱；去的是什么？去的是自见、自贵。</t>
+  </si>
+  <si>
+    <t>第七十三章</t>
+  </si>
+  <si>
+    <t>勇于敢则杀，勇于不敢则活。此两者，或利或害。天之所恶，孰知其故？是以圣人犹难之。天之道，不争而善胜，不言而善应，不召而自来，繟然而善谋。天网恢恢，疏而不失。</t>
+  </si>
+  <si>
+    <t>勇于表现坚强的人就会不得善终，勇于表现柔弱的人可以保存生命。这两种“勇”，有的获利，有的遭害。天所厌恶的，谁知道其中的原因呢？所以圣人也认为这非常困难。天之道，不争而善于得胜，不发布命令、政令而能得到好的响应，不强行去征召而大家自行来到，坦然从容而善于谋划。天网虽然稀疏，但不会遗漏。</t>
+  </si>
+  <si>
+    <t>这一章首先谈的话题是“勇敢”。关于“勇敢”，《道德经》并不像我们一般认识那么简单，表达那么直白，它把“勇敢”分为“勇敢”和“勇于不敢”，这个说法的妙处我们后边再做解说。接着读这一章，大家会发现熟悉的语句“天网恢恢，疏而不漏”，其原文就出自第七十三章“天网恢恢，疏而不失”。我们中国人读失去的“失”啊，总觉得有点绕口，换了一个字，意思都是一模一样的。天网恢恢，疏而不漏，天道如此。庄子也讲过这样一段话，一个人做了亏心事之后，在客观世界上把有形的痕迹抹掉容易，可是抹不掉内心的痕迹。即便是不受客观世界的惩罚，也得受良知的惩罚。那么第七十三章的结尾，怎么得出“天网恢恢，失而不漏”的结论呢？是怎么过渡到“天网”、“天道”的呢？“勇于敢则杀”，毛泽东在《贺新郎·读史》这首词里面就讲：“铜铁炉中翻火焰，为问何时猜得？不过几千寒热。人世难逢开口笑，上疆场彼此弯弓月。流遍了，郊原血。”人类的历史都是在这种血与火的洗礼中前进的，老子在他那个时代，肯定也看到过这种情况。“勇于敢则杀”，也包括很多违背了国家法律法令的不法之徒，从直观地来看，也是属于勇敢，“勇于敢则杀”。“勇于不敢则活”，“勇于不敢”直观上看上去，我们把它叫做“懦弱”、“退缩”，但其实这样的“懦弱和退缩”还有另外的一类人，他们懂得保护自己的生命，以期谋得更大的成就与发展。其实，我们说懂得拒绝的人也是一种“勇于不敢”，有些该做的事情，勇敢去做；有些不该做的事情，勇于不敢，拒绝。老子接着说，“此两者，或利或害。”“此两者”指勇敢和勇于不敢。勇敢和勇于不敢这两种情况“或利或害”，就是说有时有利，有时有害，那到底何时有利，何时有害呢？谁能把握这个度呢？“天之所恶，孰知其故？”天呢，到底是喜欢还是厌恶？到底是怎么一回事？谁能够了解这里边的最根本的原因、缘故呢？“是以圣人犹难之”，就是再有智慧的人、有智慧的领导者，在这个方面也难以去理解清楚。所以你看这个认知啊，非常困难，到底是该杀还是该活，到底该怎么对待，这是一个非常难的选择。那老子是不是就放弃了对这个难题的解决呢？不是的，事实上，老子是认为，只有站在更高的视野才能解决这个困扰，也就是第四章说的“解其纷”。所以老子在下边就说，如果从天道的角度来认知这个事情是什么样呢？“天之道，不争而善胜”，不争斗，却能够获得胜利，这是符合天道的。“不言而善应”，要行不言之教，不是老去命令、政令，大家对他反而非常支持，非常响应。言教不如身教，“不召而自来”，大家自然而然就聚拢到你的麾下，这是符合天道的。“繟然而善谋”，“繟”就是坦然、从容。天道看不出来痕迹，从从容容地向那个方向发展，就像一个善于谋划的人一样，不露痕迹地谋划。所以后面就讲“天网恢恢，疏而不失”，天网虽然好像有很多疏漏，但是最后你会发现，这天道如此，天网恢恢，疏而不漏。我们中国人经常把这个讲做“人在做天在看”、“为人别做亏心事，古往今来放过谁。”到这里，逻辑就逐渐清晰了：天道不争，不强制，自然而然，所以为民，不能滥用所谓勇敢；为王，也不能滥用强制，这都是不符合天道的，不符合天道，则是必然要失败的，也就是讲“天网恢恢，疏而不失”。所有违逆天道的所谓“勇敢”最后都会受到惩罚，天网虽然好像有很多疏漏，但是最后你会发现，这天道如此，天网恢恢，疏而不漏。关于这一点，我们再引证下孔子这句话：“人之生也直，罔之生也幸而免”，就更清楚了。意思就是那些不正直的勇于敢者、对抗天道天理的人，也许会侥幸漏掉一时，但终究逃不脱天道天理的惩罚。孔子的真正意义在于，若靠侥幸活着，你是活不好的。而老子对于敢对抗天道天理的人、与天争胜的人，警告更为严厉：“天网恢恢，疏而不漏。”换句话说就是“人在做天在看”、“为人别做亏心事，古往今来放过谁。</t>
+  </si>
+  <si>
+    <t>第七十四章</t>
+  </si>
+  <si>
+    <t>民不畏死，奈何以死惧之？若使民常畏死，而为奇者吾得执而杀之，孰敢？常有司杀者杀，夫代司杀者杀，是谓代大匠斫。夫代大匠斫者，希有不伤其手矣。</t>
+  </si>
+  <si>
+    <t>人民不畏惧死亡，为什么还要用死亡来吓唬他们？如果使人民都经常性地、普遍性地畏惧死亡，而为非作歹的人我们可以把他抓来杀掉，那么谁还敢胡作非为？常有专管杀人的去执行杀人的任务，代替专管杀人的去杀人，就是代替大工匠去做砍斫的工作。代替大工匠去砍斫，很少有不伤到自己手的。</t>
+  </si>
+  <si>
+    <t>七十四章开头这句话，在讲什么呢？“民不畏死，奈何以死惧之？”假如这国家的人民都不怕死了，都感觉到生无可恋了，你还能有什么方法去管理他们呢？上一章不是说过吗，“狎其所居，厌其所生”，百姓感觉到压力太大，感觉到生不如死，那就会产生“民不畏死”的情况。这个时候，你拿死去吓唬他还有什么用呢？毛泽东在《别了，司徒雷登》中引用过这一句，并引申说，“中国人死都不怕，还怕困难吗？”接着老先生做了一个假设，“若使民常畏死”，假如这个国家的人民经常地、普遍性地害怕死，老百姓对生活抱有憧憬和希望，这个时候，如果有搞幺蛾子的人，铤而走险犯法的人，“而为奇者吾得执而杀之”，做领导的、做统治者的，把这些人逮过来杀掉了。“孰敢”，没有人会响应这些人，大家不都不吭声了，国家也就恢复了平和、安定。大家注意，这话里暗含着一种假设，事实是什么呢？老百姓生活没有希望，不畏惧死亡。这时候，你杀的人越多，反抗的人越多；镇压得越多，起来呼应的人更多。所以，老子说你管理靠镇压是不行的，这不是根本的方法。历史上还有比秦朝法令更严苛、更严酷的时代吗？满大街都是被砍断手脚的人，严刑重罚，稍有违犯，立马严惩。最终，大家不还是起来造反了吗？秦朝之前，老先生就已经提醒过，靠残酷的镇压是不管用的，这不是处理问题的根本方法。下面上升到了更高层面，“常有司杀者杀”，大家知道，我们讲“秋后问斩”。秋天是代表肃杀的，杀人的时候是在秋天，这个代表符合天道、天杀。《道德经》的这句话是说，人的生死是由天来司管的。再退一步讲，国家也是按照国家的法令、按照符合道的方式制定的法律，来约束人的。当然这句话就《道德经》的本身而言，是在讲天操管着人的生杀予夺大权，人没有这个权力去决定别人生死的，即便是有的话，也应该有专门的部门来管。“夫代司杀者杀”，代天来杀人，这叫什么？“代大匠斫”，我们知道木匠的锛凿斧锯别人是不能动的，太锋利了，只能他们自己使用。你不熟悉这一行，你不懂怎么使用，你代替他们，“希有不伤其手矣”，哪会有不伤到自己的？老先生拿这个来做类比：你应该不用这些东西，不善于用这些东西，你越俎代庖，那么你自己肯定也会受伤的。因此，只用杀戮、镇压的方式，是不符合天道的，对自己的统治、领导也有着重大的损伤。这段话其实对统治者提出的警告：靠镇压的政策、残杀的政策，也会影响威胁到自己的统治，不要相信武力能解决一切问题。三十五章讲“执大象，天下往。往而不害，安平太。”应该用符合“道”的方式来管理国家，以民为本，注重根基，这样才能够和谐相处，才能够“安”、“平”、“太”。</t>
+  </si>
+  <si>
+    <t>第七十五章</t>
+  </si>
+  <si>
+    <t>民之饥，以其上食税之多，是以饥。民之难治，以其上之有为，是以难治。民之轻死，以其求生之厚，是以轻死。夫唯无以生为者，是贤于贵生。</t>
+  </si>
+  <si>
+    <t>人民之所以饥饿，是因为统治者收取挥霍的税负太多，所以人民饥饿。人民之所以难以治理，是因为统治者总是胡为、妄为，所以人民难以治理。人民之所以不怕死，是因为统治者所求奉养过多，所以人民不怕死。不把自己生命看得绝对重要的，不搜刮剥夺人民以奉养自己生命的，才是胜过了贵养厚养自己生命的人。</t>
+  </si>
+  <si>
+    <t>这一章的核心话题还是“民”，解释了三个问题。第一，百姓为什么饥寒交迫；第二，百姓为什么难以治理；第三百姓为什么不怕死。解释完三个内容，然后对领导者、统治者提出要求。“民之饥，以其上食税之多”，百姓为什么饥寒交迫？“上”，上面的领导者、统治者，“食税”，收的税太多了，而且收的税都被这些人挥霍。“民之难治，以其上之有为”，百姓为什么难以治理呢？原因不在他们这儿，是因为上边胡来、瞎折腾。在《道德经》里，“有为”这个词就是妄为，胡折腾，上边老瞎折腾，就把民心折腾乱了。“信不足焉，有不信焉”，折腾得多了，讲的话也不诚信了，也失去百姓的信任，说什么都没用了。“是以难治”，“是”，“这是”的意思。这话讲得就比较理性，你老说他们是刁民，老在他们身上找，其实这原因就在自己的“有为”。老子对坐在对面的那些领导者、统治者就讲，你得找到真正的原因，百姓为什么饥寒交迫？你们收税收得太多了，收的税都被挥霍了。百姓为什么难以治理？你们整天瞎折腾，胡来妄为，把民心搞乱了。“民之轻死，以其求生之厚”。“其”指谁？领导者、统治者。百姓为什么轻死，把死不当一回事？是因为你们这些统治者，把自己的生命看得那么重要，不惜用剥夺的方式积累财富，花天酒地，穷奢极欲，这财富都聚积在他们自己手里，老百姓难以生存。就像国民党时期，财富都积累在“四大家族”手中，很少的人占有了绝大部分的财富，底下的人都生活在水深火热之中。当你“求生之厚”的时候，底下的百姓就觉得没什么活路和希望了，也就不把死当一回事，“是以轻死”。那么应该怎么做呢？“夫唯无以生为者”，不要把自己的生命看作是绝对重要的。不要把财富、好吃的好用的，全都集中在自己这儿来，认为只有自己的生命才是生命，对别人的生命、生存视而不见，感到无足轻重。不把聚敛、穷奢极欲当作生命的重要的部分，这个就是“贤于贵生”。百姓为什么饥寒交迫？上食税之多；为什么难以治理？上面胡来妄为；为什么不怕死？求生之厚。这章三个并列句，像诗一样的语言，讲得又非常深刻、非常理性。把七十五章和七十四章结合起来理解，我们就能发现，老先生苦口婆心地劝坐在对面的那些领导者、统治者：你们要对自己国家的人民好一点，否则啊，他们日子过不好，你们的日子也不安稳，你们只靠这种高压的政策，这不是解决问题的根本的方法。我们完全可以说在这几章里看到了《道德经》的“真实面目”，很多话是针对那些统治者讲的，苦口婆心地劝他们，应该怎么样对待这个国家的人民，才能使国家长久地、持续地发展。</t>
+  </si>
+  <si>
+    <t>第七十六章</t>
+  </si>
+  <si>
+    <t>人之生也柔弱，其死也坚强。万物草木之生也柔脆，其死也枯槁。故坚强者死之徒，柔弱者生之徒。是以兵强则不胜，木强则折。强大处下，柔弱处上。</t>
+  </si>
+  <si>
+    <t>人活着的时候身体柔软，死之后身体便会僵硬。万物草木活着的时候形质柔软，死后变得干枯。所以坚强的东西属于死的那一类，柔弱的东西属于生的那一类。所以穷兵黩武一定会遭受灭亡，树木坚硬就会一折就断。总认为自己强大的、夸耀自己强大的，反而会处在下面；懂得柔弱、谦逊的，反而会居于上面。</t>
+  </si>
+  <si>
+    <t>现在我们来说一下第七十六章，王弼本子的编辑是有着内在逻辑的。前两章，老先生劝统治者，不要用这种“强”的方式、镇压的方式来实施自己的统治，那么应该怎么做呢？要懂得以柔克刚、强大处下，这样才能形成一种和谐。有的人确实是没有认真地读这本书的原文，他们认为《道德经》是一个弱者斗争的哲学，这是不了解坐在老子对面的向他提问的那些人，他们并不是一般的平民，而是手握权力的领导者、统治者。要站在这个层面来理解第七十六章，知道他这些话是对是对那些认为自己自身或者自己国家很强大的统治者们讲的。老子劝他们用“柔弱”的方式来实施自己的统治，这个是非常有智慧的，这个非常能够体现老先生的慈悲仁爱之心。这一章强调两个字“柔弱”，所以一开始讲“人之生也柔弱”，最后强调“强大处下，柔弱处上”。“人之生也柔弱，其死也坚强。”人活着的时候是什么状态？柔韧性非常好。我们看跳舞的、练杂技的，就觉得这柔韧性好。柔弱柔软，这是生命昂扬、鲜活的状态。而人死的时候是什么样的一种情况呢？硬了、僵了，“其死也坚强”。老子首先拿人的生命的状态来说明柔弱具有的意义。如果这个问题大家觉得还没有理解到位，再换一个角度来理解。在苏州金鸡湖苏州新区里曾经出现过一尊老子的雕像，这尊雕像太丑陋了，老子张着嘴，吐着舌头，一颗门牙。很多人很不理解，心里想有大智慧的老子，怎么会是这样的形象，还有人打趣说，这个老子是来卖萌的……这个雕塑者姓田，他就站出来解释说，我这个雕塑叫“刚柔”，它的出处是说，当时孔子见老子的时候，老子没有给他多说什么，张开嘴巴让孔子看了看。孔子一看就明白了，老子当时已经都七十多岁了，牙早掉光了，但是舌头还在，讲的就是“柔弱更长久”的意思。雕塑者说“刚柔”倒没错，但是这段话不是出自正史，记载的也不是指孔子和老子之间的事，其实是当年老子毕业的时候，跟自己的老师讲的。您有什么送给我？老师也没说话，张开嘴巴给他看了看，老子就看明白了，老师年纪大了，牙掉光了，但舌头还在。牙齿是坚硬之物，到一定年龄就掉了，舌头没事，柔软更长久。所以，柔弱更有生命力、更长久，柔弱是生命的状态，而强硬、僵硬是死亡的状态。这是第一个，拿人来做比方。第二个以草木为例，“其生也柔脆，其死也枯槁。”我们以草为例，李世民在诗里说“疾风知劲草”。草，风往这边吹了，它这边倒，往那边吹了，往那边倒，风走了，它再站起来坚守脚下这片土地。什么时候草坚定了，不随风倒了，那草就死了、枯了。正因为草很柔弱，所以它能迎风起舞；正因为草很柔弱，所以“天涯何处无芳草”。下面得出结论，“坚强者死之徒”，“徒”就是那一类。认为自己坚强、强硬、强暴，其实这是属于走向死亡一类的。而“柔弱者生之徒”，柔软、柔韧，这是富有生命力的表现。沿着这个方向再往下推，就说到了人类社会，“兵强则不胜”，一个国家穷兵黩武，认为自己的军事力量强大，稍一不如意就动用军队发起战争，“国虽大，好战必亡。”“兵强则不胜”，不是说你这场战役打不胜，但穷兵黩武的最后结果一定是失败的。历史上多少强大的帝国，比如说秦朝，被称为“虎狼之师”，最后的结果怎么样？“兵强则不胜”“木强则折”，这个“强”就是僵硬。春天，万物复苏，一根细小的柳枝也很有韧性，很难去折断它。秋天，柳枝水分干枯，好像很强硬地挺在那里，可是它内在枯槁了，一折就断。小的时候，我在石厂里边劳动，砸石子做铺路之用。那时候我就见了一个非常奇怪的现象，石场里石匠用的榔头把儿，一种是很粗大的木棒，看着很稳定；一种是很细的木棒，看起来很危险。我去问那个石匠，怎么用这么细的斧柄？他说这个东西叫“水曲柳”，你别看它细，但它韧性非常好，你用多大劲儿也没事儿。所以每当读到这个地方，我就想起这个事情。“木强则折”，看似强大僵硬，其实没有了韧性，它就没有了生命力，一碰就断掉了。讲完这个了，再看这里边两层的推论。第一层推论：“坚强者死之徒，柔弱者生之徒”，然后推到人类社会，表达他对用这种强横的方式予以统治、用这种强横的方式予以领导的不认同，指出这个方式的致命的弱点。战争中也是如此，“兵强则不胜”，就像“木强则折”一样。讲完这个，推论到第二层：“强大处下”，老是炫耀自己强大，去任意地凌辱别的小的国家；自己有了高的位置，可以盛气颐指，不符合道，这是向死亡方向去发展。“强大处下，柔弱处上。”懂得以柔克刚，懂得以退为进，懂得谦逊谦让，这才是符合道的，才是真正有智慧的表现。第六十一章，“天下之牝，牝常以静胜牡”，讲以静制动、以柔克刚的道理。所以对人生来讲，强大、用强，这事儿大家都知道，也并不是说老子对这个东西一味排斥，因为人生有的时候强也是需要的，但是大家都把这个事情推到极端了，认为“强”是解决问题唯一的方式，所以，老先生在面对那些领导者、统治者的时候，苦口婆心，形象具体地讲述柔弱处下的道理。我们现在读这一章，也可以把智慧扩大到我们的为人处事，不要只认为用强才能解决问题，要懂得强弱两者的相辅相成，老去逞强，不是真正智慧的做法，这是只是智慧的一个方面，而“以柔克刚”才是一种真正高级的智慧。适当的时候，我们要懂得示弱，这是我们在和社会、和别人打交道的时候，非常重要的智慧，有重要的启迪。</t>
+  </si>
+  <si>
+    <t>第七十七章</t>
+  </si>
+  <si>
+    <t>天之道，其犹张弓与？高者抑之，下者举之；有余者损之，不足者补之。天之道，损有余而补不足。人之道则不然，损不足以奉有余。孰能有余以奉天下？唯有道者。是以圣人为而不恃，功成而不处，其不欲见贤。</t>
+  </si>
+  <si>
+    <t>天的规则，不就像拉弓射箭一样吗？瞄得高了就往下压，瞄得低了就往上抬；有多余的就减少，不足的就给补充。天的规则，减损有余的来补充不足的。人类社会的规则不是这样，减损不足的来供奉有余的。谁能让那些有余的人奉献出来为天下做贡献？只有得道的人。所以圣人把事情做成而不把这当成一种倚仗、凭借甚至勒索的手段，有了功劳却不居功自傲，不想表现自己的贤能。</t>
+  </si>
+  <si>
+    <t>第七十七章，这一章重要在什么地方呢？大家都知道“马太效应”，马太效应出自《圣经·马太福音》，直观的解释是穷者越穷，富者越富，越穷越倒霉，越富反而财富滚滚而来，这也是我们人类社会大家都认同的一个普遍的现象。怎么解决这个问题呢？怎么样解决这样的一种贫富的两极分化呢？《道德经》很早就给出了一个方案，所以我们把这一章叫什么呢？叫“张弓效应”。在这一章里边我们可以看到一句话，这句话和马太效应讲的意思是一样的，叫“损不足以奉有余”。“天之道，其犹张弓与？”老子在这一章里面就讲，说天道就像拉弓射箭一样，拉弓射箭要有的放矢。这个箭，你瞄得高了，往下压一下；低了，往起抬一下，“高者抑之，下者举之”。沿着这样的一个比喻，自然就得出这个结论，对于人类社会也是这样，“有余者损之，不足者补之”。财富多的人应该拿出更多帮助这些不足的人，收入高的人当然应该多交税。这就是“天道”，天道如此，天道均衡，“天之道，损有余而补不足”。可是人道，这个社会是怎么做的呢？“人之道则不然”，老子对他当时的情况看得很清楚，财富都掌握在少数人的手里，“损不足以奉有余”，越是不足的、穷的，反而被压榨得越厉害，富的反而越来越富。于是，老子面对那些统治者讲，一个好的领导者、统治者应该向“圣人”的方面去发展，做一个好王。大家注意古代那个“圣”的写法，王上边并列两个字，耳和口，听得进别人的意见，说话温暖。通达事理的王，称之为圣。老子就对他们讲，你们应该向这个方面努力，怎么做呢？“有余以奉天下”，让那些更富的人来为这个天下做贡献。“唯有道者”，就是了解道的人，按照道的方式去行事的人，才能做到这一点。说到这儿，我就得给大家说一下我们的文化背景。一句话大家都熟，叫“不患寡而患不均”，贫富不均，很容易产生问题。历史上那些农民起义，他们用的口号，你也能感觉到这一点，比如说王小波、李顺，“均贫富等贵贱”；比如说黄巢，“冲天平均大将军”……从社会心理能分析到这一点。所以老先生就讲，统治者、领导者，什么样的人才能够真正注意到、做到让贫穷的得以扶持，让富有的贡献更多呢？“唯有道者”，“是以圣人”。“是以圣人为而不恃，功成而不处，其不欲见贤。”一个好的领导者，“为而不恃”，他把这件事情做了，有作为了，却不把这个当作一种倚仗、凭借甚至勒索的手段。“功成而不处”，不居功自傲，“不欲见贤”，不想表现出自己的这种贤能贤明。这是有道者的表现，懂得让天下向共同富裕的方面发展，让那些先富起来的人懂得奉养天下，哪怕是把这些做成了，也不居功自傲，因为他们知道，这只是按照道的方式来做的。</t>
+  </si>
+  <si>
+    <t>第七十八章</t>
+  </si>
+  <si>
+    <t>天下莫柔弱于水，而攻坚强者莫之能胜，其无以易之。弱之胜强，柔之胜刚，天下莫不知，莫能行。是以圣人云：受国之垢，是谓社稷主；受国不祥，是为天下王。正言若反。</t>
+  </si>
+  <si>
+    <t>天下没有比水更柔弱的了，但攻克坚强的东西却没有能胜过它的，没有什么东西可以代替水。柔弱胜过刚强的道理，天下都知道，但不能真正做到。所以圣人说：能忍受全国的屈辱，才能做社稷的君主；能承受全国的灾难，才能成为天下的君王。符合正道的话都好像反话一样。</t>
+  </si>
+  <si>
+    <t>第七十八章体现了这本书里的一个非常重要的理念，“善于处下”。这些内容我们之前都有过接触，甚至直接引用七十八章做过讲解，所以这一章我们并不需要花费太多的时间来解释，大家也能够明了。“天下莫柔弱于水，而攻坚强者莫之能胜”，天下没有什么东西比水更柔弱了，你拿什么容器装，它就是什么样，随方就圆。但天下也没有什么东西比水的力量更强大了，攻无不克，战无不胜。水就是以柔克刚、以弱胜强的最好的形象的代表。“以其无以易之”，因为没有什么东西能够替代水，天下最柔弱的东西，它力量又最为强大，最能够体现柔弱胜刚强的道理。“弱之胜强，柔之胜刚，天下莫不知，莫能行。”天下都知道，这东西表面上看似柔弱，但发挥作用的时候力量太强大了，但是真的要这样却非常不容易，为什么？人都有脾气，“柔弱胜刚强”得懂得忍耐、等待，忍耐是我们人最难练的一种功夫。水滴锲而不舍方能穿石，一条溪流不舍昼夜，慢慢积累，等待时机，才能发挥大用。“柔弱胜刚强”也是需要条件的，只是老子没有明说。“是以圣人云”，我再给大家强调一下，在老子心里，以前有很多好的统治者、有智慧的领导者，他称其为“圣人”，让大家向他们学习。我们在前面谈到过，他的很多话并不是原创的，是他引用的以前的圣人的，下边这话就表达得非常明确，所以这些圣人讲，“受国之垢”“受国不祥”。这两句话就是《道德经》里边从头至尾强调的，就是我们经常讲的善于处下。古往今来，夺得天下的表面看是一家一姓，实际上不都是一个团队吗？用我们现在的话讲是一个党派。什么样的团队，什么样的党派才能夺得天下，并且坐得了江山呢？之前，我们在第八章讲“处众人之所恶”时，也拿这个地方作为印证。吃苦在前，享受在后，有困难还得担着，有错误勇于改正，这不就是“受国之垢”“受国不祥”吗？所以真正想要夺得天下，坐稳江山，也就是所谓“处其上”，首先要懂得“处其下”，要“受国之垢”，要能忍受别人忍受不了的艰难困苦，要能承受别人承受不了的屈辱诟骂，这样才能成为江山社稷的主人。“受国不祥，是为天下王。”有灾难有困难，你别跑，要挺身而出，勇于担当，有错误要勇于承认，勇于改正。毛泽东把共产党的宗旨概括为五个字，叫“为人民服务”。两千多年前的“受国之垢”，“受国不祥”，“处众人之所恶”，两千多年后的“为人民服务”，这本质上的意思不是一样的吗？这就是《道德经》里面从头强调的，也是古往今来的大道。我们在讲第十四章的时候说过一句话，“执古之道以御今之有”。了解古往今来的大道，我们才能更好地做好今天的事情。读到这儿大家就会发现，这《道德经》里边蕴含着古往今来的大道，蕴含着一个人、一个团队、一个党派成功的最深的密码，值得大家认真地品味。总结上面这个表达的方式叫什么呢？叫“正言若反”，也就是第四十章讲的“反者，道之动”。看着是讲反话，大家都不愿意去做的事情：“受国之垢”，“受国之不祥”，“处众人之所恶”，可实际上，这才是能够让我们“处上”、取得成功的真正的智慧与奥妙。看似好像说的反话，其实深刻的道理就在这里边。</t>
+  </si>
+  <si>
+    <t>第七十九章</t>
+  </si>
+  <si>
+    <t>和大怨，必有余怨，安可以为善？是以圣人执左契，而不责于人。有德司契，无德司彻。天道无亲，常与善人。</t>
+  </si>
+  <si>
+    <t>调和了大的矛盾，也必定会有遗留的怨恨，这怎么能是妥善的方法呢？所以圣人收执借据却不苛责别人偿还。有德的人就像执左契而不责于人的，无德的人就像掌管税收的人那样严苛残酷。天道没有偏私，规律给予善于此道的人。</t>
+  </si>
+  <si>
+    <t>针对坐在对面的那些统治者、领导者，老子前面一直在讲，不要用高压的方式，要懂得用柔和的方式。如果一直用高压的方式，一直用“损不足以奉有余”的方式，这社会就积累了大的矛盾。老先生认为，有了这个矛盾之后，不管用什么方式解决，它都会遗留下很多的不满、埋怨、祸端。在这个基础上，我们才能够深入理解第七十九章的内容。这一章只有这么几句话，但道理非常丰富而深刻。“和大怨，必有余怨，安可以为善？”如果社会已经积累了大量的矛盾，即使用调和的方式，“和大怨”，可是，依旧会留下很多的这个埋怨、祸端。“安可以为善”？即使用和谐的方式，也不是一种善举，为什么呢？第六十四章讲“为之于未有，治之于未乱”，从一开始你就不应该让这社会积累了这么多的矛盾。我们之前举过晏子“救灾”的例子，其实针对我们目前的环境问题，也是一样。大家知道有一句话叫“反对先污染后治理”，你污染完了，你再治理，其难度之大，难以预料。“病来如山倒，病去如抽丝”，社会不也一样吗？积累了这么多复杂的矛盾，你老用调和的方式，你说现在已经柔和了、缓和了，但留下那么多的祸端，这当然不算是好的方法，不可以叫做善举。对应我们人际交往也是一样，我们不要本着“无所谓”的态度，想着跟别人、朋友之间有了裂痕，我们说以后自会解决的，事情往往没有我们想得那么简单。所以，平时做事就要小心，朋友之间要珍惜，家庭之间感情要珍惜，别真的等得了埋怨之后，再想办法去解决。这跟钉子钉在墙上一样，你拔出了钉子，那个眼还在。最好的“善”是什么？提前做出预防，“为之于未有，治之于未乱。”“是以圣人执左契，而不责于人。”有智慧的领导者、统治者，就像拿着契约的人。“左契”，契约，一撕两半，左边一个，右边一个，左边那个是借据。拿着这个契约借据而不责于人，不是天天去追着要，而是表达出圣人的一种宽容。老先生拿这个举例子，意思说，一个好的领导者，哪怕是你对大家都有恩德，对天下都有恩德，你别以为大家都欠你的，“不责于人”。所以“有德司契，无德司彻”，有德的人就像执左契而不责于人的人。“彻”，就是税官，收税的。这是代表着两种态度，一种是和缓的态度，另一种是苛刻的残酷的态度。所以平日里，应该像“有德司契”的样子，那就不会积累那么多的埋怨。反之如果像那个税官一样，苛捐杂税多，还步步紧逼，不肯放松，老子认为这是无德的表现，这样会留下大怨！下面两句话很容易引起误解，“天道无亲，常与善人。”在第五章曾经讲过，“天地不仁，以万物为刍狗”，天地是没有感情的，它并不因为你做了好事，就来奖赏你，也不因为你做了坏事，便来惩罚你。既然“天道无亲”，那为什么“常与善人”呢？又怎么把这个规律规则让那些善人能够理解，并按照它去做呢？这个事情我换一个角度让大家来理解，美国有一个报社的主编，他经常接到读者的来信，读者来信都反映一个什么问题呢？做好事不得好报。特别是其中有一个小孩就说，我弟弟什么都不干，我天天在家里干活那么勤奋，可是我妈妈就把好的东西都给我弟弟，就是喜欢他，这不是不公平吗？上帝在哪里？上帝怎么能够这么不公平？这个主编呢，一直不知道怎么解释这个问题。后来有一次，他参加了一个婚礼，新郎新娘互戴戒指，出现问题了，两人把戒指戴错手了，本来应该戴到左手，但都戴到了右手上。主持婚礼的牧师就用一种诙谐的方式说，右手已经够完美了，不用再修饰了，还是用戒指来装扮左手吧。这个主编就在那个时候领悟到一个道理：一个已经够好的人，你不用去奖励他，他已经够完美，最大的奖励是什么？就是他已经成为一个好人。天道对好人最大的奖赏是什么？放到西方的文化里边来讲，上帝对好人最大的奖赏是什么？就是让你成为一个好人，这已经就是最大的回报了。这里讲“天道无亲”，它是说天道是公平的，没有偏私的。让一个人成为一个好人，那么一个好人吃点亏，这是正常的，因为你作为一个好人，这已经就是最大“道”给你的回报了。天道是公平的，没有亲疏之分，但是，它把规律、规则赋予了那些做善事的人。做一个好人，我们免去了很多的祸端祸殃，成为一个好人——这就是对我们做好人的最大的回报，不需要其他的东西来“修饰”了。所以用“有德司契”的境界去管理、去治国，就不会有大怨；用“有德司契”的境界去为人、去处事，会让你成为一个“好人”，“福虽未至，祸已远离”。</t>
+  </si>
+  <si>
+    <t>第八十章</t>
+  </si>
+  <si>
+    <t>小国寡民，使有什伯之器而不用，使民重死而不远徙。虽有舟舆，无所乘之；虽有甲兵，无所陈之；使人复结绳而用之。甘其食，美其服，安其居，乐其俗。邻国相望，鸡犬之声相闻，民至老死不相往来。</t>
+  </si>
+  <si>
+    <t>（理想的国家是这样的：）国土小且百姓少，就算有十倍百倍于人力的工具器械也不实用，让人民都看重死亡而不远离故乡。即使有船有车，也没有人去乘坐；即使有盔甲兵器，也没有机会陈列；使人民回归到结绳记事的淳朴状态。觉得自己的食物是香甜的，觉得自己的衣服是很美的，安于自己的居所，乐于自己的风俗习惯。邻国可以相互望见，鸡鸣狗叫之声可以相互听见，人民至死也不来往。</t>
+  </si>
+  <si>
+    <t>第八十章历来被认为是老子思想中的一个非常重要的部分——老子的理想国。大家一听都知道，在哲学上，柏拉图有《理想国》，后来就出现了康帕内拉的《太阳城》、莫尔的《乌托邦》，就是对理想社会的设定。哲学家设定理想社会都有一个非常有趣的现象：要了解人类的未来啊，先看人类的开始。因为哲学里边讲否定之否定的规律，就讲事物到最后都回归到出发点，严格地讲叫“仿佛回到出发点的运动”，是在更高的层次上重复第一阶段的某些特征，所以我们看看人类的开始。人类开始的时候，大家是平等的，所以未来人类社会的也是平等的。你看三个阶段：平等——不平等——平等。沿着这样一种哲学思路，我们来理解老子这个小国寡民，也就知道，这也是他的一种空想，但是，这种空想代表了他理想的寄托。他理想的这个国家是什么样子？别天天老打仗，别弄那么多人，大家不要经常地过多地交往，过多交往就会产生的矛盾、冲突、隔阂、战争，他想让大家和平地和谐相处，所以要把这个国家变成一个“村”。“小国寡民”，让这个国家变小，人民变少，大家就像在一个乡村里边生活。在小国寡民的理念下，他就要限定，要这样做，即使有各种器皿也不用，为什么不用呢？因为在中国的历史上有一个说法，其实和西方后来的一些思想也遥相呼应。西方有一个哲学家叫卢梭，法国的启蒙思想家，当年给法国的自然科学院写过一篇论文，获了奖，叫《科学和技术的进步使人类道德堕落》，在中国历史上也有很多人认可这种看法。庄子文章里就讲了一件关于“抱瓮老人”的事：说一次孔子带着学生去游学，子贡就看见一个老头，有这个先进的工具不用，抱着瓦罐去井里打水。当时的先进的工具是什么呢？就是辘轳，现在大家都看不见了。自己跑到井里边抱着瓦罐去打水，子贡就觉得很奇怪：这老先生怎么这么笨，辘轳就在旁边，摇一摇不就上来了吗？你自己下去干嘛呢？老先生就郑重其事地跟他讲，我的老师讲过，人如果使用机器就会有投机取巧之心，为了保持我的朴素的道德，所以我不用这个机器，不会有投机取巧之心。大家仔细思量，我们使用的工具，确实对我们的思维的方式、性格也有很大的影响，所以《道德经》讲什伯之器，不用，用最简单的工具，保持简单的心灵，保持朴素的品德。当年曾国藩在做官的时候，经常给家里边写信，告诉他儿子，你每天得下地劳动；告诉他女儿，你得给我做鞋。其实，曾国藩在乎的不是地，不是鞋子，他是觉得这样的方式，会让子女形成他要的那种性格、品德。这个东西倒是真值得研究，人类使用的工具在不断进步，千奇百怪，人要想回归到朴素的道德，就很困难。“使民重死而不远徙”，人离开家乡之后成为流民，那么很多方面就无法保证。我们前面也讲过，这国家到处都是流民，它无法稳定，因为“无恒产者无恒心”，所以你离开了自己家乡的土地，成为一个流民，这就没有办法回归到一个小国寡民的所需要的品德和素质。下边一样，“虽有舟舆，无所乘之”，这也是工具，有这个船，有这个车，不要经常去坐。我们现在也有很多人领悟出来了，打趣说，汽车是毒药，自行车是泻药，走路是补药。现在，很多人也确实奇怪，开车节省出时间了，然后回家在跑步机上跑步，这个东西确实是挺难理解，有时间走走路，不也是一种锻炼吗？下边这句话重要了，是这段话里要表达的核心意思，“虽有甲兵，无所陈之”，有军队没地方放。我不打仗，我要军队干嘛？大家注意，咱们中国的“国”字，原来氏族的时候，它是没有边界、国界的。“国”字外面这个方框是代表着城墙，“国”字的繁体字，最常用的是哪个呢？就是里边的“或”。大家仔细琢磨“或”，你看它是什么？用武器，那个“戈”不就是武器吗？用武器来看守一定的人口。这国家一出现，国家一大了，它就需要军队，所以老子为什么要小国寡民呢？不要军队，大家干脆都别打仗。在他的理想国里是没有军队存在的位置的，反对战争，祈求和平。《淮南子》里也讲了这样一件事，大禹的父亲夏鲧治国的时候，修了一座很大的城池，弄了很多的军队，结果四海有反心，诸侯都准备起来背叛。大禹即位后怎么处理的呢？他把城拆了，把军队散了，结果四海归心。其实这故事表达的也是这个意思，《淮南子》主要解读道家思想，举的这个例子也是用来印证《道德经》里讲的这一理念。“使人复结绳而用之”，有的本子叫做“民”，都一样。百姓不再用文字了，人类最早不就结绳记事吗？据说当年文字出现的时候，天雨粟，鬼夜哭。当然我们这个文明延续到今天，受惠于文字太多了，但是《道德经》里说，文字有时候也让人变得复杂，有投机取巧之心。有的人说这老子是倒退，反对文明。其实大家要理解他的苦心，他主要是让人类回归到那种朴素的、平等的、和谐的、互相不冲突的理想国的状态。我们换一个角度给大家一个直观的印象，大家都知道陶渊明的《桃花源记》，那里的人都是什么样？都活得非常的和谐，“甘其食”，吃什么都觉得很香，不挑剔。“美其服”，不是说穿着漂亮的衣服，是穿什么衣服都觉得很好，都觉得很开心。“安其居，乐其俗”，安居乐业，觉得自己那个风俗大家很喜欢，很开心。“邻国相望”，因为现在搞得这国家都跟一个村子一样，国与国之间不打仗了，邻国相望，离得很近，“鸡犬之声相闻”。读《桃花源记》，很多的时候，你能感觉到这一章的影子，“狗吠深巷里，鸡鸣桑树颠”。老子也给我们勾画了一个美丽的，看似平凡但不可企及的生活。当然，“民至老死不相往来”，不是强调不相往来，而是强调没冲突、不打仗。这一章的核心是这句话：“虽有甲兵，无所陈之。”春秋无义战，那时候战争此起彼伏，没一场是正义的战争，尸横遍野，血流成河。在这个背景下，老子就想这解决办法是什么呢？国家小一点，各过各的日子，不打仗。哲学家讲的理想国，不管是柏拉图的《理想国》、康帕内拉的《太阳城》、莫尔的《乌托邦》，还是老子讲的这个小国寡民，还是陶渊明讲的《桃花源记》，都代表着对纷乱社会的不满，都希望人类回归和谐相处的、没有冲突的、没有战争的状态。如果我们理解中国历史上的非常沉痛的两句诗，我们也就明白“小国寡民”的良苦之用心，这两句诗叫“宁做太平犬，不做乱世人”，宁可做太平世界的一条狗，也不做乱世冲突、战争频仍时候的人，因为这时候人活得连狗都不如，没有尊严。所以我常讲，有些经常叫嚣战争的人，其实都是不懂战争。真正懂得战争的残忍，就知道这和平、平静，是多么可贵。大家上中学的时候学过一篇课文，叫《最可爱的人》，里边讲的一段话让人非常有同感。它说也许你正走在去上班的路上，也许你正背着书包走在上学的路上，你觉得这很平常，可是从朝鲜回来的人会告诉你，你是生活在幸福之中。经历过战争的人会告诉你，这种情况是生活在幸福之中。这对我们也有所启示，不能简单地说小国寡民是一个倒退，得看它的现实背景，得了解它的语境，我们才能真正地理解老子的用心，我们对这些历史上有智慧的人、有慈悲心肠的人，对他们才能有深深的敬佩。见到这样有智慧、有品德的人，我们身体不在鞠躬，心灵在鞠躬。读这样的书也是一样，我们应该有敬畏，在敬畏的基础上，认真阅读，认真品味，珍惜和平与幸福的生活。</t>
+  </si>
+  <si>
+    <t>第八十一章</t>
+  </si>
+  <si>
+    <t>信言不美，美言不信；善者不辩，辩者不善；知者不博，博者不知。圣人不积，既以为人，己愈有；既以与人，己愈多。天之道，利而不害；圣人之道，为而不争。</t>
+  </si>
+  <si>
+    <t>真诚的话不华美，漂亮的话不真诚；行善的人不去争辩，总是争辩的人不是良善的人；真正有智慧的人不认为自己博学，总是认为自己博学无所不知的人其实是没有智慧的。圣人不积累私藏，帮助别人的越多，自己越是充足；给予别人的越多，自己越是感觉获得的多。天道，利万物而不伤害；圣人之道，做好事情却不为自己争名夺利。</t>
+  </si>
+  <si>
+    <t>说起《道德经》的分章，大家一般认为最早是河上公以九九归一为神秘的数字指向，把它分成了八十一章。第八十一章可以看作是全书的总结，全书思想的总结和概括就是最后这两句话，“天之道，利而不害。”天道如此，人道应该效法天道，所以下一句“圣人之道，为而不争”，一个好的领导人、统治者是如此，对我们大家来讲也是如此。韩国有一个连任联合国秘书长的聪明人，叫潘基文。他在连任就职典礼上，开口讲的就是《道德经》的这两句话，只不过他引用的是这两句话中的八个字：“利而不害，为而不争。”我怎么做联合国秘书长？我对大家有利，不起坏心，为大家谋福利，“利而不害”。我把事情做了，不为自己争名夺利，“为而不争”。我们应该有一个非常深刻的体验：道家并不是消极的、被动的、什么事都不做。什么叫无为？“为而不争”是无为的一个重要的方面，这可以看作是全部《道德经》的核心的总结。我们回头去想，“上善若水”讲“善利万物而不争”；天道讲“为而不争”。这样我们就把整个的思想落地了，知道了《道德经》最后的核心落在什么地方。现在来看一下原文，“信言不美，美言不信”，真正诚信的话，不漂亮，只会讲漂亮话的，没诚信，过度漂亮的话里，往往隐含欺骗的内容，所以大家说，真理是朴素的，真理是赤裸裸的。“善者不辩，辩者不善”，真正善良的人，不老去争辩。庄子在他文章里边经常讲，老去靠争辩，争辩胜了，又能够体现什么？“善者不辩，辩者不善”，老去争辩，老为自己找借口，老觉得自己受了无尽的委屈，这个不是善良者的表现。“知者不博，博者不知”，一个有智慧的人，不是老是吹嘘自己渊博、博学、无所不知，老是吹嘘自己无所不知的人，其实是没有智慧的。下面就讲一个有智慧的领导者应该怎么去做事。“圣人不积”，一个有智慧的领导者，不是老想着去积累财富、有形的资产。“既以为人，己愈有”，什么叫做富？什么叫做有？我老去帮助别人，为别人做事，在给别人做事情，帮助别人的过程中，获得了无尽的快乐，这不是无形资产吗？这不是精神世界的充盈吗？“既以与人，己愈多”，给别人的越多，帮别人的越多，要财富发挥它的真正的作用，在“舍”的过程中反而自己得到更多。“既以为人，己愈有；既以与人，己愈多。”2014年习近平在斐济《斐济时报》发表署名文章，也用过这两句话。中国人喜欢双赢，帮助别人。我们的理念是什么？我们给别人做的事情越多，我们感觉到自己越富有；对别人帮得越多，感觉到自己获得的更多。所以我们经常讲，我们很多的快乐是在帮助别人成长，别人有困难的时候，我们帮扶的时候，感觉到自己的内心的充盈快乐。“为人”是什么？“与人”是什么？是善利。看似付出，自己反而获得更多，自己的精神世界也更为充盈。如果我们只一味地为自己积累财富，结果呢？我们经常讲一句话，叫穷得只剩下钱了，我们的物质世界越发达，财富越多，我们的精神家园就越花果飘零。“善利万物而不争”，这是全书的最后总结。不争什么？不争言语的漂亮，只为了它的实质；不为了争辩的胜利，只为它的真理；不吹嘘自己的知识的渊博，只让知识发挥它正确的作用；不积累那么多所谓的财富，而是让财富发挥它真正的作用，让我们的精神世界越来越充盈、越来越丰富。帮人越多，自己越富有；给人越多，自己获得越多。舍得、舍得，舍的同时，也是一种获得；帮人的过程，也是一种快乐。“既以为人，己愈有；既以与人，己愈多”，这两句话仔细思量，其即是天道。“天之道，利而不害”，天道如此，善利万物不起坏心。“圣人之道，为而不争”，把事情做了，不为自己争名夺利。“为而不争”和前面我们讲过的“善利万物而不争”、“生而不有，为而不恃，长而不宰”、“功成而弗居”、“衣养万物而不为主”，这些重要的语句遥相呼应。这样，我们就把思想穿成了一串珍珠，看清楚了这本书的真正的逻辑，也看清了这本书的“落脚点”。这些成为我们生活中的座右铭，指南针，对我们的思维方式、人生格局、精神境界都会有很大的启发和启迪。第八十一章的内容，我们解读完了。到这最后一章，我们看到这一章最后落在这句话上“圣人之道，为而不争”，可以清楚的看到这本经典的目的就是把士和王修养、培养成圣。这就是这本书的内在逻辑，也是老子的良苦用心。读这本经典要掌握以下几个关键性问题。一是《道德经》本质上是一本对话体，也就是对面坐着人问的问题。只不过老子在刻书时把对面坐的人是谁、问的什么问题都省略了，而只是把他当时给的答案概括、总结、提炼、升华形成的一本著作。当我们从书里找到士、王、圣这三类问问题的人时，也就很容易抓住问题的关键了。二是王弼本《道德经》哲学思维水平非常高。在第一章就提出有无相互统一思维方式的重要性，并指出“无”是全书的众妙之门，从而让我们清楚地知道了无为、无声、无色、无味、无色……在这本书中的重要性，也借此步入众妙之门。三是我们这种以经解经的方法前后参照，避免了八十一章本子的“碎片化”倾向，并且在通篇解读中发现了老子对他认为重要问题的强调方式：首先是用重复的方式强调。比如在第十章、第五十章都重复出现“生而不有，为而不恃，长而不宰”，并且在第二章、第三十四章也都出现类似的意思。其次是用首尾呼应的方式来强调，比如二十二章就是如此。其三是用正反两个方面的方式来强调一个观点的重要性，比如第六十七章就是如此。了解了上面这些导读的内容，我们再来听课、阅读，我们就会更深刻地了解这本书的深刻内容，这本“善建者不拔”的伟大经典指导下：“修之于身，其德乃真；修之于家，其德乃余；修之于乡，其德乃长；修之于国，其德乃丰；修之于天下，其德乃普。”当然即便是逐章解决了很多问题，讲的恐怕也是蜻蜓点水，就《道德经》而言，最重要的是大家自己的阅读和领悟。</t>
   </si>
 </sst>
 </file>
@@ -186,7 +1105,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,9 +1122,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -658,169 +1596,175 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1347,156 +2291,1431 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="23.75" defaultRowHeight="30" customHeight="1" outlineLevelCol="3"/>
+  <dimension ref="A1:E83"/>
+  <sheetFormatPr defaultColWidth="23.75" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="23.75" style="3" customWidth="1"/>
-    <col min="2" max="4" width="54.25" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="23.75" style="3" customWidth="1"/>
+    <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="54.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="56.875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="75.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="7.375" style="2" customWidth="1"/>
+    <col min="6" max="16383" width="23.75" style="2" customWidth="1"/>
+    <col min="16384" max="16384" width="23.75" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" ht="14.25" spans="1:5">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" customHeight="1" spans="1:4">
-      <c r="A2" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="2" s="2" customFormat="1" ht="384.75" spans="1:5">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:4">
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" ht="213.75" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:4">
+    </row>
+    <row r="4" ht="213.75" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="1:4">
+        <v>17</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" ht="213.75" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:4">
+        <v>21</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" ht="213.75" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:4">
+        <v>25</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" ht="199.5" spans="1:5">
       <c r="A7" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:4">
+        <v>29</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" ht="171" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:4">
+        <v>33</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" ht="199.5" spans="1:5">
       <c r="A9" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:4">
+        <v>35</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" ht="213.75" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="3" t="s">
         <v>38</v>
       </c>
+      <c r="B10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" ht="199.5" spans="1:5">
+      <c r="A11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" ht="199.5" spans="1:5">
+      <c r="A12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" ht="185.25" spans="1:5">
+      <c r="A13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" ht="185.25" spans="1:5">
+      <c r="A14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" ht="213.75" spans="1:5">
+      <c r="A15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" ht="213.75" spans="1:5">
+      <c r="A16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" ht="228" spans="1:5">
+      <c r="A17" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" ht="213.75" spans="1:5">
+      <c r="A18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" ht="213.75" spans="1:5">
+      <c r="A19" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" ht="199.5" spans="1:5">
+      <c r="A20" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" ht="185.25" spans="1:5">
+      <c r="A21" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" ht="242.25" spans="1:5">
+      <c r="A22" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" ht="213.75" spans="1:5">
+      <c r="A23" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" ht="213.75" spans="1:5">
+      <c r="A24" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" ht="199.5" spans="1:5">
+      <c r="A25" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" ht="199.5" spans="1:5">
+      <c r="A26" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" ht="213.75" spans="1:5">
+      <c r="A27" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" ht="213.75" spans="1:5">
+      <c r="A28" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" ht="228" spans="1:5">
+      <c r="A29" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" ht="213.75" spans="1:5">
+      <c r="A30" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" ht="228" spans="1:5">
+      <c r="A31" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" ht="213.75" spans="1:5">
+      <c r="A32" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" ht="213.75" spans="1:5">
+      <c r="A33" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" ht="213.75" spans="1:5">
+      <c r="A34" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" ht="199.5" spans="1:5">
+      <c r="A35" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" ht="199.5" spans="1:5">
+      <c r="A36" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" ht="185.25" spans="1:5">
+      <c r="A37" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" ht="213.75" spans="1:5">
+      <c r="A38" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" ht="171" spans="1:5">
+      <c r="A39" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" ht="228" spans="1:5">
+      <c r="A40" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="41" ht="213.75" spans="1:5">
+      <c r="A41" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="42" ht="171" spans="1:5">
+      <c r="A42" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="43" ht="409.5" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="44" ht="409.5" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="45" ht="409.5" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="46" ht="409.5" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="47" ht="409.5" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="48" ht="409.5" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="49" ht="409.5" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="50" ht="409.5" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="51" ht="409.5" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="52" ht="409.5" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="53" ht="409.5" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="54" ht="409.5" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="55" ht="409.5" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="56" ht="409.5" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="57" ht="409.5" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="58" ht="409.5" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="59" ht="409.5" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="60" ht="409.5" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="61" ht="409.5" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="62" ht="409.5" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="63" ht="409.5" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="64" ht="409.5" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="65" ht="409.5" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="66" ht="409.5" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="67" ht="409.5" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="68" ht="409.5" spans="1:5">
+      <c r="A68" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="69" ht="409.5" spans="1:5">
+      <c r="A69" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="70" ht="409.5" spans="1:5">
+      <c r="A70" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="71" ht="409.5" spans="1:5">
+      <c r="A71" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="72" ht="409.5" spans="1:5">
+      <c r="A72" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="73" ht="409.5" spans="1:5">
+      <c r="A73" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="74" ht="409.5" spans="1:5">
+      <c r="A74" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="75" ht="409.5" spans="1:5">
+      <c r="A75" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="76" ht="409.5" spans="1:5">
+      <c r="A76" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="77" ht="409.5" spans="1:5">
+      <c r="A77" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="78" ht="409.5" spans="1:5">
+      <c r="A78" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="79" ht="409.5" spans="1:5">
+      <c r="A79" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="80" ht="409.5" spans="1:5">
+      <c r="A80" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="81" ht="409.5" spans="1:5">
+      <c r="A81" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="82" ht="409.5" spans="1:5">
+      <c r="A82" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="83" ht="409.5" spans="1:5">
+      <c r="A83" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>162</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D9" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D42" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/book.xlsx
+++ b/book.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="336">
   <si>
     <t>chapter</t>
   </si>
@@ -71,7 +71,7 @@
 其书：经考古验证，帛书版最接近老子亲笔原貌，后人为了便于理解不断优化，后世多沿用魏晋王弼的经典本；书名因“道”“德”出现频率最高而得名；道落实到现实生活，包含目标、方向、规则、境界、边界、底线六个方面。其道：本书主要写给三类人——士（基层领导者，推十为一、把自己放在最后）、王（主要领导者，善用人者为之下）、圣（品德修养高、通情达理的领导者，为而不争、为大家谋福利）。书中讲的是治国之道、为官之道与人生之道，为逐章解读打下基础。</t>
   </si>
   <si>
-    <t>道经</t>
+    <t>道德经</t>
   </si>
   <si>
     <t>第一章</t>
@@ -85,6 +85,9 @@
   <si>
     <t>本章是《道德经》的门户，核心是“有”和“无”，特别强调常被忽略的“无”。道可道，非常道；名可名，非常名：道是最高、最全面的存在，用语言和逻辑讲出来就变成有局限的道，所以要借形象来领悟。无，名天地之始；有，名万物之母：天地起源时混沌无形，称为无；天地成形、万物出现，称为有。任何事物都有有和无两个方面，观察事物既要从“有”的角度看它的边界，也要从“无”的角度看它的妙处。
 此两者同出而异名，同谓之玄：能把有和无合起来理解，已是高级的思维水平，叫做玄；再进一步看到无形力量（精神、信仰、家风、作风等）的巨大作用，就是玄之又玄、众妙之门。韩鹏杰以“风”为形象：风无形却力量无尽，正如人的精神世界。老子提醒人们不要只看到金钱、财富等有形的东西，更要看到精神、思想、理想信念这些无形的力量；只重有形，物质越发达，精神家园就越花果飘零。</t>
+  </si>
+  <si>
+    <t>道经</t>
   </si>
   <si>
     <t>第二章</t>
@@ -1741,7 +1744,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1758,9 +1761,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2337,7 +2337,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" ht="213.75" spans="1:5">
+    <row r="3" ht="156.75" spans="1:5">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -2351,1371 +2351,1371 @@
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" ht="213.75" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" ht="156.75" spans="1:5">
       <c r="A4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" ht="213.75" spans="1:5">
+    </row>
+    <row r="5" ht="156.75" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" ht="213.75" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" ht="156.75" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" ht="199.5" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" ht="142.5" spans="1:5">
       <c r="A7" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" ht="171" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" ht="128.25" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" ht="199.5" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" ht="156.75" spans="1:5">
       <c r="A9" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" ht="213.75" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="156.75" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" ht="199.5" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" ht="142.5" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" ht="199.5" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" ht="156.75" spans="1:5">
       <c r="A12" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" ht="185.25" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" ht="142.5" spans="1:5">
       <c r="A13" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" ht="185.25" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" ht="142.5" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" ht="213.75" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" ht="156.75" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" ht="213.75" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" ht="171" spans="1:5">
       <c r="A16" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" ht="228" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" ht="213.75" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" ht="213.75" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" ht="156.75" spans="1:5">
       <c r="A18" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" ht="213.75" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" ht="156.75" spans="1:5">
       <c r="A19" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" ht="199.5" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" ht="142.5" spans="1:5">
       <c r="A20" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" ht="185.25" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" ht="156.75" spans="1:5">
       <c r="A21" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" ht="242.25" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" ht="185.25" spans="1:5">
       <c r="A22" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" ht="213.75" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" ht="156.75" spans="1:5">
       <c r="A23" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" ht="213.75" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" ht="171" spans="1:5">
       <c r="A24" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" ht="199.5" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" ht="156.75" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" ht="199.5" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" ht="156.75" spans="1:5">
       <c r="A26" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" ht="213.75" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" ht="156.75" spans="1:5">
       <c r="A27" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" ht="213.75" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" ht="156.75" spans="1:5">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" ht="228" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" ht="171" spans="1:5">
       <c r="A29" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" ht="213.75" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" ht="171" spans="1:5">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" ht="228" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" ht="171" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" ht="213.75" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" ht="156.75" spans="1:5">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" ht="213.75" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" ht="171" spans="1:5">
       <c r="A33" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" ht="213.75" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" ht="171" spans="1:5">
       <c r="A34" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" ht="199.5" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" ht="142.5" spans="1:5">
       <c r="A35" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" ht="199.5" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" ht="156.75" spans="1:5">
       <c r="A36" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" ht="185.25" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" ht="142.5" spans="1:5">
       <c r="A37" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" ht="213.75" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" ht="156.75" spans="1:5">
       <c r="A38" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" ht="171" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" ht="142.5" spans="1:5">
       <c r="A39" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" ht="228" spans="1:5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" ht="185.25" spans="1:5">
       <c r="A40" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="41" ht="213.75" spans="1:5">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="41" ht="156.75" spans="1:5">
       <c r="A41" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="42" ht="171" spans="1:5">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="42" ht="142.5" spans="1:5">
       <c r="A42" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="43" ht="409.5" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="B43" s="7" t="s">
+      <c r="A43" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="B43" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="C43" s="6" t="s">
         <v>174</v>
       </c>
+      <c r="D43" s="6" t="s">
+        <v>175</v>
+      </c>
       <c r="E43" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" ht="409.5" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="B44" s="7" t="s">
+      <c r="A44" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="B44" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="C44" s="6" t="s">
         <v>178</v>
       </c>
+      <c r="D44" s="6" t="s">
+        <v>179</v>
+      </c>
       <c r="E44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="45" ht="409.5" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B45" s="7" t="s">
+      <c r="A45" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="B45" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="C45" s="6" t="s">
         <v>182</v>
       </c>
+      <c r="D45" s="6" t="s">
+        <v>183</v>
+      </c>
       <c r="E45" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" ht="409.5" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="B46" s="7" t="s">
+      <c r="A46" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="B46" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="C46" s="6" t="s">
         <v>186</v>
       </c>
+      <c r="D46" s="6" t="s">
+        <v>187</v>
+      </c>
       <c r="E46" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" ht="409.5" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="B47" s="7" t="s">
+      <c r="A47" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="B47" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="C47" s="6" t="s">
         <v>190</v>
       </c>
+      <c r="D47" s="6" t="s">
+        <v>191</v>
+      </c>
       <c r="E47" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" ht="409.5" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="B48" s="7" t="s">
+      <c r="A48" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="B48" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="C48" s="6" t="s">
         <v>194</v>
       </c>
+      <c r="D48" s="6" t="s">
+        <v>195</v>
+      </c>
       <c r="E48" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49" ht="409.5" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="B49" s="7" t="s">
+      <c r="A49" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="B49" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="C49" s="6" t="s">
         <v>198</v>
       </c>
+      <c r="D49" s="6" t="s">
+        <v>199</v>
+      </c>
       <c r="E49" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="50" ht="409.5" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="B50" s="7" t="s">
+      <c r="A50" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="B50" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="C50" s="6" t="s">
         <v>202</v>
       </c>
+      <c r="D50" s="6" t="s">
+        <v>203</v>
+      </c>
       <c r="E50" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="51" ht="409.5" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B51" s="7" t="s">
+      <c r="A51" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="B51" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="C51" s="6" t="s">
         <v>206</v>
       </c>
+      <c r="D51" s="6" t="s">
+        <v>207</v>
+      </c>
       <c r="E51" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52" ht="409.5" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="B52" s="7" t="s">
+      <c r="A52" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="B52" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="C52" s="6" t="s">
         <v>210</v>
       </c>
+      <c r="D52" s="6" t="s">
+        <v>211</v>
+      </c>
       <c r="E52" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" ht="409.5" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="B53" s="7" t="s">
+      <c r="A53" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="B53" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="C53" s="6" t="s">
         <v>214</v>
       </c>
+      <c r="D53" s="6" t="s">
+        <v>215</v>
+      </c>
       <c r="E53" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54" ht="409.5" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="B54" s="7" t="s">
+      <c r="A54" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="B54" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="C54" s="6" t="s">
         <v>218</v>
       </c>
+      <c r="D54" s="6" t="s">
+        <v>219</v>
+      </c>
       <c r="E54" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" ht="409.5" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B55" s="7" t="s">
+      <c r="A55" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="B55" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="D55" s="7" t="s">
+      <c r="C55" s="6" t="s">
         <v>222</v>
       </c>
+      <c r="D55" s="6" t="s">
+        <v>223</v>
+      </c>
       <c r="E55" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" ht="409.5" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="B56" s="7" t="s">
+      <c r="A56" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="B56" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D56" s="7" t="s">
+      <c r="C56" s="6" t="s">
         <v>226</v>
       </c>
+      <c r="D56" s="6" t="s">
+        <v>227</v>
+      </c>
       <c r="E56" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="57" ht="409.5" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="B57" s="7" t="s">
+      <c r="A57" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="B57" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D57" s="7" t="s">
+      <c r="C57" s="6" t="s">
         <v>230</v>
       </c>
+      <c r="D57" s="6" t="s">
+        <v>231</v>
+      </c>
       <c r="E57" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="58" ht="409.5" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="B58" s="7" t="s">
+      <c r="A58" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="B58" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="C58" s="6" t="s">
         <v>234</v>
       </c>
+      <c r="D58" s="6" t="s">
+        <v>235</v>
+      </c>
       <c r="E58" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" ht="409.5" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="B59" s="7" t="s">
+      <c r="A59" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="B59" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="C59" s="6" t="s">
         <v>238</v>
       </c>
+      <c r="D59" s="6" t="s">
+        <v>239</v>
+      </c>
       <c r="E59" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="60" ht="409.5" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="B60" s="7" t="s">
+      <c r="A60" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="B60" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="D60" s="7" t="s">
+      <c r="C60" s="6" t="s">
         <v>242</v>
       </c>
+      <c r="D60" s="6" t="s">
+        <v>243</v>
+      </c>
       <c r="E60" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="61" ht="409.5" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="B61" s="7" t="s">
+      <c r="A61" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="B61" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="C61" s="6" t="s">
         <v>246</v>
       </c>
+      <c r="D61" s="6" t="s">
+        <v>247</v>
+      </c>
       <c r="E61" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="62" ht="409.5" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="B62" s="7" t="s">
+      <c r="A62" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="B62" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="D62" s="7" t="s">
+      <c r="C62" s="6" t="s">
         <v>250</v>
       </c>
+      <c r="D62" s="6" t="s">
+        <v>251</v>
+      </c>
       <c r="E62" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="63" ht="409.5" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="B63" s="7" t="s">
+      <c r="A63" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="B63" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D63" s="7" t="s">
+      <c r="C63" s="6" t="s">
         <v>254</v>
       </c>
+      <c r="D63" s="6" t="s">
+        <v>255</v>
+      </c>
       <c r="E63" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="64" ht="409.5" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B64" s="7" t="s">
+      <c r="A64" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="B64" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D64" s="7" t="s">
+      <c r="C64" s="6" t="s">
         <v>258</v>
       </c>
+      <c r="D64" s="6" t="s">
+        <v>259</v>
+      </c>
       <c r="E64" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="65" ht="409.5" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="B65" s="7" t="s">
+      <c r="A65" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="B65" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="C65" s="6" t="s">
         <v>262</v>
       </c>
+      <c r="D65" s="6" t="s">
+        <v>263</v>
+      </c>
       <c r="E65" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="66" ht="409.5" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="B66" s="7" t="s">
+      <c r="A66" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="B66" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="C66" s="6" t="s">
         <v>266</v>
       </c>
+      <c r="D66" s="6" t="s">
+        <v>267</v>
+      </c>
       <c r="E66" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="67" ht="409.5" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="B67" s="7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="67" ht="393.75" spans="1:5">
+      <c r="A67" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="B67" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="C67" s="6" t="s">
         <v>270</v>
       </c>
+      <c r="D67" s="6" t="s">
+        <v>271</v>
+      </c>
       <c r="E67" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="68" ht="409.5" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="B68" s="7" t="s">
+      <c r="A68" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="B68" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="C68" s="6" t="s">
         <v>274</v>
       </c>
+      <c r="D68" s="6" t="s">
+        <v>275</v>
+      </c>
       <c r="E68" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69" ht="409.5" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="B69" s="7" t="s">
+      <c r="A69" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="B69" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="C69" s="6" t="s">
         <v>278</v>
       </c>
+      <c r="D69" s="6" t="s">
+        <v>279</v>
+      </c>
       <c r="E69" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="70" ht="409.5" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="B70" s="7" t="s">
+      <c r="A70" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="B70" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="C70" s="6" t="s">
         <v>282</v>
       </c>
+      <c r="D70" s="6" t="s">
+        <v>283</v>
+      </c>
       <c r="E70" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="71" ht="409.5" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="B71" s="7" t="s">
+      <c r="A71" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="B71" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="D71" s="7" t="s">
+      <c r="C71" s="6" t="s">
         <v>286</v>
       </c>
+      <c r="D71" s="6" t="s">
+        <v>287</v>
+      </c>
       <c r="E71" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="72" ht="409.5" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="B72" s="7" t="s">
+      <c r="A72" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="B72" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="D72" s="7" t="s">
+      <c r="C72" s="6" t="s">
         <v>290</v>
       </c>
+      <c r="D72" s="6" t="s">
+        <v>291</v>
+      </c>
       <c r="E72" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="73" ht="409.5" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="B73" s="7" t="s">
+      <c r="A73" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="B73" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D73" s="7" t="s">
+      <c r="C73" s="6" t="s">
         <v>294</v>
       </c>
+      <c r="D73" s="6" t="s">
+        <v>295</v>
+      </c>
       <c r="E73" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="74" ht="409.5" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="B74" s="7" t="s">
+      <c r="A74" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="B74" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="C74" s="6" t="s">
         <v>298</v>
       </c>
+      <c r="D74" s="6" t="s">
+        <v>299</v>
+      </c>
       <c r="E74" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="75" ht="409.5" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="B75" s="7" t="s">
+      <c r="A75" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="B75" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="C75" s="6" t="s">
         <v>302</v>
       </c>
+      <c r="D75" s="6" t="s">
+        <v>303</v>
+      </c>
       <c r="E75" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="76" ht="409.5" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="B76" s="7" t="s">
+      <c r="A76" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="B76" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="D76" s="7" t="s">
+      <c r="C76" s="6" t="s">
         <v>306</v>
       </c>
+      <c r="D76" s="6" t="s">
+        <v>307</v>
+      </c>
       <c r="E76" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="77" ht="409.5" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="B77" s="7" t="s">
+      <c r="A77" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="B77" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="D77" s="7" t="s">
+      <c r="C77" s="6" t="s">
         <v>310</v>
       </c>
+      <c r="D77" s="6" t="s">
+        <v>311</v>
+      </c>
       <c r="E77" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="78" ht="409.5" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="B78" s="7" t="s">
+      <c r="A78" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="B78" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="C78" s="6" t="s">
         <v>314</v>
       </c>
+      <c r="D78" s="6" t="s">
+        <v>315</v>
+      </c>
       <c r="E78" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="79" ht="409.5" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="B79" s="7" t="s">
+      <c r="A79" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="B79" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="D79" s="7" t="s">
+      <c r="C79" s="6" t="s">
         <v>318</v>
       </c>
+      <c r="D79" s="6" t="s">
+        <v>319</v>
+      </c>
       <c r="E79" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="80" ht="409.5" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="B80" s="7" t="s">
+      <c r="A80" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="B80" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="D80" s="7" t="s">
+      <c r="C80" s="6" t="s">
         <v>322</v>
       </c>
+      <c r="D80" s="6" t="s">
+        <v>323</v>
+      </c>
       <c r="E80" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="81" ht="409.5" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="B81" s="7" t="s">
+      <c r="A81" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="C81" s="7" t="s">
+      <c r="B81" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="D81" s="7" t="s">
+      <c r="C81" s="6" t="s">
         <v>326</v>
       </c>
+      <c r="D81" s="6" t="s">
+        <v>327</v>
+      </c>
       <c r="E81" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="82" ht="409.5" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="B82" s="7" t="s">
+      <c r="A82" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="B82" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="D82" s="7" t="s">
+      <c r="C82" s="6" t="s">
         <v>330</v>
       </c>
+      <c r="D82" s="6" t="s">
+        <v>331</v>
+      </c>
       <c r="E82" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="83" ht="409.5" spans="1:5">
-      <c r="A83" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="B83" s="7" t="s">
+      <c r="A83" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="C83" s="7" t="s">
+      <c r="B83" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="D83" s="7" t="s">
+      <c r="C83" s="6" t="s">
         <v>334</v>
       </c>
+      <c r="D83" s="6" t="s">
+        <v>335</v>
+      </c>
       <c r="E83" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D42" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D83" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/book.xlsx
+++ b/book.xlsx
@@ -67,8 +67,10 @@
     <t>摘自：韩鹏杰《道德经说什么》</t>
   </si>
   <si>
-    <t>本章是全书导读，回答为什么读《道德经》、这本书讲什么、写给谁三个问题。为什么要学经典：经典是一个民族文化传承的途径与道路，认真读透一本经典胜过泛读百书，也是在为往圣继绝学、为万世开太平。其人：老子曾任周朝守藏史，掌管天下图书，能读到别人看不到的著作，知识渊博；因尹喜在函谷关要求他写下“道”的思想，才留下这部经典。
-其书：经考古验证，帛书版最接近老子亲笔原貌，后人为了便于理解不断优化，后世多沿用魏晋王弼的经典本；书名因“道”“德”出现频率最高而得名；道落实到现实生活，包含目标、方向、规则、境界、边界、底线六个方面。其道：本书主要写给三类人——士（基层领导者，推十为一、把自己放在最后）、王（主要领导者，善用人者为之下）、圣（品德修养高、通情达理的领导者，为而不争、为大家谋福利）。书中讲的是治国之道、为官之道与人生之道，为逐章解读打下基础。</t>
+    <t>本章是全书导读，回答为什么读《道德经》、这本书讲什么、写给谁三个问题。为什么要学经典：经典是一个民族文化传承的途径与道路，认真读透一本经典胜过泛读百书，也是在为往圣继绝学、为万世开太平。
+其人：老子曾任周朝守藏史，掌管天下图书，能读到别人看不到的著作，知识渊博；因尹喜在函谷关要求他写下“道”的思想，才留下这部经典。
+其书：经考古验证，帛书版最接近老子亲笔原貌，后人为了便于理解不断优化，后世多沿用魏晋王弼的经典本；书名因“道”“德”出现频率最高而得名；道落实到现实生活，包含目标、方向、规则、境界、边界、底线六个方面。
+其道：本书主要写给三类人——士（基层领导者，推十为一、把自己放在最后）、王（主要领导者，善用人者为之下）、圣（品德修养高、通情达理的领导者，为而不争、为大家谋福利）。书中讲的是治国之道、为官之道与人生之道，为逐章解读打下基础。</t>
   </si>
   <si>
     <t>道德经</t>
@@ -358,7 +360,7 @@
     <t>第二十二章</t>
   </si>
   <si>
-    <t>曲则全，枉则直，洼则盈，敝则新，少则得，多则惑。是以圣人抱一为天下式。不自见，故明；不自是，故彰；不自伐，故有功；不自矜，故长。夫唯不争，故天下莫能与之争。古之所谓“曲则全”者，岂虚言哉？诚全而归之。</t>
+    <t>曲则全，枉则直，洼则盈，敝则新，少则得，多则惑。是以圣人抱一为天下式。不自见，故明；不自是，故彰；不自伐，故有功；不自矜（jīn），故长。夫唯不争，故天下莫能与之争。古之所谓“曲则全”者，岂虚言哉？诚全而归之。</t>
   </si>
   <si>
     <t>忍受委屈则能保全自我，先弯曲反而能够伸直，低洼反而能够变得充盈，守旧反而能够创新，少取一些则有所收获，贪得无厌反而会变得迷惑。因此圣人能够同以上原则保持一致（持守道作为天下的法则）。他们不仅仅依靠自己的眼睛去观察，所以才能够看得清楚；从不自以为是，所以才能够彰显名声；从不自我夸耀，所以才能够保有功劳；从不自高自大，所以才能够成为领导者。正因为他们从不与别人争夺，所以天下没有任何人能够争得赢他们。古人所说的“委屈则能求全”这句话，难道是句空话吗？确实应该把保全自我的功劳归于这一原则（回归道）。</t>
@@ -609,7 +611,7 @@
     <t>第四十一章</t>
   </si>
   <si>
-    <t>上士闻道，勤而行之；中士闻道，若存若亡；下士闻道，大笑之，不笑不足以为道。故建言有之﹕明道若昧，进道若退，夷道若颣。上德若谷，大白若辱，广德若不足，建德若偷，质真若渝。大方无隅，大器晚成，大音希声，大象无形。道隐无名，夫唯道善贷且成。</t>
+    <t>上士闻道，勤而行之；中士闻道，若存若亡（wú）；下士闻道，大笑之，不笑不足以为道。故建言有之﹕明道若昧，进道若退，夷道若颣（lèi）。上德若谷，大白若辱，广德若不足，建德若偷，质真若渝（yú）。大方无隅（yú），大器晚成，大音希声，大象无形。道隐无名，夫唯道善贷且成。</t>
   </si>
   <si>
     <t>上等的士听到道，就会努力去实行；中等的士听到道，将信将疑；下等的士听到道，大声嘲笑。不被嘲笑，就不足以成为道了。所以古时候立言的人说过这样的话：光明的道路好像是昏暗不明的；前进的道路好像是后退的；平坦的道路好像是不平的。最高的德好像是山谷，最光明纯洁的内心好像是蒙受屈辱，广大的德好像不足的样子，刚健的德好像是软弱的样子，质性真的东西仿佛都是有缺点一样。最大的方没有棱角，最大的器件最晚做成，大音平时少讲话，关键时刻掷地有声，最大的形象没有形状。道隐藏于事物背后，没有名字。道善于帮助万物并成就万物。</t>
@@ -621,7 +623,7 @@
     <t>第四十二章</t>
   </si>
   <si>
-    <t>道生一，一生二，二生三，三生万物。万物负阴而抱阳，冲气以为和。人之所恶，唯孤寡不穀，而王公以为称。故物或损之而益，或益之而损。人之所教，我亦教之。强梁者不得其死，吾将以为教父。</t>
+    <t>道生一，一生二，二生三，三生万物。万物负阴而抱阳，冲气以为和。人之所恶（wù），唯孤寡不穀（gǔ），而王公以为称。故物或损之而益，或益之而损。人之所教，我亦教之。强梁者不得其死，吾将以为教父。</t>
   </si>
   <si>
     <t>“道”即阴阳二者的统一，“一”中蕴含着阴阳两个方面，阴阳二者参与到一起相互作用形成万事万物。万物背阴而向阳，阴阳二者相互中和形成和谐状态。人人都厌恶的是孤、寡、不穀，但王侯却以此自称。所以有的东西减损它反而得到增加，有的东西增加它反而得到减损。别人教给我的，我也教给别人。喜欢强大暴力的人不得好死，我把它当作座右铭。</t>
@@ -657,7 +659,7 @@
     <t>第四十五章</t>
   </si>
   <si>
-    <t>大成若缺，其用不弊；大盈若冲，其用不穷。大直若屈，大巧若拙，大辩若讷。躁胜寒，静胜热，清静为天下正。</t>
+    <t>大成若缺，其用不弊；大盈若冲，其用不穷。大直若屈，大巧若拙，大辩若讷（nè）。躁胜寒，静胜热，清静为天下正。</t>
   </si>
   <si>
     <t>最完满的东西好像有欠缺，但它的作用不会衰竭；最充盈的东西好像是空虚的，但它的作用没有穷尽。最直的东西好像是弯曲的，最精巧的东西好像是笨拙的，真正辩才高的人出语谨慎。运动可以克服寒冷，静可以战胜热，（治天下的人）保持内心清静才能将天下领上正道。</t>
@@ -669,7 +671,7 @@
     <t>第四十六章</t>
   </si>
   <si>
-    <t>天下有道，却走马以粪；天下无道，戎马生于郊。祸莫大于不知足，咎莫大于欲得。故知足之足，常足矣。</t>
+    <t>天下有道，却走马以粪；天下无道，戎马生于郊。祸莫大于不知足，咎（jiù）莫大于欲得。故知足之足，常足矣。</t>
   </si>
   <si>
     <t>天下有道，善跑的马退还给农夫用来耕田；天下无道，所有的马用来征战甚至母马都要在疆场生小马。祸患没有大于不知足的了，罪过没有大于什么都想占有的了。所以知足的满足，才是长久的满足。</t>
@@ -681,7 +683,7 @@
     <t>第四十七章</t>
   </si>
   <si>
-    <t>不出户，知天下；不窥牖，见天道。其出弥远，其知弥少。是以圣人不行而知，不见而名，不为而成。</t>
+    <t>不出户，知天下；不窥牖（yǒu），见天道。其出弥远，其知弥少。是以圣人不行而知，不见而名，不为而成。</t>
   </si>
   <si>
     <t>不用出家门，便能知天下之事；不用通过窗户去看，就能知道自然的规律法则。越是向外寻找求索，对道的认识就越少。所以圣人不用出行却能知事理，不观察却能明白道理，无为却能成功。</t>
@@ -705,7 +707,7 @@
     <t>第四十九章</t>
   </si>
   <si>
-    <t>圣人无常心，以百姓心为心。善者，吾善之；不善者，吾亦善之，德善。信者，吾信之；不信者，吾亦信之，德信。圣人在天下歙歙，为天下浑其心。百姓皆注其耳目，圣人皆孩之。</t>
+    <t>圣人无常心，以百姓心为心。善者，吾善之；不善者，吾亦善之，德善。信者，吾信之；不信者，吾亦信之，德信。圣人在天下歙（xī）歙（xī），为天下浑其心。百姓皆注其耳目，圣人皆孩之。</t>
   </si>
   <si>
     <t>圣人没有成心，以百姓之心为心。善良的百姓我善待他们，不善良的百姓我也善待他们，这样使人向善；讲诚信的人我以诚信对待他们，不讲诚信的人我也以诚信对待他们，这样使人诚信。圣人领导天下，收敛自己的私欲，使天下百姓的心灵都变得淳朴。百姓都只关注耳听眼见的事，圣人将百姓像孩童一样对待。</t>
@@ -717,7 +719,7 @@
     <t>第五十章</t>
   </si>
   <si>
-    <t>出生入死。生之徒十有三，死之徒十有三。人之生，动之死地，亦十有三。夫何故？以其生生之厚。盖闻善摄生者，陆行不遇兕虎，入军不被甲兵。兕无所投其角，虎无所措其爪，兵无所容其刃。夫何故？以其无死地。</t>
+    <t>出生入死。生之徒十有三，死之徒十有三。人之生，动之死地，亦十有三。夫何故？以其生生之厚。盖闻善摄生者，陆行不遇兕虎，入军不被甲兵。兕（sì）无所投其角，虎无所措其爪，兵无所容其刃。夫何故？以其无死地。</t>
   </si>
   <si>
     <t>人生就是从出生到死亡的历程。长寿的人占十分之三，短命的人占十分之三，本可以长寿但妄为把自己置于死地的人也占十分之三。为什么？因为他们过分地追求奉养自己以求生。听说善于养生的人，在陆地上行走不会遇到兕、虎，在战场上不会被兵器所伤。兕的角无处可用，虎的爪也没了用处，兵器的刃也用不上。为什么？因为他不把自己置于死地。</t>
@@ -741,7 +743,7 @@
     <t>第五十二章</t>
   </si>
   <si>
-    <t>天下有始，以为天下母。既得其母，以知其子；既知其子，复守其母，没身不殆。塞其兑，闭其门，终身不勤。开其兑，济其事，终身不救。见小曰明，守柔曰强。用其光，复归其明，无遗身殃，是为习常。</t>
+    <t>天下有始，以为天下母。既得其母，以知其子；既知其子，复守其母，没（mò）身不殆。塞其兑（duì），闭其门，终身不勤。开其兑，济其事，终身不救。见小曰明，守柔曰强。用其光，复归其明，无遗身殃，是为习常。</t>
   </si>
   <si>
     <t>天下万物都有本原（即道），作为万物的母亲。认识了作为万物之母的道，就能认知万物；认知了万物，就能坚守作为万物之母的道。这样终身都没有危险。塞上欲望的孔穴，闭上欲望的门户，终身都没有忧劳；打开感官欲望的门户，增添纷繁的事件，终身都不可挽救。察见细微的事物叫“明”，坚守柔弱叫“强”。用道的光芒来了解具体事物中的规律、规则，复归到事物的光明的状态，不会给自己留下那么多的祸殃，这就叫普遍永恒的规律。</t>
@@ -753,7 +755,7 @@
     <t>第五十三章</t>
   </si>
   <si>
-    <t>使我介然有知，行于大道，唯施是畏。大道甚夷，而民好径。朝甚除，田甚芜，仓甚虚。服文彩，带利剑，厌饮食，财货有余，是为盗夸。非道也哉！</t>
+    <t>使我介然有知，行于大道，唯施（yí）是畏。大道甚夷，而民好径。朝甚除，田甚芜，仓甚虚。服文彩，带利剑，厌饮食，财货有余，是为盗夸。非道也哉！</t>
   </si>
   <si>
     <t>假如让我稍微有些认知，行走在大道上，最害怕走到斜路上去。大道非常平坦，但一般人喜欢走捷径。（无道之君）朝政非常混乱，田园非常荒芜，仓库非常空虚。穿着华美的衣服，佩带锋利的宝剑，吃饱喝足，积存财货有余，这是夸耀自己的强盗途径。无道啊！</t>
@@ -777,7 +779,7 @@
     <t>第五十五章</t>
   </si>
   <si>
-    <t>含德之厚，比于赤子。蜂虿虺蛇不螫，猛兽不据，攫鸟不搏。骨弱筋柔而握固，未知牝牡之合而全作，精之至也。终日号而不嗄，和之至也。知和曰常，知常曰明，益生曰祥，心使气曰强。物壮则老，谓之不道，不道早已。</t>
+    <t>含德之厚，比于赤子。蜂虿（chài）虺（huǐ）蛇不螫（shì），猛兽不据，攫（jué）鸟不搏。骨弱筋柔而握固，未知牝牡之合而全作，精之至也。终日号（háo）而不嗄（shà），和之至也。知和曰常，知常曰明，益生曰祥，心使气曰强。物壮则老，谓之不道，不道早已。</t>
   </si>
   <si>
     <t>含德深厚的人，可比于刚出生的小孩。蜂蝎毒蛇等都不会刺咬他，猛兽不抓他，猛禽不攫取他。筋骨柔弱但小拳头握得很牢固，不知道男女交合之事但生殖器会举起，这是因为他精气充足。整天嚎哭但嗓子不会哭哑，这是因为他元气醇和。知道醇和、平和就是了解了道的规律、规则，了解这个事物规律、规则的人才是明智，让我们的生命有益才是一个吉祥，纵心任气，是强暴、强蛮的表现。强壮会趋于衰老，这叫做不合于道，不合于道便会早早灭亡。</t>
@@ -813,7 +815,7 @@
     <t>第五十八章</t>
   </si>
   <si>
-    <t>其政闷闷，其民淳淳；其政察察，其民缺缺。祸兮福之所倚，福兮祸之所伏。孰知其极？其无正。正复为奇，善复为妖。人之迷，其日固久。是以圣人方而不割，廉而不刿，直而不肆，光而不耀。</t>
+    <t>其政闷闷，其民淳淳；其政察察，其民缺缺。祸兮福之所倚，福兮祸之所伏。孰知其极？其无正。正复为奇，善复为妖。人之迷，其日固久。是以圣人方而不割，廉而不刿（guì），直而不肆，光而不耀。</t>
   </si>
   <si>
     <t>（治国者）为政宽容，人民就会淳厚；为政苛察，人民就会因感觉不足而欺上。祸啊，福倚靠着它；福啊，祸就藏伏其中。谁知它们的极点在哪呢？没有确定的标准。正转变为邪，善转变为恶。人们的迷惑，已经有很长的时间了。所以圣人方正而不割伤别人，有棱角但不刺伤别人，直率但不会放肆，有光芒但内敛，不刺眼炫耀。</t>
@@ -825,7 +827,7 @@
     <t>第五十九章</t>
   </si>
   <si>
-    <t>治人事天莫若啬。夫唯啬，是谓早服，早服谓之重积德。重积德则无不克，无不克则莫知其极。莫知其极，可以有国。有国之母，可以长久。是谓深根固柢，长生久视之道。</t>
+    <t>治人事天莫若啬。夫唯啬，是谓早服，早服谓之重积德。重积德则无不克，无不克则莫知其极。莫知其极，可以有国。有国之母，可以长久。是谓深根固柢（dǐ），长生久视之道。</t>
   </si>
   <si>
     <t>治理人民要顺应天理，莫过于节俭节制。只有节俭节制，才能早得道。早得道就是不断地积德。不断地积德就没有什么是克服不了的，没有什么克服不了就不知道它的力量有多强大。不知道其力量有多强大，就可以掌管国家。掌握了治国的根本，就可以长久存在。这是可以把根本扎深、扎牢固，长久存在的道。</t>
@@ -885,7 +887,7 @@
     <t>第六十四章</t>
   </si>
   <si>
-    <t>其安易持，其未兆易谋，其脆易泮，其微易散。为之于未有，治之于未乱。合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。为者败之，执者失之。是以圣人无为，故无败；无执，故无失。民之从事，常于几成而败之。慎终如始，则无败事。是以圣人欲不欲，不贵难得之货；学不学，复众人之所过。以辅万物之自然，而不敢为。</t>
+    <t>其安易持，其未兆易谋，其脆易泮（pàn），其微易散。为之于未有，治之于未乱。合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。为者败之，执者失之。是以圣人无为，故无败；无执，故无失。民之从事，常于几成而败之。慎终如始，则无败事。是以圣人欲不欲，不贵难得之货；学不学，复众人之所过。以辅万物之自然，而不敢为。</t>
   </si>
   <si>
     <t>局面稳定的时候容易掌控，事情没有征兆的时候容易去谋划，脆弱的东西容易分开，微小的东西容易解散。在事情还没有开始的时候就要作为，在还没有出现乱象时就处理好。合抱的大树，都是从细小的萌芽一点一点长起来的。九层的高台，也是一层一层的土积累起来的。想要走千里的路，就要从脚下一步一步走起。强为、妄为就会失败，执意把控就会失去。所以圣人不强为、不妄为，所以不会失败；不强执、不固执，所以不会失去。众人做事常常在快要接近成功的时候惨遭失败。在事情快要做完的时候还像一开始时候那样谨慎、慎重，就不会有失败。所以圣人所想的都是别人不愿意去想的，不以难得的货物为珍贵；学别人不愿意学的，对别人的错误引以为鉴。只是按照道的规律自然而然地去做，而不敢妄为。</t>
@@ -945,7 +947,7 @@
     <t>第六十九章</t>
   </si>
   <si>
-    <t>用兵有言：吾不敢为主而为客，不敢进寸而退尺。是谓行无行，攘无臂，扔无敌，执无兵。祸莫大于轻敌，轻敌几丧吾宝。故抗兵相加，哀者胜矣。</t>
+    <t>用兵有言：吾不敢为主而为客，不敢进寸而退尺。是谓行无行（háng），攘无臂，扔无敌，执无兵。祸莫大于轻敌，轻敌几丧吾宝。故抗兵相加，哀者胜矣。</t>
   </si>
   <si>
     <t>懂得用兵的人曾说：我不敢主动发动战争进犯别人，而只在被进犯时不得已而应战；作战时不敢盲目进军哪怕一寸，而要后退一尺，以退为进。（在入侵国家的领土上）虽然人民没有排成行列阵势，没有面对人民奋臂作怒，虽然好像没有面对敌人，虽然人民手中没有兵器，但四处都是侵略者的敌人。没有比轻敌更大的祸患，轻敌就几乎丧失了我的“三宝”。所以两军相持时，被同情、被支持的一方会获胜。</t>
@@ -981,7 +983,7 @@
     <t>第七十二章</t>
   </si>
   <si>
-    <t>民不畏威，则大威至。无狎其所居，无厌其所生。夫唯不厌，是以不厌。是以圣人自知，不自见；自爱，不自贵。故去彼取此。</t>
+    <t>民不畏威，则大威至。无狎（xiá）其所居，无厌其所生。夫唯不厌，是以不厌。是以圣人自知，不自见（xiàn）；自爱，不自贵。故去彼取此。</t>
   </si>
   <si>
     <t>人民不畏惧统治者的威严，就会发生大的麻烦。不要让人民住的地方越来越狭小，不让他们的生存受到压迫。不去压迫人民，他们才不会对统治者的行为感到厌烦。所以圣人有自知之明，不自我表现；珍爱自己的生命但不自认为高贵。所以舍弃后者而取前者。</t>
@@ -1005,7 +1007,7 @@
     <t>第七十四章</t>
   </si>
   <si>
-    <t>民不畏死，奈何以死惧之？若使民常畏死，而为奇者吾得执而杀之，孰敢？常有司杀者杀，夫代司杀者杀，是谓代大匠斫。夫代大匠斫者，希有不伤其手矣。</t>
+    <t>民不畏死，奈何以死惧之？若使民常畏死，而为奇者吾得执而杀之，孰敢？常有司杀者杀，夫代司杀者杀，是谓代大匠斫。夫代大匠斫（zhuó）者，希有不伤其手矣。</t>
   </si>
   <si>
     <t>人民不畏惧死亡，为什么还要用死亡来吓唬他们？如果使人民都经常性地、普遍性地畏惧死亡，而为非作歹的人我们可以把他抓来杀掉，那么谁还敢胡作非为？常有专管杀人的去执行杀人的任务，代替专管杀人的去杀人，就是代替大工匠去做砍斫的工作。代替大工匠去砍斫，很少有不伤到自己手的。</t>
@@ -1029,7 +1031,7 @@
     <t>第七十六章</t>
   </si>
   <si>
-    <t>人之生也柔弱，其死也坚强。万物草木之生也柔脆，其死也枯槁。故坚强者死之徒，柔弱者生之徒。是以兵强则不胜，木强则折。强大处下，柔弱处上。</t>
+    <t>人之生也柔弱，其死也坚强。万物草木之生也柔脆，其死也枯槁。故坚强者死之徒，柔弱者生之徒。是以兵强则不胜，木强则折（shé）。强大处下，柔弱处上。</t>
   </si>
   <si>
     <t>人活着的时候身体柔软，死之后身体便会僵硬。万物草木活着的时候形质柔软，死后变得干枯。所以坚强的东西属于死的那一类，柔弱的东西属于生的那一类。所以穷兵黩武一定会遭受灭亡，树木坚硬就会一折就断。总认为自己强大的、夸耀自己强大的，反而会处在下面；懂得柔弱、谦逊的，反而会居于上面。</t>
@@ -1053,7 +1055,7 @@
     <t>第七十八章</t>
   </si>
   <si>
-    <t>天下莫柔弱于水，而攻坚强者莫之能胜，其无以易之。弱之胜强，柔之胜刚，天下莫不知，莫能行。是以圣人云：受国之垢，是谓社稷主；受国不祥，是为天下王。正言若反。</t>
+    <t>天下莫柔弱于水，而攻坚强者莫之能胜，其无以易之。弱之胜强，柔之胜刚，天下莫不知，莫能行。是以圣人云：受国之垢（gòu），是谓社稷（jì）主；受国不祥，是为天下王。正言若反。</t>
   </si>
   <si>
     <t>天下没有比水更柔弱的了，但攻克坚强的东西却没有能胜过它的，没有什么东西可以代替水。柔弱胜过刚强的道理，天下都知道，但不能真正做到。所以圣人说：能忍受全国的屈辱，才能做社稷的君主；能承受全国的灾难，才能成为天下的君王。符合正道的话都好像反话一样。</t>

--- a/book.xlsx
+++ b/book.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="13668" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 (3)第三类人 - 圣：品德修养高，通情达理的领导者（圣人之道为而不争，为大家谋福利）。</t>
   </si>
   <si>
-    <t>摘自：韩鹏杰《道德经说什么》</t>
+    <t>译者·韩鹏杰《道德经说什么》</t>
   </si>
   <si>
     <t>本章是全书导读，回答为什么读《道德经》、这本书讲什么、写给谁三个问题。为什么要学经典：经典是一个民族文化传承的途径与道路，认真读透一本经典胜过泛读百书，也是在为往圣继绝学、为万世开太平。
@@ -86,7 +86,7 @@
   </si>
   <si>
     <t>本章是《道德经》的门户，核心是“有”和“无”，特别强调常被忽略的“无”。道可道，非常道；名可名，非常名：道是最高、最全面的存在，用语言和逻辑讲出来就变成有局限的道，所以要借形象来领悟。无，名天地之始；有，名万物之母：天地起源时混沌无形，称为无；天地成形、万物出现，称为有。任何事物都有有和无两个方面，观察事物既要从“有”的角度看它的边界，也要从“无”的角度看它的妙处。
-此两者同出而异名，同谓之玄：能把有和无合起来理解，已是高级的思维水平，叫做玄；再进一步看到无形力量（精神、信仰、家风、作风等）的巨大作用，就是玄之又玄、众妙之门。韩鹏杰以“风”为形象：风无形却力量无尽，正如人的精神世界。老子提醒人们不要只看到金钱、财富等有形的东西，更要看到精神、思想、理想信念这些无形的力量；只重有形，物质越发达，精神家园就越花果飘零。</t>
+此两者同出而异名，同谓之玄：能把有和无合起来理解，已是高级的思维水平，叫做玄；再进一步看到无形力量（精神、信仰、家风、作风等）的巨大作用，就是玄之又玄、众妙之门。译者·韩鹏杰以“风”为形象：风无形却力量无尽，正如人的精神世界。老子提醒人们不要只看到金钱、财富等有形的东西，更要看到精神、思想、理想信念这些无形的力量；只重有形，物质越发达，精神家园就越花果飘零。</t>
   </si>
   <si>
     <t>道经</t>
@@ -98,11 +98,11 @@
     <t>天下皆知美之为美，斯恶（è）已；皆知善之为善，斯不善已。故有无相（xiāng）生，难易相成，长短相较，高下相倾，音声相和，前后相随。是以圣人处无为之事，行不言之教，万物作焉而不辞，生而不有，为而不恃（shì），功成而弗居。夫唯弗居，是以不（bù）去。</t>
   </si>
   <si>
-    <t>天下都知道美是什么，丑自然就存在了；都知道什么是善，不善自然也就出现了。所以有和无相待而生，难和易相待而成，长和短相待而显，高和下相待而倾倚，音和声相待而和谐，前和后相待而顺序相随。所以圣人行事 顺乎自然 崇尚无为，实行不言的教诲，顺应万物自然的生长而不加干预，创造万物而不占有，施泽万物而不将这当成是倚仗、凭借的手段，有了功劳而不居功自傲。正因为他不居功自傲，所以他的功德永存不灭。</t>
+    <t>天下都知道美是什么，丑自然就存在了；都知道什么是善，不善自然也就出现了。所以有和无相待而生，难和易相待而成，长和短相待而显，高和下相待而倾倚，音和声相待而和谐，前和后相待而顺序相随。所以圣人行事 顺乎自然 崇尚无为，实行不言的教诲，顺应万物自然的生长而不加干预，创造万物而不占有，施泽万物而不将这当成是倚仗、凭借的手段，有了功劳而不居功（自傲）。正因为他不居功自傲，所以也就不会失去自己的功劳。</t>
   </si>
   <si>
     <t>本章讲世界运动的规律和认识世界的方法，是理解《道德经》的另一扇门。用哲学的语言概括：相比较而存在，相对立而发展。天下皆知美之为美，斯恶已；皆知善之为善，斯不善已：知道美就知道丑，知道善就知道不善，对立双方互相规定、互相依存。老子随后列出有无相生、难易相成、长短相较、高下相倾、音声相和、前后相随，指出这些对立面并非固定不变，而是在对立中运动、转化。
-因此圣人处无为之事，行不言之教：越是懂得有为，越要知道哪些该无为、该舍掉，从反面认识事情，才能达到更好的有为效果，千万不要把无为理解成消极。万物作焉而不辞，生而不有，为而不恃，功成而弗居：顺应万物自然生长而不干预，创造而不占有，做事而不依仗，有功而不居功，正因不居功，功德才不离去。本章还像目录一样，把后文许多重要内容提前概括出来，读熟这一章，后面很多章节都能以经解经。</t>
+因此圣人处无为之事，行不言之教：越是懂得有为，越要知道哪些该无为、该舍掉，从反面认识事情，才能达到更好的有为效果，千万不要把无为理解成消极。万物作焉而不辞，生而不有，为而不恃，功成而弗居：顺应万物自然生长而不干预，创造而不占有，做事而不依仗，有功而不居功，正因不居功，功德才不离去。本章后文许多重要内容提前概括出来，读熟这一章，后面很多章节都能以经解经。</t>
   </si>
   <si>
     <t>第三章</t>
@@ -115,7 +115,7 @@
   </si>
   <si>
     <t>本章与第二章紧密相连，讲看问题不能一点论，要两点论：好事发展到一定程度会向反面转化。不尚贤，使民不争：尚贤本是重视人才的好事，但一旦立了标准，就有人按标准投机取巧、自我包装，真正有才能的人不屑于此，反而被过滤掉，贤名被投机者占据，所以尚贤过了头反而害了人才选拔。不贵难得之货，使民不为盗；不见可欲，使民心不乱：不炒作珍贵物品、不显露引发欲望的东西，民心才不会乱。
-圣人之治，虚其心，实其腹，弱其志，强其骨：使民心虚静、生活温饱、欲望减弱、身体强健。常使民无知无欲，使夫智者不敢为也：少用智巧套路，投机者才不敢妄为。为无为，则无不治：治理者不妄为、不折腾，按规律和规则办事，天下自然治理得好。韩鹏杰强调，老子的话对面坐着的是领导者，这些话是对治理者提出的警醒：任何事都有尺度，把握不好度，好事也会变成坏事。</t>
+圣人之治，虚其心，实其腹，弱其志，强其骨：使民心虚静、生活温饱、欲望减弱、身体强健。常使民无知无欲，使夫智者不敢为也：少用智巧套路，投机者才不敢妄为。为无为，则无不治：治理者不妄为、不折腾，按规律和规则办事，天下自然治理得好。译者·韩鹏杰强调，老子的话对面坐着的是领导者，这些话是对治理者提出的警醒：任何事都有尺度，把握不好度，好事也会变成坏事。</t>
   </si>
   <si>
     <t>第四章</t>
@@ -128,20 +128,20 @@
   </si>
   <si>
     <t>本章强调道是万物的本源，理解的关键在“冲”字。冲是组合字，把两点放平就是“二中”，二指阴阳；冲的本义是两股水冲到一块，象征阴阳两种力量相互中和、相互作用、动态转化。道冲，而用之或不盈：阴阳中和而成道，作用无穷无尽。渊兮似万物之宗：道渊深博厚，像万物的宗主。挫其锐，解其纷，和其光，同其尘：道收敛锋芒、化解纷争，与光明融合、与尘垢同一，深远幽暗却无处不在。吾不知谁之子，象帝之先：道先于天帝而存在，是万事万物的本源。
-韩鹏杰用第四十二章“道生一，一生二，二生三，三生万物；万物负阴而抱阳，冲气以为和”来印证：三即参，阴阳参与到一起而生万物，万事万物都同时具有阴阳两面，无论怎么转都像太极图一样保持和谐。了解道冲，就掌握了一种重要思维：任何事物都是两种相反力量在动态中达成的和谐，看问题、做决策都不能只偏执一方。</t>
+译者·韩鹏杰用第四十二章“道生一，一生二，二生三，三生万物；万物负阴而抱阳，冲气以为和”来印证：三即参，阴阳参与到一起而生万物，万事万物都同时具有阴阳两面，无论怎么转都像太极图一样保持和谐。了解道冲，就掌握了一种重要思维：任何事物都是两种相反力量在动态中达成的和谐，看问题、做决策都不能只偏执一方。</t>
   </si>
   <si>
     <t>第五章</t>
   </si>
   <si>
-    <t>天地不仁，以万物为刍（chú）狗；圣人不仁，以百姓为刍狗。天地之间，其犹橐籥（tuó yuè）乎？虚而不屈（qū），动而愈出。多言数（shuò）穷，不如守中。</t>
+    <t>天地不仁，以万物为刍（chú）狗；圣人不仁，以百姓为刍狗。天地之间，其犹橐（tuó）籥（ yuè）乎？虚而不屈（qū），动而愈出。多言数（shuò）穷，不如守中。</t>
   </si>
   <si>
     <t>天地无所偏爱，将万物像刍狗（草扎的狗）一样平等看待；圣人没有偏私，对百姓像刍狗一样平等看待。天地这个大空间，不就像一个大风箱吗？因其中间虚静才能鼓出风，越动鼓出的风越多。政令繁多会招致败亡，不如保持虚静才能恰如其分。</t>
   </si>
   <si>
     <t>本章讲天地对万物的平等和治理者的虚静。天地不仁，以万物为刍狗：不仁不是残忍，而是不偏爱、不干预；天地看待万物一视同仁，像草扎的祭狗，祭祀前被尊重，祭祀后被丢弃，无所爱惜。圣人不仁，以百姓为刍狗：好的领导者对百姓也应一律公平，制定规则法令，谁都不能例外；不要因为谁弱就特殊照顾，那反而是一种偏私，让被照顾者失去自立。道家讲的不仁是“大仁”，天地不偏私地让万物自己去奋斗、去努力。
-天地之间，其犹橐籥乎：天地像风箱，中间虚静，一拉动就能鼓出风来；政令也应如此，保持虚静、简要稳定，不能今天一变明天一变。多言数穷，不如守中：政令繁多、变动频繁会把自己逼入困境，不如恰到好处、大道至简。韩鹏杰提醒，这些话都是讲给领导者听的：治理要公平无私，政令要少而稳定，靠规则而不是靠折腾。</t>
+天地之间，其犹橐籥乎：天地像风箱，中间虚静，一拉动就能鼓出风来；政令也应如此，保持虚静、简要稳定，不能今天一变明天一变。多言数穷，不如守中：政令繁多、变动频繁会把自己逼入困境，不如恰到好处、大道至简。译者·韩鹏杰提醒，这些话都是讲给领导者听的：治理要公平无私，政令要少而稳定，靠规则而不是靠折腾。</t>
   </si>
   <si>
     <t>第六章</t>
@@ -150,11 +150,11 @@
     <t>谷神不死，是谓玄牝（pìn）。玄牝之门，是谓天地根。绵绵若存，用之不勤。</t>
   </si>
   <si>
-    <t>道虚无莫测 永存不灭，称为“玄牝”，“玄牝”之门，是天地万物的根源。连绵不绝地永存，取之不尽用之不竭。</t>
+    <t>道虚无莫测 永存不灭，它好像是一个玄妙的母体。而这一母体的生殖器官，就是产生天地万物的根源。空间连绵不断似乎永远存在，万物使用它却又用不完它。</t>
   </si>
   <si>
     <t>本章以谷与牝为喻，把道比作孕育万物的母体，根本精神是对母亲的尊重、对生命的敬畏。谷神不死，是谓玄牝：谷指空虚的山谷，神指精神、生机；牝指女性生殖器，代表母亲。谷神不死，即这种孕育生命的力量绵延不绝，称为玄牝。玄牝之门，是谓天地根：玄牝之门是天地万物的根源，道生万物与母亲生育生命是同一个道理。绵绵若存，用之不勤：它连绵不断地存在，取之不尽、用之不竭。
-韩鹏杰强调，老子用神、玄这些最高字眼来称呼谷与牝，绝不允许亵渎；一个文化里若失去对母亲的尊重、对生命的敬畏，其他方面都会崩塌。读这一章不要陷入玄虚，要读出其中朴素而伟大的情感：尊重母亲、敬畏生命，是文化延续的根基。</t>
+译者·韩鹏杰强调，老子用神、玄这些最高字眼来称呼谷与牝，绝不允许亵渎；一个文化里若失去对母亲的尊重、对生命的敬畏，其他方面都会崩塌。读这一章不要陷入玄虚，要读出其中朴素而伟大的情感：尊重母亲、敬畏生命，是文化延续的根基。</t>
   </si>
   <si>
     <t>第七章</t>
@@ -163,11 +163,12 @@
     <t>天长地久。天地所以能长且久者，以其不自生，故能长生。是以圣人后其身而身先，外其身而身存。非以其无私邪？故能成其私。</t>
   </si>
   <si>
-    <t>天地长长久久啊。天地之所以能长长久久，就是因为天地不自私、不只是只为了自己的生存，所以能长久啊。所以有智慧的领导者总是把自己的利益放在后面，这样才被大家乐推而不厌 乐于接受他们的领导，不贪身外之物 才让自己有更好的存在状态。天地和效法天地的圣人 不就是因为他们没有私心嘛，所以才更好地成就了他们的被人尊敬、平安无事的私心吗！</t>
+    <t>天地能够长久存在。天地之所以能够长久存在，原因就在于它们不
+是为了自我而生存，所以能长久存在。因此有智慧的领导者总是把自己的利益放在后面，反而能够站到别人的前面；不贪身外之物，反而有利于自己的生存。不就是因为他们没有私心嘛，所以才更好地成就了他们的被人尊敬、平安无事的私心吗？！</t>
   </si>
   <si>
     <t>本章与第八、九章共同讲进退、争让、强弱：人们习惯强调争、进、强，老子偏要讲被忽略的不争、退、弱，因为它们与争、进、强是阴阳的两个方面，具有同等力量。天长地久：天地之所以长久，是因为天地不自私，不以自己的生存为唯一目的，而是为万物提供阳光雨露土壤，任万物自由生长，因此赢得人们长久的敬畏。后其身而身先，外其身而身存：圣人把自身利益放在后面，反而被众人推举到前面；把自身安危置之度外，反而安然长存。非以其无私邪，故能成其私：正因无私，才更好地成就了自己的长久与被人敬仰，这是人人都有的潜意识私心。
-本章是典型的“天道人道”两段论：先讲天道，再讲人道，人道效法天道。韩鹏杰用“公仪休不受鱼”的故事说明：懂得从长远看问题、不贪眼前不该得的利益，才能长久地满足自己的愿望；只盯着私利的人，最后连私利也保不住。</t>
+本章是典型的“天道人道”两段论：先讲天道，再讲人道，人道效法天道。译者·韩鹏杰用“公仪休不受鱼”的故事说明：懂得从长远看问题、不贪眼前不该得的利益，才能长久地满足自己的愿望；只盯着私利的人，最后连私利也保不住。</t>
   </si>
   <si>
     <t>第八章</t>
@@ -180,7 +181,7 @@
   </si>
   <si>
     <t>本章“上善若水”是《道德经》最著名的命题，也是中华民族精神的重要代表。上善若水，水善利万物而不争：最高的智慧与品德像水一样，滋润万物、成就他人而不争功，甘处众人不愿去的低处，所以最接近道。老子借水讲了善下、善渊、善仁、善信、善治、善能、善时等品质：居善地，甘居下位；心善渊，静水深流、宁静致远；与善仁，平等仁爱地给予；言善信，说话像潮信一样讲信用；政善治，政治清正公平如水；事善能，有多种本事又专一向前；动善时，该动则动、该静则静、该绕行则绕行。
-水的“不争”有丰富含义：有边界不争（湖有湖畔、河有河堤、海有海岸），有秩序不争（前后相随、循序渐进），有牺牲不争（成就万物而默默无闻）。夫唯不争，故无尤：不争就不会招来怨恨和过错。韩鹏杰指出，老子不是趴在河边悟道，而是借水的形象传达从战争、政治、人生中领悟的智慧：善于成就别人，同时也成就自己，这正是双赢。</t>
+水的“不争”有丰富含义：有边界不争（湖有湖畔、河有河堤、海有海岸），有秩序不争（前后相随、循序渐进），有牺牲不争（成就万物而默默无闻）。夫唯不争，故无尤：不争就不会招来怨恨和过错。译者·韩鹏杰指出，老子不是趴在河边悟道，而是借水的形象传达从战争、政治、人生中领悟的智慧：善于成就别人，同时也成就自己，这正是双赢。</t>
   </si>
   <si>
     <t>第九章</t>
@@ -189,11 +190,11 @@
     <t>持而盈之，不如其已（yǐ）。揣（zhuī）而锐之，不可长保。金玉满堂，莫之能守。富贵而骄，自遗其咎。功遂身退，天之道也。</t>
   </si>
   <si>
-    <t>如果做事一定要做到盈满，还不如停止不做。刀刃捶锻得尖锐锋利，其锋刃就不能长期保持锋利。家中充满财富和珍宝，没有人能够守住。因富贵而骄傲自满，是自取灾难。功成而懂得不居功自傲的道理，才真正符合天道天理。</t>
+    <t>如果做事一定要做到盈满，还不如停止不做。刀刃捶锻得尖锐锋利，其锋刃就不能长期保持锋利。家中充满财富和珍宝，没有人能够守住。炫富炫贵骄狂放纵，会给自己留下无尽祸殃。功成而懂得不居功自傲的道理，才真正符合天道天理。</t>
   </si>
   <si>
     <t>本章讲“不盈”：凡事勿求满，适可而止。持而盈之，不如其已：端着一盘盛满的水走路，战战兢兢还不断洒出，不如少装一点，走得更轻松。揣而锐之，不可长保：把锥子磨得极锋利，一碰就断；削铅笔削到只剩笔头，再尖也保不住。金玉满堂，莫之能守：家中满是财富珍宝，反而守不住。富贵而骄，自遗其咎：因富贵而骄傲自满，是自取灾难。功遂身退，天之道也：功成而不居功、懂得退让，才符合天道。
-韩鹏杰用民间故事讲这个道理：弟弟只拿一点金子平安回家，哥哥贪心装满全身，被太阳晒化。第七章讲先后，第八章讲不争，第九章讲不盈，都提醒人知进退、懂谦让。中国文化的“中”就是恰到好处，不走到极端：物极必反、乐极生悲、泰极否来，好事到了极端容易向坏处转化，所以要战战兢兢、如履薄冰地把握分寸。</t>
+译者·韩鹏杰用民间故事讲这个道理：弟弟只拿一点金子平安回家，哥哥贪心装满全身，被太阳晒化。第七章讲先后，第八章讲不争，第九章讲不盈，都提醒人知进退、懂谦让。中国文化的“中”就是恰到好处，不走到极端：物极必反、乐极生悲、泰极否来，好事到了极端容易向坏处转化，所以要战战兢兢、如履薄冰地把握分寸。</t>
   </si>
   <si>
     <t>第十章</t>
@@ -202,11 +203,11 @@
     <t>载（zài）营魄抱一，能无离乎？专气致柔，能如婴儿乎？涤除玄览，能无疵（cī）乎？爱民治国，能无为乎？天门开阖，能为雌乎？明白四达，能无知乎？生之畜（xù）之，生而不有，为而不恃，长（zhǎng）而不宰，是谓玄德。</t>
   </si>
   <si>
-    <t>身体像车一样载着魂魄，它们能不能不要分离？聚结精气以致柔和温顺，能不能像婴儿那样的纯粹呢？像玄镜照心一样清除杂念而深入观察心灵，能不能让心灵没有瑕疵呢？爱民治国能不能遵行自然无为的规律呢？感官与外界的对立变化相接触，能不能守住雌柔宁静呢？明白四达，能不能不用心机诈术呢？万物生长繁殖，产生万物、养育万物而不占为己有，作万物之长而不主宰它们，这就叫做“玄德”。</t>
+    <t>身体像车一样载着魂魄，它们能不能不要分离？聚结精气以致柔和温顺，能不能像婴儿那样的纯粹呢？像玄镜照心一样清除杂念而深入观察心灵，能不能让心灵没有瑕疵呢？爱民治国能不能遵行自然无为的规律呢？感官与外界的对立变化相接触，能不能守住雌柔宁静呢？明白四达，能不能不用心机诈术呢？万物生长繁殖，产生万物、养育万物而不占为己有，作万物之长而不主宰它们，这就叫做“玄德”（高尚的品德）。</t>
   </si>
   <si>
     <t>本章与十一、十二章共讲“虚静”：心里放空才能宁静，宁静才能看清事物本质，抵抗外在诱惑。载营魄抱一，能无离乎：身体像车载着魂魄，灵魂与肉体能否合一不分离？不要做丢了灵魂的行尸走肉。专气致柔，能如婴儿乎：聚结精气、身心柔软，能否像婴儿一样纯粹？涤除玄览，能无疵乎：清除内心杂念，能否像明镜一样无瑕疵？爱民治国，能无为乎：治理能否顺其自然、不妄为？天门开阖，能为雌乎：面对外界纷扰，能否守住柔静？明白四达，能无知乎：通达事理之后，能否不用机巧套路？
-一连串反问都在讲修养路径：魂魄不离、身心合一、少欲守静、厚道不用智巧。最后点出玄德：生之畜之，生而不有，为而不恃，长而不宰——生养万物而不占有、不倚仗、不主宰，这是最高深的德。韩鹏杰认为这一章是后面九章的总纲，虚静既是个人修养，也是治国的基础。</t>
+一连串反问都在讲修养路径：魂魄不离、身心合一、少欲守静、厚道不用智巧。最后点出玄德：生之畜之，生而不有，为而不恃，长而不宰——生养万物而不占有、不倚仗、不主宰，这是最高深的德。译者·韩鹏杰认为这一章是后面九章的总纲，虚静既是个人修养，也是治国的基础。</t>
   </si>
   <si>
     <t>第十一章</t>
@@ -215,11 +216,11 @@
     <t>三十辐（fú）共一毂（gǔ），当其无，有车之用。埏（shān）埴（zhí）以为器，当其无，有器之用。凿户牖（yǒu）以为室，当其无，有室之用。故有之以为利，无之以为用。</t>
   </si>
   <si>
-    <t>三十根辐条集中在一个车毂上，正是因为有了车厢中的空间，才有了车子的作用。用水和着黏土制造各种陶器，正是因为有了陶器里的空间，才有了陶器的作用。开凿门窗修建房屋，正是因为有了房屋中的空间，才有了房屋的作用。所以说各种器物的物质部分（实有部分）给人带来了利益，而器物里的空间（空虚部分）才使这些器物能够发挥自己的作用。</t>
+    <t>三十根辐条集中在一个车毂（轴承）上，正是因为有了车轴中的空间，才有了车子的作用。用水和黏土制造各种陶器，正是因为有了陶器里的空间，才有了陶器的作用。开凿门窗修建房屋，正是因为有了房屋中的空间，才有了房屋的作用。所以说各种器物的物质部分（实有部分）给人带来了利益，而器物里的空间（空虚部分）才使这些器物能够发挥自己的作用。</t>
   </si>
   <si>
     <t>本章讲“无”的作用，用三个日常形象说明虚空的巨大价值。三十辐共一毂，当其无，有车之用：车轮有三十根辐条，车毂中间是空的，车轮才能转动，才有车的功用。埏埴以为器，当其无，有器之用：黏土烧成器皿，中间是空的，才能盛水装物。凿户牖以为室，当其无，有室之用：开凿门窗建成房屋，中间是空的，人才能居住。有之以为利，无之以为用：实体提供便利条件，虚空成就实际功用，有与无相互成全。
-韩鹏杰指出，“利用”这个词就来自本章。第十章讲虚静，本章讲怎样虚静——心里放空，去掉杂念，才能听得进别人的意见、看得见别人的长处、学得到别人的优点，虚怀若谷、满招损谦受益。中国文化的悟道方式是“给一个形象，自己领悟”，本章就是最好的示范：通过车、器、室三个形象，让人领悟空与用的道理。</t>
+译者·韩鹏杰指出，“利用”这个词就来自本章。第十章讲虚静，本章讲怎样虚静——心里放空，去掉杂念，才能听得进别人的意见、看得见别人的长处、学得到别人的优点，虚怀若谷、满招损谦受益。中国文化的悟道方式是“给一个形象，自己领悟”，本章就是最好的示范：通过车、器、室三个形象，让人领悟空与用的道理。</t>
   </si>
   <si>
     <t>第十二章</t>
@@ -228,11 +229,11 @@
     <t>五色令人目盲；五音令人耳聋；五味令人口爽；驰骋畋（tián）猎，令人心发狂；难得之货，令人行妨。是以圣人为腹不为目，故去彼取此。</t>
   </si>
   <si>
-    <t>艳丽的色彩看多了会伤害人的视力；美妙的音乐听多了会伤害人的听力；味美的食物吃多了会伤害人的味觉；沉溺于驰马打猎，会使人心神狂乱；珍贵的金银财宝，会使人的行为受到妨碍。所以圣人只求吃饱肚子而不求感官享受，因此要舍弃感官享受（过度的欲望）而选择简单朴素的生活。</t>
+    <t>艳丽的色彩看多了会让人眼花缭乱；嘈杂的声音会让人听觉失灵；过于丰盛的食物吃多了会让人味觉错乱；沉溺于驰马打猎，会让人心神狂乱；珍贵的金银财宝，会让人行为不轨。因此圣人只求吃饱肚子而不求感官享受，摒弃感官享受（过度的欲望）而选择简单朴素安定知足的生活方式。</t>
   </si>
   <si>
     <t>本章讲外在诱惑对心灵的扰乱，以及如何以内心的虚静守住根本。五色令人目盲：颜色太多太杂，反而区分不出好坏，视觉被迷乱；五音令人耳聋：高音快节奏听多了，好音乐也分辨不出来；五味令人口爽：厚食重味吃多了，味觉被破坏（爽是错乱）；驰骋畋猎令人心发狂：声色犬马让人心静不下来；难得之货令人行妨：被炒作的珍奇之物让人行为失当。老子并不要求消灭这些享受，而是说要以内心的虚静合理把握，适可而止。
-是以圣人为腹不为目，故去彼取此：圣人重实质内容，不重外在浮华；取舍的标准是看什么最重要——健康、营养、真实比外表颜色更重要。韩鹏杰把本章与第十章、十一章连起来读：虚静的心才能看清本质，处其厚不居其薄，掌握生命中真正重要的东西，返璞归真。</t>
+是以圣人为腹不为目，故去彼取此：圣人重实质内容，不重外在浮华；取舍的标准是看什么最重要——健康、营养、真实比外表颜色更重要。译者·韩鹏杰把本章与第十章、十一章连起来读：虚静的心才能看清本质，处其厚不居其薄，掌握生命中真正重要的东西，返璞归真。</t>
   </si>
   <si>
     <t>第十三章</t>
@@ -241,11 +242,11 @@
     <t>宠辱若惊，贵大患若身。何谓宠辱若惊？宠为下，得之若惊，失之若惊，是谓宠辱若惊。何谓贵大患若身？吾所以有大患者，为吾有身，及吾无身，吾有何患！故贵以身为天下，若可寄天下；爱以身为天下，若可托天下。</t>
   </si>
   <si>
-    <t>受到宠爱和受到侮辱都好像受到惊恐，把荣辱这样的大患看得与自身生命一样珍贵。那么为什么会得宠和受辱都感到惊慌失措呢？受宠者是卑下的，得到宠爱又怕失去会感觉惊恐，失去宠爱则更令人惊慌不安；受辱时惊恐，失去时又害怕辱再来也会惊恐，这就叫做得宠和受辱都感到惊恐。什么叫做重视大患像重视自身生命一样？我之所以有大患，是因为我有身体；如果我没有身体，我还会有什么祸患呢？所以，珍贵、爱惜自己的身体，而为了天下这个更重要的价值可以奉献生命，这样的人可以把天下寄托给他了。</t>
+    <t>受到宠爱和受到侮辱都好像受到惊恐，这是把荣辱这样的大患看得与自身生命一样珍贵。那么为什么得宠和受辱都感到惊慌失措呢？受宠者是卑下的，得到宠爱又怕失去所以会感觉惊恐，失去宠爱则更令人惊慌不安，这就叫做得宠和受辱都感到惊恐。什么叫做重视大患像重视自身生命一样？我之所以有大患，是因为我有身体；如果我没有身体，我还会有什么祸患呢？所以，珍贵、爱惜自己的身体，用自己全部身心去治理天下的人，才可以把天下交给他；只有那些愿意以自己全部身心去治理天下的人，才可以把天下托付给他。</t>
   </si>
   <si>
     <t>本章讲宠辱与生命，核心是如何看待得失、珍视生命，什么样的人才可托付天下。宠辱若惊：得到宠幸和失去宠幸都会惊恐。为什么？宠为下：被宠的人在下面，宠我们的人在上面，所以得之若惊（怕失去），失之若惊（更恐惧），这叫宠辱若惊。能做到宠辱不惊、淡然处之，是难得的人生境界。贵大患若身：有身体就有祸患，身体代表利益，也带来疾病与麻烦；但身体是摆脱不掉的，所以更要珍视它。
-吾所以有大患者，为吾有身，及吾无身，吾有何患——不把身体和生命当回事的人，坐到重要位置上是很可怕的；声色犬马、厚食重味正是戕害生命。贵以身为天下，若可寄天下；爱以身为天下，若可托天下：真正把自身生命看得与天下一样贵重、肯为天下担当牺牲的人，才值得把天下托付给他。韩鹏杰区分两种勇敢：无赖式的勇敢不把命当回事，有责任的勇敢珍视生命又肯担当，后者才值得托付。</t>
+吾所以有大患者，为吾有身，及吾无身，吾有何患——不把身体和生命当回事的人，坐到重要位置上是很可怕的；声色犬马、厚食重味正是戕害生命。贵以身为天下，若可寄天下；爱以身为天下，若可托天下：真正把自身生命看得与天下一样贵重、肯为天下担当牺牲的人，才值得把天下托付给他。译者·韩鹏杰区分两种勇敢：无赖式的勇敢不把命当回事，有责任的勇敢珍视生命又肯担当，后者才值得托付。</t>
   </si>
   <si>
     <t>第十四章</t>
@@ -260,7 +261,7 @@
   </si>
   <si>
     <t>本章形容道大象无形却无处不在，并指出知古通今的方法。视之不见名曰夷，听之不闻名曰希，搏之不得名曰微：道太细微，看不见、听不到、摸不着，三个词都说明道不可用感官把握。此三者不可致诘，故混而为一：不能用语言追问道在哪里，它混然一体。其上不皦，其下不昧，绳绳不可名：道不明不暗、不上不下，绵延存在却无法命名。无状之状，无物之象，是谓惚恍：道没有具体形状和物象，似有若无。迎之不见其首，随之不见其后：寻不到它的首尾。
-执古之道，以御今之有：了解古往今来的大道，才能把握今天、做好今天的事；能知古始，是谓道纪：知道万物开始的道理，就是把握了道的纲领。韩鹏杰用庄子的“道在瓦片、稗草、大小便中”来说明道无在无不在，越往下越有；用风的形象说明道无形却左右万物。学习本章要记住：道看不见摸不着，但真实存在、无处不在，了解它才能做好今天的事。</t>
+执古之道，以御今之有：了解古往今来的大道，才能把握今天、做好今天的事；能知古始，是谓道纪：知道万物开始的道理，就是把握了道的纲领。译者·韩鹏杰用庄子的“道在瓦片、稗草、大小便中”来说明道无在无不在，越往下越有；用风的形象说明道无形却左右万物。学习本章要记住：道看不见摸不着，但真实存在、无处不在，了解它才能做好今天的事。</t>
   </si>
   <si>
     <t>第十五章</t>
@@ -269,14 +270,14 @@
     <t>古之善为士者，微妙玄通，深不可识。夫唯不可识，故强为之容。豫焉若冬涉川，犹兮若畏四邻，俨（yǎn）兮其若客，涣兮若冰之将释，敦兮其若朴，旷兮其若谷，混兮其若浊。孰能浊以止？静之徐清。孰能安以久？动之徐生。保此道者不欲盈，夫唯不盈，故能蔽而新成。</t>
   </si>
   <si>
-    <t>古代那些掌握大道的人，其思想微妙通达，深刻得难以理解。正因为他们难以被理解，所以要勉强对他们的言行加以描述：
+    <t>古代那些掌握大道的人，其思想微妙通达，深刻得难以理解。正因为他们难以被理解，所以要勉强对他们的言行加以描述。
 他们做事反复考虑，就好像寒冬要徒步过河一样；谨慎小心，就好像畏惧四邻的围攻一般；恭敬庄重，就好像一位做客的人；通达而不固执，就好像将要融化的冰块；朴实敦厚，就好像未经雕饰的原木；胸怀空阔宽广，就好像那深山的幽谷；能够包容一切，就好像那混浊的大水。
-谁能够持久地像混浊的大水那样去包容一切呢？世人总是要让浊水安静下来，慢慢加以澄清；但是谁又能够永远坚持这种安定清静的状态呢？世人又总是搅动这种清静状态，慢慢产生各种追名逐利的活动。
-掌握大道的人，办事不求盈满。正因为不求盈满，所以能够安于有缺陷的旧状态而不去创造新的事物。</t>
+谁能够持久地像混浊的大水那样去包容一切呢？世人总是要让浊水安静下来，慢慢加以澄清；但是谁又能够永远坚持这种安定清静的状态呢？顺势而动，万物便能徐徐生发。
+掌握大道的人，办事不求盈满。正因为不求盈满，所以能去旧存新、不断新生。</t>
   </si>
   <si>
     <t>本章讲基层领导者“士”应有的修养。古之善为士者，微妙玄通，深不可识：善于做士的人，智慧微妙、通达深远，难以被了解，所以要强为之容（勉强形容）。豫兮若冬涉川：像冬天过河一样谨慎，一步一探；犹兮若畏四邻：像敬畏四邻一样不敢妄动；俨兮其若客：庄重像做客；涣兮若冰之将释：温和像冰雪消融；敦兮其若朴：敦厚像未经雕琢的木头；旷兮其若谷：胸怀开阔像山谷；混兮其若浊：包容混同像浊水。
-孰能浊以静之徐清？孰能安以久动之徐生：浊水静下来才能慢慢澄清，安定的状态动起来才能慢慢焕发生机，这是“静中求清、动中求生”的修养。保此道者不欲盈，夫唯不盈，故能蔽而新成：守道者不求满，留出空间，舍弃旧的东西才能革故鼎新。韩鹏杰强调，书中的话多针对具体的人讲，本章针对带领十几人做事的小组长等“士”阶层，说明基层领导者也需要很高的素质：谨慎、敬畏、质朴、虚怀、不盈。</t>
+孰能浊以静之徐清？孰能安以久动之徐生：浊水静下来才能慢慢澄清，安定的状态动起来才能慢慢焕发生机，这是“静中求清、动中求生”的修养。保此道者不欲盈，夫唯不盈，故能蔽而新成：守道者不求满，留出空间，舍弃旧的东西才能革故鼎新。译者·韩鹏杰强调，书中的话多针对具体的人讲，本章针对带领十几人做事的小组长等“士”阶层，说明基层领导者也需要很高的素质：谨慎、敬畏、质朴、虚怀、不盈。</t>
   </si>
   <si>
     <t>第十六章</t>
@@ -289,7 +290,7 @@
   </si>
   <si>
     <t>本章承第十五章，进一步讲虚静观复、知常守根。致虚极，守静笃：把心放到极度虚空、极度宁静的状态，不是枯木死灰，而是心灵安稳、不受杂念干扰。万物并作，吾以观复：万物纷繁生长，观察它的根本规律就是一个“复”字，反复循环、复归本根。夫物芸芸，各复归其根：万物虽然纷纭，最终都要回归自己的根本。归根曰静，静曰复命，复命曰常：归根就是静，静就是复归本性，复归本性就是恒常之道。
-知常容，容乃公，公乃王，王乃天，天乃道，道乃久，没身不殆：懂得恒常之道就能包容，包容就公正，公正就周全，周全就合天，合天就合道，合道就长久，终身不会遇到危险。韩鹏杰说，从草的枯荣到人的生死，都体现“复”的规律；观察规律是为了认识自己、掌控自己：知道哪些因素会带来负面状态，就主动避免；知道哪些条件带来积极状态，就主动创造，让好的状态恢复。</t>
+知常容，容乃公，公乃王，王乃天，天乃道，道乃久，没身不殆：懂得恒常之道就能包容，包容就公正，公正就周全，周全就合天，合天就合道，合道就长久，终身不会遇到危险。译者·韩鹏杰说，从草的枯荣到人的生死，都体现“复”的规律；观察规律是为了认识自己、掌控自己：知道哪些因素会带来负面状态，就主动避免；知道哪些条件带来积极状态，就主动创造，让好的状态恢复。</t>
   </si>
   <si>
     <t>第十七章</t>
@@ -298,11 +299,11 @@
     <t>太上，不知有之；其次，亲而誉之；其次，畏之；其次，侮之。信不足焉，有不信焉。悠兮其贵言。功成事遂，百姓皆谓我自然。</t>
   </si>
   <si>
-    <t>最高层次的统治者，百姓感觉不到他们的存在；低一层次的统治者，百姓亲近他们、赞美他们；更低层次的统治者，百姓害怕他们；最低层次的统治者，百姓轻视、羞辱他们。正是因为统治者本身的诚信不足，所以才出现不被百姓信任的情况。最好的统治者清静无为 很少发号施令。国家治理得美满祥和，而百姓都认为“我们本来就是这个样子”。</t>
+    <t>最高层次的统治者（叫“太上”），百姓感觉不到他们的存在；低一层次的统治者，百姓亲近他们、赞美他们；更低层次的统治者，百姓害怕他们；最低层次的统治者，百姓轻视、羞辱他们。正是因为统治者本身的诚信不足，所以才出现不被百姓信任的情况。最好的统治者清静无为 很少发号施令。国家治理得美满祥和，而百姓都认为“我们本来就是这个样子”。</t>
   </si>
   <si>
     <t>本章讲领导者的层次与境界。太上，下知有之：最高明的领导者，百姓只隐隐知道有他这个人，因为他不过多干预、不越边界，该管的事管好，不该管的放手。其次，亲而誉之：次一等的领导者被百姓亲近、赞誉。其次，畏之：再次一等的，百姓畏惧他。其次，侮之：最差的，百姓轻侮他。信不足焉，有不信焉：领导者自身诚信不足，百姓自然不会信任他。悠兮其贵言：最高境界是少言、贵言，不唠里唠叨，把话讲得有分量。功成事遂，百姓皆谓我自然：事情办成了，百姓都觉得是我们自己自然而然做成的，而不是领导者的功劳和主宰。
-韩鹏杰用“太上”的拆字讲：大上加一点才是太，点放下才成太，放到上面就成犬，寓意善于处下才能真正居上，太太、处长等词都蕴含此理。最好的教育和管理也是如此：不越俎代庖，让孩子、下属自己把事情做成，他们才有自信和成长，功成事遂皆谓我自然。</t>
+译者·韩鹏杰用“太上”的拆字讲：大上加一点才是太，点放下才成太，放到上面就成犬，寓意善于处下才能真正居上，太太、处长等词都蕴含此理。最好的教育和管理也是如此：不越俎代庖，让孩子、下属自己把事情做成，他们才有自信和成长，功成事遂皆谓我自然。</t>
   </si>
   <si>
     <t>第十八章</t>
@@ -311,24 +312,24 @@
     <t>大道废，有仁义；慧智出，有大伪；六亲不和，有孝慈；国家昏乱，有忠臣。</t>
   </si>
   <si>
-    <t>大道被废弃之后，人们开始提倡仁义；智慧出现之后，就产生了严重的虚伪；亲人之间关系不和睦，才会强调孝顺和慈爱；国家动乱时，才会出现忠臣。</t>
-  </si>
-  <si>
-    <t>本章与第十九章原为一章，讲“越缺什么越提倡什么”的历史递降逻辑。大道废，有仁义：大道被废弃了，才需要提倡仁义；六亲不和，有孝慈：家庭不和睦了，才强调孝慈；国家昏乱，有忠臣：国家混乱了，才显出忠臣。智慧出，有大伪：智巧盛行，反而产生大伪诈。韩鹏杰指出，这是老子的历史观：有道的时候不需要讲德，失道才讲德，失德才讲仁，失仁才讲义，失义才讲礼，一层一层往下掉。
+    <t>大道被废弃之后，就有人开始站出来提倡仁义；智慧、谋略、心机被推崇之后，就会产生严重的虚伪（大奸大伪）；亲人之间关系不和睦，才会强调孝顺和慈爱；国家动乱时，才会看出谁是忠臣。</t>
+  </si>
+  <si>
+    <t>本章与第十九章原为一章，讲“越缺什么越提倡什么”的历史递降逻辑。大道废，有仁义：大道被废弃了，才需要提倡仁义；六亲不和，有孝慈：家庭不和睦了，才强调孝慈；国家昏乱，有忠臣：国家混乱了，才显出忠臣。智慧出，有大伪：智巧盛行，反而产生大伪诈。译者·韩鹏杰指出，这是老子的历史观：有道的时候不需要讲德，失道才讲德，失德才讲仁，失仁才讲义，失义才讲礼，一层一层往下掉。
 一个社会天天提倡道德，正说明道德已经滑坡；什么时候妇女节、教师节不再成为问题，才说明相关地位真正提高了。这不是否定仁义孝慈，而是提醒人们不要靠表面提倡来补救，要从根本上回到道。把第十八、十九章连起来读：与其用仁义、智巧等外在名目补救，不如回归素朴本心，做个好人、存点好心、行些好事。</t>
   </si>
   <si>
     <t>第十九章</t>
   </si>
   <si>
-    <t>绝圣弃智，民利百倍；绝仁弃义，民复孝慈；绝巧弃利，盗贼无有。此三者以为文，不足。故令有所属：见（xiàn）素抱朴，少私寡欲，绝学无忧。</t>
-  </si>
-  <si>
-    <t>抛弃圣贤和智慧，百姓反而会得到百倍的利益；不去提倡仁义，百姓反而能够做到孝慈；清除技巧和利益，盗贼就不会产生。以上三条原则仅仅作为理论谈谈，是不够的。所以要为它们分别落实一些施行的具体措施：行为单纯 内心淳朴，减少私心 降低欲望，抛弃学问 没有忧虑。</t>
+    <t>绝圣弃智，民利百倍；绝仁弃义，民复孝慈；绝巧弃利，盗贼无有。此三者以为文不足。故令有所属：见（xiàn）素抱朴，少私寡欲，绝学无忧。</t>
+  </si>
+  <si>
+    <t>（为政者）弃绝智谋算和巧言令色，百姓反而会得到百倍的利益；不去提倡仁义，百姓反而能够做到孝慈；弃绝投机取巧和功利之心，盗贼就不会产生。以上三条原则仅仅作为理论谈谈是不够的。所以要为它们分别落实一些施行的具体措施：行为单纯 内心淳朴，减少私心 降低欲望，抛弃巧、利 没有忧虑。</t>
   </si>
   <si>
     <t>本章主张绝弃外在名目，回归素朴本心。绝圣弃智，民利百倍：抛弃圣贤名号和智巧机心，百姓反而得到百倍利益；绝仁弃义，民复孝慈：不刻意提倡仁义，百姓反而自然做到孝慈；绝巧弃利，盗贼无有：清除技巧和利益诱惑，盗贼就不会产生。此三者以为文不足：仅仅在理论上讲这三条还不够，要落实为具体方向——见素抱朴，少私寡欲，绝学无忧：行为单纯、内心淳朴，减少私心、降低欲望，不为纷繁的学问和机巧所惑，就没有忧虑。
-韩鹏杰说，道家认为人的本心就是真心，真心就是朴素之心，朴素之心就是少私寡欲；外在花花绿绿的学问看多了，反而把人搞乱。读经典要由博返约，最后陪我们一生的可能只是一两本书、一两句话，真传一句话，假传万卷书。绝学无忧不是不要学习，而是学真正的大道，不被浮华知识蒙蔽。</t>
+译者·韩鹏杰说，道家认为人的本心就是真心，真心就是朴素之心，朴素之心就是少私寡欲；外在花花绿绿的学问看多了，反而把人搞乱。读经典要由博返约，最后陪我们一生的可能只是一两本书、一两句话，真传一句话，假传万卷书。绝学无忧不是不要学习，而是学真正的大道，不被浮华知识蒙蔽。</t>
   </si>
   <si>
     <t>第二十章</t>
@@ -337,7 +338,7 @@
     <t>唯之与阿（hē），相去几何？善之与恶，相去若何？人之所畏，不可不畏。荒兮，其未央哉！众人熙熙，如享太牢，如春登台。我独泊兮，其未兆，如婴儿之未孩。儽（léi）儽兮，若无所归。众人皆有余，而我独若遗。我愚人之心也哉，沌（dùn）沌兮！俗人昭昭，我独昏昏；俗人察察，我独闷闷。澹（dàn）兮其若海； 飂（liù）兮若无止 。众人皆有以，而我独顽似鄙。我独异于人，而贵食母。</t>
   </si>
   <si>
-    <t>赞成与反对，相差有多远？善良与丑恶，相差又有多远？然而别人所害怕的，我不能不怕。前面的道路多么漫长啊，就像没有尽头！众人是那样的快乐，就好像参加盛大宴会，春日登台赏景一样。而只有我淡泊处之，无动于衷，就如同一个还不会笑的婴儿一般。我是如此狼狈不堪，就像个无家可归的人一样。众人都过着富裕幸福的生活，只有我却像被遗弃了一样。因为我有一副愚人的心肠，太笨拙了！世人是那样的明白，只有我是如此的糊涂；世人是那样的聪慧，只有我是这样的宽厚。我的生活是那样的坎坷多难 就好像那动荡不安的大海一样；我如同那飘忽不定的长风 不知何处才是归宿。众人活得都是那样的有用，只有我如此冥顽无能。虽然我和世人格格不入，但我还要继续以大道为依归。</t>
+    <t>赞成与反对，相差有多远？善良与丑恶，相差又有多远？大家都敬畏的不能不去敬畏！前面的道路多么漫长啊，就像没有尽头！众人是那样的快乐，就好像参加盛大宴会，春日登台赏景一样。而只有我淡泊处之，无动于衷，就如同一个还不会笑的婴儿一般。我是如此狼狈不堪，就像个无家可归的人一样。众人都过着富裕幸福的生活，只有我却像被遗弃了一样。因为我有一副愚人的心肠，太笨拙了！世人是那样的明白，只有我是如此的糊涂；世人是那样的聪慧，只有我是这样的宽厚。我的生活是那样的坎坷多难 就好像那动荡不安的大海一样；我如同那飘忽不定的长风 不知何处才是归宿。众人活得都是那样的有用，只有我如此冥顽无能。虽然我和世人格格不入，但我还要继续以大道为依归。</t>
   </si>
   <si>
     <t>本章是得道者的自画像。唯之与阿，相去几何？善之与恶，相去若何：恭敬的应答与呵斥相差多远？善与恶又相差多少？老子提醒，是非善恶的界限并非表面看起来那么分明，好事也可能带来坏结果。人之所畏，不可不畏：但众人共同敬畏的规则，也要敬守，不要为了标新立异而违背公认的规范。众人熙熙，如享太牢，如春登台：众人都热热闹闹，像参加盛宴、春日登台；我独泊兮，其未兆，如婴儿之未孩：得道者独自淡泊、无动于衷，像还不会笑的婴儿。
@@ -350,11 +351,11 @@
     <t>孔德之容，惟道是从。道之为物，惟恍惟惚。惚兮恍兮，其中有象；恍兮惚兮，其中有物。窈（yǎo）兮冥兮，其中有精；其精甚真，其中有信。自古及今，其名不去，以阅众甫。吾何以知众甫之状哉？以此。</t>
   </si>
   <si>
-    <t>高尚品德的内容，与大道是一致的。大道这种事物，是恍恍惚惚而没有形体的。它虽然是那样的恍惚迷离，但其中确实有一定内容；它虽然是那样的迷离恍惚，但其中确实有自己的内涵。大道是那样的深邃而难以认识，但它却有着自己的内容；它的内容是那样的真实无妄，充满了诚信。从古至今，大道都是无法被废弃的，凭借着它就可以知道万物开始时的情况。我凭什么知道万物开始时的情况呢？就是凭借大道。</t>
+    <t>有大德气质和形象的人，是会坚定地按照大道来行事。大道这种事物，是恍恍惚惚而没有形体的。它虽然是那样的恍惚迷离，但其中确实有征兆显现、有东西存在；它虽然是那样的迷离恍惚，但其中确实有自己的内涵。大道是那样的深邃而难以认识，但它却有着自己的内容；它的内容是那样的真实无妄，充满了诚信。从古至今，大道都是无法被废弃的，凭借着它就可以知道万物开始时的情况。我凭什么知道万物开始时的情况呢？就是凭借大道。</t>
   </si>
   <si>
     <t>本章讲大德与道的关系，证明道真实存在、可以验证。孔德之容，惟道是从：大德之人的样子，就是坚定地依道而行，“孔”是大，高僧大德即此意。道之为物，惟恍惟惚：道这个东西恍恍惚惚、没有固定形体；恍惚不是迷糊，而是心中忽然有光、有所领悟的顿悟状态。惚兮恍兮，其中有象；恍兮惚兮，其中有物：恍惚之中有境界、有内容。窈兮冥兮，其中有精：深远幽暗之中有精神；其精甚真，其中有信：这精神真实不虚，其中包含可信、可验证的规律。
-自古及今，其名不去，以阅众甫：从古至今，道的名字不曾消失，凭借它可以认识万物起始。吾何以知众甫之状哉？以此：我就是凭借道来认识圣人得道的状态。韩鹏杰强调，道不仅是万物的本源和规律，也是人生的境界；离开了道，人就变成无源之水、无本之木。这一章让人对道建立确信：它看不见摸不着，但真实存在，是精神世界的根基。</t>
+自古及今，其名不去，以阅众甫：从古至今，道的名字不曾消失，凭借它可以认识万物起始。吾何以知众甫之状哉？以此：我就是凭借道来认识圣人得道的状态。译者·韩鹏杰强调，道不仅是万物的本源和规律，也是人生的境界；离开了道，人就变成无源之水、无本之木。这一章让人对道建立确信：它看不见摸不着，但真实存在，是精神世界的根基。</t>
   </si>
   <si>
     <t>第二十二章</t>
@@ -376,11 +377,11 @@
     <t>希言自然。故飘风不终朝（zhāo），骤雨不终日。孰为此者？天地。天地尚不能久，而况于人乎？故从事于道者，同于道；德者，同于德；失者，同于失。同于道者，道亦乐得之；同于德者，德亦乐得之；同于失者，失亦乐得之。信不足焉，有不信焉。</t>
   </si>
   <si>
-    <t>君主要很少发号施令而让百姓自由发展。所以说狂风刮不了整整一个早晨，暴雨下不了整整一天。谁制造了这些狂风暴雨？是天地。天地尚且不能长久维持这种剧烈动荡的局面，更何况人呢？因此那些寻求大道的人，言行就会符合大道；修养美德的人，就会具备美德；坚持错误的人，就会永远犯错误。愿意同大道在一起的人，大道也乐于同他在一起；愿意同美德在一起的人，美德也乐于同他在一起；愿意同错误在一起的人，错误也乐于同他在一起。由于自己的诚信不足，才会不被信任。</t>
+    <t>君主要很少发号施令而让百姓自由发展 这样才是合乎自然的。所以说狂风刮不了整整一个早晨，暴雨下不了整整一天。谁制造了这些狂风暴雨？是天地。天地尚且不能长久维持这种剧烈动荡的局面，更何况人呢？因此那些寻求大道的人，言行就会符合大道；修养美德的人，就会具备美德；坚持错误的人，就会永远犯错误。愿意同大道在一起的人，大道也乐于同他在一起；愿意同美德在一起的人，美德也乐于同他在一起；愿意同错误在一起的人，错误也乐于同他在一起。因为失道失德的人诚信不足，大家都不信任他们。</t>
   </si>
   <si>
     <t>本章讲少言自然、同气相求。希言自然：珍惜言语、少发号施令，顺其自然才是规律。飘风不终朝，骤雨不终日：狂风刮不过一个早晨，暴雨下不了一整天，天地发的“脾气”尚且不能长久，何况人呢？人不应长期处于急躁、暴躁、浮躁的情绪状态。从事于道者，同于道；德者，同于德；失者，同于失：追求道的人与道相合，修养德的人与德相合，放任过失的人与过失相合。
-同于道者，道亦乐得之；同于德者，德亦乐得之；同于失者，失亦乐得之：你喜欢什么、亲近什么，就会被什么吸引和成就，人身边聚集什么样的人，往往取决于你自己是什么样的人。信不足焉，有不信焉：自己诚信不足，别人自然不会信任你。韩鹏杰指出，本章看似同语反复，其实在反复劝告：要让自己的境界不断提高，就要亲近有道有德的人和事，勇于发现并改正缺点，路是自己走出来的。</t>
+同于道者，道亦乐得之；同于德者，德亦乐得之；同于失者，失亦乐得之：你喜欢什么、亲近什么，就会被什么吸引和成就，人身边聚集什么样的人，往往取决于你自己是什么样的人。信不足焉，有不信焉：自己诚信不足，别人自然不会信任你。译者·韩鹏杰指出，本章看似同语反复，其实在反复劝告：要让自己的境界不断提高，就要亲近有道有德的人和事，勇于发现并改正缺点，路是自己走出来的。</t>
   </si>
   <si>
     <t>第二十四章</t>
@@ -393,7 +394,7 @@
   </si>
   <si>
     <t>本章列举自见、自是、自伐、自矜四种毛病，提醒人们平稳谦逊。企者不立：踮起脚尖想站得高，反而站不稳；跨者不行：跨着大步想走得快，反而走不远，稳定才能致远。自见者不明：固执己见的人看不清，兼听则明、偏听则暗；自是者不彰：自以为是，德行和功绩反不能彰显；自伐者无功：自我夸耀、攻击别人，反而把功劳送掉；自矜者不长：自高自大、放不下虚荣，反而失去成长机会。
-其在道也，曰余食赘行：这些行为在道看来，就像吃饱了再吃、身上长赘瘤，多余无用；物或恶之，故有道者不处：人们厌恶它们，有道的人不做这些事。韩鹏杰用项羽举例：力拔山兮气盖世，却因骄傲自大、听不进意见，落得自刎乌江的下场。孔子讲毋意、毋必、毋固、毋我，佛家讲无我相，与老子相通。做事要稳扎稳打，收敛自见、自是、自伐、自矜，才能不断进步。</t>
+其在道也，曰余食赘行：这些行为在道看来，就像吃饱了再吃、身上长赘瘤，多余无用；物或恶之，故有道者不处：人们厌恶它们，有道的人不做这些事。译者·韩鹏杰用项羽举例：力拔山兮气盖世，却因骄傲自大、听不进意见，落得自刎乌江的下场。孔子讲毋意、毋必、毋固、毋我，佛家讲无我相，与老子相通。做事要稳扎稳打，收敛自见、自是、自伐、自矜，才能不断进步。</t>
   </si>
   <si>
     <t>第二十五章</t>
@@ -406,7 +407,7 @@
   </si>
   <si>
     <t>本章是《道德经》极重要的一章，把道确立为宇宙本源，并提出全书最高法则道法自然。有物混成，先天地生：有一个混然一体的东西，先于天地而存在；寂兮寥兮：它无声无形；独立不改，周行而不殆：独立存在、永不改变，循环运行、永不停止，可以为天下母：可以看作天地万物的母亲。吾不知其名，字之曰道，强为之名曰大：不知它叫什么名字，勉强称它为道，再勉强称它为大。大曰逝，逝曰远，远曰反：大则向前运行，运行则越走越远，远到极点又返回本根，这是道的运动轨迹——周而复始。
-道大，天大，地大，王亦大，域中有四大，而王居其一焉：道、天、地、人（王）都是大的，人只是四大之一，不能自大。人法地，地法天，天法道，道法自然：人效法地，地效法天，天效法道，道效法它本来的样子，自然就是本该如此。韩鹏杰强调，道法自然是全书信仰和规则的源头，人要敬畏天道，与天地和谐相处。</t>
+道大，天大，地大，王亦大，域中有四大，而王居其一焉：道、天、地、人（王）都是大的，人只是四大之一，不能自大。人法地，地法天，天法道，道法自然：人效法地，地效法天，天效法道，道效法它本来的样子，自然就是本该如此。译者·韩鹏杰强调，道法自然是全书信仰和规则的源头，人要敬畏天道，与天地和谐相处。</t>
   </si>
   <si>
     <t>第二十六章</t>
@@ -415,11 +416,11 @@
     <t>重为轻根，静为躁君。是以圣人终日行不离辎（zī）重。虽有荣观，燕处超然。奈何万乘（shèng）之主，而以身轻天下？轻则失本，躁则失君。</t>
   </si>
   <si>
-    <t>重是轻的基础，静是动的根本。因此圣人整天在外旅行而从不离开自己的衣食行李。即使有奇观美景，也安处超然。为什么一个大国君主，却为了个人享乐而不重视自己的国家呢？不重视国家就会丧失自己的生存基础，轻举妄动就会丢掉自己的生存根本。</t>
+    <t>重是轻的基础，静是动的根本。因此圣人每天总是保持稳重 就像军队离不开自己的衣食行李。即使有奇观美景，也安处超然。为什么一个大国君主，却为了个人享乐而不重视自己的国家呢？不重视国家就会丧失自己的生存基础，轻举妄动就会丢掉自己的生存根本。</t>
   </si>
   <si>
     <t>本章讲重与轻、静与躁的关系。重为轻根：稳重是轻率的根本，要拿稳重控制住轻率，不让它表露、掌控自己；静为躁君：宁静是急躁的主宰，用安静、宁静、冷静控制浮躁、急躁、暴躁。是以圣人终日行不离辎重：有修养的人像行军不离粮草辎重一样，始终持守稳重这个根本。虽有荣观，燕处超然：面对华美堂皇的外在诱惑，依然安处超然，不为其所动。奈何万乘之主，而以身轻天下：为什么掌握大权的君主，却为了个人享乐而轻率地对待天下大事？
-轻则失根：轻率轻浮就失去根本，像飘蓬浮萍没有根基；躁则失君：浮躁急躁就失去对自己的掌控，冲动之下常常酿成大祸。韩鹏杰用“路怒”举例：开车偶有小摩擦就粗口相向甚至拔刀，动手前问自己要不要动手、后果如何、有无别的办法，几秒钟的冷静可能改变结果。开头八字“重为轻根，静为躁君”与结尾“轻则失根，躁则失君”都是至理名言。</t>
+轻则失根：轻率轻浮就失去根本，像飘蓬浮萍没有根基；躁则失君：浮躁急躁就失去对自己的掌控，冲动之下常常酿成大祸。译者·韩鹏杰用“路怒”举例：开车偶有小摩擦就粗口相向甚至拔刀，动手前问自己要不要动手、后果如何、有无别的办法，几秒钟的冷静可能改变结果。开头八字“重为轻根，静为躁君”与结尾“轻则失根，躁则失君”都是至理名言。</t>
   </si>
   <si>
     <t>第二十七章</t>
@@ -438,14 +439,14 @@
     <t>第二十八章</t>
   </si>
   <si>
-    <t>知其雄，守其雌，为天下谿（xi1）。为天下谿，常德不离，复归于婴儿。知其白，守其黑，为天下式。为天下式，常德不忒（te4），复归于无极。知其荣，守其辱，为天下谷。为天下谷，常德乃足，复归于朴（pu3）。朴散则为器，圣人用之则为官长，故大制不割。</t>
+    <t>知其雄，守其雌，为天下谿（xī）。为天下谿，常德不离，复归于婴儿。知其白，守其黑，为天下式。为天下式，常德不忒（tè），复归于无极。知其荣，守其辱，为天下谷。为天下谷，常德乃足，复归于朴（pǔ）。朴散则为器，圣人用之则为官长，故大制不割。</t>
   </si>
   <si>
     <t>知道什么是刚健，却要安于柔顺的地位，甘愿做天下的沟谿（溪谷）。甘愿做天下的沟谿（溪谷），高尚的品德就永远不会丧失，就能恢复到婴儿的纯真状态。知道什么是显赫地位，却要安于低下的地位，做天下人的榜样。做天下人的榜样，高尚的品德就永远不会出差错，就能具有无穷的力量。知道什么是荣耀，却要安于屈辱的地位，甘愿做天下的虚谷。甘愿做天下的虚谷，高尚品德就会永远保持圆满，就能够同大道保持一致。大道会分散显现为万物各自的本性，圣人就顺应着万物各自的本性去进行管理，所以说最完美的治理是不去伤害万物的本性。</t>
   </si>
   <si>
     <t>本章是“抱一为天下式”的例证，讲刚柔、黑白、荣辱的辩证统一。知其雄，守其雌，为天下谿：知道自己强大，却不恃强，安守柔雌，甘做天下的溪谷，水都汇到低处来，反而源远流长，复归于婴儿：回归婴儿般纯真柔软。知其白，守其黑，为天下式：知道明亮，却安守暗黑，做天下范式，常德不忒，复归于无极：德行不出差错，回归无穷的境界。知其荣，守其辱，为天下谷：知道荣耀，却安守屈辱，甘做天下的虚谷，常德乃足，复归于朴：德行充足，回归素朴。
-朴散则为器，圣人用之则为官长，故大制不割：素朴分散为万物之器，圣人顺应本性管理，最好的制度不伤害本性。韩鹏杰强调，守雌、守黑、守辱不是没有经历过强、白、荣就假装谦卑，而是先有实力和成就，再有资格谈守，比如书法先经历精巧，才能返璞归真。记住十八个字：知其雄守其雌，知其白守其黑，知其荣守其辱，就是这一章的核心智慧。</t>
+朴散则为器，圣人用之则为官长，故大制不割：素朴分散为万物之器，圣人顺应本性管理，最好的制度不伤害本性。译者·韩鹏杰强调，守雌、守黑、守辱不是没有经历过强、白、荣就假装谦卑，而是先有实力和成就，再有资格谈守，比如书法先经历精巧，才能返璞归真。记住十八个字：知其雄守其雌，知其白守其黑，知其荣守其辱，就是这一章的核心智慧。</t>
   </si>
   <si>
     <t>第二十九章</t>
@@ -455,11 +456,11 @@
 是以圣人去甚，去奢，去泰。</t>
   </si>
   <si>
-    <t>君主想要治理好天下却又按照个人意志去采取行动，我将会看到他达不到自己的目的（断定必然会失败）。天下这个神圣的器物，是不可以按照个人意志强行干预，强行把持。随心所欲地去治理天下的君主，一定会搞乱天下。想把天下据为己有的君主，一定会失去天下。因此圣人顺应自然 不妄为，故无失败；不强行把持，故无损失。（所以事情往往如此）本意也许是想走在前面 结果可能反而落在后面；本意也许是想轻轻哈气为物取暖 结果可能因为吹气太快而使物变凉；本意也许是想强壮 结果可能反而变得瘦弱；本意也许是想稍微减损一点儿 结果可能是全部毁掉了。因此圣人去掉那些极端的，奢侈的，过分的言行和欲望。</t>
+    <t>君主想要治理好天下却又按照个人意志去采取行动，我将会看到他达不到自己的目的（断定必然会失败）。天下这个神圣的器物，是不可以按照个人意志强行干预，强行把持。随心所欲地去治理天下的君主，一定会搞乱天下。想把天下据为己有的君主，一定会失去天下。因此圣人顺应自然 不妄为，故无失败；不强行把持，故无损失。（所以事情往往如此）本意也许是想走在前面 结果可能反而落在后面；本意也许是想轻轻哈气为物取暖 结果可能因为吹气太快而使物变凉；本意也许是想强壮 结果可能反而变得瘦弱；本意也许是想稍微减损一点儿 结果可能是全部毁掉了。因此圣人要去掉那些极端的，奢侈的，过分的言行和欲望。</t>
   </si>
   <si>
     <t>本章讲天下不可强为、强取。将欲取天下而为之，吾见其不得已：想用强力、武力夺取天下并按个人意志治理，注定达不到目的。天下神器，不可为也，不可执也：天下是神圣之物，不可强行干预，不可强行把持；为者败之，执者失之：强行去做的必失败，死死抓住的必失去。是以圣人无为，故无败；无执，故无失：圣人顺其自然、不妄为，所以不会失败；不强行把持，所以不会失去。
-故物或行或随，或嘘或吹，或强或羸，或载或隳：万物本性各不相同，有前行有跟随，有轻嘘有急吹，有强壮有羸弱，有安稳有毁坏，不能用一个标准、一种方式强求。是以圣人去甚，去奢，去泰：圣人去掉极端的、奢侈的、过分的言行和欲望。韩鹏杰指出，这一章要结合时代背景理解：春秋末期诸侯争霸、生灵涂炭，老子提出小国寡民设想，反对强为；读这一章要体会其中的沉痛感，任何事有生必有灭、有成必有败，强求和把持都违背天道。</t>
+故物或行或随，或嘘或吹，或强或羸，或载或隳：万物本性各不相同，有前行有跟随，有轻嘘有急吹，有强壮有羸弱，有安稳有毁坏，不能用一个标准、一种方式强求。是以圣人去甚，去奢，去泰：圣人去掉极端的、奢侈的、过分的言行和欲望。译者·韩鹏杰指出，这一章要结合时代背景理解：春秋末期诸侯争霸、生灵涂炭，老子提出小国寡民设想，反对强为；读这一章要体会其中的沉痛感，任何事有生必有灭、有成必有败，强求和把持都违背天道。</t>
   </si>
   <si>
     <t>第三十章</t>
@@ -472,7 +473,7 @@
   </si>
   <si>
     <t>本章与三十一章表达中国人对战争的痛恨与对和平的热爱。以道佐人主者，不以兵强天下：用道辅佐君主的人，不靠武力逞强天下。其事好还：用兵之事很快有报应，你打人多重，反作用力就多重。师之所处，荆棘生焉：军队到过的地方，荆棘丛生、断壁残垣；大军之后，必有凶年：大战之后必有灾荒凶年。善有果而已，不敢以取强：不得已打仗，达到保卫目的就停手，不敢逞强。
-果而勿矜，果而勿伐，果而勿骄：胜利了不自大、不夸耀、不骄傲；果而不得已，果而勿强：胜利是出于不得已，胜了也不逞强。物壮则老，是谓不道，不道早已：事物强盛到极点就走向衰败，逞强求壮不合道，不合道就很快灭亡。韩鹏杰说，这章最后三句话值得牢记：师之所处荆棘生焉，大军之后必有凶年，物壮则老。战争不可轻易发动，对待战争的态度就是对待同胞生命的态度；中华民族热爱和平，不惹事也不怕事。</t>
+果而勿矜，果而勿伐，果而勿骄：胜利了不自大、不夸耀、不骄傲；果而不得已，果而勿强：胜利是出于不得已，胜了也不逞强。物壮则老，是谓不道，不道早已：事物强盛到极点就走向衰败，逞强求壮不合道，不合道就很快灭亡。译者·韩鹏杰说，这章最后三句话值得牢记：师之所处荆棘生焉，大军之后必有凶年，物壮则老。战争不可轻易发动，对待战争的态度就是对待同胞生命的态度；中华民族热爱和平，不惹事也不怕事。</t>
   </si>
   <si>
     <t>第三十一章</t>
@@ -485,7 +486,7 @@
   </si>
   <si>
     <t>本章继续讲对待战争的态度，主张以丧礼对待战争。夫兵者，不祥之器：兵器是不祥之物，人们都厌恶它，所以有道的人不使用它。君子居则贵左，用兵则贵右：平时以左为尊，作战时以右为尊，用兵属于凶事。兵者不祥之器，非君子之器，不得已而用之，恬淡为上：战争不是君子常用的东西，万不得已才用，还要淡然处之。胜而不美，而美之者，是乐杀人：打了胜仗不应赞美庆祝，赞美胜利就是以杀人为乐；以杀人为乐的人，不可能得志于天下。
-吉事尚左，凶事尚右：吉庆之事尚左，凶丧之事尚右；偏将军居左，上将军居右，就是用办理丧事的礼节来对待战争。杀人之众，以悲哀泣之，战胜以丧礼处之：战争杀人众多，要带着悲哀的心情参与，战胜了也要用丧礼的仪式对待。韩鹏杰强调，这两章应该进小学课本，让和平的种子从小种下；战争胜利后第一件事不是放肆庆祝，而是祭奠双方的死者，因为他们都是生命。</t>
+吉事尚左，凶事尚右：吉庆之事尚左，凶丧之事尚右；偏将军居左，上将军居右，就是用办理丧事的礼节来对待战争。杀人之众，以悲哀泣之，战胜以丧礼处之：战争杀人众多，要带着悲哀的心情参与，战胜了也要用丧礼的仪式对待。译者·韩鹏杰强调，这两章应该进小学课本，让和平的种子从小种下；战争胜利后第一件事不是放肆庆祝，而是祭奠双方的死者，因为他们都是生命。</t>
   </si>
   <si>
     <t>第三十二章</t>
@@ -498,7 +499,7 @@
   </si>
   <si>
     <t>本章讲道的特点和知止的智慧。道常无名，朴虽小，天下莫能臣：道恒常无名，它的重要属性是朴实厚道；朴像原木，看似微小，却没有任何东西能让它臣服。侯王若能守之，万物将自宾：领导者若能守住朴实厚道，万物自然宾服归附。天地相合，以降甘露，民莫之令而自均：天地阴阳相合降下甘露，没有人命令，雨露自然均匀，治理也应如此自然而然。
-始制有名，名亦既有，夫亦将知止，知止可以不殆：人类社会开始有制度、名分是合理的，但有了名分制度要懂得边界，不能制度崇拜、名分崇拜，做过了头就走向反面；知道适可而止，才能避免危险。譬道之在天下，犹川谷之于江海：道在天下，就像川谷流向江海，是自然归附的过程，不是强迫。韩鹏杰强调，老子反复用重复和强调来突出重要思想，本章的核心就是朴与知止：做事朴实厚道，对制度名分保持克制，知道边界和限度，物极必反，知止不殆。</t>
+始制有名，名亦既有，夫亦将知止，知止可以不殆：人类社会开始有制度、名分是合理的，但有了名分制度要懂得边界，不能制度崇拜、名分崇拜，做过了头就走向反面；知道适可而止，才能避免危险。譬道之在天下，犹川谷之于江海：道在天下，就像川谷流向江海，是自然归附的过程，不是强迫。译者·韩鹏杰强调，老子反复用重复和强调来突出重要思想，本章的核心就是朴与知止：做事朴实厚道，对制度名分保持克制，知道边界和限度，物极必反，知止不殆。</t>
   </si>
   <si>
     <t>第三十三章</t>
@@ -511,7 +512,7 @@
   </si>
   <si>
     <t>本章像一首哲理诗，讲认识自己、战胜自己。知人者智，自知者明：了解别人是智慧，了解自己才是高明，人贵有自知之明，眼睛能看远方却看不见自己的眉毛。胜人者有力，自胜者强：战胜别人只是有力，能战胜自己的欲望、弱点才是真正的强大，西方强国强调强加于人，只是胜人者有力。知足者富：知道满足才是真正的富有，贪得无厌永远觉得匮乏；强行者有志：坚持按道去做、知难而进的人才有志向。
-不失其所者久：不离开自己的归宿才能长久，“所”就是精神家园，物质再发达也不能让精神家园花果飘零。死而不亡者寿：身死而精神不亡，才是真正的长寿，那些思想家的光芒像群星，在黑暗时指引方向。韩鹏杰说，这一章既写给领导者也写给普通人：自知、自胜、知足、强行、守所、精神不亡，六层递进，是中国文化中极高的人生境界。</t>
+不失其所者久：不离开自己的归宿才能长久，“所”就是精神家园，物质再发达也不能让精神家园花果飘零。死而不亡者寿：身死而精神不亡，才是真正的长寿，那些思想家的光芒像群星，在黑暗时指引方向。译者·韩鹏杰说，这一章既写给领导者也写给普通人：自知、自胜、知足、强行、守所、精神不亡，六层递进，是中国文化中极高的人生境界。</t>
   </si>
   <si>
     <t>第三十四章</t>
@@ -524,7 +525,7 @@
   </si>
   <si>
     <t>本章讲道无处不在、成就万物而不主宰，因不自大而成其大。大道泛兮，其可左右：道如水、如风，无处不在，左右逢源。万物恃之而生而不辞：万物依赖道生长，道从不推辞；功成而不名有：成就万物却不居功留名。衣养万物而不为主：护养万物却不做主宰，不要求感恩戴德。常无欲，可名于小：道无欲谦下，可以说它渺小；万物归焉而不为主，可名为大：万物归附它却不自居为主，又可以说它伟大。以其终不自为大，故能成其大：正因为它始终不自以为大，才真正成就了伟大。
-韩鹏杰强调，这一章讲量变质变、从小到大的道理：合抱之木生于毫末，九层之台起于累土，千里之行始于足下；天下难事必作于易，天下大事必作于细。做人做事不要自高自大、好高骛远，要虚怀若谷、脚踏实地，把容易的事当难事做，把小事做好，一步一步成就伟大。</t>
+译者·韩鹏杰强调，这一章讲量变质变、从小到大的道理：合抱之木生于毫末，九层之台起于累土，千里之行始于足下；天下难事必作于易，天下大事必作于细。做人做事不要自高自大、好高骛远，要虚怀若谷、脚踏实地，把容易的事当难事做，把小事做好，一步一步成就伟大。</t>
   </si>
   <si>
     <t>第三十五章</t>
@@ -537,7 +538,7 @@
   </si>
   <si>
     <t>本章讲守道则天下归往，平淡才是真。执大象，天下往：掌握大道（大象即道），天下人都会归附；往而不害，安平太：归附而不受伤害，安详、平稳、太平。乐与饵，过客止：音乐与美食能让人停下脚步，这些外在享受有吸引力，但也容易让人半途而废，不能沉溺其中。道之出口，淡乎其无味：道说出来淡而无味，不像美食音乐那样刺激；视之不足见，听之不足闻，用之不足既：看不见、听不到，却取之不尽、用之不竭。
-韩鹏杰说，我们日常所用而不知，天天都在用道却不自知；饮食清淡有益健康，人格返璞归真才接近道，清水出芙蓉、天然去雕饰是艺术的高境界。年轻人都觉得自己会成为伟大人物，最后发现伟大来自平凡，把自己看得平凡，才能重归于朴、重归于真、重归于道。真正的力量不是热闹炫耀，而是平淡之中无穷无尽。</t>
+译者·韩鹏杰说，我们日常所用而不知，天天都在用道却不自知；饮食清淡有益健康，人格返璞归真才接近道，清水出芙蓉、天然去雕饰是艺术的高境界。年轻人都觉得自己会成为伟大人物，最后发现伟大来自平凡，把自己看得平凡，才能重归于朴、重归于真、重归于道。真正的力量不是热闹炫耀，而是平淡之中无穷无尽。</t>
   </si>
   <si>
     <t>第三十六章</t>
@@ -550,7 +551,7 @@
   </si>
   <si>
     <t>本章把相反相成的思维讲得最直白，并提醒含藏的力量与边界。将欲歙之，必固张之：想收敛它，先让它张开；将欲弱之，必固强之：想削弱它，先让它强大（捧杀）；将欲废之，必固兴之：想废弃它，先让它兴盛，举得越高摔得越重；将欲夺之，必固与之：想夺取它，先给予它，钓鱼先下鱼饵。是谓微明：这种微妙而明确的智慧叫微明。柔弱胜刚强：柔弱可以战胜刚强。鱼不可脱于渊：鱼不能离开水，策略不能脱离客观条件；国之利器不可以示人：国家的利器不能轻易示人，时时亮剑威胁别人，别人就想折断你的剑。
-韩鹏杰用捧杀典故解释：杀君马者道旁儿，过分夸奖、吹捧使人骄傲自满、退步失败，关羽过不了奉承关而败走麦城；两军对垒时老弱残兵挑衅、敌人弃辎重诱敌，都是将欲夺之必固与之。本章不是说用阴谋，而是讲事物转化的规律：看清对立面的运动，力量与边界都要含藏，不能张扬炫耀。</t>
+译者·韩鹏杰用捧杀典故解释：杀君马者道旁儿，过分夸奖、吹捧使人骄傲自满、退步失败，关羽过不了奉承关而败走麦城；两军对垒时老弱残兵挑衅、敌人弃辎重诱敌，都是将欲夺之必固与之。本章不是说用阴谋，而是讲事物转化的规律：看清对立面的运动，力量与边界都要含藏，不能张扬炫耀。</t>
   </si>
   <si>
     <t>第三十七章</t>
@@ -563,7 +564,7 @@
   </si>
   <si>
     <t>本章是《道经》的收束，讲无为而无不为。道常无为而无不为：道恒常无为，不妄为、不干预，却成就万事万物。侯王若能守之，万物将自化：领导者若能守住道，万物自然化育成长。化而欲作，吾将镇之以无名之朴：万物生长中欲望萌动时，用无名的素朴去镇服安定。无名之朴，亦将无欲：素朴本身没有欲望。不欲以静，天下将自定：没有欲望就能安静，天下自然安定。
-韩鹏杰把无为理解为：不违背规律、不妄为、不折腾，而不是消极不作为；治理的最高境界是让事物按自己的本性生长，让百姓自然发展生产、自然安定。从第一章到第三十七章是《道经》，讲道本身；后三十八章起是《德经》，讲道落实到人。把这两部分合起来读，“道在前而德在后”，做一切事才能顺理成章。</t>
+译者·韩鹏杰把无为理解为：不违背规律、不妄为、不折腾，而不是消极不作为；治理的最高境界是让事物按自己的本性生长，让百姓自然发展生产、自然安定。从第一章到第三十七章是《道经》，讲道本身；后三十八章起是《德经》，讲道落实到人。把这两部分合起来读，“道在前而德在后”，做一切事才能顺理成章。</t>
   </si>
   <si>
     <t>第三十八章</t>
@@ -576,7 +577,7 @@
   </si>
   <si>
     <t>本章开启《德经》，讲真正的德是自然无心的。上德不德，是以有德：真正有德的人不把德行当回事，做了好事自然忘掉，反而真有德；下德不失德，是以无德：境界不高的人总怕德行失去，处处表现、宣扬，反而无德。上德无为而无以为：有德者自然作为，没有功利目的；下德为之而有以为：无德者做事带着目的。上仁为之而无以为：仁者做好事不为私欲；上义为之而有以为：讲义的人制定规则，多少带着私心；上礼为之而莫之应，则攘臂而扔之：讲礼的人若没人响应，就卷起袖子强推。
-失道而后德，失德而后仁，失仁而后义，失义而后礼：道、德、仁、义、礼逐层下降。夫礼者，忠信之薄而乱之首：礼是忠信稀薄、祸乱开始的标志。前识者，道之华而愚之始：自诩能预知未来的人，只是道的浮华外表，是愚昧的开始。是以大丈夫处其厚，不居其薄；处其实，不居其华：大丈夫要居厚实、弃浮华，去彼取此。韩鹏杰说，上德不德也是相反相成思维：越在意形式越失去内容。</t>
+失道而后德，失德而后仁，失仁而后义，失义而后礼：道、德、仁、义、礼逐层下降。夫礼者，忠信之薄而乱之首：礼是忠信稀薄、祸乱开始的标志。前识者，道之华而愚之始：自诩能预知未来的人，只是道的浮华外表，是愚昧的开始。是以大丈夫处其厚，不居其薄；处其实，不居其华：大丈夫要居厚实、弃浮华，去彼取此。译者·韩鹏杰说，上德不德也是相反相成思维：越在意形式越失去内容。</t>
   </si>
   <si>
     <t>德经</t>
@@ -592,7 +593,7 @@
   </si>
   <si>
     <t>本章讲“得一”的力量和贵以贱为本。昔之得一者：天得一以清，地得一以宁，神得一以灵，谷得一以盈，万物得一以生，侯王得一以为天下正：天得道而清明，地得道而安宁，神得道而有灵，河谷得道而充盈，万物得道而生长，侯王得道而成为天下首领。“一”就是阴阳两者的统一，也就是道。其致之也：若失去道，天将裂、地将废、神将歇、谷将竭、万物将灭、侯王将蹶。故贵以贱为本，高以下为基：贵以贱为根本，高以下为基础。
-是以侯王自谓孤、寡、不穀：侯王自称孤、寡、不穀，正是以贱为本、以下为基。致数舆无舆：刻意追求众多荣誉反而失去荣誉。是故不欲琭琭如玉，珞珞如石：不要像华美的玉，要像坚硬的石头，石头能铺路济人，华美的玉看似高贵却少有用处。韩鹏杰强调两个重点：一是“一”即道，是阴阳统一；二是“贵以贱为本，高以下为基”，位置越高越要善于处下，把根基打牢，做人要处实不居华。</t>
+是以侯王自谓孤、寡、不穀：侯王自称孤、寡、不穀，正是以贱为本、以下为基。致数舆无舆：刻意追求众多荣誉反而失去荣誉。是故不欲琭琭如玉，珞珞如石：不要像华美的玉，要像坚硬的石头，石头能铺路济人，华美的玉看似高贵却少有用处。译者·韩鹏杰强调两个重点：一是“一”即道，是阴阳统一；二是“贵以贱为本，高以下为基”，位置越高越要善于处下，把根基打牢，做人要处实不居华。</t>
   </si>
   <si>
     <t>第四十章</t>
@@ -605,7 +606,7 @@
   </si>
   <si>
     <t>本章只有三句话，却是全书思维总纲。反者道之动：道向相反的方向运动，事物发展到极点就走向反面，又终而复返，回到更高层次的本根。所以看问题不能只站在自己的角度，要换位思考、正反合地看：正面看、反面看、合起来看，才能全面。弱者道之用：道的作用体现在柔弱一面，大家都逞强，柔弱反被强调，这是阴阳统一的思维方式。天下万物生于有，有生于无：万物产生于有，有产生于无；任何事物都有有和无两个方面，有让我们观察边界，无让我们观察妙处。
-韩鹏杰强调，如果只看到有形东西的作用，忽略无形东西的作用，物质世界越发达，精神家园就越花果飘零；既要看到物质财富，更要看到精神、信仰、理论这些无形力量。前三章讲道，第四十章用三句话总结全书思维方式，后边各章都是它的展开和例证。</t>
+译者·韩鹏杰强调，如果只看到有形东西的作用，忽略无形东西的作用，物质世界越发达，精神家园就越花果飘零；既要看到物质财富，更要看到精神、信仰、理论这些无形力量。前三章讲道，第四十章用三句话总结全书思维方式，后边各章都是它的展开和例证。</t>
   </si>
   <si>
     <t>第四十一章</t>
@@ -1110,7 +1111,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1135,18 +1136,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -1616,137 +1605,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1762,10 +1751,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2294,18 +2280,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E83"/>
-  <sheetFormatPr defaultColWidth="23.75" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="23.75" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="54.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="56.875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.8796296296296" style="2" customWidth="1"/>
+    <col min="2" max="2" width="50" style="2" customWidth="1"/>
+    <col min="3" max="3" width="56.8796296296296" style="2" customWidth="1"/>
     <col min="4" max="4" width="75.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="7.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="7.37962962962963" style="2" customWidth="1"/>
     <col min="6" max="16383" width="23.75" style="2" customWidth="1"/>
     <col min="16384" max="16384" width="23.75" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.25" spans="1:5">
+    <row r="1" s="1" customFormat="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2322,7 +2308,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="384.75" spans="1:5">
+    <row r="2" s="2" customFormat="1" ht="372.6" spans="1:5">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -2339,7 +2325,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" ht="156.75" spans="1:5">
+    <row r="3" ht="151.8" spans="1:5">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -2356,7 +2342,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" ht="156.75" spans="1:5">
+    <row r="4" ht="151.8" spans="1:5">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
@@ -2373,7 +2359,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" ht="156.75" spans="1:5">
+    <row r="5" ht="151.8" spans="1:5">
       <c r="A5" s="4" t="s">
         <v>19</v>
       </c>
@@ -2390,7 +2376,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="156.75" spans="1:5">
+    <row r="6" ht="151.8" spans="1:5">
       <c r="A6" s="4" t="s">
         <v>23</v>
       </c>
@@ -2407,7 +2393,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" ht="142.5" spans="1:5">
+    <row r="7" ht="151.8" spans="1:5">
       <c r="A7" s="4" t="s">
         <v>27</v>
       </c>
@@ -2424,7 +2410,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" ht="128.25" spans="1:5">
+    <row r="8" ht="124.2" spans="1:5">
       <c r="A8" s="4" t="s">
         <v>31</v>
       </c>
@@ -2441,11 +2427,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" ht="156.75" spans="1:5">
+    <row r="9" ht="151.8" spans="1:5">
       <c r="A9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="4" t="s">
@@ -2458,7 +2444,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" ht="156.75" spans="1:5">
+    <row r="10" ht="179.4" spans="1:5">
       <c r="A10" s="4" t="s">
         <v>39</v>
       </c>
@@ -2475,7 +2461,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" ht="142.5" spans="1:5">
+    <row r="11" ht="138" spans="1:5">
       <c r="A11" s="4" t="s">
         <v>43</v>
       </c>
@@ -2492,7 +2478,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" ht="156.75" spans="1:5">
+    <row r="12" ht="151.8" spans="1:5">
       <c r="A12" s="4" t="s">
         <v>47</v>
       </c>
@@ -2509,7 +2495,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" ht="142.5" spans="1:5">
+    <row r="13" ht="138" spans="1:5">
       <c r="A13" s="4" t="s">
         <v>51</v>
       </c>
@@ -2526,7 +2512,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" ht="142.5" spans="1:5">
+    <row r="14" ht="151.8" spans="1:5">
       <c r="A14" s="4" t="s">
         <v>55</v>
       </c>
@@ -2543,7 +2529,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" ht="156.75" spans="1:5">
+    <row r="15" ht="151.8" spans="1:5">
       <c r="A15" s="4" t="s">
         <v>59</v>
       </c>
@@ -2560,7 +2546,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" ht="171" spans="1:5">
+    <row r="16" ht="179.4" spans="1:5">
       <c r="A16" s="4" t="s">
         <v>63</v>
       </c>
@@ -2577,7 +2563,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" ht="213.75" spans="1:5">
+    <row r="17" ht="207" spans="1:5">
       <c r="A17" s="4" t="s">
         <v>67</v>
       </c>
@@ -2594,7 +2580,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" ht="156.75" spans="1:5">
+    <row r="18" ht="151.8" spans="1:5">
       <c r="A18" s="4" t="s">
         <v>71</v>
       </c>
@@ -2611,7 +2597,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" ht="156.75" spans="1:5">
+    <row r="19" ht="165.6" spans="1:5">
       <c r="A19" s="4" t="s">
         <v>75</v>
       </c>
@@ -2628,7 +2614,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" ht="142.5" spans="1:5">
+    <row r="20" ht="138" spans="1:5">
       <c r="A20" s="4" t="s">
         <v>79</v>
       </c>
@@ -2645,7 +2631,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" ht="156.75" spans="1:5">
+    <row r="21" ht="151.8" spans="1:5">
       <c r="A21" s="4" t="s">
         <v>83</v>
       </c>
@@ -2662,7 +2648,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" ht="185.25" spans="1:5">
+    <row r="22" ht="179.4" spans="1:5">
       <c r="A22" s="4" t="s">
         <v>87</v>
       </c>
@@ -2679,7 +2665,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" ht="156.75" spans="1:5">
+    <row r="23" ht="165.6" spans="1:5">
       <c r="A23" s="4" t="s">
         <v>91</v>
       </c>
@@ -2696,7 +2682,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" ht="171" spans="1:5">
+    <row r="24" ht="165.6" spans="1:5">
       <c r="A24" s="4" t="s">
         <v>95</v>
       </c>
@@ -2713,7 +2699,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" ht="156.75" spans="1:5">
+    <row r="25" ht="151.8" spans="1:5">
       <c r="A25" s="4" t="s">
         <v>99</v>
       </c>
@@ -2730,7 +2716,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" ht="156.75" spans="1:5">
+    <row r="26" ht="151.8" spans="1:5">
       <c r="A26" s="4" t="s">
         <v>103</v>
       </c>
@@ -2747,7 +2733,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" ht="156.75" spans="1:5">
+    <row r="27" ht="165.6" spans="1:5">
       <c r="A27" s="4" t="s">
         <v>107</v>
       </c>
@@ -2764,7 +2750,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" ht="156.75" spans="1:5">
+    <row r="28" ht="165.6" spans="1:5">
       <c r="A28" s="4" t="s">
         <v>111</v>
       </c>
@@ -2781,7 +2767,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" ht="171" spans="1:5">
+    <row r="29" ht="179.4" spans="1:5">
       <c r="A29" s="4" t="s">
         <v>115</v>
       </c>
@@ -2798,7 +2784,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" ht="171" spans="1:5">
+    <row r="30" ht="165.6" spans="1:5">
       <c r="A30" s="4" t="s">
         <v>119</v>
       </c>
@@ -2815,7 +2801,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" ht="171" spans="1:5">
+    <row r="31" ht="165.6" spans="1:5">
       <c r="A31" s="4" t="s">
         <v>123</v>
       </c>
@@ -2832,7 +2818,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" ht="156.75" spans="1:5">
+    <row r="32" ht="165.6" spans="1:5">
       <c r="A32" s="4" t="s">
         <v>127</v>
       </c>
@@ -2849,7 +2835,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" ht="171" spans="1:5">
+    <row r="33" ht="165.6" spans="1:5">
       <c r="A33" s="4" t="s">
         <v>131</v>
       </c>
@@ -2866,7 +2852,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" ht="171" spans="1:5">
+    <row r="34" ht="165.6" spans="1:5">
       <c r="A34" s="4" t="s">
         <v>135</v>
       </c>
@@ -2883,7 +2869,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" ht="142.5" spans="1:5">
+    <row r="35" ht="151.8" spans="1:5">
       <c r="A35" s="4" t="s">
         <v>139</v>
       </c>
@@ -2900,7 +2886,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" ht="156.75" spans="1:5">
+    <row r="36" ht="151.8" spans="1:5">
       <c r="A36" s="4" t="s">
         <v>143</v>
       </c>
@@ -2917,7 +2903,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" ht="142.5" spans="1:5">
+    <row r="37" ht="151.8" spans="1:5">
       <c r="A37" s="4" t="s">
         <v>147</v>
       </c>
@@ -2934,7 +2920,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" ht="156.75" spans="1:5">
+    <row r="38" ht="165.6" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>151</v>
       </c>
@@ -2951,7 +2937,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" ht="142.5" spans="1:5">
+    <row r="39" ht="138" spans="1:5">
       <c r="A39" s="4" t="s">
         <v>155</v>
       </c>
@@ -2968,7 +2954,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" ht="185.25" spans="1:5">
+    <row r="40" ht="193.2" spans="1:5">
       <c r="A40" s="4" t="s">
         <v>159</v>
       </c>
@@ -2985,7 +2971,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="41" ht="156.75" spans="1:5">
+    <row r="41" ht="165.6" spans="1:5">
       <c r="A41" s="4" t="s">
         <v>164</v>
       </c>
@@ -3002,7 +2988,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="42" ht="142.5" spans="1:5">
+    <row r="42" ht="151.8" spans="1:5">
       <c r="A42" s="4" t="s">
         <v>168</v>
       </c>
@@ -3023,13 +3009,13 @@
       <c r="A43" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="5" t="s">
         <v>175</v>
       </c>
       <c r="E43" s="4" t="s">
@@ -3040,13 +3026,13 @@
       <c r="A44" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="5" t="s">
         <v>179</v>
       </c>
       <c r="E44" s="4" t="s">
@@ -3057,13 +3043,13 @@
       <c r="A45" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D45" s="5" t="s">
         <v>183</v>
       </c>
       <c r="E45" s="4" t="s">
@@ -3074,13 +3060,13 @@
       <c r="A46" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D46" s="5" t="s">
         <v>187</v>
       </c>
       <c r="E46" s="4" t="s">
@@ -3091,13 +3077,13 @@
       <c r="A47" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="5" t="s">
         <v>191</v>
       </c>
       <c r="E47" s="4" t="s">
@@ -3108,13 +3094,13 @@
       <c r="A48" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D48" s="5" t="s">
         <v>195</v>
       </c>
       <c r="E48" s="4" t="s">
@@ -3125,13 +3111,13 @@
       <c r="A49" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="5" t="s">
         <v>199</v>
       </c>
       <c r="E49" s="4" t="s">
@@ -3142,13 +3128,13 @@
       <c r="A50" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="5" t="s">
         <v>203</v>
       </c>
       <c r="E50" s="4" t="s">
@@ -3159,13 +3145,13 @@
       <c r="A51" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="5" t="s">
         <v>207</v>
       </c>
       <c r="E51" s="4" t="s">
@@ -3176,13 +3162,13 @@
       <c r="A52" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D52" s="5" t="s">
         <v>211</v>
       </c>
       <c r="E52" s="4" t="s">
@@ -3193,13 +3179,13 @@
       <c r="A53" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D53" s="5" t="s">
         <v>215</v>
       </c>
       <c r="E53" s="4" t="s">
@@ -3210,30 +3196,30 @@
       <c r="A54" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="5" t="s">
         <v>219</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="55" ht="409.5" spans="1:5">
+    <row r="55" ht="400.2" spans="1:5">
       <c r="A55" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="5" t="s">
         <v>223</v>
       </c>
       <c r="E55" s="4" t="s">
@@ -3244,13 +3230,13 @@
       <c r="A56" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="D56" s="5" t="s">
         <v>227</v>
       </c>
       <c r="E56" s="4" t="s">
@@ -3261,30 +3247,30 @@
       <c r="A57" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="D57" s="5" t="s">
         <v>231</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="58" ht="409.5" spans="1:5">
+    <row r="58" ht="372.6" spans="1:5">
       <c r="A58" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="D58" s="5" t="s">
         <v>235</v>
       </c>
       <c r="E58" s="4" t="s">
@@ -3295,13 +3281,13 @@
       <c r="A59" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D59" s="5" t="s">
         <v>239</v>
       </c>
       <c r="E59" s="4" t="s">
@@ -3312,13 +3298,13 @@
       <c r="A60" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="D60" s="5" t="s">
         <v>243</v>
       </c>
       <c r="E60" s="4" t="s">
@@ -3329,13 +3315,13 @@
       <c r="A61" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="D61" s="5" t="s">
         <v>247</v>
       </c>
       <c r="E61" s="4" t="s">
@@ -3346,13 +3332,13 @@
       <c r="A62" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="D62" s="6" t="s">
+      <c r="D62" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E62" s="4" t="s">
@@ -3363,13 +3349,13 @@
       <c r="A63" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="D63" s="6" t="s">
+      <c r="D63" s="5" t="s">
         <v>255</v>
       </c>
       <c r="E63" s="4" t="s">
@@ -3380,13 +3366,13 @@
       <c r="A64" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="D64" s="6" t="s">
+      <c r="D64" s="5" t="s">
         <v>259</v>
       </c>
       <c r="E64" s="4" t="s">
@@ -3397,13 +3383,13 @@
       <c r="A65" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="D65" s="5" t="s">
         <v>263</v>
       </c>
       <c r="E65" s="4" t="s">
@@ -3414,30 +3400,30 @@
       <c r="A66" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="D66" s="6" t="s">
+      <c r="D66" s="5" t="s">
         <v>267</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="67" ht="393.75" spans="1:5">
+    <row r="67" ht="345" spans="1:5">
       <c r="A67" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="D67" s="6" t="s">
+      <c r="D67" s="5" t="s">
         <v>271</v>
       </c>
       <c r="E67" s="4" t="s">
@@ -3448,13 +3434,13 @@
       <c r="A68" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="D68" s="5" t="s">
         <v>275</v>
       </c>
       <c r="E68" s="4" t="s">
@@ -3465,13 +3451,13 @@
       <c r="A69" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="C69" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D69" s="5" t="s">
         <v>279</v>
       </c>
       <c r="E69" s="4" t="s">
@@ -3482,13 +3468,13 @@
       <c r="A70" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C70" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D70" s="5" t="s">
         <v>283</v>
       </c>
       <c r="E70" s="4" t="s">
@@ -3499,13 +3485,13 @@
       <c r="A71" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="D71" s="6" t="s">
+      <c r="D71" s="5" t="s">
         <v>287</v>
       </c>
       <c r="E71" s="4" t="s">
@@ -3516,13 +3502,13 @@
       <c r="A72" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C72" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="D72" s="6" t="s">
+      <c r="D72" s="5" t="s">
         <v>291</v>
       </c>
       <c r="E72" s="4" t="s">
@@ -3533,30 +3519,30 @@
       <c r="A73" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="B73" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="C73" s="6" t="s">
+      <c r="C73" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="D73" s="6" t="s">
+      <c r="D73" s="5" t="s">
         <v>295</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="74" ht="409.5" spans="1:5">
+    <row r="74" ht="358.8" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="C74" s="6" t="s">
+      <c r="C74" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="D74" s="6" t="s">
+      <c r="D74" s="5" t="s">
         <v>299</v>
       </c>
       <c r="E74" s="4" t="s">
@@ -3567,47 +3553,47 @@
       <c r="A75" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="B75" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="C75" s="6" t="s">
+      <c r="C75" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="D75" s="6" t="s">
+      <c r="D75" s="5" t="s">
         <v>303</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="76" ht="409.5" spans="1:5">
+    <row r="76" ht="400.2" spans="1:5">
       <c r="A76" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="B76" s="6" t="s">
+      <c r="B76" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="D76" s="6" t="s">
+      <c r="D76" s="5" t="s">
         <v>307</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="77" ht="409.5" spans="1:5">
+    <row r="77" ht="386.4" spans="1:5">
       <c r="A77" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="C77" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="D77" s="6" t="s">
+      <c r="D77" s="5" t="s">
         <v>311</v>
       </c>
       <c r="E77" s="4" t="s">
@@ -3618,30 +3604,30 @@
       <c r="A78" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="C78" s="6" t="s">
+      <c r="C78" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="D78" s="6" t="s">
+      <c r="D78" s="5" t="s">
         <v>315</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="79" ht="409.5" spans="1:5">
+    <row r="79" ht="400.2" spans="1:5">
       <c r="A79" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="B79" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="C79" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="D79" s="6" t="s">
+      <c r="D79" s="5" t="s">
         <v>319</v>
       </c>
       <c r="E79" s="4" t="s">
@@ -3652,13 +3638,13 @@
       <c r="A80" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="B80" s="6" t="s">
+      <c r="B80" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="C80" s="6" t="s">
+      <c r="C80" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="D80" s="6" t="s">
+      <c r="D80" s="5" t="s">
         <v>323</v>
       </c>
       <c r="E80" s="4" t="s">
@@ -3669,13 +3655,13 @@
       <c r="A81" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="B81" s="6" t="s">
+      <c r="B81" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="C81" s="6" t="s">
+      <c r="C81" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="D81" s="6" t="s">
+      <c r="D81" s="5" t="s">
         <v>327</v>
       </c>
       <c r="E81" s="4" t="s">
@@ -3686,13 +3672,13 @@
       <c r="A82" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="C82" s="6" t="s">
+      <c r="C82" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="D82" s="6" t="s">
+      <c r="D82" s="5" t="s">
         <v>331</v>
       </c>
       <c r="E82" s="4" t="s">
@@ -3703,13 +3689,13 @@
       <c r="A83" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="B83" s="6" t="s">
+      <c r="B83" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="C83" s="6" t="s">
+      <c r="C83" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="D83" s="6" t="s">
+      <c r="D83" s="5" t="s">
         <v>335</v>
       </c>
       <c r="E83" s="4" t="s">

--- a/book.xlsx
+++ b/book.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13668" windowHeight="13380"/>
+    <workbookView windowWidth="13668" windowHeight="12000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -469,7 +469,7 @@
     <t>以道佐人主者，不以兵强天下。其事好还（huán）。师之所处，荆棘生焉。大军之后，必有凶年。善有果而已，不敢以取强。果而勿矜，果而勿伐，果而勿骄。果而不得已，果而勿强。物壮则老，是谓不道，不道早已。</t>
   </si>
   <si>
-    <t>遵循大道去辅佐君主的人，是不会凭借武力去逞强于天下的。用兵打仗的事很快就会得到报应。战争发生过的地区，荆棘丛生。大战之后，必有一个灾荒年。只要很好地取得胜利就罢手，不敢依仗武力称王称霸。胜利了而不自大，胜利了而不夸耀，胜利了而不骄傲。胜利之后还要感到自己是出于不得已才打的这次胜仗，胜利了而不逞强。事物强盛了就会走向衰败，求强求壮的做法是不符合大道的，不符合大道就会很快灭亡。</t>
+    <t>遵循大道去辅佐君主的人，是不会凭借武力去逞强于天下的。用兵打仗的事很快就会得到报应。战争发生过的地区，荆棘丛生。大战之后，必有一个灾荒年。（真正善于用兵的人）取得胜利就罢手，不敢依仗武力称王称霸。胜利了而不自大，胜利了而不夸耀，胜利了而不骄傲。胜利之后还要感到自己是出于不得已才打的这次胜仗，胜利了而不逞强。事物强盛了就会走向衰败，求强求壮的做法是不符合大道的，不符合大道就会很快灭亡。</t>
   </si>
   <si>
     <t>本章与三十一章表达中国人对战争的痛恨与对和平的热爱。以道佐人主者，不以兵强天下：用道辅佐君主的人，不靠武力逞强天下。其事好还：用兵之事很快有报应，你打人多重，反作用力就多重。师之所处，荆棘生焉：军队到过的地方，荆棘丛生、断壁残垣；大军之后，必有凶年：大战之后必有灾荒凶年。善有果而已，不敢以取强：不得已打仗，达到保卫目的就停手，不敢逞强。
@@ -495,7 +495,7 @@
     <t>道常无名，朴虽小，天下莫能臣也。侯王若能守之，万物将自宾。天地相合，以降甘露，民莫之令而自均。始制有名，名亦既有，夫亦将知止。知止可以不殆。譬道之在天下，犹川谷之于江海。</t>
   </si>
   <si>
-    <t>大道永远处于一种看不见、摸不着的虚无状态，它好像未加工过的原木一样，虽然微不足道 但是天下没有人能够改变它。王侯如果能够遵循大道，万物将会自然而然地宾服于他。天之气和地之气就会相互交融，降下甘露一类的美好事物，没有人指使人们该如何做而自然均平安定。人们开始制作各种各样有名称的器物和制度，各种器物和制度出现以后，也应该知道适可而止。知道适可而止就能避免危险。打个比方 大道与天下万物的关系，就好像江海与河川的关系一样。</t>
+    <t>大道永远处于一种看不见、摸不着的虚无状态，它好像未加工过的原木一样（朴素而不张扬），虽然微不足道 但是天下没有人能够改变它。王侯如果能够遵循大道，万物将会自然而然地宾服于他（大家才能真正的信任他、支持他）。天之气和地之气就会相互交融，降下甘露一类的美好事物，没有人指使人们该如何做而自然均平安定。人们开始制作各种各样有名称的器物和制度，各种器物和制度出现以后，也应该知道适可而止。知道适可而止就能避免危险。打个比方 大道与天下万物的关系，就好像江海与河川的关系一样。</t>
   </si>
   <si>
     <t>本章讲道的特点和知止的智慧。道常无名，朴虽小，天下莫能臣：道恒常无名，它的重要属性是朴实厚道；朴像原木，看似微小，却没有任何东西能让它臣服。侯王若能守之，万物将自宾：领导者若能守住朴实厚道，万物自然宾服归附。天地相合，以降甘露，民莫之令而自均：天地阴阳相合降下甘露，没有人命令，雨露自然均匀，治理也应如此自然而然。
@@ -508,7 +508,7 @@
     <t>知人者智，自知者明。胜人者有力，自胜者强。知足者富，强行者有志。不失其所者久，死而不亡者寿。</t>
   </si>
   <si>
-    <t>能够认识别人的人是聪明的，能够认识自我的人则更为睿智。能够战胜别人的人是有力量的，能够战胜自我的人则更为强大。知道满足的人是富有的，遵循大道坚持力行的人是有志的。不违背大道的人就能长久生存，死而精神永存的人是真正的长寿之人。</t>
+    <t>能够了解别人的人是聪明的，能够了解自己的人则更为睿智。能够战胜别人的人是有力量的，能够战胜自我的人则更为强大。知道满足的人是富有的，遵循大道坚持力行的人是有志的。不违背大道的人就能长久生存，身体没了但精神永存的人才是真正的寿命长久。</t>
   </si>
   <si>
     <t>本章像一首哲理诗，讲认识自己、战胜自己。知人者智，自知者明：了解别人是智慧，了解自己才是高明，人贵有自知之明，眼睛能看远方却看不见自己的眉毛。胜人者有力，自胜者强：战胜别人只是有力，能战胜自己的欲望、弱点才是真正的强大，西方强国强调强加于人，只是胜人者有力。知足者富：知道满足才是真正的富有，贪得无厌永远觉得匮乏；强行者有志：坚持按道去做、知难而进的人才有志向。
@@ -521,7 +521,7 @@
     <t>大道泛兮，其可左右。万物恃之而生而不辞，功成而不名有。衣养万物而不为主，常无欲，可名于小。万物归焉而不为主，可名为大。以其终不自为大，故能成其大。</t>
   </si>
   <si>
-    <t>大道的作用是那样的广大而普遍，可以说无处不在。万物依靠它才能生存 而它从不限制万物，大功告成也不去求名、不去占有。护养了万物而不做万物的主宰者，永远没有什么欲望，可以把道看作是卑微的。因为虽然万物归附于它 而它却不当万物的主宰者，也可以把它看作是伟大的。因为它始终不追求成为伟大者，所以才能成为伟大者。</t>
+    <t>大道的作用是那样的广大而普遍，可以说无处不在。万物依靠它才能生存 而它从不限制万物，大功告成也不去求名、不去占有。护养了万物而不做万物的主宰者，它无欲而静，隐微虚无，所以可以把道称作为“小”。虽然万物归附于道 而它却不当万物的主宰者，所以把它看作是伟大的。因为它始终不追求成为伟大者，所以才能成为伟大者。</t>
   </si>
   <si>
     <t>本章讲道无处不在、成就万物而不主宰，因不自大而成其大。大道泛兮，其可左右：道如水、如风，无处不在，左右逢源。万物恃之而生而不辞：万物依赖道生长，道从不推辞；功成而不名有：成就万物却不居功留名。衣养万物而不为主：护养万物却不做主宰，不要求感恩戴德。常无欲，可名于小：道无欲谦下，可以说它渺小；万物归焉而不为主，可名为大：万物归附它却不自居为主，又可以说它伟大。以其终不自为大，故能成其大：正因为它始终不自以为大，才真正成就了伟大。
@@ -544,7 +544,7 @@
     <t>第三十六章</t>
   </si>
   <si>
-    <t>将欲歙之，必固张之；将欲弱之，必固强之；将欲废之，必固兴之；将欲夺之，必固与之。是谓微明。柔弱胜刚强。鱼不可脱于渊，国之利器不可以示人。</t>
+    <t>将欲歙（xī）之，必固张之；将欲弱之，必固强之；将欲废之，必固兴之；将欲夺之，必固与之。是谓微明。柔弱胜刚强。鱼不可脱于渊，国之利器不可以示人。</t>
   </si>
   <si>
     <t>要想收缩自己的对手，必须暂时让对手扩张开来；要想削弱自己的对手，必须暂时加强自己的对手；要想废除自己的对手，必须暂时让对手振兴起来；要想夺取对手的东西，必须暂时先赠予一些东西给对手。这就叫作含而不露的聪明。也即以柔弱的手段战胜刚强之人的策略。使用这些策略时要像鱼不可离开水那样不能脱离一定的客观条件，也像国家的优良武器一样 不能让别人知道。</t>
@@ -557,10 +557,10 @@
     <t>第三十七章</t>
   </si>
   <si>
-    <t>道常无为而无不为。侯王若能守之，万物将自化。化而欲作，吾将镇之以无名之朴。无名之朴，亦将无欲。不欲以静，天下将自定。</t>
-  </si>
-  <si>
-    <t>大道永远是清静无为的 然而却又成就了万事万物。王侯如果能够遵循着它，百姓将会自然而然地发展生产。生产发展繁荣之后如有欲望产生，我将用无形无象的大道使他们安定下来。这种无名的质朴状态，本身也不会产生欲望。如果人们没有欲望就能保持平静，天下将自然会太平安定。</t>
+    <t>道常无为而无不为。侯王若能守之，万物将自化。化而欲作，吾将镇之以无名之朴。无名之朴，夫亦将无欲。不欲以静，天下将自定。</t>
+  </si>
+  <si>
+    <t>大道永远是清静无为的 然而却又成就了万事万物。王侯如果能够遵循着它，百姓将会自然而然地发展生产（自我化育、自我成长）。生产发展繁荣之后如有欲望产生，我将用无形无象的大道使他们安定下来。这种无名的质朴状态，本身也不会产生欲望。如果人们没有欲望就能保持平静（治理天下的人要做表率，少私寡欲，清静无为），天下将自然会太平安定。</t>
   </si>
   <si>
     <t>本章是《道经》的收束，讲无为而无不为。道常无为而无不为：道恒常无为，不妄为、不干预，却成就万事万物。侯王若能守之，万物将自化：领导者若能守住道，万物自然化育成长。化而欲作，吾将镇之以无名之朴：万物生长中欲望萌动时，用无名的素朴去镇服安定。无名之朴，亦将无欲：素朴本身没有欲望。不欲以静，天下将自定：没有欲望就能安静，天下自然安定。
@@ -573,7 +573,7 @@
     <t>上德不德，是以有德；下德不失德，是以无德。上德无为而无以为；下德为之而有以为；上仁为之而无以为；上义为之而有以为；上礼为之而莫之应，则攘（rǎng）臂而扔之。故失道而后德，失德而后仁，失仁而后义，失义而后礼。夫礼者，忠信之薄而乱之首。前识者，道之华而愚之始。是以大丈夫处其厚，不居其薄；处其实，不居其华。故去彼取此。</t>
   </si>
   <si>
-    <t>真正崇尚美德的人并不去有意表现自己的美德，所以他才真正具有美德；不是真正崇尚美德的人却处处要表现自己的美德，所以他并不具有美德。真正崇尚美德的人清静无为 是因为他们没有个人功利目的需要多为；不是真正崇尚美德的人碌碌多为 多为是为了达到个人的功利目的；真正崇尚仁的人去做好事 做好事不是为了满足个人私欲；那些非常重视义的人去制定各种规则 制定规则是为了满足个人私心；那些非常重视礼的人去推行礼仪，如果没有人响应 他就会卷起袖子。因此说失去了道而后才去提倡德，失去了德而后才去提倡仁，失去了仁而后才去提倡义，失去了义而后才去提倡礼。礼仪，是忠信不足的标志 是祸乱的开始。那些超越时代的思想主张，站在道的角度来看 属于华而不实的东西，是愚昧的开始。因此大丈夫要笃守忠信，排除虚礼；要遵循规律，不要提倡超越时代的思想主张。所以要舍弃虚礼和超越时代的思想主张 笃守大道。</t>
+    <t>德高的人做了有德的事不自认为有德，所以他才真正具有美德；不是真正崇尚美德的人却处处要表现自己的美德，所以他并不具有美德。真正崇尚美德的人清静无为 是因为他们没有个人功利目的需要多为；不是真正崇尚美德的人碌碌多为 多为是为了达到个人的功利目的；真正崇尚仁的人去做好事 做好事不是为了满足个人私欲；那些非常重视义的人去制定各种规则 制定规则是为了满足个人私心；那些非常重视礼的人去推行礼仪，如果没有人响应 他就会卷起袖子强迫别人遵从。因此说失去了道而后才去提倡德，失去了德而后才去提倡仁，失去了仁而后才去提倡义，失去了义而后才去提倡礼。礼仪，是忠信不足的标志 是祸乱的开始。那些超越时代的思想主张，站在道的角度来看 属于华而不实的东西，是愚昧的开始。因此大丈夫要笃守忠信，排除虚礼；要遵循规律，不要提倡超越时代的思想主张。所以要舍弃虚礼和超越时代的思想主张 笃守大道。</t>
   </si>
   <si>
     <t>本章开启《德经》，讲真正的德是自然无心的。上德不德，是以有德：真正有德的人不把德行当回事，做了好事自然忘掉，反而真有德；下德不失德，是以无德：境界不高的人总怕德行失去，处处表现、宣扬，反而无德。上德无为而无以为：有德者自然作为，没有功利目的；下德为之而有以为：无德者做事带着目的。上仁为之而无以为：仁者做好事不为私欲；上义为之而有以为：讲义的人制定规则，多少带着私心；上礼为之而莫之应，则攘臂而扔之：讲礼的人若没人响应，就卷起袖子强推。
@@ -602,7 +602,7 @@
     <t>反者道之动。弱者道之用。天下万物生于有，有生于无。</t>
   </si>
   <si>
-    <t>万物在大道的支配下向相反的方向发展，大道的作用就在于它能够提醒万物保持柔弱的状态。天下万物产生于某种物质，而物质产生于空间。</t>
+    <t>万物在大道的支配下向相反的方向发展，大道的作用就在于它能够提醒万物保持柔弱的状态。天下万物产生于某种物质，而物质产生于空间。（有和无是天下万物生成的根源）</t>
   </si>
   <si>
     <t>本章只有三句话，却是全书思维总纲。反者道之动：道向相反的方向运动，事物发展到极点就走向反面，又终而复返，回到更高层次的本根。所以看问题不能只站在自己的角度，要换位思考、正反合地看：正面看、反面看、合起来看，才能全面。弱者道之用：道的作用体现在柔弱一面，大家都逞强，柔弱反被强调，这是阴阳统一的思维方式。天下万物生于有，有生于无：万物产生于有，有产生于无；任何事物都有有和无两个方面，有让我们观察边界，无让我们观察妙处。
@@ -627,7 +627,7 @@
     <t>道生一，一生二，二生三，三生万物。万物负阴而抱阳，冲气以为和。人之所恶（wù），唯孤寡不穀（gǔ），而王公以为称。故物或损之而益，或益之而损。人之所教，我亦教之。强梁者不得其死，吾将以为教父。</t>
   </si>
   <si>
-    <t>“道”即阴阳二者的统一，“一”中蕴含着阴阳两个方面，阴阳二者参与到一起相互作用形成万事万物。万物背阴而向阳，阴阳二者相互中和形成和谐状态。人人都厌恶的是孤、寡、不穀，但王侯却以此自称。所以有的东西减损它反而得到增加，有的东西增加它反而得到减损。别人教给我的，我也教给别人。喜欢强大暴力的人不得好死，我把它当作座右铭。</t>
+    <t>“道”即阴阳二者的统一，“一”中蕴含着阴阳两个方面，阴阳二者参与到一起相互作用形成万事万物。万物背阴而向阳，阴阳二者相互中和形成和谐状态。人人都厌恶的是孤、寡、不穀，但王侯却以此自称。所以有的东西减损它反而得到增加，有的东西增加它反而得到减损。别人教给我的，我也教给别人。喜欢强大暴力的人不得好死，我将把这一原则当作教育人的重要内容。</t>
   </si>
   <si>
     <t>《德经》部分我们今天讲四十二章。老规矩，把以前的这几章我们再顺一下。《德经》从第三十八章开始，第三十八章讲“上德不德，是以有德；下德不失德，是以无德。”第三十九章我们讲了两个重要的部分，一个就是这个“一”，因为第四十二章又出现了这个“一”，就是阴阳两者的相互平衡，形成的统一体。在第三十九章里边有两句话每一次我都要重申一下，以求让大家牢牢地记忆，“贵以贱为本，高以下为基”。第四十章有一个全部这本书思维的总纲，“反者，道之动”。下边举的这些都是“反者，道之动”的一些例证。比如说“弱者，道之用，天下万物生于有，生于无”。第四十一章的时候，我们是花了比较多的时间来说，为什么呢？因为这一章里边有非常多的“反者，道之动”的例证。比如说“大音希声，大象无形，大器晚成……”这些都是我们平时经常讲的成语。上次讲完了大家应该知道了它的出处。那么今天我们讲第四十二章，这一章并不难理解，但是非常的重要。因为这一章开头这段话，大家经常在很多地方看到，比如北京故宫是建筑的典范，故宫的太和、保和、中和三大殿都是三层台基，也就是建在三层高台之上，为什么选择“三”这个数字呢？再比如我所在的学校叫做西安交通大学，在交大的管理学院，我的一个朋友也在那做了一面墙的雕塑：太极，大家有机会到交大管理学院的时候就会看到，就在一楼。这两个地方的解释，用的都是这段话：“道生一，一生二，二生三，三生万物。”我们来解释这段话，原文大家都看到了：“道生一，一生二，二生三，三生万物。万物负阴而抱阳，冲气以为和。”这个“冲”字，读成中，一下就理解了。下面这段话其实大家也耳熟，起码意思在前边已经说过。“人之所恶，为孤寡不穀，而王公以为称。”大家讨厌的孤、寡、不榖，王公却用来称呼自己，这不是我们前面第三十九章的时候已经说过的这个意思嘛。“故物或损之而益，或益之而损。人之所教，我亦教之，强梁者不得其死，吾将以为教父。”这是第四十二章原文。我们一段一段来解释。先说第一段，“道生一”。“一”我们俗称叫太极。其实“一”就是道的具体的特点，强调道就是“一”，是说道的最重要的一个特点，就是它强调阴阳两者的统一，“一”里边蕴含着阴和阳两种力量，两个方面。“道生一，一生二”，这个“一”里边蕴含着“二”，也就是道里边蕴含着阴阳两种力量，两个方面，两种状态。中国人讲，事物都是相互对立而存在的，万事万物归结到最后，它也不会是一个单一的元素。你看咱们中国历史上的《易经》，落到最后就是两个符号，阴和阳。那已经到了事物的极致了，极点了。把阴和阳统一起来叫太极，但是这两个元素是最基本的。所以“一生二”，是说太极道里边蕴涵着阴阳两个方面，两种力量。“二生三”，很多人对这个“二生三”解释得太费劲。“三”是什么？很简单，就是繁体字那个“叁”，就是参。阴阳两者参与到一起，相互作用，形成了万事万物，多简单的事情。它们两者孤阴不生，孤阳不长，两者相互作用，形成万事万物，“三生万物”。所以我们用的那个《中庸》的名言叫“参天地，赞化育”。人能参与到天地之间的运动发展，天地人三才嘛。三才你看人不也参与其中嘛。这个赞可不是赞扬的意思，也是参与的意思。两者参与到一起，产生万事万物，这是从正面。然后再反过来推，既然是三生万物，那么万事万物里边都包含着这两种力量，两个方面，阴阳两个方面，所以叫“万物负阴而抱阳”。随便找，哪一个事物内部都有阴有阳，都包含着阴阳两种状态、两种力量。“万物负阴而抱阳，冲气以为和”。为什么要把这个“冲”念成“中”呢？大家看“冲”的写法，前边这两点其实就代表着阴和阳，那个中就是中和的意思，就是参的意思。阴阳两种力量，中国人把它叫做气，阴气、阳气嘛。通天下一气，形成和谐的、动态的、运动的世界，这就是冲气以为和。这一段讲了我们中国哲学中的宇宙生成模式，也讲了这个世界存在的状态，以及这个状态的原因。这种状态都是阴阳两者运动所形成的，动态的、和谐的状态。冲气以为和。再重复一遍。“道生一，一生二，二生三，三生万物。”所以万事万物都有阴阳两个方面，“万物负阴而抱阳，冲气以为和。”下边就开始讲。用这种思维方式你来理解世界，你就不能只站在一个方面了，明确地告诉你了。事物都是统一的，两个方面不可偏颇，不可偏废。所以对侯王讲，“人之所恶，唯孤寡不穀。”你说大家最讨厌的就是这些词，孤家、寡人、吃不上饭、饿死。可是你看这些王公大人，包括后来的皇帝，他们都拿这个来称呼自己。干嘛呢？“故物，或损之而益，或益之而损。”这个“物”大家不要解释成物质，就是我们中国人常讲的那个“东西”。中国人这个“东西”太奥妙了，什么都可以称之为东西，不管是物质的、精神的都可以称之为东西。所以老子就说你看说到万事万物存在的这些各类各样的东西，“或损之而益”，你以为它受损了，其实它得到了益处。有的时候我们受到一点挫折，我们觉得自己受了多大的这种屈辱一样，可是你知道人都是在不断地受的这种损中逐渐地成长起来的，你认为它是祸，其实它是福，“损之而益”。有的时候你认为自己是得到了，其实反而是一种损失。比如偷了东西的，得到了，其实把人格给损失掉了。有的人用不光彩的手段，不择手段得到的，其实他们损失的反而更大，“或益之而损”。所以老子讲的是相反相成的道理。我们中国人常用什么事情来说这个事？叫破财免灾，叫大难不死必有后福，叫祸福相依，叫塞翁失马焉知非福，你看这讲的都是“损之而益，益之而损”。刚才举的例子不就是这样吗？这侯王王公们不都在损自己吗？把自己叫做“孤寡不穀”。其实有这个提醒之后，反而避免了自己变成孤寡不穀。以前中国人也有这个习惯，给小孩起名起个贱名，好养活。当然现在这种习俗很少再看到了，它讲究的就是“损之而益，益之而损”。民间很多的道理大家也得认真对待，别以为我们上了学之后自己水平就高了，其实真正的高手在民间。很多老人讲的话，到最后你一生体会，反而你发现真的是有道理。“人之所教，我亦教之，强梁者不得其死”。老子也说这些东西，也都是别人教给我的，给我讲的。我再把这些写出来教给大家。这一句我们可得好好地来给大家说道说道。为什么呢？因为这涉及老子的思想的来源，老子的思想来源当然有很多方面，主要的两条，两条道路。一条道路自然就是《易经》。因为你看，《易经》它把这个叫易以道阴阳，老子也讲阴阳，而且这里边的损和益，这不就是《易经》里边的损卦和益卦嘛，损和益这也是《易经》里边经常强调的。另外一个，我觉得这一章里边非常奥妙，一个是讲这阴阳的事情，让我们知道他的思想里边《易经》是中国文化之源，众经之首，损之而益，益之而损。另外一个也表现出他的思想的来源，就是“强梁者不得其死”，这句话也不是老子自己的，它出自《金人铭》。传说黄帝写了六篇铭文，叫《黄帝六铭》。其中有一个是刻在周朝台阶右面立着的金人背后，金人就是青铜做的，这金人的背后有铭文。经过汉朝的刘向《说苑》的考证对比，发现《金人铭》里边的这句话：“强梁者不得其死”。“强梁”就是处处逞强。喜欢暴力的人，最后不会有好的结果。我们讲死得其所，叫得其死，得好死，不得好死，不得其死。强梁者不得其死。说到“强梁”这个词，我想读过《水浒传》的人一定记得，在《水浒传》里边用到“强梁”这个词的时候，是用在了矮脚虎王英的身上。矮脚虎王英，这个是梁山泊里边大家都瞧不上的那么一个人。原来是个车夫，后来抢劫，后来落草。所以用这个词来形容他，“强梁者”。“强梁者不得其死”，老子非常反对强暴，而强调和平、守弱，认为“强梁者不得其死”，“木强则折，兵强则灭”，这是他后边关于这个问题的一个延伸。“吾将以为教父”，这个“教父”就是说，这是别人教给我的，我也把它拿来作为座右铭，来指导我自己。总结一下，大家看这一章，第一段话是我们大家都耳熟能详的，“道生一，一生二，三生万物，万物负阴而抱阳，冲气以为和。”第二段是我们前边讲过的内容，在这个里边又重申了一遍，注意这些重申可不是排版排错了。因为《道德经》里边它讲的几条重要的原则，遇到机会的时候，它就会反复，用重复的方式来强调。“人之所恶，唯孤寡不穀，而王公以为称。”所以对于万事万物而言，对这个世界存在的东西而言，“或损之而益，或益之而损”。有的你觉得是损失了，结果反而是得到了。有的你认为自己得到了，反而是损失掉了。因此不可一概而论。遇到了乐事的时候，不要过于高兴，以免乐极生悲。遇到不好的事，祸事的时候，也不要丧气，因为这些可以成为我们的经验，塞翁失马，焉知非福！这是别人教给我的，我也把它来教给别人。然后下边这句话是老子也非常强调的，“强梁者不得其死”，还是要和平，还是要守弱，处处逞强，总和别人结梁子，最后不会有好的结果。国家也一样，“国虽大，好战必亡”。老子说我也要把这个当作座右铭，这就明显地透露出他思想的来源，一源于《易经》，阴阳之学，损益之论，谦卑之礼。二源于《金人铭》，尤其是《金人铭》里这句话对老子影响是非常大的，所以他把它叫做“教父”，座右铭。</t>
@@ -639,7 +639,7 @@
     <t>天下之至柔，驰骋天下之至坚，无有入无间，吾是以知无为之有益。不言之教，无为之益，天下希及之。</t>
   </si>
   <si>
-    <t>天下最柔弱的东西，可以攻克天下最坚强的东西，无形的东西能够穿过没有缝隙的地方，我因此知道了“无为”的益处。不言的教导，无为的益处，天下很少有人能做到。</t>
+    <t>天下最柔弱的东西，可以攻克天下最坚强的东西，无形的东西能够穿过没有缝隙的地方，我因此知道了“无为”（清静无为）的益处。不用言语的教育，清净无为的好处，天下很少有人能做到。</t>
   </si>
   <si>
     <t>我们说“反者，道之动”是整个这本书思维的总纲，也就是说它是一种思维模式、思维方法。第四十章一开头就讲“反者，道之动，弱者，道之用。天下万物生于有，生于无。”这里边出现了两个在《道德经》里边非常重要的字，一个是“弱”，也可以称其为“柔”，另一个就是“无”。第四十三章是对这些内容进一步的引申和展开。第一句“天下之至柔，驰骋于天下之至坚，无有入无间”。最柔弱的东西，反而能够攻克最坚硬的东西。那些没有间隙的地方，无形的东西却能够进入，能攻克。就像风，没有什么地方它进不去的。这些就是“道”，道讲完了。老子开始讲“德”。“吾是以知无为之有益”。我从“至柔驰骋于至坚”，“无有入无间”中知道：人类也是一样，有些事情，无为比有为效果更好——“无为之有益”。可是话说回来，“不言之教，无为之益，天下希及之”按照无为的道理去做事，所获得的好处、益处，天下的人却很少能够知道，很少能够达到。这些话该怎样进一步理解呢？老子在第七十章讲过，“吾言甚易知，甚易行，天下莫能知，莫能行”。什么意思？其实，我讲的道理都是非常简单的、平常。但是大家为什么不知道呢？做不到呢？因为这里边就隔了一个东西——欲望。有些事情大家明知道是这么回事，但是很多东西被欲望牵引就变得难做了。就像我们说“不贪为宝”，但为什么还有那么多人上当？有些人上当了还不好意思说出来。因为自己心里清楚，自己是因为贪心才是上当受骗了嘛。没有这个贪心，很多事情理解起来就太容易，太简单了。但一个骗局，往往能骗很多很多人！再说回来，“天下之至柔，驰骋天下之至坚，无有入无间”。天下的“至柔”是什么？无形是风，有形是水。第七十八章就说，”天下莫柔弱于水，而攻坚强者莫之能胜”。这不是正是“天下之至柔，驰骋天下之至坚”吗？天下什么东西最坚硬，石头？水滴石穿；金属？水刀切可以割金属。有什么坚硬的东西是水它克服不了的呢？风更是弥漫天下，摧枯拉朽，无所不在，力量无尽。你说这个东西没有间隙，但是无形的东西，它反而能够穿透它。现在，科学发现有一些微小的东西，比如说中子、粒子、量子……他们是无形的，你看不见，但没间隙的地方，它们都能够进入。我们眼里没有间隙的地方，对于它们来讲，缝隙简直太大了。“无有入无间”，在强调无的东西的作用。道家的“无为”相当一部分内容在讲“无之为”——这些无形的东西、无用的东西的作为。所以，不要把“无”理解为“没有”，把“无为”理解为“不做事”。“吾不言之教”，第二章讲过“行不言之教”，为什么？身教重于言教，话太多了，老去教化，训导别人，反而会起负面的作用。老师也罢，家长也罢，国家的领导也罢，做一个好的榜样，上行下效。孔子也讲了一句话，叫“君子之德风，小人之德草”。这里小人不是道德上的低下，而是指人民、平民、一般人。榜样的“不言之教”就像风一样，一般人就像草一样。风向哪个方向吹，他们跟随着风而倒。无之为所带来的益处，天下却很少有人能够达到——“希及之”！在讲第三十七章的时候我们说，“道常无为而无不为”，道的规律、规则就是“无为”，而“无为”的效果却是“无不为”——覆盖面更广，效果更好。这不就是“无为之益”吗？一开始讲第一章的时候，我就给大家说过，道家讲的“無”和舞蹈的“舞”字形极为相近。因为对于原始人来讲，舞蹈起到的作用实在太大了。有形的几个姿势，产生出的力量却是巨大的。既然是“无”是“无之为”，那么“无用”，也就是“无用之用”。你认为没用的东西，其实不是它没用，只是你没有看见它的用处。书法有什么用，绘画有什么用？不能当吃，不能当穿，可是如果大家否定了这些，那不就进入了一种狭隘的功利主义的境地了吗？人生最没用的事是什么？睡觉。睡着了什么都做不成。小孩最讨厌睡觉了，可是大家都知道现在有多少人被失眠所折磨，为睡不着觉而痛苦。这些“没用”的事你做不成，那么有用的事你也做不来。最后一句，“无为之益，天下希及之”是老子的感慨。大家老看不到这一点，老觉得无为的事情没用。殊不知你不做这些无为的事，就不能真正的有为。不了解这些无用东西的作用，你也就不知道什么才算是真正的有用。从“反者，道之动”，一直到现在，都在讲述一个道理。</t>
@@ -651,7 +651,7 @@
     <t>名与身孰亲？身与货孰多？得与亡孰病？是故甚爱必大费，多藏必厚亡。知足不辱，知止不殆，可以长久。</t>
   </si>
   <si>
-    <t>名声与身体哪一个更亲近？生命和财货哪一个更重要？得到和失去哪一个更有害？过于爱惜必定会有大的耗费，过多的藏货必然会导致惨重的损失。所以知道满足就不会遭受屈辱，知道停止就不会遭到危险失败，这样才能长久。</t>
+    <t>名声（美名）与身体（生命）哪一个更亲近？生命和财富哪一个更重要？得到名利和失去生命哪一个更有害？所以说过于爱惜必定会有大的耗费/破费，过多的藏货（聚财）必然会导致惨重的损失。所以知道满足就不会遭受屈辱，知道停止就不会遭到危险，这样才能长久平安。</t>
   </si>
   <si>
     <t>前面我们说了第四十三章，最后说“不言之教，无为之益，天下希及之”。然后说这都是前面“反者，道之动”这种思维方式的进一步的延伸和具体的例证。这种方法我们大家已经习惯了，在哲学上叫做“二分法”，叫做“对立的统一”。第四十四章讲的也是这个。一开始先列出来三个对立的事物——名与身、身与货、得与亡，进行比较。“名与身孰亲？”“名”和“身”哪一个更重要？哪一个是对大家来讲是更亲的东西？“身与货孰多？”我们的生命和外在的物质相，财富哪一个更重要？“亲”也罢，“多”也罢，意思都在说哪一个更重要。我们常说“身外之物”，常说名和利生不带来，死不带去。你看，这一章就在解读这个问题了。第三个，“得与亡孰病？”这个好理解，参照我们前面讲的“或损之而益，或益之而损”，是得到的好还是失去的好？哪一个危害更大呢？“病”当然不是什么好词了，“得与亡孰病？”其实在问的时候这个答案已经有了。这就是一种反问的语气，表示强调。因为有的人在名和自己生命的选择之中选择了殉名；有的人，“人为财死，鸟为食亡”——因为财富的事，把自己的生命搭上去了。真的是得到就好，失去就不好吗？比如，我们读像《道德经》这样的书，我们会得到什么？也许什么都没得到，但是我们失去了焦虑，失去了急躁，失去了自高自大，这些东西失去了，那不就是一种得到吗？不是说得到就好，失去就不好。有的东西失去，反而是获得；有些东西得到，反而是真正地失去。三个反问句，答案其实都在里边。下面这几句话，讲得就更深刻了。“甚爱必大费，多藏必厚亡”，对一个东西太珍爱了，最后一定会付出大的代价。比如，有的人他有这种癖好，他喜欢古玩，别人送的别的东西他不要，你拿着古玩一贿赂他就收下来，最后就因为这个自己犯了事儿——“甚爱必大费”。有的人把减肥当作唯一的事业，尝试各种各样靠谱不靠谱的方法，把身体折腾得一塌糊涂，那不就得付出大的代价吗？很多事情都是这样的结果。“甚爱”，太过分了，不是说不好，但是过分了，这就走向了它的反面，物极必反嘛！“多藏必厚亡”，很多东西收敛、搜刮到了，自己把它藏起来，能藏得住吗？最后这个搜刮来的东西一定都成为自己的污点和罪证。多藏必厚亡，“厚”也是大的意思。下边这两句话大家都熟：“知足不辱”。我们知道满足有边界，这样才不会受屈辱。这事我知足，我不卑躬屈膝求别人，我觉得我这个已经很好了，这是我自己奋斗来的，额外的，不择手段得来的东西，我不需要，“知足不辱”。“知止不殆”。这个地方，我得给大家多说几句。老子这个人真的是不得了，他只用一个“走道”的形象，就说清楚了很多问题。我们走在道上，应该注意什么呢？有几个最重要的内容：方向、目标、规则、境界、边界、底线。我们要去什么地方？方向、目标。我们什么时候该停下来呢？只要是道就有边界，道外边往往就是深沟，就是深渊，就是歧路。我们了解边界底线，不贸然地前闯，有“底线思维”，“红线思维”，给我们的欲望划出边界，就是“知足”。知足才能不辱。“知止不殆”，“殆”就是危险失败。知道边界、底线不闯，我们才能没有危险，没有失败。当年杨虎城在陕西把他办公的行园就改名叫“止园”。出处就是这四个字，“知止不殆”。“知足不辱，知止不殆”的意义在哪儿呢？——“可以长久”。其实这些事情不用举太多的例证，为什么？因为例证太多了，不了解边界、底线，冒进、冒险，肯定会导致大的，糟糕的后果。这一章没有什么难以理解的，但是内容也非常深刻，尤其是前边这三个提问或者叫反问，都是我们应该深深思考，并做出回答的。拿我们的生命和名声去交换名利，到底划得来划不来？到底哪个更重要？哪个对我们更亲？身与货和这些财富进行比较的时候，到底哪个更重要？我们拿生命去换财富，回头再拿财富来换健康——有时候，甚至换不回来。“得与亡孰病？”不要认为得到就高兴，失去就不高兴，其实得失就是这样的相反相成。很多事情反而是损之而益，有的是益之而损。祸福相依，相互转化，物极必反。既然物极必反，下面这几句话就好理解了，“甚爱必大费，多藏必厚亡”，因此应该“知足不辱，知止不殆”——知足可以不辱，知止可以不殆。知足、知止，我们才能长久。不管是对于生命，还是对于事业而言，才能稳定致远，长久地发展。这是第四十四章的内容，内容不多，但是我们应该熟记，尤其是几个对偶的句子：“甚爱必大费，多藏必厚亡”；“知足不辱，知止不殆”。</t>
@@ -663,7 +663,7 @@
     <t>大成若缺，其用不弊；大盈若冲，其用不穷。大直若屈，大巧若拙，大辩若讷（nè）。躁胜寒，静胜热，清静为天下正。</t>
   </si>
   <si>
-    <t>最完满的东西好像有欠缺，但它的作用不会衰竭；最充盈的东西好像是空虚的，但它的作用没有穷尽。最直的东西好像是弯曲的，最精巧的东西好像是笨拙的，真正辩才高的人出语谨慎。运动可以克服寒冷，静可以战胜热，（治天下的人）保持内心清静才能将天下领上正道。</t>
+    <t>最完满的东西好像有欠缺，但它的作用不会衰竭；最充盈的东西好像是空虚的，但它的作用没有穷尽。最直的东西好像是弯曲的，最精巧的东西好像是笨拙的，真正辩才高（善辩）的人出语谨慎。运动可以克服寒冷，静可以战胜热，（治天下的人）保持内心清静才能将天下领上正道。</t>
   </si>
   <si>
     <t>我们先来看一下原文，有几个词我们要注意先区分一下。比如说大辩若讷，这个讷呢，我们知道一个词叫做木讷，也就是说，说话不是那么样的流利，不是那么样的辩才无碍。但实际上在这章里，它所要表达的是谨慎，说话严谨、谨慎。为什么要给大家说“讷”这个字呢？大家知道，毛泽东两个女儿，一个叫李敏，一个叫李讷。可是包括中央电视台的广播员都把这个念成nà，其实这个讷，只有一个读音，应该读作nè（讷）。毛泽东两个女儿的名字出自《论语》，“讷于言而敏于行”。先把这个事情给大家说一下，然后我们从头一句一句来解释。“大成若缺，其用不弊。”这个是在讲，完满的东西都仿佛有缺陷。我们平常讲一句话叫完美诚不易。其实这个世界上没有真正完美的东西，任何事物都是有缺点的。了解到这一点，引申到道家的思想，那么这句话想要表达的真正的含义就是，一个越是有大成就的人，他越了解自己的缺点，越觉得自己有缺点，有缺憾。所以，他就不断学习，不断努力，这样的一种动力，它发挥的作用，那么是无穷无尽的。认识到自己有缺点，这样他才能够很好地避免自己的弊端，很好地使自己的缺点得以改正和进步。这个道理在《道德经》里边多处谈到，比如说第七十一章就在讲，“知不知，上；不知知，病”。你知道自己不知道，这个才是水平高的。你不知道自己不知道，这就出问题了，出弊端了。所以大成若缺，其用不弊。一个越是有大成就的人，越懂得应该不断学习，不断进步，不断努力，不断充电。反而是一些有一点小小成就的人，喜欢到处吹嘘，不把旁边人吹得感觉到活不下去，他都不松口。其实遇到这种人，我们根本不用去揭穿他，淡然一笑就可以了。一个越是喜欢自我吹嘘的人，其实越不会有什么大的成就。反之，大成若缺，其用不弊。其实这个道理不止局限于此，我们还可以把这个道理向更深处延展一下。比如说中国人从月圆月缺，领悟出一个道理，其实任何事物发展到到它的极点的时候，它就会向相反的方面转化。人生的最美的境界，花未全开月未圆。花全开了，就往凋零的方向走了，月圆了就往缺的方向走了。所以在临近全圆和全开那时候，才是最美的境界。其实大家注意，我们在生活中经常喜欢用一个词，来对人表示一种赞赏，叫如日中天。其实这个不是一个好的事情。你说人如日中天，不是马上就说他要走下坡路了吗？用道家的这种思想我们来理解。明白在我们生活中讲的很多事情，和这个道理的吻合。大成若缺，其用不弊。“大盈若冲，其用不穷。”“盈”就是满，“大盈”就是大满。“大盈若冲”，“冲”就是冲虚。我们经常讲，用这个冲虚来代表着谦逊谦虚，就像大家看《笑傲江湖》里边的武当的掌门，冲虚道长，大盈若冲。一个越是智慧高的人，智慧聪明的人，他越谦虚，越谦逊。在前面我们曾经说过，“满招损，谦受益”，这话出自《尚书》——中国第一部历史总集。在《尚书》里边有一篇讲到了君臣之间探讨治国的谋略，大禹手下的第二号人物叫伯益。就给他的领导讲了这样的一句话，“满招损，谦受益”，并且伯益还制作了一件警戒器，叫欹器。这个东西非常奥妙，水装满了就颠倒了，倾覆了。装得不满的时候，它稳稳当当。提醒告诫我们这个道理，“满招损，谦受益。”孔子的后半生这个警戒器也一直放在身旁，这么大的一个学问家，还经常提醒自己，“满招损，谦受益”的道理，何况我们。所以“大盈若冲”！一个越是知识充盈的人，知识多的人，越表现得外在的谦逊谦虚，感觉到自己的不足，不断学习，不断努力。“其用不穷”，这样他的知识才能够更好地发挥作用，它的作用无穷无尽，不会出现上边所说的那些弊端，其用不穷。这都是相反相成的道理，按照这个道理我们再解释下边的内容，就比较容易了。“大直若屈，大巧若拙。”一个越是正直的人，越是有正直的、高尚的境界的人，反而外在表现得都比较随和，对很多的事情不那么喜欢争锋，对很多的事情都能够宽容。若屈并不是真的屈枉，他只是懂得外圆而内方，用这种方式和外面的人相处、相衔接，“大直若屈”。关于“大巧若拙，”这个我们得多说几句，在第二十五章里我们讲过，“大曰逝，逝曰远，远曰反”，这是一个逐步发展的过程。就像中国的艺术品一样，一开始没有技巧，后来学到了很多技巧。真正达到一个更高的境界的时候，反而把这些技巧忘掉了，返璞归真。中国雕塑的最高的境界是什么呢？有机会大家到汉武帝的陵墓——茂陵看一看，就会有所体会。那儿被认为是中国雕塑的顶峰。可是大家进去一看却发现非常奇怪，汉代的雕塑几乎一件精巧的东西都没有，都是那样的笨拙、朴拙。特别是霍去病墓前的《马踏匈奴》，那简直笨拙到了极点。团块、圆雕。可是那是中国象征雕塑的顶峰，正因为它这个拙，反而体现出大气势、大气象、大境界，“大巧若拙。”中国诗歌的最高境界是什么呢？清水出芙蓉，天然去雕饰，自然而然，返璞归真。中国书法的最高境界是什么呢？大的书法家最后写得越来越笨拙，越来越稚拙，反而开拓出一片新的气象。我读过一本书法书，是凌云超先生的《中国五千年书法史》。凌云超先生讲到这样一件事，他说中国的书法到后来写得越来越精巧，越来越美，但是像小家碧玉。而中国早期的书法，比如说石鼓文、金文，如旷野风月，给人一种大开大合的气象，这当然是我们在欣赏过程中感觉到的。越是这种稚拙、朴拙、笨拙，反而给人带来更强烈的一种审美的气势和感觉，崇高的一种味道。所以“大巧若拙”。其实《道德经》里边主要讲的并不只是这些，主要说的是人格。一个人格发展到一种高点的时候，他就达到了一种自然而然，返璞归真，忘记了那些小的技巧，心眼、套路，回归到一种真正的高尚的人格的境界。“大巧若拙”，返璞归真，自然而然，明月清风。这是我们说“大巧若拙”。“大辩若讷”。“讷”字我们前面解释过了，这个意思也就非常清楚。真正辩才高的人，他出语反而非常谨慎，让人感觉到仿佛他语言不是那么样的流畅，辩才无碍。其实他不只是为了用语言和人争锋，用语言和人争辩，出语谨慎，这也是我们讲的道家思想里边的一个重要的方面，这样的人才是真正有大的这种辩才的人，“大辩若讷”。下边这几句话原文上就有争论了。我们按照原文先解释一下。“躁胜寒，静胜热”。这个“躁”，表面上意思是急躁，燥热，实际上在讲的是运动。运动可以战胜寒冷。“静胜热”是说冷静可以战胜昏热。因为比如说我们夏天的时候用冰镇，这个方式可以解暑，战胜暑热，但这个地方要讲的实际上是内心的这样的一种冷静，可以战胜我们头脑发热，“静胜热”。但有的人也认为，其实这句话应该是静胜躁，寒胜热。这样和原文连接起来就更顺了，我倒是同意这样的一种说法。因为比如说我们夏天的时候用冰镇，这个方式可以解暑，战胜暑热，所比喻的也是冷静下来时才能战胜头脑发热，而且句式更为对称。现在很多本子也这样做了这样的一种改动。我觉得这个说法更为成立。总之都是讲，内心冷静、宁静、安静，它可以战胜我们的急躁。如果我们能够保持内心的宁静、安静、冷静，这样就可以战胜我们的浮躁、急躁、暴躁、狂躁，宁静以致远，这个和原文意思比较吻合。寒胜热，也是这样一个意思的表现，就像我们刚才说的，一个人冷静下来，可以战胜头脑发热，万物静观犹自得，我们冷静下来才能看清事物的本来面貌，冷静下来才能找到解决问题的正确方法。所以这六个字，大家不妨把它理解为静胜躁，寒胜热。这样后边这句话就自然而然地引申出来了，“清静为天下正”。我们保持内心的清静，一个王者、统治者、领导者保持内心的清静，这样才能够引导天下走上正道。“我好静而民自正”，“清静为天下正”，让内心的清静、冷静、宁静，又具备这样的一种修养。这才能够引导天下走向正道。这个是天下最正的一种领导的方式方法，也是我们修养的由内圣而外王的一种正确的修养的方式方法。</t>
@@ -675,7 +675,7 @@
     <t>天下有道，却走马以粪；天下无道，戎马生于郊。祸莫大于不知足，咎（jiù）莫大于欲得。故知足之足，常足矣。</t>
   </si>
   <si>
-    <t>天下有道，善跑的马退还给农夫用来耕田；天下无道，所有的马用来征战甚至母马都要在疆场生小马。祸患没有大于不知足的了，罪过没有大于什么都想占有的了。所以知足的满足，才是长久的满足。</t>
+    <t>国家的政治措施如果符合大道，那么连跑得快的马也可以拉回来耕地；国家的政治措施如果违背了大道，那么连怀孕的母马都要在疆场作战，以至于在战场生子。最大的祸患是不知满足，最大的危险是贪得无厌。因此懂得满足的这种满足，才是长久永恒的满足。</t>
   </si>
   <si>
     <t>“天下有道，却走马以粪；天下无道，戎马生于郊，祸莫大于不知足，咎莫大于欲得，故知足之足，常足矣。”这段话也是《道德经》里边非常精彩的一章。因为它体现了我们中国人对待战争的态度，对待和平的热爱。前面我们讲的第三十章的内容，不知道大家是否还有印象，“师之所处，荆棘生焉。”军队打过仗的地方，一片衰草枯杨，断壁残垣，“大军之后，必有凶年。”打过仗以后，灾荒瘟疫都来了。第三十一章，老子讲得更为沉痛，说中国人把战争当作丧礼一样来对待，“以悲哀泣之，以丧礼处之，胜而不美，胜而美者是乐于杀人。”我以前讲过，通过“四大名著”让国外了解我们的文化，效果恐怕不尽如人意，应该让他们看什么呢？让他们看《道德经》，这部能真正代表中国人思想理念、境界和智慧的经典，像我们讲过的三十章、三十一章和现在要讲的第四十六章，就是如此。“天下有道”，普天下清明有道，这个“天下”包括各个诸侯国了。“天下有道，却走马以粪”，“却”就是推却，“走马”就是跑马，也就是好马。这好马不用来打仗，离开战场，推却战争，干吗呢？回来耕田。当然，古人耕田是要上肥的，撒上粪肥，马耕着田，把地耕好，也就是我们经常讲的，卸甲归田，“卸马归田”，把马从战场上拉回来，干它的本务工作。“天下无道，戎马生于郊”，普天下无道的时候，混乱不堪不清明的时候，是什么情况呢？战马把小马驹生到了战场之上，“郊”就是郊野，此处指疆场，战马把小马驹生到了疆场之上。打仗公马不够用了，母马也上去了，最后出现这种情况——“戎马生于郊”，说得非常形象。我要重点强调一下，这四句是以马喻道，马之却为有道，戎马生于郊为无道，也就是以马的“却”与“生”，比拟天下之有道与无道：以“粪马”与“戎马”，象征国家之治与不治。比喻巧妙，寓意深远。纵观《道德经》的治国之道，当以无为自然以养民，以无欲之事而安民。好像马匹一样，虽是有用之物，用之于疆场可以卫国，用之于战阵可以御敌，用之于农事可以耕田。道行天下之时，国泰民安，上下祥和，无兵甲之患，天下太平安然，百姓安居乐业，故用走马耕田种地，积粪肥田。所以说：“天下有道，却走马以粪。天下无道，戎马生于郊。”太精辟了。“祸莫大于不知足，咎莫大于欲得。”这个大家清楚，老子生活在春秋，春秋无义战——没有什么正义的战争。大家都为了争夺财富、城池、人口，相互混战，战火频仍，烽火四起。面对这种情况，老子在当时总结出这两句话：“祸莫大于不知足，咎莫大于欲得。”惹祸最大的原因在哪呢？在于内心的贪念，贪心不足，得到了还想更多，只会做加法，不会做减法。“人心不足蛇吞象”，其实这句话，不单只对当时的现实概括，对我们现在也有这种启发的意义。生活中这种情况也比比皆是：有了还想更有，多了还想更多，衣架里边永远缺一件衣服，房子永远少一间，总是处在不知足的这种状态。“祸莫大于不知足，咎莫大于欲得”，“咎”罪过，过错，动辄得咎，过往不咎。这个“欲得”，就是别人的东西，自己也想要，把别人东西尽量弄到自己手上——这就成了一种罪过了。前面讲“不知足”是一种“祸”，祸患，而“欲得”就是一种罪过了，甚至可以是一种罪恶。别人的城，想要；别人的人民，想要，什么都想占有，用占有的态度对待这个世界，天下是我的。他说古代封建时代皇帝是什么样子呢？“离散天下人之儿女，屠毒天下人之肝脑，以博我一人之产业。”是说皇帝他觉得天下都是自己的，什么东西想拿就拿，想要就要，想占有就占有。这不就是“欲得”吗，这不就是一种大的过错、罪过吗？“咎莫大于欲得。”这个事情该怎么样来处理呢？该我们得的，我们应该得，不该我们的，“虽一毫而莫取也”。这段话大家也知道，东坡先生的《前赤壁赋》，“物各有主，苟非吾之所有，虽一毫而莫取。”划清边界，该得的得，不该得的不要老去强占，不要老是欲得。我们有了边界、底线、标准，那么就知道知足，知足的满足才是长久的满足。知足者富，所以如果永远处在不知足的状态，人也就永远不会有心灵的安宁。我们把这段话和第四十四章联系起来理解就更加明确了。第四十四章最后的三句话讲，“知足不辱，知止不殆，可以长久。”这一章说，“祸莫大于不知足，咎莫大于欲得。故知足之足，常足矣。”</t>
@@ -687,7 +687,7 @@
     <t>不出户，知天下；不窥牖（yǒu），见天道。其出弥远，其知弥少。是以圣人不行而知，不见而名，不为而成。</t>
   </si>
   <si>
-    <t>不用出家门，便能知天下之事；不用通过窗户去看，就能知道自然的规律法则。越是向外寻找求索，对道的认识就越少。所以圣人不用出行却能知事理，不观察却能明白道理，无为却能成功。</t>
+    <t>不用出家门，便能知天下之事；不用通过窗户去看，就能知道自然的规律法则。越是向外寻找求索，对道的认识就越少。所以圣人不用出行却能知事理，不必亲自观察却能明白道理，不必亲自去做却能成功。</t>
   </si>
   <si>
     <t>由于这两章的内容非常相吻合、相近，所以我们合到一起作为一章来讲解。四十七章讲的是一个什么事儿呢？是说人的感性认识，从哲学上说就是我们的感官接触客观世界，有时候接触得多了，它反而会造成一种迷乱和混乱，要通过人的智慧、理性认识，这样我们才能了解事物的规律，也就是这一章里边所说的“天道”。在这个基础上，我们一句句来解释。“不出户，知天下。”“户”就是门户，也就是大门。我不用走出家门，不用去外边到处跑，也能了解天下的大事。为什么？因为道家认为，天下大道归根到底，融于人的内心。内心里边有道，也就了解了天下的正道，了解了天下的大事。“不窥牖，见天道。”“窥”，从小孔里看；“牖”，就是窗户。我不用通过窗户去看，也知道天地之间日月星辰运行的规律。所以你看这个地方，“出户”是行走，出行，行万里路；“窥牖”是眼睛看，用感官接触客观世界，我不用这样。所以这个地方大家就感觉到，直观的一开始看，就觉得老子这个人有点轻视感性认识，人得通过实践嘛，人得通过感官接触客观世界，才能产生对客观世界的认识。是不是老子把这些东西全部都否认了呢？不是的。因为大家从书里已经看得非常的清楚，《道德经》举了很多生活中的例子，比如说“治大国若烹小鲜”，比如说“凿户牖以为室”，比如“说三十辐共一毂”，前面讲过的，这不都是生活中的例证吗？他对这个东西也很熟悉，怎么知道的呢？通过接触、了解。为什么在这一章里一开始他就讲这个事呢？要落到下面这八个字上。“其出弥远，其知弥少。”“弥”就是越来越，有的人走的地方越多，见得越多，不懂得甄别，不懂得筛选，不懂得提炼概括，“乱花渐欲迷人眼”，出得越远，反而了解到的真知越少，进步越少，为什么？不懂得反观自省，不懂得人心像一面镜子，如果你这个镜子是被灰尘蒙蔽的，你见得越多，其实反而获得的真知越少。这八个字在强调什么？我们要反观自省，要自我修行，自我修养，从哲学上说，从那些感性认识要上升到一种理性认识，达到对事物本质和规律的认识。所以你看，天下、天道代表着对事物全面的、本质的、规律性的认识，这个规律性的认识，需要我们安静地学习，在家里边读古往今来的著作，这不也是“不出户”嘛，也是“不窥牖”！我们了解这些间接的经验，从前人那里得到根本性的、全面的、通过理论阐释的这些知识，我们才能更了解事物的本质，更了解事物的规律。所以不要只把希望寄托在我们出去跑一跑，看一看，以为这样我们的知识就会越来越深刻，很多事情其实要通过理性的思维，这样我们才能进入到对事物本质和规律的认识，“其出弥远，其知弥少”。如果从中国的文化的角度来进一步理解的话，它还探讨一个什么问题、强调一个什么问题呢？就是人的品德。“大道之行，以心之知。”就是我们的心，我们的自我的内在的精神世界，这是道的重要的方面。所以很多人认为知识就是智慧，知识就是品德。不是的，很多人知识很多，不一定有智慧，知识多也不一定有境界、有品德。所以《道德经》强调的根本的“知”，从前面的比较中，相对于我们的感官而言，是人的理性的思维，理性认识、智慧，相对于外面的世界而言，它又是人的道德品德、人的品德。明朝的时候，关学的代表人物冯从吾先生讲过的一句话，我觉得冯从吾先生的这句话就非常能够解释这个道理，冯先生认为，古往今来的大学问都不出乎三句话：“做个好人，存点好心，行些好事。”做个好人，心正，身安，魂梦稳；行些好事，天知，地鉴，鬼神钦。所以一个人内心的品德、境界，通过自我的反省，自我的修养，达到了一个更高的水平，返璞归真，“归根曰静”，这些也是通过内在的自我修养来达到的。所以《道德经》认为人的理性认识，人这样的内心、这样的根本，它可以通过“不出户”、“不窥牖”，也可以自我修养，自我认知，不断地进步以达到。“是以圣人不行而知，不见而明，不为而成。”“是以圣人不行而知”，“是以”，“是”就是这样，“以”就是用，“是”可以解释为所以。“圣人”，好的统治者、领导者，在《道德经》称其为圣人。这些圣人，好的领导者、统治者要经常反躬自省，要经常内心关照，提高自己对大道和规律的认知水平。“不行而知”，不用到处跑，这一点也是可以得到的。“不见而明”，不用亲自去看，也能够明了道理，明了了这个道理，那就内心清净、无欲。“不为而成”，“不为”就是无为，就是按照大道的方式自然而然地去做，而不去妄为，这样一切都会顺理成章。这是我们第四十七章里边讲的内容，字虽然不多，但道理需要我们认真体会，“不出户，知天下；不窥牖，见天道。其出弥远，其知弥少。是以圣人不行而知，不见而明，不为而成。”当然对这一章的更进一步的理解需要我们和第四十八章，也就是我后面要讲的这一章相互参照，我们对这个理解才会更深刻、更准确。一开始就给大家说第四十七章、第四十八章我们要合起来，相互参照，为什么？这两章的内容讲的是非常吻合的，事实上也应该是一章的内容。第四十七章里边讲，“其出弥远，其知弥少”，第四十八章一开头就讲：“为学日益，为道日损。损之又损，以至于无为，无为而无不为。”这八个字一下子和上边的内容就衔接起来，为什么跑得越远反而知道的越少，这是站在道的角度来讲的。“为学”，在学知识，学到的知识内容越来越多。当然从学知识的角度来讲，这是非常有益的，不断地增多，可是我们获得很多的东西，见到了很多的东西，其实对我们了解根本性的规律和本质，了解大道并没有好处。站在一个更高的层次理解，就是说我们“为学”，讲究的是越多越好，见得多，看得多，见多识广。但是“为道”讲究的是什么呢？讲究的是内心的修行，讲究的是减少，用我们前面讲的话来讲，为学做的是加法，为道做的是减法，减少我们内心的欲念，减少我们的贪念，减少我们对很多问题的一种受了外界的影响而导致的内心的纷扰、困惑、迷乱，把这些东西损之又损，一点一点地把它减少，就像那镜子的灰尘一点点擦掉一样，“损之又损，以至于无为。”“无为”就是自然而为，把欲望减少，减少再减少，就达到了一种“无为”的境界，没那么多的贪念，没那么多的纷扰。我们用镜子来照这个天下，来照事物，万物进入到镜子里边，呈现出它本来的面貌。我们了解了事物的本质规律，了解了大道按照它来做，“无为而无不为”达到的是“无不为”的效果。所以在这儿借着这个机会，我再说一下道家自然无为的具体的含义：第一，不妄为；第十六章里边就讲，“不知常，妄作，凶。”你不了解事物的规律、规则，瞎折腾、胡折腾，那结果是非常糟糕的。我们“损之又损”，减少了这些遮挡着我们的认识，遮挡了我们的心窍的这些外在的事物、灰尘、迷乱，我们就照见了事物的本质和规律，我们就“不妄为”。第二，不多为；抓住关键，举重若轻，静观，看到事物的本质，找到解决问题的正确的方法，抓住关键，举重若轻。第三，有所不为；人要想有所为，必须有所不为，要想有所得，必须有所舍。我们舍弃了那些阻碍了我们正确行动、阻碍我们沿着大道行走的那些纷纷扰扰，这样能达到一个无不为的效果，也就是覆盖面广，效果更好，“无为而无不为”。下面这一段就讲，按照“无为”的方式来理解天下万事万物。“取天下常以无事，及其有事，不足以取天下。”“取天下”的规则是什么呢？“无事”。“无事”就是不多事，不干涉，不扰民，这样一切就自然而然顺理成章。所以第五十七章里边讲的这个事情就比较明确，“我无事而民自富，我无为而民自化”。“及其有事”，如果老是多事，老是妄为，不懂得事物的规律、规则，瞎折腾、胡折腾，这就是“及其有事”。则“不足以取天下”，那就不能够获得天下。得到的天下也得失去，因为它违背了大道。</t>
@@ -699,7 +699,7 @@
     <t>为学日益，为道日损。损之又损，以至于无为，无为而无不为。取天下常以无事，及其有事，不足以取天下。</t>
   </si>
   <si>
-    <t>为学是一天一天地增加知识，为道是一天一天地减少私欲。减少又减少，以致达到无为的境界。“无为”就能达到“无不为”的效果。取得天下要常常不多事不扰民，如果妄为滋扰，就不配取得天下。</t>
+    <t>为学是一天一天地增加知识，为道是一天一天地减少私欲。减少又减少，以致达到无为的境界。“无为”就能达到“无不为”的效果（做成一切事）。治理天下要常常不多事不扰民，如果妄为滋扰，就无法治理好天下。</t>
   </si>
   <si>
     <t>由于四十七、四十八这两章的内容非常相吻合、相近，所以我们合到一起作为一章来讲解。四十七章讲的是一个什么事儿呢？是说人的感性认识，从哲学上说就是我们的感官接触客观世界，有时候接触得多了，它反而会造成一种迷乱和混乱，要通过人的智慧、理性认识，这样我们才能了解事物的规律，也就是这一章里边所说的“天道”。在这个基础上，我们一句句来解释。“不出户，知天下。”“户”就是门户，也就是大门。我不用走出家门，不用去外边到处跑，也能了解天下的大事。为什么？因为道家认为，天下大道归根到底，融于人的内心。内心里边有道，也就了解了天下的正道，了解了天下的大事。“不窥牖，见天道。”“窥”，从小孔里看；“牖”，就是窗户。我不用通过窗户去看，也知道天地之间日月星辰运行的规律。所以你看这个地方，“出户”是行走，出行，行万里路；“窥牖”是眼睛看，用感官接触客观世界，我不用这样。所以这个地方大家就感觉到，直观的一开始看，就觉得老子这个人有点轻视感性认识，人得通过实践嘛，人得通过感官接触客观世界，才能产生对客观世界的认识。是不是老子把这些东西全部都否认了呢？不是的。因为大家从书里已经看得非常的清楚，《道德经》举了很多生活中的例子，比如说“治大国若烹小鲜”，比如说“凿户牖以为室”，比如“说三十辐共一毂”，前面讲过的，这不都是生活中的例证吗？他对这个东西也很熟悉，怎么知道的呢？通过接触、了解。为什么在这一章里一开始他就讲这个事呢？要落到下面这八个字上。“其出弥远，其知弥少。”“弥”就是越来越，有的人走的地方越多，见得越多，不懂得甄别，不懂得筛选，不懂得提炼概括，“乱花渐欲迷人眼”，出得越远，反而了解到的真知越少，进步越少，为什么？不懂得反观自省，不懂得人心像一面镜子，如果你这个镜子是被灰尘蒙蔽的，你见得越多，其实反而获得的真知越少。这八个字在强调什么？我们要反观自省，要自我修行，自我修养，从哲学上说，从那些感性认识要上升到一种理性认识，达到对事物本质和规律的认识。所以你看，天下、天道代表着对事物全面的、本质的、规律性的认识，这个规律性的认识，需要我们安静地学习，在家里边读古往今来的著作，这不也是“不出户”嘛，也是“不窥牖”！我们了解这些间接的经验，从前人那里得到根本性的、全面的、通过理论阐释的这些知识，我们才能更了解事物的本质，更了解事物的规律。所以不要只把希望寄托在我们出去跑一跑，看一看，以为这样我们的知识就会越来越深刻，很多事情其实要通过理性的思维，这样我们才能进入到对事物本质和规律的认识，“其出弥远，其知弥少”。如果从中国的文化的角度来进一步理解的话，它还探讨一个什么问题、强调一个什么问题呢？就是人的品德。“大道之行，以心之知。”就是我们的心，我们的自我的内在的精神世界，这是道的重要的方面。所以很多人认为知识就是智慧，知识就是品德。不是的，很多人知识很多，不一定有智慧，知识多也不一定有境界、有品德。所以《道德经》强调的根本的“知”，从前面的比较中，相对于我们的感官而言，是人的理性的思维，理性认识、智慧，相对于外面的世界而言，它又是人的道德品德、人的品德。明朝的时候，关学的代表人物冯从吾先生讲过的一句话，我觉得冯从吾先生的这句话就非常能够解释这个道理，冯先生认为，古往今来的大学问都不出乎三句话：“做个好人，存点好心，行些好事。”做个好人，心正，身安，魂梦稳；行些好事，天知，地鉴，鬼神钦。所以一个人内心的品德、境界，通过自我的反省，自我的修养，达到了一个更高的水平，返璞归真，“归根曰静”，这些也是通过内在的自我修养来达到的。所以《道德经》认为人的理性认识，人这样的内心、这样的根本，它可以通过“不出户”、“不窥牖”，也可以自我修养，自我认知，不断地进步以达到。“是以圣人不行而知，不见而明，不为而成。”“是以圣人不行而知”，“是以”，“是”就是这样，“以”就是用，“是”可以解释为所以。“圣人”，好的统治者、领导者，在《道德经》称其为圣人。这些圣人，好的领导者、统治者要经常反躬自省，要经常内心关照，提高自己对大道和规律的认知水平。“不行而知”，不用到处跑，这一点也是可以得到的。“不见而明”，不用亲自去看，也能够明了道理，明了了这个道理，那就内心清净、无欲。“不为而成”，“不为”就是无为，就是按照大道的方式自然而然地去做，而不去妄为，这样一切都会顺理成章。这是我们第四十七章里边讲的内容，字虽然不多，但道理需要我们认真体会，“不出户，知天下；不窥牖，见天道。其出弥远，其知弥少。是以圣人不行而知，不见而明，不为而成。”当然对这一章的更进一步的理解需要我们和第四十八章，也就是我后面要讲的这一章相互参照，我们对这个理解才会更深刻、更准确。一开始就给大家说第四十七章、第四十八章我们要合起来，相互参照，为什么？这两章的内容讲的是非常吻合的，事实上也应该是一章的内容。第四十七章里边讲，“其出弥远，其知弥少”，第四十八章一开头就讲：“为学日益，为道日损。损之又损，以至于无为，无为而无不为。”这八个字一下子和上边的内容就衔接起来，为什么跑得越远反而知道的越少，这是站在道的角度来讲的。“为学”，在学知识，学到的知识内容越来越多。当然从学知识的角度来讲，这是非常有益的，不断地增多，可是我们获得很多的东西，见到了很多的东西，其实对我们了解根本性的规律和本质，了解大道并没有好处。站在一个更高的层次理解，就是说我们“为学”，讲究的是越多越好，见得多，看得多，见多识广。但是“为道”讲究的是什么呢？讲究的是内心的修行，讲究的是减少，用我们前面讲的话来讲，为学做的是加法，为道做的是减法，减少我们内心的欲念，减少我们的贪念，减少我们对很多问题的一种受了外界的影响而导致的内心的纷扰、困惑、迷乱，把这些东西损之又损，一点一点地把它减少，就像那镜子的灰尘一点点擦掉一样，“损之又损，以至于无为。”“无为”就是自然而为，把欲望减少，减少再减少，就达到了一种“无为”的境界，没那么多的贪念，没那么多的纷扰。我们用镜子来照这个天下，来照事物，万物进入到镜子里边，呈现出它本来的面貌。我们了解了事物的本质规律，了解了大道按照它来做，“无为而无不为”达到的是“无不为”的效果。所以在这儿借着这个机会，我再说一下道家自然无为的具体的含义：第一，不妄为；第十六章里边就讲，“不知常，妄作，凶。”你不了解事物的规律、规则，瞎折腾、胡折腾，那结果是非常糟糕的。我们“损之又损”，减少了这些遮挡着我们的认识，遮挡了我们的心窍的这些外在的事物、灰尘、迷乱，我们就照见了事物的本质和规律，我们就“不妄为”。第二，不多为；抓住关键，举重若轻，静观，看到事物的本质，找到解决问题的正确的方法，抓住关键，举重若轻。第三，有所不为；人要想有所为，必须有所不为，要想有所得，必须有所舍。我们舍弃了那些阻碍了我们正确行动、阻碍我们沿着大道行走的那些纷纷扰扰，这样能达到一个无不为的效果，也就是覆盖面广，效果更好，“无为而无不为”。下面这一段就讲，按照“无为”的方式来理解天下万事万物。“取天下常以无事，及其有事，不足以取天下。”“取天下”的规则是什么呢？“无事”。“无事”就是不多事，不干涉，不扰民，这样一切就自然而然顺理成章。所以第五十七章里边讲的这个事情就比较明确，“我无事而民自富，我无为而民自化”。“及其有事”，如果老是多事，老是妄为，不懂得事物的规律、规则，瞎折腾、胡折腾，这就是“及其有事”。则“不足以取天下”，那就不能够获得天下。得到的天下也得失去，因为它违背了大道。</t>
@@ -708,10 +708,11 @@
     <t>第四十九章</t>
   </si>
   <si>
-    <t>圣人无常心，以百姓心为心。善者，吾善之；不善者，吾亦善之，德善。信者，吾信之；不信者，吾亦信之，德信。圣人在天下歙（xī）歙（xī），为天下浑其心。百姓皆注其耳目，圣人皆孩之。</t>
-  </si>
-  <si>
-    <t>圣人没有成心，以百姓之心为心。善良的百姓我善待他们，不善良的百姓我也善待他们，这样使人向善；讲诚信的人我以诚信对待他们，不讲诚信的人我也以诚信对待他们，这样使人诚信。圣人领导天下，收敛自己的私欲，使天下百姓的心灵都变得淳朴。百姓都只关注耳听眼见的事，圣人将百姓像孩童一样对待。</t>
+    <t>圣人无常心，以百姓心为心。善者，吾善之；不善者，吾亦善之，德善。信者，吾信之；不信者，吾亦信之，德信。圣人在天下歙（xī）歙，为天下浑其心。百姓皆注其耳目，圣人皆孩之。</t>
+  </si>
+  <si>
+    <t>圣人没有固执不变的思想，而是把百姓的思想当作自己的思想。。善良的百姓我善待他们，不善良的百姓我也善待他们，结果就会使他也变得善良；讲诚信的人我以诚信对待他们，不讲诚信的人我也以诚信对待他们，结果就会使他也变得诚信。圣人领导天下，收敛自己的私欲，使天下百姓的心灵都变得淳朴。百姓都只关注耳听眼见的事，而圣人要使他们都变得像无知无欲的婴儿一
+样。</t>
   </si>
   <si>
     <t>第四十九章是《道德经》里边比较重要的一章，因为这里边有一句话大家都很熟悉，我们领导者讲话的时候也经常引用，就是以“百姓心为心”。从前面讲的内容，大家会知道这是一个通过换位思考，得出来这样的一种结论。这一章开头这句话我们先说一下。“圣人无常心，以百姓心为心。”是说一个好的领导者、统治者，不要老固执己见。“常心”就是固定的心思，自我的执着，不要老固执己见，不要老把自己的意志强加给别人，乃至强加给人民。应该怎么样呢？换位思考，将心比心，“以百姓心为心”，倾听民众的呼声，关注民众的利益，吸取民众的智慧，这都是“以百姓心为心”的表现。我们先体会一下这一章的宗旨在讲什么？其实这个道理就是讲了，换位思考，将心比心。百姓善良，我也对他善良；不善良，我也对他善良；信任我的，我信任他；不信任我的，我也信任他。干吗呢？这样我就能让人向善，让大家讲诚信。最后这一段就说一个好的领导者、统治者，让百姓都回归到他本来的这种生活，关注的是自己的生活中的事情。不要想那么多，不要心思混乱，不要烦乱，这样才能够形成一种良好的和谐的状态。这是老子的想法。我们一句一句来解释。“圣人无常心”，我再重申一遍，“圣”的繁体字，上面是个耳和口——聖，这两个字并列就代表着通达事理，下面是个王，也就是说一个好的领导者、领导人称其为“圣”。在这一章里体现得最为明显。“圣人无常心”，有的本子也叫“常无心”，意思都是一样的，就是不固执己见，没有自己僵化固定的思维，懂得换位思考。其实关于这个意思，我们通过前面讲过的第二十二章参照着理解，就比较容易了。我在前面多次说过，读《道德经》最好的方法就是不看注解，以经解经，相互参照，明白它要讲的真正的含义，谁的解读也不如他本人对这个东西的解释更符合他的本意。第二十二章里边就讲“不自是”“不自见”“不自矜”“不自伐”这“四不”。“不自是，故彰。不自伐，故有功。不自矜，故长。”这样我们才能不断成长，不断进步。一个好的领导人也是这样的，领导者、统治者，也应该“四不”，也就是“无常心”。你没有这样的智慧，老是固执己见，老是自我吹嘘，老是自我夸耀，老是觉得自己了不起，那你就没办法换位思考，将心比心了。所以“无常心”才能以百姓之心为心，倾听民众的呼声，吸取民众的智慧，关注民众的利益。沿着这个思路下面也好理解了。“善者，吾善之；不善者，吾亦善之，德善。”善良的人我用善良去对待他，不善良的人，我也用善良的方式去对待他，干嘛呀？教化、感化，这样我就得到了真正的善良。为什么呢？你这样做，起代表带头作用，大家也就人心向善了。大家注意这个“德”，王弼的解释非常明确，“德者，得也”，这样做就得到了这个天下、这个社会，这个国家就会人心向善。“信者，吾信之；不信者，吾亦信之，德信。”信我的人，我相信他，我跟他讲诚信；不相信我的人，我也相信他，跟他讲诚信。干嘛呀？这样天下人就会觉得诚信可贵，也就往诚信的方向去努力去发展了——“德信”。“圣人在天下歙歙”，“歙”就是合，就是收敛。你说圣人怎么样领导、管理这个天下呢？先要收敛自己的欲望，要想领导好别人，你先领导好自己，要想领导好自己，你先领导好自己的情绪，领导好自己的欲念，上梁不正则下梁歪嘛。“歙歙”，收敛自己的欲望，减少自己的欲念。“为天下浑其心”，让这个天下都怎么样呢？大家都没那么精明。不总是为了什么事都去争，“浑其心”，都那么样地浑厚、淳朴、厚道，关心自己的现实生活，而不是那么多纷乱的思维，那么多胡乱的想法，那么多的技巧、智谋、套路、心眼，用这种方式让大家和谐相处。“圣人皆孩之”，一个好的领导者把天下人都当作儿童，当作自己的孩子，一方面对他们非常关爱，另一方面也不要让百姓人心混乱，都像孩童一样纯净、淳朴。当然了，后边这一段大家也看得出来，这也是老子的一厢情愿。他希望统治者减少自己的欲望，天下人跟着也减少自己的欲望，关注自己的现实的生活，没有那么多的争斗、心眼、套路、技巧、欺骗、欺诈。这是老子生活的理想状态，也是他认为是和谐世界的前景，我们权当这也是他的一种理念和希望，毕竟这个社会的和谐也是我们的一种希望。只是他这种方法大家要辩证对待，大概用这种方法实现天下的太平，也只能是一种理想和理念，很难真正得以实现。但这一章里边大家要注意，开头这句话，我们要熟记，因为在我们国家的领导人的很多讲话里边都能看到这句话的出现，“以百姓心为心”，这是道家思想里边非常重要的一句话，让我们感觉到老子这个人在他冷静的、甚至有点冷酷的外表之下，内心涌动的热流，对于天下人的关注，对于天下人的关爱。这一章的原文我们解释完了，再强调一下这章的逻辑和重点，这章里边的关键在哪呢？这一章里边的关键是讲“圣人”和“百姓”，他们是国家不同层面的人，这一章讲究什么呢？讲究各安其位，各循其理。老子对这些做统治者的讲，你们要“以百姓之心为心”，善良的人呢你要好好地对待，不善良的人呢你也要好好对待，这样你才能得到这个国家人心向善的风气。信你的人你要讲诚信，不信你的人你也要讲诚信，这样才能得到天下诚信的风气。“圣人在天下”，圣人在上，领导天下。应该怎么样呢？怎么样叫循理循道呢？应该清静，无为，少折腾，少多事儿，这是上边的理，给他们讲的，你应该这样做，收敛自己的欲望，减少自己的奢靡、奢华，“清静为天下正”，这是对他们。对下边怎么讲呢？你这个在上边的人应该让下边遵循一个什么样的道理呢？“为天下浑其心”，让这个百姓浑厚，淳朴，宁静，没有那么多纷乱的想法，那么多技巧、心眼、套路、欺诈、欺骗，按照这个方向，百姓都关注自己现实的生活，把自己的日子过好，少管别的事儿，你让百姓能够做到这一点，上边的管上边的事，循上边之理，下边的循下边之理，这天下不就和谐了嘛。大家看出来了吧，“圣人皆孩之”，好的领导，一个国家的领导者，让这国家的百姓都像小孩一样，纯净、淳朴，没有那么多的欺瞒欺诈。上按上边的道理，下按下边的道理，这不就形成了一个和谐的状态了嘛。我们知道，真正的和谐是有差别的统一，大家都应该有表达自己的意见的机会，表达自己观点的机会，“各美其美，美人之美”，有差别的统一。但是老子这个地方讲的道理不是这样的，他讲的是“圣人无常心”，你要考虑到百姓，百姓在圣人的领导下应该怎么做呢？应该浑厚淳朴，没有那么多的智谋、欺诈、心眼，关注自己的现实生活，干好自己的事情，像儿童一样，纯净、干净、宁静，形成这个社会的和谐状态。所以我们只能说，老子这个想法呀追求一种和谐的目标，但是这个所用的方法在我们看来，这还是有很多地方值得检讨的，因为真的把百姓都变成小孩，还是不免有一点愚民政策的感觉。这一点大家还是要正确地理解。</t>
@@ -720,10 +721,10 @@
     <t>第五十章</t>
   </si>
   <si>
-    <t>出生入死。生之徒十有三，死之徒十有三。人之生，动之死地，亦十有三。夫何故？以其生生之厚。盖闻善摄生者，陆行不遇兕虎，入军不被甲兵。兕（sì）无所投其角，虎无所措其爪，兵无所容其刃。夫何故？以其无死地。</t>
-  </si>
-  <si>
-    <t>人生就是从出生到死亡的历程。长寿的人占十分之三，短命的人占十分之三，本可以长寿但妄为把自己置于死地的人也占十分之三。为什么？因为他们过分地追求奉养自己以求生。听说善于养生的人，在陆地上行走不会遇到兕、虎，在战场上不会被兵器所伤。兕的角无处可用，虎的爪也没了用处，兵器的刃也用不上。为什么？因为他不把自己置于死地。</t>
+    <t>出生入死。生之徒十有三，死之徒十有三。人之生，动之死地，亦十有三。夫何故？以其生生之厚。盖闻善摄生者，陆行不遇兕（sì）虎，入军不被甲兵。兕（sì）无所投其角，虎无所措其爪，兵无所容其刃。夫何故？以其无死地。</t>
+  </si>
+  <si>
+    <t>人生就是从出生到死亡的历程。长寿的人占十分之三，短命的人占十分之三，本可以长寿但妄为把自己置于死地的人也占十分之三。为什么？因为他们过分地追求奉养自己以求生。听说善于养生的人，在陆地上行走不会遇到犀牛和猛虎的伤害，在战场上不会被兵器所伤。犀牛的角无处可用，老虎的爪也没了用处，兵器的刃也用不上。为什么？因为他不把自己置于死地。</t>
   </si>
   <si>
     <t>我们来讲第五十章，这一章表面上在讲养生之道，也就是文章所说的“摄生”，实际上表达的是更为深刻的道理。我们看书、看电视剧的时候，会发现有那么一些大师、大医生，一些位重权高的人向他们请教养生之道，“我怎么样能活得更加长寿？”这些医生、养生大师啊，大都是告诉他们要清心寡欲，不要奢靡奢华，不要胡吃海塞，其实这就是道家对于养生这事儿往更高的一个层次所要修养的内容，我们也可以把它概括为道家的生死观。道家认为养生跟生死密切关联。养生要顺应自然，要自然而然，要掌握规律、规则。你看我们读《庄子·养生主》里边的“庖丁解牛”，讲的不就是这个道理吗？目无全牛，游刃有余！这牛解得跟跳舞一样，跟音乐一样。所以文惠君最后就对这个庖丁讲：“吾闻庖丁之言，得养生焉。”养生要顺应自然规律，自然而然，自然而为。“生之徒十有三，死之徒十有三。”然后老子做分析，如果把天下的人分做十成，那么有十分之三的人是“生之徒”，也就是长寿的，还有十分之三的人是“死之徒”，是短命的。还有十分之三的人是怎么样的呢？“人之生，动之死地，亦十有三。”这些人本来可以长寿，最后由于自己的胡为、妄为、折腾，就把自己置于死地了。所以你看它的分类很有趣，十成的人中，三分之一的人应该是长寿的，三分之一的人本身体质各方面就是短寿的，还有三分之一的人本来可以长寿，但是妄动、胡为而置于死地。为什么会这样？《道德经》给了我们这样一句话：“以其生生之厚。”生，养生，或者可以解释得更明确，叫“求生”。太着急了，太迫切了，老想延长自己的性命，老害怕自己的营养不够，最后营养过剩了，反而把自己置于一个另外的相反的方向。当下一些有智慧的医生就提醒，我们现在不是营养不良，而是营养过剩，“生生之厚”。当然《道德经》讲的这句话只针对当时的统治者、位高权重的人而言，老是生活得这样奢靡奢华，“五色令人目盲，五音令人耳聋，五味令人口爽，驰骋畋猎，令人心发狂……”老是这样，还以为是让自己生命不亏，活得不亏。求生之厚，太急、太迫切，营养过剩，自己本来可以长寿，反而被置于成“死之徒”了，到短寿的那一拨去了。所以下面老子就讲了：“盖闻善摄生者”，听说这善于养生的人是什么样子呢？他们用了下边一段形容：“陆行不遇兕虎，入军不被甲兵。兕无所投其角，虎无所措其爪，兵无所容其刃。”习惯上我们以为“兕”是犀牛，或者有的叫母犀牛，其实这两种动物还不一样。这个“兕”是古代的一种瑞兽，比较凶猛，所以在古代的文字中，经常用这个“兕虎熊”比喻凶险之地。懂得养生的人，懂得正确对待自己生命的人，不去冒这个险。陆行的时候，尽量不碰这些凶猛的动物，如果你碰上它了，那你就没办法了，谁让你冒那个险呢？明知道野生动物园人家不让下车，你非得下车，遇到老虎了吧。有些地方人家告诉这个规则，这里边有危险，你偏不听，明知山有虎，偏向虎山行，明知山有狼，偏要做狼餐，这不就是“人之生，动之死地”吗？“入军不被甲兵”，上阵打仗的时候不为兵器所伤。为什么呢？“兕无所投其角”，你不遇到这个兕，那当然它那个凶猛的角就没有办法发挥它的作用了，没有办法针对你。一般我们画“兕”的时候都习惯把它画成独角兽。“兕”最有名的代表就是太上老君骑的那个板角青牛了，角非常锋利，尖锐，杀伤力强，你不遇到它，尽量别碰到，别把自己置于危险的境地，它的角当然就无所用了。“虎无所措其爪”，你不往虎山行，不遇到它，提前准备好避免这种凶险，老虎爪子再尖利，牙齿再锋利，它也无法对你发挥作用。“兵无所容其刃”，上阵不为甲兵所伤，尖锐的兵器，也没有办法发挥它的作用。“夫何故？”为什么会这样？“以其无死地”，不把自己置于死地，这样也就不会让自己的生命受到戕害。这是就是五十章。这一章体现了道家的养生之道：简单地说就是不要“作死”，自己不要找死，本来可以长寿的，自己作死把自己置于死地。很多人非得触犯法律的界限，甚至因此送掉了自己的生命，这不就是把自己置于死地嘛！所以我们说“NoZuoNoDie”，不作不死。从养生的角度来讲，你看道家讲的顺应自然，不单只是生活中的清心寡欲，而且还指不触犯边界底线，不触犯红线，知足不辱，知止不殆，不置身于死地，不让自己冒这种凶险，这也是道家养生之道里边的一个重要的内容，而且是更接近于哲学层面的、更有智慧的内容。那么这一段我们讲完了之后，我还要跟大家强调一下，道家的养生观，其实也是道家的生命观。道家对于生命的看法讲究的是自然而然，意思是什么呢？过于求生，过于厌恶死，这都不是一种自然而然的智慧，因为死亡本身就是生命的一部分，人自然而生，自然而死，真的到了生命结束的时候，那也应该开朗地、乐观地对待。这一点在道家的继承者那里，也就是道家的第二号人物庄子那里，讲得非常的明确——“之所以善吾生者，乃所以善吾死”。我们很好地对待自己的生命，不把自己的生命主动地置于死地，不求生之厚，真的面临死亡的时候，也应该把它好好地对待。自然而生，自然而亡，这是生命的自然而然的规律，谁也阻挡不了。第五十章，老子借养生之道讲了一个更重要的道理：有的人求生太急迫，太厌恶死亡，太害怕死亡，越是求生之厚，服了大量的药，用各种各样的营养的方式，推开死亡，想要避免，没想到越想避免的反而来得越快。所以，道家讲究自然而然的思想，这有着重要、杰出的意义。我们做个小小的梳理。第五十章，我们从开始讲的时候就给大家讲过，这一章可以分成两段，一段是讲有的人本来可以长寿，却进入了短命的行列，是因为“求生之厚”，太急迫、营养过剩导致的，另外一个是由于妄为、“作”，把自己置于死地的。怎样才能避免这两点呢？还是道家的这种思想，顺其自然，清心寡欲，清静为天下正。正确地对待生命和死亡，不把死亡当作是完全可以避免的事情，真的面临死亡的时候，也能够开朗地、乐观地对待。</t>
@@ -732,10 +733,11 @@
     <t>第五十一章</t>
   </si>
   <si>
-    <t>道生之，德畜之，物形之，势成之。是以万物莫不尊道而贵德。道之尊，德之贵，夫莫之命而常自然。故道生之，德畜之：长之、育之、亭之、毒之、养之、覆之。生而不有，为而不恃，长而不宰，是谓玄德。</t>
-  </si>
-  <si>
-    <t>道生成万物，德蓄养万物，万物有了具体的形状，周围的环境使万物得以成长。道受尊崇，德被珍贵，不妄加干涉而使万物顺应自然。所以道生成万物，德蓄养万物：使万物成长作育，使万物成长成熟，使万物得到养覆保护。生成万物而不占有，化作万物却不把这当成是凭借、倚仗，长养万物却不主宰，这就叫“玄德”。</t>
+    <t>道生之，德畜（xù）之，物形之，势成之。是以万物莫不尊道而贵德。道之尊，德之贵，夫莫之命而常自然。故道生之，德畜之：长之育之、亭之毒之、养之覆之。生而不有，为而不恃，长而不宰，是谓玄德。</t>
+  </si>
+  <si>
+    <t>道生成万物，德蓄养万物，万物有了具体的形状，周围的环境使万物得以成长。因此万物没有不尊崇道和重视德的，道受到尊崇，德受到重视，并没有人如此命令 而是万物本身自然而然地永远去这样做。所以道生成万物，德蓄养万物：使万物成长作育，使万物成长成熟，使万物得到养覆保护。道、德养育了万物
+却不据为己有，帮助了万物却不求它们的回报，成就了万物却不做它们的主宰者，这可以说是最高尚的品德。</t>
   </si>
   <si>
     <t>第五十一章逐句地来解释一下。“道生之”，“生”，创造，生养。道创造了万事万物。“德畜之”，德畜养了万事万物。“物形之”，万事万物有了具体的形状。“势成之”，周围的环境使它得以成长。正因为如此，所以“万物莫不尊道而贵德”，以道为尊，以德为贵。“道之尊，德之贵，夫莫之命而常自然。”尊道贵德，那自然会得到一个良好的结局和结果，这不是命，这就是自然而然的规律、规则。“故道生之，德畜之。”所以道生养万物，德蓄养万事万物。“长之、育之”，使它成长，使它不断地培育长大。“亭之、毒之”，这个“亭”呢，其实也好理解，我们常说亭亭玉立，这个“亭”就是成长的意思。这个“毒”就是成熟的意思，使万事万物成长，使其成熟。“养之、覆之”，“养”和“覆”都是保护的意思。养育万物，保护万物。“生而不有，为而不恃，长而不宰。”生养了万事万物，却不把它当作私有的产品，对万事万物有作为，却不把这个当作一种倚仗、凭借，甚至勒索的手段，对万事万物有这么大的功德，却不是以主宰者的身份出现。这个就是“玄德”，这就是最高深的、最深刻的智慧与品德。这是我们对这一段的直观的解释。其实，这一段的深意远不止于此。因为中国人讲哲学讲究“知行合一”，讲道的品性，其实也是为了人向道的品性去学习，按照道去做，这个也就是“德”。所以第五十一章里边讲道养育万物，德蓄养万物，也是人应该效法学习的。在这个层面上，我们深入地理解这一段话。“道生之，德畜之”，道创造了万事万物，但是它不把万事万物作为一种私有产品，并不是以一种主宰者的身份，以求其回报。由此我们可以看到，老子给我们提供了想要做成一件事的四个核心的要素和条件，也就是一种应有的程序和原则。第一个，要有道，因为道是创造万事万物的本源，所以我们要坚守大道，按大道的方式来创造。第二个，“德畜之”，“畜”就是积累的意思。在有道的基础上，我们要不断地、坚定地按照道去做，也就是“积德”。德就像水一样，我们就像一条船一样，我们积累的水越多，我们这条船在水上才能够航行得更自由。所以朱熹有一首诗说：“昨夜江边春水生，艨艟巨舰一毛轻。向来枉费推移力，此日中流自在行。”昨天江边涨水了，平常推也推不动的大船，现在根本不用推了，水多了，自然而然地就航行更加自由。他讲的是读书的积累达到一种自由的境界，其实人生又何尝不是如此呢？我们积累的德多了，按照道做事，更坚定、坚持、持久，那也就给我们人生提供了更广阔的空间与平台，不断地积德，我们的行为也就更加自由，我们的行为也就更加能够符合大道。庄子在《逍遥游》里面也讲了这样一句话，“且夫水之积也不厚，则其负大舟也无力”。水积累不多的时候，大船是浮不起来的，只要积累得多了，结果就是自然而然的事情，和朱熹所讲的道理不谋而合。第三个，“物形之”。人有道有德，是不是就可以把事情做成了呢？不够的，还需要一定的物质条件和手段，巧妇也难为无米之炊。有条件要上，没有条件我们创造条件，这样才能把事情向更成功的方向去发展。道、德、物三个条件总够了吧？不够的。要想把事情真正做成，还有一个很重要的条件，就是“势”，“势成之”。道家讲的无为，更强调的是顺势而为，掌握这个形势，了解大势，这样才能把事情做成。《淮南子》中举过这样的一个例子，大禹为什么能把水治成呢？顺水势而为。商汤周武为什么能夺得天下呢？顺民心而为。民心所向，就是历史发展的大势与潮流。所以大家在第二个层面把这四个字提炼出来，它是一个很好的成功学的例证，我觉得比现在讲的一些所谓的零零散散的成功学，不知道要深刻多少倍。道、德、物、势，“道生之，德畜之，物形之，势成之”。既然这四个要素，道和德是排在最前面的，“是以万物莫不尊道贵德”，所以万事万物没有不尊道而贵德的。人更是如此，有道有德，后边的事情才能继续发展，所以“道之尊，德之贵，夫莫之命而常自然”，这不是命，这就是一个永恒的自然而然的规律、规则。你按照道，按照德，尊道而贵德，会得到一个自然而然的良好的结局和结果，这是自然而然的事情。这不是命，这就是自然而然的规律和规则。所以大家注意，我们中国的这些经典，比如说《易经》，比如说《道德经》，都不是用来算卦占卜的，它就讲一个重要的内容：按照规律、规则来做，结果水到渠成、自然而然。下面这一段是对上面做的一个延伸。“道生之，德畜之”，道和德，生养万物，为万物提供条件，让它生长发展。“长之、育之”，培育万事万物使其生长、发展。“亭之、毒之”，使它成长、成熟。“养之、覆之”，不仅如此，还要养护万物，覆盖万物。道和德让万物长大，培育万物的成长，使它成熟又予以保护，功德可谓无量。孔子有一段名言：子曰：“予欲无言。”子贡曰：“子如不言，则小子何述焉？”子曰：“天何言哉？四时行焉，百物生焉，天何言哉？”这段话的直译是：孔子说：“我现在只想沉默。”子贡说：“如果你不说出心里想什么，那么我们这些学生还拿什么去记述呢？”孔子说：“自然说过些什么？不过放纵四季周而复始，任由百物蓬勃生长。自然你又何曾告诉别人什么啊？”很多人把这段话中的“天”翻译成神灵，这是不对的。其实这个“天”指的是大自然，也就是《道德经》里的天地，天地无语而泽被苍生万物，确又无语不居功自傲，不把自己当做万物主宰。这不也是《道德经》第五十一章的核心吗？培育万物的成长，使它成熟又予以保护，功德可谓无量。其实，在这样的智慧层面，孔子和老子的见解都是一样，“生而不有，为而不恃，长而不宰，是谓玄德”。关于这段重要的话，我们在第十章已经详细说过，不再重复。</t>
@@ -747,7 +749,7 @@
     <t>天下有始，以为天下母。既得其母，以知其子；既知其子，复守其母，没（mò）身不殆。塞其兑（duì），闭其门，终身不勤。开其兑，济其事，终身不救。见小曰明，守柔曰强。用其光，复归其明，无遗身殃，是为习常。</t>
   </si>
   <si>
-    <t>天下万物都有本原（即道），作为万物的母亲。认识了作为万物之母的道，就能认知万物；认知了万物，就能坚守作为万物之母的道。这样终身都没有危险。塞上欲望的孔穴，闭上欲望的门户，终身都没有忧劳；打开感官欲望的门户，增添纷繁的事件，终身都不可挽救。察见细微的事物叫“明”，坚守柔弱叫“强”。用道的光芒来了解具体事物中的规律、规则，复归到事物的光明的状态，不会给自己留下那么多的祸殃，这就叫普遍永恒的规律。</t>
+    <t>天下万事万物都有本源（即道），可以把这个本源作为万物的母亲。认识了作为万物之母的道，就能认知万物；认知了万物，就能坚守作为万物之母的道。这样终身都没有危险。塞上欲望的孔穴，闭上欲望的门户，终身都没有忧劳；打开感官欲望的门户，增添纷繁的事件，终身都不可挽救。察见细微的事物叫“明”，坚守柔弱叫“强”。用道的光芒来了解具体事物中的规律、规则，复归到事物的光明的状态，不会给自己留下那么多的祸殃，这就叫普遍永恒的规律（可以说是掌握了大道）。</t>
   </si>
   <si>
     <t>一开始我们就说过，《道德经》里边有一个非常好的“正能量”，就是每当说到高大上的、特别伟大的事情，都喜欢用母亲的“母”字来作为代替和概括，或者说用“母”来做一个形象的比喻。如果我们的孩子读这样的文字，潜意识里就会有对母亲有一种敬畏与尊重。我们在第一章里边就说到，“无，名天地之始；有，名万物之母”。在这一章里边，又出现了母亲的这个“母”的概念。“天下有始，以为天下母。”就像动物、人类都是由母亲生养的一样，万事万物也都是由道创造的。老子用“母”来比喻大道，生动形象且让人充满对道的敬畏，意思就是说，天地一开始的时候，其实大道已经就在了。“既得其母，以知其子。”我们了解了大道，就是“既得其母”。知晓了大道，那我们就“以知其子”，也就了解了儿女。这个意思是什么呢？道是万事万物的普遍规律，它永恒存在，具体的事物都拥有具体的道，也就是具体的规律。你了解了大道，就可以以此来了解万事万物的具体规律。茶有茶道，花有花道，练武有武道，下棋有棋道……了解了普遍的道，也就更能够了解这些具体事物间的规律与规则。反过来也一样，“既知其子，复守其母。”我们从具体的事物之间，比如棋道、花道、茶道，从这具体的事物之间，我们了解了大道，感知了大道，那也就能更好地坚定地坚守大道。“没身不殆”，这样地做事情永远没有危险，没有失败，为什么？以道佑之，以道护之，这样我们做事情才能没有危险，没有失败。下面就说了解大道的方式方法。大道的了解，不是靠感性来体验到的，就像我们前边说的，“为学日增，为道日损。”“不出户，知天下；不窥牖，见天道。”所以如果是跟着感觉走的话，你是了解不了真正的大道的。因此“塞其兑，闭其门，终身不勤”，不要依赖感觉，不要把我们所见所知的就当作大道，重要的要用心，也就是哲学上讲的，用理性的思维，来了解认知大道。反过来讲，“开其兑，济其事，终身不救”，如果跟着感觉走，打开我们的感官的门户，感官这个东西，它是有很大的局限的。第十二章里面就讲，“五色令人目盲，五音令人耳聋，五味令人口爽”。你只靠这个是了解不了大道的。“见小曰明，守柔曰强。”什么叫“见小”啊？“小”就是具体的事物，具体的事物里面也蕴含着规律、规则。你能够从具体事物里了解具体的道、具体的规律，这也是一种明智。“守柔曰强”，道家是讲“柔弱胜刚强”的，道家是讲“知其雄，守其雌”的，“柔”就是雌柔，不管我们多么强大，我们也懂得坚守这个柔弱，因为柔弱更能长久。力量不够的时候，我们懂得用守柔的方式、韬晦的方式，来使自己的力量不断增大、不断增强，这样才能成为真正的强大。“用其光，复归其明”，用道的光芒，“复归其明”，来了解具体事物中的规律、规则，复归到事物光明的、明智的状态，我们才能走在光明的大道上。“无遗身殃”，不会给自己留下那么多的祸殃。“是为习常”，这个“习”，不同的本子有不同的写法。习，就是普遍、永恒的意思，就是普遍的永恒的规律、规则。也有的本子用的是沿袭的“袭”，也就是遮盖的意思。《道德经》里边用这个“袭”字的意思就是说，这是被大家认识不到的、被遮盖的规律规则，了解了这一点，我们也就对事物的了解更加深入。这两个意思都通，我们这里边用的是复习的“习”，学习的“习”，也就是经常的、普遍的、永恒的意思。“是为习常”，这就是一个经常的、普遍的、永恒的规律、规则。这一章核心的内容是说，道是一个普遍的规律，它存在于天地之间，所以叫“大道”。我们了解了大道，掌握了普遍的规律、规则，再来认识具体事物中的规律、规则，这是非常有帮助的，也是非常重要的。反过来也是一样，了解了具体事物中的规律、规则，也能够让我们更加坚信大道的存在，更加了解大道的伟大。这一章以母和子为喻，大和小对照，就讲述了这样的一个哲学的道理。这样的智慧能让我们用到大道的光芒，走在光明的大道上。</t>
@@ -756,10 +758,10 @@
     <t>第五十三章</t>
   </si>
   <si>
-    <t>使我介然有知，行于大道，唯施（yí）是畏。大道甚夷，而民好径。朝甚除，田甚芜，仓甚虚。服文彩，带利剑，厌饮食，财货有余，是为盗夸。非道也哉！</t>
-  </si>
-  <si>
-    <t>假如让我稍微有些认知，行走在大道上，最害怕走到斜路上去。大道非常平坦，但一般人喜欢走捷径。（无道之君）朝政非常混乱，田园非常荒芜，仓库非常空虚。穿着华美的衣服，佩带锋利的宝剑，吃饱喝足，积存财货有余，这是夸耀自己的强盗途径。无道啊！</t>
+    <t>使我介然有知，行于大道，唯施（yí）是畏。大道甚夷，而民好径。朝甚除，田甚芜，仓甚虚。服文彩，带利剑，厌饮食，财货有余，是为盗滥竽（yú）。非道也哉！</t>
+  </si>
+  <si>
+    <t>假如让我稍微有些认知，行走在大道上，最害怕走到斜路上去。大道非常平坦，但一般人喜欢走捷径。（无道之君）朝政非常混乱，田园非常荒芜，仓库非常空虚。穿着华美的衣服，佩带锋利的宝剑，吃饱喝足，积存财货有余，这样的人叫做强盗头子（滥竽：强盗头子）途径。这种行为是不符合大道的！</t>
   </si>
   <si>
     <t>讲到这里大家已经非常清楚了，老子衡量事情的最高原则就是大道。“使我介然有知”，“芥”就是小的、稍微的意思。假如让我稍微有知识、有智慧，“行于大道”，走在大道上。我最怕的是什么呢？“唯施是畏”，“施”，就是逶迤、曲折，在这里指的是邪路、歧路。走在大道上最可怕的是什么呢？就是害怕歧路太多，害怕走到邪路上去。“大道甚夷，而民好径。”其实大道是非常平坦的，但是一般人都喜欢走捷径，老想抄近道。“朝甚除”，朝政非常得混乱。“田甚芜”，田园都已经荒芜了。“仓甚虚”，仓廪实才好嘛，现在仓库里边都是空虚的。可是那些统治者在干吗呢？“服文采，带利剑。”穿着漂亮的、非常昂贵的衣服，带着珍珠宝石装饰的利剑。“厌饮食”，什么东西都吃腻了，对什么好吃的东西都已经感觉到厌烦了。“财货有余”，家里的财宝有那么多的富余。这叫什么？“是为盗夸。”《道德经》认为这个就叫“盗夸”，强盗，还夸耀自己的强盗行为。《道德经》在第七十七章里边就讲，“天之道，损有余而补不足”。现在这些人做的是什么呢？“损不足，以奉有余”。“非道也哉”，这完全不符合道的规律、规则，完全不是按照道的方式来做嘛。这一章表现了老子的平民的思想、公平的思想，指责在“朝甚除，田甚芜，仓甚虚”的情况下，那些人“服文彩，带利剑，厌饮食，财货有余”夸耀自己的强盗行为。这一章有一些字，我们还得具体地、细致地解释一下。“唯施是畏”，凭什么把这个“施”念成“迤”，解释成歧路呢？因为道弯弯曲曲的时候，歧路众多。在《列子•说符篇》里边讲的一件事——歧路亡羊。杨朱他们家的邻居羊丢了，很多人都出去找，杨朱就觉得很奇怪就问，就一只羊怎么这么多人去找啊？邻居就告诉他，歧路多，岔路太多了。找羊的人回来了，杨朱问找到了吗？邻居说没找到。又派更多的人去找，还没有找到。歧路中又有歧路，岔路中又有岔路，所以常常使人丧失了大道，迷失了大道，所以杨朱听了之后几天都不说话。古人有“歧路亡羊”，也有遇穷途而哭，走道遇到没有路了，痛哭而返，其实都是感觉到了人生道路上的一些很值得人害怕的事情。行于大道，最害怕的就是歧路、岔路，一旦走错路，方向一错，后边的一切麻烦就都来了。所以老子说“大道甚夷”，“夷”就是平坦的意思，大道其实极为平坦。“而民好径”，人却老喜欢去走这个捷径，走了捷径之后，最后发现回到正确的大道上是非常困难的。其实，很多的所谓捷径就是歧路，就是邪路，人要脚踏实地，这样才能够行走在正确的大道上。通过努力获得成功，而不要投机取巧，更不要把投机取巧里边得到的东西当作一种炫耀夸耀，这个叫什么？“盗夸，非道也哉。”</t>
@@ -771,7 +773,7 @@
     <t>善建者不拔，善抱者不脱，子孙以祭祀不辍。修之于身，其德乃真；修之于家，其德乃余；修之于乡，其德乃长；修之于国，其德乃丰；修之于天下，其德乃普。故以身观身，以家观家，以乡观乡，以国观国，以天下观天下。吾何以知天下然哉？以此。</t>
   </si>
   <si>
-    <t>善于进行精神上的建设这是不可拔除的，善于掌握道的人不会脱离道，子孙世世代代不断尊敬、学习这个原则。用这个道理来修身，他的德会是真实的；将这个道理贯彻到修家，这样他的德才能有余；用这个道理来治乡，他的德才能不断丰富成长；用这个道理来治国，他的德才会丰盛；用这个道理来治理天下，他的德才会是普遍的。所以按照修身的原则来观察个人，按照齐家的原则来观察家庭，按照治乡的原则来观照乡，按照治国的原则来观照国，按照治天下的原则来观照天下。我怎么知道天下是这样的呢？就是因为这个道理。</t>
+    <t>善于进行精神上的建设这是不可拔除的，善于掌握道的人不会脱离道，子孙世世代代不断尊敬、学习这个原则。用这个道理来修身，他的德会是真实的；将这个道理贯彻到修家，这样他的德才能有余；用这个道理来治全乡，他的德才能不断丰富成长；用这个道理来治国，他的德才会丰盛；用这个道理来治理天下，他的德才会是普遍的（遍及全国）。所以按照修身的原则来观察个人，按照齐家的原则来观察家庭，按照治乡的原则来观照乡，按照治国的原则来观照国，按照治天下的原则来观照天下。我怎么知道天下是这样的呢（我凭什么来了解天下情况的好坏呢）？就是因为这个道理。</t>
   </si>
   <si>
     <t>第五十四章由三段构成。第一段：“善建者不拔，善抱者不脱，子孙以祭祀不辍。”这一段在讲按照大道来建设，没有人能够攻击倒它，把它拔除掉。大家想，人类建设的很多的东西，有成必有毁，都是会被拔除掉的，而大自然呢，比如说山川，这是大自然建筑的东西，有的或许可以被拔除掉，但这一章讲的不是这个意思。“善建者”指的是人精神方面的建设，大道方面的建设，这个伟大的思想是不会被攻击倒、被拔除掉的。比如我们现在学的《道德经》，历经两千多年，很多人都在攻击，在否定，在嘲笑，可是这无碍于它伟大的思想，现在学的人越来越多，大家越来越从里边得到一种智慧的启迪。另外像佛祖释迦牟尼，像孔子，历史上一些伟大人物的思想，他们的思想像什么？就像夜幕中的星光，给我们在黑暗中指引方向，有的甚至像光明普照的太阳。这些思想属于“善建者”，是没有办法把它攻击倒、拔除掉的。“善抱者”是什么意思呢？直观的理解就是善于把你抱住的人，你是脱离不开他的掌控的，其实这只是望文生义的理解。在《道德经》里边多次提到“抱”字，比如说第二十二章，“抱一为天下式”；比如说第四十二章，“万物负阴而抱阳，冲气以为和”。抱的是什么？“负阴抱阳”。所以这个“善抱者”就是掌握阴阳之不测，掌握阴阳相互作用、相互变化的规律规则，而“一阴一阳之谓道”，所谓“善抱者”，也就是了解大道的人。“不脱”，脱离不开大道的掌控，脱离了大道就走到了一个危险的境界。“子孙以祭祀不辍”，一代一代，千秋万代，按照“善建者”、“善抱者”这些伟大的思想来做，对他们表示一种尊重、敬仰，不断地学习。“修之于身，其德乃真。”按照这个伟大的思想来做事、来修身，这样所得到的德，才是真实的、纯净的。“修之于家，其德乃余。”按照大道来修家，一家人遵循大道，这样获得的家的品德才是丰盈有余的，积德之家必有余庆嘛。“修之于乡，其德乃长。”拿大道来传达给一个乡，按照这个方式形成一种良好的乡风。“长”就是领导的意思。你把这个方式在乡里边普及，让大家坚定地按照道的方式来做，你才能成为这个乡的好的领导者。我们知道，在宋朝的时候，陕西“蓝田四吕”首先制定了乡约，它对我们中国良好的乡风的培育起了非常大的作用，这不就是“修之于乡，其德乃长”的具体表现嘛。“修之于国，其德乃丰。”按照这样的一个方式来治理国家，让国家按照大道去做，所收获的德才是丰盛的、伟大的。同样的道理，“修之于天下，其德乃普。”天下是天下人的天下，不是一人之天下，所以大道之行，天下为公。按照善建、善抱的大道来做，修之于天下，这样大家得到的才是普遍的，如光明之普照。这是第二段，老子在讲按照“善建”、“善抱”的原则来做，所获得的伟大的结果。“以身观身”，“观”就是观察。我们按照修身的要求，大道修身的方式来观察这个人，他修身方面是不是善建、善抱，是不是没有脱离大道。“以家观家”，按照家庭的修养的要求来观察家庭的品德、家风。当然这个“观”的时候就自然有对比的意思，和其他的家里边进行对比，相互比较，看哪一个是更能按照“善建”、“善抱”的这种符合大道的原则方式来修身、来齐家。下边也是同样的道理，“以乡观乡”，乡自有乡的要求，和家是不一样的，范围扩展了，有很多家庭。但是如果这个大道一以贯穿，都是按照对“善建”的、“善抱”的原则祭祀不辍、尊敬，敬仰，以按照这样的一种规则来作为荣耀，都为良好的家风、乡风做出贡献，这不就是道一以贯之吗？同样的道理，“以国观国”，一个国家有这个国家的精神、思想、风貌，按照大道要求来做，在和其他国家比较中，取长补短。同样的道理，“以天下观天下”。大道一以贯之，一条主线，一切顺理成章，自然而然，无往而不胜。所以最后老子说，我怎么知道天下也会是这个样子？“以此”。大道所向无往而不胜，虽然人世间有那么多的枝枝蔓蔓，但是核心“善建”、“善抱”之大道，不要脱离开大道，坚定地、坚持地按照它去做，按照道去做就是“有德”。修身得到的是“真”，修家得到的是“余”，修乡得到的是“长”，修国得到的是“丰”，修天下得到的是“普”。所以，从修身开始，最后落到天下，不就是这样一个简单的道理吗？其实读这一章的时候，大家会有一个非常深刻的感受，中国先秦时代是中国的轴心时代，各个思想流派之间的思想，虽然有差别，但是也有相同的地方。所以我们看这和儒家的思想，修身、齐家、治国、平天下一样，都是从修身开始，最后才能够成为国家的好的领导者，才能把这种思想普及到天下。“天下难事必做于易，天下大事必做于细。”从自身做起，要求自己按照大道的这种修养、修为，按照“善建”、“善抱”的原则，坚持地、坚定地去做，我们才能真正地有德。</t>
@@ -783,7 +785,7 @@
     <t>含德之厚，比于赤子。蜂虿（chài）虺（huǐ）蛇不螫（shì），猛兽不据，攫（jué）鸟不搏。骨弱筋柔而握固，未知牝牡之合而全作，精之至也。终日号（háo）而不嗄（shà），和之至也。知和曰常，知常曰明，益生曰祥，心使气曰强。物壮则老，谓之不道，不道早已。</t>
   </si>
   <si>
-    <t>含德深厚的人，可比于刚出生的小孩。蜂蝎毒蛇等都不会刺咬他，猛兽不抓他，猛禽不攫取他。筋骨柔弱但小拳头握得很牢固，不知道男女交合之事但生殖器会举起，这是因为他精气充足。整天嚎哭但嗓子不会哭哑，这是因为他元气醇和。知道醇和、平和就是了解了道的规律、规则，了解这个事物规律、规则的人才是明智，让我们的生命有益才是一个吉祥，纵心任气，是强暴、强蛮的表现。强壮会趋于衰老，这叫做不合于道，不合于道便会早早灭亡。</t>
+    <t>含德深厚（品德极为高尚）的人，就好比刚出生的小孩。蜂蝎毒蛇等都不会刺咬他，猛兽不抓他，猛禽不攫取他。筋骨柔弱但小拳头握得很牢固，不知道男女交合之事但生殖器会举起，这是因为他精气充足。整天嚎哭但嗓子不会哭哑，这是因为他元气醇和。知道醇和、平和就是了解了道的规律、规则，了解这个事物规律、规则的人才是明智，让我们的生命有益才是一个吉祥，纵心任气，是强暴、强蛮的表现。事物太强盛了就会走向衰老，（追求过分强盛）这叫做不合于道，不合于道便会早早灭亡。</t>
   </si>
   <si>
     <t>这章开头讲了一个非常有意思的概念，就是“赤子”，这是因为婴儿刚出生的时候浑身是红色的，但这个词更重要的作用是比喻心地的纯净、纯洁。“含德之厚，比于赤子。”按照道的标准来衡量，赤子心地纯净，无恃无为。这是含德浑厚的一种表现。其实，不只老子，孔子也对婴儿的状态充满了景仰，认为这是一种有道的含德之厚的表现。孟子也说，“大人者不失其赤子心”。老子更是把婴儿作为一个范本与榜样，第十章就说“专气致柔，能如婴儿乎？”人精神集中，气息平和，那不就是像婴儿的样子吗？下边这些都是从经验的角度来讲获得的感受。小孩的他精神状态很安稳，蜂子、毒虫、蛇也不蜇他，也不咬他，为什么呢？因为小孩没有危险，没有对这些动物造成威胁的举动。其实有时候蜂子落到我们脸上，也许只是为了得一滴汗液，没有汗液，它采的蜜也不能凝固，可是我们一打它，它当作危险的时候，就要用它的毒针来蜇我们。很多动物也是这样，人没有危险动作的时候，其实也不会攻击人，但人见到它就害怕，就有一种防范甚至攻击性的动作，这也是难免的。老子说你看，这婴儿啊，“毒虫不螫”，毒虫不蜇他。“猛兽不据”，虎啊、狼啊这些猛兽，也不把它叼走，不用爪子把他抓走。我们经常会听到这样的一些事，很多动物还喂养、抚育这些落在田野里边的荒野上的小孩，当然这也不是全部的情况，我估计老子也是拿这个做一个说明而已。“攫鸟不搏”，攫，攫取。有的时候，人手上拿着一个什么东西，比如说拿着肉，在一些荒远的地方，老鹰就飞下来把这肉抢走了，但是对小孩它却不这样做，除非是尸体。“骨弱筋柔而握固”，这小孩其实身体是最柔软的，但是你看他这小拳头却握得很紧固。这人生啊，深究起来是有点意思。小孩刚出生的时候，都是握着拳头，似乎想抓住点什么，但人最后离开这个世界的时候，却是放手了，知道什么也抓不住。“未知牝牡之合而全作”，“牝牡”本来指的是雄性和雌性的动物，但是这个地方指的是男女。小孩刚出生不知道什么男女的事情，但是你看他的小生殖器却非常坚挺。老子用这样的一个方式来做形容，说婴儿精气很纯、很多、很壮，“精之至也”，达到了一个最好的状态，老子是这样认为。下边这个描述确实挺有意思，叫“终日号而不嗄”，小孩终日啼哭，但是嗓子却不哑，那不是精气足的表现吗？我现在讲课，讲一段时间喉咙就哑了，我们现在为什么会这样？老子可能认为，这人长大了，欲望多了，精气耗费得多了，所以就不像小孩那样精气充足。这一段把婴儿作为一个得道者的良好状态的表现讲完了，下边老子该阐述自己的观点了。“知和曰常”，“常”就是规律、规则。了解了这个“和”，通过婴儿引出来的“和之至”，谁能够像婴儿一样，让我们气息平和，让我们的欲望平和，不那么欲壑难填，就了解大道的规律、规则。“知常曰明”，了解这个事物规律、规则的人，那才是明智。“益生曰祥”，让我们的生命有益，这个才是一个吉祥的表现。这是正面，那负面呢？“心使气曰强”，老是盛气凌人，体现的是这种强横、强暴，这个是道家所反对的。气息不平和，纵心任气、任性，这个是强暴、强蛮的表现。在前面第二十三章讲过，“飘风不终朝，骤雨不终日，孰为此者？天地。天地尚不能久，而况于人乎？”暴风骤雨它不会持久，天地的使强也不过只是持续一阵子，它告诉我们这个道理，强不能持久。“心使气曰强”，这不是一种好现象。“物壮则老”，事物发展到顶峰的时候，就开始走下坡路了，人到了壮年之后，就逐渐向衰老的方向发展了。“谓之不道”，这已经使气，老是以强壮来作为目标、作为处理问题的方式，这是不符合大道的。“不道早已”，既然不符合大道，那这个事情就不能持久，很快就会结束了。你看这婴儿的状态，其实应该能存活得更长久、寿命更长，为什么后来很多人变得短寿了呢？那就是让自己脱离了大道，没有像婴儿那样，“精之至”，“和之至”。所以人应该“知和，知常，益生”，而不应该使气，不应该“物壮”，如日中天的时候就走下坡路了。人生最美的境界是什么？花未全开月未圆。所以，按照大道的方式来处事、认知事物，这样我们才能够明，才能够益，否则的话就会“不道早已”。</t>
@@ -795,7 +797,7 @@
     <t>知者不言，言者不知。塞其兑，闭其门，挫其锐，解其分，和其光，同其尘，是谓玄同。故不可得而亲，不可得而疏；不可得而利，不可得而害；不可得而贵，不可得而贱，故为天下贵。</t>
   </si>
   <si>
-    <t>有智慧的人不多言，多说话的人不是有智慧的。塞上欲望的孔穴，闭上欲望的门户，收敛锋芒，解除纷扰，在光明之处便与光融合，在尘垢之处便与尘垢同一，这就叫“玄同”。这样就没有了亲疏之别、利害之分、贵贱之差。所以为天下所尊贵。</t>
+    <t>有智慧（懂得大道）的人不多言，多说话的人不是有智慧的。圣人塞上欲望的孔穴，闭上欲望的门户，收敛锋芒，解除纷扰，在光明之处便与光融合，在尘垢之处便与尘垢同一，这就叫“玄同”。所以既不可能与这样的圣人亲近，也不可能与他们疏远；既不可能使他们得利，也不可能使他们受害；既不可能使他们尊贵，也不可能使他们卑贱。所以他们被天下人所尊崇。</t>
   </si>
   <si>
     <t>这一章还是比较容易理解的。“知者不言，言者不知。”开头的第一句话就讲，有智慧的人是不多言的，所谓“行不言之教”，还有“悠兮其贵言”，都在讲这个道理，有智慧的人是不会多嘴多舌的，不会去乱说的。“知者不言，言者不知”，老是认为自己无所不知、以为自己有智慧的人，其实是不具备真正的智慧的。“塞其兑，闭其门。”我们前边解释过，“兑”指的就是耳、目、鼻、舌这些感官，所以它强调的是感性对事物的认识，是不可信的。“塞其兑，闭其门”，这样才能对事物本质的根本的内容有真正的理解。下面讲处理问题的方式方法，做人的思想与智慧，要“挫其锐，解其分，和其光，同其尘”，不要锋芒外露，这样才能长久。要解除那些纷纷扰扰，不要让纷纷扰扰在心里打成结——心有千千结。真正了解道的含义的人，按照道去做事的人，是很容易摆脱这些纷纷扰扰的。“和光同尘”，也就是讲同流而不合污，所谓外圆而内方，所谓与世推移。那么这个叫什么呢？就叫做“玄同”。“玄”本来是天的颜色，意味着深远，这样的同是深远的、深刻的，同流而不合污，当然里边就非常有玄妙了。下面的内容讲得也非常清楚，就是说道并不是为人谋利益的，得道的人他怎么样来和万事万物打交道呢？就像道一样，“不可得而亲，不可得而疏”，道并不是对谁更亲近，或者对谁更疏远。有亲就必有疏，有疏就必有亲，这个就不平等了，这就不“玄同”了。所以，按照道的、“玄同”的方式来做，没有亲疏之别，无差别。“不可得而利，不可得而害”，有利必有害，有害也必有利。所以你并不能凭借道而获利，也不能用这个道来危害别人，无差别，无利无害。“不可得而贵，不可得而贱”，道对谁也没有贵贱之分，还是依然玄同、平等，一旦有贵贱之别，便也就丧失了道的本质的属性。所以庄子讲，“以物观之，自贵而相贱。以俗观之，贵贱不在己。”从物的角度来看，都认为自己是珍贵的、宝贵的，其他的东西比不上自己的尊贵。用世俗的观点来看，贵和贱不在于自己，而在于别人的评价，在于外在的标准。而“以道观之，物无贵贱”，从道的角度来看，这万事万物并没有什么贵贱之分，所谓公正、平等、无差别、无贵贱之分。正是因为这样，所以它成为天下最尊贵的，“故为天下贵”。所以这章的内容啊，道表现为玄同，按照这样的深远的玄同的道理来理解事物，就是从道的角度来观察问题。道没有亲疏之别，没有利害之分，没有贵贱之差，所以用这样的一个角度来观察世界，这个才使它成为天下最令人敬重尊仰的，“故为天下贵”。</t>

--- a/book.xlsx
+++ b/book.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13668" windowHeight="12000"/>
+    <workbookView windowWidth="25068" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -809,7 +809,7 @@
     <t>以正治国，以奇用兵，以无事取天下。吾何以知其然哉？以此。天下多忌讳，而民弥贫；民多利器，国家滋昏；人多伎巧，奇物滋起；法令滋彰，盗贼多有。故圣人云：我无为而民自化，我好静而民自正，我无事而民自富，我无欲而民自朴。</t>
   </si>
   <si>
-    <t>以清静无为之正道治国，以奇巧诡计用兵，以不多事滋扰来取得天下。我怎么知道是这样呢？因为上述。天下的忌讳太多，人民就越来越贫穷；百姓拥有很多锋利武器，国家就会越来越混乱；人民拥有很多奇技淫巧，奇怪甚至邪恶之事就会越来越多；法律条文越严苛，盗贼反而会越来越多。所以圣人说：我无为，人民便自我化育成长；我喜好清静，人民就会自己走上正道；我不多事不扰民，人民自己就会富起来；我没有私欲，人民自然就会淳朴。</t>
+    <t>以清静无为之正道治国，以奇巧诡计用兵，以不多事滋扰来取得天下。我怎么知道是这样呢？因为如下情况：天下的忌讳（禁令）太多，人民就越来越贫穷；百姓拥有很多锋利武器，国家就会越来越混乱；人民拥有很多奇技淫巧，奇怪甚至邪恶之事就会越来越多；法律条文越严苛，盗贼反而会越来越多。所以圣人说：我无为（不去人为干涉），人民便自我化育成长；我做到内心清静，人民就会自己走上正道（品行端正）；我不多事不扰民，人民自己就会富起来；我没有私欲，人民自然就会淳朴。</t>
   </si>
   <si>
     <t>第五十七章的这段话非常有智慧，因为这段话一开始就指出来了，事物之间的不同，有本质的区别，所以处理问题、解决问题的方式方法也不一样。“以正治国，以奇用兵”，治国讲究的是堂堂正道。道家讲的“正”当然就是清静无为，不多事，不扰民，这就是道家讲的正道，是治国的大道理。可是用兵讲究的是“以奇用兵”，“兵者诡道也”，兵不厌诈。所以不能把用兵的方式、战争的方式用到治国的上面来，这两者不同，解决的方式也不一样。“以无事取天下”，无事就是不多事、不扰民、不刁难，这样才能够得到天下，并且坐得了江山。道家“无事”是“无为”的一个重要的方面，不多事、不扰民、不刁难，而“有为”讲的是妄为，多事、扰民、刁难，我们在前边这一点已经非常明确了。“吾何以知其然哉”，我怎么知道是这个样子呢？所谓“以此”就是依据上边“以正治国，以奇用兵”它们之间的本质不一样，所以解决的方式方法也不同而得出的结论。下面，老子开始谈他对治理天下的重要的看法。违背了大道，违背了道家的以“清静无为”为根本来治理国家的方式，会出现什么问题呢？“天下多忌讳，而民弥贫”，治理天下、领导国家忌讳太多，这个也不能动，那个也不能动，这个人的职务比较高，法令涉及不到他，当然出现了忌讳，不敢动，这个地方一定会形成一个空场，形成一个腐败的群体。百姓当然越来越穷了，财富都集中在少数人的手上。“民多利器，国家滋昏”，“滋”就是越来越。如果民间利器众多，武器众多，民与民之间械斗、抗法，那国家当然越来越混乱。“人多伎巧，奇物滋起”，“伎巧”就是各种各样的奇技淫巧，越来越多，大家对这些越来越感兴趣，这个技巧能够给他们带来利益，那么各种各样的奇奇怪怪的东西，甚至包括那些妖孽的东西，就不断兴起。“法令滋彰，盗贼多有”，既然这样，要用法律来管，法条定得越来越多，越来越严苛，反而盗贼越来越多。在前面这一段讲完之后，《道德经》说“故圣人云”，很明显，这是引用以往的通达事理的王们的话，老子用自己心中有智慧的人的语言来作为结尾。“我无为而民自化”，道家讲的无为，第一，“不妄为”。第十六章里边说“不知常，妄作，凶”，不了解事物的规律、规则，瞎折腾、胡折腾，这个结果是非常糟糕的。第二是“不多为”。抓住关键，举重若轻，多言数穷，不如守中，适可而止，恰到好处。第三讲究的是“有所不为”。人要想有所为，必须有所不为。一个政府也罢，一个领导者也罢，所有的事情都抓在自己手上，那底下的人怎么得到锻炼呢？不把担子压给他，他怎么练出独当一面的能力呢？什么事都控制在自己手上，那众人怎么样自我化育自我成长呢？所以无为才能让国家的人民、才能让自己的属下自我化育自我成长。事情成了应该怎么样呢？第十七章“功成事遂，百姓皆谓‘我自然’”，事情做成了，百姓都说这是我们的努力把这事情做成的，这就叫“民自化”。“我好静而民自正”，前面我们讲过，道家讲的静，内心的清净，静下来才能找到解决事物的正确的方法。我清静，走正道，不那么浮躁、急躁、暴躁、狂躁，做一个好的表率，上梁而正，百姓当然也就正了，百姓当然也就好静而走正道了。“我无事而民自富”，不多事、不扰民、不刁难，那百姓自然就富起来了。“我无欲而民自朴”，“朴”就是原木，《道德经》里用原木喻指做事敦厚、朴实、厚道，没那么多欲望，不是老想抢夺别人、占有别人的。就像黄宗羲在《明夷待访录》里边讲的，古代的那些皇帝都是什么样的？“离散天下人之儿女，荼毒天下人之肝脑，以供一人之淫乐。”这是我的，普天之下都是我的。所以欲望无止境，你让百姓能够朴实厚道，这也不可能。所以不要欲壑难填，不要什么东西都看作是自己的，可以任意掠夺，这样百姓自然就朴实、厚道，民心淳朴。这里边的两句话，我们国家的领导者讲话的时候也经常引用：“我无为而民自化，我无事而民自富。”所以，第五十七章讲了两个重要的道理，第一个不能把打仗的这一套用到治国之上。治国讲究的是堂堂大道，讲究的是清静无为，所以以无事取天下。第二个就讲站在领导者的角度，站在统治者的角度，应该怎么做呢？无为、好静、无事、无欲，这样自然一切顺理成章，百姓就会自化、自正、自富、自朴，事成了也会“功遂身退，百姓皆谓我自然”。这是一个好的领导者、好的政府做事的道理之所在，反之越多事儿，越是用那种严苛的法令，导致的结果适得其反。忌讳多了，百姓就越来越穷，民间的利器多了，国家就越来越混乱，大家都倾向于奇技淫巧，把这个当作一种喜欢的甚至不停地去追求的目标，那这个国家就越来越怪，各种奇葩的事情都纷至沓来。越觉得法令不够，越制定得严格、细致，以为单靠着法令就可以解决所有问题，反而适得其反，盗贼多有。所以，这一章里边讲的，也是我们经常说的——这本书的总纲：“反者，道之动”。我们考虑问题，不要只考虑它一面，要相反相成，用一个更高的观察事物的角度来理解。</t>
@@ -821,7 +821,7 @@
     <t>其政闷闷，其民淳淳；其政察察，其民缺缺。祸兮福之所倚，福兮祸之所伏。孰知其极？其无正。正复为奇，善复为妖。人之迷，其日固久。是以圣人方而不割，廉而不刿（guì），直而不肆，光而不耀。</t>
   </si>
   <si>
-    <t>（治国者）为政宽容，人民就会淳厚；为政苛察，人民就会因感觉不足而欺上。祸啊，福倚靠着它；福啊，祸就藏伏其中。谁知它们的极点在哪呢？没有确定的标准。正转变为邪，善转变为恶。人们的迷惑，已经有很长的时间了。所以圣人方正而不割伤别人，有棱角但不刺伤别人，直率但不会放肆，有光芒但内敛，不刺眼炫耀。</t>
+    <t>（治国者）为政宽容，人民就会淳朴善良；为政苛察，人民就会变得狡猾奸诈。灾祸啊，幸福就依靠在它的旁边；幸福啊，灾祸就埋伏在它的里面。谁能知道最终的结果是祸是福呢？没有确定的标准（永恒正确的事情）。正确会变为邪恶，善良会化作妖孽。人们不懂得这一道理，已经有很长的时间了。因此圣人方方正正却不去为难别人，有棱角但不去伤害别人，自己坚持正直品德却不强迫人去做，有光芒但内敛，不刺眼炫耀。</t>
   </si>
   <si>
     <t>第五十八章有两个我们非常熟悉的成语，一个叫“祸福相依”，一个叫“光而不耀”，也是这一章核心的内容。祸福相依，福和祸是相互转化的，两者也是相辅相成的，分不开的。“光而不耀”在讲什么呢？我们大家看到过月亮，月光是明亮的，在黑暗中给我们指引以方向；同时月光也是不张扬的、不炫耀的、不刺眼的。中国人喜欢拿月亮来比喻君子的形象，做君子得先有光，但是不管我们有什么，都不要老想着去张扬、炫耀，让别人感觉到刺眼。所以《道德经》很多章节，都向我们揭示了这样一个道理：有才华、有知识、有道德的人，不要老想着去张扬、炫耀。以这两个成语为切入点，我们会对这一章的内容有个直观的感觉。我们来逐字逐句地解释一下。“其政闷闷”，“闷”就是淳厚。就说政治比较淳厚宽容，那么这个国家的百姓也就是敦朴淳厚，不耍心眼。“其政察察，其民缺缺”，假如这个政治非常苛察，对一切都监控得到位，那老百姓就会感觉到有很多的缺陷与不足，就要耍心眼。所谓上有政策，下有对策，也就失去了原本的淳朴。“祸兮福之所倚，福兮祸之所伏。”福和祸是相辅相成的，在一定条件下是相互转化的。民间的很多说法，大家都能够体会到这意思的延伸和运用，比如，我们经常说“大难不死必有后福”、“好事多磨”……福和祸是相伴而行的，有时候我们认为是福的事情，它可以转化为祸，反过来也是一样，所以这就叫“祸福相依”。怎么样来理解这个事情呢？给大家举个例子，大家就清楚了。其实各民族的智慧到达高点的时候，往往是相互重合的，印度有一本佛经叫《大般涅槃经》，在这里面讲了这样一个故事。有一天早晨，一家主人一开门，门口站着一个衣着光鲜、非常漂亮的女子，主人就问你是谁，女子说我是“功德大天”，我到谁家谁家就一切兴旺。主人高兴地请进来，焚香供拜。刚一关门又有人敲门，开门一看，门口站着一个衣衫褴褛，非常丑陋的、黑瘦的女子，主人就没好气了，主人就问你是谁呀，那女子说我是“黑暗”，我到谁家，谁家就一切破败！主人当然不让她进来，拿着刀驱赶。结果这女孩说你太笨了，刚进去的是我姐姐，我们俩从出生这天起就没有分开过，你把我赶走了，她也留不下。主人不信，进去一问果然是这样。福跟祸是相伴而行的，所以它就提醒我们，遇到福事的时候就要小心谨慎，避免乐极生悲；遇到祸事的时候，也不要感觉到沮丧，因为我们对灾祸有所警惕，它可以避免后面更大的灾难。韩非子讲过“千里之堤，溃于蚁穴”，我们发现了这个蚂蚁窝，知道它是一个祸患，很早的把它堵上，那就避免了以后更大祸事的发生。这就是“祸福相依”的道理，在我们文化中影响是非常深刻的。讲完这一段后，《道德经》就说“孰知其极？”这个事物到达极点的时候，向它相反的方面转化，所谓两极相通，所谓物极必反，但是这个极在哪里呢？这个是需要我们认真去体会把握的。“其无正”，其实并没有确定的标准，所以并没有说我们到了一个什么程度，一定会向它相反的方面转化，这是要根据不同的时间、地点、条件，需要我们认真去领会把握的、体悟的一种智慧。“正复为奇，善复为妖。”“正”，你把它弄到极点它就偏了，“善”到达极点的时候，它就转化为它相反的方面。有些人老想寻找一个固定的标准，《道德经》就说：“人之迷，其日固久。”在这个方面的迷惑，时间已经由来已久。所以我们总是要寻找一个固定的标准，总是觉得做事情有一个固定的程序，固定的套路，这个就不圆融。下面就讲，“是以圣人方而不割”，“方”就是方正，“割”就是生硬。有原则但是不生硬，人要懂得去碰硬，但是不要去硬碰。方正而不生硬，这样才能圆融，我们把它叫做“外圆而内方”。“廉而不刿”，“廉”就是棱角，“刿”就是锐利。有棱角但是不要老用锐利之处去刺伤人。“直而不肆”，有人经常就说，我说这话你别在意，我这人很直。其实有的时候不是直而是自私，是放肆、过分。所以我们说直率，它是一种心态，但是你讲话的方式得懂得圆融，直率而不放肆。“光而不耀”，有光芒，但是不要老去张扬、炫耀，让别人感觉到刺眼。咱们中国人喜欢讲君子，什么样的人是君子呢？中国人除了用月亮来代表君子“光而不耀”的特点之外，另外，也喜欢用玉来代表君子的形象，所谓“谦谦君子，温润如玉”。“谦谦君子”出自《易经·谦卦》，原话叫“谦谦君子，用涉大川”，一个人保持这种内敛的、谦逊的风度，这样才能走好人生长远的坎坷的道路。另外一个是出自《诗经》的“温润如玉”，谁都知道闪着贼光的肯定不是什么好玉，真正的好玉都是光芒内敛，给人一种温润感。我认为“光而不耀”是中国文化里，对君子形象用得最好的一个比喻。我们有知识，不要老想着去张扬、炫耀，大家聚到一块的时候，一个人老去炫耀自己的知识，对别人的说法都嗤之以鼻，认为自己什么都懂，百事通，时间长了，大家就不喜欢跟这人打交道了。有道德，道德是约束我们内心的，不是老是向别人去张扬炫耀。《道德经》第三十八章开头这句话，大家都知道——“上德不德”，最有道德的人从来不去张扬、炫耀自己的道德。当然，至于炫官、炫富，这不仅不是一种君子的形象，还会给自己惹来无尽的祸殃。是否还记得第九章里“金玉满堂，莫之能守；富贵而骄，自遗其咎”，炫富炫贵，会给自己惹来无尽的祸殃。在第二章里“功成而弗居”，哪怕我们有功劳，不管是对家庭、对单位、对国家有功劳，也不要老想着去张扬、炫耀，越是不张扬、不炫耀，这个才能在人心里长久地存在。第九章里面也说“功遂身退，天之道”，这是符合自然的道理。第五十八章讲完之后，我再做一下梳理和强调。这一章有两点需要注意，一个是“祸福相依”的道理，一个是“光而不耀”的形象，怎么样能做到这一点？我们要明白“物极必反，两极相通”。了解这样的智慧与道理，我们做事情才能够圆融。所以一个有智慧的人，有智慧的领导者，为人处事应该方正而不生硬，要圆融，有棱角，但不要老去割伤人，要懂得委婉迂回地处理问题的方式。直率，但又不越界进入到了放肆、无所顾忌的程度，光芒内敛而不要老去张扬、炫耀，要给人留下一种谦谦君子、温润如玉的形象。这是我们和别人、和这个社会打交道的一个重要的思想与智慧。</t>
@@ -830,10 +830,10 @@
     <t>第五十九章</t>
   </si>
   <si>
-    <t>治人事天莫若啬。夫唯啬，是谓早服，早服谓之重积德。重积德则无不克，无不克则莫知其极。莫知其极，可以有国。有国之母，可以长久。是谓深根固柢（dǐ），长生久视之道。</t>
-  </si>
-  <si>
-    <t>治理人民要顺应天理，莫过于节俭节制。只有节俭节制，才能早得道。早得道就是不断地积德。不断地积德就没有什么是克服不了的，没有什么克服不了就不知道它的力量有多强大。不知道其力量有多强大，就可以掌管国家。掌握了治国的根本，就可以长久存在。这是可以把根本扎深、扎牢固，长久存在的道。</t>
+    <t>治人事天莫若啬（sè）。夫唯啬，是谓早服，早服谓之重积德。重积德则无不克，无不克则莫知其极。莫知其极，可以有国。有国之母，可以长久。是谓深根固柢（dǐ），长生久视之道。</t>
+  </si>
+  <si>
+    <t>治理人民要顺应天理，最好的办法莫过于节俭节制。只有节俭节制，才能早得道。早得道就是不断地积德修养自己。不断地积德就没有什么是克服不了的，没有什么克服不了就不知道它的力量有多强大。不知道其力量有多强大，（有了无可估量的力量）就可以掌管国家。掌握了治国的根本，就可以长久存在。这就是根本扎深、扎牢固，永世长存的办法。</t>
   </si>
   <si>
     <t>这一章讲了两种生活的态度：一种是做“加法”，不断地叠加，不断地累积，有了还想更有，多了还想更多；另外一种是要懂得做减法，要节俭节制，有的时候我们的欲望减少一分，其实我们的幸福也就多一分。这两种人生态度也是相辅相成的，可是大家更注重的是第一种，所以一章就强调我们这种做减法的态度的重要性。其实这一章核心就讲四个字：节俭节制，讲节俭节制对一个国家、对社会的重要意义。“治人事天莫若啬。”一开始就讲“治人事天”，领导这个国家的人民要顺应天理。“莫若啬”，什么事情最顺应天理呢？节俭节制。我们现在用的这个词叫“吝啬”，这个词有点负面的含义，在《道德经》中这个“啬”，我们把它译成节俭节制，这样更符合于我们的接受习惯。“夫唯啬，是谓早服”，“夫唯”是个语气助词，“啬”是节俭节制。“是谓早服”，“早服”就是早得道。懂得节俭节制的道理，就是可以早得道的人。“早服谓之重积德”，“重”就是不断。懂得节俭节制就是在不断地积累自己的品德，积累自己的德行。因为我们说《道德经》道和德要分开理解，按照道去做，就是有德，不断地按照道去做，就是不断地积德。重积德就是不断地积德，所以你看“早服谓之重积德”，早得道，一直坚定地坚持按照这个去做，就是不断地积累自己的德性，积累自己的品德，积德。我们就像一条船，我们积的德就像水，水积累得越多，我们船才能自由地航行，不管你船多大，如果没有水，在那儿搁浅，它也发挥不了船的这种作用。“重积德则无不克”，“克”就是克服，按照这个“啬”的方式，也就是节俭节制的方式去做事情，那就没有什么困难克服不了的。因为在节俭节制里边磨练的就是人的思想品德，磨练的就是人的意志，磨练的就是人面对困难无所畏惧的态度。“无不克则莫知其极”，你说这个东西力量这么强大，没有什么东西它克服不了，所以它的力量“莫知其极”，你不知道它的力量有多么强大，对一个人是这样，对一个国家更是如此。“莫知其极，可以有国。”你看这话是给谁讲的？给统治者、领导者讲的。一个领导者领导团队，领导这个国家的人民培养出一种节俭节制之风，你这样才能让你的国家长久地存在，长久地发展。毛泽东主席在中华人民共和国成立的时候就指出，“贪污和浪费是极大的犯罪”，自己也以身作则。你领导团队，领导全国人民培养出一种节俭节制之风，这样面临什么样的困难的时候，大家都有信心去克服。“有国之母，可以长久。”“母”就是根本。节俭节制是立国，是国家长久发展的根本。我们现在叫“八项规定”“反四风”，领导国家的人民培养出节俭节制之风，国家才能长久持续地发展。有一件事儿大家都知道，电视经常打出一个公益广告，说现在每年中国人浪费的粮食就是世界上两亿人的口粮。你说世界上现在每天都有人在饿死，可我们中国人这么浪费，能符合天道，能符合天理吗？如果因为这种浪费有什么惩罚落到我们头上，那么我们也无话可讲。你从这一章里面就可以感觉到，一个人浪费，糟蹋的是自己的福分；一个国家浪费，糟蹋的是国家的福分，对国家的根本有所损伤。“是谓深根固柢，长生久视之道。”国家培养出节俭节制之风，才能长久发展，这样做叫什么？叫“深根固柢”。我们讲叫根深蒂固，你让这个根本、让根扎得深，扎得稳固，深根固柢。“长生久视之道”，于人来讲是如此，可以让我们的生命更为长久，因为一个人的节制节俭，不去放纵自己的欲望，这也是一种养生之道。得以长久地存在，长久地发展，得以长寿，对国家来讲也是如此。所以“长生久视”，长久地存在，大家能够长久地看到它。《道德经》强调“做减法”的这个方面，在世界哲学界，有着非常重要的影响。我们中国人有一个优良的文化传统，讲勤俭持家，讲勤俭治国，所以这个是我们文化中非常重要的方面，但是很少在哪一本著作里面把它强调到这样的一个高度。“治人事天莫若啬。夫唯啬，是谓早服。”这就是早得道，坚定地按照这个道去做，就叫积德。不断地积德，那就使我们能够根深蒂固，长久存在，长久发展。人如此，国家亦如此，道理是相同的。第五十九章，希望大家认真地品味体会老先生给我们讲的“根深蒂固”的道理。</t>
@@ -842,10 +842,10 @@
     <t>第六十章</t>
   </si>
   <si>
-    <t>治大国若烹小鲜。以道莅天下，其鬼不神。非其鬼不神，其神不伤人；非其神不伤人，圣人亦不伤人。夫两不相伤，故德交归焉。</t>
-  </si>
-  <si>
-    <t>治理大国就像烹调小鱼一样。用道来领导、指引天下，鬼也就没有神秘莫测的力量。不是说鬼不神秘莫测了，是它的神秘莫测伤害不了得道的人。不但鬼的神秘力量伤不了人，圣人也不伤害人。鬼和圣人都不伤人，所以德不断地积累交汇，形成有道有德的世界。</t>
+    <t>治大国若烹（pēng）小鲜。以道莅天下，其鬼不神。非其鬼不神，其神不伤人；非其神不伤人，圣人亦不伤人。夫两不相伤，故德交归焉。</t>
+  </si>
+  <si>
+    <t>治理大国就像烹调小鱼一样（不要经常折腾它）。（君主如果能够）用道来领导、指引天下，鬼也就没有神秘莫测的力量。不是说鬼不神秘莫测了，而是它的神秘莫测伤害不了得道的人。不但鬼的神秘力量伤不了民众，圣人也不伤害民众。鬼和圣人都不伤害民众，所以德不断地积累交汇，形成有道有德的世界（恩德都将施与民众）。</t>
   </si>
   <si>
     <t>这一章有一句话，大家都非常熟，叫“治大国若烹小鲜”，这句话也是这一章的核心。一九八七年，美国前总统里根在发表国情咨文的时候也引过这句话。二〇一三年，“金砖各国”开会，在一个联合的采访中，有一位巴西记者问过习近平这样的一个问题：你担任这么大的一个国家的这么重要的职位是一种什么心态？你用什么样的态度来对待自己的职位？习近平答记者问，先引的是《诗经》，来回答第一个问题：“战战兢兢，如临深渊，如履薄冰。”这话出自《诗经·小雅·小旻》。治理国家要小心谨慎，就像行走在结着薄冰的冰面上一样，就像站在悬崖边一样，要小心谨慎，因为稍不谨慎就会出大的问题、大的危险。然后引用这句话来回答第二个问题，我要以“治大国若烹小鲜”的态度来对待我的职位。“治大国若烹小鲜”是什么意思呢？大家如果上网去搜对这句话的解释，类型就有二十多种，每一种解释都不一样，有的甚至把它直接翻译为“治理一个大的国家就像烹一碟小菜那么简单”，这是完全没有理解这句话的真正的含义。“小鲜”就是小鱼儿，鱼肉很细很嫩，拿它的时候就得小心谨慎，尤其是在高温里烹炒它的时候，都要小心谨慎，要有耐心。火候不到的时候你老折腾，甚至锅铲飞舞，翻腾，鱼不就成了碎片了吗？汉朝的毛亨，喜欢《诗经》的人都知道，这个人写过《毛诗传》的，他就用两句话来解读这句话，其实最符合它的本意。第一句话叫“烹鱼烦则碎”，环节太多老折腾它，那鱼就成了碎片了。第二句话“治民烦则乱”，治理一个国家也是一样，讲究的是制度的稳定，不能今天一个制度，明天一个制度，朝令夕改；你不能今天一个运动，明天一个运动来回折腾，国家不就被折腾散架了嘛。“治大国若烹小鲜”和“战战兢兢，如履薄冰”的道理是相同的，讲究的是小心谨慎，有耐心，掌握火候。“以道莅天下，其鬼不神。”“莅”就是莅临。用道来领导天下，指引天下。大家注意，这个“神”字很多的理解有问题，其实并不是神鬼的神，不是说我们后来的人格神、神化了的神。这个“神”在《易传》里面的解释是非常明确的，“阴阳之不测之谓神”，也就是神秘莫测。用道来领导天下、指引天下，鬼也没有什么神秘莫测的力量，因为你走的是正道，你走的是堂堂大道，鬼也没有办法去伤害到你，所以“以道莅天下，其鬼不神”。《道德经》里用它的道，把大家所恐惧的鬼的位置给取代了，你堂堂大道，鬼也近不了你的身，“其鬼不神；非其鬼不神”，不是鬼不神秘莫测，是因为你走大道，它的神秘、莫测、玄妙、诡秘已经没有办法伤害到你。所以把下一句话作为上一句话“其鬼不神”的注解，就很容易理解了。“非其鬼不神”，不是说这鬼不神秘莫测了，神秘莫测是它的本性。“其神不伤人”，但是它的神秘莫测已经伤害不了这种走在大道上的人、得道的人。“非其神不伤人，圣人亦不伤人”，不单是指鬼的力量伤害不了人了，反过来说，圣人他智慧高，但圣人智慧高也得返璞归真。圣人不会因为自己的智慧高，心眼多套路深，就使用这种“技巧”，这个东西不是正道。所以，鬼的神秘莫测伤不了人，圣人的智慧在领导大家的时候也会“善利万物而不争”，对人民没有伤害，“夫两不相伤”，你看鬼的神秘莫测也伤不了人，圣人领导也伤不了人。“夫两不相伤，故德交归焉。”所以有德的事情，积德的事情，两者交汇到一起，两不相伤。因为你按照道来做事情的话，鬼伤不了你，圣人也是按照道来做的，彼此也不相伤。这样大家就走在正确的道上，按照道去做，不断地积德，所以叫“德交归焉”，交汇，归到一块。“治大国若烹小鲜。以道莅天下，其鬼不神。非其鬼不神，其神不伤人；非其神不伤人，圣人亦不伤人。”如果这样两不相伤的，那就是“德交归焉”，这样就形成了一个和谐的、有道的、有德的世界。</t>

--- a/book.xlsx
+++ b/book.xlsx
@@ -47,7 +47,7 @@
     <t>type</t>
   </si>
   <si>
-    <t>总述</t>
+    <t>序章</t>
   </si>
   <si>
     <t>学习道德经之前，先了解《道德经》的背景（其人，其书，其道）
@@ -854,10 +854,10 @@
     <t>第六十一章</t>
   </si>
   <si>
-    <t>大国者下流。天下之交，天下之牝。牝常以静胜牡，以静为下。故大国以下小国，则取小国；小国以下大国，则取大国。故或下以取，或下而取。大国不过欲兼畜人，小国不过欲入事人。夫两者各得其所欲，大者宜为下。</t>
-  </si>
-  <si>
-    <t>大国要善于处下，就像处在江河的下游。处在天下交汇的地方，处在天下最雌柔的地方。雌性常以柔静胜过雄性，是因为柔静又善于处下。所以大国以谦下的态度对待小国，就可以争取到小国的支持；小国以谦下的态度对待大国，就可以得到大国的庇护。所以有的“取”是从上面抓取，有的“取”是从下面托起。大国所希望的不过是得到小国的支持，小国所希望的不过是得到大国的庇护。大国小国都达成了各自的愿望，越是大国越要懂得善于处下。</t>
+    <t>大国者下流。天下之交，天下之牝（pìn）。牝常以静胜牡，以静为下。故大国以下小国，则取小国；小国以下大国，则取大国。故或下以取，或下而取。大国不过欲兼畜人，小国不过欲入事人。夫两者各得其所欲，大者宜为下。</t>
+  </si>
+  <si>
+    <t>大国要像大海一样居于百川的下游，就像处在江河的下游。处在天下交汇的地方，处在天下最雌柔的地方。雌性常以柔静胜过雄性，是因为柔静的性格是一种谦下的表现。所以大国以谦下的态度对待小国，就可以争取到小国的支持；小国以谦下的态度对待大国，就可以得到大国的庇护。因此有的谦下能够取得别人的拥戴，有的谦下能够取得别人的庇护。大国所希望的不过是得到小国的支持，小国所希望的不过是得到大国的庇护。大国小国都达成了各自的愿望，越是大国越要懂得善于处下（谦下）。</t>
   </si>
   <si>
     <t>《道德经》从头至尾有一个非常重要的智慧与理念：善于处下。在第八章里面就说，“处众人之所恶，故几于道”，水去的是又低又脏的地方，把那里的污浊洗净，在那个地方滋润万物，跟道最接近的。做人要做“上善若水”的人，才能称其为“大人”，这个“大”代表的是品德。国家要成为一个大的国家，该怎么样做呢？它的处事的态度是什么呢？第六十一章里边开头这句话说得简要、明确、深刻：“大国者下流。”所以，这一章的核心我们看一下，开头“大国者下流”；结尾“大者宜为下”。越是大的国家越懂得善于处下，和小的国家打交道的时候谦逊谦和，和谐相处，你就把小的国家争取了。人也如此，位置越高，越要善于处下，这样才能真正居上。这是这一章的开头、结尾，也是这一章的核心。我们在解读“大国者下流”之前，我们需要采用以经解经的方式，拿第六十六章开头这句话，用这个形象先来让大家直观地感知一下，这个直观的形象我们了解了，再来看这一章就容易了。第六十六章开头这句话：“江海所以能为百谷王者，以其善下之，故能为百谷王。”大江大海为什么能成其大呢？它地势低，善于处下，其他的水系就都汇到它这来了，用我们习惯的话讲，就叫“善于团结一切可以团结的力量”。不辞细流，所以成为大江大海。然后我们再来看第六十一章开头这个五个字就很容易理解了。“大国者下流。”所谓“下流”，就是善于处下、处在水的下游，最好是处在大海的入海口，涓涓细流慢慢地汇成大江大海。那么善于处下《道德经》拿什么来比喻它呢？这个地方是什么？是天下的水交汇的地方，所以叫“天下之交”。拿什么来比喻“天下之交”的呢？《道德经》把它叫“天下之牝”，“牝”代表母性、女性，本来这个“牝”是指母性的生殖部分。因为在《道德经》里边母性、女性代表着慈，代表着柔，代表着静，“牝常以静胜牡”，“牡”是雄性，“牝”是雌性。这世界上的事情便是如此，这雌性善于柔，善于静，所以她的力量更长久。拿这个道理来说明什么呢？以静为下，什么叫善于处下？就是以静为下。别那么急躁、暴躁、浮躁、狂躁，善于处下，这样才能具有更大的力量、更长久的力量。这段讲完了，下边又接着“大国者下流”的道理。上面那一段是在论述它力量产生的源泉。一个大国老去动武，喜欢好战，好战者必亡，看着很强大，其实这都不是长生久视之道。所以下面就讲，“故大国以下小国，则取小国。”不是以静为下吗？善于处下吗？一个大的国家在跟小的国家打交道的时候，态度谦逊谦和，善于处下，不是居高临下、盛气凌人、不可一世的处事的方式方法，把这个小的国家就争取了。你和它平等相待，它觉得你这个大国可以倚靠，它喜欢跟你交往，遇到事情的时候喜欢支持你，帮助你，为你出力。“小国以下大国，则取大国。”为什么小国会这样做呢？因为小的国家也得找倚靠。小的国家在和大的国家打交道的时候，也善于处下，也把自己的位置放低，那么它就成了大国的朋友，有事的时候，大国才能给予支持，用我们现在习惯的话叫“罩着你”。大国也罢小国也罢，都得善于处下，这样才能形成一种和谐的关系。下面这两句话是比较难以理解的。“故或下以取，或下而取。”什么叫“以取”呢？争取有两种方式，一种是从上边抓起来，还有一种方式是更为有智慧的从下面轻轻地托起来。别小看这两个虚字、连词，“以”和“而”，这表示不同的动作。“或下以取”，要抓住你掌控你，“执者失之”，越想抓住越想掌控，失去得越快。“或下而取”，其实我们在帮助别人的时候，也就获得了别人的这样一种真心的敬佩，遇到事情的时候才能够得到人家帮助。“大国不过欲兼畜人”，大国想要更强大，就得需要更强大地支持，大国就得团结更多的小的国家，形成一个相互支持、相互帮助的局面。我给大家举一个例子，大家对这个问题就理解更深刻一点。我们中国文化的图腾——龙，大家都熟悉，我们叫“龙的传人”。可是，龙在自然界里面是没有的，它是怎么形成的呢？原来这些氏族部落，我们也可以把它看作是一个一个小的国家，那个时候他们互相征战、合并。龙的主体的部分就是蛇图腾，源自中原地区一个力量非常强大的部落，后来这个部落把很多小的部落合并到自己大的部落里边，它们收归一个部落就加上一个部落的图腾，这样，逐渐形成了龙的样子：蛇的身，马的头，鬣的尾……这不就是“兼畜人”吗？其实落到国家的层面也是一样，形成了一个团结的阵营，当然最好是正义的，遇到事情力量不就强大了吗？“大国不过欲兼畜人，小国不过欲入事人。”小国不过也想加入这个里面，大家一起做事，遇到事情的时候，大国还可以帮助、支持，这不是挺好的事儿吗？各得其所，所以叫“夫两者各得其所欲”，都得到自己所想要的。话讲完了，下边这句话又来了，“大者宜为下”，越是大的国家，越是位置高的人，越要懂得善于处下。</t>
@@ -866,10 +866,10 @@
     <t>第六十二章</t>
   </si>
   <si>
-    <t>道者万物之奥，善人之宝，不善人之所保。美言可以市尊，美行可以加人。人之不善，何弃之有？故立天子，置三公，虽有拱璧以先驷马，不如坐进此道。古之所以贵此道者何？不曰以求得，有罪以免邪？故为天下贵。</t>
-  </si>
-  <si>
-    <t>道是万事万物的奥妙所在，是善良的人珍贵的宝贝，是不善的人得以拯救的保障。说好的话、正确的话可以得到人们的尊重，美好的品行可以增加人的尊贵。品行不善的人，为什么就要把他抛弃掉？所以设立天子，设置三公，用珍贵的玉璧在前、驷马在后的礼仪来进奉，都不如静坐修道。为什么自古至今都把道看得这么珍贵呢？不就是说，按照道去做，我们所希望的就能得到，我们的过错就能改正免除吗？所以被天下人所珍视。</t>
+    <t>道者万物之奥，善人之宝，不善人之所保。美言可以市尊，美行可以加人。人之不善，何弃之有？故立天子，置三公，虽有拱璧以先驷（sì）马，不如坐进此道。古之所以贵此道者何？不曰以求得，有罪以免邪？故为天下贵。</t>
+  </si>
+  <si>
+    <t>道是万事万物的奥妙所在，是善良的人珍贵的宝贝，是不善的人得以拯救的保障。说好的话、正确的话可以得到人们的尊重，美好的品行可以增加人的尊贵。品行不善的人，为什么就要把他抛弃掉？所以在天子即位时，设置三公，用珍贵的玉璧在前、驷马在后的礼仪来进奉，都不如静坐修道（把大道传授给他们）。为什么自古至今都把道看得这么珍贵呢？不就是因为按照道去做，我们所希望的就能得到，我们的过错就能改正免除吗？所以大道被天下人所尊崇。</t>
   </si>
   <si>
     <t>这一章比较难理解，先说一下这一章的断句，有很多不一样的版本。现在大家基本上能够认可的是“美言可以市尊，美行可以加人”，有的本子是“美言可以市，尊行可以加人”，断句的差别就在这两句上。这一章讲什么呢？这一章是讲“道”的重要性，“善人之宝”，善人要不停地按照道去做，是善人的宝贝。但是，不善人也不会被道所抛弃，道可以来拯救他，所以叫“不善人之所保”。现在我们从头来解释。“道者万物之奥，善人之宝，不善人之所保。”这个道是万事万物的奥妙之所在，所以它是“善人之宝”，是善良人的珍贵的宝贝，也是“不善人之所保”，是不善人得以被拯救的保障，道可以拯救这些走错路的人，让他回到正道上来。“美言可以市尊”，美言，好的话。说好的话、正确的话，它可以得到人们的尊重。“美行可以加人”，好的品行，可以增加人的尊贵，团结更多的人。其实这个道理也比较容易理解，我们熟悉的三个人——魏徵、李世民和长孙皇后。魏徵是美言，他劝李世民，你要做一个好皇帝，有些事你不能做。李世民很愤怒，回来之后在家里边发火，说要把魏徵给杀掉。长孙皇后反而衣服穿得很整齐，给他道喜，说你遇到了一个好的臣子，我应该向你贺喜。李世民后来领悟到这一点，他说镜子可以正衣冠，魏徵就像一面镜子可以正我的品行。历史上，三个人留下的都是美言，都得到了人们的尊重，所以叫“美言可以市尊”。既然道是“善人之宝，不善人之所保”，那么“人之不善，何弃之有”。有的人走错路了，你为什么就觉得要把他抛弃掉？让他回到正道上来，用道去教化、去拯救。这是从正面来说它的作用。下面就讲的这个事就有针对性了。“故立天子，置三公。”国家的制度慢慢地有了天子，作为最高的领导者，还有三公——辅佐天子的最重要的职位。“虽有拱璧以先驷马”，古代敬献礼的时候，拱璧，捧着玉璧，捧璧的人在前边，乘着高头大马进献。珍贵吧？不如“道”珍贵！这里面有两个意思：一个就讲国家的制度，有天子，有三公，很重要，但这也只是形式。还有呢，用高头大马进献珍贵的玉璧，这也是很珍贵。但是“不如坐进此道”，这些都不如按照道来做，大道才是“万物之奥”，“万物之宝”。“古之所以贵此道者何？不曰以求得，有罪以免邪？故为天下贵。”意犹未尽，讲到这地方，《道德经》还觉得这个话就应该再强调一下，说古往今来，为什么都要把这个道看得这样珍贵呢？“古之所以贵此道者何？”不就是说你按照道去做，你才能得到自己真正想要得到的吗？“以求得”，你要的那个东西才能真正得到。这里的“以求得”并不是像我们烧香拜佛求得发财。“有罪以免邪”，因为前面讲过，“不善人之所保”，就算走错路了，但是我们重归正道，浪子回头金不换，原来的这个罪，也能得以补偿。这个并不像有的宗教里边说你犯了什么罪去忏悔一下，这个罪就免除了，它是让你按照大道来做，回到正道。我们来分分类，人不就是这两类：“善人”、“不善人”，对那些不善良的人，走错路的人，你为什么要抛弃他呢？“坐进此道”，回归此道就可以啊。弄了那么多的官职，天子、三公，有那么多珍贵的财宝，拱璧、驷马，还不如“坐进此道”。既然如此，“道”就是天下人最珍贵、最宝贵的，“故为天下贵”。</t>
@@ -881,7 +881,8 @@
     <t>为无为，事无事，味无味。大小、多少，报怨以德。图难于其易，为大于其细。天下难事必作于易，天下大事必作于细。是以圣人终不为大，故能成其大。夫轻诺必寡信，多易必多难。是以圣人犹难之，故终无难矣。</t>
   </si>
   <si>
-    <t>用无为的态度、方式来作为，用不找事、不多事的方式来做事，最好的味道反而是没有味道。大其小，因为大事都从小事做起；多其少，因为积少才能成多。用德来对待别人的怨。计划做难的事情要先从容易的做起，想做大的事情要先从小事做起。天下所有的难事都是从容易的做起，天下所有的大事都是从小事做起。所以圣人不自以为大，不说大话空话，所以最后能成就大事。没有把握的事轻易许诺别人一定会失去别人的信任，把事情看得太容易一定会遇到更多的困难。所以圣人把所有事情都看得很难，反而没有什么难事。</t>
+    <t>用无为的态度、方式来作为，用不找事、不多事的方式来做事，最好的味道反而是没有味道。以小为大，因为大事都从小事做起；以少为多，因为积少才能成多。用德来对待别人的怨。对付困难事情要在它还容易解决的时候开始，成就大业要从很小的
+事情做起。天下所有的难事都是从容易的做起，天下所有的大事都是从小事做起。因此圣人始终不去直接做大事，不说大话空话，所以最后能成就大事。没有把握的事轻易许诺别人一定会失去别人的信任，把事情看得太容易一定会遇到更多的困难。因此圣人把所有事情都看得很难，反而没有什么难事。</t>
   </si>
   <si>
     <t>第六十三章的内容，我们在前边已经有所接触。之前我们说，第二章就是《道德经》的“目录”，第二章列出来了后边讲的六个重要内容，有无相生、难易相成等等，这一章的核心就是“难”和“易”。这一章的核心意思就说，要想做大事，先从小事做起，想要以后攻坚克难，你得从容易的事情做起。还有一个重要的问题、重要的智慧：你要把容易的事情当作难的事情来做，要有充分的、认真的准备，提前思考它的步骤、程序、会遇到的问题，这样再出什么问题的时候，你就能从容应对。有这样的态度，天下也没什么难事。天下无难事，但天下都是难事，看你怎么对待。开头这九个字非常有趣：“为无为，事无事，味无味。”“为无为”——想要有为吗？你得先懂得无为的道理。为什么？因为有些事你越有为，越强求，什么事都管，反而最后结果非常不好。道家讲的无为，就是按照道的方式来作为，想要有为，先要懂得无为的道理，不要妄为，要抓住关键，举重若轻，有所舍才能有所得，所以为无为。其实也就是第三十七章里边讲的“道常无为而无不为”，道的规律、规则是什么？用无为的方式达到无不为的效果，更好的效果。我再强调一下，《道德经》里出现得最多的一个词是“天下”。《道德经》针对的是天下，千万不要把道家当作一种消极的被动的思想，它是“想为”，但是强调要通过正确的道路和手段，懂得无为的正确的道路和手段，才能达到真正的有效的为，也就是用无为的方式，达到无不为的这种效果。下边再落一层，“事无事”。大家都想做事，可是大家有没有注意到，有些人他是“找事”，他是捣乱，是阻碍、多事，天下本无事，庸人自扰之。所以我们做事的时候要懂得无事的道理，不要多事，不要找事，不要刁难。尤其是做领导者，没事找事，权力就是刁难，你这不就麻烦了吗？“事无事”，想做事，得懂得无事的道理，不要多事，不要扰民。再落一层，“味无味”。我们经常讲一个词叫“真水无香”，真正好的饮料，就像那白开水一样，没有味道。我们饮食讲究清淡，寡味，少油少盐。最高的味道，反而是没有味道，无味。当然，这三个词核心还是“为无为”，让大家能够更明白一点。老子展开来讲，“事无事”，不要多事，不要扰民，不要刁难，就像“味无味”的道理一样。按照这样的一个逻辑推下来，下面四个字大家就能明白了，“大小、多少”，千万不要把它念成“大小多少”，这个东西就没意义了。这是告诉大家要“大其小”、要“多其少”，要把小事看得很重要，细节决定成败，千万不要忽略这个细节。为什么要“大其小”呢？因为天下的大事，都是从小事做起，为什么要“多其少”呢？因为积少才能成多。想要多，你得从少的一点一点积累，积少成多。就像我们学习《道德经》，一章一章讲，一章一章学，不要着急，最后达到一个整体的理解。我们经常讲“聚沙成塔”、“集腋成裘”，这不都是“多其少”的道理吗？“报怨以德”，按照这种相反相成的道理，对别人的埋怨、恩怨，也应该站在一个“德”的角度，因为德是符合道，用道的东西里面去感化。第六十二章不是讲了吗？“人之不善，何弃之有？”人家有这个埋怨，怎么正确地对待呢？“报怨以德”。用这种智慧和层次，让大家一起能回归到正途，回归到正道。“图难于其易，为大于其细。天下难事必作于易，天下大事必作于细。”这几句话，在我们文化里边名气非常大，因为讲的是哲学上的量的积累达到质的变化的道理。“图难于其易”，“图”就是图谋、计划。你计划想要做难的事情，要从容易的事情做起。“为大于其细”，想要做大的事情，得从小的事情一步一步来。我们大家都知道要脚踏实地，循序渐进，有条不紊，一屋不扫，何以扫天下？“天下难事必作于易”，天下所有的难事，都要从容易的事情做起。就像小孩的培养，让他们在处理小的事情中就形成良好的习惯，把小的事情、容易的事当成培养良好习惯的重要途径，将来，小孩在遇到大事、难事都能从容应对。现在很多人都有一个致命的弱点，大概是人的通病，就是好高骛远，老觉得自己应该是做大事的人，对小的事情不屑一顾。《道德经》就告诉我们这个智慧：想要做难的事情，从容易的事情做起；想要做大的事情，从小的事情做起，“天下大事必作于细”。“是以圣人终不为大，故能成其大。”“是以”，“是”就是这样，“以”就是所以。所以有智慧的领导者就是这样：“终不为大”，不是老说大话，不是老给大家画饼充饥，而是脚踏实地，一步一步地做起，“故能成其大”。一步一步把这个事情完成了，一步一步地完成计划，最后实现一个大的蓝图，好的结果，水到渠成。所以一个有智慧的人，不是老用那些虚幻的东西来画饼充饥，老是给大家讲大话、空话。“终不为大，故能成其大”，最后反而成就了大事，这话讲得非常好。我建议大家学习《道德经》，有一种重要的学习方法，就是反复看。有的人看《道德经》，也许一年就看一章，反复地看，反复地体会，“少则得，多则惑”，“终不为大，故能成其大”。以管窥天，以锥扎地，我们视力更集中，这样把这个事情才能做得更踏实，扎得更透。我们每一次的进步，虽然看起来好像只是一点点，但是这一点点积累起来就不得了了，“终不为大，故能成其大”。“轻诺必寡信”，大家还记得我们在讲《道德经》第八章的时候，就讲过“言善信”，我们中国人喜欢拿潮水作为讲信用的代表和象征，所以，有一个词就叫“潮信”。你看那钱塘潮每到农历八月十八前后就来了，人也应该如此，说话要讲信用，要有诚信，能给别人做成的事我们再去允诺，没把握做成的事，不要轻易去答应，不管我们有多热情。如果我们答应人家的很多事最后都做不成，时间长了，人家一定认为我们是食言而肥，不讲信用。《道德经》讲话是比较宽缓的，但这句话用的就是强逻辑判断，“轻诺必寡信”，这不是对我们委婉的劝告，这简直就是对我们严厉的警告。所以要讲诚信，君子重一诺，一诺千金嘛，所以“轻诺必寡信”，要避免这种结果出现。“多易必多难”，你把这个事情看得很容易，做什么事情，最后一定出问题。世界上哪有容易的事情，吃个饭喝个水，这都需要功夫，需要本事，小事情我们都要认真对待。我们经常讲“小河沟里翻船”，把一个事情看得太容易了，太简单了，往往会在这个事情上出问题。面对很多难的事情，大家战战兢兢，小心谨慎，反而没事，反而就是在一些认为最容易的事情出问题。很多学生做题、考试也是一样，难题没事，在容易的题上，出了问题，回去捶胸顿足，懊悔无比。所以，我们平常要形成一种把容易的事情当作难的事情来做的习惯，你要懂得“多易必多难”，凡事太容易，后面一定会出现很多的困难，出现很多的问题。所以，下边这句话就讲：“是以圣人犹难之”，所以有智慧的人，把这容易的事情都看作很难。天下的事情都当作难的事情来做，反而结果没有什么难的事情，“故终无难矣”。这个道理非常有趣，其实就是相反相成的道理，这个叫“难易相成”。世界上有没有难事呢？有，也没有。你把这个难的事情当作难的事情，看作是无法克服的，它就是难的事情；你把容易的事情当作容易的事情，没有认真对待，最后也会变成难的事情。我们把容易的事情当作难的事情来做，最后那个难的事也就做成了；真正难的事情，我们认真准备，有充分的信心，最后这难的事情也就克服了。“故终无难矣！”世上无难事，这就是“难易相成”的智慧。很多事情，决定于我们的想法、态度，态度不同，难易之间就会相互转化。</t>
@@ -893,7 +894,7 @@
     <t>其安易持，其未兆易谋，其脆易泮（pàn），其微易散。为之于未有，治之于未乱。合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。为者败之，执者失之。是以圣人无为，故无败；无执，故无失。民之从事，常于几成而败之。慎终如始，则无败事。是以圣人欲不欲，不贵难得之货；学不学，复众人之所过。以辅万物之自然，而不敢为。</t>
   </si>
   <si>
-    <t>局面稳定的时候容易掌控，事情没有征兆的时候容易去谋划，脆弱的东西容易分开，微小的东西容易解散。在事情还没有开始的时候就要作为，在还没有出现乱象时就处理好。合抱的大树，都是从细小的萌芽一点一点长起来的。九层的高台，也是一层一层的土积累起来的。想要走千里的路，就要从脚下一步一步走起。强为、妄为就会失败，执意把控就会失去。所以圣人不强为、不妄为，所以不会失败；不强执、不固执，所以不会失去。众人做事常常在快要接近成功的时候惨遭失败。在事情快要做完的时候还像一开始时候那样谨慎、慎重，就不会有失败。所以圣人所想的都是别人不愿意去想的，不以难得的货物为珍贵；学别人不愿意学的，对别人的错误引以为鉴。只是按照道的规律自然而然地去做，而不敢妄为。</t>
+    <t>局面稳定的时候容易掌控，事情没有征兆（国家还没有出现动乱）的时候容易去谋划/对付，事物脆弱时，容易消除，事物微小时，容易消散。在危险局面还没有发生的时候就做好准备，在国家还没有混乱的时候就注意治理。合抱（两个人用手臂围起来，能够环抱住）的大树，都是从细小的萌芽一点一点长起来的。九层的高台，也是一层一层的土积累起来的。想要走千里的路，就要从脚下一步一步走起。强为、妄为就会失败，执意把控就会失去。所以圣人不强为、不妄为，所以不会失败；不强执、不固执，所以不会失去。众人做事常常在快要接近成功的时候惨遭失败。在事情快要做完的时候还像一开始时候那样谨慎、慎重，就不会有失败。所以圣人所想的都是别人不愿意去想的，不以难得的货物为珍贵；学别人不愿意学的，对别人的错误引以为鉴。圣人顺应着万物的自然天性去帮助它们成功，而不敢按照个人意志去做事。</t>
   </si>
   <si>
     <t>第六十三章、第六十四章讲的道理，就是大家熟悉的量变和质变的道理，量的积累达到质的变化。但是大家注意，这个量的积累，有向好的方面，也有向不好的方面。前面讲了“为大于其细”，要做大事，从小的事情做起，这样才能最后达到想要的结果，假如积累的是一个不好的量，最后就积重难返。第六十四章一开始就要把两个方面，都给大家做了说明，有的事情在它刚出现向坏的方面发展苗头的时候，我们在这个阶段就把它解决了。这一章里有两个非常重要的内容，一个是大家都熟悉的一段话：“合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。”第二个就告诉我们，做事情要“慎终如始，则无败事”。这两个重要内容，我们先有一个直观的认识，再来读就好理解了。我们一句一句来解释。“其安易持”，“安”就是稳定，局面稳定的时候，容易掌控，就像一个东西，它稳定的时候，你容易把它把握住；它活蹦乱跳的时候，你把握起来就困难了。“其未兆易谋”，“未兆”，没有征兆的时候，苗头还没有开始的时候，容易去谋划。“其脆易泮”，脆的时候一打就打散了。“其微易散”，很微小的时候，很容易把它解散。比如说一件事情，很小的时候，人数很少的时候，你把它处理起来很容易。众怒难犯，一大群人轰起来、闹起来的时候，这事情解决起来就困难。前面告诉大家这些现象，然后告诉大家处理的方法。什么方法呢？“为之于未有”——在事情没有出现的时候，没有开始的时候，要有预见性，就要有作为，凡事预则立，不预则废。“治之于未乱”，还没有出现这种乱象的时候，就把它治理了、解决了。这也是习近平讲话时经常引用的两句话。怎么来理解呢？先给大家说第一个例证。有一次晏子出巡，齐国发大水，把一座石桥给冲毁了，晏子就把自己的船让给了灾民，大家都赞誉晏子爱民如子。然而一位有智慧的高人就批评晏子，就说你做这个国家的宰相，齐国发大水能把一座桥梁冲毁，你都没有预见到，没有提前做出预防，你失职。所以应该是怎么样？“为之于未有”，你别等这个事情都已经成为这个样子，再去处理它，不管你处理的方式多么巧妙，多么有智慧，但是不如让这件事情没有发生。另外一个例证更能说明这个道理。有一次，扁鹊的国王问扁鹊：扁鹊你名气太大了，你是不是国家医术最高的？扁鹊说不是，别人我不知道，起码我大哥、我二哥都比我的医术高。所以这个国王就很奇怪，你大哥、你二哥是谁？他们医术那么高，怎么大家都不知道他们呀？扁鹊就说，我大哥怎么治病的呢？人家还没有病，他告诉人家怎么预防、怎么不得病。这不是“为之于未有”吗？提前就有作为了，预防得病。我二哥怎么治病的呢？人家刚有一点小病，他就把人治好了，不让他酿成大病，“治之于未乱”。所以我们经常讲，凡事预则立，不预则废，要有远见，要有预见，要未雨绸缪。这是讲负面，因为有些事情量的积累是向不好的方面发展的，所以要提前把这个问题给处理掉。下面讲的这个事，非常重要。我们做大事情都要从容易的事情、小的事情，一步一步积累才能达到这种质的变化，要脚踏实地，循序渐进。因为什么呢？“合抱之木，生于毫末”，合抱之木，它是一点一点长起来的。“九层之台，起于累土”，中国文化中，三六九都代表着高、多。那么高的高台也是一层一层土积累起来的。“千里之行，始于足下”，走这么远的路，要脚踏实地一步一步地做起。说到这里，我得加一句，有人老认为道家思想是消极的、被动的、无为的。“合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。”这不就是自强不息吗？所以有些事我们不能人云亦云，我们得看原文，以原典作为证据。“为者败之，执者失之。”“为”就是强为、妄为。因为《道德经》讲的真正的为叫“无为”，就是按照道的方式来作为，不按照道的方式来作为就是强为、妄为。越是强为，最后的结果越糟糕，因为量的积累还不到，你老想强行地发生质变，这不是急躁冒进吗？“执者失之”，就像我们抓沙子一样，你握得越紧，流出来越多，越想用力地把它抓住，反而失去得越来越快。所以一个有智慧的领导者，“无为”，按照道的方式来作为，不妄为，不强为，不多为，有所不为，所以也不会有急躁冒进的失败。“无执故无失”，没有这样的强执，最后也不会失去。“民之从事”，平常人做事，或者说领着大家做事，在什么时候最容易把事情给做砸了呢？“常于几成而败之”，经常在快要接近成功的时候，把事情给做砸了。那应该怎么办？“慎终如始，则无败事。”什么叫慎终如始呢？我先给大家打一个比方，大家走在结着冰的冰面上的时候，刚一下到冰面上都是小心谨慎，战战兢兢。走一会儿，觉得自己走熟了，就放松警惕了，有的干脆最后开始跑了，有的甚至在冰面上炫耀，危险往往就在这个时候发生了。所以我们中国人经常讲一句话叫“行百里者半九十”，一百里的路，走到九十里路的时候，还要当才走了一半，越是剩下那一段的时候越紧要，民间讲“编筐编篓，全在收口”，即最后这个结尾。“慎终如始”，走到最后那几步，还像开始下到冰面上一样小心谨慎，一步都不放松，那就没什么败事，没什么事情做不成。“慎终如始，则无败事”，就是我们现在经常讲的不忘初心，善始善终，那就没有什么事情做不成的。“是以圣人欲不欲”，一个有智慧的人，特别是一个有智慧的领导者，想要的东西是什么呢？是别人都不关心的，都不想要的。因为“天下熙熙，皆为利来；天下攘攘，皆为利往”，大家关心的是获取利益的方式方法，而一个有智慧的人，有智慧的领导者，应该有这种无功利之心。“欲不欲”，别人都不想这样的，反而是你应该考虑的。大家都针对“有”的东西，这有智慧的人、好的领导者得针对这无形的东西：人的精神财富，人的精神世界，人的修养。既然“欲不欲”，你跟一般人的欲望不一样，他们认为那个东西是珍贵的、难得的，反而在你的眼里是不重要的，不把它看作是难得的。领导国家的时候也是如此，第三章讲的，“不贵难得之货，使民不为盗”，形成一种淳朴的风气。“学不学，复众人之所过。”《道德经》讲的道理，叫“绝学”，一般人不愿意学，学这个东西能带来什么样的好处、利益吗？人的境界高的时候，学的很多的东西不就是和一般人不一样的嘛。一般人不愿意学的东西，又花功夫，又不能带来什么实际的利益，可是“学”这些东西代表了真正的智慧与学问。学这些东西干吗呢？“复众人之所过”，这个“复”不是重复，我们下围棋的人都知道有个词叫“复盘”，通过不断的重复模拟来检视，哪个地方下得好，哪个地方下得不好。别人犯的过错像复盘一样历历在目，以此为鉴，别再犯大家都经常犯的错误。“以辅万物之自然，而不敢为。”“以辅万物之自然”，就是按照自然的规律去做，追求的是一种水到渠成、自然而然的结果。“辅自然”就是无为。“而不敢为”，就是不敢妄为。因为我们违背了道，违背了自然规律，哪怕是短时间取得成功，其实也会受到更大的一种惩罚。这章告诉我们，一是我们做事情要“为之于未有，治之于未乱”，懂得预防，懂得不好的事情在苗头出现的时候就把它解决掉；二是我们做事情要脚踏实地，循序渐进；三是我们要“慎终如始”，不忘初心，善始善终，因为我们做事情经常在快要成功的时候，结果功亏一篑，所以要懂得这样一个道理。</t>
@@ -905,7 +906,7 @@
     <t>古之善为道者，非以明民，将以愚之。民之难治，以其智多。故以智治国，国之贼；不以智治国，国之福。知此两者，亦稽式。常知稽式，是谓玄德。玄德深矣，远矣，与物反矣，然后乃至大顺。</t>
   </si>
   <si>
-    <t>以前那些善于按照道来治理国家的人，不教百姓有心眼、技巧，而是使人民敦厚淳朴。百姓之所以难以治理，是因为他们奇技淫巧太多。所以用技巧来治理国家，是国家的灾难。不用技巧治理国家，是国家的福分。知道这两者的差别，这就是治国的法则。按照规律了解这个法则，就是“玄德”。玄德深啊，远啊，最后又返回了宁静朴实的根本，这样就符合自然，达到了最大的和顺。</t>
+    <t>古代那些善于按照道来治理国家的人，并不是用大道使百姓变得聪明伶俐，而是使人民敦厚淳朴。百姓之所以难以治理，是因为他们奇技淫巧太多。所以用技巧来治理国家，是国家的灾难。不用技巧治理国家，是国家的福分。知道这两者的差别，这就是治国的法则。能够永远把握住这些原则，就可以说是具备了微妙高尚的品德。高尚的品德高远深邃，好像与一般事理相反，最后又返回了宁静朴实的根本，然而具有这样的品质之后办起事来却十分顺利。</t>
   </si>
   <si>
     <t>这一章所涉及的，也是我们现在哲学里面经常讲的一个道理，叫“否定之否定”规律，讲事物的发展分为三个阶段，第一个阶段是肯定，第二个阶段是否定，第三个阶段是否定之否定。比如说麦粒长出麦苗，最后结出更多的麦粒，这就是一个否定之否定的阶段。第三个阶段常常重复第一个阶段的某些特征，却是在更高的程度上重复第一阶段的某些特征。这一章和第四十章讲的“反者，道之动”，所运用的哲学的智慧和道理是一样的，既然这样，把这个道理运用到治国上，应该如何呢？这就用到了一个我们大家熟悉的词，叫“返璞归真”，《道德经》认为治民最关键的是要使民风纯朴，不要那么多的技巧，不要那么多的套路。了解了这一点，我们再来看这一章，就明白了老先生的良苦用心。“古之善为道者”，以前的那些善于按照道来治理国家的人。“非以明民，将以愚之”，不是让百姓有那么多的心眼技巧。这个“愚”，不是愚民，而是敦厚、厚道，让人民的民风纯朴。“民之难治，以其智多。”百姓为什么难以治理？因为他心眼多、技巧多。“智”就是技巧、心眼、套路。“故以智治国，国之贼”，用技巧来治国，经常用骗术谎言，这是国家的灾难。“不以智治国，国之福”，不用这些技巧，让民风纯朴、敦厚，这个才是国家的福祉、国家的福分。“知此两者，亦稽式。”“稽式”就是法则。知道这两个的差别，这就是一个法则，治国的一个法则。“常知稽式”，“常”就是规律。按照规律，我们来了解这个法则。这叫什么？“是谓玄德”，“玄”就是深远的意思，这个就是深远的智慧与品德。下面这句话就是我一开头讲的，这个品德“深矣，远矣，与物反矣”，“与物反矣”不就是“反者，道之动”吗？我们都能看到事物的正向的发展，所以《道德经》经常提醒我们，“反者，道之动”，道是向它相反的方向运动，所以你理解问题也不能只看一面。“与物反矣”怎么解释呢？第二十五章，“大曰逝，逝曰远，远曰反”，最后又回到了它的根本。根本是什么？“归根曰静”。民心没那么多的躁动，变得清静宁静、敦厚朴实，这不就符合大道了嘛。“然后乃至大顺”，这样慢慢地就回归到了正确的道路，符合自然之道。所以，这一章讲的就一个问题：你用什么方式治国呢？要让民心变得纯朴、敦厚，返璞归真，没那么多的技巧，没那么多的套路，没那么多骗人的把戏，这样才是符合大道。</t>
@@ -917,7 +918,7 @@
     <t>江海所以能为百谷王者，以其善下之，故能为百谷王。是以欲上民，必以言下之；欲先民，必以身后之。是以圣人处上而民不重，处前而民不害。是以天下乐推而不厌。以其不争，故天下莫能与之争。</t>
   </si>
   <si>
-    <t>江海之所以能成为百川之王，是因为善于处下，所以能成为百川之王。所以要想站在上面领导好人民，必须在言语上懂得谦逊；要想站在前面领导好人民，必须要把自己的利益放在后面。所以圣人在上面领导大家而大家没有感到沉重的负担，在前面领导大家而大家没有感觉受到伤害。所以天下人都乐于拥戴他而不会感觉厌倦。因为他不争，所以天下没有人能与他争。</t>
+    <t>江海之所以能成为百川之王，是因为善于处下，所以能成为百川之王。所以要想站在上面领导好人民，必须在言语上懂得谦逊；要想站在前面领导好人民，必须要把自己的利益放在后面。所以圣人在上面领导大家而大家没有感到沉重的负担，在前面领导大家而大家没有感觉受到伤害。所以天下人都乐于拥戴他而不会感觉厌倦。因为圣人不与人争，所以天下也没有人能够与他相争。</t>
   </si>
   <si>
     <t>这一章所讲的这个道理是《道德经》从头至尾所强调的“善于处下”，只有善于处下，才能真正居上。我们在一开始说过，《道德经》的很多话是针对那些领导者、统治者讲的，所以老先生认为越是位置高的领导者、统治者，越要善于处下，为什么呢？首先从处下的结果上来看，“江海所以能为百谷王者，以其善下之，故能为百谷王。”这句话我在前面也多次引用过。大江大海之所以能成为大江大海，是因为善于处下，不辞细流，能团结一切可以团结的力量，故能为“百谷王”。老子先拿“百川归海”的形象讲了这个道理，让大家有一个感知。下面就开始讲具体的做法和内容。“是以欲上民，必以言下之。”所以你要想站在上面领导好下面这些人，在语言上要懂得谦逊、谦让。领导者，尤其国君、皇帝这一类的，讲话的时候不能够居高临下，盛气凌人，自尊自大，不可一世。第三十九章说过“贵以贱为本，高以下为基。是以侯王自称孤寡不穀”，所以在语言上要谦逊。“欲先民，必以身后之。”想要站在前面当好领导、当好领头的，要懂得把自己的利益放在后面，想要领导别人就得给别人利益。一个人既要领导别人，又想什么好处、利益、功名都抢在自己手上，这个人下场不是不言而喻的吗？范仲淹的《岳阳楼记》里说“先天下之忧而忧，后天下之乐而乐”，做官、做领导不得如此吗？钱钟书先生认为范仲淹这两句话就是出自《道德经》的。但是人家学得比较好，不也成了大家都熟悉的名句了吗？“是以圣人处上而民不重”，所以一个好的领导者，你在上面领导大家，大家没有感觉到沉重的压力。“处前而民不害”，你在前面领导大家，大家没有感觉到你对他的危害。因为你要想领导别人，得让别人得到利益。西汉史学家司马迁在《史记·循吏列传》说：“公仪休者，鲁博士也。以高弟为鲁相。奉法循理，无所变更，百官自正。使食禄者不得与下民争利，受大者不得取小。”这里的食禄者不与民争利，意思是做官的人不许和百姓争夺利益。“是以天下乐推而不厌”，所以天下的人民都往高举你，往前推你，不感觉到厌倦、厌烦。如果统治者穷奢极欲，危害百姓，草菅人命，下面的人就会感觉到“害”、感觉到“重”，这样的人百姓会“乐推”吗？当然不会。“以其不争，故天下莫能与之争。”一个领导者，能得到了大家的拥护、拥戴，正因为你不争，不与民争利，不与其他人争名，“利而不害，为而不争”，结果是“以其不争，故天下莫能与之争”。越是争的人，最后往往失败得越惨，因为你的位置已经规定了你应有的担当、使命和责任。陈毅元帅讲过“手莫伸，伸手必被捉”，形象而深刻，那么，反过来用这个道理讲，就得以更加明确了。“以其不争，故天下莫能与之争”，所谓“不争”，并不是消极被动，“不争”，当然要了解边界，不争边界之外的东西，这样的话才能“天下乐推而不厌”。</t>
@@ -929,7 +930,8 @@
     <t>天下皆谓我道大，似不肖。夫唯大，故似不肖。若肖，久矣其细也夫。我有三宝，持而保之。一曰慈，二曰俭，三曰不敢为天下先。慈，故能勇；俭，故能广；不敢为天下先，故能成器长。今舍慈且勇，舍俭且广，舍后且先，死矣！夫慈，以战则胜，以守则固。天将救之，以慈卫之。</t>
   </si>
   <si>
-    <t>天下都说我的道大，似乎不像任何具体的东西。正是因为道大，所以不像。如果像，就早已归为具体事物了。我有三件最珍贵的宝物，值得永久保持。一个是“慈”，一个是“俭”，一个是“不敢为天下先”。有了慈母的情怀，才能真正的勇敢；节俭才能长久持续地发展；遇到利益不争先，懂得先人后己，才能成器、成长。现在的人舍弃慈母的情怀而炫耀勇武，舍弃节俭还奢求长久持续的发展，遇到利益争先恐后、一点都不退让，这是自寻死路！拥有慈母的情怀，自然是攻无不克，守无不固。如果天要拯救谁的话，一定是以慈母的情怀来守卫。</t>
+    <t>天下都说我讲的道太大了，似乎不像任何具体的东西。正是因为道大，所以什么也不像。如果像，就早已归为具体事物了。我有三件最珍贵的宝物，值得永久保持。一个是“慈”（守柔），一个是“俭”（节俭），一个是“不敢为天下先”。能做到守柔，才能真正的勇敢刚强；节俭才能长久持续地发展；遇到利益不争先，懂得先人后己，才能成器、成长（成为万物的领导者）。现在的人舍弃守柔而只求勇武，舍弃节俭还奢求长久持续的发展，遇到利益争先恐后、一点都不退让，这是自寻死路！如果能做到守柔，凭它作战就能胜利，凭它守卫就能坚不可摧。上天要救助一个
+人，保护这个人的办法就是让他具备柔和的品性。</t>
   </si>
   <si>
     <t>老子、孔子、释迦牟尼、柏拉图，这都是同时代人，在他们那个时代，书其实只有一种题材，就是对话体。《论语》是孔子弟子记的，记得非常清楚，坐在对面的是什么人，提了什么问题，老师怎么回答，所以大家读起来一目了然。佛经呢？很多的佛经也都是释迦牟尼对弟子问题的回答，大家看《金刚经》，是回答须菩提的，《心经》是回答舍利子的，都是针对他们的问题的回答。古希腊哲学家苏格拉底的学生叫柏拉图，写了一本《对话录》，就是记载当时苏格拉底跟学生之间的互动，对各种问题的解答。其实《道德经》的最早的形成也是这种形式，也是对面坐的人问的问题，老先生给予回答，也是对话体，所以我们读这本书，始终要感觉到这是在回答对方的问题，是有针对性的解释和回答，这样很多问题我们才能够得以正确地理解。那么这一章是在回答什么问题呢？对面坐的人，问老子关于道和德的事，老先生给他讲半天，他没听懂，于是提出要求：能不能把你的思想概括得简单点？你让我也能听得明白。大家自然会有疑问，我怎么知道是这样的？是不是我自己在杜撰？让我们回到原文，大家看一下这一章的开头就清楚了。“天下皆谓我道大，似不肖。”老子这个意思就是说，不仅是你，天下人都认为我把道讲得太大、太宽泛了，听不懂。你听不懂，我得给你打比方，类比虽然不能够说明问题，但是它可以让人理解问题。我说道就像风一样，大象无形，你们说不像；我说道就像水一样，大道汜兮，其可左右，你们还说不像……“夫唯大，故似不肖。”正因为把道讲得这么大，拿什么给他打比方，他都说不肖，所以老子就感慨，假如真的像的话，“久矣其细也夫”。意思是假如真的像，那早就归到小道了。比如，说道像一条大河，你拿这个比方，要像的话，就像支流了。道就像一条大道，你要说比方像的话，就像小道。其实意思就说，拿道打比方，要是真的像的话，就是把道说得太小、太细了。那怎么办？不跟你讲那么多了，把我的思想概括到简单得不能再简单。只剩下三个方面，“我有三宝，持而保之。”把我的思想概括到最后，简单得不能再简单了，就剩下三个方面拿出去，按照去做就行。那这“三宝”是什么呢？“一曰慈，二曰俭，三曰不敢为天下先。”大家解读这三组词的时候，不可以单独先解释几个字词，一定要把“三宝”里边的字词和后面的语句连接来解读：“一曰慈，慈故能勇；二曰俭，俭故能广；三曰不敢为天下先，故能成器长。”否则，会失之宽泛。“一曰慈，慈故能勇。”“慈”是指什么？指的是慈母的情怀。做领导、做家长，有了慈母的情怀，才能有真正的担当、勇敢。如果你单独解释这个“慈”就麻烦了，慈母有时候也唠里唠叨，有时也无原则地爱，不是经常说“慈母多败儿”吗？可是《道德经》为什么把“慈”放到第一位呢？这是针对坐在对面的提问者的。作为领导、作为诸侯王，你在这个位置，就要有慈母的情怀，才能有真正的担当、勇敢。如果没有慈母的情怀，一出事就会出卖国家和人民，一出事就把自己的部下当做替罪羊推到前边。“二曰俭，俭故能广。”我还是觉得这位老先生对咱们中国人了解得非常深刻，我们中国人致命的弱点是什么？好面子，好虚荣，好攀比。所以一旦是公开的场合，一旦是监督不力，往往就奢靡之风盛行，浪费之风盛行。没有节俭节制，而是有奢靡之风浪费之风，那就没办法“广”，“广”就是长久持续。家庭没有培养出节俭、节制之风，家庭就没有办法长久持续地发展，所以要勤俭持家。国家人民没有培养出节俭节制之风，而是奢靡浪费，这个国家也没有办法长久持续地发展。“三曰不敢为天下先，故能成器长。”先理解“成器长”，咱们中国很多的词是组合性的，所以大家理解的时候，也要把它组合的东西拆开，“成器长”拆成四个字“成器成长”。我们怎么样才能不断地成长，终成大器呢？“不敢为天下先”，现在咱们天天讲叫“敢为天下先”，这又来一个“不敢为天下先”，这两句话不就怼上了吗？其实这两句话根本不矛盾，讲的不是一回事儿。我们现在强调的“敢为天下先”，是敢闯敢创新，这是一种很好的品质，创新是一个民族的灵魂。《道德经》讲的“不敢为天下先”是什么意思呢？做领导，领着大家做事，要懂得把自己的利益放在后面，要懂得先人后己，不要私欲膨胀，不要什么事情只关注自己，这样才能够不断地进步，不断地成长，终成大器。各位是否还记得我在前面给大家说过，其实读这本书的时候，不用别人给你画出重点，你自己都能感觉到，因为老子在书里不断地强调自己的重点，一种强调的方法是重复，第二种强调的方法是头尾，第三种强调的方式就叫正反，也就是他正面讲完了，觉得是还言犹未尽，要从相反方面给大家再论证一下，你看这一章不就是这样吗？现在的人是什么样的，本来应该按照道的方式来做，要慈、俭、不敢为天下先，我们把这“不敢为天下先”也可以概括成两个字叫“谦让”，或者概括一个字叫“让”。我有三宝，慈、俭、让。可是老子对当时的人不满意，这些人都怎么做的？“舍慈且勇”，根本没有这种情怀，还到处炫耀自己的勇敢。我们现在不也经常看到这种情况？酒驾了，还拍个视频给警察发过去，我醉驾，警察你来抓我呀，炫耀自己无赖似的勇敢。“舍俭且广”，没有这种节俭、节制，还奢求长久持续地发展，不可能。“舍后且先”，遇到好处、利益，争先恐后，一点都不肯让，甚至不该自己的也抢，这样做的结果是什么呢？“死矣！”这样做的最终结果，就把自己弄到死路上去了。“夫慈，以战则胜，以守则固。天将救之，以慈卫之。”这些讲完了，又把他讲的第一个“慈”再说一遍。有这种慈母情怀的人，那么面临事情的时候就会“以战则胜”。他勇于担当，真正遇到困难的时候，领着这个大家当然攻无不克，战无不胜。“以守则固”，国家遇到侵犯的时候，领导者的这种情怀，力量无尽，守无不固。“天将救之，以慈卫之”，如果天真的有情感的话，他要拯救国家的人民，拯救团队团体，一定是“以慈卫之”，你一定有这种慈母的情怀才值得，因为它本身就拥有无穷无尽的力量。第六十七章，核心的就是“我有三宝，持而保之”，要坚定、坚持地按照去做。</t>
@@ -950,10 +952,10 @@
     <t>第六十九章</t>
   </si>
   <si>
-    <t>用兵有言：吾不敢为主而为客，不敢进寸而退尺。是谓行无行（háng），攘无臂，扔无敌，执无兵。祸莫大于轻敌，轻敌几丧吾宝。故抗兵相加，哀者胜矣。</t>
-  </si>
-  <si>
-    <t>懂得用兵的人曾说：我不敢主动发动战争进犯别人，而只在被进犯时不得已而应战；作战时不敢盲目进军哪怕一寸，而要后退一尺，以退为进。（在入侵国家的领土上）虽然人民没有排成行列阵势，没有面对人民奋臂作怒，虽然好像没有面对敌人，虽然人民手中没有兵器，但四处都是侵略者的敌人。没有比轻敌更大的祸患，轻敌就几乎丧失了我的“三宝”。所以两军相持时，被同情、被支持的一方会获胜。</t>
+    <t>用兵有言：吾不敢为主而为客，不敢进寸而退尺。是谓行无行（háng），攘（rǎng）无臂，扔无敌，执无兵。祸莫大于轻敌，轻敌几丧吾宝。故抗兵相加，哀者胜矣。</t>
+  </si>
+  <si>
+    <t>用兵打仗的人说过：我不敢主动发动战争进犯别人，而只在被进犯时不得已而应战；作战时不敢盲目进军哪怕一寸，而要后退一尺，以退为进。（在入侵国家的领土上）虽然人民没有排成行列阵势，没有面对人民奋臂作怒，虽然好像没有面对敌人，虽然人民手中没有兵器，但四处都是侵略者的敌人。没有比轻敌更大的祸患，轻敌就几乎丧失了我的“三宝”。所以两军相持时，被同情、被支持的一方会获胜。</t>
   </si>
   <si>
     <t>第六十八章是用战争的术语来做比方，讲的道理当然比仅局限于战争更为广泛。第六十九章我们也当作如是观，他讲的是战争的事情，但是这个道理我们也可以做延伸、做扩展，成为我们生活中的、工作中的普遍的思想与智慧。我们知道《道德经》里边很多的内容并不是老子本人的话语，他也是一个“集大成者”。他经常在回答坐在对面的圣、王、士这些领导者的问题的时候，引用当时或者以前那些智者的语言。第一句话，“用兵者言”，懂得用兵的人怎么做谋划？怎么来认识问题呢？“吾不敢为主而为客”，我才不去老是发动战争去侵略别人，“国虽大，好战必亡。”“我不敢进寸而退尺”，打不过的时候，对手力量太强大的时候，就要懂得以退为进，这个叫什么呢？这个就叫“行无行，攘无臂，扔无敌，执无兵”，这十二个字怎么理解？我先换一个角度给大家来认知这个问题。抗日战争胜利之后，有很多日本人就对这场战争表示不是很服气，因为他们有的认为，是因为东条英机改变了战略，才导致这场战争在中国的战场上的失利；有的人认为，日本战败是因为美军的加入，所以他们也想专门研究战败的原因。有一位日本学者专程来到了中国，他也是通过一本经典来了解我们中国人在这方面的思想与智慧，这本经典就是毛泽东的《论持久战》。各位知道，一九三七年七月七日卢沟桥事变，抗日战争全面爆发，同年的八月二十二日到二十五日，就在陕北洛川召开了洛川会议。在这次会议上，毛泽东就已经开始讲持久战的思想，一九三八年的时候这本书就面世，这不是战后的马后炮，是战前的预测。他把整个战争的进程就概括为六个字，而历史就是沿着这六个字发展：退却，相持，反攻。一开始当然日本侵略者锋芒外露，我们没有办法直接跟他们对抗，因为日本是一个统一的国家，而当时我们的中国四分五裂，军阀混战，政令不统一。日本军队装备精良，又蓄谋已久，所以一开始没有可能把他们赶出去，他们肯定会占领我们很多地方。所以这个时候我们就要懂得退却，以退为进。但是日本的军队又不多，占领我们的地方多了，双方就进入了一种相持的阶段。因为武汉和鄂西会战之后，双方就进入相持阶段，咬牙坚持。我们中国是站在正义的一方，况且我们是一个统一的世界反法西斯战场的一部分，为整个世界反法西斯战场拖住了那么多的日本军队，自然要得到国际舆论的支持、国际力量的援助，最后获得胜利。那么日本为什么会陷在中国的战场上？因为原本按照日本人的想法，中国战场很快就能拿下来，以此为基地，北面是针对苏联，南面是针对南洋的那些国家，很多是英国的殖民地，所以它的主要的目标并不是在中国。可是没想到中国的战场，几乎拖住了它绝大部分的力量，为什么会这样？我们来看一下下面这几句话，“行无行，攘无臂，扔无敌，执无兵”。侵略者进入了另外一个国家，虽然这个国家的人民没有站成军队的样子，“行无行”，但是他们不都是你的敌人吗？“攘无臂”，打击你非得用拳头吗？有各种各样的方式，坚壁清野可不可以？游击战可不可以？全民皆兵，所以叫“扔无敌”。“执无兵”，虽然他们手中没有兵器，但他们用多种多样的方式和侵略者对抗，到处都是敌人。所以为什么说“国虽大，好战必亡”？因为你侵略者是不得人心的，进入到别的国家的军队会遭到别的国家人民的反抗，到处都是你的敌人，“扔无敌，执无兵”。所以对于战争而言，你不要认为一个小的国家就好侵略，“祸莫大于轻敌”，对双方皆是如此。战略上藐视敌人，战术上要重视敌人。“祸莫大于轻敌，轻敌几丧吾宝”，轻敌，就把最宝贵的东西也就是“道”丢掉。所以在战争中要冷静理智，要对对方予以重视，在战略上藐视敌人，但是在战术上要重视敌人，不要轻敌。下面这句话基于上面的这个意思就好理解，“故抗兵相加，哀者胜矣。”就是站在正义一方的抵抗的军队、防御的军队，对抗侵略者，处在相持的阶段，双方相持不下、在那较劲的时候，旁边只要有人帮一下，都会起大的作用。可是大家知道问题的决定性作用并不在旁人，没有形成相持的状态谁帮也没用。所以我们说这句话让我们领悟到一个重要的问题，中国人获得这场抗日战争的胜利，根本的原因在于我们中国人自身，而不在于外面力量的援助。斯大林曾经说过，拉开窗帘天是亮，你不拉开窗帘，天也是亮，反正中国人会获胜，应该帮一下。所以这决定的作用不在外部，而在于我们中国自身。讲得最妙的是最后一句话，最后谁获胜呢？“哀者胜矣”，“哀”可不是哀伤的意思。鲁迅先生写的《阿Q正传》中有一句话叫“哀其不幸，怒其不争”，“哀”就是同情。我们中国人从古汉语里面延续了一个习惯，讲话的时候这种使动用法，通俗地说就是被动型用法。比如我们说老头晒太阳，其实是老头被太阳晒。比如大家到陕西来吃的肉夹馍，那是肉夹馍吗？那是肉被馍夹住了。所以这种使动的用法，用这个来理解，这句话就很清楚了，“哀者胜矣”，谁是被同情、被支持的一方，最后获得胜利。“退却，相持，反攻”——惊人的一致。毛泽东从十几岁就开始读《道德经》，我觉得他从这本书里得到的最大的启发就是这种格局上的、战略上的。人站得高了才能看得远，对未来才能有一个正确的这种预测。所以我说第六十九章，大家不要只局限在战争的一个方面，它也可以把我们的智慧得以扩展和延伸，成为一个普遍性的思想与智慧，成为一个普遍性的原则。</t>
@@ -962,10 +964,10 @@
     <t>第七十章</t>
   </si>
   <si>
-    <t>吾言甚易知，甚易行。天下莫能知，莫能行。言有宗，事有君。夫唯无知，是以不我知。知我者希，则我者贵。是以圣人被褐怀玉。</t>
-  </si>
-  <si>
-    <t>我的话很容易被了解，很容易去实行。然而天下之人都不了解，也不按照这个去做。说话得有核心宗旨，做事得掌握事情的关键。正是因为不知道这个道理，所以不了解我。了解我的人很少，按我说的道理去做的人更是难得。所以圣人穿着粗布衣服而怀抱美玉。</t>
+    <t>吾言甚易知，甚易行。天下莫能知，莫能行。言有宗，事有君。夫唯无知，是以不我知。知我者希，则我者贵。是以圣人被（pī）褐（hè）怀玉。</t>
+  </si>
+  <si>
+    <t>我的话很容易被了解，很容易去践行。然而天下之人都不了解，也不按照这个去做。我提出的主张都是有所依据的，我要求做的事情也是有一定根据的。正是因为人们不知道这个道理，所以不了解我。了解我的人太少了，按我说的道理去做的人更是难得。因此圣人虽然怀着美好的才能，却过着贫贱的生活。</t>
   </si>
   <si>
     <t>从第七十章开始，老子强调的重点又发生了改变，他在强调什么呢？他说，我们看问题要“以道观物”，可是有道的人往往为人所误解。老子在书里经常用“吾”这个字，“吾”是人格化的我。“吾”作为一个有道者的代表，一个人格化的有道者的身份，并不一定是指老子本人。第七十章开始就讲人认知的重要性。“吾言甚易知，甚易行。”得道者讲的话，其实很容易被了解，很容易去实行。“天下莫能知，莫能行。”可是结果是什么？这天下的人都是没办法了解，或者说不去了解，也不去按照这个去做。这是一种沉重而深刻的感慨。我们常说道很玄妙，很难把握，而老子在这一章讲，按照道去行事并不难知，不难行，那为什么“莫能知，莫能行”呢？是因为大家根本不愿意去相信它，也不愿意按照它去做，是因为大家认识不到这个事情的重要的意义，认识不到“道”在我们生活中的重要的作用。老子这段话主要是针对领导者、统治者来讲的，老子在对他们讲了很多次之后，发现“万言不值一杯水，犹如东风射马耳”，那些话语仿佛随风而去，并没改变什么。所以，他有此感慨：“莫能知，莫能行”。“言有宗，事有君。”“宗”就是宗旨，说话你得有宗旨，得有核心。“君”是领导控制，做事情也得掌握这个事情的关键。言外之意就是讲，你看我讲的这些话，它是有核心宗旨的。他告诉大家做事怎么样掌握事物的关键，了解事物的本质，把事情做好。“夫唯无知，是以不我知。”可是正因为这些人无知、不了解、不想知道，所以他对我们得道的这些人也就不了解。“知我者希，则我者贵。”了解我的人太少了，懂我的人太少了。我们现在经常有这种感慨，有没有人懂我？其实我们真的了解一个人的精神世界，尤其是了解这些富有大智慧的人的精神世界，不是一件容易的事情。我们中国人经常说一个词叫“知道”，现在大家再说一下这个词，它的分量就不一样，并不是你听到了就叫“知道”，“知”还得去“行”。所以了解我的人太少了，按照我这个去做的人那就更为珍贵了。“是以圣人被褐怀玉”，“褐”，褐色，粗布衣服的颜色。所以得道的人，就像穿着粗布衣服可是身上却怀着珍宝的人一样。得道者讲了很多道理，可是很多人，因为“以貌取人”就是不信。所以，我们经常要透过现象来认识事物的本质，不要以貌取人，不要认为《道德经》里的语言不是那么华丽，就否定其思想与智慧。《道德经》的很多章节都在讲人贵有自知之明。第三十三章“知人者智”，我们真正能够去了解别人，这是一种非常有智慧的表现，可是比这个了解别人更重要的，是我们要了解自己，“自知者明”。人认识最少，却自认为认识最多的知识就是关于自己的知识。因为我们自我的认知，经常被一些假象所迷惑，被情绪所左右，所以“知人者智，自知者明”。其实，老子不仅是感叹“吾言甚易知，甚易行。天下莫能知，莫能行”，他对当时的领导者这种认知的不足及其原因，是有深刻认识的。一千多年后，王阳明提出“知是行之始，行是知之成”，也是这个话题的延伸。</t>
@@ -977,7 +979,7 @@
     <t>知不知，上；不知知，病。夫唯病病，是以不病。圣人不病，以其病病，是以不病。</t>
   </si>
   <si>
-    <t>知道自己有所不知，这是有智慧的；不知道却自以为知道，这就是思想上出了问题。把缺点当作缺点，这样才能没有缺点。得道圣人没有缺点，正是因为他把缺点当作缺点，所以才能没有缺点。</t>
+    <t>知道自己有所不知，这是有智慧的；不知道却自以为知道，这就是思想上出了问题（毛病）。把缺点当作缺点，这样才能没有缺点。得道圣人没有缺点，正是因为他把缺点当作缺点，所以才能没有缺点。</t>
   </si>
   <si>
     <t>第七十章讲“夫唯无知，是以不我知”，由于我们的认识上出了偏差，出了问题，所以没有办法了解有高超智慧的人、得道的，很多的时候，我们也没有办法真正地去了解自己，那么问题出在什么地方呢？这一章在分析问题的原因。我经常开玩笑说，这一章是我见过的中国历史上最有智慧的一段绕口令，比那些相声演员用来练贯口的绕口令更富有思想与智慧。“知不知，上”，我们知道自己不知道，我们知道自己的认识有局限，我们知道自己有缺点需要弥补，这是最有智慧的。后来庄子在《秋水》篇里面把这个意思给大家演绎得非常清楚，而且富有哲理。秋天发大水的时候，河伯就以为自己这个地方就是天下最大的，“以天下之美为尽在己”。后来流到了大海，见到了北海若，发现自己太渺小了。北海若又说，其实我在天下所占的位置，也就是像一粒米那样……这就叫“知不知”，知道自己不知道，那才能够不断地进步。“不知知，病”，不知道，却把它当作知道，也就是不懂装懂，这就是一个思想上的大病。怎么样来让我们病得以痊愈？“夫唯病病，是以不病”，我们知道自己有很多的东西不知道，我们知道这是我们的缺点，我们向别人学习，取长补短，谦逊努力。知道自己“有病”，却不讳疾忌医，这反而是没有病。大家熟悉的是《论语》里边的一句话：“由，诲汝知之乎？知之为知之，不知为不知，是知也。”知道就是知道，不知道就是不知道，坦率承认，不要不懂装懂，这个达到的结果“是知也”。这不是一样的意思吗？“夫唯病病，是以不病。”所以对一个有智慧的人，特别是对于领导者、统治者来讲，周边的人都在说好话，阿谀奉承，这样就经常让自己飘飘然，如果这个时候还能保持清醒的头脑，那就是一个有智慧的好的领导者和统治者。他在这个认知上的表现是什么呢？“圣人不病”，一个有智慧的人在这个方面没有病，没有缺点。为什么说它没有缺点？“以其病病”，因为他知道自己的问题在什么地方，知道哪个地方是自己所不擅长的。就像刘邦一样，虽然不能说刘邦为一位圣人，但是他讲的这段话却可以给很多领导者、统治者以启发：“夫运筹策帷帐之中，决胜于千里之外，吾不如子房。镇国家，抚百姓，给馈饷，不绝粮道，吾不如萧何。连百万之军，战必胜，攻必取，吾不如韩信。此三者，皆人杰也，吾能用之，此吾所以取天下也。”刘邦知道自己的短处，借人之力得以弥补，因为有这种清醒的认识，反而成了一个长项。有人总认为自己什么都可以，哪个地方都是自己水平最高，比如说诸葛亮从来也不听别人的意见，打仗的时候都自己谋划，要不就弄个锦囊远程指挥，像这样的人，很难成为一个优秀的领导者。我们经常讲一个人浑身是铁，能打多少钉，要懂得用人之力，懂得借别人的智慧。现在不是有很多的智库、智囊吗？历史上很多杰出的人，比如像曾国藩，手下有多少谋士啊！很多的问题不是他一个人想出来的，得集众人之力，一个优秀的领导者得知道自己弱项、短板在哪儿。对我们个人来讲，一定要知道，其实我们的认知视野都是非常狭窄的，了解了这一点，我们也就不会把自己当作是一个完人，当作什么都知道，不懂装懂。人有什么不懂的，坦率承认没有什么可丢脸的，即便是圣贤，也有自己认知的局限，可是他们的做法和平常人的不同在哪儿呢？“圣人不病，以其病病，是以不病。”知道自己这方面有弱点、有问题，因此不断学习，不断进步，不断成长。这一章虽然很短，但是意蕴深长，道理深刻。这段绕口令大家既可以当作练表达能力、练嘴皮子的体操，也可以当作思想上的体操，一举而双得，何乐而不为？</t>
@@ -989,7 +991,8 @@
     <t>民不畏威，则大威至。无狎（xiá）其所居，无厌其所生。夫唯不厌，是以不厌。是以圣人自知，不自见（xiàn）；自爱，不自贵。故去彼取此。</t>
   </si>
   <si>
-    <t>人民不畏惧统治者的威严，就会发生大的麻烦。不要让人民住的地方越来越狭小，不让他们的生存受到压迫。不去压迫人民，他们才不会对统治者的行为感到厌烦。所以圣人有自知之明，不自我表现；珍爱自己的生命但不自认为高贵。所以舍弃后者而取前者。</t>
+    <t>百姓不畏惧统治者的威严，暴君就用更大的恐怖政策施加于百
+姓头上。不要让百姓住的地方越来越狭小，不让他们的生存受到压迫。不去压迫百姓，他们才不会对统治者的行为感到厌烦。所以圣人有自知之明，不自我表现；珍爱自己的生命但不自认为高贵。所以圣君抛弃暴君的做法而不去炫耀、抬高自己。</t>
   </si>
   <si>
     <t>七十二章到七十五章，这一部分都出现了一个核心的概念——“民”。在中国历史上有“民本”的思想，我们大家熟悉孟子讲的“民为贵，社稷次之，君为轻”，大家觉得讲得好。但是，在孟子之前，《道德经》已经从哲学的层面把民本思想发展到非常高的程度，而且讲得更为具体。这一章最后一句话讲得非常明白，这两条路摆在这儿了，你应该走哪条路？“故去彼取此。”有哪些路可以选择呢？走哪条路是符合道的呢？我们从头来看。“民不畏威，则大威至。”如果一个国家的人民不害怕统治者、领导者的威严，那么对统治者、领导者来讲，大的麻烦就来了。什么大的麻烦呢？“民无信不立”，领导者在民众中丧失了诚信，就没法统治领导他们了，这不是一种大威吗？所以“无狎其所居”，“狎”通“狭”，也是使动用法。领导者，不要让百姓住的地方越来越狭小，最后都流离失所。因为“无恒产者无恒心”，一个国家如果到处都是流民，它能稳定才怪。“无厌其所生”，“厌”通“压”。不要让他们感觉到生存受到了压迫，不要去压迫他们，不要让他们感觉到厌倦生活，因为哪里有压迫，哪里就有反抗。所以这个“厌”，大家可以把它理解为两个意思，一个就是压迫，一个就是导致的结果感觉到生不如死，厌倦自己的生活。“夫唯不厌，是以不厌。”你不去压迫他们，不让他们感觉到生活的局迫、窘迫、生不如死，他们才不会对你的统治行为、领导行为感觉到厌烦。第六十六章说“处上而民不重，处前而民不害”，处上又重，处前而害，他当然会感觉到这种受压迫的厌烦的感觉。那么，真正有智慧的领导者、统治者应该是什么样呢？“自知，不自见”，自己有自知之明，不是有一点功劳，有一点什么就去自我表现。“自爱，不自贵”，很珍爱自己的生命，珍爱自己名声，自爱自重，但是不自以为高贵。第三十九章最重要的两句话，第一句话就是“贵以贱为本”，不要认为自己身份高贵，没有这个国家的人民，也就是很多人眼中的贱民，哪来你高贵的身份？自爱是对的，因为一个人不爱惜自己的生命，也就不会珍惜别人的生命。第十三章讲过，什么样的人才能把天下寄托给他呢？“贵以身为天下”、“爱以身为天下”。所以好的领导者对自己的生命非常珍视，但是为了天下的使命，可以奉献自己的生命，这样的人我们才能把天下寄托给他。“故去彼取此”，取的是什么呢？取的是自知自爱；去的是什么？去的是自见、自贵。</t>
@@ -998,10 +1001,10 @@
     <t>第七十三章</t>
   </si>
   <si>
-    <t>勇于敢则杀，勇于不敢则活。此两者，或利或害。天之所恶，孰知其故？是以圣人犹难之。天之道，不争而善胜，不言而善应，不召而自来，繟然而善谋。天网恢恢，疏而不失。</t>
-  </si>
-  <si>
-    <t>勇于表现坚强的人就会不得善终，勇于表现柔弱的人可以保存生命。这两种“勇”，有的获利，有的遭害。天所厌恶的，谁知道其中的原因呢？所以圣人也认为这非常困难。天之道，不争而善于得胜，不发布命令、政令而能得到好的响应，不强行去征召而大家自行来到，坦然从容而善于谋划。天网虽然稀疏，但不会遗漏。</t>
+    <t>勇于敢则杀，勇于不敢则活。此两者，或利或害。天之所恶（wù），孰知其故？是以圣人犹难之。天之道，不争而善胜，不言而善应，不召而自来，繟（chǎn）然而善谋。天网恢恢，疏而不失。</t>
+  </si>
+  <si>
+    <t>勇于表现坚强的人就会不得善终，勇于表现柔弱的人可以保存生命。这两种“勇”（努力），有的使人得益，有的使人受害。上天厌恶一些品行，谁能知道它讨厌这些品行的原因是什么呢？所以连圣人也认为难以回答这个问题。天之道（大自然的运行规律），不争而善于得胜，不发布命令、政令而能得到好的响应，不强行去征召而大家自行来到，坦然从容而善于谋划。天网虽然稀疏（大自然的规律就像一张广大无边的网一样），但不会遗漏（网孔看似稀疏却从不遗漏任何东西）。</t>
   </si>
   <si>
     <t>这一章首先谈的话题是“勇敢”。关于“勇敢”，《道德经》并不像我们一般认识那么简单，表达那么直白，它把“勇敢”分为“勇敢”和“勇于不敢”，这个说法的妙处我们后边再做解说。接着读这一章，大家会发现熟悉的语句“天网恢恢，疏而不漏”，其原文就出自第七十三章“天网恢恢，疏而不失”。我们中国人读失去的“失”啊，总觉得有点绕口，换了一个字，意思都是一模一样的。天网恢恢，疏而不漏，天道如此。庄子也讲过这样一段话，一个人做了亏心事之后，在客观世界上把有形的痕迹抹掉容易，可是抹不掉内心的痕迹。即便是不受客观世界的惩罚，也得受良知的惩罚。那么第七十三章的结尾，怎么得出“天网恢恢，失而不漏”的结论呢？是怎么过渡到“天网”、“天道”的呢？“勇于敢则杀”，毛泽东在《贺新郎·读史》这首词里面就讲：“铜铁炉中翻火焰，为问何时猜得？不过几千寒热。人世难逢开口笑，上疆场彼此弯弓月。流遍了，郊原血。”人类的历史都是在这种血与火的洗礼中前进的，老子在他那个时代，肯定也看到过这种情况。“勇于敢则杀”，也包括很多违背了国家法律法令的不法之徒，从直观地来看，也是属于勇敢，“勇于敢则杀”。“勇于不敢则活”，“勇于不敢”直观上看上去，我们把它叫做“懦弱”、“退缩”，但其实这样的“懦弱和退缩”还有另外的一类人，他们懂得保护自己的生命，以期谋得更大的成就与发展。其实，我们说懂得拒绝的人也是一种“勇于不敢”，有些该做的事情，勇敢去做；有些不该做的事情，勇于不敢，拒绝。老子接着说，“此两者，或利或害。”“此两者”指勇敢和勇于不敢。勇敢和勇于不敢这两种情况“或利或害”，就是说有时有利，有时有害，那到底何时有利，何时有害呢？谁能把握这个度呢？“天之所恶，孰知其故？”天呢，到底是喜欢还是厌恶？到底是怎么一回事？谁能够了解这里边的最根本的原因、缘故呢？“是以圣人犹难之”，就是再有智慧的人、有智慧的领导者，在这个方面也难以去理解清楚。所以你看这个认知啊，非常困难，到底是该杀还是该活，到底该怎么对待，这是一个非常难的选择。那老子是不是就放弃了对这个难题的解决呢？不是的，事实上，老子是认为，只有站在更高的视野才能解决这个困扰，也就是第四章说的“解其纷”。所以老子在下边就说，如果从天道的角度来认知这个事情是什么样呢？“天之道，不争而善胜”，不争斗，却能够获得胜利，这是符合天道的。“不言而善应”，要行不言之教，不是老去命令、政令，大家对他反而非常支持，非常响应。言教不如身教，“不召而自来”，大家自然而然就聚拢到你的麾下，这是符合天道的。“繟然而善谋”，“繟”就是坦然、从容。天道看不出来痕迹，从从容容地向那个方向发展，就像一个善于谋划的人一样，不露痕迹地谋划。所以后面就讲“天网恢恢，疏而不失”，天网虽然好像有很多疏漏，但是最后你会发现，这天道如此，天网恢恢，疏而不漏。我们中国人经常把这个讲做“人在做天在看”、“为人别做亏心事，古往今来放过谁。”到这里，逻辑就逐渐清晰了：天道不争，不强制，自然而然，所以为民，不能滥用所谓勇敢；为王，也不能滥用强制，这都是不符合天道的，不符合天道，则是必然要失败的，也就是讲“天网恢恢，疏而不失”。所有违逆天道的所谓“勇敢”最后都会受到惩罚，天网虽然好像有很多疏漏，但是最后你会发现，这天道如此，天网恢恢，疏而不漏。关于这一点，我们再引证下孔子这句话：“人之生也直，罔之生也幸而免”，就更清楚了。意思就是那些不正直的勇于敢者、对抗天道天理的人，也许会侥幸漏掉一时，但终究逃不脱天道天理的惩罚。孔子的真正意义在于，若靠侥幸活着，你是活不好的。而老子对于敢对抗天道天理的人、与天争胜的人，警告更为严厉：“天网恢恢，疏而不漏。”换句话说就是“人在做天在看”、“为人别做亏心事，古往今来放过谁。</t>
@@ -1025,7 +1028,7 @@
     <t>民之饥，以其上食税之多，是以饥。民之难治，以其上之有为，是以难治。民之轻死，以其求生之厚，是以轻死。夫唯无以生为者，是贤于贵生。</t>
   </si>
   <si>
-    <t>人民之所以饥饿，是因为统治者收取挥霍的税负太多，所以人民饥饿。人民之所以难以治理，是因为统治者总是胡为、妄为，所以人民难以治理。人民之所以不怕死，是因为统治者所求奉养过多，所以人民不怕死。不把自己生命看得绝对重要的，不搜刮剥夺人民以奉养自己生命的，才是胜过了贵养厚养自己生命的人。</t>
+    <t>人民之所以饥饿，是因为统治者收取挥霍的税负太多，所以人民饥饿。人民之所以难以治理，是因为统治者总是胡为、妄为，所以人民难以治理。人民之所以不怕死，是因为统治者所求奉养过多，所以人民不怕死。不把自己生命看得绝对重要的，不搜刮剥夺人民以奉养自己生命的，胜过那些过分重视自我生命的统治者。</t>
   </si>
   <si>
     <t>这一章的核心话题还是“民”，解释了三个问题。第一，百姓为什么饥寒交迫；第二，百姓为什么难以治理；第三百姓为什么不怕死。解释完三个内容，然后对领导者、统治者提出要求。“民之饥，以其上食税之多”，百姓为什么饥寒交迫？“上”，上面的领导者、统治者，“食税”，收的税太多了，而且收的税都被这些人挥霍。“民之难治，以其上之有为”，百姓为什么难以治理呢？原因不在他们这儿，是因为上边胡来、瞎折腾。在《道德经》里，“有为”这个词就是妄为，胡折腾，上边老瞎折腾，就把民心折腾乱了。“信不足焉，有不信焉”，折腾得多了，讲的话也不诚信了，也失去百姓的信任，说什么都没用了。“是以难治”，“是”，“这是”的意思。这话讲得就比较理性，你老说他们是刁民，老在他们身上找，其实这原因就在自己的“有为”。老子对坐在对面的那些领导者、统治者就讲，你得找到真正的原因，百姓为什么饥寒交迫？你们收税收得太多了，收的税都被挥霍了。百姓为什么难以治理？你们整天瞎折腾，胡来妄为，把民心搞乱了。“民之轻死，以其求生之厚”。“其”指谁？领导者、统治者。百姓为什么轻死，把死不当一回事？是因为你们这些统治者，把自己的生命看得那么重要，不惜用剥夺的方式积累财富，花天酒地，穷奢极欲，这财富都聚积在他们自己手里，老百姓难以生存。就像国民党时期，财富都积累在“四大家族”手中，很少的人占有了绝大部分的财富，底下的人都生活在水深火热之中。当你“求生之厚”的时候，底下的百姓就觉得没什么活路和希望了，也就不把死当一回事，“是以轻死”。那么应该怎么做呢？“夫唯无以生为者”，不要把自己的生命看作是绝对重要的。不要把财富、好吃的好用的，全都集中在自己这儿来，认为只有自己的生命才是生命，对别人的生命、生存视而不见，感到无足轻重。不把聚敛、穷奢极欲当作生命的重要的部分，这个就是“贤于贵生”。百姓为什么饥寒交迫？上食税之多；为什么难以治理？上面胡来妄为；为什么不怕死？求生之厚。这章三个并列句，像诗一样的语言，讲得又非常深刻、非常理性。把七十五章和七十四章结合起来理解，我们就能发现，老先生苦口婆心地劝坐在对面的那些领导者、统治者：你们要对自己国家的人民好一点，否则啊，他们日子过不好，你们的日子也不安稳，你们只靠这种高压的政策，这不是解决问题的根本的方法。我们完全可以说在这几章里看到了《道德经》的“真实面目”，很多话是针对那些统治者讲的，苦口婆心地劝他们，应该怎么样对待这个国家的人民，才能使国家长久地、持续地发展。</t>
@@ -1034,10 +1037,10 @@
     <t>第七十六章</t>
   </si>
   <si>
-    <t>人之生也柔弱，其死也坚强。万物草木之生也柔脆，其死也枯槁。故坚强者死之徒，柔弱者生之徒。是以兵强则不胜，木强则折（shé）。强大处下，柔弱处上。</t>
-  </si>
-  <si>
-    <t>人活着的时候身体柔软，死之后身体便会僵硬。万物草木活着的时候形质柔软，死后变得干枯。所以坚强的东西属于死的那一类，柔弱的东西属于生的那一类。所以穷兵黩武一定会遭受灭亡，树木坚硬就会一折就断。总认为自己强大的、夸耀自己强大的，反而会处在下面；懂得柔弱、谦逊的，反而会居于上面。</t>
+    <t>人之生也柔弱，其死也坚强。万物草木之生也柔脆，其死也枯槁（gǎo）。故坚强者死之徒，柔弱者生之徒。是以兵强则不胜，木强则折（shé）。强大处下，柔弱处上。</t>
+  </si>
+  <si>
+    <t>人活着的时候身体柔软，死之后身体便会僵硬。万物草木活着的时候形质柔软，死后变得干枯。所以坚强的东西属于死的那一类（追求刚强是条死路），柔弱的东西属于生的那一类（保持柔弱是条生路）。因此兵力强大了就会灭亡，树木坚硬就会一折就断。总认为自己强大的、夸耀自己强大的，反而会处在下面；懂得柔弱、谦逊的，反而会居于上面。</t>
   </si>
   <si>
     <t>现在我们来说一下第七十六章，王弼本子的编辑是有着内在逻辑的。前两章，老先生劝统治者，不要用这种“强”的方式、镇压的方式来实施自己的统治，那么应该怎么做呢？要懂得以柔克刚、强大处下，这样才能形成一种和谐。有的人确实是没有认真地读这本书的原文，他们认为《道德经》是一个弱者斗争的哲学，这是不了解坐在老子对面的向他提问的那些人，他们并不是一般的平民，而是手握权力的领导者、统治者。要站在这个层面来理解第七十六章，知道他这些话是对是对那些认为自己自身或者自己国家很强大的统治者们讲的。老子劝他们用“柔弱”的方式来实施自己的统治，这个是非常有智慧的，这个非常能够体现老先生的慈悲仁爱之心。这一章强调两个字“柔弱”，所以一开始讲“人之生也柔弱”，最后强调“强大处下，柔弱处上”。“人之生也柔弱，其死也坚强。”人活着的时候是什么状态？柔韧性非常好。我们看跳舞的、练杂技的，就觉得这柔韧性好。柔弱柔软，这是生命昂扬、鲜活的状态。而人死的时候是什么样的一种情况呢？硬了、僵了，“其死也坚强”。老子首先拿人的生命的状态来说明柔弱具有的意义。如果这个问题大家觉得还没有理解到位，再换一个角度来理解。在苏州金鸡湖苏州新区里曾经出现过一尊老子的雕像，这尊雕像太丑陋了，老子张着嘴，吐着舌头，一颗门牙。很多人很不理解，心里想有大智慧的老子，怎么会是这样的形象，还有人打趣说，这个老子是来卖萌的……这个雕塑者姓田，他就站出来解释说，我这个雕塑叫“刚柔”，它的出处是说，当时孔子见老子的时候，老子没有给他多说什么，张开嘴巴让孔子看了看。孔子一看就明白了，老子当时已经都七十多岁了，牙早掉光了，但是舌头还在，讲的就是“柔弱更长久”的意思。雕塑者说“刚柔”倒没错，但是这段话不是出自正史，记载的也不是指孔子和老子之间的事，其实是当年老子毕业的时候，跟自己的老师讲的。您有什么送给我？老师也没说话，张开嘴巴给他看了看，老子就看明白了，老师年纪大了，牙掉光了，但舌头还在。牙齿是坚硬之物，到一定年龄就掉了，舌头没事，柔软更长久。所以，柔弱更有生命力、更长久，柔弱是生命的状态，而强硬、僵硬是死亡的状态。这是第一个，拿人来做比方。第二个以草木为例，“其生也柔脆，其死也枯槁。”我们以草为例，李世民在诗里说“疾风知劲草”。草，风往这边吹了，它这边倒，往那边吹了，往那边倒，风走了，它再站起来坚守脚下这片土地。什么时候草坚定了，不随风倒了，那草就死了、枯了。正因为草很柔弱，所以它能迎风起舞；正因为草很柔弱，所以“天涯何处无芳草”。下面得出结论，“坚强者死之徒”，“徒”就是那一类。认为自己坚强、强硬、强暴，其实这是属于走向死亡一类的。而“柔弱者生之徒”，柔软、柔韧，这是富有生命力的表现。沿着这个方向再往下推，就说到了人类社会，“兵强则不胜”，一个国家穷兵黩武，认为自己的军事力量强大，稍一不如意就动用军队发起战争，“国虽大，好战必亡。”“兵强则不胜”，不是说你这场战役打不胜，但穷兵黩武的最后结果一定是失败的。历史上多少强大的帝国，比如说秦朝，被称为“虎狼之师”，最后的结果怎么样？“兵强则不胜”“木强则折”，这个“强”就是僵硬。春天，万物复苏，一根细小的柳枝也很有韧性，很难去折断它。秋天，柳枝水分干枯，好像很强硬地挺在那里，可是它内在枯槁了，一折就断。小的时候，我在石厂里边劳动，砸石子做铺路之用。那时候我就见了一个非常奇怪的现象，石场里石匠用的榔头把儿，一种是很粗大的木棒，看着很稳定；一种是很细的木棒，看起来很危险。我去问那个石匠，怎么用这么细的斧柄？他说这个东西叫“水曲柳”，你别看它细，但它韧性非常好，你用多大劲儿也没事儿。所以每当读到这个地方，我就想起这个事情。“木强则折”，看似强大僵硬，其实没有了韧性，它就没有了生命力，一碰就断掉了。讲完这个了，再看这里边两层的推论。第一层推论：“坚强者死之徒，柔弱者生之徒”，然后推到人类社会，表达他对用这种强横的方式予以统治、用这种强横的方式予以领导的不认同，指出这个方式的致命的弱点。战争中也是如此，“兵强则不胜”，就像“木强则折”一样。讲完这个，推论到第二层：“强大处下”，老是炫耀自己强大，去任意地凌辱别的小的国家；自己有了高的位置，可以盛气颐指，不符合道，这是向死亡方向去发展。“强大处下，柔弱处上。”懂得以柔克刚，懂得以退为进，懂得谦逊谦让，这才是符合道的，才是真正有智慧的表现。第六十一章，“天下之牝，牝常以静胜牡”，讲以静制动、以柔克刚的道理。所以对人生来讲，强大、用强，这事儿大家都知道，也并不是说老子对这个东西一味排斥，因为人生有的时候强也是需要的，但是大家都把这个事情推到极端了，认为“强”是解决问题唯一的方式，所以，老先生在面对那些领导者、统治者的时候，苦口婆心，形象具体地讲述柔弱处下的道理。我们现在读这一章，也可以把智慧扩大到我们的为人处事，不要只认为用强才能解决问题，要懂得强弱两者的相辅相成，老去逞强，不是真正智慧的做法，这是只是智慧的一个方面，而“以柔克刚”才是一种真正高级的智慧。适当的时候，我们要懂得示弱，这是我们在和社会、和别人打交道的时候，非常重要的智慧，有重要的启迪。</t>
@@ -1046,10 +1049,10 @@
     <t>第七十七章</t>
   </si>
   <si>
-    <t>天之道，其犹张弓与？高者抑之，下者举之；有余者损之，不足者补之。天之道，损有余而补不足。人之道则不然，损不足以奉有余。孰能有余以奉天下？唯有道者。是以圣人为而不恃，功成而不处，其不欲见贤。</t>
-  </si>
-  <si>
-    <t>天的规则，不就像拉弓射箭一样吗？瞄得高了就往下压，瞄得低了就往上抬；有多余的就减少，不足的就给补充。天的规则，减损有余的来补充不足的。人类社会的规则不是这样，减损不足的来供奉有余的。谁能让那些有余的人奉献出来为天下做贡献？只有得道的人。所以圣人把事情做成而不把这当成一种倚仗、凭借甚至勒索的手段，有了功劳却不居功自傲，不想表现自己的贤能。</t>
+    <t>天之道，其犹张弓与？高者抑之，下者举之；有余者损之，不足者补之。天之道，损有余而补不足。人之道则不然，损不足以奉有余。孰能有余以奉天下？唯有道者。是以圣人为而不恃（shì），功成而不处，其不欲见（xiàn）贤。</t>
+  </si>
+  <si>
+    <t>大自然的运行规律，不就像拉弓射箭一样吗？瞄得高了就往下压，瞄得低了就往上抬；有多余的就减少，不足的就给补充。大自然的运行规律，是减损有余的来补充不足的。人类社会的规则却不是这样，减损不足的来供奉有余的。谁能够把多余的财富奉献给天下人？只有懂得大道的人才能如此。因此圣人帮助了万物而不求它们回报，有了功劳却不居功自傲，他们不愿表现自己的恩德和才能。</t>
   </si>
   <si>
     <t>第七十七章，这一章重要在什么地方呢？大家都知道“马太效应”，马太效应出自《圣经·马太福音》，直观的解释是穷者越穷，富者越富，越穷越倒霉，越富反而财富滚滚而来，这也是我们人类社会大家都认同的一个普遍的现象。怎么解决这个问题呢？怎么样解决这样的一种贫富的两极分化呢？《道德经》很早就给出了一个方案，所以我们把这一章叫什么呢？叫“张弓效应”。在这一章里边我们可以看到一句话，这句话和马太效应讲的意思是一样的，叫“损不足以奉有余”。“天之道，其犹张弓与？”老子在这一章里面就讲，说天道就像拉弓射箭一样，拉弓射箭要有的放矢。这个箭，你瞄得高了，往下压一下；低了，往起抬一下，“高者抑之，下者举之”。沿着这样的一个比喻，自然就得出这个结论，对于人类社会也是这样，“有余者损之，不足者补之”。财富多的人应该拿出更多帮助这些不足的人，收入高的人当然应该多交税。这就是“天道”，天道如此，天道均衡，“天之道，损有余而补不足”。可是人道，这个社会是怎么做的呢？“人之道则不然”，老子对他当时的情况看得很清楚，财富都掌握在少数人的手里，“损不足以奉有余”，越是不足的、穷的，反而被压榨得越厉害，富的反而越来越富。于是，老子面对那些统治者讲，一个好的领导者、统治者应该向“圣人”的方面去发展，做一个好王。大家注意古代那个“圣”的写法，王上边并列两个字，耳和口，听得进别人的意见，说话温暖。通达事理的王，称之为圣。老子就对他们讲，你们应该向这个方面努力，怎么做呢？“有余以奉天下”，让那些更富的人来为这个天下做贡献。“唯有道者”，就是了解道的人，按照道的方式去行事的人，才能做到这一点。说到这儿，我就得给大家说一下我们的文化背景。一句话大家都熟，叫“不患寡而患不均”，贫富不均，很容易产生问题。历史上那些农民起义，他们用的口号，你也能感觉到这一点，比如说王小波、李顺，“均贫富等贵贱”；比如说黄巢，“冲天平均大将军”……从社会心理能分析到这一点。所以老先生就讲，统治者、领导者，什么样的人才能够真正注意到、做到让贫穷的得以扶持，让富有的贡献更多呢？“唯有道者”，“是以圣人”。“是以圣人为而不恃，功成而不处，其不欲见贤。”一个好的领导者，“为而不恃”，他把这件事情做了，有作为了，却不把这个当作一种倚仗、凭借甚至勒索的手段。“功成而不处”，不居功自傲，“不欲见贤”，不想表现出自己的这种贤能贤明。这是有道者的表现，懂得让天下向共同富裕的方面发展，让那些先富起来的人懂得奉养天下，哪怕是把这些做成了，也不居功自傲，因为他们知道，这只是按照道的方式来做的。</t>
@@ -1061,7 +1064,7 @@
     <t>天下莫柔弱于水，而攻坚强者莫之能胜，其无以易之。弱之胜强，柔之胜刚，天下莫不知，莫能行。是以圣人云：受国之垢（gòu），是谓社稷（jì）主；受国不祥，是为天下王。正言若反。</t>
   </si>
   <si>
-    <t>天下没有比水更柔弱的了，但攻克坚强的东西却没有能胜过它的，没有什么东西可以代替水。柔弱胜过刚强的道理，天下都知道，但不能真正做到。所以圣人说：能忍受全国的屈辱，才能做社稷的君主；能承受全国的灾难，才能成为天下的君王。符合正道的话都好像反话一样。</t>
+    <t>天下没有比水更柔弱的了，然而摧毁坚固物体的力量没有能够超过它的，没有什么东西可以代替水。柔弱胜过刚强的道理，天下都知道，但不能真正做到。所以圣人说：能忍受全国的屈辱，才能做社稷的君主；能承受全国的灾难，才能成为天下的君王。符合正道的话听起来都好像反话一样。</t>
   </si>
   <si>
     <t>第七十八章体现了这本书里的一个非常重要的理念，“善于处下”。这些内容我们之前都有过接触，甚至直接引用七十八章做过讲解，所以这一章我们并不需要花费太多的时间来解释，大家也能够明了。“天下莫柔弱于水，而攻坚强者莫之能胜”，天下没有什么东西比水更柔弱了，你拿什么容器装，它就是什么样，随方就圆。但天下也没有什么东西比水的力量更强大了，攻无不克，战无不胜。水就是以柔克刚、以弱胜强的最好的形象的代表。“以其无以易之”，因为没有什么东西能够替代水，天下最柔弱的东西，它力量又最为强大，最能够体现柔弱胜刚强的道理。“弱之胜强，柔之胜刚，天下莫不知，莫能行。”天下都知道，这东西表面上看似柔弱，但发挥作用的时候力量太强大了，但是真的要这样却非常不容易，为什么？人都有脾气，“柔弱胜刚强”得懂得忍耐、等待，忍耐是我们人最难练的一种功夫。水滴锲而不舍方能穿石，一条溪流不舍昼夜，慢慢积累，等待时机，才能发挥大用。“柔弱胜刚强”也是需要条件的，只是老子没有明说。“是以圣人云”，我再给大家强调一下，在老子心里，以前有很多好的统治者、有智慧的领导者，他称其为“圣人”，让大家向他们学习。我们在前面谈到过，他的很多话并不是原创的，是他引用的以前的圣人的，下边这话就表达得非常明确，所以这些圣人讲，“受国之垢”“受国不祥”。这两句话就是《道德经》里边从头至尾强调的，就是我们经常讲的善于处下。古往今来，夺得天下的表面看是一家一姓，实际上不都是一个团队吗？用我们现在的话讲是一个党派。什么样的团队，什么样的党派才能夺得天下，并且坐得了江山呢？之前，我们在第八章讲“处众人之所恶”时，也拿这个地方作为印证。吃苦在前，享受在后，有困难还得担着，有错误勇于改正，这不就是“受国之垢”“受国不祥”吗？所以真正想要夺得天下，坐稳江山，也就是所谓“处其上”，首先要懂得“处其下”，要“受国之垢”，要能忍受别人忍受不了的艰难困苦，要能承受别人承受不了的屈辱诟骂，这样才能成为江山社稷的主人。“受国不祥，是为天下王。”有灾难有困难，你别跑，要挺身而出，勇于担当，有错误要勇于承认，勇于改正。毛泽东把共产党的宗旨概括为五个字，叫“为人民服务”。两千多年前的“受国之垢”，“受国不祥”，“处众人之所恶”，两千多年后的“为人民服务”，这本质上的意思不是一样的吗？这就是《道德经》里面从头强调的，也是古往今来的大道。我们在讲第十四章的时候说过一句话，“执古之道以御今之有”。了解古往今来的大道，我们才能更好地做好今天的事情。读到这儿大家就会发现，这《道德经》里边蕴含着古往今来的大道，蕴含着一个人、一个团队、一个党派成功的最深的密码，值得大家认真地品味。总结上面这个表达的方式叫什么呢？叫“正言若反”，也就是第四十章讲的“反者，道之动”。看着是讲反话，大家都不愿意去做的事情：“受国之垢”，“受国之不祥”，“处众人之所恶”，可实际上，这才是能够让我们“处上”、取得成功的真正的智慧与奥妙。看似好像说的反话，其实深刻的道理就在这里边。</t>
@@ -1070,10 +1073,10 @@
     <t>第七十九章</t>
   </si>
   <si>
-    <t>和大怨，必有余怨，安可以为善？是以圣人执左契，而不责于人。有德司契，无德司彻。天道无亲，常与善人。</t>
-  </si>
-  <si>
-    <t>调和了大的矛盾，也必定会有遗留的怨恨，这怎么能是妥善的方法呢？所以圣人收执借据却不苛责别人偿还。有德的人就像执左契而不责于人的，无德的人就像掌管税收的人那样严苛残酷。天道没有偏私，规律给予善于此道的人。</t>
+    <t>和大怨，必有余怨，安可以为善？是以圣人执左契（qì），而不责于人。有德司契，无德司彻。天道无亲，常与善人。</t>
+  </si>
+  <si>
+    <t>即使调和了大的矛盾，也必定会有遗留的怨恨，这怎么能算是尽善尽美呢？因此圣人即使握有讨债的契约，也不向人索取欠债。具有高尚品德的人就像握有契约而不向人索取债务的圣人一样宽容，没有高尚品德的人就像主管收税的税务官员一样苛刻。大道对谁也不偏爱，它总是帮助那些按照大道办事的好人。</t>
   </si>
   <si>
     <t>针对坐在对面的那些统治者、领导者，老子前面一直在讲，不要用高压的方式，要懂得用柔和的方式。如果一直用高压的方式，一直用“损不足以奉有余”的方式，这社会就积累了大的矛盾。老先生认为，有了这个矛盾之后，不管用什么方式解决，它都会遗留下很多的不满、埋怨、祸端。在这个基础上，我们才能够深入理解第七十九章的内容。这一章只有这么几句话，但道理非常丰富而深刻。“和大怨，必有余怨，安可以为善？”如果社会已经积累了大量的矛盾，即使用调和的方式，“和大怨”，可是，依旧会留下很多的这个埋怨、祸端。“安可以为善”？即使用和谐的方式，也不是一种善举，为什么呢？第六十四章讲“为之于未有，治之于未乱”，从一开始你就不应该让这社会积累了这么多的矛盾。我们之前举过晏子“救灾”的例子，其实针对我们目前的环境问题，也是一样。大家知道有一句话叫“反对先污染后治理”，你污染完了，你再治理，其难度之大，难以预料。“病来如山倒，病去如抽丝”，社会不也一样吗？积累了这么多复杂的矛盾，你老用调和的方式，你说现在已经柔和了、缓和了，但留下那么多的祸端，这当然不算是好的方法，不可以叫做善举。对应我们人际交往也是一样，我们不要本着“无所谓”的态度，想着跟别人、朋友之间有了裂痕，我们说以后自会解决的，事情往往没有我们想得那么简单。所以，平时做事就要小心，朋友之间要珍惜，家庭之间感情要珍惜，别真的等得了埋怨之后，再想办法去解决。这跟钉子钉在墙上一样，你拔出了钉子，那个眼还在。最好的“善”是什么？提前做出预防，“为之于未有，治之于未乱。”“是以圣人执左契，而不责于人。”有智慧的领导者、统治者，就像拿着契约的人。“左契”，契约，一撕两半，左边一个，右边一个，左边那个是借据。拿着这个契约借据而不责于人，不是天天去追着要，而是表达出圣人的一种宽容。老先生拿这个举例子，意思说，一个好的领导者，哪怕是你对大家都有恩德，对天下都有恩德，你别以为大家都欠你的，“不责于人”。所以“有德司契，无德司彻”，有德的人就像执左契而不责于人的人。“彻”，就是税官，收税的。这是代表着两种态度，一种是和缓的态度，另一种是苛刻的残酷的态度。所以平日里，应该像“有德司契”的样子，那就不会积累那么多的埋怨。反之如果像那个税官一样，苛捐杂税多，还步步紧逼，不肯放松，老子认为这是无德的表现，这样会留下大怨！下面两句话很容易引起误解，“天道无亲，常与善人。”在第五章曾经讲过，“天地不仁，以万物为刍狗”，天地是没有感情的，它并不因为你做了好事，就来奖赏你，也不因为你做了坏事，便来惩罚你。既然“天道无亲”，那为什么“常与善人”呢？又怎么把这个规律规则让那些善人能够理解，并按照它去做呢？这个事情我换一个角度让大家来理解，美国有一个报社的主编，他经常接到读者的来信，读者来信都反映一个什么问题呢？做好事不得好报。特别是其中有一个小孩就说，我弟弟什么都不干，我天天在家里干活那么勤奋，可是我妈妈就把好的东西都给我弟弟，就是喜欢他，这不是不公平吗？上帝在哪里？上帝怎么能够这么不公平？这个主编呢，一直不知道怎么解释这个问题。后来有一次，他参加了一个婚礼，新郎新娘互戴戒指，出现问题了，两人把戒指戴错手了，本来应该戴到左手，但都戴到了右手上。主持婚礼的牧师就用一种诙谐的方式说，右手已经够完美了，不用再修饰了，还是用戒指来装扮左手吧。这个主编就在那个时候领悟到一个道理：一个已经够好的人，你不用去奖励他，他已经够完美，最大的奖励是什么？就是他已经成为一个好人。天道对好人最大的奖赏是什么？放到西方的文化里边来讲，上帝对好人最大的奖赏是什么？就是让你成为一个好人，这已经就是最大的回报了。这里讲“天道无亲”，它是说天道是公平的，没有偏私的。让一个人成为一个好人，那么一个好人吃点亏，这是正常的，因为你作为一个好人，这已经就是最大“道”给你的回报了。天道是公平的，没有亲疏之分，但是，它把规律、规则赋予了那些做善事的人。做一个好人，我们免去了很多的祸端祸殃，成为一个好人——这就是对我们做好人的最大的回报，不需要其他的东西来“修饰”了。所以用“有德司契”的境界去管理、去治国，就不会有大怨；用“有德司契”的境界去为人、去处事，会让你成为一个“好人”，“福虽未至，祸已远离”。</t>
@@ -1082,10 +1085,10 @@
     <t>第八十章</t>
   </si>
   <si>
-    <t>小国寡民，使有什伯之器而不用，使民重死而不远徙。虽有舟舆，无所乘之；虽有甲兵，无所陈之；使人复结绳而用之。甘其食，美其服，安其居，乐其俗。邻国相望，鸡犬之声相闻，民至老死不相往来。</t>
-  </si>
-  <si>
-    <t>（理想的国家是这样的：）国土小且百姓少，就算有十倍百倍于人力的工具器械也不实用，让人民都看重死亡而不远离故乡。即使有船有车，也没有人去乘坐；即使有盔甲兵器，也没有机会陈列；使人民回归到结绳记事的淳朴状态。觉得自己的食物是香甜的，觉得自己的衣服是很美的，安于自己的居所，乐于自己的风俗习惯。邻国可以相互望见，鸡鸣狗叫之声可以相互听见，人民至死也不来往。</t>
+    <t>小国寡民，使有什伯之器而不用，使民重死而不远徙。虽有舟舆（yú），无所乘之；虽有甲兵，无所陈之；使人复结绳而用之。甘其食，美其服，安其居，乐其俗。邻国相望，鸡犬之声相闻，民至老死，不相往来。</t>
+  </si>
+  <si>
+    <t>（理想的国家是这样的：）国土小且百姓少，就算有十倍百倍于人力的工具器械也不使用，让人民都看重死亡而不远离故乡。即使有船有车，也没有人去乘坐；即使有盔甲兵器，也没有机会陈列；使人民回归到结绳记事的淳朴状态。人民觉得自己的食物是香甜的，觉得自己的衣服是很舒适的，安于自己的居所，乐于自己的风俗习惯。邻国可以相互望见，鸡鸣狗叫之声可以相互听见，而人们直到老死，也不相往来。</t>
   </si>
   <si>
     <t>第八十章历来被认为是老子思想中的一个非常重要的部分——老子的理想国。大家一听都知道，在哲学上，柏拉图有《理想国》，后来就出现了康帕内拉的《太阳城》、莫尔的《乌托邦》，就是对理想社会的设定。哲学家设定理想社会都有一个非常有趣的现象：要了解人类的未来啊，先看人类的开始。因为哲学里边讲否定之否定的规律，就讲事物到最后都回归到出发点，严格地讲叫“仿佛回到出发点的运动”，是在更高的层次上重复第一阶段的某些特征，所以我们看看人类的开始。人类开始的时候，大家是平等的，所以未来人类社会的也是平等的。你看三个阶段：平等——不平等——平等。沿着这样一种哲学思路，我们来理解老子这个小国寡民，也就知道，这也是他的一种空想，但是，这种空想代表了他理想的寄托。他理想的这个国家是什么样子？别天天老打仗，别弄那么多人，大家不要经常地过多地交往，过多交往就会产生的矛盾、冲突、隔阂、战争，他想让大家和平地和谐相处，所以要把这个国家变成一个“村”。“小国寡民”，让这个国家变小，人民变少，大家就像在一个乡村里边生活。在小国寡民的理念下，他就要限定，要这样做，即使有各种器皿也不用，为什么不用呢？因为在中国的历史上有一个说法，其实和西方后来的一些思想也遥相呼应。西方有一个哲学家叫卢梭，法国的启蒙思想家，当年给法国的自然科学院写过一篇论文，获了奖，叫《科学和技术的进步使人类道德堕落》，在中国历史上也有很多人认可这种看法。庄子文章里就讲了一件关于“抱瓮老人”的事：说一次孔子带着学生去游学，子贡就看见一个老头，有这个先进的工具不用，抱着瓦罐去井里打水。当时的先进的工具是什么呢？就是辘轳，现在大家都看不见了。自己跑到井里边抱着瓦罐去打水，子贡就觉得很奇怪：这老先生怎么这么笨，辘轳就在旁边，摇一摇不就上来了吗？你自己下去干嘛呢？老先生就郑重其事地跟他讲，我的老师讲过，人如果使用机器就会有投机取巧之心，为了保持我的朴素的道德，所以我不用这个机器，不会有投机取巧之心。大家仔细思量，我们使用的工具，确实对我们的思维的方式、性格也有很大的影响，所以《道德经》讲什伯之器，不用，用最简单的工具，保持简单的心灵，保持朴素的品德。当年曾国藩在做官的时候，经常给家里边写信，告诉他儿子，你每天得下地劳动；告诉他女儿，你得给我做鞋。其实，曾国藩在乎的不是地，不是鞋子，他是觉得这样的方式，会让子女形成他要的那种性格、品德。这个东西倒是真值得研究，人类使用的工具在不断进步，千奇百怪，人要想回归到朴素的道德，就很困难。“使民重死而不远徙”，人离开家乡之后成为流民，那么很多方面就无法保证。我们前面也讲过，这国家到处都是流民，它无法稳定，因为“无恒产者无恒心”，所以你离开了自己家乡的土地，成为一个流民，这就没有办法回归到一个小国寡民的所需要的品德和素质。下边一样，“虽有舟舆，无所乘之”，这也是工具，有这个船，有这个车，不要经常去坐。我们现在也有很多人领悟出来了，打趣说，汽车是毒药，自行车是泻药，走路是补药。现在，很多人也确实奇怪，开车节省出时间了，然后回家在跑步机上跑步，这个东西确实是挺难理解，有时间走走路，不也是一种锻炼吗？下边这句话重要了，是这段话里要表达的核心意思，“虽有甲兵，无所陈之”，有军队没地方放。我不打仗，我要军队干嘛？大家注意，咱们中国的“国”字，原来氏族的时候，它是没有边界、国界的。“国”字外面这个方框是代表着城墙，“国”字的繁体字，最常用的是哪个呢？就是里边的“或”。大家仔细琢磨“或”，你看它是什么？用武器，那个“戈”不就是武器吗？用武器来看守一定的人口。这国家一出现，国家一大了，它就需要军队，所以老子为什么要小国寡民呢？不要军队，大家干脆都别打仗。在他的理想国里是没有军队存在的位置的，反对战争，祈求和平。《淮南子》里也讲了这样一件事，大禹的父亲夏鲧治国的时候，修了一座很大的城池，弄了很多的军队，结果四海有反心，诸侯都准备起来背叛。大禹即位后怎么处理的呢？他把城拆了，把军队散了，结果四海归心。其实这故事表达的也是这个意思，《淮南子》主要解读道家思想，举的这个例子也是用来印证《道德经》里讲的这一理念。“使人复结绳而用之”，有的本子叫做“民”，都一样。百姓不再用文字了，人类最早不就结绳记事吗？据说当年文字出现的时候，天雨粟，鬼夜哭。当然我们这个文明延续到今天，受惠于文字太多了，但是《道德经》里说，文字有时候也让人变得复杂，有投机取巧之心。有的人说这老子是倒退，反对文明。其实大家要理解他的苦心，他主要是让人类回归到那种朴素的、平等的、和谐的、互相不冲突的理想国的状态。我们换一个角度给大家一个直观的印象，大家都知道陶渊明的《桃花源记》，那里的人都是什么样？都活得非常的和谐，“甘其食”，吃什么都觉得很香，不挑剔。“美其服”，不是说穿着漂亮的衣服，是穿什么衣服都觉得很好，都觉得很开心。“安其居，乐其俗”，安居乐业，觉得自己那个风俗大家很喜欢，很开心。“邻国相望”，因为现在搞得这国家都跟一个村子一样，国与国之间不打仗了，邻国相望，离得很近，“鸡犬之声相闻”。读《桃花源记》，很多的时候，你能感觉到这一章的影子，“狗吠深巷里，鸡鸣桑树颠”。老子也给我们勾画了一个美丽的，看似平凡但不可企及的生活。当然，“民至老死不相往来”，不是强调不相往来，而是强调没冲突、不打仗。这一章的核心是这句话：“虽有甲兵，无所陈之。”春秋无义战，那时候战争此起彼伏，没一场是正义的战争，尸横遍野，血流成河。在这个背景下，老子就想这解决办法是什么呢？国家小一点，各过各的日子，不打仗。哲学家讲的理想国，不管是柏拉图的《理想国》、康帕内拉的《太阳城》、莫尔的《乌托邦》，还是老子讲的这个小国寡民，还是陶渊明讲的《桃花源记》，都代表着对纷乱社会的不满，都希望人类回归和谐相处的、没有冲突的、没有战争的状态。如果我们理解中国历史上的非常沉痛的两句诗，我们也就明白“小国寡民”的良苦之用心，这两句诗叫“宁做太平犬，不做乱世人”，宁可做太平世界的一条狗，也不做乱世冲突、战争频仍时候的人，因为这时候人活得连狗都不如，没有尊严。所以我常讲，有些经常叫嚣战争的人，其实都是不懂战争。真正懂得战争的残忍，就知道这和平、平静，是多么可贵。大家上中学的时候学过一篇课文，叫《最可爱的人》，里边讲的一段话让人非常有同感。它说也许你正走在去上班的路上，也许你正背着书包走在上学的路上，你觉得这很平常，可是从朝鲜回来的人会告诉你，你是生活在幸福之中。经历过战争的人会告诉你，这种情况是生活在幸福之中。这对我们也有所启示，不能简单地说小国寡民是一个倒退，得看它的现实背景，得了解它的语境，我们才能真正地理解老子的用心，我们对这些历史上有智慧的人、有慈悲心肠的人，对他们才能有深深的敬佩。见到这样有智慧、有品德的人，我们身体不在鞠躬，心灵在鞠躬。读这样的书也是一样，我们应该有敬畏，在敬畏的基础上，认真阅读，认真品味，珍惜和平与幸福的生活。</t>
@@ -1097,7 +1100,7 @@
     <t>信言不美，美言不信；善者不辩，辩者不善；知者不博，博者不知。圣人不积，既以为人，己愈有；既以与人，己愈多。天之道，利而不害；圣人之道，为而不争。</t>
   </si>
   <si>
-    <t>真诚的话不华美，漂亮的话不真诚；行善的人不去争辩，总是争辩的人不是良善的人；真正有智慧的人不认为自己博学，总是认为自己博学无所不知的人其实是没有智慧的。圣人不积累私藏，帮助别人的越多，自己越是充足；给予别人的越多，自己越是感觉获得的多。天道，利万物而不伤害；圣人之道，做好事情却不为自己争名夺利。</t>
+    <t>真诚的话不华美，漂亮的话不真诚；行善的人不去巧辩，总是巧辩的人不是良善的人；真正有智慧的人不认为自己博学，总是认为自己博学无所不知的人其实是没有智慧的。圣人不积累财富名利，帮助别人的越多，自己越是充足；给予别人的越多，自己越是感觉获得的多。大自然的运行规律，是施恩惠于万物而从不损害它们；圣人的处世原则，是只帮助别人而从不与别人争夺。</t>
   </si>
   <si>
     <t>说起《道德经》的分章，大家一般认为最早是河上公以九九归一为神秘的数字指向，把它分成了八十一章。第八十一章可以看作是全书的总结，全书思想的总结和概括就是最后这两句话，“天之道，利而不害。”天道如此，人道应该效法天道，所以下一句“圣人之道，为而不争”，一个好的领导人、统治者是如此，对我们大家来讲也是如此。韩国有一个连任联合国秘书长的聪明人，叫潘基文。他在连任就职典礼上，开口讲的就是《道德经》的这两句话，只不过他引用的是这两句话中的八个字：“利而不害，为而不争。”我怎么做联合国秘书长？我对大家有利，不起坏心，为大家谋福利，“利而不害”。我把事情做了，不为自己争名夺利，“为而不争”。我们应该有一个非常深刻的体验：道家并不是消极的、被动的、什么事都不做。什么叫无为？“为而不争”是无为的一个重要的方面，这可以看作是全部《道德经》的核心的总结。我们回头去想，“上善若水”讲“善利万物而不争”；天道讲“为而不争”。这样我们就把整个的思想落地了，知道了《道德经》最后的核心落在什么地方。现在来看一下原文，“信言不美，美言不信”，真正诚信的话，不漂亮，只会讲漂亮话的，没诚信，过度漂亮的话里，往往隐含欺骗的内容，所以大家说，真理是朴素的，真理是赤裸裸的。“善者不辩，辩者不善”，真正善良的人，不老去争辩。庄子在他文章里边经常讲，老去靠争辩，争辩胜了，又能够体现什么？“善者不辩，辩者不善”，老去争辩，老为自己找借口，老觉得自己受了无尽的委屈，这个不是善良者的表现。“知者不博，博者不知”，一个有智慧的人，不是老是吹嘘自己渊博、博学、无所不知，老是吹嘘自己无所不知的人，其实是没有智慧的。下面就讲一个有智慧的领导者应该怎么去做事。“圣人不积”，一个有智慧的领导者，不是老想着去积累财富、有形的资产。“既以为人，己愈有”，什么叫做富？什么叫做有？我老去帮助别人，为别人做事，在给别人做事情，帮助别人的过程中，获得了无尽的快乐，这不是无形资产吗？这不是精神世界的充盈吗？“既以与人，己愈多”，给别人的越多，帮别人的越多，要财富发挥它的真正的作用，在“舍”的过程中反而自己得到更多。“既以为人，己愈有；既以与人，己愈多。”2014年习近平在斐济《斐济时报》发表署名文章，也用过这两句话。中国人喜欢双赢，帮助别人。我们的理念是什么？我们给别人做的事情越多，我们感觉到自己越富有；对别人帮得越多，感觉到自己获得的更多。所以我们经常讲，我们很多的快乐是在帮助别人成长，别人有困难的时候，我们帮扶的时候，感觉到自己的内心的充盈快乐。“为人”是什么？“与人”是什么？是善利。看似付出，自己反而获得更多，自己的精神世界也更为充盈。如果我们只一味地为自己积累财富，结果呢？我们经常讲一句话，叫穷得只剩下钱了，我们的物质世界越发达，财富越多，我们的精神家园就越花果飘零。“善利万物而不争”，这是全书的最后总结。不争什么？不争言语的漂亮，只为了它的实质；不为了争辩的胜利，只为它的真理；不吹嘘自己的知识的渊博，只让知识发挥它正确的作用；不积累那么多所谓的财富，而是让财富发挥它真正的作用，让我们的精神世界越来越充盈、越来越丰富。帮人越多，自己越富有；给人越多，自己获得越多。舍得、舍得，舍的同时，也是一种获得；帮人的过程，也是一种快乐。“既以为人，己愈有；既以与人，己愈多”，这两句话仔细思量，其即是天道。“天之道，利而不害”，天道如此，善利万物不起坏心。“圣人之道，为而不争”，把事情做了，不为自己争名夺利。“为而不争”和前面我们讲过的“善利万物而不争”、“生而不有，为而不恃，长而不宰”、“功成而弗居”、“衣养万物而不为主”，这些重要的语句遥相呼应。这样，我们就把思想穿成了一串珍珠，看清楚了这本书的真正的逻辑，也看清了这本书的“落脚点”。这些成为我们生活中的座右铭，指南针，对我们的思维方式、人生格局、精神境界都会有很大的启发和启迪。第八十一章的内容，我们解读完了。到这最后一章，我们看到这一章最后落在这句话上“圣人之道，为而不争”，可以清楚的看到这本经典的目的就是把士和王修养、培养成圣。这就是这本书的内在逻辑，也是老子的良苦用心。读这本经典要掌握以下几个关键性问题。一是《道德经》本质上是一本对话体，也就是对面坐着人问的问题。只不过老子在刻书时把对面坐的人是谁、问的什么问题都省略了，而只是把他当时给的答案概括、总结、提炼、升华形成的一本著作。当我们从书里找到士、王、圣这三类问问题的人时，也就很容易抓住问题的关键了。二是王弼本《道德经》哲学思维水平非常高。在第一章就提出有无相互统一思维方式的重要性，并指出“无”是全书的众妙之门，从而让我们清楚地知道了无为、无声、无色、无味、无色……在这本书中的重要性，也借此步入众妙之门。三是我们这种以经解经的方法前后参照，避免了八十一章本子的“碎片化”倾向，并且在通篇解读中发现了老子对他认为重要问题的强调方式：首先是用重复的方式强调。比如在第十章、第五十章都重复出现“生而不有，为而不恃，长而不宰”，并且在第二章、第三十四章也都出现类似的意思。其次是用首尾呼应的方式来强调，比如二十二章就是如此。其三是用正反两个方面的方式来强调一个观点的重要性，比如第六十七章就是如此。了解了上面这些导读的内容，我们再来听课、阅读，我们就会更深刻地了解这本书的深刻内容，这本“善建者不拔”的伟大经典指导下：“修之于身，其德乃真；修之于家，其德乃余；修之于乡，其德乃长；修之于国，其德乃丰；修之于天下，其德乃普。”当然即便是逐章解决了很多问题，讲的恐怕也是蜻蜓点水，就《道德经》而言，最重要的是大家自己的阅读和领悟。</t>
@@ -2284,7 +2287,7 @@
   <dimension ref="A1:E83"/>
   <sheetFormatPr defaultColWidth="23.75" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="10.8796296296296" style="2" customWidth="1"/>
+    <col min="1" max="1" width="13.7777777777778" style="2" customWidth="1"/>
     <col min="2" max="2" width="50" style="2" customWidth="1"/>
     <col min="3" max="3" width="56.8796296296296" style="2" customWidth="1"/>
     <col min="4" max="4" width="75.25" style="2" customWidth="1"/>

--- a/book.xlsx
+++ b/book.xlsx
@@ -76,7 +76,7 @@
     <t>道德经</t>
   </si>
   <si>
-    <t>第一章</t>
+    <t>第一章（1）</t>
   </si>
   <si>
     <t>道可道，非常道；名可名，非常名。无，名天地之始；有，名万物之母。故常无，欲以观其妙；常有，欲以观其徼（jiào）。此两者同出而异名，同谓之玄，玄之又玄，众妙之门。</t>
@@ -92,7 +92,7 @@
     <t>道经</t>
   </si>
   <si>
-    <t>第二章</t>
+    <t>第二章（2）</t>
   </si>
   <si>
     <t>天下皆知美之为美，斯恶（è）已；皆知善之为善，斯不善已。故有无相（xiāng）生，难易相成，长短相较，高下相倾，音声相和，前后相随。是以圣人处无为之事，行不言之教，万物作焉而不辞，生而不有，为而不恃（shì），功成而弗居。夫唯弗居，是以不（bù）去。</t>
@@ -105,7 +105,7 @@
 因此圣人处无为之事，行不言之教：越是懂得有为，越要知道哪些该无为、该舍掉，从反面认识事情，才能达到更好的有为效果，千万不要把无为理解成消极。万物作焉而不辞，生而不有，为而不恃，功成而弗居：顺应万物自然生长而不干预，创造而不占有，做事而不依仗，有功而不居功，正因不居功，功德才不离去。本章后文许多重要内容提前概括出来，读熟这一章，后面很多章节都能以经解经。</t>
   </si>
   <si>
-    <t>第三章</t>
+    <t>第三章（3）</t>
   </si>
   <si>
     <t>不尚贤，使民不争；不贵难得之货，使民不为盗；不见（xiàn）可欲，使民心不乱。是以圣人之治，虚其心，实其腹；弱其志，强其骨。常使民无知无欲，使夫智者不敢为也。为无为，则无不治。</t>
@@ -118,7 +118,7 @@
 圣人之治，虚其心，实其腹，弱其志，强其骨：使民心虚静、生活温饱、欲望减弱、身体强健。常使民无知无欲，使夫智者不敢为也：少用智巧套路，投机者才不敢妄为。为无为，则无不治：治理者不妄为、不折腾，按规律和规则办事，天下自然治理得好。译者·韩鹏杰强调，老子的话对面坐着的是领导者，这些话是对治理者提出的警醒：任何事都有尺度，把握不好度，好事也会变成坏事。</t>
   </si>
   <si>
-    <t>第四章</t>
+    <t>第四章（4）</t>
   </si>
   <si>
     <t>道冲，而用之或不盈。渊兮，似万物之宗。挫其锐，解其纷，和其光，同其尘。湛兮似或存，吾不知谁（shuí）之子，象帝之先。</t>
@@ -131,7 +131,7 @@
 译者·韩鹏杰用第四十二章“道生一，一生二，二生三，三生万物；万物负阴而抱阳，冲气以为和”来印证：三即参，阴阳参与到一起而生万物，万事万物都同时具有阴阳两面，无论怎么转都像太极图一样保持和谐。了解道冲，就掌握了一种重要思维：任何事物都是两种相反力量在动态中达成的和谐，看问题、做决策都不能只偏执一方。</t>
   </si>
   <si>
-    <t>第五章</t>
+    <t>第五章（5）</t>
   </si>
   <si>
     <t>天地不仁，以万物为刍（chú）狗；圣人不仁，以百姓为刍狗。天地之间，其犹橐（tuó）籥（ yuè）乎？虚而不屈（qū），动而愈出。多言数（shuò）穷，不如守中。</t>
@@ -144,7 +144,7 @@
 天地之间，其犹橐籥乎：天地像风箱，中间虚静，一拉动就能鼓出风来；政令也应如此，保持虚静、简要稳定，不能今天一变明天一变。多言数穷，不如守中：政令繁多、变动频繁会把自己逼入困境，不如恰到好处、大道至简。译者·韩鹏杰提醒，这些话都是讲给领导者听的：治理要公平无私，政令要少而稳定，靠规则而不是靠折腾。</t>
   </si>
   <si>
-    <t>第六章</t>
+    <t>第六章（6）</t>
   </si>
   <si>
     <t>谷神不死，是谓玄牝（pìn）。玄牝之门，是谓天地根。绵绵若存，用之不勤。</t>
@@ -157,21 +157,20 @@
 译者·韩鹏杰强调，老子用神、玄这些最高字眼来称呼谷与牝，绝不允许亵渎；一个文化里若失去对母亲的尊重、对生命的敬畏，其他方面都会崩塌。读这一章不要陷入玄虚，要读出其中朴素而伟大的情感：尊重母亲、敬畏生命，是文化延续的根基。</t>
   </si>
   <si>
-    <t>第七章</t>
+    <t>第七章（7）</t>
   </si>
   <si>
     <t>天长地久。天地所以能长且久者，以其不自生，故能长生。是以圣人后其身而身先，外其身而身存。非以其无私邪？故能成其私。</t>
   </si>
   <si>
-    <t>天地能够长久存在。天地之所以能够长久存在，原因就在于它们不
-是为了自我而生存，所以能长久存在。因此有智慧的领导者总是把自己的利益放在后面，反而能够站到别人的前面；不贪身外之物，反而有利于自己的生存。不就是因为他们没有私心嘛，所以才更好地成就了他们的被人尊敬、平安无事的私心吗？！</t>
+    <t>天地能够长久存在。天地之所以能够长久存在，原因就在于它们不是为了自我而生存，所以能长久存在。因此有智慧的领导者总是把自己的利益放在后面，反而能够站到别人的前面；不贪身外之物，反而有利于自己的生存。不就是因为他们没有私心嘛，所以才更好地成就了他们的被人尊敬、平安无事的私心吗？！</t>
   </si>
   <si>
     <t>本章与第八、九章共同讲进退、争让、强弱：人们习惯强调争、进、强，老子偏要讲被忽略的不争、退、弱，因为它们与争、进、强是阴阳的两个方面，具有同等力量。天长地久：天地之所以长久，是因为天地不自私，不以自己的生存为唯一目的，而是为万物提供阳光雨露土壤，任万物自由生长，因此赢得人们长久的敬畏。后其身而身先，外其身而身存：圣人把自身利益放在后面，反而被众人推举到前面；把自身安危置之度外，反而安然长存。非以其无私邪，故能成其私：正因无私，才更好地成就了自己的长久与被人敬仰，这是人人都有的潜意识私心。
 本章是典型的“天道人道”两段论：先讲天道，再讲人道，人道效法天道。译者·韩鹏杰用“公仪休不受鱼”的故事说明：懂得从长远看问题、不贪眼前不该得的利益，才能长久地满足自己的愿望；只盯着私利的人，最后连私利也保不住。</t>
   </si>
   <si>
-    <t>第八章</t>
+    <t>第八章（8）</t>
   </si>
   <si>
     <t>上善若水，水善利万物而不争，处众人之所恶（wù），故几于道，居善地；心善渊；与善仁；言善信；正善治；事善能；动善时。夫唯不争，故无尤。</t>
@@ -184,7 +183,7 @@
 水的“不争”有丰富含义：有边界不争（湖有湖畔、河有河堤、海有海岸），有秩序不争（前后相随、循序渐进），有牺牲不争（成就万物而默默无闻）。夫唯不争，故无尤：不争就不会招来怨恨和过错。译者·韩鹏杰指出，老子不是趴在河边悟道，而是借水的形象传达从战争、政治、人生中领悟的智慧：善于成就别人，同时也成就自己，这正是双赢。</t>
   </si>
   <si>
-    <t>第九章</t>
+    <t>第九章（9）</t>
   </si>
   <si>
     <t>持而盈之，不如其已（yǐ）。揣（zhuī）而锐之，不可长保。金玉满堂，莫之能守。富贵而骄，自遗其咎。功遂身退，天之道也。</t>
@@ -197,7 +196,7 @@
 译者·韩鹏杰用民间故事讲这个道理：弟弟只拿一点金子平安回家，哥哥贪心装满全身，被太阳晒化。第七章讲先后，第八章讲不争，第九章讲不盈，都提醒人知进退、懂谦让。中国文化的“中”就是恰到好处，不走到极端：物极必反、乐极生悲、泰极否来，好事到了极端容易向坏处转化，所以要战战兢兢、如履薄冰地把握分寸。</t>
   </si>
   <si>
-    <t>第十章</t>
+    <t>第十章（10）</t>
   </si>
   <si>
     <t>载（zài）营魄抱一，能无离乎？专气致柔，能如婴儿乎？涤除玄览，能无疵（cī）乎？爱民治国，能无为乎？天门开阖，能为雌乎？明白四达，能无知乎？生之畜（xù）之，生而不有，为而不恃，长（zhǎng）而不宰，是谓玄德。</t>
@@ -210,7 +209,7 @@
 一连串反问都在讲修养路径：魂魄不离、身心合一、少欲守静、厚道不用智巧。最后点出玄德：生之畜之，生而不有，为而不恃，长而不宰——生养万物而不占有、不倚仗、不主宰，这是最高深的德。译者·韩鹏杰认为这一章是后面九章的总纲，虚静既是个人修养，也是治国的基础。</t>
   </si>
   <si>
-    <t>第十一章</t>
+    <t>第十一章（11）</t>
   </si>
   <si>
     <t>三十辐（fú）共一毂（gǔ），当其无，有车之用。埏（shān）埴（zhí）以为器，当其无，有器之用。凿户牖（yǒu）以为室，当其无，有室之用。故有之以为利，无之以为用。</t>
@@ -223,7 +222,7 @@
 译者·韩鹏杰指出，“利用”这个词就来自本章。第十章讲虚静，本章讲怎样虚静——心里放空，去掉杂念，才能听得进别人的意见、看得见别人的长处、学得到别人的优点，虚怀若谷、满招损谦受益。中国文化的悟道方式是“给一个形象，自己领悟”，本章就是最好的示范：通过车、器、室三个形象，让人领悟空与用的道理。</t>
   </si>
   <si>
-    <t>第十二章</t>
+    <t>第十二章（12）</t>
   </si>
   <si>
     <t>五色令人目盲；五音令人耳聋；五味令人口爽；驰骋畋（tián）猎，令人心发狂；难得之货，令人行妨。是以圣人为腹不为目，故去彼取此。</t>
@@ -236,7 +235,7 @@
 是以圣人为腹不为目，故去彼取此：圣人重实质内容，不重外在浮华；取舍的标准是看什么最重要——健康、营养、真实比外表颜色更重要。译者·韩鹏杰把本章与第十章、十一章连起来读：虚静的心才能看清本质，处其厚不居其薄，掌握生命中真正重要的东西，返璞归真。</t>
   </si>
   <si>
-    <t>第十三章</t>
+    <t>第十三章（13）</t>
   </si>
   <si>
     <t>宠辱若惊，贵大患若身。何谓宠辱若惊？宠为下，得之若惊，失之若惊，是谓宠辱若惊。何谓贵大患若身？吾所以有大患者，为吾有身，及吾无身，吾有何患！故贵以身为天下，若可寄天下；爱以身为天下，若可托天下。</t>
@@ -249,7 +248,7 @@
 吾所以有大患者，为吾有身，及吾无身，吾有何患——不把身体和生命当回事的人，坐到重要位置上是很可怕的；声色犬马、厚食重味正是戕害生命。贵以身为天下，若可寄天下；爱以身为天下，若可托天下：真正把自身生命看得与天下一样贵重、肯为天下担当牺牲的人，才值得把天下托付给他。译者·韩鹏杰区分两种勇敢：无赖式的勇敢不把命当回事，有责任的勇敢珍视生命又肯担当，后者才值得托付。</t>
   </si>
   <si>
-    <t>第十四章</t>
+    <t>第十四章（14）</t>
   </si>
   <si>
     <t>视之不见名曰夷（yí），听之不闻名曰希，搏之不得名曰微。此三者不可致诘（jié），故混而为一。其上不皦（jiǎo），其下不昧，绳（mǐn）绳（mǐn）不可名，复归于无物。是谓无状之状，无物之象，是谓惚恍。迎之不见其首，随之不见其后。执古之道，以御今之有。能知古始，是谓道纪。</t>
@@ -264,7 +263,7 @@
 执古之道，以御今之有：了解古往今来的大道，才能把握今天、做好今天的事；能知古始，是谓道纪：知道万物开始的道理，就是把握了道的纲领。译者·韩鹏杰用庄子的“道在瓦片、稗草、大小便中”来说明道无在无不在，越往下越有；用风的形象说明道无形却左右万物。学习本章要记住：道看不见摸不着，但真实存在、无处不在，了解它才能做好今天的事。</t>
   </si>
   <si>
-    <t>第十五章</t>
+    <t>第十五章（15）</t>
   </si>
   <si>
     <t>古之善为士者，微妙玄通，深不可识。夫唯不可识，故强为之容。豫焉若冬涉川，犹兮若畏四邻，俨（yǎn）兮其若客，涣兮若冰之将释，敦兮其若朴，旷兮其若谷，混兮其若浊。孰能浊以止？静之徐清。孰能安以久？动之徐生。保此道者不欲盈，夫唯不盈，故能蔽而新成。</t>
@@ -280,7 +279,7 @@
 孰能浊以静之徐清？孰能安以久动之徐生：浊水静下来才能慢慢澄清，安定的状态动起来才能慢慢焕发生机，这是“静中求清、动中求生”的修养。保此道者不欲盈，夫唯不盈，故能蔽而新成：守道者不求满，留出空间，舍弃旧的东西才能革故鼎新。译者·韩鹏杰强调，书中的话多针对具体的人讲，本章针对带领十几人做事的小组长等“士”阶层，说明基层领导者也需要很高的素质：谨慎、敬畏、质朴、虚怀、不盈。</t>
   </si>
   <si>
-    <t>第十六章</t>
+    <t>第十六章（16）</t>
   </si>
   <si>
     <t>致虚极，守静笃，万物并作，吾以观复。夫物芸芸，各复归其根。归根曰静，是谓复命。复命曰常，知常曰明。不知常，妄作，凶。知常容，容乃公，公乃王（wàng），王乃天，天乃道，道乃久。没身不殆。</t>
@@ -293,7 +292,7 @@
 知常容，容乃公，公乃王，王乃天，天乃道，道乃久，没身不殆：懂得恒常之道就能包容，包容就公正，公正就周全，周全就合天，合天就合道，合道就长久，终身不会遇到危险。译者·韩鹏杰说，从草的枯荣到人的生死，都体现“复”的规律；观察规律是为了认识自己、掌控自己：知道哪些因素会带来负面状态，就主动避免；知道哪些条件带来积极状态，就主动创造，让好的状态恢复。</t>
   </si>
   <si>
-    <t>第十七章</t>
+    <t>第十七章（17）</t>
   </si>
   <si>
     <t>太上，不知有之；其次，亲而誉之；其次，畏之；其次，侮之。信不足焉，有不信焉。悠兮其贵言。功成事遂，百姓皆谓我自然。</t>
@@ -306,7 +305,7 @@
 译者·韩鹏杰用“太上”的拆字讲：大上加一点才是太，点放下才成太，放到上面就成犬，寓意善于处下才能真正居上，太太、处长等词都蕴含此理。最好的教育和管理也是如此：不越俎代庖，让孩子、下属自己把事情做成，他们才有自信和成长，功成事遂皆谓我自然。</t>
   </si>
   <si>
-    <t>第十八章</t>
+    <t>第十八章（18）</t>
   </si>
   <si>
     <t>大道废，有仁义；慧智出，有大伪；六亲不和，有孝慈；国家昏乱，有忠臣。</t>
@@ -319,7 +318,7 @@
 一个社会天天提倡道德，正说明道德已经滑坡；什么时候妇女节、教师节不再成为问题，才说明相关地位真正提高了。这不是否定仁义孝慈，而是提醒人们不要靠表面提倡来补救，要从根本上回到道。把第十八、十九章连起来读：与其用仁义、智巧等外在名目补救，不如回归素朴本心，做个好人、存点好心、行些好事。</t>
   </si>
   <si>
-    <t>第十九章</t>
+    <t>第十九章（19）</t>
   </si>
   <si>
     <t>绝圣弃智，民利百倍；绝仁弃义，民复孝慈；绝巧弃利，盗贼无有。此三者以为文不足。故令有所属：见（xiàn）素抱朴，少私寡欲，绝学无忧。</t>
@@ -332,7 +331,7 @@
 译者·韩鹏杰说，道家认为人的本心就是真心，真心就是朴素之心，朴素之心就是少私寡欲；外在花花绿绿的学问看多了，反而把人搞乱。读经典要由博返约，最后陪我们一生的可能只是一两本书、一两句话，真传一句话，假传万卷书。绝学无忧不是不要学习，而是学真正的大道，不被浮华知识蒙蔽。</t>
   </si>
   <si>
-    <t>第二十章</t>
+    <t>第二十章（20）</t>
   </si>
   <si>
     <t>唯之与阿（hē），相去几何？善之与恶，相去若何？人之所畏，不可不畏。荒兮，其未央哉！众人熙熙，如享太牢，如春登台。我独泊兮，其未兆，如婴儿之未孩。儽（léi）儽兮，若无所归。众人皆有余，而我独若遗。我愚人之心也哉，沌（dùn）沌兮！俗人昭昭，我独昏昏；俗人察察，我独闷闷。澹（dàn）兮其若海； 飂（liù）兮若无止 。众人皆有以，而我独顽似鄙。我独异于人，而贵食母。</t>
@@ -345,7 +344,7 @@
 众人皆有余，而我独若遗：众人都显得富足有余，得道者却像有所遗失。我愚人之心也哉，沌沌兮：一副愚人心肠，混沌淳朴。俗人昭昭，我独昏昏；俗人察察，我独闷闷：世人精明，得道者看似糊涂宽厚。澹兮其若海，飂兮若无止：他像大海一样淡泊深沉，像长风一样自由无羁。众人皆有以，而我独顽似鄙：世人都有用处，他看似冥顽无能。我独异于人，而贵食母：与众人不同，因为他以大道为归依。本章刻画了不随波逐流、独立守道的精神境界。</t>
   </si>
   <si>
-    <t>第二十一章</t>
+    <t>第二十一章（21）</t>
   </si>
   <si>
     <t>孔德之容，惟道是从。道之为物，惟恍惟惚。惚兮恍兮，其中有象；恍兮惚兮，其中有物。窈（yǎo）兮冥兮，其中有精；其精甚真，其中有信。自古及今，其名不去，以阅众甫。吾何以知众甫之状哉？以此。</t>
@@ -358,7 +357,7 @@
 自古及今，其名不去，以阅众甫：从古至今，道的名字不曾消失，凭借它可以认识万物起始。吾何以知众甫之状哉？以此：我就是凭借道来认识圣人得道的状态。译者·韩鹏杰强调，道不仅是万物的本源和规律，也是人生的境界；离开了道，人就变成无源之水、无本之木。这一章让人对道建立确信：它看不见摸不着，但真实存在，是精神世界的根基。</t>
   </si>
   <si>
-    <t>第二十二章</t>
+    <t>第二十二章（22）</t>
   </si>
   <si>
     <t>曲则全，枉则直，洼则盈，敝则新，少则得，多则惑。是以圣人抱一为天下式。不自见，故明；不自是，故彰；不自伐，故有功；不自矜（jīn），故长。夫唯不争，故天下莫能与之争。古之所谓“曲则全”者，岂虚言哉？诚全而归之。</t>
@@ -371,7 +370,7 @@
 不自见故明，不自是故彰，不自伐故有功，不自矜故长：不固执己见才看得清，不自以为是才声名彰显，不自我夸耀才保有功劳，不自高自大才长久。夫唯不争，故天下莫能与之争：因为不与别人争夺，天下没有人能争得过他。古之所谓曲则全者，岂虚言哉，诚全而归之：古人说的曲则全，确实能把圆满的结果带回来。本章教人以迂回、谦下、统一的思维处理问题。</t>
   </si>
   <si>
-    <t>第二十三章</t>
+    <t>第二十三章（23）</t>
   </si>
   <si>
     <t>希言自然。故飘风不终朝（zhāo），骤雨不终日。孰为此者？天地。天地尚不能久，而况于人乎？故从事于道者，同于道；德者，同于德；失者，同于失。同于道者，道亦乐得之；同于德者，德亦乐得之；同于失者，失亦乐得之。信不足焉，有不信焉。</t>
@@ -384,7 +383,7 @@
 同于道者，道亦乐得之；同于德者，德亦乐得之；同于失者，失亦乐得之：你喜欢什么、亲近什么，就会被什么吸引和成就，人身边聚集什么样的人，往往取决于你自己是什么样的人。信不足焉，有不信焉：自己诚信不足，别人自然不会信任你。译者·韩鹏杰指出，本章看似同语反复，其实在反复劝告：要让自己的境界不断提高，就要亲近有道有德的人和事，勇于发现并改正缺点，路是自己走出来的。</t>
   </si>
   <si>
-    <t>第二十四章</t>
+    <t>第二十四章（24）</t>
   </si>
   <si>
     <t>企者不立；跨者不行；自见者不明；自是者不彰；自伐者无功；自矜者不长。其在道也，曰余食赘（zhuì）行。物或恶（wù）之，故有道者不处。</t>
@@ -397,7 +396,7 @@
 其在道也，曰余食赘行：这些行为在道看来，就像吃饱了再吃、身上长赘瘤，多余无用；物或恶之，故有道者不处：人们厌恶它们，有道的人不做这些事。译者·韩鹏杰用项羽举例：力拔山兮气盖世，却因骄傲自大、听不进意见，落得自刎乌江的下场。孔子讲毋意、毋必、毋固、毋我，佛家讲无我相，与老子相通。做事要稳扎稳打，收敛自见、自是、自伐、自矜，才能不断进步。</t>
   </si>
   <si>
-    <t>第二十五章</t>
+    <t>第二十五章（25）</t>
   </si>
   <si>
     <t>有物混成，先天地生。寂兮寥兮，独立不改，周行而不殆，可以为天下母。吾不知其名，字之曰“道”，强为之名曰“大”。大曰逝，逝曰远，远曰反。故道大，天大，地大，王（wàng）亦大。域中有四大，而王居其一焉。人法地，地法天，天法道，道法自然。</t>
@@ -410,7 +409,7 @@
 道大，天大，地大，王亦大，域中有四大，而王居其一焉：道、天、地、人（王）都是大的，人只是四大之一，不能自大。人法地，地法天，天法道，道法自然：人效法地，地效法天，天效法道，道效法它本来的样子，自然就是本该如此。译者·韩鹏杰强调，道法自然是全书信仰和规则的源头，人要敬畏天道，与天地和谐相处。</t>
   </si>
   <si>
-    <t>第二十六章</t>
+    <t>第二十六章（26）</t>
   </si>
   <si>
     <t>重为轻根，静为躁君。是以圣人终日行不离辎（zī）重。虽有荣观，燕处超然。奈何万乘（shèng）之主，而以身轻天下？轻则失本，躁则失君。</t>
@@ -423,7 +422,7 @@
 轻则失根：轻率轻浮就失去根本，像飘蓬浮萍没有根基；躁则失君：浮躁急躁就失去对自己的掌控，冲动之下常常酿成大祸。译者·韩鹏杰用“路怒”举例：开车偶有小摩擦就粗口相向甚至拔刀，动手前问自己要不要动手、后果如何、有无别的办法，几秒钟的冷静可能改变结果。开头八字“重为轻根，静为躁君”与结尾“轻则失根，躁则失君”都是至理名言。</t>
   </si>
   <si>
-    <t>第二十七章</t>
+    <t>第二十七章（27）</t>
   </si>
   <si>
     <t>善行，无辙迹；善言，无瑕谪（zhé）；善数，不用筹策；善闭，无关楗（jiàn）而不可开；善结，无绳约而不可解。是以圣人常善救人，故无弃人；常善救物，故无弃物。是谓袭明。故善人者，不善人之师；不善人者，善人之资。不贵其师，不爱其资，虽智大迷，是谓要妙。</t>
@@ -436,7 +435,7 @@
 是以圣人常善救人，故无弃人；常善救物，故无弃物：圣人善于救人救物，天下没有可抛弃的人、没有可抛弃之物，你没发现用处不等于无用，无用方为大用。善人者，不善人之师；不善人者，善人之资：善人是恶人的老师，恶人是善人的借鉴，“师资”一词正源于此。不贵其师，不爱其资，虽智大迷：不尊重老师、不爱惜借鉴，再聪明也是大迷惑，这是道的枢要。做人要善行不留痕迹，看人看物发现其用处，并善于从正反两方面学习。</t>
   </si>
   <si>
-    <t>第二十八章</t>
+    <t>第二十八章（28）</t>
   </si>
   <si>
     <t>知其雄，守其雌，为天下谿（xī）。为天下谿，常德不离，复归于婴儿。知其白，守其黑，为天下式。为天下式，常德不忒（tè），复归于无极。知其荣，守其辱，为天下谷。为天下谷，常德乃足，复归于朴（pǔ）。朴散则为器，圣人用之则为官长，故大制不割。</t>
@@ -449,7 +448,7 @@
 朴散则为器，圣人用之则为官长，故大制不割：素朴分散为万物之器，圣人顺应本性管理，最好的制度不伤害本性。译者·韩鹏杰强调，守雌、守黑、守辱不是没有经历过强、白、荣就假装谦卑，而是先有实力和成就，再有资格谈守，比如书法先经历精巧，才能返璞归真。记住十八个字：知其雄守其雌，知其白守其黑，知其荣守其辱，就是这一章的核心智慧。</t>
   </si>
   <si>
-    <t>第二十九章</t>
+    <t>第二十九章（29）</t>
   </si>
   <si>
     <t>将欲取天下而为之，吾见其不得已。天下神器，不可为也，不可执也。为者败之，执者失之。是以圣人无为，故无败；无执，故无失。故物或行或随；或歔（xū）或吹；或强或羸（léi）；或载（zài）或隳（huī）。
@@ -463,7 +462,7 @@
 故物或行或随，或嘘或吹，或强或羸，或载或隳：万物本性各不相同，有前行有跟随，有轻嘘有急吹，有强壮有羸弱，有安稳有毁坏，不能用一个标准、一种方式强求。是以圣人去甚，去奢，去泰：圣人去掉极端的、奢侈的、过分的言行和欲望。译者·韩鹏杰指出，这一章要结合时代背景理解：春秋末期诸侯争霸、生灵涂炭，老子提出小国寡民设想，反对强为；读这一章要体会其中的沉痛感，任何事有生必有灭、有成必有败，强求和把持都违背天道。</t>
   </si>
   <si>
-    <t>第三十章</t>
+    <t>第三十章（30）</t>
   </si>
   <si>
     <t>以道佐人主者，不以兵强天下。其事好还（huán）。师之所处，荆棘生焉。大军之后，必有凶年。善有果而已，不敢以取强。果而勿矜，果而勿伐，果而勿骄。果而不得已，果而勿强。物壮则老，是谓不道，不道早已。</t>
@@ -476,7 +475,7 @@
 果而勿矜，果而勿伐，果而勿骄：胜利了不自大、不夸耀、不骄傲；果而不得已，果而勿强：胜利是出于不得已，胜了也不逞强。物壮则老，是谓不道，不道早已：事物强盛到极点就走向衰败，逞强求壮不合道，不合道就很快灭亡。译者·韩鹏杰说，这章最后三句话值得牢记：师之所处荆棘生焉，大军之后必有凶年，物壮则老。战争不可轻易发动，对待战争的态度就是对待同胞生命的态度；中华民族热爱和平，不惹事也不怕事。</t>
   </si>
   <si>
-    <t>第三十一章</t>
+    <t>第三十一章（31）</t>
   </si>
   <si>
     <t>夫兵者，不祥之器，物或恶（wù）之，故有道者不处。君子居则贵左，用兵则贵右。兵者不祥之器，非君子之器，不得已而用之，恬淡为上。胜而不美，而美之者，是乐杀人。夫乐杀人者，则不可以得志于天下矣。吉事尚左，凶事尚右。偏将军居左，上将军居右，言以丧礼处之。杀人之众，以悲哀泣之，战胜以丧礼处之。</t>
@@ -489,7 +488,7 @@
 吉事尚左，凶事尚右：吉庆之事尚左，凶丧之事尚右；偏将军居左，上将军居右，就是用办理丧事的礼节来对待战争。杀人之众，以悲哀泣之，战胜以丧礼处之：战争杀人众多，要带着悲哀的心情参与，战胜了也要用丧礼的仪式对待。译者·韩鹏杰强调，这两章应该进小学课本，让和平的种子从小种下；战争胜利后第一件事不是放肆庆祝，而是祭奠双方的死者，因为他们都是生命。</t>
   </si>
   <si>
-    <t>第三十二章</t>
+    <t>第三十二章（32）</t>
   </si>
   <si>
     <t>道常无名，朴虽小，天下莫能臣也。侯王若能守之，万物将自宾。天地相合，以降甘露，民莫之令而自均。始制有名，名亦既有，夫亦将知止。知止可以不殆。譬道之在天下，犹川谷之于江海。</t>
@@ -502,7 +501,7 @@
 始制有名，名亦既有，夫亦将知止，知止可以不殆：人类社会开始有制度、名分是合理的，但有了名分制度要懂得边界，不能制度崇拜、名分崇拜，做过了头就走向反面；知道适可而止，才能避免危险。譬道之在天下，犹川谷之于江海：道在天下，就像川谷流向江海，是自然归附的过程，不是强迫。译者·韩鹏杰强调，老子反复用重复和强调来突出重要思想，本章的核心就是朴与知止：做事朴实厚道，对制度名分保持克制，知道边界和限度，物极必反，知止不殆。</t>
   </si>
   <si>
-    <t>第三十三章</t>
+    <t>第三十三章（33）</t>
   </si>
   <si>
     <t>知人者智，自知者明。胜人者有力，自胜者强。知足者富，强行者有志。不失其所者久，死而不亡者寿。</t>
@@ -515,7 +514,7 @@
 不失其所者久：不离开自己的归宿才能长久，“所”就是精神家园，物质再发达也不能让精神家园花果飘零。死而不亡者寿：身死而精神不亡，才是真正的长寿，那些思想家的光芒像群星，在黑暗时指引方向。译者·韩鹏杰说，这一章既写给领导者也写给普通人：自知、自胜、知足、强行、守所、精神不亡，六层递进，是中国文化中极高的人生境界。</t>
   </si>
   <si>
-    <t>第三十四章</t>
+    <t>第三十四章（34）</t>
   </si>
   <si>
     <t>大道泛兮，其可左右。万物恃之而生而不辞，功成而不名有。衣养万物而不为主，常无欲，可名于小。万物归焉而不为主，可名为大。以其终不自为大，故能成其大。</t>
@@ -528,7 +527,7 @@
 译者·韩鹏杰强调，这一章讲量变质变、从小到大的道理：合抱之木生于毫末，九层之台起于累土，千里之行始于足下；天下难事必作于易，天下大事必作于细。做人做事不要自高自大、好高骛远，要虚怀若谷、脚踏实地，把容易的事当难事做，把小事做好，一步一步成就伟大。</t>
   </si>
   <si>
-    <t>第三十五章</t>
+    <t>第三十五章（35）</t>
   </si>
   <si>
     <t>执大象，天下往。往而不害，安平泰。乐与饵，过客止。道之出口，淡乎其无味。视之不足见，听之不足闻，用之不足既。</t>
@@ -541,7 +540,7 @@
 译者·韩鹏杰说，我们日常所用而不知，天天都在用道却不自知；饮食清淡有益健康，人格返璞归真才接近道，清水出芙蓉、天然去雕饰是艺术的高境界。年轻人都觉得自己会成为伟大人物，最后发现伟大来自平凡，把自己看得平凡，才能重归于朴、重归于真、重归于道。真正的力量不是热闹炫耀，而是平淡之中无穷无尽。</t>
   </si>
   <si>
-    <t>第三十六章</t>
+    <t>第三十六章（36）</t>
   </si>
   <si>
     <t>将欲歙（xī）之，必固张之；将欲弱之，必固强之；将欲废之，必固兴之；将欲夺之，必固与之。是谓微明。柔弱胜刚强。鱼不可脱于渊，国之利器不可以示人。</t>
@@ -554,7 +553,7 @@
 译者·韩鹏杰用捧杀典故解释：杀君马者道旁儿，过分夸奖、吹捧使人骄傲自满、退步失败，关羽过不了奉承关而败走麦城；两军对垒时老弱残兵挑衅、敌人弃辎重诱敌，都是将欲夺之必固与之。本章不是说用阴谋，而是讲事物转化的规律：看清对立面的运动，力量与边界都要含藏，不能张扬炫耀。</t>
   </si>
   <si>
-    <t>第三十七章</t>
+    <t>第三十七章（37）</t>
   </si>
   <si>
     <t>道常无为而无不为。侯王若能守之，万物将自化。化而欲作，吾将镇之以无名之朴。无名之朴，夫亦将无欲。不欲以静，天下将自定。</t>
@@ -567,7 +566,7 @@
 译者·韩鹏杰把无为理解为：不违背规律、不妄为、不折腾，而不是消极不作为；治理的最高境界是让事物按自己的本性生长，让百姓自然发展生产、自然安定。从第一章到第三十七章是《道经》，讲道本身；后三十八章起是《德经》，讲道落实到人。把这两部分合起来读，“道在前而德在后”，做一切事才能顺理成章。</t>
   </si>
   <si>
-    <t>第三十八章</t>
+    <t>第三十八章（38）</t>
   </si>
   <si>
     <t>上德不德，是以有德；下德不失德，是以无德。上德无为而无以为；下德为之而有以为；上仁为之而无以为；上义为之而有以为；上礼为之而莫之应，则攘（rǎng）臂而扔之。故失道而后德，失德而后仁，失仁而后义，失义而后礼。夫礼者，忠信之薄而乱之首。前识者，道之华而愚之始。是以大丈夫处其厚，不居其薄；处其实，不居其华。故去彼取此。</t>
@@ -583,7 +582,7 @@
     <t>德经</t>
   </si>
   <si>
-    <t>第三十九章</t>
+    <t>第三十九章（39）</t>
   </si>
   <si>
     <t>昔之得一者：天得一以清；地得一以宁；神得一以灵；谷得一以盈；万物得一以生；侯王得一以为天下正。其致之也，天无以清，将恐裂；地无以宁，将恐发；神无以灵，将恐歇；谷无以盈，将恐竭；万物无以生，将恐灭；侯王无以贵高，将恐蹶（jué）。故贵以贱为本，高以下为基。是以侯王自谓孤、寡、不穀（gǔ）。此非以贱为本邪（yé）？非乎？故致数舆无舆。是故不欲琭（lù）琭如玉，珞（luò）珞如石。</t>
@@ -596,7 +595,7 @@
 是以侯王自谓孤、寡、不穀：侯王自称孤、寡、不穀，正是以贱为本、以下为基。致数舆无舆：刻意追求众多荣誉反而失去荣誉。是故不欲琭琭如玉，珞珞如石：不要像华美的玉，要像坚硬的石头，石头能铺路济人，华美的玉看似高贵却少有用处。译者·韩鹏杰强调两个重点：一是“一”即道，是阴阳统一；二是“贵以贱为本，高以下为基”，位置越高越要善于处下，把根基打牢，做人要处实不居华。</t>
   </si>
   <si>
-    <t>第四十章</t>
+    <t>第四十章（40）</t>
   </si>
   <si>
     <t>反者道之动。弱者道之用。天下万物生于有，有生于无。</t>
@@ -609,7 +608,7 @@
 译者·韩鹏杰强调，如果只看到有形东西的作用，忽略无形东西的作用，物质世界越发达，精神家园就越花果飘零；既要看到物质财富，更要看到精神、信仰、理论这些无形力量。前三章讲道，第四十章用三句话总结全书思维方式，后边各章都是它的展开和例证。</t>
   </si>
   <si>
-    <t>第四十一章</t>
+    <t>第四十一章（41）</t>
   </si>
   <si>
     <t>上士闻道，勤而行之；中士闻道，若存若亡（wú）；下士闻道，大笑之，不笑不足以为道。故建言有之﹕明道若昧，进道若退，夷道若颣（lèi）。上德若谷，大白若辱，广德若不足，建德若偷，质真若渝（yú）。大方无隅（yú），大器晚成，大音希声，大象无形。道隐无名，夫唯道善贷且成。</t>
@@ -621,7 +620,7 @@
     <t>前边《德经》的部分我们讲了第三十八章，“上德不德，是以有德，下德不失德，是以无德。”讲了第三十九章，第三十九章第一个重要的概念是“一”。我再重申一遍，是阴阳两者的统一，也就是道。第三十九章里边的重点词，我们要不断地重申、重复，以求达到大家的记忆。“贵以贱为本，高以下为基。”第四十章我们极为看重。因为这一章开头五个字，是整个这一本书里思维的总纲：“反者，道之动”，下边是它的具体的体现，“弱者，道之用。天下万物生于有，生于无。”现在我们具体来讲第四十一章，这一章内容也非常丰富。首先我们在前边就强调过，《道德经》是对面有人问问题，老子给予的回答。现在对面有人问关于“士”的问题了。“士”这个阶层，把它理解为做官的阶层也可以，“士”这个概念，它的原意就是做事。延伸意指的是一个领导阶层。推十为一嘛，十个人里边推举出来一个领导大家，服务大家，管理大家。所以有人问老子，你看这些士，怎么来判断他们境界的高低呢？水平的高低呢？老子也是拿道来评价的。所以在这一章里边，一开始老子就讲“上士闻道，勤而行之”，境界高的、水平高的士这个阶层这些人，听到了道，比如说他的领导者讲的话，他觉得有道，有道理，“勤而行之”，就是执行力最强，坚定不移地按照它去做。有问题呢？自己勤勉、勤奋地把它解决，“勤而行之”，知行合一了嘛。知道了就按照道去做。中等境界的是什么呢？“中士闻道，若存若亡”，将信将疑。也想去按照道去做，但是一遇到事了就怀疑了。“若存若亡”，将信将疑，迟迟疑疑，犹犹豫豫，执行力不够。“下士闻道，大笑之”。境界最低的、最差的是干吗呢？嘲笑。人家说什么，制定什么样的制度规则，他都嘲笑，讲什么他都觉得不对，但是又提不出建设性意见，什么叫建设性意见？你觉得人家这个不好，你有没有更好的方案？觉得有问题，客观地指出来、提出来怎么改进，不是为了嘲笑而嘲笑，不是为了讽刺而讽刺。我觉得现在很多语言类的节目只是为了讽刺别人，讲话的时候只是为了打击别人，没有其他什么善良的目的。所以这就属于“大笑之”。别人给他讲道理，他还在那嘲笑，甚至羞辱人家。当然对这个事老子是想得开的。告诉坐在对面问他问题的人，怎么接待这些人，对待这些问题。别当回事，不笑不足以为道。这个世界现在已经没有哪件事是大家都赞成的了，所以有人嘲笑这是正常的。你要跟这些人计较，那就把自己的生命全都浪费了。说到这儿我就得插一句话，我觉得这个境界的差别，格局的差别，心胸的差别在什么地方呢？就在对待攻击者的身上。你看孟子也是我们文化里非常不得了的一个人，但是你看孟子的书里，会有一个什么感觉呢？年轻人，气势太盛。孟子对待当时的一些学术大咖，比如说墨子，比如说杨朱，当时杨墨是显学，名气很大。孟子怎么来评价他们呢？孟子就说墨子这个人讲“兼爱，是无父也”。兼爱嘛，你都平等，没有差别嘛，你置于你父亲于何地？没有把你父亲凸显出来，没有把对父亲的爱突出出来，无父也。杨朱不是讲，“拔一毛而利天下，吾不为也”。大家不要误解这句话，它的原意是你拿天下来换我的身体，让我损害自己的生命去换天下，我不干。它是强调自己的生命的重要。“拔一毛而利天下，吾不为也”。杨朱讲“为我”，所以孟子骂他是无君。你老为自己，你把君置于何地？“无父无君是禽兽也”——他骂杨朱和墨子两个人是禽兽。反过来看老子对待这些人的态度是——“不笑不足以为道”，淡然一笑，过了——很值得人佩服的一种态度。这就叫“明月清风”。对待别人的嘲讽，对待别人的攻击，有这样一个态度，也是很不得了的一种智慧与境界。这一段是本章里边的核心。因为我觉得他上中下的这种区分非常明了，很实用。“上士闻道，勤而行之”。坐而论道，不如起来行嘛。大家看道字的写法，首是头脑、思维、想。“走”之旁是行。所以这个道本身就是一个知行统一的概念。“上士闻道，勤而行之。中士闻道，若存若亡。”犹犹豫豫，不坚定，不能够坚定坚持的按照道去做。“下士闻道，大笑之。”我们千万不要做这种老是嘲笑别人，讽刺别人的，否则就会落于下乘，不笑不足以为道，太好了。明月清风一般地对待这种嘲讽辱骂的这种态度。下面这一段开头这句话非常有意思，叫“建言有之”，“建言”就是我们说的常言。常言说得好，这是我们经常用的，所以下面这句话大家注意，不是他本人的话。就是告诉大家了，明确下边讲的很多都是常言，在当时就是一句俗语。他讲的这些道理都是什么呢？都是前边我们讲的“反者，道之动”的例证。所以我在前面给大家说，第四十章是全书的总纲，可以举的例证会无限多，下边都是。“明道若昧”，光明的道路好像是昏暗不明的。为什么？有些给你指出的光明大道说得多么多么得好，指出光明大道简直就是美得不得了，你要小心了，前面有陷阱。真正的大道，反而像是昏暗不明的，就是把路上的艰险，遇到的阻碍，遇到的问题，都给你说清楚，让你看得清楚，这才是明道。给你说这条路没问题，太直了，平坦了，你沿着这条路走，肯定光明无限；沿着这条路走，肯定兴旺发达，一点阻碍都不会有，这个事绝对没问题。坏事了，这个时候你就得小心了。要知道“明道若昧”。再举个关于“朋友”的例子说明这个问题。朋友有三类，友直，友谅，友多闻。第一类的朋友直率，你有问题给你直接指出来。你走的道有问题的时候直接告诉你，跟你讲，怕你犯错误，怕你在这个地方出现问题。不是你的朋友呢？你走在道上遇到什么问题与他有什么关系啊，你问他这条道怎么样？他就告诉你，好好好，走走走，这条路没有任何问题。你给我提点建议，没什么建议，走就是了。你掉到坑里边他管你呀！所以我们说这“明道若昧”，暗昧，昏暗不明。“进道若退”。我们有的时候自己老觉得自己进步太小，人有时候都不免太着急，老觉得“一万年太久，只争朝夕”。只争朝夕，我每天都得进步，我都得看到自己的进步，一感觉到自己没有进步，就着急了。其实你别忘了，人呢，走在路上没有直线的，“进道若退”，有时候我们感觉是退步的时候，其实我们是在进步。比如说练书法，大家都有这个感觉，刚练这几天觉得进步很大，我以后每天按照这个速度会很快成为书法大家，过一段时间感觉怎么回事？怎么我这字越写越差了，还不如开始呢。好多事情开始都是这样。其实这就是我们前进中的一个必然的现象。懂得以退为进，懂得退就是进，有时候退不就是进嘛。“进道若退”，这不就是相反相成嘛。所以我在想，在老子那个时代，你说这些常言都在。这得说中国古代的这些人的哲学的思维水平竟然达到这样一个高度。所以有的时候我们做的事情感觉退步的时候不要着急，退是前进中的必须经历的。就像我们经常讲一个词叫“能屈能伸”，想要伸不得先屈回来吗？这是不是退？退之后才更加有力量，进道若退。“夷道若颣”，颣就是不平，夷就是平，夷道就是平坦的路。真正平坦的路像什么？它是不平的，高低起伏的。为什么？开车人都有一个体会，你说开车的路太平坦了，这就很容易放松警惕了，感觉无聊疲惫了，就很容易出事。假如前边一会儿出现一点坡，则高度警惕，有的不是故意把道做得有坡嘛，这才是平坦的道。所以我们经常讲的一句话叫“曲折是一种常态”，平坦的大道里边有这样的一些坡，不平的地方，这才是真正的大道。它告诉我们的道理就是，其实我们走在路上不会是绝对平坦的。对路上遇到的这些，我们要有高度的戒备和警惕，这样才属于真正的夷道，也就是平坦的大道。“夷道若颣”，又是一个“反者，道之动”，相反相成。“上德若谷”，谷就是无穷无尽。我们经常讲不是虚怀若谷嘛，真正有“上德”的这些表现是什么？就像虚怀若谷。比如说谦虚，听得进别人的意见，比如说做了好的事情，自己把它像山谷里的风一样，过而无形，“上德若谷”，就是讲它“满招损，谦受益”，不自满，做了事情不居功自傲，“上德若谷”。“大白若辱”，“白”，我们在第二十八章讲过，知白守黑，那个时候给大家说过白，白就是内心的光明信念与远大的抱负，内心有光明、信念和远大的抱负，那他就能忍受很多的屈辱。为什么？能屈能伸嘛，有远大的抱负，那么这些羞辱也就不必被自己挂在心中了。知白守黑，内心有光明、信念和远大的抱负，才能守得住这个黑。不管是别人黑，还是有时候的这种自黑，这就是“大白若辱”。说一事，有一次我在云南楚雄给医生讲课。我说你们穿着白大褂，大家把你们叫“白衣天使”，那对病人偶尔几句话不合适的话，也应该不那么太在意了。因为“知其白，守其黑”，忍得屈辱、羞辱，吞得下委屈，也就扩大了格局。“广德若不足”，“广”当然是大的意思。越是有广博的、大的德的人，反而好像自己有缺陷，不足就是不满，满招损，谦受益嘛。知道自己有不足，大成若缺，才能不断地进步，不断地学习，不断地努力，提高自己的境界，让自己的德行更伟大、更广博，“广德若不足”。下面这四个字理解起来不太容易，叫“建德若偷”。这个“偷”字是大家不喜欢的，怎么能跟德并列到一块呢？说到一起呢？首先我们说这个“建德”是什么意思？刚健。刚健的德好像是软弱的样子。这不就又符合“反者，道之动”了吗？偷，懒惰、懈怠、疲软，有着刚健的德的人，他反而正好有的时候表现为他的反面，而不是说我认为自己有这种刚健的德，谁要惹到我了，我一定跟他较量到底，我一定坚咬不放。这其实反而不是刚健的德，也不是强的真正的表现。刚健的德往往表现出宽容，忍让，甚至软、弱、懈怠等，“建德若偷”。当然有人也把这个“偷”解释为偷偷摸摸，意思就是不去表现。这个也说得过去。“质真若渝”，这个“渝”和我们讲的“瑕不掩瑜”意思相似，真的东西不会是完美无缺的。“大方无隅”，最大的方是没有棱角的，没有棱角那不就成了圆了吗？所以我们经常讲“外圆而内方”。“大方无隅”，没有角落，不留死角，这才是真正的大方。其实再说一遍，大家仔细想，这大方已经变成圆了，因为咱们中国人对这个圆的印象非常好。所以老用圆满这样的词来形容一个好的事情。进而言之，人有了这个原则是对的，但是这个原则不是老去像割伤别人，外面是圆的，可以和外界相衔接。而内部方的，坚守自己的原则，所以这叫大方无隅。“大器晚成”，最大的器件最晚做成。这个很好，提醒我们不用着急。想终成大器吗？那就要踏踏实实，不断地努力，不断地学习，机会总是留给有准备的人。心智不成熟的时候，早出名并没有什么太大的好处。因为人早出名，心智不成熟，他一定就气锐，盛气凌人，盛气凌人则敛怨。就会得到很多来自各方很多的这种怨言，而这个就形成自己未来的一种发展的阻碍。所以古人讲，松柏必经岁寒之后，可从栋梁之任。你看松树、柏树经历一次又一次的寒暑的磨练，最后才可成为栋梁之材。人类历史上大器晚成的例子比比皆是，比如，姜子牙八十岁为相。历史上记载了很多人，都是在有准备的情况下遇到机会，把以前自己积累的经验、智慧，充分地发扬出来，终成大器，人生最坏的结局也不过是大器晚成，又有什么可着急，可焦虑的呢？“大音希声”，“希”不是没有。这个“希”大家可以从两个角度来理解，一个“希”是前面有声，而中间出现的停顿，比如，白居易的《琵琶行》，“别有幽愁暗恨生，此时无声胜有声。”前面有声，可是这个地方的停顿，它反而蕴含了更加丰富的内容，用有声表达不出来的这种情感，这是一个希声。“希声”还有一个表现是乐曲结束，声音之后的余响。苏轼的《前赤壁赋》里边叫“余音袅袅，不绝如缕”。这一个也是“大音希声”。《道德经》里面讲的“大音希声”的道理，其实它是有延伸的。一个是说我们的语言。第五章里边讲“多言数穷，不如守中。”发号施令多了，话多了，声多了，唠叨多了，就不起作用了。真正的大音呢，一定是平常少讲，关键时候掷地有声，说得恰到好处——大音希声。一个是说我们的制度。制度太繁琐了，反而它走向了负面，恰到好处就好。“大象无形”，这个在我们前边讲的时候也经常引用。“大象”本来就很大了，反正中国人一开始指的这个“象”，也是拿这个“大象”说事，本来就很大的。当然这个“象”是一个延伸。最大的形象是没有形状的。天有形状吗？风有形状吗？精神有形状吗？理论有形状吗？都没有，“大象无形”。虽然无形却力量巨大。所以我们拿风来说大象无形是最恰当的。没有人看见过风，风是没有形状的，我们只能够通过水面的波纹，麦浪的翻滚，柳梢的摇曳，我们知道风是存在的。虽然无形，但是它客观存在的，并且力量无比巨大。所以我们写文章才经常用这样的词，“民风”“党风”“作风”“家风”。风没有形状，但是力量巨大，“大象无形”，就像道一样。拿什么东西来比方这个道最为恰当？那就是风。道就像风一样，你看不见但它无处不在？“大象无形”。前边这些其实都是一些相反相成的例证，尤其是“大白若辱，大器晚成，大音希声，大象无形”，都已经成了我们生活中常用的成语了。就这一章里边的成语，你算算就有多少！咱们也不说这本书别的方面的价值。单说它在让我们了解中国文化中的成语的角度，它的作用就有这么大，而且这些成语直到今天，我们还经常使用，发挥着巨大的作用。所以，我们说文化，“文”就在这儿。你把它变成自己的，化入自己的内心，化入自己的精神世界，就叫“文化”。大象无形，却力量无尽，永远存在。道隐无名，道是没有名的。你没办法定义它的。第二十五章的时候我们就讲“有物混成，先天地生，寂兮寥兮”，“寂”就是无声，“寥”就是无形。它是无形无声的，你没有办法去定义它。道隐无名，它就隐到事物的背后，但是它却是事物的本质。道隐无名，就像风一样，在万事万物的背后你看不见，但它能吹绿万物，它能够摧枯拉朽，作用无比巨大。下边这句话就好理解了，“夫唯道”，也只有道啊，“善贷且成”，“贷”就是帮助，意思是资助万物，贷款给你，不就是资助你嘛？善于帮助万事万物成长、成功。“道”有多伟大，你看不见。“道”也不求回报，但它帮助万事万物成为现在这个样子。本章内容非常深刻。首先，有一个恒定的标准“道”来衡量事物。“士”可以分出上中下：“上士闻道，勤而行之；中士闻道，若存若亡；下士闻道，大笑之。”胸怀宽广的人对待这事情，如清风掠过，淡然一笑。你笑你的我笑我的，你不笑不足以为道。没有哪一件事情非得是全部大家都认可的。做事情按照“道”去走，被人嘲笑，被人嘲讽，这是正常的。内心应该有这样的宽容，有这样的接纳，有这样的态度。所以下边告诉大家，那个时代的一些常言、俗语，作为第四十章“反者，道之动”的例证：“明道若昧，进道若退，夷道若颣，上德若谷，广德若不足”。我把这两个排列在一块，然后再说“大白若辱”“知白守黑”。是说什么羞辱都受不了的人，受到一点羞辱就暴跳如雷的人，甚至只是自以为受到了羞辱就拔拳相向的人，其实就是自以为刚健而事实上是匹夫之勇，往往会“勇于敢则杀”，所以真正刚健的德反而像软弱的一样。真的完美的东西是有瑕疵的一样，即大成若缺。所以要懂得“知白守黑”，“知荣守辱”。这几个成语前边带过了之后，重点强调“大器晚成”——不着急，有准备终成大器，机会终究会有的。“大音希声”，真正的大音不是絮絮叨叨，而要掌握尺度，“多言数穷，不如守中”，“无声胜有声”，所以要懂得无言之教，大音希声。接着，“大象无形。道隐无名，夫唯道善贷且成”。只有“道”才能善贷且成，资助万物，帮助万物成长，帮助万物成功。这一章给人很多的启发，很多的回味。每个人读，都会有不同的感受。随着年龄的增长，我们也会不断获得新的体会。</t>
   </si>
   <si>
-    <t>第四十二章</t>
+    <t>第四十二章（42）</t>
   </si>
   <si>
     <t>道生一，一生二，二生三，三生万物。万物负阴而抱阳，冲气以为和。人之所恶（wù），唯孤寡不穀（gǔ），而王公以为称。故物或损之而益，或益之而损。人之所教，我亦教之。强梁者不得其死，吾将以为教父。</t>
@@ -633,7 +632,7 @@
     <t>《德经》部分我们今天讲四十二章。老规矩，把以前的这几章我们再顺一下。《德经》从第三十八章开始，第三十八章讲“上德不德，是以有德；下德不失德，是以无德。”第三十九章我们讲了两个重要的部分，一个就是这个“一”，因为第四十二章又出现了这个“一”，就是阴阳两者的相互平衡，形成的统一体。在第三十九章里边有两句话每一次我都要重申一下，以求让大家牢牢地记忆，“贵以贱为本，高以下为基”。第四十章有一个全部这本书思维的总纲，“反者，道之动”。下边举的这些都是“反者，道之动”的一些例证。比如说“弱者，道之用，天下万物生于有，生于无”。第四十一章的时候，我们是花了比较多的时间来说，为什么呢？因为这一章里边有非常多的“反者，道之动”的例证。比如说“大音希声，大象无形，大器晚成……”这些都是我们平时经常讲的成语。上次讲完了大家应该知道了它的出处。那么今天我们讲第四十二章，这一章并不难理解，但是非常的重要。因为这一章开头这段话，大家经常在很多地方看到，比如北京故宫是建筑的典范，故宫的太和、保和、中和三大殿都是三层台基，也就是建在三层高台之上，为什么选择“三”这个数字呢？再比如我所在的学校叫做西安交通大学，在交大的管理学院，我的一个朋友也在那做了一面墙的雕塑：太极，大家有机会到交大管理学院的时候就会看到，就在一楼。这两个地方的解释，用的都是这段话：“道生一，一生二，二生三，三生万物。”我们来解释这段话，原文大家都看到了：“道生一，一生二，二生三，三生万物。万物负阴而抱阳，冲气以为和。”这个“冲”字，读成中，一下就理解了。下面这段话其实大家也耳熟，起码意思在前边已经说过。“人之所恶，为孤寡不穀，而王公以为称。”大家讨厌的孤、寡、不榖，王公却用来称呼自己，这不是我们前面第三十九章的时候已经说过的这个意思嘛。“故物或损之而益，或益之而损。人之所教，我亦教之，强梁者不得其死，吾将以为教父。”这是第四十二章原文。我们一段一段来解释。先说第一段，“道生一”。“一”我们俗称叫太极。其实“一”就是道的具体的特点，强调道就是“一”，是说道的最重要的一个特点，就是它强调阴阳两者的统一，“一”里边蕴含着阴和阳两种力量，两个方面。“道生一，一生二”，这个“一”里边蕴含着“二”，也就是道里边蕴含着阴阳两种力量，两个方面，两种状态。中国人讲，事物都是相互对立而存在的，万事万物归结到最后，它也不会是一个单一的元素。你看咱们中国历史上的《易经》，落到最后就是两个符号，阴和阳。那已经到了事物的极致了，极点了。把阴和阳统一起来叫太极，但是这两个元素是最基本的。所以“一生二”，是说太极道里边蕴涵着阴阳两个方面，两种力量。“二生三”，很多人对这个“二生三”解释得太费劲。“三”是什么？很简单，就是繁体字那个“叁”，就是参。阴阳两者参与到一起，相互作用，形成了万事万物，多简单的事情。它们两者孤阴不生，孤阳不长，两者相互作用，形成万事万物，“三生万物”。所以我们用的那个《中庸》的名言叫“参天地，赞化育”。人能参与到天地之间的运动发展，天地人三才嘛。三才你看人不也参与其中嘛。这个赞可不是赞扬的意思，也是参与的意思。两者参与到一起，产生万事万物，这是从正面。然后再反过来推，既然是三生万物，那么万事万物里边都包含着这两种力量，两个方面，阴阳两个方面，所以叫“万物负阴而抱阳”。随便找，哪一个事物内部都有阴有阳，都包含着阴阳两种状态、两种力量。“万物负阴而抱阳，冲气以为和”。为什么要把这个“冲”念成“中”呢？大家看“冲”的写法，前边这两点其实就代表着阴和阳，那个中就是中和的意思，就是参的意思。阴阳两种力量，中国人把它叫做气，阴气、阳气嘛。通天下一气，形成和谐的、动态的、运动的世界，这就是冲气以为和。这一段讲了我们中国哲学中的宇宙生成模式，也讲了这个世界存在的状态，以及这个状态的原因。这种状态都是阴阳两者运动所形成的，动态的、和谐的状态。冲气以为和。再重复一遍。“道生一，一生二，二生三，三生万物。”所以万事万物都有阴阳两个方面，“万物负阴而抱阳，冲气以为和。”下边就开始讲。用这种思维方式你来理解世界，你就不能只站在一个方面了，明确地告诉你了。事物都是统一的，两个方面不可偏颇，不可偏废。所以对侯王讲，“人之所恶，唯孤寡不穀。”你说大家最讨厌的就是这些词，孤家、寡人、吃不上饭、饿死。可是你看这些王公大人，包括后来的皇帝，他们都拿这个来称呼自己。干嘛呢？“故物，或损之而益，或益之而损。”这个“物”大家不要解释成物质，就是我们中国人常讲的那个“东西”。中国人这个“东西”太奥妙了，什么都可以称之为东西，不管是物质的、精神的都可以称之为东西。所以老子就说你看说到万事万物存在的这些各类各样的东西，“或损之而益”，你以为它受损了，其实它得到了益处。有的时候我们受到一点挫折，我们觉得自己受了多大的这种屈辱一样，可是你知道人都是在不断地受的这种损中逐渐地成长起来的，你认为它是祸，其实它是福，“损之而益”。有的时候你认为自己是得到了，其实反而是一种损失。比如偷了东西的，得到了，其实把人格给损失掉了。有的人用不光彩的手段，不择手段得到的，其实他们损失的反而更大，“或益之而损”。所以老子讲的是相反相成的道理。我们中国人常用什么事情来说这个事？叫破财免灾，叫大难不死必有后福，叫祸福相依，叫塞翁失马焉知非福，你看这讲的都是“损之而益，益之而损”。刚才举的例子不就是这样吗？这侯王王公们不都在损自己吗？把自己叫做“孤寡不穀”。其实有这个提醒之后，反而避免了自己变成孤寡不穀。以前中国人也有这个习惯，给小孩起名起个贱名，好养活。当然现在这种习俗很少再看到了，它讲究的就是“损之而益，益之而损”。民间很多的道理大家也得认真对待，别以为我们上了学之后自己水平就高了，其实真正的高手在民间。很多老人讲的话，到最后你一生体会，反而你发现真的是有道理。“人之所教，我亦教之，强梁者不得其死”。老子也说这些东西，也都是别人教给我的，给我讲的。我再把这些写出来教给大家。这一句我们可得好好地来给大家说道说道。为什么呢？因为这涉及老子的思想的来源，老子的思想来源当然有很多方面，主要的两条，两条道路。一条道路自然就是《易经》。因为你看，《易经》它把这个叫易以道阴阳，老子也讲阴阳，而且这里边的损和益，这不就是《易经》里边的损卦和益卦嘛，损和益这也是《易经》里边经常强调的。另外一个，我觉得这一章里边非常奥妙，一个是讲这阴阳的事情，让我们知道他的思想里边《易经》是中国文化之源，众经之首，损之而益，益之而损。另外一个也表现出他的思想的来源，就是“强梁者不得其死”，这句话也不是老子自己的，它出自《金人铭》。传说黄帝写了六篇铭文，叫《黄帝六铭》。其中有一个是刻在周朝台阶右面立着的金人背后，金人就是青铜做的，这金人的背后有铭文。经过汉朝的刘向《说苑》的考证对比，发现《金人铭》里边的这句话：“强梁者不得其死”。“强梁”就是处处逞强。喜欢暴力的人，最后不会有好的结果。我们讲死得其所，叫得其死，得好死，不得好死，不得其死。强梁者不得其死。说到“强梁”这个词，我想读过《水浒传》的人一定记得，在《水浒传》里边用到“强梁”这个词的时候，是用在了矮脚虎王英的身上。矮脚虎王英，这个是梁山泊里边大家都瞧不上的那么一个人。原来是个车夫，后来抢劫，后来落草。所以用这个词来形容他，“强梁者”。“强梁者不得其死”，老子非常反对强暴，而强调和平、守弱，认为“强梁者不得其死”，“木强则折，兵强则灭”，这是他后边关于这个问题的一个延伸。“吾将以为教父”，这个“教父”就是说，这是别人教给我的，我也把它拿来作为座右铭，来指导我自己。总结一下，大家看这一章，第一段话是我们大家都耳熟能详的，“道生一，一生二，三生万物，万物负阴而抱阳，冲气以为和。”第二段是我们前边讲过的内容，在这个里边又重申了一遍，注意这些重申可不是排版排错了。因为《道德经》里边它讲的几条重要的原则，遇到机会的时候，它就会反复，用重复的方式来强调。“人之所恶，唯孤寡不穀，而王公以为称。”所以对于万事万物而言，对这个世界存在的东西而言，“或损之而益，或益之而损”。有的你觉得是损失了，结果反而是得到了。有的你认为自己得到了，反而是损失掉了。因此不可一概而论。遇到了乐事的时候，不要过于高兴，以免乐极生悲。遇到不好的事，祸事的时候，也不要丧气，因为这些可以成为我们的经验，塞翁失马，焉知非福！这是别人教给我的，我也把它来教给别人。然后下边这句话是老子也非常强调的，“强梁者不得其死”，还是要和平，还是要守弱，处处逞强，总和别人结梁子，最后不会有好的结果。国家也一样，“国虽大，好战必亡”。老子说我也要把这个当作座右铭，这就明显地透露出他思想的来源，一源于《易经》，阴阳之学，损益之论，谦卑之礼。二源于《金人铭》，尤其是《金人铭》里这句话对老子影响是非常大的，所以他把它叫做“教父”，座右铭。</t>
   </si>
   <si>
-    <t>第四十三章</t>
+    <t>第四十三章（43）</t>
   </si>
   <si>
     <t>天下之至柔，驰骋天下之至坚，无有入无间，吾是以知无为之有益。不言之教，无为之益，天下希及之。</t>
@@ -645,7 +644,7 @@
     <t>我们说“反者，道之动”是整个这本书思维的总纲，也就是说它是一种思维模式、思维方法。第四十章一开头就讲“反者，道之动，弱者，道之用。天下万物生于有，生于无。”这里边出现了两个在《道德经》里边非常重要的字，一个是“弱”，也可以称其为“柔”，另一个就是“无”。第四十三章是对这些内容进一步的引申和展开。第一句“天下之至柔，驰骋于天下之至坚，无有入无间”。最柔弱的东西，反而能够攻克最坚硬的东西。那些没有间隙的地方，无形的东西却能够进入，能攻克。就像风，没有什么地方它进不去的。这些就是“道”，道讲完了。老子开始讲“德”。“吾是以知无为之有益”。我从“至柔驰骋于至坚”，“无有入无间”中知道：人类也是一样，有些事情，无为比有为效果更好——“无为之有益”。可是话说回来，“不言之教，无为之益，天下希及之”按照无为的道理去做事，所获得的好处、益处，天下的人却很少能够知道，很少能够达到。这些话该怎样进一步理解呢？老子在第七十章讲过，“吾言甚易知，甚易行，天下莫能知，莫能行”。什么意思？其实，我讲的道理都是非常简单的、平常。但是大家为什么不知道呢？做不到呢？因为这里边就隔了一个东西——欲望。有些事情大家明知道是这么回事，但是很多东西被欲望牵引就变得难做了。就像我们说“不贪为宝”，但为什么还有那么多人上当？有些人上当了还不好意思说出来。因为自己心里清楚，自己是因为贪心才是上当受骗了嘛。没有这个贪心，很多事情理解起来就太容易，太简单了。但一个骗局，往往能骗很多很多人！再说回来，“天下之至柔，驰骋天下之至坚，无有入无间”。天下的“至柔”是什么？无形是风，有形是水。第七十八章就说，”天下莫柔弱于水，而攻坚强者莫之能胜”。这不是正是“天下之至柔，驰骋天下之至坚”吗？天下什么东西最坚硬，石头？水滴石穿；金属？水刀切可以割金属。有什么坚硬的东西是水它克服不了的呢？风更是弥漫天下，摧枯拉朽，无所不在，力量无尽。你说这个东西没有间隙，但是无形的东西，它反而能够穿透它。现在，科学发现有一些微小的东西，比如说中子、粒子、量子……他们是无形的，你看不见，但没间隙的地方，它们都能够进入。我们眼里没有间隙的地方，对于它们来讲，缝隙简直太大了。“无有入无间”，在强调无的东西的作用。道家的“无为”相当一部分内容在讲“无之为”——这些无形的东西、无用的东西的作为。所以，不要把“无”理解为“没有”，把“无为”理解为“不做事”。“吾不言之教”，第二章讲过“行不言之教”，为什么？身教重于言教，话太多了，老去教化，训导别人，反而会起负面的作用。老师也罢，家长也罢，国家的领导也罢，做一个好的榜样，上行下效。孔子也讲了一句话，叫“君子之德风，小人之德草”。这里小人不是道德上的低下，而是指人民、平民、一般人。榜样的“不言之教”就像风一样，一般人就像草一样。风向哪个方向吹，他们跟随着风而倒。无之为所带来的益处，天下却很少有人能够达到——“希及之”！在讲第三十七章的时候我们说，“道常无为而无不为”，道的规律、规则就是“无为”，而“无为”的效果却是“无不为”——覆盖面更广，效果更好。这不就是“无为之益”吗？一开始讲第一章的时候，我就给大家说过，道家讲的“無”和舞蹈的“舞”字形极为相近。因为对于原始人来讲，舞蹈起到的作用实在太大了。有形的几个姿势，产生出的力量却是巨大的。既然是“无”是“无之为”，那么“无用”，也就是“无用之用”。你认为没用的东西，其实不是它没用，只是你没有看见它的用处。书法有什么用，绘画有什么用？不能当吃，不能当穿，可是如果大家否定了这些，那不就进入了一种狭隘的功利主义的境地了吗？人生最没用的事是什么？睡觉。睡着了什么都做不成。小孩最讨厌睡觉了，可是大家都知道现在有多少人被失眠所折磨，为睡不着觉而痛苦。这些“没用”的事你做不成，那么有用的事你也做不来。最后一句，“无为之益，天下希及之”是老子的感慨。大家老看不到这一点，老觉得无为的事情没用。殊不知你不做这些无为的事，就不能真正的有为。不了解这些无用东西的作用，你也就不知道什么才算是真正的有用。从“反者，道之动”，一直到现在，都在讲述一个道理。</t>
   </si>
   <si>
-    <t>第四十四章</t>
+    <t>第四十四章（44）</t>
   </si>
   <si>
     <t>名与身孰亲？身与货孰多？得与亡孰病？是故甚爱必大费，多藏必厚亡。知足不辱，知止不殆，可以长久。</t>
@@ -657,7 +656,7 @@
     <t>前面我们说了第四十三章，最后说“不言之教，无为之益，天下希及之”。然后说这都是前面“反者，道之动”这种思维方式的进一步的延伸和具体的例证。这种方法我们大家已经习惯了，在哲学上叫做“二分法”，叫做“对立的统一”。第四十四章讲的也是这个。一开始先列出来三个对立的事物——名与身、身与货、得与亡，进行比较。“名与身孰亲？”“名”和“身”哪一个更重要？哪一个是对大家来讲是更亲的东西？“身与货孰多？”我们的生命和外在的物质相，财富哪一个更重要？“亲”也罢，“多”也罢，意思都在说哪一个更重要。我们常说“身外之物”，常说名和利生不带来，死不带去。你看，这一章就在解读这个问题了。第三个，“得与亡孰病？”这个好理解，参照我们前面讲的“或损之而益，或益之而损”，是得到的好还是失去的好？哪一个危害更大呢？“病”当然不是什么好词了，“得与亡孰病？”其实在问的时候这个答案已经有了。这就是一种反问的语气，表示强调。因为有的人在名和自己生命的选择之中选择了殉名；有的人，“人为财死，鸟为食亡”——因为财富的事，把自己的生命搭上去了。真的是得到就好，失去就不好吗？比如，我们读像《道德经》这样的书，我们会得到什么？也许什么都没得到，但是我们失去了焦虑，失去了急躁，失去了自高自大，这些东西失去了，那不就是一种得到吗？不是说得到就好，失去就不好。有的东西失去，反而是获得；有些东西得到，反而是真正地失去。三个反问句，答案其实都在里边。下面这几句话，讲得就更深刻了。“甚爱必大费，多藏必厚亡”，对一个东西太珍爱了，最后一定会付出大的代价。比如，有的人他有这种癖好，他喜欢古玩，别人送的别的东西他不要，你拿着古玩一贿赂他就收下来，最后就因为这个自己犯了事儿——“甚爱必大费”。有的人把减肥当作唯一的事业，尝试各种各样靠谱不靠谱的方法，把身体折腾得一塌糊涂，那不就得付出大的代价吗？很多事情都是这样的结果。“甚爱”，太过分了，不是说不好，但是过分了，这就走向了它的反面，物极必反嘛！“多藏必厚亡”，很多东西收敛、搜刮到了，自己把它藏起来，能藏得住吗？最后这个搜刮来的东西一定都成为自己的污点和罪证。多藏必厚亡，“厚”也是大的意思。下边这两句话大家都熟：“知足不辱”。我们知道满足有边界，这样才不会受屈辱。这事我知足，我不卑躬屈膝求别人，我觉得我这个已经很好了，这是我自己奋斗来的，额外的，不择手段得来的东西，我不需要，“知足不辱”。“知止不殆”。这个地方，我得给大家多说几句。老子这个人真的是不得了，他只用一个“走道”的形象，就说清楚了很多问题。我们走在道上，应该注意什么呢？有几个最重要的内容：方向、目标、规则、境界、边界、底线。我们要去什么地方？方向、目标。我们什么时候该停下来呢？只要是道就有边界，道外边往往就是深沟，就是深渊，就是歧路。我们了解边界底线，不贸然地前闯，有“底线思维”，“红线思维”，给我们的欲望划出边界，就是“知足”。知足才能不辱。“知止不殆”，“殆”就是危险失败。知道边界、底线不闯，我们才能没有危险，没有失败。当年杨虎城在陕西把他办公的行园就改名叫“止园”。出处就是这四个字，“知止不殆”。“知足不辱，知止不殆”的意义在哪儿呢？——“可以长久”。其实这些事情不用举太多的例证，为什么？因为例证太多了，不了解边界、底线，冒进、冒险，肯定会导致大的，糟糕的后果。这一章没有什么难以理解的，但是内容也非常深刻，尤其是前边这三个提问或者叫反问，都是我们应该深深思考，并做出回答的。拿我们的生命和名声去交换名利，到底划得来划不来？到底哪个更重要？哪个对我们更亲？身与货和这些财富进行比较的时候，到底哪个更重要？我们拿生命去换财富，回头再拿财富来换健康——有时候，甚至换不回来。“得与亡孰病？”不要认为得到就高兴，失去就不高兴，其实得失就是这样的相反相成。很多事情反而是损之而益，有的是益之而损。祸福相依，相互转化，物极必反。既然物极必反，下面这几句话就好理解了，“甚爱必大费，多藏必厚亡”，因此应该“知足不辱，知止不殆”——知足可以不辱，知止可以不殆。知足、知止，我们才能长久。不管是对于生命，还是对于事业而言，才能稳定致远，长久地发展。这是第四十四章的内容，内容不多，但是我们应该熟记，尤其是几个对偶的句子：“甚爱必大费，多藏必厚亡”；“知足不辱，知止不殆”。</t>
   </si>
   <si>
-    <t>第四十五章</t>
+    <t>第四十五章（45）</t>
   </si>
   <si>
     <t>大成若缺，其用不弊；大盈若冲，其用不穷。大直若屈，大巧若拙，大辩若讷（nè）。躁胜寒，静胜热，清静为天下正。</t>
@@ -669,7 +668,7 @@
     <t>我们先来看一下原文，有几个词我们要注意先区分一下。比如说大辩若讷，这个讷呢，我们知道一个词叫做木讷，也就是说，说话不是那么样的流利，不是那么样的辩才无碍。但实际上在这章里，它所要表达的是谨慎，说话严谨、谨慎。为什么要给大家说“讷”这个字呢？大家知道，毛泽东两个女儿，一个叫李敏，一个叫李讷。可是包括中央电视台的广播员都把这个念成nà，其实这个讷，只有一个读音，应该读作nè（讷）。毛泽东两个女儿的名字出自《论语》，“讷于言而敏于行”。先把这个事情给大家说一下，然后我们从头一句一句来解释。“大成若缺，其用不弊。”这个是在讲，完满的东西都仿佛有缺陷。我们平常讲一句话叫完美诚不易。其实这个世界上没有真正完美的东西，任何事物都是有缺点的。了解到这一点，引申到道家的思想，那么这句话想要表达的真正的含义就是，一个越是有大成就的人，他越了解自己的缺点，越觉得自己有缺点，有缺憾。所以，他就不断学习，不断努力，这样的一种动力，它发挥的作用，那么是无穷无尽的。认识到自己有缺点，这样他才能够很好地避免自己的弊端，很好地使自己的缺点得以改正和进步。这个道理在《道德经》里边多处谈到，比如说第七十一章就在讲，“知不知，上；不知知，病”。你知道自己不知道，这个才是水平高的。你不知道自己不知道，这就出问题了，出弊端了。所以大成若缺，其用不弊。一个越是有大成就的人，越懂得应该不断学习，不断进步，不断努力，不断充电。反而是一些有一点小小成就的人，喜欢到处吹嘘，不把旁边人吹得感觉到活不下去，他都不松口。其实遇到这种人，我们根本不用去揭穿他，淡然一笑就可以了。一个越是喜欢自我吹嘘的人，其实越不会有什么大的成就。反之，大成若缺，其用不弊。其实这个道理不止局限于此，我们还可以把这个道理向更深处延展一下。比如说中国人从月圆月缺，领悟出一个道理，其实任何事物发展到到它的极点的时候，它就会向相反的方面转化。人生的最美的境界，花未全开月未圆。花全开了，就往凋零的方向走了，月圆了就往缺的方向走了。所以在临近全圆和全开那时候，才是最美的境界。其实大家注意，我们在生活中经常喜欢用一个词，来对人表示一种赞赏，叫如日中天。其实这个不是一个好的事情。你说人如日中天，不是马上就说他要走下坡路了吗？用道家的这种思想我们来理解。明白在我们生活中讲的很多事情，和这个道理的吻合。大成若缺，其用不弊。“大盈若冲，其用不穷。”“盈”就是满，“大盈”就是大满。“大盈若冲”，“冲”就是冲虚。我们经常讲，用这个冲虚来代表着谦逊谦虚，就像大家看《笑傲江湖》里边的武当的掌门，冲虚道长，大盈若冲。一个越是智慧高的人，智慧聪明的人，他越谦虚，越谦逊。在前面我们曾经说过，“满招损，谦受益”，这话出自《尚书》——中国第一部历史总集。在《尚书》里边有一篇讲到了君臣之间探讨治国的谋略，大禹手下的第二号人物叫伯益。就给他的领导讲了这样的一句话，“满招损，谦受益”，并且伯益还制作了一件警戒器，叫欹器。这个东西非常奥妙，水装满了就颠倒了，倾覆了。装得不满的时候，它稳稳当当。提醒告诫我们这个道理，“满招损，谦受益。”孔子的后半生这个警戒器也一直放在身旁，这么大的一个学问家，还经常提醒自己，“满招损，谦受益”的道理，何况我们。所以“大盈若冲”！一个越是知识充盈的人，知识多的人，越表现得外在的谦逊谦虚，感觉到自己的不足，不断学习，不断努力。“其用不穷”，这样他的知识才能够更好地发挥作用，它的作用无穷无尽，不会出现上边所说的那些弊端，其用不穷。这都是相反相成的道理，按照这个道理我们再解释下边的内容，就比较容易了。“大直若屈，大巧若拙。”一个越是正直的人，越是有正直的、高尚的境界的人，反而外在表现得都比较随和，对很多的事情不那么喜欢争锋，对很多的事情都能够宽容。若屈并不是真的屈枉，他只是懂得外圆而内方，用这种方式和外面的人相处、相衔接，“大直若屈”。关于“大巧若拙，”这个我们得多说几句，在第二十五章里我们讲过，“大曰逝，逝曰远，远曰反”，这是一个逐步发展的过程。就像中国的艺术品一样，一开始没有技巧，后来学到了很多技巧。真正达到一个更高的境界的时候，反而把这些技巧忘掉了，返璞归真。中国雕塑的最高的境界是什么呢？有机会大家到汉武帝的陵墓——茂陵看一看，就会有所体会。那儿被认为是中国雕塑的顶峰。可是大家进去一看却发现非常奇怪，汉代的雕塑几乎一件精巧的东西都没有，都是那样的笨拙、朴拙。特别是霍去病墓前的《马踏匈奴》，那简直笨拙到了极点。团块、圆雕。可是那是中国象征雕塑的顶峰，正因为它这个拙，反而体现出大气势、大气象、大境界，“大巧若拙。”中国诗歌的最高境界是什么呢？清水出芙蓉，天然去雕饰，自然而然，返璞归真。中国书法的最高境界是什么呢？大的书法家最后写得越来越笨拙，越来越稚拙，反而开拓出一片新的气象。我读过一本书法书，是凌云超先生的《中国五千年书法史》。凌云超先生讲到这样一件事，他说中国的书法到后来写得越来越精巧，越来越美，但是像小家碧玉。而中国早期的书法，比如说石鼓文、金文，如旷野风月，给人一种大开大合的气象，这当然是我们在欣赏过程中感觉到的。越是这种稚拙、朴拙、笨拙，反而给人带来更强烈的一种审美的气势和感觉，崇高的一种味道。所以“大巧若拙”。其实《道德经》里边主要讲的并不只是这些，主要说的是人格。一个人格发展到一种高点的时候，他就达到了一种自然而然，返璞归真，忘记了那些小的技巧，心眼、套路，回归到一种真正的高尚的人格的境界。“大巧若拙”，返璞归真，自然而然，明月清风。这是我们说“大巧若拙”。“大辩若讷”。“讷”字我们前面解释过了，这个意思也就非常清楚。真正辩才高的人，他出语反而非常谨慎，让人感觉到仿佛他语言不是那么样的流畅，辩才无碍。其实他不只是为了用语言和人争锋，用语言和人争辩，出语谨慎，这也是我们讲的道家思想里边的一个重要的方面，这样的人才是真正有大的这种辩才的人，“大辩若讷”。下边这几句话原文上就有争论了。我们按照原文先解释一下。“躁胜寒，静胜热”。这个“躁”，表面上意思是急躁，燥热，实际上在讲的是运动。运动可以战胜寒冷。“静胜热”是说冷静可以战胜昏热。因为比如说我们夏天的时候用冰镇，这个方式可以解暑，战胜暑热，但这个地方要讲的实际上是内心的这样的一种冷静，可以战胜我们头脑发热，“静胜热”。但有的人也认为，其实这句话应该是静胜躁，寒胜热。这样和原文连接起来就更顺了，我倒是同意这样的一种说法。因为比如说我们夏天的时候用冰镇，这个方式可以解暑，战胜暑热，所比喻的也是冷静下来时才能战胜头脑发热，而且句式更为对称。现在很多本子也这样做了这样的一种改动。我觉得这个说法更为成立。总之都是讲，内心冷静、宁静、安静，它可以战胜我们的急躁。如果我们能够保持内心的宁静、安静、冷静，这样就可以战胜我们的浮躁、急躁、暴躁、狂躁，宁静以致远，这个和原文意思比较吻合。寒胜热，也是这样一个意思的表现，就像我们刚才说的，一个人冷静下来，可以战胜头脑发热，万物静观犹自得，我们冷静下来才能看清事物的本来面貌，冷静下来才能找到解决问题的正确方法。所以这六个字，大家不妨把它理解为静胜躁，寒胜热。这样后边这句话就自然而然地引申出来了，“清静为天下正”。我们保持内心的清静，一个王者、统治者、领导者保持内心的清静，这样才能够引导天下走上正道。“我好静而民自正”，“清静为天下正”，让内心的清静、冷静、宁静，又具备这样的一种修养。这才能够引导天下走向正道。这个是天下最正的一种领导的方式方法，也是我们修养的由内圣而外王的一种正确的修养的方式方法。</t>
   </si>
   <si>
-    <t>第四十六章</t>
+    <t>第四十六章（46）</t>
   </si>
   <si>
     <t>天下有道，却走马以粪；天下无道，戎马生于郊。祸莫大于不知足，咎（jiù）莫大于欲得。故知足之足，常足矣。</t>
@@ -681,7 +680,7 @@
     <t>“天下有道，却走马以粪；天下无道，戎马生于郊，祸莫大于不知足，咎莫大于欲得，故知足之足，常足矣。”这段话也是《道德经》里边非常精彩的一章。因为它体现了我们中国人对待战争的态度，对待和平的热爱。前面我们讲的第三十章的内容，不知道大家是否还有印象，“师之所处，荆棘生焉。”军队打过仗的地方，一片衰草枯杨，断壁残垣，“大军之后，必有凶年。”打过仗以后，灾荒瘟疫都来了。第三十一章，老子讲得更为沉痛，说中国人把战争当作丧礼一样来对待，“以悲哀泣之，以丧礼处之，胜而不美，胜而美者是乐于杀人。”我以前讲过，通过“四大名著”让国外了解我们的文化，效果恐怕不尽如人意，应该让他们看什么呢？让他们看《道德经》，这部能真正代表中国人思想理念、境界和智慧的经典，像我们讲过的三十章、三十一章和现在要讲的第四十六章，就是如此。“天下有道”，普天下清明有道，这个“天下”包括各个诸侯国了。“天下有道，却走马以粪”，“却”就是推却，“走马”就是跑马，也就是好马。这好马不用来打仗，离开战场，推却战争，干吗呢？回来耕田。当然，古人耕田是要上肥的，撒上粪肥，马耕着田，把地耕好，也就是我们经常讲的，卸甲归田，“卸马归田”，把马从战场上拉回来，干它的本务工作。“天下无道，戎马生于郊”，普天下无道的时候，混乱不堪不清明的时候，是什么情况呢？战马把小马驹生到了战场之上，“郊”就是郊野，此处指疆场，战马把小马驹生到了疆场之上。打仗公马不够用了，母马也上去了，最后出现这种情况——“戎马生于郊”，说得非常形象。我要重点强调一下，这四句是以马喻道，马之却为有道，戎马生于郊为无道，也就是以马的“却”与“生”，比拟天下之有道与无道：以“粪马”与“戎马”，象征国家之治与不治。比喻巧妙，寓意深远。纵观《道德经》的治国之道，当以无为自然以养民，以无欲之事而安民。好像马匹一样，虽是有用之物，用之于疆场可以卫国，用之于战阵可以御敌，用之于农事可以耕田。道行天下之时，国泰民安，上下祥和，无兵甲之患，天下太平安然，百姓安居乐业，故用走马耕田种地，积粪肥田。所以说：“天下有道，却走马以粪。天下无道，戎马生于郊。”太精辟了。“祸莫大于不知足，咎莫大于欲得。”这个大家清楚，老子生活在春秋，春秋无义战——没有什么正义的战争。大家都为了争夺财富、城池、人口，相互混战，战火频仍，烽火四起。面对这种情况，老子在当时总结出这两句话：“祸莫大于不知足，咎莫大于欲得。”惹祸最大的原因在哪呢？在于内心的贪念，贪心不足，得到了还想更多，只会做加法，不会做减法。“人心不足蛇吞象”，其实这句话，不单只对当时的现实概括，对我们现在也有这种启发的意义。生活中这种情况也比比皆是：有了还想更有，多了还想更多，衣架里边永远缺一件衣服，房子永远少一间，总是处在不知足的这种状态。“祸莫大于不知足，咎莫大于欲得”，“咎”罪过，过错，动辄得咎，过往不咎。这个“欲得”，就是别人的东西，自己也想要，把别人东西尽量弄到自己手上——这就成了一种罪过了。前面讲“不知足”是一种“祸”，祸患，而“欲得”就是一种罪过了，甚至可以是一种罪恶。别人的城，想要；别人的人民，想要，什么都想占有，用占有的态度对待这个世界，天下是我的。他说古代封建时代皇帝是什么样子呢？“离散天下人之儿女，屠毒天下人之肝脑，以博我一人之产业。”是说皇帝他觉得天下都是自己的，什么东西想拿就拿，想要就要，想占有就占有。这不就是“欲得”吗，这不就是一种大的过错、罪过吗？“咎莫大于欲得。”这个事情该怎么样来处理呢？该我们得的，我们应该得，不该我们的，“虽一毫而莫取也”。这段话大家也知道，东坡先生的《前赤壁赋》，“物各有主，苟非吾之所有，虽一毫而莫取。”划清边界，该得的得，不该得的不要老去强占，不要老是欲得。我们有了边界、底线、标准，那么就知道知足，知足的满足才是长久的满足。知足者富，所以如果永远处在不知足的状态，人也就永远不会有心灵的安宁。我们把这段话和第四十四章联系起来理解就更加明确了。第四十四章最后的三句话讲，“知足不辱，知止不殆，可以长久。”这一章说，“祸莫大于不知足，咎莫大于欲得。故知足之足，常足矣。”</t>
   </si>
   <si>
-    <t>第四十七章</t>
+    <t>第四十七章（47）</t>
   </si>
   <si>
     <t>不出户，知天下；不窥牖（yǒu），见天道。其出弥远，其知弥少。是以圣人不行而知，不见而名，不为而成。</t>
@@ -693,7 +692,7 @@
     <t>由于这两章的内容非常相吻合、相近，所以我们合到一起作为一章来讲解。四十七章讲的是一个什么事儿呢？是说人的感性认识，从哲学上说就是我们的感官接触客观世界，有时候接触得多了，它反而会造成一种迷乱和混乱，要通过人的智慧、理性认识，这样我们才能了解事物的规律，也就是这一章里边所说的“天道”。在这个基础上，我们一句句来解释。“不出户，知天下。”“户”就是门户，也就是大门。我不用走出家门，不用去外边到处跑，也能了解天下的大事。为什么？因为道家认为，天下大道归根到底，融于人的内心。内心里边有道，也就了解了天下的正道，了解了天下的大事。“不窥牖，见天道。”“窥”，从小孔里看；“牖”，就是窗户。我不用通过窗户去看，也知道天地之间日月星辰运行的规律。所以你看这个地方，“出户”是行走，出行，行万里路；“窥牖”是眼睛看，用感官接触客观世界，我不用这样。所以这个地方大家就感觉到，直观的一开始看，就觉得老子这个人有点轻视感性认识，人得通过实践嘛，人得通过感官接触客观世界，才能产生对客观世界的认识。是不是老子把这些东西全部都否认了呢？不是的。因为大家从书里已经看得非常的清楚，《道德经》举了很多生活中的例子，比如说“治大国若烹小鲜”，比如说“凿户牖以为室”，比如“说三十辐共一毂”，前面讲过的，这不都是生活中的例证吗？他对这个东西也很熟悉，怎么知道的呢？通过接触、了解。为什么在这一章里一开始他就讲这个事呢？要落到下面这八个字上。“其出弥远，其知弥少。”“弥”就是越来越，有的人走的地方越多，见得越多，不懂得甄别，不懂得筛选，不懂得提炼概括，“乱花渐欲迷人眼”，出得越远，反而了解到的真知越少，进步越少，为什么？不懂得反观自省，不懂得人心像一面镜子，如果你这个镜子是被灰尘蒙蔽的，你见得越多，其实反而获得的真知越少。这八个字在强调什么？我们要反观自省，要自我修行，自我修养，从哲学上说，从那些感性认识要上升到一种理性认识，达到对事物本质和规律的认识。所以你看，天下、天道代表着对事物全面的、本质的、规律性的认识，这个规律性的认识，需要我们安静地学习，在家里边读古往今来的著作，这不也是“不出户”嘛，也是“不窥牖”！我们了解这些间接的经验，从前人那里得到根本性的、全面的、通过理论阐释的这些知识，我们才能更了解事物的本质，更了解事物的规律。所以不要只把希望寄托在我们出去跑一跑，看一看，以为这样我们的知识就会越来越深刻，很多事情其实要通过理性的思维，这样我们才能进入到对事物本质和规律的认识，“其出弥远，其知弥少”。如果从中国的文化的角度来进一步理解的话，它还探讨一个什么问题、强调一个什么问题呢？就是人的品德。“大道之行，以心之知。”就是我们的心，我们的自我的内在的精神世界，这是道的重要的方面。所以很多人认为知识就是智慧，知识就是品德。不是的，很多人知识很多，不一定有智慧，知识多也不一定有境界、有品德。所以《道德经》强调的根本的“知”，从前面的比较中，相对于我们的感官而言，是人的理性的思维，理性认识、智慧，相对于外面的世界而言，它又是人的道德品德、人的品德。明朝的时候，关学的代表人物冯从吾先生讲过的一句话，我觉得冯从吾先生的这句话就非常能够解释这个道理，冯先生认为，古往今来的大学问都不出乎三句话：“做个好人，存点好心，行些好事。”做个好人，心正，身安，魂梦稳；行些好事，天知，地鉴，鬼神钦。所以一个人内心的品德、境界，通过自我的反省，自我的修养，达到了一个更高的水平，返璞归真，“归根曰静”，这些也是通过内在的自我修养来达到的。所以《道德经》认为人的理性认识，人这样的内心、这样的根本，它可以通过“不出户”、“不窥牖”，也可以自我修养，自我认知，不断地进步以达到。“是以圣人不行而知，不见而明，不为而成。”“是以圣人不行而知”，“是以”，“是”就是这样，“以”就是用，“是”可以解释为所以。“圣人”，好的统治者、领导者，在《道德经》称其为圣人。这些圣人，好的领导者、统治者要经常反躬自省，要经常内心关照，提高自己对大道和规律的认知水平。“不行而知”，不用到处跑，这一点也是可以得到的。“不见而明”，不用亲自去看，也能够明了道理，明了了这个道理，那就内心清净、无欲。“不为而成”，“不为”就是无为，就是按照大道的方式自然而然地去做，而不去妄为，这样一切都会顺理成章。这是我们第四十七章里边讲的内容，字虽然不多，但道理需要我们认真体会，“不出户，知天下；不窥牖，见天道。其出弥远，其知弥少。是以圣人不行而知，不见而明，不为而成。”当然对这一章的更进一步的理解需要我们和第四十八章，也就是我后面要讲的这一章相互参照，我们对这个理解才会更深刻、更准确。一开始就给大家说第四十七章、第四十八章我们要合起来，相互参照，为什么？这两章的内容讲的是非常吻合的，事实上也应该是一章的内容。第四十七章里边讲，“其出弥远，其知弥少”，第四十八章一开头就讲：“为学日益，为道日损。损之又损，以至于无为，无为而无不为。”这八个字一下子和上边的内容就衔接起来，为什么跑得越远反而知道的越少，这是站在道的角度来讲的。“为学”，在学知识，学到的知识内容越来越多。当然从学知识的角度来讲，这是非常有益的，不断地增多，可是我们获得很多的东西，见到了很多的东西，其实对我们了解根本性的规律和本质，了解大道并没有好处。站在一个更高的层次理解，就是说我们“为学”，讲究的是越多越好，见得多，看得多，见多识广。但是“为道”讲究的是什么呢？讲究的是内心的修行，讲究的是减少，用我们前面讲的话来讲，为学做的是加法，为道做的是减法，减少我们内心的欲念，减少我们的贪念，减少我们对很多问题的一种受了外界的影响而导致的内心的纷扰、困惑、迷乱，把这些东西损之又损，一点一点地把它减少，就像那镜子的灰尘一点点擦掉一样，“损之又损，以至于无为。”“无为”就是自然而为，把欲望减少，减少再减少，就达到了一种“无为”的境界，没那么多的贪念，没那么多的纷扰。我们用镜子来照这个天下，来照事物，万物进入到镜子里边，呈现出它本来的面貌。我们了解了事物的本质规律，了解了大道按照它来做，“无为而无不为”达到的是“无不为”的效果。所以在这儿借着这个机会，我再说一下道家自然无为的具体的含义：第一，不妄为；第十六章里边就讲，“不知常，妄作，凶。”你不了解事物的规律、规则，瞎折腾、胡折腾，那结果是非常糟糕的。我们“损之又损”，减少了这些遮挡着我们的认识，遮挡了我们的心窍的这些外在的事物、灰尘、迷乱，我们就照见了事物的本质和规律，我们就“不妄为”。第二，不多为；抓住关键，举重若轻，静观，看到事物的本质，找到解决问题的正确的方法，抓住关键，举重若轻。第三，有所不为；人要想有所为，必须有所不为，要想有所得，必须有所舍。我们舍弃了那些阻碍了我们正确行动、阻碍我们沿着大道行走的那些纷纷扰扰，这样能达到一个无不为的效果，也就是覆盖面广，效果更好，“无为而无不为”。下面这一段就讲，按照“无为”的方式来理解天下万事万物。“取天下常以无事，及其有事，不足以取天下。”“取天下”的规则是什么呢？“无事”。“无事”就是不多事，不干涉，不扰民，这样一切就自然而然顺理成章。所以第五十七章里边讲的这个事情就比较明确，“我无事而民自富，我无为而民自化”。“及其有事”，如果老是多事，老是妄为，不懂得事物的规律、规则，瞎折腾、胡折腾，这就是“及其有事”。则“不足以取天下”，那就不能够获得天下。得到的天下也得失去，因为它违背了大道。</t>
   </si>
   <si>
-    <t>第四十八章</t>
+    <t>第四十八章（48）</t>
   </si>
   <si>
     <t>为学日益，为道日损。损之又损，以至于无为，无为而无不为。取天下常以无事，及其有事，不足以取天下。</t>
@@ -705,20 +704,19 @@
     <t>由于四十七、四十八这两章的内容非常相吻合、相近，所以我们合到一起作为一章来讲解。四十七章讲的是一个什么事儿呢？是说人的感性认识，从哲学上说就是我们的感官接触客观世界，有时候接触得多了，它反而会造成一种迷乱和混乱，要通过人的智慧、理性认识，这样我们才能了解事物的规律，也就是这一章里边所说的“天道”。在这个基础上，我们一句句来解释。“不出户，知天下。”“户”就是门户，也就是大门。我不用走出家门，不用去外边到处跑，也能了解天下的大事。为什么？因为道家认为，天下大道归根到底，融于人的内心。内心里边有道，也就了解了天下的正道，了解了天下的大事。“不窥牖，见天道。”“窥”，从小孔里看；“牖”，就是窗户。我不用通过窗户去看，也知道天地之间日月星辰运行的规律。所以你看这个地方，“出户”是行走，出行，行万里路；“窥牖”是眼睛看，用感官接触客观世界，我不用这样。所以这个地方大家就感觉到，直观的一开始看，就觉得老子这个人有点轻视感性认识，人得通过实践嘛，人得通过感官接触客观世界，才能产生对客观世界的认识。是不是老子把这些东西全部都否认了呢？不是的。因为大家从书里已经看得非常的清楚，《道德经》举了很多生活中的例子，比如说“治大国若烹小鲜”，比如说“凿户牖以为室”，比如“说三十辐共一毂”，前面讲过的，这不都是生活中的例证吗？他对这个东西也很熟悉，怎么知道的呢？通过接触、了解。为什么在这一章里一开始他就讲这个事呢？要落到下面这八个字上。“其出弥远，其知弥少。”“弥”就是越来越，有的人走的地方越多，见得越多，不懂得甄别，不懂得筛选，不懂得提炼概括，“乱花渐欲迷人眼”，出得越远，反而了解到的真知越少，进步越少，为什么？不懂得反观自省，不懂得人心像一面镜子，如果你这个镜子是被灰尘蒙蔽的，你见得越多，其实反而获得的真知越少。这八个字在强调什么？我们要反观自省，要自我修行，自我修养，从哲学上说，从那些感性认识要上升到一种理性认识，达到对事物本质和规律的认识。所以你看，天下、天道代表着对事物全面的、本质的、规律性的认识，这个规律性的认识，需要我们安静地学习，在家里边读古往今来的著作，这不也是“不出户”嘛，也是“不窥牖”！我们了解这些间接的经验，从前人那里得到根本性的、全面的、通过理论阐释的这些知识，我们才能更了解事物的本质，更了解事物的规律。所以不要只把希望寄托在我们出去跑一跑，看一看，以为这样我们的知识就会越来越深刻，很多事情其实要通过理性的思维，这样我们才能进入到对事物本质和规律的认识，“其出弥远，其知弥少”。如果从中国的文化的角度来进一步理解的话，它还探讨一个什么问题、强调一个什么问题呢？就是人的品德。“大道之行，以心之知。”就是我们的心，我们的自我的内在的精神世界，这是道的重要的方面。所以很多人认为知识就是智慧，知识就是品德。不是的，很多人知识很多，不一定有智慧，知识多也不一定有境界、有品德。所以《道德经》强调的根本的“知”，从前面的比较中，相对于我们的感官而言，是人的理性的思维，理性认识、智慧，相对于外面的世界而言，它又是人的道德品德、人的品德。明朝的时候，关学的代表人物冯从吾先生讲过的一句话，我觉得冯从吾先生的这句话就非常能够解释这个道理，冯先生认为，古往今来的大学问都不出乎三句话：“做个好人，存点好心，行些好事。”做个好人，心正，身安，魂梦稳；行些好事，天知，地鉴，鬼神钦。所以一个人内心的品德、境界，通过自我的反省，自我的修养，达到了一个更高的水平，返璞归真，“归根曰静”，这些也是通过内在的自我修养来达到的。所以《道德经》认为人的理性认识，人这样的内心、这样的根本，它可以通过“不出户”、“不窥牖”，也可以自我修养，自我认知，不断地进步以达到。“是以圣人不行而知，不见而明，不为而成。”“是以圣人不行而知”，“是以”，“是”就是这样，“以”就是用，“是”可以解释为所以。“圣人”，好的统治者、领导者，在《道德经》称其为圣人。这些圣人，好的领导者、统治者要经常反躬自省，要经常内心关照，提高自己对大道和规律的认知水平。“不行而知”，不用到处跑，这一点也是可以得到的。“不见而明”，不用亲自去看，也能够明了道理，明了了这个道理，那就内心清净、无欲。“不为而成”，“不为”就是无为，就是按照大道的方式自然而然地去做，而不去妄为，这样一切都会顺理成章。这是我们第四十七章里边讲的内容，字虽然不多，但道理需要我们认真体会，“不出户，知天下；不窥牖，见天道。其出弥远，其知弥少。是以圣人不行而知，不见而明，不为而成。”当然对这一章的更进一步的理解需要我们和第四十八章，也就是我后面要讲的这一章相互参照，我们对这个理解才会更深刻、更准确。一开始就给大家说第四十七章、第四十八章我们要合起来，相互参照，为什么？这两章的内容讲的是非常吻合的，事实上也应该是一章的内容。第四十七章里边讲，“其出弥远，其知弥少”，第四十八章一开头就讲：“为学日益，为道日损。损之又损，以至于无为，无为而无不为。”这八个字一下子和上边的内容就衔接起来，为什么跑得越远反而知道的越少，这是站在道的角度来讲的。“为学”，在学知识，学到的知识内容越来越多。当然从学知识的角度来讲，这是非常有益的，不断地增多，可是我们获得很多的东西，见到了很多的东西，其实对我们了解根本性的规律和本质，了解大道并没有好处。站在一个更高的层次理解，就是说我们“为学”，讲究的是越多越好，见得多，看得多，见多识广。但是“为道”讲究的是什么呢？讲究的是内心的修行，讲究的是减少，用我们前面讲的话来讲，为学做的是加法，为道做的是减法，减少我们内心的欲念，减少我们的贪念，减少我们对很多问题的一种受了外界的影响而导致的内心的纷扰、困惑、迷乱，把这些东西损之又损，一点一点地把它减少，就像那镜子的灰尘一点点擦掉一样，“损之又损，以至于无为。”“无为”就是自然而为，把欲望减少，减少再减少，就达到了一种“无为”的境界，没那么多的贪念，没那么多的纷扰。我们用镜子来照这个天下，来照事物，万物进入到镜子里边，呈现出它本来的面貌。我们了解了事物的本质规律，了解了大道按照它来做，“无为而无不为”达到的是“无不为”的效果。所以在这儿借着这个机会，我再说一下道家自然无为的具体的含义：第一，不妄为；第十六章里边就讲，“不知常，妄作，凶。”你不了解事物的规律、规则，瞎折腾、胡折腾，那结果是非常糟糕的。我们“损之又损”，减少了这些遮挡着我们的认识，遮挡了我们的心窍的这些外在的事物、灰尘、迷乱，我们就照见了事物的本质和规律，我们就“不妄为”。第二，不多为；抓住关键，举重若轻，静观，看到事物的本质，找到解决问题的正确的方法，抓住关键，举重若轻。第三，有所不为；人要想有所为，必须有所不为，要想有所得，必须有所舍。我们舍弃了那些阻碍了我们正确行动、阻碍我们沿着大道行走的那些纷纷扰扰，这样能达到一个无不为的效果，也就是覆盖面广，效果更好，“无为而无不为”。下面这一段就讲，按照“无为”的方式来理解天下万事万物。“取天下常以无事，及其有事，不足以取天下。”“取天下”的规则是什么呢？“无事”。“无事”就是不多事，不干涉，不扰民，这样一切就自然而然顺理成章。所以第五十七章里边讲的这个事情就比较明确，“我无事而民自富，我无为而民自化”。“及其有事”，如果老是多事，老是妄为，不懂得事物的规律、规则，瞎折腾、胡折腾，这就是“及其有事”。则“不足以取天下”，那就不能够获得天下。得到的天下也得失去，因为它违背了大道。</t>
   </si>
   <si>
-    <t>第四十九章</t>
+    <t>第四十九章（49）</t>
   </si>
   <si>
     <t>圣人无常心，以百姓心为心。善者，吾善之；不善者，吾亦善之，德善。信者，吾信之；不信者，吾亦信之，德信。圣人在天下歙（xī）歙，为天下浑其心。百姓皆注其耳目，圣人皆孩之。</t>
   </si>
   <si>
-    <t>圣人没有固执不变的思想，而是把百姓的思想当作自己的思想。。善良的百姓我善待他们，不善良的百姓我也善待他们，结果就会使他也变得善良；讲诚信的人我以诚信对待他们，不讲诚信的人我也以诚信对待他们，结果就会使他也变得诚信。圣人领导天下，收敛自己的私欲，使天下百姓的心灵都变得淳朴。百姓都只关注耳听眼见的事，而圣人要使他们都变得像无知无欲的婴儿一
-样。</t>
+    <t>圣人没有固执不变的思想，而是把百姓的思想当作自己的思想。。善良的百姓我善待他们，不善良的百姓我也善待他们，结果就会使他也变得善良；讲诚信的人我以诚信对待他们，不讲诚信的人我也以诚信对待他们，结果就会使他也变得诚信。圣人领导天下，收敛自己的私欲，使天下百姓的心灵都变得淳朴。百姓都只关注耳听眼见的事，而圣人要使他们都变得像无知无欲的婴儿一样。</t>
   </si>
   <si>
     <t>第四十九章是《道德经》里边比较重要的一章，因为这里边有一句话大家都很熟悉，我们领导者讲话的时候也经常引用，就是以“百姓心为心”。从前面讲的内容，大家会知道这是一个通过换位思考，得出来这样的一种结论。这一章开头这句话我们先说一下。“圣人无常心，以百姓心为心。”是说一个好的领导者、统治者，不要老固执己见。“常心”就是固定的心思，自我的执着，不要老固执己见，不要老把自己的意志强加给别人，乃至强加给人民。应该怎么样呢？换位思考，将心比心，“以百姓心为心”，倾听民众的呼声，关注民众的利益，吸取民众的智慧，这都是“以百姓心为心”的表现。我们先体会一下这一章的宗旨在讲什么？其实这个道理就是讲了，换位思考，将心比心。百姓善良，我也对他善良；不善良，我也对他善良；信任我的，我信任他；不信任我的，我也信任他。干吗呢？这样我就能让人向善，让大家讲诚信。最后这一段就说一个好的领导者、统治者，让百姓都回归到他本来的这种生活，关注的是自己的生活中的事情。不要想那么多，不要心思混乱，不要烦乱，这样才能够形成一种良好的和谐的状态。这是老子的想法。我们一句一句来解释。“圣人无常心”，我再重申一遍，“圣”的繁体字，上面是个耳和口——聖，这两个字并列就代表着通达事理，下面是个王，也就是说一个好的领导者、领导人称其为“圣”。在这一章里体现得最为明显。“圣人无常心”，有的本子也叫“常无心”，意思都是一样的，就是不固执己见，没有自己僵化固定的思维，懂得换位思考。其实关于这个意思，我们通过前面讲过的第二十二章参照着理解，就比较容易了。我在前面多次说过，读《道德经》最好的方法就是不看注解，以经解经，相互参照，明白它要讲的真正的含义，谁的解读也不如他本人对这个东西的解释更符合他的本意。第二十二章里边就讲“不自是”“不自见”“不自矜”“不自伐”这“四不”。“不自是，故彰。不自伐，故有功。不自矜，故长。”这样我们才能不断成长，不断进步。一个好的领导人也是这样的，领导者、统治者，也应该“四不”，也就是“无常心”。你没有这样的智慧，老是固执己见，老是自我吹嘘，老是自我夸耀，老是觉得自己了不起，那你就没办法换位思考，将心比心了。所以“无常心”才能以百姓之心为心，倾听民众的呼声，吸取民众的智慧，关注民众的利益。沿着这个思路下面也好理解了。“善者，吾善之；不善者，吾亦善之，德善。”善良的人我用善良去对待他，不善良的人，我也用善良的方式去对待他，干嘛呀？教化、感化，这样我就得到了真正的善良。为什么呢？你这样做，起代表带头作用，大家也就人心向善了。大家注意这个“德”，王弼的解释非常明确，“德者，得也”，这样做就得到了这个天下、这个社会，这个国家就会人心向善。“信者，吾信之；不信者，吾亦信之，德信。”信我的人，我相信他，我跟他讲诚信；不相信我的人，我也相信他，跟他讲诚信。干嘛呀？这样天下人就会觉得诚信可贵，也就往诚信的方向去努力去发展了——“德信”。“圣人在天下歙歙”，“歙”就是合，就是收敛。你说圣人怎么样领导、管理这个天下呢？先要收敛自己的欲望，要想领导好别人，你先领导好自己，要想领导好自己，你先领导好自己的情绪，领导好自己的欲念，上梁不正则下梁歪嘛。“歙歙”，收敛自己的欲望，减少自己的欲念。“为天下浑其心”，让这个天下都怎么样呢？大家都没那么精明。不总是为了什么事都去争，“浑其心”，都那么样地浑厚、淳朴、厚道，关心自己的现实生活，而不是那么多纷乱的思维，那么多胡乱的想法，那么多的技巧、智谋、套路、心眼，用这种方式让大家和谐相处。“圣人皆孩之”，一个好的领导者把天下人都当作儿童，当作自己的孩子，一方面对他们非常关爱，另一方面也不要让百姓人心混乱，都像孩童一样纯净、淳朴。当然了，后边这一段大家也看得出来，这也是老子的一厢情愿。他希望统治者减少自己的欲望，天下人跟着也减少自己的欲望，关注自己的现实的生活，没有那么多的争斗、心眼、套路、技巧、欺骗、欺诈。这是老子生活的理想状态，也是他认为是和谐世界的前景，我们权当这也是他的一种理念和希望，毕竟这个社会的和谐也是我们的一种希望。只是他这种方法大家要辩证对待，大概用这种方法实现天下的太平，也只能是一种理想和理念，很难真正得以实现。但这一章里边大家要注意，开头这句话，我们要熟记，因为在我们国家的领导人的很多讲话里边都能看到这句话的出现，“以百姓心为心”，这是道家思想里边非常重要的一句话，让我们感觉到老子这个人在他冷静的、甚至有点冷酷的外表之下，内心涌动的热流，对于天下人的关注，对于天下人的关爱。这一章的原文我们解释完了，再强调一下这章的逻辑和重点，这章里边的关键在哪呢？这一章里边的关键是讲“圣人”和“百姓”，他们是国家不同层面的人，这一章讲究什么呢？讲究各安其位，各循其理。老子对这些做统治者的讲，你们要“以百姓之心为心”，善良的人呢你要好好地对待，不善良的人呢你也要好好对待，这样你才能得到这个国家人心向善的风气。信你的人你要讲诚信，不信你的人你也要讲诚信，这样才能得到天下诚信的风气。“圣人在天下”，圣人在上，领导天下。应该怎么样呢？怎么样叫循理循道呢？应该清静，无为，少折腾，少多事儿，这是上边的理，给他们讲的，你应该这样做，收敛自己的欲望，减少自己的奢靡、奢华，“清静为天下正”，这是对他们。对下边怎么讲呢？你这个在上边的人应该让下边遵循一个什么样的道理呢？“为天下浑其心”，让这个百姓浑厚，淳朴，宁静，没有那么多纷乱的想法，那么多技巧、心眼、套路、欺诈、欺骗，按照这个方向，百姓都关注自己现实的生活，把自己的日子过好，少管别的事儿，你让百姓能够做到这一点，上边的管上边的事，循上边之理，下边的循下边之理，这天下不就和谐了嘛。大家看出来了吧，“圣人皆孩之”，好的领导，一个国家的领导者，让这国家的百姓都像小孩一样，纯净、淳朴，没有那么多的欺瞒欺诈。上按上边的道理，下按下边的道理，这不就形成了一个和谐的状态了嘛。我们知道，真正的和谐是有差别的统一，大家都应该有表达自己的意见的机会，表达自己观点的机会，“各美其美，美人之美”，有差别的统一。但是老子这个地方讲的道理不是这样的，他讲的是“圣人无常心”，你要考虑到百姓，百姓在圣人的领导下应该怎么做呢？应该浑厚淳朴，没有那么多的智谋、欺诈、心眼，关注自己的现实生活，干好自己的事情，像儿童一样，纯净、干净、宁静，形成这个社会的和谐状态。所以我们只能说，老子这个想法呀追求一种和谐的目标，但是这个所用的方法在我们看来，这还是有很多地方值得检讨的，因为真的把百姓都变成小孩，还是不免有一点愚民政策的感觉。这一点大家还是要正确地理解。</t>
   </si>
   <si>
-    <t>第五十章</t>
+    <t>第五十章（50）</t>
   </si>
   <si>
     <t>出生入死。生之徒十有三，死之徒十有三。人之生，动之死地，亦十有三。夫何故？以其生生之厚。盖闻善摄生者，陆行不遇兕（sì）虎，入军不被甲兵。兕（sì）无所投其角，虎无所措其爪，兵无所容其刃。夫何故？以其无死地。</t>
@@ -730,20 +728,19 @@
     <t>我们来讲第五十章，这一章表面上在讲养生之道，也就是文章所说的“摄生”，实际上表达的是更为深刻的道理。我们看书、看电视剧的时候，会发现有那么一些大师、大医生，一些位重权高的人向他们请教养生之道，“我怎么样能活得更加长寿？”这些医生、养生大师啊，大都是告诉他们要清心寡欲，不要奢靡奢华，不要胡吃海塞，其实这就是道家对于养生这事儿往更高的一个层次所要修养的内容，我们也可以把它概括为道家的生死观。道家认为养生跟生死密切关联。养生要顺应自然，要自然而然，要掌握规律、规则。你看我们读《庄子·养生主》里边的“庖丁解牛”，讲的不就是这个道理吗？目无全牛，游刃有余！这牛解得跟跳舞一样，跟音乐一样。所以文惠君最后就对这个庖丁讲：“吾闻庖丁之言，得养生焉。”养生要顺应自然规律，自然而然，自然而为。“生之徒十有三，死之徒十有三。”然后老子做分析，如果把天下的人分做十成，那么有十分之三的人是“生之徒”，也就是长寿的，还有十分之三的人是“死之徒”，是短命的。还有十分之三的人是怎么样的呢？“人之生，动之死地，亦十有三。”这些人本来可以长寿，最后由于自己的胡为、妄为、折腾，就把自己置于死地了。所以你看它的分类很有趣，十成的人中，三分之一的人应该是长寿的，三分之一的人本身体质各方面就是短寿的，还有三分之一的人本来可以长寿，但是妄动、胡为而置于死地。为什么会这样？《道德经》给了我们这样一句话：“以其生生之厚。”生，养生，或者可以解释得更明确，叫“求生”。太着急了，太迫切了，老想延长自己的性命，老害怕自己的营养不够，最后营养过剩了，反而把自己置于一个另外的相反的方向。当下一些有智慧的医生就提醒，我们现在不是营养不良，而是营养过剩，“生生之厚”。当然《道德经》讲的这句话只针对当时的统治者、位高权重的人而言，老是生活得这样奢靡奢华，“五色令人目盲，五音令人耳聋，五味令人口爽，驰骋畋猎，令人心发狂……”老是这样，还以为是让自己生命不亏，活得不亏。求生之厚，太急、太迫切，营养过剩，自己本来可以长寿，反而被置于成“死之徒”了，到短寿的那一拨去了。所以下面老子就讲了：“盖闻善摄生者”，听说这善于养生的人是什么样子呢？他们用了下边一段形容：“陆行不遇兕虎，入军不被甲兵。兕无所投其角，虎无所措其爪，兵无所容其刃。”习惯上我们以为“兕”是犀牛，或者有的叫母犀牛，其实这两种动物还不一样。这个“兕”是古代的一种瑞兽，比较凶猛，所以在古代的文字中，经常用这个“兕虎熊”比喻凶险之地。懂得养生的人，懂得正确对待自己生命的人，不去冒这个险。陆行的时候，尽量不碰这些凶猛的动物，如果你碰上它了，那你就没办法了，谁让你冒那个险呢？明知道野生动物园人家不让下车，你非得下车，遇到老虎了吧。有些地方人家告诉这个规则，这里边有危险，你偏不听，明知山有虎，偏向虎山行，明知山有狼，偏要做狼餐，这不就是“人之生，动之死地”吗？“入军不被甲兵”，上阵打仗的时候不为兵器所伤。为什么呢？“兕无所投其角”，你不遇到这个兕，那当然它那个凶猛的角就没有办法发挥它的作用了，没有办法针对你。一般我们画“兕”的时候都习惯把它画成独角兽。“兕”最有名的代表就是太上老君骑的那个板角青牛了，角非常锋利，尖锐，杀伤力强，你不遇到它，尽量别碰到，别把自己置于危险的境地，它的角当然就无所用了。“虎无所措其爪”，你不往虎山行，不遇到它，提前准备好避免这种凶险，老虎爪子再尖利，牙齿再锋利，它也无法对你发挥作用。“兵无所容其刃”，上阵不为甲兵所伤，尖锐的兵器，也没有办法发挥它的作用。“夫何故？”为什么会这样？“以其无死地”，不把自己置于死地，这样也就不会让自己的生命受到戕害。这是就是五十章。这一章体现了道家的养生之道：简单地说就是不要“作死”，自己不要找死，本来可以长寿的，自己作死把自己置于死地。很多人非得触犯法律的界限，甚至因此送掉了自己的生命，这不就是把自己置于死地嘛！所以我们说“NoZuoNoDie”，不作不死。从养生的角度来讲，你看道家讲的顺应自然，不单只是生活中的清心寡欲，而且还指不触犯边界底线，不触犯红线，知足不辱，知止不殆，不置身于死地，不让自己冒这种凶险，这也是道家养生之道里边的一个重要的内容，而且是更接近于哲学层面的、更有智慧的内容。那么这一段我们讲完了之后，我还要跟大家强调一下，道家的养生观，其实也是道家的生命观。道家对于生命的看法讲究的是自然而然，意思是什么呢？过于求生，过于厌恶死，这都不是一种自然而然的智慧，因为死亡本身就是生命的一部分，人自然而生，自然而死，真的到了生命结束的时候，那也应该开朗地、乐观地对待。这一点在道家的继承者那里，也就是道家的第二号人物庄子那里，讲得非常的明确——“之所以善吾生者，乃所以善吾死”。我们很好地对待自己的生命，不把自己的生命主动地置于死地，不求生之厚，真的面临死亡的时候，也应该把它好好地对待。自然而生，自然而亡，这是生命的自然而然的规律，谁也阻挡不了。第五十章，老子借养生之道讲了一个更重要的道理：有的人求生太急迫，太厌恶死亡，太害怕死亡，越是求生之厚，服了大量的药，用各种各样的营养的方式，推开死亡，想要避免，没想到越想避免的反而来得越快。所以，道家讲究自然而然的思想，这有着重要、杰出的意义。我们做个小小的梳理。第五十章，我们从开始讲的时候就给大家讲过，这一章可以分成两段，一段是讲有的人本来可以长寿，却进入了短命的行列，是因为“求生之厚”，太急迫、营养过剩导致的，另外一个是由于妄为、“作”，把自己置于死地的。怎样才能避免这两点呢？还是道家的这种思想，顺其自然，清心寡欲，清静为天下正。正确地对待生命和死亡，不把死亡当作是完全可以避免的事情，真的面临死亡的时候，也能够开朗地、乐观地对待。</t>
   </si>
   <si>
-    <t>第五十一章</t>
+    <t>第五十一章（51）</t>
   </si>
   <si>
     <t>道生之，德畜（xù）之，物形之，势成之。是以万物莫不尊道而贵德。道之尊，德之贵，夫莫之命而常自然。故道生之，德畜之：长之育之、亭之毒之、养之覆之。生而不有，为而不恃，长而不宰，是谓玄德。</t>
   </si>
   <si>
-    <t>道生成万物，德蓄养万物，万物有了具体的形状，周围的环境使万物得以成长。因此万物没有不尊崇道和重视德的，道受到尊崇，德受到重视，并没有人如此命令 而是万物本身自然而然地永远去这样做。所以道生成万物，德蓄养万物：使万物成长作育，使万物成长成熟，使万物得到养覆保护。道、德养育了万物
-却不据为己有，帮助了万物却不求它们的回报，成就了万物却不做它们的主宰者，这可以说是最高尚的品德。</t>
+    <t>道生成万物，德蓄养万物，万物有了具体的形状，周围的环境使万物得以成长。因此万物没有不尊崇道和重视德的，道受到尊崇，德受到重视，并没有人如此命令 而是万物本身自然而然地永远去这样做。所以道生成万物，德蓄养万物：使万物成长作育，使万物成长成熟，使万物得到养覆保护。道、德养育了万物却不据为己有，帮助了万物却不求它们的回报，成就了万物却不做它们的主宰者，这可以说是最高尚的品德。</t>
   </si>
   <si>
     <t>第五十一章逐句地来解释一下。“道生之”，“生”，创造，生养。道创造了万事万物。“德畜之”，德畜养了万事万物。“物形之”，万事万物有了具体的形状。“势成之”，周围的环境使它得以成长。正因为如此，所以“万物莫不尊道而贵德”，以道为尊，以德为贵。“道之尊，德之贵，夫莫之命而常自然。”尊道贵德，那自然会得到一个良好的结局和结果，这不是命，这就是自然而然的规律、规则。“故道生之，德畜之。”所以道生养万物，德蓄养万事万物。“长之、育之”，使它成长，使它不断地培育长大。“亭之、毒之”，这个“亭”呢，其实也好理解，我们常说亭亭玉立，这个“亭”就是成长的意思。这个“毒”就是成熟的意思，使万事万物成长，使其成熟。“养之、覆之”，“养”和“覆”都是保护的意思。养育万物，保护万物。“生而不有，为而不恃，长而不宰。”生养了万事万物，却不把它当作私有的产品，对万事万物有作为，却不把这个当作一种倚仗、凭借，甚至勒索的手段，对万事万物有这么大的功德，却不是以主宰者的身份出现。这个就是“玄德”，这就是最高深的、最深刻的智慧与品德。这是我们对这一段的直观的解释。其实，这一段的深意远不止于此。因为中国人讲哲学讲究“知行合一”，讲道的品性，其实也是为了人向道的品性去学习，按照道去做，这个也就是“德”。所以第五十一章里边讲道养育万物，德蓄养万物，也是人应该效法学习的。在这个层面上，我们深入地理解这一段话。“道生之，德畜之”，道创造了万事万物，但是它不把万事万物作为一种私有产品，并不是以一种主宰者的身份，以求其回报。由此我们可以看到，老子给我们提供了想要做成一件事的四个核心的要素和条件，也就是一种应有的程序和原则。第一个，要有道，因为道是创造万事万物的本源，所以我们要坚守大道，按大道的方式来创造。第二个，“德畜之”，“畜”就是积累的意思。在有道的基础上，我们要不断地、坚定地按照道去做，也就是“积德”。德就像水一样，我们就像一条船一样，我们积累的水越多，我们这条船在水上才能够航行得更自由。所以朱熹有一首诗说：“昨夜江边春水生，艨艟巨舰一毛轻。向来枉费推移力，此日中流自在行。”昨天江边涨水了，平常推也推不动的大船，现在根本不用推了，水多了，自然而然地就航行更加自由。他讲的是读书的积累达到一种自由的境界，其实人生又何尝不是如此呢？我们积累的德多了，按照道做事，更坚定、坚持、持久，那也就给我们人生提供了更广阔的空间与平台，不断地积德，我们的行为也就更加自由，我们的行为也就更加能够符合大道。庄子在《逍遥游》里面也讲了这样一句话，“且夫水之积也不厚，则其负大舟也无力”。水积累不多的时候，大船是浮不起来的，只要积累得多了，结果就是自然而然的事情，和朱熹所讲的道理不谋而合。第三个，“物形之”。人有道有德，是不是就可以把事情做成了呢？不够的，还需要一定的物质条件和手段，巧妇也难为无米之炊。有条件要上，没有条件我们创造条件，这样才能把事情向更成功的方向去发展。道、德、物三个条件总够了吧？不够的。要想把事情真正做成，还有一个很重要的条件，就是“势”，“势成之”。道家讲的无为，更强调的是顺势而为，掌握这个形势，了解大势，这样才能把事情做成。《淮南子》中举过这样的一个例子，大禹为什么能把水治成呢？顺水势而为。商汤周武为什么能夺得天下呢？顺民心而为。民心所向，就是历史发展的大势与潮流。所以大家在第二个层面把这四个字提炼出来，它是一个很好的成功学的例证，我觉得比现在讲的一些所谓的零零散散的成功学，不知道要深刻多少倍。道、德、物、势，“道生之，德畜之，物形之，势成之”。既然这四个要素，道和德是排在最前面的，“是以万物莫不尊道贵德”，所以万事万物没有不尊道而贵德的。人更是如此，有道有德，后边的事情才能继续发展，所以“道之尊，德之贵，夫莫之命而常自然”，这不是命，这就是一个永恒的自然而然的规律、规则。你按照道，按照德，尊道而贵德，会得到一个自然而然的良好的结局和结果，这是自然而然的事情。这不是命，这就是自然而然的规律和规则。所以大家注意，我们中国的这些经典，比如说《易经》，比如说《道德经》，都不是用来算卦占卜的，它就讲一个重要的内容：按照规律、规则来做，结果水到渠成、自然而然。下面这一段是对上面做的一个延伸。“道生之，德畜之”，道和德，生养万物，为万物提供条件，让它生长发展。“长之、育之”，培育万事万物使其生长、发展。“亭之、毒之”，使它成长、成熟。“养之、覆之”，不仅如此，还要养护万物，覆盖万物。道和德让万物长大，培育万物的成长，使它成熟又予以保护，功德可谓无量。孔子有一段名言：子曰：“予欲无言。”子贡曰：“子如不言，则小子何述焉？”子曰：“天何言哉？四时行焉，百物生焉，天何言哉？”这段话的直译是：孔子说：“我现在只想沉默。”子贡说：“如果你不说出心里想什么，那么我们这些学生还拿什么去记述呢？”孔子说：“自然说过些什么？不过放纵四季周而复始，任由百物蓬勃生长。自然你又何曾告诉别人什么啊？”很多人把这段话中的“天”翻译成神灵，这是不对的。其实这个“天”指的是大自然，也就是《道德经》里的天地，天地无语而泽被苍生万物，确又无语不居功自傲，不把自己当做万物主宰。这不也是《道德经》第五十一章的核心吗？培育万物的成长，使它成熟又予以保护，功德可谓无量。其实，在这样的智慧层面，孔子和老子的见解都是一样，“生而不有，为而不恃，长而不宰，是谓玄德”。关于这段重要的话，我们在第十章已经详细说过，不再重复。</t>
   </si>
   <si>
-    <t>第五十二章</t>
+    <t>第五十二章（52）</t>
   </si>
   <si>
     <t>天下有始，以为天下母。既得其母，以知其子；既知其子，复守其母，没（mò）身不殆。塞其兑（duì），闭其门，终身不勤。开其兑，济其事，终身不救。见小曰明，守柔曰强。用其光，复归其明，无遗身殃，是为习常。</t>
@@ -755,7 +752,7 @@
     <t>一开始我们就说过，《道德经》里边有一个非常好的“正能量”，就是每当说到高大上的、特别伟大的事情，都喜欢用母亲的“母”字来作为代替和概括，或者说用“母”来做一个形象的比喻。如果我们的孩子读这样的文字，潜意识里就会有对母亲有一种敬畏与尊重。我们在第一章里边就说到，“无，名天地之始；有，名万物之母”。在这一章里边，又出现了母亲的这个“母”的概念。“天下有始，以为天下母。”就像动物、人类都是由母亲生养的一样，万事万物也都是由道创造的。老子用“母”来比喻大道，生动形象且让人充满对道的敬畏，意思就是说，天地一开始的时候，其实大道已经就在了。“既得其母，以知其子。”我们了解了大道，就是“既得其母”。知晓了大道，那我们就“以知其子”，也就了解了儿女。这个意思是什么呢？道是万事万物的普遍规律，它永恒存在，具体的事物都拥有具体的道，也就是具体的规律。你了解了大道，就可以以此来了解万事万物的具体规律。茶有茶道，花有花道，练武有武道，下棋有棋道……了解了普遍的道，也就更能够了解这些具体事物间的规律与规则。反过来也一样，“既知其子，复守其母。”我们从具体的事物之间，比如棋道、花道、茶道，从这具体的事物之间，我们了解了大道，感知了大道，那也就能更好地坚定地坚守大道。“没身不殆”，这样地做事情永远没有危险，没有失败，为什么？以道佑之，以道护之，这样我们做事情才能没有危险，没有失败。下面就说了解大道的方式方法。大道的了解，不是靠感性来体验到的，就像我们前边说的，“为学日增，为道日损。”“不出户，知天下；不窥牖，见天道。”所以如果是跟着感觉走的话，你是了解不了真正的大道的。因此“塞其兑，闭其门，终身不勤”，不要依赖感觉，不要把我们所见所知的就当作大道，重要的要用心，也就是哲学上讲的，用理性的思维，来了解认知大道。反过来讲，“开其兑，济其事，终身不救”，如果跟着感觉走，打开我们的感官的门户，感官这个东西，它是有很大的局限的。第十二章里面就讲，“五色令人目盲，五音令人耳聋，五味令人口爽”。你只靠这个是了解不了大道的。“见小曰明，守柔曰强。”什么叫“见小”啊？“小”就是具体的事物，具体的事物里面也蕴含着规律、规则。你能够从具体事物里了解具体的道、具体的规律，这也是一种明智。“守柔曰强”，道家是讲“柔弱胜刚强”的，道家是讲“知其雄，守其雌”的，“柔”就是雌柔，不管我们多么强大，我们也懂得坚守这个柔弱，因为柔弱更能长久。力量不够的时候，我们懂得用守柔的方式、韬晦的方式，来使自己的力量不断增大、不断增强，这样才能成为真正的强大。“用其光，复归其明”，用道的光芒，“复归其明”，来了解具体事物中的规律、规则，复归到事物光明的、明智的状态，我们才能走在光明的大道上。“无遗身殃”，不会给自己留下那么多的祸殃。“是为习常”，这个“习”，不同的本子有不同的写法。习，就是普遍、永恒的意思，就是普遍的永恒的规律、规则。也有的本子用的是沿袭的“袭”，也就是遮盖的意思。《道德经》里边用这个“袭”字的意思就是说，这是被大家认识不到的、被遮盖的规律规则，了解了这一点，我们也就对事物的了解更加深入。这两个意思都通，我们这里边用的是复习的“习”，学习的“习”，也就是经常的、普遍的、永恒的意思。“是为习常”，这就是一个经常的、普遍的、永恒的规律、规则。这一章核心的内容是说，道是一个普遍的规律，它存在于天地之间，所以叫“大道”。我们了解了大道，掌握了普遍的规律、规则，再来认识具体事物中的规律、规则，这是非常有帮助的，也是非常重要的。反过来也是一样，了解了具体事物中的规律、规则，也能够让我们更加坚信大道的存在，更加了解大道的伟大。这一章以母和子为喻，大和小对照，就讲述了这样的一个哲学的道理。这样的智慧能让我们用到大道的光芒，走在光明的大道上。</t>
   </si>
   <si>
-    <t>第五十三章</t>
+    <t>第五十三章（53）</t>
   </si>
   <si>
     <t>使我介然有知，行于大道，唯施（yí）是畏。大道甚夷，而民好径。朝甚除，田甚芜，仓甚虚。服文彩，带利剑，厌饮食，财货有余，是为盗滥竽（yú）。非道也哉！</t>
@@ -767,7 +764,7 @@
     <t>讲到这里大家已经非常清楚了，老子衡量事情的最高原则就是大道。“使我介然有知”，“芥”就是小的、稍微的意思。假如让我稍微有知识、有智慧，“行于大道”，走在大道上。我最怕的是什么呢？“唯施是畏”，“施”，就是逶迤、曲折，在这里指的是邪路、歧路。走在大道上最可怕的是什么呢？就是害怕歧路太多，害怕走到邪路上去。“大道甚夷，而民好径。”其实大道是非常平坦的，但是一般人都喜欢走捷径，老想抄近道。“朝甚除”，朝政非常得混乱。“田甚芜”，田园都已经荒芜了。“仓甚虚”，仓廪实才好嘛，现在仓库里边都是空虚的。可是那些统治者在干吗呢？“服文采，带利剑。”穿着漂亮的、非常昂贵的衣服，带着珍珠宝石装饰的利剑。“厌饮食”，什么东西都吃腻了，对什么好吃的东西都已经感觉到厌烦了。“财货有余”，家里的财宝有那么多的富余。这叫什么？“是为盗夸。”《道德经》认为这个就叫“盗夸”，强盗，还夸耀自己的强盗行为。《道德经》在第七十七章里边就讲，“天之道，损有余而补不足”。现在这些人做的是什么呢？“损不足，以奉有余”。“非道也哉”，这完全不符合道的规律、规则，完全不是按照道的方式来做嘛。这一章表现了老子的平民的思想、公平的思想，指责在“朝甚除，田甚芜，仓甚虚”的情况下，那些人“服文彩，带利剑，厌饮食，财货有余”夸耀自己的强盗行为。这一章有一些字，我们还得具体地、细致地解释一下。“唯施是畏”，凭什么把这个“施”念成“迤”，解释成歧路呢？因为道弯弯曲曲的时候，歧路众多。在《列子•说符篇》里边讲的一件事——歧路亡羊。杨朱他们家的邻居羊丢了，很多人都出去找，杨朱就觉得很奇怪就问，就一只羊怎么这么多人去找啊？邻居就告诉他，歧路多，岔路太多了。找羊的人回来了，杨朱问找到了吗？邻居说没找到。又派更多的人去找，还没有找到。歧路中又有歧路，岔路中又有岔路，所以常常使人丧失了大道，迷失了大道，所以杨朱听了之后几天都不说话。古人有“歧路亡羊”，也有遇穷途而哭，走道遇到没有路了，痛哭而返，其实都是感觉到了人生道路上的一些很值得人害怕的事情。行于大道，最害怕的就是歧路、岔路，一旦走错路，方向一错，后边的一切麻烦就都来了。所以老子说“大道甚夷”，“夷”就是平坦的意思，大道其实极为平坦。“而民好径”，人却老喜欢去走这个捷径，走了捷径之后，最后发现回到正确的大道上是非常困难的。其实，很多的所谓捷径就是歧路，就是邪路，人要脚踏实地，这样才能够行走在正确的大道上。通过努力获得成功，而不要投机取巧，更不要把投机取巧里边得到的东西当作一种炫耀夸耀，这个叫什么？“盗夸，非道也哉。”</t>
   </si>
   <si>
-    <t>第五十四章</t>
+    <t>第五十四章（54）</t>
   </si>
   <si>
     <t>善建者不拔，善抱者不脱，子孙以祭祀不辍。修之于身，其德乃真；修之于家，其德乃余；修之于乡，其德乃长；修之于国，其德乃丰；修之于天下，其德乃普。故以身观身，以家观家，以乡观乡，以国观国，以天下观天下。吾何以知天下然哉？以此。</t>
@@ -779,7 +776,7 @@
     <t>第五十四章由三段构成。第一段：“善建者不拔，善抱者不脱，子孙以祭祀不辍。”这一段在讲按照大道来建设，没有人能够攻击倒它，把它拔除掉。大家想，人类建设的很多的东西，有成必有毁，都是会被拔除掉的，而大自然呢，比如说山川，这是大自然建筑的东西，有的或许可以被拔除掉，但这一章讲的不是这个意思。“善建者”指的是人精神方面的建设，大道方面的建设，这个伟大的思想是不会被攻击倒、被拔除掉的。比如我们现在学的《道德经》，历经两千多年，很多人都在攻击，在否定，在嘲笑，可是这无碍于它伟大的思想，现在学的人越来越多，大家越来越从里边得到一种智慧的启迪。另外像佛祖释迦牟尼，像孔子，历史上一些伟大人物的思想，他们的思想像什么？就像夜幕中的星光，给我们在黑暗中指引方向，有的甚至像光明普照的太阳。这些思想属于“善建者”，是没有办法把它攻击倒、拔除掉的。“善抱者”是什么意思呢？直观的理解就是善于把你抱住的人，你是脱离不开他的掌控的，其实这只是望文生义的理解。在《道德经》里边多次提到“抱”字，比如说第二十二章，“抱一为天下式”；比如说第四十二章，“万物负阴而抱阳，冲气以为和”。抱的是什么？“负阴抱阳”。所以这个“善抱者”就是掌握阴阳之不测，掌握阴阳相互作用、相互变化的规律规则，而“一阴一阳之谓道”，所谓“善抱者”，也就是了解大道的人。“不脱”，脱离不开大道的掌控，脱离了大道就走到了一个危险的境界。“子孙以祭祀不辍”，一代一代，千秋万代，按照“善建者”、“善抱者”这些伟大的思想来做，对他们表示一种尊重、敬仰，不断地学习。“修之于身，其德乃真。”按照这个伟大的思想来做事、来修身，这样所得到的德，才是真实的、纯净的。“修之于家，其德乃余。”按照大道来修家，一家人遵循大道，这样获得的家的品德才是丰盈有余的，积德之家必有余庆嘛。“修之于乡，其德乃长。”拿大道来传达给一个乡，按照这个方式形成一种良好的乡风。“长”就是领导的意思。你把这个方式在乡里边普及，让大家坚定地按照道的方式来做，你才能成为这个乡的好的领导者。我们知道，在宋朝的时候，陕西“蓝田四吕”首先制定了乡约，它对我们中国良好的乡风的培育起了非常大的作用，这不就是“修之于乡，其德乃长”的具体表现嘛。“修之于国，其德乃丰。”按照这样的一个方式来治理国家，让国家按照大道去做，所收获的德才是丰盛的、伟大的。同样的道理，“修之于天下，其德乃普。”天下是天下人的天下，不是一人之天下，所以大道之行，天下为公。按照善建、善抱的大道来做，修之于天下，这样大家得到的才是普遍的，如光明之普照。这是第二段，老子在讲按照“善建”、“善抱”的原则来做，所获得的伟大的结果。“以身观身”，“观”就是观察。我们按照修身的要求，大道修身的方式来观察这个人，他修身方面是不是善建、善抱，是不是没有脱离大道。“以家观家”，按照家庭的修养的要求来观察家庭的品德、家风。当然这个“观”的时候就自然有对比的意思，和其他的家里边进行对比，相互比较，看哪一个是更能按照“善建”、“善抱”的这种符合大道的原则方式来修身、来齐家。下边也是同样的道理，“以乡观乡”，乡自有乡的要求，和家是不一样的，范围扩展了，有很多家庭。但是如果这个大道一以贯穿，都是按照对“善建”的、“善抱”的原则祭祀不辍、尊敬，敬仰，以按照这样的一种规则来作为荣耀，都为良好的家风、乡风做出贡献，这不就是道一以贯之吗？同样的道理，“以国观国”，一个国家有这个国家的精神、思想、风貌，按照大道要求来做，在和其他国家比较中，取长补短。同样的道理，“以天下观天下”。大道一以贯之，一条主线，一切顺理成章，自然而然，无往而不胜。所以最后老子说，我怎么知道天下也会是这个样子？“以此”。大道所向无往而不胜，虽然人世间有那么多的枝枝蔓蔓，但是核心“善建”、“善抱”之大道，不要脱离开大道，坚定地、坚持地按照它去做，按照道去做就是“有德”。修身得到的是“真”，修家得到的是“余”，修乡得到的是“长”，修国得到的是“丰”，修天下得到的是“普”。所以，从修身开始，最后落到天下，不就是这样一个简单的道理吗？其实读这一章的时候，大家会有一个非常深刻的感受，中国先秦时代是中国的轴心时代，各个思想流派之间的思想，虽然有差别，但是也有相同的地方。所以我们看这和儒家的思想，修身、齐家、治国、平天下一样，都是从修身开始，最后才能够成为国家的好的领导者，才能把这种思想普及到天下。“天下难事必做于易，天下大事必做于细。”从自身做起，要求自己按照大道的这种修养、修为，按照“善建”、“善抱”的原则，坚持地、坚定地去做，我们才能真正地有德。</t>
   </si>
   <si>
-    <t>第五十五章</t>
+    <t>第五十五章（55）</t>
   </si>
   <si>
     <t>含德之厚，比于赤子。蜂虿（chài）虺（huǐ）蛇不螫（shì），猛兽不据，攫（jué）鸟不搏。骨弱筋柔而握固，未知牝牡之合而全作，精之至也。终日号（háo）而不嗄（shà），和之至也。知和曰常，知常曰明，益生曰祥，心使气曰强。物壮则老，谓之不道，不道早已。</t>
@@ -791,7 +788,7 @@
     <t>这章开头讲了一个非常有意思的概念，就是“赤子”，这是因为婴儿刚出生的时候浑身是红色的，但这个词更重要的作用是比喻心地的纯净、纯洁。“含德之厚，比于赤子。”按照道的标准来衡量，赤子心地纯净，无恃无为。这是含德浑厚的一种表现。其实，不只老子，孔子也对婴儿的状态充满了景仰，认为这是一种有道的含德之厚的表现。孟子也说，“大人者不失其赤子心”。老子更是把婴儿作为一个范本与榜样，第十章就说“专气致柔，能如婴儿乎？”人精神集中，气息平和，那不就是像婴儿的样子吗？下边这些都是从经验的角度来讲获得的感受。小孩的他精神状态很安稳，蜂子、毒虫、蛇也不蜇他，也不咬他，为什么呢？因为小孩没有危险，没有对这些动物造成威胁的举动。其实有时候蜂子落到我们脸上，也许只是为了得一滴汗液，没有汗液，它采的蜜也不能凝固，可是我们一打它，它当作危险的时候，就要用它的毒针来蜇我们。很多动物也是这样，人没有危险动作的时候，其实也不会攻击人，但人见到它就害怕，就有一种防范甚至攻击性的动作，这也是难免的。老子说你看，这婴儿啊，“毒虫不螫”，毒虫不蜇他。“猛兽不据”，虎啊、狼啊这些猛兽，也不把它叼走，不用爪子把他抓走。我们经常会听到这样的一些事，很多动物还喂养、抚育这些落在田野里边的荒野上的小孩，当然这也不是全部的情况，我估计老子也是拿这个做一个说明而已。“攫鸟不搏”，攫，攫取。有的时候，人手上拿着一个什么东西，比如说拿着肉，在一些荒远的地方，老鹰就飞下来把这肉抢走了，但是对小孩它却不这样做，除非是尸体。“骨弱筋柔而握固”，这小孩其实身体是最柔软的，但是你看他这小拳头却握得很紧固。这人生啊，深究起来是有点意思。小孩刚出生的时候，都是握着拳头，似乎想抓住点什么，但人最后离开这个世界的时候，却是放手了，知道什么也抓不住。“未知牝牡之合而全作”，“牝牡”本来指的是雄性和雌性的动物，但是这个地方指的是男女。小孩刚出生不知道什么男女的事情，但是你看他的小生殖器却非常坚挺。老子用这样的一个方式来做形容，说婴儿精气很纯、很多、很壮，“精之至也”，达到了一个最好的状态，老子是这样认为。下边这个描述确实挺有意思，叫“终日号而不嗄”，小孩终日啼哭，但是嗓子却不哑，那不是精气足的表现吗？我现在讲课，讲一段时间喉咙就哑了，我们现在为什么会这样？老子可能认为，这人长大了，欲望多了，精气耗费得多了，所以就不像小孩那样精气充足。这一段把婴儿作为一个得道者的良好状态的表现讲完了，下边老子该阐述自己的观点了。“知和曰常”，“常”就是规律、规则。了解了这个“和”，通过婴儿引出来的“和之至”，谁能够像婴儿一样，让我们气息平和，让我们的欲望平和，不那么欲壑难填，就了解大道的规律、规则。“知常曰明”，了解这个事物规律、规则的人，那才是明智。“益生曰祥”，让我们的生命有益，这个才是一个吉祥的表现。这是正面，那负面呢？“心使气曰强”，老是盛气凌人，体现的是这种强横、强暴，这个是道家所反对的。气息不平和，纵心任气、任性，这个是强暴、强蛮的表现。在前面第二十三章讲过，“飘风不终朝，骤雨不终日，孰为此者？天地。天地尚不能久，而况于人乎？”暴风骤雨它不会持久，天地的使强也不过只是持续一阵子，它告诉我们这个道理，强不能持久。“心使气曰强”，这不是一种好现象。“物壮则老”，事物发展到顶峰的时候，就开始走下坡路了，人到了壮年之后，就逐渐向衰老的方向发展了。“谓之不道”，这已经使气，老是以强壮来作为目标、作为处理问题的方式，这是不符合大道的。“不道早已”，既然不符合大道，那这个事情就不能持久，很快就会结束了。你看这婴儿的状态，其实应该能存活得更长久、寿命更长，为什么后来很多人变得短寿了呢？那就是让自己脱离了大道，没有像婴儿那样，“精之至”，“和之至”。所以人应该“知和，知常，益生”，而不应该使气，不应该“物壮”，如日中天的时候就走下坡路了。人生最美的境界是什么？花未全开月未圆。所以，按照大道的方式来处事、认知事物，这样我们才能够明，才能够益，否则的话就会“不道早已”。</t>
   </si>
   <si>
-    <t>第五十六章</t>
+    <t>第五十六章（56）</t>
   </si>
   <si>
     <t>知者不言，言者不知。塞其兑，闭其门，挫其锐，解其分，和其光，同其尘，是谓玄同。故不可得而亲，不可得而疏；不可得而利，不可得而害；不可得而贵，不可得而贱，故为天下贵。</t>
@@ -803,7 +800,7 @@
     <t>这一章还是比较容易理解的。“知者不言，言者不知。”开头的第一句话就讲，有智慧的人是不多言的，所谓“行不言之教”，还有“悠兮其贵言”，都在讲这个道理，有智慧的人是不会多嘴多舌的，不会去乱说的。“知者不言，言者不知”，老是认为自己无所不知、以为自己有智慧的人，其实是不具备真正的智慧的。“塞其兑，闭其门。”我们前边解释过，“兑”指的就是耳、目、鼻、舌这些感官，所以它强调的是感性对事物的认识，是不可信的。“塞其兑，闭其门”，这样才能对事物本质的根本的内容有真正的理解。下面讲处理问题的方式方法，做人的思想与智慧，要“挫其锐，解其分，和其光，同其尘”，不要锋芒外露，这样才能长久。要解除那些纷纷扰扰，不要让纷纷扰扰在心里打成结——心有千千结。真正了解道的含义的人，按照道去做事的人，是很容易摆脱这些纷纷扰扰的。“和光同尘”，也就是讲同流而不合污，所谓外圆而内方，所谓与世推移。那么这个叫什么呢？就叫做“玄同”。“玄”本来是天的颜色，意味着深远，这样的同是深远的、深刻的，同流而不合污，当然里边就非常有玄妙了。下面的内容讲得也非常清楚，就是说道并不是为人谋利益的，得道的人他怎么样来和万事万物打交道呢？就像道一样，“不可得而亲，不可得而疏”，道并不是对谁更亲近，或者对谁更疏远。有亲就必有疏，有疏就必有亲，这个就不平等了，这就不“玄同”了。所以，按照道的、“玄同”的方式来做，没有亲疏之别，无差别。“不可得而利，不可得而害”，有利必有害，有害也必有利。所以你并不能凭借道而获利，也不能用这个道来危害别人，无差别，无利无害。“不可得而贵，不可得而贱”，道对谁也没有贵贱之分，还是依然玄同、平等，一旦有贵贱之别，便也就丧失了道的本质的属性。所以庄子讲，“以物观之，自贵而相贱。以俗观之，贵贱不在己。”从物的角度来看，都认为自己是珍贵的、宝贵的，其他的东西比不上自己的尊贵。用世俗的观点来看，贵和贱不在于自己，而在于别人的评价，在于外在的标准。而“以道观之，物无贵贱”，从道的角度来看，这万事万物并没有什么贵贱之分，所谓公正、平等、无差别、无贵贱之分。正是因为这样，所以它成为天下最尊贵的，“故为天下贵”。所以这章的内容啊，道表现为玄同，按照这样的深远的玄同的道理来理解事物，就是从道的角度来观察问题。道没有亲疏之别，没有利害之分，没有贵贱之差，所以用这样的一个角度来观察世界，这个才使它成为天下最令人敬重尊仰的，“故为天下贵”。</t>
   </si>
   <si>
-    <t>第五十七章</t>
+    <t>第五十七章（57）</t>
   </si>
   <si>
     <t>以正治国，以奇用兵，以无事取天下。吾何以知其然哉？以此。天下多忌讳，而民弥贫；民多利器，国家滋昏；人多伎巧，奇物滋起；法令滋彰，盗贼多有。故圣人云：我无为而民自化，我好静而民自正，我无事而民自富，我无欲而民自朴。</t>
@@ -815,7 +812,7 @@
     <t>第五十七章的这段话非常有智慧，因为这段话一开始就指出来了，事物之间的不同，有本质的区别，所以处理问题、解决问题的方式方法也不一样。“以正治国，以奇用兵”，治国讲究的是堂堂正道。道家讲的“正”当然就是清静无为，不多事，不扰民，这就是道家讲的正道，是治国的大道理。可是用兵讲究的是“以奇用兵”，“兵者诡道也”，兵不厌诈。所以不能把用兵的方式、战争的方式用到治国的上面来，这两者不同，解决的方式也不一样。“以无事取天下”，无事就是不多事、不扰民、不刁难，这样才能够得到天下，并且坐得了江山。道家“无事”是“无为”的一个重要的方面，不多事、不扰民、不刁难，而“有为”讲的是妄为，多事、扰民、刁难，我们在前边这一点已经非常明确了。“吾何以知其然哉”，我怎么知道是这个样子呢？所谓“以此”就是依据上边“以正治国，以奇用兵”它们之间的本质不一样，所以解决的方式方法也不同而得出的结论。下面，老子开始谈他对治理天下的重要的看法。违背了大道，违背了道家的以“清静无为”为根本来治理国家的方式，会出现什么问题呢？“天下多忌讳，而民弥贫”，治理天下、领导国家忌讳太多，这个也不能动，那个也不能动，这个人的职务比较高，法令涉及不到他，当然出现了忌讳，不敢动，这个地方一定会形成一个空场，形成一个腐败的群体。百姓当然越来越穷了，财富都集中在少数人的手上。“民多利器，国家滋昏”，“滋”就是越来越。如果民间利器众多，武器众多，民与民之间械斗、抗法，那国家当然越来越混乱。“人多伎巧，奇物滋起”，“伎巧”就是各种各样的奇技淫巧，越来越多，大家对这些越来越感兴趣，这个技巧能够给他们带来利益，那么各种各样的奇奇怪怪的东西，甚至包括那些妖孽的东西，就不断兴起。“法令滋彰，盗贼多有”，既然这样，要用法律来管，法条定得越来越多，越来越严苛，反而盗贼越来越多。在前面这一段讲完之后，《道德经》说“故圣人云”，很明显，这是引用以往的通达事理的王们的话，老子用自己心中有智慧的人的语言来作为结尾。“我无为而民自化”，道家讲的无为，第一，“不妄为”。第十六章里边说“不知常，妄作，凶”，不了解事物的规律、规则，瞎折腾、胡折腾，这个结果是非常糟糕的。第二是“不多为”。抓住关键，举重若轻，多言数穷，不如守中，适可而止，恰到好处。第三讲究的是“有所不为”。人要想有所为，必须有所不为。一个政府也罢，一个领导者也罢，所有的事情都抓在自己手上，那底下的人怎么得到锻炼呢？不把担子压给他，他怎么练出独当一面的能力呢？什么事都控制在自己手上，那众人怎么样自我化育自我成长呢？所以无为才能让国家的人民、才能让自己的属下自我化育自我成长。事情成了应该怎么样呢？第十七章“功成事遂，百姓皆谓‘我自然’”，事情做成了，百姓都说这是我们的努力把这事情做成的，这就叫“民自化”。“我好静而民自正”，前面我们讲过，道家讲的静，内心的清净，静下来才能找到解决事物的正确的方法。我清静，走正道，不那么浮躁、急躁、暴躁、狂躁，做一个好的表率，上梁而正，百姓当然也就正了，百姓当然也就好静而走正道了。“我无事而民自富”，不多事、不扰民、不刁难，那百姓自然就富起来了。“我无欲而民自朴”，“朴”就是原木，《道德经》里用原木喻指做事敦厚、朴实、厚道，没那么多欲望，不是老想抢夺别人、占有别人的。就像黄宗羲在《明夷待访录》里边讲的，古代的那些皇帝都是什么样的？“离散天下人之儿女，荼毒天下人之肝脑，以供一人之淫乐。”这是我的，普天之下都是我的。所以欲望无止境，你让百姓能够朴实厚道，这也不可能。所以不要欲壑难填，不要什么东西都看作是自己的，可以任意掠夺，这样百姓自然就朴实、厚道，民心淳朴。这里边的两句话，我们国家的领导者讲话的时候也经常引用：“我无为而民自化，我无事而民自富。”所以，第五十七章讲了两个重要的道理，第一个不能把打仗的这一套用到治国之上。治国讲究的是堂堂大道，讲究的是清静无为，所以以无事取天下。第二个就讲站在领导者的角度，站在统治者的角度，应该怎么做呢？无为、好静、无事、无欲，这样自然一切顺理成章，百姓就会自化、自正、自富、自朴，事成了也会“功遂身退，百姓皆谓我自然”。这是一个好的领导者、好的政府做事的道理之所在，反之越多事儿，越是用那种严苛的法令，导致的结果适得其反。忌讳多了，百姓就越来越穷，民间的利器多了，国家就越来越混乱，大家都倾向于奇技淫巧，把这个当作一种喜欢的甚至不停地去追求的目标，那这个国家就越来越怪，各种奇葩的事情都纷至沓来。越觉得法令不够，越制定得严格、细致，以为单靠着法令就可以解决所有问题，反而适得其反，盗贼多有。所以，这一章里边讲的，也是我们经常说的——这本书的总纲：“反者，道之动”。我们考虑问题，不要只考虑它一面，要相反相成，用一个更高的观察事物的角度来理解。</t>
   </si>
   <si>
-    <t>第五十八章</t>
+    <t>第五十八章（58）</t>
   </si>
   <si>
     <t>其政闷闷，其民淳淳；其政察察，其民缺缺。祸兮福之所倚，福兮祸之所伏。孰知其极？其无正。正复为奇，善复为妖。人之迷，其日固久。是以圣人方而不割，廉而不刿（guì），直而不肆，光而不耀。</t>
@@ -827,7 +824,7 @@
     <t>第五十八章有两个我们非常熟悉的成语，一个叫“祸福相依”，一个叫“光而不耀”，也是这一章核心的内容。祸福相依，福和祸是相互转化的，两者也是相辅相成的，分不开的。“光而不耀”在讲什么呢？我们大家看到过月亮，月光是明亮的，在黑暗中给我们指引以方向；同时月光也是不张扬的、不炫耀的、不刺眼的。中国人喜欢拿月亮来比喻君子的形象，做君子得先有光，但是不管我们有什么，都不要老想着去张扬、炫耀，让别人感觉到刺眼。所以《道德经》很多章节，都向我们揭示了这样一个道理：有才华、有知识、有道德的人，不要老想着去张扬、炫耀。以这两个成语为切入点，我们会对这一章的内容有个直观的感觉。我们来逐字逐句地解释一下。“其政闷闷”，“闷”就是淳厚。就说政治比较淳厚宽容，那么这个国家的百姓也就是敦朴淳厚，不耍心眼。“其政察察，其民缺缺”，假如这个政治非常苛察，对一切都监控得到位，那老百姓就会感觉到有很多的缺陷与不足，就要耍心眼。所谓上有政策，下有对策，也就失去了原本的淳朴。“祸兮福之所倚，福兮祸之所伏。”福和祸是相辅相成的，在一定条件下是相互转化的。民间的很多说法，大家都能够体会到这意思的延伸和运用，比如，我们经常说“大难不死必有后福”、“好事多磨”……福和祸是相伴而行的，有时候我们认为是福的事情，它可以转化为祸，反过来也是一样，所以这就叫“祸福相依”。怎么样来理解这个事情呢？给大家举个例子，大家就清楚了。其实各民族的智慧到达高点的时候，往往是相互重合的，印度有一本佛经叫《大般涅槃经》，在这里面讲了这样一个故事。有一天早晨，一家主人一开门，门口站着一个衣着光鲜、非常漂亮的女子，主人就问你是谁，女子说我是“功德大天”，我到谁家谁家就一切兴旺。主人高兴地请进来，焚香供拜。刚一关门又有人敲门，开门一看，门口站着一个衣衫褴褛，非常丑陋的、黑瘦的女子，主人就没好气了，主人就问你是谁呀，那女子说我是“黑暗”，我到谁家，谁家就一切破败！主人当然不让她进来，拿着刀驱赶。结果这女孩说你太笨了，刚进去的是我姐姐，我们俩从出生这天起就没有分开过，你把我赶走了，她也留不下。主人不信，进去一问果然是这样。福跟祸是相伴而行的，所以它就提醒我们，遇到福事的时候就要小心谨慎，避免乐极生悲；遇到祸事的时候，也不要感觉到沮丧，因为我们对灾祸有所警惕，它可以避免后面更大的灾难。韩非子讲过“千里之堤，溃于蚁穴”，我们发现了这个蚂蚁窝，知道它是一个祸患，很早的把它堵上，那就避免了以后更大祸事的发生。这就是“祸福相依”的道理，在我们文化中影响是非常深刻的。讲完这一段后，《道德经》就说“孰知其极？”这个事物到达极点的时候，向它相反的方面转化，所谓两极相通，所谓物极必反，但是这个极在哪里呢？这个是需要我们认真去体会把握的。“其无正”，其实并没有确定的标准，所以并没有说我们到了一个什么程度，一定会向它相反的方面转化，这是要根据不同的时间、地点、条件，需要我们认真去领会把握的、体悟的一种智慧。“正复为奇，善复为妖。”“正”，你把它弄到极点它就偏了，“善”到达极点的时候，它就转化为它相反的方面。有些人老想寻找一个固定的标准，《道德经》就说：“人之迷，其日固久。”在这个方面的迷惑，时间已经由来已久。所以我们总是要寻找一个固定的标准，总是觉得做事情有一个固定的程序，固定的套路，这个就不圆融。下面就讲，“是以圣人方而不割”，“方”就是方正，“割”就是生硬。有原则但是不生硬，人要懂得去碰硬，但是不要去硬碰。方正而不生硬，这样才能圆融，我们把它叫做“外圆而内方”。“廉而不刿”，“廉”就是棱角，“刿”就是锐利。有棱角但是不要老用锐利之处去刺伤人。“直而不肆”，有人经常就说，我说这话你别在意，我这人很直。其实有的时候不是直而是自私，是放肆、过分。所以我们说直率，它是一种心态，但是你讲话的方式得懂得圆融，直率而不放肆。“光而不耀”，有光芒，但是不要老去张扬、炫耀，让别人感觉到刺眼。咱们中国人喜欢讲君子，什么样的人是君子呢？中国人除了用月亮来代表君子“光而不耀”的特点之外，另外，也喜欢用玉来代表君子的形象，所谓“谦谦君子，温润如玉”。“谦谦君子”出自《易经·谦卦》，原话叫“谦谦君子，用涉大川”，一个人保持这种内敛的、谦逊的风度，这样才能走好人生长远的坎坷的道路。另外一个是出自《诗经》的“温润如玉”，谁都知道闪着贼光的肯定不是什么好玉，真正的好玉都是光芒内敛，给人一种温润感。我认为“光而不耀”是中国文化里，对君子形象用得最好的一个比喻。我们有知识，不要老想着去张扬、炫耀，大家聚到一块的时候，一个人老去炫耀自己的知识，对别人的说法都嗤之以鼻，认为自己什么都懂，百事通，时间长了，大家就不喜欢跟这人打交道了。有道德，道德是约束我们内心的，不是老是向别人去张扬炫耀。《道德经》第三十八章开头这句话，大家都知道——“上德不德”，最有道德的人从来不去张扬、炫耀自己的道德。当然，至于炫官、炫富，这不仅不是一种君子的形象，还会给自己惹来无尽的祸殃。是否还记得第九章里“金玉满堂，莫之能守；富贵而骄，自遗其咎”，炫富炫贵，会给自己惹来无尽的祸殃。在第二章里“功成而弗居”，哪怕我们有功劳，不管是对家庭、对单位、对国家有功劳，也不要老想着去张扬、炫耀，越是不张扬、不炫耀，这个才能在人心里长久地存在。第九章里面也说“功遂身退，天之道”，这是符合自然的道理。第五十八章讲完之后，我再做一下梳理和强调。这一章有两点需要注意，一个是“祸福相依”的道理，一个是“光而不耀”的形象，怎么样能做到这一点？我们要明白“物极必反，两极相通”。了解这样的智慧与道理，我们做事情才能够圆融。所以一个有智慧的人，有智慧的领导者，为人处事应该方正而不生硬，要圆融，有棱角，但不要老去割伤人，要懂得委婉迂回地处理问题的方式。直率，但又不越界进入到了放肆、无所顾忌的程度，光芒内敛而不要老去张扬、炫耀，要给人留下一种谦谦君子、温润如玉的形象。这是我们和别人、和这个社会打交道的一个重要的思想与智慧。</t>
   </si>
   <si>
-    <t>第五十九章</t>
+    <t>第五十九章（59）</t>
   </si>
   <si>
     <t>治人事天莫若啬（sè）。夫唯啬，是谓早服，早服谓之重积德。重积德则无不克，无不克则莫知其极。莫知其极，可以有国。有国之母，可以长久。是谓深根固柢（dǐ），长生久视之道。</t>
@@ -839,7 +836,7 @@
     <t>这一章讲了两种生活的态度：一种是做“加法”，不断地叠加，不断地累积，有了还想更有，多了还想更多；另外一种是要懂得做减法，要节俭节制，有的时候我们的欲望减少一分，其实我们的幸福也就多一分。这两种人生态度也是相辅相成的，可是大家更注重的是第一种，所以一章就强调我们这种做减法的态度的重要性。其实这一章核心就讲四个字：节俭节制，讲节俭节制对一个国家、对社会的重要意义。“治人事天莫若啬。”一开始就讲“治人事天”，领导这个国家的人民要顺应天理。“莫若啬”，什么事情最顺应天理呢？节俭节制。我们现在用的这个词叫“吝啬”，这个词有点负面的含义，在《道德经》中这个“啬”，我们把它译成节俭节制，这样更符合于我们的接受习惯。“夫唯啬，是谓早服”，“夫唯”是个语气助词，“啬”是节俭节制。“是谓早服”，“早服”就是早得道。懂得节俭节制的道理，就是可以早得道的人。“早服谓之重积德”，“重”就是不断。懂得节俭节制就是在不断地积累自己的品德，积累自己的德行。因为我们说《道德经》道和德要分开理解，按照道去做，就是有德，不断地按照道去做，就是不断地积德。重积德就是不断地积德，所以你看“早服谓之重积德”，早得道，一直坚定地坚持按照这个去做，就是不断地积累自己的德性，积累自己的品德，积德。我们就像一条船，我们积的德就像水，水积累得越多，我们船才能自由地航行，不管你船多大，如果没有水，在那儿搁浅，它也发挥不了船的这种作用。“重积德则无不克”，“克”就是克服，按照这个“啬”的方式，也就是节俭节制的方式去做事情，那就没有什么困难克服不了的。因为在节俭节制里边磨练的就是人的思想品德，磨练的就是人的意志，磨练的就是人面对困难无所畏惧的态度。“无不克则莫知其极”，你说这个东西力量这么强大，没有什么东西它克服不了，所以它的力量“莫知其极”，你不知道它的力量有多么强大，对一个人是这样，对一个国家更是如此。“莫知其极，可以有国。”你看这话是给谁讲的？给统治者、领导者讲的。一个领导者领导团队，领导这个国家的人民培养出一种节俭节制之风，你这样才能让你的国家长久地存在，长久地发展。毛泽东主席在中华人民共和国成立的时候就指出，“贪污和浪费是极大的犯罪”，自己也以身作则。你领导团队，领导全国人民培养出一种节俭节制之风，这样面临什么样的困难的时候，大家都有信心去克服。“有国之母，可以长久。”“母”就是根本。节俭节制是立国，是国家长久发展的根本。我们现在叫“八项规定”“反四风”，领导国家的人民培养出节俭节制之风，国家才能长久持续地发展。有一件事儿大家都知道，电视经常打出一个公益广告，说现在每年中国人浪费的粮食就是世界上两亿人的口粮。你说世界上现在每天都有人在饿死，可我们中国人这么浪费，能符合天道，能符合天理吗？如果因为这种浪费有什么惩罚落到我们头上，那么我们也无话可讲。你从这一章里面就可以感觉到，一个人浪费，糟蹋的是自己的福分；一个国家浪费，糟蹋的是国家的福分，对国家的根本有所损伤。“是谓深根固柢，长生久视之道。”国家培养出节俭节制之风，才能长久发展，这样做叫什么？叫“深根固柢”。我们讲叫根深蒂固，你让这个根本、让根扎得深，扎得稳固，深根固柢。“长生久视之道”，于人来讲是如此，可以让我们的生命更为长久，因为一个人的节制节俭，不去放纵自己的欲望，这也是一种养生之道。得以长久地存在，长久地发展，得以长寿，对国家来讲也是如此。所以“长生久视”，长久地存在，大家能够长久地看到它。《道德经》强调“做减法”的这个方面，在世界哲学界，有着非常重要的影响。我们中国人有一个优良的文化传统，讲勤俭持家，讲勤俭治国，所以这个是我们文化中非常重要的方面，但是很少在哪一本著作里面把它强调到这样的一个高度。“治人事天莫若啬。夫唯啬，是谓早服。”这就是早得道，坚定地按照这个道去做，就叫积德。不断地积德，那就使我们能够根深蒂固，长久存在，长久发展。人如此，国家亦如此，道理是相同的。第五十九章，希望大家认真地品味体会老先生给我们讲的“根深蒂固”的道理。</t>
   </si>
   <si>
-    <t>第六十章</t>
+    <t>第六十章（60）</t>
   </si>
   <si>
     <t>治大国若烹（pēng）小鲜。以道莅天下，其鬼不神。非其鬼不神，其神不伤人；非其神不伤人，圣人亦不伤人。夫两不相伤，故德交归焉。</t>
@@ -851,7 +848,7 @@
     <t>这一章有一句话，大家都非常熟，叫“治大国若烹小鲜”，这句话也是这一章的核心。一九八七年，美国前总统里根在发表国情咨文的时候也引过这句话。二〇一三年，“金砖各国”开会，在一个联合的采访中，有一位巴西记者问过习近平这样的一个问题：你担任这么大的一个国家的这么重要的职位是一种什么心态？你用什么样的态度来对待自己的职位？习近平答记者问，先引的是《诗经》，来回答第一个问题：“战战兢兢，如临深渊，如履薄冰。”这话出自《诗经·小雅·小旻》。治理国家要小心谨慎，就像行走在结着薄冰的冰面上一样，就像站在悬崖边一样，要小心谨慎，因为稍不谨慎就会出大的问题、大的危险。然后引用这句话来回答第二个问题，我要以“治大国若烹小鲜”的态度来对待我的职位。“治大国若烹小鲜”是什么意思呢？大家如果上网去搜对这句话的解释，类型就有二十多种，每一种解释都不一样，有的甚至把它直接翻译为“治理一个大的国家就像烹一碟小菜那么简单”，这是完全没有理解这句话的真正的含义。“小鲜”就是小鱼儿，鱼肉很细很嫩，拿它的时候就得小心谨慎，尤其是在高温里烹炒它的时候，都要小心谨慎，要有耐心。火候不到的时候你老折腾，甚至锅铲飞舞，翻腾，鱼不就成了碎片了吗？汉朝的毛亨，喜欢《诗经》的人都知道，这个人写过《毛诗传》的，他就用两句话来解读这句话，其实最符合它的本意。第一句话叫“烹鱼烦则碎”，环节太多老折腾它，那鱼就成了碎片了。第二句话“治民烦则乱”，治理一个国家也是一样，讲究的是制度的稳定，不能今天一个制度，明天一个制度，朝令夕改；你不能今天一个运动，明天一个运动来回折腾，国家不就被折腾散架了嘛。“治大国若烹小鲜”和“战战兢兢，如履薄冰”的道理是相同的，讲究的是小心谨慎，有耐心，掌握火候。“以道莅天下，其鬼不神。”“莅”就是莅临。用道来领导天下，指引天下。大家注意，这个“神”字很多的理解有问题，其实并不是神鬼的神，不是说我们后来的人格神、神化了的神。这个“神”在《易传》里面的解释是非常明确的，“阴阳之不测之谓神”，也就是神秘莫测。用道来领导天下、指引天下，鬼也没有什么神秘莫测的力量，因为你走的是正道，你走的是堂堂大道，鬼也没有办法去伤害到你，所以“以道莅天下，其鬼不神”。《道德经》里用它的道，把大家所恐惧的鬼的位置给取代了，你堂堂大道，鬼也近不了你的身，“其鬼不神；非其鬼不神”，不是鬼不神秘莫测，是因为你走大道，它的神秘、莫测、玄妙、诡秘已经没有办法伤害到你。所以把下一句话作为上一句话“其鬼不神”的注解，就很容易理解了。“非其鬼不神”，不是说这鬼不神秘莫测了，神秘莫测是它的本性。“其神不伤人”，但是它的神秘莫测已经伤害不了这种走在大道上的人、得道的人。“非其神不伤人，圣人亦不伤人”，不单是指鬼的力量伤害不了人了，反过来说，圣人他智慧高，但圣人智慧高也得返璞归真。圣人不会因为自己的智慧高，心眼多套路深，就使用这种“技巧”，这个东西不是正道。所以，鬼的神秘莫测伤不了人，圣人的智慧在领导大家的时候也会“善利万物而不争”，对人民没有伤害，“夫两不相伤”，你看鬼的神秘莫测也伤不了人，圣人领导也伤不了人。“夫两不相伤，故德交归焉。”所以有德的事情，积德的事情，两者交汇到一起，两不相伤。因为你按照道来做事情的话，鬼伤不了你，圣人也是按照道来做的，彼此也不相伤。这样大家就走在正确的道上，按照道去做，不断地积德，所以叫“德交归焉”，交汇，归到一块。“治大国若烹小鲜。以道莅天下，其鬼不神。非其鬼不神，其神不伤人；非其神不伤人，圣人亦不伤人。”如果这样两不相伤的，那就是“德交归焉”，这样就形成了一个和谐的、有道的、有德的世界。</t>
   </si>
   <si>
-    <t>第六十一章</t>
+    <t>第六十一章（61）</t>
   </si>
   <si>
     <t>大国者下流。天下之交，天下之牝（pìn）。牝常以静胜牡，以静为下。故大国以下小国，则取小国；小国以下大国，则取大国。故或下以取，或下而取。大国不过欲兼畜人，小国不过欲入事人。夫两者各得其所欲，大者宜为下。</t>
@@ -863,7 +860,7 @@
     <t>《道德经》从头至尾有一个非常重要的智慧与理念：善于处下。在第八章里面就说，“处众人之所恶，故几于道”，水去的是又低又脏的地方，把那里的污浊洗净，在那个地方滋润万物，跟道最接近的。做人要做“上善若水”的人，才能称其为“大人”，这个“大”代表的是品德。国家要成为一个大的国家，该怎么样做呢？它的处事的态度是什么呢？第六十一章里边开头这句话说得简要、明确、深刻：“大国者下流。”所以，这一章的核心我们看一下，开头“大国者下流”；结尾“大者宜为下”。越是大的国家越懂得善于处下，和小的国家打交道的时候谦逊谦和，和谐相处，你就把小的国家争取了。人也如此，位置越高，越要善于处下，这样才能真正居上。这是这一章的开头、结尾，也是这一章的核心。我们在解读“大国者下流”之前，我们需要采用以经解经的方式，拿第六十六章开头这句话，用这个形象先来让大家直观地感知一下，这个直观的形象我们了解了，再来看这一章就容易了。第六十六章开头这句话：“江海所以能为百谷王者，以其善下之，故能为百谷王。”大江大海为什么能成其大呢？它地势低，善于处下，其他的水系就都汇到它这来了，用我们习惯的话讲，就叫“善于团结一切可以团结的力量”。不辞细流，所以成为大江大海。然后我们再来看第六十一章开头这个五个字就很容易理解了。“大国者下流。”所谓“下流”，就是善于处下、处在水的下游，最好是处在大海的入海口，涓涓细流慢慢地汇成大江大海。那么善于处下《道德经》拿什么来比喻它呢？这个地方是什么？是天下的水交汇的地方，所以叫“天下之交”。拿什么来比喻“天下之交”的呢？《道德经》把它叫“天下之牝”，“牝”代表母性、女性，本来这个“牝”是指母性的生殖部分。因为在《道德经》里边母性、女性代表着慈，代表着柔，代表着静，“牝常以静胜牡”，“牡”是雄性，“牝”是雌性。这世界上的事情便是如此，这雌性善于柔，善于静，所以她的力量更长久。拿这个道理来说明什么呢？以静为下，什么叫善于处下？就是以静为下。别那么急躁、暴躁、浮躁、狂躁，善于处下，这样才能具有更大的力量、更长久的力量。这段讲完了，下边又接着“大国者下流”的道理。上面那一段是在论述它力量产生的源泉。一个大国老去动武，喜欢好战，好战者必亡，看着很强大，其实这都不是长生久视之道。所以下面就讲，“故大国以下小国，则取小国。”不是以静为下吗？善于处下吗？一个大的国家在跟小的国家打交道的时候，态度谦逊谦和，善于处下，不是居高临下、盛气凌人、不可一世的处事的方式方法，把这个小的国家就争取了。你和它平等相待，它觉得你这个大国可以倚靠，它喜欢跟你交往，遇到事情的时候喜欢支持你，帮助你，为你出力。“小国以下大国，则取大国。”为什么小国会这样做呢？因为小的国家也得找倚靠。小的国家在和大的国家打交道的时候，也善于处下，也把自己的位置放低，那么它就成了大国的朋友，有事的时候，大国才能给予支持，用我们现在习惯的话叫“罩着你”。大国也罢小国也罢，都得善于处下，这样才能形成一种和谐的关系。下面这两句话是比较难以理解的。“故或下以取，或下而取。”什么叫“以取”呢？争取有两种方式，一种是从上边抓起来，还有一种方式是更为有智慧的从下面轻轻地托起来。别小看这两个虚字、连词，“以”和“而”，这表示不同的动作。“或下以取”，要抓住你掌控你，“执者失之”，越想抓住越想掌控，失去得越快。“或下而取”，其实我们在帮助别人的时候，也就获得了别人的这样一种真心的敬佩，遇到事情的时候才能够得到人家帮助。“大国不过欲兼畜人”，大国想要更强大，就得需要更强大地支持，大国就得团结更多的小的国家，形成一个相互支持、相互帮助的局面。我给大家举一个例子，大家对这个问题就理解更深刻一点。我们中国文化的图腾——龙，大家都熟悉，我们叫“龙的传人”。可是，龙在自然界里面是没有的，它是怎么形成的呢？原来这些氏族部落，我们也可以把它看作是一个一个小的国家，那个时候他们互相征战、合并。龙的主体的部分就是蛇图腾，源自中原地区一个力量非常强大的部落，后来这个部落把很多小的部落合并到自己大的部落里边，它们收归一个部落就加上一个部落的图腾，这样，逐渐形成了龙的样子：蛇的身，马的头，鬣的尾……这不就是“兼畜人”吗？其实落到国家的层面也是一样，形成了一个团结的阵营，当然最好是正义的，遇到事情力量不就强大了吗？“大国不过欲兼畜人，小国不过欲入事人。”小国不过也想加入这个里面，大家一起做事，遇到事情的时候，大国还可以帮助、支持，这不是挺好的事儿吗？各得其所，所以叫“夫两者各得其所欲”，都得到自己所想要的。话讲完了，下边这句话又来了，“大者宜为下”，越是大的国家，越是位置高的人，越要懂得善于处下。</t>
   </si>
   <si>
-    <t>第六十二章</t>
+    <t>第六十二章（62）</t>
   </si>
   <si>
     <t>道者万物之奥，善人之宝，不善人之所保。美言可以市尊，美行可以加人。人之不善，何弃之有？故立天子，置三公，虽有拱璧以先驷（sì）马，不如坐进此道。古之所以贵此道者何？不曰以求得，有罪以免邪？故为天下贵。</t>
@@ -875,20 +872,19 @@
     <t>这一章比较难理解，先说一下这一章的断句，有很多不一样的版本。现在大家基本上能够认可的是“美言可以市尊，美行可以加人”，有的本子是“美言可以市，尊行可以加人”，断句的差别就在这两句上。这一章讲什么呢？这一章是讲“道”的重要性，“善人之宝”，善人要不停地按照道去做，是善人的宝贝。但是，不善人也不会被道所抛弃，道可以来拯救他，所以叫“不善人之所保”。现在我们从头来解释。“道者万物之奥，善人之宝，不善人之所保。”这个道是万事万物的奥妙之所在，所以它是“善人之宝”，是善良人的珍贵的宝贝，也是“不善人之所保”，是不善人得以被拯救的保障，道可以拯救这些走错路的人，让他回到正道上来。“美言可以市尊”，美言，好的话。说好的话、正确的话，它可以得到人们的尊重。“美行可以加人”，好的品行，可以增加人的尊贵，团结更多的人。其实这个道理也比较容易理解，我们熟悉的三个人——魏徵、李世民和长孙皇后。魏徵是美言，他劝李世民，你要做一个好皇帝，有些事你不能做。李世民很愤怒，回来之后在家里边发火，说要把魏徵给杀掉。长孙皇后反而衣服穿得很整齐，给他道喜，说你遇到了一个好的臣子，我应该向你贺喜。李世民后来领悟到这一点，他说镜子可以正衣冠，魏徵就像一面镜子可以正我的品行。历史上，三个人留下的都是美言，都得到了人们的尊重，所以叫“美言可以市尊”。既然道是“善人之宝，不善人之所保”，那么“人之不善，何弃之有”。有的人走错路了，你为什么就觉得要把他抛弃掉？让他回到正道上来，用道去教化、去拯救。这是从正面来说它的作用。下面就讲的这个事就有针对性了。“故立天子，置三公。”国家的制度慢慢地有了天子，作为最高的领导者，还有三公——辅佐天子的最重要的职位。“虽有拱璧以先驷马”，古代敬献礼的时候，拱璧，捧着玉璧，捧璧的人在前边，乘着高头大马进献。珍贵吧？不如“道”珍贵！这里面有两个意思：一个就讲国家的制度，有天子，有三公，很重要，但这也只是形式。还有呢，用高头大马进献珍贵的玉璧，这也是很珍贵。但是“不如坐进此道”，这些都不如按照道来做，大道才是“万物之奥”，“万物之宝”。“古之所以贵此道者何？不曰以求得，有罪以免邪？故为天下贵。”意犹未尽，讲到这地方，《道德经》还觉得这个话就应该再强调一下，说古往今来，为什么都要把这个道看得这样珍贵呢？“古之所以贵此道者何？”不就是说你按照道去做，你才能得到自己真正想要得到的吗？“以求得”，你要的那个东西才能真正得到。这里的“以求得”并不是像我们烧香拜佛求得发财。“有罪以免邪”，因为前面讲过，“不善人之所保”，就算走错路了，但是我们重归正道，浪子回头金不换，原来的这个罪，也能得以补偿。这个并不像有的宗教里边说你犯了什么罪去忏悔一下，这个罪就免除了，它是让你按照大道来做，回到正道。我们来分分类，人不就是这两类：“善人”、“不善人”，对那些不善良的人，走错路的人，你为什么要抛弃他呢？“坐进此道”，回归此道就可以啊。弄了那么多的官职，天子、三公，有那么多珍贵的财宝，拱璧、驷马，还不如“坐进此道”。既然如此，“道”就是天下人最珍贵、最宝贵的，“故为天下贵”。</t>
   </si>
   <si>
-    <t>第六十三章</t>
+    <t>第六十三章（63）</t>
   </si>
   <si>
     <t>为无为，事无事，味无味。大小、多少，报怨以德。图难于其易，为大于其细。天下难事必作于易，天下大事必作于细。是以圣人终不为大，故能成其大。夫轻诺必寡信，多易必多难。是以圣人犹难之，故终无难矣。</t>
   </si>
   <si>
-    <t>用无为的态度、方式来作为，用不找事、不多事的方式来做事，最好的味道反而是没有味道。以小为大，因为大事都从小事做起；以少为多，因为积少才能成多。用德来对待别人的怨。对付困难事情要在它还容易解决的时候开始，成就大业要从很小的
-事情做起。天下所有的难事都是从容易的做起，天下所有的大事都是从小事做起。因此圣人始终不去直接做大事，不说大话空话，所以最后能成就大事。没有把握的事轻易许诺别人一定会失去别人的信任，把事情看得太容易一定会遇到更多的困难。因此圣人把所有事情都看得很难，反而没有什么难事。</t>
+    <t>用无为的态度、方式来作为，用不找事、不多事的方式来做事，最好的味道反而是没有味道。以小为大，因为大事都从小事做起；以少为多，因为积少才能成多。用德来对待别人的怨。对付困难事情要在它还容易解决的时候开始，成就大业要从很小的事情做起。天下所有的难事都是从容易的做起，天下所有的大事都是从小事做起。因此圣人始终不去直接做大事，不说大话空话，所以最后能成就大事。没有把握的事轻易许诺别人一定会失去别人的信任，把事情看得太容易一定会遇到更多的困难。因此圣人把所有事情都看得很难，反而没有什么难事。</t>
   </si>
   <si>
     <t>第六十三章的内容，我们在前边已经有所接触。之前我们说，第二章就是《道德经》的“目录”，第二章列出来了后边讲的六个重要内容，有无相生、难易相成等等，这一章的核心就是“难”和“易”。这一章的核心意思就说，要想做大事，先从小事做起，想要以后攻坚克难，你得从容易的事情做起。还有一个重要的问题、重要的智慧：你要把容易的事情当作难的事情来做，要有充分的、认真的准备，提前思考它的步骤、程序、会遇到的问题，这样再出什么问题的时候，你就能从容应对。有这样的态度，天下也没什么难事。天下无难事，但天下都是难事，看你怎么对待。开头这九个字非常有趣：“为无为，事无事，味无味。”“为无为”——想要有为吗？你得先懂得无为的道理。为什么？因为有些事你越有为，越强求，什么事都管，反而最后结果非常不好。道家讲的无为，就是按照道的方式来作为，想要有为，先要懂得无为的道理，不要妄为，要抓住关键，举重若轻，有所舍才能有所得，所以为无为。其实也就是第三十七章里边讲的“道常无为而无不为”，道的规律、规则是什么？用无为的方式达到无不为的效果，更好的效果。我再强调一下，《道德经》里出现得最多的一个词是“天下”。《道德经》针对的是天下，千万不要把道家当作一种消极的被动的思想，它是“想为”，但是强调要通过正确的道路和手段，懂得无为的正确的道路和手段，才能达到真正的有效的为，也就是用无为的方式，达到无不为的这种效果。下边再落一层，“事无事”。大家都想做事，可是大家有没有注意到，有些人他是“找事”，他是捣乱，是阻碍、多事，天下本无事，庸人自扰之。所以我们做事的时候要懂得无事的道理，不要多事，不要找事，不要刁难。尤其是做领导者，没事找事，权力就是刁难，你这不就麻烦了吗？“事无事”，想做事，得懂得无事的道理，不要多事，不要扰民。再落一层，“味无味”。我们经常讲一个词叫“真水无香”，真正好的饮料，就像那白开水一样，没有味道。我们饮食讲究清淡，寡味，少油少盐。最高的味道，反而是没有味道，无味。当然，这三个词核心还是“为无为”，让大家能够更明白一点。老子展开来讲，“事无事”，不要多事，不要扰民，不要刁难，就像“味无味”的道理一样。按照这样的一个逻辑推下来，下面四个字大家就能明白了，“大小、多少”，千万不要把它念成“大小多少”，这个东西就没意义了。这是告诉大家要“大其小”、要“多其少”，要把小事看得很重要，细节决定成败，千万不要忽略这个细节。为什么要“大其小”呢？因为天下的大事，都是从小事做起，为什么要“多其少”呢？因为积少才能成多。想要多，你得从少的一点一点积累，积少成多。就像我们学习《道德经》，一章一章讲，一章一章学，不要着急，最后达到一个整体的理解。我们经常讲“聚沙成塔”、“集腋成裘”，这不都是“多其少”的道理吗？“报怨以德”，按照这种相反相成的道理，对别人的埋怨、恩怨，也应该站在一个“德”的角度，因为德是符合道，用道的东西里面去感化。第六十二章不是讲了吗？“人之不善，何弃之有？”人家有这个埋怨，怎么正确地对待呢？“报怨以德”。用这种智慧和层次，让大家一起能回归到正途，回归到正道。“图难于其易，为大于其细。天下难事必作于易，天下大事必作于细。”这几句话，在我们文化里边名气非常大，因为讲的是哲学上的量的积累达到质的变化的道理。“图难于其易”，“图”就是图谋、计划。你计划想要做难的事情，要从容易的事情做起。“为大于其细”，想要做大的事情，得从小的事情一步一步来。我们大家都知道要脚踏实地，循序渐进，有条不紊，一屋不扫，何以扫天下？“天下难事必作于易”，天下所有的难事，都要从容易的事情做起。就像小孩的培养，让他们在处理小的事情中就形成良好的习惯，把小的事情、容易的事当成培养良好习惯的重要途径，将来，小孩在遇到大事、难事都能从容应对。现在很多人都有一个致命的弱点，大概是人的通病，就是好高骛远，老觉得自己应该是做大事的人，对小的事情不屑一顾。《道德经》就告诉我们这个智慧：想要做难的事情，从容易的事情做起；想要做大的事情，从小的事情做起，“天下大事必作于细”。“是以圣人终不为大，故能成其大。”“是以”，“是”就是这样，“以”就是所以。所以有智慧的领导者就是这样：“终不为大”，不是老说大话，不是老给大家画饼充饥，而是脚踏实地，一步一步地做起，“故能成其大”。一步一步把这个事情完成了，一步一步地完成计划，最后实现一个大的蓝图，好的结果，水到渠成。所以一个有智慧的人，不是老用那些虚幻的东西来画饼充饥，老是给大家讲大话、空话。“终不为大，故能成其大”，最后反而成就了大事，这话讲得非常好。我建议大家学习《道德经》，有一种重要的学习方法，就是反复看。有的人看《道德经》，也许一年就看一章，反复地看，反复地体会，“少则得，多则惑”，“终不为大，故能成其大”。以管窥天，以锥扎地，我们视力更集中，这样把这个事情才能做得更踏实，扎得更透。我们每一次的进步，虽然看起来好像只是一点点，但是这一点点积累起来就不得了了，“终不为大，故能成其大”。“轻诺必寡信”，大家还记得我们在讲《道德经》第八章的时候，就讲过“言善信”，我们中国人喜欢拿潮水作为讲信用的代表和象征，所以，有一个词就叫“潮信”。你看那钱塘潮每到农历八月十八前后就来了，人也应该如此，说话要讲信用，要有诚信，能给别人做成的事我们再去允诺，没把握做成的事，不要轻易去答应，不管我们有多热情。如果我们答应人家的很多事最后都做不成，时间长了，人家一定认为我们是食言而肥，不讲信用。《道德经》讲话是比较宽缓的，但这句话用的就是强逻辑判断，“轻诺必寡信”，这不是对我们委婉的劝告，这简直就是对我们严厉的警告。所以要讲诚信，君子重一诺，一诺千金嘛，所以“轻诺必寡信”，要避免这种结果出现。“多易必多难”，你把这个事情看得很容易，做什么事情，最后一定出问题。世界上哪有容易的事情，吃个饭喝个水，这都需要功夫，需要本事，小事情我们都要认真对待。我们经常讲“小河沟里翻船”，把一个事情看得太容易了，太简单了，往往会在这个事情上出问题。面对很多难的事情，大家战战兢兢，小心谨慎，反而没事，反而就是在一些认为最容易的事情出问题。很多学生做题、考试也是一样，难题没事，在容易的题上，出了问题，回去捶胸顿足，懊悔无比。所以，我们平常要形成一种把容易的事情当作难的事情来做的习惯，你要懂得“多易必多难”，凡事太容易，后面一定会出现很多的困难，出现很多的问题。所以，下边这句话就讲：“是以圣人犹难之”，所以有智慧的人，把这容易的事情都看作很难。天下的事情都当作难的事情来做，反而结果没有什么难的事情，“故终无难矣”。这个道理非常有趣，其实就是相反相成的道理，这个叫“难易相成”。世界上有没有难事呢？有，也没有。你把这个难的事情当作难的事情，看作是无法克服的，它就是难的事情；你把容易的事情当作容易的事情，没有认真对待，最后也会变成难的事情。我们把容易的事情当作难的事情来做，最后那个难的事也就做成了；真正难的事情，我们认真准备，有充分的信心，最后这难的事情也就克服了。“故终无难矣！”世上无难事，这就是“难易相成”的智慧。很多事情，决定于我们的想法、态度，态度不同，难易之间就会相互转化。</t>
   </si>
   <si>
-    <t>第六十四章</t>
+    <t>第六十四章（64）</t>
   </si>
   <si>
     <t>其安易持，其未兆易谋，其脆易泮（pàn），其微易散。为之于未有，治之于未乱。合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。为者败之，执者失之。是以圣人无为，故无败；无执，故无失。民之从事，常于几成而败之。慎终如始，则无败事。是以圣人欲不欲，不贵难得之货；学不学，复众人之所过。以辅万物之自然，而不敢为。</t>
@@ -900,7 +896,7 @@
     <t>第六十三章、第六十四章讲的道理，就是大家熟悉的量变和质变的道理，量的积累达到质的变化。但是大家注意，这个量的积累，有向好的方面，也有向不好的方面。前面讲了“为大于其细”，要做大事，从小的事情做起，这样才能最后达到想要的结果，假如积累的是一个不好的量，最后就积重难返。第六十四章一开始就要把两个方面，都给大家做了说明，有的事情在它刚出现向坏的方面发展苗头的时候，我们在这个阶段就把它解决了。这一章里有两个非常重要的内容，一个是大家都熟悉的一段话：“合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。”第二个就告诉我们，做事情要“慎终如始，则无败事”。这两个重要内容，我们先有一个直观的认识，再来读就好理解了。我们一句一句来解释。“其安易持”，“安”就是稳定，局面稳定的时候，容易掌控，就像一个东西，它稳定的时候，你容易把它把握住；它活蹦乱跳的时候，你把握起来就困难了。“其未兆易谋”，“未兆”，没有征兆的时候，苗头还没有开始的时候，容易去谋划。“其脆易泮”，脆的时候一打就打散了。“其微易散”，很微小的时候，很容易把它解散。比如说一件事情，很小的时候，人数很少的时候，你把它处理起来很容易。众怒难犯，一大群人轰起来、闹起来的时候，这事情解决起来就困难。前面告诉大家这些现象，然后告诉大家处理的方法。什么方法呢？“为之于未有”——在事情没有出现的时候，没有开始的时候，要有预见性，就要有作为，凡事预则立，不预则废。“治之于未乱”，还没有出现这种乱象的时候，就把它治理了、解决了。这也是习近平讲话时经常引用的两句话。怎么来理解呢？先给大家说第一个例证。有一次晏子出巡，齐国发大水，把一座石桥给冲毁了，晏子就把自己的船让给了灾民，大家都赞誉晏子爱民如子。然而一位有智慧的高人就批评晏子，就说你做这个国家的宰相，齐国发大水能把一座桥梁冲毁，你都没有预见到，没有提前做出预防，你失职。所以应该是怎么样？“为之于未有”，你别等这个事情都已经成为这个样子，再去处理它，不管你处理的方式多么巧妙，多么有智慧，但是不如让这件事情没有发生。另外一个例证更能说明这个道理。有一次，扁鹊的国王问扁鹊：扁鹊你名气太大了，你是不是国家医术最高的？扁鹊说不是，别人我不知道，起码我大哥、我二哥都比我的医术高。所以这个国王就很奇怪，你大哥、你二哥是谁？他们医术那么高，怎么大家都不知道他们呀？扁鹊就说，我大哥怎么治病的呢？人家还没有病，他告诉人家怎么预防、怎么不得病。这不是“为之于未有”吗？提前就有作为了，预防得病。我二哥怎么治病的呢？人家刚有一点小病，他就把人治好了，不让他酿成大病，“治之于未乱”。所以我们经常讲，凡事预则立，不预则废，要有远见，要有预见，要未雨绸缪。这是讲负面，因为有些事情量的积累是向不好的方面发展的，所以要提前把这个问题给处理掉。下面讲的这个事，非常重要。我们做大事情都要从容易的事情、小的事情，一步一步积累才能达到这种质的变化，要脚踏实地，循序渐进。因为什么呢？“合抱之木，生于毫末”，合抱之木，它是一点一点长起来的。“九层之台，起于累土”，中国文化中，三六九都代表着高、多。那么高的高台也是一层一层土积累起来的。“千里之行，始于足下”，走这么远的路，要脚踏实地一步一步地做起。说到这里，我得加一句，有人老认为道家思想是消极的、被动的、无为的。“合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。”这不就是自强不息吗？所以有些事我们不能人云亦云，我们得看原文，以原典作为证据。“为者败之，执者失之。”“为”就是强为、妄为。因为《道德经》讲的真正的为叫“无为”，就是按照道的方式来作为，不按照道的方式来作为就是强为、妄为。越是强为，最后的结果越糟糕，因为量的积累还不到，你老想强行地发生质变，这不是急躁冒进吗？“执者失之”，就像我们抓沙子一样，你握得越紧，流出来越多，越想用力地把它抓住，反而失去得越来越快。所以一个有智慧的领导者，“无为”，按照道的方式来作为，不妄为，不强为，不多为，有所不为，所以也不会有急躁冒进的失败。“无执故无失”，没有这样的强执，最后也不会失去。“民之从事”，平常人做事，或者说领着大家做事，在什么时候最容易把事情给做砸了呢？“常于几成而败之”，经常在快要接近成功的时候，把事情给做砸了。那应该怎么办？“慎终如始，则无败事。”什么叫慎终如始呢？我先给大家打一个比方，大家走在结着冰的冰面上的时候，刚一下到冰面上都是小心谨慎，战战兢兢。走一会儿，觉得自己走熟了，就放松警惕了，有的干脆最后开始跑了，有的甚至在冰面上炫耀，危险往往就在这个时候发生了。所以我们中国人经常讲一句话叫“行百里者半九十”，一百里的路，走到九十里路的时候，还要当才走了一半，越是剩下那一段的时候越紧要，民间讲“编筐编篓，全在收口”，即最后这个结尾。“慎终如始”，走到最后那几步，还像开始下到冰面上一样小心谨慎，一步都不放松，那就没什么败事，没什么事情做不成。“慎终如始，则无败事”，就是我们现在经常讲的不忘初心，善始善终，那就没有什么事情做不成的。“是以圣人欲不欲”，一个有智慧的人，特别是一个有智慧的领导者，想要的东西是什么呢？是别人都不关心的，都不想要的。因为“天下熙熙，皆为利来；天下攘攘，皆为利往”，大家关心的是获取利益的方式方法，而一个有智慧的人，有智慧的领导者，应该有这种无功利之心。“欲不欲”，别人都不想这样的，反而是你应该考虑的。大家都针对“有”的东西，这有智慧的人、好的领导者得针对这无形的东西：人的精神财富，人的精神世界，人的修养。既然“欲不欲”，你跟一般人的欲望不一样，他们认为那个东西是珍贵的、难得的，反而在你的眼里是不重要的，不把它看作是难得的。领导国家的时候也是如此，第三章讲的，“不贵难得之货，使民不为盗”，形成一种淳朴的风气。“学不学，复众人之所过。”《道德经》讲的道理，叫“绝学”，一般人不愿意学，学这个东西能带来什么样的好处、利益吗？人的境界高的时候，学的很多的东西不就是和一般人不一样的嘛。一般人不愿意学的东西，又花功夫，又不能带来什么实际的利益，可是“学”这些东西代表了真正的智慧与学问。学这些东西干吗呢？“复众人之所过”，这个“复”不是重复，我们下围棋的人都知道有个词叫“复盘”，通过不断的重复模拟来检视，哪个地方下得好，哪个地方下得不好。别人犯的过错像复盘一样历历在目，以此为鉴，别再犯大家都经常犯的错误。“以辅万物之自然，而不敢为。”“以辅万物之自然”，就是按照自然的规律去做，追求的是一种水到渠成、自然而然的结果。“辅自然”就是无为。“而不敢为”，就是不敢妄为。因为我们违背了道，违背了自然规律，哪怕是短时间取得成功，其实也会受到更大的一种惩罚。这章告诉我们，一是我们做事情要“为之于未有，治之于未乱”，懂得预防，懂得不好的事情在苗头出现的时候就把它解决掉；二是我们做事情要脚踏实地，循序渐进；三是我们要“慎终如始”，不忘初心，善始善终，因为我们做事情经常在快要成功的时候，结果功亏一篑，所以要懂得这样一个道理。</t>
   </si>
   <si>
-    <t>第六十五章</t>
+    <t>第六十五章（65）</t>
   </si>
   <si>
     <t>古之善为道者，非以明民，将以愚之。民之难治，以其智多。故以智治国，国之贼；不以智治国，国之福。知此两者，亦稽式。常知稽式，是谓玄德。玄德深矣，远矣，与物反矣，然后乃至大顺。</t>
@@ -912,7 +908,7 @@
     <t>这一章所涉及的，也是我们现在哲学里面经常讲的一个道理，叫“否定之否定”规律，讲事物的发展分为三个阶段，第一个阶段是肯定，第二个阶段是否定，第三个阶段是否定之否定。比如说麦粒长出麦苗，最后结出更多的麦粒，这就是一个否定之否定的阶段。第三个阶段常常重复第一个阶段的某些特征，却是在更高的程度上重复第一阶段的某些特征。这一章和第四十章讲的“反者，道之动”，所运用的哲学的智慧和道理是一样的，既然这样，把这个道理运用到治国上，应该如何呢？这就用到了一个我们大家熟悉的词，叫“返璞归真”，《道德经》认为治民最关键的是要使民风纯朴，不要那么多的技巧，不要那么多的套路。了解了这一点，我们再来看这一章，就明白了老先生的良苦用心。“古之善为道者”，以前的那些善于按照道来治理国家的人。“非以明民，将以愚之”，不是让百姓有那么多的心眼技巧。这个“愚”，不是愚民，而是敦厚、厚道，让人民的民风纯朴。“民之难治，以其智多。”百姓为什么难以治理？因为他心眼多、技巧多。“智”就是技巧、心眼、套路。“故以智治国，国之贼”，用技巧来治国，经常用骗术谎言，这是国家的灾难。“不以智治国，国之福”，不用这些技巧，让民风纯朴、敦厚，这个才是国家的福祉、国家的福分。“知此两者，亦稽式。”“稽式”就是法则。知道这两个的差别，这就是一个法则，治国的一个法则。“常知稽式”，“常”就是规律。按照规律，我们来了解这个法则。这叫什么？“是谓玄德”，“玄”就是深远的意思，这个就是深远的智慧与品德。下面这句话就是我一开头讲的，这个品德“深矣，远矣，与物反矣”，“与物反矣”不就是“反者，道之动”吗？我们都能看到事物的正向的发展，所以《道德经》经常提醒我们，“反者，道之动”，道是向它相反的方向运动，所以你理解问题也不能只看一面。“与物反矣”怎么解释呢？第二十五章，“大曰逝，逝曰远，远曰反”，最后又回到了它的根本。根本是什么？“归根曰静”。民心没那么多的躁动，变得清静宁静、敦厚朴实，这不就符合大道了嘛。“然后乃至大顺”，这样慢慢地就回归到了正确的道路，符合自然之道。所以，这一章讲的就一个问题：你用什么方式治国呢？要让民心变得纯朴、敦厚，返璞归真，没那么多的技巧，没那么多的套路，没那么多骗人的把戏，这样才是符合大道。</t>
   </si>
   <si>
-    <t>第六十六章</t>
+    <t>第六十六章（66）</t>
   </si>
   <si>
     <t>江海所以能为百谷王者，以其善下之，故能为百谷王。是以欲上民，必以言下之；欲先民，必以身后之。是以圣人处上而民不重，处前而民不害。是以天下乐推而不厌。以其不争，故天下莫能与之争。</t>
@@ -924,20 +920,19 @@
     <t>这一章所讲的这个道理是《道德经》从头至尾所强调的“善于处下”，只有善于处下，才能真正居上。我们在一开始说过，《道德经》的很多话是针对那些领导者、统治者讲的，所以老先生认为越是位置高的领导者、统治者，越要善于处下，为什么呢？首先从处下的结果上来看，“江海所以能为百谷王者，以其善下之，故能为百谷王。”这句话我在前面也多次引用过。大江大海之所以能成为大江大海，是因为善于处下，不辞细流，能团结一切可以团结的力量，故能为“百谷王”。老子先拿“百川归海”的形象讲了这个道理，让大家有一个感知。下面就开始讲具体的做法和内容。“是以欲上民，必以言下之。”所以你要想站在上面领导好下面这些人，在语言上要懂得谦逊、谦让。领导者，尤其国君、皇帝这一类的，讲话的时候不能够居高临下，盛气凌人，自尊自大，不可一世。第三十九章说过“贵以贱为本，高以下为基。是以侯王自称孤寡不穀”，所以在语言上要谦逊。“欲先民，必以身后之。”想要站在前面当好领导、当好领头的，要懂得把自己的利益放在后面，想要领导别人就得给别人利益。一个人既要领导别人，又想什么好处、利益、功名都抢在自己手上，这个人下场不是不言而喻的吗？范仲淹的《岳阳楼记》里说“先天下之忧而忧，后天下之乐而乐”，做官、做领导不得如此吗？钱钟书先生认为范仲淹这两句话就是出自《道德经》的。但是人家学得比较好，不也成了大家都熟悉的名句了吗？“是以圣人处上而民不重”，所以一个好的领导者，你在上面领导大家，大家没有感觉到沉重的压力。“处前而民不害”，你在前面领导大家，大家没有感觉到你对他的危害。因为你要想领导别人，得让别人得到利益。西汉史学家司马迁在《史记·循吏列传》说：“公仪休者，鲁博士也。以高弟为鲁相。奉法循理，无所变更，百官自正。使食禄者不得与下民争利，受大者不得取小。”这里的食禄者不与民争利，意思是做官的人不许和百姓争夺利益。“是以天下乐推而不厌”，所以天下的人民都往高举你，往前推你，不感觉到厌倦、厌烦。如果统治者穷奢极欲，危害百姓，草菅人命，下面的人就会感觉到“害”、感觉到“重”，这样的人百姓会“乐推”吗？当然不会。“以其不争，故天下莫能与之争。”一个领导者，能得到了大家的拥护、拥戴，正因为你不争，不与民争利，不与其他人争名，“利而不害，为而不争”，结果是“以其不争，故天下莫能与之争”。越是争的人，最后往往失败得越惨，因为你的位置已经规定了你应有的担当、使命和责任。陈毅元帅讲过“手莫伸，伸手必被捉”，形象而深刻，那么，反过来用这个道理讲，就得以更加明确了。“以其不争，故天下莫能与之争”，所谓“不争”，并不是消极被动，“不争”，当然要了解边界，不争边界之外的东西，这样的话才能“天下乐推而不厌”。</t>
   </si>
   <si>
-    <t>第六十七章</t>
+    <t>第六十七章（67）</t>
   </si>
   <si>
     <t>天下皆谓我道大，似不肖。夫唯大，故似不肖。若肖，久矣其细也夫。我有三宝，持而保之。一曰慈，二曰俭，三曰不敢为天下先。慈，故能勇；俭，故能广；不敢为天下先，故能成器长。今舍慈且勇，舍俭且广，舍后且先，死矣！夫慈，以战则胜，以守则固。天将救之，以慈卫之。</t>
   </si>
   <si>
-    <t>天下都说我讲的道太大了，似乎不像任何具体的东西。正是因为道大，所以什么也不像。如果像，就早已归为具体事物了。我有三件最珍贵的宝物，值得永久保持。一个是“慈”（守柔），一个是“俭”（节俭），一个是“不敢为天下先”。能做到守柔，才能真正的勇敢刚强；节俭才能长久持续地发展；遇到利益不争先，懂得先人后己，才能成器、成长（成为万物的领导者）。现在的人舍弃守柔而只求勇武，舍弃节俭还奢求长久持续的发展，遇到利益争先恐后、一点都不退让，这是自寻死路！如果能做到守柔，凭它作战就能胜利，凭它守卫就能坚不可摧。上天要救助一个
-人，保护这个人的办法就是让他具备柔和的品性。</t>
+    <t>天下都说我讲的道太大了，似乎不像任何具体的东西。正是因为道大，所以什么也不像。如果像，就早已归为具体事物了。我有三件最珍贵的宝物，值得永久保持。一个是“慈”（守柔），一个是“俭”（节俭），一个是“不敢为天下先”。能做到守柔，才能真正的勇敢刚强；节俭才能长久持续地发展；遇到利益不争先，懂得先人后己，才能成器、成长（成为万物的领导者）。现在的人舍弃守柔而只求勇武，舍弃节俭还奢求长久持续的发展，遇到利益争先恐后、一点都不退让，这是自寻死路！如果能做到守柔，凭它作战就能胜利，凭它守卫就能坚不可摧。上天要救助一个人，保护这个人的办法就是让他具备柔和的品性。</t>
   </si>
   <si>
     <t>老子、孔子、释迦牟尼、柏拉图，这都是同时代人，在他们那个时代，书其实只有一种题材，就是对话体。《论语》是孔子弟子记的，记得非常清楚，坐在对面的是什么人，提了什么问题，老师怎么回答，所以大家读起来一目了然。佛经呢？很多的佛经也都是释迦牟尼对弟子问题的回答，大家看《金刚经》，是回答须菩提的，《心经》是回答舍利子的，都是针对他们的问题的回答。古希腊哲学家苏格拉底的学生叫柏拉图，写了一本《对话录》，就是记载当时苏格拉底跟学生之间的互动，对各种问题的解答。其实《道德经》的最早的形成也是这种形式，也是对面坐的人问的问题，老先生给予回答，也是对话体，所以我们读这本书，始终要感觉到这是在回答对方的问题，是有针对性的解释和回答，这样很多问题我们才能够得以正确地理解。那么这一章是在回答什么问题呢？对面坐的人，问老子关于道和德的事，老先生给他讲半天，他没听懂，于是提出要求：能不能把你的思想概括得简单点？你让我也能听得明白。大家自然会有疑问，我怎么知道是这样的？是不是我自己在杜撰？让我们回到原文，大家看一下这一章的开头就清楚了。“天下皆谓我道大，似不肖。”老子这个意思就是说，不仅是你，天下人都认为我把道讲得太大、太宽泛了，听不懂。你听不懂，我得给你打比方，类比虽然不能够说明问题，但是它可以让人理解问题。我说道就像风一样，大象无形，你们说不像；我说道就像水一样，大道汜兮，其可左右，你们还说不像……“夫唯大，故似不肖。”正因为把道讲得这么大，拿什么给他打比方，他都说不肖，所以老子就感慨，假如真的像的话，“久矣其细也夫”。意思是假如真的像，那早就归到小道了。比如，说道像一条大河，你拿这个比方，要像的话，就像支流了。道就像一条大道，你要说比方像的话，就像小道。其实意思就说，拿道打比方，要是真的像的话，就是把道说得太小、太细了。那怎么办？不跟你讲那么多了，把我的思想概括到简单得不能再简单。只剩下三个方面，“我有三宝，持而保之。”把我的思想概括到最后，简单得不能再简单了，就剩下三个方面拿出去，按照去做就行。那这“三宝”是什么呢？“一曰慈，二曰俭，三曰不敢为天下先。”大家解读这三组词的时候，不可以单独先解释几个字词，一定要把“三宝”里边的字词和后面的语句连接来解读：“一曰慈，慈故能勇；二曰俭，俭故能广；三曰不敢为天下先，故能成器长。”否则，会失之宽泛。“一曰慈，慈故能勇。”“慈”是指什么？指的是慈母的情怀。做领导、做家长，有了慈母的情怀，才能有真正的担当、勇敢。如果你单独解释这个“慈”就麻烦了，慈母有时候也唠里唠叨，有时也无原则地爱，不是经常说“慈母多败儿”吗？可是《道德经》为什么把“慈”放到第一位呢？这是针对坐在对面的提问者的。作为领导、作为诸侯王，你在这个位置，就要有慈母的情怀，才能有真正的担当、勇敢。如果没有慈母的情怀，一出事就会出卖国家和人民，一出事就把自己的部下当做替罪羊推到前边。“二曰俭，俭故能广。”我还是觉得这位老先生对咱们中国人了解得非常深刻，我们中国人致命的弱点是什么？好面子，好虚荣，好攀比。所以一旦是公开的场合，一旦是监督不力，往往就奢靡之风盛行，浪费之风盛行。没有节俭节制，而是有奢靡之风浪费之风，那就没办法“广”，“广”就是长久持续。家庭没有培养出节俭、节制之风，家庭就没有办法长久持续地发展，所以要勤俭持家。国家人民没有培养出节俭节制之风，而是奢靡浪费，这个国家也没有办法长久持续地发展。“三曰不敢为天下先，故能成器长。”先理解“成器长”，咱们中国很多的词是组合性的，所以大家理解的时候，也要把它组合的东西拆开，“成器长”拆成四个字“成器成长”。我们怎么样才能不断地成长，终成大器呢？“不敢为天下先”，现在咱们天天讲叫“敢为天下先”，这又来一个“不敢为天下先”，这两句话不就怼上了吗？其实这两句话根本不矛盾，讲的不是一回事儿。我们现在强调的“敢为天下先”，是敢闯敢创新，这是一种很好的品质，创新是一个民族的灵魂。《道德经》讲的“不敢为天下先”是什么意思呢？做领导，领着大家做事，要懂得把自己的利益放在后面，要懂得先人后己，不要私欲膨胀，不要什么事情只关注自己，这样才能够不断地进步，不断地成长，终成大器。各位是否还记得我在前面给大家说过，其实读这本书的时候，不用别人给你画出重点，你自己都能感觉到，因为老子在书里不断地强调自己的重点，一种强调的方法是重复，第二种强调的方法是头尾，第三种强调的方式就叫正反，也就是他正面讲完了，觉得是还言犹未尽，要从相反方面给大家再论证一下，你看这一章不就是这样吗？现在的人是什么样的，本来应该按照道的方式来做，要慈、俭、不敢为天下先，我们把这“不敢为天下先”也可以概括成两个字叫“谦让”，或者概括一个字叫“让”。我有三宝，慈、俭、让。可是老子对当时的人不满意，这些人都怎么做的？“舍慈且勇”，根本没有这种情怀，还到处炫耀自己的勇敢。我们现在不也经常看到这种情况？酒驾了，还拍个视频给警察发过去，我醉驾，警察你来抓我呀，炫耀自己无赖似的勇敢。“舍俭且广”，没有这种节俭、节制，还奢求长久持续地发展，不可能。“舍后且先”，遇到好处、利益，争先恐后，一点都不肯让，甚至不该自己的也抢，这样做的结果是什么呢？“死矣！”这样做的最终结果，就把自己弄到死路上去了。“夫慈，以战则胜，以守则固。天将救之，以慈卫之。”这些讲完了，又把他讲的第一个“慈”再说一遍。有这种慈母情怀的人，那么面临事情的时候就会“以战则胜”。他勇于担当，真正遇到困难的时候，领着这个大家当然攻无不克，战无不胜。“以守则固”，国家遇到侵犯的时候，领导者的这种情怀，力量无尽，守无不固。“天将救之，以慈卫之”，如果天真的有情感的话，他要拯救国家的人民，拯救团队团体，一定是“以慈卫之”，你一定有这种慈母的情怀才值得，因为它本身就拥有无穷无尽的力量。第六十七章，核心的就是“我有三宝，持而保之”，要坚定、坚持地按照去做。</t>
   </si>
   <si>
-    <t>第六十八章</t>
+    <t>第六十八章（68）</t>
   </si>
   <si>
     <t>善为士者不武，善战者不怒，善胜敌者不与，善用人者为之下。是谓不争之德，是谓用人之力，是谓配天古之极。</t>
@@ -949,7 +944,7 @@
     <t>这一章讲什么呢？我们中国人有一个习惯，喜欢拿战争的术语来打比方，比如说我们现在吃个饭，也可以说“打个冲锋”，来个“歼灭战”，平常我们也经常讲“占领制高点”。这一章既是在讲战争，又通过战争延伸开来，讲普遍性的制度。“善为士者不武”，“武”的意思就是耀武扬威。善于做基层领导者的人，或者说指挥打仗的士官，不耀武扬威。不要有了这样的一个位置，就耀武扬威，趾高气扬，盛气凌人，不可一世。“善为士者不武”，保持一种谦逊的、平和的、冷静的心态。“善战者不怒”，善于指挥作战的人，不是动不动就暴跳如雷。“不怒”，懂得制怒。任何一个人不管他位置多高，在急躁、浮躁、暴躁、狂躁的心理状态下都谈不上智慧。我们看一下“怒”的写法，上面是个“奴隶”的“奴”，下面是个“心”，当我们控制不了自己的情绪，心成了情绪的奴隶，没有办法保持清醒、冷静、理智的心理状态，才会发怒。所以真正善于作战的人，善于做事的人，要保持这种清醒、冷静、理智的心理状态。“善胜敌者不与”，“不与”，就是不和他发生正面的冲突。从字面的意义上来讲，善于制胜的人，懂得用委婉迂回的方式获得胜利。我们把这个“战争术语”延伸一下，其实在家里也一样，两个人情绪都到达高点、发生剧烈的冲突，这时候解决起来就比较困难。所以，越是到这个时候，越要懂得以退为进，懂得用委婉迂回的方式来解决问题、处理问题，这样才能很好地战胜对方，说服对方。“善用人者为之下”，我在前面多次说过，这是《道德经》从头至尾强调的一个最普遍的原则，善于处下者方能真正居上。一个领导者也是如此，朋友之间相处也是如此，保持自己这种谦逊处下的态度，这样才能够跟人和谐相处，才能“用人之力”。这个叫什么？“是谓不争之德”。“善为士者不武，善战者不怒，善胜敌者不与”，尤其是“善用人者为之下”，都是《道德经》里边从头至尾强调的“不争之德”。说到“不争之德”，我们的思路又回到第八章，“上善若水，水善利万物而不争”，后边讲了“不争”的七种品德：去大家不愿意去的地方——“居善地”；我们要保持内心的宁静，静水流深——“心善渊”；和别人相处，要懂得关爱，一视同仁——“与善仁”；讲话要讲诚信——“言善信”；公平、公正、清廉，所谓政清如水——“政善治”；做事情的时候要尽其所能，像水一样有多种多样的这种本领——“事善能”；善于把握时机，掌握机会——“动善时”。所以，这里的“不武”、“不怒”、“不与”、“为之下”，也是对这个“不争之德”的进一步说明。这个就叫“用人之力”，我们熟悉的一个词叫“借力打力”，熟悉的一句话叫“孤举者不起，众行者易趋”。一个人举重物举不起来，大家同心协力，形成这种趋势，这样才能把事情做成。既然如此，就要懂得用人之力，而不是孤军奋斗，这样做才能够很好地和别人和谐团结。再往高了说“是谓配天古之极”，“古”就是古往今来，所谓“配天”就是符合天道，这些是古往今来的大智慧。第六十八章没有什么难的地方。大家要明白一点，我们中国人习惯用战争的术语来讲生活中的事情，所以我们的理解不能停留在字面上。</t>
   </si>
   <si>
-    <t>第六十九章</t>
+    <t>第六十九章（69）</t>
   </si>
   <si>
     <t>用兵有言：吾不敢为主而为客，不敢进寸而退尺。是谓行无行（háng），攘（rǎng）无臂，扔无敌，执无兵。祸莫大于轻敌，轻敌几丧吾宝。故抗兵相加，哀者胜矣。</t>
@@ -961,7 +956,7 @@
     <t>第六十八章是用战争的术语来做比方，讲的道理当然比仅局限于战争更为广泛。第六十九章我们也当作如是观，他讲的是战争的事情，但是这个道理我们也可以做延伸、做扩展，成为我们生活中的、工作中的普遍的思想与智慧。我们知道《道德经》里边很多的内容并不是老子本人的话语，他也是一个“集大成者”。他经常在回答坐在对面的圣、王、士这些领导者的问题的时候，引用当时或者以前那些智者的语言。第一句话，“用兵者言”，懂得用兵的人怎么做谋划？怎么来认识问题呢？“吾不敢为主而为客”，我才不去老是发动战争去侵略别人，“国虽大，好战必亡。”“我不敢进寸而退尺”，打不过的时候，对手力量太强大的时候，就要懂得以退为进，这个叫什么呢？这个就叫“行无行，攘无臂，扔无敌，执无兵”，这十二个字怎么理解？我先换一个角度给大家来认知这个问题。抗日战争胜利之后，有很多日本人就对这场战争表示不是很服气，因为他们有的认为，是因为东条英机改变了战略，才导致这场战争在中国的战场上的失利；有的人认为，日本战败是因为美军的加入，所以他们也想专门研究战败的原因。有一位日本学者专程来到了中国，他也是通过一本经典来了解我们中国人在这方面的思想与智慧，这本经典就是毛泽东的《论持久战》。各位知道，一九三七年七月七日卢沟桥事变，抗日战争全面爆发，同年的八月二十二日到二十五日，就在陕北洛川召开了洛川会议。在这次会议上，毛泽东就已经开始讲持久战的思想，一九三八年的时候这本书就面世，这不是战后的马后炮，是战前的预测。他把整个战争的进程就概括为六个字，而历史就是沿着这六个字发展：退却，相持，反攻。一开始当然日本侵略者锋芒外露，我们没有办法直接跟他们对抗，因为日本是一个统一的国家，而当时我们的中国四分五裂，军阀混战，政令不统一。日本军队装备精良，又蓄谋已久，所以一开始没有可能把他们赶出去，他们肯定会占领我们很多地方。所以这个时候我们就要懂得退却，以退为进。但是日本的军队又不多，占领我们的地方多了，双方就进入了一种相持的阶段。因为武汉和鄂西会战之后，双方就进入相持阶段，咬牙坚持。我们中国是站在正义的一方，况且我们是一个统一的世界反法西斯战场的一部分，为整个世界反法西斯战场拖住了那么多的日本军队，自然要得到国际舆论的支持、国际力量的援助，最后获得胜利。那么日本为什么会陷在中国的战场上？因为原本按照日本人的想法，中国战场很快就能拿下来，以此为基地，北面是针对苏联，南面是针对南洋的那些国家，很多是英国的殖民地，所以它的主要的目标并不是在中国。可是没想到中国的战场，几乎拖住了它绝大部分的力量，为什么会这样？我们来看一下下面这几句话，“行无行，攘无臂，扔无敌，执无兵”。侵略者进入了另外一个国家，虽然这个国家的人民没有站成军队的样子，“行无行”，但是他们不都是你的敌人吗？“攘无臂”，打击你非得用拳头吗？有各种各样的方式，坚壁清野可不可以？游击战可不可以？全民皆兵，所以叫“扔无敌”。“执无兵”，虽然他们手中没有兵器，但他们用多种多样的方式和侵略者对抗，到处都是敌人。所以为什么说“国虽大，好战必亡”？因为你侵略者是不得人心的，进入到别的国家的军队会遭到别的国家人民的反抗，到处都是你的敌人，“扔无敌，执无兵”。所以对于战争而言，你不要认为一个小的国家就好侵略，“祸莫大于轻敌”，对双方皆是如此。战略上藐视敌人，战术上要重视敌人。“祸莫大于轻敌，轻敌几丧吾宝”，轻敌，就把最宝贵的东西也就是“道”丢掉。所以在战争中要冷静理智，要对对方予以重视，在战略上藐视敌人，但是在战术上要重视敌人，不要轻敌。下面这句话基于上面的这个意思就好理解，“故抗兵相加，哀者胜矣。”就是站在正义一方的抵抗的军队、防御的军队，对抗侵略者，处在相持的阶段，双方相持不下、在那较劲的时候，旁边只要有人帮一下，都会起大的作用。可是大家知道问题的决定性作用并不在旁人，没有形成相持的状态谁帮也没用。所以我们说这句话让我们领悟到一个重要的问题，中国人获得这场抗日战争的胜利，根本的原因在于我们中国人自身，而不在于外面力量的援助。斯大林曾经说过，拉开窗帘天是亮，你不拉开窗帘，天也是亮，反正中国人会获胜，应该帮一下。所以这决定的作用不在外部，而在于我们中国自身。讲得最妙的是最后一句话，最后谁获胜呢？“哀者胜矣”，“哀”可不是哀伤的意思。鲁迅先生写的《阿Q正传》中有一句话叫“哀其不幸，怒其不争”，“哀”就是同情。我们中国人从古汉语里面延续了一个习惯，讲话的时候这种使动用法，通俗地说就是被动型用法。比如我们说老头晒太阳，其实是老头被太阳晒。比如大家到陕西来吃的肉夹馍，那是肉夹馍吗？那是肉被馍夹住了。所以这种使动的用法，用这个来理解，这句话就很清楚了，“哀者胜矣”，谁是被同情、被支持的一方，最后获得胜利。“退却，相持，反攻”——惊人的一致。毛泽东从十几岁就开始读《道德经》，我觉得他从这本书里得到的最大的启发就是这种格局上的、战略上的。人站得高了才能看得远，对未来才能有一个正确的这种预测。所以我说第六十九章，大家不要只局限在战争的一个方面，它也可以把我们的智慧得以扩展和延伸，成为一个普遍性的思想与智慧，成为一个普遍性的原则。</t>
   </si>
   <si>
-    <t>第七十章</t>
+    <t>第七十章（70）</t>
   </si>
   <si>
     <t>吾言甚易知，甚易行。天下莫能知，莫能行。言有宗，事有君。夫唯无知，是以不我知。知我者希，则我者贵。是以圣人被（pī）褐（hè）怀玉。</t>
@@ -973,7 +968,7 @@
     <t>从第七十章开始，老子强调的重点又发生了改变，他在强调什么呢？他说，我们看问题要“以道观物”，可是有道的人往往为人所误解。老子在书里经常用“吾”这个字，“吾”是人格化的我。“吾”作为一个有道者的代表，一个人格化的有道者的身份，并不一定是指老子本人。第七十章开始就讲人认知的重要性。“吾言甚易知，甚易行。”得道者讲的话，其实很容易被了解，很容易去实行。“天下莫能知，莫能行。”可是结果是什么？这天下的人都是没办法了解，或者说不去了解，也不去按照这个去做。这是一种沉重而深刻的感慨。我们常说道很玄妙，很难把握，而老子在这一章讲，按照道去行事并不难知，不难行，那为什么“莫能知，莫能行”呢？是因为大家根本不愿意去相信它，也不愿意按照它去做，是因为大家认识不到这个事情的重要的意义，认识不到“道”在我们生活中的重要的作用。老子这段话主要是针对领导者、统治者来讲的，老子在对他们讲了很多次之后，发现“万言不值一杯水，犹如东风射马耳”，那些话语仿佛随风而去，并没改变什么。所以，他有此感慨：“莫能知，莫能行”。“言有宗，事有君。”“宗”就是宗旨，说话你得有宗旨，得有核心。“君”是领导控制，做事情也得掌握这个事情的关键。言外之意就是讲，你看我讲的这些话，它是有核心宗旨的。他告诉大家做事怎么样掌握事物的关键，了解事物的本质，把事情做好。“夫唯无知，是以不我知。”可是正因为这些人无知、不了解、不想知道，所以他对我们得道的这些人也就不了解。“知我者希，则我者贵。”了解我的人太少了，懂我的人太少了。我们现在经常有这种感慨，有没有人懂我？其实我们真的了解一个人的精神世界，尤其是了解这些富有大智慧的人的精神世界，不是一件容易的事情。我们中国人经常说一个词叫“知道”，现在大家再说一下这个词，它的分量就不一样，并不是你听到了就叫“知道”，“知”还得去“行”。所以了解我的人太少了，按照我这个去做的人那就更为珍贵了。“是以圣人被褐怀玉”，“褐”，褐色，粗布衣服的颜色。所以得道的人，就像穿着粗布衣服可是身上却怀着珍宝的人一样。得道者讲了很多道理，可是很多人，因为“以貌取人”就是不信。所以，我们经常要透过现象来认识事物的本质，不要以貌取人，不要认为《道德经》里的语言不是那么华丽，就否定其思想与智慧。《道德经》的很多章节都在讲人贵有自知之明。第三十三章“知人者智”，我们真正能够去了解别人，这是一种非常有智慧的表现，可是比这个了解别人更重要的，是我们要了解自己，“自知者明”。人认识最少，却自认为认识最多的知识就是关于自己的知识。因为我们自我的认知，经常被一些假象所迷惑，被情绪所左右，所以“知人者智，自知者明”。其实，老子不仅是感叹“吾言甚易知，甚易行。天下莫能知，莫能行”，他对当时的领导者这种认知的不足及其原因，是有深刻认识的。一千多年后，王阳明提出“知是行之始，行是知之成”，也是这个话题的延伸。</t>
   </si>
   <si>
-    <t>第七十一章</t>
+    <t>第七十一章（71）</t>
   </si>
   <si>
     <t>知不知，上；不知知，病。夫唯病病，是以不病。圣人不病，以其病病，是以不病。</t>
@@ -985,20 +980,19 @@
     <t>第七十章讲“夫唯无知，是以不我知”，由于我们的认识上出了偏差，出了问题，所以没有办法了解有高超智慧的人、得道的，很多的时候，我们也没有办法真正地去了解自己，那么问题出在什么地方呢？这一章在分析问题的原因。我经常开玩笑说，这一章是我见过的中国历史上最有智慧的一段绕口令，比那些相声演员用来练贯口的绕口令更富有思想与智慧。“知不知，上”，我们知道自己不知道，我们知道自己的认识有局限，我们知道自己有缺点需要弥补，这是最有智慧的。后来庄子在《秋水》篇里面把这个意思给大家演绎得非常清楚，而且富有哲理。秋天发大水的时候，河伯就以为自己这个地方就是天下最大的，“以天下之美为尽在己”。后来流到了大海，见到了北海若，发现自己太渺小了。北海若又说，其实我在天下所占的位置，也就是像一粒米那样……这就叫“知不知”，知道自己不知道，那才能够不断地进步。“不知知，病”，不知道，却把它当作知道，也就是不懂装懂，这就是一个思想上的大病。怎么样来让我们病得以痊愈？“夫唯病病，是以不病”，我们知道自己有很多的东西不知道，我们知道这是我们的缺点，我们向别人学习，取长补短，谦逊努力。知道自己“有病”，却不讳疾忌医，这反而是没有病。大家熟悉的是《论语》里边的一句话：“由，诲汝知之乎？知之为知之，不知为不知，是知也。”知道就是知道，不知道就是不知道，坦率承认，不要不懂装懂，这个达到的结果“是知也”。这不是一样的意思吗？“夫唯病病，是以不病。”所以对一个有智慧的人，特别是对于领导者、统治者来讲，周边的人都在说好话，阿谀奉承，这样就经常让自己飘飘然，如果这个时候还能保持清醒的头脑，那就是一个有智慧的好的领导者和统治者。他在这个认知上的表现是什么呢？“圣人不病”，一个有智慧的人在这个方面没有病，没有缺点。为什么说它没有缺点？“以其病病”，因为他知道自己的问题在什么地方，知道哪个地方是自己所不擅长的。就像刘邦一样，虽然不能说刘邦为一位圣人，但是他讲的这段话却可以给很多领导者、统治者以启发：“夫运筹策帷帐之中，决胜于千里之外，吾不如子房。镇国家，抚百姓，给馈饷，不绝粮道，吾不如萧何。连百万之军，战必胜，攻必取，吾不如韩信。此三者，皆人杰也，吾能用之，此吾所以取天下也。”刘邦知道自己的短处，借人之力得以弥补，因为有这种清醒的认识，反而成了一个长项。有人总认为自己什么都可以，哪个地方都是自己水平最高，比如说诸葛亮从来也不听别人的意见，打仗的时候都自己谋划，要不就弄个锦囊远程指挥，像这样的人，很难成为一个优秀的领导者。我们经常讲一个人浑身是铁，能打多少钉，要懂得用人之力，懂得借别人的智慧。现在不是有很多的智库、智囊吗？历史上很多杰出的人，比如像曾国藩，手下有多少谋士啊！很多的问题不是他一个人想出来的，得集众人之力，一个优秀的领导者得知道自己弱项、短板在哪儿。对我们个人来讲，一定要知道，其实我们的认知视野都是非常狭窄的，了解了这一点，我们也就不会把自己当作是一个完人，当作什么都知道，不懂装懂。人有什么不懂的，坦率承认没有什么可丢脸的，即便是圣贤，也有自己认知的局限，可是他们的做法和平常人的不同在哪儿呢？“圣人不病，以其病病，是以不病。”知道自己这方面有弱点、有问题，因此不断学习，不断进步，不断成长。这一章虽然很短，但是意蕴深长，道理深刻。这段绕口令大家既可以当作练表达能力、练嘴皮子的体操，也可以当作思想上的体操，一举而双得，何乐而不为？</t>
   </si>
   <si>
-    <t>第七十二章</t>
+    <t>第七十二章（72）</t>
   </si>
   <si>
     <t>民不畏威，则大威至。无狎（xiá）其所居，无厌其所生。夫唯不厌，是以不厌。是以圣人自知，不自见（xiàn）；自爱，不自贵。故去彼取此。</t>
   </si>
   <si>
-    <t>百姓不畏惧统治者的威严，暴君就用更大的恐怖政策施加于百
-姓头上。不要让百姓住的地方越来越狭小，不让他们的生存受到压迫。不去压迫百姓，他们才不会对统治者的行为感到厌烦。所以圣人有自知之明，不自我表现；珍爱自己的生命但不自认为高贵。所以圣君抛弃暴君的做法而不去炫耀、抬高自己。</t>
+    <t>百姓不畏惧统治者的威严，暴君就用更大的恐怖政策施加于百姓头上。不要让百姓住的地方越来越狭小，不让他们的生存受到压迫。不去压迫百姓，他们才不会对统治者的行为感到厌烦。所以圣人有自知之明，不自我表现；珍爱自己的生命但不自认为高贵。所以圣君抛弃暴君的做法而不去炫耀、抬高自己。</t>
   </si>
   <si>
     <t>七十二章到七十五章，这一部分都出现了一个核心的概念——“民”。在中国历史上有“民本”的思想，我们大家熟悉孟子讲的“民为贵，社稷次之，君为轻”，大家觉得讲得好。但是，在孟子之前，《道德经》已经从哲学的层面把民本思想发展到非常高的程度，而且讲得更为具体。这一章最后一句话讲得非常明白，这两条路摆在这儿了，你应该走哪条路？“故去彼取此。”有哪些路可以选择呢？走哪条路是符合道的呢？我们从头来看。“民不畏威，则大威至。”如果一个国家的人民不害怕统治者、领导者的威严，那么对统治者、领导者来讲，大的麻烦就来了。什么大的麻烦呢？“民无信不立”，领导者在民众中丧失了诚信，就没法统治领导他们了，这不是一种大威吗？所以“无狎其所居”，“狎”通“狭”，也是使动用法。领导者，不要让百姓住的地方越来越狭小，最后都流离失所。因为“无恒产者无恒心”，一个国家如果到处都是流民，它能稳定才怪。“无厌其所生”，“厌”通“压”。不要让他们感觉到生存受到了压迫，不要去压迫他们，不要让他们感觉到厌倦生活，因为哪里有压迫，哪里就有反抗。所以这个“厌”，大家可以把它理解为两个意思，一个就是压迫，一个就是导致的结果感觉到生不如死，厌倦自己的生活。“夫唯不厌，是以不厌。”你不去压迫他们，不让他们感觉到生活的局迫、窘迫、生不如死，他们才不会对你的统治行为、领导行为感觉到厌烦。第六十六章说“处上而民不重，处前而民不害”，处上又重，处前而害，他当然会感觉到这种受压迫的厌烦的感觉。那么，真正有智慧的领导者、统治者应该是什么样呢？“自知，不自见”，自己有自知之明，不是有一点功劳，有一点什么就去自我表现。“自爱，不自贵”，很珍爱自己的生命，珍爱自己名声，自爱自重，但是不自以为高贵。第三十九章最重要的两句话，第一句话就是“贵以贱为本”，不要认为自己身份高贵，没有这个国家的人民，也就是很多人眼中的贱民，哪来你高贵的身份？自爱是对的，因为一个人不爱惜自己的生命，也就不会珍惜别人的生命。第十三章讲过，什么样的人才能把天下寄托给他呢？“贵以身为天下”、“爱以身为天下”。所以好的领导者对自己的生命非常珍视，但是为了天下的使命，可以奉献自己的生命，这样的人我们才能把天下寄托给他。“故去彼取此”，取的是什么呢？取的是自知自爱；去的是什么？去的是自见、自贵。</t>
   </si>
   <si>
-    <t>第七十三章</t>
+    <t>第七十三章（73）</t>
   </si>
   <si>
     <t>勇于敢则杀，勇于不敢则活。此两者，或利或害。天之所恶（wù），孰知其故？是以圣人犹难之。天之道，不争而善胜，不言而善应，不召而自来，繟（chǎn）然而善谋。天网恢恢，疏而不失。</t>
@@ -1010,7 +1004,7 @@
     <t>这一章首先谈的话题是“勇敢”。关于“勇敢”，《道德经》并不像我们一般认识那么简单，表达那么直白，它把“勇敢”分为“勇敢”和“勇于不敢”，这个说法的妙处我们后边再做解说。接着读这一章，大家会发现熟悉的语句“天网恢恢，疏而不漏”，其原文就出自第七十三章“天网恢恢，疏而不失”。我们中国人读失去的“失”啊，总觉得有点绕口，换了一个字，意思都是一模一样的。天网恢恢，疏而不漏，天道如此。庄子也讲过这样一段话，一个人做了亏心事之后，在客观世界上把有形的痕迹抹掉容易，可是抹不掉内心的痕迹。即便是不受客观世界的惩罚，也得受良知的惩罚。那么第七十三章的结尾，怎么得出“天网恢恢，失而不漏”的结论呢？是怎么过渡到“天网”、“天道”的呢？“勇于敢则杀”，毛泽东在《贺新郎·读史》这首词里面就讲：“铜铁炉中翻火焰，为问何时猜得？不过几千寒热。人世难逢开口笑，上疆场彼此弯弓月。流遍了，郊原血。”人类的历史都是在这种血与火的洗礼中前进的，老子在他那个时代，肯定也看到过这种情况。“勇于敢则杀”，也包括很多违背了国家法律法令的不法之徒，从直观地来看，也是属于勇敢，“勇于敢则杀”。“勇于不敢则活”，“勇于不敢”直观上看上去，我们把它叫做“懦弱”、“退缩”，但其实这样的“懦弱和退缩”还有另外的一类人，他们懂得保护自己的生命，以期谋得更大的成就与发展。其实，我们说懂得拒绝的人也是一种“勇于不敢”，有些该做的事情，勇敢去做；有些不该做的事情，勇于不敢，拒绝。老子接着说，“此两者，或利或害。”“此两者”指勇敢和勇于不敢。勇敢和勇于不敢这两种情况“或利或害”，就是说有时有利，有时有害，那到底何时有利，何时有害呢？谁能把握这个度呢？“天之所恶，孰知其故？”天呢，到底是喜欢还是厌恶？到底是怎么一回事？谁能够了解这里边的最根本的原因、缘故呢？“是以圣人犹难之”，就是再有智慧的人、有智慧的领导者，在这个方面也难以去理解清楚。所以你看这个认知啊，非常困难，到底是该杀还是该活，到底该怎么对待，这是一个非常难的选择。那老子是不是就放弃了对这个难题的解决呢？不是的，事实上，老子是认为，只有站在更高的视野才能解决这个困扰，也就是第四章说的“解其纷”。所以老子在下边就说，如果从天道的角度来认知这个事情是什么样呢？“天之道，不争而善胜”，不争斗，却能够获得胜利，这是符合天道的。“不言而善应”，要行不言之教，不是老去命令、政令，大家对他反而非常支持，非常响应。言教不如身教，“不召而自来”，大家自然而然就聚拢到你的麾下，这是符合天道的。“繟然而善谋”，“繟”就是坦然、从容。天道看不出来痕迹，从从容容地向那个方向发展，就像一个善于谋划的人一样，不露痕迹地谋划。所以后面就讲“天网恢恢，疏而不失”，天网虽然好像有很多疏漏，但是最后你会发现，这天道如此，天网恢恢，疏而不漏。我们中国人经常把这个讲做“人在做天在看”、“为人别做亏心事，古往今来放过谁。”到这里，逻辑就逐渐清晰了：天道不争，不强制，自然而然，所以为民，不能滥用所谓勇敢；为王，也不能滥用强制，这都是不符合天道的，不符合天道，则是必然要失败的，也就是讲“天网恢恢，疏而不失”。所有违逆天道的所谓“勇敢”最后都会受到惩罚，天网虽然好像有很多疏漏，但是最后你会发现，这天道如此，天网恢恢，疏而不漏。关于这一点，我们再引证下孔子这句话：“人之生也直，罔之生也幸而免”，就更清楚了。意思就是那些不正直的勇于敢者、对抗天道天理的人，也许会侥幸漏掉一时，但终究逃不脱天道天理的惩罚。孔子的真正意义在于，若靠侥幸活着，你是活不好的。而老子对于敢对抗天道天理的人、与天争胜的人，警告更为严厉：“天网恢恢，疏而不漏。”换句话说就是“人在做天在看”、“为人别做亏心事，古往今来放过谁。</t>
   </si>
   <si>
-    <t>第七十四章</t>
+    <t>第七十四章（74）</t>
   </si>
   <si>
     <t>民不畏死，奈何以死惧之？若使民常畏死，而为奇者吾得执而杀之，孰敢？常有司杀者杀，夫代司杀者杀，是谓代大匠斫。夫代大匠斫（zhuó）者，希有不伤其手矣。</t>
@@ -1022,7 +1016,7 @@
     <t>七十四章开头这句话，在讲什么呢？“民不畏死，奈何以死惧之？”假如这国家的人民都不怕死了，都感觉到生无可恋了，你还能有什么方法去管理他们呢？上一章不是说过吗，“狎其所居，厌其所生”，百姓感觉到压力太大，感觉到生不如死，那就会产生“民不畏死”的情况。这个时候，你拿死去吓唬他还有什么用呢？毛泽东在《别了，司徒雷登》中引用过这一句，并引申说，“中国人死都不怕，还怕困难吗？”接着老先生做了一个假设，“若使民常畏死”，假如这个国家的人民经常地、普遍性地害怕死，老百姓对生活抱有憧憬和希望，这个时候，如果有搞幺蛾子的人，铤而走险犯法的人，“而为奇者吾得执而杀之”，做领导的、做统治者的，把这些人逮过来杀掉了。“孰敢”，没有人会响应这些人，大家不都不吭声了，国家也就恢复了平和、安定。大家注意，这话里暗含着一种假设，事实是什么呢？老百姓生活没有希望，不畏惧死亡。这时候，你杀的人越多，反抗的人越多；镇压得越多，起来呼应的人更多。所以，老子说你管理靠镇压是不行的，这不是根本的方法。历史上还有比秦朝法令更严苛、更严酷的时代吗？满大街都是被砍断手脚的人，严刑重罚，稍有违犯，立马严惩。最终，大家不还是起来造反了吗？秦朝之前，老先生就已经提醒过，靠残酷的镇压是不管用的，这不是处理问题的根本方法。下面上升到了更高层面，“常有司杀者杀”，大家知道，我们讲“秋后问斩”。秋天是代表肃杀的，杀人的时候是在秋天，这个代表符合天道、天杀。《道德经》的这句话是说，人的生死是由天来司管的。再退一步讲，国家也是按照国家的法令、按照符合道的方式制定的法律，来约束人的。当然这句话就《道德经》的本身而言，是在讲天操管着人的生杀予夺大权，人没有这个权力去决定别人生死的，即便是有的话，也应该有专门的部门来管。“夫代司杀者杀”，代天来杀人，这叫什么？“代大匠斫”，我们知道木匠的锛凿斧锯别人是不能动的，太锋利了，只能他们自己使用。你不熟悉这一行，你不懂怎么使用，你代替他们，“希有不伤其手矣”，哪会有不伤到自己的？老先生拿这个来做类比：你应该不用这些东西，不善于用这些东西，你越俎代庖，那么你自己肯定也会受伤的。因此，只用杀戮、镇压的方式，是不符合天道的，对自己的统治、领导也有着重大的损伤。这段话其实对统治者提出的警告：靠镇压的政策、残杀的政策，也会影响威胁到自己的统治，不要相信武力能解决一切问题。三十五章讲“执大象，天下往。往而不害，安平太。”应该用符合“道”的方式来管理国家，以民为本，注重根基，这样才能够和谐相处，才能够“安”、“平”、“太”。</t>
   </si>
   <si>
-    <t>第七十五章</t>
+    <t>第七十五章（75）</t>
   </si>
   <si>
     <t>民之饥，以其上食税之多，是以饥。民之难治，以其上之有为，是以难治。民之轻死，以其求生之厚，是以轻死。夫唯无以生为者，是贤于贵生。</t>
@@ -1034,7 +1028,7 @@
     <t>这一章的核心话题还是“民”，解释了三个问题。第一，百姓为什么饥寒交迫；第二，百姓为什么难以治理；第三百姓为什么不怕死。解释完三个内容，然后对领导者、统治者提出要求。“民之饥，以其上食税之多”，百姓为什么饥寒交迫？“上”，上面的领导者、统治者，“食税”，收的税太多了，而且收的税都被这些人挥霍。“民之难治，以其上之有为”，百姓为什么难以治理呢？原因不在他们这儿，是因为上边胡来、瞎折腾。在《道德经》里，“有为”这个词就是妄为，胡折腾，上边老瞎折腾，就把民心折腾乱了。“信不足焉，有不信焉”，折腾得多了，讲的话也不诚信了，也失去百姓的信任，说什么都没用了。“是以难治”，“是”，“这是”的意思。这话讲得就比较理性，你老说他们是刁民，老在他们身上找，其实这原因就在自己的“有为”。老子对坐在对面的那些领导者、统治者就讲，你得找到真正的原因，百姓为什么饥寒交迫？你们收税收得太多了，收的税都被挥霍了。百姓为什么难以治理？你们整天瞎折腾，胡来妄为，把民心搞乱了。“民之轻死，以其求生之厚”。“其”指谁？领导者、统治者。百姓为什么轻死，把死不当一回事？是因为你们这些统治者，把自己的生命看得那么重要，不惜用剥夺的方式积累财富，花天酒地，穷奢极欲，这财富都聚积在他们自己手里，老百姓难以生存。就像国民党时期，财富都积累在“四大家族”手中，很少的人占有了绝大部分的财富，底下的人都生活在水深火热之中。当你“求生之厚”的时候，底下的百姓就觉得没什么活路和希望了，也就不把死当一回事，“是以轻死”。那么应该怎么做呢？“夫唯无以生为者”，不要把自己的生命看作是绝对重要的。不要把财富、好吃的好用的，全都集中在自己这儿来，认为只有自己的生命才是生命，对别人的生命、生存视而不见，感到无足轻重。不把聚敛、穷奢极欲当作生命的重要的部分，这个就是“贤于贵生”。百姓为什么饥寒交迫？上食税之多；为什么难以治理？上面胡来妄为；为什么不怕死？求生之厚。这章三个并列句，像诗一样的语言，讲得又非常深刻、非常理性。把七十五章和七十四章结合起来理解，我们就能发现，老先生苦口婆心地劝坐在对面的那些领导者、统治者：你们要对自己国家的人民好一点，否则啊，他们日子过不好，你们的日子也不安稳，你们只靠这种高压的政策，这不是解决问题的根本的方法。我们完全可以说在这几章里看到了《道德经》的“真实面目”，很多话是针对那些统治者讲的，苦口婆心地劝他们，应该怎么样对待这个国家的人民，才能使国家长久地、持续地发展。</t>
   </si>
   <si>
-    <t>第七十六章</t>
+    <t>第七十六章（76）</t>
   </si>
   <si>
     <t>人之生也柔弱，其死也坚强。万物草木之生也柔脆，其死也枯槁（gǎo）。故坚强者死之徒，柔弱者生之徒。是以兵强则不胜，木强则折（shé）。强大处下，柔弱处上。</t>
@@ -1046,7 +1040,7 @@
     <t>现在我们来说一下第七十六章，王弼本子的编辑是有着内在逻辑的。前两章，老先生劝统治者，不要用这种“强”的方式、镇压的方式来实施自己的统治，那么应该怎么做呢？要懂得以柔克刚、强大处下，这样才能形成一种和谐。有的人确实是没有认真地读这本书的原文，他们认为《道德经》是一个弱者斗争的哲学，这是不了解坐在老子对面的向他提问的那些人，他们并不是一般的平民，而是手握权力的领导者、统治者。要站在这个层面来理解第七十六章，知道他这些话是对是对那些认为自己自身或者自己国家很强大的统治者们讲的。老子劝他们用“柔弱”的方式来实施自己的统治，这个是非常有智慧的，这个非常能够体现老先生的慈悲仁爱之心。这一章强调两个字“柔弱”，所以一开始讲“人之生也柔弱”，最后强调“强大处下，柔弱处上”。“人之生也柔弱，其死也坚强。”人活着的时候是什么状态？柔韧性非常好。我们看跳舞的、练杂技的，就觉得这柔韧性好。柔弱柔软，这是生命昂扬、鲜活的状态。而人死的时候是什么样的一种情况呢？硬了、僵了，“其死也坚强”。老子首先拿人的生命的状态来说明柔弱具有的意义。如果这个问题大家觉得还没有理解到位，再换一个角度来理解。在苏州金鸡湖苏州新区里曾经出现过一尊老子的雕像，这尊雕像太丑陋了，老子张着嘴，吐着舌头，一颗门牙。很多人很不理解，心里想有大智慧的老子，怎么会是这样的形象，还有人打趣说，这个老子是来卖萌的……这个雕塑者姓田，他就站出来解释说，我这个雕塑叫“刚柔”，它的出处是说，当时孔子见老子的时候，老子没有给他多说什么，张开嘴巴让孔子看了看。孔子一看就明白了，老子当时已经都七十多岁了，牙早掉光了，但是舌头还在，讲的就是“柔弱更长久”的意思。雕塑者说“刚柔”倒没错，但是这段话不是出自正史，记载的也不是指孔子和老子之间的事，其实是当年老子毕业的时候，跟自己的老师讲的。您有什么送给我？老师也没说话，张开嘴巴给他看了看，老子就看明白了，老师年纪大了，牙掉光了，但舌头还在。牙齿是坚硬之物，到一定年龄就掉了，舌头没事，柔软更长久。所以，柔弱更有生命力、更长久，柔弱是生命的状态，而强硬、僵硬是死亡的状态。这是第一个，拿人来做比方。第二个以草木为例，“其生也柔脆，其死也枯槁。”我们以草为例，李世民在诗里说“疾风知劲草”。草，风往这边吹了，它这边倒，往那边吹了，往那边倒，风走了，它再站起来坚守脚下这片土地。什么时候草坚定了，不随风倒了，那草就死了、枯了。正因为草很柔弱，所以它能迎风起舞；正因为草很柔弱，所以“天涯何处无芳草”。下面得出结论，“坚强者死之徒”，“徒”就是那一类。认为自己坚强、强硬、强暴，其实这是属于走向死亡一类的。而“柔弱者生之徒”，柔软、柔韧，这是富有生命力的表现。沿着这个方向再往下推，就说到了人类社会，“兵强则不胜”，一个国家穷兵黩武，认为自己的军事力量强大，稍一不如意就动用军队发起战争，“国虽大，好战必亡。”“兵强则不胜”，不是说你这场战役打不胜，但穷兵黩武的最后结果一定是失败的。历史上多少强大的帝国，比如说秦朝，被称为“虎狼之师”，最后的结果怎么样？“兵强则不胜”“木强则折”，这个“强”就是僵硬。春天，万物复苏，一根细小的柳枝也很有韧性，很难去折断它。秋天，柳枝水分干枯，好像很强硬地挺在那里，可是它内在枯槁了，一折就断。小的时候，我在石厂里边劳动，砸石子做铺路之用。那时候我就见了一个非常奇怪的现象，石场里石匠用的榔头把儿，一种是很粗大的木棒，看着很稳定；一种是很细的木棒，看起来很危险。我去问那个石匠，怎么用这么细的斧柄？他说这个东西叫“水曲柳”，你别看它细，但它韧性非常好，你用多大劲儿也没事儿。所以每当读到这个地方，我就想起这个事情。“木强则折”，看似强大僵硬，其实没有了韧性，它就没有了生命力，一碰就断掉了。讲完这个了，再看这里边两层的推论。第一层推论：“坚强者死之徒，柔弱者生之徒”，然后推到人类社会，表达他对用这种强横的方式予以统治、用这种强横的方式予以领导的不认同，指出这个方式的致命的弱点。战争中也是如此，“兵强则不胜”，就像“木强则折”一样。讲完这个，推论到第二层：“强大处下”，老是炫耀自己强大，去任意地凌辱别的小的国家；自己有了高的位置，可以盛气颐指，不符合道，这是向死亡方向去发展。“强大处下，柔弱处上。”懂得以柔克刚，懂得以退为进，懂得谦逊谦让，这才是符合道的，才是真正有智慧的表现。第六十一章，“天下之牝，牝常以静胜牡”，讲以静制动、以柔克刚的道理。所以对人生来讲，强大、用强，这事儿大家都知道，也并不是说老子对这个东西一味排斥，因为人生有的时候强也是需要的，但是大家都把这个事情推到极端了，认为“强”是解决问题唯一的方式，所以，老先生在面对那些领导者、统治者的时候，苦口婆心，形象具体地讲述柔弱处下的道理。我们现在读这一章，也可以把智慧扩大到我们的为人处事，不要只认为用强才能解决问题，要懂得强弱两者的相辅相成，老去逞强，不是真正智慧的做法，这是只是智慧的一个方面，而“以柔克刚”才是一种真正高级的智慧。适当的时候，我们要懂得示弱，这是我们在和社会、和别人打交道的时候，非常重要的智慧，有重要的启迪。</t>
   </si>
   <si>
-    <t>第七十七章</t>
+    <t>第七十七章（77）</t>
   </si>
   <si>
     <t>天之道，其犹张弓与？高者抑之，下者举之；有余者损之，不足者补之。天之道，损有余而补不足。人之道则不然，损不足以奉有余。孰能有余以奉天下？唯有道者。是以圣人为而不恃（shì），功成而不处，其不欲见（xiàn）贤。</t>
@@ -1058,7 +1052,7 @@
     <t>第七十七章，这一章重要在什么地方呢？大家都知道“马太效应”，马太效应出自《圣经·马太福音》，直观的解释是穷者越穷，富者越富，越穷越倒霉，越富反而财富滚滚而来，这也是我们人类社会大家都认同的一个普遍的现象。怎么解决这个问题呢？怎么样解决这样的一种贫富的两极分化呢？《道德经》很早就给出了一个方案，所以我们把这一章叫什么呢？叫“张弓效应”。在这一章里边我们可以看到一句话，这句话和马太效应讲的意思是一样的，叫“损不足以奉有余”。“天之道，其犹张弓与？”老子在这一章里面就讲，说天道就像拉弓射箭一样，拉弓射箭要有的放矢。这个箭，你瞄得高了，往下压一下；低了，往起抬一下，“高者抑之，下者举之”。沿着这样的一个比喻，自然就得出这个结论，对于人类社会也是这样，“有余者损之，不足者补之”。财富多的人应该拿出更多帮助这些不足的人，收入高的人当然应该多交税。这就是“天道”，天道如此，天道均衡，“天之道，损有余而补不足”。可是人道，这个社会是怎么做的呢？“人之道则不然”，老子对他当时的情况看得很清楚，财富都掌握在少数人的手里，“损不足以奉有余”，越是不足的、穷的，反而被压榨得越厉害，富的反而越来越富。于是，老子面对那些统治者讲，一个好的领导者、统治者应该向“圣人”的方面去发展，做一个好王。大家注意古代那个“圣”的写法，王上边并列两个字，耳和口，听得进别人的意见，说话温暖。通达事理的王，称之为圣。老子就对他们讲，你们应该向这个方面努力，怎么做呢？“有余以奉天下”，让那些更富的人来为这个天下做贡献。“唯有道者”，就是了解道的人，按照道的方式去行事的人，才能做到这一点。说到这儿，我就得给大家说一下我们的文化背景。一句话大家都熟，叫“不患寡而患不均”，贫富不均，很容易产生问题。历史上那些农民起义，他们用的口号，你也能感觉到这一点，比如说王小波、李顺，“均贫富等贵贱”；比如说黄巢，“冲天平均大将军”……从社会心理能分析到这一点。所以老先生就讲，统治者、领导者，什么样的人才能够真正注意到、做到让贫穷的得以扶持，让富有的贡献更多呢？“唯有道者”，“是以圣人”。“是以圣人为而不恃，功成而不处，其不欲见贤。”一个好的领导者，“为而不恃”，他把这件事情做了，有作为了，却不把这个当作一种倚仗、凭借甚至勒索的手段。“功成而不处”，不居功自傲，“不欲见贤”，不想表现出自己的这种贤能贤明。这是有道者的表现，懂得让天下向共同富裕的方面发展，让那些先富起来的人懂得奉养天下，哪怕是把这些做成了，也不居功自傲，因为他们知道，这只是按照道的方式来做的。</t>
   </si>
   <si>
-    <t>第七十八章</t>
+    <t>第七十八章（78）</t>
   </si>
   <si>
     <t>天下莫柔弱于水，而攻坚强者莫之能胜，其无以易之。弱之胜强，柔之胜刚，天下莫不知，莫能行。是以圣人云：受国之垢（gòu），是谓社稷（jì）主；受国不祥，是为天下王。正言若反。</t>
@@ -1070,7 +1064,7 @@
     <t>第七十八章体现了这本书里的一个非常重要的理念，“善于处下”。这些内容我们之前都有过接触，甚至直接引用七十八章做过讲解，所以这一章我们并不需要花费太多的时间来解释，大家也能够明了。“天下莫柔弱于水，而攻坚强者莫之能胜”，天下没有什么东西比水更柔弱了，你拿什么容器装，它就是什么样，随方就圆。但天下也没有什么东西比水的力量更强大了，攻无不克，战无不胜。水就是以柔克刚、以弱胜强的最好的形象的代表。“以其无以易之”，因为没有什么东西能够替代水，天下最柔弱的东西，它力量又最为强大，最能够体现柔弱胜刚强的道理。“弱之胜强，柔之胜刚，天下莫不知，莫能行。”天下都知道，这东西表面上看似柔弱，但发挥作用的时候力量太强大了，但是真的要这样却非常不容易，为什么？人都有脾气，“柔弱胜刚强”得懂得忍耐、等待，忍耐是我们人最难练的一种功夫。水滴锲而不舍方能穿石，一条溪流不舍昼夜，慢慢积累，等待时机，才能发挥大用。“柔弱胜刚强”也是需要条件的，只是老子没有明说。“是以圣人云”，我再给大家强调一下，在老子心里，以前有很多好的统治者、有智慧的领导者，他称其为“圣人”，让大家向他们学习。我们在前面谈到过，他的很多话并不是原创的，是他引用的以前的圣人的，下边这话就表达得非常明确，所以这些圣人讲，“受国之垢”“受国不祥”。这两句话就是《道德经》里边从头至尾强调的，就是我们经常讲的善于处下。古往今来，夺得天下的表面看是一家一姓，实际上不都是一个团队吗？用我们现在的话讲是一个党派。什么样的团队，什么样的党派才能夺得天下，并且坐得了江山呢？之前，我们在第八章讲“处众人之所恶”时，也拿这个地方作为印证。吃苦在前，享受在后，有困难还得担着，有错误勇于改正，这不就是“受国之垢”“受国不祥”吗？所以真正想要夺得天下，坐稳江山，也就是所谓“处其上”，首先要懂得“处其下”，要“受国之垢”，要能忍受别人忍受不了的艰难困苦，要能承受别人承受不了的屈辱诟骂，这样才能成为江山社稷的主人。“受国不祥，是为天下王。”有灾难有困难，你别跑，要挺身而出，勇于担当，有错误要勇于承认，勇于改正。毛泽东把共产党的宗旨概括为五个字，叫“为人民服务”。两千多年前的“受国之垢”，“受国不祥”，“处众人之所恶”，两千多年后的“为人民服务”，这本质上的意思不是一样的吗？这就是《道德经》里面从头强调的，也是古往今来的大道。我们在讲第十四章的时候说过一句话，“执古之道以御今之有”。了解古往今来的大道，我们才能更好地做好今天的事情。读到这儿大家就会发现，这《道德经》里边蕴含着古往今来的大道，蕴含着一个人、一个团队、一个党派成功的最深的密码，值得大家认真地品味。总结上面这个表达的方式叫什么呢？叫“正言若反”，也就是第四十章讲的“反者，道之动”。看着是讲反话，大家都不愿意去做的事情：“受国之垢”，“受国之不祥”，“处众人之所恶”，可实际上，这才是能够让我们“处上”、取得成功的真正的智慧与奥妙。看似好像说的反话，其实深刻的道理就在这里边。</t>
   </si>
   <si>
-    <t>第七十九章</t>
+    <t>第七十九章（79）</t>
   </si>
   <si>
     <t>和大怨，必有余怨，安可以为善？是以圣人执左契（qì），而不责于人。有德司契，无德司彻。天道无亲，常与善人。</t>
@@ -1082,7 +1076,7 @@
     <t>针对坐在对面的那些统治者、领导者，老子前面一直在讲，不要用高压的方式，要懂得用柔和的方式。如果一直用高压的方式，一直用“损不足以奉有余”的方式，这社会就积累了大的矛盾。老先生认为，有了这个矛盾之后，不管用什么方式解决，它都会遗留下很多的不满、埋怨、祸端。在这个基础上，我们才能够深入理解第七十九章的内容。这一章只有这么几句话，但道理非常丰富而深刻。“和大怨，必有余怨，安可以为善？”如果社会已经积累了大量的矛盾，即使用调和的方式，“和大怨”，可是，依旧会留下很多的这个埋怨、祸端。“安可以为善”？即使用和谐的方式，也不是一种善举，为什么呢？第六十四章讲“为之于未有，治之于未乱”，从一开始你就不应该让这社会积累了这么多的矛盾。我们之前举过晏子“救灾”的例子，其实针对我们目前的环境问题，也是一样。大家知道有一句话叫“反对先污染后治理”，你污染完了，你再治理，其难度之大，难以预料。“病来如山倒，病去如抽丝”，社会不也一样吗？积累了这么多复杂的矛盾，你老用调和的方式，你说现在已经柔和了、缓和了，但留下那么多的祸端，这当然不算是好的方法，不可以叫做善举。对应我们人际交往也是一样，我们不要本着“无所谓”的态度，想着跟别人、朋友之间有了裂痕，我们说以后自会解决的，事情往往没有我们想得那么简单。所以，平时做事就要小心，朋友之间要珍惜，家庭之间感情要珍惜，别真的等得了埋怨之后，再想办法去解决。这跟钉子钉在墙上一样，你拔出了钉子，那个眼还在。最好的“善”是什么？提前做出预防，“为之于未有，治之于未乱。”“是以圣人执左契，而不责于人。”有智慧的领导者、统治者，就像拿着契约的人。“左契”，契约，一撕两半，左边一个，右边一个，左边那个是借据。拿着这个契约借据而不责于人，不是天天去追着要，而是表达出圣人的一种宽容。老先生拿这个举例子，意思说，一个好的领导者，哪怕是你对大家都有恩德，对天下都有恩德，你别以为大家都欠你的，“不责于人”。所以“有德司契，无德司彻”，有德的人就像执左契而不责于人的人。“彻”，就是税官，收税的。这是代表着两种态度，一种是和缓的态度，另一种是苛刻的残酷的态度。所以平日里，应该像“有德司契”的样子，那就不会积累那么多的埋怨。反之如果像那个税官一样，苛捐杂税多，还步步紧逼，不肯放松，老子认为这是无德的表现，这样会留下大怨！下面两句话很容易引起误解，“天道无亲，常与善人。”在第五章曾经讲过，“天地不仁，以万物为刍狗”，天地是没有感情的，它并不因为你做了好事，就来奖赏你，也不因为你做了坏事，便来惩罚你。既然“天道无亲”，那为什么“常与善人”呢？又怎么把这个规律规则让那些善人能够理解，并按照它去做呢？这个事情我换一个角度让大家来理解，美国有一个报社的主编，他经常接到读者的来信，读者来信都反映一个什么问题呢？做好事不得好报。特别是其中有一个小孩就说，我弟弟什么都不干，我天天在家里干活那么勤奋，可是我妈妈就把好的东西都给我弟弟，就是喜欢他，这不是不公平吗？上帝在哪里？上帝怎么能够这么不公平？这个主编呢，一直不知道怎么解释这个问题。后来有一次，他参加了一个婚礼，新郎新娘互戴戒指，出现问题了，两人把戒指戴错手了，本来应该戴到左手，但都戴到了右手上。主持婚礼的牧师就用一种诙谐的方式说，右手已经够完美了，不用再修饰了，还是用戒指来装扮左手吧。这个主编就在那个时候领悟到一个道理：一个已经够好的人，你不用去奖励他，他已经够完美，最大的奖励是什么？就是他已经成为一个好人。天道对好人最大的奖赏是什么？放到西方的文化里边来讲，上帝对好人最大的奖赏是什么？就是让你成为一个好人，这已经就是最大的回报了。这里讲“天道无亲”，它是说天道是公平的，没有偏私的。让一个人成为一个好人，那么一个好人吃点亏，这是正常的，因为你作为一个好人，这已经就是最大“道”给你的回报了。天道是公平的，没有亲疏之分，但是，它把规律、规则赋予了那些做善事的人。做一个好人，我们免去了很多的祸端祸殃，成为一个好人——这就是对我们做好人的最大的回报，不需要其他的东西来“修饰”了。所以用“有德司契”的境界去管理、去治国，就不会有大怨；用“有德司契”的境界去为人、去处事，会让你成为一个“好人”，“福虽未至，祸已远离”。</t>
   </si>
   <si>
-    <t>第八十章</t>
+    <t>第八十章（80）</t>
   </si>
   <si>
     <t>小国寡民，使有什伯之器而不用，使民重死而不远徙。虽有舟舆（yú），无所乘之；虽有甲兵，无所陈之；使人复结绳而用之。甘其食，美其服，安其居，乐其俗。邻国相望，鸡犬之声相闻，民至老死，不相往来。</t>
@@ -1094,7 +1088,7 @@
     <t>第八十章历来被认为是老子思想中的一个非常重要的部分——老子的理想国。大家一听都知道，在哲学上，柏拉图有《理想国》，后来就出现了康帕内拉的《太阳城》、莫尔的《乌托邦》，就是对理想社会的设定。哲学家设定理想社会都有一个非常有趣的现象：要了解人类的未来啊，先看人类的开始。因为哲学里边讲否定之否定的规律，就讲事物到最后都回归到出发点，严格地讲叫“仿佛回到出发点的运动”，是在更高的层次上重复第一阶段的某些特征，所以我们看看人类的开始。人类开始的时候，大家是平等的，所以未来人类社会的也是平等的。你看三个阶段：平等——不平等——平等。沿着这样一种哲学思路，我们来理解老子这个小国寡民，也就知道，这也是他的一种空想，但是，这种空想代表了他理想的寄托。他理想的这个国家是什么样子？别天天老打仗，别弄那么多人，大家不要经常地过多地交往，过多交往就会产生的矛盾、冲突、隔阂、战争，他想让大家和平地和谐相处，所以要把这个国家变成一个“村”。“小国寡民”，让这个国家变小，人民变少，大家就像在一个乡村里边生活。在小国寡民的理念下，他就要限定，要这样做，即使有各种器皿也不用，为什么不用呢？因为在中国的历史上有一个说法，其实和西方后来的一些思想也遥相呼应。西方有一个哲学家叫卢梭，法国的启蒙思想家，当年给法国的自然科学院写过一篇论文，获了奖，叫《科学和技术的进步使人类道德堕落》，在中国历史上也有很多人认可这种看法。庄子文章里就讲了一件关于“抱瓮老人”的事：说一次孔子带着学生去游学，子贡就看见一个老头，有这个先进的工具不用，抱着瓦罐去井里打水。当时的先进的工具是什么呢？就是辘轳，现在大家都看不见了。自己跑到井里边抱着瓦罐去打水，子贡就觉得很奇怪：这老先生怎么这么笨，辘轳就在旁边，摇一摇不就上来了吗？你自己下去干嘛呢？老先生就郑重其事地跟他讲，我的老师讲过，人如果使用机器就会有投机取巧之心，为了保持我的朴素的道德，所以我不用这个机器，不会有投机取巧之心。大家仔细思量，我们使用的工具，确实对我们的思维的方式、性格也有很大的影响，所以《道德经》讲什伯之器，不用，用最简单的工具，保持简单的心灵，保持朴素的品德。当年曾国藩在做官的时候，经常给家里边写信，告诉他儿子，你每天得下地劳动；告诉他女儿，你得给我做鞋。其实，曾国藩在乎的不是地，不是鞋子，他是觉得这样的方式，会让子女形成他要的那种性格、品德。这个东西倒是真值得研究，人类使用的工具在不断进步，千奇百怪，人要想回归到朴素的道德，就很困难。“使民重死而不远徙”，人离开家乡之后成为流民，那么很多方面就无法保证。我们前面也讲过，这国家到处都是流民，它无法稳定，因为“无恒产者无恒心”，所以你离开了自己家乡的土地，成为一个流民，这就没有办法回归到一个小国寡民的所需要的品德和素质。下边一样，“虽有舟舆，无所乘之”，这也是工具，有这个船，有这个车，不要经常去坐。我们现在也有很多人领悟出来了，打趣说，汽车是毒药，自行车是泻药，走路是补药。现在，很多人也确实奇怪，开车节省出时间了，然后回家在跑步机上跑步，这个东西确实是挺难理解，有时间走走路，不也是一种锻炼吗？下边这句话重要了，是这段话里要表达的核心意思，“虽有甲兵，无所陈之”，有军队没地方放。我不打仗，我要军队干嘛？大家注意，咱们中国的“国”字，原来氏族的时候，它是没有边界、国界的。“国”字外面这个方框是代表着城墙，“国”字的繁体字，最常用的是哪个呢？就是里边的“或”。大家仔细琢磨“或”，你看它是什么？用武器，那个“戈”不就是武器吗？用武器来看守一定的人口。这国家一出现，国家一大了，它就需要军队，所以老子为什么要小国寡民呢？不要军队，大家干脆都别打仗。在他的理想国里是没有军队存在的位置的，反对战争，祈求和平。《淮南子》里也讲了这样一件事，大禹的父亲夏鲧治国的时候，修了一座很大的城池，弄了很多的军队，结果四海有反心，诸侯都准备起来背叛。大禹即位后怎么处理的呢？他把城拆了，把军队散了，结果四海归心。其实这故事表达的也是这个意思，《淮南子》主要解读道家思想，举的这个例子也是用来印证《道德经》里讲的这一理念。“使人复结绳而用之”，有的本子叫做“民”，都一样。百姓不再用文字了，人类最早不就结绳记事吗？据说当年文字出现的时候，天雨粟，鬼夜哭。当然我们这个文明延续到今天，受惠于文字太多了，但是《道德经》里说，文字有时候也让人变得复杂，有投机取巧之心。有的人说这老子是倒退，反对文明。其实大家要理解他的苦心，他主要是让人类回归到那种朴素的、平等的、和谐的、互相不冲突的理想国的状态。我们换一个角度给大家一个直观的印象，大家都知道陶渊明的《桃花源记》，那里的人都是什么样？都活得非常的和谐，“甘其食”，吃什么都觉得很香，不挑剔。“美其服”，不是说穿着漂亮的衣服，是穿什么衣服都觉得很好，都觉得很开心。“安其居，乐其俗”，安居乐业，觉得自己那个风俗大家很喜欢，很开心。“邻国相望”，因为现在搞得这国家都跟一个村子一样，国与国之间不打仗了，邻国相望，离得很近，“鸡犬之声相闻”。读《桃花源记》，很多的时候，你能感觉到这一章的影子，“狗吠深巷里，鸡鸣桑树颠”。老子也给我们勾画了一个美丽的，看似平凡但不可企及的生活。当然，“民至老死不相往来”，不是强调不相往来，而是强调没冲突、不打仗。这一章的核心是这句话：“虽有甲兵，无所陈之。”春秋无义战，那时候战争此起彼伏，没一场是正义的战争，尸横遍野，血流成河。在这个背景下，老子就想这解决办法是什么呢？国家小一点，各过各的日子，不打仗。哲学家讲的理想国，不管是柏拉图的《理想国》、康帕内拉的《太阳城》、莫尔的《乌托邦》，还是老子讲的这个小国寡民，还是陶渊明讲的《桃花源记》，都代表着对纷乱社会的不满，都希望人类回归和谐相处的、没有冲突的、没有战争的状态。如果我们理解中国历史上的非常沉痛的两句诗，我们也就明白“小国寡民”的良苦之用心，这两句诗叫“宁做太平犬，不做乱世人”，宁可做太平世界的一条狗，也不做乱世冲突、战争频仍时候的人，因为这时候人活得连狗都不如，没有尊严。所以我常讲，有些经常叫嚣战争的人，其实都是不懂战争。真正懂得战争的残忍，就知道这和平、平静，是多么可贵。大家上中学的时候学过一篇课文，叫《最可爱的人》，里边讲的一段话让人非常有同感。它说也许你正走在去上班的路上，也许你正背着书包走在上学的路上，你觉得这很平常，可是从朝鲜回来的人会告诉你，你是生活在幸福之中。经历过战争的人会告诉你，这种情况是生活在幸福之中。这对我们也有所启示，不能简单地说小国寡民是一个倒退，得看它的现实背景，得了解它的语境，我们才能真正地理解老子的用心，我们对这些历史上有智慧的人、有慈悲心肠的人，对他们才能有深深的敬佩。见到这样有智慧、有品德的人，我们身体不在鞠躬，心灵在鞠躬。读这样的书也是一样，我们应该有敬畏，在敬畏的基础上，认真阅读，认真品味，珍惜和平与幸福的生活。</t>
   </si>
   <si>
-    <t>第八十一章</t>
+    <t>第八十一章（81）</t>
   </si>
   <si>
     <t>信言不美，美言不信；善者不辩，辩者不善；知者不博，博者不知。圣人不积，既以为人，己愈有；既以与人，己愈多。天之道，利而不害；圣人之道，为而不争。</t>
@@ -1110,11 +1104,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -1740,7 +1735,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1750,7 +1745,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2287,1423 +2288,1423 @@
   <dimension ref="A1:E83"/>
   <sheetFormatPr defaultColWidth="23.75" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.7777777777778" style="2" customWidth="1"/>
+    <col min="1" max="1" width="15.287037037037" style="3" customWidth="1"/>
     <col min="2" max="2" width="50" style="2" customWidth="1"/>
     <col min="3" max="3" width="56.8796296296296" style="2" customWidth="1"/>
     <col min="4" max="4" width="75.25" style="2" customWidth="1"/>
     <col min="5" max="5" width="7.37962962962963" style="2" customWidth="1"/>
-    <col min="6" max="16383" width="23.75" style="2" customWidth="1"/>
-    <col min="16384" max="16384" width="23.75" style="2"/>
+    <col min="6" max="16380" width="23.75" style="2" customWidth="1"/>
+    <col min="16381" max="16384" width="23.75" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:5">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="372.6" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="151.8" spans="1:5">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" ht="151.8" spans="1:5">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" ht="151.8" spans="1:5">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" ht="151.8" spans="1:5">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" ht="151.8" spans="1:5">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" ht="124.2" spans="1:5">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" ht="151.8" spans="1:5">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" ht="179.4" spans="1:5">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" ht="138" spans="1:5">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" ht="151.8" spans="1:5">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" ht="138" spans="1:5">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" ht="151.8" spans="1:5">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" ht="151.8" spans="1:5">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" ht="179.4" spans="1:5">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17" ht="207" spans="1:5">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" ht="151.8" spans="1:5">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="19" ht="165.6" spans="1:5">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" ht="138" spans="1:5">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" ht="151.8" spans="1:5">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="22" ht="179.4" spans="1:5">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" ht="165.6" spans="1:5">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="24" ht="165.6" spans="1:5">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="25" ht="151.8" spans="1:5">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="26" ht="151.8" spans="1:5">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="27" ht="165.6" spans="1:5">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" ht="165.6" spans="1:5">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="29" ht="179.4" spans="1:5">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="30" ht="165.6" spans="1:5">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="31" ht="165.6" spans="1:5">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="32" ht="165.6" spans="1:5">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" ht="165.6" spans="1:5">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="34" ht="165.6" spans="1:5">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="35" ht="151.8" spans="1:5">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="36" ht="151.8" spans="1:5">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="37" ht="151.8" spans="1:5">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" ht="165.6" spans="1:5">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="39" ht="138" spans="1:5">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="40" ht="193.2" spans="1:5">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="41" ht="165.6" spans="1:5">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="42" ht="151.8" spans="1:5">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="43" ht="409.5" spans="1:5">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="44" ht="409.5" spans="1:5">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="45" ht="409.5" spans="1:5">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D45" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="46" ht="409.5" spans="1:5">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D46" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="47" ht="409.5" spans="1:5">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="48" ht="409.5" spans="1:5">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="D48" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="49" ht="409.5" spans="1:5">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D49" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="50" ht="409.5" spans="1:5">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="51" ht="409.5" spans="1:5">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="D51" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="52" ht="409.5" spans="1:5">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="D52" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="53" ht="409.5" spans="1:5">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="D53" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E53" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="54" ht="409.5" spans="1:5">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="D54" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="E54" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="55" ht="400.2" spans="1:5">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="D55" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="E55" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="56" ht="409.5" spans="1:5">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D56" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E56" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="57" ht="409.5" spans="1:5">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D57" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="E57" s="4" t="s">
+      <c r="E57" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="58" ht="372.6" spans="1:5">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D58" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="E58" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="59" ht="409.5" spans="1:5">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C59" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="D59" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="E59" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="60" ht="409.5" spans="1:5">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C60" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="D60" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="E60" s="4" t="s">
+      <c r="E60" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="61" ht="409.5" spans="1:5">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="C61" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="D61" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="E61" s="4" t="s">
+      <c r="E61" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="62" ht="409.5" spans="1:5">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="D62" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="E62" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="63" ht="409.5" spans="1:5">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C63" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="D63" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="E63" s="4" t="s">
+      <c r="E63" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="64" ht="409.5" spans="1:5">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B64" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C64" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D64" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="E64" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="65" ht="409.5" spans="1:5">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B65" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="C65" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="D65" s="5" t="s">
+      <c r="D65" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="E65" s="4" t="s">
+      <c r="E65" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="66" ht="409.5" spans="1:5">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B66" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="C66" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="D66" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="E66" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="67" ht="345" spans="1:5">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B67" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C67" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="D67" s="5" t="s">
+      <c r="D67" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="E67" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="68" ht="409.5" spans="1:5">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B68" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="C68" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="D68" s="5" t="s">
+      <c r="D68" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="E68" s="4" t="s">
+      <c r="E68" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="69" ht="409.5" spans="1:5">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B69" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="C69" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="D69" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="E69" s="4" t="s">
+      <c r="E69" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="70" ht="409.5" spans="1:5">
-      <c r="A70" s="4" t="s">
+      <c r="A70" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B70" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="C70" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="D70" s="5" t="s">
+      <c r="D70" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="E70" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="71" ht="409.5" spans="1:5">
-      <c r="A71" s="4" t="s">
+      <c r="A71" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B71" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C71" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="D71" s="5" t="s">
+      <c r="D71" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="E71" s="4" t="s">
+      <c r="E71" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="72" ht="409.5" spans="1:5">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B72" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="C72" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="D72" s="5" t="s">
+      <c r="D72" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="E72" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="73" ht="409.5" spans="1:5">
-      <c r="A73" s="4" t="s">
+      <c r="A73" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B73" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="C73" s="5" t="s">
+      <c r="C73" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="D73" s="5" t="s">
+      <c r="D73" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="E73" s="4" t="s">
+      <c r="E73" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="74" ht="358.8" spans="1:5">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="D74" s="5" t="s">
+      <c r="D74" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="E74" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="75" ht="409.5" spans="1:5">
-      <c r="A75" s="4" t="s">
+      <c r="A75" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B75" s="5" t="s">
+      <c r="B75" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="C75" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="D75" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="E75" s="4" t="s">
+      <c r="E75" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="76" ht="400.2" spans="1:5">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="D76" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="E76" s="4" t="s">
+      <c r="E76" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="77" ht="386.4" spans="1:5">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="B77" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="C77" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="D77" s="5" t="s">
+      <c r="D77" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="E77" s="4" t="s">
+      <c r="E77" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="78" ht="409.5" spans="1:5">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="B78" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="C78" s="5" t="s">
+      <c r="C78" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="D78" s="5" t="s">
+      <c r="D78" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="E78" s="4" t="s">
+      <c r="E78" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="79" ht="400.2" spans="1:5">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B79" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="C79" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="D79" s="5" t="s">
+      <c r="D79" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="E79" s="4" t="s">
+      <c r="E79" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="80" ht="409.5" spans="1:5">
-      <c r="A80" s="4" t="s">
+      <c r="A80" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="B80" s="5" t="s">
+      <c r="B80" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="C80" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="D80" s="5" t="s">
+      <c r="D80" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="E80" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="81" ht="409.5" spans="1:5">
-      <c r="A81" s="4" t="s">
+      <c r="A81" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="B81" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="C81" s="5" t="s">
+      <c r="C81" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="D81" s="5" t="s">
+      <c r="D81" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="E81" s="4" t="s">
+      <c r="E81" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="82" ht="409.5" spans="1:5">
-      <c r="A82" s="4" t="s">
+      <c r="A82" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="B82" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="C82" s="5" t="s">
+      <c r="C82" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="D82" s="5" t="s">
+      <c r="D82" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="E82" s="4" t="s">
+      <c r="E82" s="6" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="83" ht="409.5" spans="1:5">
-      <c r="A83" s="4" t="s">
+      <c r="A83" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="B83" s="5" t="s">
+      <c r="B83" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="C83" s="5" t="s">
+      <c r="C83" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="D83" s="5" t="s">
+      <c r="D83" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="E83" s="4" t="s">
+      <c r="E83" s="6" t="s">
         <v>163</v>
       </c>
     </row>

--- a/book.xlsx
+++ b/book.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="338">
   <si>
     <t>chapter</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t>type</t>
+  </si>
+  <si>
+    <t>linkchapter</t>
   </si>
   <si>
     <t>序章</t>
@@ -90,6 +93,9 @@
   </si>
   <si>
     <t>道经</t>
+  </si>
+  <si>
+    <t>第二章、第三章、第四章</t>
   </si>
   <si>
     <t>第二章（2）</t>
@@ -2285,8 +2291,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E83"/>
-  <sheetFormatPr defaultColWidth="23.75" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <dimension ref="A1:F83"/>
+  <sheetFormatPr defaultColWidth="23.75" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.287037037037" style="3" customWidth="1"/>
     <col min="2" max="2" width="50" style="2" customWidth="1"/>
@@ -2297,7 +2303,7 @@
     <col min="16381" max="16384" width="23.75" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:5">
+    <row r="1" s="1" customFormat="1" spans="1:6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2313,1399 +2319,1405 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="372.6" spans="1:5">
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="372.6" spans="1:6">
       <c r="A2" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="151.8" spans="1:5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" ht="151.8" spans="1:6">
       <c r="A3" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" ht="151.8" spans="1:5">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="151.8" spans="1:6">
       <c r="A4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" ht="151.8" spans="1:5">
+    </row>
+    <row r="5" ht="151.8" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" ht="151.8" spans="1:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="151.8" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" ht="151.8" spans="1:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" ht="151.8" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" ht="124.2" spans="1:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" ht="124.2" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" ht="151.8" spans="1:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" ht="151.8" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" ht="179.4" spans="1:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" ht="179.4" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" ht="138" spans="1:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" ht="138" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" ht="151.8" spans="1:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" ht="151.8" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" ht="138" spans="1:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" ht="138" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" ht="151.8" spans="1:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" ht="151.8" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" ht="151.8" spans="1:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" ht="151.8" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" ht="179.4" spans="1:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" ht="179.4" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" ht="207" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" ht="151.8" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" ht="165.6" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" ht="138" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="151.8" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" ht="179.4" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" ht="165.6" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="165.6" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" ht="151.8" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" ht="151.8" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" ht="165.6" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" ht="165.6" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" ht="179.4" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" ht="165.6" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" ht="165.6" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" ht="165.6" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" ht="165.6" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" ht="165.6" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" ht="151.8" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" ht="151.8" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" ht="151.8" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" ht="165.6" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" ht="138" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" ht="193.2" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" ht="165.6" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="42" ht="151.8" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" ht="409.5" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="44" ht="409.5" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45" ht="409.5" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" ht="409.5" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47" ht="409.5" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" ht="409.5" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="49" ht="409.5" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50" ht="409.5" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" ht="409.5" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="52" ht="409.5" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53" ht="409.5" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="54" ht="409.5" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="55" ht="400.2" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="56" ht="409.5" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="57" ht="409.5" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="58" ht="372.6" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="59" ht="409.5" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="60" ht="409.5" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="61" ht="409.5" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="62" ht="409.5" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="63" ht="409.5" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="64" ht="409.5" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="65" ht="409.5" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="66" ht="409.5" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="67" ht="345" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="68" ht="409.5" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="69" ht="409.5" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="70" ht="409.5" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="71" ht="409.5" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="72" ht="409.5" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="73" ht="409.5" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="74" ht="358.8" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="75" ht="409.5" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="76" ht="400.2" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="77" ht="386.4" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="78" ht="409.5" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="79" ht="400.2" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="80" ht="409.5" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="81" ht="409.5" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="82" ht="409.5" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="83" ht="409.5" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/book.xlsx
+++ b/book.xlsx
@@ -4,14 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25068" windowHeight="13380"/>
+    <workbookView windowWidth="25068" windowHeight="13380" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="道德经" sheetId="1" r:id="rId1"/>
+    <sheet name="大学" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$83</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -30,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="456">
   <si>
     <t>chapter</t>
   </si>
@@ -1105,6 +1103,363 @@
   <si>
     <t>说起《道德经》的分章，大家一般认为最早是河上公以九九归一为神秘的数字指向，把它分成了八十一章。第八十一章可以看作是全书的总结，全书思想的总结和概括就是最后这两句话，“天之道，利而不害。”天道如此，人道应该效法天道，所以下一句“圣人之道，为而不争”，一个好的领导人、统治者是如此，对我们大家来讲也是如此。韩国有一个连任联合国秘书长的聪明人，叫潘基文。他在连任就职典礼上，开口讲的就是《道德经》的这两句话，只不过他引用的是这两句话中的八个字：“利而不害，为而不争。”我怎么做联合国秘书长？我对大家有利，不起坏心，为大家谋福利，“利而不害”。我把事情做了，不为自己争名夺利，“为而不争”。我们应该有一个非常深刻的体验：道家并不是消极的、被动的、什么事都不做。什么叫无为？“为而不争”是无为的一个重要的方面，这可以看作是全部《道德经》的核心的总结。我们回头去想，“上善若水”讲“善利万物而不争”；天道讲“为而不争”。这样我们就把整个的思想落地了，知道了《道德经》最后的核心落在什么地方。现在来看一下原文，“信言不美，美言不信”，真正诚信的话，不漂亮，只会讲漂亮话的，没诚信，过度漂亮的话里，往往隐含欺骗的内容，所以大家说，真理是朴素的，真理是赤裸裸的。“善者不辩，辩者不善”，真正善良的人，不老去争辩。庄子在他文章里边经常讲，老去靠争辩，争辩胜了，又能够体现什么？“善者不辩，辩者不善”，老去争辩，老为自己找借口，老觉得自己受了无尽的委屈，这个不是善良者的表现。“知者不博，博者不知”，一个有智慧的人，不是老是吹嘘自己渊博、博学、无所不知，老是吹嘘自己无所不知的人，其实是没有智慧的。下面就讲一个有智慧的领导者应该怎么去做事。“圣人不积”，一个有智慧的领导者，不是老想着去积累财富、有形的资产。“既以为人，己愈有”，什么叫做富？什么叫做有？我老去帮助别人，为别人做事，在给别人做事情，帮助别人的过程中，获得了无尽的快乐，这不是无形资产吗？这不是精神世界的充盈吗？“既以与人，己愈多”，给别人的越多，帮别人的越多，要财富发挥它的真正的作用，在“舍”的过程中反而自己得到更多。“既以为人，己愈有；既以与人，己愈多。”2014年习近平在斐济《斐济时报》发表署名文章，也用过这两句话。中国人喜欢双赢，帮助别人。我们的理念是什么？我们给别人做的事情越多，我们感觉到自己越富有；对别人帮得越多，感觉到自己获得的更多。所以我们经常讲，我们很多的快乐是在帮助别人成长，别人有困难的时候，我们帮扶的时候，感觉到自己的内心的充盈快乐。“为人”是什么？“与人”是什么？是善利。看似付出，自己反而获得更多，自己的精神世界也更为充盈。如果我们只一味地为自己积累财富，结果呢？我们经常讲一句话，叫穷得只剩下钱了，我们的物质世界越发达，财富越多，我们的精神家园就越花果飘零。“善利万物而不争”，这是全书的最后总结。不争什么？不争言语的漂亮，只为了它的实质；不为了争辩的胜利，只为它的真理；不吹嘘自己的知识的渊博，只让知识发挥它正确的作用；不积累那么多所谓的财富，而是让财富发挥它真正的作用，让我们的精神世界越来越充盈、越来越丰富。帮人越多，自己越富有；给人越多，自己获得越多。舍得、舍得，舍的同时，也是一种获得；帮人的过程，也是一种快乐。“既以为人，己愈有；既以与人，己愈多”，这两句话仔细思量，其即是天道。“天之道，利而不害”，天道如此，善利万物不起坏心。“圣人之道，为而不争”，把事情做了，不为自己争名夺利。“为而不争”和前面我们讲过的“善利万物而不争”、“生而不有，为而不恃，长而不宰”、“功成而弗居”、“衣养万物而不为主”，这些重要的语句遥相呼应。这样，我们就把思想穿成了一串珍珠，看清楚了这本书的真正的逻辑，也看清了这本书的“落脚点”。这些成为我们生活中的座右铭，指南针，对我们的思维方式、人生格局、精神境界都会有很大的启发和启迪。第八十一章的内容，我们解读完了。到这最后一章，我们看到这一章最后落在这句话上“圣人之道，为而不争”，可以清楚的看到这本经典的目的就是把士和王修养、培养成圣。这就是这本书的内在逻辑，也是老子的良苦用心。读这本经典要掌握以下几个关键性问题。一是《道德经》本质上是一本对话体，也就是对面坐着人问的问题。只不过老子在刻书时把对面坐的人是谁、问的什么问题都省略了，而只是把他当时给的答案概括、总结、提炼、升华形成的一本著作。当我们从书里找到士、王、圣这三类问问题的人时，也就很容易抓住问题的关键了。二是王弼本《道德经》哲学思维水平非常高。在第一章就提出有无相互统一思维方式的重要性，并指出“无”是全书的众妙之门，从而让我们清楚地知道了无为、无声、无色、无味、无色……在这本书中的重要性，也借此步入众妙之门。三是我们这种以经解经的方法前后参照，避免了八十一章本子的“碎片化”倾向，并且在通篇解读中发现了老子对他认为重要问题的强调方式：首先是用重复的方式强调。比如在第十章、第五十章都重复出现“生而不有，为而不恃，长而不宰”，并且在第二章、第三十四章也都出现类似的意思。其次是用首尾呼应的方式来强调，比如二十二章就是如此。其三是用正反两个方面的方式来强调一个观点的重要性，比如第六十七章就是如此。了解了上面这些导读的内容，我们再来听课、阅读，我们就会更深刻地了解这本书的深刻内容，这本“善建者不拔”的伟大经典指导下：“修之于身，其德乃真；修之于家，其德乃余；修之于乡，其德乃长；修之于国，其德乃丰；修之于天下，其德乃普。”当然即便是逐章解决了很多问题，讲的恐怕也是蜻蜓点水，就《道德经》而言，最重要的是大家自己的阅读和领悟。</t>
   </si>
+  <si>
+    <t>经第一章（1-1）</t>
+  </si>
+  <si>
+    <t>大学之道，在明明德，在亲（新）民，在止于至善。知止而后有定，定而后能静，静而后能安，安而后能虑，虑而后能得。物有本末(mò)，事有终始。知所先后，则近道矣。</t>
+  </si>
+  <si>
+    <t>大学的宗旨，在于弘扬光明正大的品德，在于使民众弃旧图新，在于达到最完善的境界。知道应该达到的目标，然后才能有确定的志向，有了确定的志向，然后才能心静，心静然后才能神安，神安然后才能周详地思虑，思虑周详然后才能处事得宜。凡物都有本有末，凡事都有始有终，知道事物的先后次序，就接近大道（事物发展的规律）了。</t>
+  </si>
+  <si>
+    <t>本章是《大学》全篇的总纲，提出“三纲领”：明明德、亲（新）民、止于至善。明明德是要用学问之功冲开气禀之拘、克去物欲之蔽，使人心虚灵不昧的本体恢复光明；亲民（读作新民）是在自明其德之后鼓舞作兴天下之人，革去旧染之污；止于至善则是明己德、新民德都要做到事理当然之极，如赴家一般到极好处才止。止于至善，一个人只有达到很高的道德水平之后，才能做到，有所必为有所不为，有所能有所不能，运用之妙存乎一心，从心所欲而不逾矩，穷则独善其身，达则兼济天下。“至善”是一种理想化的人生取向。</t>
+  </si>
+  <si>
+    <t>总纲</t>
+  </si>
+  <si>
+    <t>经第一章（1-2）</t>
+  </si>
+  <si>
+    <t>古之欲明明德于天下者，先治其国；欲治其国者，先齐其家；欲齐其家者，先修其身；欲修其身者，先正其心；欲正其心者，先诚其意；欲诚其意者，先致其知；致知在格物。物格而后知至；知至而后意诚；意诚而后心正；心正而后身修；身修而后家齐；家齐而后国治；国治而后天下平。</t>
+  </si>
+  <si>
+    <t>古代有想要彰明光明德性于天下的人，先要治理好自己的国家;想要治理好自己的国家，先要整顿好自己的家庭;想要整顿好自己的家庭，先要修养自身;想要修养自身，先要端正自心;想要端正自心，先要诚实自己的意念;想要诚实自己的意念，先要获得知识;获得知识就在于推究事物的原理。推究了事物的原理才能得到真知，得到真知然后才能意念诚实，意念诚实然后才能心正，心正然后才能提高自身修养，提高了自身修养然后才能整顿好家庭，家庭整顿好了然后才能治理好国家，国家治理好了然后才能使天下太平。</t>
+  </si>
+  <si>
+    <t>本节讲《大学》的条目功夫“八目”：格物、致知、诚意、正心、修身、齐家、治国、平天下。从“欲明明德于天下”逐层倒推，天下之本在国，国之本在家，家之本在身，身之主在心，心之发动在意的，要正心先诚意，要诚意先致知，而致知在格物，即穷究事物之理到极处。
+后半段再顺着推演：物格而后知至，知至而后意诚，意诚而后心正，心正而后身修，身修而后家齐，家齐而后国治，国治而后天下平。格物、致知、诚意、正心、修身是明明德的条目，齐家、治国、平天下是新民的条目，其次第不可紊乱、功夫不可缺略，这是入大学者所当知的根本次序。</t>
+  </si>
+  <si>
+    <t>经第一章（1-3）</t>
+  </si>
+  <si>
+    <t>自天子以至于庶（shù）人，壹是皆以修身为本。其本乱而末治者，否矣。其所厚者薄，而其所薄者厚，未之有也。此谓知本，此谓知之至也。</t>
+  </si>
+  <si>
+    <t>从天子下至平民百姓，一律要以修身为根本。若这个根本坏了乱了，而天下、国家、家族要治理好，那是不可能的。对自己关系亲厚的人情意淡薄，而对自己关系淡薄的人却情意浓厚，没有这样的情理。这就叫做知本，这就叫做认知的极致。</t>
+  </si>
+  <si>
+    <t>本节强调“修身为本”：大学的条目虽有八件，但上自天子、下至庶人，一切都要以修身为根本。格物、致知、诚意、正心都是修身的功夫，齐家、治国、平天下都是从修身推出去的事。
+身是家国天下的根本，本乱而末治绝无可能，如同树根枯了却要枝叶茂盛。对家人（厚者）当厚，对国与天下之人（薄者）当薄，不能齐家却要治国平天下，必无此理。因此“知本”才是“知之至也”，修身既是个人修养的起点，也是家国天下治理的基石。</t>
+  </si>
+  <si>
+    <t>传第一章（1）</t>
+  </si>
+  <si>
+    <t>《康诰》曰：“克明德。”《太甲》曰：“顾諟（shì）天之明命。”《帝典》曰：“克明峻德。”皆自明也。</t>
+  </si>
+  <si>
+    <t>《尚书·康诰》篇中说:“能够弘扬光明的美德。”《尚书·太甲》篇中说:“要顾念熟思上天赋予的光明使命。”《尚书·帝典》篇中说:“能够彰明伟大的品德。”这些说的都是去彰明光大自己的德性。</t>
+  </si>
+  <si>
+    <t>本章是曾子解释经文“明明德”。引《康诰》“克明德”、《太甲》“顾諟天之明命”、《帝典》“克明峻德”三处古书为证：文王能明其德而无昏昧，成汤时时存养天命所赋予的明命而无怠玩，尧能明其大德而光被四表。\n\n三书所言虽有不同，但所谓德、明命、峻德都是指人心中本有的明德，克明、顾諟、克明都是自明己德的意思，所以说“皆自明也”。儒家以先王德治为历史渊源，说明治国先要自己内心光明。</t>
+  </si>
+  <si>
+    <t>明明德</t>
+  </si>
+  <si>
+    <t>传第二章（2）</t>
+  </si>
+  <si>
+    <t>汤之《盘铭》曰：“苟日新，日日新，又日新。”《康诰》曰：“作新民。”《诗》曰：“周虽旧邦，其命维新。”是故君子无所不用其极。</t>
+  </si>
+  <si>
+    <t>商汤浴盘上的铭辞说:“假如今天洗净污垢更新自身，那么就要天天清洗更新，每日不间断地清洗更新。”《尚书·康诰》中说:“使他们作为新的人民。（激励民众自新）”《诗经·大雅·文王》篇中说:“周国虽然是个古旧的邦国，但其因时代的趋势而成为一个新的邦国。”所以，英明的国君都应尽心竭力，达到至善至美。</t>
+  </si>
+  <si>
+    <t>本章解释“新民”。汤之盘铭“苟日新，日日新，又日新”讲自新是根本：人心本自清明，被私欲污染，要像沐浴洗去尘垢一样天天用力洗去旧染之污，这是新民之本。《康诰》“作新民”讲新民之事：百姓旧日不善，若能改过从善，为君者要鼓舞振作他们。《诗》“周虽旧邦，其命维新”讲自新新民之极：周自后稷以来虽是旧邦，文王能新其德并推及于民，才受天命而有天下。\n\n所以君子无所不用其极，自新与新民都要做到至善的去处；日新是明德之事，用其极是止至善之事，三纲领都在其中。</t>
+  </si>
+  <si>
+    <t>新民</t>
+  </si>
+  <si>
+    <t>传第三章（3-1）</t>
+  </si>
+  <si>
+    <t>《诗》云：“邦畿（jī）千里，惟民所止。”《诗》云：“缗（mín）蛮黄鸟，止于丘隅（yú）。”子曰：“于止，知其所止，可以人而不如鸟乎？”</t>
+  </si>
+  <si>
+    <t>《诗经·商颂·玄鸟》篇中说:“一个邦国的土地疆域有千里之广，但只能局限在有人民居住的地方。”《诗经·小雅·缗蛮》篇中说:“缗缗蛮蛮地鸣叫的黄鸟，栖息于山丘多树的一角。”孔子说:“关于栖息，黄鸟还知道自己该栖止的处所，怎么可以人还不如鸟呢!”</t>
+  </si>
+  <si>
+    <t>本章释“止于至善”。《诗》“邦畿千里，惟民所止”说明凡物各有所当止之处，国家的意义正在于让百姓安居；《诗》“缗蛮黄鸟，止于丘隅”以黄鸟栖于山阜树多之处起兴，孔子借物警人：黄鸟尚知所止，人为万物之灵，岂可反而不如鸟？\n\n鸟所当止的是林木，人所当止的是至善。“止”意味着节制与限度，人要知道自己的道德界限和行为准则，有所为有所不为，这才是人的自省与理性。</t>
+  </si>
+  <si>
+    <t>止于至善</t>
+  </si>
+  <si>
+    <t>传第三章（3-2）</t>
+  </si>
+  <si>
+    <t>《诗》云：“穆穆文王，於（wū）缉（qì）熙敬止！”为人君，止于仁；为人臣，止于敬；为人子，止于孝；为人父，止于慈；与国人交，止于信。子曰：“听讼，吾犹人也。必也使无讼乎！”无情者不得尽其辞，大畏民志。此谓知本。</t>
+  </si>
+  <si>
+    <t>《诗经·大雅·文王》篇中说:“德行深厚的文王啊，他的美德使人们无不崇敬。”所以，作为人君要居心于仁爱，作为人臣要居心于恭敬，作为人子要居心于孝顺，作为人父要居心于慈爱，与民众的交往要居心于诚信。孔子说:“审理诉讼案件，我犹如诉讼的人心情一样，一定要使人们不再发生争讼。”一定要让那些没有实情的人不敢虚词矫饰，使人们心悦诚服，这就称为知道了根本。</t>
+  </si>
+  <si>
+    <t>本节以文王为例说明圣人能得所止。文王“于缉熙敬止”，德继续光明、无不敬而安所止：为人君止于仁，为人臣止于敬，为人子止于孝，为人父止于慈，与国人交止于信。仁、敬、孝、慈、信是五伦中最重要的准则，随身份各尽其道，便能近于至善。\n\n后半引孔子“听讼”之言释本末：听断词讼使曲直分明不难，可贵的是使民相敬相爱、自然无讼。圣人能使无情者不得尽其虚诞之辞，靠的不是刑罚，而是盛德畏服民志。己德明是根本，民德新是末梢，明德在先、新民在后，这就是“知本”。</t>
+  </si>
+  <si>
+    <t>传第三章（3-3）</t>
+  </si>
+  <si>
+    <t>《诗》云：“瞻（zhān）彼淇（qí）澳（yù），菉（lù）竹猗（yī）猗。有斐（fěi）君子，如切如磋，如琢如磨（mó）。瑟兮僴（xiàn）兮，赫兮喧兮。有斐君子，终不可喧兮！”“如切如磋”者，道学也；“如琢如磨”者，自修也；“瑟兮僴兮”者，恂（xún）慄（lì）也；“赫兮喧兮”者，威仪也；“有斐君子，终不可喧兮”者，道盛德至善，民之不能忘也。</t>
+  </si>
+  <si>
+    <t>《诗经·卫风·淇奥》篇说:“瞧那淇水的水湾，箓竹草茂盛美观。有位文采焕发的君子，犹如骨角经过切磋，犹如玉石经过琢磨。庄严而又刚毅，显赫而又坦荡。斐然文雅的君子啊，让人始终难以忘怀！”“如切如磋”的意思，喻指君子的努力治学;“如琢如磨”的意思，喻指君子认真地自修;“瑟兮悯兮”的意思，是说君子端庄恭慎的心态;“赫兮喧兮”的意思，是说君子的威严仪表;“有斐君子终不可谊兮”的意思，是说君子盛大的品德尽美尽善，人民不能忘记他。</t>
+  </si>
+  <si>
+    <t>本节以卫武公为典范，说明明明德达到至善的表现。诗以淇澳绿竹起兴，赞美君子学问精密的“如切如磋”、自修细密的“如琢如磨”，就像治骨角、治玉石一样精益求精；有得于心则瑟然严密、僩然武毅，形于外则赫然宣著、喧然盛大，所以百姓感仰爱戴、终身不忘。\n\n曾子逐一解释：切磋是讲习讨论、穷究到极精透处；琢磨是省察克治、不留一点瑕玷；恂栗是战战兢兢、无一时懈惰；威仪是有威可畏、有仪可象。德极全备而为盛德，善极精纯而为至善，这便是明德止于至善的境界。</t>
+  </si>
+  <si>
+    <t>传第三章（3-4）</t>
+  </si>
+  <si>
+    <t>《诗》云：“於（wū）戏（hū），前王不（bù）忘！”君子贤其贤而亲其亲，小人乐其乐而利其利，此以没（mò）世不忘也。</t>
+  </si>
+  <si>
+    <t>《诗经·周颂·烈文》篇说:“呜呼，前代的君王不能让人忘怀。”后代的君子推崇其遵行的贤德而承继他的业绩。后世的人民享受着前王留下的恩泽，安居乐业，所以前代的君王虽然去世，但是他的功德永远不会被人们忘记。</t>
+  </si>
+  <si>
+    <t>本节用《诗》“於戏，前王不忘”说明新民之止于至善。文王武王留下无穷功德，所以去世虽远而天下人思慕不忘：后贤后王守其模范而贤其贤、承其基业而亲其亲，后世百姓享其所遗的太平之乐与恒产之利，所以没世不忘。\n\n无论贤愚都能从先王的功德中各得其所，这正是盛德至善感动人心、泽被后世的证明。</t>
+  </si>
+  <si>
+    <t>传第四章（4）</t>
+  </si>
+  <si>
+    <t>所谓致知在格物者，言欲致吾之知，在即物而穷其理也。盖人心之灵莫不有知，而天下之物莫不有理，惟于理有未穷，故其知有不尽也。是以《大学》始教，必使学者即凡天下之物，莫不因其已知之理而益穷之，以求至乎其极。至于用力之久，而一旦豁然贯通焉，则众物之表里精粗无不到，而吾心之全体大用无不明矣。此谓物格，此谓知之至也。</t>
+  </si>
+  <si>
+    <t>想要获得知识，就必须根据具体事物穷究其理。人的心是具有灵性的，而万事万物也具有自身的规律，只是我们没有用自己的理性去穷究这些规律，所以知识便不全面。因此《大学》开篇明义，就让学习者根据自己掌握的知识对于天下的事物，都要穷究其理，以求达到明理知性，通达完美。下的功夫久了，就会豁然开朗，融会贯通，许多事物的里外和粗精都会一清二楚，而自己心灵的终极追求无所不明了。这就是格物的意思，这就是到达极致的理性。</t>
+  </si>
+  <si>
+    <t>本章是朱子取程子之意补足亡佚的“格物致知”传文，也是《大学》功夫的第一段、最紧要处。经文所谓致知在格物，是说人要推及吾心的知识，须随事随物穷究其理；人心至虚至灵本有知，天下之物莫不有理，惟于理有未穷，故知有不尽。\n\n《大学》始教，要使学者就已知之理益加穷究，一事不穷、一毫不尽，直到极处；用力之久，一旦豁然贯通，则众物表里精粗无不到，吾心全体大用无不明，这便是物格、知至。没有这一节，诚意正心、修齐治平都做不成，所以格物致知是境界不断提升的前提。</t>
+  </si>
+  <si>
+    <t>格物致知</t>
+  </si>
+  <si>
+    <t>传第五章（5）</t>
+  </si>
+  <si>
+    <t>所谓诚其意者，毋自欺也。如恶（wù）恶（è）臭（xiù），如好（hào）好（hǎo）色，此之谓自谦（qiàn）。故君子必慎其独也。小人闲居为不善，无所不至，见君子而后厌（yǎn）然，揜（yǎn）其不善而著其善。人之视己，如见（jiàn）其肺肝然，则何益矣？此谓诚于中，形于外。故君子必慎其独也。曾子曰：“十目所视，十手所指，其严乎！”富润屋，德润身，心广体胖。故君子必诚其意。</t>
+  </si>
+  <si>
+    <t>所谓诚实自己的意念，是说不要自己欺骗自己，就像厌恶恶臭气味、爱好美色那样自然真实。这样诚实不欺，才称得上是自我满足。为了做到诚实不欺，所以君子必须谨慎自己独处的时候。小人平日闲居时为非作歹，没有哪样坏事做不出来的，及至见到君子，然后遮遮盖盖地掩藏他那不光彩的行径，而故意显露他的“善良”，却不知别人看自己，就如同看见了自己的肺肝一样，那装模作样又有什么益处呢!这就是所谓内心的真实意念会显露于外表，所以君子必须谨慎自己一人独处的时候。曾子说:“独处的时候其实也有无数人的眼睛注视着你，无数人的手指着你，这难道不严峻吗？”财富能够润饰房屋，道德能够润饰人身，心胸宽广从而身体舒适，所以君子必须使自己意念真诚。</t>
+  </si>
+  <si>
+    <t>本章释“诚意”，是为学功夫极要紧处。诚意就是于意念发动时真真实实禁止自欺，恶恶如恶恶臭、好善如好好色，务要决去其恶、必得其善，如此才是好善恶恶的本心，心中快足，谓之自慊。自欺与否，人不及知而自己独知，所以君子必慎其独。\n\n小人闲居为不善，见君子便遮掩伪装，但人之视己如见肺肝，诚于中必形于外，掩恶诈善毫无益处。曾子又说“十目所视，十手所指”，幽独之中有迹必露、无微不彰，甚可畏也。能慎独则德润身、心广体胖，故君子必诚其意。</t>
+  </si>
+  <si>
+    <t>诚意</t>
+  </si>
+  <si>
+    <t>传第六章（6）</t>
+  </si>
+  <si>
+    <t>所谓修身在正其心者：身有所忿（fèn）懥（zhì），则不得其正；有所恐惧，则不得其正；有所好乐（yào），则不得其正；有所忧患，则不得其正。心不在焉，视而不见，听而不闻，食而不知其味。此谓修身在正其心。</t>
+  </si>
+  <si>
+    <t>所谓修身在于端正自心，意思是说：自身有所忿怒，心就不能端正;有所恐惧，心就不能端正;有所偏好，心就不能端正;有所忧虑，心就不能端正。被忿怒、恐惧、偏好、忧虑所困扰，导致神不守舍，心不在焉，看也看不明了，听也听不清了，吃着却不知食物的滋味。这说的是修身在于端正自心的道理。</t>
+  </si>
+  <si>
+    <t>本章释“正心修身”。心是一身的主宰，心体至虚、着不得一物；有所忿懥、恐惧、好乐、忧患，即是把一件事执着横在胸中，心为其所累而不得其正。喜怒哀乐是情之所不能免，若能随事顺应、事已即化，心如明镜，便无牵累；若发之过当、留滞于中，就失了正。\n\n心不在焉，则眼虽视而不见，耳虽听而不闻，食而不知其味，耳目口体的视听食味都靠心主宰。心不正则身不修，所以修身必先正心；静而存养、动而省察，喜怒忧惧各中其则，心正身修，家国天下才能从之而理。</t>
+  </si>
+  <si>
+    <t>正心修身</t>
+  </si>
+  <si>
+    <t>传第七章（7）</t>
+  </si>
+  <si>
+    <t>所谓齐其家在修其身者：人之其所亲爱而辟（pì）焉，之其所贱恶（wù）而辟焉，之其所畏敬而辟焉，之其所哀矜而辟焉，之其所敖惰而辟焉。故好而知其恶（è），恶（wù）而知其美者，天下鲜矣！故谚有之曰：“人莫知其子之恶，莫知其苗之硕。”此谓身不修，不可以齐其家。</t>
+  </si>
+  <si>
+    <t>所谓齐其家在于修养自身，意思是说：一般不能修身的人，对于自己所亲爱的人，往往有过分亲爱的偏向;对于自己所轻贱厌恶的人，往往有过分轻贱厌恶的偏向;对于自己所畏服敬重的人，往往有过分畏服敬重的偏向;对于自己所哀怜矜恤的人，往往有过分哀怜矜恤的偏向;对于自己所傲视慢待的人，往往有过分傲视慢待的偏向。所以，喜欢某人同时又知道他的缺点，厌恶某人同时又知道他的优点，这种人天下就很少了。所以谚语有这样的说法:“由于溺爱，人们不知道自己孩子的过错;由于贪得，人们不知道自家禾苗的壮硕。”这说的是自身不提高修养就不能治好自家的道理。</t>
+  </si>
+  <si>
+    <t>本章释“修身齐家”。一家之本在我一身，但人情多任性好恶、陷于一偏：亲爱、贱恶、畏敬、哀矜、敖惰五种情感若只凭私情、不论义理，便都偏了。好一个人只见其善、恶一个人只见其恶，能好而知其恶、恶而知其美者，天下少有。\n\n俗语“人莫知其子之恶，莫知其苗之硕”正说明偏见蔽目与贪得无厌之害。身不修则情有所偏、事皆任意，要感化一家使人各循伦理，绝无此理；所以欲齐家者必须先修其身，养成中正无偏的心态。</t>
+  </si>
+  <si>
+    <t>修身齐家</t>
+  </si>
+  <si>
+    <t>传第八章（8-1）</t>
+  </si>
+  <si>
+    <t>所谓治国必先齐其家者，其家不可教而能教（jiào）人者，无之。故君子不出家而成教于国。孝者，所以事君也；弟者，所以事长也；慈者，所以使众也。</t>
+  </si>
+  <si>
+    <t>所谓治理国家必定先要治好自己家庭，意思是说：连自己家里人都不能教育好而能教育好别人，这是没有的事。所以，在位的君子不出家门就能够完成对全国的教育。孝顺父母的感情，同样可以用来事奉国君的;敬重兄长的感情，同样可以用来事奉尊长的;慈爱子女的感情，同样可以用来对待民众的。</t>
+  </si>
+  <si>
+    <t>本章释“齐家治国”。家乃国之本，不能修身教家却能教训一国之人，绝无此理；君子修身以教于家，使父子、兄弟、夫妇各尽其道，身不出家庭，标准立而风声传，一国百姓自然感化。\n\n理由是家国虽异、其理则同：善事其亲之孝，即是事君之道；善事其兄之弟，即是事长之道；抚爱卑幼之慈，即是使众之道。孝、弟、慈三件在家行之，就是治国事君、事长、使众的道理，所以君子不出家而成教于国。</t>
+  </si>
+  <si>
+    <t>齐家治国</t>
+  </si>
+  <si>
+    <t>传第八章（8-2）</t>
+  </si>
+  <si>
+    <t>《康诰》曰：“如保赤子。”心诚求之，虽不中，不远矣。未有学养子而后嫁者也。</t>
+  </si>
+  <si>
+    <t>《尚书·康诰》中说:“爱人民如同保护婴儿。”心里如果真有这种博爱的追求，即使不能做得完全合格，那也差得不远了。自古以来，没有哪个女子先学养育婴儿、疼爱婴儿，而后才去嫁人的。</t>
+  </si>
+  <si>
+    <t>本节承上文说明孝、弟、慈之理是人心原有、不待强为。《康诰》“如保赤子”说人君保爱百姓当如慈母保爱初生小儿；赤子不会说话，母亲凭着诚切恳至的爱子之心去忖度他的意思，虽不能一一皆合，也差不远。\n\n“未有学养子而后嫁者也”说明保赤子之心不学自会、出于自然；慈幼之心既出于自然，孝弟之心亦不出于自然，只要识其端而推广之，便能不出家而成教于国。心诚则虽不中不远，这是儒家把“诚”看得极重的缘故。</t>
+  </si>
+  <si>
+    <t>传第八章（8-3）</t>
+  </si>
+  <si>
+    <t>一家仁，一国兴仁；一家让，一国兴让；一人贪戾，一国作乱。其机如此。此谓一言偾（fèn）事，一人定国。尧、舜率天下以仁，而民从之；桀（jié）、纣（zhòu）率天下以暴，而民从之。其所令反其所好，而民不从。是故君子有诸己而后求诸人，无诸己而后非诸人。所藏乎身不恕，而能喻诸人者，未之有也。故治国在齐其家。</t>
+  </si>
+  <si>
+    <t>国君一家人仁爱相亲，那么一国人就会受到感化，兴起仁爱的风气;国君一家人谦让相敬，那么一国人就会受到感化，兴起谦让的风气;国君一人贪婪暴戾，那么一国人就会受到影响，纷纷为非作乱:国君一人一家对国家治乱的关键作用就是这样。这就叫做一句话可以败坏大事，一个人可以安定国家。尧舜用仁政统率天下，于是人民就跟从他们学仁爱;桀纣用暴政统率天下，于是人民就跟从他们学残暴。国君所颁布的政令与他本人的爱好相反，人民就不肯依从了。所以，国君自己有了好的德行，然后才去要求别人;无法要求自己做到，也就无法要求别人做到。自身有不合道理的思想，而能教育好别人，那是没有的事。所以说，君主要治好国家，在于先治好自己的家庭。</t>
+  </si>
+  <si>
+    <t>本节讲教成于国之效与君主的表率作用。一家仁则一国兴仁，一家让则一国兴让，一人贪戾则一国作乱，其机如此，所以“一言偾事，一人定国”。尧舜率天下以仁而民从之，桀纣率天下以暴而民从之，上行下效、理势自然；若所令反其所好，民必不从。\n\n因此君子有诸己而后求诸人，无诸己而后非诸人，自己所藏乎身的不恕，而能晓喻他人，绝无此理。治国不必远求，只在修身以教于家，齐家是治国的根本。</t>
+  </si>
+  <si>
+    <t>传第八章（8-4）</t>
+  </si>
+  <si>
+    <t>《诗》云：“桃之夭夭，其叶蓁（zhēn）蓁。之子于归，宜其家人。”宜其家人，而后可以教国人。</t>
+  </si>
+  <si>
+    <t>《诗经·周南·桃天》篇中说:“桃花娇艳艳，桃叶绿蓁蓁，这位女子出嫁，一定会让一家人都其乐融融。”一家人和睦，而后才能教化全国的人。</t>
+  </si>
+  <si>
+    <t>本节引《诗·周南·桃夭》咏叹齐家治国的道理。桃树夭夭少好、其叶蓁蓁美盛，兴起女子归于夫家，必能事舅姑以孝、事夫子以敬、处妯娌以和、待下人以惠，使一家之人无不相宜。\n\n曾子引诗说：为人君者必能处得一家之人个个停当，如诗所谓“宜其家人”，然后才可以教一国之人各宜其家；家人尚且不相宜，又怎能教国人呢？以家道和睦为教化国人的前提。</t>
+  </si>
+  <si>
+    <t>传第八章（8-5）</t>
+  </si>
+  <si>
+    <t>《诗》云：“宜兄宜弟。”宜兄宜弟，而后可以教国人。</t>
+  </si>
+  <si>
+    <t>《诗经·小雅·蓼萧》篇中说:“使兄弟和睦。”与兄弟合心友爱，然后才可以教育一国人。</t>
+  </si>
+  <si>
+    <t>本节引《诗·小雅·蓼萧》“宜兄宜弟”申说齐家治国。一家之中，我能尽恭敬而善事兄长，感得兄长也爱我，便是宜兄；我能尽友爱而善抚弟弟，感得弟弟也敬我，便是宜弟。\n\n曾子说：为人君者必能善处自家兄弟，然后可以教一国之人使之各宜兄弟；自家骨肉尚不能相容，又凭什么教导国人？先齐家而后治国，次序不可颠倒。</t>
+  </si>
+  <si>
+    <t>传第八章（8-6）</t>
+  </si>
+  <si>
+    <t>《诗》云：“其仪不忒（tè），正是四国。”其为（wéi）父子兄弟足法，而后民法之也。此谓治国在齐其家。</t>
+  </si>
+  <si>
+    <t>《诗经·曹风·鸬鸠》篇中说:“礼仪没有差错，才能成为四方各国的表率。”作为父亲、作为儿子、作为兄弟都值得效法，然后人民才能效法他。这说的是治国在于先治其家的道理。</t>
+  </si>
+  <si>
+    <t>本节引《诗·曹风·鸤鸠》“其仪不忒，正是四国”总结齐家治国。人君一身所行的礼仪没有一件差错，便能表正四方之国；为父能慈、为子能孝、为兄能友、为弟能恭，所行件件足以为人法则，百姓才取法于他。\n\n曾子引三诗后总结：治国在齐其家，欲治其国者必先齐家以为根本；家是国的缩影与细胞，家庭和睦有序，国家才能安定团结，这就是“治国在齐其家”的道理。</t>
+  </si>
+  <si>
+    <t>传第九章(9-1)</t>
+  </si>
+  <si>
+    <t>所谓平天下在治其国者：上老老而民兴孝，上长长而民兴弟，上恤孤而民不倍，是以君子有絜（xié）矩之道也。所恶（wù）于上，毋以使下；所恶于下，毋以事上；所恶于前，毋以先后；所恶于后，毋以从前；所恶于右，毋以交于左；所恶于左，毋以交于右。此之谓絜矩之道。</t>
+  </si>
+  <si>
+    <t>所谓平定天下在于先治理好国家，意思是说，国君要尊敬老人，从而国民就会兴起孝敬的风气;国君尊重年长的，从而国民就会兴起敬长的风气;国君怜恤孤儿，从而国民就会不背弃孤弱。所以君子要有一定的方圆之规，国人才会上行下效。（按:絮是量围长的绳子，矩是画直角的尺子。首先絮矩本身就是标准，然后才能衡量、规范外物。絮矩之道喻指君子以身作则、推己及人之道）。既然厌恶在上者的所作所为，就不要用来对待在下者;既然厌恶在下者的所作所为，就不要用来侍奉在上者。既然厌恶前者的所作所为，就不要用来对待后者;既然厌恶后者的所作所为，就不要用来对待前
+者。既然厌恶在右者的所作所为，就不要用来对待在左者;既然厌恶在左者的所作所为，就不要用来对待在右者。这就叫做“絮矩”（有方圆规矩）之道。</t>
+  </si>
+  <si>
+    <t>本章释“治国平天下”。天下无不同之心、人心无不同之理，上老老而民兴孝，上长长而民兴弟，上恤孤而民不倍，可见人心之理无不同，一国既异于一家，天下亦不异于国。因此君子有絜矩之道：度其必同之心，处以各足之理，如匠人以矩制器，使天下皆方。\n\n絜矩即推己及人：所恶于上毋以使下，所恶于下毋以事上，前后左右亦然，将人比己、以己处人，上下四方均齐方正，一句话说就是“己所不欲，勿施于人”。平天下要从善待身边的人做起，这是修身齐家治国平天下由内向外扩展的枢纽。</t>
+  </si>
+  <si>
+    <t>治国平天下</t>
+  </si>
+  <si>
+    <t>传第九章(9-2)</t>
+  </si>
+  <si>
+    <t>《诗》云：“乐只君子，民之父母。”民之所好（hào）好（hào）之，民之所恶（wù）恶（wù）之，此之谓民之父母。</t>
+  </si>
+  <si>
+    <t>《诗经·小雅·南山有台》篇中说:“快乐的君子，是人民的父母。”人民喜爱的他就喜爱，人民憎恶的他就憎恶，这样的国君才称得上是人民的父母。</t>
+  </si>
+  <si>
+    <t>本节引《诗·小雅·南山有台》“乐只君子，民之父母”说明能絜矩的效验。君子居民之上而有君之尊，何以称父母？因为君子能以民心为己心：百姓所喜好的饱暖安逸，君子因其所好而好之，务使其各得其所；百姓所憎恶的饥寒劳苦，君子因其所恶而恶之，务使其得免于患。\n\n与民同其好恶，如父母爱子，百姓爱戴君子也如爱父母。执政者无论职位高低，都应心系百姓疾苦、为人民的利益着想，才配得上“民之父母”。</t>
+  </si>
+  <si>
+    <t>传第九章(9-3)</t>
+  </si>
+  <si>
+    <t>《诗》云：“节彼南山，维石岩岩。赫赫师尹，民具尔瞻。”有国者不可以不慎，辟，则为天下僇（lù）矣。</t>
+  </si>
+  <si>
+    <t>《诗经·小雅·节南山》篇中说:“雄伟高大的终南山，山崖险峻不可攀。权势显赫的太师，民众瞩目。”所以拥有国家大权的人，不可以不谨慎，如果你有所偏私，就会被天下人民所讨伐了。</t>
+  </si>
+  <si>
+    <t>本节引《诗·小雅·节南山》说明不能絜矩的祸害。诗人讥刺太师尹氏势位赫赫如高山，百姓都瞻仰着他，却好恶不公、罔上行私，以致天下大乱。曾子解说：有国家者既为民所瞻仰，必须常常谨慎、凡事合乎人心。\n\n若不能絜矩，只徇一己之偏，民所好的不从民便、民所恶的不肯体恤，天下人都生怨恨，必然众叛亲离，身与国不能保守，所以说“辟则为天下僇矣”。民心向背如水能载舟亦能覆舟，执政者不可不慎。</t>
+  </si>
+  <si>
+    <t>传第九章(9-4)</t>
+  </si>
+  <si>
+    <t>《诗》云：“殷之未丧师，克配上帝。仪监（jiàn）于殷，峻命不易。”道得众则得国，失众则失国。是故君子先慎乎德。有德此有人，有人此有土，有土此有财，有财此有用。德者本也，财者末也。外本内末，争民施夺。是故财聚则民散，财散则民聚。是故言悖而出者，亦悖而入；货悖而入者，亦悖而出。</t>
+  </si>
+  <si>
+    <t>《诗经·大雅·文王》篇说:“殷朝还没有丧失大众民心的时候，能够得到上天的保佑；应当用殷朝的兴亡作为鉴戒，认识到长保天命并非容易的事。”这是说，得到民众的承认和拥护就能保有国家；失去民众的承认和拥护就会失去国家。所以大人君子首先要在道德上谨慎从事。有了道德这才会有人民，有了人民这才会有土地，有了土地这才会有财富，有了财富这才会有用度。道德是根本，财富是末节。假若轻根本而重末节，那么争利的人民就要横施掠夺之术了。所以，国君聚敛财富，就将迫使人民离散;国君散发财富，就将激励人民聚集。所以，话悖逆情理地说出，也就有悖逆情理的话来回报;财富悖逆情理地敛人，也就要悖逆情理地散出。</t>
+  </si>
+  <si>
+    <t>本节释“得众则得国，失众则失国”并落到“德者本也，财者末也”。《诗》以殷为鉴：殷先世未失众人时能配上帝、受天命，后世子孙失人心而天命去之；为人君者能絜矩则得众得国，不能絜矩则失众失国。所以君子先慎乎德，有德则有人，有人则有土，有土则有财，有财则有用。\n\n德为本、财为末，外本内末就会争民施夺；财聚则民散，财散则民聚；言语悖出者亦悖入，财货悖入者亦悖出。治国当以修德得人心为根本，不可把聚财放在首位。</t>
+  </si>
+  <si>
+    <t>传第九章(9-5)</t>
+  </si>
+  <si>
+    <t>《康诰》曰：“惟命不于常。”道善则得之，不善则失之矣。</t>
+  </si>
+  <si>
+    <t>《尚书·康诰》篇中说:“惟有天命是不常留驻的。”国家实行仁政则会得到天命，倒行逆施就会失去天命。</t>
+  </si>
+  <si>
+    <t>本节引《康诰》“惟命不于常”总结絜矩得失与天命人心。《康诰》说上天的命或去或留不可为常，曾子解说：为君者能絜矩、散财以得民心，便得了天命，是得众则得国；不能絜矩、聚财以失民心，便失了天命，是失众则失国。\n\n天命以人心为依归，得人心者得天命，失人心者失天命；天命不常，所以人君不可外本内末，务必慎德以尽絜矩之道。</t>
+  </si>
+  <si>
+    <t>传第九章(9-6)</t>
+  </si>
+  <si>
+    <t>《楚书》曰：“楚国无以为宝，惟善以为宝。”舅犯曰：“亡人无以为宝，仁亲以为宝。”</t>
+  </si>
+  <si>
+    <t>《楚书》上记载楚大夫王孙圈出使晋国，在宴会上回答晋国执政大臣赵简子时说:“楚国没有物件可以当作宝贝的，只把善人当作宝贝。”晋公子重耳流亡到秦国，秦穆公劝他兴兵回国夺取大位，重耳的舅父狐子犯教他回答说:“流亡在外的人，没有什么物件可以当作宝贝的，只把对父亲的热爱当作宝贝。”</t>
+  </si>
+  <si>
+    <t>本节引《楚书》与舅犯之言，说明“不外本而内末”的治国观。《楚书》载楚国王孙圉对晋国赵简子说：楚国不以金玉珠石为宝，只以能利生民、安社稷的善人为宝；舅犯教晋文公对秦穆公说：出亡之人不以富贵为宝，而以仁亲为宝。\n\n楚国所宝在善人而不在金玉，晋文公所宝在爱亲而不在得国，都是重根本、轻末利。为政在人，人的根本在德，这是儒家“以德为政治运作基础”的体现。</t>
+  </si>
+  <si>
+    <t>传第九章(9-7)</t>
+  </si>
+  <si>
+    <t>《秦誓》曰：“若有一个臣，断断兮无他技，其心休休焉，其如有容焉。人之有技，若己有之；人之彦圣，其心好之，不啻（chì）若自其口出。实能容之，以能保我子孙黎民，尚亦有利哉！人之有技，媢（mào）疾以恶之；人之彦圣，而违之俾（bǐ）不通。实不能容，以不能保我子孙黎民，亦曰殆哉！”唯仁人放流之，迸（bǐng）诸四夷，不与同中国。此谓唯仁人为能爱人，能恶人。见贤而不能举，举而不能先，命也；见不善而不能退，退而不能远，过也。好人之所恶，恶人之所好，是谓拂人之性，菑（zāi）必逮（dài）夫身。是故君子有大道，必忠信以得之，骄泰以失之。</t>
+  </si>
+  <si>
+    <t>《尚书:秦誓》中说:“假如有一个臣子，老老实实而没有其他技能，他的心胸宽广，大有容人之量。别人有技能，就好像他自己有技能一样;别人贤良明智，他由衷地喜爱人家，不仅仅像他口中说出的那样，他确实能够容人。任用他能保护我的子孙和黎民，也还是有利的呀!假如别人有技能，他就心生妒忌，厌恶人家;别人贤良明智，他就压制阻挠，使人家的功绩不能通达于君上，他确实是不能容人。任用他就不能保护我的子孙和黎民，也可说是危险哩!”只有仁德的国君才会把这种人流放，驱逐到四方蛮夷之地，不与他们同住在中原。这就叫做只有仁德的国君才真能爱护好人，才真能憎恨坏人。发现了贤人而不能举荐，或者举荐了而不能提前任用，这就是怠慢了。发现了不善的人而不能黜退，或者黜退了而不能把他驱逐到远方，这就是过错了。作为国君竟喜爱人们所憎恶的，憎恶人们所喜爱的，这就叫做违背人的本性，灾祸必将降临他的身上。君子当政临国自有正道，必然是:忠信诚实就能得到它，骄恣放肆就要失掉它。</t>
+  </si>
+  <si>
+    <t>本节以《秦誓》论用人与好恶之公，是平天下的大关键。能容贤的大臣，断断然诚一，心休休然宽弘，见人有技若己有之，见人彦圣衷心好之，用他能保子孙黎民；妒贤嫉能之臣，见人有技则媢疾以恶之，见人彦圣则违之俾不通，用他则乱亡随之。所以仁人能爱人能恶人，把嫉贤妒能者放流到四夷，不与同中国。\n\n见贤不能举、举而不能先，是慢；见不善不能退、退而不能远，是过。好人之所恶、恶人之所好，是拂人之性，灾必逮夫身。君子有大道的得失全在存心：忠信以得之，骄泰以失之。用人之公正是絜矩在人才上的体现。</t>
+  </si>
+  <si>
+    <t>传第九章(9-8)</t>
+  </si>
+  <si>
+    <t>生财有大道：生之者众，食之者寡，为之者疾，用之者舒，则财恒足矣。仁者以财发身，不仁者以身发财。未有上好仁而下不好义者也，未有好义其事不终者也，未有府库财非其财者也。孟献子曰：“畜马乘（shèng），不察于鸡豚（tún）；伐冰之家，不畜牛羊；百乘之家，不畜聚敛之臣。与其有聚敛之臣，宁有盗臣。”此谓国不以利为利，以义为利也。长国家而务财用者，必自小人矣。彼为善之，小人之使为国家，菑（zāi）害并至。虽有善者，亦无如之何矣！此谓国不以利为利，以义为利也。</t>
+  </si>
+  <si>
+    <t>生产财富有重大原则。生产财物的人多，消费财物的人少，创造财物的人生产迅速，使用财物的人消费舒缓，那么国家的财物自然就能常常充足了。仁德的人利用财富来发扬自身的理想，不仁的人却滥用自身的条件去拼命地发财。没有上面的君长爱好仁德而下面的臣民不爱好道义的，没有臣民爱好道义而国事半途而废的，也没有臣民爱好道义而府库的财货竟不属于国家所有的。鲁国大夫孟献子说:“具备马匹车辆的士大夫之家，就不该去计较喂鸡喂猪的小利;有资格伐冰备用的大夫之家，就不该饲养牛羊去牟利;拥有百辆兵车的有领地的卿大夫之家，就不该养活那聚敛民财的家臣。与其有这种聚敛民财的家臣，还不如有偷盗自家财物的小臣。”这就是说，国君治理国家不能以私利为利益，而应该以道义为利益。统管国家而致力于聚敛财富的国君，必定是来自小人的怂恿，而那国君认为他的主意好，使小人来治理国家，那么天灾人祸就会一起到来。到那时，即使有贤能的人接管，也无可奈何了。这就是说，治理国家不能以私利为利益，而应该以道义为利益。</t>
+  </si>
+  <si>
+    <t>本节讲生财有大道，即“生之者众，食之者寡，为之者疾，用之者舒”，开源节流、量入为出，财用自然恒足，这是经国久远的规模。仁者以财发身，散财于民而得民心；不仁者以身发财，聚财于上而丧身亡国。上好仁则下好义，下好义则事有终、府库之财可保。\n\n孟献子说畜马乘之家不察鸡豚、伐冰之家不畜牛羊、百乘之家不畜聚敛之臣，宁有盗臣而无聚敛之臣，因为聚敛伤民之命，此谓国不以利为利、以义为利。长国家而专务财用必自小人始，小人为国家则灾害并至，虽有善者也无可奈何。治国平天下的大要在絜矩，絜矩之大事在用人理财，而其本在于慎德、忠信。</t>
+  </si>
 </sst>
 </file>
 
@@ -1117,13 +1472,12 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1131,7 +1485,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0F1115"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1147,27 +1506,22 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1175,15 +1529,13 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1191,7 +1543,6 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1199,7 +1550,6 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1207,88 +1557,63 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1348,19 +1673,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1372,19 +1697,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1396,19 +1721,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1420,19 +1745,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1444,19 +1769,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1468,19 +1793,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1522,7 +1847,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1611,52 +1936,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
@@ -1671,10 +1996,10 @@
     <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
@@ -1683,10 +2008,10 @@
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
@@ -1695,10 +2020,10 @@
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
@@ -1707,10 +2032,10 @@
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
@@ -1719,10 +2044,10 @@
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
@@ -1731,17 +2056,17 @@
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1749,21 +2074,36 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2082,76 +2422,16 @@
         <a:srgbClr val="7E1FAD"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="WPS">
@@ -2175,9 +2455,7 @@
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr"/>
@@ -2187,27 +2465,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:gradFill>
             <a:gsLst>
               <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
+                <a:schemeClr val="phClr"/>
               </a:gs>
               <a:gs pos="100000">
                 <a:schemeClr val="phClr"/>
@@ -2216,7 +2490,6 @@
             <a:lin ang="2700000" scaled="1"/>
           </a:gradFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -2259,17 +2532,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -2294,1437 +2567,1960 @@
   <dimension ref="A1:F83"/>
   <sheetFormatPr defaultColWidth="23.75" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="15.287037037037" style="3" customWidth="1"/>
-    <col min="2" max="2" width="50" style="2" customWidth="1"/>
-    <col min="3" max="3" width="56.8796296296296" style="2" customWidth="1"/>
-    <col min="4" max="4" width="75.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="7.37962962962963" style="2" customWidth="1"/>
-    <col min="6" max="16380" width="23.75" style="2" customWidth="1"/>
-    <col min="16381" max="16384" width="23.75" style="2"/>
+    <col min="1" max="1" width="21" style="8" customWidth="1"/>
+    <col min="2" max="2" width="68.2222222222222" style="6" customWidth="1"/>
+    <col min="3" max="3" width="60.6666666666667" style="6" customWidth="1"/>
+    <col min="4" max="4" width="75.25" style="6" customWidth="1"/>
+    <col min="5" max="5" width="7.37962962962963" style="6" customWidth="1"/>
+    <col min="6" max="16380" width="23.75" style="6" customWidth="1"/>
+    <col min="16381" max="16384" width="23.75" style="6"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="372.6" spans="1:6">
-      <c r="A2" s="5" t="s">
+    <row r="2" s="6" customFormat="1" ht="317.4" spans="1:6">
+      <c r="A2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" ht="151.8" spans="1:6">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" ht="151.8" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" ht="151.8" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" ht="151.8" spans="1:6">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" ht="151.8" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" ht="124.2" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" ht="151.8" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" ht="179.4" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" ht="138" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" ht="151.8" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" ht="138" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" ht="151.8" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" ht="151.8" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" ht="179.4" spans="1:6">
-      <c r="A16" s="5" t="s">
+    <row r="16" ht="165.6" spans="1:6">
+      <c r="A16" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" ht="207" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" ht="151.8" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" ht="165.6" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" ht="138" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" ht="151.8" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="22" ht="179.4" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="23" ht="165.6" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" ht="165.6" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="25" ht="151.8" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" ht="151.8" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="27" ht="165.6" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="28" ht="165.6" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" ht="179.4" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="30" ht="165.6" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="31" ht="165.6" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="32" ht="165.6" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="33" ht="165.6" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" ht="165.6" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="35" ht="151.8" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" ht="151.8" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="37" ht="151.8" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="38" ht="165.6" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E38" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" ht="138" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="40" ht="193.2" spans="1:5">
-      <c r="A40" s="5" t="s">
+    <row r="40" ht="179.4" spans="1:5">
+      <c r="A40" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="41" ht="165.6" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="42" ht="151.8" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="43" ht="409.5" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="44" ht="409.5" spans="1:5">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="45" ht="409.5" spans="1:5">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="46" ht="409.5" spans="1:5">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="47" ht="409.5" spans="1:5">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D47" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="48" ht="409.5" spans="1:5">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E48" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="49" ht="409.5" spans="1:5">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="E49" s="6" t="s">
+      <c r="E49" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="50" ht="409.5" spans="1:5">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="E50" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="51" ht="409.5" spans="1:5">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="E51" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="52" ht="409.5" spans="1:5">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="E52" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="53" ht="409.5" spans="1:5">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D53" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E53" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="54" ht="409.5" spans="1:5">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="D54" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="E54" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="55" ht="400.2" spans="1:5">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="D55" s="7" t="s">
+      <c r="D55" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="E55" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="56" ht="409.5" spans="1:5">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="D56" s="7" t="s">
+      <c r="D56" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="E56" s="6" t="s">
+      <c r="E56" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="57" ht="409.5" spans="1:5">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="D57" s="7" t="s">
+      <c r="D57" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="E57" s="6" t="s">
+      <c r="E57" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="58" ht="372.6" spans="1:5">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="D58" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="E58" s="6" t="s">
+      <c r="E58" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="59" ht="409.5" spans="1:5">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="D59" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="E59" s="6" t="s">
+      <c r="E59" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="60" ht="409.5" spans="1:5">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="D60" s="7" t="s">
+      <c r="D60" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="E60" s="6" t="s">
+      <c r="E60" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="61" ht="409.5" spans="1:5">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="D61" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="E61" s="6" t="s">
+      <c r="E61" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="62" ht="409.5" spans="1:5">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="D62" s="7" t="s">
+      <c r="D62" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="E62" s="6" t="s">
+      <c r="E62" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="63" ht="409.5" spans="1:5">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="D63" s="7" t="s">
+      <c r="D63" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="E63" s="6" t="s">
+      <c r="E63" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="64" ht="409.5" spans="1:5">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="D64" s="7" t="s">
+      <c r="D64" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="E64" s="6" t="s">
+      <c r="E64" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="65" ht="409.5" spans="1:5">
-      <c r="A65" s="5" t="s">
+      <c r="A65" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B65" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="D65" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="E65" s="6" t="s">
+      <c r="E65" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="66" ht="409.5" spans="1:5">
-      <c r="A66" s="5" t="s">
+      <c r="A66" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="B66" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="D66" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="E66" s="6" t="s">
+      <c r="E66" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="67" ht="345" spans="1:5">
-      <c r="A67" s="5" t="s">
+      <c r="A67" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C67" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="D67" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="E67" s="6" t="s">
+      <c r="E67" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="68" ht="409.5" spans="1:5">
-      <c r="A68" s="5" t="s">
+      <c r="A68" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="B68" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C68" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="D68" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="E68" s="6" t="s">
+      <c r="E68" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="69" ht="409.5" spans="1:5">
-      <c r="A69" s="5" t="s">
+      <c r="A69" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="B69" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="C69" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="D69" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="E69" s="6" t="s">
+      <c r="E69" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="70" ht="409.5" spans="1:5">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="B70" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="C70" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="D70" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="E70" s="6" t="s">
+      <c r="E70" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="71" ht="409.5" spans="1:5">
-      <c r="A71" s="5" t="s">
+      <c r="A71" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="B71" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="C71" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="D71" s="7" t="s">
+      <c r="D71" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="E71" s="6" t="s">
+      <c r="E71" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="72" ht="409.5" spans="1:5">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B72" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="C72" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="D72" s="7" t="s">
+      <c r="D72" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="E72" s="6" t="s">
+      <c r="E72" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="73" ht="409.5" spans="1:5">
-      <c r="A73" s="5" t="s">
+      <c r="A73" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="B73" s="7" t="s">
+      <c r="B73" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="C73" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="D73" s="7" t="s">
+      <c r="D73" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="E73" s="6" t="s">
+      <c r="E73" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="74" ht="358.8" spans="1:5">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="B74" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="C74" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="D74" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="E74" s="6" t="s">
+      <c r="E74" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="75" ht="409.5" spans="1:5">
-      <c r="A75" s="5" t="s">
+      <c r="A75" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B75" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="C75" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="D75" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="E75" s="6" t="s">
+      <c r="E75" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="76" ht="400.2" spans="1:5">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="D76" s="7" t="s">
+      <c r="D76" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="E76" s="6" t="s">
+      <c r="E76" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="77" ht="386.4" spans="1:5">
-      <c r="A77" s="5" t="s">
+      <c r="A77" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="B77" s="12" t="s">
         <v>311</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C77" s="12" t="s">
         <v>312</v>
       </c>
-      <c r="D77" s="7" t="s">
+      <c r="D77" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="E77" s="6" t="s">
+      <c r="E77" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="78" ht="409.5" spans="1:5">
-      <c r="A78" s="5" t="s">
+      <c r="A78" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="B78" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="C78" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="D78" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="E78" s="6" t="s">
+      <c r="E78" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="79" ht="400.2" spans="1:5">
-      <c r="A79" s="5" t="s">
+      <c r="A79" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="B79" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="C79" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="D79" s="7" t="s">
+      <c r="D79" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="E79" s="6" t="s">
+      <c r="E79" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="80" ht="409.5" spans="1:5">
-      <c r="A80" s="5" t="s">
+      <c r="A80" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="B80" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="C80" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="D80" s="7" t="s">
+      <c r="D80" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="E80" s="6" t="s">
+      <c r="E80" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="81" ht="409.5" spans="1:5">
-      <c r="A81" s="5" t="s">
+      <c r="A81" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="B81" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="C81" s="7" t="s">
+      <c r="C81" s="12" t="s">
         <v>328</v>
       </c>
-      <c r="D81" s="7" t="s">
+      <c r="D81" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="E81" s="6" t="s">
+      <c r="E81" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="82" ht="409.5" spans="1:5">
-      <c r="A82" s="5" t="s">
+      <c r="A82" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="B82" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="C82" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="D82" s="7" t="s">
+      <c r="D82" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="E82" s="6" t="s">
+      <c r="E82" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="83" ht="409.5" spans="1:5">
-      <c r="A83" s="5" t="s">
+      <c r="A83" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="B83" s="7" t="s">
+      <c r="B83" s="12" t="s">
         <v>335</v>
       </c>
-      <c r="C83" s="7" t="s">
+      <c r="C83" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="D83" s="7" t="s">
+      <c r="D83" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="E83" s="6" t="s">
+      <c r="E83" s="11" t="s">
         <v>165</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D83" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr defaultColWidth="15.8796296296296" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="17.6481481481481" customWidth="1"/>
+    <col min="2" max="2" width="51.8240740740741" style="2" customWidth="1"/>
+    <col min="3" max="3" width="55.8240740740741" style="2" customWidth="1"/>
+    <col min="4" max="4" width="75.25" customWidth="1"/>
+    <col min="5" max="6" width="28.5" customWidth="1"/>
+    <col min="7" max="16384" width="15.8796296296296" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="145.2" customHeight="1" spans="1:6">
+      <c r="A2" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" ht="132" customHeight="1" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" ht="105.6" customHeight="1" spans="1:6">
+      <c r="A4" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" ht="92.4" customHeight="1" spans="1:6">
+      <c r="A5" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" ht="118.8" customHeight="1" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" ht="92.4" customHeight="1" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" ht="118.8" customHeight="1" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" ht="118.8" customHeight="1" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" ht="79.2" customHeight="1" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" ht="118.8" customHeight="1" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" ht="105.6" customHeight="1" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" ht="105.6" customHeight="1" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" ht="105.6" customHeight="1" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" ht="92.4" customHeight="1" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" ht="105.6" customHeight="1" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" ht="92.4" customHeight="1" spans="1:6">
+      <c r="A17" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" ht="79.2" customHeight="1" spans="1:6">
+      <c r="A18" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" ht="79.2" customHeight="1" spans="1:6">
+      <c r="A19" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" ht="92.4" customHeight="1" spans="1:6">
+      <c r="A20" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" ht="118.8" customHeight="1" spans="1:6">
+      <c r="A21" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" ht="92.4" customHeight="1" spans="1:6">
+      <c r="A22" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" ht="92.4" customHeight="1" spans="1:6">
+      <c r="A23" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" ht="105.6" customHeight="1" spans="1:6">
+      <c r="A24" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" ht="79.2" customHeight="1" spans="1:6">
+      <c r="A25" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" ht="92.4" customHeight="1" spans="1:6">
+      <c r="A26" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" ht="118.8" customHeight="1" spans="1:6">
+      <c r="A27" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" ht="132" customHeight="1" spans="1:6">
+      <c r="A28" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F28" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/book.xlsx
+++ b/book.xlsx
@@ -4,12 +4,16 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25068" windowHeight="13380" activeTab="1"/>
+    <workbookView windowWidth="25068" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="道德经" sheetId="1" r:id="rId1"/>
     <sheet name="大学" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">道德经!$A$1:$F$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">大学!$A$1:$F$28</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -28,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="462">
   <si>
     <t>chapter</t>
   </si>
@@ -93,7 +97,7 @@
     <t>道经</t>
   </si>
   <si>
-    <t>第二章、第三章、第四章</t>
+    <t>第四章</t>
   </si>
   <si>
     <t>第二章（2）</t>
@@ -109,6 +113,9 @@
 因此圣人处无为之事，行不言之教：越是懂得有为，越要知道哪些该无为、该舍掉，从反面认识事情，才能达到更好的有为效果，千万不要把无为理解成消极。万物作焉而不辞，生而不有，为而不恃，功成而弗居：顺应万物自然生长而不干预，创造而不占有，做事而不依仗，有功而不居功，正因不居功，功德才不离去。本章后文许多重要内容提前概括出来，读熟这一章，后面很多章节都能以经解经。</t>
   </si>
   <si>
+    <t>第十一章、第三十九章、第六十三章、第六十六章</t>
+  </si>
+  <si>
     <t>第三章（3）</t>
   </si>
   <si>
@@ -200,6 +207,9 @@
 译者·韩鹏杰用民间故事讲这个道理：弟弟只拿一点金子平安回家，哥哥贪心装满全身，被太阳晒化。第七章讲先后，第八章讲不争，第九章讲不盈，都提醒人知进退、懂谦让。中国文化的“中”就是恰到好处，不走到极端：物极必反、乐极生悲、泰极否来，好事到了极端容易向坏处转化，所以要战战兢兢、如履薄冰地把握分寸。</t>
   </si>
   <si>
+    <t>第七十八章</t>
+  </si>
+  <si>
     <t>第十章（10）</t>
   </si>
   <si>
@@ -224,6 +234,9 @@
   <si>
     <t>本章讲“无”的作用，用三个日常形象说明虚空的巨大价值。三十辐共一毂，当其无，有车之用：车轮有三十根辐条，车毂中间是空的，车轮才能转动，才有车的功用。埏埴以为器，当其无，有器之用：黏土烧成器皿，中间是空的，才能盛水装物。凿户牖以为室，当其无，有室之用：开凿门窗建成房屋，中间是空的，人才能居住。有之以为利，无之以为用：实体提供便利条件，虚空成就实际功用，有与无相互成全。
 译者·韩鹏杰指出，“利用”这个词就来自本章。第十章讲虚静，本章讲怎样虚静——心里放空，去掉杂念，才能听得进别人的意见、看得见别人的长处、学得到别人的优点，虚怀若谷、满招损谦受益。中国文化的悟道方式是“给一个形象，自己领悟”，本章就是最好的示范：通过车、器、室三个形象，让人领悟空与用的道理。</t>
+  </si>
+  <si>
+    <t>第二章</t>
   </si>
   <si>
     <t>第十二章（12）</t>
@@ -888,6 +901,9 @@
     <t>第六十三章的内容，我们在前边已经有所接触。之前我们说，第二章就是《道德经》的“目录”，第二章列出来了后边讲的六个重要内容，有无相生、难易相成等等，这一章的核心就是“难”和“易”。这一章的核心意思就说，要想做大事，先从小事做起，想要以后攻坚克难，你得从容易的事情做起。还有一个重要的问题、重要的智慧：你要把容易的事情当作难的事情来做，要有充分的、认真的准备，提前思考它的步骤、程序、会遇到的问题，这样再出什么问题的时候，你就能从容应对。有这样的态度，天下也没什么难事。天下无难事，但天下都是难事，看你怎么对待。开头这九个字非常有趣：“为无为，事无事，味无味。”“为无为”——想要有为吗？你得先懂得无为的道理。为什么？因为有些事你越有为，越强求，什么事都管，反而最后结果非常不好。道家讲的无为，就是按照道的方式来作为，想要有为，先要懂得无为的道理，不要妄为，要抓住关键，举重若轻，有所舍才能有所得，所以为无为。其实也就是第三十七章里边讲的“道常无为而无不为”，道的规律、规则是什么？用无为的方式达到无不为的效果，更好的效果。我再强调一下，《道德经》里出现得最多的一个词是“天下”。《道德经》针对的是天下，千万不要把道家当作一种消极的被动的思想，它是“想为”，但是强调要通过正确的道路和手段，懂得无为的正确的道路和手段，才能达到真正的有效的为，也就是用无为的方式，达到无不为的这种效果。下边再落一层，“事无事”。大家都想做事，可是大家有没有注意到，有些人他是“找事”，他是捣乱，是阻碍、多事，天下本无事，庸人自扰之。所以我们做事的时候要懂得无事的道理，不要多事，不要找事，不要刁难。尤其是做领导者，没事找事，权力就是刁难，你这不就麻烦了吗？“事无事”，想做事，得懂得无事的道理，不要多事，不要扰民。再落一层，“味无味”。我们经常讲一个词叫“真水无香”，真正好的饮料，就像那白开水一样，没有味道。我们饮食讲究清淡，寡味，少油少盐。最高的味道，反而是没有味道，无味。当然，这三个词核心还是“为无为”，让大家能够更明白一点。老子展开来讲，“事无事”，不要多事，不要扰民，不要刁难，就像“味无味”的道理一样。按照这样的一个逻辑推下来，下面四个字大家就能明白了，“大小、多少”，千万不要把它念成“大小多少”，这个东西就没意义了。这是告诉大家要“大其小”、要“多其少”，要把小事看得很重要，细节决定成败，千万不要忽略这个细节。为什么要“大其小”呢？因为天下的大事，都是从小事做起，为什么要“多其少”呢？因为积少才能成多。想要多，你得从少的一点一点积累，积少成多。就像我们学习《道德经》，一章一章讲，一章一章学，不要着急，最后达到一个整体的理解。我们经常讲“聚沙成塔”、“集腋成裘”，这不都是“多其少”的道理吗？“报怨以德”，按照这种相反相成的道理，对别人的埋怨、恩怨，也应该站在一个“德”的角度，因为德是符合道，用道的东西里面去感化。第六十二章不是讲了吗？“人之不善，何弃之有？”人家有这个埋怨，怎么正确地对待呢？“报怨以德”。用这种智慧和层次，让大家一起能回归到正途，回归到正道。“图难于其易，为大于其细。天下难事必作于易，天下大事必作于细。”这几句话，在我们文化里边名气非常大，因为讲的是哲学上的量的积累达到质的变化的道理。“图难于其易”，“图”就是图谋、计划。你计划想要做难的事情，要从容易的事情做起。“为大于其细”，想要做大的事情，得从小的事情一步一步来。我们大家都知道要脚踏实地，循序渐进，有条不紊，一屋不扫，何以扫天下？“天下难事必作于易”，天下所有的难事，都要从容易的事情做起。就像小孩的培养，让他们在处理小的事情中就形成良好的习惯，把小的事情、容易的事当成培养良好习惯的重要途径，将来，小孩在遇到大事、难事都能从容应对。现在很多人都有一个致命的弱点，大概是人的通病，就是好高骛远，老觉得自己应该是做大事的人，对小的事情不屑一顾。《道德经》就告诉我们这个智慧：想要做难的事情，从容易的事情做起；想要做大的事情，从小的事情做起，“天下大事必作于细”。“是以圣人终不为大，故能成其大。”“是以”，“是”就是这样，“以”就是所以。所以有智慧的领导者就是这样：“终不为大”，不是老说大话，不是老给大家画饼充饥，而是脚踏实地，一步一步地做起，“故能成其大”。一步一步把这个事情完成了，一步一步地完成计划，最后实现一个大的蓝图，好的结果，水到渠成。所以一个有智慧的人，不是老用那些虚幻的东西来画饼充饥，老是给大家讲大话、空话。“终不为大，故能成其大”，最后反而成就了大事，这话讲得非常好。我建议大家学习《道德经》，有一种重要的学习方法，就是反复看。有的人看《道德经》，也许一年就看一章，反复地看，反复地体会，“少则得，多则惑”，“终不为大，故能成其大”。以管窥天，以锥扎地，我们视力更集中，这样把这个事情才能做得更踏实，扎得更透。我们每一次的进步，虽然看起来好像只是一点点，但是这一点点积累起来就不得了了，“终不为大，故能成其大”。“轻诺必寡信”，大家还记得我们在讲《道德经》第八章的时候，就讲过“言善信”，我们中国人喜欢拿潮水作为讲信用的代表和象征，所以，有一个词就叫“潮信”。你看那钱塘潮每到农历八月十八前后就来了，人也应该如此，说话要讲信用，要有诚信，能给别人做成的事我们再去允诺，没把握做成的事，不要轻易去答应，不管我们有多热情。如果我们答应人家的很多事最后都做不成，时间长了，人家一定认为我们是食言而肥，不讲信用。《道德经》讲话是比较宽缓的，但这句话用的就是强逻辑判断，“轻诺必寡信”，这不是对我们委婉的劝告，这简直就是对我们严厉的警告。所以要讲诚信，君子重一诺，一诺千金嘛，所以“轻诺必寡信”，要避免这种结果出现。“多易必多难”，你把这个事情看得很容易，做什么事情，最后一定出问题。世界上哪有容易的事情，吃个饭喝个水，这都需要功夫，需要本事，小事情我们都要认真对待。我们经常讲“小河沟里翻船”，把一个事情看得太容易了，太简单了，往往会在这个事情上出问题。面对很多难的事情，大家战战兢兢，小心谨慎，反而没事，反而就是在一些认为最容易的事情出问题。很多学生做题、考试也是一样，难题没事，在容易的题上，出了问题，回去捶胸顿足，懊悔无比。所以，我们平常要形成一种把容易的事情当作难的事情来做的习惯，你要懂得“多易必多难”，凡事太容易，后面一定会出现很多的困难，出现很多的问题。所以，下边这句话就讲：“是以圣人犹难之”，所以有智慧的人，把这容易的事情都看作很难。天下的事情都当作难的事情来做，反而结果没有什么难的事情，“故终无难矣”。这个道理非常有趣，其实就是相反相成的道理，这个叫“难易相成”。世界上有没有难事呢？有，也没有。你把这个难的事情当作难的事情，看作是无法克服的，它就是难的事情；你把容易的事情当作容易的事情，没有认真对待，最后也会变成难的事情。我们把容易的事情当作难的事情来做，最后那个难的事也就做成了；真正难的事情，我们认真准备，有充分的信心，最后这难的事情也就克服了。“故终无难矣！”世上无难事，这就是“难易相成”的智慧。很多事情，决定于我们的想法、态度，态度不同，难易之间就会相互转化。</t>
   </si>
   <si>
+    <t>第二章、第六十四章</t>
+  </si>
+  <si>
     <t>第六十四章（64）</t>
   </si>
   <si>
@@ -900,6 +916,9 @@
     <t>第六十三章、第六十四章讲的道理，就是大家熟悉的量变和质变的道理，量的积累达到质的变化。但是大家注意，这个量的积累，有向好的方面，也有向不好的方面。前面讲了“为大于其细”，要做大事，从小的事情做起，这样才能最后达到想要的结果，假如积累的是一个不好的量，最后就积重难返。第六十四章一开始就要把两个方面，都给大家做了说明，有的事情在它刚出现向坏的方面发展苗头的时候，我们在这个阶段就把它解决了。这一章里有两个非常重要的内容，一个是大家都熟悉的一段话：“合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。”第二个就告诉我们，做事情要“慎终如始，则无败事”。这两个重要内容，我们先有一个直观的认识，再来读就好理解了。我们一句一句来解释。“其安易持”，“安”就是稳定，局面稳定的时候，容易掌控，就像一个东西，它稳定的时候，你容易把它把握住；它活蹦乱跳的时候，你把握起来就困难了。“其未兆易谋”，“未兆”，没有征兆的时候，苗头还没有开始的时候，容易去谋划。“其脆易泮”，脆的时候一打就打散了。“其微易散”，很微小的时候，很容易把它解散。比如说一件事情，很小的时候，人数很少的时候，你把它处理起来很容易。众怒难犯，一大群人轰起来、闹起来的时候，这事情解决起来就困难。前面告诉大家这些现象，然后告诉大家处理的方法。什么方法呢？“为之于未有”——在事情没有出现的时候，没有开始的时候，要有预见性，就要有作为，凡事预则立，不预则废。“治之于未乱”，还没有出现这种乱象的时候，就把它治理了、解决了。这也是习近平讲话时经常引用的两句话。怎么来理解呢？先给大家说第一个例证。有一次晏子出巡，齐国发大水，把一座石桥给冲毁了，晏子就把自己的船让给了灾民，大家都赞誉晏子爱民如子。然而一位有智慧的高人就批评晏子，就说你做这个国家的宰相，齐国发大水能把一座桥梁冲毁，你都没有预见到，没有提前做出预防，你失职。所以应该是怎么样？“为之于未有”，你别等这个事情都已经成为这个样子，再去处理它，不管你处理的方式多么巧妙，多么有智慧，但是不如让这件事情没有发生。另外一个例证更能说明这个道理。有一次，扁鹊的国王问扁鹊：扁鹊你名气太大了，你是不是国家医术最高的？扁鹊说不是，别人我不知道，起码我大哥、我二哥都比我的医术高。所以这个国王就很奇怪，你大哥、你二哥是谁？他们医术那么高，怎么大家都不知道他们呀？扁鹊就说，我大哥怎么治病的呢？人家还没有病，他告诉人家怎么预防、怎么不得病。这不是“为之于未有”吗？提前就有作为了，预防得病。我二哥怎么治病的呢？人家刚有一点小病，他就把人治好了，不让他酿成大病，“治之于未乱”。所以我们经常讲，凡事预则立，不预则废，要有远见，要有预见，要未雨绸缪。这是讲负面，因为有些事情量的积累是向不好的方面发展的，所以要提前把这个问题给处理掉。下面讲的这个事，非常重要。我们做大事情都要从容易的事情、小的事情，一步一步积累才能达到这种质的变化，要脚踏实地，循序渐进。因为什么呢？“合抱之木，生于毫末”，合抱之木，它是一点一点长起来的。“九层之台，起于累土”，中国文化中，三六九都代表着高、多。那么高的高台也是一层一层土积累起来的。“千里之行，始于足下”，走这么远的路，要脚踏实地一步一步地做起。说到这里，我得加一句，有人老认为道家思想是消极的、被动的、无为的。“合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。”这不就是自强不息吗？所以有些事我们不能人云亦云，我们得看原文，以原典作为证据。“为者败之，执者失之。”“为”就是强为、妄为。因为《道德经》讲的真正的为叫“无为”，就是按照道的方式来作为，不按照道的方式来作为就是强为、妄为。越是强为，最后的结果越糟糕，因为量的积累还不到，你老想强行地发生质变，这不是急躁冒进吗？“执者失之”，就像我们抓沙子一样，你握得越紧，流出来越多，越想用力地把它抓住，反而失去得越来越快。所以一个有智慧的领导者，“无为”，按照道的方式来作为，不妄为，不强为，不多为，有所不为，所以也不会有急躁冒进的失败。“无执故无失”，没有这样的强执，最后也不会失去。“民之从事”，平常人做事，或者说领着大家做事，在什么时候最容易把事情给做砸了呢？“常于几成而败之”，经常在快要接近成功的时候，把事情给做砸了。那应该怎么办？“慎终如始，则无败事。”什么叫慎终如始呢？我先给大家打一个比方，大家走在结着冰的冰面上的时候，刚一下到冰面上都是小心谨慎，战战兢兢。走一会儿，觉得自己走熟了，就放松警惕了，有的干脆最后开始跑了，有的甚至在冰面上炫耀，危险往往就在这个时候发生了。所以我们中国人经常讲一句话叫“行百里者半九十”，一百里的路，走到九十里路的时候，还要当才走了一半，越是剩下那一段的时候越紧要，民间讲“编筐编篓，全在收口”，即最后这个结尾。“慎终如始”，走到最后那几步，还像开始下到冰面上一样小心谨慎，一步都不放松，那就没什么败事，没什么事情做不成。“慎终如始，则无败事”，就是我们现在经常讲的不忘初心，善始善终，那就没有什么事情做不成的。“是以圣人欲不欲”，一个有智慧的人，特别是一个有智慧的领导者，想要的东西是什么呢？是别人都不关心的，都不想要的。因为“天下熙熙，皆为利来；天下攘攘，皆为利往”，大家关心的是获取利益的方式方法，而一个有智慧的人，有智慧的领导者，应该有这种无功利之心。“欲不欲”，别人都不想这样的，反而是你应该考虑的。大家都针对“有”的东西，这有智慧的人、好的领导者得针对这无形的东西：人的精神财富，人的精神世界，人的修养。既然“欲不欲”，你跟一般人的欲望不一样，他们认为那个东西是珍贵的、难得的，反而在你的眼里是不重要的，不把它看作是难得的。领导国家的时候也是如此，第三章讲的，“不贵难得之货，使民不为盗”，形成一种淳朴的风气。“学不学，复众人之所过。”《道德经》讲的道理，叫“绝学”，一般人不愿意学，学这个东西能带来什么样的好处、利益吗？人的境界高的时候，学的很多的东西不就是和一般人不一样的嘛。一般人不愿意学的东西，又花功夫，又不能带来什么实际的利益，可是“学”这些东西代表了真正的智慧与学问。学这些东西干吗呢？“复众人之所过”，这个“复”不是重复，我们下围棋的人都知道有个词叫“复盘”，通过不断的重复模拟来检视，哪个地方下得好，哪个地方下得不好。别人犯的过错像复盘一样历历在目，以此为鉴，别再犯大家都经常犯的错误。“以辅万物之自然，而不敢为。”“以辅万物之自然”，就是按照自然的规律去做，追求的是一种水到渠成、自然而然的结果。“辅自然”就是无为。“而不敢为”，就是不敢妄为。因为我们违背了道，违背了自然规律，哪怕是短时间取得成功，其实也会受到更大的一种惩罚。这章告诉我们，一是我们做事情要“为之于未有，治之于未乱”，懂得预防，懂得不好的事情在苗头出现的时候就把它解决掉；二是我们做事情要脚踏实地，循序渐进；三是我们要“慎终如始”，不忘初心，善始善终，因为我们做事情经常在快要成功的时候，结果功亏一篑，所以要懂得这样一个道理。</t>
   </si>
   <si>
+    <t>第六十三章</t>
+  </si>
+  <si>
     <t>第六十五章（65）</t>
   </si>
   <si>
@@ -1066,6 +1085,9 @@
   </si>
   <si>
     <t>第七十八章体现了这本书里的一个非常重要的理念，“善于处下”。这些内容我们之前都有过接触，甚至直接引用七十八章做过讲解，所以这一章我们并不需要花费太多的时间来解释，大家也能够明了。“天下莫柔弱于水，而攻坚强者莫之能胜”，天下没有什么东西比水更柔弱了，你拿什么容器装，它就是什么样，随方就圆。但天下也没有什么东西比水的力量更强大了，攻无不克，战无不胜。水就是以柔克刚、以弱胜强的最好的形象的代表。“以其无以易之”，因为没有什么东西能够替代水，天下最柔弱的东西，它力量又最为强大，最能够体现柔弱胜刚强的道理。“弱之胜强，柔之胜刚，天下莫不知，莫能行。”天下都知道，这东西表面上看似柔弱，但发挥作用的时候力量太强大了，但是真的要这样却非常不容易，为什么？人都有脾气，“柔弱胜刚强”得懂得忍耐、等待，忍耐是我们人最难练的一种功夫。水滴锲而不舍方能穿石，一条溪流不舍昼夜，慢慢积累，等待时机，才能发挥大用。“柔弱胜刚强”也是需要条件的，只是老子没有明说。“是以圣人云”，我再给大家强调一下，在老子心里，以前有很多好的统治者、有智慧的领导者，他称其为“圣人”，让大家向他们学习。我们在前面谈到过，他的很多话并不是原创的，是他引用的以前的圣人的，下边这话就表达得非常明确，所以这些圣人讲，“受国之垢”“受国不祥”。这两句话就是《道德经》里边从头至尾强调的，就是我们经常讲的善于处下。古往今来，夺得天下的表面看是一家一姓，实际上不都是一个团队吗？用我们现在的话讲是一个党派。什么样的团队，什么样的党派才能夺得天下，并且坐得了江山呢？之前，我们在第八章讲“处众人之所恶”时，也拿这个地方作为印证。吃苦在前，享受在后，有困难还得担着，有错误勇于改正，这不就是“受国之垢”“受国不祥”吗？所以真正想要夺得天下，坐稳江山，也就是所谓“处其上”，首先要懂得“处其下”，要“受国之垢”，要能忍受别人忍受不了的艰难困苦，要能承受别人承受不了的屈辱诟骂，这样才能成为江山社稷的主人。“受国不祥，是为天下王。”有灾难有困难，你别跑，要挺身而出，勇于担当，有错误要勇于承认，勇于改正。毛泽东把共产党的宗旨概括为五个字，叫“为人民服务”。两千多年前的“受国之垢”，“受国不祥”，“处众人之所恶”，两千多年后的“为人民服务”，这本质上的意思不是一样的吗？这就是《道德经》里面从头强调的，也是古往今来的大道。我们在讲第十四章的时候说过一句话，“执古之道以御今之有”。了解古往今来的大道，我们才能更好地做好今天的事情。读到这儿大家就会发现，这《道德经》里边蕴含着古往今来的大道，蕴含着一个人、一个团队、一个党派成功的最深的密码，值得大家认真地品味。总结上面这个表达的方式叫什么呢？叫“正言若反”，也就是第四十章讲的“反者，道之动”。看着是讲反话，大家都不愿意去做的事情：“受国之垢”，“受国之不祥”，“处众人之所恶”，可实际上，这才是能够让我们“处上”、取得成功的真正的智慧与奥妙。看似好像说的反话，其实深刻的道理就在这里边。</t>
+  </si>
+  <si>
+    <t>第九章</t>
   </si>
   <si>
     <t>第七十九章（79）</t>
@@ -2563,12 +2585,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F83"/>
   <sheetFormatPr defaultColWidth="23.75" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21" style="8" customWidth="1"/>
-    <col min="2" max="2" width="68.2222222222222" style="6" customWidth="1"/>
+    <col min="2" max="2" width="59.25" style="6" customWidth="1"/>
     <col min="3" max="3" width="60.6666666666667" style="6" customWidth="1"/>
     <col min="4" max="4" width="75.25" style="6" customWidth="1"/>
     <col min="5" max="5" width="7.37962962962963" style="6" customWidth="1"/>
@@ -2596,7 +2618,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="6" customFormat="1" ht="317.4" spans="1:6">
+    <row r="2" s="6" customFormat="1" ht="358.8" hidden="1" spans="1:6">
       <c r="A2" s="10" t="s">
         <v>6</v>
       </c>
@@ -2613,7 +2635,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="151.8" spans="1:6">
+    <row r="3" ht="151.8" hidden="1" spans="1:6">
       <c r="A3" s="10" t="s">
         <v>11</v>
       </c>
@@ -2633,7 +2655,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" ht="151.8" spans="1:6">
+    <row r="4" ht="151.8" hidden="1" spans="1:6">
       <c r="A4" s="10" t="s">
         <v>17</v>
       </c>
@@ -2649,189 +2671,198 @@
       <c r="E4" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" ht="151.8" spans="1:6">
+      <c r="F4" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" ht="151.8" hidden="1" spans="1:6">
       <c r="A5" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" ht="151.8" spans="1:6">
+    <row r="6" ht="151.8" hidden="1" spans="1:6">
       <c r="A6" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" ht="151.8" spans="1:6">
+    <row r="7" ht="151.8" hidden="1" spans="1:6">
       <c r="A7" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="124.2" spans="1:6">
+    <row r="8" ht="124.2" hidden="1" spans="1:6">
       <c r="A8" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="151.8" spans="1:6">
+    <row r="9" ht="151.8" hidden="1" spans="1:6">
       <c r="A9" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" ht="179.4" spans="1:6">
+    <row r="10" ht="179.4" hidden="1" spans="1:6">
       <c r="A10" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" ht="138" spans="1:6">
+    <row r="11" ht="138" hidden="1" spans="1:6">
       <c r="A11" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" ht="151.8" spans="1:6">
+      <c r="F11" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" ht="151.8" hidden="1" spans="1:6">
       <c r="A12" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" ht="138" spans="1:6">
+    <row r="13" ht="138" hidden="1" spans="1:6">
       <c r="A13" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" ht="151.8" spans="1:6">
+      <c r="F13" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" ht="151.8" hidden="1" spans="1:6">
       <c r="A14" s="10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" ht="151.8" spans="1:6">
+    <row r="15" ht="151.8" hidden="1" spans="1:6">
       <c r="A15" s="10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>15</v>
@@ -2839,1161 +2870,1187 @@
     </row>
     <row r="16" ht="165.6" spans="1:6">
       <c r="A16" s="10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" ht="207" spans="1:5">
+    <row r="17" ht="207" hidden="1" spans="1:5">
       <c r="A17" s="10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" ht="151.8" spans="1:5">
+    <row r="18" ht="151.8" hidden="1" spans="1:5">
       <c r="A18" s="10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" ht="165.6" spans="1:5">
+    <row r="19" ht="165.6" hidden="1" spans="1:5">
       <c r="A19" s="10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" ht="138" spans="1:5">
+    <row r="20" ht="138" hidden="1" spans="1:5">
       <c r="A20" s="10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" ht="151.8" spans="1:5">
+    <row r="21" ht="151.8" hidden="1" spans="1:5">
       <c r="A21" s="10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" ht="179.4" spans="1:5">
+    <row r="22" ht="179.4" hidden="1" spans="1:5">
       <c r="A22" s="10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" ht="165.6" spans="1:5">
+    <row r="23" ht="165.6" hidden="1" spans="1:5">
       <c r="A23" s="10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" ht="165.6" spans="1:5">
+    <row r="24" ht="165.6" hidden="1" spans="1:5">
       <c r="A24" s="10" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="25" ht="151.8" spans="1:5">
+    <row r="25" ht="151.8" hidden="1" spans="1:5">
       <c r="A25" s="10" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" ht="151.8" spans="1:5">
+    <row r="26" ht="151.8" hidden="1" spans="1:5">
       <c r="A26" s="10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="27" ht="165.6" spans="1:5">
+    <row r="27" ht="165.6" hidden="1" spans="1:5">
       <c r="A27" s="10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="28" ht="165.6" spans="1:5">
+    <row r="28" ht="165.6" hidden="1" spans="1:5">
       <c r="A28" s="10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="29" ht="179.4" spans="1:5">
+    <row r="29" ht="179.4" hidden="1" spans="1:5">
       <c r="A29" s="10" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="30" ht="165.6" spans="1:5">
+    <row r="30" ht="165.6" hidden="1" spans="1:5">
       <c r="A30" s="10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="31" ht="165.6" spans="1:5">
+    <row r="31" ht="165.6" hidden="1" spans="1:5">
       <c r="A31" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="32" ht="165.6" spans="1:5">
+    <row r="32" ht="165.6" hidden="1" spans="1:5">
       <c r="A32" s="10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="33" ht="165.6" spans="1:5">
+    <row r="33" ht="165.6" hidden="1" spans="1:6">
       <c r="A33" s="10" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="34" ht="165.6" spans="1:5">
+    <row r="34" ht="165.6" hidden="1" spans="1:6">
       <c r="A34" s="10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="35" ht="151.8" spans="1:5">
+    <row r="35" ht="151.8" hidden="1" spans="1:6">
       <c r="A35" s="10" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="36" ht="151.8" spans="1:5">
+    <row r="36" ht="151.8" hidden="1" spans="1:6">
       <c r="A36" s="10" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="37" ht="151.8" spans="1:5">
+    <row r="37" ht="151.8" hidden="1" spans="1:6">
       <c r="A37" s="10" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="38" ht="165.6" spans="1:5">
+    <row r="38" ht="165.6" hidden="1" spans="1:6">
       <c r="A38" s="10" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" ht="138" spans="1:5">
+    <row r="39" ht="138" hidden="1" spans="1:6">
       <c r="A39" s="10" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="40" ht="179.4" spans="1:5">
+    <row r="40" ht="179.4" hidden="1" spans="1:6">
       <c r="A40" s="10" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="41" ht="165.6" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="41" ht="165.6" hidden="1" spans="1:6">
       <c r="A41" s="10" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C41" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E41" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="D41" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="42" ht="151.8" spans="1:5">
+      <c r="F41" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" ht="151.8" hidden="1" spans="1:6">
       <c r="A42" s="10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="43" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="43" ht="409.5" hidden="1" spans="1:6">
       <c r="A43" s="10" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="44" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="44" ht="409.5" hidden="1" spans="1:6">
       <c r="A44" s="10" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="45" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="45" ht="409.5" hidden="1" spans="1:6">
       <c r="A45" s="10" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="46" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="46" ht="409.5" hidden="1" spans="1:6">
       <c r="A46" s="10" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="47" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="47" ht="409.5" hidden="1" spans="1:6">
       <c r="A47" s="10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="48" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="48" ht="409.5" hidden="1" spans="1:6">
       <c r="A48" s="10" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="49" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="49" ht="409.5" hidden="1" spans="1:6">
       <c r="A49" s="10" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="50" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="50" ht="409.5" hidden="1" spans="1:6">
       <c r="A50" s="10" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="51" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="51" ht="409.5" hidden="1" spans="1:6">
       <c r="A51" s="10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="52" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="52" ht="409.5" hidden="1" spans="1:6">
       <c r="A52" s="10" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="53" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="53" ht="409.5" hidden="1" spans="1:6">
       <c r="A53" s="10" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="54" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="54" ht="409.5" hidden="1" spans="1:6">
       <c r="A54" s="10" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="55" ht="400.2" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="55" ht="400.2" hidden="1" spans="1:6">
       <c r="A55" s="10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="56" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="56" ht="409.5" hidden="1" spans="1:6">
       <c r="A56" s="10" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="57" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="57" ht="409.5" hidden="1" spans="1:6">
       <c r="A57" s="10" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="58" ht="372.6" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="58" ht="372.6" hidden="1" spans="1:6">
       <c r="A58" s="10" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="59" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="59" ht="409.5" hidden="1" spans="1:6">
       <c r="A59" s="10" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="60" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" ht="409.5" hidden="1" spans="1:6">
       <c r="A60" s="10" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="61" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="61" ht="409.5" hidden="1" spans="1:6">
       <c r="A61" s="10" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="62" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="62" ht="409.5" hidden="1" spans="1:6">
       <c r="A62" s="10" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="63" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="63" ht="409.5" hidden="1" spans="1:6">
       <c r="A63" s="10" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="64" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="64" ht="409.5" hidden="1" spans="1:6">
       <c r="A64" s="10" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="65" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="65" ht="409.5" hidden="1" spans="1:6">
       <c r="A65" s="10" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="66" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="66" ht="409.5" hidden="1" spans="1:6">
       <c r="A66" s="10" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="67" ht="345" spans="1:5">
+        <v>168</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="67" ht="345" hidden="1" spans="1:6">
       <c r="A67" s="10" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="68" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="68" ht="409.5" hidden="1" spans="1:6">
       <c r="A68" s="10" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="69" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="69" ht="409.5" hidden="1" spans="1:6">
       <c r="A69" s="10" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="70" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="70" ht="409.5" hidden="1" spans="1:6">
       <c r="A70" s="10" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="71" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="71" ht="409.5" hidden="1" spans="1:6">
       <c r="A71" s="10" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="72" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="72" ht="409.5" hidden="1" spans="1:6">
       <c r="A72" s="10" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="73" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="73" ht="409.5" hidden="1" spans="1:6">
       <c r="A73" s="10" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="74" ht="358.8" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="74" ht="358.8" hidden="1" spans="1:6">
       <c r="A74" s="10" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="75" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="75" ht="409.5" hidden="1" spans="1:6">
       <c r="A75" s="10" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="76" ht="400.2" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="76" ht="400.2" hidden="1" spans="1:6">
       <c r="A76" s="10" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="77" ht="386.4" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="77" ht="386.4" hidden="1" spans="1:6">
       <c r="A77" s="10" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="78" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="78" ht="409.5" hidden="1" spans="1:6">
       <c r="A78" s="10" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="79" ht="400.2" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="79" ht="400.2" hidden="1" spans="1:6">
       <c r="A79" s="10" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="80" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="80" ht="409.5" hidden="1" spans="1:6">
       <c r="A80" s="10" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="81" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="81" ht="409.5" hidden="1" spans="1:5">
       <c r="A81" s="10" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="82" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="82" ht="409.5" hidden="1" spans="1:5">
       <c r="A82" s="10" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="83" ht="409.5" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="83" ht="409.5" hidden="1" spans="1:5">
       <c r="A83" s="10" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F83" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="第十四章（14）"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
@@ -4035,491 +4092,494 @@
     </row>
     <row r="2" ht="145.2" customHeight="1" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="F2" s="6"/>
     </row>
     <row r="3" ht="132" customHeight="1" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="F3" s="3"/>
     </row>
     <row r="4" ht="105.6" customHeight="1" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>342</v>
       </c>
       <c r="F4" s="3"/>
     </row>
     <row r="5" ht="92.4" customHeight="1" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="F5" s="3"/>
     </row>
     <row r="6" ht="118.8" customHeight="1" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="F6" s="3"/>
     </row>
     <row r="7" ht="92.4" customHeight="1" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="F7" s="3"/>
     </row>
     <row r="8" ht="118.8" customHeight="1" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="F8" s="3"/>
     </row>
     <row r="9" ht="118.8" customHeight="1" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>365</v>
       </c>
       <c r="F9" s="3"/>
     </row>
     <row r="10" ht="79.2" customHeight="1" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="F10" s="3"/>
     </row>
     <row r="11" ht="118.8" customHeight="1" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="F11" s="3"/>
     </row>
     <row r="12" ht="105.6" customHeight="1" spans="1:6">
       <c r="A12" s="3" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="F12" s="3"/>
     </row>
     <row r="13" ht="105.6" customHeight="1" spans="1:6">
       <c r="A13" s="3" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F13" s="3"/>
     </row>
     <row r="14" ht="105.6" customHeight="1" spans="1:6">
       <c r="A14" s="3" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="F14" s="3"/>
     </row>
     <row r="15" ht="92.4" customHeight="1" spans="1:6">
       <c r="A15" s="3" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F15" s="3"/>
     </row>
     <row r="16" ht="105.6" customHeight="1" spans="1:6">
       <c r="A16" s="3" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F16" s="3"/>
     </row>
     <row r="17" ht="92.4" customHeight="1" spans="1:6">
       <c r="A17" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>402</v>
       </c>
       <c r="F17" s="3"/>
     </row>
     <row r="18" ht="79.2" customHeight="1" spans="1:6">
       <c r="A18" s="3" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F18" s="3"/>
     </row>
     <row r="19" ht="79.2" customHeight="1" spans="1:6">
       <c r="A19" s="3" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F19" s="3"/>
     </row>
     <row r="20" ht="92.4" customHeight="1" spans="1:6">
       <c r="A20" s="3" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F20" s="3"/>
     </row>
     <row r="21" ht="118.8" customHeight="1" spans="1:6">
       <c r="A21" s="3" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="F21" s="3"/>
     </row>
     <row r="22" ht="92.4" customHeight="1" spans="1:6">
       <c r="A22" s="3" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="F22" s="3"/>
     </row>
     <row r="23" ht="92.4" customHeight="1" spans="1:6">
       <c r="A23" s="3" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>433</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>427</v>
       </c>
       <c r="F23" s="3"/>
     </row>
     <row r="24" ht="105.6" customHeight="1" spans="1:6">
       <c r="A24" s="3" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="F24" s="3"/>
     </row>
     <row r="25" ht="79.2" customHeight="1" spans="1:6">
       <c r="A25" s="3" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="F25" s="3"/>
     </row>
     <row r="26" ht="92.4" customHeight="1" spans="1:6">
       <c r="A26" s="3" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="F26" s="3"/>
     </row>
     <row r="27" ht="118.8" customHeight="1" spans="1:6">
       <c r="A27" s="3" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="F27" s="3"/>
     </row>
     <row r="28" ht="132" customHeight="1" spans="1:6">
       <c r="A28" s="3" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="F28" s="3"/>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F28" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/book.xlsx
+++ b/book.xlsx
@@ -4,15 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25068" windowHeight="13380"/>
+    <workbookView windowWidth="19644" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="道德经" sheetId="1" r:id="rId1"/>
     <sheet name="大学" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">道德经!$A$1:$F$83</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">大学!$A$1:$F$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">道德经!$A$1:$G$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">大学!$A$1:$G$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="482">
+  <si>
+    <t>no</t>
+  </si>
   <si>
     <t>chapter</t>
   </si>
@@ -90,14 +93,14 @@
     <t>可以言说的道，就不是永恒的道；能够用来称呼的具体名称，就不是永恒的名称。天地开始的时候，把它叫做“无”；万物的母亲，把它叫做“有”。所以常处于无，从无的角度来观察它的妙处；常处于有，从有的角度来观察它的边界。有和无是任何事物都具有的两个方面，来源相同但名称不同，都可以称之为“玄妙深远”，玄而又玄，是一切奥妙的源头。</t>
   </si>
   <si>
-    <t>本章是《道德经》的门户，核心是“有”和“无”，特别强调常被忽略的“无”。道可道，非常道；名可名，非常名：道是最高、最全面的存在，用语言和逻辑讲出来就变成有局限的道，所以要借形象来领悟。无，名天地之始；有，名万物之母：天地起源时混沌无形，称为无；天地成形、万物出现，称为有。任何事物都有有和无两个方面，观察事物既要从“有”的角度看它的边界，也要从“无”的角度看它的妙处。
+    <t>【大象无形】本章是《道德经》的门户，核心是“有”和“无”，特别强调常被忽略的“无”。道可道，非常道；名可名，非常名：道是最高、最全面的存在，用语言和逻辑讲出来就变成有局限的道，所以要借形象来领悟。无，名天地之始；有，名万物之母：天地起源时混沌无形，称为无；天地成形、万物出现，称为有。任何事物都有有和无两个方面，观察事物既要从“有”的角度看它的边界，也要从“无”的角度看它的妙处。
 此两者同出而异名，同谓之玄：能把有和无合起来理解，已是高级的思维水平，叫做玄；再进一步看到无形力量（精神、信仰、家风、作风等）的巨大作用，就是玄之又玄、众妙之门。译者·韩鹏杰以“风”为形象：风无形却力量无尽，正如人的精神世界。老子提醒人们不要只看到金钱、财富等有形的东西，更要看到精神、思想、理想信念这些无形的力量；只重有形，物质越发达，精神家园就越花果飘零。</t>
   </si>
   <si>
     <t>道经</t>
   </si>
   <si>
-    <t>第四章</t>
+    <t>第四章、第十四章</t>
   </si>
   <si>
     <t>第二章（2）</t>
@@ -109,7 +112,7 @@
     <t>天下都知道美是什么，丑自然就存在了；都知道什么是善，不善自然也就出现了。所以有和无相待而生，难和易相待而成，长和短相待而显，高和下相待而倾倚，音和声相待而和谐，前和后相待而顺序相随。所以圣人行事 顺乎自然 崇尚无为，实行不言的教诲，顺应万物自然的生长而不加干预，创造万物而不占有，施泽万物而不将这当成是倚仗、凭借的手段，有了功劳而不居功（自傲）。正因为他不居功自傲，所以也就不会失去自己的功劳。</t>
   </si>
   <si>
-    <t>本章讲世界运动的规律和认识世界的方法，是理解《道德经》的另一扇门。用哲学的语言概括：相比较而存在，相对立而发展。天下皆知美之为美，斯恶已；皆知善之为善，斯不善已：知道美就知道丑，知道善就知道不善，对立双方互相规定、互相依存。老子随后列出有无相生、难易相成、长短相较、高下相倾、音声相和、前后相随，指出这些对立面并非固定不变，而是在对立中运动、转化。
+    <t>【相比较而存在 相对立而发展】本章讲世界运动的规律和认识世界的方法，是理解《道德经》的另一扇门。用哲学的语言概括：相比较而存在，相对立而发展。天下皆知美之为美，斯恶已；皆知善之为善，斯不善已：知道美就知道丑，知道善就知道不善，对立双方互相规定、互相依存。老子随后列出有无相生、难易相成、长短相较、高下相倾、音声相和、前后相随，指出这些对立面并非固定不变，而是在对立中运动、转化。
 因此圣人处无为之事，行不言之教：越是懂得有为，越要知道哪些该无为、该舍掉，从反面认识事情，才能达到更好的有为效果，千万不要把无为理解成消极。万物作焉而不辞，生而不有，为而不恃，功成而弗居：顺应万物自然生长而不干预，创造而不占有，做事而不依仗，有功而不居功，正因不居功，功德才不离去。本章后文许多重要内容提前概括出来，读熟这一章，后面很多章节都能以经解经。</t>
   </si>
   <si>
@@ -125,10 +128,13 @@
     <t>不崇尚标榜贤才，使民众不起争心；不炒作炫耀难得的物品，使民众不去做盗贼；不展现能引起人私欲的东西，使民众心不受惑乱。所以圣人的治理，使民众虚心、饱腹；减弱民众的欲望，强壮民众的身体。使民众常保持无知无欲的自然淳朴状态，那些诡计多端的人就不敢耍诈。以顺应自然、不强行干预、不违背规律的方式来治世，则没有治理不好的。</t>
   </si>
   <si>
-    <t>本章与第二章紧密相连，讲看问题不能一点论，要两点论：好事发展到一定程度会向反面转化。不尚贤，使民不争：尚贤本是重视人才的好事，但一旦立了标准，就有人按标准投机取巧、自我包装，真正有才能的人不屑于此，反而被过滤掉，贤名被投机者占据，所以尚贤过了头反而害了人才选拔。不贵难得之货，使民不为盗；不见可欲，使民心不乱：不炒作珍贵物品、不显露引发欲望的东西，民心才不会乱。
+    <t>【两点论来看问题】本章与第二章紧密相连，讲看问题不能一点论，要两点论：好事发展到一定程度会向反面转化。不尚贤，使民不争：尚贤本是重视人才的好事，但一旦立了标准，就有人按标准投机取巧、自我包装，真正有才能的人不屑于此，反而被过滤掉，贤名被投机者占据，所以尚贤过了头反而害了人才选拔。不贵难得之货，使民不为盗；不见可欲，使民心不乱：不炒作珍贵物品、不显露引发欲望的东西，民心才不会乱。
 圣人之治，虚其心，实其腹，弱其志，强其骨：使民心虚静、生活温饱、欲望减弱、身体强健。常使民无知无欲，使夫智者不敢为也：少用智巧套路，投机者才不敢妄为。为无为，则无不治：治理者不妄为、不折腾，按规律和规则办事，天下自然治理得好。译者·韩鹏杰强调，老子的话对面坐着的是领导者，这些话是对治理者提出的警醒：任何事都有尺度，把握不好度，好事也会变成坏事。</t>
   </si>
   <si>
+    <t>第三十二章</t>
+  </si>
+  <si>
     <t>第四章（4）</t>
   </si>
   <si>
@@ -138,10 +144,13 @@
     <t>道是阴阳两者相互中和，其作用无穷无尽，其渊深、渊博好像万物的宗主。它锋芒不外露，解除纷扰，在光明之处便与光融合，在尘垢之处便与尘垢同一。其深远幽暗好像无处不在。我不知它是从何而来，只知道在象帝之前便已存在。</t>
   </si>
   <si>
-    <t>本章强调道是万物的本源，理解的关键在“冲”字。冲是组合字，把两点放平就是“二中”，二指阴阳；冲的本义是两股水冲到一块，象征阴阳两种力量相互中和、相互作用、动态转化。道冲，而用之或不盈：阴阳中和而成道，作用无穷无尽。渊兮似万物之宗：道渊深博厚，像万物的宗主。挫其锐，解其纷，和其光，同其尘：道收敛锋芒、化解纷争，与光明融合、与尘垢同一，深远幽暗却无处不在。吾不知谁之子，象帝之先：道先于天帝而存在，是万事万物的本源。
+    <t>【相反力量在动态中达到和谐】本章强调道是万物的本源，理解的关键在“冲”字。冲是组合字，把两点放平就是“二中”，二指阴阳；冲的本义是两股水冲到一块，象征阴阳两种力量相互中和、相互作用、动态转化。道冲，而用之或不盈：阴阳中和而成道，作用无穷无尽。渊兮似万物之宗：道渊深博厚，像万物的宗主。挫其锐，解其纷，和其光，同其尘：道收敛锋芒、化解纷争，与光明融合、与尘垢同一，深远幽暗却无处不在。吾不知谁之子，象帝之先：道先于天帝而存在，是万事万物的本源。
 译者·韩鹏杰用第四十二章“道生一，一生二，二生三，三生万物；万物负阴而抱阳，冲气以为和”来印证：三即参，阴阳参与到一起而生万物，万事万物都同时具有阴阳两面，无论怎么转都像太极图一样保持和谐。了解道冲，就掌握了一种重要思维：任何事物都是两种相反力量在动态中达成的和谐，看问题、做决策都不能只偏执一方。</t>
   </si>
   <si>
+    <t>第九章、第四十二章、第七十一章</t>
+  </si>
+  <si>
     <t>第五章（5）</t>
   </si>
   <si>
@@ -151,10 +160,13 @@
     <t>天地无所偏爱，将万物像刍狗（草扎的狗）一样平等看待；圣人没有偏私，对百姓像刍狗一样平等看待。天地这个大空间，不就像一个大风箱吗？因其中间虚静才能鼓出风，越动鼓出的风越多。政令繁多会招致败亡，不如保持虚静才能恰如其分。</t>
   </si>
   <si>
-    <t>本章讲天地对万物的平等和治理者的虚静。天地不仁，以万物为刍狗：不仁不是残忍，而是不偏爱、不干预；天地看待万物一视同仁，像草扎的祭狗，祭祀前被尊重，祭祀后被丢弃，无所爱惜。圣人不仁，以百姓为刍狗：好的领导者对百姓也应一律公平，制定规则法令，谁都不能例外；不要因为谁弱就特殊照顾，那反而是一种偏私，让被照顾者失去自立。道家讲的不仁是“大仁”，天地不偏私地让万物自己去奋斗、去努力。
+    <t>【圣人对百姓要一视同仁】本章讲天地对万物的平等和治理者的虚静。天地不仁，以万物为刍狗：不仁不是残忍，而是不偏爱、不干预；天地看待万物一视同仁，像草扎的祭狗，祭祀前被尊重，祭祀后被丢弃，无所爱惜。圣人不仁，以百姓为刍狗：好的领导者对百姓也应一律公平，制定规则法令，谁都不能例外；不要因为谁弱就特殊照顾，那反而是一种偏私，让被照顾者失去自立。道家讲的不仁是“大仁”，天地不偏私地让万物自己去奋斗、去努力。
 天地之间，其犹橐籥乎：天地像风箱，中间虚静，一拉动就能鼓出风来；政令也应如此，保持虚静、简要稳定，不能今天一变明天一变。多言数穷，不如守中：政令繁多、变动频繁会把自己逼入困境，不如恰到好处、大道至简。译者·韩鹏杰提醒，这些话都是讲给领导者听的：治理要公平无私，政令要少而稳定，靠规则而不是靠折腾。</t>
   </si>
   <si>
+    <t>第五十七章</t>
+  </si>
+  <si>
     <t>第六章（6）</t>
   </si>
   <si>
@@ -164,10 +176,13 @@
     <t>道虚无莫测 永存不灭，它好像是一个玄妙的母体。而这一母体的生殖器官，就是产生天地万物的根源。空间连绵不断似乎永远存在，万物使用它却又用不完它。</t>
   </si>
   <si>
-    <t>本章以谷与牝为喻，把道比作孕育万物的母体，根本精神是对母亲的尊重、对生命的敬畏。谷神不死，是谓玄牝：谷指空虚的山谷，神指精神、生机；牝指女性生殖器，代表母亲。谷神不死，即这种孕育生命的力量绵延不绝，称为玄牝。玄牝之门，是谓天地根：玄牝之门是天地万物的根源，道生万物与母亲生育生命是同一个道理。绵绵若存，用之不勤：它连绵不断地存在，取之不尽、用之不竭。
+    <t>【尊重母亲(道) 敬畏生命】本章以谷与牝为喻，把道比作孕育万物的母体，根本精神是对母亲的尊重、对生命的敬畏。谷神不死，是谓玄牝：谷指空虚的山谷，神指精神、生机；牝指女性生殖器，代表母亲。谷神不死，即这种孕育生命的力量绵延不绝，称为玄牝。玄牝之门，是谓天地根：玄牝之门是天地万物的根源，道生万物与母亲生育生命是同一个道理。绵绵若存，用之不勤：它连绵不断地存在，取之不尽、用之不竭。
 译者·韩鹏杰强调，老子用神、玄这些最高字眼来称呼谷与牝，绝不允许亵渎；一个文化里若失去对母亲的尊重、对生命的敬畏，其他方面都会崩塌。读这一章不要陷入玄虚，要读出其中朴素而伟大的情感：尊重母亲、敬畏生命，是文化延续的根基。</t>
   </si>
   <si>
+    <t>第二十章、第二十五章、第五十二章</t>
+  </si>
+  <si>
     <t>第七章（7）</t>
   </si>
   <si>
@@ -177,23 +192,29 @@
     <t>天地能够长久存在。天地之所以能够长久存在，原因就在于它们不是为了自我而生存，所以能长久存在。因此有智慧的领导者总是把自己的利益放在后面，反而能够站到别人的前面；不贪身外之物，反而有利于自己的生存。不就是因为他们没有私心嘛，所以才更好地成就了他们的被人尊敬、平安无事的私心吗？！</t>
   </si>
   <si>
-    <t>本章与第八、九章共同讲进退、争让、强弱：人们习惯强调争、进、强，老子偏要讲被忽略的不争、退、弱，因为它们与争、进、强是阴阳的两个方面，具有同等力量。天长地久：天地之所以长久，是因为天地不自私，不以自己的生存为唯一目的，而是为万物提供阳光雨露土壤，任万物自由生长，因此赢得人们长久的敬畏。后其身而身先，外其身而身存：圣人把自身利益放在后面，反而被众人推举到前面；把自身安危置之度外，反而安然长存。非以其无私邪，故能成其私：正因无私，才更好地成就了自己的长久与被人敬仰，这是人人都有的潜意识私心。
+    <t>【无私 才能天长地久】本章与第八、九章共同讲进退、争让、强弱：人们习惯强调争、进、强，老子偏要讲被忽略的不争、退、弱，因为它们与争、进、强是阴阳的两个方面，具有同等力量。天长地久：天地之所以长久，是因为天地不自私，不以自己的生存为唯一目的，而是为万物提供阳光雨露土壤，任万物自由生长，因此赢得人们长久的敬畏。后其身而身先，外其身而身存：圣人把自身利益放在后面，反而被众人推举到前面；把自身安危置之度外，反而安然长存。非以其无私邪，故能成其私：正因无私，才更好地成就了自己的长久与被人敬仰，这是人人都有的潜意识私心。
 本章是典型的“天道人道”两段论：先讲天道，再讲人道，人道效法天道。译者·韩鹏杰用“公仪休不受鱼”的故事说明：懂得从长远看问题、不贪眼前不该得的利益，才能长久地满足自己的愿望；只盯着私利的人，最后连私利也保不住。</t>
   </si>
   <si>
+    <t>第六十六章、第八十一章</t>
+  </si>
+  <si>
     <t>第八章（8）</t>
   </si>
   <si>
-    <t>上善若水，水善利万物而不争，处众人之所恶（wù），故几于道，居善地；心善渊；与善仁；言善信；正善治；事善能；动善时。夫唯不争，故无尤。</t>
-  </si>
-  <si>
-    <t>最高的智慧和品德就像水一样，水善于利万物而不争，水处于众人最不愿去的地方，这是它最接近道的品性，它处于的是行善之地；人心也要像深水一样静水流深、要宁静致远、要善于沉淀；与人相处时、给人东西时、对人有恩德时要像水一样平等仁爱 要“生而不有，为而不恃，长而不宰”；说话也要像潮水一样“潮信” 讲信用、要言善信；政治清明像水一样公平公正清廉 要政善治 政清如水 为人做事要像水一样有多种多样的本事却又做事专一 奔流向海；处事智慧也像水一样 懂得寻找时机 该动则动 该静则静 该隐则隐 该绕行则绕行。所以像水一样有善利不争的品性，也就没有忧愁烦恼。</t>
-  </si>
-  <si>
-    <t>本章“上善若水”是《道德经》最著名的命题，也是中华民族精神的重要代表。上善若水，水善利万物而不争：最高的智慧与品德像水一样，滋润万物、成就他人而不争功，甘处众人不愿去的低处，所以最接近道。老子借水讲了善下、善渊、善仁、善信、善治、善能、善时等品质：居善地，甘居下位；心善渊，静水深流、宁静致远；与善仁，平等仁爱地给予；言善信，说话像潮信一样讲信用；政善治，政治清正公平如水；事善能，有多种本事又专一向前；动善时，该动则动、该静则静、该绕行则绕行。
+    <t>上善若水。水善利万物而不争，处众人之所恶（wù），故几于道，居善地；心善渊；与善仁；言善信；正善治；事善能；动善时。夫唯不争，故无尤。</t>
+  </si>
+  <si>
+    <t>最高的智慧和品德就像水一样。水善于利万物而不争，水处于众人最不愿去的低洼地方，这是它最接近道的品性，它处于的是行善之地；人心也要像深水一样静水流深、要宁静致远、要善于沉淀；与人相处时、给人东西时、对人有恩德时要像水一样平等仁爱 要“生而不有，为而不恃，长而不宰”；说话也要像潮水一样“潮信” 讲信用、要言善信；政治清明像水一样公平公正清廉 要政善治 政清如水 为人做事要像水一样有多种多样的本事却又做事专一 奔流向海；处事智慧也像水一样 懂得寻找时机 该动则动 该静则静 该隐则隐 该绕行则绕行。所以像水一样有善利不争的品性，也就没有忧愁烦恼。</t>
+  </si>
+  <si>
+    <t>【最高的品德——水】本章“上善若水”是《道德经》最著名的命题，也是中华民族精神的重要代表。上善若水，水善利万物而不争：最高的智慧与品德像水一样，滋润万物、成就他人而不争功，甘处众人不愿去的低处，所以最接近道。老子借水讲了善下、善渊、善仁、善信、善治、善能、善时等品质：居善地，甘居下位；心善渊，静水深流、宁静致远；与善仁，平等仁爱地给予；言善信，说话像潮信一样讲信用；政善治，政治清正公平如水；事善能，有多种本事又专一向前；动善时，该动则动、该静则静、该绕行则绕行。
 水的“不争”有丰富含义：有边界不争（湖有湖畔、河有河堤、海有海岸），有秩序不争（前后相随、循序渐进），有牺牲不争（成就万物而默默无闻）。夫唯不争，故无尤：不争就不会招来怨恨和过错。译者·韩鹏杰指出，老子不是趴在河边悟道，而是借水的形象传达从战争、政治、人生中领悟的智慧：善于成就别人，同时也成就自己，这正是双赢。</t>
   </si>
   <si>
+    <t>第六十三章、第六十九章、第七十八章</t>
+  </si>
+  <si>
     <t>第九章（9）</t>
   </si>
   <si>
@@ -203,11 +224,11 @@
     <t>如果做事一定要做到盈满，还不如停止不做。刀刃捶锻得尖锐锋利，其锋刃就不能长期保持锋利。家中充满财富和珍宝，没有人能够守住。炫富炫贵骄狂放纵，会给自己留下无尽祸殃。功成而懂得不居功自傲的道理，才真正符合天道天理。</t>
   </si>
   <si>
-    <t>本章讲“不盈”：凡事勿求满，适可而止。持而盈之，不如其已：端着一盘盛满的水走路，战战兢兢还不断洒出，不如少装一点，走得更轻松。揣而锐之，不可长保：把锥子磨得极锋利，一碰就断；削铅笔削到只剩笔头，再尖也保不住。金玉满堂，莫之能守：家中满是财富珍宝，反而守不住。富贵而骄，自遗其咎：因富贵而骄傲自满，是自取灾难。功遂身退，天之道也：功成而不居功、懂得退让，才符合天道。
+    <t>【凡事勿求满 适可而止】本章讲“不盈”：凡事勿求满，适可而止。持而盈之，不如其已：端着一盘盛满的水走路，战战兢兢还不断洒出，不如少装一点，走得更轻松。揣而锐之，不可长保：把锥子磨得极锋利，一碰就断；削铅笔削到只剩笔头，再尖也保不住。金玉满堂，莫之能守：家中满是财富珍宝，反而守不住。富贵而骄，自遗其咎：因富贵而骄傲自满，是自取灾难。功遂身退，天之道也：功成而不居功、懂得退让，才符合天道。
 译者·韩鹏杰用民间故事讲这个道理：弟弟只拿一点金子平安回家，哥哥贪心装满全身，被太阳晒化。第七章讲先后，第八章讲不争，第九章讲不盈，都提醒人知进退、懂谦让。中国文化的“中”就是恰到好处，不走到极端：物极必反、乐极生悲、泰极否来，好事到了极端容易向坏处转化，所以要战战兢兢、如履薄冰地把握分寸。</t>
   </si>
   <si>
-    <t>第七十八章</t>
+    <t>第二章、第四章、第七十八章</t>
   </si>
   <si>
     <t>第十章（10）</t>
@@ -219,10 +240,13 @@
     <t>身体像车一样载着魂魄，它们能不能不要分离？聚结精气以致柔和温顺，能不能像婴儿那样的纯粹呢？像玄镜照心一样清除杂念而深入观察心灵，能不能让心灵没有瑕疵呢？爱民治国能不能遵行自然无为的规律呢？感官与外界的对立变化相接触，能不能守住雌柔宁静呢？明白四达，能不能不用心机诈术呢？万物生长繁殖，产生万物、养育万物而不占为己有，作万物之长而不主宰它们，这就叫做“玄德”（高尚的品德）。</t>
   </si>
   <si>
-    <t>本章与十一、十二章共讲“虚静”：心里放空才能宁静，宁静才能看清事物本质，抵抗外在诱惑。载营魄抱一，能无离乎：身体像车载着魂魄，灵魂与肉体能否合一不分离？不要做丢了灵魂的行尸走肉。专气致柔，能如婴儿乎：聚结精气、身心柔软，能否像婴儿一样纯粹？涤除玄览，能无疵乎：清除内心杂念，能否像明镜一样无瑕疵？爱民治国，能无为乎：治理能否顺其自然、不妄为？天门开阖，能为雌乎：面对外界纷扰，能否守住柔静？明白四达，能无知乎：通达事理之后，能否不用机巧套路？
+    <t>【心里放空 保持虚静】本章与十一、十二章共讲“虚静”：心里放空才能宁静，宁静才能看清事物本质，抵抗外在诱惑。载营魄抱一，能无离乎：身体像车载着魂魄，灵魂与肉体能否合一不分离？不要做丢了灵魂的行尸走肉。专气致柔，能如婴儿乎：聚结精气、身心柔软，能否像婴儿一样纯粹？涤除玄览，能无疵乎：清除内心杂念，能否像明镜一样无瑕疵？爱民治国，能无为乎：治理能否顺其自然、不妄为？天门开阖，能为雌乎：面对外界纷扰，能否守住柔静？明白四达，能无知乎：通达事理之后，能否不用机巧套路？
 一连串反问都在讲修养路径：魂魄不离、身心合一、少欲守静、厚道不用智巧。最后点出玄德：生之畜之，生而不有，为而不恃，长而不宰——生养万物而不占有、不倚仗、不主宰，这是最高深的德。译者·韩鹏杰认为这一章是后面九章的总纲，虚静既是个人修养，也是治国的基础。</t>
   </si>
   <si>
+    <t>第四十二章、第五十七章、第七十一章、第七十五章</t>
+  </si>
+  <si>
     <t>第十一章（11）</t>
   </si>
   <si>
@@ -232,11 +256,11 @@
     <t>三十根辐条集中在一个车毂（轴承）上，正是因为有了车轴中的空间，才有了车子的作用。用水和黏土制造各种陶器，正是因为有了陶器里的空间，才有了陶器的作用。开凿门窗修建房屋，正是因为有了房屋中的空间，才有了房屋的作用。所以说各种器物的物质部分（实有部分）给人带来了利益，而器物里的空间（空虚部分）才使这些器物能够发挥自己的作用。</t>
   </si>
   <si>
-    <t>本章讲“无”的作用，用三个日常形象说明虚空的巨大价值。三十辐共一毂，当其无，有车之用：车轮有三十根辐条，车毂中间是空的，车轮才能转动，才有车的功用。埏埴以为器，当其无，有器之用：黏土烧成器皿，中间是空的，才能盛水装物。凿户牖以为室，当其无，有室之用：开凿门窗建成房屋，中间是空的，人才能居住。有之以为利，无之以为用：实体提供便利条件，虚空成就实际功用，有与无相互成全。
+    <t>【从有中看到无的作用】本章讲“无”的作用，用三个日常形象说明虚空的巨大价值。三十辐共一毂，当其无，有车之用：车轮有三十根辐条，车毂中间是空的，车轮才能转动，才有车的功用。埏埴以为器，当其无，有器之用：黏土烧成器皿，中间是空的，才能盛水装物。凿户牖以为室，当其无，有室之用：开凿门窗建成房屋，中间是空的，人才能居住。有之以为利，无之以为用：实体提供便利条件，虚空成就实际功用，有与无相互成全。
 译者·韩鹏杰指出，“利用”这个词就来自本章。第十章讲虚静，本章讲怎样虚静——心里放空，去掉杂念，才能听得进别人的意见、看得见别人的长处、学得到别人的优点，虚怀若谷、满招损谦受益。中国文化的悟道方式是“给一个形象，自己领悟”，本章就是最好的示范：通过车、器、室三个形象，让人领悟空与用的道理。</t>
   </si>
   <si>
-    <t>第二章</t>
+    <t>第二章、第六十六章</t>
   </si>
   <si>
     <t>第十二章（12）</t>
@@ -248,10 +272,13 @@
     <t>艳丽的色彩看多了会让人眼花缭乱；嘈杂的声音会让人听觉失灵；过于丰盛的食物吃多了会让人味觉错乱；沉溺于驰马打猎，会让人心神狂乱；珍贵的金银财宝，会让人行为不轨。因此圣人只求吃饱肚子而不求感官享受，摒弃感官享受（过度的欲望）而选择简单朴素安定知足的生活方式。</t>
   </si>
   <si>
-    <t>本章讲外在诱惑对心灵的扰乱，以及如何以内心的虚静守住根本。五色令人目盲：颜色太多太杂，反而区分不出好坏，视觉被迷乱；五音令人耳聋：高音快节奏听多了，好音乐也分辨不出来；五味令人口爽：厚食重味吃多了，味觉被破坏（爽是错乱）；驰骋畋猎令人心发狂：声色犬马让人心静不下来；难得之货令人行妨：被炒作的珍奇之物让人行为失当。老子并不要求消灭这些享受，而是说要以内心的虚静合理把握，适可而止。
+    <t>【心里放空 保持虚静】本章讲外在诱惑对心灵的扰乱，以及如何以内心的虚静守住根本。五色令人目盲：颜色太多太杂，反而区分不出好坏，视觉被迷乱；五音令人耳聋：高音快节奏听多了，好音乐也分辨不出来；五味令人口爽：厚食重味吃多了，味觉被破坏（爽是错乱）；驰骋畋猎令人心发狂：声色犬马让人心静不下来；难得之货令人行妨：被炒作的珍奇之物让人行为失当。老子并不要求消灭这些享受，而是说要以内心的虚静合理把握，适可而止。
 是以圣人为腹不为目，故去彼取此：圣人重实质内容，不重外在浮华；取舍的标准是看什么最重要——健康、营养、真实比外表颜色更重要。译者·韩鹏杰把本章与第十章、十一章连起来读：虚静的心才能看清本质，处其厚不居其薄，掌握生命中真正重要的东西，返璞归真。</t>
   </si>
   <si>
+    <t>第十章、第十一章</t>
+  </si>
+  <si>
     <t>第十三章（13）</t>
   </si>
   <si>
@@ -261,7 +288,7 @@
     <t>受到宠爱和受到侮辱都好像受到惊恐，这是把荣辱这样的大患看得与自身生命一样珍贵。那么为什么得宠和受辱都感到惊慌失措呢？受宠者是卑下的，得到宠爱又怕失去所以会感觉惊恐，失去宠爱则更令人惊慌不安，这就叫做得宠和受辱都感到惊恐。什么叫做重视大患像重视自身生命一样？我之所以有大患，是因为我有身体；如果我没有身体，我还会有什么祸患呢？所以，珍贵、爱惜自己的身体，用自己全部身心去治理天下的人，才可以把天下交给他；只有那些愿意以自己全部身心去治理天下的人，才可以把天下托付给他。</t>
   </si>
   <si>
-    <t>本章讲宠辱与生命，核心是如何看待得失、珍视生命，什么样的人才可托付天下。宠辱若惊：得到宠幸和失去宠幸都会惊恐。为什么？宠为下：被宠的人在下面，宠我们的人在上面，所以得之若惊（怕失去），失之若惊（更恐惧），这叫宠辱若惊。能做到宠辱不惊、淡然处之，是难得的人生境界。贵大患若身：有身体就有祸患，身体代表利益，也带来疾病与麻烦；但身体是摆脱不掉的，所以更要珍视它。
+    <t>【看待得失 珍视生命】本章讲宠辱与生命，核心是如何看待得失、珍视生命，什么样的人才可托付天下。宠辱若惊：得到宠幸和失去宠幸都会惊恐。为什么？宠为下：被宠的人在下面，宠我们的人在上面，所以得之若惊（怕失去），失之若惊（更恐惧），这叫宠辱若惊。能做到宠辱不惊、淡然处之，是难得的人生境界。贵大患若身：有身体就有祸患，身体代表利益，也带来疾病与麻烦；但身体是摆脱不掉的，所以更要珍视它。
 吾所以有大患者，为吾有身，及吾无身，吾有何患——不把身体和生命当回事的人，坐到重要位置上是很可怕的；声色犬马、厚食重味正是戕害生命。贵以身为天下，若可寄天下；爱以身为天下，若可托天下：真正把自身生命看得与天下一样贵重、肯为天下担当牺牲的人，才值得把天下托付给他。译者·韩鹏杰区分两种勇敢：无赖式的勇敢不把命当回事，有责任的勇敢珍视生命又肯担当，后者才值得托付。</t>
   </si>
   <si>
@@ -271,29 +298,30 @@
     <t>视之不见名曰夷（yí），听之不闻名曰希，搏之不得名曰微。此三者不可致诘（jié），故混而为一。其上不皦（jiǎo），其下不昧，绳（mǐn）绳（mǐn）不可名，复归于无物。是谓无状之状，无物之象，是谓惚恍。迎之不见其首，随之不见其后。执古之道，以御今之有。能知古始，是谓道纪。</t>
   </si>
   <si>
-    <t>察看大道又看不见，这叫作无形；聆听大道又听不到，这叫作无声；触摸大道又摸不着，这叫作无体。这三种特性都是无法进一步追究考察的，它们混合于一体。
-大道的上面不会显得明亮，它的下面也不会显得昏暗，它无形无象难以描述，可以说它不是一个物质性的实体。可以说大道是没有形状的形状，没有形体的形象，它可以说是迷离恍惚、无法捉摸的。站在它前面却看不见它的头部，尾随着它也看不见它的尾部。
-掌握了自古以来就存在的大道，就能够凭借它来驾驭、支配现在的万物，就能够了解远古时代的情况。以上所讲的就是关于大道的大致情况。</t>
-  </si>
-  <si>
-    <t>本章形容道大象无形却无处不在，并指出知古通今的方法。视之不见名曰夷，听之不闻名曰希，搏之不得名曰微：道太细微，看不见、听不到、摸不着，三个词都说明道不可用感官把握。此三者不可致诘，故混而为一：不能用语言追问道在哪里，它混然一体。其上不皦，其下不昧，绳绳不可名：道不明不暗、不上不下，绵延存在却无法命名。无状之状，无物之象，是谓惚恍：道没有具体形状和物象，似有若无。迎之不见其首，随之不见其后：寻不到它的首尾。
+    <t>察看大道又看不见，这叫作无形；聆听大道又听不到，这叫作无声；触摸大道又摸不着，这叫作无体。这三种特性都是无法进一步追究考察的，它们混合于一体。大道的上面不会显得明亮，它的下面也不会显得昏暗，它无形无象难以描述，可以说它不是一个物质性的实体。可以说大道是没有形状的形状，没有形体的形象，它可以说是迷离恍惚、无法捉摸的。站在它前面却看不见它的头部，尾随着它也看不见它的尾部。掌握了自古以来就存在的大道，就能够凭借它来驾驭、支配现在的万物，就能够了解远古时代的情况。以上所讲的就是关于大道的大致情况。</t>
+  </si>
+  <si>
+    <t>【大象无形】本章形容道大象无形却无处不在，并指出知古通今的方法。视之不见名曰夷，听之不闻名曰希，搏之不得名曰微：道太细微，看不见、听不到、摸不着，三个词都说明道不可用感官把握。此三者不可致诘，故混而为一：不能用语言追问道在哪里，它混然一体。其上不皦，其下不昧，绳绳不可名：道不明不暗、不上不下，绵延存在却无法命名。无状之状，无物之象，是谓惚恍：道没有具体形状和物象，似有若无。迎之不见其首，随之不见其后：寻不到它的首尾。
 执古之道，以御今之有：了解古往今来的大道，才能把握今天、做好今天的事；能知古始，是谓道纪：知道万物开始的道理，就是把握了道的纲领。译者·韩鹏杰用庄子的“道在瓦片、稗草、大小便中”来说明道无在无不在，越往下越有；用风的形象说明道无形却左右万物。学习本章要记住：道看不见摸不着，但真实存在、无处不在，了解它才能做好今天的事。</t>
   </si>
   <si>
+    <t>第一章</t>
+  </si>
+  <si>
     <t>第十五章（15）</t>
   </si>
   <si>
     <t>古之善为士者，微妙玄通，深不可识。夫唯不可识，故强为之容。豫焉若冬涉川，犹兮若畏四邻，俨（yǎn）兮其若客，涣兮若冰之将释，敦兮其若朴，旷兮其若谷，混兮其若浊。孰能浊以止？静之徐清。孰能安以久？动之徐生。保此道者不欲盈，夫唯不盈，故能蔽而新成。</t>
   </si>
   <si>
-    <t>古代那些掌握大道的人，其思想微妙通达，深刻得难以理解。正因为他们难以被理解，所以要勉强对他们的言行加以描述。
-他们做事反复考虑，就好像寒冬要徒步过河一样；谨慎小心，就好像畏惧四邻的围攻一般；恭敬庄重，就好像一位做客的人；通达而不固执，就好像将要融化的冰块；朴实敦厚，就好像未经雕饰的原木；胸怀空阔宽广，就好像那深山的幽谷；能够包容一切，就好像那混浊的大水。
-谁能够持久地像混浊的大水那样去包容一切呢？世人总是要让浊水安静下来，慢慢加以澄清；但是谁又能够永远坚持这种安定清静的状态呢？顺势而动，万物便能徐徐生发。
-掌握大道的人，办事不求盈满。正因为不求盈满，所以能去旧存新、不断新生。</t>
-  </si>
-  <si>
-    <t>本章讲基层领导者“士”应有的修养。古之善为士者，微妙玄通，深不可识：善于做士的人，智慧微妙、通达深远，难以被了解，所以要强为之容（勉强形容）。豫兮若冬涉川：像冬天过河一样谨慎，一步一探；犹兮若畏四邻：像敬畏四邻一样不敢妄动；俨兮其若客：庄重像做客；涣兮若冰之将释：温和像冰雪消融；敦兮其若朴：敦厚像未经雕琢的木头；旷兮其若谷：胸怀开阔像山谷；混兮其若浊：包容混同像浊水。
+    <t>古代那些掌握大道的人（士：推十为一，基层的、领导大家做事的这类人），其思想微妙通达，深刻得难以理解。正因为他们难以被理解，所以要勉强对他们的言行加以描述。他们做事反复考虑，就好像寒冬要徒步过河一样；谨慎小心，就好像畏惧四邻的围攻一般；恭敬庄重，就好像一位做客的人；通达而不固执，就好像将要融化的冰块；朴实敦厚，就好像未经雕饰的原木；胸怀空阔宽广，就好像那深山的幽谷；能够包容一切，就好像那混浊的大水。谁能够持久地像混浊的大水那样去包容一切呢？世人总是要让浊水安静下来，慢慢加以澄清；但是谁又能够永远坚持这种安定清静的状态呢？顺势而动，万物便能徐徐生发（生命在于运动）。掌握大道的人，办事不求盈满。正因为不求盈满，所以能去旧存新、不断新生。</t>
+  </si>
+  <si>
+    <t>【基层领导要具备的素质】本章讲基层领导者“士”应有的修养。古之善为士者，微妙玄通，深不可识：善于做士的人，智慧微妙、通达深远，难以被了解，所以要强为之容（勉强形容）。豫兮若冬涉川：像冬天过河一样谨慎，一步一探；犹兮若畏四邻：像敬畏四邻一样不敢妄动；俨兮其若客：庄重像做客；涣兮若冰之将释：温和像冰雪消融；敦兮其若朴：敦厚像未经雕琢的木头；旷兮其若谷：胸怀开阔像山谷；混兮其若浊：包容混同像浊水。
 孰能浊以静之徐清？孰能安以久动之徐生：浊水静下来才能慢慢澄清，安定的状态动起来才能慢慢焕发生机，这是“静中求清、动中求生”的修养。保此道者不欲盈，夫唯不盈，故能蔽而新成：守道者不求满，留出空间，舍弃旧的东西才能革故鼎新。译者·韩鹏杰强调，书中的话多针对具体的人讲，本章针对带领十几人做事的小组长等“士”阶层，说明基层领导者也需要很高的素质：谨慎、敬畏、质朴、虚怀、不盈。</t>
+  </si>
+  <si>
+    <t>第二十六章</t>
   </si>
   <si>
     <t>第十六章（16）</t>
@@ -361,6 +389,9 @@
 众人皆有余，而我独若遗：众人都显得富足有余，得道者却像有所遗失。我愚人之心也哉，沌沌兮：一副愚人心肠，混沌淳朴。俗人昭昭，我独昏昏；俗人察察，我独闷闷：世人精明，得道者看似糊涂宽厚。澹兮其若海，飂兮若无止：他像大海一样淡泊深沉，像长风一样自由无羁。众人皆有以，而我独顽似鄙：世人都有用处，他看似冥顽无能。我独异于人，而贵食母：与众人不同，因为他以大道为归依。本章刻画了不随波逐流、独立守道的精神境界。</t>
   </si>
   <si>
+    <t>第六章</t>
+  </si>
+  <si>
     <t>第二十一章（21）</t>
   </si>
   <si>
@@ -439,6 +470,9 @@
 轻则失根：轻率轻浮就失去根本，像飘蓬浮萍没有根基；躁则失君：浮躁急躁就失去对自己的掌控，冲动之下常常酿成大祸。译者·韩鹏杰用“路怒”举例：开车偶有小摩擦就粗口相向甚至拔刀，动手前问自己要不要动手、后果如何、有无别的办法，几秒钟的冷静可能改变结果。开头八字“重为轻根，静为躁君”与结尾“轻则失根，躁则失君”都是至理名言。</t>
   </si>
   <si>
+    <t>第十五章</t>
+  </si>
+  <si>
     <t>第二十七章（27）</t>
   </si>
   <si>
@@ -518,6 +552,9 @@
 始制有名，名亦既有，夫亦将知止，知止可以不殆：人类社会开始有制度、名分是合理的，但有了名分制度要懂得边界，不能制度崇拜、名分崇拜，做过了头就走向反面；知道适可而止，才能避免危险。譬道之在天下，犹川谷之于江海：道在天下，就像川谷流向江海，是自然归附的过程，不是强迫。译者·韩鹏杰强调，老子反复用重复和强调来突出重要思想，本章的核心就是朴与知止：做事朴实厚道，对制度名分保持克制，知道边界和限度，物极必反，知止不殆。</t>
   </si>
   <si>
+    <t>第三章</t>
+  </si>
+  <si>
     <t>第三十三章（33）</t>
   </si>
   <si>
@@ -612,6 +649,9 @@
 是以侯王自谓孤、寡、不穀：侯王自称孤、寡、不穀，正是以贱为本、以下为基。致数舆无舆：刻意追求众多荣誉反而失去荣誉。是故不欲琭琭如玉，珞珞如石：不要像华美的玉，要像坚硬的石头，石头能铺路济人，华美的玉看似高贵却少有用处。译者·韩鹏杰强调两个重点：一是“一”即道，是阴阳统一；二是“贵以贱为本，高以下为基”，位置越高越要善于处下，把根基打牢，做人要处实不居华。</t>
   </si>
   <si>
+    <t>第二章</t>
+  </si>
+  <si>
     <t>第四十章（40）</t>
   </si>
   <si>
@@ -649,6 +689,9 @@
     <t>《德经》部分我们今天讲四十二章。老规矩，把以前的这几章我们再顺一下。《德经》从第三十八章开始，第三十八章讲“上德不德，是以有德；下德不失德，是以无德。”第三十九章我们讲了两个重要的部分，一个就是这个“一”，因为第四十二章又出现了这个“一”，就是阴阳两者的相互平衡，形成的统一体。在第三十九章里边有两句话每一次我都要重申一下，以求让大家牢牢地记忆，“贵以贱为本，高以下为基”。第四十章有一个全部这本书思维的总纲，“反者，道之动”。下边举的这些都是“反者，道之动”的一些例证。比如说“弱者，道之用，天下万物生于有，生于无”。第四十一章的时候，我们是花了比较多的时间来说，为什么呢？因为这一章里边有非常多的“反者，道之动”的例证。比如说“大音希声，大象无形，大器晚成……”这些都是我们平时经常讲的成语。上次讲完了大家应该知道了它的出处。那么今天我们讲第四十二章，这一章并不难理解，但是非常的重要。因为这一章开头这段话，大家经常在很多地方看到，比如北京故宫是建筑的典范，故宫的太和、保和、中和三大殿都是三层台基，也就是建在三层高台之上，为什么选择“三”这个数字呢？再比如我所在的学校叫做西安交通大学，在交大的管理学院，我的一个朋友也在那做了一面墙的雕塑：太极，大家有机会到交大管理学院的时候就会看到，就在一楼。这两个地方的解释，用的都是这段话：“道生一，一生二，二生三，三生万物。”我们来解释这段话，原文大家都看到了：“道生一，一生二，二生三，三生万物。万物负阴而抱阳，冲气以为和。”这个“冲”字，读成中，一下就理解了。下面这段话其实大家也耳熟，起码意思在前边已经说过。“人之所恶，为孤寡不穀，而王公以为称。”大家讨厌的孤、寡、不榖，王公却用来称呼自己，这不是我们前面第三十九章的时候已经说过的这个意思嘛。“故物或损之而益，或益之而损。人之所教，我亦教之，强梁者不得其死，吾将以为教父。”这是第四十二章原文。我们一段一段来解释。先说第一段，“道生一”。“一”我们俗称叫太极。其实“一”就是道的具体的特点，强调道就是“一”，是说道的最重要的一个特点，就是它强调阴阳两者的统一，“一”里边蕴含着阴和阳两种力量，两个方面。“道生一，一生二”，这个“一”里边蕴含着“二”，也就是道里边蕴含着阴阳两种力量，两个方面，两种状态。中国人讲，事物都是相互对立而存在的，万事万物归结到最后，它也不会是一个单一的元素。你看咱们中国历史上的《易经》，落到最后就是两个符号，阴和阳。那已经到了事物的极致了，极点了。把阴和阳统一起来叫太极，但是这两个元素是最基本的。所以“一生二”，是说太极道里边蕴涵着阴阳两个方面，两种力量。“二生三”，很多人对这个“二生三”解释得太费劲。“三”是什么？很简单，就是繁体字那个“叁”，就是参。阴阳两者参与到一起，相互作用，形成了万事万物，多简单的事情。它们两者孤阴不生，孤阳不长，两者相互作用，形成万事万物，“三生万物”。所以我们用的那个《中庸》的名言叫“参天地，赞化育”。人能参与到天地之间的运动发展，天地人三才嘛。三才你看人不也参与其中嘛。这个赞可不是赞扬的意思，也是参与的意思。两者参与到一起，产生万事万物，这是从正面。然后再反过来推，既然是三生万物，那么万事万物里边都包含着这两种力量，两个方面，阴阳两个方面，所以叫“万物负阴而抱阳”。随便找，哪一个事物内部都有阴有阳，都包含着阴阳两种状态、两种力量。“万物负阴而抱阳，冲气以为和”。为什么要把这个“冲”念成“中”呢？大家看“冲”的写法，前边这两点其实就代表着阴和阳，那个中就是中和的意思，就是参的意思。阴阳两种力量，中国人把它叫做气，阴气、阳气嘛。通天下一气，形成和谐的、动态的、运动的世界，这就是冲气以为和。这一段讲了我们中国哲学中的宇宙生成模式，也讲了这个世界存在的状态，以及这个状态的原因。这种状态都是阴阳两者运动所形成的，动态的、和谐的状态。冲气以为和。再重复一遍。“道生一，一生二，二生三，三生万物。”所以万事万物都有阴阳两个方面，“万物负阴而抱阳，冲气以为和。”下边就开始讲。用这种思维方式你来理解世界，你就不能只站在一个方面了，明确地告诉你了。事物都是统一的，两个方面不可偏颇，不可偏废。所以对侯王讲，“人之所恶，唯孤寡不穀。”你说大家最讨厌的就是这些词，孤家、寡人、吃不上饭、饿死。可是你看这些王公大人，包括后来的皇帝，他们都拿这个来称呼自己。干嘛呢？“故物，或损之而益，或益之而损。”这个“物”大家不要解释成物质，就是我们中国人常讲的那个“东西”。中国人这个“东西”太奥妙了，什么都可以称之为东西，不管是物质的、精神的都可以称之为东西。所以老子就说你看说到万事万物存在的这些各类各样的东西，“或损之而益”，你以为它受损了，其实它得到了益处。有的时候我们受到一点挫折，我们觉得自己受了多大的这种屈辱一样，可是你知道人都是在不断地受的这种损中逐渐地成长起来的，你认为它是祸，其实它是福，“损之而益”。有的时候你认为自己是得到了，其实反而是一种损失。比如偷了东西的，得到了，其实把人格给损失掉了。有的人用不光彩的手段，不择手段得到的，其实他们损失的反而更大，“或益之而损”。所以老子讲的是相反相成的道理。我们中国人常用什么事情来说这个事？叫破财免灾，叫大难不死必有后福，叫祸福相依，叫塞翁失马焉知非福，你看这讲的都是“损之而益，益之而损”。刚才举的例子不就是这样吗？这侯王王公们不都在损自己吗？把自己叫做“孤寡不穀”。其实有这个提醒之后，反而避免了自己变成孤寡不穀。以前中国人也有这个习惯，给小孩起名起个贱名，好养活。当然现在这种习俗很少再看到了，它讲究的就是“损之而益，益之而损”。民间很多的道理大家也得认真对待，别以为我们上了学之后自己水平就高了，其实真正的高手在民间。很多老人讲的话，到最后你一生体会，反而你发现真的是有道理。“人之所教，我亦教之，强梁者不得其死”。老子也说这些东西，也都是别人教给我的，给我讲的。我再把这些写出来教给大家。这一句我们可得好好地来给大家说道说道。为什么呢？因为这涉及老子的思想的来源，老子的思想来源当然有很多方面，主要的两条，两条道路。一条道路自然就是《易经》。因为你看，《易经》它把这个叫易以道阴阳，老子也讲阴阳，而且这里边的损和益，这不就是《易经》里边的损卦和益卦嘛，损和益这也是《易经》里边经常强调的。另外一个，我觉得这一章里边非常奥妙，一个是讲这阴阳的事情，让我们知道他的思想里边《易经》是中国文化之源，众经之首，损之而益，益之而损。另外一个也表现出他的思想的来源，就是“强梁者不得其死”，这句话也不是老子自己的，它出自《金人铭》。传说黄帝写了六篇铭文，叫《黄帝六铭》。其中有一个是刻在周朝台阶右面立着的金人背后，金人就是青铜做的，这金人的背后有铭文。经过汉朝的刘向《说苑》的考证对比，发现《金人铭》里边的这句话：“强梁者不得其死”。“强梁”就是处处逞强。喜欢暴力的人，最后不会有好的结果。我们讲死得其所，叫得其死，得好死，不得好死，不得其死。强梁者不得其死。说到“强梁”这个词，我想读过《水浒传》的人一定记得，在《水浒传》里边用到“强梁”这个词的时候，是用在了矮脚虎王英的身上。矮脚虎王英，这个是梁山泊里边大家都瞧不上的那么一个人。原来是个车夫，后来抢劫，后来落草。所以用这个词来形容他，“强梁者”。“强梁者不得其死”，老子非常反对强暴，而强调和平、守弱，认为“强梁者不得其死”，“木强则折，兵强则灭”，这是他后边关于这个问题的一个延伸。“吾将以为教父”，这个“教父”就是说，这是别人教给我的，我也把它拿来作为座右铭，来指导我自己。总结一下，大家看这一章，第一段话是我们大家都耳熟能详的，“道生一，一生二，三生万物，万物负阴而抱阳，冲气以为和。”第二段是我们前边讲过的内容，在这个里边又重申了一遍，注意这些重申可不是排版排错了。因为《道德经》里边它讲的几条重要的原则，遇到机会的时候，它就会反复，用重复的方式来强调。“人之所恶，唯孤寡不穀，而王公以为称。”所以对于万事万物而言，对这个世界存在的东西而言，“或损之而益，或益之而损”。有的你觉得是损失了，结果反而是得到了。有的你认为自己得到了，反而是损失掉了。因此不可一概而论。遇到了乐事的时候，不要过于高兴，以免乐极生悲。遇到不好的事，祸事的时候，也不要丧气，因为这些可以成为我们的经验，塞翁失马，焉知非福！这是别人教给我的，我也把它来教给别人。然后下边这句话是老子也非常强调的，“强梁者不得其死”，还是要和平，还是要守弱，处处逞强，总和别人结梁子，最后不会有好的结果。国家也一样，“国虽大，好战必亡”。老子说我也要把这个当作座右铭，这就明显地透露出他思想的来源，一源于《易经》，阴阳之学，损益之论，谦卑之礼。二源于《金人铭》，尤其是《金人铭》里这句话对老子影响是非常大的，所以他把它叫做“教父”，座右铭。</t>
   </si>
   <si>
+    <t>第四章、第十章</t>
+  </si>
+  <si>
     <t>第四十三章（43）</t>
   </si>
   <si>
@@ -829,6 +872,9 @@
     <t>第五十七章的这段话非常有智慧，因为这段话一开始就指出来了，事物之间的不同，有本质的区别，所以处理问题、解决问题的方式方法也不一样。“以正治国，以奇用兵”，治国讲究的是堂堂正道。道家讲的“正”当然就是清静无为，不多事，不扰民，这就是道家讲的正道，是治国的大道理。可是用兵讲究的是“以奇用兵”，“兵者诡道也”，兵不厌诈。所以不能把用兵的方式、战争的方式用到治国的上面来，这两者不同，解决的方式也不一样。“以无事取天下”，无事就是不多事、不扰民、不刁难，这样才能够得到天下，并且坐得了江山。道家“无事”是“无为”的一个重要的方面，不多事、不扰民、不刁难，而“有为”讲的是妄为，多事、扰民、刁难，我们在前边这一点已经非常明确了。“吾何以知其然哉”，我怎么知道是这个样子呢？所谓“以此”就是依据上边“以正治国，以奇用兵”它们之间的本质不一样，所以解决的方式方法也不同而得出的结论。下面，老子开始谈他对治理天下的重要的看法。违背了大道，违背了道家的以“清静无为”为根本来治理国家的方式，会出现什么问题呢？“天下多忌讳，而民弥贫”，治理天下、领导国家忌讳太多，这个也不能动，那个也不能动，这个人的职务比较高，法令涉及不到他，当然出现了忌讳，不敢动，这个地方一定会形成一个空场，形成一个腐败的群体。百姓当然越来越穷了，财富都集中在少数人的手上。“民多利器，国家滋昏”，“滋”就是越来越。如果民间利器众多，武器众多，民与民之间械斗、抗法，那国家当然越来越混乱。“人多伎巧，奇物滋起”，“伎巧”就是各种各样的奇技淫巧，越来越多，大家对这些越来越感兴趣，这个技巧能够给他们带来利益，那么各种各样的奇奇怪怪的东西，甚至包括那些妖孽的东西，就不断兴起。“法令滋彰，盗贼多有”，既然这样，要用法律来管，法条定得越来越多，越来越严苛，反而盗贼越来越多。在前面这一段讲完之后，《道德经》说“故圣人云”，很明显，这是引用以往的通达事理的王们的话，老子用自己心中有智慧的人的语言来作为结尾。“我无为而民自化”，道家讲的无为，第一，“不妄为”。第十六章里边说“不知常，妄作，凶”，不了解事物的规律、规则，瞎折腾、胡折腾，这个结果是非常糟糕的。第二是“不多为”。抓住关键，举重若轻，多言数穷，不如守中，适可而止，恰到好处。第三讲究的是“有所不为”。人要想有所为，必须有所不为。一个政府也罢，一个领导者也罢，所有的事情都抓在自己手上，那底下的人怎么得到锻炼呢？不把担子压给他，他怎么练出独当一面的能力呢？什么事都控制在自己手上，那众人怎么样自我化育自我成长呢？所以无为才能让国家的人民、才能让自己的属下自我化育自我成长。事情成了应该怎么样呢？第十七章“功成事遂，百姓皆谓‘我自然’”，事情做成了，百姓都说这是我们的努力把这事情做成的，这就叫“民自化”。“我好静而民自正”，前面我们讲过，道家讲的静，内心的清净，静下来才能找到解决事物的正确的方法。我清静，走正道，不那么浮躁、急躁、暴躁、狂躁，做一个好的表率，上梁而正，百姓当然也就正了，百姓当然也就好静而走正道了。“我无事而民自富”，不多事、不扰民、不刁难，那百姓自然就富起来了。“我无欲而民自朴”，“朴”就是原木，《道德经》里用原木喻指做事敦厚、朴实、厚道，没那么多欲望，不是老想抢夺别人、占有别人的。就像黄宗羲在《明夷待访录》里边讲的，古代的那些皇帝都是什么样的？“离散天下人之儿女，荼毒天下人之肝脑，以供一人之淫乐。”这是我的，普天之下都是我的。所以欲望无止境，你让百姓能够朴实厚道，这也不可能。所以不要欲壑难填，不要什么东西都看作是自己的，可以任意掠夺，这样百姓自然就朴实、厚道，民心淳朴。这里边的两句话，我们国家的领导者讲话的时候也经常引用：“我无为而民自化，我无事而民自富。”所以，第五十七章讲了两个重要的道理，第一个不能把打仗的这一套用到治国之上。治国讲究的是堂堂大道，讲究的是清静无为，所以以无事取天下。第二个就讲站在领导者的角度，站在统治者的角度，应该怎么做呢？无为、好静、无事、无欲，这样自然一切顺理成章，百姓就会自化、自正、自富、自朴，事成了也会“功遂身退，百姓皆谓我自然”。这是一个好的领导者、好的政府做事的道理之所在，反之越多事儿，越是用那种严苛的法令，导致的结果适得其反。忌讳多了，百姓就越来越穷，民间的利器多了，国家就越来越混乱，大家都倾向于奇技淫巧，把这个当作一种喜欢的甚至不停地去追求的目标，那这个国家就越来越怪，各种奇葩的事情都纷至沓来。越觉得法令不够，越制定得严格、细致，以为单靠着法令就可以解决所有问题，反而适得其反，盗贼多有。所以，这一章里边讲的，也是我们经常说的——这本书的总纲：“反者，道之动”。我们考虑问题，不要只考虑它一面，要相反相成，用一个更高的观察事物的角度来理解。</t>
   </si>
   <si>
+    <t>第二章、第五章、第十章</t>
+  </si>
+  <si>
     <t>第五十八章（58）</t>
   </si>
   <si>
@@ -901,7 +947,7 @@
     <t>第六十三章的内容，我们在前边已经有所接触。之前我们说，第二章就是《道德经》的“目录”，第二章列出来了后边讲的六个重要内容，有无相生、难易相成等等，这一章的核心就是“难”和“易”。这一章的核心意思就说，要想做大事，先从小事做起，想要以后攻坚克难，你得从容易的事情做起。还有一个重要的问题、重要的智慧：你要把容易的事情当作难的事情来做，要有充分的、认真的准备，提前思考它的步骤、程序、会遇到的问题，这样再出什么问题的时候，你就能从容应对。有这样的态度，天下也没什么难事。天下无难事，但天下都是难事，看你怎么对待。开头这九个字非常有趣：“为无为，事无事，味无味。”“为无为”——想要有为吗？你得先懂得无为的道理。为什么？因为有些事你越有为，越强求，什么事都管，反而最后结果非常不好。道家讲的无为，就是按照道的方式来作为，想要有为，先要懂得无为的道理，不要妄为，要抓住关键，举重若轻，有所舍才能有所得，所以为无为。其实也就是第三十七章里边讲的“道常无为而无不为”，道的规律、规则是什么？用无为的方式达到无不为的效果，更好的效果。我再强调一下，《道德经》里出现得最多的一个词是“天下”。《道德经》针对的是天下，千万不要把道家当作一种消极的被动的思想，它是“想为”，但是强调要通过正确的道路和手段，懂得无为的正确的道路和手段，才能达到真正的有效的为，也就是用无为的方式，达到无不为的这种效果。下边再落一层，“事无事”。大家都想做事，可是大家有没有注意到，有些人他是“找事”，他是捣乱，是阻碍、多事，天下本无事，庸人自扰之。所以我们做事的时候要懂得无事的道理，不要多事，不要找事，不要刁难。尤其是做领导者，没事找事，权力就是刁难，你这不就麻烦了吗？“事无事”，想做事，得懂得无事的道理，不要多事，不要扰民。再落一层，“味无味”。我们经常讲一个词叫“真水无香”，真正好的饮料，就像那白开水一样，没有味道。我们饮食讲究清淡，寡味，少油少盐。最高的味道，反而是没有味道，无味。当然，这三个词核心还是“为无为”，让大家能够更明白一点。老子展开来讲，“事无事”，不要多事，不要扰民，不要刁难，就像“味无味”的道理一样。按照这样的一个逻辑推下来，下面四个字大家就能明白了，“大小、多少”，千万不要把它念成“大小多少”，这个东西就没意义了。这是告诉大家要“大其小”、要“多其少”，要把小事看得很重要，细节决定成败，千万不要忽略这个细节。为什么要“大其小”呢？因为天下的大事，都是从小事做起，为什么要“多其少”呢？因为积少才能成多。想要多，你得从少的一点一点积累，积少成多。就像我们学习《道德经》，一章一章讲，一章一章学，不要着急，最后达到一个整体的理解。我们经常讲“聚沙成塔”、“集腋成裘”，这不都是“多其少”的道理吗？“报怨以德”，按照这种相反相成的道理，对别人的埋怨、恩怨，也应该站在一个“德”的角度，因为德是符合道，用道的东西里面去感化。第六十二章不是讲了吗？“人之不善，何弃之有？”人家有这个埋怨，怎么正确地对待呢？“报怨以德”。用这种智慧和层次，让大家一起能回归到正途，回归到正道。“图难于其易，为大于其细。天下难事必作于易，天下大事必作于细。”这几句话，在我们文化里边名气非常大，因为讲的是哲学上的量的积累达到质的变化的道理。“图难于其易”，“图”就是图谋、计划。你计划想要做难的事情，要从容易的事情做起。“为大于其细”，想要做大的事情，得从小的事情一步一步来。我们大家都知道要脚踏实地，循序渐进，有条不紊，一屋不扫，何以扫天下？“天下难事必作于易”，天下所有的难事，都要从容易的事情做起。就像小孩的培养，让他们在处理小的事情中就形成良好的习惯，把小的事情、容易的事当成培养良好习惯的重要途径，将来，小孩在遇到大事、难事都能从容应对。现在很多人都有一个致命的弱点，大概是人的通病，就是好高骛远，老觉得自己应该是做大事的人，对小的事情不屑一顾。《道德经》就告诉我们这个智慧：想要做难的事情，从容易的事情做起；想要做大的事情，从小的事情做起，“天下大事必作于细”。“是以圣人终不为大，故能成其大。”“是以”，“是”就是这样，“以”就是所以。所以有智慧的领导者就是这样：“终不为大”，不是老说大话，不是老给大家画饼充饥，而是脚踏实地，一步一步地做起，“故能成其大”。一步一步把这个事情完成了，一步一步地完成计划，最后实现一个大的蓝图，好的结果，水到渠成。所以一个有智慧的人，不是老用那些虚幻的东西来画饼充饥，老是给大家讲大话、空话。“终不为大，故能成其大”，最后反而成就了大事，这话讲得非常好。我建议大家学习《道德经》，有一种重要的学习方法，就是反复看。有的人看《道德经》，也许一年就看一章，反复地看，反复地体会，“少则得，多则惑”，“终不为大，故能成其大”。以管窥天，以锥扎地，我们视力更集中，这样把这个事情才能做得更踏实，扎得更透。我们每一次的进步，虽然看起来好像只是一点点，但是这一点点积累起来就不得了了，“终不为大，故能成其大”。“轻诺必寡信”，大家还记得我们在讲《道德经》第八章的时候，就讲过“言善信”，我们中国人喜欢拿潮水作为讲信用的代表和象征，所以，有一个词就叫“潮信”。你看那钱塘潮每到农历八月十八前后就来了，人也应该如此，说话要讲信用，要有诚信，能给别人做成的事我们再去允诺，没把握做成的事，不要轻易去答应，不管我们有多热情。如果我们答应人家的很多事最后都做不成，时间长了，人家一定认为我们是食言而肥，不讲信用。《道德经》讲话是比较宽缓的，但这句话用的就是强逻辑判断，“轻诺必寡信”，这不是对我们委婉的劝告，这简直就是对我们严厉的警告。所以要讲诚信，君子重一诺，一诺千金嘛，所以“轻诺必寡信”，要避免这种结果出现。“多易必多难”，你把这个事情看得很容易，做什么事情，最后一定出问题。世界上哪有容易的事情，吃个饭喝个水，这都需要功夫，需要本事，小事情我们都要认真对待。我们经常讲“小河沟里翻船”，把一个事情看得太容易了，太简单了，往往会在这个事情上出问题。面对很多难的事情，大家战战兢兢，小心谨慎，反而没事，反而就是在一些认为最容易的事情出问题。很多学生做题、考试也是一样，难题没事，在容易的题上，出了问题，回去捶胸顿足，懊悔无比。所以，我们平常要形成一种把容易的事情当作难的事情来做的习惯，你要懂得“多易必多难”，凡事太容易，后面一定会出现很多的困难，出现很多的问题。所以，下边这句话就讲：“是以圣人犹难之”，所以有智慧的人，把这容易的事情都看作很难。天下的事情都当作难的事情来做，反而结果没有什么难的事情，“故终无难矣”。这个道理非常有趣，其实就是相反相成的道理，这个叫“难易相成”。世界上有没有难事呢？有，也没有。你把这个难的事情当作难的事情，看作是无法克服的，它就是难的事情；你把容易的事情当作容易的事情，没有认真对待，最后也会变成难的事情。我们把容易的事情当作难的事情来做，最后那个难的事也就做成了；真正难的事情，我们认真准备，有充分的信心，最后这难的事情也就克服了。“故终无难矣！”世上无难事，这就是“难易相成”的智慧。很多事情，决定于我们的想法、态度，态度不同，难易之间就会相互转化。</t>
   </si>
   <si>
-    <t>第二章、第六十四章</t>
+    <t>第二章、第八章、第六十四章</t>
   </si>
   <si>
     <t>第六十四章（64）</t>
@@ -943,6 +989,9 @@
     <t>这一章所讲的这个道理是《道德经》从头至尾所强调的“善于处下”，只有善于处下，才能真正居上。我们在一开始说过，《道德经》的很多话是针对那些领导者、统治者讲的，所以老先生认为越是位置高的领导者、统治者，越要善于处下，为什么呢？首先从处下的结果上来看，“江海所以能为百谷王者，以其善下之，故能为百谷王。”这句话我在前面也多次引用过。大江大海之所以能成为大江大海，是因为善于处下，不辞细流，能团结一切可以团结的力量，故能为“百谷王”。老子先拿“百川归海”的形象讲了这个道理，让大家有一个感知。下面就开始讲具体的做法和内容。“是以欲上民，必以言下之。”所以你要想站在上面领导好下面这些人，在语言上要懂得谦逊、谦让。领导者，尤其国君、皇帝这一类的，讲话的时候不能够居高临下，盛气凌人，自尊自大，不可一世。第三十九章说过“贵以贱为本，高以下为基。是以侯王自称孤寡不穀”，所以在语言上要谦逊。“欲先民，必以身后之。”想要站在前面当好领导、当好领头的，要懂得把自己的利益放在后面，想要领导别人就得给别人利益。一个人既要领导别人，又想什么好处、利益、功名都抢在自己手上，这个人下场不是不言而喻的吗？范仲淹的《岳阳楼记》里说“先天下之忧而忧，后天下之乐而乐”，做官、做领导不得如此吗？钱钟书先生认为范仲淹这两句话就是出自《道德经》的。但是人家学得比较好，不也成了大家都熟悉的名句了吗？“是以圣人处上而民不重”，所以一个好的领导者，你在上面领导大家，大家没有感觉到沉重的压力。“处前而民不害”，你在前面领导大家，大家没有感觉到你对他的危害。因为你要想领导别人，得让别人得到利益。西汉史学家司马迁在《史记·循吏列传》说：“公仪休者，鲁博士也。以高弟为鲁相。奉法循理，无所变更，百官自正。使食禄者不得与下民争利，受大者不得取小。”这里的食禄者不与民争利，意思是做官的人不许和百姓争夺利益。“是以天下乐推而不厌”，所以天下的人民都往高举你，往前推你，不感觉到厌倦、厌烦。如果统治者穷奢极欲，危害百姓，草菅人命，下面的人就会感觉到“害”、感觉到“重”，这样的人百姓会“乐推”吗？当然不会。“以其不争，故天下莫能与之争。”一个领导者，能得到了大家的拥护、拥戴，正因为你不争，不与民争利，不与其他人争名，“利而不害，为而不争”，结果是“以其不争，故天下莫能与之争”。越是争的人，最后往往失败得越惨，因为你的位置已经规定了你应有的担当、使命和责任。陈毅元帅讲过“手莫伸，伸手必被捉”，形象而深刻，那么，反过来用这个道理讲，就得以更加明确了。“以其不争，故天下莫能与之争”，所谓“不争”，并不是消极被动，“不争”，当然要了解边界，不争边界之外的东西，这样的话才能“天下乐推而不厌”。</t>
   </si>
   <si>
+    <t>第二章、第七章、第十一章</t>
+  </si>
+  <si>
     <t>第六十七章（67）</t>
   </si>
   <si>
@@ -1051,6 +1100,9 @@
     <t>这一章的核心话题还是“民”，解释了三个问题。第一，百姓为什么饥寒交迫；第二，百姓为什么难以治理；第三百姓为什么不怕死。解释完三个内容，然后对领导者、统治者提出要求。“民之饥，以其上食税之多”，百姓为什么饥寒交迫？“上”，上面的领导者、统治者，“食税”，收的税太多了，而且收的税都被这些人挥霍。“民之难治，以其上之有为”，百姓为什么难以治理呢？原因不在他们这儿，是因为上边胡来、瞎折腾。在《道德经》里，“有为”这个词就是妄为，胡折腾，上边老瞎折腾，就把民心折腾乱了。“信不足焉，有不信焉”，折腾得多了，讲的话也不诚信了，也失去百姓的信任，说什么都没用了。“是以难治”，“是”，“这是”的意思。这话讲得就比较理性，你老说他们是刁民，老在他们身上找，其实这原因就在自己的“有为”。老子对坐在对面的那些领导者、统治者就讲，你得找到真正的原因，百姓为什么饥寒交迫？你们收税收得太多了，收的税都被挥霍了。百姓为什么难以治理？你们整天瞎折腾，胡来妄为，把民心搞乱了。“民之轻死，以其求生之厚”。“其”指谁？领导者、统治者。百姓为什么轻死，把死不当一回事？是因为你们这些统治者，把自己的生命看得那么重要，不惜用剥夺的方式积累财富，花天酒地，穷奢极欲，这财富都聚积在他们自己手里，老百姓难以生存。就像国民党时期，财富都积累在“四大家族”手中，很少的人占有了绝大部分的财富，底下的人都生活在水深火热之中。当你“求生之厚”的时候，底下的百姓就觉得没什么活路和希望了，也就不把死当一回事，“是以轻死”。那么应该怎么做呢？“夫唯无以生为者”，不要把自己的生命看作是绝对重要的。不要把财富、好吃的好用的，全都集中在自己这儿来，认为只有自己的生命才是生命，对别人的生命、生存视而不见，感到无足轻重。不把聚敛、穷奢极欲当作生命的重要的部分，这个就是“贤于贵生”。百姓为什么饥寒交迫？上食税之多；为什么难以治理？上面胡来妄为；为什么不怕死？求生之厚。这章三个并列句，像诗一样的语言，讲得又非常深刻、非常理性。把七十五章和七十四章结合起来理解，我们就能发现，老先生苦口婆心地劝坐在对面的那些领导者、统治者：你们要对自己国家的人民好一点，否则啊，他们日子过不好，你们的日子也不安稳，你们只靠这种高压的政策，这不是解决问题的根本的方法。我们完全可以说在这几章里看到了《道德经》的“真实面目”，很多话是针对那些统治者讲的，苦口婆心地劝他们，应该怎么样对待这个国家的人民，才能使国家长久地、持续地发展。</t>
   </si>
   <si>
+    <t>第十章</t>
+  </si>
+  <si>
     <t>第七十六章（76）</t>
   </si>
   <si>
@@ -1087,7 +1139,7 @@
     <t>第七十八章体现了这本书里的一个非常重要的理念，“善于处下”。这些内容我们之前都有过接触，甚至直接引用七十八章做过讲解，所以这一章我们并不需要花费太多的时间来解释，大家也能够明了。“天下莫柔弱于水，而攻坚强者莫之能胜”，天下没有什么东西比水更柔弱了，你拿什么容器装，它就是什么样，随方就圆。但天下也没有什么东西比水的力量更强大了，攻无不克，战无不胜。水就是以柔克刚、以弱胜强的最好的形象的代表。“以其无以易之”，因为没有什么东西能够替代水，天下最柔弱的东西，它力量又最为强大，最能够体现柔弱胜刚强的道理。“弱之胜强，柔之胜刚，天下莫不知，莫能行。”天下都知道，这东西表面上看似柔弱，但发挥作用的时候力量太强大了，但是真的要这样却非常不容易，为什么？人都有脾气，“柔弱胜刚强”得懂得忍耐、等待，忍耐是我们人最难练的一种功夫。水滴锲而不舍方能穿石，一条溪流不舍昼夜，慢慢积累，等待时机，才能发挥大用。“柔弱胜刚强”也是需要条件的，只是老子没有明说。“是以圣人云”，我再给大家强调一下，在老子心里，以前有很多好的统治者、有智慧的领导者，他称其为“圣人”，让大家向他们学习。我们在前面谈到过，他的很多话并不是原创的，是他引用的以前的圣人的，下边这话就表达得非常明确，所以这些圣人讲，“受国之垢”“受国不祥”。这两句话就是《道德经》里边从头至尾强调的，就是我们经常讲的善于处下。古往今来，夺得天下的表面看是一家一姓，实际上不都是一个团队吗？用我们现在的话讲是一个党派。什么样的团队，什么样的党派才能夺得天下，并且坐得了江山呢？之前，我们在第八章讲“处众人之所恶”时，也拿这个地方作为印证。吃苦在前，享受在后，有困难还得担着，有错误勇于改正，这不就是“受国之垢”“受国不祥”吗？所以真正想要夺得天下，坐稳江山，也就是所谓“处其上”，首先要懂得“处其下”，要“受国之垢”，要能忍受别人忍受不了的艰难困苦，要能承受别人承受不了的屈辱诟骂，这样才能成为江山社稷的主人。“受国不祥，是为天下王。”有灾难有困难，你别跑，要挺身而出，勇于担当，有错误要勇于承认，勇于改正。毛泽东把共产党的宗旨概括为五个字，叫“为人民服务”。两千多年前的“受国之垢”，“受国不祥”，“处众人之所恶”，两千多年后的“为人民服务”，这本质上的意思不是一样的吗？这就是《道德经》里面从头强调的，也是古往今来的大道。我们在讲第十四章的时候说过一句话，“执古之道以御今之有”。了解古往今来的大道，我们才能更好地做好今天的事情。读到这儿大家就会发现，这《道德经》里边蕴含着古往今来的大道，蕴含着一个人、一个团队、一个党派成功的最深的密码，值得大家认真地品味。总结上面这个表达的方式叫什么呢？叫“正言若反”，也就是第四十章讲的“反者，道之动”。看着是讲反话，大家都不愿意去做的事情：“受国之垢”，“受国之不祥”，“处众人之所恶”，可实际上，这才是能够让我们“处上”、取得成功的真正的智慧与奥妙。看似好像说的反话，其实深刻的道理就在这里边。</t>
   </si>
   <si>
-    <t>第九章</t>
+    <t>第八章、第九章</t>
   </si>
   <si>
     <t>第七十九章（79）</t>
@@ -1124,6 +1176,9 @@
   </si>
   <si>
     <t>说起《道德经》的分章，大家一般认为最早是河上公以九九归一为神秘的数字指向，把它分成了八十一章。第八十一章可以看作是全书的总结，全书思想的总结和概括就是最后这两句话，“天之道，利而不害。”天道如此，人道应该效法天道，所以下一句“圣人之道，为而不争”，一个好的领导人、统治者是如此，对我们大家来讲也是如此。韩国有一个连任联合国秘书长的聪明人，叫潘基文。他在连任就职典礼上，开口讲的就是《道德经》的这两句话，只不过他引用的是这两句话中的八个字：“利而不害，为而不争。”我怎么做联合国秘书长？我对大家有利，不起坏心，为大家谋福利，“利而不害”。我把事情做了，不为自己争名夺利，“为而不争”。我们应该有一个非常深刻的体验：道家并不是消极的、被动的、什么事都不做。什么叫无为？“为而不争”是无为的一个重要的方面，这可以看作是全部《道德经》的核心的总结。我们回头去想，“上善若水”讲“善利万物而不争”；天道讲“为而不争”。这样我们就把整个的思想落地了，知道了《道德经》最后的核心落在什么地方。现在来看一下原文，“信言不美，美言不信”，真正诚信的话，不漂亮，只会讲漂亮话的，没诚信，过度漂亮的话里，往往隐含欺骗的内容，所以大家说，真理是朴素的，真理是赤裸裸的。“善者不辩，辩者不善”，真正善良的人，不老去争辩。庄子在他文章里边经常讲，老去靠争辩，争辩胜了，又能够体现什么？“善者不辩，辩者不善”，老去争辩，老为自己找借口，老觉得自己受了无尽的委屈，这个不是善良者的表现。“知者不博，博者不知”，一个有智慧的人，不是老是吹嘘自己渊博、博学、无所不知，老是吹嘘自己无所不知的人，其实是没有智慧的。下面就讲一个有智慧的领导者应该怎么去做事。“圣人不积”，一个有智慧的领导者，不是老想着去积累财富、有形的资产。“既以为人，己愈有”，什么叫做富？什么叫做有？我老去帮助别人，为别人做事，在给别人做事情，帮助别人的过程中，获得了无尽的快乐，这不是无形资产吗？这不是精神世界的充盈吗？“既以与人，己愈多”，给别人的越多，帮别人的越多，要财富发挥它的真正的作用，在“舍”的过程中反而自己得到更多。“既以为人，己愈有；既以与人，己愈多。”2014年习近平在斐济《斐济时报》发表署名文章，也用过这两句话。中国人喜欢双赢，帮助别人。我们的理念是什么？我们给别人做的事情越多，我们感觉到自己越富有；对别人帮得越多，感觉到自己获得的更多。所以我们经常讲，我们很多的快乐是在帮助别人成长，别人有困难的时候，我们帮扶的时候，感觉到自己的内心的充盈快乐。“为人”是什么？“与人”是什么？是善利。看似付出，自己反而获得更多，自己的精神世界也更为充盈。如果我们只一味地为自己积累财富，结果呢？我们经常讲一句话，叫穷得只剩下钱了，我们的物质世界越发达，财富越多，我们的精神家园就越花果飘零。“善利万物而不争”，这是全书的最后总结。不争什么？不争言语的漂亮，只为了它的实质；不为了争辩的胜利，只为它的真理；不吹嘘自己的知识的渊博，只让知识发挥它正确的作用；不积累那么多所谓的财富，而是让财富发挥它真正的作用，让我们的精神世界越来越充盈、越来越丰富。帮人越多，自己越富有；给人越多，自己获得越多。舍得、舍得，舍的同时，也是一种获得；帮人的过程，也是一种快乐。“既以为人，己愈有；既以与人，己愈多”，这两句话仔细思量，其即是天道。“天之道，利而不害”，天道如此，善利万物不起坏心。“圣人之道，为而不争”，把事情做了，不为自己争名夺利。“为而不争”和前面我们讲过的“善利万物而不争”、“生而不有，为而不恃，长而不宰”、“功成而弗居”、“衣养万物而不为主”，这些重要的语句遥相呼应。这样，我们就把思想穿成了一串珍珠，看清楚了这本书的真正的逻辑，也看清了这本书的“落脚点”。这些成为我们生活中的座右铭，指南针，对我们的思维方式、人生格局、精神境界都会有很大的启发和启迪。第八十一章的内容，我们解读完了。到这最后一章，我们看到这一章最后落在这句话上“圣人之道，为而不争”，可以清楚的看到这本经典的目的就是把士和王修养、培养成圣。这就是这本书的内在逻辑，也是老子的良苦用心。读这本经典要掌握以下几个关键性问题。一是《道德经》本质上是一本对话体，也就是对面坐着人问的问题。只不过老子在刻书时把对面坐的人是谁、问的什么问题都省略了，而只是把他当时给的答案概括、总结、提炼、升华形成的一本著作。当我们从书里找到士、王、圣这三类问问题的人时，也就很容易抓住问题的关键了。二是王弼本《道德经》哲学思维水平非常高。在第一章就提出有无相互统一思维方式的重要性，并指出“无”是全书的众妙之门，从而让我们清楚地知道了无为、无声、无色、无味、无色……在这本书中的重要性，也借此步入众妙之门。三是我们这种以经解经的方法前后参照，避免了八十一章本子的“碎片化”倾向，并且在通篇解读中发现了老子对他认为重要问题的强调方式：首先是用重复的方式强调。比如在第十章、第五十章都重复出现“生而不有，为而不恃，长而不宰”，并且在第二章、第三十四章也都出现类似的意思。其次是用首尾呼应的方式来强调，比如二十二章就是如此。其三是用正反两个方面的方式来强调一个观点的重要性，比如第六十七章就是如此。了解了上面这些导读的内容，我们再来听课、阅读，我们就会更深刻地了解这本书的深刻内容，这本“善建者不拔”的伟大经典指导下：“修之于身，其德乃真；修之于家，其德乃余；修之于乡，其德乃长；修之于国，其德乃丰；修之于天下，其德乃普。”当然即便是逐章解决了很多问题，讲的恐怕也是蜻蜓点水，就《道德经》而言，最重要的是大家自己的阅读和领悟。</t>
+  </si>
+  <si>
+    <t>第七章</t>
   </si>
   <si>
     <t>经第一章（1-1）</t>
@@ -1517,14 +1572,12 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2088,7 +2141,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2096,22 +2149,22 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2120,6 +2173,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2585,20 +2641,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:F83"/>
-  <sheetFormatPr defaultColWidth="23.75" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetPr/>
+  <dimension ref="A1:G83"/>
+  <sheetFormatPr defaultColWidth="23.75" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="21" style="8" customWidth="1"/>
-    <col min="2" max="2" width="59.25" style="6" customWidth="1"/>
-    <col min="3" max="3" width="60.6666666666667" style="6" customWidth="1"/>
-    <col min="4" max="4" width="75.25" style="6" customWidth="1"/>
-    <col min="5" max="5" width="7.37962962962963" style="6" customWidth="1"/>
-    <col min="6" max="16380" width="23.75" style="6" customWidth="1"/>
-    <col min="16381" max="16384" width="23.75" style="6"/>
+    <col min="1" max="1" width="6.36111111111111" style="8" customWidth="1"/>
+    <col min="2" max="2" width="21" style="8" customWidth="1"/>
+    <col min="3" max="3" width="59.25" style="3" customWidth="1"/>
+    <col min="4" max="4" width="60.6666666666667" style="3" customWidth="1"/>
+    <col min="5" max="5" width="75.25" style="3" customWidth="1"/>
+    <col min="6" max="6" width="7.37962962962963" style="3" customWidth="1"/>
+    <col min="7" max="7" width="29.3981481481481" style="3" customWidth="1"/>
+    <col min="8" max="16381" width="23.75" style="3" customWidth="1"/>
+    <col min="16382" max="16384" width="23.75" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -2617,12 +2675,15 @@
       <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" s="6" customFormat="1" ht="358.8" hidden="1" spans="1:6">
-      <c r="A2" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="11" t="s">
+    </row>
+    <row r="2" s="3" customFormat="1" ht="374.4" spans="1:7">
+      <c r="A2" s="10">
+        <v>0</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="11" t="s">
@@ -2634,12 +2695,16 @@
       <c r="E2" s="11" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" ht="151.8" hidden="1" spans="1:6">
-      <c r="A3" s="10" t="s">
+      <c r="F2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="G2" s="12"/>
+    </row>
+    <row r="3" ht="172.8" spans="1:7">
+      <c r="A3" s="10">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="11" t="s">
@@ -2651,15 +2716,18 @@
       <c r="E3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" ht="151.8" hidden="1" spans="1:6">
-      <c r="A4" s="10" t="s">
+      <c r="G3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="11" t="s">
+    </row>
+    <row r="4" ht="172.8" spans="1:7">
+      <c r="A4" s="10">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="11" t="s">
@@ -2669,17 +2737,20 @@
         <v>20</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" ht="151.8" hidden="1" spans="1:6">
-      <c r="A5" s="10" t="s">
+      <c r="F4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="11" t="s">
+    </row>
+    <row r="5" ht="172.8" spans="1:7">
+      <c r="A5" s="10">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="11" t="s">
@@ -2689,1366 +2760,1707 @@
         <v>25</v>
       </c>
       <c r="E5" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" ht="172.8" spans="1:7">
+      <c r="A6" s="10">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" ht="158.4" spans="1:7">
+      <c r="A7" s="10">
+        <v>5</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" ht="144" spans="1:7">
+      <c r="A8" s="10">
+        <v>6</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" ht="158.4" spans="1:7">
+      <c r="A9" s="10">
+        <v>7</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" ht="187.2" spans="1:7">
+      <c r="A10" s="10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" ht="158.4" spans="1:7">
+      <c r="A11" s="10">
+        <v>9</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" ht="172.8" spans="1:7">
+      <c r="A12" s="10">
+        <v>10</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" ht="158.4" spans="1:7">
+      <c r="A13" s="10">
+        <v>11</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" ht="158.4" spans="1:7">
+      <c r="A14" s="10">
+        <v>12</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" ht="172.8" spans="1:7">
+      <c r="A15" s="10">
+        <v>13</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="12"/>
+    </row>
+    <row r="16" ht="172.8" spans="1:7">
+      <c r="A16" s="10">
+        <v>14</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" ht="172.8" spans="1:7">
+      <c r="A17" s="10">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" ht="151.8" hidden="1" spans="1:6">
-      <c r="A6" s="10" t="s">
+      <c r="B17" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" ht="158.4" spans="1:7">
+      <c r="A18" s="10">
+        <v>16</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="12"/>
+    </row>
+    <row r="19" ht="172.8" spans="1:7">
+      <c r="A19" s="10">
+        <v>17</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="12"/>
+    </row>
+    <row r="20" ht="144" spans="1:7">
+      <c r="A20" s="10">
+        <v>18</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="12"/>
+    </row>
+    <row r="21" ht="158.4" spans="1:7">
+      <c r="A21" s="10">
+        <v>19</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="12"/>
+    </row>
+    <row r="22" ht="187.2" spans="1:7">
+      <c r="A22" s="10">
+        <v>20</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" ht="172.8" spans="1:7">
+      <c r="A23" s="10">
+        <v>21</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="12"/>
+    </row>
+    <row r="24" ht="172.8" spans="1:7">
+      <c r="A24" s="10">
+        <v>22</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="12"/>
+    </row>
+    <row r="25" ht="158.4" spans="1:7">
+      <c r="A25" s="10">
+        <v>23</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="12"/>
+    </row>
+    <row r="26" ht="158.4" spans="1:7">
+      <c r="A26" s="10">
+        <v>24</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="12"/>
+    </row>
+    <row r="27" ht="172.8" spans="1:7">
+      <c r="A27" s="10">
+        <v>25</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" ht="172.8" spans="1:7">
+      <c r="A28" s="10">
         <v>26</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B28" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" ht="187.2" spans="1:7">
+      <c r="A29" s="10">
         <v>27</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="B29" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="12"/>
+    </row>
+    <row r="30" ht="172.8" spans="1:7">
+      <c r="A30" s="10">
         <v>28</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="B30" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" s="12"/>
+    </row>
+    <row r="31" ht="172.8" spans="1:7">
+      <c r="A31" s="10">
         <v>29</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" ht="151.8" hidden="1" spans="1:6">
-      <c r="A7" s="10" t="s">
+      <c r="B31" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" s="12"/>
+    </row>
+    <row r="32" ht="172.8" spans="1:7">
+      <c r="A32" s="10">
         <v>30</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B32" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="12"/>
+    </row>
+    <row r="33" ht="172.8" spans="1:7">
+      <c r="A33" s="10">
         <v>31</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="B33" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="12"/>
+    </row>
+    <row r="34" ht="172.8" spans="1:7">
+      <c r="A34" s="10">
         <v>32</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="B34" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" ht="158.4" spans="1:7">
+      <c r="A35" s="10">
         <v>33</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" ht="124.2" hidden="1" spans="1:6">
-      <c r="A8" s="10" t="s">
+      <c r="B35" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="12"/>
+    </row>
+    <row r="36" ht="158.4" spans="1:7">
+      <c r="A36" s="10">
         <v>34</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B36" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" s="12"/>
+    </row>
+    <row r="37" ht="158.4" spans="1:7">
+      <c r="A37" s="10">
         <v>35</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="B37" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37" s="12"/>
+    </row>
+    <row r="38" ht="172.8" spans="1:7">
+      <c r="A38" s="10">
         <v>36</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="B38" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38" s="12"/>
+    </row>
+    <row r="39" ht="144" spans="1:7">
+      <c r="A39" s="10">
         <v>37</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" ht="151.8" hidden="1" spans="1:6">
-      <c r="A9" s="10" t="s">
+      <c r="B39" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" s="12"/>
+    </row>
+    <row r="40" ht="187.2" spans="1:7">
+      <c r="A40" s="10">
         <v>38</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B40" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G40" s="12"/>
+    </row>
+    <row r="41" ht="172.8" spans="1:7">
+      <c r="A41" s="10">
         <v>39</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="B41" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="42" ht="158.4" spans="1:7">
+      <c r="A42" s="10">
         <v>40</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="B42" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G42" s="12"/>
+    </row>
+    <row r="43" ht="409.5" spans="1:7">
+      <c r="A43" s="10">
         <v>41</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" ht="179.4" hidden="1" spans="1:6">
-      <c r="A10" s="10" t="s">
+      <c r="B43" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G43" s="12"/>
+    </row>
+    <row r="44" ht="409.5" spans="1:7">
+      <c r="A44" s="10">
         <v>42</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B44" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" ht="409.5" spans="1:7">
+      <c r="A45" s="10">
         <v>43</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="B45" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G45" s="12"/>
+    </row>
+    <row r="46" ht="409.5" spans="1:7">
+      <c r="A46" s="10">
         <v>44</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="B46" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G46" s="12"/>
+    </row>
+    <row r="47" ht="409.5" spans="1:7">
+      <c r="A47" s="10">
         <v>45</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" ht="138" hidden="1" spans="1:6">
-      <c r="A11" s="10" t="s">
+      <c r="B47" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G47" s="12"/>
+    </row>
+    <row r="48" ht="409.5" spans="1:7">
+      <c r="A48" s="10">
         <v>46</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B48" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G48" s="12"/>
+    </row>
+    <row r="49" ht="409.5" spans="1:7">
+      <c r="A49" s="10">
         <v>47</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="B49" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G49" s="12"/>
+    </row>
+    <row r="50" ht="409.5" spans="1:7">
+      <c r="A50" s="10">
         <v>48</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="B50" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G50" s="12"/>
+    </row>
+    <row r="51" ht="409.5" spans="1:7">
+      <c r="A51" s="10">
         <v>49</v>
       </c>
-      <c r="E11" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="6" t="s">
+      <c r="B51" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G51" s="12"/>
+    </row>
+    <row r="52" ht="409.5" spans="1:7">
+      <c r="A52" s="10">
         <v>50</v>
       </c>
-    </row>
-    <row r="12" ht="151.8" hidden="1" spans="1:6">
-      <c r="A12" s="10" t="s">
+      <c r="B52" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G52" s="12"/>
+    </row>
+    <row r="53" ht="409.5" spans="1:7">
+      <c r="A53" s="10">
         <v>51</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B53" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G53" s="12"/>
+    </row>
+    <row r="54" ht="409.5" spans="1:7">
+      <c r="A54" s="10">
         <v>52</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="B54" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55" ht="409.5" spans="1:7">
+      <c r="A55" s="10">
         <v>53</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="B55" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G55" s="12"/>
+    </row>
+    <row r="56" ht="409.5" spans="1:7">
+      <c r="A56" s="10">
         <v>54</v>
       </c>
-      <c r="E12" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" ht="138" hidden="1" spans="1:6">
-      <c r="A13" s="10" t="s">
+      <c r="B56" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G56" s="12"/>
+    </row>
+    <row r="57" ht="409.5" spans="1:7">
+      <c r="A57" s="10">
         <v>55</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B57" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G57" s="12"/>
+    </row>
+    <row r="58" ht="403.2" spans="1:7">
+      <c r="A58" s="10">
         <v>56</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="B58" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="F58" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G58" s="12"/>
+    </row>
+    <row r="59" ht="409.5" spans="1:7">
+      <c r="A59" s="10">
         <v>57</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="B59" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="F59" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G59" s="11" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="60" ht="409.5" spans="1:7">
+      <c r="A60" s="10">
         <v>58</v>
       </c>
-      <c r="E13" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="6" t="s">
+      <c r="B60" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G60" s="12"/>
+    </row>
+    <row r="61" ht="409.5" spans="1:7">
+      <c r="A61" s="10">
         <v>59</v>
       </c>
-    </row>
-    <row r="14" ht="151.8" hidden="1" spans="1:6">
-      <c r="A14" s="10" t="s">
+      <c r="B61" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G61" s="12"/>
+    </row>
+    <row r="62" ht="409.5" spans="1:7">
+      <c r="A62" s="10">
         <v>60</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B62" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G62" s="12"/>
+    </row>
+    <row r="63" ht="409.5" spans="1:7">
+      <c r="A63" s="10">
         <v>61</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="B63" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G63" s="12"/>
+    </row>
+    <row r="64" ht="409.5" spans="1:7">
+      <c r="A64" s="10">
         <v>62</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="B64" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G64" s="12"/>
+    </row>
+    <row r="65" ht="409.5" spans="1:7">
+      <c r="A65" s="10">
         <v>63</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" ht="151.8" hidden="1" spans="1:6">
-      <c r="A15" s="10" t="s">
+      <c r="B65" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G65" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="66" ht="409.5" spans="1:7">
+      <c r="A66" s="10">
         <v>64</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B66" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="67" ht="374.4" spans="1:7">
+      <c r="A67" s="10">
         <v>65</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="B67" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G67" s="12"/>
+    </row>
+    <row r="68" ht="409.5" spans="1:7">
+      <c r="A68" s="10">
         <v>66</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="B68" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G68" s="11" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="69" ht="409.5" spans="1:7">
+      <c r="A69" s="10">
         <v>67</v>
       </c>
-      <c r="E15" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" ht="165.6" spans="1:6">
-      <c r="A16" s="10" t="s">
+      <c r="B69" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G69" s="12"/>
+    </row>
+    <row r="70" ht="409.5" spans="1:7">
+      <c r="A70" s="10">
         <v>68</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B70" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="F70" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G70" s="12"/>
+    </row>
+    <row r="71" ht="409.5" spans="1:7">
+      <c r="A71" s="10">
         <v>69</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="B71" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="F71" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G71" s="12"/>
+    </row>
+    <row r="72" ht="409.5" spans="1:7">
+      <c r="A72" s="10">
         <v>70</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="B72" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="F72" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G72" s="12"/>
+    </row>
+    <row r="73" ht="409.5" spans="1:7">
+      <c r="A73" s="10">
         <v>71</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" ht="207" hidden="1" spans="1:5">
-      <c r="A17" s="10" t="s">
+      <c r="B73" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="74" ht="374.4" spans="1:7">
+      <c r="A74" s="10">
         <v>72</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B74" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="F74" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G74" s="12"/>
+    </row>
+    <row r="75" ht="409.5" spans="1:7">
+      <c r="A75" s="10">
         <v>73</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="B75" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>326</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="F75" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G75" s="12"/>
+    </row>
+    <row r="76" ht="409.5" spans="1:7">
+      <c r="A76" s="10">
         <v>74</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="B76" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="F76" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G76" s="12"/>
+    </row>
+    <row r="77" ht="403.2" spans="1:7">
+      <c r="A77" s="10">
         <v>75</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" ht="151.8" hidden="1" spans="1:5">
-      <c r="A18" s="10" t="s">
+      <c r="B77" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="F77" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G77" s="12" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="78" ht="409.5" spans="1:7">
+      <c r="A78" s="10">
         <v>76</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B78" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="F78" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G78" s="12"/>
+    </row>
+    <row r="79" ht="409.5" spans="1:7">
+      <c r="A79" s="10">
         <v>77</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="B79" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="D79" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="E79" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="F79" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G79" s="12"/>
+    </row>
+    <row r="80" ht="409.5" spans="1:7">
+      <c r="A80" s="10">
         <v>78</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="B80" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="D80" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="F80" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G80" s="11" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="81" ht="409.5" spans="1:7">
+      <c r="A81" s="10">
         <v>79</v>
       </c>
-      <c r="E18" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" ht="165.6" hidden="1" spans="1:5">
-      <c r="A19" s="10" t="s">
+      <c r="B81" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="F81" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G81" s="12"/>
+    </row>
+    <row r="82" ht="409.5" spans="1:7">
+      <c r="A82" s="10">
         <v>80</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B82" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="D82" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="F82" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G82" s="12"/>
+    </row>
+    <row r="83" ht="409.5" spans="1:7">
+      <c r="A83" s="10">
         <v>81</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" ht="138" hidden="1" spans="1:5">
-      <c r="A20" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" ht="151.8" hidden="1" spans="1:5">
-      <c r="A21" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" ht="179.4" hidden="1" spans="1:5">
-      <c r="A22" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" ht="165.6" hidden="1" spans="1:5">
-      <c r="A23" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" ht="165.6" hidden="1" spans="1:5">
-      <c r="A24" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" ht="151.8" hidden="1" spans="1:5">
-      <c r="A25" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" ht="151.8" hidden="1" spans="1:5">
-      <c r="A26" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" ht="165.6" hidden="1" spans="1:5">
-      <c r="A27" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" ht="165.6" hidden="1" spans="1:5">
-      <c r="A28" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" ht="179.4" hidden="1" spans="1:5">
-      <c r="A29" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" ht="165.6" hidden="1" spans="1:5">
-      <c r="A30" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" ht="165.6" hidden="1" spans="1:5">
-      <c r="A31" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" ht="165.6" hidden="1" spans="1:5">
-      <c r="A32" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" ht="165.6" hidden="1" spans="1:6">
-      <c r="A33" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" ht="165.6" hidden="1" spans="1:6">
-      <c r="A34" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" ht="151.8" hidden="1" spans="1:6">
-      <c r="A35" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" ht="151.8" hidden="1" spans="1:6">
-      <c r="A36" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" ht="151.8" hidden="1" spans="1:6">
-      <c r="A37" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" ht="165.6" hidden="1" spans="1:6">
-      <c r="A38" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" ht="138" hidden="1" spans="1:6">
-      <c r="A39" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" ht="179.4" hidden="1" spans="1:6">
-      <c r="A40" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="41" ht="165.6" hidden="1" spans="1:6">
-      <c r="A41" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B41" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="42" ht="151.8" hidden="1" spans="1:6">
-      <c r="A42" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="43" ht="409.5" hidden="1" spans="1:6">
-      <c r="A43" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="44" ht="409.5" hidden="1" spans="1:6">
-      <c r="A44" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="B44" s="12" t="s">
+      <c r="B83" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="D83" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="F83" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="C44" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="45" ht="409.5" hidden="1" spans="1:6">
-      <c r="A45" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="46" ht="409.5" hidden="1" spans="1:6">
-      <c r="A46" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="47" ht="409.5" hidden="1" spans="1:6">
-      <c r="A47" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="E47" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="48" ht="409.5" hidden="1" spans="1:6">
-      <c r="A48" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="49" ht="409.5" hidden="1" spans="1:6">
-      <c r="A49" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="50" ht="409.5" hidden="1" spans="1:6">
-      <c r="A50" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="51" ht="409.5" hidden="1" spans="1:6">
-      <c r="A51" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="52" ht="409.5" hidden="1" spans="1:6">
-      <c r="A52" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="53" ht="409.5" hidden="1" spans="1:6">
-      <c r="A53" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="C53" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="54" ht="409.5" hidden="1" spans="1:6">
-      <c r="A54" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="B54" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="E54" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="55" ht="400.2" hidden="1" spans="1:6">
-      <c r="A55" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="C55" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="56" ht="409.5" hidden="1" spans="1:6">
-      <c r="A56" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="B56" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="C56" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="57" ht="409.5" hidden="1" spans="1:6">
-      <c r="A57" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="C57" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="E57" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="58" ht="372.6" hidden="1" spans="1:6">
-      <c r="A58" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="B58" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="C58" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="E58" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="59" ht="409.5" hidden="1" spans="1:6">
-      <c r="A59" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="C59" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="E59" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F59" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="60" ht="409.5" hidden="1" spans="1:6">
-      <c r="A60" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="C60" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="E60" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="61" ht="409.5" hidden="1" spans="1:6">
-      <c r="A61" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="B61" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="C61" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="E61" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="62" ht="409.5" hidden="1" spans="1:6">
-      <c r="A62" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="B62" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="E62" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="63" ht="409.5" hidden="1" spans="1:6">
-      <c r="A63" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="E63" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="64" ht="409.5" hidden="1" spans="1:6">
-      <c r="A64" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="B64" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="E64" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="65" ht="409.5" hidden="1" spans="1:6">
-      <c r="A65" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="B65" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="D65" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="66" ht="409.5" hidden="1" spans="1:6">
-      <c r="A66" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="B66" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="C66" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="67" ht="345" hidden="1" spans="1:6">
-      <c r="A67" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="B67" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="68" ht="409.5" hidden="1" spans="1:6">
-      <c r="A68" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="B68" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="C68" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="D68" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F68" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="69" ht="409.5" hidden="1" spans="1:6">
-      <c r="A69" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="B69" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="C69" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="E69" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="70" ht="409.5" hidden="1" spans="1:6">
-      <c r="A70" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="B70" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="C70" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="D70" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="E70" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="71" ht="409.5" hidden="1" spans="1:6">
-      <c r="A71" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="B71" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="D71" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="E71" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="72" ht="409.5" hidden="1" spans="1:6">
-      <c r="A72" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="B72" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="C72" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="E72" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="73" ht="409.5" hidden="1" spans="1:6">
-      <c r="A73" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="B73" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="C73" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="E73" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="74" ht="358.8" hidden="1" spans="1:6">
-      <c r="A74" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="B74" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="C74" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="E74" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="75" ht="409.5" hidden="1" spans="1:6">
-      <c r="A75" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="B75" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="C75" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="D75" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="E75" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="76" ht="400.2" hidden="1" spans="1:6">
-      <c r="A76" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="B76" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="C76" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="77" ht="386.4" hidden="1" spans="1:6">
-      <c r="A77" s="10" t="s">
-        <v>315</v>
-      </c>
-      <c r="B77" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="C77" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="E77" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="78" ht="409.5" hidden="1" spans="1:6">
-      <c r="A78" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="B78" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="C78" s="12" t="s">
-        <v>321</v>
-      </c>
-      <c r="D78" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="E78" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="79" ht="400.2" hidden="1" spans="1:6">
-      <c r="A79" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="B79" s="12" t="s">
-        <v>324</v>
-      </c>
-      <c r="C79" s="12" t="s">
-        <v>325</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="E79" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="80" ht="409.5" hidden="1" spans="1:6">
-      <c r="A80" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="B80" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="C80" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="D80" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="E80" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="81" ht="409.5" hidden="1" spans="1:5">
-      <c r="A81" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="B81" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="C81" s="12" t="s">
-        <v>334</v>
-      </c>
-      <c r="D81" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="E81" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="82" ht="409.5" hidden="1" spans="1:5">
-      <c r="A82" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="B82" s="12" t="s">
-        <v>337</v>
-      </c>
-      <c r="C82" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D82" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="E82" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="83" ht="409.5" hidden="1" spans="1:5">
-      <c r="A83" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="B83" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="C83" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="E83" s="11" t="s">
-        <v>168</v>
+      <c r="G83" s="11" t="s">
+        <v>363</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F83" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="第十四章（14）"/>
-      </filters>
-    </filterColumn>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G83" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4059,18 +4471,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultColWidth="15.8796296296296" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr defaultColWidth="15.8796296296296" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="17.6481481481481" customWidth="1"/>
-    <col min="2" max="2" width="51.8240740740741" style="2" customWidth="1"/>
-    <col min="3" max="3" width="55.8240740740741" style="2" customWidth="1"/>
-    <col min="4" max="4" width="75.25" customWidth="1"/>
-    <col min="5" max="6" width="28.5" customWidth="1"/>
-    <col min="7" max="16384" width="15.8796296296296" customWidth="1"/>
+    <col min="1" max="1" width="5.5462962962963" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.6481481481481" style="2" customWidth="1"/>
+    <col min="3" max="3" width="51.8240740740741" style="3" customWidth="1"/>
+    <col min="4" max="4" width="55.8240740740741" style="3" customWidth="1"/>
+    <col min="5" max="5" width="75.25" style="2" customWidth="1"/>
+    <col min="6" max="7" width="28.5" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="15.8796296296296" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4089,495 +4502,579 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" ht="145.2" customHeight="1" spans="1:6">
-      <c r="A2" s="3" t="s">
-        <v>344</v>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" ht="145.2" customHeight="1" spans="1:7">
+      <c r="A2" s="2">
+        <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>346</v>
+        <v>364</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>365</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="3" ht="132" customHeight="1" spans="1:6">
-      <c r="A3" s="3" t="s">
-        <v>349</v>
+        <v>366</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" ht="132" customHeight="1" spans="1:7">
+      <c r="A3" s="2">
+        <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>351</v>
+        <v>369</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>370</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" ht="105.6" customHeight="1" spans="1:6">
-      <c r="A4" s="3" t="s">
-        <v>353</v>
+        <v>371</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" ht="105.6" customHeight="1" spans="1:7">
+      <c r="A4" s="2">
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>355</v>
+        <v>373</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>374</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" ht="92.4" customHeight="1" spans="1:6">
-      <c r="A5" s="3" t="s">
-        <v>357</v>
+        <v>375</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" ht="92.4" customHeight="1" spans="1:7">
+      <c r="A5" s="2">
+        <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>359</v>
+        <v>377</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>378</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" ht="118.8" customHeight="1" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>362</v>
+        <v>379</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" ht="118.8" customHeight="1" spans="1:7">
+      <c r="A6" s="2">
+        <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>364</v>
+        <v>382</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>383</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" ht="92.4" customHeight="1" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>367</v>
+        <v>384</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" ht="92.4" customHeight="1" spans="1:7">
+      <c r="A7" s="2">
+        <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>369</v>
+        <v>387</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>388</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" ht="118.8" customHeight="1" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>372</v>
+        <v>389</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" ht="118.8" customHeight="1" spans="1:7">
+      <c r="A8" s="2">
+        <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>374</v>
+        <v>392</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>393</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" ht="118.8" customHeight="1" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>376</v>
+        <v>394</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" ht="118.8" customHeight="1" spans="1:7">
+      <c r="A9" s="2">
+        <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>378</v>
+        <v>396</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>397</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" ht="79.2" customHeight="1" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>380</v>
+        <v>398</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" ht="79.2" customHeight="1" spans="1:7">
+      <c r="A10" s="2">
+        <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>382</v>
+        <v>400</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>401</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" ht="118.8" customHeight="1" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>384</v>
+        <v>402</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" ht="118.8" customHeight="1" spans="1:7">
+      <c r="A11" s="2">
+        <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>386</v>
+        <v>404</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>405</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" ht="105.6" customHeight="1" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>389</v>
+        <v>406</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" ht="105.6" customHeight="1" spans="1:7">
+      <c r="A12" s="2">
+        <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>391</v>
+        <v>409</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>410</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" ht="105.6" customHeight="1" spans="1:6">
-      <c r="A13" s="3" t="s">
-        <v>394</v>
+        <v>411</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" ht="105.6" customHeight="1" spans="1:7">
+      <c r="A13" s="2">
+        <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>396</v>
+        <v>414</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>415</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" ht="105.6" customHeight="1" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>399</v>
+        <v>416</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" ht="105.6" customHeight="1" spans="1:7">
+      <c r="A14" s="2">
+        <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>401</v>
+        <v>419</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>420</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" ht="92.4" customHeight="1" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>404</v>
+        <v>421</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" ht="92.4" customHeight="1" spans="1:7">
+      <c r="A15" s="2">
+        <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>406</v>
+        <v>424</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>425</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" ht="105.6" customHeight="1" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>409</v>
+        <v>426</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" ht="105.6" customHeight="1" spans="1:7">
+      <c r="A16" s="2">
+        <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>411</v>
+        <v>429</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" ht="92.4" customHeight="1" spans="1:6">
-      <c r="A17" s="3" t="s">
-        <v>413</v>
+        <v>431</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" ht="92.4" customHeight="1" spans="1:7">
+      <c r="A17" s="2">
+        <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>415</v>
+        <v>433</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>434</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" ht="79.2" customHeight="1" spans="1:6">
-      <c r="A18" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>419</v>
+        <v>435</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" ht="79.2" customHeight="1" spans="1:7">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>438</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" ht="79.2" customHeight="1" spans="1:6">
-      <c r="A19" s="3" t="s">
-        <v>421</v>
+        <v>439</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" ht="79.2" customHeight="1" spans="1:7">
+      <c r="A19" s="2">
+        <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>423</v>
+        <v>441</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>442</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="F19" s="3"/>
-    </row>
-    <row r="20" ht="92.4" customHeight="1" spans="1:6">
-      <c r="A20" s="3" t="s">
-        <v>425</v>
+        <v>443</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" ht="92.4" customHeight="1" spans="1:7">
+      <c r="A20" s="2">
+        <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>427</v>
+        <v>445</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>446</v>
       </c>
       <c r="D20" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="F20" s="3"/>
-    </row>
-    <row r="21" ht="118.8" customHeight="1" spans="1:6">
-      <c r="A21" s="3" t="s">
-        <v>429</v>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" ht="118.8" customHeight="1" spans="1:7">
+      <c r="A21" s="2">
+        <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>431</v>
+        <v>449</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>450</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="F21" s="3"/>
-    </row>
-    <row r="22" ht="92.4" customHeight="1" spans="1:6">
-      <c r="A22" s="3" t="s">
-        <v>434</v>
+        <v>451</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" ht="92.4" customHeight="1" spans="1:7">
+      <c r="A22" s="2">
+        <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>436</v>
+        <v>454</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>455</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="F22" s="3"/>
-    </row>
-    <row r="23" ht="92.4" customHeight="1" spans="1:6">
-      <c r="A23" s="3" t="s">
-        <v>438</v>
+        <v>456</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="G22" s="4"/>
+    </row>
+    <row r="23" ht="92.4" customHeight="1" spans="1:7">
+      <c r="A23" s="2">
+        <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>440</v>
+        <v>458</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>459</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="F23" s="3"/>
-    </row>
-    <row r="24" ht="105.6" customHeight="1" spans="1:6">
-      <c r="A24" s="3" t="s">
-        <v>442</v>
+        <v>460</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" ht="105.6" customHeight="1" spans="1:7">
+      <c r="A24" s="2">
+        <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>444</v>
+        <v>462</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>463</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" ht="79.2" customHeight="1" spans="1:6">
-      <c r="A25" s="3" t="s">
-        <v>446</v>
+        <v>464</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" ht="79.2" customHeight="1" spans="1:7">
+      <c r="A25" s="2">
+        <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>448</v>
+        <v>466</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>467</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="F25" s="3"/>
-    </row>
-    <row r="26" ht="92.4" customHeight="1" spans="1:6">
-      <c r="A26" s="3" t="s">
-        <v>450</v>
+        <v>468</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26" ht="92.4" customHeight="1" spans="1:7">
+      <c r="A26" s="2">
+        <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>452</v>
+        <v>470</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>471</v>
       </c>
       <c r="D26" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="F26" s="3"/>
-    </row>
-    <row r="27" ht="118.8" customHeight="1" spans="1:6">
-      <c r="A27" s="3" t="s">
-        <v>454</v>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" ht="118.8" customHeight="1" spans="1:7">
+      <c r="A27" s="2">
+        <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>455</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>456</v>
+        <v>474</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>475</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="F27" s="3"/>
-    </row>
-    <row r="28" ht="132" customHeight="1" spans="1:6">
-      <c r="A28" s="3" t="s">
-        <v>458</v>
+        <v>476</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" ht="132" customHeight="1" spans="1:7">
+      <c r="A28" s="2">
+        <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>460</v>
+        <v>478</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>479</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="F28" s="3"/>
+        <v>480</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="G28" s="4"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F28" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G28" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/book.xlsx
+++ b/book.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19644" windowHeight="7620"/>
+    <workbookView windowWidth="25068" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="道德经" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="471">
   <si>
     <t>no</t>
   </si>
@@ -100,7 +100,7 @@
     <t>道经</t>
   </si>
   <si>
-    <t>第四章、第十四章</t>
+    <t>4、14</t>
   </si>
   <si>
     <t>第二章（2）</t>
@@ -116,7 +116,7 @@
 因此圣人处无为之事，行不言之教：越是懂得有为，越要知道哪些该无为、该舍掉，从反面认识事情，才能达到更好的有为效果，千万不要把无为理解成消极。万物作焉而不辞，生而不有，为而不恃，功成而弗居：顺应万物自然生长而不干预，创造而不占有，做事而不依仗，有功而不居功，正因不居功，功德才不离去。本章后文许多重要内容提前概括出来，读熟这一章，后面很多章节都能以经解经。</t>
   </si>
   <si>
-    <t>第十一章、第三十九章、第六十三章、第六十六章</t>
+    <t>11、39、63、66</t>
   </si>
   <si>
     <t>第三章（3）</t>
@@ -132,9 +132,6 @@
 圣人之治，虚其心，实其腹，弱其志，强其骨：使民心虚静、生活温饱、欲望减弱、身体强健。常使民无知无欲，使夫智者不敢为也：少用智巧套路，投机者才不敢妄为。为无为，则无不治：治理者不妄为、不折腾，按规律和规则办事，天下自然治理得好。译者·韩鹏杰强调，老子的话对面坐着的是领导者，这些话是对治理者提出的警醒：任何事都有尺度，把握不好度，好事也会变成坏事。</t>
   </si>
   <si>
-    <t>第三十二章</t>
-  </si>
-  <si>
     <t>第四章（4）</t>
   </si>
   <si>
@@ -148,7 +145,7 @@
 译者·韩鹏杰用第四十二章“道生一，一生二，二生三，三生万物；万物负阴而抱阳，冲气以为和”来印证：三即参，阴阳参与到一起而生万物，万事万物都同时具有阴阳两面，无论怎么转都像太极图一样保持和谐。了解道冲，就掌握了一种重要思维：任何事物都是两种相反力量在动态中达成的和谐，看问题、做决策都不能只偏执一方。</t>
   </si>
   <si>
-    <t>第九章、第四十二章、第七十一章</t>
+    <t>9、42、71</t>
   </si>
   <si>
     <t>第五章（5）</t>
@@ -164,9 +161,6 @@
 天地之间，其犹橐籥乎：天地像风箱，中间虚静，一拉动就能鼓出风来；政令也应如此，保持虚静、简要稳定，不能今天一变明天一变。多言数穷，不如守中：政令繁多、变动频繁会把自己逼入困境，不如恰到好处、大道至简。译者·韩鹏杰提醒，这些话都是讲给领导者听的：治理要公平无私，政令要少而稳定，靠规则而不是靠折腾。</t>
   </si>
   <si>
-    <t>第五十七章</t>
-  </si>
-  <si>
     <t>第六章（6）</t>
   </si>
   <si>
@@ -180,7 +174,7 @@
 译者·韩鹏杰强调，老子用神、玄这些最高字眼来称呼谷与牝，绝不允许亵渎；一个文化里若失去对母亲的尊重、对生命的敬畏，其他方面都会崩塌。读这一章不要陷入玄虚，要读出其中朴素而伟大的情感：尊重母亲、敬畏生命，是文化延续的根基。</t>
   </si>
   <si>
-    <t>第二十章、第二十五章、第五十二章</t>
+    <t>20、25、52</t>
   </si>
   <si>
     <t>第七章（7）</t>
@@ -196,7 +190,7 @@
 本章是典型的“天道人道”两段论：先讲天道，再讲人道，人道效法天道。译者·韩鹏杰用“公仪休不受鱼”的故事说明：懂得从长远看问题、不贪眼前不该得的利益，才能长久地满足自己的愿望；只盯着私利的人，最后连私利也保不住。</t>
   </si>
   <si>
-    <t>第六十六章、第八十一章</t>
+    <t>66、81</t>
   </si>
   <si>
     <t>第八章（8）</t>
@@ -212,7 +206,7 @@
 水的“不争”有丰富含义：有边界不争（湖有湖畔、河有河堤、海有海岸），有秩序不争（前后相随、循序渐进），有牺牲不争（成就万物而默默无闻）。夫唯不争，故无尤：不争就不会招来怨恨和过错。译者·韩鹏杰指出，老子不是趴在河边悟道，而是借水的形象传达从战争、政治、人生中领悟的智慧：善于成就别人，同时也成就自己，这正是双赢。</t>
   </si>
   <si>
-    <t>第六十三章、第六十九章、第七十八章</t>
+    <t>63、69、78</t>
   </si>
   <si>
     <t>第九章（9）</t>
@@ -228,7 +222,7 @@
 译者·韩鹏杰用民间故事讲这个道理：弟弟只拿一点金子平安回家，哥哥贪心装满全身，被太阳晒化。第七章讲先后，第八章讲不争，第九章讲不盈，都提醒人知进退、懂谦让。中国文化的“中”就是恰到好处，不走到极端：物极必反、乐极生悲、泰极否来，好事到了极端容易向坏处转化，所以要战战兢兢、如履薄冰地把握分寸。</t>
   </si>
   <si>
-    <t>第二章、第四章、第七十八章</t>
+    <t>2、4、78</t>
   </si>
   <si>
     <t>第十章（10）</t>
@@ -244,7 +238,7 @@
 一连串反问都在讲修养路径：魂魄不离、身心合一、少欲守静、厚道不用智巧。最后点出玄德：生之畜之，生而不有，为而不恃，长而不宰——生养万物而不占有、不倚仗、不主宰，这是最高深的德。译者·韩鹏杰认为这一章是后面九章的总纲，虚静既是个人修养，也是治国的基础。</t>
   </si>
   <si>
-    <t>第四十二章、第五十七章、第七十一章、第七十五章</t>
+    <t>42、57、71、75</t>
   </si>
   <si>
     <t>第十一章（11）</t>
@@ -260,7 +254,7 @@
 译者·韩鹏杰指出，“利用”这个词就来自本章。第十章讲虚静，本章讲怎样虚静——心里放空，去掉杂念，才能听得进别人的意见、看得见别人的长处、学得到别人的优点，虚怀若谷、满招损谦受益。中国文化的悟道方式是“给一个形象，自己领悟”，本章就是最好的示范：通过车、器、室三个形象，让人领悟空与用的道理。</t>
   </si>
   <si>
-    <t>第二章、第六十六章</t>
+    <t>2、66</t>
   </si>
   <si>
     <t>第十二章（12）</t>
@@ -276,7 +270,7 @@
 是以圣人为腹不为目，故去彼取此：圣人重实质内容，不重外在浮华；取舍的标准是看什么最重要——健康、营养、真实比外表颜色更重要。译者·韩鹏杰把本章与第十章、十一章连起来读：虚静的心才能看清本质，处其厚不居其薄，掌握生命中真正重要的东西，返璞归真。</t>
   </si>
   <si>
-    <t>第十章、第十一章</t>
+    <t>10、11</t>
   </si>
   <si>
     <t>第十三章（13）</t>
@@ -305,9 +299,6 @@
 执古之道，以御今之有：了解古往今来的大道，才能把握今天、做好今天的事；能知古始，是谓道纪：知道万物开始的道理，就是把握了道的纲领。译者·韩鹏杰用庄子的“道在瓦片、稗草、大小便中”来说明道无在无不在，越往下越有；用风的形象说明道无形却左右万物。学习本章要记住：道看不见摸不着，但真实存在、无处不在，了解它才能做好今天的事。</t>
   </si>
   <si>
-    <t>第一章</t>
-  </si>
-  <si>
     <t>第十五章（15）</t>
   </si>
   <si>
@@ -321,9 +312,6 @@
 孰能浊以静之徐清？孰能安以久动之徐生：浊水静下来才能慢慢澄清，安定的状态动起来才能慢慢焕发生机，这是“静中求清、动中求生”的修养。保此道者不欲盈，夫唯不盈，故能蔽而新成：守道者不求满，留出空间，舍弃旧的东西才能革故鼎新。译者·韩鹏杰强调，书中的话多针对具体的人讲，本章针对带领十几人做事的小组长等“士”阶层，说明基层领导者也需要很高的素质：谨慎、敬畏、质朴、虚怀、不盈。</t>
   </si>
   <si>
-    <t>第二十六章</t>
-  </si>
-  <si>
     <t>第十六章（16）</t>
   </si>
   <si>
@@ -389,9 +377,6 @@
 众人皆有余，而我独若遗：众人都显得富足有余，得道者却像有所遗失。我愚人之心也哉，沌沌兮：一副愚人心肠，混沌淳朴。俗人昭昭，我独昏昏；俗人察察，我独闷闷：世人精明，得道者看似糊涂宽厚。澹兮其若海，飂兮若无止：他像大海一样淡泊深沉，像长风一样自由无羁。众人皆有以，而我独顽似鄙：世人都有用处，他看似冥顽无能。我独异于人，而贵食母：与众人不同，因为他以大道为归依。本章刻画了不随波逐流、独立守道的精神境界。</t>
   </si>
   <si>
-    <t>第六章</t>
-  </si>
-  <si>
     <t>第二十一章（21）</t>
   </si>
   <si>
@@ -470,9 +455,6 @@
 轻则失根：轻率轻浮就失去根本，像飘蓬浮萍没有根基；躁则失君：浮躁急躁就失去对自己的掌控，冲动之下常常酿成大祸。译者·韩鹏杰用“路怒”举例：开车偶有小摩擦就粗口相向甚至拔刀，动手前问自己要不要动手、后果如何、有无别的办法，几秒钟的冷静可能改变结果。开头八字“重为轻根，静为躁君”与结尾“轻则失根，躁则失君”都是至理名言。</t>
   </si>
   <si>
-    <t>第十五章</t>
-  </si>
-  <si>
     <t>第二十七章（27）</t>
   </si>
   <si>
@@ -552,9 +534,6 @@
 始制有名，名亦既有，夫亦将知止，知止可以不殆：人类社会开始有制度、名分是合理的，但有了名分制度要懂得边界，不能制度崇拜、名分崇拜，做过了头就走向反面；知道适可而止，才能避免危险。譬道之在天下，犹川谷之于江海：道在天下，就像川谷流向江海，是自然归附的过程，不是强迫。译者·韩鹏杰强调，老子反复用重复和强调来突出重要思想，本章的核心就是朴与知止：做事朴实厚道，对制度名分保持克制，知道边界和限度，物极必反，知止不殆。</t>
   </si>
   <si>
-    <t>第三章</t>
-  </si>
-  <si>
     <t>第三十三章（33）</t>
   </si>
   <si>
@@ -649,9 +628,6 @@
 是以侯王自谓孤、寡、不穀：侯王自称孤、寡、不穀，正是以贱为本、以下为基。致数舆无舆：刻意追求众多荣誉反而失去荣誉。是故不欲琭琭如玉，珞珞如石：不要像华美的玉，要像坚硬的石头，石头能铺路济人，华美的玉看似高贵却少有用处。译者·韩鹏杰强调两个重点：一是“一”即道，是阴阳统一；二是“贵以贱为本，高以下为基”，位置越高越要善于处下，把根基打牢，做人要处实不居华。</t>
   </si>
   <si>
-    <t>第二章</t>
-  </si>
-  <si>
     <t>第四十章（40）</t>
   </si>
   <si>
@@ -689,7 +665,7 @@
     <t>《德经》部分我们今天讲四十二章。老规矩，把以前的这几章我们再顺一下。《德经》从第三十八章开始，第三十八章讲“上德不德，是以有德；下德不失德，是以无德。”第三十九章我们讲了两个重要的部分，一个就是这个“一”，因为第四十二章又出现了这个“一”，就是阴阳两者的相互平衡，形成的统一体。在第三十九章里边有两句话每一次我都要重申一下，以求让大家牢牢地记忆，“贵以贱为本，高以下为基”。第四十章有一个全部这本书思维的总纲，“反者，道之动”。下边举的这些都是“反者，道之动”的一些例证。比如说“弱者，道之用，天下万物生于有，生于无”。第四十一章的时候，我们是花了比较多的时间来说，为什么呢？因为这一章里边有非常多的“反者，道之动”的例证。比如说“大音希声，大象无形，大器晚成……”这些都是我们平时经常讲的成语。上次讲完了大家应该知道了它的出处。那么今天我们讲第四十二章，这一章并不难理解，但是非常的重要。因为这一章开头这段话，大家经常在很多地方看到，比如北京故宫是建筑的典范，故宫的太和、保和、中和三大殿都是三层台基，也就是建在三层高台之上，为什么选择“三”这个数字呢？再比如我所在的学校叫做西安交通大学，在交大的管理学院，我的一个朋友也在那做了一面墙的雕塑：太极，大家有机会到交大管理学院的时候就会看到，就在一楼。这两个地方的解释，用的都是这段话：“道生一，一生二，二生三，三生万物。”我们来解释这段话，原文大家都看到了：“道生一，一生二，二生三，三生万物。万物负阴而抱阳，冲气以为和。”这个“冲”字，读成中，一下就理解了。下面这段话其实大家也耳熟，起码意思在前边已经说过。“人之所恶，为孤寡不穀，而王公以为称。”大家讨厌的孤、寡、不榖，王公却用来称呼自己，这不是我们前面第三十九章的时候已经说过的这个意思嘛。“故物或损之而益，或益之而损。人之所教，我亦教之，强梁者不得其死，吾将以为教父。”这是第四十二章原文。我们一段一段来解释。先说第一段，“道生一”。“一”我们俗称叫太极。其实“一”就是道的具体的特点，强调道就是“一”，是说道的最重要的一个特点，就是它强调阴阳两者的统一，“一”里边蕴含着阴和阳两种力量，两个方面。“道生一，一生二”，这个“一”里边蕴含着“二”，也就是道里边蕴含着阴阳两种力量，两个方面，两种状态。中国人讲，事物都是相互对立而存在的，万事万物归结到最后，它也不会是一个单一的元素。你看咱们中国历史上的《易经》，落到最后就是两个符号，阴和阳。那已经到了事物的极致了，极点了。把阴和阳统一起来叫太极，但是这两个元素是最基本的。所以“一生二”，是说太极道里边蕴涵着阴阳两个方面，两种力量。“二生三”，很多人对这个“二生三”解释得太费劲。“三”是什么？很简单，就是繁体字那个“叁”，就是参。阴阳两者参与到一起，相互作用，形成了万事万物，多简单的事情。它们两者孤阴不生，孤阳不长，两者相互作用，形成万事万物，“三生万物”。所以我们用的那个《中庸》的名言叫“参天地，赞化育”。人能参与到天地之间的运动发展，天地人三才嘛。三才你看人不也参与其中嘛。这个赞可不是赞扬的意思，也是参与的意思。两者参与到一起，产生万事万物，这是从正面。然后再反过来推，既然是三生万物，那么万事万物里边都包含着这两种力量，两个方面，阴阳两个方面，所以叫“万物负阴而抱阳”。随便找，哪一个事物内部都有阴有阳，都包含着阴阳两种状态、两种力量。“万物负阴而抱阳，冲气以为和”。为什么要把这个“冲”念成“中”呢？大家看“冲”的写法，前边这两点其实就代表着阴和阳，那个中就是中和的意思，就是参的意思。阴阳两种力量，中国人把它叫做气，阴气、阳气嘛。通天下一气，形成和谐的、动态的、运动的世界，这就是冲气以为和。这一段讲了我们中国哲学中的宇宙生成模式，也讲了这个世界存在的状态，以及这个状态的原因。这种状态都是阴阳两者运动所形成的，动态的、和谐的状态。冲气以为和。再重复一遍。“道生一，一生二，二生三，三生万物。”所以万事万物都有阴阳两个方面，“万物负阴而抱阳，冲气以为和。”下边就开始讲。用这种思维方式你来理解世界，你就不能只站在一个方面了，明确地告诉你了。事物都是统一的，两个方面不可偏颇，不可偏废。所以对侯王讲，“人之所恶，唯孤寡不穀。”你说大家最讨厌的就是这些词，孤家、寡人、吃不上饭、饿死。可是你看这些王公大人，包括后来的皇帝，他们都拿这个来称呼自己。干嘛呢？“故物，或损之而益，或益之而损。”这个“物”大家不要解释成物质，就是我们中国人常讲的那个“东西”。中国人这个“东西”太奥妙了，什么都可以称之为东西，不管是物质的、精神的都可以称之为东西。所以老子就说你看说到万事万物存在的这些各类各样的东西，“或损之而益”，你以为它受损了，其实它得到了益处。有的时候我们受到一点挫折，我们觉得自己受了多大的这种屈辱一样，可是你知道人都是在不断地受的这种损中逐渐地成长起来的，你认为它是祸，其实它是福，“损之而益”。有的时候你认为自己是得到了，其实反而是一种损失。比如偷了东西的，得到了，其实把人格给损失掉了。有的人用不光彩的手段，不择手段得到的，其实他们损失的反而更大，“或益之而损”。所以老子讲的是相反相成的道理。我们中国人常用什么事情来说这个事？叫破财免灾，叫大难不死必有后福，叫祸福相依，叫塞翁失马焉知非福，你看这讲的都是“损之而益，益之而损”。刚才举的例子不就是这样吗？这侯王王公们不都在损自己吗？把自己叫做“孤寡不穀”。其实有这个提醒之后，反而避免了自己变成孤寡不穀。以前中国人也有这个习惯，给小孩起名起个贱名，好养活。当然现在这种习俗很少再看到了，它讲究的就是“损之而益，益之而损”。民间很多的道理大家也得认真对待，别以为我们上了学之后自己水平就高了，其实真正的高手在民间。很多老人讲的话，到最后你一生体会，反而你发现真的是有道理。“人之所教，我亦教之，强梁者不得其死”。老子也说这些东西，也都是别人教给我的，给我讲的。我再把这些写出来教给大家。这一句我们可得好好地来给大家说道说道。为什么呢？因为这涉及老子的思想的来源，老子的思想来源当然有很多方面，主要的两条，两条道路。一条道路自然就是《易经》。因为你看，《易经》它把这个叫易以道阴阳，老子也讲阴阳，而且这里边的损和益，这不就是《易经》里边的损卦和益卦嘛，损和益这也是《易经》里边经常强调的。另外一个，我觉得这一章里边非常奥妙，一个是讲这阴阳的事情，让我们知道他的思想里边《易经》是中国文化之源，众经之首，损之而益，益之而损。另外一个也表现出他的思想的来源，就是“强梁者不得其死”，这句话也不是老子自己的，它出自《金人铭》。传说黄帝写了六篇铭文，叫《黄帝六铭》。其中有一个是刻在周朝台阶右面立着的金人背后，金人就是青铜做的，这金人的背后有铭文。经过汉朝的刘向《说苑》的考证对比，发现《金人铭》里边的这句话：“强梁者不得其死”。“强梁”就是处处逞强。喜欢暴力的人，最后不会有好的结果。我们讲死得其所，叫得其死，得好死，不得好死，不得其死。强梁者不得其死。说到“强梁”这个词，我想读过《水浒传》的人一定记得，在《水浒传》里边用到“强梁”这个词的时候，是用在了矮脚虎王英的身上。矮脚虎王英，这个是梁山泊里边大家都瞧不上的那么一个人。原来是个车夫，后来抢劫，后来落草。所以用这个词来形容他，“强梁者”。“强梁者不得其死”，老子非常反对强暴，而强调和平、守弱，认为“强梁者不得其死”，“木强则折，兵强则灭”，这是他后边关于这个问题的一个延伸。“吾将以为教父”，这个“教父”就是说，这是别人教给我的，我也把它拿来作为座右铭，来指导我自己。总结一下，大家看这一章，第一段话是我们大家都耳熟能详的，“道生一，一生二，三生万物，万物负阴而抱阳，冲气以为和。”第二段是我们前边讲过的内容，在这个里边又重申了一遍，注意这些重申可不是排版排错了。因为《道德经》里边它讲的几条重要的原则，遇到机会的时候，它就会反复，用重复的方式来强调。“人之所恶，唯孤寡不穀，而王公以为称。”所以对于万事万物而言，对这个世界存在的东西而言，“或损之而益，或益之而损”。有的你觉得是损失了，结果反而是得到了。有的你认为自己得到了，反而是损失掉了。因此不可一概而论。遇到了乐事的时候，不要过于高兴，以免乐极生悲。遇到不好的事，祸事的时候，也不要丧气，因为这些可以成为我们的经验，塞翁失马，焉知非福！这是别人教给我的，我也把它来教给别人。然后下边这句话是老子也非常强调的，“强梁者不得其死”，还是要和平，还是要守弱，处处逞强，总和别人结梁子，最后不会有好的结果。国家也一样，“国虽大，好战必亡”。老子说我也要把这个当作座右铭，这就明显地透露出他思想的来源，一源于《易经》，阴阳之学，损益之论，谦卑之礼。二源于《金人铭》，尤其是《金人铭》里这句话对老子影响是非常大的，所以他把它叫做“教父”，座右铭。</t>
   </si>
   <si>
-    <t>第四章、第十章</t>
+    <t>4、10</t>
   </si>
   <si>
     <t>第四十三章（43）</t>
@@ -872,7 +848,7 @@
     <t>第五十七章的这段话非常有智慧，因为这段话一开始就指出来了，事物之间的不同，有本质的区别，所以处理问题、解决问题的方式方法也不一样。“以正治国，以奇用兵”，治国讲究的是堂堂正道。道家讲的“正”当然就是清静无为，不多事，不扰民，这就是道家讲的正道，是治国的大道理。可是用兵讲究的是“以奇用兵”，“兵者诡道也”，兵不厌诈。所以不能把用兵的方式、战争的方式用到治国的上面来，这两者不同，解决的方式也不一样。“以无事取天下”，无事就是不多事、不扰民、不刁难，这样才能够得到天下，并且坐得了江山。道家“无事”是“无为”的一个重要的方面，不多事、不扰民、不刁难，而“有为”讲的是妄为，多事、扰民、刁难，我们在前边这一点已经非常明确了。“吾何以知其然哉”，我怎么知道是这个样子呢？所谓“以此”就是依据上边“以正治国，以奇用兵”它们之间的本质不一样，所以解决的方式方法也不同而得出的结论。下面，老子开始谈他对治理天下的重要的看法。违背了大道，违背了道家的以“清静无为”为根本来治理国家的方式，会出现什么问题呢？“天下多忌讳，而民弥贫”，治理天下、领导国家忌讳太多，这个也不能动，那个也不能动，这个人的职务比较高，法令涉及不到他，当然出现了忌讳，不敢动，这个地方一定会形成一个空场，形成一个腐败的群体。百姓当然越来越穷了，财富都集中在少数人的手上。“民多利器，国家滋昏”，“滋”就是越来越。如果民间利器众多，武器众多，民与民之间械斗、抗法，那国家当然越来越混乱。“人多伎巧，奇物滋起”，“伎巧”就是各种各样的奇技淫巧，越来越多，大家对这些越来越感兴趣，这个技巧能够给他们带来利益，那么各种各样的奇奇怪怪的东西，甚至包括那些妖孽的东西，就不断兴起。“法令滋彰，盗贼多有”，既然这样，要用法律来管，法条定得越来越多，越来越严苛，反而盗贼越来越多。在前面这一段讲完之后，《道德经》说“故圣人云”，很明显，这是引用以往的通达事理的王们的话，老子用自己心中有智慧的人的语言来作为结尾。“我无为而民自化”，道家讲的无为，第一，“不妄为”。第十六章里边说“不知常，妄作，凶”，不了解事物的规律、规则，瞎折腾、胡折腾，这个结果是非常糟糕的。第二是“不多为”。抓住关键，举重若轻，多言数穷，不如守中，适可而止，恰到好处。第三讲究的是“有所不为”。人要想有所为，必须有所不为。一个政府也罢，一个领导者也罢，所有的事情都抓在自己手上，那底下的人怎么得到锻炼呢？不把担子压给他，他怎么练出独当一面的能力呢？什么事都控制在自己手上，那众人怎么样自我化育自我成长呢？所以无为才能让国家的人民、才能让自己的属下自我化育自我成长。事情成了应该怎么样呢？第十七章“功成事遂，百姓皆谓‘我自然’”，事情做成了，百姓都说这是我们的努力把这事情做成的，这就叫“民自化”。“我好静而民自正”，前面我们讲过，道家讲的静，内心的清净，静下来才能找到解决事物的正确的方法。我清静，走正道，不那么浮躁、急躁、暴躁、狂躁，做一个好的表率，上梁而正，百姓当然也就正了，百姓当然也就好静而走正道了。“我无事而民自富”，不多事、不扰民、不刁难，那百姓自然就富起来了。“我无欲而民自朴”，“朴”就是原木，《道德经》里用原木喻指做事敦厚、朴实、厚道，没那么多欲望，不是老想抢夺别人、占有别人的。就像黄宗羲在《明夷待访录》里边讲的，古代的那些皇帝都是什么样的？“离散天下人之儿女，荼毒天下人之肝脑，以供一人之淫乐。”这是我的，普天之下都是我的。所以欲望无止境，你让百姓能够朴实厚道，这也不可能。所以不要欲壑难填，不要什么东西都看作是自己的，可以任意掠夺，这样百姓自然就朴实、厚道，民心淳朴。这里边的两句话，我们国家的领导者讲话的时候也经常引用：“我无为而民自化，我无事而民自富。”所以，第五十七章讲了两个重要的道理，第一个不能把打仗的这一套用到治国之上。治国讲究的是堂堂大道，讲究的是清静无为，所以以无事取天下。第二个就讲站在领导者的角度，站在统治者的角度，应该怎么做呢？无为、好静、无事、无欲，这样自然一切顺理成章，百姓就会自化、自正、自富、自朴，事成了也会“功遂身退，百姓皆谓我自然”。这是一个好的领导者、好的政府做事的道理之所在，反之越多事儿，越是用那种严苛的法令，导致的结果适得其反。忌讳多了，百姓就越来越穷，民间的利器多了，国家就越来越混乱，大家都倾向于奇技淫巧，把这个当作一种喜欢的甚至不停地去追求的目标，那这个国家就越来越怪，各种奇葩的事情都纷至沓来。越觉得法令不够，越制定得严格、细致，以为单靠着法令就可以解决所有问题，反而适得其反，盗贼多有。所以，这一章里边讲的，也是我们经常说的——这本书的总纲：“反者，道之动”。我们考虑问题，不要只考虑它一面，要相反相成，用一个更高的观察事物的角度来理解。</t>
   </si>
   <si>
-    <t>第二章、第五章、第十章</t>
+    <t>2、5、10</t>
   </si>
   <si>
     <t>第五十八章（58）</t>
@@ -947,7 +923,7 @@
     <t>第六十三章的内容，我们在前边已经有所接触。之前我们说，第二章就是《道德经》的“目录”，第二章列出来了后边讲的六个重要内容，有无相生、难易相成等等，这一章的核心就是“难”和“易”。这一章的核心意思就说，要想做大事，先从小事做起，想要以后攻坚克难，你得从容易的事情做起。还有一个重要的问题、重要的智慧：你要把容易的事情当作难的事情来做，要有充分的、认真的准备，提前思考它的步骤、程序、会遇到的问题，这样再出什么问题的时候，你就能从容应对。有这样的态度，天下也没什么难事。天下无难事，但天下都是难事，看你怎么对待。开头这九个字非常有趣：“为无为，事无事，味无味。”“为无为”——想要有为吗？你得先懂得无为的道理。为什么？因为有些事你越有为，越强求，什么事都管，反而最后结果非常不好。道家讲的无为，就是按照道的方式来作为，想要有为，先要懂得无为的道理，不要妄为，要抓住关键，举重若轻，有所舍才能有所得，所以为无为。其实也就是第三十七章里边讲的“道常无为而无不为”，道的规律、规则是什么？用无为的方式达到无不为的效果，更好的效果。我再强调一下，《道德经》里出现得最多的一个词是“天下”。《道德经》针对的是天下，千万不要把道家当作一种消极的被动的思想，它是“想为”，但是强调要通过正确的道路和手段，懂得无为的正确的道路和手段，才能达到真正的有效的为，也就是用无为的方式，达到无不为的这种效果。下边再落一层，“事无事”。大家都想做事，可是大家有没有注意到，有些人他是“找事”，他是捣乱，是阻碍、多事，天下本无事，庸人自扰之。所以我们做事的时候要懂得无事的道理，不要多事，不要找事，不要刁难。尤其是做领导者，没事找事，权力就是刁难，你这不就麻烦了吗？“事无事”，想做事，得懂得无事的道理，不要多事，不要扰民。再落一层，“味无味”。我们经常讲一个词叫“真水无香”，真正好的饮料，就像那白开水一样，没有味道。我们饮食讲究清淡，寡味，少油少盐。最高的味道，反而是没有味道，无味。当然，这三个词核心还是“为无为”，让大家能够更明白一点。老子展开来讲，“事无事”，不要多事，不要扰民，不要刁难，就像“味无味”的道理一样。按照这样的一个逻辑推下来，下面四个字大家就能明白了，“大小、多少”，千万不要把它念成“大小多少”，这个东西就没意义了。这是告诉大家要“大其小”、要“多其少”，要把小事看得很重要，细节决定成败，千万不要忽略这个细节。为什么要“大其小”呢？因为天下的大事，都是从小事做起，为什么要“多其少”呢？因为积少才能成多。想要多，你得从少的一点一点积累，积少成多。就像我们学习《道德经》，一章一章讲，一章一章学，不要着急，最后达到一个整体的理解。我们经常讲“聚沙成塔”、“集腋成裘”，这不都是“多其少”的道理吗？“报怨以德”，按照这种相反相成的道理，对别人的埋怨、恩怨，也应该站在一个“德”的角度，因为德是符合道，用道的东西里面去感化。第六十二章不是讲了吗？“人之不善，何弃之有？”人家有这个埋怨，怎么正确地对待呢？“报怨以德”。用这种智慧和层次，让大家一起能回归到正途，回归到正道。“图难于其易，为大于其细。天下难事必作于易，天下大事必作于细。”这几句话，在我们文化里边名气非常大，因为讲的是哲学上的量的积累达到质的变化的道理。“图难于其易”，“图”就是图谋、计划。你计划想要做难的事情，要从容易的事情做起。“为大于其细”，想要做大的事情，得从小的事情一步一步来。我们大家都知道要脚踏实地，循序渐进，有条不紊，一屋不扫，何以扫天下？“天下难事必作于易”，天下所有的难事，都要从容易的事情做起。就像小孩的培养，让他们在处理小的事情中就形成良好的习惯，把小的事情、容易的事当成培养良好习惯的重要途径，将来，小孩在遇到大事、难事都能从容应对。现在很多人都有一个致命的弱点，大概是人的通病，就是好高骛远，老觉得自己应该是做大事的人，对小的事情不屑一顾。《道德经》就告诉我们这个智慧：想要做难的事情，从容易的事情做起；想要做大的事情，从小的事情做起，“天下大事必作于细”。“是以圣人终不为大，故能成其大。”“是以”，“是”就是这样，“以”就是所以。所以有智慧的领导者就是这样：“终不为大”，不是老说大话，不是老给大家画饼充饥，而是脚踏实地，一步一步地做起，“故能成其大”。一步一步把这个事情完成了，一步一步地完成计划，最后实现一个大的蓝图，好的结果，水到渠成。所以一个有智慧的人，不是老用那些虚幻的东西来画饼充饥，老是给大家讲大话、空话。“终不为大，故能成其大”，最后反而成就了大事，这话讲得非常好。我建议大家学习《道德经》，有一种重要的学习方法，就是反复看。有的人看《道德经》，也许一年就看一章，反复地看，反复地体会，“少则得，多则惑”，“终不为大，故能成其大”。以管窥天，以锥扎地，我们视力更集中，这样把这个事情才能做得更踏实，扎得更透。我们每一次的进步，虽然看起来好像只是一点点，但是这一点点积累起来就不得了了，“终不为大，故能成其大”。“轻诺必寡信”，大家还记得我们在讲《道德经》第八章的时候，就讲过“言善信”，我们中国人喜欢拿潮水作为讲信用的代表和象征，所以，有一个词就叫“潮信”。你看那钱塘潮每到农历八月十八前后就来了，人也应该如此，说话要讲信用，要有诚信，能给别人做成的事我们再去允诺，没把握做成的事，不要轻易去答应，不管我们有多热情。如果我们答应人家的很多事最后都做不成，时间长了，人家一定认为我们是食言而肥，不讲信用。《道德经》讲话是比较宽缓的，但这句话用的就是强逻辑判断，“轻诺必寡信”，这不是对我们委婉的劝告，这简直就是对我们严厉的警告。所以要讲诚信，君子重一诺，一诺千金嘛，所以“轻诺必寡信”，要避免这种结果出现。“多易必多难”，你把这个事情看得很容易，做什么事情，最后一定出问题。世界上哪有容易的事情，吃个饭喝个水，这都需要功夫，需要本事，小事情我们都要认真对待。我们经常讲“小河沟里翻船”，把一个事情看得太容易了，太简单了，往往会在这个事情上出问题。面对很多难的事情，大家战战兢兢，小心谨慎，反而没事，反而就是在一些认为最容易的事情出问题。很多学生做题、考试也是一样，难题没事，在容易的题上，出了问题，回去捶胸顿足，懊悔无比。所以，我们平常要形成一种把容易的事情当作难的事情来做的习惯，你要懂得“多易必多难”，凡事太容易，后面一定会出现很多的困难，出现很多的问题。所以，下边这句话就讲：“是以圣人犹难之”，所以有智慧的人，把这容易的事情都看作很难。天下的事情都当作难的事情来做，反而结果没有什么难的事情，“故终无难矣”。这个道理非常有趣，其实就是相反相成的道理，这个叫“难易相成”。世界上有没有难事呢？有，也没有。你把这个难的事情当作难的事情，看作是无法克服的，它就是难的事情；你把容易的事情当作容易的事情，没有认真对待，最后也会变成难的事情。我们把容易的事情当作难的事情来做，最后那个难的事也就做成了；真正难的事情，我们认真准备，有充分的信心，最后这难的事情也就克服了。“故终无难矣！”世上无难事，这就是“难易相成”的智慧。很多事情，决定于我们的想法、态度，态度不同，难易之间就会相互转化。</t>
   </si>
   <si>
-    <t>第二章、第八章、第六十四章</t>
+    <t>2、8、64</t>
   </si>
   <si>
     <t>第六十四章（64）</t>
@@ -962,9 +938,6 @@
     <t>第六十三章、第六十四章讲的道理，就是大家熟悉的量变和质变的道理，量的积累达到质的变化。但是大家注意，这个量的积累，有向好的方面，也有向不好的方面。前面讲了“为大于其细”，要做大事，从小的事情做起，这样才能最后达到想要的结果，假如积累的是一个不好的量，最后就积重难返。第六十四章一开始就要把两个方面，都给大家做了说明，有的事情在它刚出现向坏的方面发展苗头的时候，我们在这个阶段就把它解决了。这一章里有两个非常重要的内容，一个是大家都熟悉的一段话：“合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。”第二个就告诉我们，做事情要“慎终如始，则无败事”。这两个重要内容，我们先有一个直观的认识，再来读就好理解了。我们一句一句来解释。“其安易持”，“安”就是稳定，局面稳定的时候，容易掌控，就像一个东西，它稳定的时候，你容易把它把握住；它活蹦乱跳的时候，你把握起来就困难了。“其未兆易谋”，“未兆”，没有征兆的时候，苗头还没有开始的时候，容易去谋划。“其脆易泮”，脆的时候一打就打散了。“其微易散”，很微小的时候，很容易把它解散。比如说一件事情，很小的时候，人数很少的时候，你把它处理起来很容易。众怒难犯，一大群人轰起来、闹起来的时候，这事情解决起来就困难。前面告诉大家这些现象，然后告诉大家处理的方法。什么方法呢？“为之于未有”——在事情没有出现的时候，没有开始的时候，要有预见性，就要有作为，凡事预则立，不预则废。“治之于未乱”，还没有出现这种乱象的时候，就把它治理了、解决了。这也是习近平讲话时经常引用的两句话。怎么来理解呢？先给大家说第一个例证。有一次晏子出巡，齐国发大水，把一座石桥给冲毁了，晏子就把自己的船让给了灾民，大家都赞誉晏子爱民如子。然而一位有智慧的高人就批评晏子，就说你做这个国家的宰相，齐国发大水能把一座桥梁冲毁，你都没有预见到，没有提前做出预防，你失职。所以应该是怎么样？“为之于未有”，你别等这个事情都已经成为这个样子，再去处理它，不管你处理的方式多么巧妙，多么有智慧，但是不如让这件事情没有发生。另外一个例证更能说明这个道理。有一次，扁鹊的国王问扁鹊：扁鹊你名气太大了，你是不是国家医术最高的？扁鹊说不是，别人我不知道，起码我大哥、我二哥都比我的医术高。所以这个国王就很奇怪，你大哥、你二哥是谁？他们医术那么高，怎么大家都不知道他们呀？扁鹊就说，我大哥怎么治病的呢？人家还没有病，他告诉人家怎么预防、怎么不得病。这不是“为之于未有”吗？提前就有作为了，预防得病。我二哥怎么治病的呢？人家刚有一点小病，他就把人治好了，不让他酿成大病，“治之于未乱”。所以我们经常讲，凡事预则立，不预则废，要有远见，要有预见，要未雨绸缪。这是讲负面，因为有些事情量的积累是向不好的方面发展的，所以要提前把这个问题给处理掉。下面讲的这个事，非常重要。我们做大事情都要从容易的事情、小的事情，一步一步积累才能达到这种质的变化，要脚踏实地，循序渐进。因为什么呢？“合抱之木，生于毫末”，合抱之木，它是一点一点长起来的。“九层之台，起于累土”，中国文化中，三六九都代表着高、多。那么高的高台也是一层一层土积累起来的。“千里之行，始于足下”，走这么远的路，要脚踏实地一步一步地做起。说到这里，我得加一句，有人老认为道家思想是消极的、被动的、无为的。“合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。”这不就是自强不息吗？所以有些事我们不能人云亦云，我们得看原文，以原典作为证据。“为者败之，执者失之。”“为”就是强为、妄为。因为《道德经》讲的真正的为叫“无为”，就是按照道的方式来作为，不按照道的方式来作为就是强为、妄为。越是强为，最后的结果越糟糕，因为量的积累还不到，你老想强行地发生质变，这不是急躁冒进吗？“执者失之”，就像我们抓沙子一样，你握得越紧，流出来越多，越想用力地把它抓住，反而失去得越来越快。所以一个有智慧的领导者，“无为”，按照道的方式来作为，不妄为，不强为，不多为，有所不为，所以也不会有急躁冒进的失败。“无执故无失”，没有这样的强执，最后也不会失去。“民之从事”，平常人做事，或者说领着大家做事，在什么时候最容易把事情给做砸了呢？“常于几成而败之”，经常在快要接近成功的时候，把事情给做砸了。那应该怎么办？“慎终如始，则无败事。”什么叫慎终如始呢？我先给大家打一个比方，大家走在结着冰的冰面上的时候，刚一下到冰面上都是小心谨慎，战战兢兢。走一会儿，觉得自己走熟了，就放松警惕了，有的干脆最后开始跑了，有的甚至在冰面上炫耀，危险往往就在这个时候发生了。所以我们中国人经常讲一句话叫“行百里者半九十”，一百里的路，走到九十里路的时候，还要当才走了一半，越是剩下那一段的时候越紧要，民间讲“编筐编篓，全在收口”，即最后这个结尾。“慎终如始”，走到最后那几步，还像开始下到冰面上一样小心谨慎，一步都不放松，那就没什么败事，没什么事情做不成。“慎终如始，则无败事”，就是我们现在经常讲的不忘初心，善始善终，那就没有什么事情做不成的。“是以圣人欲不欲”，一个有智慧的人，特别是一个有智慧的领导者，想要的东西是什么呢？是别人都不关心的，都不想要的。因为“天下熙熙，皆为利来；天下攘攘，皆为利往”，大家关心的是获取利益的方式方法，而一个有智慧的人，有智慧的领导者，应该有这种无功利之心。“欲不欲”，别人都不想这样的，反而是你应该考虑的。大家都针对“有”的东西，这有智慧的人、好的领导者得针对这无形的东西：人的精神财富，人的精神世界，人的修养。既然“欲不欲”，你跟一般人的欲望不一样，他们认为那个东西是珍贵的、难得的，反而在你的眼里是不重要的，不把它看作是难得的。领导国家的时候也是如此，第三章讲的，“不贵难得之货，使民不为盗”，形成一种淳朴的风气。“学不学，复众人之所过。”《道德经》讲的道理，叫“绝学”，一般人不愿意学，学这个东西能带来什么样的好处、利益吗？人的境界高的时候，学的很多的东西不就是和一般人不一样的嘛。一般人不愿意学的东西，又花功夫，又不能带来什么实际的利益，可是“学”这些东西代表了真正的智慧与学问。学这些东西干吗呢？“复众人之所过”，这个“复”不是重复，我们下围棋的人都知道有个词叫“复盘”，通过不断的重复模拟来检视，哪个地方下得好，哪个地方下得不好。别人犯的过错像复盘一样历历在目，以此为鉴，别再犯大家都经常犯的错误。“以辅万物之自然，而不敢为。”“以辅万物之自然”，就是按照自然的规律去做，追求的是一种水到渠成、自然而然的结果。“辅自然”就是无为。“而不敢为”，就是不敢妄为。因为我们违背了道，违背了自然规律，哪怕是短时间取得成功，其实也会受到更大的一种惩罚。这章告诉我们，一是我们做事情要“为之于未有，治之于未乱”，懂得预防，懂得不好的事情在苗头出现的时候就把它解决掉；二是我们做事情要脚踏实地，循序渐进；三是我们要“慎终如始”，不忘初心，善始善终，因为我们做事情经常在快要成功的时候，结果功亏一篑，所以要懂得这样一个道理。</t>
   </si>
   <si>
-    <t>第六十三章</t>
-  </si>
-  <si>
     <t>第六十五章（65）</t>
   </si>
   <si>
@@ -989,7 +962,7 @@
     <t>这一章所讲的这个道理是《道德经》从头至尾所强调的“善于处下”，只有善于处下，才能真正居上。我们在一开始说过，《道德经》的很多话是针对那些领导者、统治者讲的，所以老先生认为越是位置高的领导者、统治者，越要善于处下，为什么呢？首先从处下的结果上来看，“江海所以能为百谷王者，以其善下之，故能为百谷王。”这句话我在前面也多次引用过。大江大海之所以能成为大江大海，是因为善于处下，不辞细流，能团结一切可以团结的力量，故能为“百谷王”。老子先拿“百川归海”的形象讲了这个道理，让大家有一个感知。下面就开始讲具体的做法和内容。“是以欲上民，必以言下之。”所以你要想站在上面领导好下面这些人，在语言上要懂得谦逊、谦让。领导者，尤其国君、皇帝这一类的，讲话的时候不能够居高临下，盛气凌人，自尊自大，不可一世。第三十九章说过“贵以贱为本，高以下为基。是以侯王自称孤寡不穀”，所以在语言上要谦逊。“欲先民，必以身后之。”想要站在前面当好领导、当好领头的，要懂得把自己的利益放在后面，想要领导别人就得给别人利益。一个人既要领导别人，又想什么好处、利益、功名都抢在自己手上，这个人下场不是不言而喻的吗？范仲淹的《岳阳楼记》里说“先天下之忧而忧，后天下之乐而乐”，做官、做领导不得如此吗？钱钟书先生认为范仲淹这两句话就是出自《道德经》的。但是人家学得比较好，不也成了大家都熟悉的名句了吗？“是以圣人处上而民不重”，所以一个好的领导者，你在上面领导大家，大家没有感觉到沉重的压力。“处前而民不害”，你在前面领导大家，大家没有感觉到你对他的危害。因为你要想领导别人，得让别人得到利益。西汉史学家司马迁在《史记·循吏列传》说：“公仪休者，鲁博士也。以高弟为鲁相。奉法循理，无所变更，百官自正。使食禄者不得与下民争利，受大者不得取小。”这里的食禄者不与民争利，意思是做官的人不许和百姓争夺利益。“是以天下乐推而不厌”，所以天下的人民都往高举你，往前推你，不感觉到厌倦、厌烦。如果统治者穷奢极欲，危害百姓，草菅人命，下面的人就会感觉到“害”、感觉到“重”，这样的人百姓会“乐推”吗？当然不会。“以其不争，故天下莫能与之争。”一个领导者，能得到了大家的拥护、拥戴，正因为你不争，不与民争利，不与其他人争名，“利而不害，为而不争”，结果是“以其不争，故天下莫能与之争”。越是争的人，最后往往失败得越惨，因为你的位置已经规定了你应有的担当、使命和责任。陈毅元帅讲过“手莫伸，伸手必被捉”，形象而深刻，那么，反过来用这个道理讲，就得以更加明确了。“以其不争，故天下莫能与之争”，所谓“不争”，并不是消极被动，“不争”，当然要了解边界，不争边界之外的东西，这样的话才能“天下乐推而不厌”。</t>
   </si>
   <si>
-    <t>第二章、第七章、第十一章</t>
+    <t>2、7、11</t>
   </si>
   <si>
     <t>第六十七章（67）</t>
@@ -1100,9 +1073,6 @@
     <t>这一章的核心话题还是“民”，解释了三个问题。第一，百姓为什么饥寒交迫；第二，百姓为什么难以治理；第三百姓为什么不怕死。解释完三个内容，然后对领导者、统治者提出要求。“民之饥，以其上食税之多”，百姓为什么饥寒交迫？“上”，上面的领导者、统治者，“食税”，收的税太多了，而且收的税都被这些人挥霍。“民之难治，以其上之有为”，百姓为什么难以治理呢？原因不在他们这儿，是因为上边胡来、瞎折腾。在《道德经》里，“有为”这个词就是妄为，胡折腾，上边老瞎折腾，就把民心折腾乱了。“信不足焉，有不信焉”，折腾得多了，讲的话也不诚信了，也失去百姓的信任，说什么都没用了。“是以难治”，“是”，“这是”的意思。这话讲得就比较理性，你老说他们是刁民，老在他们身上找，其实这原因就在自己的“有为”。老子对坐在对面的那些领导者、统治者就讲，你得找到真正的原因，百姓为什么饥寒交迫？你们收税收得太多了，收的税都被挥霍了。百姓为什么难以治理？你们整天瞎折腾，胡来妄为，把民心搞乱了。“民之轻死，以其求生之厚”。“其”指谁？领导者、统治者。百姓为什么轻死，把死不当一回事？是因为你们这些统治者，把自己的生命看得那么重要，不惜用剥夺的方式积累财富，花天酒地，穷奢极欲，这财富都聚积在他们自己手里，老百姓难以生存。就像国民党时期，财富都积累在“四大家族”手中，很少的人占有了绝大部分的财富，底下的人都生活在水深火热之中。当你“求生之厚”的时候，底下的百姓就觉得没什么活路和希望了，也就不把死当一回事，“是以轻死”。那么应该怎么做呢？“夫唯无以生为者”，不要把自己的生命看作是绝对重要的。不要把财富、好吃的好用的，全都集中在自己这儿来，认为只有自己的生命才是生命，对别人的生命、生存视而不见，感到无足轻重。不把聚敛、穷奢极欲当作生命的重要的部分，这个就是“贤于贵生”。百姓为什么饥寒交迫？上食税之多；为什么难以治理？上面胡来妄为；为什么不怕死？求生之厚。这章三个并列句，像诗一样的语言，讲得又非常深刻、非常理性。把七十五章和七十四章结合起来理解，我们就能发现，老先生苦口婆心地劝坐在对面的那些领导者、统治者：你们要对自己国家的人民好一点，否则啊，他们日子过不好，你们的日子也不安稳，你们只靠这种高压的政策，这不是解决问题的根本的方法。我们完全可以说在这几章里看到了《道德经》的“真实面目”，很多话是针对那些统治者讲的，苦口婆心地劝他们，应该怎么样对待这个国家的人民，才能使国家长久地、持续地发展。</t>
   </si>
   <si>
-    <t>第十章</t>
-  </si>
-  <si>
     <t>第七十六章（76）</t>
   </si>
   <si>
@@ -1139,7 +1109,7 @@
     <t>第七十八章体现了这本书里的一个非常重要的理念，“善于处下”。这些内容我们之前都有过接触，甚至直接引用七十八章做过讲解，所以这一章我们并不需要花费太多的时间来解释，大家也能够明了。“天下莫柔弱于水，而攻坚强者莫之能胜”，天下没有什么东西比水更柔弱了，你拿什么容器装，它就是什么样，随方就圆。但天下也没有什么东西比水的力量更强大了，攻无不克，战无不胜。水就是以柔克刚、以弱胜强的最好的形象的代表。“以其无以易之”，因为没有什么东西能够替代水，天下最柔弱的东西，它力量又最为强大，最能够体现柔弱胜刚强的道理。“弱之胜强，柔之胜刚，天下莫不知，莫能行。”天下都知道，这东西表面上看似柔弱，但发挥作用的时候力量太强大了，但是真的要这样却非常不容易，为什么？人都有脾气，“柔弱胜刚强”得懂得忍耐、等待，忍耐是我们人最难练的一种功夫。水滴锲而不舍方能穿石，一条溪流不舍昼夜，慢慢积累，等待时机，才能发挥大用。“柔弱胜刚强”也是需要条件的，只是老子没有明说。“是以圣人云”，我再给大家强调一下，在老子心里，以前有很多好的统治者、有智慧的领导者，他称其为“圣人”，让大家向他们学习。我们在前面谈到过，他的很多话并不是原创的，是他引用的以前的圣人的，下边这话就表达得非常明确，所以这些圣人讲，“受国之垢”“受国不祥”。这两句话就是《道德经》里边从头至尾强调的，就是我们经常讲的善于处下。古往今来，夺得天下的表面看是一家一姓，实际上不都是一个团队吗？用我们现在的话讲是一个党派。什么样的团队，什么样的党派才能夺得天下，并且坐得了江山呢？之前，我们在第八章讲“处众人之所恶”时，也拿这个地方作为印证。吃苦在前，享受在后，有困难还得担着，有错误勇于改正，这不就是“受国之垢”“受国不祥”吗？所以真正想要夺得天下，坐稳江山，也就是所谓“处其上”，首先要懂得“处其下”，要“受国之垢”，要能忍受别人忍受不了的艰难困苦，要能承受别人承受不了的屈辱诟骂，这样才能成为江山社稷的主人。“受国不祥，是为天下王。”有灾难有困难，你别跑，要挺身而出，勇于担当，有错误要勇于承认，勇于改正。毛泽东把共产党的宗旨概括为五个字，叫“为人民服务”。两千多年前的“受国之垢”，“受国不祥”，“处众人之所恶”，两千多年后的“为人民服务”，这本质上的意思不是一样的吗？这就是《道德经》里面从头强调的，也是古往今来的大道。我们在讲第十四章的时候说过一句话，“执古之道以御今之有”。了解古往今来的大道，我们才能更好地做好今天的事情。读到这儿大家就会发现，这《道德经》里边蕴含着古往今来的大道，蕴含着一个人、一个团队、一个党派成功的最深的密码，值得大家认真地品味。总结上面这个表达的方式叫什么呢？叫“正言若反”，也就是第四十章讲的“反者，道之动”。看着是讲反话，大家都不愿意去做的事情：“受国之垢”，“受国之不祥”，“处众人之所恶”，可实际上，这才是能够让我们“处上”、取得成功的真正的智慧与奥妙。看似好像说的反话，其实深刻的道理就在这里边。</t>
   </si>
   <si>
-    <t>第八章、第九章</t>
+    <t>8、9</t>
   </si>
   <si>
     <t>第七十九章（79）</t>
@@ -1176,9 +1146,6 @@
   </si>
   <si>
     <t>说起《道德经》的分章，大家一般认为最早是河上公以九九归一为神秘的数字指向，把它分成了八十一章。第八十一章可以看作是全书的总结，全书思想的总结和概括就是最后这两句话，“天之道，利而不害。”天道如此，人道应该效法天道，所以下一句“圣人之道，为而不争”，一个好的领导人、统治者是如此，对我们大家来讲也是如此。韩国有一个连任联合国秘书长的聪明人，叫潘基文。他在连任就职典礼上，开口讲的就是《道德经》的这两句话，只不过他引用的是这两句话中的八个字：“利而不害，为而不争。”我怎么做联合国秘书长？我对大家有利，不起坏心，为大家谋福利，“利而不害”。我把事情做了，不为自己争名夺利，“为而不争”。我们应该有一个非常深刻的体验：道家并不是消极的、被动的、什么事都不做。什么叫无为？“为而不争”是无为的一个重要的方面，这可以看作是全部《道德经》的核心的总结。我们回头去想，“上善若水”讲“善利万物而不争”；天道讲“为而不争”。这样我们就把整个的思想落地了，知道了《道德经》最后的核心落在什么地方。现在来看一下原文，“信言不美，美言不信”，真正诚信的话，不漂亮，只会讲漂亮话的，没诚信，过度漂亮的话里，往往隐含欺骗的内容，所以大家说，真理是朴素的，真理是赤裸裸的。“善者不辩，辩者不善”，真正善良的人，不老去争辩。庄子在他文章里边经常讲，老去靠争辩，争辩胜了，又能够体现什么？“善者不辩，辩者不善”，老去争辩，老为自己找借口，老觉得自己受了无尽的委屈，这个不是善良者的表现。“知者不博，博者不知”，一个有智慧的人，不是老是吹嘘自己渊博、博学、无所不知，老是吹嘘自己无所不知的人，其实是没有智慧的。下面就讲一个有智慧的领导者应该怎么去做事。“圣人不积”，一个有智慧的领导者，不是老想着去积累财富、有形的资产。“既以为人，己愈有”，什么叫做富？什么叫做有？我老去帮助别人，为别人做事，在给别人做事情，帮助别人的过程中，获得了无尽的快乐，这不是无形资产吗？这不是精神世界的充盈吗？“既以与人，己愈多”，给别人的越多，帮别人的越多，要财富发挥它的真正的作用，在“舍”的过程中反而自己得到更多。“既以为人，己愈有；既以与人，己愈多。”2014年习近平在斐济《斐济时报》发表署名文章，也用过这两句话。中国人喜欢双赢，帮助别人。我们的理念是什么？我们给别人做的事情越多，我们感觉到自己越富有；对别人帮得越多，感觉到自己获得的更多。所以我们经常讲，我们很多的快乐是在帮助别人成长，别人有困难的时候，我们帮扶的时候，感觉到自己的内心的充盈快乐。“为人”是什么？“与人”是什么？是善利。看似付出，自己反而获得更多，自己的精神世界也更为充盈。如果我们只一味地为自己积累财富，结果呢？我们经常讲一句话，叫穷得只剩下钱了，我们的物质世界越发达，财富越多，我们的精神家园就越花果飘零。“善利万物而不争”，这是全书的最后总结。不争什么？不争言语的漂亮，只为了它的实质；不为了争辩的胜利，只为它的真理；不吹嘘自己的知识的渊博，只让知识发挥它正确的作用；不积累那么多所谓的财富，而是让财富发挥它真正的作用，让我们的精神世界越来越充盈、越来越丰富。帮人越多，自己越富有；给人越多，自己获得越多。舍得、舍得，舍的同时，也是一种获得；帮人的过程，也是一种快乐。“既以为人，己愈有；既以与人，己愈多”，这两句话仔细思量，其即是天道。“天之道，利而不害”，天道如此，善利万物不起坏心。“圣人之道，为而不争”，把事情做了，不为自己争名夺利。“为而不争”和前面我们讲过的“善利万物而不争”、“生而不有，为而不恃，长而不宰”、“功成而弗居”、“衣养万物而不为主”，这些重要的语句遥相呼应。这样，我们就把思想穿成了一串珍珠，看清楚了这本书的真正的逻辑，也看清了这本书的“落脚点”。这些成为我们生活中的座右铭，指南针，对我们的思维方式、人生格局、精神境界都会有很大的启发和启迪。第八十一章的内容，我们解读完了。到这最后一章，我们看到这一章最后落在这句话上“圣人之道，为而不争”，可以清楚的看到这本经典的目的就是把士和王修养、培养成圣。这就是这本书的内在逻辑，也是老子的良苦用心。读这本经典要掌握以下几个关键性问题。一是《道德经》本质上是一本对话体，也就是对面坐着人问的问题。只不过老子在刻书时把对面坐的人是谁、问的什么问题都省略了，而只是把他当时给的答案概括、总结、提炼、升华形成的一本著作。当我们从书里找到士、王、圣这三类问问题的人时，也就很容易抓住问题的关键了。二是王弼本《道德经》哲学思维水平非常高。在第一章就提出有无相互统一思维方式的重要性，并指出“无”是全书的众妙之门，从而让我们清楚地知道了无为、无声、无色、无味、无色……在这本书中的重要性，也借此步入众妙之门。三是我们这种以经解经的方法前后参照，避免了八十一章本子的“碎片化”倾向，并且在通篇解读中发现了老子对他认为重要问题的强调方式：首先是用重复的方式强调。比如在第十章、第五十章都重复出现“生而不有，为而不恃，长而不宰”，并且在第二章、第三十四章也都出现类似的意思。其次是用首尾呼应的方式来强调，比如二十二章就是如此。其三是用正反两个方面的方式来强调一个观点的重要性，比如第六十七章就是如此。了解了上面这些导读的内容，我们再来听课、阅读，我们就会更深刻地了解这本书的深刻内容，这本“善建者不拔”的伟大经典指导下：“修之于身，其德乃真；修之于家，其德乃余；修之于乡，其德乃长；修之于国，其德乃丰；修之于天下，其德乃普。”当然即便是逐章解决了很多问题，讲的恐怕也是蜻蜓点水，就《道德经》而言，最重要的是大家自己的阅读和领悟。</t>
-  </si>
-  <si>
-    <t>第七章</t>
   </si>
   <si>
     <t>经第一章（1-1）</t>
@@ -2141,7 +2108,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2173,9 +2140,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2698,7 +2662,7 @@
       <c r="F2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="12"/>
+      <c r="G2" s="11"/>
     </row>
     <row r="3" ht="172.8" spans="1:7">
       <c r="A3" s="10">
@@ -2765,8 +2729,8 @@
       <c r="F5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>27</v>
+      <c r="G5" s="11">
+        <v>32</v>
       </c>
     </row>
     <row r="6" ht="172.8" spans="1:7">
@@ -2774,22 +2738,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="D6" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>31</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" ht="158.4" spans="1:7">
@@ -2797,22 +2761,22 @@
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="D7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="E7" s="11" t="s">
         <v>35</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>36</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="11" t="s">
-        <v>37</v>
+      <c r="G7" s="11">
+        <v>57</v>
       </c>
     </row>
     <row r="8" ht="144" spans="1:7">
@@ -2820,22 +2784,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="E8" s="11" t="s">
         <v>39</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>41</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" ht="158.4" spans="1:7">
@@ -2843,22 +2807,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="E9" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>46</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" ht="187.2" spans="1:7">
@@ -2866,22 +2830,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="E10" s="11" t="s">
         <v>49</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>51</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" ht="158.4" spans="1:7">
@@ -2889,22 +2853,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="E11" s="11" t="s">
         <v>54</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>56</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" ht="172.8" spans="1:7">
@@ -2912,22 +2876,22 @@
         <v>10</v>
       </c>
       <c r="B12" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="E12" s="11" t="s">
         <v>59</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>61</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="12" t="s">
-        <v>62</v>
+      <c r="G12" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="13" ht="158.4" spans="1:7">
@@ -2935,22 +2899,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="E13" s="11" t="s">
         <v>64</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>66</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" ht="158.4" spans="1:7">
@@ -2958,22 +2922,22 @@
         <v>12</v>
       </c>
       <c r="B14" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="E14" s="11" t="s">
         <v>69</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>71</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="12" t="s">
-        <v>72</v>
+      <c r="G14" s="11" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="15" ht="172.8" spans="1:7">
@@ -2981,43 +2945,43 @@
         <v>13</v>
       </c>
       <c r="B15" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="E15" s="11" t="s">
         <v>74</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>76</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="12"/>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" ht="172.8" spans="1:7">
       <c r="A16" s="10">
         <v>14</v>
       </c>
       <c r="B16" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="E16" s="11" t="s">
         <v>78</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>80</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="12" t="s">
-        <v>81</v>
+      <c r="G16" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="172.8" spans="1:7">
@@ -3025,22 +2989,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>82</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>85</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="12" t="s">
-        <v>86</v>
+      <c r="G17" s="11">
+        <v>26</v>
       </c>
     </row>
     <row r="18" ht="158.4" spans="1:7">
@@ -3048,106 +3012,106 @@
         <v>16</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="12"/>
+      <c r="G18" s="11"/>
     </row>
     <row r="19" ht="172.8" spans="1:7">
       <c r="A19" s="10">
         <v>17</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="12"/>
+      <c r="G19" s="11"/>
     </row>
     <row r="20" ht="144" spans="1:7">
       <c r="A20" s="10">
         <v>18</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="12"/>
+      <c r="G20" s="11"/>
     </row>
     <row r="21" ht="158.4" spans="1:7">
       <c r="A21" s="10">
         <v>19</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G21" s="12"/>
+      <c r="G21" s="11"/>
     </row>
     <row r="22" ht="187.2" spans="1:7">
       <c r="A22" s="10">
         <v>20</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="11" t="s">
-        <v>107</v>
+      <c r="G22" s="11">
+        <v>6</v>
       </c>
     </row>
     <row r="23" ht="172.8" spans="1:7">
@@ -3155,106 +3119,106 @@
         <v>21</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G23" s="12"/>
+      <c r="G23" s="11"/>
     </row>
     <row r="24" ht="172.8" spans="1:7">
       <c r="A24" s="10">
         <v>22</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="12"/>
+      <c r="G24" s="11"/>
     </row>
     <row r="25" ht="158.4" spans="1:7">
       <c r="A25" s="10">
         <v>23</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G25" s="12"/>
+      <c r="G25" s="11"/>
     </row>
     <row r="26" ht="158.4" spans="1:7">
       <c r="A26" s="10">
         <v>24</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="12"/>
+      <c r="G26" s="11"/>
     </row>
     <row r="27" ht="172.8" spans="1:7">
       <c r="A27" s="10">
         <v>25</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="11" t="s">
-        <v>107</v>
+      <c r="G27" s="11">
+        <v>6</v>
       </c>
     </row>
     <row r="28" ht="172.8" spans="1:7">
@@ -3262,22 +3226,22 @@
         <v>26</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G28" s="12" t="s">
-        <v>132</v>
+      <c r="G28" s="11">
+        <v>15</v>
       </c>
     </row>
     <row r="29" ht="187.2" spans="1:7">
@@ -3285,127 +3249,127 @@
         <v>27</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G29" s="12"/>
+      <c r="G29" s="11"/>
     </row>
     <row r="30" ht="172.8" spans="1:7">
       <c r="A30" s="10">
         <v>28</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G30" s="12"/>
+      <c r="G30" s="11"/>
     </row>
     <row r="31" ht="172.8" spans="1:7">
       <c r="A31" s="10">
         <v>29</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G31" s="12"/>
+      <c r="G31" s="11"/>
     </row>
     <row r="32" ht="172.8" spans="1:7">
       <c r="A32" s="10">
         <v>30</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G32" s="12"/>
+      <c r="G32" s="11"/>
     </row>
     <row r="33" ht="172.8" spans="1:7">
       <c r="A33" s="10">
         <v>31</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G33" s="12"/>
+      <c r="G33" s="11"/>
     </row>
     <row r="34" ht="172.8" spans="1:7">
       <c r="A34" s="10">
         <v>32</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G34" s="11" t="s">
-        <v>157</v>
+      <c r="G34" s="11">
+        <v>3</v>
       </c>
     </row>
     <row r="35" ht="158.4" spans="1:7">
@@ -3413,148 +3377,148 @@
         <v>33</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="F35" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G35" s="12"/>
+      <c r="G35" s="11"/>
     </row>
     <row r="36" ht="158.4" spans="1:7">
       <c r="A36" s="10">
         <v>34</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G36" s="12"/>
+      <c r="G36" s="11"/>
     </row>
     <row r="37" ht="158.4" spans="1:7">
       <c r="A37" s="10">
         <v>35</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G37" s="12"/>
+      <c r="G37" s="11"/>
     </row>
     <row r="38" ht="172.8" spans="1:7">
       <c r="A38" s="10">
         <v>36</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G38" s="12"/>
+      <c r="G38" s="11"/>
     </row>
     <row r="39" ht="144" spans="1:7">
       <c r="A39" s="10">
         <v>37</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G39" s="12"/>
+      <c r="G39" s="11"/>
     </row>
     <row r="40" ht="187.2" spans="1:7">
       <c r="A40" s="10">
         <v>38</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G40" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G40" s="11"/>
     </row>
     <row r="41" ht="172.8" spans="1:7">
       <c r="A41" s="10">
         <v>39</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G41" s="11" t="s">
-        <v>187</v>
+        <v>175</v>
+      </c>
+      <c r="G41" s="11">
+        <v>2</v>
       </c>
     </row>
     <row r="42" ht="158.4" spans="1:7">
@@ -3562,64 +3526,64 @@
         <v>40</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G42" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G42" s="11"/>
     </row>
     <row r="43" ht="409.5" spans="1:7">
       <c r="A43" s="10">
         <v>41</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>195</v>
+        <v>184</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>187</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G43" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G43" s="11"/>
     </row>
     <row r="44" ht="409.5" spans="1:7">
       <c r="A44" s="10">
         <v>42</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>199</v>
+        <v>188</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>191</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G44" s="12" t="s">
-        <v>200</v>
+        <v>175</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="45" ht="409.5" spans="1:7">
@@ -3627,211 +3591,211 @@
         <v>43</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>204</v>
+        <v>193</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>196</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G45" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G45" s="11"/>
     </row>
     <row r="46" ht="409.5" spans="1:7">
       <c r="A46" s="10">
         <v>44</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>208</v>
+        <v>197</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>200</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G46" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G46" s="11"/>
     </row>
     <row r="47" ht="409.5" spans="1:7">
       <c r="A47" s="10">
         <v>45</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>212</v>
+        <v>201</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>204</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G47" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G47" s="11"/>
     </row>
     <row r="48" ht="409.5" spans="1:7">
       <c r="A48" s="10">
         <v>46</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>216</v>
+        <v>205</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>208</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G48" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G48" s="11"/>
     </row>
     <row r="49" ht="409.5" spans="1:7">
       <c r="A49" s="10">
         <v>47</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>220</v>
+        <v>209</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>212</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G49" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G49" s="11"/>
     </row>
     <row r="50" ht="409.5" spans="1:7">
       <c r="A50" s="10">
         <v>48</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>224</v>
+        <v>213</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>216</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G50" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G50" s="11"/>
     </row>
     <row r="51" ht="409.5" spans="1:7">
       <c r="A51" s="10">
         <v>49</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>228</v>
+        <v>217</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>220</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G51" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G51" s="11"/>
     </row>
     <row r="52" ht="409.5" spans="1:7">
       <c r="A52" s="10">
         <v>50</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="D52" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>232</v>
+        <v>221</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G52" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G52" s="11"/>
     </row>
     <row r="53" ht="409.5" spans="1:7">
       <c r="A53" s="10">
         <v>51</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="D53" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>236</v>
+        <v>225</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G53" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G53" s="11"/>
     </row>
     <row r="54" ht="409.5" spans="1:7">
       <c r="A54" s="10">
         <v>52</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="C54" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="E54" s="13" t="s">
-        <v>240</v>
+        <v>229</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>232</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G54" s="11" t="s">
-        <v>107</v>
+        <v>175</v>
+      </c>
+      <c r="G54" s="11">
+        <v>6</v>
       </c>
     </row>
     <row r="55" ht="409.5" spans="1:7">
@@ -3839,106 +3803,106 @@
         <v>53</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="D55" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="E55" s="13" t="s">
-        <v>244</v>
+        <v>233</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>236</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G55" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G55" s="11"/>
     </row>
     <row r="56" ht="409.5" spans="1:7">
       <c r="A56" s="10">
         <v>54</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="D56" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="E56" s="13" t="s">
-        <v>248</v>
+        <v>237</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>240</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G56" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G56" s="11"/>
     </row>
     <row r="57" ht="409.5" spans="1:7">
       <c r="A57" s="10">
         <v>55</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="E57" s="13" t="s">
-        <v>252</v>
+        <v>241</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>244</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G57" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G57" s="11"/>
     </row>
     <row r="58" ht="403.2" spans="1:7">
       <c r="A58" s="10">
         <v>56</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="C58" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>256</v>
+        <v>245</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>248</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G58" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G58" s="11"/>
     </row>
     <row r="59" ht="409.5" spans="1:7">
       <c r="A59" s="10">
         <v>57</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>260</v>
+        <v>249</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>252</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
     </row>
     <row r="60" ht="409.5" spans="1:7">
@@ -3946,127 +3910,127 @@
         <v>58</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>265</v>
+        <v>254</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>257</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G60" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G60" s="11"/>
     </row>
     <row r="61" ht="409.5" spans="1:7">
       <c r="A61" s="10">
         <v>59</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="C61" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="E61" s="13" t="s">
-        <v>269</v>
+        <v>258</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>261</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G61" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G61" s="11"/>
     </row>
     <row r="62" ht="409.5" spans="1:7">
       <c r="A62" s="10">
         <v>60</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="C62" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="D62" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>273</v>
+        <v>262</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>265</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G62" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G62" s="11"/>
     </row>
     <row r="63" ht="409.5" spans="1:7">
       <c r="A63" s="10">
         <v>61</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="C63" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="D63" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="E63" s="13" t="s">
-        <v>277</v>
+        <v>266</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>269</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G63" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G63" s="11"/>
     </row>
     <row r="64" ht="409.5" spans="1:7">
       <c r="A64" s="10">
         <v>62</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="C64" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>281</v>
+        <v>270</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>273</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G64" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G64" s="11"/>
     </row>
     <row r="65" ht="409.5" spans="1:7">
       <c r="A65" s="10">
         <v>63</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="C65" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="E65" s="13" t="s">
-        <v>285</v>
+        <v>274</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>277</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
     </row>
     <row r="66" ht="409.5" spans="1:7">
@@ -4074,22 +4038,22 @@
         <v>64</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="C66" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="D66" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="E66" s="13" t="s">
-        <v>290</v>
+        <v>279</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>282</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G66" s="11" t="s">
-        <v>291</v>
+        <v>175</v>
+      </c>
+      <c r="G66" s="11">
+        <v>63</v>
       </c>
     </row>
     <row r="67" ht="374.4" spans="1:7">
@@ -4097,43 +4061,43 @@
         <v>65</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="C67" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="D67" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="E67" s="13" t="s">
-        <v>295</v>
+        <v>283</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>286</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G67" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G67" s="11"/>
     </row>
     <row r="68" ht="409.5" spans="1:7">
       <c r="A68" s="10">
         <v>66</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="C68" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="D68" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="E68" s="13" t="s">
-        <v>299</v>
+        <v>287</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>290</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="69" ht="409.5" spans="1:7">
@@ -4141,106 +4105,106 @@
         <v>67</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="C69" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="D69" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="E69" s="13" t="s">
-        <v>304</v>
+        <v>292</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>295</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G69" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G69" s="11"/>
     </row>
     <row r="70" ht="409.5" spans="1:7">
       <c r="A70" s="10">
         <v>68</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="C70" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="D70" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="E70" s="13" t="s">
-        <v>308</v>
+        <v>296</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>299</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G70" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G70" s="11"/>
     </row>
     <row r="71" ht="409.5" spans="1:7">
       <c r="A71" s="10">
         <v>69</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="C71" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="D71" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>312</v>
+        <v>300</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>303</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G71" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G71" s="11"/>
     </row>
     <row r="72" ht="409.5" spans="1:7">
       <c r="A72" s="10">
         <v>70</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="C72" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="E72" s="13" t="s">
-        <v>316</v>
+        <v>304</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>307</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G72" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G72" s="11"/>
     </row>
     <row r="73" ht="409.5" spans="1:7">
       <c r="A73" s="10">
         <v>71</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="C73" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="D73" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="E73" s="13" t="s">
-        <v>320</v>
+        <v>308</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>311</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="74" ht="374.4" spans="1:7">
@@ -4248,85 +4212,85 @@
         <v>72</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>321</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="E74" s="13" t="s">
-        <v>324</v>
+        <v>312</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>315</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G74" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G74" s="11"/>
     </row>
     <row r="75" ht="409.5" spans="1:7">
       <c r="A75" s="10">
         <v>73</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="C75" s="13" t="s">
-        <v>326</v>
-      </c>
-      <c r="D75" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="E75" s="13" t="s">
-        <v>328</v>
+        <v>316</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>319</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G75" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G75" s="11"/>
     </row>
     <row r="76" ht="409.5" spans="1:7">
       <c r="A76" s="10">
         <v>74</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="C76" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="D76" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>332</v>
+        <v>320</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>323</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G76" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G76" s="11"/>
     </row>
     <row r="77" ht="403.2" spans="1:7">
       <c r="A77" s="10">
         <v>75</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="C77" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="D77" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="E77" s="13" t="s">
-        <v>336</v>
+        <v>324</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>327</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G77" s="12" t="s">
-        <v>337</v>
+        <v>175</v>
+      </c>
+      <c r="G77" s="11">
+        <v>10</v>
       </c>
     </row>
     <row r="78" ht="409.5" spans="1:7">
@@ -4334,64 +4298,64 @@
         <v>76</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="C78" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="D78" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="E78" s="13" t="s">
-        <v>341</v>
+        <v>328</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>331</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G78" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G78" s="11"/>
     </row>
     <row r="79" ht="409.5" spans="1:7">
       <c r="A79" s="10">
         <v>77</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="C79" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="D79" s="13" t="s">
-        <v>344</v>
-      </c>
-      <c r="E79" s="13" t="s">
-        <v>345</v>
+        <v>332</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>335</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G79" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G79" s="11"/>
     </row>
     <row r="80" ht="409.5" spans="1:7">
       <c r="A80" s="10">
         <v>78</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="C80" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="D80" s="13" t="s">
-        <v>348</v>
-      </c>
-      <c r="E80" s="13" t="s">
-        <v>349</v>
+        <v>336</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>339</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" ht="409.5" spans="1:7">
@@ -4399,64 +4363,64 @@
         <v>79</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>351</v>
-      </c>
-      <c r="C81" s="13" t="s">
-        <v>352</v>
-      </c>
-      <c r="D81" s="13" t="s">
-        <v>353</v>
-      </c>
-      <c r="E81" s="13" t="s">
-        <v>354</v>
+        <v>341</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>344</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G81" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G81" s="11"/>
     </row>
     <row r="82" ht="409.5" spans="1:7">
       <c r="A82" s="10">
         <v>80</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="C82" s="13" t="s">
-        <v>356</v>
-      </c>
-      <c r="D82" s="13" t="s">
-        <v>357</v>
-      </c>
-      <c r="E82" s="13" t="s">
-        <v>358</v>
+        <v>345</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="E82" s="12" t="s">
+        <v>348</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G82" s="12"/>
+        <v>175</v>
+      </c>
+      <c r="G82" s="11"/>
     </row>
     <row r="83" ht="409.5" spans="1:7">
       <c r="A83" s="10">
         <v>81</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="C83" s="13" t="s">
-        <v>360</v>
-      </c>
-      <c r="D83" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="E83" s="13" t="s">
-        <v>362</v>
+        <v>349</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>352</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="G83" s="11" t="s">
-        <v>363</v>
+        <v>175</v>
+      </c>
+      <c r="G83" s="11">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4511,19 +4475,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="G2" s="3"/>
     </row>
@@ -4532,19 +4496,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="G3" s="4"/>
     </row>
@@ -4553,19 +4517,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -4574,19 +4538,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="G5" s="4"/>
     </row>
@@ -4595,19 +4559,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="G6" s="4"/>
     </row>
@@ -4616,19 +4580,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -4637,19 +4601,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -4658,19 +4622,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="G9" s="4"/>
     </row>
@@ -4679,19 +4643,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="G10" s="4"/>
     </row>
@@ -4700,19 +4664,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="G11" s="4"/>
     </row>
@@ -4721,19 +4685,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="G12" s="4"/>
     </row>
@@ -4742,19 +4706,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="G13" s="4"/>
     </row>
@@ -4763,19 +4727,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -4784,19 +4748,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="G15" s="4"/>
     </row>
@@ -4805,19 +4769,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="G16" s="4"/>
     </row>
@@ -4826,19 +4790,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="G17" s="4"/>
     </row>
@@ -4847,19 +4811,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="G18" s="4"/>
     </row>
@@ -4868,19 +4832,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="G19" s="4"/>
     </row>
@@ -4889,19 +4853,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="G20" s="4"/>
     </row>
@@ -4910,19 +4874,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="G21" s="4"/>
     </row>
@@ -4931,19 +4895,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="G22" s="4"/>
     </row>
@@ -4952,19 +4916,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="G23" s="4"/>
     </row>
@@ -4973,19 +4937,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="G24" s="4"/>
     </row>
@@ -4994,19 +4958,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="G25" s="4"/>
     </row>
@@ -5015,19 +4979,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="G26" s="4"/>
     </row>
@@ -5036,19 +5000,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="G27" s="4"/>
     </row>
@@ -5057,19 +5021,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="G28" s="4"/>
     </row>

--- a/book.xlsx
+++ b/book.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25068" windowHeight="13380"/>
+    <workbookView windowWidth="19644" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="道德经" sheetId="1" r:id="rId1"/>
@@ -315,7 +315,7 @@
     <t>第十六章（16）</t>
   </si>
   <si>
-    <t>致虚极，守静笃，万物并作，吾以观复。夫物芸芸，各复归其根。归根曰静，是谓复命。复命曰常，知常曰明。不知常，妄作，凶。知常容，容乃公，公乃王（wàng），王乃天，天乃道，道乃久。没身不殆。</t>
+    <t>致虚极，守静笃，万物并作，吾以观复。夫物芸芸，各复归其根。归根曰静，是谓复命。复命曰常，知常曰明。不知常，妄作凶。知常容，容乃公，公乃王（wàng），王乃天，天乃道，道乃久。没（mò）身不殆。</t>
   </si>
   <si>
     <t>尽力使心灵的谦虚达到极点，使生活清静坚守不变。万物都一齐蓬勃生长，有道之人在纷繁中考察其往复的道理。万事万物纷纷芸芸，各自返回它的本根。返回到它的本根就是清静，清静就能使生命复归而再次续命；复命续命就是自然，认识了自然规律就叫做明智，不认识自然规律的轻妄举止，往往会出乱子和灾凶。认识自然规律的人是宽容的，宽容才会坦然公正，公正才能内圣外王，内圣外王才能符合自然的“道”，符合自然的道才能长久，终身不会遭到危险。</t>
@@ -2610,7 +2610,7 @@
   <sheetFormatPr defaultColWidth="23.75" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="6.36111111111111" style="8" customWidth="1"/>
-    <col min="2" max="2" width="21" style="8" customWidth="1"/>
+    <col min="2" max="2" width="15" style="8" customWidth="1"/>
     <col min="3" max="3" width="59.25" style="3" customWidth="1"/>
     <col min="4" max="4" width="60.6666666666667" style="3" customWidth="1"/>
     <col min="5" max="5" width="75.25" style="3" customWidth="1"/>

--- a/book.xlsx
+++ b/book.xlsx
@@ -106,7 +106,7 @@
     <t>第二章（2）</t>
   </si>
   <si>
-    <t>天下皆知美之为美，斯恶（è）已；皆知善之为善，斯不善已。故有无相（xiāng）生，难易相成，长短相较，高下相倾，音声相和，前后相随。是以圣人处无为之事，行不言之教，万物作焉而不辞，生而不有，为而不恃（shì），功成而弗居。夫唯弗居，是以不（bù）去。</t>
+    <t>天下皆知美之为美，斯恶（è）已；皆知善之为善，斯不善已。故有无相（xiāng）生，难易相成，长短相较，高下相倾，音声相和（hè），前后相随。是以圣人处无为之事，行不言之教（jiào），万物作焉而不辞，生而不有，为而不恃（shì），功成而弗居。夫唯弗居，是以不（bù）去。</t>
   </si>
   <si>
     <t>天下都知道美是什么，丑自然就存在了；都知道什么是善，不善自然也就出现了。所以有和无相待而生，难和易相待而成，长和短相待而显，高和下相待而倾倚，音和声相待而和谐，前和后相待而顺序相随。所以圣人行事 顺乎自然 崇尚无为，实行不言的教诲，顺应万物自然的生长而不加干预，创造万物而不占有，施泽万物而不将这当成是倚仗、凭借的手段，有了功劳而不居功（自傲）。正因为他不居功自傲，所以也就不会失去自己的功劳。</t>

--- a/book.xlsx
+++ b/book.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="476">
   <si>
     <t>no</t>
   </si>
@@ -100,7 +100,7 @@
     <t>道经</t>
   </si>
   <si>
-    <t>4、14</t>
+    <t>4、14、21、25</t>
   </si>
   <si>
     <t>第二章（2）</t>
@@ -299,6 +299,9 @@
 执古之道，以御今之有：了解古往今来的大道，才能把握今天、做好今天的事；能知古始，是谓道纪：知道万物开始的道理，就是把握了道的纲领。译者·韩鹏杰用庄子的“道在瓦片、稗草、大小便中”来说明道无在无不在，越往下越有；用风的形象说明道无形却左右万物。学习本章要记住：道看不见摸不着，但真实存在、无处不在，了解它才能做好今天的事。</t>
   </si>
   <si>
+    <t>1、21</t>
+  </si>
+  <si>
     <t>第十五章（15）</t>
   </si>
   <si>
@@ -321,7 +324,7 @@
     <t>尽力使心灵的谦虚达到极点，使生活清静坚守不变。万物都一齐蓬勃生长，有道之人在纷繁中考察其往复的道理。万事万物纷纷芸芸，各自返回它的本根。返回到它的本根就是清静，清静就能使生命复归而再次续命；复命续命就是自然，认识了自然规律就叫做明智，不认识自然规律的轻妄举止，往往会出乱子和灾凶。认识自然规律的人是宽容的，宽容才会坦然公正，公正才能内圣外王，内圣外王才能符合自然的“道”，符合自然的道才能长久，终身不会遭到危险。</t>
   </si>
   <si>
-    <t>本章承第十五章，进一步讲虚静观复、知常守根。致虚极，守静笃：把心放到极度虚空、极度宁静的状态，不是枯木死灰，而是心灵安稳、不受杂念干扰。万物并作，吾以观复：万物纷繁生长，观察它的根本规律就是一个“复”字，反复循环、复归本根。夫物芸芸，各复归其根：万物虽然纷纭，最终都要回归自己的根本。归根曰静，静曰复命，复命曰常：归根就是静，静就是复归本性，复归本性就是恒常之道。
+    <t>【基层领导要具备的素质】本章承第十五章，进一步讲虚静观复、知常守根。致虚极，守静笃：把心放到极度虚空、极度宁静的状态，不是枯木死灰，而是心灵安稳、不受杂念干扰。万物并作，吾以观复：万物纷繁生长，观察它的根本规律就是一个“复”字，反复循环、复归本根。夫物芸芸，各复归其根：万物虽然纷纭，最终都要回归自己的根本。归根曰静，静曰复命，复命曰常：归根就是静，静就是复归本性，复归本性就是恒常之道。
 知常容，容乃公，公乃王，王乃天，天乃道，道乃久，没身不殆：懂得恒常之道就能包容，包容就公正，公正就周全，周全就合天，合天就合道，合道就长久，终身不会遇到危险。译者·韩鹏杰说，从草的枯荣到人的生死，都体现“复”的规律；观察规律是为了认识自己、掌控自己：知道哪些因素会带来负面状态，就主动避免；知道哪些条件带来积极状态，就主动创造，让好的状态恢复。</t>
   </si>
   <si>
@@ -334,7 +337,7 @@
     <t>最高层次的统治者（叫“太上”），百姓感觉不到他们的存在；低一层次的统治者，百姓亲近他们、赞美他们；更低层次的统治者，百姓害怕他们；最低层次的统治者，百姓轻视、羞辱他们。正是因为统治者本身的诚信不足，所以才出现不被百姓信任的情况。最好的统治者清静无为 很少发号施令。国家治理得美满祥和，而百姓都认为“我们本来就是这个样子”。</t>
   </si>
   <si>
-    <t>本章讲领导者的层次与境界。太上，下知有之：最高明的领导者，百姓只隐隐知道有他这个人，因为他不过多干预、不越边界，该管的事管好，不该管的放手。其次，亲而誉之：次一等的领导者被百姓亲近、赞誉。其次，畏之：再次一等的，百姓畏惧他。其次，侮之：最差的，百姓轻侮他。信不足焉，有不信焉：领导者自身诚信不足，百姓自然不会信任他。悠兮其贵言：最高境界是少言、贵言，不唠里唠叨，把话讲得有分量。功成事遂，百姓皆谓我自然：事情办成了，百姓都觉得是我们自己自然而然做成的，而不是领导者的功劳和主宰。
+    <t>【领导者的层次与境界】本章讲领导者的层次与境界。太上，下知有之：最高明的领导者，百姓只隐隐知道有他这个人，因为他不过多干预、不越边界，该管的事管好，不该管的放手。其次，亲而誉之：次一等的领导者被百姓亲近、赞誉。其次，畏之：再次一等的，百姓畏惧他。其次，侮之：最差的，百姓轻侮他。信不足焉，有不信焉：领导者自身诚信不足，百姓自然不会信任他。悠兮其贵言：最高境界是少言、贵言，不唠里唠叨，把话讲得有分量。功成事遂，百姓皆谓我自然：事情办成了，百姓都觉得是我们自己自然而然做成的，而不是领导者的功劳和主宰。
 译者·韩鹏杰用“太上”的拆字讲：大上加一点才是太，点放下才成太，放到上面就成犬，寓意善于处下才能真正居上，太太、处长等词都蕴含此理。最好的教育和管理也是如此：不越俎代庖，让孩子、下属自己把事情做成，他们才有自信和成长，功成事遂皆谓我自然。</t>
   </si>
   <si>
@@ -347,10 +350,13 @@
     <t>大道被废弃之后，就有人开始站出来提倡仁义；智慧、谋略、心机被推崇之后，就会产生严重的虚伪（大奸大伪）；亲人之间关系不和睦，才会强调孝顺和慈爱；国家动乱时，才会看出谁是忠臣。</t>
   </si>
   <si>
-    <t>本章与第十九章原为一章，讲“越缺什么越提倡什么”的历史递降逻辑。大道废，有仁义：大道被废弃了，才需要提倡仁义；六亲不和，有孝慈：家庭不和睦了，才强调孝慈；国家昏乱，有忠臣：国家混乱了，才显出忠臣。智慧出，有大伪：智巧盛行，反而产生大伪诈。译者·韩鹏杰指出，这是老子的历史观：有道的时候不需要讲德，失道才讲德，失德才讲仁，失仁才讲义，失义才讲礼，一层一层往下掉。
+    <t>【这个世界越缺什么越会提倡什么】本章与第十九章原为一章，讲“越缺什么越提倡什么”的历史递降逻辑。大道废，有仁义：大道被废弃了，才需要提倡仁义；六亲不和，有孝慈：家庭不和睦了，才强调孝慈；国家昏乱，有忠臣：国家混乱了，才显出忠臣。智慧出，有大伪：智巧盛行，反而产生大伪诈。译者·韩鹏杰指出，这是老子的历史观：有道的时候不需要讲德，失道才讲德，失德才讲仁，失仁才讲义，失义才讲礼，一层一层往下掉。
 一个社会天天提倡道德，正说明道德已经滑坡；什么时候妇女节、教师节不再成为问题，才说明相关地位真正提高了。这不是否定仁义孝慈，而是提醒人们不要靠表面提倡来补救，要从根本上回到道。把第十八、十九章连起来读：与其用仁义、智巧等外在名目补救，不如回归素朴本心，做个好人、存点好心、行些好事。</t>
   </si>
   <si>
+    <t>19、（18/19章可融合为一章）</t>
+  </si>
+  <si>
     <t>第十九章（19）</t>
   </si>
   <si>
@@ -360,20 +366,23 @@
     <t>（为政者）弃绝智谋算和巧言令色，百姓反而会得到百倍的利益；不去提倡仁义，百姓反而能够做到孝慈；弃绝投机取巧和功利之心，盗贼就不会产生。以上三条原则仅仅作为理论谈谈是不够的。所以要为它们分别落实一些施行的具体措施：行为单纯 内心淳朴，减少私心 降低欲望，抛弃巧、利 没有忧虑。</t>
   </si>
   <si>
-    <t>本章主张绝弃外在名目，回归素朴本心。绝圣弃智，民利百倍：抛弃圣贤名号和智巧机心，百姓反而得到百倍利益；绝仁弃义，民复孝慈：不刻意提倡仁义，百姓反而自然做到孝慈；绝巧弃利，盗贼无有：清除技巧和利益诱惑，盗贼就不会产生。此三者以为文不足：仅仅在理论上讲这三条还不够，要落实为具体方向——见素抱朴，少私寡欲，绝学无忧：行为单纯、内心淳朴，减少私心、降低欲望，不为纷繁的学问和机巧所惑，就没有忧虑。
+    <t>【朴素之心 少私寡欲】本章主张绝弃外在名目，回归素朴本心。绝圣弃智，民利百倍：抛弃圣贤名号和智巧机心，百姓反而得到百倍利益；绝仁弃义，民复孝慈：不刻意提倡仁义，百姓反而自然做到孝慈；绝巧弃利，盗贼无有：清除技巧和利益诱惑，盗贼就不会产生。此三者以为文不足：仅仅在理论上讲这三条还不够，要落实为具体方向——见素抱朴，少私寡欲，绝学无忧：行为单纯、内心淳朴，减少私心、降低欲望，不为纷繁的学问和机巧所惑，就没有忧虑。
 译者·韩鹏杰说，道家认为人的本心就是真心，真心就是朴素之心，朴素之心就是少私寡欲；外在花花绿绿的学问看多了，反而把人搞乱。读经典要由博返约，最后陪我们一生的可能只是一两本书、一两句话，真传一句话，假传万卷书。绝学无忧不是不要学习，而是学真正的大道，不被浮华知识蒙蔽。</t>
   </si>
   <si>
+    <t>18、（18/19章可融合为一章）</t>
+  </si>
+  <si>
     <t>第二十章（20）</t>
   </si>
   <si>
-    <t>唯之与阿（hē），相去几何？善之与恶，相去若何？人之所畏，不可不畏。荒兮，其未央哉！众人熙熙，如享太牢，如春登台。我独泊兮，其未兆，如婴儿之未孩。儽（léi）儽兮，若无所归。众人皆有余，而我独若遗。我愚人之心也哉，沌（dùn）沌兮！俗人昭昭，我独昏昏；俗人察察，我独闷闷。澹（dàn）兮其若海； 飂（liù）兮若无止 。众人皆有以，而我独顽似鄙。我独异于人，而贵食母。</t>
-  </si>
-  <si>
-    <t>赞成与反对，相差有多远？善良与丑恶，相差又有多远？大家都敬畏的不能不去敬畏！前面的道路多么漫长啊，就像没有尽头！众人是那样的快乐，就好像参加盛大宴会，春日登台赏景一样。而只有我淡泊处之，无动于衷，就如同一个还不会笑的婴儿一般。我是如此狼狈不堪，就像个无家可归的人一样。众人都过着富裕幸福的生活，只有我却像被遗弃了一样。因为我有一副愚人的心肠，太笨拙了！世人是那样的明白，只有我是如此的糊涂；世人是那样的聪慧，只有我是这样的宽厚。我的生活是那样的坎坷多难 就好像那动荡不安的大海一样；我如同那飘忽不定的长风 不知何处才是归宿。众人活得都是那样的有用，只有我如此冥顽无能。虽然我和世人格格不入，但我还要继续以大道为依归。</t>
-  </si>
-  <si>
-    <t>本章是得道者的自画像。唯之与阿，相去几何？善之与恶，相去若何：恭敬的应答与呵斥相差多远？善与恶又相差多少？老子提醒，是非善恶的界限并非表面看起来那么分明，好事也可能带来坏结果。人之所畏，不可不畏：但众人共同敬畏的规则，也要敬守，不要为了标新立异而违背公认的规范。众人熙熙，如享太牢，如春登台：众人都热热闹闹，像参加盛宴、春日登台；我独泊兮，其未兆，如婴儿之未孩：得道者独自淡泊、无动于衷，像还不会笑的婴儿。
+    <t>唯之与阿（hē），相去几何？善之与恶，相去若何？人之所畏，不可不畏。荒兮，其未央哉！众人熙熙，如享太牢，如春登台。我独泊兮，其未兆，如婴儿之未孩。儽（léi）儽兮，若无所归。众人皆有余，而我独若遗。我愚人之心也哉，沌（dùn）沌兮！俗人昭昭，我独昏昏；俗人察察，我独闷闷。澹（dàn）兮其若海； 飂（liáo）兮若无止 。众人皆有以，而我独顽似鄙。我独异于人，而贵食母。</t>
+  </si>
+  <si>
+    <t>赞成与反对，相差有多远？善良与丑恶，相差又有多远？大家都敬畏的不能不去敬畏！前面的道路多么漫长啊，就像没有尽头！众人是那样的快乐，就好像参加盛大宴会，春日登台赏景一样。而只有我淡泊处之，无动于衷，就如同一个还不会笑的婴儿一般。我是如此狼狈不堪，就像个无家可归的人一样。众人都过着富裕幸福的生活，只有我却像被遗弃了一样。因为我有一副愚人的心肠，太笨拙了！世人是那样的明白，只有我是如此的糊涂；世人是那样的聪慧，只有我是这样的宽厚。我的生活是那样的坎坷多难 就好像那动荡不安的大海一样；我如同那飘忽不定的长风 不知何处才是归宿。众人活得都是那样的有用，只有我如此冥顽无能。虽然我和世人格格不入（追求的目标不一样），但我还要继续以大道为依归。</t>
+  </si>
+  <si>
+    <t>【描述了老子的自画像】本章是得道者的自画像。唯之与阿，相去几何？善之与恶，相去若何：恭敬的应答与呵斥相差多远？善与恶又相差多少？老子提醒，是非善恶的界限并非表面看起来那么分明，好事也可能带来坏结果。人之所畏，不可不畏：但众人共同敬畏的规则，也要敬守，不要为了标新立异而违背公认的规范。众人熙熙，如享太牢，如春登台：众人都热热闹闹，像参加盛宴、春日登台；我独泊兮，其未兆，如婴儿之未孩：得道者独自淡泊、无动于衷，像还不会笑的婴儿。
 众人皆有余，而我独若遗：众人都显得富足有余，得道者却像有所遗失。我愚人之心也哉，沌沌兮：一副愚人心肠，混沌淳朴。俗人昭昭，我独昏昏；俗人察察，我独闷闷：世人精明，得道者看似糊涂宽厚。澹兮其若海，飂兮若无止：他像大海一样淡泊深沉，像长风一样自由无羁。众人皆有以，而我独顽似鄙：世人都有用处，他看似冥顽无能。我独异于人，而贵食母：与众人不同，因为他以大道为归依。本章刻画了不随波逐流、独立守道的精神境界。</t>
   </si>
   <si>
@@ -386,46 +395,52 @@
     <t>有大德气质和形象的人，是会坚定地按照大道来行事。大道这种事物，是恍恍惚惚而没有形体的。它虽然是那样的恍惚迷离，但其中确实有征兆显现、有东西存在；它虽然是那样的迷离恍惚，但其中确实有自己的内涵。大道是那样的深邃而难以认识，但它却有着自己的内容；它的内容是那样的真实无妄，充满了诚信。从古至今，大道都是无法被废弃的，凭借着它就可以知道万物开始时的情况。我凭什么知道万物开始时的情况呢？就是凭借大道。</t>
   </si>
   <si>
-    <t>本章讲大德与道的关系，证明道真实存在、可以验证。孔德之容，惟道是从：大德之人的样子，就是坚定地依道而行，“孔”是大，高僧大德即此意。道之为物，惟恍惟惚：道这个东西恍恍惚惚、没有固定形体；恍惚不是迷糊，而是心中忽然有光、有所领悟的顿悟状态。惚兮恍兮，其中有象；恍兮惚兮，其中有物：恍惚之中有境界、有内容。窈兮冥兮，其中有精：深远幽暗之中有精神；其精甚真，其中有信：这精神真实不虚，其中包含可信、可验证的规律。
+    <t>【道 看不见 但存在】本章讲大德与道的关系，证明道真实存在、可以验证。孔德之容，惟道是从：大德之人的样子，就是坚定地依道而行，“孔”是大，高僧大德即此意。道之为物，惟恍惟惚：道这个东西恍恍惚惚、没有固定形体；恍惚不是迷糊，而是心中忽然有光、有所领悟的顿悟状态。惚兮恍兮，其中有象；恍兮惚兮，其中有物：恍惚之中有境界、有内容。窈兮冥兮，其中有精：深远幽暗之中有精神；其精甚真，其中有信：这精神真实不虚，其中包含可信、可验证的规律。
 自古及今，其名不去，以阅众甫：从古至今，道的名字不曾消失，凭借它可以认识万物起始。吾何以知众甫之状哉？以此：我就是凭借道来认识圣人得道的状态。译者·韩鹏杰强调，道不仅是万物的本源和规律，也是人生的境界；离开了道，人就变成无源之水、无本之木。这一章让人对道建立确信：它看不见摸不着，但真实存在，是精神世界的根基。</t>
   </si>
   <si>
+    <t>1、14、21、42</t>
+  </si>
+  <si>
     <t>第二十二章（22）</t>
   </si>
   <si>
-    <t>曲则全，枉则直，洼则盈，敝则新，少则得，多则惑。是以圣人抱一为天下式。不自见，故明；不自是，故彰；不自伐，故有功；不自矜（jīn），故长。夫唯不争，故天下莫能与之争。古之所谓“曲则全”者，岂虚言哉？诚全而归之。</t>
+    <t>曲则全，枉则直，洼则盈，敝则新，少则得，多则惑。是以圣人抱一为天下式。不自见（xiàn），故明；不自是，故彰；不自伐，故有功；不自矜（jīn），故长（cháng）。夫唯不争，故天下莫能与之争。古之所谓“曲则全”者，岂虚言哉？诚全而归之。</t>
   </si>
   <si>
     <t>忍受委屈则能保全自我，先弯曲反而能够伸直，低洼反而能够变得充盈，守旧反而能够创新，少取一些则有所收获，贪得无厌反而会变得迷惑。因此圣人能够同以上原则保持一致（持守道作为天下的法则）。他们不仅仅依靠自己的眼睛去观察，所以才能够看得清楚；从不自以为是，所以才能够彰显名声；从不自我夸耀，所以才能够保有功劳；从不自高自大，所以才能够成为领导者。正因为他们从不与别人争夺，所以天下没有任何人能够争得赢他们。古人所说的“委屈则能求全”这句话，难道是句空话吗？确实应该把保全自我的功劳归于这一原则（回归道）。</t>
   </si>
   <si>
-    <t>本章开头即主旨：曲则全，枉则直——懂得委婉迂回，才有更圆满的结果，像水一样绕开障碍、曲折流淌，才能到达目标；洼则盈——低洼处先被水灌满，善于处下才能获得更多；敝则新——破旧才有更新，世界有生有灭才生生不息；少则得，多则惑——知道自己懂得少才会努力学习，贪多反而迷惑。是以圣人抱一为天下式：圣人持守“一”作为天下范式，“一”就是阴阳两者的统一，看问题不能偏颇，要把对立两面合起来理解，就像同是数字6，对面看是9，各有立场。
+    <t>【迂回 谦下 统一的思维处理问题】本章开头即主旨：曲则全，枉则直——懂得委婉迂回，才有更圆满的结果，像水一样绕开障碍、曲折流淌，才能到达目标；洼则盈——低洼处先被水灌满，善于处下才能获得更多；敝则新——破旧才有更新，世界有生有灭才生生不息；少则得，多则惑——知道自己懂得少才会努力学习，贪多反而迷惑。是以圣人抱一为天下式：圣人持守“一”作为天下范式，“一”就是阴阳两者的统一，看问题不能偏颇，要把对立两面合起来理解，就像同是数字6，对面看是9，各有立场。
 不自见故明，不自是故彰，不自伐故有功，不自矜故长：不固执己见才看得清，不自以为是才声名彰显，不自我夸耀才保有功劳，不自高自大才长久。夫唯不争，故天下莫能与之争：因为不与别人争夺，天下没有人能争得过他。古之所谓曲则全者，岂虚言哉，诚全而归之：古人说的曲则全，确实能把圆满的结果带回来。本章教人以迂回、谦下、统一的思维处理问题。</t>
   </si>
   <si>
+    <t>28、66</t>
+  </si>
+  <si>
     <t>第二十三章（23）</t>
   </si>
   <si>
     <t>希言自然。故飘风不终朝（zhāo），骤雨不终日。孰为此者？天地。天地尚不能久，而况于人乎？故从事于道者，同于道；德者，同于德；失者，同于失。同于道者，道亦乐得之；同于德者，德亦乐得之；同于失者，失亦乐得之。信不足焉，有不信焉。</t>
   </si>
   <si>
-    <t>君主要很少发号施令而让百姓自由发展 这样才是合乎自然的。所以说狂风刮不了整整一个早晨，暴雨下不了整整一天。谁制造了这些狂风暴雨？是天地。天地尚且不能长久维持这种剧烈动荡的局面，更何况人呢？因此那些寻求大道的人，言行就会符合大道；修养美德的人，就会具备美德；坚持错误的人，就会永远犯错误。愿意同大道在一起的人，大道也乐于同他在一起；愿意同美德在一起的人，美德也乐于同他在一起；愿意同错误在一起的人，错误也乐于同他在一起。因为失道失德的人诚信不足，大家都不信任他们。</t>
-  </si>
-  <si>
-    <t>本章讲少言自然、同气相求。希言自然：珍惜言语、少发号施令，顺其自然才是规律。飘风不终朝，骤雨不终日：狂风刮不过一个早晨，暴雨下不了一整天，天地发的“脾气”尚且不能长久，何况人呢？人不应长期处于急躁、暴躁、浮躁的情绪状态。从事于道者，同于道；德者，同于德；失者，同于失：追求道的人与道相合，修养德的人与德相合，放任过失的人与过失相合。
+    <t>君主要很少发号施令而让百姓自由发展 这样才是合乎自然的。所以说狂风不会一直刮，暴雨不会一直下。谁制造了这些狂风暴雨？是天地。天地尚且不能长久维持这种剧烈动荡（大风大雨）的局面，更何况人呢？因此那些寻求大道的人，言行就会符合大道；修养美德的人，就会具备美德；坚持错误的人，就会永远犯错误。愿意同大道在一起的人，大道也乐于同他在一起；愿意同美德在一起的人，美德也乐于同他在一起；愿意同错误在一起的人，错误也乐于同他在一起。因为失道失德的人诚信不足，大家都不信任他们。</t>
+  </si>
+  <si>
+    <t>【要亲近有道有德的人和事】本章讲少言自然、同气相求。希言自然：珍惜言语、少发号施令，顺其自然才是规律。飘风不终朝，骤雨不终日：狂风刮不过一个早晨，暴雨下不了一整天，天地发的“脾气”尚且不能长久，何况人呢？人不应长期处于急躁、暴躁、浮躁的情绪状态。从事于道者，同于道；德者，同于德；失者，同于失：追求道的人与道相合，修养德的人与德相合，放任过失的人与过失相合。
 同于道者，道亦乐得之；同于德者，德亦乐得之；同于失者，失亦乐得之：你喜欢什么、亲近什么，就会被什么吸引和成就，人身边聚集什么样的人，往往取决于你自己是什么样的人。信不足焉，有不信焉：自己诚信不足，别人自然不会信任你。译者·韩鹏杰指出，本章看似同语反复，其实在反复劝告：要让自己的境界不断提高，就要亲近有道有德的人和事，勇于发现并改正缺点，路是自己走出来的。</t>
   </si>
   <si>
     <t>第二十四章（24）</t>
   </si>
   <si>
-    <t>企者不立；跨者不行；自见者不明；自是者不彰；自伐者无功；自矜者不长。其在道也，曰余食赘（zhuì）行。物或恶（wù）之，故有道者不处。</t>
-  </si>
-  <si>
-    <t>踮起脚跟想站得高一些的人反而站不稳；跨着大步想走得快一些的人反而走不远；仅仅依靠自己的眼睛去观察反而看不清楚；自以为是反而名声不高；自我夸功反而会把功劳夸没了；自高自大反而做不了领导者。站在大道的立场上去衡量这些行为，可以说这些行为都像剩饭肉瘤一样多余无用。人们大概都很讨厌这些行为，所以懂得大道的人不去做这样的事情。</t>
-  </si>
-  <si>
-    <t>本章列举自见、自是、自伐、自矜四种毛病，提醒人们平稳谦逊。企者不立：踮起脚尖想站得高，反而站不稳；跨者不行：跨着大步想走得快，反而走不远，稳定才能致远。自见者不明：固执己见的人看不清，兼听则明、偏听则暗；自是者不彰：自以为是，德行和功绩反不能彰显；自伐者无功：自我夸耀、攻击别人，反而把功劳送掉；自矜者不长：自高自大、放不下虚荣，反而失去成长机会。
+    <t>企者不立；跨者不行；自见(jiàn)者不明；自是者不彰；自伐者无功；自矜者不长（zhǎng）。其在道也，曰余食赘（zhuì）行。物或恶（wù）之，故有道者不处。</t>
+  </si>
+  <si>
+    <t>踮起脚跟想站得高一些的人反而站不稳；跨着大步想走得快一些的人反而走不远；仅仅依靠自己的眼睛去观察反而看不清楚；自以为是反而名声不高；自我夸功表扬反而会把功劳夸没了；自高自大反而做不了领导者。站在大道的立场上去衡量这些行为，可以说这些行为都像剩饭肉瘤一样多余无用。人们大概都很讨厌这些行为，所以懂得大道的人不去做这样的事情。</t>
+  </si>
+  <si>
+    <t>【做事稳扎稳打 平稳谦逊】本章列举自见、自是、自伐、自矜四种毛病，提醒人们平稳谦逊。企者不立：踮起脚尖想站得高，反而站不稳；跨者不行：跨着大步想走得快，反而走不远，稳定才能致远。自见者不明：固执己见的人看不清，兼听则明、偏听则暗；自是者不彰：自以为是，德行和功绩反不能彰显；自伐者无功：自我夸耀、攻击别人，反而把功劳送掉；自矜者不长：自高自大、放不下虚荣，反而失去成长机会。
 其在道也，曰余食赘行：这些行为在道看来，就像吃饱了再吃、身上长赘瘤，多余无用；物或恶之，故有道者不处：人们厌恶它们，有道的人不做这些事。译者·韩鹏杰用项羽举例：力拔山兮气盖世，却因骄傲自大、听不进意见，落得自刎乌江的下场。孔子讲毋意、毋必、毋固、毋我，佛家讲无我相，与老子相通。做事要稳扎稳打，收敛自见、自是、自伐、自矜，才能不断进步。</t>
   </si>
   <si>
@@ -438,7 +453,7 @@
     <t>有一个事物混然而成，它出现在天地之先。它无声无形，独立存在永不改变，它支配万物循环运动永不停止，可以把它看作是天地万物产生的根源。我不知道这个事物的名字，就给它起个字叫“道”，再勉强给它起个名叫“大”。“大”使万物向前发展，发展下去就会走向极盛，走向极盛后又要返回到起点。所以说道有道的规律，天有天的规律，地有地的规律，治国也有治国的规律。天地间有四种主要规律，而治国的规律只占其中之一。人要效法地，地要效法天，天要效法大道，大道就效法它自身的样子。</t>
   </si>
   <si>
-    <t>本章是《道德经》极重要的一章，把道确立为宇宙本源，并提出全书最高法则道法自然。有物混成，先天地生：有一个混然一体的东西，先于天地而存在；寂兮寥兮：它无声无形；独立不改，周行而不殆：独立存在、永不改变，循环运行、永不停止，可以为天下母：可以看作天地万物的母亲。吾不知其名，字之曰道，强为之名曰大：不知它叫什么名字，勉强称它为道，再勉强称它为大。大曰逝，逝曰远，远曰反：大则向前运行，运行则越走越远，远到极点又返回本根，这是道的运动轨迹——周而复始。
+    <t>【人要敬畏天道 与天地和谐相处】本章是《道德经》极重要的一章，把道确立为宇宙本源，并提出全书最高法则道法自然。有物混成，先天地生：有一个混然一体的东西，先于天地而存在；寂兮寥兮：它无声无形；独立不改，周行而不殆：独立存在、永不改变，循环运行、永不停止，可以为天下母：可以看作天地万物的母亲。吾不知其名，字之曰道，强为之名曰大：不知它叫什么名字，勉强称它为道，再勉强称它为大。大曰逝，逝曰远，远曰反：大则向前运行，运行则越走越远，远到极点又返回本根，这是道的运动轨迹——周而复始。
 道大，天大，地大，王亦大，域中有四大，而王居其一焉：道、天、地、人（王）都是大的，人只是四大之一，不能自大。人法地，地法天，天法道，道法自然：人效法地，地效法天，天效法道，道效法它本来的样子，自然就是本该如此。译者·韩鹏杰强调，道法自然是全书信仰和规则的源头，人要敬畏天道，与天地和谐相处。</t>
   </si>
   <si>
@@ -451,7 +466,7 @@
     <t>重是轻的基础，静是动的根本。因此圣人每天总是保持稳重 就像军队离不开自己的衣食行李。即使有奇观美景，也安处超然。为什么一个大国君主，却为了个人享乐而不重视自己的国家呢？不重视国家就会丧失自己的生存基础，轻举妄动就会丢掉自己的生存根本。</t>
   </si>
   <si>
-    <t>本章讲重与轻、静与躁的关系。重为轻根：稳重是轻率的根本，要拿稳重控制住轻率，不让它表露、掌控自己；静为躁君：宁静是急躁的主宰，用安静、宁静、冷静控制浮躁、急躁、暴躁。是以圣人终日行不离辎重：有修养的人像行军不离粮草辎重一样，始终持守稳重这个根本。虽有荣观，燕处超然：面对华美堂皇的外在诱惑，依然安处超然，不为其所动。奈何万乘之主，而以身轻天下：为什么掌握大权的君主，却为了个人享乐而轻率地对待天下大事？
+    <t>【重与轻、静与躁的关系】本章讲重与轻、静与躁的关系。重为轻根：稳重是轻率的根本，要拿稳重控制住轻率，不让它表露、掌控自己；静为躁君：宁静是急躁的主宰，用安静、宁静、冷静控制浮躁、急躁、暴躁。是以圣人终日行不离辎重：有修养的人像行军不离粮草辎重一样，始终持守稳重这个根本。虽有荣观，燕处超然：面对华美堂皇的外在诱惑，依然安处超然，不为其所动。奈何万乘之主，而以身轻天下：为什么掌握大权的君主，却为了个人享乐而轻率地对待天下大事？
 轻则失根：轻率轻浮就失去根本，像飘蓬浮萍没有根基；躁则失君：浮躁急躁就失去对自己的掌控，冲动之下常常酿成大祸。译者·韩鹏杰用“路怒”举例：开车偶有小摩擦就粗口相向甚至拔刀，动手前问自己要不要动手、后果如何、有无别的办法，几秒钟的冷静可能改变结果。开头八字“重为轻根，静为躁君”与结尾“轻则失根，躁则失君”都是至理名言。</t>
   </si>
   <si>
@@ -461,10 +476,10 @@
     <t>善行，无辙迹；善言，无瑕谪（zhé）；善数，不用筹策；善闭，无关楗（jiàn）而不可开；善结，无绳约而不可解。是以圣人常善救人，故无弃人；常善救物，故无弃物。是谓袭明。故善人者，不善人之师；不善人者，善人之资。不贵其师，不爱其资，虽智大迷，是谓要妙。</t>
   </si>
   <si>
-    <t>善于行走的人，不会留下车辙痕迹；善于讲话的人，不会出现语言瑕疵；善于计算的人，不必使用筹策；善于关门的人，不用关楗却固不可开；善于打结的人，不用绳索却牢不可解。因此圣人总是善于感化、以道救人，所以没有被遗弃的人。这是承袭道的智慧。善良的人，是不善人的老师；不善良的人，是善人的借鉴。不善人如果不尊重他们的老师，善人如果不爱惜他们的借鉴，即使是明智的人也会变得十分糊涂，善人与不善人之间的关系是非常重要而微妙的。</t>
-  </si>
-  <si>
-    <t>本章讲善行无迹、善救无弃。善行无辙迹：真正的善行不留下痕迹，做了好事为了留名、作秀，就走到反面；善言无瑕谪：会说话的人语言没有瑕疵，与其多言被挑毛病，不如大音希声、无言胜有声；善数不用筹策：真正会计算的人不用算盘筹码，很多事情越算计越被算计，厚道才是最高的聪明；善闭无关楗而不可开：真正会关闭的人不用门闩门锁，心门上锁就找不到锁在哪里；善结无绳约而不可解：真正会捆绑的人不用绳索，情丝情网看似无形却解不开。
+    <t>善于行走的人，不会留下车辙痕迹；善于讲话的人，不会出现语言瑕疵；善于计算的人，不必使用筹策工具；善于关门的人，不用关楗却固不可开；善于打结的人，不用绳索却牢不可解。因此圣人总是善于感化、以道救人，所以没有被遗弃的人。这是承袭道的智慧。善良的人，是不善人的老师；不善良的人，是善人的借鉴。不善人如果不尊重他们的老师，善人如果不爱惜他们的借鉴，即使是明智的人也会变得十分糊涂，善人与不善人之间的关系是非常重要而微妙的。</t>
+  </si>
+  <si>
+    <t>【瑕不掩瑜 看人看物要发现其用处】本章讲善行无迹、善救无弃。善行无辙迹：真正的善行不留下痕迹，做了好事为了留名、作秀，就走到反面；善言无瑕谪：会说话的人语言没有瑕疵，与其多言被挑毛病，不如大音希声、无言胜有声；善数不用筹策：真正会计算的人不用算盘筹码，很多事情越算计越被算计，厚道才是最高的聪明；善闭无关楗而不可开：真正会关闭的人不用门闩门锁，心门上锁就找不到锁在哪里；善结无绳约而不可解：真正会捆绑的人不用绳索，情丝情网看似无形却解不开。
 是以圣人常善救人，故无弃人；常善救物，故无弃物：圣人善于救人救物，天下没有可抛弃的人、没有可抛弃之物，你没发现用处不等于无用，无用方为大用。善人者，不善人之师；不善人者，善人之资：善人是恶人的老师，恶人是善人的借鉴，“师资”一词正源于此。不贵其师，不爱其资，虽智大迷：不尊重老师、不爱惜借鉴，再聪明也是大迷惑，这是道的枢要。做人要善行不留痕迹，看人看物发现其用处，并善于从正反两方面学习。</t>
   </si>
   <si>
@@ -962,7 +977,7 @@
     <t>这一章所讲的这个道理是《道德经》从头至尾所强调的“善于处下”，只有善于处下，才能真正居上。我们在一开始说过，《道德经》的很多话是针对那些领导者、统治者讲的，所以老先生认为越是位置高的领导者、统治者，越要善于处下，为什么呢？首先从处下的结果上来看，“江海所以能为百谷王者，以其善下之，故能为百谷王。”这句话我在前面也多次引用过。大江大海之所以能成为大江大海，是因为善于处下，不辞细流，能团结一切可以团结的力量，故能为“百谷王”。老子先拿“百川归海”的形象讲了这个道理，让大家有一个感知。下面就开始讲具体的做法和内容。“是以欲上民，必以言下之。”所以你要想站在上面领导好下面这些人，在语言上要懂得谦逊、谦让。领导者，尤其国君、皇帝这一类的，讲话的时候不能够居高临下，盛气凌人，自尊自大，不可一世。第三十九章说过“贵以贱为本，高以下为基。是以侯王自称孤寡不穀”，所以在语言上要谦逊。“欲先民，必以身后之。”想要站在前面当好领导、当好领头的，要懂得把自己的利益放在后面，想要领导别人就得给别人利益。一个人既要领导别人，又想什么好处、利益、功名都抢在自己手上，这个人下场不是不言而喻的吗？范仲淹的《岳阳楼记》里说“先天下之忧而忧，后天下之乐而乐”，做官、做领导不得如此吗？钱钟书先生认为范仲淹这两句话就是出自《道德经》的。但是人家学得比较好，不也成了大家都熟悉的名句了吗？“是以圣人处上而民不重”，所以一个好的领导者，你在上面领导大家，大家没有感觉到沉重的压力。“处前而民不害”，你在前面领导大家，大家没有感觉到你对他的危害。因为你要想领导别人，得让别人得到利益。西汉史学家司马迁在《史记·循吏列传》说：“公仪休者，鲁博士也。以高弟为鲁相。奉法循理，无所变更，百官自正。使食禄者不得与下民争利，受大者不得取小。”这里的食禄者不与民争利，意思是做官的人不许和百姓争夺利益。“是以天下乐推而不厌”，所以天下的人民都往高举你，往前推你，不感觉到厌倦、厌烦。如果统治者穷奢极欲，危害百姓，草菅人命，下面的人就会感觉到“害”、感觉到“重”，这样的人百姓会“乐推”吗？当然不会。“以其不争，故天下莫能与之争。”一个领导者，能得到了大家的拥护、拥戴，正因为你不争，不与民争利，不与其他人争名，“利而不害，为而不争”，结果是“以其不争，故天下莫能与之争”。越是争的人，最后往往失败得越惨，因为你的位置已经规定了你应有的担当、使命和责任。陈毅元帅讲过“手莫伸，伸手必被捉”，形象而深刻，那么，反过来用这个道理讲，就得以更加明确了。“以其不争，故天下莫能与之争”，所谓“不争”，并不是消极被动，“不争”，当然要了解边界，不争边界之外的东西，这样的话才能“天下乐推而不厌”。</t>
   </si>
   <si>
-    <t>2、7、11</t>
+    <t>2、7、11、22</t>
   </si>
   <si>
     <t>第六十七章（67）</t>
@@ -2980,8 +2995,8 @@
       <c r="F16" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="11">
-        <v>1</v>
+      <c r="G16" s="11" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="17" ht="172.8" spans="1:7">
@@ -2989,16 +3004,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>16</v>
@@ -3007,21 +3022,21 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" ht="158.4" spans="1:7">
+    <row r="18" ht="172.8" spans="1:7">
       <c r="A18" s="10">
         <v>16</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>16</v>
@@ -3033,79 +3048,85 @@
         <v>17</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G19" s="11"/>
-    </row>
-    <row r="20" ht="144" spans="1:7">
+      <c r="G19" s="11">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" ht="158.4" spans="1:7">
       <c r="A20" s="10">
         <v>18</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="11"/>
+      <c r="G20" s="11" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="21" ht="158.4" spans="1:7">
       <c r="A21" s="10">
         <v>19</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G21" s="11"/>
+      <c r="G21" s="11" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="22" ht="187.2" spans="1:7">
       <c r="A22" s="10">
         <v>20</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>16</v>
@@ -3119,106 +3140,112 @@
         <v>21</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G23" s="11"/>
-    </row>
-    <row r="24" ht="172.8" spans="1:7">
+      <c r="G23" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" ht="187.2" spans="1:7">
       <c r="A24" s="10">
         <v>22</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="11"/>
+      <c r="G24" s="11" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="25" ht="158.4" spans="1:7">
       <c r="A25" s="10">
         <v>23</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G25" s="11"/>
     </row>
-    <row r="26" ht="158.4" spans="1:7">
+    <row r="26" ht="172.8" spans="1:7">
       <c r="A26" s="10">
         <v>24</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="11"/>
+      <c r="G26" s="11">
+        <v>2</v>
+      </c>
     </row>
     <row r="27" ht="172.8" spans="1:7">
       <c r="A27" s="10">
         <v>25</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G27" s="11">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" ht="172.8" spans="1:7">
@@ -3226,16 +3253,16 @@
         <v>26</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>16</v>
@@ -3249,16 +3276,16 @@
         <v>27</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>16</v>
@@ -3270,37 +3297,39 @@
         <v>28</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G30" s="11"/>
+      <c r="G30" s="11">
+        <v>22</v>
+      </c>
     </row>
     <row r="31" ht="172.8" spans="1:7">
       <c r="A31" s="10">
         <v>29</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>16</v>
@@ -3312,16 +3341,16 @@
         <v>30</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>16</v>
@@ -3333,16 +3362,16 @@
         <v>31</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>16</v>
@@ -3354,16 +3383,16 @@
         <v>32</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>16</v>
@@ -3377,16 +3406,16 @@
         <v>33</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F35" s="11" t="s">
         <v>16</v>
@@ -3398,16 +3427,16 @@
         <v>34</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>16</v>
@@ -3419,16 +3448,16 @@
         <v>35</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>16</v>
@@ -3440,16 +3469,16 @@
         <v>36</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>16</v>
@@ -3461,16 +3490,16 @@
         <v>37</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>16</v>
@@ -3482,19 +3511,19 @@
         <v>38</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G40" s="11"/>
     </row>
@@ -3503,19 +3532,19 @@
         <v>39</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G41" s="11">
         <v>2</v>
@@ -3526,19 +3555,19 @@
         <v>40</v>
       </c>
       <c r="B42" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="F42" s="11" t="s">
         <v>180</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>175</v>
       </c>
       <c r="G42" s="11"/>
     </row>
@@ -3547,19 +3576,19 @@
         <v>41</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G43" s="11"/>
     </row>
@@ -3568,22 +3597,22 @@
         <v>42</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="45" ht="409.5" spans="1:7">
@@ -3591,19 +3620,19 @@
         <v>43</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G45" s="11"/>
     </row>
@@ -3612,19 +3641,19 @@
         <v>44</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G46" s="11"/>
     </row>
@@ -3633,19 +3662,19 @@
         <v>45</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G47" s="11"/>
     </row>
@@ -3654,19 +3683,19 @@
         <v>46</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G48" s="11"/>
     </row>
@@ -3675,19 +3704,19 @@
         <v>47</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G49" s="11"/>
     </row>
@@ -3696,19 +3725,19 @@
         <v>48</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G50" s="11"/>
     </row>
@@ -3717,19 +3746,19 @@
         <v>49</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G51" s="11"/>
     </row>
@@ -3738,19 +3767,19 @@
         <v>50</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G52" s="11"/>
     </row>
@@ -3759,19 +3788,19 @@
         <v>51</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G53" s="11"/>
     </row>
@@ -3780,19 +3809,19 @@
         <v>52</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G54" s="11">
         <v>6</v>
@@ -3803,19 +3832,19 @@
         <v>53</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G55" s="11"/>
     </row>
@@ -3824,19 +3853,19 @@
         <v>54</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G56" s="11"/>
     </row>
@@ -3845,19 +3874,19 @@
         <v>55</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G57" s="11"/>
     </row>
@@ -3866,19 +3895,19 @@
         <v>56</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G58" s="11"/>
     </row>
@@ -3887,22 +3916,22 @@
         <v>57</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="60" ht="409.5" spans="1:7">
@@ -3910,19 +3939,19 @@
         <v>58</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G60" s="11"/>
     </row>
@@ -3931,19 +3960,19 @@
         <v>59</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G61" s="11"/>
     </row>
@@ -3952,19 +3981,19 @@
         <v>60</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G62" s="11"/>
     </row>
@@ -3973,19 +4002,19 @@
         <v>61</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G63" s="11"/>
     </row>
@@ -3994,19 +4023,19 @@
         <v>62</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G64" s="11"/>
     </row>
@@ -4015,22 +4044,22 @@
         <v>63</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="66" ht="409.5" spans="1:7">
@@ -4038,19 +4067,19 @@
         <v>64</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G66" s="11">
         <v>63</v>
@@ -4061,19 +4090,19 @@
         <v>65</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G67" s="11"/>
     </row>
@@ -4082,22 +4111,22 @@
         <v>66</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="69" ht="409.5" spans="1:7">
@@ -4105,19 +4134,19 @@
         <v>67</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G69" s="11"/>
     </row>
@@ -4126,19 +4155,19 @@
         <v>68</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G70" s="11"/>
     </row>
@@ -4147,40 +4176,42 @@
         <v>69</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="G71" s="11"/>
+        <v>180</v>
+      </c>
+      <c r="G71" s="11">
+        <v>17</v>
+      </c>
     </row>
     <row r="72" ht="409.5" spans="1:7">
       <c r="A72" s="10">
         <v>70</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G72" s="11"/>
     </row>
@@ -4189,22 +4220,22 @@
         <v>71</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="74" ht="374.4" spans="1:7">
@@ -4212,19 +4243,19 @@
         <v>72</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G74" s="11"/>
     </row>
@@ -4233,19 +4264,19 @@
         <v>73</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G75" s="11"/>
     </row>
@@ -4254,19 +4285,19 @@
         <v>74</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G76" s="11"/>
     </row>
@@ -4275,19 +4306,19 @@
         <v>75</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G77" s="11">
         <v>10</v>
@@ -4298,19 +4329,19 @@
         <v>76</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G78" s="11"/>
     </row>
@@ -4319,19 +4350,19 @@
         <v>77</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G79" s="11"/>
     </row>
@@ -4340,22 +4371,22 @@
         <v>78</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" ht="409.5" spans="1:7">
@@ -4363,19 +4394,19 @@
         <v>79</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G81" s="11"/>
     </row>
@@ -4384,19 +4415,19 @@
         <v>80</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G82" s="11"/>
     </row>
@@ -4405,19 +4436,19 @@
         <v>81</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G83" s="11">
         <v>7</v>
@@ -4475,19 +4506,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="G2" s="3"/>
     </row>
@@ -4496,19 +4527,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="G3" s="4"/>
     </row>
@@ -4517,19 +4548,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>362</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>357</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -4538,19 +4569,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="G5" s="4"/>
     </row>
@@ -4559,19 +4590,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="G6" s="4"/>
     </row>
@@ -4580,19 +4611,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -4601,19 +4632,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -4622,19 +4653,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>385</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>380</v>
       </c>
       <c r="G9" s="4"/>
     </row>
@@ -4643,19 +4674,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G10" s="4"/>
     </row>
@@ -4664,19 +4695,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="G11" s="4"/>
     </row>
@@ -4685,19 +4716,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="G12" s="4"/>
     </row>
@@ -4706,19 +4737,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="G13" s="4"/>
     </row>
@@ -4727,19 +4758,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -4748,19 +4779,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="G15" s="4"/>
     </row>
@@ -4769,19 +4800,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="G16" s="4"/>
     </row>
@@ -4790,19 +4821,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>422</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>417</v>
       </c>
       <c r="G17" s="4"/>
     </row>
@@ -4811,19 +4842,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="G18" s="4"/>
     </row>
@@ -4832,19 +4863,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="G19" s="4"/>
     </row>
@@ -4853,19 +4884,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="G20" s="4"/>
     </row>
@@ -4874,19 +4905,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="G21" s="4"/>
     </row>
@@ -4895,19 +4926,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="G22" s="4"/>
     </row>
@@ -4916,19 +4947,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>447</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>450</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>442</v>
       </c>
       <c r="G23" s="4"/>
     </row>
@@ -4937,19 +4968,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="G24" s="4"/>
     </row>
@@ -4958,19 +4989,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="G25" s="4"/>
     </row>
@@ -4979,19 +5010,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="G26" s="4"/>
     </row>
@@ -5000,19 +5031,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="G27" s="4"/>
     </row>
@@ -5021,19 +5052,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="G28" s="4"/>
     </row>

--- a/book.xlsx
+++ b/book.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="495">
   <si>
     <t>no</t>
   </si>
@@ -60,16 +60,16 @@
   <si>
     <t>学习道德经之前，先了解《道德经》的背景（其人，其书，其道）
 1、其人：老子这个人，我们要讲两个内容：一个是老子的职业背景；另一个是这本书的写作背景。
-(1)老子的职业：先他掌管天下的图书，别人看不到的很多的著作他都能读得到，知识渊博。
-(2)写作的背景：尹喜在函谷关对老子说，如果不写“道”的思想，就不让其过关。
+（1）老子的职业：先他掌管天下的图书，别人看不到的很多的著作他都能读得到，知识渊博。
+（2）写作的背景：尹喜在函谷关对老子说，如果不写“道”的思想，就不让其过关。
 2、其书：经过考古验证发现，老子亲手撰写的版本为帛书版，为了便后人理解，前人进行了优化。
-(1)版本的迭代：道德经被历史名人修改后很多版，后人多以魏晋王弼的经典版进行学习和传诵。
-(2)书名的由来：因为“道”和“德”出现的频率最高，故汉朝时期又名《老子》。
-(3)形象的体现：《道德经》落实到现实中包含的内容——目标、方向、规则、境界、边界、底线。
+（1）版本的迭代：道德经被历史名人修改后很多版，后人多以魏晋王弼的经典版进行学习和传诵。
+（2）书名的由来：因为“道”和“德”出现的频率最高，故汉朝时期又名《老子》。
+（3）形象的体现：《道德经》落实到现实中包含的内容——目标、方向、规则、境界、边界、底线。
 3、其道：老子所写的《道德经》的受众对象主要是针对三类人而写的。
-(1)第一类人 - 士：基层的领导者和管理者（推十为一，把自己放在最后的位置）。
-(2)第二类人 - 王：主要的领导者（善用人者为之下，姿态谦卑尊重对方）。
-(3)第三类人 - 圣：品德修养高，通情达理的领导者（圣人之道为而不争，为大家谋福利）。</t>
+（1）第一类人 - 士：基层的领导者和管理者（推十为一，把自己放在最后的位置）。
+（2）第二类人 - 王：主要的领导者（善用人者为之下，姿态谦卑尊重对方）。
+（3）第三类人 - 圣：品德修养高，通情达理的领导者（圣人之道为而不争，为大家谋福利）。</t>
   </si>
   <si>
     <t>译者·韩鹏杰《道德经说什么》</t>
@@ -77,8 +77,8 @@
   <si>
     <t>本章是全书导读，回答为什么读《道德经》、这本书讲什么、写给谁三个问题。为什么要学经典：经典是一个民族文化传承的途径与道路，认真读透一本经典胜过泛读百书，也是在为往圣继绝学、为万世开太平。
 其人：老子曾任周朝守藏史，掌管天下图书，能读到别人看不到的著作，知识渊博；因尹喜在函谷关要求他写下“道”的思想，才留下这部经典。
-其书：经考古验证，帛书版最接近老子亲笔原貌，后人为了便于理解不断优化，后世多沿用魏晋王弼的经典本；书名因“道”“德”出现频率最高而得名；道落实到现实生活，包含目标、方向、规则、境界、边界、底线六个方面。
-其道：本书主要写给三类人——士（基层领导者，推十为一、把自己放在最后）、王（主要领导者，善用人者为之下）、圣（品德修养高、通情达理的领导者，为而不争、为大家谋福利）。书中讲的是治国之道、为官之道与人生之道，为逐章解读打下基础。</t>
+其书：经考古验证，帛书版最接近老子亲笔原貌，后人为了便于理解不断优化，后世多沿用魏晋王弼的经典本；书名因“道”、“德”出现频率最高而得名；道落实到现实生活，包含目标、方向、规则、境界、边界、底线六个方面。
+其道：本书主要写给三类人——士（基层领导者，推十为一、把自己放在最后）、王（主要领导者，善用人者为之下）、圣（品德修养高、通情达理的领导者，为而不争、为大家谋福利）。书中讲的是治国之道、为官之道、人生之道。</t>
   </si>
   <si>
     <t>道德经</t>
@@ -90,14 +90,14 @@
     <t>道可道，非常道；名可名，非常名。无，名天地之始；有，名万物之母。故常无，欲以观其妙；常有，欲以观其徼（jiào）。此两者同出而异名，同谓之玄，玄之又玄，众妙之门。</t>
   </si>
   <si>
-    <t>可以言说的道，就不是永恒的道；能够用来称呼的具体名称，就不是永恒的名称。天地开始的时候，把它叫做“无”；万物的母亲，把它叫做“有”。所以常处于无，从无的角度来观察它的妙处；常处于有，从有的角度来观察它的边界。有和无是任何事物都具有的两个方面，来源相同但名称不同，都可以称之为“玄妙深远”，玄而又玄，是一切奥妙的源头。</t>
-  </si>
-  <si>
-    <t>【大象无形】本章是《道德经》的门户，核心是“有”和“无”，特别强调常被忽略的“无”。道可道，非常道；名可名，非常名：道是最高、最全面的存在，用语言和逻辑讲出来就变成有局限的道，所以要借形象来领悟。无，名天地之始；有，名万物之母：天地起源时混沌无形，称为无；天地成形、万物出现，称为有。任何事物都有有和无两个方面，观察事物既要从“有”的角度看它的边界，也要从“无”的角度看它的妙处。
+    <t>可以言说的道，就不是永恒的道；能够用来称呼的具体名称，就不是永恒的名称。天地开始的时候，把它叫做“无”；万物的母亲，把它叫做“有”。所以常处于无，从无的角度来观察它的妙处；常处于有，从有的角度来观察它的边界。有和无是任何事物都具有的两个方面，来源相同（同出于道）但名称不同 都可以称之为“幽深玄远”，幽深之中更幽深，是一切奥妙的源头。</t>
+  </si>
+  <si>
+    <t>【大象（道）无形】本章是《道德经》的门户，核心是“有”和“无”，特别强调常被忽略的“无”。道可道，非常道；名可名，非常名：道是最高、最全面的存在，用语言和逻辑讲出来就变成有局限的道，所以要借形象来领悟（如 把道比喻成风）。无，名天地之始；有，名万物之母：天地起源时混沌无形，称为无；天地成形、万物出现，称为有。任何事物都有有和无两个方面，观察事物既要从“有”的角度看它的边界，也要从“无”的角度看它的妙处。
 此两者同出而异名，同谓之玄：能把有和无合起来理解，已是高级的思维水平，叫做玄；再进一步看到无形力量（精神、信仰、家风、作风等）的巨大作用，就是玄之又玄、众妙之门。译者·韩鹏杰以“风”为形象：风无形却力量无尽，正如人的精神世界。老子提醒人们不要只看到金钱、财富等有形的东西，更要看到精神、思想、理想信念这些无形的力量；只重有形，物质越发达，精神家园就越花果飘零。</t>
   </si>
   <si>
-    <t>道经</t>
+    <t>道经 | 自然之道</t>
   </si>
   <si>
     <t>4、14、21、25</t>
@@ -109,14 +109,17 @@
     <t>天下皆知美之为美，斯恶（è）已；皆知善之为善，斯不善已。故有无相（xiāng）生，难易相成，长短相较，高下相倾，音声相和（hè），前后相随。是以圣人处无为之事，行不言之教（jiào），万物作焉而不辞，生而不有，为而不恃（shì），功成而弗居。夫唯弗居，是以不（bù）去。</t>
   </si>
   <si>
-    <t>天下都知道美是什么，丑自然就存在了；都知道什么是善，不善自然也就出现了。所以有和无相待而生，难和易相待而成，长和短相待而显，高和下相待而倾倚，音和声相待而和谐，前和后相待而顺序相随。所以圣人行事 顺乎自然 崇尚无为，实行不言的教诲，顺应万物自然的生长而不加干预，创造万物而不占有，施泽万物而不将这当成是倚仗、凭借的手段，有了功劳而不居功（自傲）。正因为他不居功自傲，所以也就不会失去自己的功劳。</t>
+    <t>天下都知道美是什么，丑自然就显现出来了；都知道什么是善，不善自然也就出现了。所以有和无相待而生，难和易相待而成，长和短相待而显，高和下相待而倾倚，音和声相待而和谐，前和后相待而顺序相随。所以圣人行事 顺乎自然 崇尚无为（无为：不妄为、不强行、不主观强行干扰），实行不言的教诲，顺应万物自然的生长而不加干预，创造万物而不占有，施泽万物而不将这当成是倚仗、凭借的手段，有了功劳而不居功（自傲）。正因为它不居功（自傲），所以它也就不会失去自己的功劳。</t>
   </si>
   <si>
     <t>【相比较而存在 相对立而发展】本章讲世界运动的规律和认识世界的方法，是理解《道德经》的另一扇门。用哲学的语言概括：相比较而存在，相对立而发展。天下皆知美之为美，斯恶已；皆知善之为善，斯不善已：知道美就知道丑，知道善就知道不善，对立双方互相规定、互相依存。老子随后列出有无相生、难易相成、长短相较、高下相倾、音声相和、前后相随，指出这些对立面并非固定不变，而是在对立中运动、转化。
-因此圣人处无为之事，行不言之教：越是懂得有为，越要知道哪些该无为、该舍掉，从反面认识事情，才能达到更好的有为效果，千万不要把无为理解成消极。万物作焉而不辞，生而不有，为而不恃，功成而弗居：顺应万物自然生长而不干预，创造而不占有，做事而不依仗，有功而不居功，正因不居功，功德才不离去。本章后文许多重要内容提前概括出来，读熟这一章，后面很多章节都能以经解经。</t>
-  </si>
-  <si>
-    <t>11、39、63、66</t>
+因此圣人处无为之事，行不言之教：越是懂得有为，越要知道哪些该无为、该舍掉，从反面认识事情，才能达到更好的有为效果，千万不要把无为理解成消极。万物作焉而不辞，生而不有，为而不恃，功成而弗居：顺应万物自然生长而不干预，创造而不占有，做事而不依仗，有功而不居功，正因不居功，功德才不离去。后文许多重要内容都已在本章提前概括出来，读熟这一章，后面很多章节都能以经解经。</t>
+  </si>
+  <si>
+    <t>道经 | 无为之道</t>
+  </si>
+  <si>
+    <t>3、11、34、36、39、63、66</t>
   </si>
   <si>
     <t>第三章（3）</t>
@@ -125,26 +128,35 @@
     <t>不尚贤，使民不争；不贵难得之货，使民不为盗；不见（xiàn）可欲，使民心不乱。是以圣人之治，虚其心，实其腹；弱其志，强其骨。常使民无知无欲，使夫智者不敢为也。为无为，则无不治。</t>
   </si>
   <si>
-    <t>不崇尚标榜贤才，使民众不起争心；不炒作炫耀难得的物品，使民众不去做盗贼；不展现能引起人私欲的东西，使民众心不受惑乱。所以圣人的治理，使民众虚心、饱腹；减弱民众的欲望，强壮民众的身体。使民众常保持无知无欲的自然淳朴状态，那些诡计多端的人就不敢耍诈。以顺应自然、不强行干预、不违背规律的方式来治世，则没有治理不好的。</t>
+    <t>不崇尚标榜贤才，使百姓不起争心；不炒作炫耀难得的物品，使百姓不去做盗贼；不展现能引起人私欲的东西，使百姓心不受惑乱。所以圣人的治理，使百姓虚心，饱腹；减弱百姓的欲望，强壮百姓的身体。使百姓常保持无知无欲的自然淳朴状态，那些诡计多端的人就不敢耍诈。以顺应自然、不强行干预、不违背规律的方式来治世，则没有治理不好的。</t>
   </si>
   <si>
     <t>【两点论来看问题】本章与第二章紧密相连，讲看问题不能一点论，要两点论：好事发展到一定程度会向反面转化。不尚贤，使民不争：尚贤本是重视人才的好事，但一旦立了标准，就有人按标准投机取巧、自我包装，真正有才能的人不屑于此，反而被过滤掉，贤名被投机者占据，所以尚贤过了头反而害了人才选拔。不贵难得之货，使民不为盗；不见可欲，使民心不乱：不炒作珍贵物品、不显露引发欲望的东西，民心才不会乱。
 圣人之治，虚其心，实其腹，弱其志，强其骨：使民心虚静、生活温饱、欲望减弱、身体强健。常使民无知无欲，使夫智者不敢为也：少用智巧套路，投机者才不敢妄为。为无为，则无不治：治理者不妄为、不折腾，按规律和规则办事，天下自然治理得好。译者·韩鹏杰强调，老子的话对面坐着的是领导者，这些话是对治理者提出的警醒：任何事都有尺度，把握不好度，好事也会变成坏事。</t>
   </si>
   <si>
+    <t>道经 | 逆反之道</t>
+  </si>
+  <si>
+    <t>2、32</t>
+  </si>
+  <si>
     <t>第四章（4）</t>
   </si>
   <si>
     <t>道冲，而用之或不盈。渊兮，似万物之宗。挫其锐，解其纷，和其光，同其尘。湛兮似或存，吾不知谁（shuí）之子，象帝之先。</t>
   </si>
   <si>
-    <t>道是阴阳两者相互中和，其作用无穷无尽，其渊深、渊博好像万物的宗主。它锋芒不外露，解除纷扰，在光明之处便与光融合，在尘垢之处便与尘垢同一。其深远幽暗好像无处不在。我不知它是从何而来，只知道在象帝之前便已存在。</t>
+    <t>道是阴阳两者相互中和，其作用无穷无尽。其渊深、渊博，好像万物的宗主。它锋芒不外露，解除纷扰，在光明之处便与光融合，在尘垢之处便与尘垢同一。其深远幽暗好像无处不在，我不知它是从何而来（谁的儿子），只知道在象帝（上帝）之前便已存在。</t>
   </si>
   <si>
     <t>【相反力量在动态中达到和谐】本章强调道是万物的本源，理解的关键在“冲”字。冲是组合字，把两点放平就是“二中”，二指阴阳；冲的本义是两股水冲到一块，象征阴阳两种力量相互中和、相互作用、动态转化。道冲，而用之或不盈：阴阳中和而成道，作用无穷无尽。渊兮似万物之宗：道渊深博厚，像万物的宗主。挫其锐，解其纷，和其光，同其尘：道收敛锋芒、化解纷争，与光明融合、与尘垢同一，深远幽暗却无处不在。吾不知谁之子，象帝之先：道先于天帝而存在，是万事万物的本源。
 译者·韩鹏杰用第四十二章“道生一，一生二，二生三，三生万物；万物负阴而抱阳，冲气以为和”来印证：三即参，阴阳参与到一起而生万物，万事万物都同时具有阴阳两面，无论怎么转都像太极图一样保持和谐。了解道冲，就掌握了一种重要思维：任何事物都是两种相反力量在动态中达成的和谐，看问题、做决策都不能只偏执一方。</t>
   </si>
   <si>
+    <t>道经 | 本原之道</t>
+  </si>
+  <si>
     <t>9、42、71</t>
   </si>
   <si>
@@ -154,13 +166,16 @@
     <t>天地不仁，以万物为刍（chú）狗；圣人不仁，以百姓为刍狗。天地之间，其犹橐（tuó）籥（ yuè）乎？虚而不屈（qū），动而愈出。多言数（shuò）穷，不如守中。</t>
   </si>
   <si>
-    <t>天地无所偏爱，将万物像刍狗（草扎的狗）一样平等看待；圣人没有偏私，对百姓像刍狗一样平等看待。天地这个大空间，不就像一个大风箱吗？因其中间虚静才能鼓出风，越动鼓出的风越多。政令繁多会招致败亡，不如保持虚静才能恰如其分。</t>
+    <t>天地无所偏爱，将万物像刍狗（草扎的狗）一样平等看待；圣人没有偏私，对百姓像刍狗一样平等看待。天地这个大空间，不就像一个大风箱吗？虽然中间空虚却不匮乏，越是拉动它 鼓出的风就越多。政令繁多会招致败亡，不如保持虚静才能恰如其分。</t>
   </si>
   <si>
     <t>【圣人对百姓要一视同仁】本章讲天地对万物的平等和治理者的虚静。天地不仁，以万物为刍狗：不仁不是残忍，而是不偏爱、不干预；天地看待万物一视同仁，像草扎的祭狗，祭祀前被尊重，祭祀后被丢弃，无所爱惜。圣人不仁，以百姓为刍狗：好的领导者对百姓也应一律公平，制定规则法令，谁都不能例外；不要因为谁弱就特殊照顾，那反而是一种偏私，让被照顾者失去自立。道家讲的不仁是“大仁”，天地不偏私地让万物自己去奋斗、去努力。
 天地之间，其犹橐籥乎：天地像风箱，中间虚静，一拉动就能鼓出风来；政令也应如此，保持虚静、简要稳定，不能今天一变明天一变。多言数穷，不如守中：政令繁多、变动频繁会把自己逼入困境，不如恰到好处、大道至简。译者·韩鹏杰提醒，这些话都是讲给领导者听的：治理要公平无私，政令要少而稳定，靠规则而不是靠折腾。</t>
   </si>
   <si>
+    <t>道经 | 客观之道</t>
+  </si>
+  <si>
     <t>第六章（6）</t>
   </si>
   <si>
@@ -174,6 +189,9 @@
 译者·韩鹏杰强调，老子用神、玄这些最高字眼来称呼谷与牝，绝不允许亵渎；一个文化里若失去对母亲的尊重、对生命的敬畏，其他方面都会崩塌。读这一章不要陷入玄虚，要读出其中朴素而伟大的情感：尊重母亲、敬畏生命，是文化延续的根基。</t>
   </si>
   <si>
+    <t>道经 | 无限之道</t>
+  </si>
+  <si>
     <t>20、25、52</t>
   </si>
   <si>
@@ -183,13 +201,16 @@
     <t>天长地久。天地所以能长且久者，以其不自生，故能长生。是以圣人后其身而身先，外其身而身存。非以其无私邪？故能成其私。</t>
   </si>
   <si>
-    <t>天地能够长久存在。天地之所以能够长久存在，原因就在于它们不是为了自我而生存，所以能长久存在。因此有智慧的领导者总是把自己的利益放在后面，反而能够站到别人的前面；不贪身外之物，反而有利于自己的生存。不就是因为他们没有私心嘛，所以才更好地成就了他们的被人尊敬、平安无事的私心吗？！</t>
+    <t>天地能够长久存在。天地之所以能够长久存在，原因就在于它们不是为了自我而生存，所以能长久存在。因此有智慧的领导者总是把自己的利益放在后面 反而能够站到别人的前面，不贪身外之物 反而有利于自己的生存。不就是因为他们没有私心，所以才更好地成就了他们的被人尊敬、平安无事的私心吗？！</t>
   </si>
   <si>
     <t>【无私 才能天长地久】本章与第八、九章共同讲进退、争让、强弱：人们习惯强调争、进、强，老子偏要讲被忽略的不争、退、弱，因为它们与争、进、强是阴阳的两个方面，具有同等力量。天长地久：天地之所以长久，是因为天地不自私，不以自己的生存为唯一目的，而是为万物提供阳光雨露土壤，任万物自由生长，因此赢得人们长久的敬畏。后其身而身先，外其身而身存：圣人把自身利益放在后面，反而被众人推举到前面；把自身安危置之度外，反而安然长存。非以其无私邪，故能成其私：正因无私，才更好地成就了自己的长久与被人敬仰，这是人人都有的潜意识私心。
 本章是典型的“天道人道”两段论：先讲天道，再讲人道，人道效法天道。译者·韩鹏杰用“公仪休不受鱼”的故事说明：懂得从长远看问题、不贪眼前不该得的利益，才能长久地满足自己的愿望；只盯着私利的人，最后连私利也保不住。</t>
   </si>
   <si>
+    <t>道经 | 长久之道</t>
+  </si>
+  <si>
     <t>66、81</t>
   </si>
   <si>
@@ -199,13 +220,16 @@
     <t>上善若水。水善利万物而不争，处众人之所恶（wù），故几于道，居善地；心善渊；与善仁；言善信；正善治；事善能；动善时。夫唯不争，故无尤。</t>
   </si>
   <si>
-    <t>最高的智慧和品德就像水一样。水善于利万物而不争，水处于众人最不愿去的低洼地方，这是它最接近道的品性，它处于的是行善之地；人心也要像深水一样静水流深、要宁静致远、要善于沉淀；与人相处时、给人东西时、对人有恩德时要像水一样平等仁爱 要“生而不有，为而不恃，长而不宰”；说话也要像潮水一样“潮信” 讲信用、要言善信；政治清明像水一样公平公正清廉 要政善治 政清如水 为人做事要像水一样有多种多样的本事却又做事专一 奔流向海；处事智慧也像水一样 懂得寻找时机 该动则动 该静则静 该隐则隐 该绕行则绕行。所以像水一样有善利不争的品性，也就没有忧愁烦恼。</t>
+    <t>最高的智慧和品德就像水一样。水善于滋润万物生长而不与万物竞争，水总是居住在众人最不愿去的低洼之处，这是它最接近道的品性了，它处于的是行善之地；人心也要像深水一样静水流深、要宁静致远、要善于沉淀；与人相处时、给人东西时、对人有恩德时要像水一样平等仁爱 要“生而不有，为而不恃，长而不宰”；说话也要像潮水一样“潮信” 讲信用；政治清明像水一样公平公正清廉 要政善治 政清如水 为人做事要像水一样有多种多样的本事却又做事专一 奔流向海；处事智慧也像水一样 懂得寻找时机 该动则动 该静则静 该隐则隐 该绕行则绕行 择时而动。所有这一切的根本原则是不与之争，（正因为没有竞争）所以才不会有失败的危险。（或者招来怨恨，也就没有忧愁烦恼）</t>
   </si>
   <si>
     <t>【最高的品德——水】本章“上善若水”是《道德经》最著名的命题，也是中华民族精神的重要代表。上善若水，水善利万物而不争：最高的智慧与品德像水一样，滋润万物、成就他人而不争功，甘处众人不愿去的低处，所以最接近道。老子借水讲了善下、善渊、善仁、善信、善治、善能、善时等品质：居善地，甘居下位；心善渊，静水深流、宁静致远；与善仁，平等仁爱地给予；言善信，说话像潮信一样讲信用；政善治，政治清正公平如水；事善能，有多种本事又专一向前；动善时，该动则动、该静则静、该绕行则绕行。
 水的“不争”有丰富含义：有边界不争（湖有湖畔、河有河堤、海有海岸），有秩序不争（前后相随、循序渐进），有牺牲不争（成就万物而默默无闻）。夫唯不争，故无尤：不争就不会招来怨恨和过错。译者·韩鹏杰指出，老子不是趴在河边悟道，而是借水的形象传达从战争、政治、人生中领悟的智慧：善于成就别人，同时也成就自己，这正是双赢。</t>
   </si>
   <si>
+    <t>道经 | 不争之道</t>
+  </si>
+  <si>
     <t>63、69、78</t>
   </si>
   <si>
@@ -215,13 +239,16 @@
     <t>持而盈之，不如其已（yǐ）。揣（zhuī）而锐之，不可长保。金玉满堂，莫之能守。富贵而骄，自遗其咎。功遂身退，天之道也。</t>
   </si>
   <si>
-    <t>如果做事一定要做到盈满，还不如停止不做。刀刃捶锻得尖锐锋利，其锋刃就不能长期保持锋利。家中充满财富和珍宝，没有人能够守住。炫富炫贵骄狂放纵，会给自己留下无尽祸殃。功成而懂得不居功自傲的道理，才真正符合天道天理。</t>
+    <t>如果做事一定要做到盈满，还不如停止不做。刀刃捶锻得尖锐锋利，其锋刃就无法长期保持锋利。家中充满财富和珍宝，没有人能够守住。炫富炫贵骄狂放纵，会给自己留下无尽祸殃。所以功成而懂得不居功自傲、急流勇退的道理，才真正符合自然之道。</t>
   </si>
   <si>
     <t>【凡事勿求满 适可而止】本章讲“不盈”：凡事勿求满，适可而止。持而盈之，不如其已：端着一盘盛满的水走路，战战兢兢还不断洒出，不如少装一点，走得更轻松。揣而锐之，不可长保：把锥子磨得极锋利，一碰就断；削铅笔削到只剩笔头，再尖也保不住。金玉满堂，莫之能守：家中满是财富珍宝，反而守不住。富贵而骄，自遗其咎：因富贵而骄傲自满，是自取灾难。功遂身退，天之道也：功成而不居功、懂得退让，才符合天道。
 译者·韩鹏杰用民间故事讲这个道理：弟弟只拿一点金子平安回家，哥哥贪心装满全身，被太阳晒化。第七章讲先后，第八章讲不争，第九章讲不盈，都提醒人知进退、懂谦让。中国文化的“中”就是恰到好处，不走到极端：物极必反、乐极生悲、泰极否来，好事到了极端容易向坏处转化，所以要战战兢兢、如履薄冰地把握分寸。</t>
   </si>
   <si>
+    <t>道经 | 人生之道</t>
+  </si>
+  <si>
     <t>2、4、78</t>
   </si>
   <si>
@@ -231,13 +258,16 @@
     <t>载（zài）营魄抱一，能无离乎？专气致柔，能如婴儿乎？涤除玄览，能无疵（cī）乎？爱民治国，能无为乎？天门开阖，能为雌乎？明白四达，能无知乎？生之畜（xù）之，生而不有，为而不恃，长（zhǎng）而不宰，是谓玄德。</t>
   </si>
   <si>
-    <t>身体像车一样载着魂魄，它们能不能不要分离？聚结精气以致柔和温顺，能不能像婴儿那样的纯粹呢？像玄镜照心一样清除杂念而深入观察心灵，能不能让心灵没有瑕疵呢？爱民治国能不能遵行自然无为的规律呢？感官与外界的对立变化相接触，能不能守住雌柔宁静呢？明白四达，能不能不用心机诈术呢？万物生长繁殖，产生万物、养育万物而不占为己有，作万物之长而不主宰它们，这就叫做“玄德”（高尚的品德）。</t>
+    <t>身体像车一样载着魂魄，它们能融合一体永不分离吗？聚结精气以致柔和温顺，能不能像婴儿那样的纯粹呢？像玄镜照心一样清除杂念而深入观察心灵，能不能让心灵没有瑕疵呢？治理国家关爱百姓，能不能遵行自然无为的规律呢？感官（身体）与外界（诱惑）的对立变化相接触，能不能守住内心宁静而不轻举妄动呢？大彻大悟明察秋毫，能不能不用心机诈术呢？天地创造万物养育万物，生养了万物（为它们提供繁衍生息的环境）而不占为己有，有所施为却不认为是自己的功劳，助万物成长而不主宰支配它们，这就叫做“玄德”（高尚的品德）。</t>
   </si>
   <si>
     <t>【心里放空 保持虚静】本章与十一、十二章共讲“虚静”：心里放空才能宁静，宁静才能看清事物本质，抵抗外在诱惑。载营魄抱一，能无离乎：身体像车载着魂魄，灵魂与肉体能否合一不分离？不要做丢了灵魂的行尸走肉。专气致柔，能如婴儿乎：聚结精气、身心柔软，能否像婴儿一样纯粹？涤除玄览，能无疵乎：清除内心杂念，能否像明镜一样无瑕疵？爱民治国，能无为乎：治理能否顺其自然、不妄为？天门开阖，能为雌乎：面对外界纷扰，能否守住柔静？明白四达，能无知乎：通达事理之后，能否不用机巧套路？
 一连串反问都在讲修养路径：魂魄不离、身心合一、少欲守静、厚道不用智巧。最后点出玄德：生之畜之，生而不有，为而不恃，长而不宰——生养万物而不占有、不倚仗、不主宰，这是最高深的德。译者·韩鹏杰认为这一章是后面九章的总纲，虚静既是个人修养，也是治国的基础。</t>
   </si>
   <si>
+    <t>道经 | 方法之道</t>
+  </si>
+  <si>
     <t>42、57、71、75</t>
   </si>
   <si>
@@ -247,13 +277,16 @@
     <t>三十辐（fú）共一毂（gǔ），当其无，有车之用。埏（shān）埴（zhí）以为器，当其无，有器之用。凿户牖（yǒu）以为室，当其无，有室之用。故有之以为利，无之以为用。</t>
   </si>
   <si>
-    <t>三十根辐条集中在一个车毂（轴承）上，正是因为有了车轴中的空间，才有了车子的作用。用水和黏土制造各种陶器，正是因为有了陶器里的空间，才有了陶器的作用。开凿门窗修建房屋，正是因为有了房屋中的空间，才有了房屋的作用。所以说各种器物的物质部分（实有部分）给人带来了利益，而器物里的空间（空虚部分）才使这些器物能够发挥自己的作用。</t>
+    <t>三十根辐条集中在一个车毂（轴承）上，正是因为有了车轴中的空间，车轮才能发挥作用。用水和黏土制造各种陶器，正是因为有了陶器里的空间，才有了陶器（器皿）的作用。开凿门窗修建房屋，正是因为有了房屋中的空间，才有了房屋的作用。所以说物质部分（实有部分）给人带来了利益/便利，而空间部分（空虚部分）才发挥了它的作用。</t>
   </si>
   <si>
     <t>【从有中看到无的作用】本章讲“无”的作用，用三个日常形象说明虚空的巨大价值。三十辐共一毂，当其无，有车之用：车轮有三十根辐条，车毂中间是空的，车轮才能转动，才有车的功用。埏埴以为器，当其无，有器之用：黏土烧成器皿，中间是空的，才能盛水装物。凿户牖以为室，当其无，有室之用：开凿门窗建成房屋，中间是空的，人才能居住。有之以为利，无之以为用：实体提供便利条件，虚空成就实际功用，有与无相互成全。
 译者·韩鹏杰指出，“利用”这个词就来自本章。第十章讲虚静，本章讲怎样虚静——心里放空，去掉杂念，才能听得进别人的意见、看得见别人的长处、学得到别人的优点，虚怀若谷、满招损谦受益。中国文化的悟道方式是“给一个形象，自己领悟”，本章就是最好的示范：通过车、器、室三个形象，让人领悟空与用的道理。</t>
   </si>
   <si>
+    <t>道经 | 察无之道</t>
+  </si>
+  <si>
     <t>2、66</t>
   </si>
   <si>
@@ -263,14 +296,18 @@
     <t>五色令人目盲；五音令人耳聋；五味令人口爽；驰骋畋（tián）猎，令人心发狂；难得之货，令人行妨。是以圣人为腹不为目，故去彼取此。</t>
   </si>
   <si>
-    <t>艳丽的色彩看多了会让人眼花缭乱；嘈杂的声音会让人听觉失灵；过于丰盛的食物吃多了会让人味觉错乱；沉溺于驰马打猎，会让人心神狂乱；珍贵的金银财宝，会让人行为不轨。因此圣人只求吃饱肚子而不求感官享受，摒弃感官享受（过度的欲望）而选择简单朴素安定知足的生活方式。</t>
+    <t>艳丽的色彩看多了会让人眼花缭乱；美妙的音乐听多了会伤害人的
+听力；过于丰盛的食物吃多了会让人味觉错乱；沉溺于驰马打猎，会让人心神狂乱；珍贵的金银财宝，会让人行为不轨。因此圣人只求吃饱肚子而不求感官享受，摒弃感官享受（过度的欲望）而选择简单朴素安定知足的生活方式。</t>
   </si>
   <si>
     <t>【心里放空 保持虚静】本章讲外在诱惑对心灵的扰乱，以及如何以内心的虚静守住根本。五色令人目盲：颜色太多太杂，反而区分不出好坏，视觉被迷乱；五音令人耳聋：高音快节奏听多了，好音乐也分辨不出来；五味令人口爽：厚食重味吃多了，味觉被破坏（爽是错乱）；驰骋畋猎令人心发狂：声色犬马让人心静不下来；难得之货令人行妨：被炒作的珍奇之物让人行为失当。老子并不要求消灭这些享受，而是说要以内心的虚静合理把握，适可而止。
 是以圣人为腹不为目，故去彼取此：圣人重实质内容，不重外在浮华；取舍的标准是看什么最重要——健康、营养、真实比外表颜色更重要。译者·韩鹏杰把本章与第十章、十一章连起来读：虚静的心才能看清本质，处其厚不居其薄，掌握生命中真正重要的东西，返璞归真。</t>
   </si>
   <si>
-    <t>10、11</t>
+    <t>道经 | 修心之道</t>
+  </si>
+  <si>
+    <t>10、11、35</t>
   </si>
   <si>
     <t>第十三章（13）</t>
@@ -279,55 +316,67 @@
     <t>宠辱若惊，贵大患若身。何谓宠辱若惊？宠为下，得之若惊，失之若惊，是谓宠辱若惊。何谓贵大患若身？吾所以有大患者，为吾有身，及吾无身，吾有何患！故贵以身为天下，若可寄天下；爱以身为天下，若可托天下。</t>
   </si>
   <si>
-    <t>受到宠爱和受到侮辱都好像受到惊恐，这是把荣辱这样的大患看得与自身生命一样珍贵。那么为什么得宠和受辱都感到惊慌失措呢？受宠者是卑下的，得到宠爱又怕失去所以会感觉惊恐，失去宠爱则更令人惊慌不安，这就叫做得宠和受辱都感到惊恐。什么叫做重视大患像重视自身生命一样？我之所以有大患，是因为我有身体；如果我没有身体，我还会有什么祸患呢？所以，珍贵、爱惜自己的身体，用自己全部身心去治理天下的人，才可以把天下交给他；只有那些愿意以自己全部身心去治理天下的人，才可以把天下托付给他。</t>
+    <t>受到宠爱和受到侮辱都好像受到惊恐，这是把荣辱这样的大患看得与自身生命一样珍贵。那么为什么得宠和受辱都感到惊慌失措呢？受宠者是卑下的，得到宠爱又怕失去所以会感觉惊恐，失去宠爱则更令人惊慌不安，这就叫做得宠和受辱都感到惊恐。什么叫做重视大患（灾祸）像重视自身生命一样？我之所以有大患，是因为我有身体（珍爱自己的生命）；如果我没有身体（不珍爱自己的生命），我还会有什么祸患呢？所以，珍贵、爱惜自己的身体，用自己全部身心去治理天下的人，才可以把天下交给他；只有那些愿意以自己全部身心去治理天下的人，才可以把天下托付给他。</t>
   </si>
   <si>
     <t>【看待得失 珍视生命】本章讲宠辱与生命，核心是如何看待得失、珍视生命，什么样的人才可托付天下。宠辱若惊：得到宠幸和失去宠幸都会惊恐。为什么？宠为下：被宠的人在下面，宠我们的人在上面，所以得之若惊（怕失去），失之若惊（更恐惧），这叫宠辱若惊。能做到宠辱不惊、淡然处之，是难得的人生境界。贵大患若身：有身体就有祸患，身体代表利益，也带来疾病与麻烦；但身体是摆脱不掉的，所以更要珍视它。
 吾所以有大患者，为吾有身，及吾无身，吾有何患——不把身体和生命当回事的人，坐到重要位置上是很可怕的；声色犬马、厚食重味正是戕害生命。贵以身为天下，若可寄天下；爱以身为天下，若可托天下：真正把自身生命看得与天下一样贵重、肯为天下担当牺牲的人，才值得把天下托付给他。译者·韩鹏杰区分两种勇敢：无赖式的勇敢不把命当回事，有责任的勇敢珍视生命又肯担当，后者才值得托付。</t>
   </si>
   <si>
+    <t>道经 | 超脱之道</t>
+  </si>
+  <si>
     <t>第十四章（14）</t>
   </si>
   <si>
-    <t>视之不见名曰夷（yí），听之不闻名曰希，搏之不得名曰微。此三者不可致诘（jié），故混而为一。其上不皦（jiǎo），其下不昧，绳（mǐn）绳（mǐn）不可名，复归于无物。是谓无状之状，无物之象，是谓惚恍。迎之不见其首，随之不见其后。执古之道，以御今之有。能知古始，是谓道纪。</t>
-  </si>
-  <si>
-    <t>察看大道又看不见，这叫作无形；聆听大道又听不到，这叫作无声；触摸大道又摸不着，这叫作无体。这三种特性都是无法进一步追究考察的，它们混合于一体。大道的上面不会显得明亮，它的下面也不会显得昏暗，它无形无象难以描述，可以说它不是一个物质性的实体。可以说大道是没有形状的形状，没有形体的形象，它可以说是迷离恍惚、无法捉摸的。站在它前面却看不见它的头部，尾随着它也看不见它的尾部。掌握了自古以来就存在的大道，就能够凭借它来驾驭、支配现在的万物，就能够了解远古时代的情况。以上所讲的就是关于大道的大致情况。</t>
+    <t>视之不见名曰夷（yí），听之不闻名曰希，搏之不得名曰微。此三者不可致诘（jié），故混而为一。其上不皦（jiǎo），其下不昧，绳（mǐn）绳（mǐn）不可名，复归于无物。是谓无状之状，无物之象，是谓惚恍。迎之不见其首，随之不见其后。执古之道，以御今之有，能知古始，是谓道纪。</t>
+  </si>
+  <si>
+    <t>察看大道又看不见 这叫作无形；聆听大道又听不到 这叫作无声；触摸大道又摸不着 这叫作无体。这三种特性都是无法进一步追究考察的，因为它们混合于一体。大道的上面不会显得明亮，它的下面也不会显得昏暗，它无形无象难以描述，可以说它不是一个物质性的实体。可以说大道是没有形状的形状，没有形体的形象，它可以说是迷离恍惚、无法捉摸的。站在它前面却看不见它的头部，尾随着它也看不见它的尾部。掌握了自古以来就存在的大道，就能够凭借它来驾驭、支配现在的万物，就能够了解远古时代的情况（了解宇宙的初始），以上所讲的就是关于大道的大致情况。</t>
   </si>
   <si>
     <t>【大象无形】本章形容道大象无形却无处不在，并指出知古通今的方法。视之不见名曰夷，听之不闻名曰希，搏之不得名曰微：道太细微，看不见、听不到、摸不着，三个词都说明道不可用感官把握。此三者不可致诘，故混而为一：不能用语言追问道在哪里，它混然一体。其上不皦，其下不昧，绳绳不可名：道不明不暗、不上不下，绵延存在却无法命名。无状之状，无物之象，是谓惚恍：道没有具体形状和物象，似有若无。迎之不见其首，随之不见其后：寻不到它的首尾。
 执古之道，以御今之有：了解古往今来的大道，才能把握今天、做好今天的事；能知古始，是谓道纪：知道万物开始的道理，就是把握了道的纲领。译者·韩鹏杰用庄子的“道在瓦片、稗草、大小便中”来说明道无在无不在，越往下越有；用风的形象说明道无形却左右万物。学习本章要记住：道看不见摸不着，但真实存在、无处不在，了解它才能做好今天的事。</t>
   </si>
   <si>
+    <t>道经 | 视虚之道</t>
+  </si>
+  <si>
     <t>1、21</t>
   </si>
   <si>
     <t>第十五章（15）</t>
   </si>
   <si>
-    <t>古之善为士者，微妙玄通，深不可识。夫唯不可识，故强为之容。豫焉若冬涉川，犹兮若畏四邻，俨（yǎn）兮其若客，涣兮若冰之将释，敦兮其若朴，旷兮其若谷，混兮其若浊。孰能浊以止？静之徐清。孰能安以久？动之徐生。保此道者不欲盈，夫唯不盈，故能蔽而新成。</t>
-  </si>
-  <si>
-    <t>古代那些掌握大道的人（士：推十为一，基层的、领导大家做事的这类人），其思想微妙通达，深刻得难以理解。正因为他们难以被理解，所以要勉强对他们的言行加以描述。他们做事反复考虑，就好像寒冬要徒步过河一样；谨慎小心，就好像畏惧四邻的围攻一般；恭敬庄重，就好像一位做客的人；通达而不固执，就好像将要融化的冰块；朴实敦厚，就好像未经雕饰的原木；胸怀空阔宽广，就好像那深山的幽谷；能够包容一切，就好像那混浊的大水。谁能够持久地像混浊的大水那样去包容一切呢？世人总是要让浊水安静下来，慢慢加以澄清；但是谁又能够永远坚持这种安定清静的状态呢？顺势而动，万物便能徐徐生发（生命在于运动）。掌握大道的人，办事不求盈满。正因为不求盈满，所以能去旧存新、不断新生。</t>
+    <t>古之善为士者，微妙玄通，深不可识。夫唯不可识，故强为之容：豫焉若冬涉川，犹兮若畏四邻，俨（yǎn）兮其若客，涣兮若冰之将释，敦兮其若朴，旷兮其若谷，混兮其若浊。孰能浊以止？静之徐清。孰能安以久？动之徐生。保此道者不欲盈，夫唯不盈，故能蔽而新成。</t>
+  </si>
+  <si>
+    <t>古代那些掌握大道的人（士：推十为一，基层的、领导大家做事的这类人），其思想微妙通达，深刻得难以理解。正因为他们难以被理解，所以我只能勉强对他们的言行加以描述：他们做事反复考虑 就好像寒冬要徒步过河一样；谨慎小心 就好像畏惧四邻的围攻一般；恭敬庄重 就好像一位做客的人；通达而不固执 就好像将要融化的冰块；朴实敦厚 就好像未经雕饰的原木；胸怀空阔宽广 就好像那深山的幽谷；能够包容一切 就好像那混浊的水。谁能够持久地像混浊的水那样去包容一切呢？世人总是要让浊水安静下来 慢慢加以澄清，但是谁又能够永远坚持这种安定清静的状态呢？顺势而动 万物便能徐徐生发（生命在于运动）。掌握大道的人，办事不求盈满，正因为不求盈满，所以能去旧存新、不断新生。</t>
   </si>
   <si>
     <t>【基层领导要具备的素质】本章讲基层领导者“士”应有的修养。古之善为士者，微妙玄通，深不可识：善于做士的人，智慧微妙、通达深远，难以被了解，所以要强为之容（勉强形容）。豫兮若冬涉川：像冬天过河一样谨慎，一步一探；犹兮若畏四邻：像敬畏四邻一样不敢妄动；俨兮其若客：庄重像做客；涣兮若冰之将释：温和像冰雪消融；敦兮其若朴：敦厚像未经雕琢的木头；旷兮其若谷：胸怀开阔像山谷；混兮其若浊：包容混同像浊水。
 孰能浊以静之徐清？孰能安以久动之徐生：浊水静下来才能慢慢澄清，安定的状态动起来才能慢慢焕发生机，这是“静中求清、动中求生”的修养。保此道者不欲盈，夫唯不盈，故能蔽而新成：守道者不求满，留出空间，舍弃旧的东西才能革故鼎新。译者·韩鹏杰强调，书中的话多针对具体的人讲，本章针对带领十几人做事的小组长等“士”阶层，说明基层领导者也需要很高的素质：谨慎、敬畏、质朴、虚怀、不盈。</t>
   </si>
   <si>
+    <t>道经 | 思维之道</t>
+  </si>
+  <si>
     <t>第十六章（16）</t>
   </si>
   <si>
     <t>致虚极，守静笃，万物并作，吾以观复。夫物芸芸，各复归其根。归根曰静，是谓复命。复命曰常，知常曰明。不知常，妄作凶。知常容，容乃公，公乃王（wàng），王乃天，天乃道，道乃久。没（mò）身不殆。</t>
   </si>
   <si>
-    <t>尽力使心灵的谦虚达到极点，使生活清静坚守不变。万物都一齐蓬勃生长，有道之人在纷繁中考察其往复的道理。万事万物纷纷芸芸，各自返回它的本根。返回到它的本根就是清静，清静就能使生命复归而再次续命；复命续命就是自然，认识了自然规律就叫做明智，不认识自然规律的轻妄举止，往往会出乱子和灾凶。认识自然规律的人是宽容的，宽容才会坦然公正，公正才能内圣外王，内圣外王才能符合自然的“道”，符合自然的道才能长久，终身不会遭到危险。</t>
+    <t>尽力使心灵的谦虚达到极点，使生活清静坚守不变，万物都一齐蓬勃生长，有道之人在纷繁中考察其往复的道理。万事万物纷纷芸芸，各自返回它的本根。返回到它的本根就是清静，清静就能使生命复归而再次续命。复命续命就是自然，认识了自然规律就叫做明智。不认识自然规律的轻妄举止，往往会出乱子和灾凶。认识自然规律的人是宽容的，宽容才会坦然公正，公正才能内圣外王，内圣外王才能符合自然的“道”，符合自然的道才能长久，终身不会遭到危险。</t>
   </si>
   <si>
     <t>【基层领导要具备的素质】本章承第十五章，进一步讲虚静观复、知常守根。致虚极，守静笃：把心放到极度虚空、极度宁静的状态，不是枯木死灰，而是心灵安稳、不受杂念干扰。万物并作，吾以观复：万物纷繁生长，观察它的根本规律就是一个“复”字，反复循环、复归本根。夫物芸芸，各复归其根：万物虽然纷纭，最终都要回归自己的根本。归根曰静，静曰复命，复命曰常：归根就是静，静就是复归本性，复归本性就是恒常之道。
 知常容，容乃公，公乃王，王乃天，天乃道，道乃久，没身不殆：懂得恒常之道就能包容，包容就公正，公正就周全，周全就合天，合天就合道，合道就长久，终身不会遇到危险。译者·韩鹏杰说，从草的枯荣到人的生死，都体现“复”的规律；观察规律是为了认识自己、掌控自己：知道哪些因素会带来负面状态，就主动避免；知道哪些条件带来积极状态，就主动创造，让好的状态恢复。</t>
   </si>
   <si>
+    <t>道经 | 观察之道</t>
+  </si>
+  <si>
     <t>第十七章（17）</t>
   </si>
   <si>
@@ -341,6 +390,9 @@
 译者·韩鹏杰用“太上”的拆字讲：大上加一点才是太，点放下才成太，放到上面就成犬，寓意善于处下才能真正居上，太太、处长等词都蕴含此理。最好的教育和管理也是如此：不越俎代庖，让孩子、下属自己把事情做成，他们才有自信和成长，功成事遂皆谓我自然。</t>
   </si>
   <si>
+    <t>道经 | 管理之道</t>
+  </si>
+  <si>
     <t>第十八章（18）</t>
   </si>
   <si>
@@ -354,6 +406,9 @@
 一个社会天天提倡道德，正说明道德已经滑坡；什么时候妇女节、教师节不再成为问题，才说明相关地位真正提高了。这不是否定仁义孝慈，而是提醒人们不要靠表面提倡来补救，要从根本上回到道。把第十八、十九章连起来读：与其用仁义、智巧等外在名目补救，不如回归素朴本心，做个好人、存点好心、行些好事。</t>
   </si>
   <si>
+    <t>道经</t>
+  </si>
+  <si>
     <t>19、（18/19章可融合为一章）</t>
   </si>
   <si>
@@ -492,21 +547,20 @@
     <t>知道什么是刚健，却要安于柔顺的地位，甘愿做天下的沟谿（溪谷）。甘愿做天下的沟谿（溪谷），高尚的品德就永远不会丧失，就能恢复到婴儿的纯真状态。知道什么是显赫地位，却要安于低下的地位，做天下人的榜样。做天下人的榜样，高尚的品德就永远不会出差错，就能具有无穷的力量。知道什么是荣耀，却要安于屈辱的地位，甘愿做天下的虚谷。甘愿做天下的虚谷，高尚品德就会永远保持圆满，就能够同大道保持一致。大道会分散显现为万物各自的本性，圣人就顺应着万物各自的本性去进行管理，所以说最完美的治理是不去伤害万物的本性。</t>
   </si>
   <si>
-    <t>本章是“抱一为天下式”的例证，讲刚柔、黑白、荣辱的辩证统一。知其雄，守其雌，为天下谿：知道自己强大，却不恃强，安守柔雌，甘做天下的溪谷，水都汇到低处来，反而源远流长，复归于婴儿：回归婴儿般纯真柔软。知其白，守其黑，为天下式：知道明亮，却安守暗黑，做天下范式，常德不忒，复归于无极：德行不出差错，回归无穷的境界。知其荣，守其辱，为天下谷：知道荣耀，却安守屈辱，甘做天下的虚谷，常德乃足，复归于朴：德行充足，回归素朴。
+    <t>【在两个方面看待事物】本章是“抱一为天下式”的例证，讲刚柔、黑白、荣辱的辩证统一。知其雄，守其雌，为天下谿：知道自己强大，却不恃强，安守柔雌，甘做天下的溪谷，水都汇到低处来，反而源远流长，复归于婴儿：回归婴儿般纯真柔软。知其白，守其黑，为天下式：知道明亮，却安守暗黑，做天下范式，常德不忒，复归于无极：德行不出差错，回归无穷的境界。知其荣，守其辱，为天下谷：知道荣耀，却安守屈辱，甘做天下的虚谷，常德乃足，复归于朴：德行充足，回归素朴。
 朴散则为器，圣人用之则为官长，故大制不割：素朴分散为万物之器，圣人顺应本性管理，最好的制度不伤害本性。译者·韩鹏杰强调，守雌、守黑、守辱不是没有经历过强、白、荣就假装谦卑，而是先有实力和成就，再有资格谈守，比如书法先经历精巧，才能返璞归真。记住十八个字：知其雄守其雌，知其白守其黑，知其荣守其辱，就是这一章的核心智慧。</t>
   </si>
   <si>
     <t>第二十九章（29）</t>
   </si>
   <si>
-    <t>将欲取天下而为之，吾见其不得已。天下神器，不可为也，不可执也。为者败之，执者失之。是以圣人无为，故无败；无执，故无失。故物或行或随；或歔（xū）或吹；或强或羸（léi）；或载（zài）或隳（huī）。
-是以圣人去甚，去奢，去泰。</t>
-  </si>
-  <si>
-    <t>君主想要治理好天下却又按照个人意志去采取行动，我将会看到他达不到自己的目的（断定必然会失败）。天下这个神圣的器物，是不可以按照个人意志强行干预，强行把持。随心所欲地去治理天下的君主，一定会搞乱天下。想把天下据为己有的君主，一定会失去天下。因此圣人顺应自然 不妄为，故无失败；不强行把持，故无损失。（所以事情往往如此）本意也许是想走在前面 结果可能反而落在后面；本意也许是想轻轻哈气为物取暖 结果可能因为吹气太快而使物变凉；本意也许是想强壮 结果可能反而变得瘦弱；本意也许是想稍微减损一点儿 结果可能是全部毁掉了。因此圣人要去掉那些极端的，奢侈的，过分的言行和欲望。</t>
-  </si>
-  <si>
-    <t>本章讲天下不可强为、强取。将欲取天下而为之，吾见其不得已：想用强力、武力夺取天下并按个人意志治理，注定达不到目的。天下神器，不可为也，不可执也：天下是神圣之物，不可强行干预，不可强行把持；为者败之，执者失之：强行去做的必失败，死死抓住的必失去。是以圣人无为，故无败；无执，故无失：圣人顺其自然、不妄为，所以不会失败；不强行把持，所以不会失去。
+    <t>将欲取天下而为之，吾见其不得已。天下神器，不可为也，不可执也。为者败之，执者失之。是以圣人无为，故无败；无执，故无失。故物或行或随；或歔（xū）或吹；或强或羸（léi）；或载（zài）或隳（huī）。是以圣人去甚，去奢，去泰。</t>
+  </si>
+  <si>
+    <t>君主想要治理好天下却又按照个人意志去采取行动，我将会看到他达不到自己的目的（断定必然会失败）。天下这个神圣的器物，是不可以按照个人意志强行干预，不可以强行把持。随心所欲地去治理天下的君主 一定会搞乱天下。想把天下据为己有的君主 一定会失去天下。因此圣人顺应自然 不妄为，故无失败；不强行把持，故无损失。（所以事情往往如此）本意也许是想走在前面 结果可能反而落在后面；本意也许是想轻轻哈气为物取暖 结果可能因为吹气太快而使物变凉；本意也许是想强壮 结果可能反而变得瘦弱；本意也许是想稍微减损一点儿 结果可能是全部毁掉了。因此圣人要去掉那些极端的，奢侈的，过分的言行和欲望。</t>
+  </si>
+  <si>
+    <t>【事不可强为 天下不可强取】本章讲天下不可强为、强取。将欲取天下而为之，吾见其不得已：想用强力、武力夺取天下并按个人意志治理，注定达不到目的。天下神器，不可为也，不可执也：天下是神圣之物，不可强行干预，不可强行把持；为者败之，执者失之：强行去做的必失败，死死抓住的必失去。是以圣人无为，故无败；无执，故无失：圣人顺其自然、不妄为，所以不会失败；不强行把持，所以不会失去。
 故物或行或随，或嘘或吹，或强或羸，或载或隳：万物本性各不相同，有前行有跟随，有轻嘘有急吹，有强壮有羸弱，有安稳有毁坏，不能用一个标准、一种方式强求。是以圣人去甚，去奢，去泰：圣人去掉极端的、奢侈的、过分的言行和欲望。译者·韩鹏杰指出，这一章要结合时代背景理解：春秋末期诸侯争霸、生灵涂炭，老子提出小国寡民设想，反对强为；读这一章要体会其中的沉痛感，任何事有生必有灭、有成必有败，强求和把持都违背天道。</t>
   </si>
   <si>
@@ -516,10 +570,10 @@
     <t>以道佐人主者，不以兵强天下。其事好还（huán）。师之所处，荆棘生焉。大军之后，必有凶年。善有果而已，不敢以取强。果而勿矜，果而勿伐，果而勿骄。果而不得已，果而勿强。物壮则老，是谓不道，不道早已。</t>
   </si>
   <si>
-    <t>遵循大道去辅佐君主的人，是不会凭借武力去逞强于天下的。用兵打仗的事很快就会得到报应。战争发生过的地区，荆棘丛生。大战之后，必有一个灾荒年。（真正善于用兵的人）取得胜利就罢手，不敢依仗武力称王称霸。胜利了而不自大，胜利了而不夸耀，胜利了而不骄傲。胜利之后还要感到自己是出于不得已才打的这次胜仗，胜利了而不逞强。事物强盛了就会走向衰败，求强求壮的做法是不符合大道的，不符合大道就会很快灭亡。</t>
-  </si>
-  <si>
-    <t>本章与三十一章表达中国人对战争的痛恨与对和平的热爱。以道佐人主者，不以兵强天下：用道辅佐君主的人，不靠武力逞强天下。其事好还：用兵之事很快有报应，你打人多重，反作用力就多重。师之所处，荆棘生焉：军队到过的地方，荆棘丛生、断壁残垣；大军之后，必有凶年：大战之后必有灾荒凶年。善有果而已，不敢以取强：不得已打仗，达到保卫目的就停手，不敢逞强。
+    <t>遵循大道去辅佐君主的人，是不会凭借武力去逞强于天下的。用兵打仗的事很快就会得到报应。战争发生过的地区，荆棘丛生。大战之后，必有一个灾荒年。（真正善于用兵的人）取得胜利（成果）就罢手，不敢依仗武力强暴称王称霸。胜利了而不自大，胜利了而不夸耀，胜利了而不骄傲。胜利之后还要感到自己是出于不得已才打的这次胜仗，胜利了而不逞强。事物强盛了就会走向衰败，求强求壮的做法是不符合大道的，不符合大道就会很快灭亡。</t>
+  </si>
+  <si>
+    <t>【热爱和平 痛恨战争】本章与三十一章表达中国人对战争的痛恨与对和平的热爱。以道佐人主者，不以兵强天下：用道辅佐君主的人，不靠武力逞强天下。其事好还：用兵之事很快有报应，你打人多重，反作用力就多重。师之所处，荆棘生焉：军队到过的地方，荆棘丛生、断壁残垣；大军之后，必有凶年：大战之后必有灾荒凶年。善有果而已，不敢以取强：不得已打仗，达到保卫目的就停手，不敢逞强。
 果而勿矜，果而勿伐，果而勿骄：胜利了不自大、不夸耀、不骄傲；果而不得已，果而勿强：胜利是出于不得已，胜了也不逞强。物壮则老，是谓不道，不道早已：事物强盛到极点就走向衰败，逞强求壮不合道，不合道就很快灭亡。译者·韩鹏杰说，这章最后三句话值得牢记：师之所处荆棘生焉，大军之后必有凶年，物壮则老。战争不可轻易发动，对待战争的态度就是对待同胞生命的态度；中华民族热爱和平，不惹事也不怕事。</t>
   </si>
   <si>
@@ -532,7 +586,7 @@
     <t>战争，是一种不吉祥的东西，人们大概都很讨厌它，所以掌握大道的人不去使用它。君子平时以左边为高贵，作战时却以右边为高贵。战争是不吉祥的东西，不是君子应该使用的，迫不得已时才使用它，最好漠然处之。即使战胜了也不应该赞美胜利，如果赞美战争的胜利，这就是以杀人为快乐。以杀人为快乐的人，不可能实现统一天下的志向。吉庆之事以左边为高贵，凶丧之事以右边为高贵。打仗时副将居于左边，主将居于右边，这是说要用办理丧事的礼节去处理战争的事情。战争杀人众多，要带着悲哀的心情参与战争，战胜了也要用办理丧事的礼节去处理它。</t>
   </si>
   <si>
-    <t>本章继续讲对待战争的态度，主张以丧礼对待战争。夫兵者，不祥之器：兵器是不祥之物，人们都厌恶它，所以有道的人不使用它。君子居则贵左，用兵则贵右：平时以左为尊，作战时以右为尊，用兵属于凶事。兵者不祥之器，非君子之器，不得已而用之，恬淡为上：战争不是君子常用的东西，万不得已才用，还要淡然处之。胜而不美，而美之者，是乐杀人：打了胜仗不应赞美庆祝，赞美胜利就是以杀人为乐；以杀人为乐的人，不可能得志于天下。
+    <t>【把战争当成对待丧礼一样】本章继续讲对待战争的态度，主张以丧礼对待战争。夫兵者，不祥之器：兵器是不祥之物，人们都厌恶它，所以有道的人不使用它。君子居则贵左，用兵则贵右：平时以左为尊，作战时以右为尊，用兵属于凶事。兵者不祥之器，非君子之器，不得已而用之，恬淡为上：战争不是君子常用的东西，万不得已才用，还要淡然处之。胜而不美，而美之者，是乐杀人：打了胜仗不应赞美庆祝，赞美胜利就是以杀人为乐；以杀人为乐的人，不可能得志于天下。
 吉事尚左，凶事尚右：吉庆之事尚左，凶丧之事尚右；偏将军居左，上将军居右，就是用办理丧事的礼节来对待战争。杀人之众，以悲哀泣之，战胜以丧礼处之：战争杀人众多，要带着悲哀的心情参与，战胜了也要用丧礼的仪式对待。译者·韩鹏杰强调，这两章应该进小学课本，让和平的种子从小种下；战争胜利后第一件事不是放肆庆祝，而是祭奠双方的死者，因为他们都是生命。</t>
   </si>
   <si>
@@ -542,13 +596,16 @@
     <t>道常无名，朴虽小，天下莫能臣也。侯王若能守之，万物将自宾。天地相合，以降甘露，民莫之令而自均。始制有名，名亦既有，夫亦将知止。知止可以不殆。譬道之在天下，犹川谷之于江海。</t>
   </si>
   <si>
-    <t>大道永远处于一种看不见、摸不着的虚无状态，它好像未加工过的原木一样（朴素而不张扬），虽然微不足道 但是天下没有人能够改变它。王侯如果能够遵循大道，万物将会自然而然地宾服于他（大家才能真正的信任他、支持他）。天之气和地之气就会相互交融，降下甘露一类的美好事物，没有人指使人们该如何做而自然均平安定。人们开始制作各种各样有名称的器物和制度，各种器物和制度出现以后，也应该知道适可而止。知道适可而止就能避免危险。打个比方 大道与天下万物的关系，就好像江海与河川的关系一样。</t>
-  </si>
-  <si>
-    <t>本章讲道的特点和知止的智慧。道常无名，朴虽小，天下莫能臣：道恒常无名，它的重要属性是朴实厚道；朴像原木，看似微小，却没有任何东西能让它臣服。侯王若能守之，万物将自宾：领导者若能守住朴实厚道，万物自然宾服归附。天地相合，以降甘露，民莫之令而自均：天地阴阳相合降下甘露，没有人命令，雨露自然均匀，治理也应如此自然而然。
+    <t>大道永远处于一种看不见、摸不着的虚无状态，它好像未加工过的原木一样（朴素而不张扬），虽然微不足道 但是天下没有人能够改变它。王侯如果能够遵循大道，万物将会自然而然地宾服于他（大家才能真正的信任他、支持他）。天之气和地之气就会相互交融，降下甘露一类的美好事物，没有人指使人们该如何做而自然均平安定。人们开始制作各种各样有名称的器物和制度，各种器物和制度出现以后，也应该知道适可而止。知道适可而止（知道边界）就能避免危险。打个比方 大道与天下万物的关系，就好像江海与河川的关系一样。</t>
+  </si>
+  <si>
+    <t>【道——朴实厚道】本章讲道的特点和知止的智慧。道常无名，朴虽小，天下莫能臣：道恒常无名，它的重要属性是朴实厚道；朴像原木，看似微小，却没有任何东西能让它臣服。侯王若能守之，万物将自宾：领导者若能守住朴实厚道，万物自然宾服归附。天地相合，以降甘露，民莫之令而自均：天地阴阳相合降下甘露，没有人命令，雨露自然均匀，治理也应如此自然而然。
 始制有名，名亦既有，夫亦将知止，知止可以不殆：人类社会开始有制度、名分是合理的，但有了名分制度要懂得边界，不能制度崇拜、名分崇拜，做过了头就走向反面；知道适可而止，才能避免危险。譬道之在天下，犹川谷之于江海：道在天下，就像川谷流向江海，是自然归附的过程，不是强迫。译者·韩鹏杰强调，老子反复用重复和强调来突出重要思想，本章的核心就是朴与知止：做事朴实厚道，对制度名分保持克制，知道边界和限度，物极必反，知止不殆。</t>
   </si>
   <si>
+    <t>3、1</t>
+  </si>
+  <si>
     <t>第三十三章（33）</t>
   </si>
   <si>
@@ -558,7 +615,7 @@
     <t>能够了解别人的人是聪明的，能够了解自己的人则更为睿智。能够战胜别人的人是有力量的，能够战胜自我的人则更为强大。知道满足的人是富有的，遵循大道坚持力行的人是有志的。不违背大道的人就能长久生存，身体没了但精神永存的人才是真正的寿命长久。</t>
   </si>
   <si>
-    <t>本章像一首哲理诗，讲认识自己、战胜自己。知人者智，自知者明：了解别人是智慧，了解自己才是高明，人贵有自知之明，眼睛能看远方却看不见自己的眉毛。胜人者有力，自胜者强：战胜别人只是有力，能战胜自己的欲望、弱点才是真正的强大，西方强国强调强加于人，只是胜人者有力。知足者富：知道满足才是真正的富有，贪得无厌永远觉得匮乏；强行者有志：坚持按道去做、知难而进的人才有志向。
+    <t>【认识自己 战胜自己】本章像一首哲理诗，讲认识自己、战胜自己。知人者智，自知者明：了解别人是智慧，了解自己才是高明，人贵有自知之明，眼睛能看远方却看不见自己的眉毛。胜人者有力，自胜者强：战胜别人只是有力，能战胜自己的欲望、弱点才是真正的强大，西方强国强调强加于人，只是胜人者有力。知足者富：知道满足才是真正的富有，贪得无厌永远觉得匮乏；强行者有志：坚持按道去做、知难而进的人才有志向。
 不失其所者久：不离开自己的归宿才能长久，“所”就是精神家园，物质再发达也不能让精神家园花果飘零。死而不亡者寿：身死而精神不亡，才是真正的长寿，那些思想家的光芒像群星，在黑暗时指引方向。译者·韩鹏杰说，这一章既写给领导者也写给普通人：自知、自胜、知足、强行、守所、精神不亡，六层递进，是中国文化中极高的人生境界。</t>
   </si>
   <si>
@@ -571,20 +628,20 @@
     <t>大道的作用是那样的广大而普遍，可以说无处不在。万物依靠它才能生存 而它从不限制万物，大功告成也不去求名、不去占有。护养了万物而不做万物的主宰者，它无欲而静，隐微虚无，所以可以把道称作为“小”。虽然万物归附于道 而它却不当万物的主宰者，所以把它看作是伟大的。因为它始终不追求成为伟大者，所以才能成为伟大者。</t>
   </si>
   <si>
-    <t>本章讲道无处不在、成就万物而不主宰，因不自大而成其大。大道泛兮，其可左右：道如水、如风，无处不在，左右逢源。万物恃之而生而不辞：万物依赖道生长，道从不推辞；功成而不名有：成就万物却不居功留名。衣养万物而不为主：护养万物却不做主宰，不要求感恩戴德。常无欲，可名于小：道无欲谦下，可以说它渺小；万物归焉而不为主，可名为大：万物归附它却不自居为主，又可以说它伟大。以其终不自为大，故能成其大：正因为它始终不自以为大，才真正成就了伟大。
+    <t>【道无处不在 成就万物而不主宰】本章讲道无处不在、成就万物而不主宰，因不自大而成其大。大道泛兮，其可左右：道如水、如风，无处不在，左右逢源。万物恃之而生而不辞：万物依赖道生长，道从不推辞；功成而不名有：成就万物却不居功留名。衣养万物而不为主：护养万物却不做主宰，不要求感恩戴德。常无欲，可名于小：道无欲谦下，可以说它渺小；万物归焉而不为主，可名为大：万物归附它却不自居为主，又可以说它伟大。以其终不自为大，故能成其大：正因为它始终不自以为大，才真正成就了伟大。
 译者·韩鹏杰强调，这一章讲量变质变、从小到大的道理：合抱之木生于毫末，九层之台起于累土，千里之行始于足下；天下难事必作于易，天下大事必作于细。做人做事不要自高自大、好高骛远，要虚怀若谷、脚踏实地，把容易的事当难事做，把小事做好，一步一步成就伟大。</t>
   </si>
   <si>
     <t>第三十五章（35）</t>
   </si>
   <si>
-    <t>执大象，天下往。往而不害，安平泰。乐与饵，过客止。道之出口，淡乎其无味。视之不足见，听之不足闻，用之不足既。</t>
+    <t>执大象，天下往。往而不害，安平泰。乐（yuè）与饵，过客止。道之出口，淡乎其无味。视之不足见，听之不足闻，用之不足既。</t>
   </si>
   <si>
     <t>如果君主掌握了大道，天下人都会归附于他。归附他不会有任何害处，都能过上太平安乐的好生活。然而由于贪图诸如音乐美食等各种安逸的事物，往往会使那些皈依大道的人半途而废。大道这种事物说出来，淡淡的没有任何味道。看它又看不见，听它又听不到，用它却用不完。</t>
   </si>
   <si>
-    <t>本章讲守道则天下归往，平淡才是真。执大象，天下往：掌握大道（大象即道），天下人都会归附；往而不害，安平太：归附而不受伤害，安详、平稳、太平。乐与饵，过客止：音乐与美食能让人停下脚步，这些外在享受有吸引力，但也容易让人半途而废，不能沉溺其中。道之出口，淡乎其无味：道说出来淡而无味，不像美食音乐那样刺激；视之不足见，听之不足闻，用之不足既：看不见、听不到，却取之不尽、用之不竭。
+    <t>【平淡才是真】本章讲守道则天下归往，平淡才是真。执大象，天下往：掌握大道（大象即道），天下人都会归附；往而不害，安平太：归附而不受伤害，安详、平稳、太平。乐与饵，过客止：音乐与美食能让人停下脚步，这些外在享受有吸引力，但也容易让人半途而废，不能沉溺其中。道之出口，淡乎其无味：道说出来淡而无味，不像美食音乐那样刺激；视之不足见，听之不足闻，用之不足既：看不见、听不到，却取之不尽、用之不竭。
 译者·韩鹏杰说，我们日常所用而不知，天天都在用道却不自知；饮食清淡有益健康，人格返璞归真才接近道，清水出芙蓉、天然去雕饰是艺术的高境界。年轻人都觉得自己会成为伟大人物，最后发现伟大来自平凡，把自己看得平凡，才能重归于朴、重归于真、重归于道。真正的力量不是热闹炫耀，而是平淡之中无穷无尽。</t>
   </si>
   <si>
@@ -597,7 +654,7 @@
     <t>要想收缩自己的对手，必须暂时让对手扩张开来；要想削弱自己的对手，必须暂时加强自己的对手；要想废除自己的对手，必须暂时让对手振兴起来；要想夺取对手的东西，必须暂时先赠予一些东西给对手。这就叫作含而不露的聪明。也即以柔弱的手段战胜刚强之人的策略。使用这些策略时要像鱼不可离开水那样不能脱离一定的客观条件，也像国家的优良武器一样 不能让别人知道。</t>
   </si>
   <si>
-    <t>本章把相反相成的思维讲得最直白，并提醒含藏的力量与边界。将欲歙之，必固张之：想收敛它，先让它张开；将欲弱之，必固强之：想削弱它，先让它强大（捧杀）；将欲废之，必固兴之：想废弃它，先让它兴盛，举得越高摔得越重；将欲夺之，必固与之：想夺取它，先给予它，钓鱼先下鱼饵。是谓微明：这种微妙而明确的智慧叫微明。柔弱胜刚强：柔弱可以战胜刚强。鱼不可脱于渊：鱼不能离开水，策略不能脱离客观条件；国之利器不可以示人：国家的利器不能轻易示人，时时亮剑威胁别人，别人就想折断你的剑。
+    <t>【看清对立面】本章把相反相成的思维讲得最直白，并提醒含藏的力量与边界。将欲歙之，必固张之：想收敛它，先让它张开；将欲弱之，必固强之：想削弱它，先让它强大（捧杀）；将欲废之，必固兴之：想废弃它，先让它兴盛，举得越高摔得越重；将欲夺之，必固与之：想夺取它，先给予它，钓鱼先下鱼饵。是谓微明：这种微妙而明确的智慧叫微明。柔弱胜刚强：柔弱可以战胜刚强。鱼不可脱于渊：鱼不能离开水，策略不能脱离客观条件；国之利器不可以示人：国家的利器不能轻易示人，时时亮剑威胁别人，别人就想折断你的剑。
 译者·韩鹏杰用捧杀典故解释：杀君马者道旁儿，过分夸奖、吹捧使人骄傲自满、退步失败，关羽过不了奉承关而败走麦城；两军对垒时老弱残兵挑衅、敌人弃辎重诱敌，都是将欲夺之必固与之。本章不是说用阴谋，而是讲事物转化的规律：看清对立面的运动，力量与边界都要含藏，不能张扬炫耀。</t>
   </si>
   <si>
@@ -610,7 +667,7 @@
     <t>大道永远是清静无为的 然而却又成就了万事万物。王侯如果能够遵循着它，百姓将会自然而然地发展生产（自我化育、自我成长）。生产发展繁荣之后如有欲望产生，我将用无形无象的大道使他们安定下来。这种无名的质朴状态，本身也不会产生欲望。如果人们没有欲望就能保持平静（治理天下的人要做表率，少私寡欲，清静无为），天下将自然会太平安定。</t>
   </si>
   <si>
-    <t>本章是《道经》的收束，讲无为而无不为。道常无为而无不为：道恒常无为，不妄为、不干预，却成就万事万物。侯王若能守之，万物将自化：领导者若能守住道，万物自然化育成长。化而欲作，吾将镇之以无名之朴：万物生长中欲望萌动时，用无名的素朴去镇服安定。无名之朴，亦将无欲：素朴本身没有欲望。不欲以静，天下将自定：没有欲望就能安静，天下自然安定。
+    <t>【不违背事物本身的规律 则没有做不成的】本章是《道经》的收束，讲无为而无不为。道常无为而无不为：道恒常无为，不妄为、不干预，却成就万事万物。侯王若能守之，万物将自化：领导者若能守住道，万物自然化育成长。化而欲作，吾将镇之以无名之朴：万物生长中欲望萌动时，用无名的素朴去镇服安定。无名之朴，亦将无欲：素朴本身没有欲望。不欲以静，天下将自定：没有欲望就能安静，天下自然安定。
 译者·韩鹏杰把无为理解为：不违背规律、不妄为、不折腾，而不是消极不作为；治理的最高境界是让事物按自己的本性生长，让百姓自然发展生产、自然安定。从第一章到第三十七章是《道经》，讲道本身；后三十八章起是《德经》，讲道落实到人。把这两部分合起来读，“道在前而德在后”，做一切事才能顺理成章。</t>
   </si>
   <si>
@@ -896,7 +953,7 @@
     <t>治大国若烹（pēng）小鲜。以道莅天下，其鬼不神。非其鬼不神，其神不伤人；非其神不伤人，圣人亦不伤人。夫两不相伤，故德交归焉。</t>
   </si>
   <si>
-    <t>治理大国就像烹调小鱼一样（不要经常折腾它）。（君主如果能够）用道来领导、指引天下，鬼也就没有神秘莫测的力量。不是说鬼不神秘莫测了，而是它的神秘莫测伤害不了得道的人。不但鬼的神秘力量伤不了民众，圣人也不伤害民众。鬼和圣人都不伤害民众，所以德不断地积累交汇，形成有道有德的世界（恩德都将施与民众）。</t>
+    <t>治理大国就像烹调小鱼一样（不要经常折腾它）。（君主如果能够）用道来领导、指引天下，鬼也就没有神秘莫测的力量。不是说鬼不神秘莫测了，而是它的神秘莫测伤害不了得道的人。不但鬼的神秘力量伤不了百姓，圣人也不伤害百姓。鬼和圣人都不伤害百姓，所以德不断地积累交汇，形成有道有德的世界（恩德都将施与百姓）。</t>
   </si>
   <si>
     <t>这一章有一句话，大家都非常熟，叫“治大国若烹小鲜”，这句话也是这一章的核心。一九八七年，美国前总统里根在发表国情咨文的时候也引过这句话。二〇一三年，“金砖各国”开会，在一个联合的采访中，有一位巴西记者问过习近平这样的一个问题：你担任这么大的一个国家的这么重要的职位是一种什么心态？你用什么样的态度来对待自己的职位？习近平答记者问，先引的是《诗经》，来回答第一个问题：“战战兢兢，如临深渊，如履薄冰。”这话出自《诗经·小雅·小旻》。治理国家要小心谨慎，就像行走在结着薄冰的冰面上一样，就像站在悬崖边一样，要小心谨慎，因为稍不谨慎就会出大的问题、大的危险。然后引用这句话来回答第二个问题，我要以“治大国若烹小鲜”的态度来对待我的职位。“治大国若烹小鲜”是什么意思呢？大家如果上网去搜对这句话的解释，类型就有二十多种，每一种解释都不一样，有的甚至把它直接翻译为“治理一个大的国家就像烹一碟小菜那么简单”，这是完全没有理解这句话的真正的含义。“小鲜”就是小鱼儿，鱼肉很细很嫩，拿它的时候就得小心谨慎，尤其是在高温里烹炒它的时候，都要小心谨慎，要有耐心。火候不到的时候你老折腾，甚至锅铲飞舞，翻腾，鱼不就成了碎片了吗？汉朝的毛亨，喜欢《诗经》的人都知道，这个人写过《毛诗传》的，他就用两句话来解读这句话，其实最符合它的本意。第一句话叫“烹鱼烦则碎”，环节太多老折腾它，那鱼就成了碎片了。第二句话“治民烦则乱”，治理一个国家也是一样，讲究的是制度的稳定，不能今天一个制度，明天一个制度，朝令夕改；你不能今天一个运动，明天一个运动来回折腾，国家不就被折腾散架了嘛。“治大国若烹小鲜”和“战战兢兢，如履薄冰”的道理是相同的，讲究的是小心谨慎，有耐心，掌握火候。“以道莅天下，其鬼不神。”“莅”就是莅临。用道来领导天下，指引天下。大家注意，这个“神”字很多的理解有问题，其实并不是神鬼的神，不是说我们后来的人格神、神化了的神。这个“神”在《易传》里面的解释是非常明确的，“阴阳之不测之谓神”，也就是神秘莫测。用道来领导天下、指引天下，鬼也没有什么神秘莫测的力量，因为你走的是正道，你走的是堂堂大道，鬼也没有办法去伤害到你，所以“以道莅天下，其鬼不神”。《道德经》里用它的道，把大家所恐惧的鬼的位置给取代了，你堂堂大道，鬼也近不了你的身，“其鬼不神；非其鬼不神”，不是鬼不神秘莫测，是因为你走大道，它的神秘、莫测、玄妙、诡秘已经没有办法伤害到你。所以把下一句话作为上一句话“其鬼不神”的注解，就很容易理解了。“非其鬼不神”，不是说这鬼不神秘莫测了，神秘莫测是它的本性。“其神不伤人”，但是它的神秘莫测已经伤害不了这种走在大道上的人、得道的人。“非其神不伤人，圣人亦不伤人”，不单是指鬼的力量伤害不了人了，反过来说，圣人他智慧高，但圣人智慧高也得返璞归真。圣人不会因为自己的智慧高，心眼多套路深，就使用这种“技巧”，这个东西不是正道。所以，鬼的神秘莫测伤不了人，圣人的智慧在领导大家的时候也会“善利万物而不争”，对人民没有伤害，“夫两不相伤”，你看鬼的神秘莫测也伤不了人，圣人领导也伤不了人。“夫两不相伤，故德交归焉。”所以有德的事情，积德的事情，两者交汇到一起，两不相伤。因为你按照道来做事情的话，鬼伤不了你，圣人也是按照道来做的，彼此也不相伤。这样大家就走在正确的道上，按照道去做，不断地积德，所以叫“德交归焉”，交汇，归到一块。“治大国若烹小鲜。以道莅天下，其鬼不神。非其鬼不神，其神不伤人；非其神不伤人，圣人亦不伤人。”如果这样两不相伤的，那就是“德交归焉”，这样就形成了一个和谐的、有道的、有德的世界。</t>
@@ -2629,7 +2686,7 @@
     <col min="3" max="3" width="59.25" style="3" customWidth="1"/>
     <col min="4" max="4" width="60.6666666666667" style="3" customWidth="1"/>
     <col min="5" max="5" width="75.25" style="3" customWidth="1"/>
-    <col min="6" max="6" width="7.37962962962963" style="3" customWidth="1"/>
+    <col min="6" max="6" width="20.037037037037" style="3" customWidth="1"/>
     <col min="7" max="7" width="29.3981481481481" style="3" customWidth="1"/>
     <col min="8" max="16381" width="23.75" style="3" customWidth="1"/>
     <col min="16382" max="16384" width="23.75" style="3"/>
@@ -2719,10 +2776,10 @@
         <v>21</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="172.8" spans="1:7">
@@ -2730,22 +2787,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="11">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="172.8" spans="1:7">
@@ -2753,22 +2810,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" ht="158.4" spans="1:7">
@@ -2776,19 +2833,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G7" s="11">
         <v>57</v>
@@ -2799,22 +2856,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" ht="158.4" spans="1:7">
@@ -2822,22 +2879,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" ht="187.2" spans="1:7">
@@ -2845,22 +2902,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" ht="158.4" spans="1:7">
@@ -2868,22 +2925,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" ht="172.8" spans="1:7">
@@ -2891,22 +2948,22 @@
         <v>10</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" ht="158.4" spans="1:7">
@@ -2914,22 +2971,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" ht="158.4" spans="1:7">
@@ -2937,22 +2994,22 @@
         <v>12</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" ht="172.8" spans="1:7">
@@ -2960,19 +3017,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="G15" s="11"/>
     </row>
@@ -2981,22 +3038,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" ht="172.8" spans="1:7">
@@ -3004,19 +3061,19 @@
         <v>15</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="G17" s="11">
         <v>26</v>
@@ -3027,19 +3084,19 @@
         <v>16</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="G18" s="11"/>
     </row>
@@ -3048,19 +3105,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="G19" s="11">
         <v>69</v>
@@ -3071,22 +3128,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" ht="158.4" spans="1:7">
@@ -3094,22 +3151,22 @@
         <v>19</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" ht="187.2" spans="1:7">
@@ -3117,19 +3174,19 @@
         <v>20</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="G22" s="11">
         <v>6</v>
@@ -3140,22 +3197,22 @@
         <v>21</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" ht="187.2" spans="1:7">
@@ -3163,22 +3220,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="D24" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E24" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>16</v>
-      </c>
       <c r="G24" s="11" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" ht="158.4" spans="1:7">
@@ -3186,19 +3243,19 @@
         <v>23</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="G25" s="11"/>
     </row>
@@ -3207,19 +3264,19 @@
         <v>24</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="G26" s="11">
         <v>2</v>
@@ -3230,19 +3287,19 @@
         <v>25</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="G27" s="11">
         <v>1</v>
@@ -3253,19 +3310,19 @@
         <v>26</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="G28" s="11">
         <v>15</v>
@@ -3276,19 +3333,19 @@
         <v>27</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="G29" s="11"/>
     </row>
@@ -3297,19 +3354,19 @@
         <v>28</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="G30" s="11">
         <v>22</v>
@@ -3320,19 +3377,19 @@
         <v>29</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="G31" s="11"/>
     </row>
@@ -3341,168 +3398,178 @@
         <v>30</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G32" s="11"/>
+        <v>113</v>
+      </c>
+      <c r="G32" s="11">
+        <v>31</v>
+      </c>
     </row>
     <row r="33" ht="172.8" spans="1:7">
       <c r="A33" s="10">
         <v>31</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G33" s="11"/>
+        <v>113</v>
+      </c>
+      <c r="G33" s="11">
+        <v>30</v>
+      </c>
     </row>
     <row r="34" ht="172.8" spans="1:7">
       <c r="A34" s="10">
         <v>32</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G34" s="11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" ht="158.4" spans="1:7">
+        <v>113</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" ht="172.8" spans="1:7">
       <c r="A35" s="10">
         <v>33</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="G35" s="11"/>
     </row>
-    <row r="36" ht="158.4" spans="1:7">
+    <row r="36" ht="172.8" spans="1:7">
       <c r="A36" s="10">
         <v>34</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G36" s="11"/>
+        <v>113</v>
+      </c>
+      <c r="G36" s="11">
+        <v>2</v>
+      </c>
     </row>
     <row r="37" ht="158.4" spans="1:7">
       <c r="A37" s="10">
         <v>35</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G37" s="11"/>
+        <v>113</v>
+      </c>
+      <c r="G37" s="11">
+        <v>12</v>
+      </c>
     </row>
     <row r="38" ht="172.8" spans="1:7">
       <c r="A38" s="10">
         <v>36</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G38" s="11"/>
-    </row>
-    <row r="39" ht="144" spans="1:7">
+        <v>113</v>
+      </c>
+      <c r="G38" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" ht="158.4" spans="1:7">
       <c r="A39" s="10">
         <v>37</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>16</v>
+        <v>113</v>
       </c>
       <c r="G39" s="11"/>
     </row>
@@ -3511,19 +3578,19 @@
         <v>38</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G40" s="11"/>
     </row>
@@ -3532,19 +3599,19 @@
         <v>39</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G41" s="11">
         <v>2</v>
@@ -3555,19 +3622,19 @@
         <v>40</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G42" s="11"/>
     </row>
@@ -3576,19 +3643,19 @@
         <v>41</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G43" s="11"/>
     </row>
@@ -3597,22 +3664,22 @@
         <v>42</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
     </row>
     <row r="45" ht="409.5" spans="1:7">
@@ -3620,19 +3687,19 @@
         <v>43</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="C45" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="F45" s="11" t="s">
         <v>199</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>180</v>
       </c>
       <c r="G45" s="11"/>
     </row>
@@ -3641,19 +3708,19 @@
         <v>44</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G46" s="11"/>
     </row>
@@ -3662,19 +3729,19 @@
         <v>45</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G47" s="11"/>
     </row>
@@ -3683,19 +3750,19 @@
         <v>46</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G48" s="11"/>
     </row>
@@ -3704,19 +3771,19 @@
         <v>47</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G49" s="11"/>
     </row>
@@ -3725,19 +3792,19 @@
         <v>48</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G50" s="11"/>
     </row>
@@ -3746,19 +3813,19 @@
         <v>49</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G51" s="11"/>
     </row>
@@ -3767,19 +3834,19 @@
         <v>50</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G52" s="11"/>
     </row>
@@ -3788,19 +3855,19 @@
         <v>51</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G53" s="11"/>
     </row>
@@ -3809,19 +3876,19 @@
         <v>52</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G54" s="11">
         <v>6</v>
@@ -3832,19 +3899,19 @@
         <v>53</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G55" s="11"/>
     </row>
@@ -3853,19 +3920,19 @@
         <v>54</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G56" s="11"/>
     </row>
@@ -3874,19 +3941,19 @@
         <v>55</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G57" s="11"/>
     </row>
@@ -3895,19 +3962,19 @@
         <v>56</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G58" s="11"/>
     </row>
@@ -3916,22 +3983,22 @@
         <v>57</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
     </row>
     <row r="60" ht="409.5" spans="1:7">
@@ -3939,19 +4006,19 @@
         <v>58</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G60" s="11"/>
     </row>
@@ -3960,19 +4027,19 @@
         <v>59</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G61" s="11"/>
     </row>
@@ -3981,19 +4048,19 @@
         <v>60</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G62" s="11"/>
     </row>
@@ -4002,19 +4069,19 @@
         <v>61</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G63" s="11"/>
     </row>
@@ -4023,19 +4090,19 @@
         <v>62</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G64" s="11"/>
     </row>
@@ -4044,22 +4111,22 @@
         <v>63</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
     </row>
     <row r="66" ht="409.5" spans="1:7">
@@ -4067,19 +4134,19 @@
         <v>64</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G66" s="11">
         <v>63</v>
@@ -4090,19 +4157,19 @@
         <v>65</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G67" s="11"/>
     </row>
@@ -4111,22 +4178,22 @@
         <v>66</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
     </row>
     <row r="69" ht="409.5" spans="1:7">
@@ -4134,19 +4201,19 @@
         <v>67</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G69" s="11"/>
     </row>
@@ -4155,19 +4222,19 @@
         <v>68</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G70" s="11"/>
     </row>
@@ -4176,19 +4243,19 @@
         <v>69</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G71" s="11">
         <v>17</v>
@@ -4199,19 +4266,19 @@
         <v>70</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G72" s="11"/>
     </row>
@@ -4220,22 +4287,22 @@
         <v>71</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
     </row>
     <row r="74" ht="374.4" spans="1:7">
@@ -4243,19 +4310,19 @@
         <v>72</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G74" s="11"/>
     </row>
@@ -4264,19 +4331,19 @@
         <v>73</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G75" s="11"/>
     </row>
@@ -4285,19 +4352,19 @@
         <v>74</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G76" s="11"/>
     </row>
@@ -4306,19 +4373,19 @@
         <v>75</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>329</v>
+        <v>348</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G77" s="11">
         <v>10</v>
@@ -4329,19 +4396,19 @@
         <v>76</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G78" s="11"/>
     </row>
@@ -4350,19 +4417,19 @@
         <v>77</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G79" s="11"/>
     </row>
@@ -4371,22 +4438,22 @@
         <v>78</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
     </row>
     <row r="81" ht="409.5" spans="1:7">
@@ -4394,19 +4461,19 @@
         <v>79</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G81" s="11"/>
     </row>
@@ -4415,19 +4482,19 @@
         <v>80</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G82" s="11"/>
     </row>
@@ -4436,19 +4503,19 @@
         <v>81</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="G83" s="11">
         <v>7</v>
@@ -4506,19 +4573,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="G2" s="3"/>
     </row>
@@ -4527,19 +4594,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="G3" s="4"/>
     </row>
@@ -4548,19 +4615,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -4569,19 +4636,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="G5" s="4"/>
     </row>
@@ -4590,19 +4657,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="G6" s="4"/>
     </row>
@@ -4611,19 +4678,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -4632,19 +4699,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>388</v>
+        <v>407</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -4653,19 +4720,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="G9" s="4"/>
     </row>
@@ -4674,19 +4741,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="G10" s="4"/>
     </row>
@@ -4695,19 +4762,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="G11" s="4"/>
     </row>
@@ -4716,19 +4783,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>406</v>
+        <v>425</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="G12" s="4"/>
     </row>
@@ -4737,19 +4804,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="G13" s="4"/>
     </row>
@@ -4758,19 +4825,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>414</v>
+        <v>433</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>416</v>
+        <v>435</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -4779,19 +4846,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>420</v>
+        <v>439</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>421</v>
+        <v>440</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="G15" s="4"/>
     </row>
@@ -4800,19 +4867,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>424</v>
+        <v>443</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="G16" s="4"/>
     </row>
@@ -4821,19 +4888,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>429</v>
+        <v>448</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="G17" s="4"/>
     </row>
@@ -4842,19 +4909,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>433</v>
+        <v>452</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="G18" s="4"/>
     </row>
@@ -4863,19 +4930,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>437</v>
+        <v>456</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="G19" s="4"/>
     </row>
@@ -4884,19 +4951,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="D20" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>441</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>442</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>422</v>
       </c>
       <c r="G20" s="4"/>
     </row>
@@ -4905,19 +4972,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="G21" s="4"/>
     </row>
@@ -4926,19 +4993,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="G22" s="4"/>
     </row>
@@ -4947,19 +5014,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="G23" s="4"/>
     </row>
@@ -4968,19 +5035,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="G24" s="4"/>
     </row>
@@ -4989,19 +5056,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="G25" s="4"/>
     </row>
@@ -5010,19 +5077,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="D26" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>466</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>447</v>
       </c>
       <c r="G26" s="4"/>
     </row>
@@ -5031,19 +5098,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>471</v>
+        <v>490</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="G27" s="4"/>
     </row>
@@ -5052,19 +5119,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>475</v>
+        <v>494</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="G28" s="4"/>
     </row>

--- a/book.xlsx
+++ b/book.xlsx
@@ -320,7 +320,7 @@
   </si>
   <si>
     <t>【看待得失 珍视生命】本章讲宠辱与生命，核心是如何看待得失、珍视生命，什么样的人才可托付天下。宠辱若惊：得到宠幸和失去宠幸都会惊恐。为什么？宠为下：被宠的人在下面，宠我们的人在上面，所以得之若惊（怕失去），失之若惊（更恐惧），这叫宠辱若惊。能做到宠辱不惊、淡然处之，是难得的人生境界。贵大患若身：有身体就有祸患，身体代表利益，也带来疾病与麻烦；但身体是摆脱不掉的，所以更要珍视它。
-吾所以有大患者，为吾有身，及吾无身，吾有何患——不把身体和生命当回事的人，坐到重要位置上是很可怕的；声色犬马、厚食重味正是戕害生命。贵以身为天下，若可寄天下；爱以身为天下，若可托天下：真正把自身生命看得与天下一样贵重、肯为天下担当牺牲的人，才值得把天下托付给他。译者·韩鹏杰区分两种勇敢：无赖式的勇敢不把命当回事，有责任的勇敢珍视生命又肯担当，后者才值得托付。</t>
+吾所以有大患者，为吾有身，及吾无身，吾有何患——不把身体和生命当回事的人（为了私欲、虚荣、争斗，随便豁出性命；为了名利，把自己身体不当回事），坐到重要位置上是很可怕的；声色犬马、厚食重味正是戕害生命。贵以身为天下，若可寄天下；爱以身为天下，若可托天下：真正把自身生命看得与天下一样贵重、肯为天下担当牺牲的人，才值得把天下托付给他。译者·韩鹏杰区分两种勇敢：无赖式的勇敢不把命当回事，有责任的勇敢珍视生命又肯担当，后者才值得托付。</t>
   </si>
   <si>
     <t>道经 | 超脱之道</t>
@@ -3012,7 +3012,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15" ht="172.8" spans="1:7">
+    <row r="15" ht="187.2" spans="1:7">
       <c r="A15" s="10">
         <v>13</v>
       </c>

--- a/book.xlsx
+++ b/book.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="512">
   <si>
     <t>no</t>
   </si>
@@ -406,7 +406,7 @@
 一个社会天天提倡道德，正说明道德已经滑坡；什么时候妇女节、教师节不再成为问题，才说明相关地位真正提高了。这不是否定仁义孝慈，而是提醒人们不要靠表面提倡来补救，要从根本上回到道。把第十八、十九章连起来读：与其用仁义、智巧等外在名目补救，不如回归素朴本心，做个好人、存点好心、行些好事。</t>
   </si>
   <si>
-    <t>道经</t>
+    <t>道经 | 政治之道</t>
   </si>
   <si>
     <t>19、（18/19章可融合为一章）</t>
@@ -418,13 +418,16 @@
     <t>绝圣弃智，民利百倍；绝仁弃义，民复孝慈；绝巧弃利，盗贼无有。此三者以为文不足。故令有所属：见（xiàn）素抱朴，少私寡欲，绝学无忧。</t>
   </si>
   <si>
-    <t>（为政者）弃绝智谋算和巧言令色，百姓反而会得到百倍的利益；不去提倡仁义，百姓反而能够做到孝慈；弃绝投机取巧和功利之心，盗贼就不会产生。以上三条原则仅仅作为理论谈谈是不够的。所以要为它们分别落实一些施行的具体措施：行为单纯 内心淳朴，减少私心 降低欲望，抛弃巧、利 没有忧虑。</t>
+    <t>（为政者）弃绝智谋算和巧言令色，百姓反而会得到百倍的利益；不去提倡仁义，百姓反而能够做到孝慈；弃绝投机取巧和功利之心，盗贼就不会产生。以上三条原则仅仅作为理论谈谈是不够的。所以要为它们分别落实一些施行的具体措施：行为单纯 内心淳朴，减少私心 降低欲望，抛弃巧利 没有忧虑。</t>
   </si>
   <si>
     <t>【朴素之心 少私寡欲】本章主张绝弃外在名目，回归素朴本心。绝圣弃智，民利百倍：抛弃圣贤名号和智巧机心，百姓反而得到百倍利益；绝仁弃义，民复孝慈：不刻意提倡仁义，百姓反而自然做到孝慈；绝巧弃利，盗贼无有：清除技巧和利益诱惑，盗贼就不会产生。此三者以为文不足：仅仅在理论上讲这三条还不够，要落实为具体方向——见素抱朴，少私寡欲，绝学无忧：行为单纯、内心淳朴，减少私心、降低欲望，不为纷繁的学问和机巧所惑，就没有忧虑。
 译者·韩鹏杰说，道家认为人的本心就是真心，真心就是朴素之心，朴素之心就是少私寡欲；外在花花绿绿的学问看多了，反而把人搞乱。读经典要由博返约，最后陪我们一生的可能只是一两本书、一两句话，真传一句话，假传万卷书。绝学无忧不是不要学习，而是学真正的大道，不被浮华知识蒙蔽。</t>
   </si>
   <si>
+    <t>道经 | 归元之道</t>
+  </si>
+  <si>
     <t>18、（18/19章可融合为一章）</t>
   </si>
   <si>
@@ -434,13 +437,16 @@
     <t>唯之与阿（hē），相去几何？善之与恶，相去若何？人之所畏，不可不畏。荒兮，其未央哉！众人熙熙，如享太牢，如春登台。我独泊兮，其未兆，如婴儿之未孩。儽（léi）儽兮，若无所归。众人皆有余，而我独若遗。我愚人之心也哉，沌（dùn）沌兮！俗人昭昭，我独昏昏；俗人察察，我独闷闷。澹（dàn）兮其若海； 飂（liáo）兮若无止 。众人皆有以，而我独顽似鄙。我独异于人，而贵食母。</t>
   </si>
   <si>
-    <t>赞成与反对，相差有多远？善良与丑恶，相差又有多远？大家都敬畏的不能不去敬畏！前面的道路多么漫长啊，就像没有尽头！众人是那样的快乐，就好像参加盛大宴会，春日登台赏景一样。而只有我淡泊处之，无动于衷，就如同一个还不会笑的婴儿一般。我是如此狼狈不堪，就像个无家可归的人一样。众人都过着富裕幸福的生活，只有我却像被遗弃了一样。因为我有一副愚人的心肠，太笨拙了！世人是那样的明白，只有我是如此的糊涂；世人是那样的聪慧，只有我是这样的宽厚。我的生活是那样的坎坷多难 就好像那动荡不安的大海一样；我如同那飘忽不定的长风 不知何处才是归宿。众人活得都是那样的有用，只有我如此冥顽无能。虽然我和世人格格不入（追求的目标不一样），但我还要继续以大道为依归。</t>
+    <t>赞成与反对，相差有多远？善良与丑恶，相差又有多远？大家都敬畏的不能不去敬畏。前面的道路多么漫长啊，就像没有尽头！众人是那样的快乐，就好像参加盛大宴会，春日登台赏景一样。而只有我淡泊处之，无动于衷，就如同一个还不会笑的婴儿一般。我是如此狼狈不堪，就像个无家可归的人一样。众人都过着富裕幸福的生活，只有我却像被遗弃了一样。因为我有一副愚人的心肠，太笨拙了！世人是那样的明白，只有我是如此的糊涂；世人是那样的聪慧，只有我是这样的宽厚。我的生活是那样的坎坷多难 就好像那动荡不安的大海一样；我如同那飘忽不定的长风 不知何处才是归宿。众人活得都是那样的有用，只有我如此冥顽无能。虽然我和世人格格不入（追求的目标不一样），但我还要继续以大道为依归。</t>
   </si>
   <si>
     <t>【描述了老子的自画像】本章是得道者的自画像。唯之与阿，相去几何？善之与恶，相去若何：恭敬的应答与呵斥相差多远？善与恶又相差多少？老子提醒，是非善恶的界限并非表面看起来那么分明，好事也可能带来坏结果。人之所畏，不可不畏：但众人共同敬畏的规则，也要敬守，不要为了标新立异而违背公认的规范。众人熙熙，如享太牢，如春登台：众人都热热闹闹，像参加盛宴、春日登台；我独泊兮，其未兆，如婴儿之未孩：得道者独自淡泊、无动于衷，像还不会笑的婴儿。
 众人皆有余，而我独若遗：众人都显得富足有余，得道者却像有所遗失。我愚人之心也哉，沌沌兮：一副愚人心肠，混沌淳朴。俗人昭昭，我独昏昏；俗人察察，我独闷闷：世人精明，得道者看似糊涂宽厚。澹兮其若海，飂兮若无止：他像大海一样淡泊深沉，像长风一样自由无羁。众人皆有以，而我独顽似鄙：世人都有用处，他看似冥顽无能。我独异于人，而贵食母：与众人不同，因为他以大道为归依。本章刻画了不随波逐流、独立守道的精神境界。</t>
   </si>
   <si>
+    <t>道经 | 养智之道</t>
+  </si>
+  <si>
     <t>第二十一章（21）</t>
   </si>
   <si>
@@ -454,6 +460,9 @@
 自古及今，其名不去，以阅众甫：从古至今，道的名字不曾消失，凭借它可以认识万物起始。吾何以知众甫之状哉？以此：我就是凭借道来认识圣人得道的状态。译者·韩鹏杰强调，道不仅是万物的本源和规律，也是人生的境界；离开了道，人就变成无源之水、无本之木。这一章让人对道建立确信：它看不见摸不着，但真实存在，是精神世界的根基。</t>
   </si>
   <si>
+    <t>道经 | 有形之道</t>
+  </si>
+  <si>
     <t>1、14、21、42</t>
   </si>
   <si>
@@ -463,13 +472,16 @@
     <t>曲则全，枉则直，洼则盈，敝则新，少则得，多则惑。是以圣人抱一为天下式。不自见（xiàn），故明；不自是，故彰；不自伐，故有功；不自矜（jīn），故长（cháng）。夫唯不争，故天下莫能与之争。古之所谓“曲则全”者，岂虚言哉？诚全而归之。</t>
   </si>
   <si>
-    <t>忍受委屈则能保全自我，先弯曲反而能够伸直，低洼反而能够变得充盈，守旧反而能够创新，少取一些则有所收获，贪得无厌反而会变得迷惑。因此圣人能够同以上原则保持一致（持守道作为天下的法则）。他们不仅仅依靠自己的眼睛去观察，所以才能够看得清楚；从不自以为是，所以才能够彰显名声；从不自我夸耀，所以才能够保有功劳；从不自高自大，所以才能够成为领导者。正因为他们从不与别人争夺，所以天下没有任何人能够争得赢他们。古人所说的“委屈则能求全”这句话，难道是句空话吗？确实应该把保全自我的功劳归于这一原则（回归道）。</t>
+    <t>忍受委屈则能保全自我，先弯曲反而能够伸直，低洼反而能够变得充盈，守旧反而能够创新，少取一些则有所收获，贪得无厌反而会变得迷惑。因此圣人能够同以上原则保持一致（持守道作为天下的法则）。他们不仅仅依靠自己的眼睛去观察，所以才能够看得清楚；从不自以为是，所以才能够彰显名声；从不自我夸耀，所以才能够保有功劳；从不自高自大，所以才能够成为领导者（保持长久）。正因为他们从不与别人争夺（善于谦让），所以天下没有任何人能够争得赢他们。古人所说的“委屈则能求全”这句话，难道是句空话吗？确实应该把保全自我的功劳归于这一原则（回归道）。</t>
   </si>
   <si>
     <t>【迂回 谦下 统一的思维处理问题】本章开头即主旨：曲则全，枉则直——懂得委婉迂回，才有更圆满的结果，像水一样绕开障碍、曲折流淌，才能到达目标；洼则盈——低洼处先被水灌满，善于处下才能获得更多；敝则新——破旧才有更新，世界有生有灭才生生不息；少则得，多则惑——知道自己懂得少才会努力学习，贪多反而迷惑。是以圣人抱一为天下式：圣人持守“一”作为天下范式，“一”就是阴阳两者的统一，看问题不能偏颇，要把对立两面合起来理解，就像同是数字6，对面看是9，各有立场。
 不自见故明，不自是故彰，不自伐故有功，不自矜故长：不固执己见才看得清，不自以为是才声名彰显，不自我夸耀才保有功劳，不自高自大才长久。夫唯不争，故天下莫能与之争：因为不与别人争夺，天下没有人能争得过他。古之所谓曲则全者，岂虚言哉，诚全而归之：古人说的曲则全，确实能把圆满的结果带回来。本章教人以迂回、谦下、统一的思维处理问题。</t>
   </si>
   <si>
+    <t>道经 | 反常之道</t>
+  </si>
+  <si>
     <t>28、66</t>
   </si>
   <si>
@@ -486,6 +498,9 @@
 同于道者，道亦乐得之；同于德者，德亦乐得之；同于失者，失亦乐得之：你喜欢什么、亲近什么，就会被什么吸引和成就，人身边聚集什么样的人，往往取决于你自己是什么样的人。信不足焉，有不信焉：自己诚信不足，别人自然不会信任你。译者·韩鹏杰指出，本章看似同语反复，其实在反复劝告：要让自己的境界不断提高，就要亲近有道有德的人和事，勇于发现并改正缺点，路是自己走出来的。</t>
   </si>
   <si>
+    <t>道经 | 守恒之道</t>
+  </si>
+  <si>
     <t>第二十四章（24）</t>
   </si>
   <si>
@@ -499,6 +514,9 @@
 其在道也，曰余食赘行：这些行为在道看来，就像吃饱了再吃、身上长赘瘤，多余无用；物或恶之，故有道者不处：人们厌恶它们，有道的人不做这些事。译者·韩鹏杰用项羽举例：力拔山兮气盖世，却因骄傲自大、听不进意见，落得自刎乌江的下场。孔子讲毋意、毋必、毋固、毋我，佛家讲无我相，与老子相通。做事要稳扎稳打，收敛自见、自是、自伐、自矜，才能不断进步。</t>
   </si>
   <si>
+    <t>道经 | 实用之道</t>
+  </si>
+  <si>
     <t>第二十五章（25）</t>
   </si>
   <si>
@@ -512,6 +530,9 @@
 道大，天大，地大，王亦大，域中有四大，而王居其一焉：道、天、地、人（王）都是大的，人只是四大之一，不能自大。人法地，地法天，天法道，道法自然：人效法地，地效法天，天效法道，道效法它本来的样子，自然就是本该如此。译者·韩鹏杰强调，道法自然是全书信仰和规则的源头，人要敬畏天道，与天地和谐相处。</t>
   </si>
   <si>
+    <t>道经 | 循环之道</t>
+  </si>
+  <si>
     <t>第二十六章（26）</t>
   </si>
   <si>
@@ -525,6 +546,9 @@
 轻则失根：轻率轻浮就失去根本，像飘蓬浮萍没有根基；躁则失君：浮躁急躁就失去对自己的掌控，冲动之下常常酿成大祸。译者·韩鹏杰用“路怒”举例：开车偶有小摩擦就粗口相向甚至拔刀，动手前问自己要不要动手、后果如何、有无别的办法，几秒钟的冷静可能改变结果。开头八字“重为轻根，静为躁君”与结尾“轻则失根，躁则失君”都是至理名言。</t>
   </si>
   <si>
+    <t>道经 | 内敛之道</t>
+  </si>
+  <si>
     <t>第二十七章（27）</t>
   </si>
   <si>
@@ -538,6 +562,9 @@
 是以圣人常善救人，故无弃人；常善救物，故无弃物：圣人善于救人救物，天下没有可抛弃的人、没有可抛弃之物，你没发现用处不等于无用，无用方为大用。善人者，不善人之师；不善人者，善人之资：善人是恶人的老师，恶人是善人的借鉴，“师资”一词正源于此。不贵其师，不爱其资，虽智大迷：不尊重老师、不爱惜借鉴，再聪明也是大迷惑，这是道的枢要。做人要善行不留痕迹，看人看物发现其用处，并善于从正反两方面学习。</t>
   </si>
   <si>
+    <t>道经 | 圆融之道</t>
+  </si>
+  <si>
     <t>第二十八章（28）</t>
   </si>
   <si>
@@ -551,19 +578,25 @@
 朴散则为器，圣人用之则为官长，故大制不割：素朴分散为万物之器，圣人顺应本性管理，最好的制度不伤害本性。译者·韩鹏杰强调，守雌、守黑、守辱不是没有经历过强、白、荣就假装谦卑，而是先有实力和成就，再有资格谈守，比如书法先经历精巧，才能返璞归真。记住十八个字：知其雄守其雌，知其白守其黑，知其荣守其辱，就是这一章的核心智慧。</t>
   </si>
   <si>
+    <t>道经 | 质朴之道</t>
+  </si>
+  <si>
     <t>第二十九章（29）</t>
   </si>
   <si>
     <t>将欲取天下而为之，吾见其不得已。天下神器，不可为也，不可执也。为者败之，执者失之。是以圣人无为，故无败；无执，故无失。故物或行或随；或歔（xū）或吹；或强或羸（léi）；或载（zài）或隳（huī）。是以圣人去甚，去奢，去泰。</t>
   </si>
   <si>
-    <t>君主想要治理好天下却又按照个人意志去采取行动，我将会看到他达不到自己的目的（断定必然会失败）。天下这个神圣的器物，是不可以按照个人意志强行干预，不可以强行把持。随心所欲地去治理天下的君主 一定会搞乱天下。想把天下据为己有的君主 一定会失去天下。因此圣人顺应自然 不妄为，故无失败；不强行把持，故无损失。（所以事情往往如此）本意也许是想走在前面 结果可能反而落在后面；本意也许是想轻轻哈气为物取暖 结果可能因为吹气太快而使物变凉；本意也许是想强壮 结果可能反而变得瘦弱；本意也许是想稍微减损一点儿 结果可能是全部毁掉了。因此圣人要去掉那些极端的，奢侈的，过分的言行和欲望。</t>
+    <t>君主想要治理好天下却又按照个人意志去采取行动，我将会看到他达不到自己的目的（断定必然会失败）。天下这个神圣的器物，是不可以按照个人意志强行干预，不可以强行把持。随心所欲地去治理天下的君主 一定会搞乱天下，想把天下据为己有的君主 一定会失去天下。因此圣人顺应自然 不妄为，故无失败；不强行把持，故无损失。（所以事情往往如此）本意也许是想走在前面 结果可能反而落在后面；本意也许是想轻轻哈气为物取暖 结果可能因为吹气太快而使物变凉；本意也许是想强壮 结果可能反而变得瘦弱；本意也许是想稍微减损一点儿 结果可能是全部毁掉了。因此圣人要去掉那些极端过分的，奢侈奢靡的，太过极端的言行和欲望。</t>
   </si>
   <si>
     <t>【事不可强为 天下不可强取】本章讲天下不可强为、强取。将欲取天下而为之，吾见其不得已：想用强力、武力夺取天下并按个人意志治理，注定达不到目的。天下神器，不可为也，不可执也：天下是神圣之物，不可强行干预，不可强行把持；为者败之，执者失之：强行去做的必失败，死死抓住的必失去。是以圣人无为，故无败；无执，故无失：圣人顺其自然、不妄为，所以不会失败；不强行把持，所以不会失去。
 故物或行或随，或嘘或吹，或强或羸，或载或隳：万物本性各不相同，有前行有跟随，有轻嘘有急吹，有强壮有羸弱，有安稳有毁坏，不能用一个标准、一种方式强求。是以圣人去甚，去奢，去泰：圣人去掉极端的、奢侈的、过分的言行和欲望。译者·韩鹏杰指出，这一章要结合时代背景理解：春秋末期诸侯争霸、生灵涂炭，老子提出小国寡民设想，反对强为；读这一章要体会其中的沉痛感，任何事有生必有灭、有成必有败，强求和把持都违背天道。</t>
   </si>
   <si>
+    <t>道经 | 争雄之道</t>
+  </si>
+  <si>
     <t>第三十章（30）</t>
   </si>
   <si>
@@ -577,6 +610,9 @@
 果而勿矜，果而勿伐，果而勿骄：胜利了不自大、不夸耀、不骄傲；果而不得已，果而勿强：胜利是出于不得已，胜了也不逞强。物壮则老，是谓不道，不道早已：事物强盛到极点就走向衰败，逞强求壮不合道，不合道就很快灭亡。译者·韩鹏杰说，这章最后三句话值得牢记：师之所处荆棘生焉，大军之后必有凶年，物壮则老。战争不可轻易发动，对待战争的态度就是对待同胞生命的态度；中华民族热爱和平，不惹事也不怕事。</t>
   </si>
   <si>
+    <t>道经 | 智战之道</t>
+  </si>
+  <si>
     <t>第三十一章（31）</t>
   </si>
   <si>
@@ -590,19 +626,25 @@
 吉事尚左，凶事尚右：吉庆之事尚左，凶丧之事尚右；偏将军居左，上将军居右，就是用办理丧事的礼节来对待战争。杀人之众，以悲哀泣之，战胜以丧礼处之：战争杀人众多，要带着悲哀的心情参与，战胜了也要用丧礼的仪式对待。译者·韩鹏杰强调，这两章应该进小学课本，让和平的种子从小种下；战争胜利后第一件事不是放肆庆祝，而是祭奠双方的死者，因为他们都是生命。</t>
   </si>
   <si>
+    <t>道经 | 节制之道</t>
+  </si>
+  <si>
     <t>第三十二章（32）</t>
   </si>
   <si>
     <t>道常无名，朴虽小，天下莫能臣也。侯王若能守之，万物将自宾。天地相合，以降甘露，民莫之令而自均。始制有名，名亦既有，夫亦将知止。知止可以不殆。譬道之在天下，犹川谷之于江海。</t>
   </si>
   <si>
-    <t>大道永远处于一种看不见、摸不着的虚无状态，它好像未加工过的原木一样（朴素而不张扬），虽然微不足道 但是天下没有人能够改变它。王侯如果能够遵循大道，万物将会自然而然地宾服于他（大家才能真正的信任他、支持他）。天之气和地之气就会相互交融，降下甘露一类的美好事物，没有人指使人们该如何做而自然均平安定。人们开始制作各种各样有名称的器物和制度，各种器物和制度出现以后，也应该知道适可而止。知道适可而止（知道边界）就能避免危险。打个比方 大道与天下万物的关系，就好像江海与河川的关系一样。</t>
+    <t>大道永远处于一种看不见、摸不着的虚无状态，它好像未加工过的原木一样（朴素而不张扬），虽然微不足道 但是天下没有人能够改变它。王侯如果能够遵循大道，万物将会自然而然地宾服于他（大家才能真正的信任他、支持他）。天之气和地之气就会相互交融，降下甘露一类的美好事物，没有人指使人们该如何做而自然均平 安定。人类社会自原始状态慢慢出现了文明、制度，各种各样的名称、名分，这制度、名分有它存在的道理，但是一定要知道其作用的边界、限度。知道这些制度、名分的边界，才能没有危险、失败。打个比方 大道与天下万物的关系，就好像江海与河川的关系一样（大江大海，善于处下，不辞小流，故泽被万物，天下归之）。</t>
   </si>
   <si>
     <t>【道——朴实厚道】本章讲道的特点和知止的智慧。道常无名，朴虽小，天下莫能臣：道恒常无名，它的重要属性是朴实厚道；朴像原木，看似微小，却没有任何东西能让它臣服。侯王若能守之，万物将自宾：领导者若能守住朴实厚道，万物自然宾服归附。天地相合，以降甘露，民莫之令而自均：天地阴阳相合降下甘露，没有人命令，雨露自然均匀，治理也应如此自然而然。
 始制有名，名亦既有，夫亦将知止，知止可以不殆：人类社会开始有制度、名分是合理的，但有了名分制度要懂得边界，不能制度崇拜、名分崇拜，做过了头就走向反面；知道适可而止，才能避免危险。譬道之在天下，犹川谷之于江海：道在天下，就像川谷流向江海，是自然归附的过程，不是强迫。译者·韩鹏杰强调，老子反复用重复和强调来突出重要思想，本章的核心就是朴与知止：做事朴实厚道，对制度名分保持克制，知道边界和限度，物极必反，知止不殆。</t>
   </si>
   <si>
+    <t>道经 | 王者之道</t>
+  </si>
+  <si>
     <t>3、1</t>
   </si>
   <si>
@@ -619,6 +661,9 @@
 不失其所者久：不离开自己的归宿才能长久，“所”就是精神家园，物质再发达也不能让精神家园花果飘零。死而不亡者寿：身死而精神不亡，才是真正的长寿，那些思想家的光芒像群星，在黑暗时指引方向。译者·韩鹏杰说，这一章既写给领导者也写给普通人：自知、自胜、知足、强行、守所、精神不亡，六层递进，是中国文化中极高的人生境界。</t>
   </si>
   <si>
+    <t>道经 | 智者之道</t>
+  </si>
+  <si>
     <t>第三十四章（34）</t>
   </si>
   <si>
@@ -632,6 +677,9 @@
 译者·韩鹏杰强调，这一章讲量变质变、从小到大的道理：合抱之木生于毫末，九层之台起于累土，千里之行始于足下；天下难事必作于易，天下大事必作于细。做人做事不要自高自大、好高骛远，要虚怀若谷、脚踏实地，把容易的事当难事做，把小事做好，一步一步成就伟大。</t>
   </si>
   <si>
+    <t>道经 | 伟大之道</t>
+  </si>
+  <si>
     <t>第三十五章（35）</t>
   </si>
   <si>
@@ -643,6 +691,9 @@
   <si>
     <t>【平淡才是真】本章讲守道则天下归往，平淡才是真。执大象，天下往：掌握大道（大象即道），天下人都会归附；往而不害，安平太：归附而不受伤害，安详、平稳、太平。乐与饵，过客止：音乐与美食能让人停下脚步，这些外在享受有吸引力，但也容易让人半途而废，不能沉溺其中。道之出口，淡乎其无味：道说出来淡而无味，不像美食音乐那样刺激；视之不足见，听之不足闻，用之不足既：看不见、听不到，却取之不尽、用之不竭。
 译者·韩鹏杰说，我们日常所用而不知，天天都在用道却不自知；饮食清淡有益健康，人格返璞归真才接近道，清水出芙蓉、天然去雕饰是艺术的高境界。年轻人都觉得自己会成为伟大人物，最后发现伟大来自平凡，把自己看得平凡，才能重归于朴、重归于真、重归于道。真正的力量不是热闹炫耀，而是平淡之中无穷无尽。</t>
+  </si>
+  <si>
+    <t>道经</t>
   </si>
   <si>
     <t>第三十六章（36）</t>
@@ -3163,10 +3214,10 @@
         <v>118</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" ht="187.2" spans="1:7">
@@ -3174,19 +3225,19 @@
         <v>20</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="G22" s="11">
         <v>6</v>
@@ -3197,22 +3248,22 @@
         <v>21</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" ht="187.2" spans="1:7">
@@ -3220,22 +3271,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" ht="158.4" spans="1:7">
@@ -3243,19 +3294,19 @@
         <v>23</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="G25" s="11"/>
     </row>
@@ -3264,19 +3315,19 @@
         <v>24</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="G26" s="11">
         <v>2</v>
@@ -3287,19 +3338,19 @@
         <v>25</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="G27" s="11">
         <v>1</v>
@@ -3310,19 +3361,19 @@
         <v>26</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="G28" s="11">
         <v>15</v>
@@ -3333,19 +3384,19 @@
         <v>27</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>113</v>
+        <v>162</v>
       </c>
       <c r="G29" s="11"/>
     </row>
@@ -3354,19 +3405,19 @@
         <v>28</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>113</v>
+        <v>167</v>
       </c>
       <c r="G30" s="11">
         <v>22</v>
@@ -3377,19 +3428,19 @@
         <v>29</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>113</v>
+        <v>172</v>
       </c>
       <c r="G31" s="11"/>
     </row>
@@ -3398,19 +3449,19 @@
         <v>30</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>113</v>
+        <v>177</v>
       </c>
       <c r="G32" s="11">
         <v>31</v>
@@ -3421,19 +3472,19 @@
         <v>31</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>113</v>
+        <v>182</v>
       </c>
       <c r="G33" s="11">
         <v>30</v>
@@ -3444,22 +3495,22 @@
         <v>32</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>113</v>
+        <v>187</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
     </row>
     <row r="35" ht="172.8" spans="1:7">
@@ -3467,19 +3518,19 @@
         <v>33</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>113</v>
+        <v>193</v>
       </c>
       <c r="G35" s="11"/>
     </row>
@@ -3488,19 +3539,19 @@
         <v>34</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>113</v>
+        <v>198</v>
       </c>
       <c r="G36" s="11">
         <v>2</v>
@@ -3511,19 +3562,19 @@
         <v>35</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>113</v>
+        <v>203</v>
       </c>
       <c r="G37" s="11">
         <v>12</v>
@@ -3534,19 +3585,19 @@
         <v>36</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>113</v>
+        <v>203</v>
       </c>
       <c r="G38" s="11">
         <v>2</v>
@@ -3557,19 +3608,19 @@
         <v>37</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>113</v>
+        <v>203</v>
       </c>
       <c r="G39" s="11"/>
     </row>
@@ -3578,19 +3629,19 @@
         <v>38</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G40" s="11"/>
     </row>
@@ -3599,19 +3650,19 @@
         <v>39</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G41" s="11">
         <v>2</v>
@@ -3622,19 +3673,19 @@
         <v>40</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G42" s="11"/>
     </row>
@@ -3643,19 +3694,19 @@
         <v>41</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G43" s="11"/>
     </row>
@@ -3664,22 +3715,22 @@
         <v>42</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
     </row>
     <row r="45" ht="409.5" spans="1:7">
@@ -3687,19 +3738,19 @@
         <v>43</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G45" s="11"/>
     </row>
@@ -3708,19 +3759,19 @@
         <v>44</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G46" s="11"/>
     </row>
@@ -3729,19 +3780,19 @@
         <v>45</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G47" s="11"/>
     </row>
@@ -3750,19 +3801,19 @@
         <v>46</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G48" s="11"/>
     </row>
@@ -3771,19 +3822,19 @@
         <v>47</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G49" s="11"/>
     </row>
@@ -3792,19 +3843,19 @@
         <v>48</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G50" s="11"/>
     </row>
@@ -3813,19 +3864,19 @@
         <v>49</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G51" s="11"/>
     </row>
@@ -3834,19 +3885,19 @@
         <v>50</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G52" s="11"/>
     </row>
@@ -3855,19 +3906,19 @@
         <v>51</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G53" s="11"/>
     </row>
@@ -3876,19 +3927,19 @@
         <v>52</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G54" s="11">
         <v>6</v>
@@ -3899,19 +3950,19 @@
         <v>53</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G55" s="11"/>
     </row>
@@ -3920,19 +3971,19 @@
         <v>54</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G56" s="11"/>
     </row>
@@ -3941,19 +3992,19 @@
         <v>55</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G57" s="11"/>
     </row>
@@ -3962,19 +4013,19 @@
         <v>56</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G58" s="11"/>
     </row>
@@ -3983,22 +4034,22 @@
         <v>57</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
     </row>
     <row r="60" ht="409.5" spans="1:7">
@@ -4006,19 +4057,19 @@
         <v>58</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G60" s="11"/>
     </row>
@@ -4027,19 +4078,19 @@
         <v>59</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G61" s="11"/>
     </row>
@@ -4048,19 +4099,19 @@
         <v>60</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G62" s="11"/>
     </row>
@@ -4069,19 +4120,19 @@
         <v>61</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G63" s="11"/>
     </row>
@@ -4090,19 +4141,19 @@
         <v>62</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G64" s="11"/>
     </row>
@@ -4111,22 +4162,22 @@
         <v>63</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
     </row>
     <row r="66" ht="409.5" spans="1:7">
@@ -4134,19 +4185,19 @@
         <v>64</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G66" s="11">
         <v>63</v>
@@ -4157,19 +4208,19 @@
         <v>65</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G67" s="11"/>
     </row>
@@ -4178,22 +4229,22 @@
         <v>66</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" ht="409.5" spans="1:7">
@@ -4201,19 +4252,19 @@
         <v>67</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G69" s="11"/>
     </row>
@@ -4222,19 +4273,19 @@
         <v>68</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G70" s="11"/>
     </row>
@@ -4243,19 +4294,19 @@
         <v>69</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G71" s="11">
         <v>17</v>
@@ -4266,19 +4317,19 @@
         <v>70</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G72" s="11"/>
     </row>
@@ -4287,22 +4338,22 @@
         <v>71</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
     </row>
     <row r="74" ht="374.4" spans="1:7">
@@ -4310,19 +4361,19 @@
         <v>72</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G74" s="11"/>
     </row>
@@ -4331,19 +4382,19 @@
         <v>73</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G75" s="11"/>
     </row>
@@ -4352,19 +4403,19 @@
         <v>74</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G76" s="11"/>
     </row>
@@ -4373,19 +4424,19 @@
         <v>75</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G77" s="11">
         <v>10</v>
@@ -4396,19 +4447,19 @@
         <v>76</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G78" s="11"/>
     </row>
@@ -4417,19 +4468,19 @@
         <v>77</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G79" s="11"/>
     </row>
@@ -4438,22 +4489,22 @@
         <v>78</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
     </row>
     <row r="81" ht="409.5" spans="1:7">
@@ -4461,19 +4512,19 @@
         <v>79</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G81" s="11"/>
     </row>
@@ -4482,19 +4533,19 @@
         <v>80</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G82" s="11"/>
     </row>
@@ -4503,19 +4554,19 @@
         <v>81</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="G83" s="11">
         <v>7</v>
@@ -4573,19 +4624,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="G2" s="3"/>
     </row>
@@ -4594,19 +4645,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="G3" s="4"/>
     </row>
@@ -4615,19 +4666,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>387</v>
+        <v>404</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>389</v>
+        <v>406</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -4636,19 +4687,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>390</v>
+        <v>407</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>391</v>
+        <v>408</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="G5" s="4"/>
     </row>
@@ -4657,19 +4708,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>396</v>
+        <v>413</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>397</v>
+        <v>414</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="G6" s="4"/>
     </row>
@@ -4678,19 +4729,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -4699,19 +4750,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -4720,19 +4771,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="G9" s="4"/>
     </row>
@@ -4741,19 +4792,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="G10" s="4"/>
     </row>
@@ -4762,19 +4813,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="G11" s="4"/>
     </row>
@@ -4783,19 +4834,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>426</v>
+        <v>443</v>
       </c>
       <c r="G12" s="4"/>
     </row>
@@ -4804,19 +4855,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
       <c r="G13" s="4"/>
     </row>
@@ -4825,19 +4876,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>436</v>
+        <v>453</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -4846,19 +4897,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="G15" s="4"/>
     </row>
@@ -4867,19 +4918,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>445</v>
+        <v>462</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="G16" s="4"/>
     </row>
@@ -4888,19 +4939,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>447</v>
+        <v>464</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="G17" s="4"/>
     </row>
@@ -4909,19 +4960,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>450</v>
+        <v>467</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>451</v>
+        <v>468</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="G18" s="4"/>
     </row>
@@ -4930,19 +4981,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>455</v>
+        <v>472</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>456</v>
+        <v>473</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="G19" s="4"/>
     </row>
@@ -4951,19 +5002,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>458</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>441</v>
       </c>
       <c r="G20" s="4"/>
     </row>
@@ -4972,19 +5023,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>462</v>
+        <v>479</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>463</v>
+        <v>480</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>465</v>
+        <v>482</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="G21" s="4"/>
     </row>
@@ -4993,19 +5044,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>468</v>
+        <v>485</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="G22" s="4"/>
     </row>
@@ -5014,19 +5065,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="G23" s="4"/>
     </row>
@@ -5035,19 +5086,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="G24" s="4"/>
     </row>
@@ -5056,19 +5107,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>480</v>
+        <v>497</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="G25" s="4"/>
     </row>
@@ -5077,19 +5128,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>483</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>466</v>
       </c>
       <c r="G26" s="4"/>
     </row>
@@ -5098,19 +5149,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="G27" s="4"/>
     </row>
@@ -5119,19 +5170,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>492</v>
+        <v>509</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>494</v>
+        <v>511</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="G28" s="4"/>
     </row>

--- a/book.xlsx
+++ b/book.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19644" windowHeight="7620"/>
+    <workbookView windowWidth="19860" windowHeight="10584"/>
   </bookViews>
   <sheets>
     <sheet name="道德经" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="523">
   <si>
     <t>no</t>
   </si>
@@ -533,6 +533,9 @@
     <t>道经 | 循环之道</t>
   </si>
   <si>
+    <t>1、45</t>
+  </si>
+  <si>
     <t>第二十六章（26）</t>
   </si>
   <si>
@@ -693,7 +696,7 @@
 译者·韩鹏杰说，我们日常所用而不知，天天都在用道却不自知；饮食清淡有益健康，人格返璞归真才接近道，清水出芙蓉、天然去雕饰是艺术的高境界。年轻人都觉得自己会成为伟大人物，最后发现伟大来自平凡，把自己看得平凡，才能重归于朴、重归于真、重归于道。真正的力量不是热闹炫耀，而是平淡之中无穷无尽。</t>
   </si>
   <si>
-    <t>道经</t>
+    <t>道经 | 平凡之道</t>
   </si>
   <si>
     <t>第三十六章（36）</t>
@@ -709,6 +712,9 @@
 译者·韩鹏杰用捧杀典故解释：杀君马者道旁儿，过分夸奖、吹捧使人骄傲自满、退步失败，关羽过不了奉承关而败走麦城；两军对垒时老弱残兵挑衅、敌人弃辎重诱敌，都是将欲夺之必固与之。本章不是说用阴谋，而是讲事物转化的规律：看清对立面的运动，力量与边界都要含藏，不能张扬炫耀。</t>
   </si>
   <si>
+    <t>道经 | 谋略之道</t>
+  </si>
+  <si>
     <t>第三十七章（37）</t>
   </si>
   <si>
@@ -731,11 +737,11 @@
     <t>德高的人做了有德的事不自认为有德，所以他才真正具有美德；不是真正崇尚美德的人却处处要表现自己的美德，所以他并不具有美德。真正崇尚美德的人清静无为 是因为他们没有个人功利目的需要多为；不是真正崇尚美德的人碌碌多为 多为是为了达到个人的功利目的；真正崇尚仁的人去做好事 做好事不是为了满足个人私欲；那些非常重视义的人去制定各种规则 制定规则是为了满足个人私心；那些非常重视礼的人去推行礼仪，如果没有人响应 他就会卷起袖子强迫别人遵从。因此说失去了道而后才去提倡德，失去了德而后才去提倡仁，失去了仁而后才去提倡义，失去了义而后才去提倡礼。礼仪，是忠信不足的标志 是祸乱的开始。那些超越时代的思想主张，站在道的角度来看 属于华而不实的东西，是愚昧的开始。因此大丈夫要笃守忠信，排除虚礼；要遵循规律，不要提倡超越时代的思想主张。所以要舍弃虚礼和超越时代的思想主张 笃守大道。</t>
   </si>
   <si>
-    <t>本章开启《德经》，讲真正的德是自然无心的。上德不德，是以有德：真正有德的人不把德行当回事，做了好事自然忘掉，反而真有德；下德不失德，是以无德：境界不高的人总怕德行失去，处处表现、宣扬，反而无德。上德无为而无以为：有德者自然作为，没有功利目的；下德为之而有以为：无德者做事带着目的。上仁为之而无以为：仁者做好事不为私欲；上义为之而有以为：讲义的人制定规则，多少带着私心；上礼为之而莫之应，则攘臂而扔之：讲礼的人若没人响应，就卷起袖子强推。
+    <t>【道德仁义礼】本章开启《德经》，讲真正的德是自然无心的。上德不德，是以有德：真正有德的人不把德行当回事，做了好事自然忘掉，反而真有德；下德不失德，是以无德：境界不高的人总怕德行失去，处处表现、宣扬，反而无德。上德无为而无以为：有德者自然作为，没有功利目的；下德为之而有以为：无德者做事带着目的。上仁为之而无以为：仁者做好事不为私欲；上义为之而有以为：讲义的人制定规则，多少带着私心；上礼为之而莫之应，则攘臂而扔之：讲礼的人若没人响应，就卷起袖子强推。
 失道而后德，失德而后仁，失仁而后义，失义而后礼：道、德、仁、义、礼逐层下降。夫礼者，忠信之薄而乱之首：礼是忠信稀薄、祸乱开始的标志。前识者，道之华而愚之始：自诩能预知未来的人，只是道的浮华外表，是愚昧的开始。是以大丈夫处其厚，不居其薄；处其实，不居其华：大丈夫要居厚实、弃浮华，去彼取此。译者·韩鹏杰说，上德不德也是相反相成思维：越在意形式越失去内容。</t>
   </si>
   <si>
-    <t>德经</t>
+    <t>德经 | 成功之道</t>
   </si>
   <si>
     <t>第三十九章（39）</t>
@@ -751,19 +757,28 @@
 是以侯王自谓孤、寡、不穀：侯王自称孤、寡、不穀，正是以贱为本、以下为基。致数舆无舆：刻意追求众多荣誉反而失去荣誉。是故不欲琭琭如玉，珞珞如石：不要像华美的玉，要像坚硬的石头，石头能铺路济人，华美的玉看似高贵却少有用处。译者·韩鹏杰强调两个重点：一是“一”即道，是阴阳统一；二是“贵以贱为本，高以下为基”，位置越高越要善于处下，把根基打牢，做人要处实不居华。</t>
   </si>
   <si>
+    <t>德经 | 根本之道</t>
+  </si>
+  <si>
     <t>第四十章（40）</t>
   </si>
   <si>
     <t>反者道之动。弱者道之用。天下万物生于有，有生于无。</t>
   </si>
   <si>
-    <t>万物在大道的支配下向相反的方向发展，大道的作用就在于它能够提醒万物保持柔弱的状态。天下万物产生于某种物质，而物质产生于空间。（有和无是天下万物生成的根源）</t>
+    <t>万物在大道的支配下向相反的方向发展。大道的作用就在于它能够提醒万物保持柔弱的状态。天下万物产生于某种物质，而物质产生于空间。（有和无是天下万物生成的根源）</t>
   </si>
   <si>
     <t>本章只有三句话，却是全书思维总纲。反者道之动：道向相反的方向运动，事物发展到极点就走向反面，又终而复返，回到更高层次的本根。所以看问题不能只站在自己的角度，要换位思考、正反合地看：正面看、反面看、合起来看，才能全面。弱者道之用：道的作用体现在柔弱一面，大家都逞强，柔弱反被强调，这是阴阳统一的思维方式。天下万物生于有，有生于无：万物产生于有，有产生于无；任何事物都有有和无两个方面，有让我们观察边界，无让我们观察妙处。
 译者·韩鹏杰强调，如果只看到有形东西的作用，忽略无形东西的作用，物质世界越发达，精神家园就越花果飘零；既要看到物质财富，更要看到精神、信仰、理论这些无形力量。前三章讲道，第四十章用三句话总结全书思维方式，后边各章都是它的展开和例证。</t>
   </si>
   <si>
+    <t>德经 | 变化之道</t>
+  </si>
+  <si>
+    <t>2、25</t>
+  </si>
+  <si>
     <t>第四十一章（41）</t>
   </si>
   <si>
@@ -776,18 +791,24 @@
     <t>前边《德经》的部分我们讲了第三十八章，“上德不德，是以有德，下德不失德，是以无德。”讲了第三十九章，第三十九章第一个重要的概念是“一”。我再重申一遍，是阴阳两者的统一，也就是道。第三十九章里边的重点词，我们要不断地重申、重复，以求达到大家的记忆。“贵以贱为本，高以下为基。”第四十章我们极为看重。因为这一章开头五个字，是整个这一本书里思维的总纲：“反者，道之动”，下边是它的具体的体现，“弱者，道之用。天下万物生于有，生于无。”现在我们具体来讲第四十一章，这一章内容也非常丰富。首先我们在前边就强调过，《道德经》是对面有人问问题，老子给予的回答。现在对面有人问关于“士”的问题了。“士”这个阶层，把它理解为做官的阶层也可以，“士”这个概念，它的原意就是做事。延伸意指的是一个领导阶层。推十为一嘛，十个人里边推举出来一个领导大家，服务大家，管理大家。所以有人问老子，你看这些士，怎么来判断他们境界的高低呢？水平的高低呢？老子也是拿道来评价的。所以在这一章里边，一开始老子就讲“上士闻道，勤而行之”，境界高的、水平高的士这个阶层这些人，听到了道，比如说他的领导者讲的话，他觉得有道，有道理，“勤而行之”，就是执行力最强，坚定不移地按照它去做。有问题呢？自己勤勉、勤奋地把它解决，“勤而行之”，知行合一了嘛。知道了就按照道去做。中等境界的是什么呢？“中士闻道，若存若亡”，将信将疑。也想去按照道去做，但是一遇到事了就怀疑了。“若存若亡”，将信将疑，迟迟疑疑，犹犹豫豫，执行力不够。“下士闻道，大笑之”。境界最低的、最差的是干吗呢？嘲笑。人家说什么，制定什么样的制度规则，他都嘲笑，讲什么他都觉得不对，但是又提不出建设性意见，什么叫建设性意见？你觉得人家这个不好，你有没有更好的方案？觉得有问题，客观地指出来、提出来怎么改进，不是为了嘲笑而嘲笑，不是为了讽刺而讽刺。我觉得现在很多语言类的节目只是为了讽刺别人，讲话的时候只是为了打击别人，没有其他什么善良的目的。所以这就属于“大笑之”。别人给他讲道理，他还在那嘲笑，甚至羞辱人家。当然对这个事老子是想得开的。告诉坐在对面问他问题的人，怎么接待这些人，对待这些问题。别当回事，不笑不足以为道。这个世界现在已经没有哪件事是大家都赞成的了，所以有人嘲笑这是正常的。你要跟这些人计较，那就把自己的生命全都浪费了。说到这儿我就得插一句话，我觉得这个境界的差别，格局的差别，心胸的差别在什么地方呢？就在对待攻击者的身上。你看孟子也是我们文化里非常不得了的一个人，但是你看孟子的书里，会有一个什么感觉呢？年轻人，气势太盛。孟子对待当时的一些学术大咖，比如说墨子，比如说杨朱，当时杨墨是显学，名气很大。孟子怎么来评价他们呢？孟子就说墨子这个人讲“兼爱，是无父也”。兼爱嘛，你都平等，没有差别嘛，你置于你父亲于何地？没有把你父亲凸显出来，没有把对父亲的爱突出出来，无父也。杨朱不是讲，“拔一毛而利天下，吾不为也”。大家不要误解这句话，它的原意是你拿天下来换我的身体，让我损害自己的生命去换天下，我不干。它是强调自己的生命的重要。“拔一毛而利天下，吾不为也”。杨朱讲“为我”，所以孟子骂他是无君。你老为自己，你把君置于何地？“无父无君是禽兽也”——他骂杨朱和墨子两个人是禽兽。反过来看老子对待这些人的态度是——“不笑不足以为道”，淡然一笑，过了——很值得人佩服的一种态度。这就叫“明月清风”。对待别人的嘲讽，对待别人的攻击，有这样一个态度，也是很不得了的一种智慧与境界。这一段是本章里边的核心。因为我觉得他上中下的这种区分非常明了，很实用。“上士闻道，勤而行之”。坐而论道，不如起来行嘛。大家看道字的写法，首是头脑、思维、想。“走”之旁是行。所以这个道本身就是一个知行统一的概念。“上士闻道，勤而行之。中士闻道，若存若亡。”犹犹豫豫，不坚定，不能够坚定坚持的按照道去做。“下士闻道，大笑之。”我们千万不要做这种老是嘲笑别人，讽刺别人的，否则就会落于下乘，不笑不足以为道，太好了。明月清风一般地对待这种嘲讽辱骂的这种态度。下面这一段开头这句话非常有意思，叫“建言有之”，“建言”就是我们说的常言。常言说得好，这是我们经常用的，所以下面这句话大家注意，不是他本人的话。就是告诉大家了，明确下边讲的很多都是常言，在当时就是一句俗语。他讲的这些道理都是什么呢？都是前边我们讲的“反者，道之动”的例证。所以我在前面给大家说，第四十章是全书的总纲，可以举的例证会无限多，下边都是。“明道若昧”，光明的道路好像是昏暗不明的。为什么？有些给你指出的光明大道说得多么多么得好，指出光明大道简直就是美得不得了，你要小心了，前面有陷阱。真正的大道，反而像是昏暗不明的，就是把路上的艰险，遇到的阻碍，遇到的问题，都给你说清楚，让你看得清楚，这才是明道。给你说这条路没问题，太直了，平坦了，你沿着这条路走，肯定光明无限；沿着这条路走，肯定兴旺发达，一点阻碍都不会有，这个事绝对没问题。坏事了，这个时候你就得小心了。要知道“明道若昧”。再举个关于“朋友”的例子说明这个问题。朋友有三类，友直，友谅，友多闻。第一类的朋友直率，你有问题给你直接指出来。你走的道有问题的时候直接告诉你，跟你讲，怕你犯错误，怕你在这个地方出现问题。不是你的朋友呢？你走在道上遇到什么问题与他有什么关系啊，你问他这条道怎么样？他就告诉你，好好好，走走走，这条路没有任何问题。你给我提点建议，没什么建议，走就是了。你掉到坑里边他管你呀！所以我们说这“明道若昧”，暗昧，昏暗不明。“进道若退”。我们有的时候自己老觉得自己进步太小，人有时候都不免太着急，老觉得“一万年太久，只争朝夕”。只争朝夕，我每天都得进步，我都得看到自己的进步，一感觉到自己没有进步，就着急了。其实你别忘了，人呢，走在路上没有直线的，“进道若退”，有时候我们感觉是退步的时候，其实我们是在进步。比如说练书法，大家都有这个感觉，刚练这几天觉得进步很大，我以后每天按照这个速度会很快成为书法大家，过一段时间感觉怎么回事？怎么我这字越写越差了，还不如开始呢。好多事情开始都是这样。其实这就是我们前进中的一个必然的现象。懂得以退为进，懂得退就是进，有时候退不就是进嘛。“进道若退”，这不就是相反相成嘛。所以我在想，在老子那个时代，你说这些常言都在。这得说中国古代的这些人的哲学的思维水平竟然达到这样一个高度。所以有的时候我们做的事情感觉退步的时候不要着急，退是前进中的必须经历的。就像我们经常讲一个词叫“能屈能伸”，想要伸不得先屈回来吗？这是不是退？退之后才更加有力量，进道若退。“夷道若颣”，颣就是不平，夷就是平，夷道就是平坦的路。真正平坦的路像什么？它是不平的，高低起伏的。为什么？开车人都有一个体会，你说开车的路太平坦了，这就很容易放松警惕了，感觉无聊疲惫了，就很容易出事。假如前边一会儿出现一点坡，则高度警惕，有的不是故意把道做得有坡嘛，这才是平坦的道。所以我们经常讲的一句话叫“曲折是一种常态”，平坦的大道里边有这样的一些坡，不平的地方，这才是真正的大道。它告诉我们的道理就是，其实我们走在路上不会是绝对平坦的。对路上遇到的这些，我们要有高度的戒备和警惕，这样才属于真正的夷道，也就是平坦的大道。“夷道若颣”，又是一个“反者，道之动”，相反相成。“上德若谷”，谷就是无穷无尽。我们经常讲不是虚怀若谷嘛，真正有“上德”的这些表现是什么？就像虚怀若谷。比如说谦虚，听得进别人的意见，比如说做了好的事情，自己把它像山谷里的风一样，过而无形，“上德若谷”，就是讲它“满招损，谦受益”，不自满，做了事情不居功自傲，“上德若谷”。“大白若辱”，“白”，我们在第二十八章讲过，知白守黑，那个时候给大家说过白，白就是内心的光明信念与远大的抱负，内心有光明、信念和远大的抱负，那他就能忍受很多的屈辱。为什么？能屈能伸嘛，有远大的抱负，那么这些羞辱也就不必被自己挂在心中了。知白守黑，内心有光明、信念和远大的抱负，才能守得住这个黑。不管是别人黑，还是有时候的这种自黑，这就是“大白若辱”。说一事，有一次我在云南楚雄给医生讲课。我说你们穿着白大褂，大家把你们叫“白衣天使”，那对病人偶尔几句话不合适的话，也应该不那么太在意了。因为“知其白，守其黑”，忍得屈辱、羞辱，吞得下委屈，也就扩大了格局。“广德若不足”，“广”当然是大的意思。越是有广博的、大的德的人，反而好像自己有缺陷，不足就是不满，满招损，谦受益嘛。知道自己有不足，大成若缺，才能不断地进步，不断地学习，不断地努力，提高自己的境界，让自己的德行更伟大、更广博，“广德若不足”。下面这四个字理解起来不太容易，叫“建德若偷”。这个“偷”字是大家不喜欢的，怎么能跟德并列到一块呢？说到一起呢？首先我们说这个“建德”是什么意思？刚健。刚健的德好像是软弱的样子。这不就又符合“反者，道之动”了吗？偷，懒惰、懈怠、疲软，有着刚健的德的人，他反而正好有的时候表现为他的反面，而不是说我认为自己有这种刚健的德，谁要惹到我了，我一定跟他较量到底，我一定坚咬不放。这其实反而不是刚健的德，也不是强的真正的表现。刚健的德往往表现出宽容，忍让，甚至软、弱、懈怠等，“建德若偷”。当然有人也把这个“偷”解释为偷偷摸摸，意思就是不去表现。这个也说得过去。“质真若渝”，这个“渝”和我们讲的“瑕不掩瑜”意思相似，真的东西不会是完美无缺的。“大方无隅”，最大的方是没有棱角的，没有棱角那不就成了圆了吗？所以我们经常讲“外圆而内方”。“大方无隅”，没有角落，不留死角，这才是真正的大方。其实再说一遍，大家仔细想，这大方已经变成圆了，因为咱们中国人对这个圆的印象非常好。所以老用圆满这样的词来形容一个好的事情。进而言之，人有了这个原则是对的，但是这个原则不是老去像割伤别人，外面是圆的，可以和外界相衔接。而内部方的，坚守自己的原则，所以这叫大方无隅。“大器晚成”，最大的器件最晚做成。这个很好，提醒我们不用着急。想终成大器吗？那就要踏踏实实，不断地努力，不断地学习，机会总是留给有准备的人。心智不成熟的时候，早出名并没有什么太大的好处。因为人早出名，心智不成熟，他一定就气锐，盛气凌人，盛气凌人则敛怨。就会得到很多来自各方很多的这种怨言，而这个就形成自己未来的一种发展的阻碍。所以古人讲，松柏必经岁寒之后，可从栋梁之任。你看松树、柏树经历一次又一次的寒暑的磨练，最后才可成为栋梁之材。人类历史上大器晚成的例子比比皆是，比如，姜子牙八十岁为相。历史上记载了很多人，都是在有准备的情况下遇到机会，把以前自己积累的经验、智慧，充分地发扬出来，终成大器，人生最坏的结局也不过是大器晚成，又有什么可着急，可焦虑的呢？“大音希声”，“希”不是没有。这个“希”大家可以从两个角度来理解，一个“希”是前面有声，而中间出现的停顿，比如，白居易的《琵琶行》，“别有幽愁暗恨生，此时无声胜有声。”前面有声，可是这个地方的停顿，它反而蕴含了更加丰富的内容，用有声表达不出来的这种情感，这是一个希声。“希声”还有一个表现是乐曲结束，声音之后的余响。苏轼的《前赤壁赋》里边叫“余音袅袅，不绝如缕”。这一个也是“大音希声”。《道德经》里面讲的“大音希声”的道理，其实它是有延伸的。一个是说我们的语言。第五章里边讲“多言数穷，不如守中。”发号施令多了，话多了，声多了，唠叨多了，就不起作用了。真正的大音呢，一定是平常少讲，关键时候掷地有声，说得恰到好处——大音希声。一个是说我们的制度。制度太繁琐了，反而它走向了负面，恰到好处就好。“大象无形”，这个在我们前边讲的时候也经常引用。“大象”本来就很大了，反正中国人一开始指的这个“象”，也是拿这个“大象”说事，本来就很大的。当然这个“象”是一个延伸。最大的形象是没有形状的。天有形状吗？风有形状吗？精神有形状吗？理论有形状吗？都没有，“大象无形”。虽然无形却力量巨大。所以我们拿风来说大象无形是最恰当的。没有人看见过风，风是没有形状的，我们只能够通过水面的波纹，麦浪的翻滚，柳梢的摇曳，我们知道风是存在的。虽然无形，但是它客观存在的，并且力量无比巨大。所以我们写文章才经常用这样的词，“民风”“党风”“作风”“家风”。风没有形状，但是力量巨大，“大象无形”，就像道一样。拿什么东西来比方这个道最为恰当？那就是风。道就像风一样，你看不见但它无处不在？“大象无形”。前边这些其实都是一些相反相成的例证，尤其是“大白若辱，大器晚成，大音希声，大象无形”，都已经成了我们生活中常用的成语了。就这一章里边的成语，你算算就有多少！咱们也不说这本书别的方面的价值。单说它在让我们了解中国文化中的成语的角度，它的作用就有这么大，而且这些成语直到今天，我们还经常使用，发挥着巨大的作用。所以，我们说文化，“文”就在这儿。你把它变成自己的，化入自己的内心，化入自己的精神世界，就叫“文化”。大象无形，却力量无尽，永远存在。道隐无名，道是没有名的。你没办法定义它的。第二十五章的时候我们就讲“有物混成，先天地生，寂兮寥兮”，“寂”就是无声，“寥”就是无形。它是无形无声的，你没有办法去定义它。道隐无名，它就隐到事物的背后，但是它却是事物的本质。道隐无名，就像风一样，在万事万物的背后你看不见，但它能吹绿万物，它能够摧枯拉朽，作用无比巨大。下边这句话就好理解了，“夫唯道”，也只有道啊，“善贷且成”，“贷”就是帮助，意思是资助万物，贷款给你，不就是资助你嘛？善于帮助万事万物成长、成功。“道”有多伟大，你看不见。“道”也不求回报，但它帮助万事万物成为现在这个样子。本章内容非常深刻。首先，有一个恒定的标准“道”来衡量事物。“士”可以分出上中下：“上士闻道，勤而行之；中士闻道，若存若亡；下士闻道，大笑之。”胸怀宽广的人对待这事情，如清风掠过，淡然一笑。你笑你的我笑我的，你不笑不足以为道。没有哪一件事情非得是全部大家都认可的。做事情按照“道”去走，被人嘲笑，被人嘲讽，这是正常的。内心应该有这样的宽容，有这样的接纳，有这样的态度。所以下边告诉大家，那个时代的一些常言、俗语，作为第四十章“反者，道之动”的例证：“明道若昧，进道若退，夷道若颣，上德若谷，广德若不足”。我把这两个排列在一块，然后再说“大白若辱”“知白守黑”。是说什么羞辱都受不了的人，受到一点羞辱就暴跳如雷的人，甚至只是自以为受到了羞辱就拔拳相向的人，其实就是自以为刚健而事实上是匹夫之勇，往往会“勇于敢则杀”，所以真正刚健的德反而像软弱的一样。真的完美的东西是有瑕疵的一样，即大成若缺。所以要懂得“知白守黑”，“知荣守辱”。这几个成语前边带过了之后，重点强调“大器晚成”——不着急，有准备终成大器，机会终究会有的。“大音希声”，真正的大音不是絮絮叨叨，而要掌握尺度，“多言数穷，不如守中”，“无声胜有声”，所以要懂得无言之教，大音希声。接着，“大象无形。道隐无名，夫唯道善贷且成”。只有“道”才能善贷且成，资助万物，帮助万物成长，帮助万物成功。这一章给人很多的启发，很多的回味。每个人读，都会有不同的感受。随着年龄的增长，我们也会不断获得新的体会。</t>
   </si>
   <si>
+    <t>德经 | 高深之道</t>
+  </si>
+  <si>
     <t>第四十二章（42）</t>
   </si>
   <si>
     <t>道生一，一生二，二生三，三生万物。万物负阴而抱阳，冲气以为和。人之所恶（wù），唯孤寡不穀（gǔ），而王公以为称。故物或损之而益，或益之而损。人之所教，我亦教之。强梁者不得其死，吾将以为教父。</t>
   </si>
   <si>
-    <t>“道”即阴阳二者的统一，“一”中蕴含着阴阳两个方面，阴阳二者参与到一起相互作用形成万事万物。万物背阴而向阳，阴阳二者相互中和形成和谐状态。人人都厌恶的是孤、寡、不穀，但王侯却以此自称。所以有的东西减损它反而得到增加，有的东西增加它反而得到减损。别人教给我的，我也教给别人。喜欢强大暴力的人不得好死，我将把这一原则当作教育人的重要内容。</t>
+    <t>“道”即阴阳二者的统一，“一”中蕴含着阴阳两个方面，阴阳二者生出天、地、人，三者参与到一起相互作用形成万事万物。万物都包含着阴和阳两个对立面，阴阳二者相互中和形成和谐状态。人人都厌恶的，是孤、寡、不穀，但王侯却以此自称。所以有的东西减损它反而得到增加，有的东西增加它反而得到减损。别人教给我的，我也教给别人。喜欢强大暴力的人不得好死，我将把这一原则当作教育人的重要内容。</t>
   </si>
   <si>
     <t>《德经》部分我们今天讲四十二章。老规矩，把以前的这几章我们再顺一下。《德经》从第三十八章开始，第三十八章讲“上德不德，是以有德；下德不失德，是以无德。”第三十九章我们讲了两个重要的部分，一个就是这个“一”，因为第四十二章又出现了这个“一”，就是阴阳两者的相互平衡，形成的统一体。在第三十九章里边有两句话每一次我都要重申一下，以求让大家牢牢地记忆，“贵以贱为本，高以下为基”。第四十章有一个全部这本书思维的总纲，“反者，道之动”。下边举的这些都是“反者，道之动”的一些例证。比如说“弱者，道之用，天下万物生于有，生于无”。第四十一章的时候，我们是花了比较多的时间来说，为什么呢？因为这一章里边有非常多的“反者，道之动”的例证。比如说“大音希声，大象无形，大器晚成……”这些都是我们平时经常讲的成语。上次讲完了大家应该知道了它的出处。那么今天我们讲第四十二章，这一章并不难理解，但是非常的重要。因为这一章开头这段话，大家经常在很多地方看到，比如北京故宫是建筑的典范，故宫的太和、保和、中和三大殿都是三层台基，也就是建在三层高台之上，为什么选择“三”这个数字呢？再比如我所在的学校叫做西安交通大学，在交大的管理学院，我的一个朋友也在那做了一面墙的雕塑：太极，大家有机会到交大管理学院的时候就会看到，就在一楼。这两个地方的解释，用的都是这段话：“道生一，一生二，二生三，三生万物。”我们来解释这段话，原文大家都看到了：“道生一，一生二，二生三，三生万物。万物负阴而抱阳，冲气以为和。”这个“冲”字，读成中，一下就理解了。下面这段话其实大家也耳熟，起码意思在前边已经说过。“人之所恶，为孤寡不穀，而王公以为称。”大家讨厌的孤、寡、不榖，王公却用来称呼自己，这不是我们前面第三十九章的时候已经说过的这个意思嘛。“故物或损之而益，或益之而损。人之所教，我亦教之，强梁者不得其死，吾将以为教父。”这是第四十二章原文。我们一段一段来解释。先说第一段，“道生一”。“一”我们俗称叫太极。其实“一”就是道的具体的特点，强调道就是“一”，是说道的最重要的一个特点，就是它强调阴阳两者的统一，“一”里边蕴含着阴和阳两种力量，两个方面。“道生一，一生二”，这个“一”里边蕴含着“二”，也就是道里边蕴含着阴阳两种力量，两个方面，两种状态。中国人讲，事物都是相互对立而存在的，万事万物归结到最后，它也不会是一个单一的元素。你看咱们中国历史上的《易经》，落到最后就是两个符号，阴和阳。那已经到了事物的极致了，极点了。把阴和阳统一起来叫太极，但是这两个元素是最基本的。所以“一生二”，是说太极道里边蕴涵着阴阳两个方面，两种力量。“二生三”，很多人对这个“二生三”解释得太费劲。“三”是什么？很简单，就是繁体字那个“叁”，就是参。阴阳两者参与到一起，相互作用，形成了万事万物，多简单的事情。它们两者孤阴不生，孤阳不长，两者相互作用，形成万事万物，“三生万物”。所以我们用的那个《中庸》的名言叫“参天地，赞化育”。人能参与到天地之间的运动发展，天地人三才嘛。三才你看人不也参与其中嘛。这个赞可不是赞扬的意思，也是参与的意思。两者参与到一起，产生万事万物，这是从正面。然后再反过来推，既然是三生万物，那么万事万物里边都包含着这两种力量，两个方面，阴阳两个方面，所以叫“万物负阴而抱阳”。随便找，哪一个事物内部都有阴有阳，都包含着阴阳两种状态、两种力量。“万物负阴而抱阳，冲气以为和”。为什么要把这个“冲”念成“中”呢？大家看“冲”的写法，前边这两点其实就代表着阴和阳，那个中就是中和的意思，就是参的意思。阴阳两种力量，中国人把它叫做气，阴气、阳气嘛。通天下一气，形成和谐的、动态的、运动的世界，这就是冲气以为和。这一段讲了我们中国哲学中的宇宙生成模式，也讲了这个世界存在的状态，以及这个状态的原因。这种状态都是阴阳两者运动所形成的，动态的、和谐的状态。冲气以为和。再重复一遍。“道生一，一生二，二生三，三生万物。”所以万事万物都有阴阳两个方面，“万物负阴而抱阳，冲气以为和。”下边就开始讲。用这种思维方式你来理解世界，你就不能只站在一个方面了，明确地告诉你了。事物都是统一的，两个方面不可偏颇，不可偏废。所以对侯王讲，“人之所恶，唯孤寡不穀。”你说大家最讨厌的就是这些词，孤家、寡人、吃不上饭、饿死。可是你看这些王公大人，包括后来的皇帝，他们都拿这个来称呼自己。干嘛呢？“故物，或损之而益，或益之而损。”这个“物”大家不要解释成物质，就是我们中国人常讲的那个“东西”。中国人这个“东西”太奥妙了，什么都可以称之为东西，不管是物质的、精神的都可以称之为东西。所以老子就说你看说到万事万物存在的这些各类各样的东西，“或损之而益”，你以为它受损了，其实它得到了益处。有的时候我们受到一点挫折，我们觉得自己受了多大的这种屈辱一样，可是你知道人都是在不断地受的这种损中逐渐地成长起来的，你认为它是祸，其实它是福，“损之而益”。有的时候你认为自己是得到了，其实反而是一种损失。比如偷了东西的，得到了，其实把人格给损失掉了。有的人用不光彩的手段，不择手段得到的，其实他们损失的反而更大，“或益之而损”。所以老子讲的是相反相成的道理。我们中国人常用什么事情来说这个事？叫破财免灾，叫大难不死必有后福，叫祸福相依，叫塞翁失马焉知非福，你看这讲的都是“损之而益，益之而损”。刚才举的例子不就是这样吗？这侯王王公们不都在损自己吗？把自己叫做“孤寡不穀”。其实有这个提醒之后，反而避免了自己变成孤寡不穀。以前中国人也有这个习惯，给小孩起名起个贱名，好养活。当然现在这种习俗很少再看到了，它讲究的就是“损之而益，益之而损”。民间很多的道理大家也得认真对待，别以为我们上了学之后自己水平就高了，其实真正的高手在民间。很多老人讲的话，到最后你一生体会，反而你发现真的是有道理。“人之所教，我亦教之，强梁者不得其死”。老子也说这些东西，也都是别人教给我的，给我讲的。我再把这些写出来教给大家。这一句我们可得好好地来给大家说道说道。为什么呢？因为这涉及老子的思想的来源，老子的思想来源当然有很多方面，主要的两条，两条道路。一条道路自然就是《易经》。因为你看，《易经》它把这个叫易以道阴阳，老子也讲阴阳，而且这里边的损和益，这不就是《易经》里边的损卦和益卦嘛，损和益这也是《易经》里边经常强调的。另外一个，我觉得这一章里边非常奥妙，一个是讲这阴阳的事情，让我们知道他的思想里边《易经》是中国文化之源，众经之首，损之而益，益之而损。另外一个也表现出他的思想的来源，就是“强梁者不得其死”，这句话也不是老子自己的，它出自《金人铭》。传说黄帝写了六篇铭文，叫《黄帝六铭》。其中有一个是刻在周朝台阶右面立着的金人背后，金人就是青铜做的，这金人的背后有铭文。经过汉朝的刘向《说苑》的考证对比，发现《金人铭》里边的这句话：“强梁者不得其死”。“强梁”就是处处逞强。喜欢暴力的人，最后不会有好的结果。我们讲死得其所，叫得其死，得好死，不得好死，不得其死。强梁者不得其死。说到“强梁”这个词，我想读过《水浒传》的人一定记得，在《水浒传》里边用到“强梁”这个词的时候，是用在了矮脚虎王英的身上。矮脚虎王英，这个是梁山泊里边大家都瞧不上的那么一个人。原来是个车夫，后来抢劫，后来落草。所以用这个词来形容他，“强梁者”。“强梁者不得其死”，老子非常反对强暴，而强调和平、守弱，认为“强梁者不得其死”，“木强则折，兵强则灭”，这是他后边关于这个问题的一个延伸。“吾将以为教父”，这个“教父”就是说，这是别人教给我的，我也把它拿来作为座右铭，来指导我自己。总结一下，大家看这一章，第一段话是我们大家都耳熟能详的，“道生一，一生二，三生万物，万物负阴而抱阳，冲气以为和。”第二段是我们前边讲过的内容，在这个里边又重申了一遍，注意这些重申可不是排版排错了。因为《道德经》里边它讲的几条重要的原则，遇到机会的时候，它就会反复，用重复的方式来强调。“人之所恶，唯孤寡不穀，而王公以为称。”所以对于万事万物而言，对这个世界存在的东西而言，“或损之而益，或益之而损”。有的你觉得是损失了，结果反而是得到了。有的你认为自己得到了，反而是损失掉了。因此不可一概而论。遇到了乐事的时候，不要过于高兴，以免乐极生悲。遇到不好的事，祸事的时候，也不要丧气，因为这些可以成为我们的经验，塞翁失马，焉知非福！这是别人教给我的，我也把它来教给别人。然后下边这句话是老子也非常强调的，“强梁者不得其死”，还是要和平，还是要守弱，处处逞强，总和别人结梁子，最后不会有好的结果。国家也一样，“国虽大，好战必亡”。老子说我也要把这个当作座右铭，这就明显地透露出他思想的来源，一源于《易经》，阴阳之学，损益之论，谦卑之礼。二源于《金人铭》，尤其是《金人铭》里这句话对老子影响是非常大的，所以他把它叫做“教父”，座右铭。</t>
   </si>
   <si>
+    <t>德经 | 玄奥之道</t>
+  </si>
+  <si>
     <t>4、10</t>
   </si>
   <si>
@@ -803,18 +824,24 @@
     <t>我们说“反者，道之动”是整个这本书思维的总纲，也就是说它是一种思维模式、思维方法。第四十章一开头就讲“反者，道之动，弱者，道之用。天下万物生于有，生于无。”这里边出现了两个在《道德经》里边非常重要的字，一个是“弱”，也可以称其为“柔”，另一个就是“无”。第四十三章是对这些内容进一步的引申和展开。第一句“天下之至柔，驰骋于天下之至坚，无有入无间”。最柔弱的东西，反而能够攻克最坚硬的东西。那些没有间隙的地方，无形的东西却能够进入，能攻克。就像风，没有什么地方它进不去的。这些就是“道”，道讲完了。老子开始讲“德”。“吾是以知无为之有益”。我从“至柔驰骋于至坚”，“无有入无间”中知道：人类也是一样，有些事情，无为比有为效果更好——“无为之有益”。可是话说回来，“不言之教，无为之益，天下希及之”按照无为的道理去做事，所获得的好处、益处，天下的人却很少能够知道，很少能够达到。这些话该怎样进一步理解呢？老子在第七十章讲过，“吾言甚易知，甚易行，天下莫能知，莫能行”。什么意思？其实，我讲的道理都是非常简单的、平常。但是大家为什么不知道呢？做不到呢？因为这里边就隔了一个东西——欲望。有些事情大家明知道是这么回事，但是很多东西被欲望牵引就变得难做了。就像我们说“不贪为宝”，但为什么还有那么多人上当？有些人上当了还不好意思说出来。因为自己心里清楚，自己是因为贪心才是上当受骗了嘛。没有这个贪心，很多事情理解起来就太容易，太简单了。但一个骗局，往往能骗很多很多人！再说回来，“天下之至柔，驰骋天下之至坚，无有入无间”。天下的“至柔”是什么？无形是风，有形是水。第七十八章就说，”天下莫柔弱于水，而攻坚强者莫之能胜”。这不是正是“天下之至柔，驰骋天下之至坚”吗？天下什么东西最坚硬，石头？水滴石穿；金属？水刀切可以割金属。有什么坚硬的东西是水它克服不了的呢？风更是弥漫天下，摧枯拉朽，无所不在，力量无尽。你说这个东西没有间隙，但是无形的东西，它反而能够穿透它。现在，科学发现有一些微小的东西，比如说中子、粒子、量子……他们是无形的，你看不见，但没间隙的地方，它们都能够进入。我们眼里没有间隙的地方，对于它们来讲，缝隙简直太大了。“无有入无间”，在强调无的东西的作用。道家的“无为”相当一部分内容在讲“无之为”——这些无形的东西、无用的东西的作为。所以，不要把“无”理解为“没有”，把“无为”理解为“不做事”。“吾不言之教”，第二章讲过“行不言之教”，为什么？身教重于言教，话太多了，老去教化，训导别人，反而会起负面的作用。老师也罢，家长也罢，国家的领导也罢，做一个好的榜样，上行下效。孔子也讲了一句话，叫“君子之德风，小人之德草”。这里小人不是道德上的低下，而是指人民、平民、一般人。榜样的“不言之教”就像风一样，一般人就像草一样。风向哪个方向吹，他们跟随着风而倒。无之为所带来的益处，天下却很少有人能够达到——“希及之”！在讲第三十七章的时候我们说，“道常无为而无不为”，道的规律、规则就是“无为”，而“无为”的效果却是“无不为”——覆盖面更广，效果更好。这不就是“无为之益”吗？一开始讲第一章的时候，我就给大家说过，道家讲的“無”和舞蹈的“舞”字形极为相近。因为对于原始人来讲，舞蹈起到的作用实在太大了。有形的几个姿势，产生出的力量却是巨大的。既然是“无”是“无之为”，那么“无用”，也就是“无用之用”。你认为没用的东西，其实不是它没用，只是你没有看见它的用处。书法有什么用，绘画有什么用？不能当吃，不能当穿，可是如果大家否定了这些，那不就进入了一种狭隘的功利主义的境地了吗？人生最没用的事是什么？睡觉。睡着了什么都做不成。小孩最讨厌睡觉了，可是大家都知道现在有多少人被失眠所折磨，为睡不着觉而痛苦。这些“没用”的事你做不成，那么有用的事你也做不来。最后一句，“无为之益，天下希及之”是老子的感慨。大家老看不到这一点，老觉得无为的事情没用。殊不知你不做这些无为的事，就不能真正的有为。不了解这些无用东西的作用，你也就不知道什么才算是真正的有用。从“反者，道之动”，一直到现在，都在讲述一个道理。</t>
   </si>
   <si>
+    <t>德经 | 空无之道</t>
+  </si>
+  <si>
     <t>第四十四章（44）</t>
   </si>
   <si>
     <t>名与身孰亲？身与货孰多？得与亡孰病？是故甚爱必大费，多藏必厚亡。知足不辱，知止不殆，可以长久。</t>
   </si>
   <si>
-    <t>名声（美名）与身体（生命）哪一个更亲近？生命和财富哪一个更重要？得到名利和失去生命哪一个更有害？所以说过于爱惜必定会有大的耗费/破费，过多的藏货（聚财）必然会导致惨重的损失。所以知道满足就不会遭受屈辱，知道停止就不会遭到危险，这样才能长久平安。</t>
+    <t>名声（美名）与身体（生命）哪一个更亲近？生命和财富哪一个更重要？得到名利和失去生命哪一个更有害？所以说过于爱惜必定会有大的耗费/破费，过多的藏货（聚财）必然会导致惨重的损失。（因此）知道满足就不会遭受屈辱，知道停止就不会遭到危险，这样才能长久平安。</t>
   </si>
   <si>
     <t>前面我们说了第四十三章，最后说“不言之教，无为之益，天下希及之”。然后说这都是前面“反者，道之动”这种思维方式的进一步的延伸和具体的例证。这种方法我们大家已经习惯了，在哲学上叫做“二分法”，叫做“对立的统一”。第四十四章讲的也是这个。一开始先列出来三个对立的事物——名与身、身与货、得与亡，进行比较。“名与身孰亲？”“名”和“身”哪一个更重要？哪一个是对大家来讲是更亲的东西？“身与货孰多？”我们的生命和外在的物质相，财富哪一个更重要？“亲”也罢，“多”也罢，意思都在说哪一个更重要。我们常说“身外之物”，常说名和利生不带来，死不带去。你看，这一章就在解读这个问题了。第三个，“得与亡孰病？”这个好理解，参照我们前面讲的“或损之而益，或益之而损”，是得到的好还是失去的好？哪一个危害更大呢？“病”当然不是什么好词了，“得与亡孰病？”其实在问的时候这个答案已经有了。这就是一种反问的语气，表示强调。因为有的人在名和自己生命的选择之中选择了殉名；有的人，“人为财死，鸟为食亡”——因为财富的事，把自己的生命搭上去了。真的是得到就好，失去就不好吗？比如，我们读像《道德经》这样的书，我们会得到什么？也许什么都没得到，但是我们失去了焦虑，失去了急躁，失去了自高自大，这些东西失去了，那不就是一种得到吗？不是说得到就好，失去就不好。有的东西失去，反而是获得；有些东西得到，反而是真正地失去。三个反问句，答案其实都在里边。下面这几句话，讲得就更深刻了。“甚爱必大费，多藏必厚亡”，对一个东西太珍爱了，最后一定会付出大的代价。比如，有的人他有这种癖好，他喜欢古玩，别人送的别的东西他不要，你拿着古玩一贿赂他就收下来，最后就因为这个自己犯了事儿——“甚爱必大费”。有的人把减肥当作唯一的事业，尝试各种各样靠谱不靠谱的方法，把身体折腾得一塌糊涂，那不就得付出大的代价吗？很多事情都是这样的结果。“甚爱”，太过分了，不是说不好，但是过分了，这就走向了它的反面，物极必反嘛！“多藏必厚亡”，很多东西收敛、搜刮到了，自己把它藏起来，能藏得住吗？最后这个搜刮来的东西一定都成为自己的污点和罪证。多藏必厚亡，“厚”也是大的意思。下边这两句话大家都熟：“知足不辱”。我们知道满足有边界，这样才不会受屈辱。这事我知足，我不卑躬屈膝求别人，我觉得我这个已经很好了，这是我自己奋斗来的，额外的，不择手段得来的东西，我不需要，“知足不辱”。“知止不殆”。这个地方，我得给大家多说几句。老子这个人真的是不得了，他只用一个“走道”的形象，就说清楚了很多问题。我们走在道上，应该注意什么呢？有几个最重要的内容：方向、目标、规则、境界、边界、底线。我们要去什么地方？方向、目标。我们什么时候该停下来呢？只要是道就有边界，道外边往往就是深沟，就是深渊，就是歧路。我们了解边界底线，不贸然地前闯，有“底线思维”，“红线思维”，给我们的欲望划出边界，就是“知足”。知足才能不辱。“知止不殆”，“殆”就是危险失败。知道边界、底线不闯，我们才能没有危险，没有失败。当年杨虎城在陕西把他办公的行园就改名叫“止园”。出处就是这四个字，“知止不殆”。“知足不辱，知止不殆”的意义在哪儿呢？——“可以长久”。其实这些事情不用举太多的例证，为什么？因为例证太多了，不了解边界、底线，冒进、冒险，肯定会导致大的，糟糕的后果。这一章没有什么难以理解的，但是内容也非常深刻，尤其是前边这三个提问或者叫反问，都是我们应该深深思考，并做出回答的。拿我们的生命和名声去交换名利，到底划得来划不来？到底哪个更重要？哪个对我们更亲？身与货和这些财富进行比较的时候，到底哪个更重要？我们拿生命去换财富，回头再拿财富来换健康——有时候，甚至换不回来。“得与亡孰病？”不要认为得到就高兴，失去就不高兴，其实得失就是这样的相反相成。很多事情反而是损之而益，有的是益之而损。祸福相依，相互转化，物极必反。既然物极必反，下面这几句话就好理解了，“甚爱必大费，多藏必厚亡”，因此应该“知足不辱，知止不殆”——知足可以不辱，知止可以不殆。知足、知止，我们才能长久。不管是对于生命，还是对于事业而言，才能稳定致远，长久地发展。这是第四十四章的内容，内容不多，但是我们应该熟记，尤其是几个对偶的句子：“甚爱必大费，多藏必厚亡”；“知足不辱，知止不殆”。</t>
   </si>
   <si>
+    <t>德经 | 生活之道</t>
+  </si>
+  <si>
     <t>第四十五章（45）</t>
   </si>
   <si>
@@ -827,16 +854,22 @@
     <t>我们先来看一下原文，有几个词我们要注意先区分一下。比如说大辩若讷，这个讷呢，我们知道一个词叫做木讷，也就是说，说话不是那么样的流利，不是那么样的辩才无碍。但实际上在这章里，它所要表达的是谨慎，说话严谨、谨慎。为什么要给大家说“讷”这个字呢？大家知道，毛泽东两个女儿，一个叫李敏，一个叫李讷。可是包括中央电视台的广播员都把这个念成nà，其实这个讷，只有一个读音，应该读作nè（讷）。毛泽东两个女儿的名字出自《论语》，“讷于言而敏于行”。先把这个事情给大家说一下，然后我们从头一句一句来解释。“大成若缺，其用不弊。”这个是在讲，完满的东西都仿佛有缺陷。我们平常讲一句话叫完美诚不易。其实这个世界上没有真正完美的东西，任何事物都是有缺点的。了解到这一点，引申到道家的思想，那么这句话想要表达的真正的含义就是，一个越是有大成就的人，他越了解自己的缺点，越觉得自己有缺点，有缺憾。所以，他就不断学习，不断努力，这样的一种动力，它发挥的作用，那么是无穷无尽的。认识到自己有缺点，这样他才能够很好地避免自己的弊端，很好地使自己的缺点得以改正和进步。这个道理在《道德经》里边多处谈到，比如说第七十一章就在讲，“知不知，上；不知知，病”。你知道自己不知道，这个才是水平高的。你不知道自己不知道，这就出问题了，出弊端了。所以大成若缺，其用不弊。一个越是有大成就的人，越懂得应该不断学习，不断进步，不断努力，不断充电。反而是一些有一点小小成就的人，喜欢到处吹嘘，不把旁边人吹得感觉到活不下去，他都不松口。其实遇到这种人，我们根本不用去揭穿他，淡然一笑就可以了。一个越是喜欢自我吹嘘的人，其实越不会有什么大的成就。反之，大成若缺，其用不弊。其实这个道理不止局限于此，我们还可以把这个道理向更深处延展一下。比如说中国人从月圆月缺，领悟出一个道理，其实任何事物发展到到它的极点的时候，它就会向相反的方面转化。人生的最美的境界，花未全开月未圆。花全开了，就往凋零的方向走了，月圆了就往缺的方向走了。所以在临近全圆和全开那时候，才是最美的境界。其实大家注意，我们在生活中经常喜欢用一个词，来对人表示一种赞赏，叫如日中天。其实这个不是一个好的事情。你说人如日中天，不是马上就说他要走下坡路了吗？用道家的这种思想我们来理解。明白在我们生活中讲的很多事情，和这个道理的吻合。大成若缺，其用不弊。“大盈若冲，其用不穷。”“盈”就是满，“大盈”就是大满。“大盈若冲”，“冲”就是冲虚。我们经常讲，用这个冲虚来代表着谦逊谦虚，就像大家看《笑傲江湖》里边的武当的掌门，冲虚道长，大盈若冲。一个越是智慧高的人，智慧聪明的人，他越谦虚，越谦逊。在前面我们曾经说过，“满招损，谦受益”，这话出自《尚书》——中国第一部历史总集。在《尚书》里边有一篇讲到了君臣之间探讨治国的谋略，大禹手下的第二号人物叫伯益。就给他的领导讲了这样的一句话，“满招损，谦受益”，并且伯益还制作了一件警戒器，叫欹器。这个东西非常奥妙，水装满了就颠倒了，倾覆了。装得不满的时候，它稳稳当当。提醒告诫我们这个道理，“满招损，谦受益。”孔子的后半生这个警戒器也一直放在身旁，这么大的一个学问家，还经常提醒自己，“满招损，谦受益”的道理，何况我们。所以“大盈若冲”！一个越是知识充盈的人，知识多的人，越表现得外在的谦逊谦虚，感觉到自己的不足，不断学习，不断努力。“其用不穷”，这样他的知识才能够更好地发挥作用，它的作用无穷无尽，不会出现上边所说的那些弊端，其用不穷。这都是相反相成的道理，按照这个道理我们再解释下边的内容，就比较容易了。“大直若屈，大巧若拙。”一个越是正直的人，越是有正直的、高尚的境界的人，反而外在表现得都比较随和，对很多的事情不那么喜欢争锋，对很多的事情都能够宽容。若屈并不是真的屈枉，他只是懂得外圆而内方，用这种方式和外面的人相处、相衔接，“大直若屈”。关于“大巧若拙，”这个我们得多说几句，在第二十五章里我们讲过，“大曰逝，逝曰远，远曰反”，这是一个逐步发展的过程。就像中国的艺术品一样，一开始没有技巧，后来学到了很多技巧。真正达到一个更高的境界的时候，反而把这些技巧忘掉了，返璞归真。中国雕塑的最高的境界是什么呢？有机会大家到汉武帝的陵墓——茂陵看一看，就会有所体会。那儿被认为是中国雕塑的顶峰。可是大家进去一看却发现非常奇怪，汉代的雕塑几乎一件精巧的东西都没有，都是那样的笨拙、朴拙。特别是霍去病墓前的《马踏匈奴》，那简直笨拙到了极点。团块、圆雕。可是那是中国象征雕塑的顶峰，正因为它这个拙，反而体现出大气势、大气象、大境界，“大巧若拙。”中国诗歌的最高境界是什么呢？清水出芙蓉，天然去雕饰，自然而然，返璞归真。中国书法的最高境界是什么呢？大的书法家最后写得越来越笨拙，越来越稚拙，反而开拓出一片新的气象。我读过一本书法书，是凌云超先生的《中国五千年书法史》。凌云超先生讲到这样一件事，他说中国的书法到后来写得越来越精巧，越来越美，但是像小家碧玉。而中国早期的书法，比如说石鼓文、金文，如旷野风月，给人一种大开大合的气象，这当然是我们在欣赏过程中感觉到的。越是这种稚拙、朴拙、笨拙，反而给人带来更强烈的一种审美的气势和感觉，崇高的一种味道。所以“大巧若拙”。其实《道德经》里边主要讲的并不只是这些，主要说的是人格。一个人格发展到一种高点的时候，他就达到了一种自然而然，返璞归真，忘记了那些小的技巧，心眼、套路，回归到一种真正的高尚的人格的境界。“大巧若拙”，返璞归真，自然而然，明月清风。这是我们说“大巧若拙”。“大辩若讷”。“讷”字我们前面解释过了，这个意思也就非常清楚。真正辩才高的人，他出语反而非常谨慎，让人感觉到仿佛他语言不是那么样的流畅，辩才无碍。其实他不只是为了用语言和人争锋，用语言和人争辩，出语谨慎，这也是我们讲的道家思想里边的一个重要的方面，这样的人才是真正有大的这种辩才的人，“大辩若讷”。下边这几句话原文上就有争论了。我们按照原文先解释一下。“躁胜寒，静胜热”。这个“躁”，表面上意思是急躁，燥热，实际上在讲的是运动。运动可以战胜寒冷。“静胜热”是说冷静可以战胜昏热。因为比如说我们夏天的时候用冰镇，这个方式可以解暑，战胜暑热，但这个地方要讲的实际上是内心的这样的一种冷静，可以战胜我们头脑发热，“静胜热”。但有的人也认为，其实这句话应该是静胜躁，寒胜热。这样和原文连接起来就更顺了，我倒是同意这样的一种说法。因为比如说我们夏天的时候用冰镇，这个方式可以解暑，战胜暑热，所比喻的也是冷静下来时才能战胜头脑发热，而且句式更为对称。现在很多本子也这样做了这样的一种改动。我觉得这个说法更为成立。总之都是讲，内心冷静、宁静、安静，它可以战胜我们的急躁。如果我们能够保持内心的宁静、安静、冷静，这样就可以战胜我们的浮躁、急躁、暴躁、狂躁，宁静以致远，这个和原文意思比较吻合。寒胜热，也是这样一个意思的表现，就像我们刚才说的，一个人冷静下来，可以战胜头脑发热，万物静观犹自得，我们冷静下来才能看清事物的本来面貌，冷静下来才能找到解决问题的正确方法。所以这六个字，大家不妨把它理解为静胜躁，寒胜热。这样后边这句话就自然而然地引申出来了，“清静为天下正”。我们保持内心的清静，一个王者、统治者、领导者保持内心的清静，这样才能够引导天下走上正道。“我好静而民自正”，“清静为天下正”，让内心的清静、冷静、宁静，又具备这样的一种修养。这才能够引导天下走向正道。这个是天下最正的一种领导的方式方法，也是我们修养的由内圣而外王的一种正确的修养的方式方法。</t>
   </si>
   <si>
+    <t>德经 | 事业之道</t>
+  </si>
+  <si>
     <t>第四十六章（46）</t>
   </si>
   <si>
     <t>天下有道，却走马以粪；天下无道，戎马生于郊。祸莫大于不知足，咎（jiù）莫大于欲得。故知足之足，常足矣。</t>
   </si>
   <si>
-    <t>国家的政治措施如果符合大道，那么连跑得快的马也可以拉回来耕地；国家的政治措施如果违背了大道，那么连怀孕的母马都要在疆场作战，以至于在战场生子。最大的祸患是不知满足，最大的危险是贪得无厌。因此懂得满足的这种满足，才是长久永恒的满足。</t>
+    <t>国家的政治措施如果符合大道，那么连跑得快的马也可以拉回来耕地；国家的政治措施如果违背了大道，那么连怀孕的母马都要在疆场作战 以至于在战场生子。最大的祸患是不知满足，最大的危险是贪得无厌。因此懂得满足的这种满足，才是长久永恒的满足。</t>
   </si>
   <si>
     <t>“天下有道，却走马以粪；天下无道，戎马生于郊，祸莫大于不知足，咎莫大于欲得，故知足之足，常足矣。”这段话也是《道德经》里边非常精彩的一章。因为它体现了我们中国人对待战争的态度，对待和平的热爱。前面我们讲的第三十章的内容，不知道大家是否还有印象，“师之所处，荆棘生焉。”军队打过仗的地方，一片衰草枯杨，断壁残垣，“大军之后，必有凶年。”打过仗以后，灾荒瘟疫都来了。第三十一章，老子讲得更为沉痛，说中国人把战争当作丧礼一样来对待，“以悲哀泣之，以丧礼处之，胜而不美，胜而美者是乐于杀人。”我以前讲过，通过“四大名著”让国外了解我们的文化，效果恐怕不尽如人意，应该让他们看什么呢？让他们看《道德经》，这部能真正代表中国人思想理念、境界和智慧的经典，像我们讲过的三十章、三十一章和现在要讲的第四十六章，就是如此。“天下有道”，普天下清明有道，这个“天下”包括各个诸侯国了。“天下有道，却走马以粪”，“却”就是推却，“走马”就是跑马，也就是好马。这好马不用来打仗，离开战场，推却战争，干吗呢？回来耕田。当然，古人耕田是要上肥的，撒上粪肥，马耕着田，把地耕好，也就是我们经常讲的，卸甲归田，“卸马归田”，把马从战场上拉回来，干它的本务工作。“天下无道，戎马生于郊”，普天下无道的时候，混乱不堪不清明的时候，是什么情况呢？战马把小马驹生到了战场之上，“郊”就是郊野，此处指疆场，战马把小马驹生到了疆场之上。打仗公马不够用了，母马也上去了，最后出现这种情况——“戎马生于郊”，说得非常形象。我要重点强调一下，这四句是以马喻道，马之却为有道，戎马生于郊为无道，也就是以马的“却”与“生”，比拟天下之有道与无道：以“粪马”与“戎马”，象征国家之治与不治。比喻巧妙，寓意深远。纵观《道德经》的治国之道，当以无为自然以养民，以无欲之事而安民。好像马匹一样，虽是有用之物，用之于疆场可以卫国，用之于战阵可以御敌，用之于农事可以耕田。道行天下之时，国泰民安，上下祥和，无兵甲之患，天下太平安然，百姓安居乐业，故用走马耕田种地，积粪肥田。所以说：“天下有道，却走马以粪。天下无道，戎马生于郊。”太精辟了。“祸莫大于不知足，咎莫大于欲得。”这个大家清楚，老子生活在春秋，春秋无义战——没有什么正义的战争。大家都为了争夺财富、城池、人口，相互混战，战火频仍，烽火四起。面对这种情况，老子在当时总结出这两句话：“祸莫大于不知足，咎莫大于欲得。”惹祸最大的原因在哪呢？在于内心的贪念，贪心不足，得到了还想更多，只会做加法，不会做减法。“人心不足蛇吞象”，其实这句话，不单只对当时的现实概括，对我们现在也有这种启发的意义。生活中这种情况也比比皆是：有了还想更有，多了还想更多，衣架里边永远缺一件衣服，房子永远少一间，总是处在不知足的这种状态。“祸莫大于不知足，咎莫大于欲得”，“咎”罪过，过错，动辄得咎，过往不咎。这个“欲得”，就是别人的东西，自己也想要，把别人东西尽量弄到自己手上——这就成了一种罪过了。前面讲“不知足”是一种“祸”，祸患，而“欲得”就是一种罪过了，甚至可以是一种罪恶。别人的城，想要；别人的人民，想要，什么都想占有，用占有的态度对待这个世界，天下是我的。他说古代封建时代皇帝是什么样子呢？“离散天下人之儿女，屠毒天下人之肝脑，以博我一人之产业。”是说皇帝他觉得天下都是自己的，什么东西想拿就拿，想要就要，想占有就占有。这不就是“欲得”吗，这不就是一种大的过错、罪过吗？“咎莫大于欲得。”这个事情该怎么样来处理呢？该我们得的，我们应该得，不该我们的，“虽一毫而莫取也”。这段话大家也知道，东坡先生的《前赤壁赋》，“物各有主，苟非吾之所有，虽一毫而莫取。”划清边界，该得的得，不该得的不要老去强占，不要老是欲得。我们有了边界、底线、标准，那么就知道知足，知足的满足才是长久的满足。知足者富，所以如果永远处在不知足的状态，人也就永远不会有心灵的安宁。我们把这段话和第四十四章联系起来理解就更加明确了。第四十四章最后的三句话讲，“知足不辱，知止不殆，可以长久。”这一章说，“祸莫大于不知足，咎莫大于欲得。故知足之足，常足矣。”</t>
+  </si>
+  <si>
+    <t>德经</t>
   </si>
   <si>
     <t>第四十七章（47）</t>
@@ -3352,8 +3385,8 @@
       <c r="F27" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="G27" s="11">
-        <v>1</v>
+      <c r="G27" s="11" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="28" ht="172.8" spans="1:7">
@@ -3361,19 +3394,19 @@
         <v>26</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G28" s="11">
         <v>15</v>
@@ -3384,19 +3417,19 @@
         <v>27</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G29" s="11"/>
     </row>
@@ -3405,19 +3438,19 @@
         <v>28</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G30" s="11">
         <v>22</v>
@@ -3428,19 +3461,19 @@
         <v>29</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G31" s="11"/>
     </row>
@@ -3449,19 +3482,19 @@
         <v>30</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G32" s="11">
         <v>31</v>
@@ -3472,19 +3505,19 @@
         <v>31</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G33" s="11">
         <v>30</v>
@@ -3495,22 +3528,22 @@
         <v>32</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35" ht="172.8" spans="1:7">
@@ -3518,19 +3551,19 @@
         <v>33</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G35" s="11"/>
     </row>
@@ -3539,19 +3572,19 @@
         <v>34</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G36" s="11">
         <v>2</v>
@@ -3562,19 +3595,19 @@
         <v>35</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G37" s="11">
         <v>12</v>
@@ -3585,19 +3618,19 @@
         <v>36</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="G38" s="11">
         <v>2</v>
@@ -3608,19 +3641,19 @@
         <v>37</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>203</v>
+        <v>22</v>
       </c>
       <c r="G39" s="11"/>
     </row>
@@ -3629,19 +3662,19 @@
         <v>38</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G40" s="11"/>
     </row>
@@ -3650,19 +3683,19 @@
         <v>39</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="G41" s="11">
         <v>2</v>
@@ -3673,40 +3706,42 @@
         <v>40</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="G42" s="11"/>
+        <v>228</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="43" ht="409.5" spans="1:7">
       <c r="A43" s="10">
         <v>41</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="G43" s="11"/>
     </row>
@@ -3715,22 +3750,22 @@
         <v>42</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="45" ht="409.5" spans="1:7">
@@ -3738,19 +3773,19 @@
         <v>43</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>216</v>
+        <v>245</v>
       </c>
       <c r="G45" s="11"/>
     </row>
@@ -3759,19 +3794,19 @@
         <v>44</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>216</v>
+        <v>250</v>
       </c>
       <c r="G46" s="11"/>
     </row>
@@ -3780,40 +3815,42 @@
         <v>45</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="G47" s="11"/>
+        <v>255</v>
+      </c>
+      <c r="G47" s="11">
+        <v>25</v>
+      </c>
     </row>
     <row r="48" ht="409.5" spans="1:7">
       <c r="A48" s="10">
         <v>46</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G48" s="11"/>
     </row>
@@ -3822,19 +3859,19 @@
         <v>47</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G49" s="11"/>
     </row>
@@ -3843,19 +3880,19 @@
         <v>48</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G50" s="11"/>
     </row>
@@ -3864,19 +3901,19 @@
         <v>49</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="D51" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="F51" s="11" t="s">
         <v>260</v>
-      </c>
-      <c r="E51" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="F51" s="11" t="s">
-        <v>216</v>
       </c>
       <c r="G51" s="11"/>
     </row>
@@ -3885,19 +3922,19 @@
         <v>50</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G52" s="11"/>
     </row>
@@ -3906,19 +3943,19 @@
         <v>51</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G53" s="11"/>
     </row>
@@ -3927,19 +3964,19 @@
         <v>52</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G54" s="11">
         <v>6</v>
@@ -3950,19 +3987,19 @@
         <v>53</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G55" s="11"/>
     </row>
@@ -3971,19 +4008,19 @@
         <v>54</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G56" s="11"/>
     </row>
@@ -3992,19 +4029,19 @@
         <v>55</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G57" s="11"/>
     </row>
@@ -4013,19 +4050,19 @@
         <v>56</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G58" s="11"/>
     </row>
@@ -4034,22 +4071,22 @@
         <v>57</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
     </row>
     <row r="60" ht="409.5" spans="1:7">
@@ -4057,19 +4094,19 @@
         <v>58</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G60" s="11"/>
     </row>
@@ -4078,19 +4115,19 @@
         <v>59</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G61" s="11"/>
     </row>
@@ -4099,19 +4136,19 @@
         <v>60</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G62" s="11"/>
     </row>
@@ -4120,19 +4157,19 @@
         <v>61</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G63" s="11"/>
     </row>
@@ -4141,19 +4178,19 @@
         <v>62</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G64" s="11"/>
     </row>
@@ -4162,22 +4199,22 @@
         <v>63</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" ht="409.5" spans="1:7">
@@ -4185,19 +4222,19 @@
         <v>64</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G66" s="11">
         <v>63</v>
@@ -4208,19 +4245,19 @@
         <v>65</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G67" s="11"/>
     </row>
@@ -4229,22 +4266,22 @@
         <v>66</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
     </row>
     <row r="69" ht="409.5" spans="1:7">
@@ -4252,19 +4289,19 @@
         <v>67</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G69" s="11"/>
     </row>
@@ -4273,19 +4310,19 @@
         <v>68</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G70" s="11"/>
     </row>
@@ -4294,19 +4331,19 @@
         <v>69</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G71" s="11">
         <v>17</v>
@@ -4317,19 +4354,19 @@
         <v>70</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G72" s="11"/>
     </row>
@@ -4338,22 +4375,22 @@
         <v>71</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="74" ht="374.4" spans="1:7">
@@ -4361,19 +4398,19 @@
         <v>72</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G74" s="11"/>
     </row>
@@ -4382,19 +4419,19 @@
         <v>73</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G75" s="11"/>
     </row>
@@ -4403,19 +4440,19 @@
         <v>74</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G76" s="11"/>
     </row>
@@ -4424,19 +4461,19 @@
         <v>75</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G77" s="11">
         <v>10</v>
@@ -4447,19 +4484,19 @@
         <v>76</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G78" s="11"/>
     </row>
@@ -4468,19 +4505,19 @@
         <v>77</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G79" s="11"/>
     </row>
@@ -4489,22 +4526,22 @@
         <v>78</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
     </row>
     <row r="81" ht="409.5" spans="1:7">
@@ -4512,19 +4549,19 @@
         <v>79</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G81" s="11"/>
     </row>
@@ -4533,19 +4570,19 @@
         <v>80</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G82" s="11"/>
     </row>
@@ -4554,19 +4591,19 @@
         <v>81</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="G83" s="11">
         <v>7</v>
@@ -4624,19 +4661,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="G2" s="3"/>
     </row>
@@ -4645,19 +4682,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="G3" s="4"/>
     </row>
@@ -4666,19 +4703,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -4687,19 +4724,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="G5" s="4"/>
     </row>
@@ -4708,19 +4745,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="G6" s="4"/>
     </row>
@@ -4729,19 +4766,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -4750,19 +4787,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -4771,19 +4808,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="G9" s="4"/>
     </row>
@@ -4792,19 +4829,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="D10" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>432</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>421</v>
       </c>
       <c r="G10" s="4"/>
     </row>
@@ -4813,19 +4850,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="G11" s="4"/>
     </row>
@@ -4834,19 +4871,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="G12" s="4"/>
     </row>
@@ -4855,19 +4892,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="G13" s="4"/>
     </row>
@@ -4876,19 +4913,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -4897,19 +4934,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="G15" s="4"/>
     </row>
@@ -4918,19 +4955,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="G16" s="4"/>
     </row>
@@ -4939,19 +4976,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="G17" s="4"/>
     </row>
@@ -4960,19 +4997,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="D18" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>469</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>470</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>458</v>
       </c>
       <c r="G18" s="4"/>
     </row>
@@ -4981,19 +5018,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="G19" s="4"/>
     </row>
@@ -5002,19 +5039,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="G20" s="4"/>
     </row>
@@ -5023,19 +5060,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="G21" s="4"/>
     </row>
@@ -5044,19 +5081,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="G22" s="4"/>
     </row>
@@ -5065,19 +5102,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="G23" s="4"/>
     </row>
@@ -5086,19 +5123,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="D24" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>494</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>483</v>
       </c>
       <c r="G24" s="4"/>
     </row>
@@ -5107,19 +5144,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="G25" s="4"/>
     </row>
@@ -5128,19 +5165,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="G26" s="4"/>
     </row>
@@ -5149,19 +5186,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="G27" s="4"/>
     </row>
@@ -5170,19 +5207,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="G28" s="4"/>
     </row>

--- a/book.xlsx
+++ b/book.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19860" windowHeight="10584"/>
+    <workbookView windowWidth="25068" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="道德经" sheetId="1" r:id="rId1"/>
@@ -890,7 +890,7 @@
     <t>为学日益，为道日损。损之又损，以至于无为，无为而无不为。取天下常以无事，及其有事，不足以取天下。</t>
   </si>
   <si>
-    <t>为学是一天一天地增加知识，为道是一天一天地减少私欲。减少又减少，以致达到无为的境界。“无为”就能达到“无不为”的效果（做成一切事）。治理天下要常常不多事不扰民，如果妄为滋扰，就无法治理好天下。</t>
+    <t>为学（学习知识）是一天一天地增加知识，为道是一天一天地减少私欲（内心修行）。减少又减少，以致达到自然而为的境界。“无为”就能达到“无不为”的效果（做成一切事）。治理天下要常常不多事不扰民，如果妄为滋扰，就无法治理好天下。</t>
   </si>
   <si>
     <t>由于四十七、四十八这两章的内容非常相吻合、相近，所以我们合到一起作为一章来讲解。四十七章讲的是一个什么事儿呢？是说人的感性认识，从哲学上说就是我们的感官接触客观世界，有时候接触得多了，它反而会造成一种迷乱和混乱，要通过人的智慧、理性认识，这样我们才能了解事物的规律，也就是这一章里边所说的“天道”。在这个基础上，我们一句句来解释。“不出户，知天下。”“户”就是门户，也就是大门。我不用走出家门，不用去外边到处跑，也能了解天下的大事。为什么？因为道家认为，天下大道归根到底，融于人的内心。内心里边有道，也就了解了天下的正道，了解了天下的大事。“不窥牖，见天道。”“窥”，从小孔里看；“牖”，就是窗户。我不用通过窗户去看，也知道天地之间日月星辰运行的规律。所以你看这个地方，“出户”是行走，出行，行万里路；“窥牖”是眼睛看，用感官接触客观世界，我不用这样。所以这个地方大家就感觉到，直观的一开始看，就觉得老子这个人有点轻视感性认识，人得通过实践嘛，人得通过感官接触客观世界，才能产生对客观世界的认识。是不是老子把这些东西全部都否认了呢？不是的。因为大家从书里已经看得非常的清楚，《道德经》举了很多生活中的例子，比如说“治大国若烹小鲜”，比如说“凿户牖以为室”，比如“说三十辐共一毂”，前面讲过的，这不都是生活中的例证吗？他对这个东西也很熟悉，怎么知道的呢？通过接触、了解。为什么在这一章里一开始他就讲这个事呢？要落到下面这八个字上。“其出弥远，其知弥少。”“弥”就是越来越，有的人走的地方越多，见得越多，不懂得甄别，不懂得筛选，不懂得提炼概括，“乱花渐欲迷人眼”，出得越远，反而了解到的真知越少，进步越少，为什么？不懂得反观自省，不懂得人心像一面镜子，如果你这个镜子是被灰尘蒙蔽的，你见得越多，其实反而获得的真知越少。这八个字在强调什么？我们要反观自省，要自我修行，自我修养，从哲学上说，从那些感性认识要上升到一种理性认识，达到对事物本质和规律的认识。所以你看，天下、天道代表着对事物全面的、本质的、规律性的认识，这个规律性的认识，需要我们安静地学习，在家里边读古往今来的著作，这不也是“不出户”嘛，也是“不窥牖”！我们了解这些间接的经验，从前人那里得到根本性的、全面的、通过理论阐释的这些知识，我们才能更了解事物的本质，更了解事物的规律。所以不要只把希望寄托在我们出去跑一跑，看一看，以为这样我们的知识就会越来越深刻，很多事情其实要通过理性的思维，这样我们才能进入到对事物本质和规律的认识，“其出弥远，其知弥少”。如果从中国的文化的角度来进一步理解的话，它还探讨一个什么问题、强调一个什么问题呢？就是人的品德。“大道之行，以心之知。”就是我们的心，我们的自我的内在的精神世界，这是道的重要的方面。所以很多人认为知识就是智慧，知识就是品德。不是的，很多人知识很多，不一定有智慧，知识多也不一定有境界、有品德。所以《道德经》强调的根本的“知”，从前面的比较中，相对于我们的感官而言，是人的理性的思维，理性认识、智慧，相对于外面的世界而言，它又是人的道德品德、人的品德。明朝的时候，关学的代表人物冯从吾先生讲过的一句话，我觉得冯从吾先生的这句话就非常能够解释这个道理，冯先生认为，古往今来的大学问都不出乎三句话：“做个好人，存点好心，行些好事。”做个好人，心正，身安，魂梦稳；行些好事，天知，地鉴，鬼神钦。所以一个人内心的品德、境界，通过自我的反省，自我的修养，达到了一个更高的水平，返璞归真，“归根曰静”，这些也是通过内在的自我修养来达到的。所以《道德经》认为人的理性认识，人这样的内心、这样的根本，它可以通过“不出户”、“不窥牖”，也可以自我修养，自我认知，不断地进步以达到。“是以圣人不行而知，不见而明，不为而成。”“是以圣人不行而知”，“是以”，“是”就是这样，“以”就是用，“是”可以解释为所以。“圣人”，好的统治者、领导者，在《道德经》称其为圣人。这些圣人，好的领导者、统治者要经常反躬自省，要经常内心关照，提高自己对大道和规律的认知水平。“不行而知”，不用到处跑，这一点也是可以得到的。“不见而明”，不用亲自去看，也能够明了道理，明了了这个道理，那就内心清净、无欲。“不为而成”，“不为”就是无为，就是按照大道的方式自然而然地去做，而不去妄为，这样一切都会顺理成章。这是我们第四十七章里边讲的内容，字虽然不多，但道理需要我们认真体会，“不出户，知天下；不窥牖，见天道。其出弥远，其知弥少。是以圣人不行而知，不见而明，不为而成。”当然对这一章的更进一步的理解需要我们和第四十八章，也就是我后面要讲的这一章相互参照，我们对这个理解才会更深刻、更准确。一开始就给大家说第四十七章、第四十八章我们要合起来，相互参照，为什么？这两章的内容讲的是非常吻合的，事实上也应该是一章的内容。第四十七章里边讲，“其出弥远，其知弥少”，第四十八章一开头就讲：“为学日益，为道日损。损之又损，以至于无为，无为而无不为。”这八个字一下子和上边的内容就衔接起来，为什么跑得越远反而知道的越少，这是站在道的角度来讲的。“为学”，在学知识，学到的知识内容越来越多。当然从学知识的角度来讲，这是非常有益的，不断地增多，可是我们获得很多的东西，见到了很多的东西，其实对我们了解根本性的规律和本质，了解大道并没有好处。站在一个更高的层次理解，就是说我们“为学”，讲究的是越多越好，见得多，看得多，见多识广。但是“为道”讲究的是什么呢？讲究的是内心的修行，讲究的是减少，用我们前面讲的话来讲，为学做的是加法，为道做的是减法，减少我们内心的欲念，减少我们的贪念，减少我们对很多问题的一种受了外界的影响而导致的内心的纷扰、困惑、迷乱，把这些东西损之又损，一点一点地把它减少，就像那镜子的灰尘一点点擦掉一样，“损之又损，以至于无为。”“无为”就是自然而为，把欲望减少，减少再减少，就达到了一种“无为”的境界，没那么多的贪念，没那么多的纷扰。我们用镜子来照这个天下，来照事物，万物进入到镜子里边，呈现出它本来的面貌。我们了解了事物的本质规律，了解了大道按照它来做，“无为而无不为”达到的是“无不为”的效果。所以在这儿借着这个机会，我再说一下道家自然无为的具体的含义：第一，不妄为；第十六章里边就讲，“不知常，妄作，凶。”你不了解事物的规律、规则，瞎折腾、胡折腾，那结果是非常糟糕的。我们“损之又损”，减少了这些遮挡着我们的认识，遮挡了我们的心窍的这些外在的事物、灰尘、迷乱，我们就照见了事物的本质和规律，我们就“不妄为”。第二，不多为；抓住关键，举重若轻，静观，看到事物的本质，找到解决问题的正确的方法，抓住关键，举重若轻。第三，有所不为；人要想有所为，必须有所不为，要想有所得，必须有所舍。我们舍弃了那些阻碍了我们正确行动、阻碍我们沿着大道行走的那些纷纷扰扰，这样能达到一个无不为的效果，也就是覆盖面广，效果更好，“无为而无不为”。下面这一段就讲，按照“无为”的方式来理解天下万事万物。“取天下常以无事，及其有事，不足以取天下。”“取天下”的规则是什么呢？“无事”。“无事”就是不多事，不干涉，不扰民，这样一切就自然而然顺理成章。所以第五十七章里边讲的这个事情就比较明确，“我无事而民自富，我无为而民自化”。“及其有事”，如果老是多事，老是妄为，不懂得事物的规律、规则，瞎折腾、胡折腾，这就是“及其有事”。则“不足以取天下”，那就不能够获得天下。得到的天下也得失去，因为它违背了大道。</t>
@@ -902,10 +902,10 @@
     <t>圣人无常心，以百姓心为心。善者，吾善之；不善者，吾亦善之，德善。信者，吾信之；不信者，吾亦信之，德信。圣人在天下歙（xī）歙，为天下浑其心。百姓皆注其耳目，圣人皆孩之。</t>
   </si>
   <si>
-    <t>圣人没有固执不变的思想，而是把百姓的思想当作自己的思想。。善良的百姓我善待他们，不善良的百姓我也善待他们，结果就会使他也变得善良；讲诚信的人我以诚信对待他们，不讲诚信的人我也以诚信对待他们，结果就会使他也变得诚信。圣人领导天下，收敛自己的私欲，使天下百姓的心灵都变得淳朴。百姓都只关注耳听眼见的事，而圣人要使他们都变得像无知无欲的婴儿一样。</t>
-  </si>
-  <si>
-    <t>第四十九章是《道德经》里边比较重要的一章，因为这里边有一句话大家都很熟悉，我们领导者讲话的时候也经常引用，就是以“百姓心为心”。从前面讲的内容，大家会知道这是一个通过换位思考，得出来这样的一种结论。这一章开头这句话我们先说一下。“圣人无常心，以百姓心为心。”是说一个好的领导者、统治者，不要老固执己见。“常心”就是固定的心思，自我的执着，不要老固执己见，不要老把自己的意志强加给别人，乃至强加给人民。应该怎么样呢？换位思考，将心比心，“以百姓心为心”，倾听民众的呼声，关注民众的利益，吸取民众的智慧，这都是“以百姓心为心”的表现。我们先体会一下这一章的宗旨在讲什么？其实这个道理就是讲了，换位思考，将心比心。百姓善良，我也对他善良；不善良，我也对他善良；信任我的，我信任他；不信任我的，我也信任他。干吗呢？这样我就能让人向善，让大家讲诚信。最后这一段就说一个好的领导者、统治者，让百姓都回归到他本来的这种生活，关注的是自己的生活中的事情。不要想那么多，不要心思混乱，不要烦乱，这样才能够形成一种良好的和谐的状态。这是老子的想法。我们一句一句来解释。“圣人无常心”，我再重申一遍，“圣”的繁体字，上面是个耳和口——聖，这两个字并列就代表着通达事理，下面是个王，也就是说一个好的领导者、领导人称其为“圣”。在这一章里体现得最为明显。“圣人无常心”，有的本子也叫“常无心”，意思都是一样的，就是不固执己见，没有自己僵化固定的思维，懂得换位思考。其实关于这个意思，我们通过前面讲过的第二十二章参照着理解，就比较容易了。我在前面多次说过，读《道德经》最好的方法就是不看注解，以经解经，相互参照，明白它要讲的真正的含义，谁的解读也不如他本人对这个东西的解释更符合他的本意。第二十二章里边就讲“不自是”“不自见”“不自矜”“不自伐”这“四不”。“不自是，故彰。不自伐，故有功。不自矜，故长。”这样我们才能不断成长，不断进步。一个好的领导人也是这样的，领导者、统治者，也应该“四不”，也就是“无常心”。你没有这样的智慧，老是固执己见，老是自我吹嘘，老是自我夸耀，老是觉得自己了不起，那你就没办法换位思考，将心比心了。所以“无常心”才能以百姓之心为心，倾听民众的呼声，吸取民众的智慧，关注民众的利益。沿着这个思路下面也好理解了。“善者，吾善之；不善者，吾亦善之，德善。”善良的人我用善良去对待他，不善良的人，我也用善良的方式去对待他，干嘛呀？教化、感化，这样我就得到了真正的善良。为什么呢？你这样做，起代表带头作用，大家也就人心向善了。大家注意这个“德”，王弼的解释非常明确，“德者，得也”，这样做就得到了这个天下、这个社会，这个国家就会人心向善。“信者，吾信之；不信者，吾亦信之，德信。”信我的人，我相信他，我跟他讲诚信；不相信我的人，我也相信他，跟他讲诚信。干嘛呀？这样天下人就会觉得诚信可贵，也就往诚信的方向去努力去发展了——“德信”。“圣人在天下歙歙”，“歙”就是合，就是收敛。你说圣人怎么样领导、管理这个天下呢？先要收敛自己的欲望，要想领导好别人，你先领导好自己，要想领导好自己，你先领导好自己的情绪，领导好自己的欲念，上梁不正则下梁歪嘛。“歙歙”，收敛自己的欲望，减少自己的欲念。“为天下浑其心”，让这个天下都怎么样呢？大家都没那么精明。不总是为了什么事都去争，“浑其心”，都那么样地浑厚、淳朴、厚道，关心自己的现实生活，而不是那么多纷乱的思维，那么多胡乱的想法，那么多的技巧、智谋、套路、心眼，用这种方式让大家和谐相处。“圣人皆孩之”，一个好的领导者把天下人都当作儿童，当作自己的孩子，一方面对他们非常关爱，另一方面也不要让百姓人心混乱，都像孩童一样纯净、淳朴。当然了，后边这一段大家也看得出来，这也是老子的一厢情愿。他希望统治者减少自己的欲望，天下人跟着也减少自己的欲望，关注自己的现实的生活，没有那么多的争斗、心眼、套路、技巧、欺骗、欺诈。这是老子生活的理想状态，也是他认为是和谐世界的前景，我们权当这也是他的一种理念和希望，毕竟这个社会的和谐也是我们的一种希望。只是他这种方法大家要辩证对待，大概用这种方法实现天下的太平，也只能是一种理想和理念，很难真正得以实现。但这一章里边大家要注意，开头这句话，我们要熟记，因为在我们国家的领导人的很多讲话里边都能看到这句话的出现，“以百姓心为心”，这是道家思想里边非常重要的一句话，让我们感觉到老子这个人在他冷静的、甚至有点冷酷的外表之下，内心涌动的热流，对于天下人的关注，对于天下人的关爱。这一章的原文我们解释完了，再强调一下这章的逻辑和重点，这章里边的关键在哪呢？这一章里边的关键是讲“圣人”和“百姓”，他们是国家不同层面的人，这一章讲究什么呢？讲究各安其位，各循其理。老子对这些做统治者的讲，你们要“以百姓之心为心”，善良的人呢你要好好地对待，不善良的人呢你也要好好对待，这样你才能得到这个国家人心向善的风气。信你的人你要讲诚信，不信你的人你也要讲诚信，这样才能得到天下诚信的风气。“圣人在天下”，圣人在上，领导天下。应该怎么样呢？怎么样叫循理循道呢？应该清静，无为，少折腾，少多事儿，这是上边的理，给他们讲的，你应该这样做，收敛自己的欲望，减少自己的奢靡、奢华，“清静为天下正”，这是对他们。对下边怎么讲呢？你这个在上边的人应该让下边遵循一个什么样的道理呢？“为天下浑其心”，让这个百姓浑厚，淳朴，宁静，没有那么多纷乱的想法，那么多技巧、心眼、套路、欺诈、欺骗，按照这个方向，百姓都关注自己现实的生活，把自己的日子过好，少管别的事儿，你让百姓能够做到这一点，上边的管上边的事，循上边之理，下边的循下边之理，这天下不就和谐了嘛。大家看出来了吧，“圣人皆孩之”，好的领导，一个国家的领导者，让这国家的百姓都像小孩一样，纯净、淳朴，没有那么多的欺瞒欺诈。上按上边的道理，下按下边的道理，这不就形成了一个和谐的状态了嘛。我们知道，真正的和谐是有差别的统一，大家都应该有表达自己的意见的机会，表达自己观点的机会，“各美其美，美人之美”，有差别的统一。但是老子这个地方讲的道理不是这样的，他讲的是“圣人无常心”，你要考虑到百姓，百姓在圣人的领导下应该怎么做呢？应该浑厚淳朴，没有那么多的智谋、欺诈、心眼，关注自己的现实生活，干好自己的事情，像儿童一样，纯净、干净、宁静，形成这个社会的和谐状态。所以我们只能说，老子这个想法呀追求一种和谐的目标，但是这个所用的方法在我们看来，这还是有很多地方值得检讨的，因为真的把百姓都变成小孩，还是不免有一点愚民政策的感觉。这一点大家还是要正确地理解。</t>
+    <t>圣人不要有固执不变的思想，而是把百姓的思想当作自己的思想。。善良的百姓我善待他们，不善良的百姓我也善待他们，结果就会使他也变得善良；讲诚信的人我以诚信对待他们，不讲诚信的人我也以诚信对待他们，结果就会使他也变得诚信。圣人领导天下 收敛自己的私欲，使天下百姓的心灵都变得淳朴。百姓都只关注耳听眼见的事，而圣人要使他们都变得像无知无欲的婴儿一样。</t>
+  </si>
+  <si>
+    <t>【圣人要换位思考 将心比心】第四十九章是《道德经》里边比较重要的一章，因为这里边有一句话大家都很熟悉，我们领导者讲话的时候也经常引用，就是以“百姓心为心”。从前面讲的内容，大家会知道这是一个通过换位思考，得出来这样的一种结论。这一章开头这句话我们先说一下。“圣人无常心，以百姓心为心。”是说一个好的领导者、统治者，不要老固执己见。“常心”就是固定的心思，自我的执着，不要老固执己见，不要老把自己的意志强加给别人，乃至强加给人民。应该怎么样呢？换位思考，将心比心，“以百姓心为心”，倾听民众的呼声，关注民众的利益，吸取民众的智慧，这都是“以百姓心为心”的表现。我们先体会一下这一章的宗旨在讲什么？其实这个道理就是讲了，换位思考，将心比心。百姓善良，我也对他善良；不善良，我也对他善良；信任我的，我信任他；不信任我的，我也信任他。干吗呢？这样我就能让人向善，让大家讲诚信。最后这一段就说一个好的领导者、统治者，让百姓都回归到他本来的这种生活，关注的是自己的生活中的事情。不要想那么多，不要心思混乱，不要烦乱，这样才能够形成一种良好的和谐的状态。这是老子的想法。我们一句一句来解释。“圣人无常心”，我再重申一遍，“圣”的繁体字，上面是个耳和口——聖，这两个字并列就代表着通达事理，下面是个王，也就是说一个好的领导者、领导人称其为“圣”。在这一章里体现得最为明显。“圣人无常心”，有的本子也叫“常无心”，意思都是一样的，就是不固执己见，没有自己僵化固定的思维，懂得换位思考。其实关于这个意思，我们通过前面讲过的第二十二章参照着理解，就比较容易了。我在前面多次说过，读《道德经》最好的方法就是不看注解，以经解经，相互参照，明白它要讲的真正的含义，谁的解读也不如他本人对这个东西的解释更符合他的本意。第二十二章里边就讲“不自是”“不自见”“不自矜”“不自伐”这“四不”。“不自是，故彰。不自伐，故有功。不自矜，故长。”这样我们才能不断成长，不断进步。一个好的领导人也是这样的，领导者、统治者，也应该“四不”，也就是“无常心”。你没有这样的智慧，老是固执己见，老是自我吹嘘，老是自我夸耀，老是觉得自己了不起，那你就没办法换位思考，将心比心了。所以“无常心”才能以百姓之心为心，倾听民众的呼声，吸取民众的智慧，关注民众的利益。沿着这个思路下面也好理解了。“善者，吾善之；不善者，吾亦善之，德善。”善良的人我用善良去对待他，不善良的人，我也用善良的方式去对待他，干嘛呀？教化、感化，这样我就得到了真正的善良。为什么呢？你这样做，起代表带头作用，大家也就人心向善了。大家注意这个“德”，王弼的解释非常明确，“德者，得也”，这样做就得到了这个天下、这个社会，这个国家就会人心向善。“信者，吾信之；不信者，吾亦信之，德信。”信我的人，我相信他，我跟他讲诚信；不相信我的人，我也相信他，跟他讲诚信。干嘛呀？这样天下人就会觉得诚信可贵，也就往诚信的方向去努力去发展了——“德信”。“圣人在天下歙歙”，“歙”就是合，就是收敛。你说圣人怎么样领导、管理这个天下呢？先要收敛自己的欲望，要想领导好别人，你先领导好自己，要想领导好自己，你先领导好自己的情绪，领导好自己的欲念，上梁不正则下梁歪嘛。“歙歙”，收敛自己的欲望，减少自己的欲念。“为天下浑其心”，让这个天下都怎么样呢？大家都没那么精明。不总是为了什么事都去争，“浑其心”，都那么样地浑厚、淳朴、厚道，关心自己的现实生活，而不是那么多纷乱的思维，那么多胡乱的想法，那么多的技巧、智谋、套路、心眼，用这种方式让大家和谐相处。“圣人皆孩之”，一个好的领导者把天下人都当作儿童，当作自己的孩子，一方面对他们非常关爱，另一方面也不要让百姓人心混乱，都像孩童一样纯净、淳朴。当然了，后边这一段大家也看得出来，这也是老子的一厢情愿。他希望统治者减少自己的欲望，天下人跟着也减少自己的欲望，关注自己的现实的生活，没有那么多的争斗、心眼、套路、技巧、欺骗、欺诈。这是老子生活的理想状态，也是他认为是和谐世界的前景，我们权当这也是他的一种理念和希望，毕竟这个社会的和谐也是我们的一种希望。只是他这种方法大家要辩证对待，大概用这种方法实现天下的太平，也只能是一种理想和理念，很难真正得以实现。但这一章里边大家要注意，开头这句话，我们要熟记，因为在我们国家的领导人的很多讲话里边都能看到这句话的出现，“以百姓心为心”，这是道家思想里边非常重要的一句话，让我们感觉到老子这个人在他冷静的、甚至有点冷酷的外表之下，内心涌动的热流，对于天下人的关注，对于天下人的关爱。这一章的原文我们解释完了，再强调一下这章的逻辑和重点，这章里边的关键在哪呢？这一章里边的关键是讲“圣人”和“百姓”，他们是国家不同层面的人，这一章讲究什么呢？讲究各安其位，各循其理。老子对这些做统治者的讲，你们要“以百姓之心为心”，善良的人呢你要好好地对待，不善良的人呢你也要好好对待，这样你才能得到这个国家人心向善的风气。信你的人你要讲诚信，不信你的人你也要讲诚信，这样才能得到天下诚信的风气。“圣人在天下”，圣人在上，领导天下。应该怎么样呢？怎么样叫循理循道呢？应该清静，无为，少折腾，少多事儿，这是上边的理，给他们讲的，你应该这样做，收敛自己的欲望，减少自己的奢靡、奢华，“清静为天下正”，这是对他们。对下边怎么讲呢？你这个在上边的人应该让下边遵循一个什么样的道理呢？“为天下浑其心”，让这个百姓浑厚，淳朴，宁静，没有那么多纷乱的想法，那么多技巧、心眼、套路、欺诈、欺骗，按照这个方向，百姓都关注自己现实的生活，把自己的日子过好，少管别的事儿，你让百姓能够做到这一点，上边的管上边的事，循上边之理，下边的循下边之理，这天下不就和谐了嘛。大家看出来了吧，“圣人皆孩之”，好的领导，一个国家的领导者，让这国家的百姓都像小孩一样，纯净、淳朴，没有那么多的欺瞒欺诈。上按上边的道理，下按下边的道理，这不就形成了一个和谐的状态了嘛。我们知道，真正的和谐是有差别的统一，大家都应该有表达自己的意见的机会，表达自己观点的机会，“各美其美，美人之美”，有差别的统一。但是老子这个地方讲的道理不是这样的，他讲的是“圣人无常心”，你要考虑到百姓，百姓在圣人的领导下应该怎么做呢？应该浑厚淳朴，没有那么多的智谋、欺诈、心眼，关注自己的现实生活，干好自己的事情，像儿童一样，纯净、干净、宁静，形成这个社会的和谐状态。所以我们只能说，老子这个想法呀追求一种和谐的目标，但是这个所用的方法在我们看来，这还是有很多地方值得检讨的，因为真的把百姓都变成小孩，还是不免有一点愚民政策的感觉。这一点大家还是要正确地理解。</t>
   </si>
   <si>
     <t>第五十章（50）</t>
@@ -917,7 +917,7 @@
     <t>人生就是从出生到死亡的历程。长寿的人占十分之三，短命的人占十分之三，本可以长寿但妄为把自己置于死地的人也占十分之三。为什么？因为他们过分地追求奉养自己以求生。听说善于养生的人，在陆地上行走不会遇到犀牛和猛虎的伤害，在战场上不会被兵器所伤。犀牛的角无处可用，老虎的爪也没了用处，兵器的刃也用不上。为什么？因为他不把自己置于死地。</t>
   </si>
   <si>
-    <t>我们来讲第五十章，这一章表面上在讲养生之道，也就是文章所说的“摄生”，实际上表达的是更为深刻的道理。我们看书、看电视剧的时候，会发现有那么一些大师、大医生，一些位重权高的人向他们请教养生之道，“我怎么样能活得更加长寿？”这些医生、养生大师啊，大都是告诉他们要清心寡欲，不要奢靡奢华，不要胡吃海塞，其实这就是道家对于养生这事儿往更高的一个层次所要修养的内容，我们也可以把它概括为道家的生死观。道家认为养生跟生死密切关联。养生要顺应自然，要自然而然，要掌握规律、规则。你看我们读《庄子·养生主》里边的“庖丁解牛”，讲的不就是这个道理吗？目无全牛，游刃有余！这牛解得跟跳舞一样，跟音乐一样。所以文惠君最后就对这个庖丁讲：“吾闻庖丁之言，得养生焉。”养生要顺应自然规律，自然而然，自然而为。“生之徒十有三，死之徒十有三。”然后老子做分析，如果把天下的人分做十成，那么有十分之三的人是“生之徒”，也就是长寿的，还有十分之三的人是“死之徒”，是短命的。还有十分之三的人是怎么样的呢？“人之生，动之死地，亦十有三。”这些人本来可以长寿，最后由于自己的胡为、妄为、折腾，就把自己置于死地了。所以你看它的分类很有趣，十成的人中，三分之一的人应该是长寿的，三分之一的人本身体质各方面就是短寿的，还有三分之一的人本来可以长寿，但是妄动、胡为而置于死地。为什么会这样？《道德经》给了我们这样一句话：“以其生生之厚。”生，养生，或者可以解释得更明确，叫“求生”。太着急了，太迫切了，老想延长自己的性命，老害怕自己的营养不够，最后营养过剩了，反而把自己置于一个另外的相反的方向。当下一些有智慧的医生就提醒，我们现在不是营养不良，而是营养过剩，“生生之厚”。当然《道德经》讲的这句话只针对当时的统治者、位高权重的人而言，老是生活得这样奢靡奢华，“五色令人目盲，五音令人耳聋，五味令人口爽，驰骋畋猎，令人心发狂……”老是这样，还以为是让自己生命不亏，活得不亏。求生之厚，太急、太迫切，营养过剩，自己本来可以长寿，反而被置于成“死之徒”了，到短寿的那一拨去了。所以下面老子就讲了：“盖闻善摄生者”，听说这善于养生的人是什么样子呢？他们用了下边一段形容：“陆行不遇兕虎，入军不被甲兵。兕无所投其角，虎无所措其爪，兵无所容其刃。”习惯上我们以为“兕”是犀牛，或者有的叫母犀牛，其实这两种动物还不一样。这个“兕”是古代的一种瑞兽，比较凶猛，所以在古代的文字中，经常用这个“兕虎熊”比喻凶险之地。懂得养生的人，懂得正确对待自己生命的人，不去冒这个险。陆行的时候，尽量不碰这些凶猛的动物，如果你碰上它了，那你就没办法了，谁让你冒那个险呢？明知道野生动物园人家不让下车，你非得下车，遇到老虎了吧。有些地方人家告诉这个规则，这里边有危险，你偏不听，明知山有虎，偏向虎山行，明知山有狼，偏要做狼餐，这不就是“人之生，动之死地”吗？“入军不被甲兵”，上阵打仗的时候不为兵器所伤。为什么呢？“兕无所投其角”，你不遇到这个兕，那当然它那个凶猛的角就没有办法发挥它的作用了，没有办法针对你。一般我们画“兕”的时候都习惯把它画成独角兽。“兕”最有名的代表就是太上老君骑的那个板角青牛了，角非常锋利，尖锐，杀伤力强，你不遇到它，尽量别碰到，别把自己置于危险的境地，它的角当然就无所用了。“虎无所措其爪”，你不往虎山行，不遇到它，提前准备好避免这种凶险，老虎爪子再尖利，牙齿再锋利，它也无法对你发挥作用。“兵无所容其刃”，上阵不为甲兵所伤，尖锐的兵器，也没有办法发挥它的作用。“夫何故？”为什么会这样？“以其无死地”，不把自己置于死地，这样也就不会让自己的生命受到戕害。这是就是五十章。这一章体现了道家的养生之道：简单地说就是不要“作死”，自己不要找死，本来可以长寿的，自己作死把自己置于死地。很多人非得触犯法律的界限，甚至因此送掉了自己的生命，这不就是把自己置于死地嘛！所以我们说“NoZuoNoDie”，不作不死。从养生的角度来讲，你看道家讲的顺应自然，不单只是生活中的清心寡欲，而且还指不触犯边界底线，不触犯红线，知足不辱，知止不殆，不置身于死地，不让自己冒这种凶险，这也是道家养生之道里边的一个重要的内容，而且是更接近于哲学层面的、更有智慧的内容。那么这一段我们讲完了之后，我还要跟大家强调一下，道家的养生观，其实也是道家的生命观。道家对于生命的看法讲究的是自然而然，意思是什么呢？过于求生，过于厌恶死，这都不是一种自然而然的智慧，因为死亡本身就是生命的一部分，人自然而生，自然而死，真的到了生命结束的时候，那也应该开朗地、乐观地对待。这一点在道家的继承者那里，也就是道家的第二号人物庄子那里，讲得非常的明确——“之所以善吾生者，乃所以善吾死”。我们很好地对待自己的生命，不把自己的生命主动地置于死地，不求生之厚，真的面临死亡的时候，也应该把它好好地对待。自然而生，自然而亡，这是生命的自然而然的规律，谁也阻挡不了。第五十章，老子借养生之道讲了一个更重要的道理：有的人求生太急迫，太厌恶死亡，太害怕死亡，越是求生之厚，服了大量的药，用各种各样的营养的方式，推开死亡，想要避免，没想到越想避免的反而来得越快。所以，道家讲究自然而然的思想，这有着重要、杰出的意义。我们做个小小的梳理。第五十章，我们从开始讲的时候就给大家讲过，这一章可以分成两段，一段是讲有的人本来可以长寿，却进入了短命的行列，是因为“求生之厚”，太急迫、营养过剩导致的，另外一个是由于妄为、“作”，把自己置于死地的。怎样才能避免这两点呢？还是道家的这种思想，顺其自然，清心寡欲，清静为天下正。正确地对待生命和死亡，不把死亡当作是完全可以避免的事情，真的面临死亡的时候，也能够开朗地、乐观地对待。</t>
+    <t>【养生之道 —— 不要作死】我们来讲第五十章，这一章表面上在讲养生之道，也就是文章所说的“摄生”，实际上表达的是更为深刻的道理。我们看书、看电视剧的时候，会发现有那么一些大师、大医生，一些位重权高的人向他们请教养生之道，“我怎么样能活得更加长寿？”这些医生、养生大师啊，大都是告诉他们要清心寡欲，不要奢靡奢华，不要胡吃海塞，其实这就是道家对于养生这事儿往更高的一个层次所要修养的内容，我们也可以把它概括为道家的生死观。道家认为养生跟生死密切关联。养生要顺应自然，要自然而然，要掌握规律、规则。你看我们读《庄子·养生主》里边的“庖丁解牛”，讲的不就是这个道理吗？目无全牛，游刃有余！这牛解得跟跳舞一样，跟音乐一样。所以文惠君最后就对这个庖丁讲：“吾闻庖丁之言，得养生焉。”养生要顺应自然规律，自然而然，自然而为。“生之徒十有三，死之徒十有三。”然后老子做分析，如果把天下的人分做十成，那么有十分之三的人是“生之徒”，也就是长寿的，还有十分之三的人是“死之徒”，是短命的。还有十分之三的人是怎么样的呢？“人之生，动之死地，亦十有三。”这些人本来可以长寿，最后由于自己的胡为、妄为、折腾，就把自己置于死地了。所以你看它的分类很有趣，十成的人中，三分之一的人应该是长寿的，三分之一的人本身体质各方面就是短寿的，还有三分之一的人本来可以长寿，但是妄动、胡为而置于死地。为什么会这样？《道德经》给了我们这样一句话：“以其生生之厚。”生，养生，或者可以解释得更明确，叫“求生”。太着急了，太迫切了，老想延长自己的性命，老害怕自己的营养不够，最后营养过剩了，反而把自己置于一个另外的相反的方向。当下一些有智慧的医生就提醒，我们现在不是营养不良，而是营养过剩，“生生之厚”。当然《道德经》讲的这句话只针对当时的统治者、位高权重的人而言，老是生活得这样奢靡奢华，“五色令人目盲，五音令人耳聋，五味令人口爽，驰骋畋猎，令人心发狂……”老是这样，还以为是让自己生命不亏，活得不亏。求生之厚，太急、太迫切，营养过剩，自己本来可以长寿，反而被置于成“死之徒”了，到短寿的那一拨去了。所以下面老子就讲了：“盖闻善摄生者”，听说这善于养生的人是什么样子呢？他们用了下边一段形容：“陆行不遇兕虎，入军不被甲兵。兕无所投其角，虎无所措其爪，兵无所容其刃。”习惯上我们以为“兕”是犀牛，或者有的叫母犀牛，其实这两种动物还不一样。这个“兕”是古代的一种瑞兽，比较凶猛，所以在古代的文字中，经常用这个“兕虎熊”比喻凶险之地。懂得养生的人，懂得正确对待自己生命的人，不去冒这个险。陆行的时候，尽量不碰这些凶猛的动物，如果你碰上它了，那你就没办法了，谁让你冒那个险呢？明知道野生动物园人家不让下车，你非得下车，遇到老虎了吧。有些地方人家告诉这个规则，这里边有危险，你偏不听，明知山有虎，偏向虎山行，明知山有狼，偏要做狼餐，这不就是“人之生，动之死地”吗？“入军不被甲兵”，上阵打仗的时候不为兵器所伤。为什么呢？“兕无所投其角”，你不遇到这个兕，那当然它那个凶猛的角就没有办法发挥它的作用了，没有办法针对你。一般我们画“兕”的时候都习惯把它画成独角兽。“兕”最有名的代表就是太上老君骑的那个板角青牛了，角非常锋利，尖锐，杀伤力强，你不遇到它，尽量别碰到，别把自己置于危险的境地，它的角当然就无所用了。“虎无所措其爪”，你不往虎山行，不遇到它，提前准备好避免这种凶险，老虎爪子再尖利，牙齿再锋利，它也无法对你发挥作用。“兵无所容其刃”，上阵不为甲兵所伤，尖锐的兵器，也没有办法发挥它的作用。“夫何故？”为什么会这样？“以其无死地”，不把自己置于死地，这样也就不会让自己的生命受到戕害。这是就是五十章。这一章体现了道家的养生之道：简单地说就是不要“作死”，自己不要找死，本来可以长寿的，自己作死把自己置于死地。很多人非得触犯法律的界限，甚至因此送掉了自己的生命，这不就是把自己置于死地嘛！所以我们说“NoZuoNoDie”，不作不死。从养生的角度来讲，你看道家讲的顺应自然，不单只是生活中的清心寡欲，而且还指不触犯边界底线，不触犯红线，知足不辱，知止不殆，不置身于死地，不让自己冒这种凶险，这也是道家养生之道里边的一个重要的内容，而且是更接近于哲学层面的、更有智慧的内容。那么这一段我们讲完了之后，我还要跟大家强调一下，道家的养生观，其实也是道家的生命观。道家对于生命的看法讲究的是自然而然，意思是什么呢？过于求生，过于厌恶死，这都不是一种自然而然的智慧，因为死亡本身就是生命的一部分，人自然而生，自然而死，真的到了生命结束的时候，那也应该开朗地、乐观地对待。这一点在道家的继承者那里，也就是道家的第二号人物庄子那里，讲得非常的明确——“之所以善吾生者，乃所以善吾死”。我们很好地对待自己的生命，不把自己的生命主动地置于死地，不求生之厚，真的面临死亡的时候，也应该把它好好地对待。自然而生，自然而亡，这是生命的自然而然的规律，谁也阻挡不了。第五十章，老子借养生之道讲了一个更重要的道理：有的人求生太急迫，太厌恶死亡，太害怕死亡，越是求生之厚，服了大量的药，用各种各样的营养的方式，推开死亡，想要避免，没想到越想避免的反而来得越快。所以，道家讲究自然而然的思想，这有着重要、杰出的意义。我们做个小小的梳理。第五十章，我们从开始讲的时候就给大家讲过，这一章可以分成两段，一段是讲有的人本来可以长寿，却进入了短命的行列，是因为“求生之厚”，太急迫、营养过剩导致的，另外一个是由于妄为、“作”，把自己置于死地的。怎样才能避免这两点呢？还是道家的这种思想，顺其自然，清心寡欲，清静为天下正。正确地对待生命和死亡，不把死亡当作是完全可以避免的事情，真的面临死亡的时候，也能够开朗地、乐观地对待。</t>
   </si>
   <si>
     <t>第五十一章（51）</t>
@@ -926,7 +926,7 @@
     <t>道生之，德畜（xù）之，物形之，势成之。是以万物莫不尊道而贵德。道之尊，德之贵，夫莫之命而常自然。故道生之，德畜之：长之育之、亭之毒之、养之覆之。生而不有，为而不恃，长而不宰，是谓玄德。</t>
   </si>
   <si>
-    <t>道生成万物，德蓄养万物，万物有了具体的形状，周围的环境使万物得以成长。因此万物没有不尊崇道和重视德的，道受到尊崇，德受到重视，并没有人如此命令 而是万物本身自然而然地永远去这样做。所以道生成万物，德蓄养万物：使万物成长作育，使万物成长成熟，使万物得到养覆保护。道、德养育了万物却不据为己有，帮助了万物却不求它们的回报，成就了万物却不做它们的主宰者，这可以说是最高尚的品德。</t>
+    <t>道生成万物，德蓄养万物，万物有了具体的形状，周围的环境使万物得以成长。因此万物没有不尊崇道和重视德的。道受到尊崇，德受到重视，并没有人如此命令 而是万物本身自然而然地永远去这样做。所以道生成万物，德蓄养万物：使万物成长作育，使万物成长成熟，使万物得到养覆保护。道、德养育了万物却不据为己有，帮助了万物却不求它们的回报，成就了万物却不做它们的主宰者，这可以说是最高尚的品德。</t>
   </si>
   <si>
     <t>第五十一章逐句地来解释一下。“道生之”，“生”，创造，生养。道创造了万事万物。“德畜之”，德畜养了万事万物。“物形之”，万事万物有了具体的形状。“势成之”，周围的环境使它得以成长。正因为如此，所以“万物莫不尊道而贵德”，以道为尊，以德为贵。“道之尊，德之贵，夫莫之命而常自然。”尊道贵德，那自然会得到一个良好的结局和结果，这不是命，这就是自然而然的规律、规则。“故道生之，德畜之。”所以道生养万物，德蓄养万事万物。“长之、育之”，使它成长，使它不断地培育长大。“亭之、毒之”，这个“亭”呢，其实也好理解，我们常说亭亭玉立，这个“亭”就是成长的意思。这个“毒”就是成熟的意思，使万事万物成长，使其成熟。“养之、覆之”，“养”和“覆”都是保护的意思。养育万物，保护万物。“生而不有，为而不恃，长而不宰。”生养了万事万物，却不把它当作私有的产品，对万事万物有作为，却不把这个当作一种倚仗、凭借，甚至勒索的手段，对万事万物有这么大的功德，却不是以主宰者的身份出现。这个就是“玄德”，这就是最高深的、最深刻的智慧与品德。这是我们对这一段的直观的解释。其实，这一段的深意远不止于此。因为中国人讲哲学讲究“知行合一”，讲道的品性，其实也是为了人向道的品性去学习，按照道去做，这个也就是“德”。所以第五十一章里边讲道养育万物，德蓄养万物，也是人应该效法学习的。在这个层面上，我们深入地理解这一段话。“道生之，德畜之”，道创造了万事万物，但是它不把万事万物作为一种私有产品，并不是以一种主宰者的身份，以求其回报。由此我们可以看到，老子给我们提供了想要做成一件事的四个核心的要素和条件，也就是一种应有的程序和原则。第一个，要有道，因为道是创造万事万物的本源，所以我们要坚守大道，按大道的方式来创造。第二个，“德畜之”，“畜”就是积累的意思。在有道的基础上，我们要不断地、坚定地按照道去做，也就是“积德”。德就像水一样，我们就像一条船一样，我们积累的水越多，我们这条船在水上才能够航行得更自由。所以朱熹有一首诗说：“昨夜江边春水生，艨艟巨舰一毛轻。向来枉费推移力，此日中流自在行。”昨天江边涨水了，平常推也推不动的大船，现在根本不用推了，水多了，自然而然地就航行更加自由。他讲的是读书的积累达到一种自由的境界，其实人生又何尝不是如此呢？我们积累的德多了，按照道做事，更坚定、坚持、持久，那也就给我们人生提供了更广阔的空间与平台，不断地积德，我们的行为也就更加自由，我们的行为也就更加能够符合大道。庄子在《逍遥游》里面也讲了这样一句话，“且夫水之积也不厚，则其负大舟也无力”。水积累不多的时候，大船是浮不起来的，只要积累得多了，结果就是自然而然的事情，和朱熹所讲的道理不谋而合。第三个，“物形之”。人有道有德，是不是就可以把事情做成了呢？不够的，还需要一定的物质条件和手段，巧妇也难为无米之炊。有条件要上，没有条件我们创造条件，这样才能把事情向更成功的方向去发展。道、德、物三个条件总够了吧？不够的。要想把事情真正做成，还有一个很重要的条件，就是“势”，“势成之”。道家讲的无为，更强调的是顺势而为，掌握这个形势，了解大势，这样才能把事情做成。《淮南子》中举过这样的一个例子，大禹为什么能把水治成呢？顺水势而为。商汤周武为什么能夺得天下呢？顺民心而为。民心所向，就是历史发展的大势与潮流。所以大家在第二个层面把这四个字提炼出来，它是一个很好的成功学的例证，我觉得比现在讲的一些所谓的零零散散的成功学，不知道要深刻多少倍。道、德、物、势，“道生之，德畜之，物形之，势成之”。既然这四个要素，道和德是排在最前面的，“是以万物莫不尊道贵德”，所以万事万物没有不尊道而贵德的。人更是如此，有道有德，后边的事情才能继续发展，所以“道之尊，德之贵，夫莫之命而常自然”，这不是命，这就是一个永恒的自然而然的规律、规则。你按照道，按照德，尊道而贵德，会得到一个自然而然的良好的结局和结果，这是自然而然的事情。这不是命，这就是自然而然的规律和规则。所以大家注意，我们中国的这些经典，比如说《易经》，比如说《道德经》，都不是用来算卦占卜的，它就讲一个重要的内容：按照规律、规则来做，结果水到渠成、自然而然。下面这一段是对上面做的一个延伸。“道生之，德畜之”，道和德，生养万物，为万物提供条件，让它生长发展。“长之、育之”，培育万事万物使其生长、发展。“亭之、毒之”，使它成长、成熟。“养之、覆之”，不仅如此，还要养护万物，覆盖万物。道和德让万物长大，培育万物的成长，使它成熟又予以保护，功德可谓无量。孔子有一段名言：子曰：“予欲无言。”子贡曰：“子如不言，则小子何述焉？”子曰：“天何言哉？四时行焉，百物生焉，天何言哉？”这段话的直译是：孔子说：“我现在只想沉默。”子贡说：“如果你不说出心里想什么，那么我们这些学生还拿什么去记述呢？”孔子说：“自然说过些什么？不过放纵四季周而复始，任由百物蓬勃生长。自然你又何曾告诉别人什么啊？”很多人把这段话中的“天”翻译成神灵，这是不对的。其实这个“天”指的是大自然，也就是《道德经》里的天地，天地无语而泽被苍生万物，确又无语不居功自傲，不把自己当做万物主宰。这不也是《道德经》第五十一章的核心吗？培育万物的成长，使它成熟又予以保护，功德可谓无量。其实，在这样的智慧层面，孔子和老子的见解都是一样，“生而不有，为而不恃，长而不宰，是谓玄德”。关于这段重要的话，我们在第十章已经详细说过，不再重复。</t>
@@ -935,10 +935,10 @@
     <t>第五十二章（52）</t>
   </si>
   <si>
-    <t>天下有始，以为天下母。既得其母，以知其子；既知其子，复守其母，没（mò）身不殆。塞其兑（duì），闭其门，终身不勤。开其兑，济其事，终身不救。见小曰明，守柔曰强。用其光，复归其明，无遗身殃，是为习常。</t>
-  </si>
-  <si>
-    <t>天下万事万物都有本源（即道），可以把这个本源作为万物的母亲。认识了作为万物之母的道，就能认知万物；认知了万物，就能坚守作为万物之母的道。这样终身都没有危险。塞上欲望的孔穴，闭上欲望的门户，终身都没有忧劳；打开感官欲望的门户，增添纷繁的事件，终身都不可挽救。察见细微的事物叫“明”，坚守柔弱叫“强”。用道的光芒来了解具体事物中的规律、规则，复归到事物的光明的状态，不会给自己留下那么多的祸殃，这就叫普遍永恒的规律（可以说是掌握了大道）。</t>
+    <t>天下有始，以为天下母。既得其母，以知其子；既知其子，复守其母，没（mò）身不殆。塞（sè）其兑（duì），闭其门，终身不勤。开其兑，济其事，终身不救。见小曰明，守柔曰强。用其光，复归其明，无遗身殃，是为习常。</t>
+  </si>
+  <si>
+    <t>天下万事万物都有本源（即道），可以把这个本源作为万物的母亲。认识了作为万物之母的道，就能认知万物；认知了万物，就能坚守作为万物之母的道。这样终身都没有危险。塞上欲望的孔穴，闭上欲望的门户，终身都没有忧劳。打开感官欲望的门户，增添纷繁的事件，终身都不可挽救。察见细微的事物叫“明”，坚守柔弱叫“强”。用道的光芒来了解具体事物中的规律、规则，复归到事物的光明的状态，不会给自己留下那么多的祸殃，这就叫普遍永恒的规律（可以说是掌握了大道）。</t>
   </si>
   <si>
     <t>一开始我们就说过，《道德经》里边有一个非常好的“正能量”，就是每当说到高大上的、特别伟大的事情，都喜欢用母亲的“母”字来作为代替和概括，或者说用“母”来做一个形象的比喻。如果我们的孩子读这样的文字，潜意识里就会有对母亲有一种敬畏与尊重。我们在第一章里边就说到，“无，名天地之始；有，名万物之母”。在这一章里边，又出现了母亲的这个“母”的概念。“天下有始，以为天下母。”就像动物、人类都是由母亲生养的一样，万事万物也都是由道创造的。老子用“母”来比喻大道，生动形象且让人充满对道的敬畏，意思就是说，天地一开始的时候，其实大道已经就在了。“既得其母，以知其子。”我们了解了大道，就是“既得其母”。知晓了大道，那我们就“以知其子”，也就了解了儿女。这个意思是什么呢？道是万事万物的普遍规律，它永恒存在，具体的事物都拥有具体的道，也就是具体的规律。你了解了大道，就可以以此来了解万事万物的具体规律。茶有茶道，花有花道，练武有武道，下棋有棋道……了解了普遍的道，也就更能够了解这些具体事物间的规律与规则。反过来也一样，“既知其子，复守其母。”我们从具体的事物之间，比如棋道、花道、茶道，从这具体的事物之间，我们了解了大道，感知了大道，那也就能更好地坚定地坚守大道。“没身不殆”，这样地做事情永远没有危险，没有失败，为什么？以道佑之，以道护之，这样我们做事情才能没有危险，没有失败。下面就说了解大道的方式方法。大道的了解，不是靠感性来体验到的，就像我们前边说的，“为学日增，为道日损。”“不出户，知天下；不窥牖，见天道。”所以如果是跟着感觉走的话，你是了解不了真正的大道的。因此“塞其兑，闭其门，终身不勤”，不要依赖感觉，不要把我们所见所知的就当作大道，重要的要用心，也就是哲学上讲的，用理性的思维，来了解认知大道。反过来讲，“开其兑，济其事，终身不救”，如果跟着感觉走，打开我们的感官的门户，感官这个东西，它是有很大的局限的。第十二章里面就讲，“五色令人目盲，五音令人耳聋，五味令人口爽”。你只靠这个是了解不了大道的。“见小曰明，守柔曰强。”什么叫“见小”啊？“小”就是具体的事物，具体的事物里面也蕴含着规律、规则。你能够从具体事物里了解具体的道、具体的规律，这也是一种明智。“守柔曰强”，道家是讲“柔弱胜刚强”的，道家是讲“知其雄，守其雌”的，“柔”就是雌柔，不管我们多么强大，我们也懂得坚守这个柔弱，因为柔弱更能长久。力量不够的时候，我们懂得用守柔的方式、韬晦的方式，来使自己的力量不断增大、不断增强，这样才能成为真正的强大。“用其光，复归其明”，用道的光芒，“复归其明”，来了解具体事物中的规律、规则，复归到事物光明的、明智的状态，我们才能走在光明的大道上。“无遗身殃”，不会给自己留下那么多的祸殃。“是为习常”，这个“习”，不同的本子有不同的写法。习，就是普遍、永恒的意思，就是普遍的永恒的规律、规则。也有的本子用的是沿袭的“袭”，也就是遮盖的意思。《道德经》里边用这个“袭”字的意思就是说，这是被大家认识不到的、被遮盖的规律规则，了解了这一点，我们也就对事物的了解更加深入。这两个意思都通，我们这里边用的是复习的“习”，学习的“习”，也就是经常的、普遍的、永恒的意思。“是为习常”，这就是一个经常的、普遍的、永恒的规律、规则。这一章核心的内容是说，道是一个普遍的规律，它存在于天地之间，所以叫“大道”。我们了解了大道，掌握了普遍的规律、规则，再来认识具体事物中的规律、规则，这是非常有帮助的，也是非常重要的。反过来也是一样，了解了具体事物中的规律、规则，也能够让我们更加坚信大道的存在，更加了解大道的伟大。这一章以母和子为喻，大和小对照，就讲述了这样的一个哲学的道理。这样的智慧能让我们用到大道的光芒，走在光明的大道上。</t>
@@ -950,7 +950,7 @@
     <t>使我介然有知，行于大道，唯施（yí）是畏。大道甚夷，而民好径。朝甚除，田甚芜，仓甚虚。服文彩，带利剑，厌饮食，财货有余，是为盗滥竽（yú）。非道也哉！</t>
   </si>
   <si>
-    <t>假如让我稍微有些认知，行走在大道上，最害怕走到斜路上去。大道非常平坦，但一般人喜欢走捷径。（无道之君）朝政非常混乱，田园非常荒芜，仓库非常空虚。穿着华美的衣服，佩带锋利的宝剑，吃饱喝足，积存财货有余，这样的人叫做强盗头子（滥竽：强盗头子）途径。这种行为是不符合大道的！</t>
+    <t>假如让我稍微有些认知，行走在大道上，最害怕走到斜路上去。大道非常平坦，但一般人喜欢走捷径。（无道之君）朝政非常混乱，田园非常荒芜，仓库非常空虚。穿着华美的衣服，佩带锋利的宝剑，吃饱喝足，积存财货有余，这样的人叫做强盗头子（滥竽：强盗头子）。这种行为是不符合大道的！</t>
   </si>
   <si>
     <t>讲到这里大家已经非常清楚了，老子衡量事情的最高原则就是大道。“使我介然有知”，“芥”就是小的、稍微的意思。假如让我稍微有知识、有智慧，“行于大道”，走在大道上。我最怕的是什么呢？“唯施是畏”，“施”，就是逶迤、曲折，在这里指的是邪路、歧路。走在大道上最可怕的是什么呢？就是害怕歧路太多，害怕走到邪路上去。“大道甚夷，而民好径。”其实大道是非常平坦的，但是一般人都喜欢走捷径，老想抄近道。“朝甚除”，朝政非常得混乱。“田甚芜”，田园都已经荒芜了。“仓甚虚”，仓廪实才好嘛，现在仓库里边都是空虚的。可是那些统治者在干吗呢？“服文采，带利剑。”穿着漂亮的、非常昂贵的衣服，带着珍珠宝石装饰的利剑。“厌饮食”，什么东西都吃腻了，对什么好吃的东西都已经感觉到厌烦了。“财货有余”，家里的财宝有那么多的富余。这叫什么？“是为盗夸。”《道德经》认为这个就叫“盗夸”，强盗，还夸耀自己的强盗行为。《道德经》在第七十七章里边就讲，“天之道，损有余而补不足”。现在这些人做的是什么呢？“损不足，以奉有余”。“非道也哉”，这完全不符合道的规律、规则，完全不是按照道的方式来做嘛。这一章表现了老子的平民的思想、公平的思想，指责在“朝甚除，田甚芜，仓甚虚”的情况下，那些人“服文彩，带利剑，厌饮食，财货有余”夸耀自己的强盗行为。这一章有一些字，我们还得具体地、细致地解释一下。“唯施是畏”，凭什么把这个“施”念成“迤”，解释成歧路呢？因为道弯弯曲曲的时候，歧路众多。在《列子•说符篇》里边讲的一件事——歧路亡羊。杨朱他们家的邻居羊丢了，很多人都出去找，杨朱就觉得很奇怪就问，就一只羊怎么这么多人去找啊？邻居就告诉他，歧路多，岔路太多了。找羊的人回来了，杨朱问找到了吗？邻居说没找到。又派更多的人去找，还没有找到。歧路中又有歧路，岔路中又有岔路，所以常常使人丧失了大道，迷失了大道，所以杨朱听了之后几天都不说话。古人有“歧路亡羊”，也有遇穷途而哭，走道遇到没有路了，痛哭而返，其实都是感觉到了人生道路上的一些很值得人害怕的事情。行于大道，最害怕的就是歧路、岔路，一旦走错路，方向一错，后边的一切麻烦就都来了。所以老子说“大道甚夷”，“夷”就是平坦的意思，大道其实极为平坦。“而民好径”，人却老喜欢去走这个捷径，走了捷径之后，最后发现回到正确的大道上是非常困难的。其实，很多的所谓捷径就是歧路，就是邪路，人要脚踏实地，这样才能够行走在正确的大道上。通过努力获得成功，而不要投机取巧，更不要把投机取巧里边得到的东西当作一种炫耀夸耀，这个叫什么？“盗夸，非道也哉。”</t>
@@ -983,10 +983,10 @@
     <t>第五十六章（56）</t>
   </si>
   <si>
-    <t>知者不言，言者不知。塞其兑，闭其门，挫其锐，解其分，和其光，同其尘，是谓玄同。故不可得而亲，不可得而疏；不可得而利，不可得而害；不可得而贵，不可得而贱，故为天下贵。</t>
-  </si>
-  <si>
-    <t>有智慧（懂得大道）的人不多言，多说话的人不是有智慧的。圣人塞上欲望的孔穴，闭上欲望的门户，收敛锋芒，解除纷扰，在光明之处便与光融合，在尘垢之处便与尘垢同一，这就叫“玄同”。所以既不可能与这样的圣人亲近，也不可能与他们疏远；既不可能使他们得利，也不可能使他们受害；既不可能使他们尊贵，也不可能使他们卑贱。所以他们被天下人所尊崇。</t>
+    <t>知（zhì）者不言，言者不知（zhì）。塞其兑，闭其门，挫其锐，解其分，和其光，同其尘，是谓玄同。故不可得而亲，不可得而疏；不可得而利，不可得而害；不可得而贵，不可得而贱，故为天下贵。</t>
+  </si>
+  <si>
+    <t>有智慧（懂得大道）的人不多言，多说话的人不是有智慧的。圣人塞上欲望的孔穴，闭上欲望的门户，收敛锋芒，解除纷扰，在光明之处便与光融合，在尘垢之处便与尘垢同一，（能做到这些）这就叫“玄同”（就是与道同体）。所以既不可能与这样的圣人亲近，也不可能与他们疏远；既不可能使他们得利，也不可能使他们受害；既不可能使他们尊贵，也不可能使他们卑贱。所以他们被天下人所尊崇。</t>
   </si>
   <si>
     <t>这一章还是比较容易理解的。“知者不言，言者不知。”开头的第一句话就讲，有智慧的人是不多言的，所谓“行不言之教”，还有“悠兮其贵言”，都在讲这个道理，有智慧的人是不会多嘴多舌的，不会去乱说的。“知者不言，言者不知”，老是认为自己无所不知、以为自己有智慧的人，其实是不具备真正的智慧的。“塞其兑，闭其门。”我们前边解释过，“兑”指的就是耳、目、鼻、舌这些感官，所以它强调的是感性对事物的认识，是不可信的。“塞其兑，闭其门”，这样才能对事物本质的根本的内容有真正的理解。下面讲处理问题的方式方法，做人的思想与智慧，要“挫其锐，解其分，和其光，同其尘”，不要锋芒外露，这样才能长久。要解除那些纷纷扰扰，不要让纷纷扰扰在心里打成结——心有千千结。真正了解道的含义的人，按照道去做事的人，是很容易摆脱这些纷纷扰扰的。“和光同尘”，也就是讲同流而不合污，所谓外圆而内方，所谓与世推移。那么这个叫什么呢？就叫做“玄同”。“玄”本来是天的颜色，意味着深远，这样的同是深远的、深刻的，同流而不合污，当然里边就非常有玄妙了。下面的内容讲得也非常清楚，就是说道并不是为人谋利益的，得道的人他怎么样来和万事万物打交道呢？就像道一样，“不可得而亲，不可得而疏”，道并不是对谁更亲近，或者对谁更疏远。有亲就必有疏，有疏就必有亲，这个就不平等了，这就不“玄同”了。所以，按照道的、“玄同”的方式来做，没有亲疏之别，无差别。“不可得而利，不可得而害”，有利必有害，有害也必有利。所以你并不能凭借道而获利，也不能用这个道来危害别人，无差别，无利无害。“不可得而贵，不可得而贱”，道对谁也没有贵贱之分，还是依然玄同、平等，一旦有贵贱之别，便也就丧失了道的本质的属性。所以庄子讲，“以物观之，自贵而相贱。以俗观之，贵贱不在己。”从物的角度来看，都认为自己是珍贵的、宝贵的，其他的东西比不上自己的尊贵。用世俗的观点来看，贵和贱不在于自己，而在于别人的评价，在于外在的标准。而“以道观之，物无贵贱”，从道的角度来看，这万事万物并没有什么贵贱之分，所谓公正、平等、无差别、无贵贱之分。正是因为这样，所以它成为天下最尊贵的，“故为天下贵”。所以这章的内容啊，道表现为玄同，按照这样的深远的玄同的道理来理解事物，就是从道的角度来观察问题。道没有亲疏之别，没有利害之分，没有贵贱之差，所以用这样的一个角度来观察世界，这个才使它成为天下最令人敬重尊仰的，“故为天下贵”。</t>
@@ -998,7 +998,7 @@
     <t>以正治国，以奇用兵，以无事取天下。吾何以知其然哉？以此。天下多忌讳，而民弥贫；民多利器，国家滋昏；人多伎巧，奇物滋起；法令滋彰，盗贼多有。故圣人云：我无为而民自化，我好静而民自正，我无事而民自富，我无欲而民自朴。</t>
   </si>
   <si>
-    <t>以清静无为之正道治国，以奇巧诡计用兵，以不多事滋扰来取得天下。我怎么知道是这样呢？因为如下情况：天下的忌讳（禁令）太多，人民就越来越贫穷；百姓拥有很多锋利武器，国家就会越来越混乱；人民拥有很多奇技淫巧，奇怪甚至邪恶之事就会越来越多；法律条文越严苛，盗贼反而会越来越多。所以圣人说：我无为（不去人为干涉），人民便自我化育成长；我做到内心清静，人民就会自己走上正道（品行端正）；我不多事不扰民，人民自己就会富起来；我没有私欲，人民自然就会淳朴。</t>
+    <t>以清静无为之正道治国，以奇巧诡计用兵，以不多事滋扰来取得天下。我怎么知道是这样呢？因为如下情况：天下的忌讳（禁令）太多，人民就越来越贫穷；百姓拥有很多锋利武器，国家就会越来越混乱；人民拥有很多奇技淫巧，奇怪甚至邪恶之事就会越来越多；法律条文越严苛，盗贼反而会越来越多。所以圣人说：我无为（不去人为干涉） 人民便自我化育成长；我做到内心清静 人民就会自己走上正道（品行端正）；我不多事不扰民 人民自己就会富起来；我没有私欲 人民自然就会淳朴。</t>
   </si>
   <si>
     <t>第五十七章的这段话非常有智慧，因为这段话一开始就指出来了，事物之间的不同，有本质的区别，所以处理问题、解决问题的方式方法也不一样。“以正治国，以奇用兵”，治国讲究的是堂堂正道。道家讲的“正”当然就是清静无为，不多事，不扰民，这就是道家讲的正道，是治国的大道理。可是用兵讲究的是“以奇用兵”，“兵者诡道也”，兵不厌诈。所以不能把用兵的方式、战争的方式用到治国的上面来，这两者不同，解决的方式也不一样。“以无事取天下”，无事就是不多事、不扰民、不刁难，这样才能够得到天下，并且坐得了江山。道家“无事”是“无为”的一个重要的方面，不多事、不扰民、不刁难，而“有为”讲的是妄为，多事、扰民、刁难，我们在前边这一点已经非常明确了。“吾何以知其然哉”，我怎么知道是这个样子呢？所谓“以此”就是依据上边“以正治国，以奇用兵”它们之间的本质不一样，所以解决的方式方法也不同而得出的结论。下面，老子开始谈他对治理天下的重要的看法。违背了大道，违背了道家的以“清静无为”为根本来治理国家的方式，会出现什么问题呢？“天下多忌讳，而民弥贫”，治理天下、领导国家忌讳太多，这个也不能动，那个也不能动，这个人的职务比较高，法令涉及不到他，当然出现了忌讳，不敢动，这个地方一定会形成一个空场，形成一个腐败的群体。百姓当然越来越穷了，财富都集中在少数人的手上。“民多利器，国家滋昏”，“滋”就是越来越。如果民间利器众多，武器众多，民与民之间械斗、抗法，那国家当然越来越混乱。“人多伎巧，奇物滋起”，“伎巧”就是各种各样的奇技淫巧，越来越多，大家对这些越来越感兴趣，这个技巧能够给他们带来利益，那么各种各样的奇奇怪怪的东西，甚至包括那些妖孽的东西，就不断兴起。“法令滋彰，盗贼多有”，既然这样，要用法律来管，法条定得越来越多，越来越严苛，反而盗贼越来越多。在前面这一段讲完之后，《道德经》说“故圣人云”，很明显，这是引用以往的通达事理的王们的话，老子用自己心中有智慧的人的语言来作为结尾。“我无为而民自化”，道家讲的无为，第一，“不妄为”。第十六章里边说“不知常，妄作，凶”，不了解事物的规律、规则，瞎折腾、胡折腾，这个结果是非常糟糕的。第二是“不多为”。抓住关键，举重若轻，多言数穷，不如守中，适可而止，恰到好处。第三讲究的是“有所不为”。人要想有所为，必须有所不为。一个政府也罢，一个领导者也罢，所有的事情都抓在自己手上，那底下的人怎么得到锻炼呢？不把担子压给他，他怎么练出独当一面的能力呢？什么事都控制在自己手上，那众人怎么样自我化育自我成长呢？所以无为才能让国家的人民、才能让自己的属下自我化育自我成长。事情成了应该怎么样呢？第十七章“功成事遂，百姓皆谓‘我自然’”，事情做成了，百姓都说这是我们的努力把这事情做成的，这就叫“民自化”。“我好静而民自正”，前面我们讲过，道家讲的静，内心的清净，静下来才能找到解决事物的正确的方法。我清静，走正道，不那么浮躁、急躁、暴躁、狂躁，做一个好的表率，上梁而正，百姓当然也就正了，百姓当然也就好静而走正道了。“我无事而民自富”，不多事、不扰民、不刁难，那百姓自然就富起来了。“我无欲而民自朴”，“朴”就是原木，《道德经》里用原木喻指做事敦厚、朴实、厚道，没那么多欲望，不是老想抢夺别人、占有别人的。就像黄宗羲在《明夷待访录》里边讲的，古代的那些皇帝都是什么样的？“离散天下人之儿女，荼毒天下人之肝脑，以供一人之淫乐。”这是我的，普天之下都是我的。所以欲望无止境，你让百姓能够朴实厚道，这也不可能。所以不要欲壑难填，不要什么东西都看作是自己的，可以任意掠夺，这样百姓自然就朴实、厚道，民心淳朴。这里边的两句话，我们国家的领导者讲话的时候也经常引用：“我无为而民自化，我无事而民自富。”所以，第五十七章讲了两个重要的道理，第一个不能把打仗的这一套用到治国之上。治国讲究的是堂堂大道，讲究的是清静无为，所以以无事取天下。第二个就讲站在领导者的角度，站在统治者的角度，应该怎么做呢？无为、好静、无事、无欲，这样自然一切顺理成章，百姓就会自化、自正、自富、自朴，事成了也会“功遂身退，百姓皆谓我自然”。这是一个好的领导者、好的政府做事的道理之所在，反之越多事儿，越是用那种严苛的法令，导致的结果适得其反。忌讳多了，百姓就越来越穷，民间的利器多了，国家就越来越混乱，大家都倾向于奇技淫巧，把这个当作一种喜欢的甚至不停地去追求的目标，那这个国家就越来越怪，各种奇葩的事情都纷至沓来。越觉得法令不够，越制定得严格、细致，以为单靠着法令就可以解决所有问题，反而适得其反，盗贼多有。所以，这一章里边讲的，也是我们经常说的——这本书的总纲：“反者，道之动”。我们考虑问题，不要只考虑它一面，要相反相成，用一个更高的观察事物的角度来理解。</t>
@@ -1013,7 +1013,7 @@
     <t>其政闷闷，其民淳淳；其政察察，其民缺缺。祸兮福之所倚，福兮祸之所伏。孰知其极？其无正。正复为奇，善复为妖。人之迷，其日固久。是以圣人方而不割，廉而不刿（guì），直而不肆，光而不耀。</t>
   </si>
   <si>
-    <t>（治国者）为政宽容，人民就会淳朴善良；为政苛察，人民就会变得狡猾奸诈。灾祸啊，幸福就依靠在它的旁边；幸福啊，灾祸就埋伏在它的里面。谁能知道最终的结果是祸是福呢？没有确定的标准（永恒正确的事情）。正确会变为邪恶，善良会化作妖孽。人们不懂得这一道理，已经有很长的时间了。因此圣人方方正正却不去为难别人，有棱角但不去伤害别人，自己坚持正直品德却不强迫人去做，有光芒但内敛，不刺眼炫耀。</t>
+    <t>（治国者）为政宽容，人民就会淳朴善良；为政苛察，人民就会变得狡猾奸诈。灾祸啊 幸福就依靠在它的旁边；幸福啊 灾祸就埋伏在它的里面。谁能知道最终的结果是祸是福呢？没有确定的标准（永恒正确的事情）。正确会变为邪恶，善良会化作妖孽。人们不懂得这一道理，已经有很长的时间了。因此圣人方方正正却不去为难别人，有棱角但不去伤害别人，自己坚持正直品德却不强迫人去做，有光芒但内敛 不刺眼炫耀。</t>
   </si>
   <si>
     <t>第五十八章有两个我们非常熟悉的成语，一个叫“祸福相依”，一个叫“光而不耀”，也是这一章核心的内容。祸福相依，福和祸是相互转化的，两者也是相辅相成的，分不开的。“光而不耀”在讲什么呢？我们大家看到过月亮，月光是明亮的，在黑暗中给我们指引以方向；同时月光也是不张扬的、不炫耀的、不刺眼的。中国人喜欢拿月亮来比喻君子的形象，做君子得先有光，但是不管我们有什么，都不要老想着去张扬、炫耀，让别人感觉到刺眼。所以《道德经》很多章节，都向我们揭示了这样一个道理：有才华、有知识、有道德的人，不要老想着去张扬、炫耀。以这两个成语为切入点，我们会对这一章的内容有个直观的感觉。我们来逐字逐句地解释一下。“其政闷闷”，“闷”就是淳厚。就说政治比较淳厚宽容，那么这个国家的百姓也就是敦朴淳厚，不耍心眼。“其政察察，其民缺缺”，假如这个政治非常苛察，对一切都监控得到位，那老百姓就会感觉到有很多的缺陷与不足，就要耍心眼。所谓上有政策，下有对策，也就失去了原本的淳朴。“祸兮福之所倚，福兮祸之所伏。”福和祸是相辅相成的，在一定条件下是相互转化的。民间的很多说法，大家都能够体会到这意思的延伸和运用，比如，我们经常说“大难不死必有后福”、“好事多磨”……福和祸是相伴而行的，有时候我们认为是福的事情，它可以转化为祸，反过来也是一样，所以这就叫“祸福相依”。怎么样来理解这个事情呢？给大家举个例子，大家就清楚了。其实各民族的智慧到达高点的时候，往往是相互重合的，印度有一本佛经叫《大般涅槃经》，在这里面讲了这样一个故事。有一天早晨，一家主人一开门，门口站着一个衣着光鲜、非常漂亮的女子，主人就问你是谁，女子说我是“功德大天”，我到谁家谁家就一切兴旺。主人高兴地请进来，焚香供拜。刚一关门又有人敲门，开门一看，门口站着一个衣衫褴褛，非常丑陋的、黑瘦的女子，主人就没好气了，主人就问你是谁呀，那女子说我是“黑暗”，我到谁家，谁家就一切破败！主人当然不让她进来，拿着刀驱赶。结果这女孩说你太笨了，刚进去的是我姐姐，我们俩从出生这天起就没有分开过，你把我赶走了，她也留不下。主人不信，进去一问果然是这样。福跟祸是相伴而行的，所以它就提醒我们，遇到福事的时候就要小心谨慎，避免乐极生悲；遇到祸事的时候，也不要感觉到沮丧，因为我们对灾祸有所警惕，它可以避免后面更大的灾难。韩非子讲过“千里之堤，溃于蚁穴”，我们发现了这个蚂蚁窝，知道它是一个祸患，很早的把它堵上，那就避免了以后更大祸事的发生。这就是“祸福相依”的道理，在我们文化中影响是非常深刻的。讲完这一段后，《道德经》就说“孰知其极？”这个事物到达极点的时候，向它相反的方面转化，所谓两极相通，所谓物极必反，但是这个极在哪里呢？这个是需要我们认真去体会把握的。“其无正”，其实并没有确定的标准，所以并没有说我们到了一个什么程度，一定会向它相反的方面转化，这是要根据不同的时间、地点、条件，需要我们认真去领会把握的、体悟的一种智慧。“正复为奇，善复为妖。”“正”，你把它弄到极点它就偏了，“善”到达极点的时候，它就转化为它相反的方面。有些人老想寻找一个固定的标准，《道德经》就说：“人之迷，其日固久。”在这个方面的迷惑，时间已经由来已久。所以我们总是要寻找一个固定的标准，总是觉得做事情有一个固定的程序，固定的套路，这个就不圆融。下面就讲，“是以圣人方而不割”，“方”就是方正，“割”就是生硬。有原则但是不生硬，人要懂得去碰硬，但是不要去硬碰。方正而不生硬，这样才能圆融，我们把它叫做“外圆而内方”。“廉而不刿”，“廉”就是棱角，“刿”就是锐利。有棱角但是不要老用锐利之处去刺伤人。“直而不肆”，有人经常就说，我说这话你别在意，我这人很直。其实有的时候不是直而是自私，是放肆、过分。所以我们说直率，它是一种心态，但是你讲话的方式得懂得圆融，直率而不放肆。“光而不耀”，有光芒，但是不要老去张扬、炫耀，让别人感觉到刺眼。咱们中国人喜欢讲君子，什么样的人是君子呢？中国人除了用月亮来代表君子“光而不耀”的特点之外，另外，也喜欢用玉来代表君子的形象，所谓“谦谦君子，温润如玉”。“谦谦君子”出自《易经·谦卦》，原话叫“谦谦君子，用涉大川”，一个人保持这种内敛的、谦逊的风度，这样才能走好人生长远的坎坷的道路。另外一个是出自《诗经》的“温润如玉”，谁都知道闪着贼光的肯定不是什么好玉，真正的好玉都是光芒内敛，给人一种温润感。我认为“光而不耀”是中国文化里，对君子形象用得最好的一个比喻。我们有知识，不要老想着去张扬、炫耀，大家聚到一块的时候，一个人老去炫耀自己的知识，对别人的说法都嗤之以鼻，认为自己什么都懂，百事通，时间长了，大家就不喜欢跟这人打交道了。有道德，道德是约束我们内心的，不是老是向别人去张扬炫耀。《道德经》第三十八章开头这句话，大家都知道——“上德不德”，最有道德的人从来不去张扬、炫耀自己的道德。当然，至于炫官、炫富，这不仅不是一种君子的形象，还会给自己惹来无尽的祸殃。是否还记得第九章里“金玉满堂，莫之能守；富贵而骄，自遗其咎”，炫富炫贵，会给自己惹来无尽的祸殃。在第二章里“功成而弗居”，哪怕我们有功劳，不管是对家庭、对单位、对国家有功劳，也不要老想着去张扬、炫耀，越是不张扬、不炫耀，这个才能在人心里长久地存在。第九章里面也说“功遂身退，天之道”，这是符合自然的道理。第五十八章讲完之后，我再做一下梳理和强调。这一章有两点需要注意，一个是“祸福相依”的道理，一个是“光而不耀”的形象，怎么样能做到这一点？我们要明白“物极必反，两极相通”。了解这样的智慧与道理，我们做事情才能够圆融。所以一个有智慧的人，有智慧的领导者，为人处事应该方正而不生硬，要圆融，有棱角，但不要老去割伤人，要懂得委婉迂回地处理问题的方式。直率，但又不越界进入到了放肆、无所顾忌的程度，光芒内敛而不要老去张扬、炫耀，要给人留下一种谦谦君子、温润如玉的形象。这是我们和别人、和这个社会打交道的一个重要的思想与智慧。</t>
@@ -1022,10 +1022,10 @@
     <t>第五十九章（59）</t>
   </si>
   <si>
-    <t>治人事天莫若啬（sè）。夫唯啬，是谓早服，早服谓之重积德。重积德则无不克，无不克则莫知其极。莫知其极，可以有国。有国之母，可以长久。是谓深根固柢（dǐ），长生久视之道。</t>
-  </si>
-  <si>
-    <t>治理人民要顺应天理，最好的办法莫过于节俭节制。只有节俭节制，才能早得道。早得道就是不断地积德修养自己。不断地积德就没有什么是克服不了的，没有什么克服不了就不知道它的力量有多强大。不知道其力量有多强大，（有了无可估量的力量）就可以掌管国家。掌握了治国的根本，就可以长久存在。这就是根本扎深、扎牢固，永世长存的办法。</t>
+    <t>治人事天莫若啬（sè）。夫唯啬，是谓早服，早服谓之重积德（chóng）。重（chóng）积德则无不克，无不克则莫知其极。莫知其极，可以有国。有国之母，可以长久。是谓深根固柢（dǐ），长生久视之道。</t>
+  </si>
+  <si>
+    <t>治理人民要顺应天理 最好的办法莫过于节俭节制。只有节俭节制，才能早得道。早得道就是不断地积德修养自己。不断地积德就没有什么是克服不了的，没有什么克服不了就不知道它的力量有多强大。不知道其力量有多强大，（有了无可估量的力量）就可以掌管国家。掌握了治国的根本，就可以长久存在。这就是根本扎深、扎牢固，永世长存的办法。</t>
   </si>
   <si>
     <t>这一章讲了两种生活的态度：一种是做“加法”，不断地叠加，不断地累积，有了还想更有，多了还想更多；另外一种是要懂得做减法，要节俭节制，有的时候我们的欲望减少一分，其实我们的幸福也就多一分。这两种人生态度也是相辅相成的，可是大家更注重的是第一种，所以一章就强调我们这种做减法的态度的重要性。其实这一章核心就讲四个字：节俭节制，讲节俭节制对一个国家、对社会的重要意义。“治人事天莫若啬。”一开始就讲“治人事天”，领导这个国家的人民要顺应天理。“莫若啬”，什么事情最顺应天理呢？节俭节制。我们现在用的这个词叫“吝啬”，这个词有点负面的含义，在《道德经》中这个“啬”，我们把它译成节俭节制，这样更符合于我们的接受习惯。“夫唯啬，是谓早服”，“夫唯”是个语气助词，“啬”是节俭节制。“是谓早服”，“早服”就是早得道。懂得节俭节制的道理，就是可以早得道的人。“早服谓之重积德”，“重”就是不断。懂得节俭节制就是在不断地积累自己的品德，积累自己的德行。因为我们说《道德经》道和德要分开理解，按照道去做，就是有德，不断地按照道去做，就是不断地积德。重积德就是不断地积德，所以你看“早服谓之重积德”，早得道，一直坚定地坚持按照这个去做，就是不断地积累自己的德性，积累自己的品德，积德。我们就像一条船，我们积的德就像水，水积累得越多，我们船才能自由地航行，不管你船多大，如果没有水，在那儿搁浅，它也发挥不了船的这种作用。“重积德则无不克”，“克”就是克服，按照这个“啬”的方式，也就是节俭节制的方式去做事情，那就没有什么困难克服不了的。因为在节俭节制里边磨练的就是人的思想品德，磨练的就是人的意志，磨练的就是人面对困难无所畏惧的态度。“无不克则莫知其极”，你说这个东西力量这么强大，没有什么东西它克服不了，所以它的力量“莫知其极”，你不知道它的力量有多么强大，对一个人是这样，对一个国家更是如此。“莫知其极，可以有国。”你看这话是给谁讲的？给统治者、领导者讲的。一个领导者领导团队，领导这个国家的人民培养出一种节俭节制之风，你这样才能让你的国家长久地存在，长久地发展。毛泽东主席在中华人民共和国成立的时候就指出，“贪污和浪费是极大的犯罪”，自己也以身作则。你领导团队，领导全国人民培养出一种节俭节制之风，这样面临什么样的困难的时候，大家都有信心去克服。“有国之母，可以长久。”“母”就是根本。节俭节制是立国，是国家长久发展的根本。我们现在叫“八项规定”“反四风”，领导国家的人民培养出节俭节制之风，国家才能长久持续地发展。有一件事儿大家都知道，电视经常打出一个公益广告，说现在每年中国人浪费的粮食就是世界上两亿人的口粮。你说世界上现在每天都有人在饿死，可我们中国人这么浪费，能符合天道，能符合天理吗？如果因为这种浪费有什么惩罚落到我们头上，那么我们也无话可讲。你从这一章里面就可以感觉到，一个人浪费，糟蹋的是自己的福分；一个国家浪费，糟蹋的是国家的福分，对国家的根本有所损伤。“是谓深根固柢，长生久视之道。”国家培养出节俭节制之风，才能长久发展，这样做叫什么？叫“深根固柢”。我们讲叫根深蒂固，你让这个根本、让根扎得深，扎得稳固，深根固柢。“长生久视之道”，于人来讲是如此，可以让我们的生命更为长久，因为一个人的节制节俭，不去放纵自己的欲望，这也是一种养生之道。得以长久地存在，长久地发展，得以长寿，对国家来讲也是如此。所以“长生久视”，长久地存在，大家能够长久地看到它。《道德经》强调“做减法”的这个方面，在世界哲学界，有着非常重要的影响。我们中国人有一个优良的文化传统，讲勤俭持家，讲勤俭治国，所以这个是我们文化中非常重要的方面，但是很少在哪一本著作里面把它强调到这样的一个高度。“治人事天莫若啬。夫唯啬，是谓早服。”这就是早得道，坚定地按照这个道去做，就叫积德。不断地积德，那就使我们能够根深蒂固，长久存在，长久发展。人如此，国家亦如此，道理是相同的。第五十九章，希望大家认真地品味体会老先生给我们讲的“根深蒂固”的道理。</t>
@@ -1037,7 +1037,7 @@
     <t>治大国若烹（pēng）小鲜。以道莅天下，其鬼不神。非其鬼不神，其神不伤人；非其神不伤人，圣人亦不伤人。夫两不相伤，故德交归焉。</t>
   </si>
   <si>
-    <t>治理大国就像烹调小鱼一样（不要经常折腾它）。（君主如果能够）用道来领导、指引天下，鬼也就没有神秘莫测的力量。不是说鬼不神秘莫测了，而是它的神秘莫测伤害不了得道的人。不但鬼的神秘力量伤不了百姓，圣人也不伤害百姓。鬼和圣人都不伤害百姓，所以德不断地积累交汇，形成有道有德的世界（恩德都将施与百姓）。</t>
+    <t>治理大国就像烹调小鱼一样（不要经常折腾它）。（君主如果能够）用道来领导、指引天下，鬼也就没有神秘莫测的力量。不是说鬼不神秘莫测了，而是它的神秘莫测伤害不了得道的人；不但鬼的神秘力量伤不了百姓，圣人也不伤害百姓。鬼和圣人都不伤害百姓，所以德不断地积累交汇 形成有道有德的世界（恩德都将施与百姓）。</t>
   </si>
   <si>
     <t>这一章有一句话，大家都非常熟，叫“治大国若烹小鲜”，这句话也是这一章的核心。一九八七年，美国前总统里根在发表国情咨文的时候也引过这句话。二〇一三年，“金砖各国”开会，在一个联合的采访中，有一位巴西记者问过习近平这样的一个问题：你担任这么大的一个国家的这么重要的职位是一种什么心态？你用什么样的态度来对待自己的职位？习近平答记者问，先引的是《诗经》，来回答第一个问题：“战战兢兢，如临深渊，如履薄冰。”这话出自《诗经·小雅·小旻》。治理国家要小心谨慎，就像行走在结着薄冰的冰面上一样，就像站在悬崖边一样，要小心谨慎，因为稍不谨慎就会出大的问题、大的危险。然后引用这句话来回答第二个问题，我要以“治大国若烹小鲜”的态度来对待我的职位。“治大国若烹小鲜”是什么意思呢？大家如果上网去搜对这句话的解释，类型就有二十多种，每一种解释都不一样，有的甚至把它直接翻译为“治理一个大的国家就像烹一碟小菜那么简单”，这是完全没有理解这句话的真正的含义。“小鲜”就是小鱼儿，鱼肉很细很嫩，拿它的时候就得小心谨慎，尤其是在高温里烹炒它的时候，都要小心谨慎，要有耐心。火候不到的时候你老折腾，甚至锅铲飞舞，翻腾，鱼不就成了碎片了吗？汉朝的毛亨，喜欢《诗经》的人都知道，这个人写过《毛诗传》的，他就用两句话来解读这句话，其实最符合它的本意。第一句话叫“烹鱼烦则碎”，环节太多老折腾它，那鱼就成了碎片了。第二句话“治民烦则乱”，治理一个国家也是一样，讲究的是制度的稳定，不能今天一个制度，明天一个制度，朝令夕改；你不能今天一个运动，明天一个运动来回折腾，国家不就被折腾散架了嘛。“治大国若烹小鲜”和“战战兢兢，如履薄冰”的道理是相同的，讲究的是小心谨慎，有耐心，掌握火候。“以道莅天下，其鬼不神。”“莅”就是莅临。用道来领导天下，指引天下。大家注意，这个“神”字很多的理解有问题，其实并不是神鬼的神，不是说我们后来的人格神、神化了的神。这个“神”在《易传》里面的解释是非常明确的，“阴阳之不测之谓神”，也就是神秘莫测。用道来领导天下、指引天下，鬼也没有什么神秘莫测的力量，因为你走的是正道，你走的是堂堂大道，鬼也没有办法去伤害到你，所以“以道莅天下，其鬼不神”。《道德经》里用它的道，把大家所恐惧的鬼的位置给取代了，你堂堂大道，鬼也近不了你的身，“其鬼不神；非其鬼不神”，不是鬼不神秘莫测，是因为你走大道，它的神秘、莫测、玄妙、诡秘已经没有办法伤害到你。所以把下一句话作为上一句话“其鬼不神”的注解，就很容易理解了。“非其鬼不神”，不是说这鬼不神秘莫测了，神秘莫测是它的本性。“其神不伤人”，但是它的神秘莫测已经伤害不了这种走在大道上的人、得道的人。“非其神不伤人，圣人亦不伤人”，不单是指鬼的力量伤害不了人了，反过来说，圣人他智慧高，但圣人智慧高也得返璞归真。圣人不会因为自己的智慧高，心眼多套路深，就使用这种“技巧”，这个东西不是正道。所以，鬼的神秘莫测伤不了人，圣人的智慧在领导大家的时候也会“善利万物而不争”，对人民没有伤害，“夫两不相伤”，你看鬼的神秘莫测也伤不了人，圣人领导也伤不了人。“夫两不相伤，故德交归焉。”所以有德的事情，积德的事情，两者交汇到一起，两不相伤。因为你按照道来做事情的话，鬼伤不了你，圣人也是按照道来做的，彼此也不相伤。这样大家就走在正确的道上，按照道去做，不断地积德，所以叫“德交归焉”，交汇，归到一块。“治大国若烹小鲜。以道莅天下，其鬼不神。非其鬼不神，其神不伤人；非其神不伤人，圣人亦不伤人。”如果这样两不相伤的，那就是“德交归焉”，这样就形成了一个和谐的、有道的、有德的世界。</t>

--- a/book.xlsx
+++ b/book.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="542">
   <si>
     <t>no</t>
   </si>
@@ -869,241 +869,298 @@
     <t>“天下有道，却走马以粪；天下无道，戎马生于郊，祸莫大于不知足，咎莫大于欲得，故知足之足，常足矣。”这段话也是《道德经》里边非常精彩的一章。因为它体现了我们中国人对待战争的态度，对待和平的热爱。前面我们讲的第三十章的内容，不知道大家是否还有印象，“师之所处，荆棘生焉。”军队打过仗的地方，一片衰草枯杨，断壁残垣，“大军之后，必有凶年。”打过仗以后，灾荒瘟疫都来了。第三十一章，老子讲得更为沉痛，说中国人把战争当作丧礼一样来对待，“以悲哀泣之，以丧礼处之，胜而不美，胜而美者是乐于杀人。”我以前讲过，通过“四大名著”让国外了解我们的文化，效果恐怕不尽如人意，应该让他们看什么呢？让他们看《道德经》，这部能真正代表中国人思想理念、境界和智慧的经典，像我们讲过的三十章、三十一章和现在要讲的第四十六章，就是如此。“天下有道”，普天下清明有道，这个“天下”包括各个诸侯国了。“天下有道，却走马以粪”，“却”就是推却，“走马”就是跑马，也就是好马。这好马不用来打仗，离开战场，推却战争，干吗呢？回来耕田。当然，古人耕田是要上肥的，撒上粪肥，马耕着田，把地耕好，也就是我们经常讲的，卸甲归田，“卸马归田”，把马从战场上拉回来，干它的本务工作。“天下无道，戎马生于郊”，普天下无道的时候，混乱不堪不清明的时候，是什么情况呢？战马把小马驹生到了战场之上，“郊”就是郊野，此处指疆场，战马把小马驹生到了疆场之上。打仗公马不够用了，母马也上去了，最后出现这种情况——“戎马生于郊”，说得非常形象。我要重点强调一下，这四句是以马喻道，马之却为有道，戎马生于郊为无道，也就是以马的“却”与“生”，比拟天下之有道与无道：以“粪马”与“戎马”，象征国家之治与不治。比喻巧妙，寓意深远。纵观《道德经》的治国之道，当以无为自然以养民，以无欲之事而安民。好像马匹一样，虽是有用之物，用之于疆场可以卫国，用之于战阵可以御敌，用之于农事可以耕田。道行天下之时，国泰民安，上下祥和，无兵甲之患，天下太平安然，百姓安居乐业，故用走马耕田种地，积粪肥田。所以说：“天下有道，却走马以粪。天下无道，戎马生于郊。”太精辟了。“祸莫大于不知足，咎莫大于欲得。”这个大家清楚，老子生活在春秋，春秋无义战——没有什么正义的战争。大家都为了争夺财富、城池、人口，相互混战，战火频仍，烽火四起。面对这种情况，老子在当时总结出这两句话：“祸莫大于不知足，咎莫大于欲得。”惹祸最大的原因在哪呢？在于内心的贪念，贪心不足，得到了还想更多，只会做加法，不会做减法。“人心不足蛇吞象”，其实这句话，不单只对当时的现实概括，对我们现在也有这种启发的意义。生活中这种情况也比比皆是：有了还想更有，多了还想更多，衣架里边永远缺一件衣服，房子永远少一间，总是处在不知足的这种状态。“祸莫大于不知足，咎莫大于欲得”，“咎”罪过，过错，动辄得咎，过往不咎。这个“欲得”，就是别人的东西，自己也想要，把别人东西尽量弄到自己手上——这就成了一种罪过了。前面讲“不知足”是一种“祸”，祸患，而“欲得”就是一种罪过了，甚至可以是一种罪恶。别人的城，想要；别人的人民，想要，什么都想占有，用占有的态度对待这个世界，天下是我的。他说古代封建时代皇帝是什么样子呢？“离散天下人之儿女，屠毒天下人之肝脑，以博我一人之产业。”是说皇帝他觉得天下都是自己的，什么东西想拿就拿，想要就要，想占有就占有。这不就是“欲得”吗，这不就是一种大的过错、罪过吗？“咎莫大于欲得。”这个事情该怎么样来处理呢？该我们得的，我们应该得，不该我们的，“虽一毫而莫取也”。这段话大家也知道，东坡先生的《前赤壁赋》，“物各有主，苟非吾之所有，虽一毫而莫取。”划清边界，该得的得，不该得的不要老去强占，不要老是欲得。我们有了边界、底线、标准，那么就知道知足，知足的满足才是长久的满足。知足者富，所以如果永远处在不知足的状态，人也就永远不会有心灵的安宁。我们把这段话和第四十四章联系起来理解就更加明确了。第四十四章最后的三句话讲，“知足不辱，知止不殆，可以长久。”这一章说，“祸莫大于不知足，咎莫大于欲得。故知足之足，常足矣。”</t>
   </si>
   <si>
+    <t>德经 | 统治之道</t>
+  </si>
+  <si>
+    <t>第四十七章（47）</t>
+  </si>
+  <si>
+    <t>不出户，知天下；不窥牖（yǒu），见天道。其出弥远，其知弥少。是以圣人不行而知，不见而名，不为而成。</t>
+  </si>
+  <si>
+    <t>不用出家门，便能知天下之事；不用通过窗户去看，就能知道自然的规律法则。越是向外寻找求索，对道的认识就越少。所以圣人不用出行却能知事理，不必亲自观察却能明白道理，不必亲自去做却能成功。</t>
+  </si>
+  <si>
+    <t>由于这两章的内容非常相吻合、相近，所以我们合到一起作为一章来讲解。四十七章讲的是一个什么事儿呢？是说人的感性认识，从哲学上说就是我们的感官接触客观世界，有时候接触得多了，它反而会造成一种迷乱和混乱，要通过人的智慧、理性认识，这样我们才能了解事物的规律，也就是这一章里边所说的“天道”。在这个基础上，我们一句句来解释。“不出户，知天下。”“户”就是门户，也就是大门。我不用走出家门，不用去外边到处跑，也能了解天下的大事。为什么？因为道家认为，天下大道归根到底，融于人的内心。内心里边有道，也就了解了天下的正道，了解了天下的大事。“不窥牖，见天道。”“窥”，从小孔里看；“牖”，就是窗户。我不用通过窗户去看，也知道天地之间日月星辰运行的规律。所以你看这个地方，“出户”是行走，出行，行万里路；“窥牖”是眼睛看，用感官接触客观世界，我不用这样。所以这个地方大家就感觉到，直观的一开始看，就觉得老子这个人有点轻视感性认识，人得通过实践嘛，人得通过感官接触客观世界，才能产生对客观世界的认识。是不是老子把这些东西全部都否认了呢？不是的。因为大家从书里已经看得非常的清楚，《道德经》举了很多生活中的例子，比如说“治大国若烹小鲜”，比如说“凿户牖以为室”，比如“说三十辐共一毂”，前面讲过的，这不都是生活中的例证吗？他对这个东西也很熟悉，怎么知道的呢？通过接触、了解。为什么在这一章里一开始他就讲这个事呢？要落到下面这八个字上。“其出弥远，其知弥少。”“弥”就是越来越，有的人走的地方越多，见得越多，不懂得甄别，不懂得筛选，不懂得提炼概括，“乱花渐欲迷人眼”，出得越远，反而了解到的真知越少，进步越少，为什么？不懂得反观自省，不懂得人心像一面镜子，如果你这个镜子是被灰尘蒙蔽的，你见得越多，其实反而获得的真知越少。这八个字在强调什么？我们要反观自省，要自我修行，自我修养，从哲学上说，从那些感性认识要上升到一种理性认识，达到对事物本质和规律的认识。所以你看，天下、天道代表着对事物全面的、本质的、规律性的认识，这个规律性的认识，需要我们安静地学习，在家里边读古往今来的著作，这不也是“不出户”嘛，也是“不窥牖”！我们了解这些间接的经验，从前人那里得到根本性的、全面的、通过理论阐释的这些知识，我们才能更了解事物的本质，更了解事物的规律。所以不要只把希望寄托在我们出去跑一跑，看一看，以为这样我们的知识就会越来越深刻，很多事情其实要通过理性的思维，这样我们才能进入到对事物本质和规律的认识，“其出弥远，其知弥少”。如果从中国的文化的角度来进一步理解的话，它还探讨一个什么问题、强调一个什么问题呢？就是人的品德。“大道之行，以心之知。”就是我们的心，我们的自我的内在的精神世界，这是道的重要的方面。所以很多人认为知识就是智慧，知识就是品德。不是的，很多人知识很多，不一定有智慧，知识多也不一定有境界、有品德。所以《道德经》强调的根本的“知”，从前面的比较中，相对于我们的感官而言，是人的理性的思维，理性认识、智慧，相对于外面的世界而言，它又是人的道德品德、人的品德。明朝的时候，关学的代表人物冯从吾先生讲过的一句话，我觉得冯从吾先生的这句话就非常能够解释这个道理，冯先生认为，古往今来的大学问都不出乎三句话：“做个好人，存点好心，行些好事。”做个好人，心正，身安，魂梦稳；行些好事，天知，地鉴，鬼神钦。所以一个人内心的品德、境界，通过自我的反省，自我的修养，达到了一个更高的水平，返璞归真，“归根曰静”，这些也是通过内在的自我修养来达到的。所以《道德经》认为人的理性认识，人这样的内心、这样的根本，它可以通过“不出户”、“不窥牖”，也可以自我修养，自我认知，不断地进步以达到。“是以圣人不行而知，不见而明，不为而成。”“是以圣人不行而知”，“是以”，“是”就是这样，“以”就是用，“是”可以解释为所以。“圣人”，好的统治者、领导者，在《道德经》称其为圣人。这些圣人，好的领导者、统治者要经常反躬自省，要经常内心关照，提高自己对大道和规律的认知水平。“不行而知”，不用到处跑，这一点也是可以得到的。“不见而明”，不用亲自去看，也能够明了道理，明了了这个道理，那就内心清净、无欲。“不为而成”，“不为”就是无为，就是按照大道的方式自然而然地去做，而不去妄为，这样一切都会顺理成章。这是我们第四十七章里边讲的内容，字虽然不多，但道理需要我们认真体会，“不出户，知天下；不窥牖，见天道。其出弥远，其知弥少。是以圣人不行而知，不见而明，不为而成。”当然对这一章的更进一步的理解需要我们和第四十八章，也就是我后面要讲的这一章相互参照，我们对这个理解才会更深刻、更准确。一开始就给大家说第四十七章、第四十八章我们要合起来，相互参照，为什么？这两章的内容讲的是非常吻合的，事实上也应该是一章的内容。第四十七章里边讲，“其出弥远，其知弥少”，第四十八章一开头就讲：“为学日益，为道日损。损之又损，以至于无为，无为而无不为。”这八个字一下子和上边的内容就衔接起来，为什么跑得越远反而知道的越少，这是站在道的角度来讲的。“为学”，在学知识，学到的知识内容越来越多。当然从学知识的角度来讲，这是非常有益的，不断地增多，可是我们获得很多的东西，见到了很多的东西，其实对我们了解根本性的规律和本质，了解大道并没有好处。站在一个更高的层次理解，就是说我们“为学”，讲究的是越多越好，见得多，看得多，见多识广。但是“为道”讲究的是什么呢？讲究的是内心的修行，讲究的是减少，用我们前面讲的话来讲，为学做的是加法，为道做的是减法，减少我们内心的欲念，减少我们的贪念，减少我们对很多问题的一种受了外界的影响而导致的内心的纷扰、困惑、迷乱，把这些东西损之又损，一点一点地把它减少，就像那镜子的灰尘一点点擦掉一样，“损之又损，以至于无为。”“无为”就是自然而为，把欲望减少，减少再减少，就达到了一种“无为”的境界，没那么多的贪念，没那么多的纷扰。我们用镜子来照这个天下，来照事物，万物进入到镜子里边，呈现出它本来的面貌。我们了解了事物的本质规律，了解了大道按照它来做，“无为而无不为”达到的是“无不为”的效果。所以在这儿借着这个机会，我再说一下道家自然无为的具体的含义：第一，不妄为；第十六章里边就讲，“不知常，妄作，凶。”你不了解事物的规律、规则，瞎折腾、胡折腾，那结果是非常糟糕的。我们“损之又损”，减少了这些遮挡着我们的认识，遮挡了我们的心窍的这些外在的事物、灰尘、迷乱，我们就照见了事物的本质和规律，我们就“不妄为”。第二，不多为；抓住关键，举重若轻，静观，看到事物的本质，找到解决问题的正确的方法，抓住关键，举重若轻。第三，有所不为；人要想有所为，必须有所不为，要想有所得，必须有所舍。我们舍弃了那些阻碍了我们正确行动、阻碍我们沿着大道行走的那些纷纷扰扰，这样能达到一个无不为的效果，也就是覆盖面广，效果更好，“无为而无不为”。下面这一段就讲，按照“无为”的方式来理解天下万事万物。“取天下常以无事，及其有事，不足以取天下。”“取天下”的规则是什么呢？“无事”。“无事”就是不多事，不干涉，不扰民，这样一切就自然而然顺理成章。所以第五十七章里边讲的这个事情就比较明确，“我无事而民自富，我无为而民自化”。“及其有事”，如果老是多事，老是妄为，不懂得事物的规律、规则，瞎折腾、胡折腾，这就是“及其有事”。则“不足以取天下”，那就不能够获得天下。得到的天下也得失去，因为它违背了大道。</t>
+  </si>
+  <si>
+    <t>德经 | 内省之道</t>
+  </si>
+  <si>
+    <t>第四十八章（48）</t>
+  </si>
+  <si>
+    <t>为学日益，为道日损。损之又损，以至于无为，无为而无不为。取天下常以无事，及其有事，不足以取天下。</t>
+  </si>
+  <si>
+    <t>为学（学习知识）是一天一天地增加知识，为道是一天一天地减少私欲（内心修行）。减少又减少，以致达到自然而为的境界。“无为”就能达到“无不为”的效果（做成一切事）。治理天下要常常不多事不扰民，如果妄为滋扰，就无法治理好天下。</t>
+  </si>
+  <si>
+    <t>由于四十七、四十八这两章的内容非常相吻合、相近，所以我们合到一起作为一章来讲解。四十七章讲的是一个什么事儿呢？是说人的感性认识，从哲学上说就是我们的感官接触客观世界，有时候接触得多了，它反而会造成一种迷乱和混乱，要通过人的智慧、理性认识，这样我们才能了解事物的规律，也就是这一章里边所说的“天道”。在这个基础上，我们一句句来解释。“不出户，知天下。”“户”就是门户，也就是大门。我不用走出家门，不用去外边到处跑，也能了解天下的大事。为什么？因为道家认为，天下大道归根到底，融于人的内心。内心里边有道，也就了解了天下的正道，了解了天下的大事。“不窥牖，见天道。”“窥”，从小孔里看；“牖”，就是窗户。我不用通过窗户去看，也知道天地之间日月星辰运行的规律。所以你看这个地方，“出户”是行走，出行，行万里路；“窥牖”是眼睛看，用感官接触客观世界，我不用这样。所以这个地方大家就感觉到，直观的一开始看，就觉得老子这个人有点轻视感性认识，人得通过实践嘛，人得通过感官接触客观世界，才能产生对客观世界的认识。是不是老子把这些东西全部都否认了呢？不是的。因为大家从书里已经看得非常的清楚，《道德经》举了很多生活中的例子，比如说“治大国若烹小鲜”，比如说“凿户牖以为室”，比如“说三十辐共一毂”，前面讲过的，这不都是生活中的例证吗？他对这个东西也很熟悉，怎么知道的呢？通过接触、了解。为什么在这一章里一开始他就讲这个事呢？要落到下面这八个字上。“其出弥远，其知弥少。”“弥”就是越来越，有的人走的地方越多，见得越多，不懂得甄别，不懂得筛选，不懂得提炼概括，“乱花渐欲迷人眼”，出得越远，反而了解到的真知越少，进步越少，为什么？不懂得反观自省，不懂得人心像一面镜子，如果你这个镜子是被灰尘蒙蔽的，你见得越多，其实反而获得的真知越少。这八个字在强调什么？我们要反观自省，要自我修行，自我修养，从哲学上说，从那些感性认识要上升到一种理性认识，达到对事物本质和规律的认识。所以你看，天下、天道代表着对事物全面的、本质的、规律性的认识，这个规律性的认识，需要我们安静地学习，在家里边读古往今来的著作，这不也是“不出户”嘛，也是“不窥牖”！我们了解这些间接的经验，从前人那里得到根本性的、全面的、通过理论阐释的这些知识，我们才能更了解事物的本质，更了解事物的规律。所以不要只把希望寄托在我们出去跑一跑，看一看，以为这样我们的知识就会越来越深刻，很多事情其实要通过理性的思维，这样我们才能进入到对事物本质和规律的认识，“其出弥远，其知弥少”。如果从中国的文化的角度来进一步理解的话，它还探讨一个什么问题、强调一个什么问题呢？就是人的品德。“大道之行，以心之知。”就是我们的心，我们的自我的内在的精神世界，这是道的重要的方面。所以很多人认为知识就是智慧，知识就是品德。不是的，很多人知识很多，不一定有智慧，知识多也不一定有境界、有品德。所以《道德经》强调的根本的“知”，从前面的比较中，相对于我们的感官而言，是人的理性的思维，理性认识、智慧，相对于外面的世界而言，它又是人的道德品德、人的品德。明朝的时候，关学的代表人物冯从吾先生讲过的一句话，我觉得冯从吾先生的这句话就非常能够解释这个道理，冯先生认为，古往今来的大学问都不出乎三句话：“做个好人，存点好心，行些好事。”做个好人，心正，身安，魂梦稳；行些好事，天知，地鉴，鬼神钦。所以一个人内心的品德、境界，通过自我的反省，自我的修养，达到了一个更高的水平，返璞归真，“归根曰静”，这些也是通过内在的自我修养来达到的。所以《道德经》认为人的理性认识，人这样的内心、这样的根本，它可以通过“不出户”、“不窥牖”，也可以自我修养，自我认知，不断地进步以达到。“是以圣人不行而知，不见而明，不为而成。”“是以圣人不行而知”，“是以”，“是”就是这样，“以”就是用，“是”可以解释为所以。“圣人”，好的统治者、领导者，在《道德经》称其为圣人。这些圣人，好的领导者、统治者要经常反躬自省，要经常内心关照，提高自己对大道和规律的认知水平。“不行而知”，不用到处跑，这一点也是可以得到的。“不见而明”，不用亲自去看，也能够明了道理，明了了这个道理，那就内心清净、无欲。“不为而成”，“不为”就是无为，就是按照大道的方式自然而然地去做，而不去妄为，这样一切都会顺理成章。这是我们第四十七章里边讲的内容，字虽然不多，但道理需要我们认真体会，“不出户，知天下；不窥牖，见天道。其出弥远，其知弥少。是以圣人不行而知，不见而明，不为而成。”当然对这一章的更进一步的理解需要我们和第四十八章，也就是我后面要讲的这一章相互参照，我们对这个理解才会更深刻、更准确。一开始就给大家说第四十七章、第四十八章我们要合起来，相互参照，为什么？这两章的内容讲的是非常吻合的，事实上也应该是一章的内容。第四十七章里边讲，“其出弥远，其知弥少”，第四十八章一开头就讲：“为学日益，为道日损。损之又损，以至于无为，无为而无不为。”这八个字一下子和上边的内容就衔接起来，为什么跑得越远反而知道的越少，这是站在道的角度来讲的。“为学”，在学知识，学到的知识内容越来越多。当然从学知识的角度来讲，这是非常有益的，不断地增多，可是我们获得很多的东西，见到了很多的东西，其实对我们了解根本性的规律和本质，了解大道并没有好处。站在一个更高的层次理解，就是说我们“为学”，讲究的是越多越好，见得多，看得多，见多识广。但是“为道”讲究的是什么呢？讲究的是内心的修行，讲究的是减少，用我们前面讲的话来讲，为学做的是加法，为道做的是减法，减少我们内心的欲念，减少我们的贪念，减少我们对很多问题的一种受了外界的影响而导致的内心的纷扰、困惑、迷乱，把这些东西损之又损，一点一点地把它减少，就像那镜子的灰尘一点点擦掉一样，“损之又损，以至于无为。”“无为”就是自然而为，把欲望减少，减少再减少，就达到了一种“无为”的境界，没那么多的贪念，没那么多的纷扰。我们用镜子来照这个天下，来照事物，万物进入到镜子里边，呈现出它本来的面貌。我们了解了事物的本质规律，了解了大道按照它来做，“无为而无不为”达到的是“无不为”的效果。所以在这儿借着这个机会，我再说一下道家自然无为的具体的含义：第一，不妄为；第十六章里边就讲，“不知常，妄作，凶。”你不了解事物的规律、规则，瞎折腾、胡折腾，那结果是非常糟糕的。我们“损之又损”，减少了这些遮挡着我们的认识，遮挡了我们的心窍的这些外在的事物、灰尘、迷乱，我们就照见了事物的本质和规律，我们就“不妄为”。第二，不多为；抓住关键，举重若轻，静观，看到事物的本质，找到解决问题的正确的方法，抓住关键，举重若轻。第三，有所不为；人要想有所为，必须有所不为，要想有所得，必须有所舍。我们舍弃了那些阻碍了我们正确行动、阻碍我们沿着大道行走的那些纷纷扰扰，这样能达到一个无不为的效果，也就是覆盖面广，效果更好，“无为而无不为”。下面这一段就讲，按照“无为”的方式来理解天下万事万物。“取天下常以无事，及其有事，不足以取天下。”“取天下”的规则是什么呢？“无事”。“无事”就是不多事，不干涉，不扰民，这样一切就自然而然顺理成章。所以第五十七章里边讲的这个事情就比较明确，“我无事而民自富，我无为而民自化”。“及其有事”，如果老是多事，老是妄为，不懂得事物的规律、规则，瞎折腾、胡折腾，这就是“及其有事”。则“不足以取天下”，那就不能够获得天下。得到的天下也得失去，因为它违背了大道。</t>
+  </si>
+  <si>
+    <t>德经 | 治学之道</t>
+  </si>
+  <si>
+    <t>第四十九章（49）</t>
+  </si>
+  <si>
+    <t>圣人无常心，以百姓心为心。善者，吾善之；不善者，吾亦善之，德善。信者，吾信之；不信者，吾亦信之，德信。圣人在天下歙（xī）歙，为天下浑其心。百姓皆注其耳目，圣人皆孩之。</t>
+  </si>
+  <si>
+    <t>圣人不要有固执不变的思想，而是把百姓的思想当作自己的思想。。善良的百姓我善待他们，不善良的百姓我也善待他们，结果就会使他也变得善良；讲诚信的人我以诚信对待他们，不讲诚信的人我也以诚信对待他们，结果就会使他也变得诚信。圣人领导天下 收敛自己的私欲，使天下百姓的心灵都变得淳朴。百姓都只关注耳听眼见的事，而圣人要使他们都变得像无知无欲的婴儿一样。</t>
+  </si>
+  <si>
+    <t>【圣人要换位思考 将心比心】第四十九章是《道德经》里边比较重要的一章，因为这里边有一句话大家都很熟悉，我们领导者讲话的时候也经常引用，就是以“百姓心为心”。从前面讲的内容，大家会知道这是一个通过换位思考，得出来这样的一种结论。这一章开头这句话我们先说一下。“圣人无常心，以百姓心为心。”是说一个好的领导者、统治者，不要老固执己见。“常心”就是固定的心思，自我的执着，不要老固执己见，不要老把自己的意志强加给别人，乃至强加给人民。应该怎么样呢？换位思考，将心比心，“以百姓心为心”，倾听民众的呼声，关注民众的利益，吸取民众的智慧，这都是“以百姓心为心”的表现。我们先体会一下这一章的宗旨在讲什么？其实这个道理就是讲了，换位思考，将心比心。百姓善良，我也对他善良；不善良，我也对他善良；信任我的，我信任他；不信任我的，我也信任他。干吗呢？这样我就能让人向善，让大家讲诚信。最后这一段就说一个好的领导者、统治者，让百姓都回归到他本来的这种生活，关注的是自己的生活中的事情。不要想那么多，不要心思混乱，不要烦乱，这样才能够形成一种良好的和谐的状态。这是老子的想法。我们一句一句来解释。“圣人无常心”，我再重申一遍，“圣”的繁体字，上面是个耳和口——聖，这两个字并列就代表着通达事理，下面是个王，也就是说一个好的领导者、领导人称其为“圣”。在这一章里体现得最为明显。“圣人无常心”，有的本子也叫“常无心”，意思都是一样的，就是不固执己见，没有自己僵化固定的思维，懂得换位思考。其实关于这个意思，我们通过前面讲过的第二十二章参照着理解，就比较容易了。我在前面多次说过，读《道德经》最好的方法就是不看注解，以经解经，相互参照，明白它要讲的真正的含义，谁的解读也不如他本人对这个东西的解释更符合他的本意。第二十二章里边就讲“不自是”“不自见”“不自矜”“不自伐”这“四不”。“不自是，故彰。不自伐，故有功。不自矜，故长。”这样我们才能不断成长，不断进步。一个好的领导人也是这样的，领导者、统治者，也应该“四不”，也就是“无常心”。你没有这样的智慧，老是固执己见，老是自我吹嘘，老是自我夸耀，老是觉得自己了不起，那你就没办法换位思考，将心比心了。所以“无常心”才能以百姓之心为心，倾听民众的呼声，吸取民众的智慧，关注民众的利益。沿着这个思路下面也好理解了。“善者，吾善之；不善者，吾亦善之，德善。”善良的人我用善良去对待他，不善良的人，我也用善良的方式去对待他，干嘛呀？教化、感化，这样我就得到了真正的善良。为什么呢？你这样做，起代表带头作用，大家也就人心向善了。大家注意这个“德”，王弼的解释非常明确，“德者，得也”，这样做就得到了这个天下、这个社会，这个国家就会人心向善。“信者，吾信之；不信者，吾亦信之，德信。”信我的人，我相信他，我跟他讲诚信；不相信我的人，我也相信他，跟他讲诚信。干嘛呀？这样天下人就会觉得诚信可贵，也就往诚信的方向去努力去发展了——“德信”。“圣人在天下歙歙”，“歙”就是合，就是收敛。你说圣人怎么样领导、管理这个天下呢？先要收敛自己的欲望，要想领导好别人，你先领导好自己，要想领导好自己，你先领导好自己的情绪，领导好自己的欲念，上梁不正则下梁歪嘛。“歙歙”，收敛自己的欲望，减少自己的欲念。“为天下浑其心”，让这个天下都怎么样呢？大家都没那么精明。不总是为了什么事都去争，“浑其心”，都那么样地浑厚、淳朴、厚道，关心自己的现实生活，而不是那么多纷乱的思维，那么多胡乱的想法，那么多的技巧、智谋、套路、心眼，用这种方式让大家和谐相处。“圣人皆孩之”，一个好的领导者把天下人都当作儿童，当作自己的孩子，一方面对他们非常关爱，另一方面也不要让百姓人心混乱，都像孩童一样纯净、淳朴。当然了，后边这一段大家也看得出来，这也是老子的一厢情愿。他希望统治者减少自己的欲望，天下人跟着也减少自己的欲望，关注自己的现实的生活，没有那么多的争斗、心眼、套路、技巧、欺骗、欺诈。这是老子生活的理想状态，也是他认为是和谐世界的前景，我们权当这也是他的一种理念和希望，毕竟这个社会的和谐也是我们的一种希望。只是他这种方法大家要辩证对待，大概用这种方法实现天下的太平，也只能是一种理想和理念，很难真正得以实现。但这一章里边大家要注意，开头这句话，我们要熟记，因为在我们国家的领导人的很多讲话里边都能看到这句话的出现，“以百姓心为心”，这是道家思想里边非常重要的一句话，让我们感觉到老子这个人在他冷静的、甚至有点冷酷的外表之下，内心涌动的热流，对于天下人的关注，对于天下人的关爱。这一章的原文我们解释完了，再强调一下这章的逻辑和重点，这章里边的关键在哪呢？这一章里边的关键是讲“圣人”和“百姓”，他们是国家不同层面的人，这一章讲究什么呢？讲究各安其位，各循其理。老子对这些做统治者的讲，你们要“以百姓之心为心”，善良的人呢你要好好地对待，不善良的人呢你也要好好对待，这样你才能得到这个国家人心向善的风气。信你的人你要讲诚信，不信你的人你也要讲诚信，这样才能得到天下诚信的风气。“圣人在天下”，圣人在上，领导天下。应该怎么样呢？怎么样叫循理循道呢？应该清静，无为，少折腾，少多事儿，这是上边的理，给他们讲的，你应该这样做，收敛自己的欲望，减少自己的奢靡、奢华，“清静为天下正”，这是对他们。对下边怎么讲呢？你这个在上边的人应该让下边遵循一个什么样的道理呢？“为天下浑其心”，让这个百姓浑厚，淳朴，宁静，没有那么多纷乱的想法，那么多技巧、心眼、套路、欺诈、欺骗，按照这个方向，百姓都关注自己现实的生活，把自己的日子过好，少管别的事儿，你让百姓能够做到这一点，上边的管上边的事，循上边之理，下边的循下边之理，这天下不就和谐了嘛。大家看出来了吧，“圣人皆孩之”，好的领导，一个国家的领导者，让这国家的百姓都像小孩一样，纯净、淳朴，没有那么多的欺瞒欺诈。上按上边的道理，下按下边的道理，这不就形成了一个和谐的状态了嘛。我们知道，真正的和谐是有差别的统一，大家都应该有表达自己的意见的机会，表达自己观点的机会，“各美其美，美人之美”，有差别的统一。但是老子这个地方讲的道理不是这样的，他讲的是“圣人无常心”，你要考虑到百姓，百姓在圣人的领导下应该怎么做呢？应该浑厚淳朴，没有那么多的智谋、欺诈、心眼，关注自己的现实生活，干好自己的事情，像儿童一样，纯净、干净、宁静，形成这个社会的和谐状态。所以我们只能说，老子这个想法呀追求一种和谐的目标，但是这个所用的方法在我们看来，这还是有很多地方值得检讨的，因为真的把百姓都变成小孩，还是不免有一点愚民政策的感觉。这一点大家还是要正确地理解。</t>
+  </si>
+  <si>
+    <t>德经 | 人性之道</t>
+  </si>
+  <si>
+    <t>第五十章（50）</t>
+  </si>
+  <si>
+    <t>出生入死。生之徒十有三，死之徒十有三。人之生，动之死地，亦十有三。夫何故？以其生生之厚。盖闻善摄生者，陆行不遇兕（sì）虎，入军不被甲兵。兕（sì）无所投其角，虎无所措其爪，兵无所容其刃。夫何故？以其无死地。</t>
+  </si>
+  <si>
+    <t>人生就是从出生到死亡的历程。长寿的人占十分之三，短命的人占十分之三，本可以长寿但妄为把自己置于死地的人也占十分之三。为什么？因为他们过分地追求奉养自己以求生。听说善于养生的人，在陆地上行走不会遇到犀牛和猛虎的伤害，在战场上不会被兵器所伤。犀牛的角无处可用，老虎的爪也没了用处，兵器的刃也用不上。为什么？因为他不把自己置于死地。</t>
+  </si>
+  <si>
+    <t>【养生之道 —— 不要作死】我们来讲第五十章，这一章表面上在讲养生之道，也就是文章所说的“摄生”，实际上表达的是更为深刻的道理。我们看书、看电视剧的时候，会发现有那么一些大师、大医生，一些位重权高的人向他们请教养生之道，“我怎么样能活得更加长寿？”这些医生、养生大师啊，大都是告诉他们要清心寡欲，不要奢靡奢华，不要胡吃海塞，其实这就是道家对于养生这事儿往更高的一个层次所要修养的内容，我们也可以把它概括为道家的生死观。道家认为养生跟生死密切关联。养生要顺应自然，要自然而然，要掌握规律、规则。你看我们读《庄子·养生主》里边的“庖丁解牛”，讲的不就是这个道理吗？目无全牛，游刃有余！这牛解得跟跳舞一样，跟音乐一样。所以文惠君最后就对这个庖丁讲：“吾闻庖丁之言，得养生焉。”养生要顺应自然规律，自然而然，自然而为。“生之徒十有三，死之徒十有三。”然后老子做分析，如果把天下的人分做十成，那么有十分之三的人是“生之徒”，也就是长寿的，还有十分之三的人是“死之徒”，是短命的。还有十分之三的人是怎么样的呢？“人之生，动之死地，亦十有三。”这些人本来可以长寿，最后由于自己的胡为、妄为、折腾，就把自己置于死地了。所以你看它的分类很有趣，十成的人中，三分之一的人应该是长寿的，三分之一的人本身体质各方面就是短寿的，还有三分之一的人本来可以长寿，但是妄动、胡为而置于死地。为什么会这样？《道德经》给了我们这样一句话：“以其生生之厚。”生，养生，或者可以解释得更明确，叫“求生”。太着急了，太迫切了，老想延长自己的性命，老害怕自己的营养不够，最后营养过剩了，反而把自己置于一个另外的相反的方向。当下一些有智慧的医生就提醒，我们现在不是营养不良，而是营养过剩，“生生之厚”。当然《道德经》讲的这句话只针对当时的统治者、位高权重的人而言，老是生活得这样奢靡奢华，“五色令人目盲，五音令人耳聋，五味令人口爽，驰骋畋猎，令人心发狂……”老是这样，还以为是让自己生命不亏，活得不亏。求生之厚，太急、太迫切，营养过剩，自己本来可以长寿，反而被置于成“死之徒”了，到短寿的那一拨去了。所以下面老子就讲了：“盖闻善摄生者”，听说这善于养生的人是什么样子呢？他们用了下边一段形容：“陆行不遇兕虎，入军不被甲兵。兕无所投其角，虎无所措其爪，兵无所容其刃。”习惯上我们以为“兕”是犀牛，或者有的叫母犀牛，其实这两种动物还不一样。这个“兕”是古代的一种瑞兽，比较凶猛，所以在古代的文字中，经常用这个“兕虎熊”比喻凶险之地。懂得养生的人，懂得正确对待自己生命的人，不去冒这个险。陆行的时候，尽量不碰这些凶猛的动物，如果你碰上它了，那你就没办法了，谁让你冒那个险呢？明知道野生动物园人家不让下车，你非得下车，遇到老虎了吧。有些地方人家告诉这个规则，这里边有危险，你偏不听，明知山有虎，偏向虎山行，明知山有狼，偏要做狼餐，这不就是“人之生，动之死地”吗？“入军不被甲兵”，上阵打仗的时候不为兵器所伤。为什么呢？“兕无所投其角”，你不遇到这个兕，那当然它那个凶猛的角就没有办法发挥它的作用了，没有办法针对你。一般我们画“兕”的时候都习惯把它画成独角兽。“兕”最有名的代表就是太上老君骑的那个板角青牛了，角非常锋利，尖锐，杀伤力强，你不遇到它，尽量别碰到，别把自己置于危险的境地，它的角当然就无所用了。“虎无所措其爪”，你不往虎山行，不遇到它，提前准备好避免这种凶险，老虎爪子再尖利，牙齿再锋利，它也无法对你发挥作用。“兵无所容其刃”，上阵不为甲兵所伤，尖锐的兵器，也没有办法发挥它的作用。“夫何故？”为什么会这样？“以其无死地”，不把自己置于死地，这样也就不会让自己的生命受到戕害。这是就是五十章。这一章体现了道家的养生之道：简单地说就是不要“作死”，自己不要找死，本来可以长寿的，自己作死把自己置于死地。很多人非得触犯法律的界限，甚至因此送掉了自己的生命，这不就是把自己置于死地嘛！所以我们说“NoZuoNoDie”，不作不死。从养生的角度来讲，你看道家讲的顺应自然，不单只是生活中的清心寡欲，而且还指不触犯边界底线，不触犯红线，知足不辱，知止不殆，不置身于死地，不让自己冒这种凶险，这也是道家养生之道里边的一个重要的内容，而且是更接近于哲学层面的、更有智慧的内容。那么这一段我们讲完了之后，我还要跟大家强调一下，道家的养生观，其实也是道家的生命观。道家对于生命的看法讲究的是自然而然，意思是什么呢？过于求生，过于厌恶死，这都不是一种自然而然的智慧，因为死亡本身就是生命的一部分，人自然而生，自然而死，真的到了生命结束的时候，那也应该开朗地、乐观地对待。这一点在道家的继承者那里，也就是道家的第二号人物庄子那里，讲得非常的明确——“之所以善吾生者，乃所以善吾死”。我们很好地对待自己的生命，不把自己的生命主动地置于死地，不求生之厚，真的面临死亡的时候，也应该把它好好地对待。自然而生，自然而亡，这是生命的自然而然的规律，谁也阻挡不了。第五十章，老子借养生之道讲了一个更重要的道理：有的人求生太急迫，太厌恶死亡，太害怕死亡，越是求生之厚，服了大量的药，用各种各样的营养的方式，推开死亡，想要避免，没想到越想避免的反而来得越快。所以，道家讲究自然而然的思想，这有着重要、杰出的意义。我们做个小小的梳理。第五十章，我们从开始讲的时候就给大家讲过，这一章可以分成两段，一段是讲有的人本来可以长寿，却进入了短命的行列，是因为“求生之厚”，太急迫、营养过剩导致的，另外一个是由于妄为、“作”，把自己置于死地的。怎样才能避免这两点呢？还是道家的这种思想，顺其自然，清心寡欲，清静为天下正。正确地对待生命和死亡，不把死亡当作是完全可以避免的事情，真的面临死亡的时候，也能够开朗地、乐观地对待。</t>
+  </si>
+  <si>
+    <t>德经 | 生存之道</t>
+  </si>
+  <si>
+    <t>第五十一章（51）</t>
+  </si>
+  <si>
+    <t>道生之，德畜（xù）之，物形之，势成之。是以万物莫不尊道而贵德。道之尊，德之贵，夫莫之命而常自然。故道生之，德畜之：长之育之、亭之毒之、养之覆之。生而不有，为而不恃，长而不宰，是谓玄德。</t>
+  </si>
+  <si>
+    <t>道生成万物，德蓄养万物，万物有了具体的形状，周围的环境使万物得以成长。因此万物没有不尊崇道和重视德的。道受到尊崇，德受到重视，并没有人如此命令 而是万物本身自然而然地永远去这样做。所以道生成万物，德蓄养万物：使万物成长作育，使万物成长成熟，使万物得到养覆保护。道、德养育了万物却不据为己有，帮助了万物却不求它们的回报，成就了万物却不做它们的主宰者，这可以说是最高尚的品德。</t>
+  </si>
+  <si>
+    <t>第五十一章逐句地来解释一下。“道生之”，“生”，创造，生养。道创造了万事万物。“德畜之”，德畜养了万事万物。“物形之”，万事万物有了具体的形状。“势成之”，周围的环境使它得以成长。正因为如此，所以“万物莫不尊道而贵德”，以道为尊，以德为贵。“道之尊，德之贵，夫莫之命而常自然。”尊道贵德，那自然会得到一个良好的结局和结果，这不是命，这就是自然而然的规律、规则。“故道生之，德畜之。”所以道生养万物，德蓄养万事万物。“长之、育之”，使它成长，使它不断地培育长大。“亭之、毒之”，这个“亭”呢，其实也好理解，我们常说亭亭玉立，这个“亭”就是成长的意思。这个“毒”就是成熟的意思，使万事万物成长，使其成熟。“养之、覆之”，“养”和“覆”都是保护的意思。养育万物，保护万物。“生而不有，为而不恃，长而不宰。”生养了万事万物，却不把它当作私有的产品，对万事万物有作为，却不把这个当作一种倚仗、凭借，甚至勒索的手段，对万事万物有这么大的功德，却不是以主宰者的身份出现。这个就是“玄德”，这就是最高深的、最深刻的智慧与品德。这是我们对这一段的直观的解释。其实，这一段的深意远不止于此。因为中国人讲哲学讲究“知行合一”，讲道的品性，其实也是为了人向道的品性去学习，按照道去做，这个也就是“德”。所以第五十一章里边讲道养育万物，德蓄养万物，也是人应该效法学习的。在这个层面上，我们深入地理解这一段话。“道生之，德畜之”，道创造了万事万物，但是它不把万事万物作为一种私有产品，并不是以一种主宰者的身份，以求其回报。由此我们可以看到，老子给我们提供了想要做成一件事的四个核心的要素和条件，也就是一种应有的程序和原则。第一个，要有道，因为道是创造万事万物的本源，所以我们要坚守大道，按大道的方式来创造。第二个，“德畜之”，“畜”就是积累的意思。在有道的基础上，我们要不断地、坚定地按照道去做，也就是“积德”。德就像水一样，我们就像一条船一样，我们积累的水越多，我们这条船在水上才能够航行得更自由。所以朱熹有一首诗说：“昨夜江边春水生，艨艟巨舰一毛轻。向来枉费推移力，此日中流自在行。”昨天江边涨水了，平常推也推不动的大船，现在根本不用推了，水多了，自然而然地就航行更加自由。他讲的是读书的积累达到一种自由的境界，其实人生又何尝不是如此呢？我们积累的德多了，按照道做事，更坚定、坚持、持久，那也就给我们人生提供了更广阔的空间与平台，不断地积德，我们的行为也就更加自由，我们的行为也就更加能够符合大道。庄子在《逍遥游》里面也讲了这样一句话，“且夫水之积也不厚，则其负大舟也无力”。水积累不多的时候，大船是浮不起来的，只要积累得多了，结果就是自然而然的事情，和朱熹所讲的道理不谋而合。第三个，“物形之”。人有道有德，是不是就可以把事情做成了呢？不够的，还需要一定的物质条件和手段，巧妇也难为无米之炊。有条件要上，没有条件我们创造条件，这样才能把事情向更成功的方向去发展。道、德、物三个条件总够了吧？不够的。要想把事情真正做成，还有一个很重要的条件，就是“势”，“势成之”。道家讲的无为，更强调的是顺势而为，掌握这个形势，了解大势，这样才能把事情做成。《淮南子》中举过这样的一个例子，大禹为什么能把水治成呢？顺水势而为。商汤周武为什么能夺得天下呢？顺民心而为。民心所向，就是历史发展的大势与潮流。所以大家在第二个层面把这四个字提炼出来，它是一个很好的成功学的例证，我觉得比现在讲的一些所谓的零零散散的成功学，不知道要深刻多少倍。道、德、物、势，“道生之，德畜之，物形之，势成之”。既然这四个要素，道和德是排在最前面的，“是以万物莫不尊道贵德”，所以万事万物没有不尊道而贵德的。人更是如此，有道有德，后边的事情才能继续发展，所以“道之尊，德之贵，夫莫之命而常自然”，这不是命，这就是一个永恒的自然而然的规律、规则。你按照道，按照德，尊道而贵德，会得到一个自然而然的良好的结局和结果，这是自然而然的事情。这不是命，这就是自然而然的规律和规则。所以大家注意，我们中国的这些经典，比如说《易经》，比如说《道德经》，都不是用来算卦占卜的，它就讲一个重要的内容：按照规律、规则来做，结果水到渠成、自然而然。下面这一段是对上面做的一个延伸。“道生之，德畜之”，道和德，生养万物，为万物提供条件，让它生长发展。“长之、育之”，培育万事万物使其生长、发展。“亭之、毒之”，使它成长、成熟。“养之、覆之”，不仅如此，还要养护万物，覆盖万物。道和德让万物长大，培育万物的成长，使它成熟又予以保护，功德可谓无量。孔子有一段名言：子曰：“予欲无言。”子贡曰：“子如不言，则小子何述焉？”子曰：“天何言哉？四时行焉，百物生焉，天何言哉？”这段话的直译是：孔子说：“我现在只想沉默。”子贡说：“如果你不说出心里想什么，那么我们这些学生还拿什么去记述呢？”孔子说：“自然说过些什么？不过放纵四季周而复始，任由百物蓬勃生长。自然你又何曾告诉别人什么啊？”很多人把这段话中的“天”翻译成神灵，这是不对的。其实这个“天”指的是大自然，也就是《道德经》里的天地，天地无语而泽被苍生万物，确又无语不居功自傲，不把自己当做万物主宰。这不也是《道德经》第五十一章的核心吗？培育万物的成长，使它成熟又予以保护，功德可谓无量。其实，在这样的智慧层面，孔子和老子的见解都是一样，“生而不有，为而不恃，长而不宰，是谓玄德”。关于这段重要的话，我们在第十章已经详细说过，不再重复。</t>
+  </si>
+  <si>
+    <t>德经 | 行为之道</t>
+  </si>
+  <si>
+    <t>第五十二章（52）</t>
+  </si>
+  <si>
+    <t>天下有始，以为天下母。既得其母，以知其子；既知其子，复守其母，没（mò）身不殆。塞（sè）其兑（duì），闭其门，终身不勤。开其兑，济其事，终身不救。见小曰明，守柔曰强。用其光，复归其明，无遗身殃，是为习常。</t>
+  </si>
+  <si>
+    <t>天下万事万物都有本源（即道），可以把这个本源作为万物的母亲。认识了作为万物之母的道，就能认知万物；认知了万物，就能坚守作为万物之母的道。这样终身都没有危险。塞上欲望的孔穴，闭上欲望的门户，终身都没有忧劳。打开感官欲望的门户，增添纷繁的事件，终身都不可挽救。察见细微的事物叫“明”，坚守柔弱叫“强”。用道的光芒来了解具体事物中的规律、规则，复归到事物的光明的状态，不会给自己留下那么多的祸殃，这就叫普遍永恒的规律（可以说是掌握了大道）。</t>
+  </si>
+  <si>
+    <t>一开始我们就说过，《道德经》里边有一个非常好的“正能量”，就是每当说到高大上的、特别伟大的事情，都喜欢用母亲的“母”字来作为代替和概括，或者说用“母”来做一个形象的比喻。如果我们的孩子读这样的文字，潜意识里就会有对母亲有一种敬畏与尊重。我们在第一章里边就说到，“无，名天地之始；有，名万物之母”。在这一章里边，又出现了母亲的这个“母”的概念。“天下有始，以为天下母。”就像动物、人类都是由母亲生养的一样，万事万物也都是由道创造的。老子用“母”来比喻大道，生动形象且让人充满对道的敬畏，意思就是说，天地一开始的时候，其实大道已经就在了。“既得其母，以知其子。”我们了解了大道，就是“既得其母”。知晓了大道，那我们就“以知其子”，也就了解了儿女。这个意思是什么呢？道是万事万物的普遍规律，它永恒存在，具体的事物都拥有具体的道，也就是具体的规律。你了解了大道，就可以以此来了解万事万物的具体规律。茶有茶道，花有花道，练武有武道，下棋有棋道……了解了普遍的道，也就更能够了解这些具体事物间的规律与规则。反过来也一样，“既知其子，复守其母。”我们从具体的事物之间，比如棋道、花道、茶道，从这具体的事物之间，我们了解了大道，感知了大道，那也就能更好地坚定地坚守大道。“没身不殆”，这样地做事情永远没有危险，没有失败，为什么？以道佑之，以道护之，这样我们做事情才能没有危险，没有失败。下面就说了解大道的方式方法。大道的了解，不是靠感性来体验到的，就像我们前边说的，“为学日增，为道日损。”“不出户，知天下；不窥牖，见天道。”所以如果是跟着感觉走的话，你是了解不了真正的大道的。因此“塞其兑，闭其门，终身不勤”，不要依赖感觉，不要把我们所见所知的就当作大道，重要的要用心，也就是哲学上讲的，用理性的思维，来了解认知大道。反过来讲，“开其兑，济其事，终身不救”，如果跟着感觉走，打开我们的感官的门户，感官这个东西，它是有很大的局限的。第十二章里面就讲，“五色令人目盲，五音令人耳聋，五味令人口爽”。你只靠这个是了解不了大道的。“见小曰明，守柔曰强。”什么叫“见小”啊？“小”就是具体的事物，具体的事物里面也蕴含着规律、规则。你能够从具体事物里了解具体的道、具体的规律，这也是一种明智。“守柔曰强”，道家是讲“柔弱胜刚强”的，道家是讲“知其雄，守其雌”的，“柔”就是雌柔，不管我们多么强大，我们也懂得坚守这个柔弱，因为柔弱更能长久。力量不够的时候，我们懂得用守柔的方式、韬晦的方式，来使自己的力量不断增大、不断增强，这样才能成为真正的强大。“用其光，复归其明”，用道的光芒，“复归其明”，来了解具体事物中的规律、规则，复归到事物光明的、明智的状态，我们才能走在光明的大道上。“无遗身殃”，不会给自己留下那么多的祸殃。“是为习常”，这个“习”，不同的本子有不同的写法。习，就是普遍、永恒的意思，就是普遍的永恒的规律、规则。也有的本子用的是沿袭的“袭”，也就是遮盖的意思。《道德经》里边用这个“袭”字的意思就是说，这是被大家认识不到的、被遮盖的规律规则，了解了这一点，我们也就对事物的了解更加深入。这两个意思都通，我们这里边用的是复习的“习”，学习的“习”，也就是经常的、普遍的、永恒的意思。“是为习常”，这就是一个经常的、普遍的、永恒的规律、规则。这一章核心的内容是说，道是一个普遍的规律，它存在于天地之间，所以叫“大道”。我们了解了大道，掌握了普遍的规律、规则，再来认识具体事物中的规律、规则，这是非常有帮助的，也是非常重要的。反过来也是一样，了解了具体事物中的规律、规则，也能够让我们更加坚信大道的存在，更加了解大道的伟大。这一章以母和子为喻，大和小对照，就讲述了这样的一个哲学的道理。这样的智慧能让我们用到大道的光芒，走在光明的大道上。</t>
+  </si>
+  <si>
+    <t>德经 | 理性之道</t>
+  </si>
+  <si>
+    <t>第五十三章（53）</t>
+  </si>
+  <si>
+    <t>使我介然有知，行于大道，唯施（yí）是畏。大道甚夷，而民好径。朝甚除，田甚芜，仓甚虚。服文彩，带利剑，厌饮食，财货有余，是为盗滥竽（yú）。非道也哉！</t>
+  </si>
+  <si>
+    <t>假如让我稍微有些认知，行走在大道上，最害怕走到斜路上去。大道非常平坦，但一般人喜欢走捷径。（无道之君）朝政非常混乱，田园非常荒芜，仓库非常空虚。穿着华美的衣服，佩带锋利的宝剑，吃饱喝足，积存财货有余，这样的人叫做强盗头子（滥竽：强盗头子）。这种行为是不符合大道的！</t>
+  </si>
+  <si>
+    <t>讲到这里大家已经非常清楚了，老子衡量事情的最高原则就是大道。“使我介然有知”，“芥”就是小的、稍微的意思。假如让我稍微有知识、有智慧，“行于大道”，走在大道上。我最怕的是什么呢？“唯施是畏”，“施”，就是逶迤、曲折，在这里指的是邪路、歧路。走在大道上最可怕的是什么呢？就是害怕歧路太多，害怕走到邪路上去。“大道甚夷，而民好径。”其实大道是非常平坦的，但是一般人都喜欢走捷径，老想抄近道。“朝甚除”，朝政非常得混乱。“田甚芜”，田园都已经荒芜了。“仓甚虚”，仓廪实才好嘛，现在仓库里边都是空虚的。可是那些统治者在干吗呢？“服文采，带利剑。”穿着漂亮的、非常昂贵的衣服，带着珍珠宝石装饰的利剑。“厌饮食”，什么东西都吃腻了，对什么好吃的东西都已经感觉到厌烦了。“财货有余”，家里的财宝有那么多的富余。这叫什么？“是为盗夸。”《道德经》认为这个就叫“盗夸”，强盗，还夸耀自己的强盗行为。《道德经》在第七十七章里边就讲，“天之道，损有余而补不足”。现在这些人做的是什么呢？“损不足，以奉有余”。“非道也哉”，这完全不符合道的规律、规则，完全不是按照道的方式来做嘛。这一章表现了老子的平民的思想、公平的思想，指责在“朝甚除，田甚芜，仓甚虚”的情况下，那些人“服文彩，带利剑，厌饮食，财货有余”夸耀自己的强盗行为。这一章有一些字，我们还得具体地、细致地解释一下。“唯施是畏”，凭什么把这个“施”念成“迤”，解释成歧路呢？因为道弯弯曲曲的时候，歧路众多。在《列子•说符篇》里边讲的一件事——歧路亡羊。杨朱他们家的邻居羊丢了，很多人都出去找，杨朱就觉得很奇怪就问，就一只羊怎么这么多人去找啊？邻居就告诉他，歧路多，岔路太多了。找羊的人回来了，杨朱问找到了吗？邻居说没找到。又派更多的人去找，还没有找到。歧路中又有歧路，岔路中又有岔路，所以常常使人丧失了大道，迷失了大道，所以杨朱听了之后几天都不说话。古人有“歧路亡羊”，也有遇穷途而哭，走道遇到没有路了，痛哭而返，其实都是感觉到了人生道路上的一些很值得人害怕的事情。行于大道，最害怕的就是歧路、岔路，一旦走错路，方向一错，后边的一切麻烦就都来了。所以老子说“大道甚夷”，“夷”就是平坦的意思，大道其实极为平坦。“而民好径”，人却老喜欢去走这个捷径，走了捷径之后，最后发现回到正确的大道上是非常困难的。其实，很多的所谓捷径就是歧路，就是邪路，人要脚踏实地，这样才能够行走在正确的大道上。通过努力获得成功，而不要投机取巧，更不要把投机取巧里边得到的东西当作一种炫耀夸耀，这个叫什么？“盗夸，非道也哉。”</t>
+  </si>
+  <si>
+    <t>德经 | 错误之道</t>
+  </si>
+  <si>
+    <t>第五十四章（54）</t>
+  </si>
+  <si>
+    <t>善建者不拔，善抱者不脱，子孙以祭祀不辍。修之于身，其德乃真；修之于家，其德乃余；修之于乡，其德乃长；修之于国，其德乃丰；修之于天下，其德乃普。故以身观身，以家观家，以乡观乡，以国观国，以天下观天下。吾何以知天下然哉？以此。</t>
+  </si>
+  <si>
+    <t>善于进行精神上的建设这是不可拔除的，善于掌握道的人不会脱离道，子孙世世代代不断尊敬、学习这个原则。用这个道理来修身，他的德会是真实的；将这个道理贯彻到修家，这样他的德才能有余；用这个道理来治全乡，他的德才能不断丰富成长；用这个道理来治国，他的德才会丰盛；用这个道理来治理天下，他的德才会是普遍的（遍及全国）。所以按照修身的原则来观察个人，按照齐家的原则来观察家庭，按照治乡的原则来观照乡，按照治国的原则来观照国，按照治天下的原则来观照天下。我怎么知道天下是这样的呢（我凭什么来了解天下情况的好坏呢）？就是因为这个道理。</t>
+  </si>
+  <si>
+    <t>第五十四章由三段构成。第一段：“善建者不拔，善抱者不脱，子孙以祭祀不辍。”这一段在讲按照大道来建设，没有人能够攻击倒它，把它拔除掉。大家想，人类建设的很多的东西，有成必有毁，都是会被拔除掉的，而大自然呢，比如说山川，这是大自然建筑的东西，有的或许可以被拔除掉，但这一章讲的不是这个意思。“善建者”指的是人精神方面的建设，大道方面的建设，这个伟大的思想是不会被攻击倒、被拔除掉的。比如我们现在学的《道德经》，历经两千多年，很多人都在攻击，在否定，在嘲笑，可是这无碍于它伟大的思想，现在学的人越来越多，大家越来越从里边得到一种智慧的启迪。另外像佛祖释迦牟尼，像孔子，历史上一些伟大人物的思想，他们的思想像什么？就像夜幕中的星光，给我们在黑暗中指引方向，有的甚至像光明普照的太阳。这些思想属于“善建者”，是没有办法把它攻击倒、拔除掉的。“善抱者”是什么意思呢？直观的理解就是善于把你抱住的人，你是脱离不开他的掌控的，其实这只是望文生义的理解。在《道德经》里边多次提到“抱”字，比如说第二十二章，“抱一为天下式”；比如说第四十二章，“万物负阴而抱阳，冲气以为和”。抱的是什么？“负阴抱阳”。所以这个“善抱者”就是掌握阴阳之不测，掌握阴阳相互作用、相互变化的规律规则，而“一阴一阳之谓道”，所谓“善抱者”，也就是了解大道的人。“不脱”，脱离不开大道的掌控，脱离了大道就走到了一个危险的境界。“子孙以祭祀不辍”，一代一代，千秋万代，按照“善建者”、“善抱者”这些伟大的思想来做，对他们表示一种尊重、敬仰，不断地学习。“修之于身，其德乃真。”按照这个伟大的思想来做事、来修身，这样所得到的德，才是真实的、纯净的。“修之于家，其德乃余。”按照大道来修家，一家人遵循大道，这样获得的家的品德才是丰盈有余的，积德之家必有余庆嘛。“修之于乡，其德乃长。”拿大道来传达给一个乡，按照这个方式形成一种良好的乡风。“长”就是领导的意思。你把这个方式在乡里边普及，让大家坚定地按照道的方式来做，你才能成为这个乡的好的领导者。我们知道，在宋朝的时候，陕西“蓝田四吕”首先制定了乡约，它对我们中国良好的乡风的培育起了非常大的作用，这不就是“修之于乡，其德乃长”的具体表现嘛。“修之于国，其德乃丰。”按照这样的一个方式来治理国家，让国家按照大道去做，所收获的德才是丰盛的、伟大的。同样的道理，“修之于天下，其德乃普。”天下是天下人的天下，不是一人之天下，所以大道之行，天下为公。按照善建、善抱的大道来做，修之于天下，这样大家得到的才是普遍的，如光明之普照。这是第二段，老子在讲按照“善建”、“善抱”的原则来做，所获得的伟大的结果。“以身观身”，“观”就是观察。我们按照修身的要求，大道修身的方式来观察这个人，他修身方面是不是善建、善抱，是不是没有脱离大道。“以家观家”，按照家庭的修养的要求来观察家庭的品德、家风。当然这个“观”的时候就自然有对比的意思，和其他的家里边进行对比，相互比较，看哪一个是更能按照“善建”、“善抱”的这种符合大道的原则方式来修身、来齐家。下边也是同样的道理，“以乡观乡”，乡自有乡的要求，和家是不一样的，范围扩展了，有很多家庭。但是如果这个大道一以贯穿，都是按照对“善建”的、“善抱”的原则祭祀不辍、尊敬，敬仰，以按照这样的一种规则来作为荣耀，都为良好的家风、乡风做出贡献，这不就是道一以贯之吗？同样的道理，“以国观国”，一个国家有这个国家的精神、思想、风貌，按照大道要求来做，在和其他国家比较中，取长补短。同样的道理，“以天下观天下”。大道一以贯之，一条主线，一切顺理成章，自然而然，无往而不胜。所以最后老子说，我怎么知道天下也会是这个样子？“以此”。大道所向无往而不胜，虽然人世间有那么多的枝枝蔓蔓，但是核心“善建”、“善抱”之大道，不要脱离开大道，坚定地、坚持地按照它去做，按照道去做就是“有德”。修身得到的是“真”，修家得到的是“余”，修乡得到的是“长”，修国得到的是“丰”，修天下得到的是“普”。所以，从修身开始，最后落到天下，不就是这样一个简单的道理吗？其实读这一章的时候，大家会有一个非常深刻的感受，中国先秦时代是中国的轴心时代，各个思想流派之间的思想，虽然有差别，但是也有相同的地方。所以我们看这和儒家的思想，修身、齐家、治国、平天下一样，都是从修身开始，最后才能够成为国家的好的领导者，才能把这种思想普及到天下。“天下难事必做于易，天下大事必做于细。”从自身做起，要求自己按照大道的这种修养、修为，按照“善建”、“善抱”的原则，坚持地、坚定地去做，我们才能真正地有德。</t>
+  </si>
+  <si>
+    <t>德经 | 广大之道</t>
+  </si>
+  <si>
+    <t>第五十五章（55）</t>
+  </si>
+  <si>
+    <t>含德之厚，比于赤子。蜂虿（chài）虺（huǐ）蛇不螫（shì），猛兽不据，攫（jué）鸟不搏。骨弱筋柔而握固，未知牝牡之合而全作，精之至也。终日号（háo）而不嗄（shà），和之至也。知和曰常，知常曰明，益生曰祥，心使气曰强。物壮则老，谓之不道，不道早已。</t>
+  </si>
+  <si>
+    <t>含德深厚（品德极为高尚）的人，就好比刚出生的小孩。蜂蝎毒蛇等都不会刺咬他，猛兽不抓他，猛禽不攫取他。筋骨柔弱但小拳头握得很牢固，不知道男女交合之事但生殖器会举起，这是因为他精气充足。整天嚎哭但嗓子不会哭哑，这是因为他元气醇和。知道醇和、平和就是了解了道的规律、规则，了解这个事物规律、规则的人才是明智，让我们的生命有益才是一个吉祥，纵心任气，是强暴、强蛮的表现。事物太强盛了就会走向衰老，（追求过分强盛）这叫做不合于道，不合于道便会早早灭亡。</t>
+  </si>
+  <si>
+    <t>这章开头讲了一个非常有意思的概念，就是“赤子”，这是因为婴儿刚出生的时候浑身是红色的，但这个词更重要的作用是比喻心地的纯净、纯洁。“含德之厚，比于赤子。”按照道的标准来衡量，赤子心地纯净，无恃无为。这是含德浑厚的一种表现。其实，不只老子，孔子也对婴儿的状态充满了景仰，认为这是一种有道的含德之厚的表现。孟子也说，“大人者不失其赤子心”。老子更是把婴儿作为一个范本与榜样，第十章就说“专气致柔，能如婴儿乎？”人精神集中，气息平和，那不就是像婴儿的样子吗？下边这些都是从经验的角度来讲获得的感受。小孩的他精神状态很安稳，蜂子、毒虫、蛇也不蜇他，也不咬他，为什么呢？因为小孩没有危险，没有对这些动物造成威胁的举动。其实有时候蜂子落到我们脸上，也许只是为了得一滴汗液，没有汗液，它采的蜜也不能凝固，可是我们一打它，它当作危险的时候，就要用它的毒针来蜇我们。很多动物也是这样，人没有危险动作的时候，其实也不会攻击人，但人见到它就害怕，就有一种防范甚至攻击性的动作，这也是难免的。老子说你看，这婴儿啊，“毒虫不螫”，毒虫不蜇他。“猛兽不据”，虎啊、狼啊这些猛兽，也不把它叼走，不用爪子把他抓走。我们经常会听到这样的一些事，很多动物还喂养、抚育这些落在田野里边的荒野上的小孩，当然这也不是全部的情况，我估计老子也是拿这个做一个说明而已。“攫鸟不搏”，攫，攫取。有的时候，人手上拿着一个什么东西，比如说拿着肉，在一些荒远的地方，老鹰就飞下来把这肉抢走了，但是对小孩它却不这样做，除非是尸体。“骨弱筋柔而握固”，这小孩其实身体是最柔软的，但是你看他这小拳头却握得很紧固。这人生啊，深究起来是有点意思。小孩刚出生的时候，都是握着拳头，似乎想抓住点什么，但人最后离开这个世界的时候，却是放手了，知道什么也抓不住。“未知牝牡之合而全作”，“牝牡”本来指的是雄性和雌性的动物，但是这个地方指的是男女。小孩刚出生不知道什么男女的事情，但是你看他的小生殖器却非常坚挺。老子用这样的一个方式来做形容，说婴儿精气很纯、很多、很壮，“精之至也”，达到了一个最好的状态，老子是这样认为。下边这个描述确实挺有意思，叫“终日号而不嗄”，小孩终日啼哭，但是嗓子却不哑，那不是精气足的表现吗？我现在讲课，讲一段时间喉咙就哑了，我们现在为什么会这样？老子可能认为，这人长大了，欲望多了，精气耗费得多了，所以就不像小孩那样精气充足。这一段把婴儿作为一个得道者的良好状态的表现讲完了，下边老子该阐述自己的观点了。“知和曰常”，“常”就是规律、规则。了解了这个“和”，通过婴儿引出来的“和之至”，谁能够像婴儿一样，让我们气息平和，让我们的欲望平和，不那么欲壑难填，就了解大道的规律、规则。“知常曰明”，了解这个事物规律、规则的人，那才是明智。“益生曰祥”，让我们的生命有益，这个才是一个吉祥的表现。这是正面，那负面呢？“心使气曰强”，老是盛气凌人，体现的是这种强横、强暴，这个是道家所反对的。气息不平和，纵心任气、任性，这个是强暴、强蛮的表现。在前面第二十三章讲过，“飘风不终朝，骤雨不终日，孰为此者？天地。天地尚不能久，而况于人乎？”暴风骤雨它不会持久，天地的使强也不过只是持续一阵子，它告诉我们这个道理，强不能持久。“心使气曰强”，这不是一种好现象。“物壮则老”，事物发展到顶峰的时候，就开始走下坡路了，人到了壮年之后，就逐渐向衰老的方向发展了。“谓之不道”，这已经使气，老是以强壮来作为目标、作为处理问题的方式，这是不符合大道的。“不道早已”，既然不符合大道，那这个事情就不能持久，很快就会结束了。你看这婴儿的状态，其实应该能存活得更长久、寿命更长，为什么后来很多人变得短寿了呢？那就是让自己脱离了大道，没有像婴儿那样，“精之至”，“和之至”。所以人应该“知和，知常，益生”，而不应该使气，不应该“物壮”，如日中天的时候就走下坡路了。人生最美的境界是什么？花未全开月未圆。所以，按照大道的方式来处事、认知事物，这样我们才能够明，才能够益，否则的话就会“不道早已”。</t>
+  </si>
+  <si>
+    <t>德经 | 天真之道</t>
+  </si>
+  <si>
+    <t>第五十六章（56）</t>
+  </si>
+  <si>
+    <t>知（zhì）者不言，言者不知（zhì）。塞其兑，闭其门，挫其锐，解其分，和其光，同其尘，是谓玄同。故不可得而亲，不可得而疏；不可得而利，不可得而害；不可得而贵，不可得而贱，故为天下贵。</t>
+  </si>
+  <si>
+    <t>有智慧（懂得大道）的人不多言，多说话的人不是有智慧的。圣人塞上欲望的孔穴，闭上欲望的门户，收敛锋芒，解除纷扰，在光明之处便与光融合，在尘垢之处便与尘垢同一，（能做到这些）这就叫“玄同”（就是与道同体）。所以既不可能与这样的圣人亲近，也不可能与他们疏远；既不可能使他们得利，也不可能使他们受害；既不可能使他们尊贵，也不可能使他们卑贱。所以他们被天下人所尊崇。</t>
+  </si>
+  <si>
+    <t>这一章还是比较容易理解的。“知者不言，言者不知。”开头的第一句话就讲，有智慧的人是不多言的，所谓“行不言之教”，还有“悠兮其贵言”，都在讲这个道理，有智慧的人是不会多嘴多舌的，不会去乱说的。“知者不言，言者不知”，老是认为自己无所不知、以为自己有智慧的人，其实是不具备真正的智慧的。“塞其兑，闭其门。”我们前边解释过，“兑”指的就是耳、目、鼻、舌这些感官，所以它强调的是感性对事物的认识，是不可信的。“塞其兑，闭其门”，这样才能对事物本质的根本的内容有真正的理解。下面讲处理问题的方式方法，做人的思想与智慧，要“挫其锐，解其分，和其光，同其尘”，不要锋芒外露，这样才能长久。要解除那些纷纷扰扰，不要让纷纷扰扰在心里打成结——心有千千结。真正了解道的含义的人，按照道去做事的人，是很容易摆脱这些纷纷扰扰的。“和光同尘”，也就是讲同流而不合污，所谓外圆而内方，所谓与世推移。那么这个叫什么呢？就叫做“玄同”。“玄”本来是天的颜色，意味着深远，这样的同是深远的、深刻的，同流而不合污，当然里边就非常有玄妙了。下面的内容讲得也非常清楚，就是说道并不是为人谋利益的，得道的人他怎么样来和万事万物打交道呢？就像道一样，“不可得而亲，不可得而疏”，道并不是对谁更亲近，或者对谁更疏远。有亲就必有疏，有疏就必有亲，这个就不平等了，这就不“玄同”了。所以，按照道的、“玄同”的方式来做，没有亲疏之别，无差别。“不可得而利，不可得而害”，有利必有害，有害也必有利。所以你并不能凭借道而获利，也不能用这个道来危害别人，无差别，无利无害。“不可得而贵，不可得而贱”，道对谁也没有贵贱之分，还是依然玄同、平等，一旦有贵贱之别，便也就丧失了道的本质的属性。所以庄子讲，“以物观之，自贵而相贱。以俗观之，贵贱不在己。”从物的角度来看，都认为自己是珍贵的、宝贵的，其他的东西比不上自己的尊贵。用世俗的观点来看，贵和贱不在于自己，而在于别人的评价，在于外在的标准。而“以道观之，物无贵贱”，从道的角度来看，这万事万物并没有什么贵贱之分，所谓公正、平等、无差别、无贵贱之分。正是因为这样，所以它成为天下最尊贵的，“故为天下贵”。所以这章的内容啊，道表现为玄同，按照这样的深远的玄同的道理来理解事物，就是从道的角度来观察问题。道没有亲疏之别，没有利害之分，没有贵贱之差，所以用这样的一个角度来观察世界，这个才使它成为天下最令人敬重尊仰的，“故为天下贵”。</t>
+  </si>
+  <si>
+    <t>德经 | 普适之道</t>
+  </si>
+  <si>
+    <t>第五十七章（57）</t>
+  </si>
+  <si>
+    <t>以正治国，以奇用兵，以无事取天下。吾何以知其然哉？以此。天下多忌讳，而民弥贫；民多利器，国家滋昏；人多伎巧，奇物滋起；法令滋彰，盗贼多有。故圣人云：我无为而民自化，我好静而民自正，我无事而民自富，我无欲而民自朴。</t>
+  </si>
+  <si>
+    <t>以清静无为之正道治国，以奇巧诡计用兵，以不多事滋扰来取得天下。我怎么知道是这样呢？因为如下情况：天下的忌讳（禁令）太多，人民就越来越贫穷；百姓拥有很多锋利武器，国家就会越来越混乱；人民拥有很多奇技淫巧，奇怪甚至邪恶之事就会越来越多；法律条文越严苛，盗贼反而会越来越多。所以圣人说：我无为（不去人为干涉） 人民便自我化育成长；我做到内心清静 人民就会自己走上正道（品行端正）；我不多事不扰民 人民自己就会富起来；我没有私欲 人民自然就会淳朴。</t>
+  </si>
+  <si>
+    <t>第五十七章的这段话非常有智慧，因为这段话一开始就指出来了，事物之间的不同，有本质的区别，所以处理问题、解决问题的方式方法也不一样。“以正治国，以奇用兵”，治国讲究的是堂堂正道。道家讲的“正”当然就是清静无为，不多事，不扰民，这就是道家讲的正道，是治国的大道理。可是用兵讲究的是“以奇用兵”，“兵者诡道也”，兵不厌诈。所以不能把用兵的方式、战争的方式用到治国的上面来，这两者不同，解决的方式也不一样。“以无事取天下”，无事就是不多事、不扰民、不刁难，这样才能够得到天下，并且坐得了江山。道家“无事”是“无为”的一个重要的方面，不多事、不扰民、不刁难，而“有为”讲的是妄为，多事、扰民、刁难，我们在前边这一点已经非常明确了。“吾何以知其然哉”，我怎么知道是这个样子呢？所谓“以此”就是依据上边“以正治国，以奇用兵”它们之间的本质不一样，所以解决的方式方法也不同而得出的结论。下面，老子开始谈他对治理天下的重要的看法。违背了大道，违背了道家的以“清静无为”为根本来治理国家的方式，会出现什么问题呢？“天下多忌讳，而民弥贫”，治理天下、领导国家忌讳太多，这个也不能动，那个也不能动，这个人的职务比较高，法令涉及不到他，当然出现了忌讳，不敢动，这个地方一定会形成一个空场，形成一个腐败的群体。百姓当然越来越穷了，财富都集中在少数人的手上。“民多利器，国家滋昏”，“滋”就是越来越。如果民间利器众多，武器众多，民与民之间械斗、抗法，那国家当然越来越混乱。“人多伎巧，奇物滋起”，“伎巧”就是各种各样的奇技淫巧，越来越多，大家对这些越来越感兴趣，这个技巧能够给他们带来利益，那么各种各样的奇奇怪怪的东西，甚至包括那些妖孽的东西，就不断兴起。“法令滋彰，盗贼多有”，既然这样，要用法律来管，法条定得越来越多，越来越严苛，反而盗贼越来越多。在前面这一段讲完之后，《道德经》说“故圣人云”，很明显，这是引用以往的通达事理的王们的话，老子用自己心中有智慧的人的语言来作为结尾。“我无为而民自化”，道家讲的无为，第一，“不妄为”。第十六章里边说“不知常，妄作，凶”，不了解事物的规律、规则，瞎折腾、胡折腾，这个结果是非常糟糕的。第二是“不多为”。抓住关键，举重若轻，多言数穷，不如守中，适可而止，恰到好处。第三讲究的是“有所不为”。人要想有所为，必须有所不为。一个政府也罢，一个领导者也罢，所有的事情都抓在自己手上，那底下的人怎么得到锻炼呢？不把担子压给他，他怎么练出独当一面的能力呢？什么事都控制在自己手上，那众人怎么样自我化育自我成长呢？所以无为才能让国家的人民、才能让自己的属下自我化育自我成长。事情成了应该怎么样呢？第十七章“功成事遂，百姓皆谓‘我自然’”，事情做成了，百姓都说这是我们的努力把这事情做成的，这就叫“民自化”。“我好静而民自正”，前面我们讲过，道家讲的静，内心的清净，静下来才能找到解决事物的正确的方法。我清静，走正道，不那么浮躁、急躁、暴躁、狂躁，做一个好的表率，上梁而正，百姓当然也就正了，百姓当然也就好静而走正道了。“我无事而民自富”，不多事、不扰民、不刁难，那百姓自然就富起来了。“我无欲而民自朴”，“朴”就是原木，《道德经》里用原木喻指做事敦厚、朴实、厚道，没那么多欲望，不是老想抢夺别人、占有别人的。就像黄宗羲在《明夷待访录》里边讲的，古代的那些皇帝都是什么样的？“离散天下人之儿女，荼毒天下人之肝脑，以供一人之淫乐。”这是我的，普天之下都是我的。所以欲望无止境，你让百姓能够朴实厚道，这也不可能。所以不要欲壑难填，不要什么东西都看作是自己的，可以任意掠夺，这样百姓自然就朴实、厚道，民心淳朴。这里边的两句话，我们国家的领导者讲话的时候也经常引用：“我无为而民自化，我无事而民自富。”所以，第五十七章讲了两个重要的道理，第一个不能把打仗的这一套用到治国之上。治国讲究的是堂堂大道，讲究的是清静无为，所以以无事取天下。第二个就讲站在领导者的角度，站在统治者的角度，应该怎么做呢？无为、好静、无事、无欲，这样自然一切顺理成章，百姓就会自化、自正、自富、自朴，事成了也会“功遂身退，百姓皆谓我自然”。这是一个好的领导者、好的政府做事的道理之所在，反之越多事儿，越是用那种严苛的法令，导致的结果适得其反。忌讳多了，百姓就越来越穷，民间的利器多了，国家就越来越混乱，大家都倾向于奇技淫巧，把这个当作一种喜欢的甚至不停地去追求的目标，那这个国家就越来越怪，各种奇葩的事情都纷至沓来。越觉得法令不够，越制定得严格、细致，以为单靠着法令就可以解决所有问题，反而适得其反，盗贼多有。所以，这一章里边讲的，也是我们经常说的——这本书的总纲：“反者，道之动”。我们考虑问题，不要只考虑它一面，要相反相成，用一个更高的观察事物的角度来理解。</t>
+  </si>
+  <si>
+    <t>德经 | 特殊之道</t>
+  </si>
+  <si>
+    <t>2、5、10</t>
+  </si>
+  <si>
+    <t>第五十八章（58）</t>
+  </si>
+  <si>
+    <t>其政闷闷，其民淳淳；其政察察，其民缺缺。祸兮福之所倚，福兮祸之所伏。孰知其极？其无正。正复为奇，善复为妖。人之迷，其日固久。是以圣人方而不割，廉而不刿（guì），直而不肆，光而不耀。</t>
+  </si>
+  <si>
+    <t>（治国者）为政宽容，人民就会淳朴善良；为政苛察，人民就会变得狡猾奸诈。灾祸啊 幸福就依靠在它的旁边；幸福啊 灾祸就埋伏在它的里面。谁能知道最终的结果是祸是福呢？没有确定的标准（永恒正确的事情）。正确会变为邪恶，善良会化作妖孽。人们不懂得这一道理，已经有很长的时间了。因此圣人方方正正却不去为难别人，有棱角但不去伤害别人，自己坚持正直品德却不强迫人去做，有光芒但内敛 不刺眼炫耀。</t>
+  </si>
+  <si>
+    <t>第五十八章有两个我们非常熟悉的成语，一个叫“祸福相依”，一个叫“光而不耀”，也是这一章核心的内容。祸福相依，福和祸是相互转化的，两者也是相辅相成的，分不开的。“光而不耀”在讲什么呢？我们大家看到过月亮，月光是明亮的，在黑暗中给我们指引以方向；同时月光也是不张扬的、不炫耀的、不刺眼的。中国人喜欢拿月亮来比喻君子的形象，做君子得先有光，但是不管我们有什么，都不要老想着去张扬、炫耀，让别人感觉到刺眼。所以《道德经》很多章节，都向我们揭示了这样一个道理：有才华、有知识、有道德的人，不要老想着去张扬、炫耀。以这两个成语为切入点，我们会对这一章的内容有个直观的感觉。我们来逐字逐句地解释一下。“其政闷闷”，“闷”就是淳厚。就说政治比较淳厚宽容，那么这个国家的百姓也就是敦朴淳厚，不耍心眼。“其政察察，其民缺缺”，假如这个政治非常苛察，对一切都监控得到位，那老百姓就会感觉到有很多的缺陷与不足，就要耍心眼。所谓上有政策，下有对策，也就失去了原本的淳朴。“祸兮福之所倚，福兮祸之所伏。”福和祸是相辅相成的，在一定条件下是相互转化的。民间的很多说法，大家都能够体会到这意思的延伸和运用，比如，我们经常说“大难不死必有后福”、“好事多磨”……福和祸是相伴而行的，有时候我们认为是福的事情，它可以转化为祸，反过来也是一样，所以这就叫“祸福相依”。怎么样来理解这个事情呢？给大家举个例子，大家就清楚了。其实各民族的智慧到达高点的时候，往往是相互重合的，印度有一本佛经叫《大般涅槃经》，在这里面讲了这样一个故事。有一天早晨，一家主人一开门，门口站着一个衣着光鲜、非常漂亮的女子，主人就问你是谁，女子说我是“功德大天”，我到谁家谁家就一切兴旺。主人高兴地请进来，焚香供拜。刚一关门又有人敲门，开门一看，门口站着一个衣衫褴褛，非常丑陋的、黑瘦的女子，主人就没好气了，主人就问你是谁呀，那女子说我是“黑暗”，我到谁家，谁家就一切破败！主人当然不让她进来，拿着刀驱赶。结果这女孩说你太笨了，刚进去的是我姐姐，我们俩从出生这天起就没有分开过，你把我赶走了，她也留不下。主人不信，进去一问果然是这样。福跟祸是相伴而行的，所以它就提醒我们，遇到福事的时候就要小心谨慎，避免乐极生悲；遇到祸事的时候，也不要感觉到沮丧，因为我们对灾祸有所警惕，它可以避免后面更大的灾难。韩非子讲过“千里之堤，溃于蚁穴”，我们发现了这个蚂蚁窝，知道它是一个祸患，很早的把它堵上，那就避免了以后更大祸事的发生。这就是“祸福相依”的道理，在我们文化中影响是非常深刻的。讲完这一段后，《道德经》就说“孰知其极？”这个事物到达极点的时候，向它相反的方面转化，所谓两极相通，所谓物极必反，但是这个极在哪里呢？这个是需要我们认真去体会把握的。“其无正”，其实并没有确定的标准，所以并没有说我们到了一个什么程度，一定会向它相反的方面转化，这是要根据不同的时间、地点、条件，需要我们认真去领会把握的、体悟的一种智慧。“正复为奇，善复为妖。”“正”，你把它弄到极点它就偏了，“善”到达极点的时候，它就转化为它相反的方面。有些人老想寻找一个固定的标准，《道德经》就说：“人之迷，其日固久。”在这个方面的迷惑，时间已经由来已久。所以我们总是要寻找一个固定的标准，总是觉得做事情有一个固定的程序，固定的套路，这个就不圆融。下面就讲，“是以圣人方而不割”，“方”就是方正，“割”就是生硬。有原则但是不生硬，人要懂得去碰硬，但是不要去硬碰。方正而不生硬，这样才能圆融，我们把它叫做“外圆而内方”。“廉而不刿”，“廉”就是棱角，“刿”就是锐利。有棱角但是不要老用锐利之处去刺伤人。“直而不肆”，有人经常就说，我说这话你别在意，我这人很直。其实有的时候不是直而是自私，是放肆、过分。所以我们说直率，它是一种心态，但是你讲话的方式得懂得圆融，直率而不放肆。“光而不耀”，有光芒，但是不要老去张扬、炫耀，让别人感觉到刺眼。咱们中国人喜欢讲君子，什么样的人是君子呢？中国人除了用月亮来代表君子“光而不耀”的特点之外，另外，也喜欢用玉来代表君子的形象，所谓“谦谦君子，温润如玉”。“谦谦君子”出自《易经·谦卦》，原话叫“谦谦君子，用涉大川”，一个人保持这种内敛的、谦逊的风度，这样才能走好人生长远的坎坷的道路。另外一个是出自《诗经》的“温润如玉”，谁都知道闪着贼光的肯定不是什么好玉，真正的好玉都是光芒内敛，给人一种温润感。我认为“光而不耀”是中国文化里，对君子形象用得最好的一个比喻。我们有知识，不要老想着去张扬、炫耀，大家聚到一块的时候，一个人老去炫耀自己的知识，对别人的说法都嗤之以鼻，认为自己什么都懂，百事通，时间长了，大家就不喜欢跟这人打交道了。有道德，道德是约束我们内心的，不是老是向别人去张扬炫耀。《道德经》第三十八章开头这句话，大家都知道——“上德不德”，最有道德的人从来不去张扬、炫耀自己的道德。当然，至于炫官、炫富，这不仅不是一种君子的形象，还会给自己惹来无尽的祸殃。是否还记得第九章里“金玉满堂，莫之能守；富贵而骄，自遗其咎”，炫富炫贵，会给自己惹来无尽的祸殃。在第二章里“功成而弗居”，哪怕我们有功劳，不管是对家庭、对单位、对国家有功劳，也不要老想着去张扬、炫耀，越是不张扬、不炫耀，这个才能在人心里长久地存在。第九章里面也说“功遂身退，天之道”，这是符合自然的道理。第五十八章讲完之后，我再做一下梳理和强调。这一章有两点需要注意，一个是“祸福相依”的道理，一个是“光而不耀”的形象，怎么样能做到这一点？我们要明白“物极必反，两极相通”。了解这样的智慧与道理，我们做事情才能够圆融。所以一个有智慧的人，有智慧的领导者，为人处事应该方正而不生硬，要圆融，有棱角，但不要老去割伤人，要懂得委婉迂回地处理问题的方式。直率，但又不越界进入到了放肆、无所顾忌的程度，光芒内敛而不要老去张扬、炫耀，要给人留下一种谦谦君子、温润如玉的形象。这是我们和别人、和这个社会打交道的一个重要的思想与智慧。</t>
+  </si>
+  <si>
+    <t>德经 | 转化之道</t>
+  </si>
+  <si>
+    <t>第五十九章（59）</t>
+  </si>
+  <si>
+    <t>治人事天莫若啬（sè）。夫唯啬，是谓早服，早服谓之重积德（chóng）。重（chóng）积德则无不克，无不克则莫知其极。莫知其极，可以有国。有国之母，可以长久。是谓深根固柢（dǐ），长生久视之道。</t>
+  </si>
+  <si>
+    <t>治理人民要顺应天理 最好的办法莫过于节俭节制。只有节俭节制，才能早得道。早得道就是不断地积德修养自己。不断地积德就没有什么是克服不了的，没有什么克服不了就不知道它的力量有多强大。不知道其力量有多强大，（有了无可估量的力量）就可以掌管国家。掌握了治国的根本，就可以长久存在。这就是根本扎深、扎牢固，永世长存的办法。</t>
+  </si>
+  <si>
+    <t>这一章讲了两种生活的态度：一种是做“加法”，不断地叠加，不断地累积，有了还想更有，多了还想更多；另外一种是要懂得做减法，要节俭节制，有的时候我们的欲望减少一分，其实我们的幸福也就多一分。这两种人生态度也是相辅相成的，可是大家更注重的是第一种，所以一章就强调我们这种做减法的态度的重要性。其实这一章核心就讲四个字：节俭节制，讲节俭节制对一个国家、对社会的重要意义。“治人事天莫若啬。”一开始就讲“治人事天”，领导这个国家的人民要顺应天理。“莫若啬”，什么事情最顺应天理呢？节俭节制。我们现在用的这个词叫“吝啬”，这个词有点负面的含义，在《道德经》中这个“啬”，我们把它译成节俭节制，这样更符合于我们的接受习惯。“夫唯啬，是谓早服”，“夫唯”是个语气助词，“啬”是节俭节制。“是谓早服”，“早服”就是早得道。懂得节俭节制的道理，就是可以早得道的人。“早服谓之重积德”，“重”就是不断。懂得节俭节制就是在不断地积累自己的品德，积累自己的德行。因为我们说《道德经》道和德要分开理解，按照道去做，就是有德，不断地按照道去做，就是不断地积德。重积德就是不断地积德，所以你看“早服谓之重积德”，早得道，一直坚定地坚持按照这个去做，就是不断地积累自己的德性，积累自己的品德，积德。我们就像一条船，我们积的德就像水，水积累得越多，我们船才能自由地航行，不管你船多大，如果没有水，在那儿搁浅，它也发挥不了船的这种作用。“重积德则无不克”，“克”就是克服，按照这个“啬”的方式，也就是节俭节制的方式去做事情，那就没有什么困难克服不了的。因为在节俭节制里边磨练的就是人的思想品德，磨练的就是人的意志，磨练的就是人面对困难无所畏惧的态度。“无不克则莫知其极”，你说这个东西力量这么强大，没有什么东西它克服不了，所以它的力量“莫知其极”，你不知道它的力量有多么强大，对一个人是这样，对一个国家更是如此。“莫知其极，可以有国。”你看这话是给谁讲的？给统治者、领导者讲的。一个领导者领导团队，领导这个国家的人民培养出一种节俭节制之风，你这样才能让你的国家长久地存在，长久地发展。毛泽东主席在中华人民共和国成立的时候就指出，“贪污和浪费是极大的犯罪”，自己也以身作则。你领导团队，领导全国人民培养出一种节俭节制之风，这样面临什么样的困难的时候，大家都有信心去克服。“有国之母，可以长久。”“母”就是根本。节俭节制是立国，是国家长久发展的根本。我们现在叫“八项规定”“反四风”，领导国家的人民培养出节俭节制之风，国家才能长久持续地发展。有一件事儿大家都知道，电视经常打出一个公益广告，说现在每年中国人浪费的粮食就是世界上两亿人的口粮。你说世界上现在每天都有人在饿死，可我们中国人这么浪费，能符合天道，能符合天理吗？如果因为这种浪费有什么惩罚落到我们头上，那么我们也无话可讲。你从这一章里面就可以感觉到，一个人浪费，糟蹋的是自己的福分；一个国家浪费，糟蹋的是国家的福分，对国家的根本有所损伤。“是谓深根固柢，长生久视之道。”国家培养出节俭节制之风，才能长久发展，这样做叫什么？叫“深根固柢”。我们讲叫根深蒂固，你让这个根本、让根扎得深，扎得稳固，深根固柢。“长生久视之道”，于人来讲是如此，可以让我们的生命更为长久，因为一个人的节制节俭，不去放纵自己的欲望，这也是一种养生之道。得以长久地存在，长久地发展，得以长寿，对国家来讲也是如此。所以“长生久视”，长久地存在，大家能够长久地看到它。《道德经》强调“做减法”的这个方面，在世界哲学界，有着非常重要的影响。我们中国人有一个优良的文化传统，讲勤俭持家，讲勤俭治国，所以这个是我们文化中非常重要的方面，但是很少在哪一本著作里面把它强调到这样的一个高度。“治人事天莫若啬。夫唯啬，是谓早服。”这就是早得道，坚定地按照这个道去做，就叫积德。不断地积德，那就使我们能够根深蒂固，长久存在，长久发展。人如此，国家亦如此，道理是相同的。第五十九章，希望大家认真地品味体会老先生给我们讲的“根深蒂固”的道理。</t>
+  </si>
+  <si>
+    <t>德经 | 强大之道</t>
+  </si>
+  <si>
+    <t>第六十章（60）</t>
+  </si>
+  <si>
+    <t>治大国若烹（pēng）小鲜。以道莅天下，其鬼不神。非其鬼不神，其神不伤人；非其神不伤人，圣人亦不伤人。夫两不相伤，故德交归焉。</t>
+  </si>
+  <si>
+    <t>治理大国就像烹调小鱼一样（不要经常折腾它）。（君主如果能够）用道来领导、指引天下，鬼也就没有神秘莫测的力量。不是说鬼不神秘莫测了，而是它的神秘莫测伤害不了得道的人；不但鬼的神秘力量伤不了百姓，圣人也不伤害百姓。鬼和圣人都不伤害百姓，所以德不断地积累交汇 形成有道有德的世界（恩德都将施与百姓）。</t>
+  </si>
+  <si>
+    <t>这一章有一句话，大家都非常熟，叫“治大国若烹小鲜”，这句话也是这一章的核心。一九八七年，美国前总统里根在发表国情咨文的时候也引过这句话。二〇一三年，“金砖各国”开会，在一个联合的采访中，有一位巴西记者问过习近平这样的一个问题：你担任这么大的一个国家的这么重要的职位是一种什么心态？你用什么样的态度来对待自己的职位？习近平答记者问，先引的是《诗经》，来回答第一个问题：“战战兢兢，如临深渊，如履薄冰。”这话出自《诗经·小雅·小旻》。治理国家要小心谨慎，就像行走在结着薄冰的冰面上一样，就像站在悬崖边一样，要小心谨慎，因为稍不谨慎就会出大的问题、大的危险。然后引用这句话来回答第二个问题，我要以“治大国若烹小鲜”的态度来对待我的职位。“治大国若烹小鲜”是什么意思呢？大家如果上网去搜对这句话的解释，类型就有二十多种，每一种解释都不一样，有的甚至把它直接翻译为“治理一个大的国家就像烹一碟小菜那么简单”，这是完全没有理解这句话的真正的含义。“小鲜”就是小鱼儿，鱼肉很细很嫩，拿它的时候就得小心谨慎，尤其是在高温里烹炒它的时候，都要小心谨慎，要有耐心。火候不到的时候你老折腾，甚至锅铲飞舞，翻腾，鱼不就成了碎片了吗？汉朝的毛亨，喜欢《诗经》的人都知道，这个人写过《毛诗传》的，他就用两句话来解读这句话，其实最符合它的本意。第一句话叫“烹鱼烦则碎”，环节太多老折腾它，那鱼就成了碎片了。第二句话“治民烦则乱”，治理一个国家也是一样，讲究的是制度的稳定，不能今天一个制度，明天一个制度，朝令夕改；你不能今天一个运动，明天一个运动来回折腾，国家不就被折腾散架了嘛。“治大国若烹小鲜”和“战战兢兢，如履薄冰”的道理是相同的，讲究的是小心谨慎，有耐心，掌握火候。“以道莅天下，其鬼不神。”“莅”就是莅临。用道来领导天下，指引天下。大家注意，这个“神”字很多的理解有问题，其实并不是神鬼的神，不是说我们后来的人格神、神化了的神。这个“神”在《易传》里面的解释是非常明确的，“阴阳之不测之谓神”，也就是神秘莫测。用道来领导天下、指引天下，鬼也没有什么神秘莫测的力量，因为你走的是正道，你走的是堂堂大道，鬼也没有办法去伤害到你，所以“以道莅天下，其鬼不神”。《道德经》里用它的道，把大家所恐惧的鬼的位置给取代了，你堂堂大道，鬼也近不了你的身，“其鬼不神；非其鬼不神”，不是鬼不神秘莫测，是因为你走大道，它的神秘、莫测、玄妙、诡秘已经没有办法伤害到你。所以把下一句话作为上一句话“其鬼不神”的注解，就很容易理解了。“非其鬼不神”，不是说这鬼不神秘莫测了，神秘莫测是它的本性。“其神不伤人”，但是它的神秘莫测已经伤害不了这种走在大道上的人、得道的人。“非其神不伤人，圣人亦不伤人”，不单是指鬼的力量伤害不了人了，反过来说，圣人他智慧高，但圣人智慧高也得返璞归真。圣人不会因为自己的智慧高，心眼多套路深，就使用这种“技巧”，这个东西不是正道。所以，鬼的神秘莫测伤不了人，圣人的智慧在领导大家的时候也会“善利万物而不争”，对人民没有伤害，“夫两不相伤”，你看鬼的神秘莫测也伤不了人，圣人领导也伤不了人。“夫两不相伤，故德交归焉。”所以有德的事情，积德的事情，两者交汇到一起，两不相伤。因为你按照道来做事情的话，鬼伤不了你，圣人也是按照道来做的，彼此也不相伤。这样大家就走在正确的道上，按照道去做，不断地积德，所以叫“德交归焉”，交汇，归到一块。“治大国若烹小鲜。以道莅天下，其鬼不神。非其鬼不神，其神不伤人；非其神不伤人，圣人亦不伤人。”如果这样两不相伤的，那就是“德交归焉”，这样就形成了一个和谐的、有道的、有德的世界。</t>
+  </si>
+  <si>
+    <t>德经 | 整体之道</t>
+  </si>
+  <si>
+    <t>第六十一章（61）</t>
+  </si>
+  <si>
+    <t>大国者下流。天下之交，天下之牝（pìn）。牝常以静胜牡，以静为下。故大国以下小国，则取小国；小国以下大国，则取大国。故或下以取，或下而取。大国不过欲兼畜人，小国不过欲入事人。夫两者各得其所欲，大者宜为下。</t>
+  </si>
+  <si>
+    <t>大国要像大海一样居于百川的下游 就像处在江河的下游。处在天下交汇的地方，处在天下最雌柔的地方。雌性常以柔静胜过雄性，是因为柔静的性格是一种谦下的表现。所以大国以谦下的态度对待小国，就可以争取到小国的支持；小国以谦下的态度对待大国，就可以得到大国的庇护。因此有的谦下能够取得别人的拥戴，有的谦下能够取得别人的庇护。大国所希望的不过是得到小国的支持，小国所希望的不过是得到大国的庇护。大国小国都达成了各自的愿望，越是大国越要懂得善于处下（谦下）。</t>
+  </si>
+  <si>
+    <t>《道德经》从头至尾有一个非常重要的智慧与理念：善于处下。在第八章里面就说，“处众人之所恶，故几于道”，水去的是又低又脏的地方，把那里的污浊洗净，在那个地方滋润万物，跟道最接近的。做人要做“上善若水”的人，才能称其为“大人”，这个“大”代表的是品德。国家要成为一个大的国家，该怎么样做呢？它的处事的态度是什么呢？第六十一章里边开头这句话说得简要、明确、深刻：“大国者下流。”所以，这一章的核心我们看一下，开头“大国者下流”；结尾“大者宜为下”。越是大的国家越懂得善于处下，和小的国家打交道的时候谦逊谦和，和谐相处，你就把小的国家争取了。人也如此，位置越高，越要善于处下，这样才能真正居上。这是这一章的开头、结尾，也是这一章的核心。我们在解读“大国者下流”之前，我们需要采用以经解经的方式，拿第六十六章开头这句话，用这个形象先来让大家直观地感知一下，这个直观的形象我们了解了，再来看这一章就容易了。第六十六章开头这句话：“江海所以能为百谷王者，以其善下之，故能为百谷王。”大江大海为什么能成其大呢？它地势低，善于处下，其他的水系就都汇到它这来了，用我们习惯的话讲，就叫“善于团结一切可以团结的力量”。不辞细流，所以成为大江大海。然后我们再来看第六十一章开头这个五个字就很容易理解了。“大国者下流。”所谓“下流”，就是善于处下、处在水的下游，最好是处在大海的入海口，涓涓细流慢慢地汇成大江大海。那么善于处下《道德经》拿什么来比喻它呢？这个地方是什么？是天下的水交汇的地方，所以叫“天下之交”。拿什么来比喻“天下之交”的呢？《道德经》把它叫“天下之牝”，“牝”代表母性、女性，本来这个“牝”是指母性的生殖部分。因为在《道德经》里边母性、女性代表着慈，代表着柔，代表着静，“牝常以静胜牡”，“牡”是雄性，“牝”是雌性。这世界上的事情便是如此，这雌性善于柔，善于静，所以她的力量更长久。拿这个道理来说明什么呢？以静为下，什么叫善于处下？就是以静为下。别那么急躁、暴躁、浮躁、狂躁，善于处下，这样才能具有更大的力量、更长久的力量。这段讲完了，下边又接着“大国者下流”的道理。上面那一段是在论述它力量产生的源泉。一个大国老去动武，喜欢好战，好战者必亡，看着很强大，其实这都不是长生久视之道。所以下面就讲，“故大国以下小国，则取小国。”不是以静为下吗？善于处下吗？一个大的国家在跟小的国家打交道的时候，态度谦逊谦和，善于处下，不是居高临下、盛气凌人、不可一世的处事的方式方法，把这个小的国家就争取了。你和它平等相待，它觉得你这个大国可以倚靠，它喜欢跟你交往，遇到事情的时候喜欢支持你，帮助你，为你出力。“小国以下大国，则取大国。”为什么小国会这样做呢？因为小的国家也得找倚靠。小的国家在和大的国家打交道的时候，也善于处下，也把自己的位置放低，那么它就成了大国的朋友，有事的时候，大国才能给予支持，用我们现在习惯的话叫“罩着你”。大国也罢小国也罢，都得善于处下，这样才能形成一种和谐的关系。下面这两句话是比较难以理解的。“故或下以取，或下而取。”什么叫“以取”呢？争取有两种方式，一种是从上边抓起来，还有一种方式是更为有智慧的从下面轻轻地托起来。别小看这两个虚字、连词，“以”和“而”，这表示不同的动作。“或下以取”，要抓住你掌控你，“执者失之”，越想抓住越想掌控，失去得越快。“或下而取”，其实我们在帮助别人的时候，也就获得了别人的这样一种真心的敬佩，遇到事情的时候才能够得到人家帮助。“大国不过欲兼畜人”，大国想要更强大，就得需要更强大地支持，大国就得团结更多的小的国家，形成一个相互支持、相互帮助的局面。我给大家举一个例子，大家对这个问题就理解更深刻一点。我们中国文化的图腾——龙，大家都熟悉，我们叫“龙的传人”。可是，龙在自然界里面是没有的，它是怎么形成的呢？原来这些氏族部落，我们也可以把它看作是一个一个小的国家，那个时候他们互相征战、合并。龙的主体的部分就是蛇图腾，源自中原地区一个力量非常强大的部落，后来这个部落把很多小的部落合并到自己大的部落里边，它们收归一个部落就加上一个部落的图腾，这样，逐渐形成了龙的样子：蛇的身，马的头，鬣的尾……这不就是“兼畜人”吗？其实落到国家的层面也是一样，形成了一个团结的阵营，当然最好是正义的，遇到事情力量不就强大了吗？“大国不过欲兼畜人，小国不过欲入事人。”小国不过也想加入这个里面，大家一起做事，遇到事情的时候，大国还可以帮助、支持，这不是挺好的事儿吗？各得其所，所以叫“夫两者各得其所欲”，都得到自己所想要的。话讲完了，下边这句话又来了，“大者宜为下”，越是大的国家，越是位置高的人，越要懂得善于处下。</t>
+  </si>
+  <si>
+    <t>德经 | 静守之道</t>
+  </si>
+  <si>
+    <t>第六十二章（62）</t>
+  </si>
+  <si>
+    <t>道者万物之奥，善人之宝，不善人之所保。美言可以市尊，美行可以加人。人之不善，何弃之有？故立天子，置三公，虽有拱璧以先驷（sì）马，不如坐进此道。古之所以贵此道者何？不曰以求得，有罪以免邪？故为天下贵。</t>
+  </si>
+  <si>
+    <t>道是万事万物的奥妙所在，是善良的人珍贵的宝贝，是不善的人得以拯救的保障（道可以拯救走错路的人）。说好的话、正确的话可以得到人们的尊重，美好的品行可以增加人的尊贵。品行不善的人，为什么就要把他抛弃掉？所以在天子即位时，设置三公，用珍贵的玉璧在前、驷马在后的礼仪来进奉，都不如静坐修道（把大道传授给他们）。为什么自古至今都把道看得这么珍贵呢？不就是因为按照道去做就能够有求而得、有罪而免吗？所以大道被天下人所尊崇。</t>
+  </si>
+  <si>
+    <t>这一章比较难理解，先说一下这一章的断句，有很多不一样的版本。现在大家基本上能够认可的是“美言可以市尊，美行可以加人”，有的本子是“美言可以市，尊行可以加人”，断句的差别就在这两句上。这一章讲什么呢？这一章是讲“道”的重要性，“善人之宝”，善人要不停地按照道去做，是善人的宝贝。但是，不善人也不会被道所抛弃，道可以来拯救他，所以叫“不善人之所保”。现在我们从头来解释。“道者万物之奥，善人之宝，不善人之所保。”这个道是万事万物的奥妙之所在，所以它是“善人之宝”，是善良人的珍贵的宝贝，也是“不善人之所保”，是不善人得以被拯救的保障，道可以拯救这些走错路的人，让他回到正道上来。“美言可以市尊”，美言，好的话。说好的话、正确的话，它可以得到人们的尊重。“美行可以加人”，好的品行，可以增加人的尊贵，团结更多的人。其实这个道理也比较容易理解，我们熟悉的三个人——魏徵、李世民和长孙皇后。魏徵是美言，他劝李世民，你要做一个好皇帝，有些事你不能做。李世民很愤怒，回来之后在家里边发火，说要把魏徵给杀掉。长孙皇后反而衣服穿得很整齐，给他道喜，说你遇到了一个好的臣子，我应该向你贺喜。李世民后来领悟到这一点，他说镜子可以正衣冠，魏徵就像一面镜子可以正我的品行。历史上，三个人留下的都是美言，都得到了人们的尊重，所以叫“美言可以市尊”。既然道是“善人之宝，不善人之所保”，那么“人之不善，何弃之有”。有的人走错路了，你为什么就觉得要把他抛弃掉？让他回到正道上来，用道去教化、去拯救。这是从正面来说它的作用。下面就讲的这个事就有针对性了。“故立天子，置三公。”国家的制度慢慢地有了天子，作为最高的领导者，还有三公——辅佐天子的最重要的职位。“虽有拱璧以先驷马”，古代敬献礼的时候，拱璧，捧着玉璧，捧璧的人在前边，乘着高头大马进献。珍贵吧？不如“道”珍贵！这里面有两个意思：一个就讲国家的制度，有天子，有三公，很重要，但这也只是形式。还有呢，用高头大马进献珍贵的玉璧，这也是很珍贵。但是“不如坐进此道”，这些都不如按照道来做，大道才是“万物之奥”，“万物之宝”。“古之所以贵此道者何？不曰以求得，有罪以免邪？故为天下贵。”意犹未尽，讲到这地方，《道德经》还觉得这个话就应该再强调一下，说古往今来，为什么都要把这个道看得这样珍贵呢？“古之所以贵此道者何？”不就是说你按照道去做，你才能得到自己真正想要得到的吗？“以求得”，你要的那个东西才能真正得到。这里的“以求得”并不是像我们烧香拜佛求得发财。“有罪以免邪”，因为前面讲过，“不善人之所保”，就算走错路了，但是我们重归正道，浪子回头金不换，原来的这个罪，也能得以补偿。这个并不像有的宗教里边说你犯了什么罪去忏悔一下，这个罪就免除了，它是让你按照大道来做，回到正道。我们来分分类，人不就是这两类：“善人”、“不善人”，对那些不善良的人，走错路的人，你为什么要抛弃他呢？“坐进此道”，回归此道就可以啊。弄了那么多的官职，天子、三公，有那么多珍贵的财宝，拱璧、驷马，还不如“坐进此道”。既然如此，“道”就是天下人最珍贵、最宝贵的，“故为天下贵”。</t>
+  </si>
+  <si>
+    <t>德经 | 超然之道</t>
+  </si>
+  <si>
+    <t>第六十三章（63）</t>
+  </si>
+  <si>
+    <t>为无为，事无事，味无味。大小、多少，报怨以德。图难于其易，为大于其细。天下难事必作于易，天下大事必作于细。是以圣人终不为大，故能成其大。夫轻诺必寡信，多易必多难。是以圣人犹难之，故终无难矣。</t>
+  </si>
+  <si>
+    <t>用无为的态度、方式来作为，用不找事、不多事的方式来做事，最好的味道反而是没有味道。以小为大 因为大事都从小事做起、以少为多 因为积少才能成多，用德来对待别人的怨。对付困难事情要在它还容易解决的时候开始，成就大业要从很小的事情做起。天下所有的难事都是从容易的做起，天下所有的大事都是从小事做起。因此圣人始终不去直接做大事，不说大话空话，所以最后能成就大事。没有把握的事轻易许诺别人一定会失去别人的信任，把事情看得太容易一定会遇到更多的困难。因此圣人把所有事情都看得很难，反而没有什么难事。</t>
+  </si>
+  <si>
+    <t>第六十三章的内容，我们在前边已经有所接触。之前我们说，第二章就是《道德经》的“目录”，第二章列出来了后边讲的六个重要内容，有无相生、难易相成等等，这一章的核心就是“难”和“易”。这一章的核心意思就说，要想做大事，先从小事做起，想要以后攻坚克难，你得从容易的事情做起。还有一个重要的问题、重要的智慧：你要把容易的事情当作难的事情来做，要有充分的、认真的准备，提前思考它的步骤、程序、会遇到的问题，这样再出什么问题的时候，你就能从容应对。有这样的态度，天下也没什么难事。天下无难事，但天下都是难事，看你怎么对待。开头这九个字非常有趣：“为无为，事无事，味无味。”“为无为”——想要有为吗？你得先懂得无为的道理。为什么？因为有些事你越有为，越强求，什么事都管，反而最后结果非常不好。道家讲的无为，就是按照道的方式来作为，想要有为，先要懂得无为的道理，不要妄为，要抓住关键，举重若轻，有所舍才能有所得，所以为无为。其实也就是第三十七章里边讲的“道常无为而无不为”，道的规律、规则是什么？用无为的方式达到无不为的效果，更好的效果。我再强调一下，《道德经》里出现得最多的一个词是“天下”。《道德经》针对的是天下，千万不要把道家当作一种消极的被动的思想，它是“想为”，但是强调要通过正确的道路和手段，懂得无为的正确的道路和手段，才能达到真正的有效的为，也就是用无为的方式，达到无不为的这种效果。下边再落一层，“事无事”。大家都想做事，可是大家有没有注意到，有些人他是“找事”，他是捣乱，是阻碍、多事，天下本无事，庸人自扰之。所以我们做事的时候要懂得无事的道理，不要多事，不要找事，不要刁难。尤其是做领导者，没事找事，权力就是刁难，你这不就麻烦了吗？“事无事”，想做事，得懂得无事的道理，不要多事，不要扰民。再落一层，“味无味”。我们经常讲一个词叫“真水无香”，真正好的饮料，就像那白开水一样，没有味道。我们饮食讲究清淡，寡味，少油少盐。最高的味道，反而是没有味道，无味。当然，这三个词核心还是“为无为”，让大家能够更明白一点。老子展开来讲，“事无事”，不要多事，不要扰民，不要刁难，就像“味无味”的道理一样。按照这样的一个逻辑推下来，下面四个字大家就能明白了，“大小、多少”，千万不要把它念成“大小多少”，这个东西就没意义了。这是告诉大家要“大其小”、要“多其少”，要把小事看得很重要，细节决定成败，千万不要忽略这个细节。为什么要“大其小”呢？因为天下的大事，都是从小事做起，为什么要“多其少”呢？因为积少才能成多。想要多，你得从少的一点一点积累，积少成多。就像我们学习《道德经》，一章一章讲，一章一章学，不要着急，最后达到一个整体的理解。我们经常讲“聚沙成塔”、“集腋成裘”，这不都是“多其少”的道理吗？“报怨以德”，按照这种相反相成的道理，对别人的埋怨、恩怨，也应该站在一个“德”的角度，因为德是符合道，用道的东西里面去感化。第六十二章不是讲了吗？“人之不善，何弃之有？”人家有这个埋怨，怎么正确地对待呢？“报怨以德”。用这种智慧和层次，让大家一起能回归到正途，回归到正道。“图难于其易，为大于其细。天下难事必作于易，天下大事必作于细。”这几句话，在我们文化里边名气非常大，因为讲的是哲学上的量的积累达到质的变化的道理。“图难于其易”，“图”就是图谋、计划。你计划想要做难的事情，要从容易的事情做起。“为大于其细”，想要做大的事情，得从小的事情一步一步来。我们大家都知道要脚踏实地，循序渐进，有条不紊，一屋不扫，何以扫天下？“天下难事必作于易”，天下所有的难事，都要从容易的事情做起。就像小孩的培养，让他们在处理小的事情中就形成良好的习惯，把小的事情、容易的事当成培养良好习惯的重要途径，将来，小孩在遇到大事、难事都能从容应对。现在很多人都有一个致命的弱点，大概是人的通病，就是好高骛远，老觉得自己应该是做大事的人，对小的事情不屑一顾。《道德经》就告诉我们这个智慧：想要做难的事情，从容易的事情做起；想要做大的事情，从小的事情做起，“天下大事必作于细”。“是以圣人终不为大，故能成其大。”“是以”，“是”就是这样，“以”就是所以。所以有智慧的领导者就是这样：“终不为大”，不是老说大话，不是老给大家画饼充饥，而是脚踏实地，一步一步地做起，“故能成其大”。一步一步把这个事情完成了，一步一步地完成计划，最后实现一个大的蓝图，好的结果，水到渠成。所以一个有智慧的人，不是老用那些虚幻的东西来画饼充饥，老是给大家讲大话、空话。“终不为大，故能成其大”，最后反而成就了大事，这话讲得非常好。我建议大家学习《道德经》，有一种重要的学习方法，就是反复看。有的人看《道德经》，也许一年就看一章，反复地看，反复地体会，“少则得，多则惑”，“终不为大，故能成其大”。以管窥天，以锥扎地，我们视力更集中，这样把这个事情才能做得更踏实，扎得更透。我们每一次的进步，虽然看起来好像只是一点点，但是这一点点积累起来就不得了了，“终不为大，故能成其大”。“轻诺必寡信”，大家还记得我们在讲《道德经》第八章的时候，就讲过“言善信”，我们中国人喜欢拿潮水作为讲信用的代表和象征，所以，有一个词就叫“潮信”。你看那钱塘潮每到农历八月十八前后就来了，人也应该如此，说话要讲信用，要有诚信，能给别人做成的事我们再去允诺，没把握做成的事，不要轻易去答应，不管我们有多热情。如果我们答应人家的很多事最后都做不成，时间长了，人家一定认为我们是食言而肥，不讲信用。《道德经》讲话是比较宽缓的，但这句话用的就是强逻辑判断，“轻诺必寡信”，这不是对我们委婉的劝告，这简直就是对我们严厉的警告。所以要讲诚信，君子重一诺，一诺千金嘛，所以“轻诺必寡信”，要避免这种结果出现。“多易必多难”，你把这个事情看得很容易，做什么事情，最后一定出问题。世界上哪有容易的事情，吃个饭喝个水，这都需要功夫，需要本事，小事情我们都要认真对待。我们经常讲“小河沟里翻船”，把一个事情看得太容易了，太简单了，往往会在这个事情上出问题。面对很多难的事情，大家战战兢兢，小心谨慎，反而没事，反而就是在一些认为最容易的事情出问题。很多学生做题、考试也是一样，难题没事，在容易的题上，出了问题，回去捶胸顿足，懊悔无比。所以，我们平常要形成一种把容易的事情当作难的事情来做的习惯，你要懂得“多易必多难”，凡事太容易，后面一定会出现很多的困难，出现很多的问题。所以，下边这句话就讲：“是以圣人犹难之”，所以有智慧的人，把这容易的事情都看作很难。天下的事情都当作难的事情来做，反而结果没有什么难的事情，“故终无难矣”。这个道理非常有趣，其实就是相反相成的道理，这个叫“难易相成”。世界上有没有难事呢？有，也没有。你把这个难的事情当作难的事情，看作是无法克服的，它就是难的事情；你把容易的事情当作容易的事情，没有认真对待，最后也会变成难的事情。我们把容易的事情当作难的事情来做，最后那个难的事也就做成了；真正难的事情，我们认真准备，有充分的信心，最后这难的事情也就克服了。“故终无难矣！”世上无难事，这就是“难易相成”的智慧。很多事情，决定于我们的想法、态度，态度不同，难易之间就会相互转化。</t>
+  </si>
+  <si>
+    <t>德经 | 决策之道</t>
+  </si>
+  <si>
+    <t>2、8、64</t>
+  </si>
+  <si>
+    <t>第六十四章（64）</t>
+  </si>
+  <si>
+    <t>其安易持，其未兆易谋，其脆易泮（pàn），其微易散。为之于未有，治之于未乱。合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。为者败之，执者失之。是以圣人无为，故无败；无执，故无失。民之从事，常于几成而败之。慎终如始，则无败事。是以圣人欲不欲，不贵难得之货；学不学，复众人之所过。以辅万物之自然，而不敢为。</t>
+  </si>
+  <si>
+    <t>局面稳定的时候容易掌控，事情没有征兆（国家还没有出现动乱）的时候容易去谋划/对付，事物脆弱时容易消除，事物微小时容易消散。在危险局面还没有发生的时候就做好准备，在国家还没有混乱的时候就注意治理。合抱（两个人用手臂围起来，能够环抱住）的大树，都是从细小的萌芽一点一点长起来的。九层的高台，也是一层一层的土积累起来的；想要走千里的路，就要从脚下一步一步走起。强为、妄为就会失败，执意把控就会失去。所以圣人不强为、不妄为，所以不会失败；不强执、不固执，所以不会失去。众人做事常常在快要接近成功的时候惨遭失败。在事情快要做完的时候还像一开始时候那样谨慎、慎重，就不会有失败。所以圣人所想的都是别人不愿意去想的，不以难得的货物为珍贵；学别人不愿意学的，对别人的错误引以为鉴。圣人顺应着万物的自然天性去帮助它们成功，而不敢按照个人意志去做事。</t>
+  </si>
+  <si>
+    <t>第六十三章、第六十四章讲的道理，就是大家熟悉的量变和质变的道理，量的积累达到质的变化。但是大家注意，这个量的积累，有向好的方面，也有向不好的方面。前面讲了“为大于其细”，要做大事，从小的事情做起，这样才能最后达到想要的结果，假如积累的是一个不好的量，最后就积重难返。第六十四章一开始就要把两个方面，都给大家做了说明，有的事情在它刚出现向坏的方面发展苗头的时候，我们在这个阶段就把它解决了。这一章里有两个非常重要的内容，一个是大家都熟悉的一段话：“合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。”第二个就告诉我们，做事情要“慎终如始，则无败事”。这两个重要内容，我们先有一个直观的认识，再来读就好理解了。我们一句一句来解释。“其安易持”，“安”就是稳定，局面稳定的时候，容易掌控，就像一个东西，它稳定的时候，你容易把它把握住；它活蹦乱跳的时候，你把握起来就困难了。“其未兆易谋”，“未兆”，没有征兆的时候，苗头还没有开始的时候，容易去谋划。“其脆易泮”，脆的时候一打就打散了。“其微易散”，很微小的时候，很容易把它解散。比如说一件事情，很小的时候，人数很少的时候，你把它处理起来很容易。众怒难犯，一大群人轰起来、闹起来的时候，这事情解决起来就困难。前面告诉大家这些现象，然后告诉大家处理的方法。什么方法呢？“为之于未有”——在事情没有出现的时候，没有开始的时候，要有预见性，就要有作为，凡事预则立，不预则废。“治之于未乱”，还没有出现这种乱象的时候，就把它治理了、解决了。这也是习近平讲话时经常引用的两句话。怎么来理解呢？先给大家说第一个例证。有一次晏子出巡，齐国发大水，把一座石桥给冲毁了，晏子就把自己的船让给了灾民，大家都赞誉晏子爱民如子。然而一位有智慧的高人就批评晏子，就说你做这个国家的宰相，齐国发大水能把一座桥梁冲毁，你都没有预见到，没有提前做出预防，你失职。所以应该是怎么样？“为之于未有”，你别等这个事情都已经成为这个样子，再去处理它，不管你处理的方式多么巧妙，多么有智慧，但是不如让这件事情没有发生。另外一个例证更能说明这个道理。有一次，扁鹊的国王问扁鹊：扁鹊你名气太大了，你是不是国家医术最高的？扁鹊说不是，别人我不知道，起码我大哥、我二哥都比我的医术高。所以这个国王就很奇怪，你大哥、你二哥是谁？他们医术那么高，怎么大家都不知道他们呀？扁鹊就说，我大哥怎么治病的呢？人家还没有病，他告诉人家怎么预防、怎么不得病。这不是“为之于未有”吗？提前就有作为了，预防得病。我二哥怎么治病的呢？人家刚有一点小病，他就把人治好了，不让他酿成大病，“治之于未乱”。所以我们经常讲，凡事预则立，不预则废，要有远见，要有预见，要未雨绸缪。这是讲负面，因为有些事情量的积累是向不好的方面发展的，所以要提前把这个问题给处理掉。下面讲的这个事，非常重要。我们做大事情都要从容易的事情、小的事情，一步一步积累才能达到这种质的变化，要脚踏实地，循序渐进。因为什么呢？“合抱之木，生于毫末”，合抱之木，它是一点一点长起来的。“九层之台，起于累土”，中国文化中，三六九都代表着高、多。那么高的高台也是一层一层土积累起来的。“千里之行，始于足下”，走这么远的路，要脚踏实地一步一步地做起。说到这里，我得加一句，有人老认为道家思想是消极的、被动的、无为的。“合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。”这不就是自强不息吗？所以有些事我们不能人云亦云，我们得看原文，以原典作为证据。“为者败之，执者失之。”“为”就是强为、妄为。因为《道德经》讲的真正的为叫“无为”，就是按照道的方式来作为，不按照道的方式来作为就是强为、妄为。越是强为，最后的结果越糟糕，因为量的积累还不到，你老想强行地发生质变，这不是急躁冒进吗？“执者失之”，就像我们抓沙子一样，你握得越紧，流出来越多，越想用力地把它抓住，反而失去得越来越快。所以一个有智慧的领导者，“无为”，按照道的方式来作为，不妄为，不强为，不多为，有所不为，所以也不会有急躁冒进的失败。“无执故无失”，没有这样的强执，最后也不会失去。“民之从事”，平常人做事，或者说领着大家做事，在什么时候最容易把事情给做砸了呢？“常于几成而败之”，经常在快要接近成功的时候，把事情给做砸了。那应该怎么办？“慎终如始，则无败事。”什么叫慎终如始呢？我先给大家打一个比方，大家走在结着冰的冰面上的时候，刚一下到冰面上都是小心谨慎，战战兢兢。走一会儿，觉得自己走熟了，就放松警惕了，有的干脆最后开始跑了，有的甚至在冰面上炫耀，危险往往就在这个时候发生了。所以我们中国人经常讲一句话叫“行百里者半九十”，一百里的路，走到九十里路的时候，还要当才走了一半，越是剩下那一段的时候越紧要，民间讲“编筐编篓，全在收口”，即最后这个结尾。“慎终如始”，走到最后那几步，还像开始下到冰面上一样小心谨慎，一步都不放松，那就没什么败事，没什么事情做不成。“慎终如始，则无败事”，就是我们现在经常讲的不忘初心，善始善终，那就没有什么事情做不成的。“是以圣人欲不欲”，一个有智慧的人，特别是一个有智慧的领导者，想要的东西是什么呢？是别人都不关心的，都不想要的。因为“天下熙熙，皆为利来；天下攘攘，皆为利往”，大家关心的是获取利益的方式方法，而一个有智慧的人，有智慧的领导者，应该有这种无功利之心。“欲不欲”，别人都不想这样的，反而是你应该考虑的。大家都针对“有”的东西，这有智慧的人、好的领导者得针对这无形的东西：人的精神财富，人的精神世界，人的修养。既然“欲不欲”，你跟一般人的欲望不一样，他们认为那个东西是珍贵的、难得的，反而在你的眼里是不重要的，不把它看作是难得的。领导国家的时候也是如此，第三章讲的，“不贵难得之货，使民不为盗”，形成一种淳朴的风气。“学不学，复众人之所过。”《道德经》讲的道理，叫“绝学”，一般人不愿意学，学这个东西能带来什么样的好处、利益吗？人的境界高的时候，学的很多的东西不就是和一般人不一样的嘛。一般人不愿意学的东西，又花功夫，又不能带来什么实际的利益，可是“学”这些东西代表了真正的智慧与学问。学这些东西干吗呢？“复众人之所过”，这个“复”不是重复，我们下围棋的人都知道有个词叫“复盘”，通过不断的重复模拟来检视，哪个地方下得好，哪个地方下得不好。别人犯的过错像复盘一样历历在目，以此为鉴，别再犯大家都经常犯的错误。“以辅万物之自然，而不敢为。”“以辅万物之自然”，就是按照自然的规律去做，追求的是一种水到渠成、自然而然的结果。“辅自然”就是无为。“而不敢为”，就是不敢妄为。因为我们违背了道，违背了自然规律，哪怕是短时间取得成功，其实也会受到更大的一种惩罚。这章告诉我们，一是我们做事情要“为之于未有，治之于未乱”，懂得预防，懂得不好的事情在苗头出现的时候就把它解决掉；二是我们做事情要脚踏实地，循序渐进；三是我们要“慎终如始”，不忘初心，善始善终，因为我们做事情经常在快要成功的时候，结果功亏一篑，所以要懂得这样一个道理。</t>
+  </si>
+  <si>
+    <t>德经 | 实践之道</t>
+  </si>
+  <si>
+    <t>第六十五章（65）</t>
+  </si>
+  <si>
+    <t>古之善为道者，非以明民，将以愚之。民之难治，以其智多。故以智治国，国之贼；不以智治国，国之福。知此两者，亦稽式。常知稽式，是谓玄德。玄德深矣，远矣，与物反矣，然后乃至大顺。</t>
+  </si>
+  <si>
+    <t>古代那些善于按照道来治理国家的人，并不是用大道使百姓变得聪明伶俐，而是使人民敦厚淳朴。百姓之所以难以治理，是因为他们奇技淫巧太多。所以用技巧来治理国家，是国家的灾难。不用技巧治理国家，是国家的福分。知道这两者的差别，这就是治国的法则。能够永远把握住这些原则，就可以说是具备了微妙高尚的品德。高尚的品德高远深邃，好像与一般事理相反，最后又返回了宁静朴实的根本，然而具有这样的品质之后办起事来却十分顺利。</t>
+  </si>
+  <si>
+    <t>这一章所涉及的，也是我们现在哲学里面经常讲的一个道理，叫“否定之否定”规律，讲事物的发展分为三个阶段，第一个阶段是肯定，第二个阶段是否定，第三个阶段是否定之否定。比如说麦粒长出麦苗，最后结出更多的麦粒，这就是一个否定之否定的阶段。第三个阶段常常重复第一个阶段的某些特征，却是在更高的程度上重复第一阶段的某些特征。这一章和第四十章讲的“反者，道之动”，所运用的哲学的智慧和道理是一样的，既然这样，把这个道理运用到治国上，应该如何呢？这就用到了一个我们大家熟悉的词，叫“返璞归真”，《道德经》认为治民最关键的是要使民风纯朴，不要那么多的技巧，不要那么多的套路。了解了这一点，我们再来看这一章，就明白了老先生的良苦用心。“古之善为道者”，以前的那些善于按照道来治理国家的人。“非以明民，将以愚之”，不是让百姓有那么多的心眼技巧。这个“愚”，不是愚民，而是敦厚、厚道，让人民的民风纯朴。“民之难治，以其智多。”百姓为什么难以治理？因为他心眼多、技巧多。“智”就是技巧、心眼、套路。“故以智治国，国之贼”，用技巧来治国，经常用骗术谎言，这是国家的灾难。“不以智治国，国之福”，不用这些技巧，让民风纯朴、敦厚，这个才是国家的福祉、国家的福分。“知此两者，亦稽式。”“稽式”就是法则。知道这两个的差别，这就是一个法则，治国的一个法则。“常知稽式”，“常”就是规律。按照规律，我们来了解这个法则。这叫什么？“是谓玄德”，“玄”就是深远的意思，这个就是深远的智慧与品德。下面这句话就是我一开头讲的，这个品德“深矣，远矣，与物反矣”，“与物反矣”不就是“反者，道之动”吗？我们都能看到事物的正向的发展，所以《道德经》经常提醒我们，“反者，道之动”，道是向它相反的方向运动，所以你理解问题也不能只看一面。“与物反矣”怎么解释呢？第二十五章，“大曰逝，逝曰远，远曰反”，最后又回到了它的根本。根本是什么？“归根曰静”。民心没那么多的躁动，变得清静宁静、敦厚朴实，这不就符合大道了嘛。“然后乃至大顺”，这样慢慢地就回归到了正确的道路，符合自然之道。所以，这一章讲的就一个问题：你用什么方式治国呢？要让民心变得纯朴、敦厚，返璞归真，没那么多的技巧，没那么多的套路，没那么多骗人的把戏，这样才是符合大道。</t>
+  </si>
+  <si>
     <t>德经</t>
-  </si>
-  <si>
-    <t>第四十七章（47）</t>
-  </si>
-  <si>
-    <t>不出户，知天下；不窥牖（yǒu），见天道。其出弥远，其知弥少。是以圣人不行而知，不见而名，不为而成。</t>
-  </si>
-  <si>
-    <t>不用出家门，便能知天下之事；不用通过窗户去看，就能知道自然的规律法则。越是向外寻找求索，对道的认识就越少。所以圣人不用出行却能知事理，不必亲自观察却能明白道理，不必亲自去做却能成功。</t>
-  </si>
-  <si>
-    <t>由于这两章的内容非常相吻合、相近，所以我们合到一起作为一章来讲解。四十七章讲的是一个什么事儿呢？是说人的感性认识，从哲学上说就是我们的感官接触客观世界，有时候接触得多了，它反而会造成一种迷乱和混乱，要通过人的智慧、理性认识，这样我们才能了解事物的规律，也就是这一章里边所说的“天道”。在这个基础上，我们一句句来解释。“不出户，知天下。”“户”就是门户，也就是大门。我不用走出家门，不用去外边到处跑，也能了解天下的大事。为什么？因为道家认为，天下大道归根到底，融于人的内心。内心里边有道，也就了解了天下的正道，了解了天下的大事。“不窥牖，见天道。”“窥”，从小孔里看；“牖”，就是窗户。我不用通过窗户去看，也知道天地之间日月星辰运行的规律。所以你看这个地方，“出户”是行走，出行，行万里路；“窥牖”是眼睛看，用感官接触客观世界，我不用这样。所以这个地方大家就感觉到，直观的一开始看，就觉得老子这个人有点轻视感性认识，人得通过实践嘛，人得通过感官接触客观世界，才能产生对客观世界的认识。是不是老子把这些东西全部都否认了呢？不是的。因为大家从书里已经看得非常的清楚，《道德经》举了很多生活中的例子，比如说“治大国若烹小鲜”，比如说“凿户牖以为室”，比如“说三十辐共一毂”，前面讲过的，这不都是生活中的例证吗？他对这个东西也很熟悉，怎么知道的呢？通过接触、了解。为什么在这一章里一开始他就讲这个事呢？要落到下面这八个字上。“其出弥远，其知弥少。”“弥”就是越来越，有的人走的地方越多，见得越多，不懂得甄别，不懂得筛选，不懂得提炼概括，“乱花渐欲迷人眼”，出得越远，反而了解到的真知越少，进步越少，为什么？不懂得反观自省，不懂得人心像一面镜子，如果你这个镜子是被灰尘蒙蔽的，你见得越多，其实反而获得的真知越少。这八个字在强调什么？我们要反观自省，要自我修行，自我修养，从哲学上说，从那些感性认识要上升到一种理性认识，达到对事物本质和规律的认识。所以你看，天下、天道代表着对事物全面的、本质的、规律性的认识，这个规律性的认识，需要我们安静地学习，在家里边读古往今来的著作，这不也是“不出户”嘛，也是“不窥牖”！我们了解这些间接的经验，从前人那里得到根本性的、全面的、通过理论阐释的这些知识，我们才能更了解事物的本质，更了解事物的规律。所以不要只把希望寄托在我们出去跑一跑，看一看，以为这样我们的知识就会越来越深刻，很多事情其实要通过理性的思维，这样我们才能进入到对事物本质和规律的认识，“其出弥远，其知弥少”。如果从中国的文化的角度来进一步理解的话，它还探讨一个什么问题、强调一个什么问题呢？就是人的品德。“大道之行，以心之知。”就是我们的心，我们的自我的内在的精神世界，这是道的重要的方面。所以很多人认为知识就是智慧，知识就是品德。不是的，很多人知识很多，不一定有智慧，知识多也不一定有境界、有品德。所以《道德经》强调的根本的“知”，从前面的比较中，相对于我们的感官而言，是人的理性的思维，理性认识、智慧，相对于外面的世界而言，它又是人的道德品德、人的品德。明朝的时候，关学的代表人物冯从吾先生讲过的一句话，我觉得冯从吾先生的这句话就非常能够解释这个道理，冯先生认为，古往今来的大学问都不出乎三句话：“做个好人，存点好心，行些好事。”做个好人，心正，身安，魂梦稳；行些好事，天知，地鉴，鬼神钦。所以一个人内心的品德、境界，通过自我的反省，自我的修养，达到了一个更高的水平，返璞归真，“归根曰静”，这些也是通过内在的自我修养来达到的。所以《道德经》认为人的理性认识，人这样的内心、这样的根本，它可以通过“不出户”、“不窥牖”，也可以自我修养，自我认知，不断地进步以达到。“是以圣人不行而知，不见而明，不为而成。”“是以圣人不行而知”，“是以”，“是”就是这样，“以”就是用，“是”可以解释为所以。“圣人”，好的统治者、领导者，在《道德经》称其为圣人。这些圣人，好的领导者、统治者要经常反躬自省，要经常内心关照，提高自己对大道和规律的认知水平。“不行而知”，不用到处跑，这一点也是可以得到的。“不见而明”，不用亲自去看，也能够明了道理，明了了这个道理，那就内心清净、无欲。“不为而成”，“不为”就是无为，就是按照大道的方式自然而然地去做，而不去妄为，这样一切都会顺理成章。这是我们第四十七章里边讲的内容，字虽然不多，但道理需要我们认真体会，“不出户，知天下；不窥牖，见天道。其出弥远，其知弥少。是以圣人不行而知，不见而明，不为而成。”当然对这一章的更进一步的理解需要我们和第四十八章，也就是我后面要讲的这一章相互参照，我们对这个理解才会更深刻、更准确。一开始就给大家说第四十七章、第四十八章我们要合起来，相互参照，为什么？这两章的内容讲的是非常吻合的，事实上也应该是一章的内容。第四十七章里边讲，“其出弥远，其知弥少”，第四十八章一开头就讲：“为学日益，为道日损。损之又损，以至于无为，无为而无不为。”这八个字一下子和上边的内容就衔接起来，为什么跑得越远反而知道的越少，这是站在道的角度来讲的。“为学”，在学知识，学到的知识内容越来越多。当然从学知识的角度来讲，这是非常有益的，不断地增多，可是我们获得很多的东西，见到了很多的东西，其实对我们了解根本性的规律和本质，了解大道并没有好处。站在一个更高的层次理解，就是说我们“为学”，讲究的是越多越好，见得多，看得多，见多识广。但是“为道”讲究的是什么呢？讲究的是内心的修行，讲究的是减少，用我们前面讲的话来讲，为学做的是加法，为道做的是减法，减少我们内心的欲念，减少我们的贪念，减少我们对很多问题的一种受了外界的影响而导致的内心的纷扰、困惑、迷乱，把这些东西损之又损，一点一点地把它减少，就像那镜子的灰尘一点点擦掉一样，“损之又损，以至于无为。”“无为”就是自然而为，把欲望减少，减少再减少，就达到了一种“无为”的境界，没那么多的贪念，没那么多的纷扰。我们用镜子来照这个天下，来照事物，万物进入到镜子里边，呈现出它本来的面貌。我们了解了事物的本质规律，了解了大道按照它来做，“无为而无不为”达到的是“无不为”的效果。所以在这儿借着这个机会，我再说一下道家自然无为的具体的含义：第一，不妄为；第十六章里边就讲，“不知常，妄作，凶。”你不了解事物的规律、规则，瞎折腾、胡折腾，那结果是非常糟糕的。我们“损之又损”，减少了这些遮挡着我们的认识，遮挡了我们的心窍的这些外在的事物、灰尘、迷乱，我们就照见了事物的本质和规律，我们就“不妄为”。第二，不多为；抓住关键，举重若轻，静观，看到事物的本质，找到解决问题的正确的方法，抓住关键，举重若轻。第三，有所不为；人要想有所为，必须有所不为，要想有所得，必须有所舍。我们舍弃了那些阻碍了我们正确行动、阻碍我们沿着大道行走的那些纷纷扰扰，这样能达到一个无不为的效果，也就是覆盖面广，效果更好，“无为而无不为”。下面这一段就讲，按照“无为”的方式来理解天下万事万物。“取天下常以无事，及其有事，不足以取天下。”“取天下”的规则是什么呢？“无事”。“无事”就是不多事，不干涉，不扰民，这样一切就自然而然顺理成章。所以第五十七章里边讲的这个事情就比较明确，“我无事而民自富，我无为而民自化”。“及其有事”，如果老是多事，老是妄为，不懂得事物的规律、规则，瞎折腾、胡折腾，这就是“及其有事”。则“不足以取天下”，那就不能够获得天下。得到的天下也得失去，因为它违背了大道。</t>
-  </si>
-  <si>
-    <t>第四十八章（48）</t>
-  </si>
-  <si>
-    <t>为学日益，为道日损。损之又损，以至于无为，无为而无不为。取天下常以无事，及其有事，不足以取天下。</t>
-  </si>
-  <si>
-    <t>为学（学习知识）是一天一天地增加知识，为道是一天一天地减少私欲（内心修行）。减少又减少，以致达到自然而为的境界。“无为”就能达到“无不为”的效果（做成一切事）。治理天下要常常不多事不扰民，如果妄为滋扰，就无法治理好天下。</t>
-  </si>
-  <si>
-    <t>由于四十七、四十八这两章的内容非常相吻合、相近，所以我们合到一起作为一章来讲解。四十七章讲的是一个什么事儿呢？是说人的感性认识，从哲学上说就是我们的感官接触客观世界，有时候接触得多了，它反而会造成一种迷乱和混乱，要通过人的智慧、理性认识，这样我们才能了解事物的规律，也就是这一章里边所说的“天道”。在这个基础上，我们一句句来解释。“不出户，知天下。”“户”就是门户，也就是大门。我不用走出家门，不用去外边到处跑，也能了解天下的大事。为什么？因为道家认为，天下大道归根到底，融于人的内心。内心里边有道，也就了解了天下的正道，了解了天下的大事。“不窥牖，见天道。”“窥”，从小孔里看；“牖”，就是窗户。我不用通过窗户去看，也知道天地之间日月星辰运行的规律。所以你看这个地方，“出户”是行走，出行，行万里路；“窥牖”是眼睛看，用感官接触客观世界，我不用这样。所以这个地方大家就感觉到，直观的一开始看，就觉得老子这个人有点轻视感性认识，人得通过实践嘛，人得通过感官接触客观世界，才能产生对客观世界的认识。是不是老子把这些东西全部都否认了呢？不是的。因为大家从书里已经看得非常的清楚，《道德经》举了很多生活中的例子，比如说“治大国若烹小鲜”，比如说“凿户牖以为室”，比如“说三十辐共一毂”，前面讲过的，这不都是生活中的例证吗？他对这个东西也很熟悉，怎么知道的呢？通过接触、了解。为什么在这一章里一开始他就讲这个事呢？要落到下面这八个字上。“其出弥远，其知弥少。”“弥”就是越来越，有的人走的地方越多，见得越多，不懂得甄别，不懂得筛选，不懂得提炼概括，“乱花渐欲迷人眼”，出得越远，反而了解到的真知越少，进步越少，为什么？不懂得反观自省，不懂得人心像一面镜子，如果你这个镜子是被灰尘蒙蔽的，你见得越多，其实反而获得的真知越少。这八个字在强调什么？我们要反观自省，要自我修行，自我修养，从哲学上说，从那些感性认识要上升到一种理性认识，达到对事物本质和规律的认识。所以你看，天下、天道代表着对事物全面的、本质的、规律性的认识，这个规律性的认识，需要我们安静地学习，在家里边读古往今来的著作，这不也是“不出户”嘛，也是“不窥牖”！我们了解这些间接的经验，从前人那里得到根本性的、全面的、通过理论阐释的这些知识，我们才能更了解事物的本质，更了解事物的规律。所以不要只把希望寄托在我们出去跑一跑，看一看，以为这样我们的知识就会越来越深刻，很多事情其实要通过理性的思维，这样我们才能进入到对事物本质和规律的认识，“其出弥远，其知弥少”。如果从中国的文化的角度来进一步理解的话，它还探讨一个什么问题、强调一个什么问题呢？就是人的品德。“大道之行，以心之知。”就是我们的心，我们的自我的内在的精神世界，这是道的重要的方面。所以很多人认为知识就是智慧，知识就是品德。不是的，很多人知识很多，不一定有智慧，知识多也不一定有境界、有品德。所以《道德经》强调的根本的“知”，从前面的比较中，相对于我们的感官而言，是人的理性的思维，理性认识、智慧，相对于外面的世界而言，它又是人的道德品德、人的品德。明朝的时候，关学的代表人物冯从吾先生讲过的一句话，我觉得冯从吾先生的这句话就非常能够解释这个道理，冯先生认为，古往今来的大学问都不出乎三句话：“做个好人，存点好心，行些好事。”做个好人，心正，身安，魂梦稳；行些好事，天知，地鉴，鬼神钦。所以一个人内心的品德、境界，通过自我的反省，自我的修养，达到了一个更高的水平，返璞归真，“归根曰静”，这些也是通过内在的自我修养来达到的。所以《道德经》认为人的理性认识，人这样的内心、这样的根本，它可以通过“不出户”、“不窥牖”，也可以自我修养，自我认知，不断地进步以达到。“是以圣人不行而知，不见而明，不为而成。”“是以圣人不行而知”，“是以”，“是”就是这样，“以”就是用，“是”可以解释为所以。“圣人”，好的统治者、领导者，在《道德经》称其为圣人。这些圣人，好的领导者、统治者要经常反躬自省，要经常内心关照，提高自己对大道和规律的认知水平。“不行而知”，不用到处跑，这一点也是可以得到的。“不见而明”，不用亲自去看，也能够明了道理，明了了这个道理，那就内心清净、无欲。“不为而成”，“不为”就是无为，就是按照大道的方式自然而然地去做，而不去妄为，这样一切都会顺理成章。这是我们第四十七章里边讲的内容，字虽然不多，但道理需要我们认真体会，“不出户，知天下；不窥牖，见天道。其出弥远，其知弥少。是以圣人不行而知，不见而明，不为而成。”当然对这一章的更进一步的理解需要我们和第四十八章，也就是我后面要讲的这一章相互参照，我们对这个理解才会更深刻、更准确。一开始就给大家说第四十七章、第四十八章我们要合起来，相互参照，为什么？这两章的内容讲的是非常吻合的，事实上也应该是一章的内容。第四十七章里边讲，“其出弥远，其知弥少”，第四十八章一开头就讲：“为学日益，为道日损。损之又损，以至于无为，无为而无不为。”这八个字一下子和上边的内容就衔接起来，为什么跑得越远反而知道的越少，这是站在道的角度来讲的。“为学”，在学知识，学到的知识内容越来越多。当然从学知识的角度来讲，这是非常有益的，不断地增多，可是我们获得很多的东西，见到了很多的东西，其实对我们了解根本性的规律和本质，了解大道并没有好处。站在一个更高的层次理解，就是说我们“为学”，讲究的是越多越好，见得多，看得多，见多识广。但是“为道”讲究的是什么呢？讲究的是内心的修行，讲究的是减少，用我们前面讲的话来讲，为学做的是加法，为道做的是减法，减少我们内心的欲念，减少我们的贪念，减少我们对很多问题的一种受了外界的影响而导致的内心的纷扰、困惑、迷乱，把这些东西损之又损，一点一点地把它减少，就像那镜子的灰尘一点点擦掉一样，“损之又损，以至于无为。”“无为”就是自然而为，把欲望减少，减少再减少，就达到了一种“无为”的境界，没那么多的贪念，没那么多的纷扰。我们用镜子来照这个天下，来照事物，万物进入到镜子里边，呈现出它本来的面貌。我们了解了事物的本质规律，了解了大道按照它来做，“无为而无不为”达到的是“无不为”的效果。所以在这儿借着这个机会，我再说一下道家自然无为的具体的含义：第一，不妄为；第十六章里边就讲，“不知常，妄作，凶。”你不了解事物的规律、规则，瞎折腾、胡折腾，那结果是非常糟糕的。我们“损之又损”，减少了这些遮挡着我们的认识，遮挡了我们的心窍的这些外在的事物、灰尘、迷乱，我们就照见了事物的本质和规律，我们就“不妄为”。第二，不多为；抓住关键，举重若轻，静观，看到事物的本质，找到解决问题的正确的方法，抓住关键，举重若轻。第三，有所不为；人要想有所为，必须有所不为，要想有所得，必须有所舍。我们舍弃了那些阻碍了我们正确行动、阻碍我们沿着大道行走的那些纷纷扰扰，这样能达到一个无不为的效果，也就是覆盖面广，效果更好，“无为而无不为”。下面这一段就讲，按照“无为”的方式来理解天下万事万物。“取天下常以无事，及其有事，不足以取天下。”“取天下”的规则是什么呢？“无事”。“无事”就是不多事，不干涉，不扰民，这样一切就自然而然顺理成章。所以第五十七章里边讲的这个事情就比较明确，“我无事而民自富，我无为而民自化”。“及其有事”，如果老是多事，老是妄为，不懂得事物的规律、规则，瞎折腾、胡折腾，这就是“及其有事”。则“不足以取天下”，那就不能够获得天下。得到的天下也得失去，因为它违背了大道。</t>
-  </si>
-  <si>
-    <t>第四十九章（49）</t>
-  </si>
-  <si>
-    <t>圣人无常心，以百姓心为心。善者，吾善之；不善者，吾亦善之，德善。信者，吾信之；不信者，吾亦信之，德信。圣人在天下歙（xī）歙，为天下浑其心。百姓皆注其耳目，圣人皆孩之。</t>
-  </si>
-  <si>
-    <t>圣人不要有固执不变的思想，而是把百姓的思想当作自己的思想。。善良的百姓我善待他们，不善良的百姓我也善待他们，结果就会使他也变得善良；讲诚信的人我以诚信对待他们，不讲诚信的人我也以诚信对待他们，结果就会使他也变得诚信。圣人领导天下 收敛自己的私欲，使天下百姓的心灵都变得淳朴。百姓都只关注耳听眼见的事，而圣人要使他们都变得像无知无欲的婴儿一样。</t>
-  </si>
-  <si>
-    <t>【圣人要换位思考 将心比心】第四十九章是《道德经》里边比较重要的一章，因为这里边有一句话大家都很熟悉，我们领导者讲话的时候也经常引用，就是以“百姓心为心”。从前面讲的内容，大家会知道这是一个通过换位思考，得出来这样的一种结论。这一章开头这句话我们先说一下。“圣人无常心，以百姓心为心。”是说一个好的领导者、统治者，不要老固执己见。“常心”就是固定的心思，自我的执着，不要老固执己见，不要老把自己的意志强加给别人，乃至强加给人民。应该怎么样呢？换位思考，将心比心，“以百姓心为心”，倾听民众的呼声，关注民众的利益，吸取民众的智慧，这都是“以百姓心为心”的表现。我们先体会一下这一章的宗旨在讲什么？其实这个道理就是讲了，换位思考，将心比心。百姓善良，我也对他善良；不善良，我也对他善良；信任我的，我信任他；不信任我的，我也信任他。干吗呢？这样我就能让人向善，让大家讲诚信。最后这一段就说一个好的领导者、统治者，让百姓都回归到他本来的这种生活，关注的是自己的生活中的事情。不要想那么多，不要心思混乱，不要烦乱，这样才能够形成一种良好的和谐的状态。这是老子的想法。我们一句一句来解释。“圣人无常心”，我再重申一遍，“圣”的繁体字，上面是个耳和口——聖，这两个字并列就代表着通达事理，下面是个王，也就是说一个好的领导者、领导人称其为“圣”。在这一章里体现得最为明显。“圣人无常心”，有的本子也叫“常无心”，意思都是一样的，就是不固执己见，没有自己僵化固定的思维，懂得换位思考。其实关于这个意思，我们通过前面讲过的第二十二章参照着理解，就比较容易了。我在前面多次说过，读《道德经》最好的方法就是不看注解，以经解经，相互参照，明白它要讲的真正的含义，谁的解读也不如他本人对这个东西的解释更符合他的本意。第二十二章里边就讲“不自是”“不自见”“不自矜”“不自伐”这“四不”。“不自是，故彰。不自伐，故有功。不自矜，故长。”这样我们才能不断成长，不断进步。一个好的领导人也是这样的，领导者、统治者，也应该“四不”，也就是“无常心”。你没有这样的智慧，老是固执己见，老是自我吹嘘，老是自我夸耀，老是觉得自己了不起，那你就没办法换位思考，将心比心了。所以“无常心”才能以百姓之心为心，倾听民众的呼声，吸取民众的智慧，关注民众的利益。沿着这个思路下面也好理解了。“善者，吾善之；不善者，吾亦善之，德善。”善良的人我用善良去对待他，不善良的人，我也用善良的方式去对待他，干嘛呀？教化、感化，这样我就得到了真正的善良。为什么呢？你这样做，起代表带头作用，大家也就人心向善了。大家注意这个“德”，王弼的解释非常明确，“德者，得也”，这样做就得到了这个天下、这个社会，这个国家就会人心向善。“信者，吾信之；不信者，吾亦信之，德信。”信我的人，我相信他，我跟他讲诚信；不相信我的人，我也相信他，跟他讲诚信。干嘛呀？这样天下人就会觉得诚信可贵，也就往诚信的方向去努力去发展了——“德信”。“圣人在天下歙歙”，“歙”就是合，就是收敛。你说圣人怎么样领导、管理这个天下呢？先要收敛自己的欲望，要想领导好别人，你先领导好自己，要想领导好自己，你先领导好自己的情绪，领导好自己的欲念，上梁不正则下梁歪嘛。“歙歙”，收敛自己的欲望，减少自己的欲念。“为天下浑其心”，让这个天下都怎么样呢？大家都没那么精明。不总是为了什么事都去争，“浑其心”，都那么样地浑厚、淳朴、厚道，关心自己的现实生活，而不是那么多纷乱的思维，那么多胡乱的想法，那么多的技巧、智谋、套路、心眼，用这种方式让大家和谐相处。“圣人皆孩之”，一个好的领导者把天下人都当作儿童，当作自己的孩子，一方面对他们非常关爱，另一方面也不要让百姓人心混乱，都像孩童一样纯净、淳朴。当然了，后边这一段大家也看得出来，这也是老子的一厢情愿。他希望统治者减少自己的欲望，天下人跟着也减少自己的欲望，关注自己的现实的生活，没有那么多的争斗、心眼、套路、技巧、欺骗、欺诈。这是老子生活的理想状态，也是他认为是和谐世界的前景，我们权当这也是他的一种理念和希望，毕竟这个社会的和谐也是我们的一种希望。只是他这种方法大家要辩证对待，大概用这种方法实现天下的太平，也只能是一种理想和理念，很难真正得以实现。但这一章里边大家要注意，开头这句话，我们要熟记，因为在我们国家的领导人的很多讲话里边都能看到这句话的出现，“以百姓心为心”，这是道家思想里边非常重要的一句话，让我们感觉到老子这个人在他冷静的、甚至有点冷酷的外表之下，内心涌动的热流，对于天下人的关注，对于天下人的关爱。这一章的原文我们解释完了，再强调一下这章的逻辑和重点，这章里边的关键在哪呢？这一章里边的关键是讲“圣人”和“百姓”，他们是国家不同层面的人，这一章讲究什么呢？讲究各安其位，各循其理。老子对这些做统治者的讲，你们要“以百姓之心为心”，善良的人呢你要好好地对待，不善良的人呢你也要好好对待，这样你才能得到这个国家人心向善的风气。信你的人你要讲诚信，不信你的人你也要讲诚信，这样才能得到天下诚信的风气。“圣人在天下”，圣人在上，领导天下。应该怎么样呢？怎么样叫循理循道呢？应该清静，无为，少折腾，少多事儿，这是上边的理，给他们讲的，你应该这样做，收敛自己的欲望，减少自己的奢靡、奢华，“清静为天下正”，这是对他们。对下边怎么讲呢？你这个在上边的人应该让下边遵循一个什么样的道理呢？“为天下浑其心”，让这个百姓浑厚，淳朴，宁静，没有那么多纷乱的想法，那么多技巧、心眼、套路、欺诈、欺骗，按照这个方向，百姓都关注自己现实的生活，把自己的日子过好，少管别的事儿，你让百姓能够做到这一点，上边的管上边的事，循上边之理，下边的循下边之理，这天下不就和谐了嘛。大家看出来了吧，“圣人皆孩之”，好的领导，一个国家的领导者，让这国家的百姓都像小孩一样，纯净、淳朴，没有那么多的欺瞒欺诈。上按上边的道理，下按下边的道理，这不就形成了一个和谐的状态了嘛。我们知道，真正的和谐是有差别的统一，大家都应该有表达自己的意见的机会，表达自己观点的机会，“各美其美，美人之美”，有差别的统一。但是老子这个地方讲的道理不是这样的，他讲的是“圣人无常心”，你要考虑到百姓，百姓在圣人的领导下应该怎么做呢？应该浑厚淳朴，没有那么多的智谋、欺诈、心眼，关注自己的现实生活，干好自己的事情，像儿童一样，纯净、干净、宁静，形成这个社会的和谐状态。所以我们只能说，老子这个想法呀追求一种和谐的目标，但是这个所用的方法在我们看来，这还是有很多地方值得检讨的，因为真的把百姓都变成小孩，还是不免有一点愚民政策的感觉。这一点大家还是要正确地理解。</t>
-  </si>
-  <si>
-    <t>第五十章（50）</t>
-  </si>
-  <si>
-    <t>出生入死。生之徒十有三，死之徒十有三。人之生，动之死地，亦十有三。夫何故？以其生生之厚。盖闻善摄生者，陆行不遇兕（sì）虎，入军不被甲兵。兕（sì）无所投其角，虎无所措其爪，兵无所容其刃。夫何故？以其无死地。</t>
-  </si>
-  <si>
-    <t>人生就是从出生到死亡的历程。长寿的人占十分之三，短命的人占十分之三，本可以长寿但妄为把自己置于死地的人也占十分之三。为什么？因为他们过分地追求奉养自己以求生。听说善于养生的人，在陆地上行走不会遇到犀牛和猛虎的伤害，在战场上不会被兵器所伤。犀牛的角无处可用，老虎的爪也没了用处，兵器的刃也用不上。为什么？因为他不把自己置于死地。</t>
-  </si>
-  <si>
-    <t>【养生之道 —— 不要作死】我们来讲第五十章，这一章表面上在讲养生之道，也就是文章所说的“摄生”，实际上表达的是更为深刻的道理。我们看书、看电视剧的时候，会发现有那么一些大师、大医生，一些位重权高的人向他们请教养生之道，“我怎么样能活得更加长寿？”这些医生、养生大师啊，大都是告诉他们要清心寡欲，不要奢靡奢华，不要胡吃海塞，其实这就是道家对于养生这事儿往更高的一个层次所要修养的内容，我们也可以把它概括为道家的生死观。道家认为养生跟生死密切关联。养生要顺应自然，要自然而然，要掌握规律、规则。你看我们读《庄子·养生主》里边的“庖丁解牛”，讲的不就是这个道理吗？目无全牛，游刃有余！这牛解得跟跳舞一样，跟音乐一样。所以文惠君最后就对这个庖丁讲：“吾闻庖丁之言，得养生焉。”养生要顺应自然规律，自然而然，自然而为。“生之徒十有三，死之徒十有三。”然后老子做分析，如果把天下的人分做十成，那么有十分之三的人是“生之徒”，也就是长寿的，还有十分之三的人是“死之徒”，是短命的。还有十分之三的人是怎么样的呢？“人之生，动之死地，亦十有三。”这些人本来可以长寿，最后由于自己的胡为、妄为、折腾，就把自己置于死地了。所以你看它的分类很有趣，十成的人中，三分之一的人应该是长寿的，三分之一的人本身体质各方面就是短寿的，还有三分之一的人本来可以长寿，但是妄动、胡为而置于死地。为什么会这样？《道德经》给了我们这样一句话：“以其生生之厚。”生，养生，或者可以解释得更明确，叫“求生”。太着急了，太迫切了，老想延长自己的性命，老害怕自己的营养不够，最后营养过剩了，反而把自己置于一个另外的相反的方向。当下一些有智慧的医生就提醒，我们现在不是营养不良，而是营养过剩，“生生之厚”。当然《道德经》讲的这句话只针对当时的统治者、位高权重的人而言，老是生活得这样奢靡奢华，“五色令人目盲，五音令人耳聋，五味令人口爽，驰骋畋猎，令人心发狂……”老是这样，还以为是让自己生命不亏，活得不亏。求生之厚，太急、太迫切，营养过剩，自己本来可以长寿，反而被置于成“死之徒”了，到短寿的那一拨去了。所以下面老子就讲了：“盖闻善摄生者”，听说这善于养生的人是什么样子呢？他们用了下边一段形容：“陆行不遇兕虎，入军不被甲兵。兕无所投其角，虎无所措其爪，兵无所容其刃。”习惯上我们以为“兕”是犀牛，或者有的叫母犀牛，其实这两种动物还不一样。这个“兕”是古代的一种瑞兽，比较凶猛，所以在古代的文字中，经常用这个“兕虎熊”比喻凶险之地。懂得养生的人，懂得正确对待自己生命的人，不去冒这个险。陆行的时候，尽量不碰这些凶猛的动物，如果你碰上它了，那你就没办法了，谁让你冒那个险呢？明知道野生动物园人家不让下车，你非得下车，遇到老虎了吧。有些地方人家告诉这个规则，这里边有危险，你偏不听，明知山有虎，偏向虎山行，明知山有狼，偏要做狼餐，这不就是“人之生，动之死地”吗？“入军不被甲兵”，上阵打仗的时候不为兵器所伤。为什么呢？“兕无所投其角”，你不遇到这个兕，那当然它那个凶猛的角就没有办法发挥它的作用了，没有办法针对你。一般我们画“兕”的时候都习惯把它画成独角兽。“兕”最有名的代表就是太上老君骑的那个板角青牛了，角非常锋利，尖锐，杀伤力强，你不遇到它，尽量别碰到，别把自己置于危险的境地，它的角当然就无所用了。“虎无所措其爪”，你不往虎山行，不遇到它，提前准备好避免这种凶险，老虎爪子再尖利，牙齿再锋利，它也无法对你发挥作用。“兵无所容其刃”，上阵不为甲兵所伤，尖锐的兵器，也没有办法发挥它的作用。“夫何故？”为什么会这样？“以其无死地”，不把自己置于死地，这样也就不会让自己的生命受到戕害。这是就是五十章。这一章体现了道家的养生之道：简单地说就是不要“作死”，自己不要找死，本来可以长寿的，自己作死把自己置于死地。很多人非得触犯法律的界限，甚至因此送掉了自己的生命，这不就是把自己置于死地嘛！所以我们说“NoZuoNoDie”，不作不死。从养生的角度来讲，你看道家讲的顺应自然，不单只是生活中的清心寡欲，而且还指不触犯边界底线，不触犯红线，知足不辱，知止不殆，不置身于死地，不让自己冒这种凶险，这也是道家养生之道里边的一个重要的内容，而且是更接近于哲学层面的、更有智慧的内容。那么这一段我们讲完了之后，我还要跟大家强调一下，道家的养生观，其实也是道家的生命观。道家对于生命的看法讲究的是自然而然，意思是什么呢？过于求生，过于厌恶死，这都不是一种自然而然的智慧，因为死亡本身就是生命的一部分，人自然而生，自然而死，真的到了生命结束的时候，那也应该开朗地、乐观地对待。这一点在道家的继承者那里，也就是道家的第二号人物庄子那里，讲得非常的明确——“之所以善吾生者，乃所以善吾死”。我们很好地对待自己的生命，不把自己的生命主动地置于死地，不求生之厚，真的面临死亡的时候，也应该把它好好地对待。自然而生，自然而亡，这是生命的自然而然的规律，谁也阻挡不了。第五十章，老子借养生之道讲了一个更重要的道理：有的人求生太急迫，太厌恶死亡，太害怕死亡，越是求生之厚，服了大量的药，用各种各样的营养的方式，推开死亡，想要避免，没想到越想避免的反而来得越快。所以，道家讲究自然而然的思想，这有着重要、杰出的意义。我们做个小小的梳理。第五十章，我们从开始讲的时候就给大家讲过，这一章可以分成两段，一段是讲有的人本来可以长寿，却进入了短命的行列，是因为“求生之厚”，太急迫、营养过剩导致的，另外一个是由于妄为、“作”，把自己置于死地的。怎样才能避免这两点呢？还是道家的这种思想，顺其自然，清心寡欲，清静为天下正。正确地对待生命和死亡，不把死亡当作是完全可以避免的事情，真的面临死亡的时候，也能够开朗地、乐观地对待。</t>
-  </si>
-  <si>
-    <t>第五十一章（51）</t>
-  </si>
-  <si>
-    <t>道生之，德畜（xù）之，物形之，势成之。是以万物莫不尊道而贵德。道之尊，德之贵，夫莫之命而常自然。故道生之，德畜之：长之育之、亭之毒之、养之覆之。生而不有，为而不恃，长而不宰，是谓玄德。</t>
-  </si>
-  <si>
-    <t>道生成万物，德蓄养万物，万物有了具体的形状，周围的环境使万物得以成长。因此万物没有不尊崇道和重视德的。道受到尊崇，德受到重视，并没有人如此命令 而是万物本身自然而然地永远去这样做。所以道生成万物，德蓄养万物：使万物成长作育，使万物成长成熟，使万物得到养覆保护。道、德养育了万物却不据为己有，帮助了万物却不求它们的回报，成就了万物却不做它们的主宰者，这可以说是最高尚的品德。</t>
-  </si>
-  <si>
-    <t>第五十一章逐句地来解释一下。“道生之”，“生”，创造，生养。道创造了万事万物。“德畜之”，德畜养了万事万物。“物形之”，万事万物有了具体的形状。“势成之”，周围的环境使它得以成长。正因为如此，所以“万物莫不尊道而贵德”，以道为尊，以德为贵。“道之尊，德之贵，夫莫之命而常自然。”尊道贵德，那自然会得到一个良好的结局和结果，这不是命，这就是自然而然的规律、规则。“故道生之，德畜之。”所以道生养万物，德蓄养万事万物。“长之、育之”，使它成长，使它不断地培育长大。“亭之、毒之”，这个“亭”呢，其实也好理解，我们常说亭亭玉立，这个“亭”就是成长的意思。这个“毒”就是成熟的意思，使万事万物成长，使其成熟。“养之、覆之”，“养”和“覆”都是保护的意思。养育万物，保护万物。“生而不有，为而不恃，长而不宰。”生养了万事万物，却不把它当作私有的产品，对万事万物有作为，却不把这个当作一种倚仗、凭借，甚至勒索的手段，对万事万物有这么大的功德，却不是以主宰者的身份出现。这个就是“玄德”，这就是最高深的、最深刻的智慧与品德。这是我们对这一段的直观的解释。其实，这一段的深意远不止于此。因为中国人讲哲学讲究“知行合一”，讲道的品性，其实也是为了人向道的品性去学习，按照道去做，这个也就是“德”。所以第五十一章里边讲道养育万物，德蓄养万物，也是人应该效法学习的。在这个层面上，我们深入地理解这一段话。“道生之，德畜之”，道创造了万事万物，但是它不把万事万物作为一种私有产品，并不是以一种主宰者的身份，以求其回报。由此我们可以看到，老子给我们提供了想要做成一件事的四个核心的要素和条件，也就是一种应有的程序和原则。第一个，要有道，因为道是创造万事万物的本源，所以我们要坚守大道，按大道的方式来创造。第二个，“德畜之”，“畜”就是积累的意思。在有道的基础上，我们要不断地、坚定地按照道去做，也就是“积德”。德就像水一样，我们就像一条船一样，我们积累的水越多，我们这条船在水上才能够航行得更自由。所以朱熹有一首诗说：“昨夜江边春水生，艨艟巨舰一毛轻。向来枉费推移力，此日中流自在行。”昨天江边涨水了，平常推也推不动的大船，现在根本不用推了，水多了，自然而然地就航行更加自由。他讲的是读书的积累达到一种自由的境界，其实人生又何尝不是如此呢？我们积累的德多了，按照道做事，更坚定、坚持、持久，那也就给我们人生提供了更广阔的空间与平台，不断地积德，我们的行为也就更加自由，我们的行为也就更加能够符合大道。庄子在《逍遥游》里面也讲了这样一句话，“且夫水之积也不厚，则其负大舟也无力”。水积累不多的时候，大船是浮不起来的，只要积累得多了，结果就是自然而然的事情，和朱熹所讲的道理不谋而合。第三个，“物形之”。人有道有德，是不是就可以把事情做成了呢？不够的，还需要一定的物质条件和手段，巧妇也难为无米之炊。有条件要上，没有条件我们创造条件，这样才能把事情向更成功的方向去发展。道、德、物三个条件总够了吧？不够的。要想把事情真正做成，还有一个很重要的条件，就是“势”，“势成之”。道家讲的无为，更强调的是顺势而为，掌握这个形势，了解大势，这样才能把事情做成。《淮南子》中举过这样的一个例子，大禹为什么能把水治成呢？顺水势而为。商汤周武为什么能夺得天下呢？顺民心而为。民心所向，就是历史发展的大势与潮流。所以大家在第二个层面把这四个字提炼出来，它是一个很好的成功学的例证，我觉得比现在讲的一些所谓的零零散散的成功学，不知道要深刻多少倍。道、德、物、势，“道生之，德畜之，物形之，势成之”。既然这四个要素，道和德是排在最前面的，“是以万物莫不尊道贵德”，所以万事万物没有不尊道而贵德的。人更是如此，有道有德，后边的事情才能继续发展，所以“道之尊，德之贵，夫莫之命而常自然”，这不是命，这就是一个永恒的自然而然的规律、规则。你按照道，按照德，尊道而贵德，会得到一个自然而然的良好的结局和结果，这是自然而然的事情。这不是命，这就是自然而然的规律和规则。所以大家注意，我们中国的这些经典，比如说《易经》，比如说《道德经》，都不是用来算卦占卜的，它就讲一个重要的内容：按照规律、规则来做，结果水到渠成、自然而然。下面这一段是对上面做的一个延伸。“道生之，德畜之”，道和德，生养万物，为万物提供条件，让它生长发展。“长之、育之”，培育万事万物使其生长、发展。“亭之、毒之”，使它成长、成熟。“养之、覆之”，不仅如此，还要养护万物，覆盖万物。道和德让万物长大，培育万物的成长，使它成熟又予以保护，功德可谓无量。孔子有一段名言：子曰：“予欲无言。”子贡曰：“子如不言，则小子何述焉？”子曰：“天何言哉？四时行焉，百物生焉，天何言哉？”这段话的直译是：孔子说：“我现在只想沉默。”子贡说：“如果你不说出心里想什么，那么我们这些学生还拿什么去记述呢？”孔子说：“自然说过些什么？不过放纵四季周而复始，任由百物蓬勃生长。自然你又何曾告诉别人什么啊？”很多人把这段话中的“天”翻译成神灵，这是不对的。其实这个“天”指的是大自然，也就是《道德经》里的天地，天地无语而泽被苍生万物，确又无语不居功自傲，不把自己当做万物主宰。这不也是《道德经》第五十一章的核心吗？培育万物的成长，使它成熟又予以保护，功德可谓无量。其实，在这样的智慧层面，孔子和老子的见解都是一样，“生而不有，为而不恃，长而不宰，是谓玄德”。关于这段重要的话，我们在第十章已经详细说过，不再重复。</t>
-  </si>
-  <si>
-    <t>第五十二章（52）</t>
-  </si>
-  <si>
-    <t>天下有始，以为天下母。既得其母，以知其子；既知其子，复守其母，没（mò）身不殆。塞（sè）其兑（duì），闭其门，终身不勤。开其兑，济其事，终身不救。见小曰明，守柔曰强。用其光，复归其明，无遗身殃，是为习常。</t>
-  </si>
-  <si>
-    <t>天下万事万物都有本源（即道），可以把这个本源作为万物的母亲。认识了作为万物之母的道，就能认知万物；认知了万物，就能坚守作为万物之母的道。这样终身都没有危险。塞上欲望的孔穴，闭上欲望的门户，终身都没有忧劳。打开感官欲望的门户，增添纷繁的事件，终身都不可挽救。察见细微的事物叫“明”，坚守柔弱叫“强”。用道的光芒来了解具体事物中的规律、规则，复归到事物的光明的状态，不会给自己留下那么多的祸殃，这就叫普遍永恒的规律（可以说是掌握了大道）。</t>
-  </si>
-  <si>
-    <t>一开始我们就说过，《道德经》里边有一个非常好的“正能量”，就是每当说到高大上的、特别伟大的事情，都喜欢用母亲的“母”字来作为代替和概括，或者说用“母”来做一个形象的比喻。如果我们的孩子读这样的文字，潜意识里就会有对母亲有一种敬畏与尊重。我们在第一章里边就说到，“无，名天地之始；有，名万物之母”。在这一章里边，又出现了母亲的这个“母”的概念。“天下有始，以为天下母。”就像动物、人类都是由母亲生养的一样，万事万物也都是由道创造的。老子用“母”来比喻大道，生动形象且让人充满对道的敬畏，意思就是说，天地一开始的时候，其实大道已经就在了。“既得其母，以知其子。”我们了解了大道，就是“既得其母”。知晓了大道，那我们就“以知其子”，也就了解了儿女。这个意思是什么呢？道是万事万物的普遍规律，它永恒存在，具体的事物都拥有具体的道，也就是具体的规律。你了解了大道，就可以以此来了解万事万物的具体规律。茶有茶道，花有花道，练武有武道，下棋有棋道……了解了普遍的道，也就更能够了解这些具体事物间的规律与规则。反过来也一样，“既知其子，复守其母。”我们从具体的事物之间，比如棋道、花道、茶道，从这具体的事物之间，我们了解了大道，感知了大道，那也就能更好地坚定地坚守大道。“没身不殆”，这样地做事情永远没有危险，没有失败，为什么？以道佑之，以道护之，这样我们做事情才能没有危险，没有失败。下面就说了解大道的方式方法。大道的了解，不是靠感性来体验到的，就像我们前边说的，“为学日增，为道日损。”“不出户，知天下；不窥牖，见天道。”所以如果是跟着感觉走的话，你是了解不了真正的大道的。因此“塞其兑，闭其门，终身不勤”，不要依赖感觉，不要把我们所见所知的就当作大道，重要的要用心，也就是哲学上讲的，用理性的思维，来了解认知大道。反过来讲，“开其兑，济其事，终身不救”，如果跟着感觉走，打开我们的感官的门户，感官这个东西，它是有很大的局限的。第十二章里面就讲，“五色令人目盲，五音令人耳聋，五味令人口爽”。你只靠这个是了解不了大道的。“见小曰明，守柔曰强。”什么叫“见小”啊？“小”就是具体的事物，具体的事物里面也蕴含着规律、规则。你能够从具体事物里了解具体的道、具体的规律，这也是一种明智。“守柔曰强”，道家是讲“柔弱胜刚强”的，道家是讲“知其雄，守其雌”的，“柔”就是雌柔，不管我们多么强大，我们也懂得坚守这个柔弱，因为柔弱更能长久。力量不够的时候，我们懂得用守柔的方式、韬晦的方式，来使自己的力量不断增大、不断增强，这样才能成为真正的强大。“用其光，复归其明”，用道的光芒，“复归其明”，来了解具体事物中的规律、规则，复归到事物光明的、明智的状态，我们才能走在光明的大道上。“无遗身殃”，不会给自己留下那么多的祸殃。“是为习常”，这个“习”，不同的本子有不同的写法。习，就是普遍、永恒的意思，就是普遍的永恒的规律、规则。也有的本子用的是沿袭的“袭”，也就是遮盖的意思。《道德经》里边用这个“袭”字的意思就是说，这是被大家认识不到的、被遮盖的规律规则，了解了这一点，我们也就对事物的了解更加深入。这两个意思都通，我们这里边用的是复习的“习”，学习的“习”，也就是经常的、普遍的、永恒的意思。“是为习常”，这就是一个经常的、普遍的、永恒的规律、规则。这一章核心的内容是说，道是一个普遍的规律，它存在于天地之间，所以叫“大道”。我们了解了大道，掌握了普遍的规律、规则，再来认识具体事物中的规律、规则，这是非常有帮助的，也是非常重要的。反过来也是一样，了解了具体事物中的规律、规则，也能够让我们更加坚信大道的存在，更加了解大道的伟大。这一章以母和子为喻，大和小对照，就讲述了这样的一个哲学的道理。这样的智慧能让我们用到大道的光芒，走在光明的大道上。</t>
-  </si>
-  <si>
-    <t>第五十三章（53）</t>
-  </si>
-  <si>
-    <t>使我介然有知，行于大道，唯施（yí）是畏。大道甚夷，而民好径。朝甚除，田甚芜，仓甚虚。服文彩，带利剑，厌饮食，财货有余，是为盗滥竽（yú）。非道也哉！</t>
-  </si>
-  <si>
-    <t>假如让我稍微有些认知，行走在大道上，最害怕走到斜路上去。大道非常平坦，但一般人喜欢走捷径。（无道之君）朝政非常混乱，田园非常荒芜，仓库非常空虚。穿着华美的衣服，佩带锋利的宝剑，吃饱喝足，积存财货有余，这样的人叫做强盗头子（滥竽：强盗头子）。这种行为是不符合大道的！</t>
-  </si>
-  <si>
-    <t>讲到这里大家已经非常清楚了，老子衡量事情的最高原则就是大道。“使我介然有知”，“芥”就是小的、稍微的意思。假如让我稍微有知识、有智慧，“行于大道”，走在大道上。我最怕的是什么呢？“唯施是畏”，“施”，就是逶迤、曲折，在这里指的是邪路、歧路。走在大道上最可怕的是什么呢？就是害怕歧路太多，害怕走到邪路上去。“大道甚夷，而民好径。”其实大道是非常平坦的，但是一般人都喜欢走捷径，老想抄近道。“朝甚除”，朝政非常得混乱。“田甚芜”，田园都已经荒芜了。“仓甚虚”，仓廪实才好嘛，现在仓库里边都是空虚的。可是那些统治者在干吗呢？“服文采，带利剑。”穿着漂亮的、非常昂贵的衣服，带着珍珠宝石装饰的利剑。“厌饮食”，什么东西都吃腻了，对什么好吃的东西都已经感觉到厌烦了。“财货有余”，家里的财宝有那么多的富余。这叫什么？“是为盗夸。”《道德经》认为这个就叫“盗夸”，强盗，还夸耀自己的强盗行为。《道德经》在第七十七章里边就讲，“天之道，损有余而补不足”。现在这些人做的是什么呢？“损不足，以奉有余”。“非道也哉”，这完全不符合道的规律、规则，完全不是按照道的方式来做嘛。这一章表现了老子的平民的思想、公平的思想，指责在“朝甚除，田甚芜，仓甚虚”的情况下，那些人“服文彩，带利剑，厌饮食，财货有余”夸耀自己的强盗行为。这一章有一些字，我们还得具体地、细致地解释一下。“唯施是畏”，凭什么把这个“施”念成“迤”，解释成歧路呢？因为道弯弯曲曲的时候，歧路众多。在《列子•说符篇》里边讲的一件事——歧路亡羊。杨朱他们家的邻居羊丢了，很多人都出去找，杨朱就觉得很奇怪就问，就一只羊怎么这么多人去找啊？邻居就告诉他，歧路多，岔路太多了。找羊的人回来了，杨朱问找到了吗？邻居说没找到。又派更多的人去找，还没有找到。歧路中又有歧路，岔路中又有岔路，所以常常使人丧失了大道，迷失了大道，所以杨朱听了之后几天都不说话。古人有“歧路亡羊”，也有遇穷途而哭，走道遇到没有路了，痛哭而返，其实都是感觉到了人生道路上的一些很值得人害怕的事情。行于大道，最害怕的就是歧路、岔路，一旦走错路，方向一错，后边的一切麻烦就都来了。所以老子说“大道甚夷”，“夷”就是平坦的意思，大道其实极为平坦。“而民好径”，人却老喜欢去走这个捷径，走了捷径之后，最后发现回到正确的大道上是非常困难的。其实，很多的所谓捷径就是歧路，就是邪路，人要脚踏实地，这样才能够行走在正确的大道上。通过努力获得成功，而不要投机取巧，更不要把投机取巧里边得到的东西当作一种炫耀夸耀，这个叫什么？“盗夸，非道也哉。”</t>
-  </si>
-  <si>
-    <t>第五十四章（54）</t>
-  </si>
-  <si>
-    <t>善建者不拔，善抱者不脱，子孙以祭祀不辍。修之于身，其德乃真；修之于家，其德乃余；修之于乡，其德乃长；修之于国，其德乃丰；修之于天下，其德乃普。故以身观身，以家观家，以乡观乡，以国观国，以天下观天下。吾何以知天下然哉？以此。</t>
-  </si>
-  <si>
-    <t>善于进行精神上的建设这是不可拔除的，善于掌握道的人不会脱离道，子孙世世代代不断尊敬、学习这个原则。用这个道理来修身，他的德会是真实的；将这个道理贯彻到修家，这样他的德才能有余；用这个道理来治全乡，他的德才能不断丰富成长；用这个道理来治国，他的德才会丰盛；用这个道理来治理天下，他的德才会是普遍的（遍及全国）。所以按照修身的原则来观察个人，按照齐家的原则来观察家庭，按照治乡的原则来观照乡，按照治国的原则来观照国，按照治天下的原则来观照天下。我怎么知道天下是这样的呢（我凭什么来了解天下情况的好坏呢）？就是因为这个道理。</t>
-  </si>
-  <si>
-    <t>第五十四章由三段构成。第一段：“善建者不拔，善抱者不脱，子孙以祭祀不辍。”这一段在讲按照大道来建设，没有人能够攻击倒它，把它拔除掉。大家想，人类建设的很多的东西，有成必有毁，都是会被拔除掉的，而大自然呢，比如说山川，这是大自然建筑的东西，有的或许可以被拔除掉，但这一章讲的不是这个意思。“善建者”指的是人精神方面的建设，大道方面的建设，这个伟大的思想是不会被攻击倒、被拔除掉的。比如我们现在学的《道德经》，历经两千多年，很多人都在攻击，在否定，在嘲笑，可是这无碍于它伟大的思想，现在学的人越来越多，大家越来越从里边得到一种智慧的启迪。另外像佛祖释迦牟尼，像孔子，历史上一些伟大人物的思想，他们的思想像什么？就像夜幕中的星光，给我们在黑暗中指引方向，有的甚至像光明普照的太阳。这些思想属于“善建者”，是没有办法把它攻击倒、拔除掉的。“善抱者”是什么意思呢？直观的理解就是善于把你抱住的人，你是脱离不开他的掌控的，其实这只是望文生义的理解。在《道德经》里边多次提到“抱”字，比如说第二十二章，“抱一为天下式”；比如说第四十二章，“万物负阴而抱阳，冲气以为和”。抱的是什么？“负阴抱阳”。所以这个“善抱者”就是掌握阴阳之不测，掌握阴阳相互作用、相互变化的规律规则，而“一阴一阳之谓道”，所谓“善抱者”，也就是了解大道的人。“不脱”，脱离不开大道的掌控，脱离了大道就走到了一个危险的境界。“子孙以祭祀不辍”，一代一代，千秋万代，按照“善建者”、“善抱者”这些伟大的思想来做，对他们表示一种尊重、敬仰，不断地学习。“修之于身，其德乃真。”按照这个伟大的思想来做事、来修身，这样所得到的德，才是真实的、纯净的。“修之于家，其德乃余。”按照大道来修家，一家人遵循大道，这样获得的家的品德才是丰盈有余的，积德之家必有余庆嘛。“修之于乡，其德乃长。”拿大道来传达给一个乡，按照这个方式形成一种良好的乡风。“长”就是领导的意思。你把这个方式在乡里边普及，让大家坚定地按照道的方式来做，你才能成为这个乡的好的领导者。我们知道，在宋朝的时候，陕西“蓝田四吕”首先制定了乡约，它对我们中国良好的乡风的培育起了非常大的作用，这不就是“修之于乡，其德乃长”的具体表现嘛。“修之于国，其德乃丰。”按照这样的一个方式来治理国家，让国家按照大道去做，所收获的德才是丰盛的、伟大的。同样的道理，“修之于天下，其德乃普。”天下是天下人的天下，不是一人之天下，所以大道之行，天下为公。按照善建、善抱的大道来做，修之于天下，这样大家得到的才是普遍的，如光明之普照。这是第二段，老子在讲按照“善建”、“善抱”的原则来做，所获得的伟大的结果。“以身观身”，“观”就是观察。我们按照修身的要求，大道修身的方式来观察这个人，他修身方面是不是善建、善抱，是不是没有脱离大道。“以家观家”，按照家庭的修养的要求来观察家庭的品德、家风。当然这个“观”的时候就自然有对比的意思，和其他的家里边进行对比，相互比较，看哪一个是更能按照“善建”、“善抱”的这种符合大道的原则方式来修身、来齐家。下边也是同样的道理，“以乡观乡”，乡自有乡的要求，和家是不一样的，范围扩展了，有很多家庭。但是如果这个大道一以贯穿，都是按照对“善建”的、“善抱”的原则祭祀不辍、尊敬，敬仰，以按照这样的一种规则来作为荣耀，都为良好的家风、乡风做出贡献，这不就是道一以贯之吗？同样的道理，“以国观国”，一个国家有这个国家的精神、思想、风貌，按照大道要求来做，在和其他国家比较中，取长补短。同样的道理，“以天下观天下”。大道一以贯之，一条主线，一切顺理成章，自然而然，无往而不胜。所以最后老子说，我怎么知道天下也会是这个样子？“以此”。大道所向无往而不胜，虽然人世间有那么多的枝枝蔓蔓，但是核心“善建”、“善抱”之大道，不要脱离开大道，坚定地、坚持地按照它去做，按照道去做就是“有德”。修身得到的是“真”，修家得到的是“余”，修乡得到的是“长”，修国得到的是“丰”，修天下得到的是“普”。所以，从修身开始，最后落到天下，不就是这样一个简单的道理吗？其实读这一章的时候，大家会有一个非常深刻的感受，中国先秦时代是中国的轴心时代，各个思想流派之间的思想，虽然有差别，但是也有相同的地方。所以我们看这和儒家的思想，修身、齐家、治国、平天下一样，都是从修身开始，最后才能够成为国家的好的领导者，才能把这种思想普及到天下。“天下难事必做于易，天下大事必做于细。”从自身做起，要求自己按照大道的这种修养、修为，按照“善建”、“善抱”的原则，坚持地、坚定地去做，我们才能真正地有德。</t>
-  </si>
-  <si>
-    <t>第五十五章（55）</t>
-  </si>
-  <si>
-    <t>含德之厚，比于赤子。蜂虿（chài）虺（huǐ）蛇不螫（shì），猛兽不据，攫（jué）鸟不搏。骨弱筋柔而握固，未知牝牡之合而全作，精之至也。终日号（háo）而不嗄（shà），和之至也。知和曰常，知常曰明，益生曰祥，心使气曰强。物壮则老，谓之不道，不道早已。</t>
-  </si>
-  <si>
-    <t>含德深厚（品德极为高尚）的人，就好比刚出生的小孩。蜂蝎毒蛇等都不会刺咬他，猛兽不抓他，猛禽不攫取他。筋骨柔弱但小拳头握得很牢固，不知道男女交合之事但生殖器会举起，这是因为他精气充足。整天嚎哭但嗓子不会哭哑，这是因为他元气醇和。知道醇和、平和就是了解了道的规律、规则，了解这个事物规律、规则的人才是明智，让我们的生命有益才是一个吉祥，纵心任气，是强暴、强蛮的表现。事物太强盛了就会走向衰老，（追求过分强盛）这叫做不合于道，不合于道便会早早灭亡。</t>
-  </si>
-  <si>
-    <t>这章开头讲了一个非常有意思的概念，就是“赤子”，这是因为婴儿刚出生的时候浑身是红色的，但这个词更重要的作用是比喻心地的纯净、纯洁。“含德之厚，比于赤子。”按照道的标准来衡量，赤子心地纯净，无恃无为。这是含德浑厚的一种表现。其实，不只老子，孔子也对婴儿的状态充满了景仰，认为这是一种有道的含德之厚的表现。孟子也说，“大人者不失其赤子心”。老子更是把婴儿作为一个范本与榜样，第十章就说“专气致柔，能如婴儿乎？”人精神集中，气息平和，那不就是像婴儿的样子吗？下边这些都是从经验的角度来讲获得的感受。小孩的他精神状态很安稳，蜂子、毒虫、蛇也不蜇他，也不咬他，为什么呢？因为小孩没有危险，没有对这些动物造成威胁的举动。其实有时候蜂子落到我们脸上，也许只是为了得一滴汗液，没有汗液，它采的蜜也不能凝固，可是我们一打它，它当作危险的时候，就要用它的毒针来蜇我们。很多动物也是这样，人没有危险动作的时候，其实也不会攻击人，但人见到它就害怕，就有一种防范甚至攻击性的动作，这也是难免的。老子说你看，这婴儿啊，“毒虫不螫”，毒虫不蜇他。“猛兽不据”，虎啊、狼啊这些猛兽，也不把它叼走，不用爪子把他抓走。我们经常会听到这样的一些事，很多动物还喂养、抚育这些落在田野里边的荒野上的小孩，当然这也不是全部的情况，我估计老子也是拿这个做一个说明而已。“攫鸟不搏”，攫，攫取。有的时候，人手上拿着一个什么东西，比如说拿着肉，在一些荒远的地方，老鹰就飞下来把这肉抢走了，但是对小孩它却不这样做，除非是尸体。“骨弱筋柔而握固”，这小孩其实身体是最柔软的，但是你看他这小拳头却握得很紧固。这人生啊，深究起来是有点意思。小孩刚出生的时候，都是握着拳头，似乎想抓住点什么，但人最后离开这个世界的时候，却是放手了，知道什么也抓不住。“未知牝牡之合而全作”，“牝牡”本来指的是雄性和雌性的动物，但是这个地方指的是男女。小孩刚出生不知道什么男女的事情，但是你看他的小生殖器却非常坚挺。老子用这样的一个方式来做形容，说婴儿精气很纯、很多、很壮，“精之至也”，达到了一个最好的状态，老子是这样认为。下边这个描述确实挺有意思，叫“终日号而不嗄”，小孩终日啼哭，但是嗓子却不哑，那不是精气足的表现吗？我现在讲课，讲一段时间喉咙就哑了，我们现在为什么会这样？老子可能认为，这人长大了，欲望多了，精气耗费得多了，所以就不像小孩那样精气充足。这一段把婴儿作为一个得道者的良好状态的表现讲完了，下边老子该阐述自己的观点了。“知和曰常”，“常”就是规律、规则。了解了这个“和”，通过婴儿引出来的“和之至”，谁能够像婴儿一样，让我们气息平和，让我们的欲望平和，不那么欲壑难填，就了解大道的规律、规则。“知常曰明”，了解这个事物规律、规则的人，那才是明智。“益生曰祥”，让我们的生命有益，这个才是一个吉祥的表现。这是正面，那负面呢？“心使气曰强”，老是盛气凌人，体现的是这种强横、强暴，这个是道家所反对的。气息不平和，纵心任气、任性，这个是强暴、强蛮的表现。在前面第二十三章讲过，“飘风不终朝，骤雨不终日，孰为此者？天地。天地尚不能久，而况于人乎？”暴风骤雨它不会持久，天地的使强也不过只是持续一阵子，它告诉我们这个道理，强不能持久。“心使气曰强”，这不是一种好现象。“物壮则老”，事物发展到顶峰的时候，就开始走下坡路了，人到了壮年之后，就逐渐向衰老的方向发展了。“谓之不道”，这已经使气，老是以强壮来作为目标、作为处理问题的方式，这是不符合大道的。“不道早已”，既然不符合大道，那这个事情就不能持久，很快就会结束了。你看这婴儿的状态，其实应该能存活得更长久、寿命更长，为什么后来很多人变得短寿了呢？那就是让自己脱离了大道，没有像婴儿那样，“精之至”，“和之至”。所以人应该“知和，知常，益生”，而不应该使气，不应该“物壮”，如日中天的时候就走下坡路了。人生最美的境界是什么？花未全开月未圆。所以，按照大道的方式来处事、认知事物，这样我们才能够明，才能够益，否则的话就会“不道早已”。</t>
-  </si>
-  <si>
-    <t>第五十六章（56）</t>
-  </si>
-  <si>
-    <t>知（zhì）者不言，言者不知（zhì）。塞其兑，闭其门，挫其锐，解其分，和其光，同其尘，是谓玄同。故不可得而亲，不可得而疏；不可得而利，不可得而害；不可得而贵，不可得而贱，故为天下贵。</t>
-  </si>
-  <si>
-    <t>有智慧（懂得大道）的人不多言，多说话的人不是有智慧的。圣人塞上欲望的孔穴，闭上欲望的门户，收敛锋芒，解除纷扰，在光明之处便与光融合，在尘垢之处便与尘垢同一，（能做到这些）这就叫“玄同”（就是与道同体）。所以既不可能与这样的圣人亲近，也不可能与他们疏远；既不可能使他们得利，也不可能使他们受害；既不可能使他们尊贵，也不可能使他们卑贱。所以他们被天下人所尊崇。</t>
-  </si>
-  <si>
-    <t>这一章还是比较容易理解的。“知者不言，言者不知。”开头的第一句话就讲，有智慧的人是不多言的，所谓“行不言之教”，还有“悠兮其贵言”，都在讲这个道理，有智慧的人是不会多嘴多舌的，不会去乱说的。“知者不言，言者不知”，老是认为自己无所不知、以为自己有智慧的人，其实是不具备真正的智慧的。“塞其兑，闭其门。”我们前边解释过，“兑”指的就是耳、目、鼻、舌这些感官，所以它强调的是感性对事物的认识，是不可信的。“塞其兑，闭其门”，这样才能对事物本质的根本的内容有真正的理解。下面讲处理问题的方式方法，做人的思想与智慧，要“挫其锐，解其分，和其光，同其尘”，不要锋芒外露，这样才能长久。要解除那些纷纷扰扰，不要让纷纷扰扰在心里打成结——心有千千结。真正了解道的含义的人，按照道去做事的人，是很容易摆脱这些纷纷扰扰的。“和光同尘”，也就是讲同流而不合污，所谓外圆而内方，所谓与世推移。那么这个叫什么呢？就叫做“玄同”。“玄”本来是天的颜色，意味着深远，这样的同是深远的、深刻的，同流而不合污，当然里边就非常有玄妙了。下面的内容讲得也非常清楚，就是说道并不是为人谋利益的，得道的人他怎么样来和万事万物打交道呢？就像道一样，“不可得而亲，不可得而疏”，道并不是对谁更亲近，或者对谁更疏远。有亲就必有疏，有疏就必有亲，这个就不平等了，这就不“玄同”了。所以，按照道的、“玄同”的方式来做，没有亲疏之别，无差别。“不可得而利，不可得而害”，有利必有害，有害也必有利。所以你并不能凭借道而获利，也不能用这个道来危害别人，无差别，无利无害。“不可得而贵，不可得而贱”，道对谁也没有贵贱之分，还是依然玄同、平等，一旦有贵贱之别，便也就丧失了道的本质的属性。所以庄子讲，“以物观之，自贵而相贱。以俗观之，贵贱不在己。”从物的角度来看，都认为自己是珍贵的、宝贵的，其他的东西比不上自己的尊贵。用世俗的观点来看，贵和贱不在于自己，而在于别人的评价，在于外在的标准。而“以道观之，物无贵贱”，从道的角度来看，这万事万物并没有什么贵贱之分，所谓公正、平等、无差别、无贵贱之分。正是因为这样，所以它成为天下最尊贵的，“故为天下贵”。所以这章的内容啊，道表现为玄同，按照这样的深远的玄同的道理来理解事物，就是从道的角度来观察问题。道没有亲疏之别，没有利害之分，没有贵贱之差，所以用这样的一个角度来观察世界，这个才使它成为天下最令人敬重尊仰的，“故为天下贵”。</t>
-  </si>
-  <si>
-    <t>第五十七章（57）</t>
-  </si>
-  <si>
-    <t>以正治国，以奇用兵，以无事取天下。吾何以知其然哉？以此。天下多忌讳，而民弥贫；民多利器，国家滋昏；人多伎巧，奇物滋起；法令滋彰，盗贼多有。故圣人云：我无为而民自化，我好静而民自正，我无事而民自富，我无欲而民自朴。</t>
-  </si>
-  <si>
-    <t>以清静无为之正道治国，以奇巧诡计用兵，以不多事滋扰来取得天下。我怎么知道是这样呢？因为如下情况：天下的忌讳（禁令）太多，人民就越来越贫穷；百姓拥有很多锋利武器，国家就会越来越混乱；人民拥有很多奇技淫巧，奇怪甚至邪恶之事就会越来越多；法律条文越严苛，盗贼反而会越来越多。所以圣人说：我无为（不去人为干涉） 人民便自我化育成长；我做到内心清静 人民就会自己走上正道（品行端正）；我不多事不扰民 人民自己就会富起来；我没有私欲 人民自然就会淳朴。</t>
-  </si>
-  <si>
-    <t>第五十七章的这段话非常有智慧，因为这段话一开始就指出来了，事物之间的不同，有本质的区别，所以处理问题、解决问题的方式方法也不一样。“以正治国，以奇用兵”，治国讲究的是堂堂正道。道家讲的“正”当然就是清静无为，不多事，不扰民，这就是道家讲的正道，是治国的大道理。可是用兵讲究的是“以奇用兵”，“兵者诡道也”，兵不厌诈。所以不能把用兵的方式、战争的方式用到治国的上面来，这两者不同，解决的方式也不一样。“以无事取天下”，无事就是不多事、不扰民、不刁难，这样才能够得到天下，并且坐得了江山。道家“无事”是“无为”的一个重要的方面，不多事、不扰民、不刁难，而“有为”讲的是妄为，多事、扰民、刁难，我们在前边这一点已经非常明确了。“吾何以知其然哉”，我怎么知道是这个样子呢？所谓“以此”就是依据上边“以正治国，以奇用兵”它们之间的本质不一样，所以解决的方式方法也不同而得出的结论。下面，老子开始谈他对治理天下的重要的看法。违背了大道，违背了道家的以“清静无为”为根本来治理国家的方式，会出现什么问题呢？“天下多忌讳，而民弥贫”，治理天下、领导国家忌讳太多，这个也不能动，那个也不能动，这个人的职务比较高，法令涉及不到他，当然出现了忌讳，不敢动，这个地方一定会形成一个空场，形成一个腐败的群体。百姓当然越来越穷了，财富都集中在少数人的手上。“民多利器，国家滋昏”，“滋”就是越来越。如果民间利器众多，武器众多，民与民之间械斗、抗法，那国家当然越来越混乱。“人多伎巧，奇物滋起”，“伎巧”就是各种各样的奇技淫巧，越来越多，大家对这些越来越感兴趣，这个技巧能够给他们带来利益，那么各种各样的奇奇怪怪的东西，甚至包括那些妖孽的东西，就不断兴起。“法令滋彰，盗贼多有”，既然这样，要用法律来管，法条定得越来越多，越来越严苛，反而盗贼越来越多。在前面这一段讲完之后，《道德经》说“故圣人云”，很明显，这是引用以往的通达事理的王们的话，老子用自己心中有智慧的人的语言来作为结尾。“我无为而民自化”，道家讲的无为，第一，“不妄为”。第十六章里边说“不知常，妄作，凶”，不了解事物的规律、规则，瞎折腾、胡折腾，这个结果是非常糟糕的。第二是“不多为”。抓住关键，举重若轻，多言数穷，不如守中，适可而止，恰到好处。第三讲究的是“有所不为”。人要想有所为，必须有所不为。一个政府也罢，一个领导者也罢，所有的事情都抓在自己手上，那底下的人怎么得到锻炼呢？不把担子压给他，他怎么练出独当一面的能力呢？什么事都控制在自己手上，那众人怎么样自我化育自我成长呢？所以无为才能让国家的人民、才能让自己的属下自我化育自我成长。事情成了应该怎么样呢？第十七章“功成事遂，百姓皆谓‘我自然’”，事情做成了，百姓都说这是我们的努力把这事情做成的，这就叫“民自化”。“我好静而民自正”，前面我们讲过，道家讲的静，内心的清净，静下来才能找到解决事物的正确的方法。我清静，走正道，不那么浮躁、急躁、暴躁、狂躁，做一个好的表率，上梁而正，百姓当然也就正了，百姓当然也就好静而走正道了。“我无事而民自富”，不多事、不扰民、不刁难，那百姓自然就富起来了。“我无欲而民自朴”，“朴”就是原木，《道德经》里用原木喻指做事敦厚、朴实、厚道，没那么多欲望，不是老想抢夺别人、占有别人的。就像黄宗羲在《明夷待访录》里边讲的，古代的那些皇帝都是什么样的？“离散天下人之儿女，荼毒天下人之肝脑，以供一人之淫乐。”这是我的，普天之下都是我的。所以欲望无止境，你让百姓能够朴实厚道，这也不可能。所以不要欲壑难填，不要什么东西都看作是自己的，可以任意掠夺，这样百姓自然就朴实、厚道，民心淳朴。这里边的两句话，我们国家的领导者讲话的时候也经常引用：“我无为而民自化，我无事而民自富。”所以，第五十七章讲了两个重要的道理，第一个不能把打仗的这一套用到治国之上。治国讲究的是堂堂大道，讲究的是清静无为，所以以无事取天下。第二个就讲站在领导者的角度，站在统治者的角度，应该怎么做呢？无为、好静、无事、无欲，这样自然一切顺理成章，百姓就会自化、自正、自富、自朴，事成了也会“功遂身退，百姓皆谓我自然”。这是一个好的领导者、好的政府做事的道理之所在，反之越多事儿，越是用那种严苛的法令，导致的结果适得其反。忌讳多了，百姓就越来越穷，民间的利器多了，国家就越来越混乱，大家都倾向于奇技淫巧，把这个当作一种喜欢的甚至不停地去追求的目标，那这个国家就越来越怪，各种奇葩的事情都纷至沓来。越觉得法令不够，越制定得严格、细致，以为单靠着法令就可以解决所有问题，反而适得其反，盗贼多有。所以，这一章里边讲的，也是我们经常说的——这本书的总纲：“反者，道之动”。我们考虑问题，不要只考虑它一面，要相反相成，用一个更高的观察事物的角度来理解。</t>
-  </si>
-  <si>
-    <t>2、5、10</t>
-  </si>
-  <si>
-    <t>第五十八章（58）</t>
-  </si>
-  <si>
-    <t>其政闷闷，其民淳淳；其政察察，其民缺缺。祸兮福之所倚，福兮祸之所伏。孰知其极？其无正。正复为奇，善复为妖。人之迷，其日固久。是以圣人方而不割，廉而不刿（guì），直而不肆，光而不耀。</t>
-  </si>
-  <si>
-    <t>（治国者）为政宽容，人民就会淳朴善良；为政苛察，人民就会变得狡猾奸诈。灾祸啊 幸福就依靠在它的旁边；幸福啊 灾祸就埋伏在它的里面。谁能知道最终的结果是祸是福呢？没有确定的标准（永恒正确的事情）。正确会变为邪恶，善良会化作妖孽。人们不懂得这一道理，已经有很长的时间了。因此圣人方方正正却不去为难别人，有棱角但不去伤害别人，自己坚持正直品德却不强迫人去做，有光芒但内敛 不刺眼炫耀。</t>
-  </si>
-  <si>
-    <t>第五十八章有两个我们非常熟悉的成语，一个叫“祸福相依”，一个叫“光而不耀”，也是这一章核心的内容。祸福相依，福和祸是相互转化的，两者也是相辅相成的，分不开的。“光而不耀”在讲什么呢？我们大家看到过月亮，月光是明亮的，在黑暗中给我们指引以方向；同时月光也是不张扬的、不炫耀的、不刺眼的。中国人喜欢拿月亮来比喻君子的形象，做君子得先有光，但是不管我们有什么，都不要老想着去张扬、炫耀，让别人感觉到刺眼。所以《道德经》很多章节，都向我们揭示了这样一个道理：有才华、有知识、有道德的人，不要老想着去张扬、炫耀。以这两个成语为切入点，我们会对这一章的内容有个直观的感觉。我们来逐字逐句地解释一下。“其政闷闷”，“闷”就是淳厚。就说政治比较淳厚宽容，那么这个国家的百姓也就是敦朴淳厚，不耍心眼。“其政察察，其民缺缺”，假如这个政治非常苛察，对一切都监控得到位，那老百姓就会感觉到有很多的缺陷与不足，就要耍心眼。所谓上有政策，下有对策，也就失去了原本的淳朴。“祸兮福之所倚，福兮祸之所伏。”福和祸是相辅相成的，在一定条件下是相互转化的。民间的很多说法，大家都能够体会到这意思的延伸和运用，比如，我们经常说“大难不死必有后福”、“好事多磨”……福和祸是相伴而行的，有时候我们认为是福的事情，它可以转化为祸，反过来也是一样，所以这就叫“祸福相依”。怎么样来理解这个事情呢？给大家举个例子，大家就清楚了。其实各民族的智慧到达高点的时候，往往是相互重合的，印度有一本佛经叫《大般涅槃经》，在这里面讲了这样一个故事。有一天早晨，一家主人一开门，门口站着一个衣着光鲜、非常漂亮的女子，主人就问你是谁，女子说我是“功德大天”，我到谁家谁家就一切兴旺。主人高兴地请进来，焚香供拜。刚一关门又有人敲门，开门一看，门口站着一个衣衫褴褛，非常丑陋的、黑瘦的女子，主人就没好气了，主人就问你是谁呀，那女子说我是“黑暗”，我到谁家，谁家就一切破败！主人当然不让她进来，拿着刀驱赶。结果这女孩说你太笨了，刚进去的是我姐姐，我们俩从出生这天起就没有分开过，你把我赶走了，她也留不下。主人不信，进去一问果然是这样。福跟祸是相伴而行的，所以它就提醒我们，遇到福事的时候就要小心谨慎，避免乐极生悲；遇到祸事的时候，也不要感觉到沮丧，因为我们对灾祸有所警惕，它可以避免后面更大的灾难。韩非子讲过“千里之堤，溃于蚁穴”，我们发现了这个蚂蚁窝，知道它是一个祸患，很早的把它堵上，那就避免了以后更大祸事的发生。这就是“祸福相依”的道理，在我们文化中影响是非常深刻的。讲完这一段后，《道德经》就说“孰知其极？”这个事物到达极点的时候，向它相反的方面转化，所谓两极相通，所谓物极必反，但是这个极在哪里呢？这个是需要我们认真去体会把握的。“其无正”，其实并没有确定的标准，所以并没有说我们到了一个什么程度，一定会向它相反的方面转化，这是要根据不同的时间、地点、条件，需要我们认真去领会把握的、体悟的一种智慧。“正复为奇，善复为妖。”“正”，你把它弄到极点它就偏了，“善”到达极点的时候，它就转化为它相反的方面。有些人老想寻找一个固定的标准，《道德经》就说：“人之迷，其日固久。”在这个方面的迷惑，时间已经由来已久。所以我们总是要寻找一个固定的标准，总是觉得做事情有一个固定的程序，固定的套路，这个就不圆融。下面就讲，“是以圣人方而不割”，“方”就是方正，“割”就是生硬。有原则但是不生硬，人要懂得去碰硬，但是不要去硬碰。方正而不生硬，这样才能圆融，我们把它叫做“外圆而内方”。“廉而不刿”，“廉”就是棱角，“刿”就是锐利。有棱角但是不要老用锐利之处去刺伤人。“直而不肆”，有人经常就说，我说这话你别在意，我这人很直。其实有的时候不是直而是自私，是放肆、过分。所以我们说直率，它是一种心态，但是你讲话的方式得懂得圆融，直率而不放肆。“光而不耀”，有光芒，但是不要老去张扬、炫耀，让别人感觉到刺眼。咱们中国人喜欢讲君子，什么样的人是君子呢？中国人除了用月亮来代表君子“光而不耀”的特点之外，另外，也喜欢用玉来代表君子的形象，所谓“谦谦君子，温润如玉”。“谦谦君子”出自《易经·谦卦》，原话叫“谦谦君子，用涉大川”，一个人保持这种内敛的、谦逊的风度，这样才能走好人生长远的坎坷的道路。另外一个是出自《诗经》的“温润如玉”，谁都知道闪着贼光的肯定不是什么好玉，真正的好玉都是光芒内敛，给人一种温润感。我认为“光而不耀”是中国文化里，对君子形象用得最好的一个比喻。我们有知识，不要老想着去张扬、炫耀，大家聚到一块的时候，一个人老去炫耀自己的知识，对别人的说法都嗤之以鼻，认为自己什么都懂，百事通，时间长了，大家就不喜欢跟这人打交道了。有道德，道德是约束我们内心的，不是老是向别人去张扬炫耀。《道德经》第三十八章开头这句话，大家都知道——“上德不德”，最有道德的人从来不去张扬、炫耀自己的道德。当然，至于炫官、炫富，这不仅不是一种君子的形象，还会给自己惹来无尽的祸殃。是否还记得第九章里“金玉满堂，莫之能守；富贵而骄，自遗其咎”，炫富炫贵，会给自己惹来无尽的祸殃。在第二章里“功成而弗居”，哪怕我们有功劳，不管是对家庭、对单位、对国家有功劳，也不要老想着去张扬、炫耀，越是不张扬、不炫耀，这个才能在人心里长久地存在。第九章里面也说“功遂身退，天之道”，这是符合自然的道理。第五十八章讲完之后，我再做一下梳理和强调。这一章有两点需要注意，一个是“祸福相依”的道理，一个是“光而不耀”的形象，怎么样能做到这一点？我们要明白“物极必反，两极相通”。了解这样的智慧与道理，我们做事情才能够圆融。所以一个有智慧的人，有智慧的领导者，为人处事应该方正而不生硬，要圆融，有棱角，但不要老去割伤人，要懂得委婉迂回地处理问题的方式。直率，但又不越界进入到了放肆、无所顾忌的程度，光芒内敛而不要老去张扬、炫耀，要给人留下一种谦谦君子、温润如玉的形象。这是我们和别人、和这个社会打交道的一个重要的思想与智慧。</t>
-  </si>
-  <si>
-    <t>第五十九章（59）</t>
-  </si>
-  <si>
-    <t>治人事天莫若啬（sè）。夫唯啬，是谓早服，早服谓之重积德（chóng）。重（chóng）积德则无不克，无不克则莫知其极。莫知其极，可以有国。有国之母，可以长久。是谓深根固柢（dǐ），长生久视之道。</t>
-  </si>
-  <si>
-    <t>治理人民要顺应天理 最好的办法莫过于节俭节制。只有节俭节制，才能早得道。早得道就是不断地积德修养自己。不断地积德就没有什么是克服不了的，没有什么克服不了就不知道它的力量有多强大。不知道其力量有多强大，（有了无可估量的力量）就可以掌管国家。掌握了治国的根本，就可以长久存在。这就是根本扎深、扎牢固，永世长存的办法。</t>
-  </si>
-  <si>
-    <t>这一章讲了两种生活的态度：一种是做“加法”，不断地叠加，不断地累积，有了还想更有，多了还想更多；另外一种是要懂得做减法，要节俭节制，有的时候我们的欲望减少一分，其实我们的幸福也就多一分。这两种人生态度也是相辅相成的，可是大家更注重的是第一种，所以一章就强调我们这种做减法的态度的重要性。其实这一章核心就讲四个字：节俭节制，讲节俭节制对一个国家、对社会的重要意义。“治人事天莫若啬。”一开始就讲“治人事天”，领导这个国家的人民要顺应天理。“莫若啬”，什么事情最顺应天理呢？节俭节制。我们现在用的这个词叫“吝啬”，这个词有点负面的含义，在《道德经》中这个“啬”，我们把它译成节俭节制，这样更符合于我们的接受习惯。“夫唯啬，是谓早服”，“夫唯”是个语气助词，“啬”是节俭节制。“是谓早服”，“早服”就是早得道。懂得节俭节制的道理，就是可以早得道的人。“早服谓之重积德”，“重”就是不断。懂得节俭节制就是在不断地积累自己的品德，积累自己的德行。因为我们说《道德经》道和德要分开理解，按照道去做，就是有德，不断地按照道去做，就是不断地积德。重积德就是不断地积德，所以你看“早服谓之重积德”，早得道，一直坚定地坚持按照这个去做，就是不断地积累自己的德性，积累自己的品德，积德。我们就像一条船，我们积的德就像水，水积累得越多，我们船才能自由地航行，不管你船多大，如果没有水，在那儿搁浅，它也发挥不了船的这种作用。“重积德则无不克”，“克”就是克服，按照这个“啬”的方式，也就是节俭节制的方式去做事情，那就没有什么困难克服不了的。因为在节俭节制里边磨练的就是人的思想品德，磨练的就是人的意志，磨练的就是人面对困难无所畏惧的态度。“无不克则莫知其极”，你说这个东西力量这么强大，没有什么东西它克服不了，所以它的力量“莫知其极”，你不知道它的力量有多么强大，对一个人是这样，对一个国家更是如此。“莫知其极，可以有国。”你看这话是给谁讲的？给统治者、领导者讲的。一个领导者领导团队，领导这个国家的人民培养出一种节俭节制之风，你这样才能让你的国家长久地存在，长久地发展。毛泽东主席在中华人民共和国成立的时候就指出，“贪污和浪费是极大的犯罪”，自己也以身作则。你领导团队，领导全国人民培养出一种节俭节制之风，这样面临什么样的困难的时候，大家都有信心去克服。“有国之母，可以长久。”“母”就是根本。节俭节制是立国，是国家长久发展的根本。我们现在叫“八项规定”“反四风”，领导国家的人民培养出节俭节制之风，国家才能长久持续地发展。有一件事儿大家都知道，电视经常打出一个公益广告，说现在每年中国人浪费的粮食就是世界上两亿人的口粮。你说世界上现在每天都有人在饿死，可我们中国人这么浪费，能符合天道，能符合天理吗？如果因为这种浪费有什么惩罚落到我们头上，那么我们也无话可讲。你从这一章里面就可以感觉到，一个人浪费，糟蹋的是自己的福分；一个国家浪费，糟蹋的是国家的福分，对国家的根本有所损伤。“是谓深根固柢，长生久视之道。”国家培养出节俭节制之风，才能长久发展，这样做叫什么？叫“深根固柢”。我们讲叫根深蒂固，你让这个根本、让根扎得深，扎得稳固，深根固柢。“长生久视之道”，于人来讲是如此，可以让我们的生命更为长久，因为一个人的节制节俭，不去放纵自己的欲望，这也是一种养生之道。得以长久地存在，长久地发展，得以长寿，对国家来讲也是如此。所以“长生久视”，长久地存在，大家能够长久地看到它。《道德经》强调“做减法”的这个方面，在世界哲学界，有着非常重要的影响。我们中国人有一个优良的文化传统，讲勤俭持家，讲勤俭治国，所以这个是我们文化中非常重要的方面，但是很少在哪一本著作里面把它强调到这样的一个高度。“治人事天莫若啬。夫唯啬，是谓早服。”这就是早得道，坚定地按照这个道去做，就叫积德。不断地积德，那就使我们能够根深蒂固，长久存在，长久发展。人如此，国家亦如此，道理是相同的。第五十九章，希望大家认真地品味体会老先生给我们讲的“根深蒂固”的道理。</t>
-  </si>
-  <si>
-    <t>第六十章（60）</t>
-  </si>
-  <si>
-    <t>治大国若烹（pēng）小鲜。以道莅天下，其鬼不神。非其鬼不神，其神不伤人；非其神不伤人，圣人亦不伤人。夫两不相伤，故德交归焉。</t>
-  </si>
-  <si>
-    <t>治理大国就像烹调小鱼一样（不要经常折腾它）。（君主如果能够）用道来领导、指引天下，鬼也就没有神秘莫测的力量。不是说鬼不神秘莫测了，而是它的神秘莫测伤害不了得道的人；不但鬼的神秘力量伤不了百姓，圣人也不伤害百姓。鬼和圣人都不伤害百姓，所以德不断地积累交汇 形成有道有德的世界（恩德都将施与百姓）。</t>
-  </si>
-  <si>
-    <t>这一章有一句话，大家都非常熟，叫“治大国若烹小鲜”，这句话也是这一章的核心。一九八七年，美国前总统里根在发表国情咨文的时候也引过这句话。二〇一三年，“金砖各国”开会，在一个联合的采访中，有一位巴西记者问过习近平这样的一个问题：你担任这么大的一个国家的这么重要的职位是一种什么心态？你用什么样的态度来对待自己的职位？习近平答记者问，先引的是《诗经》，来回答第一个问题：“战战兢兢，如临深渊，如履薄冰。”这话出自《诗经·小雅·小旻》。治理国家要小心谨慎，就像行走在结着薄冰的冰面上一样，就像站在悬崖边一样，要小心谨慎，因为稍不谨慎就会出大的问题、大的危险。然后引用这句话来回答第二个问题，我要以“治大国若烹小鲜”的态度来对待我的职位。“治大国若烹小鲜”是什么意思呢？大家如果上网去搜对这句话的解释，类型就有二十多种，每一种解释都不一样，有的甚至把它直接翻译为“治理一个大的国家就像烹一碟小菜那么简单”，这是完全没有理解这句话的真正的含义。“小鲜”就是小鱼儿，鱼肉很细很嫩，拿它的时候就得小心谨慎，尤其是在高温里烹炒它的时候，都要小心谨慎，要有耐心。火候不到的时候你老折腾，甚至锅铲飞舞，翻腾，鱼不就成了碎片了吗？汉朝的毛亨，喜欢《诗经》的人都知道，这个人写过《毛诗传》的，他就用两句话来解读这句话，其实最符合它的本意。第一句话叫“烹鱼烦则碎”，环节太多老折腾它，那鱼就成了碎片了。第二句话“治民烦则乱”，治理一个国家也是一样，讲究的是制度的稳定，不能今天一个制度，明天一个制度，朝令夕改；你不能今天一个运动，明天一个运动来回折腾，国家不就被折腾散架了嘛。“治大国若烹小鲜”和“战战兢兢，如履薄冰”的道理是相同的，讲究的是小心谨慎，有耐心，掌握火候。“以道莅天下，其鬼不神。”“莅”就是莅临。用道来领导天下，指引天下。大家注意，这个“神”字很多的理解有问题，其实并不是神鬼的神，不是说我们后来的人格神、神化了的神。这个“神”在《易传》里面的解释是非常明确的，“阴阳之不测之谓神”，也就是神秘莫测。用道来领导天下、指引天下，鬼也没有什么神秘莫测的力量，因为你走的是正道，你走的是堂堂大道，鬼也没有办法去伤害到你，所以“以道莅天下，其鬼不神”。《道德经》里用它的道，把大家所恐惧的鬼的位置给取代了，你堂堂大道，鬼也近不了你的身，“其鬼不神；非其鬼不神”，不是鬼不神秘莫测，是因为你走大道，它的神秘、莫测、玄妙、诡秘已经没有办法伤害到你。所以把下一句话作为上一句话“其鬼不神”的注解，就很容易理解了。“非其鬼不神”，不是说这鬼不神秘莫测了，神秘莫测是它的本性。“其神不伤人”，但是它的神秘莫测已经伤害不了这种走在大道上的人、得道的人。“非其神不伤人，圣人亦不伤人”，不单是指鬼的力量伤害不了人了，反过来说，圣人他智慧高，但圣人智慧高也得返璞归真。圣人不会因为自己的智慧高，心眼多套路深，就使用这种“技巧”，这个东西不是正道。所以，鬼的神秘莫测伤不了人，圣人的智慧在领导大家的时候也会“善利万物而不争”，对人民没有伤害，“夫两不相伤”，你看鬼的神秘莫测也伤不了人，圣人领导也伤不了人。“夫两不相伤，故德交归焉。”所以有德的事情，积德的事情，两者交汇到一起，两不相伤。因为你按照道来做事情的话，鬼伤不了你，圣人也是按照道来做的，彼此也不相伤。这样大家就走在正确的道上，按照道去做，不断地积德，所以叫“德交归焉”，交汇，归到一块。“治大国若烹小鲜。以道莅天下，其鬼不神。非其鬼不神，其神不伤人；非其神不伤人，圣人亦不伤人。”如果这样两不相伤的，那就是“德交归焉”，这样就形成了一个和谐的、有道的、有德的世界。</t>
-  </si>
-  <si>
-    <t>第六十一章（61）</t>
-  </si>
-  <si>
-    <t>大国者下流。天下之交，天下之牝（pìn）。牝常以静胜牡，以静为下。故大国以下小国，则取小国；小国以下大国，则取大国。故或下以取，或下而取。大国不过欲兼畜人，小国不过欲入事人。夫两者各得其所欲，大者宜为下。</t>
-  </si>
-  <si>
-    <t>大国要像大海一样居于百川的下游，就像处在江河的下游。处在天下交汇的地方，处在天下最雌柔的地方。雌性常以柔静胜过雄性，是因为柔静的性格是一种谦下的表现。所以大国以谦下的态度对待小国，就可以争取到小国的支持；小国以谦下的态度对待大国，就可以得到大国的庇护。因此有的谦下能够取得别人的拥戴，有的谦下能够取得别人的庇护。大国所希望的不过是得到小国的支持，小国所希望的不过是得到大国的庇护。大国小国都达成了各自的愿望，越是大国越要懂得善于处下（谦下）。</t>
-  </si>
-  <si>
-    <t>《道德经》从头至尾有一个非常重要的智慧与理念：善于处下。在第八章里面就说，“处众人之所恶，故几于道”，水去的是又低又脏的地方，把那里的污浊洗净，在那个地方滋润万物，跟道最接近的。做人要做“上善若水”的人，才能称其为“大人”，这个“大”代表的是品德。国家要成为一个大的国家，该怎么样做呢？它的处事的态度是什么呢？第六十一章里边开头这句话说得简要、明确、深刻：“大国者下流。”所以，这一章的核心我们看一下，开头“大国者下流”；结尾“大者宜为下”。越是大的国家越懂得善于处下，和小的国家打交道的时候谦逊谦和，和谐相处，你就把小的国家争取了。人也如此，位置越高，越要善于处下，这样才能真正居上。这是这一章的开头、结尾，也是这一章的核心。我们在解读“大国者下流”之前，我们需要采用以经解经的方式，拿第六十六章开头这句话，用这个形象先来让大家直观地感知一下，这个直观的形象我们了解了，再来看这一章就容易了。第六十六章开头这句话：“江海所以能为百谷王者，以其善下之，故能为百谷王。”大江大海为什么能成其大呢？它地势低，善于处下，其他的水系就都汇到它这来了，用我们习惯的话讲，就叫“善于团结一切可以团结的力量”。不辞细流，所以成为大江大海。然后我们再来看第六十一章开头这个五个字就很容易理解了。“大国者下流。”所谓“下流”，就是善于处下、处在水的下游，最好是处在大海的入海口，涓涓细流慢慢地汇成大江大海。那么善于处下《道德经》拿什么来比喻它呢？这个地方是什么？是天下的水交汇的地方，所以叫“天下之交”。拿什么来比喻“天下之交”的呢？《道德经》把它叫“天下之牝”，“牝”代表母性、女性，本来这个“牝”是指母性的生殖部分。因为在《道德经》里边母性、女性代表着慈，代表着柔，代表着静，“牝常以静胜牡”，“牡”是雄性，“牝”是雌性。这世界上的事情便是如此，这雌性善于柔，善于静，所以她的力量更长久。拿这个道理来说明什么呢？以静为下，什么叫善于处下？就是以静为下。别那么急躁、暴躁、浮躁、狂躁，善于处下，这样才能具有更大的力量、更长久的力量。这段讲完了，下边又接着“大国者下流”的道理。上面那一段是在论述它力量产生的源泉。一个大国老去动武，喜欢好战，好战者必亡，看着很强大，其实这都不是长生久视之道。所以下面就讲，“故大国以下小国，则取小国。”不是以静为下吗？善于处下吗？一个大的国家在跟小的国家打交道的时候，态度谦逊谦和，善于处下，不是居高临下、盛气凌人、不可一世的处事的方式方法，把这个小的国家就争取了。你和它平等相待，它觉得你这个大国可以倚靠，它喜欢跟你交往，遇到事情的时候喜欢支持你，帮助你，为你出力。“小国以下大国，则取大国。”为什么小国会这样做呢？因为小的国家也得找倚靠。小的国家在和大的国家打交道的时候，也善于处下，也把自己的位置放低，那么它就成了大国的朋友，有事的时候，大国才能给予支持，用我们现在习惯的话叫“罩着你”。大国也罢小国也罢，都得善于处下，这样才能形成一种和谐的关系。下面这两句话是比较难以理解的。“故或下以取，或下而取。”什么叫“以取”呢？争取有两种方式，一种是从上边抓起来，还有一种方式是更为有智慧的从下面轻轻地托起来。别小看这两个虚字、连词，“以”和“而”，这表示不同的动作。“或下以取”，要抓住你掌控你，“执者失之”，越想抓住越想掌控，失去得越快。“或下而取”，其实我们在帮助别人的时候，也就获得了别人的这样一种真心的敬佩，遇到事情的时候才能够得到人家帮助。“大国不过欲兼畜人”，大国想要更强大，就得需要更强大地支持，大国就得团结更多的小的国家，形成一个相互支持、相互帮助的局面。我给大家举一个例子，大家对这个问题就理解更深刻一点。我们中国文化的图腾——龙，大家都熟悉，我们叫“龙的传人”。可是，龙在自然界里面是没有的，它是怎么形成的呢？原来这些氏族部落，我们也可以把它看作是一个一个小的国家，那个时候他们互相征战、合并。龙的主体的部分就是蛇图腾，源自中原地区一个力量非常强大的部落，后来这个部落把很多小的部落合并到自己大的部落里边，它们收归一个部落就加上一个部落的图腾，这样，逐渐形成了龙的样子：蛇的身，马的头，鬣的尾……这不就是“兼畜人”吗？其实落到国家的层面也是一样，形成了一个团结的阵营，当然最好是正义的，遇到事情力量不就强大了吗？“大国不过欲兼畜人，小国不过欲入事人。”小国不过也想加入这个里面，大家一起做事，遇到事情的时候，大国还可以帮助、支持，这不是挺好的事儿吗？各得其所，所以叫“夫两者各得其所欲”，都得到自己所想要的。话讲完了，下边这句话又来了，“大者宜为下”，越是大的国家，越是位置高的人，越要懂得善于处下。</t>
-  </si>
-  <si>
-    <t>第六十二章（62）</t>
-  </si>
-  <si>
-    <t>道者万物之奥，善人之宝，不善人之所保。美言可以市尊，美行可以加人。人之不善，何弃之有？故立天子，置三公，虽有拱璧以先驷（sì）马，不如坐进此道。古之所以贵此道者何？不曰以求得，有罪以免邪？故为天下贵。</t>
-  </si>
-  <si>
-    <t>道是万事万物的奥妙所在，是善良的人珍贵的宝贝，是不善的人得以拯救的保障。说好的话、正确的话可以得到人们的尊重，美好的品行可以增加人的尊贵。品行不善的人，为什么就要把他抛弃掉？所以在天子即位时，设置三公，用珍贵的玉璧在前、驷马在后的礼仪来进奉，都不如静坐修道（把大道传授给他们）。为什么自古至今都把道看得这么珍贵呢？不就是因为按照道去做，我们所希望的就能得到，我们的过错就能改正免除吗？所以大道被天下人所尊崇。</t>
-  </si>
-  <si>
-    <t>这一章比较难理解，先说一下这一章的断句，有很多不一样的版本。现在大家基本上能够认可的是“美言可以市尊，美行可以加人”，有的本子是“美言可以市，尊行可以加人”，断句的差别就在这两句上。这一章讲什么呢？这一章是讲“道”的重要性，“善人之宝”，善人要不停地按照道去做，是善人的宝贝。但是，不善人也不会被道所抛弃，道可以来拯救他，所以叫“不善人之所保”。现在我们从头来解释。“道者万物之奥，善人之宝，不善人之所保。”这个道是万事万物的奥妙之所在，所以它是“善人之宝”，是善良人的珍贵的宝贝，也是“不善人之所保”，是不善人得以被拯救的保障，道可以拯救这些走错路的人，让他回到正道上来。“美言可以市尊”，美言，好的话。说好的话、正确的话，它可以得到人们的尊重。“美行可以加人”，好的品行，可以增加人的尊贵，团结更多的人。其实这个道理也比较容易理解，我们熟悉的三个人——魏徵、李世民和长孙皇后。魏徵是美言，他劝李世民，你要做一个好皇帝，有些事你不能做。李世民很愤怒，回来之后在家里边发火，说要把魏徵给杀掉。长孙皇后反而衣服穿得很整齐，给他道喜，说你遇到了一个好的臣子，我应该向你贺喜。李世民后来领悟到这一点，他说镜子可以正衣冠，魏徵就像一面镜子可以正我的品行。历史上，三个人留下的都是美言，都得到了人们的尊重，所以叫“美言可以市尊”。既然道是“善人之宝，不善人之所保”，那么“人之不善，何弃之有”。有的人走错路了，你为什么就觉得要把他抛弃掉？让他回到正道上来，用道去教化、去拯救。这是从正面来说它的作用。下面就讲的这个事就有针对性了。“故立天子，置三公。”国家的制度慢慢地有了天子，作为最高的领导者，还有三公——辅佐天子的最重要的职位。“虽有拱璧以先驷马”，古代敬献礼的时候，拱璧，捧着玉璧，捧璧的人在前边，乘着高头大马进献。珍贵吧？不如“道”珍贵！这里面有两个意思：一个就讲国家的制度，有天子，有三公，很重要，但这也只是形式。还有呢，用高头大马进献珍贵的玉璧，这也是很珍贵。但是“不如坐进此道”，这些都不如按照道来做，大道才是“万物之奥”，“万物之宝”。“古之所以贵此道者何？不曰以求得，有罪以免邪？故为天下贵。”意犹未尽，讲到这地方，《道德经》还觉得这个话就应该再强调一下，说古往今来，为什么都要把这个道看得这样珍贵呢？“古之所以贵此道者何？”不就是说你按照道去做，你才能得到自己真正想要得到的吗？“以求得”，你要的那个东西才能真正得到。这里的“以求得”并不是像我们烧香拜佛求得发财。“有罪以免邪”，因为前面讲过，“不善人之所保”，就算走错路了，但是我们重归正道，浪子回头金不换，原来的这个罪，也能得以补偿。这个并不像有的宗教里边说你犯了什么罪去忏悔一下，这个罪就免除了，它是让你按照大道来做，回到正道。我们来分分类，人不就是这两类：“善人”、“不善人”，对那些不善良的人，走错路的人，你为什么要抛弃他呢？“坐进此道”，回归此道就可以啊。弄了那么多的官职，天子、三公，有那么多珍贵的财宝，拱璧、驷马，还不如“坐进此道”。既然如此，“道”就是天下人最珍贵、最宝贵的，“故为天下贵”。</t>
-  </si>
-  <si>
-    <t>第六十三章（63）</t>
-  </si>
-  <si>
-    <t>为无为，事无事，味无味。大小、多少，报怨以德。图难于其易，为大于其细。天下难事必作于易，天下大事必作于细。是以圣人终不为大，故能成其大。夫轻诺必寡信，多易必多难。是以圣人犹难之，故终无难矣。</t>
-  </si>
-  <si>
-    <t>用无为的态度、方式来作为，用不找事、不多事的方式来做事，最好的味道反而是没有味道。以小为大，因为大事都从小事做起；以少为多，因为积少才能成多。用德来对待别人的怨。对付困难事情要在它还容易解决的时候开始，成就大业要从很小的事情做起。天下所有的难事都是从容易的做起，天下所有的大事都是从小事做起。因此圣人始终不去直接做大事，不说大话空话，所以最后能成就大事。没有把握的事轻易许诺别人一定会失去别人的信任，把事情看得太容易一定会遇到更多的困难。因此圣人把所有事情都看得很难，反而没有什么难事。</t>
-  </si>
-  <si>
-    <t>第六十三章的内容，我们在前边已经有所接触。之前我们说，第二章就是《道德经》的“目录”，第二章列出来了后边讲的六个重要内容，有无相生、难易相成等等，这一章的核心就是“难”和“易”。这一章的核心意思就说，要想做大事，先从小事做起，想要以后攻坚克难，你得从容易的事情做起。还有一个重要的问题、重要的智慧：你要把容易的事情当作难的事情来做，要有充分的、认真的准备，提前思考它的步骤、程序、会遇到的问题，这样再出什么问题的时候，你就能从容应对。有这样的态度，天下也没什么难事。天下无难事，但天下都是难事，看你怎么对待。开头这九个字非常有趣：“为无为，事无事，味无味。”“为无为”——想要有为吗？你得先懂得无为的道理。为什么？因为有些事你越有为，越强求，什么事都管，反而最后结果非常不好。道家讲的无为，就是按照道的方式来作为，想要有为，先要懂得无为的道理，不要妄为，要抓住关键，举重若轻，有所舍才能有所得，所以为无为。其实也就是第三十七章里边讲的“道常无为而无不为”，道的规律、规则是什么？用无为的方式达到无不为的效果，更好的效果。我再强调一下，《道德经》里出现得最多的一个词是“天下”。《道德经》针对的是天下，千万不要把道家当作一种消极的被动的思想，它是“想为”，但是强调要通过正确的道路和手段，懂得无为的正确的道路和手段，才能达到真正的有效的为，也就是用无为的方式，达到无不为的这种效果。下边再落一层，“事无事”。大家都想做事，可是大家有没有注意到，有些人他是“找事”，他是捣乱，是阻碍、多事，天下本无事，庸人自扰之。所以我们做事的时候要懂得无事的道理，不要多事，不要找事，不要刁难。尤其是做领导者，没事找事，权力就是刁难，你这不就麻烦了吗？“事无事”，想做事，得懂得无事的道理，不要多事，不要扰民。再落一层，“味无味”。我们经常讲一个词叫“真水无香”，真正好的饮料，就像那白开水一样，没有味道。我们饮食讲究清淡，寡味，少油少盐。最高的味道，反而是没有味道，无味。当然，这三个词核心还是“为无为”，让大家能够更明白一点。老子展开来讲，“事无事”，不要多事，不要扰民，不要刁难，就像“味无味”的道理一样。按照这样的一个逻辑推下来，下面四个字大家就能明白了，“大小、多少”，千万不要把它念成“大小多少”，这个东西就没意义了。这是告诉大家要“大其小”、要“多其少”，要把小事看得很重要，细节决定成败，千万不要忽略这个细节。为什么要“大其小”呢？因为天下的大事，都是从小事做起，为什么要“多其少”呢？因为积少才能成多。想要多，你得从少的一点一点积累，积少成多。就像我们学习《道德经》，一章一章讲，一章一章学，不要着急，最后达到一个整体的理解。我们经常讲“聚沙成塔”、“集腋成裘”，这不都是“多其少”的道理吗？“报怨以德”，按照这种相反相成的道理，对别人的埋怨、恩怨，也应该站在一个“德”的角度，因为德是符合道，用道的东西里面去感化。第六十二章不是讲了吗？“人之不善，何弃之有？”人家有这个埋怨，怎么正确地对待呢？“报怨以德”。用这种智慧和层次，让大家一起能回归到正途，回归到正道。“图难于其易，为大于其细。天下难事必作于易，天下大事必作于细。”这几句话，在我们文化里边名气非常大，因为讲的是哲学上的量的积累达到质的变化的道理。“图难于其易”，“图”就是图谋、计划。你计划想要做难的事情，要从容易的事情做起。“为大于其细”，想要做大的事情，得从小的事情一步一步来。我们大家都知道要脚踏实地，循序渐进，有条不紊，一屋不扫，何以扫天下？“天下难事必作于易”，天下所有的难事，都要从容易的事情做起。就像小孩的培养，让他们在处理小的事情中就形成良好的习惯，把小的事情、容易的事当成培养良好习惯的重要途径，将来，小孩在遇到大事、难事都能从容应对。现在很多人都有一个致命的弱点，大概是人的通病，就是好高骛远，老觉得自己应该是做大事的人，对小的事情不屑一顾。《道德经》就告诉我们这个智慧：想要做难的事情，从容易的事情做起；想要做大的事情，从小的事情做起，“天下大事必作于细”。“是以圣人终不为大，故能成其大。”“是以”，“是”就是这样，“以”就是所以。所以有智慧的领导者就是这样：“终不为大”，不是老说大话，不是老给大家画饼充饥，而是脚踏实地，一步一步地做起，“故能成其大”。一步一步把这个事情完成了，一步一步地完成计划，最后实现一个大的蓝图，好的结果，水到渠成。所以一个有智慧的人，不是老用那些虚幻的东西来画饼充饥，老是给大家讲大话、空话。“终不为大，故能成其大”，最后反而成就了大事，这话讲得非常好。我建议大家学习《道德经》，有一种重要的学习方法，就是反复看。有的人看《道德经》，也许一年就看一章，反复地看，反复地体会，“少则得，多则惑”，“终不为大，故能成其大”。以管窥天，以锥扎地，我们视力更集中，这样把这个事情才能做得更踏实，扎得更透。我们每一次的进步，虽然看起来好像只是一点点，但是这一点点积累起来就不得了了，“终不为大，故能成其大”。“轻诺必寡信”，大家还记得我们在讲《道德经》第八章的时候，就讲过“言善信”，我们中国人喜欢拿潮水作为讲信用的代表和象征，所以，有一个词就叫“潮信”。你看那钱塘潮每到农历八月十八前后就来了，人也应该如此，说话要讲信用，要有诚信，能给别人做成的事我们再去允诺，没把握做成的事，不要轻易去答应，不管我们有多热情。如果我们答应人家的很多事最后都做不成，时间长了，人家一定认为我们是食言而肥，不讲信用。《道德经》讲话是比较宽缓的，但这句话用的就是强逻辑判断，“轻诺必寡信”，这不是对我们委婉的劝告，这简直就是对我们严厉的警告。所以要讲诚信，君子重一诺，一诺千金嘛，所以“轻诺必寡信”，要避免这种结果出现。“多易必多难”，你把这个事情看得很容易，做什么事情，最后一定出问题。世界上哪有容易的事情，吃个饭喝个水，这都需要功夫，需要本事，小事情我们都要认真对待。我们经常讲“小河沟里翻船”，把一个事情看得太容易了，太简单了，往往会在这个事情上出问题。面对很多难的事情，大家战战兢兢，小心谨慎，反而没事，反而就是在一些认为最容易的事情出问题。很多学生做题、考试也是一样，难题没事，在容易的题上，出了问题，回去捶胸顿足，懊悔无比。所以，我们平常要形成一种把容易的事情当作难的事情来做的习惯，你要懂得“多易必多难”，凡事太容易，后面一定会出现很多的困难，出现很多的问题。所以，下边这句话就讲：“是以圣人犹难之”，所以有智慧的人，把这容易的事情都看作很难。天下的事情都当作难的事情来做，反而结果没有什么难的事情，“故终无难矣”。这个道理非常有趣，其实就是相反相成的道理，这个叫“难易相成”。世界上有没有难事呢？有，也没有。你把这个难的事情当作难的事情，看作是无法克服的，它就是难的事情；你把容易的事情当作容易的事情，没有认真对待，最后也会变成难的事情。我们把容易的事情当作难的事情来做，最后那个难的事也就做成了；真正难的事情，我们认真准备，有充分的信心，最后这难的事情也就克服了。“故终无难矣！”世上无难事，这就是“难易相成”的智慧。很多事情，决定于我们的想法、态度，态度不同，难易之间就会相互转化。</t>
-  </si>
-  <si>
-    <t>2、8、64</t>
-  </si>
-  <si>
-    <t>第六十四章（64）</t>
-  </si>
-  <si>
-    <t>其安易持，其未兆易谋，其脆易泮（pàn），其微易散。为之于未有，治之于未乱。合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。为者败之，执者失之。是以圣人无为，故无败；无执，故无失。民之从事，常于几成而败之。慎终如始，则无败事。是以圣人欲不欲，不贵难得之货；学不学，复众人之所过。以辅万物之自然，而不敢为。</t>
-  </si>
-  <si>
-    <t>局面稳定的时候容易掌控，事情没有征兆（国家还没有出现动乱）的时候容易去谋划/对付，事物脆弱时，容易消除，事物微小时，容易消散。在危险局面还没有发生的时候就做好准备，在国家还没有混乱的时候就注意治理。合抱（两个人用手臂围起来，能够环抱住）的大树，都是从细小的萌芽一点一点长起来的。九层的高台，也是一层一层的土积累起来的。想要走千里的路，就要从脚下一步一步走起。强为、妄为就会失败，执意把控就会失去。所以圣人不强为、不妄为，所以不会失败；不强执、不固执，所以不会失去。众人做事常常在快要接近成功的时候惨遭失败。在事情快要做完的时候还像一开始时候那样谨慎、慎重，就不会有失败。所以圣人所想的都是别人不愿意去想的，不以难得的货物为珍贵；学别人不愿意学的，对别人的错误引以为鉴。圣人顺应着万物的自然天性去帮助它们成功，而不敢按照个人意志去做事。</t>
-  </si>
-  <si>
-    <t>第六十三章、第六十四章讲的道理，就是大家熟悉的量变和质变的道理，量的积累达到质的变化。但是大家注意，这个量的积累，有向好的方面，也有向不好的方面。前面讲了“为大于其细”，要做大事，从小的事情做起，这样才能最后达到想要的结果，假如积累的是一个不好的量，最后就积重难返。第六十四章一开始就要把两个方面，都给大家做了说明，有的事情在它刚出现向坏的方面发展苗头的时候，我们在这个阶段就把它解决了。这一章里有两个非常重要的内容，一个是大家都熟悉的一段话：“合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。”第二个就告诉我们，做事情要“慎终如始，则无败事”。这两个重要内容，我们先有一个直观的认识，再来读就好理解了。我们一句一句来解释。“其安易持”，“安”就是稳定，局面稳定的时候，容易掌控，就像一个东西，它稳定的时候，你容易把它把握住；它活蹦乱跳的时候，你把握起来就困难了。“其未兆易谋”，“未兆”，没有征兆的时候，苗头还没有开始的时候，容易去谋划。“其脆易泮”，脆的时候一打就打散了。“其微易散”，很微小的时候，很容易把它解散。比如说一件事情，很小的时候，人数很少的时候，你把它处理起来很容易。众怒难犯，一大群人轰起来、闹起来的时候，这事情解决起来就困难。前面告诉大家这些现象，然后告诉大家处理的方法。什么方法呢？“为之于未有”——在事情没有出现的时候，没有开始的时候，要有预见性，就要有作为，凡事预则立，不预则废。“治之于未乱”，还没有出现这种乱象的时候，就把它治理了、解决了。这也是习近平讲话时经常引用的两句话。怎么来理解呢？先给大家说第一个例证。有一次晏子出巡，齐国发大水，把一座石桥给冲毁了，晏子就把自己的船让给了灾民，大家都赞誉晏子爱民如子。然而一位有智慧的高人就批评晏子，就说你做这个国家的宰相，齐国发大水能把一座桥梁冲毁，你都没有预见到，没有提前做出预防，你失职。所以应该是怎么样？“为之于未有”，你别等这个事情都已经成为这个样子，再去处理它，不管你处理的方式多么巧妙，多么有智慧，但是不如让这件事情没有发生。另外一个例证更能说明这个道理。有一次，扁鹊的国王问扁鹊：扁鹊你名气太大了，你是不是国家医术最高的？扁鹊说不是，别人我不知道，起码我大哥、我二哥都比我的医术高。所以这个国王就很奇怪，你大哥、你二哥是谁？他们医术那么高，怎么大家都不知道他们呀？扁鹊就说，我大哥怎么治病的呢？人家还没有病，他告诉人家怎么预防、怎么不得病。这不是“为之于未有”吗？提前就有作为了，预防得病。我二哥怎么治病的呢？人家刚有一点小病，他就把人治好了，不让他酿成大病，“治之于未乱”。所以我们经常讲，凡事预则立，不预则废，要有远见，要有预见，要未雨绸缪。这是讲负面，因为有些事情量的积累是向不好的方面发展的，所以要提前把这个问题给处理掉。下面讲的这个事，非常重要。我们做大事情都要从容易的事情、小的事情，一步一步积累才能达到这种质的变化，要脚踏实地，循序渐进。因为什么呢？“合抱之木，生于毫末”，合抱之木，它是一点一点长起来的。“九层之台，起于累土”，中国文化中，三六九都代表着高、多。那么高的高台也是一层一层土积累起来的。“千里之行，始于足下”，走这么远的路，要脚踏实地一步一步地做起。说到这里，我得加一句，有人老认为道家思想是消极的、被动的、无为的。“合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。”这不就是自强不息吗？所以有些事我们不能人云亦云，我们得看原文，以原典作为证据。“为者败之，执者失之。”“为”就是强为、妄为。因为《道德经》讲的真正的为叫“无为”，就是按照道的方式来作为，不按照道的方式来作为就是强为、妄为。越是强为，最后的结果越糟糕，因为量的积累还不到，你老想强行地发生质变，这不是急躁冒进吗？“执者失之”，就像我们抓沙子一样，你握得越紧，流出来越多，越想用力地把它抓住，反而失去得越来越快。所以一个有智慧的领导者，“无为”，按照道的方式来作为，不妄为，不强为，不多为，有所不为，所以也不会有急躁冒进的失败。“无执故无失”，没有这样的强执，最后也不会失去。“民之从事”，平常人做事，或者说领着大家做事，在什么时候最容易把事情给做砸了呢？“常于几成而败之”，经常在快要接近成功的时候，把事情给做砸了。那应该怎么办？“慎终如始，则无败事。”什么叫慎终如始呢？我先给大家打一个比方，大家走在结着冰的冰面上的时候，刚一下到冰面上都是小心谨慎，战战兢兢。走一会儿，觉得自己走熟了，就放松警惕了，有的干脆最后开始跑了，有的甚至在冰面上炫耀，危险往往就在这个时候发生了。所以我们中国人经常讲一句话叫“行百里者半九十”，一百里的路，走到九十里路的时候，还要当才走了一半，越是剩下那一段的时候越紧要，民间讲“编筐编篓，全在收口”，即最后这个结尾。“慎终如始”，走到最后那几步，还像开始下到冰面上一样小心谨慎，一步都不放松，那就没什么败事，没什么事情做不成。“慎终如始，则无败事”，就是我们现在经常讲的不忘初心，善始善终，那就没有什么事情做不成的。“是以圣人欲不欲”，一个有智慧的人，特别是一个有智慧的领导者，想要的东西是什么呢？是别人都不关心的，都不想要的。因为“天下熙熙，皆为利来；天下攘攘，皆为利往”，大家关心的是获取利益的方式方法，而一个有智慧的人，有智慧的领导者，应该有这种无功利之心。“欲不欲”，别人都不想这样的，反而是你应该考虑的。大家都针对“有”的东西，这有智慧的人、好的领导者得针对这无形的东西：人的精神财富，人的精神世界，人的修养。既然“欲不欲”，你跟一般人的欲望不一样，他们认为那个东西是珍贵的、难得的，反而在你的眼里是不重要的，不把它看作是难得的。领导国家的时候也是如此，第三章讲的，“不贵难得之货，使民不为盗”，形成一种淳朴的风气。“学不学，复众人之所过。”《道德经》讲的道理，叫“绝学”，一般人不愿意学，学这个东西能带来什么样的好处、利益吗？人的境界高的时候，学的很多的东西不就是和一般人不一样的嘛。一般人不愿意学的东西，又花功夫，又不能带来什么实际的利益，可是“学”这些东西代表了真正的智慧与学问。学这些东西干吗呢？“复众人之所过”，这个“复”不是重复，我们下围棋的人都知道有个词叫“复盘”，通过不断的重复模拟来检视，哪个地方下得好，哪个地方下得不好。别人犯的过错像复盘一样历历在目，以此为鉴，别再犯大家都经常犯的错误。“以辅万物之自然，而不敢为。”“以辅万物之自然”，就是按照自然的规律去做，追求的是一种水到渠成、自然而然的结果。“辅自然”就是无为。“而不敢为”，就是不敢妄为。因为我们违背了道，违背了自然规律，哪怕是短时间取得成功，其实也会受到更大的一种惩罚。这章告诉我们，一是我们做事情要“为之于未有，治之于未乱”，懂得预防，懂得不好的事情在苗头出现的时候就把它解决掉；二是我们做事情要脚踏实地，循序渐进；三是我们要“慎终如始”，不忘初心，善始善终，因为我们做事情经常在快要成功的时候，结果功亏一篑，所以要懂得这样一个道理。</t>
-  </si>
-  <si>
-    <t>第六十五章（65）</t>
-  </si>
-  <si>
-    <t>古之善为道者，非以明民，将以愚之。民之难治，以其智多。故以智治国，国之贼；不以智治国，国之福。知此两者，亦稽式。常知稽式，是谓玄德。玄德深矣，远矣，与物反矣，然后乃至大顺。</t>
-  </si>
-  <si>
-    <t>古代那些善于按照道来治理国家的人，并不是用大道使百姓变得聪明伶俐，而是使人民敦厚淳朴。百姓之所以难以治理，是因为他们奇技淫巧太多。所以用技巧来治理国家，是国家的灾难。不用技巧治理国家，是国家的福分。知道这两者的差别，这就是治国的法则。能够永远把握住这些原则，就可以说是具备了微妙高尚的品德。高尚的品德高远深邃，好像与一般事理相反，最后又返回了宁静朴实的根本，然而具有这样的品质之后办起事来却十分顺利。</t>
-  </si>
-  <si>
-    <t>这一章所涉及的，也是我们现在哲学里面经常讲的一个道理，叫“否定之否定”规律，讲事物的发展分为三个阶段，第一个阶段是肯定，第二个阶段是否定，第三个阶段是否定之否定。比如说麦粒长出麦苗，最后结出更多的麦粒，这就是一个否定之否定的阶段。第三个阶段常常重复第一个阶段的某些特征，却是在更高的程度上重复第一阶段的某些特征。这一章和第四十章讲的“反者，道之动”，所运用的哲学的智慧和道理是一样的，既然这样，把这个道理运用到治国上，应该如何呢？这就用到了一个我们大家熟悉的词，叫“返璞归真”，《道德经》认为治民最关键的是要使民风纯朴，不要那么多的技巧，不要那么多的套路。了解了这一点，我们再来看这一章，就明白了老先生的良苦用心。“古之善为道者”，以前的那些善于按照道来治理国家的人。“非以明民，将以愚之”，不是让百姓有那么多的心眼技巧。这个“愚”，不是愚民，而是敦厚、厚道，让人民的民风纯朴。“民之难治，以其智多。”百姓为什么难以治理？因为他心眼多、技巧多。“智”就是技巧、心眼、套路。“故以智治国，国之贼”，用技巧来治国，经常用骗术谎言，这是国家的灾难。“不以智治国，国之福”，不用这些技巧，让民风纯朴、敦厚，这个才是国家的福祉、国家的福分。“知此两者，亦稽式。”“稽式”就是法则。知道这两个的差别，这就是一个法则，治国的一个法则。“常知稽式”，“常”就是规律。按照规律，我们来了解这个法则。这叫什么？“是谓玄德”，“玄”就是深远的意思，这个就是深远的智慧与品德。下面这句话就是我一开头讲的，这个品德“深矣，远矣，与物反矣”，“与物反矣”不就是“反者，道之动”吗？我们都能看到事物的正向的发展，所以《道德经》经常提醒我们，“反者，道之动”，道是向它相反的方向运动，所以你理解问题也不能只看一面。“与物反矣”怎么解释呢？第二十五章，“大曰逝，逝曰远，远曰反”，最后又回到了它的根本。根本是什么？“归根曰静”。民心没那么多的躁动，变得清静宁静、敦厚朴实，这不就符合大道了嘛。“然后乃至大顺”，这样慢慢地就回归到了正确的道路，符合自然之道。所以，这一章讲的就一个问题：你用什么方式治国呢？要让民心变得纯朴、敦厚，返璞归真，没那么多的技巧，没那么多的套路，没那么多骗人的把戏，这样才是符合大道。</t>
   </si>
   <si>
     <t>第六十六章（66）</t>
@@ -3871,7 +3928,7 @@
         <v>264</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="G49" s="11"/>
     </row>
@@ -3880,19 +3937,19 @@
         <v>48</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G50" s="11"/>
     </row>
@@ -3901,19 +3958,19 @@
         <v>49</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="G51" s="11"/>
     </row>
@@ -3922,19 +3979,19 @@
         <v>50</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="G52" s="11"/>
     </row>
@@ -3943,19 +4000,19 @@
         <v>51</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="G53" s="11"/>
     </row>
@@ -3964,19 +4021,19 @@
         <v>52</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="G54" s="11">
         <v>6</v>
@@ -3987,19 +4044,19 @@
         <v>53</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>260</v>
+        <v>295</v>
       </c>
       <c r="G55" s="11"/>
     </row>
@@ -4008,19 +4065,19 @@
         <v>54</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="G56" s="11"/>
     </row>
@@ -4029,19 +4086,19 @@
         <v>55</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>260</v>
+        <v>305</v>
       </c>
       <c r="G57" s="11"/>
     </row>
@@ -4050,19 +4107,19 @@
         <v>56</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="G58" s="11"/>
     </row>
@@ -4071,22 +4128,22 @@
         <v>57</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>260</v>
+        <v>315</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
     </row>
     <row r="60" ht="409.5" spans="1:7">
@@ -4094,19 +4151,19 @@
         <v>58</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>260</v>
+        <v>321</v>
       </c>
       <c r="G60" s="11"/>
     </row>
@@ -4115,19 +4172,19 @@
         <v>59</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>260</v>
+        <v>326</v>
       </c>
       <c r="G61" s="11"/>
     </row>
@@ -4136,19 +4193,19 @@
         <v>60</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>260</v>
+        <v>331</v>
       </c>
       <c r="G62" s="11"/>
     </row>
@@ -4157,40 +4214,42 @@
         <v>61</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="G63" s="11"/>
+        <v>336</v>
+      </c>
+      <c r="G63" s="11">
+        <v>68</v>
+      </c>
     </row>
     <row r="64" ht="409.5" spans="1:7">
       <c r="A64" s="10">
         <v>62</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>260</v>
+        <v>341</v>
       </c>
       <c r="G64" s="11"/>
     </row>
@@ -4199,22 +4258,22 @@
         <v>63</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>260</v>
+        <v>346</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
     </row>
     <row r="66" ht="409.5" spans="1:7">
@@ -4222,19 +4281,19 @@
         <v>64</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>260</v>
+        <v>352</v>
       </c>
       <c r="G66" s="11">
         <v>63</v>
@@ -4245,19 +4304,19 @@
         <v>65</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="G67" s="11"/>
     </row>
@@ -4266,22 +4325,22 @@
         <v>66</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
     </row>
     <row r="69" ht="409.5" spans="1:7">
@@ -4289,19 +4348,19 @@
         <v>67</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="G69" s="11"/>
     </row>
@@ -4310,40 +4369,42 @@
         <v>68</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="G70" s="11"/>
+        <v>357</v>
+      </c>
+      <c r="G70" s="11">
+        <v>61</v>
+      </c>
     </row>
     <row r="71" ht="409.5" spans="1:7">
       <c r="A71" s="10">
         <v>69</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="G71" s="11">
         <v>17</v>
@@ -4354,19 +4415,19 @@
         <v>70</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="C72" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="F72" s="11" t="s">
         <v>357</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="E72" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="F72" s="11" t="s">
-        <v>260</v>
       </c>
       <c r="G72" s="11"/>
     </row>
@@ -4375,19 +4436,19 @@
         <v>71</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="G73" s="11" t="s">
         <v>240</v>
@@ -4398,19 +4459,19 @@
         <v>72</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="G74" s="11"/>
     </row>
@@ -4419,19 +4480,19 @@
         <v>73</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="G75" s="11"/>
     </row>
@@ -4440,19 +4501,19 @@
         <v>74</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="G76" s="11"/>
     </row>
@@ -4461,19 +4522,19 @@
         <v>75</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="G77" s="11">
         <v>10</v>
@@ -4484,19 +4545,19 @@
         <v>76</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="G78" s="11"/>
     </row>
@@ -4505,19 +4566,19 @@
         <v>77</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="G79" s="11"/>
     </row>
@@ -4526,22 +4587,22 @@
         <v>78</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>388</v>
+        <v>407</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
     </row>
     <row r="81" ht="409.5" spans="1:7">
@@ -4549,19 +4610,19 @@
         <v>79</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="G81" s="11"/>
     </row>
@@ -4570,19 +4631,19 @@
         <v>80</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="G82" s="11"/>
     </row>
@@ -4591,19 +4652,19 @@
         <v>81</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>260</v>
+        <v>357</v>
       </c>
       <c r="G83" s="11">
         <v>7</v>
@@ -4661,19 +4722,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>406</v>
+        <v>425</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="G2" s="3"/>
     </row>
@@ -4682,19 +4743,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="G3" s="4"/>
     </row>
@@ -4703,19 +4764,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>414</v>
+        <v>433</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>416</v>
+        <v>435</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -4724,19 +4785,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>420</v>
+        <v>439</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>421</v>
+        <v>440</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="G5" s="4"/>
     </row>
@@ -4745,19 +4806,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>424</v>
+        <v>443</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="G6" s="4"/>
     </row>
@@ -4766,19 +4827,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>429</v>
+        <v>448</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -4787,19 +4848,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>433</v>
+        <v>452</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -4808,19 +4869,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>437</v>
+        <v>456</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="G9" s="4"/>
     </row>
@@ -4829,19 +4890,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="G10" s="4"/>
     </row>
@@ -4850,19 +4911,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="G11" s="4"/>
     </row>
@@ -4871,19 +4932,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="G12" s="4"/>
     </row>
@@ -4892,19 +4953,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="G13" s="4"/>
     </row>
@@ -4913,19 +4974,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -4934,19 +4995,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="G15" s="4"/>
     </row>
@@ -4955,19 +5016,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>471</v>
+        <v>490</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="G16" s="4"/>
     </row>
@@ -4976,19 +5037,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>475</v>
+        <v>494</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>477</v>
+        <v>496</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="G17" s="4"/>
     </row>
@@ -4997,19 +5058,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>479</v>
+        <v>498</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>480</v>
+        <v>499</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="G18" s="4"/>
     </row>
@@ -5018,19 +5079,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>483</v>
+        <v>502</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>485</v>
+        <v>504</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="G19" s="4"/>
     </row>
@@ -5039,19 +5100,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="D20" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>488</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>469</v>
       </c>
       <c r="G20" s="4"/>
     </row>
@@ -5060,19 +5121,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="G21" s="4"/>
     </row>
@@ -5081,19 +5142,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="G22" s="4"/>
     </row>
@@ -5102,19 +5163,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>500</v>
+        <v>519</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>501</v>
+        <v>520</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>502</v>
+        <v>521</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="G23" s="4"/>
     </row>
@@ -5123,19 +5184,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>504</v>
+        <v>523</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>505</v>
+        <v>524</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="G24" s="4"/>
     </row>
@@ -5144,19 +5205,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>508</v>
+        <v>527</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>509</v>
+        <v>528</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="G25" s="4"/>
     </row>
@@ -5165,19 +5226,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="D26" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>513</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>514</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>494</v>
       </c>
       <c r="G26" s="4"/>
     </row>
@@ -5186,19 +5247,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>518</v>
+        <v>537</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="G27" s="4"/>
     </row>
@@ -5207,19 +5268,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>520</v>
+        <v>539</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="G28" s="4"/>
     </row>

--- a/book.xlsx
+++ b/book.xlsx
@@ -4,15 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25068" windowHeight="13380"/>
+    <workbookView windowWidth="25068" windowHeight="13380" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="道德经" sheetId="1" r:id="rId1"/>
-    <sheet name="大学" sheetId="2" r:id="rId2"/>
+    <sheet name="道德经bak" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="道德经" sheetId="3" r:id="rId2"/>
+    <sheet name="大学" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">道德经!$A$1:$G$83</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">大学!$A$1:$G$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">道德经bak!$A$1:$G$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">道德经!$A$1:$G$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">大学!$A$1:$G$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="722">
   <si>
     <t>no</t>
   </si>
@@ -753,7 +755,7 @@
     <t>从前所有能够同大道保持一致的事物：天与大道保持一致 因而能够清明；地与大道保持一致 因而能够安宁；神与大道保持一致 因而能够有灵；河谷与大道保持一致 因而能够充盈；万物与大道保持一致 因而能够滋生；侯王与大道保持一致 因而能够做天下人的首领。如果放弃了大道，天无法清明，恐怕要破裂；地无法安宁，恐怕要废掉；神无法有灵，恐怕要绝灭；河谷无法充盈，恐怕要枯竭；万物无法滋生，恐怕要灭绝；侯王无法保持高贵的地位，恐怕要亡国。因此贵要以贱为根本，高要以下为基础。所以侯王自称孤、寡、不穀。这不正是以低贱为根本的表现吗？难道不是吗？想要获取过多的荣誉反而会失去荣誉。因此不要把自己看作是高贵的美玉，而应定位为一块丑陋的石头。</t>
   </si>
   <si>
-    <t>本章讲“得一”的力量和贵以贱为本。昔之得一者：天得一以清，地得一以宁，神得一以灵，谷得一以盈，万物得一以生，侯王得一以为天下正：天得道而清明，地得道而安宁，神得道而有灵，河谷得道而充盈，万物得道而生长，侯王得道而成为天下首领。“一”就是阴阳两者的统一，也就是道。其致之也：若失去道，天将裂、地将废、神将歇、谷将竭、万物将灭、侯王将蹶。故贵以贱为本，高以下为基：贵以贱为根本，高以下为基础。
+    <t>【以贱为本、以下为基】本章讲“得一”的力量和贵以贱为本。昔之得一者：天得一以清，地得一以宁，神得一以灵，谷得一以盈，万物得一以生，侯王得一以为天下正：天得道而清明，地得道而安宁，神得道而有灵，河谷得道而充盈，万物得道而生长，侯王得道而成为天下首领。“一”就是阴阳两者的统一，也就是道。其致之也：若失去道，天将裂、地将废、神将歇、谷将竭、万物将灭、侯王将蹶。故贵以贱为本，高以下为基：贵以贱为根本，高以下为基础。
 是以侯王自谓孤、寡、不穀：侯王自称孤、寡、不穀，正是以贱为本、以下为基。致数舆无舆：刻意追求众多荣誉反而失去荣誉。是故不欲琭琭如玉，珞珞如石：不要像华美的玉，要像坚硬的石头，石头能铺路济人，华美的玉看似高贵却少有用处。译者·韩鹏杰强调两个重点：一是“一”即道，是阴阳统一；二是“贵以贱为本，高以下为基”，位置越高越要善于处下，把根基打牢，做人要处实不居华。</t>
   </si>
   <si>
@@ -769,14 +771,14 @@
     <t>万物在大道的支配下向相反的方向发展。大道的作用就在于它能够提醒万物保持柔弱的状态。天下万物产生于某种物质，而物质产生于空间。（有和无是天下万物生成的根源）</t>
   </si>
   <si>
-    <t>本章只有三句话，却是全书思维总纲。反者道之动：道向相反的方向运动，事物发展到极点就走向反面，又终而复返，回到更高层次的本根。所以看问题不能只站在自己的角度，要换位思考、正反合地看：正面看、反面看、合起来看，才能全面。弱者道之用：道的作用体现在柔弱一面，大家都逞强，柔弱反被强调，这是阴阳统一的思维方式。天下万物生于有，有生于无：万物产生于有，有产生于无；任何事物都有有和无两个方面，有让我们观察边界，无让我们观察妙处。
+    <t>【事物发展到极点就走向反面】本章只有三句话，却是全书思维总纲。反者道之动：道向相反的方向运动，事物发展到极点就走向反面，又终而复返，回到更高层次的本根。所以看问题不能只站在自己的角度，要换位思考、正反合地看：正面看、反面看、合起来看，才能全面。弱者道之用：道的作用体现在柔弱一面，大家都逞强，柔弱反被强调，这是阴阳统一的思维方式。天下万物生于有，有生于无：万物产生于有，有产生于无；任何事物都有有和无两个方面，有让我们观察边界，无让我们观察妙处。
 译者·韩鹏杰强调，如果只看到有形东西的作用，忽略无形东西的作用，物质世界越发达，精神家园就越花果飘零；既要看到物质财富，更要看到精神、信仰、理论这些无形力量。前三章讲道，第四十章用三句话总结全书思维方式，后边各章都是它的展开和例证。</t>
   </si>
   <si>
     <t>德经 | 变化之道</t>
   </si>
   <si>
-    <t>2、25</t>
+    <t>2、25、65</t>
   </si>
   <si>
     <t>第四十一章（41）</t>
@@ -788,7 +790,7 @@
     <t>上等的士听到道，就会努力去实行；中等的士听到道，将信将疑；下等的士听到道，大声嘲笑。不被嘲笑，就不足以成为道了。所以古时候立言的人说过这样的话：光明的道路好像是昏暗不明的；前进的道路好像是后退的；平坦的道路好像是不平的。最高的德好像是山谷，最光明纯洁的内心好像是蒙受屈辱，广大的德好像不足的样子，刚健的德好像是软弱的样子，质性真的东西仿佛都是有缺点一样。最大的方没有棱角，最大的器件最晚做成，大音平时少讲话，关键时刻掷地有声，最大的形象没有形状。道隐藏于事物背后，没有名字。道善于帮助万物并成就万物。</t>
   </si>
   <si>
-    <t>前边《德经》的部分我们讲了第三十八章，“上德不德，是以有德，下德不失德，是以无德。”讲了第三十九章，第三十九章第一个重要的概念是“一”。我再重申一遍，是阴阳两者的统一，也就是道。第三十九章里边的重点词，我们要不断地重申、重复，以求达到大家的记忆。“贵以贱为本，高以下为基。”第四十章我们极为看重。因为这一章开头五个字，是整个这一本书里思维的总纲：“反者，道之动”，下边是它的具体的体现，“弱者，道之用。天下万物生于有，生于无。”现在我们具体来讲第四十一章，这一章内容也非常丰富。首先我们在前边就强调过，《道德经》是对面有人问问题，老子给予的回答。现在对面有人问关于“士”的问题了。“士”这个阶层，把它理解为做官的阶层也可以，“士”这个概念，它的原意就是做事。延伸意指的是一个领导阶层。推十为一嘛，十个人里边推举出来一个领导大家，服务大家，管理大家。所以有人问老子，你看这些士，怎么来判断他们境界的高低呢？水平的高低呢？老子也是拿道来评价的。所以在这一章里边，一开始老子就讲“上士闻道，勤而行之”，境界高的、水平高的士这个阶层这些人，听到了道，比如说他的领导者讲的话，他觉得有道，有道理，“勤而行之”，就是执行力最强，坚定不移地按照它去做。有问题呢？自己勤勉、勤奋地把它解决，“勤而行之”，知行合一了嘛。知道了就按照道去做。中等境界的是什么呢？“中士闻道，若存若亡”，将信将疑。也想去按照道去做，但是一遇到事了就怀疑了。“若存若亡”，将信将疑，迟迟疑疑，犹犹豫豫，执行力不够。“下士闻道，大笑之”。境界最低的、最差的是干吗呢？嘲笑。人家说什么，制定什么样的制度规则，他都嘲笑，讲什么他都觉得不对，但是又提不出建设性意见，什么叫建设性意见？你觉得人家这个不好，你有没有更好的方案？觉得有问题，客观地指出来、提出来怎么改进，不是为了嘲笑而嘲笑，不是为了讽刺而讽刺。我觉得现在很多语言类的节目只是为了讽刺别人，讲话的时候只是为了打击别人，没有其他什么善良的目的。所以这就属于“大笑之”。别人给他讲道理，他还在那嘲笑，甚至羞辱人家。当然对这个事老子是想得开的。告诉坐在对面问他问题的人，怎么接待这些人，对待这些问题。别当回事，不笑不足以为道。这个世界现在已经没有哪件事是大家都赞成的了，所以有人嘲笑这是正常的。你要跟这些人计较，那就把自己的生命全都浪费了。说到这儿我就得插一句话，我觉得这个境界的差别，格局的差别，心胸的差别在什么地方呢？就在对待攻击者的身上。你看孟子也是我们文化里非常不得了的一个人，但是你看孟子的书里，会有一个什么感觉呢？年轻人，气势太盛。孟子对待当时的一些学术大咖，比如说墨子，比如说杨朱，当时杨墨是显学，名气很大。孟子怎么来评价他们呢？孟子就说墨子这个人讲“兼爱，是无父也”。兼爱嘛，你都平等，没有差别嘛，你置于你父亲于何地？没有把你父亲凸显出来，没有把对父亲的爱突出出来，无父也。杨朱不是讲，“拔一毛而利天下，吾不为也”。大家不要误解这句话，它的原意是你拿天下来换我的身体，让我损害自己的生命去换天下，我不干。它是强调自己的生命的重要。“拔一毛而利天下，吾不为也”。杨朱讲“为我”，所以孟子骂他是无君。你老为自己，你把君置于何地？“无父无君是禽兽也”——他骂杨朱和墨子两个人是禽兽。反过来看老子对待这些人的态度是——“不笑不足以为道”，淡然一笑，过了——很值得人佩服的一种态度。这就叫“明月清风”。对待别人的嘲讽，对待别人的攻击，有这样一个态度，也是很不得了的一种智慧与境界。这一段是本章里边的核心。因为我觉得他上中下的这种区分非常明了，很实用。“上士闻道，勤而行之”。坐而论道，不如起来行嘛。大家看道字的写法，首是头脑、思维、想。“走”之旁是行。所以这个道本身就是一个知行统一的概念。“上士闻道，勤而行之。中士闻道，若存若亡。”犹犹豫豫，不坚定，不能够坚定坚持的按照道去做。“下士闻道，大笑之。”我们千万不要做这种老是嘲笑别人，讽刺别人的，否则就会落于下乘，不笑不足以为道，太好了。明月清风一般地对待这种嘲讽辱骂的这种态度。下面这一段开头这句话非常有意思，叫“建言有之”，“建言”就是我们说的常言。常言说得好，这是我们经常用的，所以下面这句话大家注意，不是他本人的话。就是告诉大家了，明确下边讲的很多都是常言，在当时就是一句俗语。他讲的这些道理都是什么呢？都是前边我们讲的“反者，道之动”的例证。所以我在前面给大家说，第四十章是全书的总纲，可以举的例证会无限多，下边都是。“明道若昧”，光明的道路好像是昏暗不明的。为什么？有些给你指出的光明大道说得多么多么得好，指出光明大道简直就是美得不得了，你要小心了，前面有陷阱。真正的大道，反而像是昏暗不明的，就是把路上的艰险，遇到的阻碍，遇到的问题，都给你说清楚，让你看得清楚，这才是明道。给你说这条路没问题，太直了，平坦了，你沿着这条路走，肯定光明无限；沿着这条路走，肯定兴旺发达，一点阻碍都不会有，这个事绝对没问题。坏事了，这个时候你就得小心了。要知道“明道若昧”。再举个关于“朋友”的例子说明这个问题。朋友有三类，友直，友谅，友多闻。第一类的朋友直率，你有问题给你直接指出来。你走的道有问题的时候直接告诉你，跟你讲，怕你犯错误，怕你在这个地方出现问题。不是你的朋友呢？你走在道上遇到什么问题与他有什么关系啊，你问他这条道怎么样？他就告诉你，好好好，走走走，这条路没有任何问题。你给我提点建议，没什么建议，走就是了。你掉到坑里边他管你呀！所以我们说这“明道若昧”，暗昧，昏暗不明。“进道若退”。我们有的时候自己老觉得自己进步太小，人有时候都不免太着急，老觉得“一万年太久，只争朝夕”。只争朝夕，我每天都得进步，我都得看到自己的进步，一感觉到自己没有进步，就着急了。其实你别忘了，人呢，走在路上没有直线的，“进道若退”，有时候我们感觉是退步的时候，其实我们是在进步。比如说练书法，大家都有这个感觉，刚练这几天觉得进步很大，我以后每天按照这个速度会很快成为书法大家，过一段时间感觉怎么回事？怎么我这字越写越差了，还不如开始呢。好多事情开始都是这样。其实这就是我们前进中的一个必然的现象。懂得以退为进，懂得退就是进，有时候退不就是进嘛。“进道若退”，这不就是相反相成嘛。所以我在想，在老子那个时代，你说这些常言都在。这得说中国古代的这些人的哲学的思维水平竟然达到这样一个高度。所以有的时候我们做的事情感觉退步的时候不要着急，退是前进中的必须经历的。就像我们经常讲一个词叫“能屈能伸”，想要伸不得先屈回来吗？这是不是退？退之后才更加有力量，进道若退。“夷道若颣”，颣就是不平，夷就是平，夷道就是平坦的路。真正平坦的路像什么？它是不平的，高低起伏的。为什么？开车人都有一个体会，你说开车的路太平坦了，这就很容易放松警惕了，感觉无聊疲惫了，就很容易出事。假如前边一会儿出现一点坡，则高度警惕，有的不是故意把道做得有坡嘛，这才是平坦的道。所以我们经常讲的一句话叫“曲折是一种常态”，平坦的大道里边有这样的一些坡，不平的地方，这才是真正的大道。它告诉我们的道理就是，其实我们走在路上不会是绝对平坦的。对路上遇到的这些，我们要有高度的戒备和警惕，这样才属于真正的夷道，也就是平坦的大道。“夷道若颣”，又是一个“反者，道之动”，相反相成。“上德若谷”，谷就是无穷无尽。我们经常讲不是虚怀若谷嘛，真正有“上德”的这些表现是什么？就像虚怀若谷。比如说谦虚，听得进别人的意见，比如说做了好的事情，自己把它像山谷里的风一样，过而无形，“上德若谷”，就是讲它“满招损，谦受益”，不自满，做了事情不居功自傲，“上德若谷”。“大白若辱”，“白”，我们在第二十八章讲过，知白守黑，那个时候给大家说过白，白就是内心的光明信念与远大的抱负，内心有光明、信念和远大的抱负，那他就能忍受很多的屈辱。为什么？能屈能伸嘛，有远大的抱负，那么这些羞辱也就不必被自己挂在心中了。知白守黑，内心有光明、信念和远大的抱负，才能守得住这个黑。不管是别人黑，还是有时候的这种自黑，这就是“大白若辱”。说一事，有一次我在云南楚雄给医生讲课。我说你们穿着白大褂，大家把你们叫“白衣天使”，那对病人偶尔几句话不合适的话，也应该不那么太在意了。因为“知其白，守其黑”，忍得屈辱、羞辱，吞得下委屈，也就扩大了格局。“广德若不足”，“广”当然是大的意思。越是有广博的、大的德的人，反而好像自己有缺陷，不足就是不满，满招损，谦受益嘛。知道自己有不足，大成若缺，才能不断地进步，不断地学习，不断地努力，提高自己的境界，让自己的德行更伟大、更广博，“广德若不足”。下面这四个字理解起来不太容易，叫“建德若偷”。这个“偷”字是大家不喜欢的，怎么能跟德并列到一块呢？说到一起呢？首先我们说这个“建德”是什么意思？刚健。刚健的德好像是软弱的样子。这不就又符合“反者，道之动”了吗？偷，懒惰、懈怠、疲软，有着刚健的德的人，他反而正好有的时候表现为他的反面，而不是说我认为自己有这种刚健的德，谁要惹到我了，我一定跟他较量到底，我一定坚咬不放。这其实反而不是刚健的德，也不是强的真正的表现。刚健的德往往表现出宽容，忍让，甚至软、弱、懈怠等，“建德若偷”。当然有人也把这个“偷”解释为偷偷摸摸，意思就是不去表现。这个也说得过去。“质真若渝”，这个“渝”和我们讲的“瑕不掩瑜”意思相似，真的东西不会是完美无缺的。“大方无隅”，最大的方是没有棱角的，没有棱角那不就成了圆了吗？所以我们经常讲“外圆而内方”。“大方无隅”，没有角落，不留死角，这才是真正的大方。其实再说一遍，大家仔细想，这大方已经变成圆了，因为咱们中国人对这个圆的印象非常好。所以老用圆满这样的词来形容一个好的事情。进而言之，人有了这个原则是对的，但是这个原则不是老去像割伤别人，外面是圆的，可以和外界相衔接。而内部方的，坚守自己的原则，所以这叫大方无隅。“大器晚成”，最大的器件最晚做成。这个很好，提醒我们不用着急。想终成大器吗？那就要踏踏实实，不断地努力，不断地学习，机会总是留给有准备的人。心智不成熟的时候，早出名并没有什么太大的好处。因为人早出名，心智不成熟，他一定就气锐，盛气凌人，盛气凌人则敛怨。就会得到很多来自各方很多的这种怨言，而这个就形成自己未来的一种发展的阻碍。所以古人讲，松柏必经岁寒之后，可从栋梁之任。你看松树、柏树经历一次又一次的寒暑的磨练，最后才可成为栋梁之材。人类历史上大器晚成的例子比比皆是，比如，姜子牙八十岁为相。历史上记载了很多人，都是在有准备的情况下遇到机会，把以前自己积累的经验、智慧，充分地发扬出来，终成大器，人生最坏的结局也不过是大器晚成，又有什么可着急，可焦虑的呢？“大音希声”，“希”不是没有。这个“希”大家可以从两个角度来理解，一个“希”是前面有声，而中间出现的停顿，比如，白居易的《琵琶行》，“别有幽愁暗恨生，此时无声胜有声。”前面有声，可是这个地方的停顿，它反而蕴含了更加丰富的内容，用有声表达不出来的这种情感，这是一个希声。“希声”还有一个表现是乐曲结束，声音之后的余响。苏轼的《前赤壁赋》里边叫“余音袅袅，不绝如缕”。这一个也是“大音希声”。《道德经》里面讲的“大音希声”的道理，其实它是有延伸的。一个是说我们的语言。第五章里边讲“多言数穷，不如守中。”发号施令多了，话多了，声多了，唠叨多了，就不起作用了。真正的大音呢，一定是平常少讲，关键时候掷地有声，说得恰到好处——大音希声。一个是说我们的制度。制度太繁琐了，反而它走向了负面，恰到好处就好。“大象无形”，这个在我们前边讲的时候也经常引用。“大象”本来就很大了，反正中国人一开始指的这个“象”，也是拿这个“大象”说事，本来就很大的。当然这个“象”是一个延伸。最大的形象是没有形状的。天有形状吗？风有形状吗？精神有形状吗？理论有形状吗？都没有，“大象无形”。虽然无形却力量巨大。所以我们拿风来说大象无形是最恰当的。没有人看见过风，风是没有形状的，我们只能够通过水面的波纹，麦浪的翻滚，柳梢的摇曳，我们知道风是存在的。虽然无形，但是它客观存在的，并且力量无比巨大。所以我们写文章才经常用这样的词，“民风”“党风”“作风”“家风”。风没有形状，但是力量巨大，“大象无形”，就像道一样。拿什么东西来比方这个道最为恰当？那就是风。道就像风一样，你看不见但它无处不在？“大象无形”。前边这些其实都是一些相反相成的例证，尤其是“大白若辱，大器晚成，大音希声，大象无形”，都已经成了我们生活中常用的成语了。就这一章里边的成语，你算算就有多少！咱们也不说这本书别的方面的价值。单说它在让我们了解中国文化中的成语的角度，它的作用就有这么大，而且这些成语直到今天，我们还经常使用，发挥着巨大的作用。所以，我们说文化，“文”就在这儿。你把它变成自己的，化入自己的内心，化入自己的精神世界，就叫“文化”。大象无形，却力量无尽，永远存在。道隐无名，道是没有名的。你没办法定义它的。第二十五章的时候我们就讲“有物混成，先天地生，寂兮寥兮”，“寂”就是无声，“寥”就是无形。它是无形无声的，你没有办法去定义它。道隐无名，它就隐到事物的背后，但是它却是事物的本质。道隐无名，就像风一样，在万事万物的背后你看不见，但它能吹绿万物，它能够摧枯拉朽，作用无比巨大。下边这句话就好理解了，“夫唯道”，也只有道啊，“善贷且成”，“贷”就是帮助，意思是资助万物，贷款给你，不就是资助你嘛？善于帮助万事万物成长、成功。“道”有多伟大，你看不见。“道”也不求回报，但它帮助万事万物成为现在这个样子。本章内容非常深刻。首先，有一个恒定的标准“道”来衡量事物。“士”可以分出上中下：“上士闻道，勤而行之；中士闻道，若存若亡；下士闻道，大笑之。”胸怀宽广的人对待这事情，如清风掠过，淡然一笑。你笑你的我笑我的，你不笑不足以为道。没有哪一件事情非得是全部大家都认可的。做事情按照“道”去走，被人嘲笑，被人嘲讽，这是正常的。内心应该有这样的宽容，有这样的接纳，有这样的态度。所以下边告诉大家，那个时代的一些常言、俗语，作为第四十章“反者，道之动”的例证：“明道若昧，进道若退，夷道若颣，上德若谷，广德若不足”。我把这两个排列在一块，然后再说“大白若辱”“知白守黑”。是说什么羞辱都受不了的人，受到一点羞辱就暴跳如雷的人，甚至只是自以为受到了羞辱就拔拳相向的人，其实就是自以为刚健而事实上是匹夫之勇，往往会“勇于敢则杀”，所以真正刚健的德反而像软弱的一样。真的完美的东西是有瑕疵的一样，即大成若缺。所以要懂得“知白守黑”，“知荣守辱”。这几个成语前边带过了之后，重点强调“大器晚成”——不着急，有准备终成大器，机会终究会有的。“大音希声”，真正的大音不是絮絮叨叨，而要掌握尺度，“多言数穷，不如守中”，“无声胜有声”，所以要懂得无言之教，大音希声。接着，“大象无形。道隐无名，夫唯道善贷且成”。只有“道”才能善贷且成，资助万物，帮助万物成长，帮助万物成功。这一章给人很多的启发，很多的回味。每个人读，都会有不同的感受。随着年龄的增长，我们也会不断获得新的体会。</t>
+    <t>前边《德经》的部分我们讲了第三十八章，“上德不德，是以有德，下德不失德，是以无德。”讲了第三十九章，第三十九章第一个重要的概念是“一”。我再重申一遍，是阴阳两者的统一，也就是道。第三十九章里边的重点词，我们要不断地重申、重复，以求达到大家的记忆。“贵以贱为本，高以下为基。”第四十章我们极为看重。因为这一章开头五个字，是整个这一本书里思维的总纲：“反者，道之动”，下边是它的具体的体现，“弱者，道之用。天下万物生于有，生于无。”现在我们具体来讲第四十一章，这一章内容也非常丰富。首先我们在前边就强调过，《道德经》是对面有人问问题，老子给予的回答。现在对面有人问关于“士”的问题了。“士”这个阶层，把它理解为做官的阶层也可以，“士”这个概念，它的原意就是做事。延伸意指的是一个领导阶层。推十为一嘛，十个人里边推举出来一个领导大家，服务大家，管理大家。所以有人问老子，你看这些士，怎么来判断他们境界的高低呢？水平的高低呢？老子也是拿道来评价的。所以在这一章里边，一开始老子就讲“上士闻道，勤而行之”，境界高的、水平高的士这个阶层这些人，听到了道，比如说他的领导者讲的话，他觉得有道，有道理，“勤而行之”，就是执行力最强，坚定不移地按照它去做。有问题呢？自己勤勉、勤奋地把它解决，“勤而行之”，知行合一了嘛。知道了就按照道去做。中等境界的是什么呢？“中士闻道，若存若亡”，将信将疑。也想去按照道去做，但是一遇到事了就怀疑了。“若存若亡”，将信将疑，迟迟疑疑，犹犹豫豫，执行力不够。“下士闻道，大笑之”。境界最低的、最差的是干吗呢？嘲笑。人家说什么，制定什么样的制度规则，他都嘲笑，讲什么他都觉得不对，但是又提不出建设性意见，什么叫建设性意见？你觉得人家这个不好，你有没有更好的方案？觉得有问题，客观地指出来、提出来怎么改进，不是为了嘲笑而嘲笑，不是为了讽刺而讽刺。我觉得现在很多语言类的节目只是为了讽刺别人，讲话的时候只是为了打击别人，没有其他什么善良的目的。所以这就属于“大笑之”。别人给他讲道理，他还在那嘲笑，甚至羞辱人家。当然对这个事老子是想得开的。告诉坐在对面问他问题的人，怎么接待这些人，对待这些问题。别当回事，不笑不足以为道。这个世界现在已经没有哪件事是大家都赞成的了，所以有人嘲笑这是正常的。你要跟这些人计较，那就把自己的生命全都浪费了。说到这儿我就得插一句话，我觉得这个境界的差别，格局的差别，心胸的差别在什么地方呢？就在对待攻击者的身上。你看孟子也是我们文化里非常不得了的一个人，但是你看孟子的书里，会有一个什么感觉呢？年轻人，气势太盛。孟子对待当时的一些学术大咖，比如说墨子，比如说杨朱，当时杨墨是显学，名气很大。孟子怎么来评价他们呢？孟子就说墨子这个人讲“兼爱，是无父也”。兼爱嘛，你都平等，没有差别嘛，你置于你父亲于何地？没有把你父亲凸显出来，没有把对父亲的爱突出出来，无父也。杨朱不是讲，“拔一毛而利天下，吾不为也”。大家不要误解这句话，它的原意是你拿天下来换我的身体，让我损害自己的生命去换天下，我不干。它是强调自己的生命的重要。“拔一毛而利天下，吾不为也”。杨朱讲“为我”，所以孟子骂他是无君。你老为自己，你把君置于何地？“无父无君是禽兽也”——他骂杨朱和墨子两个人是禽兽。反过来看老子对待这些人的态度是——“不笑不足以为道”，淡然一笑，过了——很值得人佩服的一种态度。这就叫“明月清风”。对待别人的嘲讽，对待别人的攻击，有这样一个态度，也是很不得了的一种智慧与境界。这一段是本章里边的核心。因为我觉得他上中下的这种区分非常明了，很实用。“上士闻道，勤而行之”。坐而论道，不如起来行嘛。大家看道字的写法，首是头脑、思维、想。“走”之旁是行。所以这个道本身就是一个知行统一的概念。“上士闻道，勤而行之。中士闻道，若存若亡。”犹犹豫豫，不坚定，不能够坚定坚持的按照道去做。“下士闻道，大笑之。”我们千万不要做这种老是嘲笑别人，讽刺别人的，否则就会落于下乘，不笑不足以为道，太好了。明月清风一般地对待这种嘲讽辱骂的这种态度。下面这一段开头这句话非常有意思，叫“建言有之”，“建言”就是我们说的常言。常言说得好，这是我们经常用的，所以下面这句话大家注意，不是他本人的话。就是告诉大家了，明确下边讲的很多都是常言，在当时就是一句俗语。他讲的这些道理都是什么呢？都是前边我们讲的“反者，道之动”的例证。所以我在前面给大家说，第四十章是全书的总纲，可以举的例证会无限多，下边都是。“明道若昧”，光明的道路好像是昏暗不明的。为什么？有些给你指出的光明大道说得多么多么得好，指出光明大道简直就是美得不得了，你要小心了，前面有陷阱。真正的大道，反而像是昏暗不明的，就是把路上的艰险，遇到的阻碍，遇到的问题，都给你说清楚，让你看得清楚，这才是明道。给你说这条路没问题，太直了，平坦了，你沿着这条路走，肯定光明无限；沿着这条路走，肯定兴旺发达，一点阻碍都不会有，这个事绝对没问题。坏事了，这个时候你就得小心了。要知道“明道若昧”。再举个关于“朋友”的例子说明这个问题。朋友有三类，友直，友谅，友多闻。第一类的朋友直率，你有问题给你直接指出来。你走的道有问题的时候直接告诉你，跟你讲，怕你犯错误，怕你在这个地方出现问题。不是你的朋友呢？你走在道上遇到什么问题与他有什么关系啊，你问他这条道怎么样？他就告诉你，好好好，走走走，这条路没有任何问题。你给我提点建议，没什么建议，走就是了。你掉到坑里边他管你呀！所以我们说这“明道若昧”，暗昧，昏暗不明。“进道若退”。我们有的时候自己老觉得自己进步太小，人有时候都不免太着急，老觉得“一万年太久，只争朝夕”。只争朝夕，我每天都得进步，我都得看到自己的进步，一感觉到自己没有进步，就着急了。其实你别忘了，人呢，走在路上没有直线的，“进道若退”，有时候我们感觉是退步的时候，其实我们是在进步。比如说练书法，大家都有这个感觉，刚练这几天觉得进步很大，我以后每天按照这个速度会很快成为书法大家，过一段时间感觉怎么回事？怎么我这字越写越差了，还不如开始呢。好多事情开始都是这样。其实这就是我们前进中的一个必然的现象。懂得以退为进，懂得退就是进，有时候退不就是进嘛。“进道若退”，这不就是相反相成嘛。所以我在想，在老子那个时代，你说这些常言都在。这得说中国古代的这些人的哲学的思维水平竟然达到这样一个高度。所以有的时候我们做的事情感觉退步的时候不要着急，退是前进中的必须经历的。“大象无形。道隐无名，夫唯道善贷且成”。只有“道”才能善贷且成，资助万物，帮助万物成长，帮助万物成功。这一章给人很多的启发，很多的回味。每个人读，都会有不同的感受。随着年龄的增长，我们也会不断获得新的体会。</t>
   </si>
   <si>
     <t>德经 | 高深之道</t>
@@ -824,7 +826,7 @@
     <t>我们说“反者，道之动”是整个这本书思维的总纲，也就是说它是一种思维模式、思维方法。第四十章一开头就讲“反者，道之动，弱者，道之用。天下万物生于有，生于无。”这里边出现了两个在《道德经》里边非常重要的字，一个是“弱”，也可以称其为“柔”，另一个就是“无”。第四十三章是对这些内容进一步的引申和展开。第一句“天下之至柔，驰骋于天下之至坚，无有入无间”。最柔弱的东西，反而能够攻克最坚硬的东西。那些没有间隙的地方，无形的东西却能够进入，能攻克。就像风，没有什么地方它进不去的。这些就是“道”，道讲完了。老子开始讲“德”。“吾是以知无为之有益”。我从“至柔驰骋于至坚”，“无有入无间”中知道：人类也是一样，有些事情，无为比有为效果更好——“无为之有益”。可是话说回来，“不言之教，无为之益，天下希及之”按照无为的道理去做事，所获得的好处、益处，天下的人却很少能够知道，很少能够达到。这些话该怎样进一步理解呢？老子在第七十章讲过，“吾言甚易知，甚易行，天下莫能知，莫能行”。什么意思？其实，我讲的道理都是非常简单的、平常。但是大家为什么不知道呢？做不到呢？因为这里边就隔了一个东西——欲望。有些事情大家明知道是这么回事，但是很多东西被欲望牵引就变得难做了。就像我们说“不贪为宝”，但为什么还有那么多人上当？有些人上当了还不好意思说出来。因为自己心里清楚，自己是因为贪心才是上当受骗了嘛。没有这个贪心，很多事情理解起来就太容易，太简单了。但一个骗局，往往能骗很多很多人！再说回来，“天下之至柔，驰骋天下之至坚，无有入无间”。天下的“至柔”是什么？无形是风，有形是水。第七十八章就说，”天下莫柔弱于水，而攻坚强者莫之能胜”。这不是正是“天下之至柔，驰骋天下之至坚”吗？天下什么东西最坚硬，石头？水滴石穿；金属？水刀切可以割金属。有什么坚硬的东西是水它克服不了的呢？风更是弥漫天下，摧枯拉朽，无所不在，力量无尽。你说这个东西没有间隙，但是无形的东西，它反而能够穿透它。现在，科学发现有一些微小的东西，比如说中子、粒子、量子……他们是无形的，你看不见，但没间隙的地方，它们都能够进入。我们眼里没有间隙的地方，对于它们来讲，缝隙简直太大了。“无有入无间”，在强调无的东西的作用。道家的“无为”相当一部分内容在讲“无之为”——这些无形的东西、无用的东西的作为。所以，不要把“无”理解为“没有”，把“无为”理解为“不做事”。“吾不言之教”，第二章讲过“行不言之教”，为什么？身教重于言教，话太多了，老去教化，训导别人，反而会起负面的作用。老师也罢，家长也罢，国家的领导也罢，做一个好的榜样，上行下效。孔子也讲了一句话，叫“君子之德风，小人之德草”。这里小人不是道德上的低下，而是指人民、平民、一般人。榜样的“不言之教”就像风一样，一般人就像草一样。风向哪个方向吹，他们跟随着风而倒。无之为所带来的益处，天下却很少有人能够达到——“希及之”！在讲第三十七章的时候我们说，“道常无为而无不为”，道的规律、规则就是“无为”，而“无为”的效果却是“无不为”——覆盖面更广，效果更好。这不就是“无为之益”吗？一开始讲第一章的时候，我就给大家说过，道家讲的“無”和舞蹈的“舞”字形极为相近。因为对于原始人来讲，舞蹈起到的作用实在太大了。有形的几个姿势，产生出的力量却是巨大的。既然是“无”是“无之为”，那么“无用”，也就是“无用之用”。你认为没用的东西，其实不是它没用，只是你没有看见它的用处。书法有什么用，绘画有什么用？不能当吃，不能当穿，可是如果大家否定了这些，那不就进入了一种狭隘的功利主义的境地了吗？人生最没用的事是什么？睡觉。睡着了什么都做不成。小孩最讨厌睡觉了，可是大家都知道现在有多少人被失眠所折磨，为睡不着觉而痛苦。这些“没用”的事你做不成，那么有用的事你也做不来。最后一句，“无为之益，天下希及之”是老子的感慨。大家老看不到这一点，老觉得无为的事情没用。殊不知你不做这些无为的事，就不能真正的有为。不了解这些无用东西的作用，你也就不知道什么才算是真正的有用。从“反者，道之动”，一直到现在，都在讲述一个道理。</t>
   </si>
   <si>
-    <t>德经 | 空无之道</t>
+    <t>德经 | 柔无之道</t>
   </si>
   <si>
     <t>第四十四章（44）</t>
@@ -1154,13 +1156,13 @@
     <t>古之善为道者，非以明民，将以愚之。民之难治，以其智多。故以智治国，国之贼；不以智治国，国之福。知此两者，亦稽式。常知稽式，是谓玄德。玄德深矣，远矣，与物反矣，然后乃至大顺。</t>
   </si>
   <si>
-    <t>古代那些善于按照道来治理国家的人，并不是用大道使百姓变得聪明伶俐，而是使人民敦厚淳朴。百姓之所以难以治理，是因为他们奇技淫巧太多。所以用技巧来治理国家，是国家的灾难。不用技巧治理国家，是国家的福分。知道这两者的差别，这就是治国的法则。能够永远把握住这些原则，就可以说是具备了微妙高尚的品德。高尚的品德高远深邃，好像与一般事理相反，最后又返回了宁静朴实的根本，然而具有这样的品质之后办起事来却十分顺利。</t>
+    <t>古代那些善于按照道来治理国家的人，并不是用大道使百姓变得聪明伶俐，而是使人民敦厚淳朴。百姓之所以难以治理，是因为他们奇技淫巧太多。所以用技巧来治理国家，是国家的灾难；不用技巧治理国家，是国家的福分。知道这两者的差别，这就是治国的法则。能够永远把握住这些原则，就可以说是具备了微妙高尚的品德。高尚的品德高远深邃，好像与一般事理相反，最后又返回了宁静朴实的根本，然而具有这样的品质之后办起事来却十分顺利。</t>
   </si>
   <si>
     <t>这一章所涉及的，也是我们现在哲学里面经常讲的一个道理，叫“否定之否定”规律，讲事物的发展分为三个阶段，第一个阶段是肯定，第二个阶段是否定，第三个阶段是否定之否定。比如说麦粒长出麦苗，最后结出更多的麦粒，这就是一个否定之否定的阶段。第三个阶段常常重复第一个阶段的某些特征，却是在更高的程度上重复第一阶段的某些特征。这一章和第四十章讲的“反者，道之动”，所运用的哲学的智慧和道理是一样的，既然这样，把这个道理运用到治国上，应该如何呢？这就用到了一个我们大家熟悉的词，叫“返璞归真”，《道德经》认为治民最关键的是要使民风纯朴，不要那么多的技巧，不要那么多的套路。了解了这一点，我们再来看这一章，就明白了老先生的良苦用心。“古之善为道者”，以前的那些善于按照道来治理国家的人。“非以明民，将以愚之”，不是让百姓有那么多的心眼技巧。这个“愚”，不是愚民，而是敦厚、厚道，让人民的民风纯朴。“民之难治，以其智多。”百姓为什么难以治理？因为他心眼多、技巧多。“智”就是技巧、心眼、套路。“故以智治国，国之贼”，用技巧来治国，经常用骗术谎言，这是国家的灾难。“不以智治国，国之福”，不用这些技巧，让民风纯朴、敦厚，这个才是国家的福祉、国家的福分。“知此两者，亦稽式。”“稽式”就是法则。知道这两个的差别，这就是一个法则，治国的一个法则。“常知稽式”，“常”就是规律。按照规律，我们来了解这个法则。这叫什么？“是谓玄德”，“玄”就是深远的意思，这个就是深远的智慧与品德。下面这句话就是我一开头讲的，这个品德“深矣，远矣，与物反矣”，“与物反矣”不就是“反者，道之动”吗？我们都能看到事物的正向的发展，所以《道德经》经常提醒我们，“反者，道之动”，道是向它相反的方向运动，所以你理解问题也不能只看一面。“与物反矣”怎么解释呢？第二十五章，“大曰逝，逝曰远，远曰反”，最后又回到了它的根本。根本是什么？“归根曰静”。民心没那么多的躁动，变得清静宁静、敦厚朴实，这不就符合大道了嘛。“然后乃至大顺”，这样慢慢地就回归到了正确的道路，符合自然之道。所以，这一章讲的就一个问题：你用什么方式治国呢？要让民心变得纯朴、敦厚，返璞归真，没那么多的技巧，没那么多的套路，没那么多骗人的把戏，这样才是符合大道。</t>
   </si>
   <si>
-    <t>德经</t>
+    <t>德经 | 深远之道</t>
   </si>
   <si>
     <t>第六十六章（66）</t>
@@ -1175,6 +1177,9 @@
     <t>这一章所讲的这个道理是《道德经》从头至尾所强调的“善于处下”，只有善于处下，才能真正居上。我们在一开始说过，《道德经》的很多话是针对那些领导者、统治者讲的，所以老先生认为越是位置高的领导者、统治者，越要善于处下，为什么呢？首先从处下的结果上来看，“江海所以能为百谷王者，以其善下之，故能为百谷王。”这句话我在前面也多次引用过。大江大海之所以能成为大江大海，是因为善于处下，不辞细流，能团结一切可以团结的力量，故能为“百谷王”。老子先拿“百川归海”的形象讲了这个道理，让大家有一个感知。下面就开始讲具体的做法和内容。“是以欲上民，必以言下之。”所以你要想站在上面领导好下面这些人，在语言上要懂得谦逊、谦让。领导者，尤其国君、皇帝这一类的，讲话的时候不能够居高临下，盛气凌人，自尊自大，不可一世。第三十九章说过“贵以贱为本，高以下为基。是以侯王自称孤寡不穀”，所以在语言上要谦逊。“欲先民，必以身后之。”想要站在前面当好领导、当好领头的，要懂得把自己的利益放在后面，想要领导别人就得给别人利益。一个人既要领导别人，又想什么好处、利益、功名都抢在自己手上，这个人下场不是不言而喻的吗？范仲淹的《岳阳楼记》里说“先天下之忧而忧，后天下之乐而乐”，做官、做领导不得如此吗？钱钟书先生认为范仲淹这两句话就是出自《道德经》的。但是人家学得比较好，不也成了大家都熟悉的名句了吗？“是以圣人处上而民不重”，所以一个好的领导者，你在上面领导大家，大家没有感觉到沉重的压力。“处前而民不害”，你在前面领导大家，大家没有感觉到你对他的危害。因为你要想领导别人，得让别人得到利益。西汉史学家司马迁在《史记·循吏列传》说：“公仪休者，鲁博士也。以高弟为鲁相。奉法循理，无所变更，百官自正。使食禄者不得与下民争利，受大者不得取小。”这里的食禄者不与民争利，意思是做官的人不许和百姓争夺利益。“是以天下乐推而不厌”，所以天下的人民都往高举你，往前推你，不感觉到厌倦、厌烦。如果统治者穷奢极欲，危害百姓，草菅人命，下面的人就会感觉到“害”、感觉到“重”，这样的人百姓会“乐推”吗？当然不会。“以其不争，故天下莫能与之争。”一个领导者，能得到了大家的拥护、拥戴，正因为你不争，不与民争利，不与其他人争名，“利而不害，为而不争”，结果是“以其不争，故天下莫能与之争”。越是争的人，最后往往失败得越惨，因为你的位置已经规定了你应有的担当、使命和责任。陈毅元帅讲过“手莫伸，伸手必被捉”，形象而深刻，那么，反过来用这个道理讲，就得以更加明确了。“以其不争，故天下莫能与之争”，所谓“不争”，并不是消极被动，“不争”，当然要了解边界，不争边界之外的东西，这样的话才能“天下乐推而不厌”。</t>
   </si>
   <si>
+    <t>德经 | 大成之道</t>
+  </si>
+  <si>
     <t>2、7、11、22</t>
   </si>
   <si>
@@ -1184,48 +1189,60 @@
     <t>天下皆谓我道大，似不肖。夫唯大，故似不肖。若肖，久矣其细也夫。我有三宝，持而保之。一曰慈，二曰俭，三曰不敢为天下先。慈，故能勇；俭，故能广；不敢为天下先，故能成器长。今舍慈且勇，舍俭且广，舍后且先，死矣！夫慈，以战则胜，以守则固。天将救之，以慈卫之。</t>
   </si>
   <si>
-    <t>天下都说我讲的道太大了，似乎不像任何具体的东西。正是因为道大，所以什么也不像。如果像，就早已归为具体事物了。我有三件最珍贵的宝物，值得永久保持。一个是“慈”（守柔），一个是“俭”（节俭），一个是“不敢为天下先”。能做到守柔，才能真正的勇敢刚强；节俭才能长久持续地发展；遇到利益不争先，懂得先人后己，才能成器、成长（成为万物的领导者）。现在的人舍弃守柔而只求勇武，舍弃节俭还奢求长久持续的发展，遇到利益争先恐后、一点都不退让，这是自寻死路！如果能做到守柔，凭它作战就能胜利，凭它守卫就能坚不可摧。上天要救助一个人，保护这个人的办法就是让他具备柔和的品性。</t>
+    <t>天下都说我讲的道太大了，似乎不像任何具体的东西。正是因为道大，所以什么也不像。如果像，就早已归为具体事物了。我有三件最珍贵的宝物，值得永久保持。一个是“慈”（守柔），一个是“俭”（节俭），一个是“不敢为天下先”。能做到守柔，才能真正的勇敢刚强；节俭才能长久持续地发展；遇到利益不争先 懂得先人后己 才能成器、成长（成为万物的领导者）。现在的人舍弃守柔而只求勇武，舍弃节俭还奢求长久持续的发展，遇到利益争先恐后、一点都不退让，这是自寻死路！如果能做到守柔，凭它作战就能胜利，凭它守卫就能坚不可摧。上天要救助一个人，保护这个人的办法就是让他具备柔和的品性。</t>
   </si>
   <si>
     <t>老子、孔子、释迦牟尼、柏拉图，这都是同时代人，在他们那个时代，书其实只有一种题材，就是对话体。《论语》是孔子弟子记的，记得非常清楚，坐在对面的是什么人，提了什么问题，老师怎么回答，所以大家读起来一目了然。佛经呢？很多的佛经也都是释迦牟尼对弟子问题的回答，大家看《金刚经》，是回答须菩提的，《心经》是回答舍利子的，都是针对他们的问题的回答。古希腊哲学家苏格拉底的学生叫柏拉图，写了一本《对话录》，就是记载当时苏格拉底跟学生之间的互动，对各种问题的解答。其实《道德经》的最早的形成也是这种形式，也是对面坐的人问的问题，老先生给予回答，也是对话体，所以我们读这本书，始终要感觉到这是在回答对方的问题，是有针对性的解释和回答，这样很多问题我们才能够得以正确地理解。那么这一章是在回答什么问题呢？对面坐的人，问老子关于道和德的事，老先生给他讲半天，他没听懂，于是提出要求：能不能把你的思想概括得简单点？你让我也能听得明白。大家自然会有疑问，我怎么知道是这样的？是不是我自己在杜撰？让我们回到原文，大家看一下这一章的开头就清楚了。“天下皆谓我道大，似不肖。”老子这个意思就是说，不仅是你，天下人都认为我把道讲得太大、太宽泛了，听不懂。你听不懂，我得给你打比方，类比虽然不能够说明问题，但是它可以让人理解问题。我说道就像风一样，大象无形，你们说不像；我说道就像水一样，大道汜兮，其可左右，你们还说不像……“夫唯大，故似不肖。”正因为把道讲得这么大，拿什么给他打比方，他都说不肖，所以老子就感慨，假如真的像的话，“久矣其细也夫”。意思是假如真的像，那早就归到小道了。比如，说道像一条大河，你拿这个比方，要像的话，就像支流了。道就像一条大道，你要说比方像的话，就像小道。其实意思就说，拿道打比方，要是真的像的话，就是把道说得太小、太细了。那怎么办？不跟你讲那么多了，把我的思想概括到简单得不能再简单。只剩下三个方面，“我有三宝，持而保之。”把我的思想概括到最后，简单得不能再简单了，就剩下三个方面拿出去，按照去做就行。那这“三宝”是什么呢？“一曰慈，二曰俭，三曰不敢为天下先。”大家解读这三组词的时候，不可以单独先解释几个字词，一定要把“三宝”里边的字词和后面的语句连接来解读：“一曰慈，慈故能勇；二曰俭，俭故能广；三曰不敢为天下先，故能成器长。”否则，会失之宽泛。“一曰慈，慈故能勇。”“慈”是指什么？指的是慈母的情怀。做领导、做家长，有了慈母的情怀，才能有真正的担当、勇敢。如果你单独解释这个“慈”就麻烦了，慈母有时候也唠里唠叨，有时也无原则地爱，不是经常说“慈母多败儿”吗？可是《道德经》为什么把“慈”放到第一位呢？这是针对坐在对面的提问者的。作为领导、作为诸侯王，你在这个位置，就要有慈母的情怀，才能有真正的担当、勇敢。如果没有慈母的情怀，一出事就会出卖国家和人民，一出事就把自己的部下当做替罪羊推到前边。“二曰俭，俭故能广。”我还是觉得这位老先生对咱们中国人了解得非常深刻，我们中国人致命的弱点是什么？好面子，好虚荣，好攀比。所以一旦是公开的场合，一旦是监督不力，往往就奢靡之风盛行，浪费之风盛行。没有节俭节制，而是有奢靡之风浪费之风，那就没办法“广”，“广”就是长久持续。家庭没有培养出节俭、节制之风，家庭就没有办法长久持续地发展，所以要勤俭持家。国家人民没有培养出节俭节制之风，而是奢靡浪费，这个国家也没有办法长久持续地发展。“三曰不敢为天下先，故能成器长。”先理解“成器长”，咱们中国很多的词是组合性的，所以大家理解的时候，也要把它组合的东西拆开，“成器长”拆成四个字“成器成长”。我们怎么样才能不断地成长，终成大器呢？“不敢为天下先”，现在咱们天天讲叫“敢为天下先”，这又来一个“不敢为天下先”，这两句话不就怼上了吗？其实这两句话根本不矛盾，讲的不是一回事儿。我们现在强调的“敢为天下先”，是敢闯敢创新，这是一种很好的品质，创新是一个民族的灵魂。《道德经》讲的“不敢为天下先”是什么意思呢？做领导，领着大家做事，要懂得把自己的利益放在后面，要懂得先人后己，不要私欲膨胀，不要什么事情只关注自己，这样才能够不断地进步，不断地成长，终成大器。各位是否还记得我在前面给大家说过，其实读这本书的时候，不用别人给你画出重点，你自己都能感觉到，因为老子在书里不断地强调自己的重点，一种强调的方法是重复，第二种强调的方法是头尾，第三种强调的方式就叫正反，也就是他正面讲完了，觉得是还言犹未尽，要从相反方面给大家再论证一下，你看这一章不就是这样吗？现在的人是什么样的，本来应该按照道的方式来做，要慈、俭、不敢为天下先，我们把这“不敢为天下先”也可以概括成两个字叫“谦让”，或者概括一个字叫“让”。我有三宝，慈、俭、让。可是老子对当时的人不满意，这些人都怎么做的？“舍慈且勇”，根本没有这种情怀，还到处炫耀自己的勇敢。我们现在不也经常看到这种情况？酒驾了，还拍个视频给警察发过去，我醉驾，警察你来抓我呀，炫耀自己无赖似的勇敢。“舍俭且广”，没有这种节俭、节制，还奢求长久持续地发展，不可能。“舍后且先”，遇到好处、利益，争先恐后，一点都不肯让，甚至不该自己的也抢，这样做的结果是什么呢？“死矣！”这样做的最终结果，就把自己弄到死路上去了。“夫慈，以战则胜，以守则固。天将救之，以慈卫之。”这些讲完了，又把他讲的第一个“慈”再说一遍。有这种慈母情怀的人，那么面临事情的时候就会“以战则胜”。他勇于担当，真正遇到困难的时候，领着这个大家当然攻无不克，战无不胜。“以守则固”，国家遇到侵犯的时候，领导者的这种情怀，力量无尽，守无不固。“天将救之，以慈卫之”，如果天真的有情感的话，他要拯救国家的人民，拯救团队团体，一定是“以慈卫之”，你一定有这种慈母的情怀才值得，因为它本身就拥有无穷无尽的力量。第六十七章，核心的就是“我有三宝，持而保之”，要坚定、坚持地按照去做。</t>
   </si>
   <si>
+    <t>德经 | 大用之道</t>
+  </si>
+  <si>
     <t>第六十八章（68）</t>
   </si>
   <si>
     <t>善为士者不武，善战者不怒，善胜敌者不与，善用人者为之下。是谓不争之德，是谓用人之力，是谓配天古之极。</t>
   </si>
   <si>
-    <t>善于做基层领导的人，不耀武扬威、盛气凌人；善于作战的人，懂得制怒而不会被激怒；善于战胜敌人的人，不和敌人发生正面冲突；善于用人的人，善于处下。这就叫不争的品德，这就叫善于集中大家的力量，这就叫符合天道，这是自古以来的最高准则。</t>
+    <t>善于做基层领导的人 不耀武扬威、盛气凌人；善于作战的人 懂得制怒而不会被激怒，善于战胜敌人的人 不和敌人发生正面冲突；善于用人的人 善于处下。这就叫不争的品德，这就叫善于集中大家的力量，这就叫符合天道 这是自古以来的最高准则。</t>
   </si>
   <si>
     <t>这一章讲什么呢？我们中国人有一个习惯，喜欢拿战争的术语来打比方，比如说我们现在吃个饭，也可以说“打个冲锋”，来个“歼灭战”，平常我们也经常讲“占领制高点”。这一章既是在讲战争，又通过战争延伸开来，讲普遍性的制度。“善为士者不武”，“武”的意思就是耀武扬威。善于做基层领导者的人，或者说指挥打仗的士官，不耀武扬威。不要有了这样的一个位置，就耀武扬威，趾高气扬，盛气凌人，不可一世。“善为士者不武”，保持一种谦逊的、平和的、冷静的心态。“善战者不怒”，善于指挥作战的人，不是动不动就暴跳如雷。“不怒”，懂得制怒。任何一个人不管他位置多高，在急躁、浮躁、暴躁、狂躁的心理状态下都谈不上智慧。我们看一下“怒”的写法，上面是个“奴隶”的“奴”，下面是个“心”，当我们控制不了自己的情绪，心成了情绪的奴隶，没有办法保持清醒、冷静、理智的心理状态，才会发怒。所以真正善于作战的人，善于做事的人，要保持这种清醒、冷静、理智的心理状态。“善胜敌者不与”，“不与”，就是不和他发生正面的冲突。从字面的意义上来讲，善于制胜的人，懂得用委婉迂回的方式获得胜利。我们把这个“战争术语”延伸一下，其实在家里也一样，两个人情绪都到达高点、发生剧烈的冲突，这时候解决起来就比较困难。所以，越是到这个时候，越要懂得以退为进，懂得用委婉迂回的方式来解决问题、处理问题，这样才能很好地战胜对方，说服对方。“善用人者为之下”，我在前面多次说过，这是《道德经》从头至尾强调的一个最普遍的原则，善于处下者方能真正居上。一个领导者也是如此，朋友之间相处也是如此，保持自己这种谦逊处下的态度，这样才能够跟人和谐相处，才能“用人之力”。这个叫什么？“是谓不争之德”。“善为士者不武，善战者不怒，善胜敌者不与”，尤其是“善用人者为之下”，都是《道德经》里边从头至尾强调的“不争之德”。说到“不争之德”，我们的思路又回到第八章，“上善若水，水善利万物而不争”，后边讲了“不争”的七种品德：去大家不愿意去的地方——“居善地”；我们要保持内心的宁静，静水流深——“心善渊”；和别人相处，要懂得关爱，一视同仁——“与善仁”；讲话要讲诚信——“言善信”；公平、公正、清廉，所谓政清如水——“政善治”；做事情的时候要尽其所能，像水一样有多种多样的这种本领——“事善能”；善于把握时机，掌握机会——“动善时”。所以，这里的“不武”、“不怒”、“不与”、“为之下”，也是对这个“不争之德”的进一步说明。这个就叫“用人之力”，我们熟悉的一个词叫“借力打力”，熟悉的一句话叫“孤举者不起，众行者易趋”。一个人举重物举不起来，大家同心协力，形成这种趋势，这样才能把事情做成。既然如此，就要懂得用人之力，而不是孤军奋斗，这样做才能够很好地和别人和谐团结。再往高了说“是谓配天古之极”，“古”就是古往今来，所谓“配天”就是符合天道，这些是古往今来的大智慧。第六十八章没有什么难的地方。大家要明白一点，我们中国人习惯用战争的术语来讲生活中的事情，所以我们的理解不能停留在字面上。</t>
   </si>
   <si>
+    <t>德经 | 反成之道</t>
+  </si>
+  <si>
     <t>第六十九章（69）</t>
   </si>
   <si>
     <t>用兵有言：吾不敢为主而为客，不敢进寸而退尺。是谓行无行（háng），攘（rǎng）无臂，扔无敌，执无兵。祸莫大于轻敌，轻敌几丧吾宝。故抗兵相加，哀者胜矣。</t>
   </si>
   <si>
-    <t>用兵打仗的人说过：我不敢主动发动战争进犯别人，而只在被进犯时不得已而应战；作战时不敢盲目进军哪怕一寸，而要后退一尺，以退为进。（在入侵国家的领土上）虽然人民没有排成行列阵势，没有面对人民奋臂作怒，虽然好像没有面对敌人，虽然人民手中没有兵器，但四处都是侵略者的敌人。没有比轻敌更大的祸患，轻敌就几乎丧失了我的“三宝”。所以两军相持时，被同情、被支持的一方会获胜。</t>
+    <t>用兵打仗的人说过：我不敢主动发动战争进犯别人 而只在被进犯时不得已而应战。作战时不敢盲目进军哪怕一寸 而要后退一尺，以退为进。（在入侵国家的领土上）虽然人民没有排成行列阵势，没有面对人民奋臂作怒，虽然好像没有面对敌人，虽然人民手中没有兵器（但四处都是侵略者的敌人）。没有比轻敌更大的祸患，轻敌就几乎丧失了我的“三宝”。所以两军相持时，被同情、被支持的一方会获胜。</t>
   </si>
   <si>
     <t>第六十八章是用战争的术语来做比方，讲的道理当然比仅局限于战争更为广泛。第六十九章我们也当作如是观，他讲的是战争的事情，但是这个道理我们也可以做延伸、做扩展，成为我们生活中的、工作中的普遍的思想与智慧。我们知道《道德经》里边很多的内容并不是老子本人的话语，他也是一个“集大成者”。他经常在回答坐在对面的圣、王、士这些领导者的问题的时候，引用当时或者以前那些智者的语言。第一句话，“用兵者言”，懂得用兵的人怎么做谋划？怎么来认识问题呢？“吾不敢为主而为客”，我才不去老是发动战争去侵略别人，“国虽大，好战必亡。”“我不敢进寸而退尺”，打不过的时候，对手力量太强大的时候，就要懂得以退为进，这个叫什么呢？这个就叫“行无行，攘无臂，扔无敌，执无兵”，这十二个字怎么理解？我先换一个角度给大家来认知这个问题。抗日战争胜利之后，有很多日本人就对这场战争表示不是很服气，因为他们有的认为，是因为东条英机改变了战略，才导致这场战争在中国的战场上的失利；有的人认为，日本战败是因为美军的加入，所以他们也想专门研究战败的原因。有一位日本学者专程来到了中国，他也是通过一本经典来了解我们中国人在这方面的思想与智慧，这本经典就是毛泽东的《论持久战》。各位知道，一九三七年七月七日卢沟桥事变，抗日战争全面爆发，同年的八月二十二日到二十五日，就在陕北洛川召开了洛川会议。在这次会议上，毛泽东就已经开始讲持久战的思想，一九三八年的时候这本书就面世，这不是战后的马后炮，是战前的预测。他把整个战争的进程就概括为六个字，而历史就是沿着这六个字发展：退却，相持，反攻。一开始当然日本侵略者锋芒外露，我们没有办法直接跟他们对抗，因为日本是一个统一的国家，而当时我们的中国四分五裂，军阀混战，政令不统一。日本军队装备精良，又蓄谋已久，所以一开始没有可能把他们赶出去，他们肯定会占领我们很多地方。所以这个时候我们就要懂得退却，以退为进。但是日本的军队又不多，占领我们的地方多了，双方就进入了一种相持的阶段。因为武汉和鄂西会战之后，双方就进入相持阶段，咬牙坚持。我们中国是站在正义的一方，况且我们是一个统一的世界反法西斯战场的一部分，为整个世界反法西斯战场拖住了那么多的日本军队，自然要得到国际舆论的支持、国际力量的援助，最后获得胜利。那么日本为什么会陷在中国的战场上？因为原本按照日本人的想法，中国战场很快就能拿下来，以此为基地，北面是针对苏联，南面是针对南洋的那些国家，很多是英国的殖民地，所以它的主要的目标并不是在中国。可是没想到中国的战场，几乎拖住了它绝大部分的力量，为什么会这样？我们来看一下下面这几句话，“行无行，攘无臂，扔无敌，执无兵”。侵略者进入了另外一个国家，虽然这个国家的人民没有站成军队的样子，“行无行”，但是他们不都是你的敌人吗？“攘无臂”，打击你非得用拳头吗？有各种各样的方式，坚壁清野可不可以？游击战可不可以？全民皆兵，所以叫“扔无敌”。“执无兵”，虽然他们手中没有兵器，但他们用多种多样的方式和侵略者对抗，到处都是敌人。所以为什么说“国虽大，好战必亡”？因为你侵略者是不得人心的，进入到别的国家的军队会遭到别的国家人民的反抗，到处都是你的敌人，“扔无敌，执无兵”。所以对于战争而言，你不要认为一个小的国家就好侵略，“祸莫大于轻敌”，对双方皆是如此。战略上藐视敌人，战术上要重视敌人。“祸莫大于轻敌，轻敌几丧吾宝”，轻敌，就把最宝贵的东西也就是“道”丢掉。所以在战争中要冷静理智，要对对方予以重视，在战略上藐视敌人，但是在战术上要重视敌人，不要轻敌。下面这句话基于上面的这个意思就好理解，“故抗兵相加，哀者胜矣。”就是站在正义一方的抵抗的军队、防御的军队，对抗侵略者，处在相持的阶段，双方相持不下、在那较劲的时候，旁边只要有人帮一下，都会起大的作用。可是大家知道问题的决定性作用并不在旁人，没有形成相持的状态谁帮也没用。所以我们说这句话让我们领悟到一个重要的问题，中国人获得这场抗日战争的胜利，根本的原因在于我们中国人自身，而不在于外面力量的援助。斯大林曾经说过，拉开窗帘天是亮，你不拉开窗帘，天也是亮，反正中国人会获胜，应该帮一下。所以这决定的作用不在外部，而在于我们中国自身。讲得最妙的是最后一句话，最后谁获胜呢？“哀者胜矣”，“哀”可不是哀伤的意思。鲁迅先生写的《阿Q正传》中有一句话叫“哀其不幸，怒其不争”，“哀”就是同情。我们中国人从古汉语里面延续了一个习惯，讲话的时候这种使动用法，通俗地说就是被动型用法。比如我们说老头晒太阳，其实是老头被太阳晒。比如大家到陕西来吃的肉夹馍，那是肉夹馍吗？那是肉被馍夹住了。所以这种使动的用法，用这个来理解，这句话就很清楚了，“哀者胜矣”，谁是被同情、被支持的一方，最后获得胜利。“退却，相持，反攻”——惊人的一致。毛泽东从十几岁就开始读《道德经》，我觉得他从这本书里得到的最大的启发就是这种格局上的、战略上的。人站得高了才能看得远，对未来才能有一个正确的这种预测。所以我说第六十九章，大家不要只局限在战争的一个方面，它也可以把我们的智慧得以扩展和延伸，成为一个普遍性的思想与智慧，成为一个普遍性的原则。</t>
   </si>
   <si>
+    <t>德经 | 非攻之道</t>
+  </si>
+  <si>
     <t>第七十章（70）</t>
   </si>
   <si>
     <t>吾言甚易知，甚易行。天下莫能知，莫能行。言有宗，事有君。夫唯无知，是以不我知。知我者希，则我者贵。是以圣人被（pī）褐（hè）怀玉。</t>
   </si>
   <si>
-    <t>我的话很容易被了解，很容易去践行。然而天下之人都不了解，也不按照这个去做。我提出的主张都是有所依据的，我要求做的事情也是有一定根据的。正是因为人们不知道这个道理，所以不了解我。了解我的人太少了，按我说的道理去做的人更是难得。因此圣人虽然怀着美好的才能，却过着贫贱的生活。</t>
+    <t>我的话很容易被了解，很容易去践行。然而天下之人都不了解，也不按照这个去做。我提出的主张都是有所依据的，我要求做的事情也是有一定根据的。正是因为人们不知道这个道理，所以不了解我。了解我的人太少了，按我说的道理去做的人更是难得。因此圣人虽然怀着美好的才能 却过着贫贱的生活。</t>
   </si>
   <si>
     <t>从第七十章开始，老子强调的重点又发生了改变，他在强调什么呢？他说，我们看问题要“以道观物”，可是有道的人往往为人所误解。老子在书里经常用“吾”这个字，“吾”是人格化的我。“吾”作为一个有道者的代表，一个人格化的有道者的身份，并不一定是指老子本人。第七十章开始就讲人认知的重要性。“吾言甚易知，甚易行。”得道者讲的话，其实很容易被了解，很容易去实行。“天下莫能知，莫能行。”可是结果是什么？这天下的人都是没办法了解，或者说不去了解，也不去按照这个去做。这是一种沉重而深刻的感慨。我们常说道很玄妙，很难把握，而老子在这一章讲，按照道去行事并不难知，不难行，那为什么“莫能知，莫能行”呢？是因为大家根本不愿意去相信它，也不愿意按照它去做，是因为大家认识不到这个事情的重要的意义，认识不到“道”在我们生活中的重要的作用。老子这段话主要是针对领导者、统治者来讲的，老子在对他们讲了很多次之后，发现“万言不值一杯水，犹如东风射马耳”，那些话语仿佛随风而去，并没改变什么。所以，他有此感慨：“莫能知，莫能行”。“言有宗，事有君。”“宗”就是宗旨，说话你得有宗旨，得有核心。“君”是领导控制，做事情也得掌握这个事情的关键。言外之意就是讲，你看我讲的这些话，它是有核心宗旨的。他告诉大家做事怎么样掌握事物的关键，了解事物的本质，把事情做好。“夫唯无知，是以不我知。”可是正因为这些人无知、不了解、不想知道，所以他对我们得道的这些人也就不了解。“知我者希，则我者贵。”了解我的人太少了，懂我的人太少了。我们现在经常有这种感慨，有没有人懂我？其实我们真的了解一个人的精神世界，尤其是了解这些富有大智慧的人的精神世界，不是一件容易的事情。我们中国人经常说一个词叫“知道”，现在大家再说一下这个词，它的分量就不一样，并不是你听到了就叫“知道”，“知”还得去“行”。所以了解我的人太少了，按照我这个去做的人那就更为珍贵了。“是以圣人被褐怀玉”，“褐”，褐色，粗布衣服的颜色。所以得道的人，就像穿着粗布衣服可是身上却怀着珍宝的人一样。得道者讲了很多道理，可是很多人，因为“以貌取人”就是不信。所以，我们经常要透过现象来认识事物的本质，不要以貌取人，不要认为《道德经》里的语言不是那么华丽，就否定其思想与智慧。《道德经》的很多章节都在讲人贵有自知之明。第三十三章“知人者智”，我们真正能够去了解别人，这是一种非常有智慧的表现，可是比这个了解别人更重要的，是我们要了解自己，“自知者明”。人认识最少，却自认为认识最多的知识就是关于自己的知识。因为我们自我的认知，经常被一些假象所迷惑，被情绪所左右，所以“知人者智，自知者明”。其实，老子不仅是感叹“吾言甚易知，甚易行。天下莫能知，莫能行”，他对当时的领导者这种认知的不足及其原因，是有深刻认识的。一千多年后，王阳明提出“知是行之始，行是知之成”，也是这个话题的延伸。</t>
   </si>
   <si>
+    <t>德经 | 超常之道</t>
+  </si>
+  <si>
     <t>第七十一章（71）</t>
   </si>
   <si>
@@ -1238,18 +1255,24 @@
     <t>第七十章讲“夫唯无知，是以不我知”，由于我们的认识上出了偏差，出了问题，所以没有办法了解有高超智慧的人、得道的，很多的时候，我们也没有办法真正地去了解自己，那么问题出在什么地方呢？这一章在分析问题的原因。我经常开玩笑说，这一章是我见过的中国历史上最有智慧的一段绕口令，比那些相声演员用来练贯口的绕口令更富有思想与智慧。“知不知，上”，我们知道自己不知道，我们知道自己的认识有局限，我们知道自己有缺点需要弥补，这是最有智慧的。后来庄子在《秋水》篇里面把这个意思给大家演绎得非常清楚，而且富有哲理。秋天发大水的时候，河伯就以为自己这个地方就是天下最大的，“以天下之美为尽在己”。后来流到了大海，见到了北海若，发现自己太渺小了。北海若又说，其实我在天下所占的位置，也就是像一粒米那样……这就叫“知不知”，知道自己不知道，那才能够不断地进步。“不知知，病”，不知道，却把它当作知道，也就是不懂装懂，这就是一个思想上的大病。怎么样来让我们病得以痊愈？“夫唯病病，是以不病”，我们知道自己有很多的东西不知道，我们知道这是我们的缺点，我们向别人学习，取长补短，谦逊努力。知道自己“有病”，却不讳疾忌医，这反而是没有病。大家熟悉的是《论语》里边的一句话：“由，诲汝知之乎？知之为知之，不知为不知，是知也。”知道就是知道，不知道就是不知道，坦率承认，不要不懂装懂，这个达到的结果“是知也”。这不是一样的意思吗？“夫唯病病，是以不病。”所以对一个有智慧的人，特别是对于领导者、统治者来讲，周边的人都在说好话，阿谀奉承，这样就经常让自己飘飘然，如果这个时候还能保持清醒的头脑，那就是一个有智慧的好的领导者和统治者。他在这个认知上的表现是什么呢？“圣人不病”，一个有智慧的人在这个方面没有病，没有缺点。为什么说它没有缺点？“以其病病”，因为他知道自己的问题在什么地方，知道哪个地方是自己所不擅长的。就像刘邦一样，虽然不能说刘邦为一位圣人，但是他讲的这段话却可以给很多领导者、统治者以启发：“夫运筹策帷帐之中，决胜于千里之外，吾不如子房。镇国家，抚百姓，给馈饷，不绝粮道，吾不如萧何。连百万之军，战必胜，攻必取，吾不如韩信。此三者，皆人杰也，吾能用之，此吾所以取天下也。”刘邦知道自己的短处，借人之力得以弥补，因为有这种清醒的认识，反而成了一个长项。有人总认为自己什么都可以，哪个地方都是自己水平最高，比如说诸葛亮从来也不听别人的意见，打仗的时候都自己谋划，要不就弄个锦囊远程指挥，像这样的人，很难成为一个优秀的领导者。我们经常讲一个人浑身是铁，能打多少钉，要懂得用人之力，懂得借别人的智慧。现在不是有很多的智库、智囊吗？历史上很多杰出的人，比如像曾国藩，手下有多少谋士啊！很多的问题不是他一个人想出来的，得集众人之力，一个优秀的领导者得知道自己弱项、短板在哪儿。对我们个人来讲，一定要知道，其实我们的认知视野都是非常狭窄的，了解了这一点，我们也就不会把自己当作是一个完人，当作什么都知道，不懂装懂。人有什么不懂的，坦率承认没有什么可丢脸的，即便是圣贤，也有自己认知的局限，可是他们的做法和平常人的不同在哪儿呢？“圣人不病，以其病病，是以不病。”知道自己这方面有弱点、有问题，因此不断学习，不断进步，不断成长。这一章虽然很短，但是意蕴深长，道理深刻。这段绕口令大家既可以当作练表达能力、练嘴皮子的体操，也可以当作思想上的体操，一举而双得，何乐而不为？</t>
   </si>
   <si>
+    <t>德经 | 自知之道</t>
+  </si>
+  <si>
     <t>第七十二章（72）</t>
   </si>
   <si>
     <t>民不畏威，则大威至。无狎（xiá）其所居，无厌其所生。夫唯不厌，是以不厌。是以圣人自知，不自见（xiàn）；自爱，不自贵。故去彼取此。</t>
   </si>
   <si>
-    <t>百姓不畏惧统治者的威严，暴君就用更大的恐怖政策施加于百姓头上。不要让百姓住的地方越来越狭小，不让他们的生存受到压迫。不去压迫百姓，他们才不会对统治者的行为感到厌烦。所以圣人有自知之明，不自我表现；珍爱自己的生命但不自认为高贵。所以圣君抛弃暴君的做法而不去炫耀、抬高自己。</t>
+    <t>百姓不畏惧统治者的威严，暴君就用更大的恐怖政策施加于百姓头上。不要让百姓住的地方越来越狭小，不让他们的生存受到压迫。（不去压迫百姓）他们才不会对统治者的行为感到厌烦。所以圣人有自知之明，不自我表现；珍爱自己的生命但不自认为高贵。所以圣君抛弃暴君的做法而不去炫耀、抬高自己。</t>
   </si>
   <si>
     <t>七十二章到七十五章，这一部分都出现了一个核心的概念——“民”。在中国历史上有“民本”的思想，我们大家熟悉孟子讲的“民为贵，社稷次之，君为轻”，大家觉得讲得好。但是，在孟子之前，《道德经》已经从哲学的层面把民本思想发展到非常高的程度，而且讲得更为具体。这一章最后一句话讲得非常明白，这两条路摆在这儿了，你应该走哪条路？“故去彼取此。”有哪些路可以选择呢？走哪条路是符合道的呢？我们从头来看。“民不畏威，则大威至。”如果一个国家的人民不害怕统治者、领导者的威严，那么对统治者、领导者来讲，大的麻烦就来了。什么大的麻烦呢？“民无信不立”，领导者在民众中丧失了诚信，就没法统治领导他们了，这不是一种大威吗？所以“无狎其所居”，“狎”通“狭”，也是使动用法。领导者，不要让百姓住的地方越来越狭小，最后都流离失所。因为“无恒产者无恒心”，一个国家如果到处都是流民，它能稳定才怪。“无厌其所生”，“厌”通“压”。不要让他们感觉到生存受到了压迫，不要去压迫他们，不要让他们感觉到厌倦生活，因为哪里有压迫，哪里就有反抗。所以这个“厌”，大家可以把它理解为两个意思，一个就是压迫，一个就是导致的结果感觉到生不如死，厌倦自己的生活。“夫唯不厌，是以不厌。”你不去压迫他们，不让他们感觉到生活的局迫、窘迫、生不如死，他们才不会对你的统治行为、领导行为感觉到厌烦。第六十六章说“处上而民不重，处前而民不害”，处上又重，处前而害，他当然会感觉到这种受压迫的厌烦的感觉。那么，真正有智慧的领导者、统治者应该是什么样呢？“自知，不自见”，自己有自知之明，不是有一点功劳，有一点什么就去自我表现。“自爱，不自贵”，很珍爱自己的生命，珍爱自己名声，自爱自重，但是不自以为高贵。第三十九章最重要的两句话，第一句话就是“贵以贱为本”，不要认为自己身份高贵，没有这个国家的人民，也就是很多人眼中的贱民，哪来你高贵的身份？自爱是对的，因为一个人不爱惜自己的生命，也就不会珍惜别人的生命。第十三章讲过，什么样的人才能把天下寄托给他呢？“贵以身为天下”、“爱以身为天下”。所以好的领导者对自己的生命非常珍视，但是为了天下的使命，可以奉献自己的生命，这样的人我们才能把天下寄托给他。“故去彼取此”，取的是什么呢？取的是自知自爱；去的是什么？去的是自见、自贵。</t>
   </si>
   <si>
+    <t>德经 | 自制之道</t>
+  </si>
+  <si>
     <t>第七十三章（73）</t>
   </si>
   <si>
@@ -1262,6 +1285,9 @@
     <t>这一章首先谈的话题是“勇敢”。关于“勇敢”，《道德经》并不像我们一般认识那么简单，表达那么直白，它把“勇敢”分为“勇敢”和“勇于不敢”，这个说法的妙处我们后边再做解说。接着读这一章，大家会发现熟悉的语句“天网恢恢，疏而不漏”，其原文就出自第七十三章“天网恢恢，疏而不失”。我们中国人读失去的“失”啊，总觉得有点绕口，换了一个字，意思都是一模一样的。天网恢恢，疏而不漏，天道如此。庄子也讲过这样一段话，一个人做了亏心事之后，在客观世界上把有形的痕迹抹掉容易，可是抹不掉内心的痕迹。即便是不受客观世界的惩罚，也得受良知的惩罚。那么第七十三章的结尾，怎么得出“天网恢恢，失而不漏”的结论呢？是怎么过渡到“天网”、“天道”的呢？“勇于敢则杀”，毛泽东在《贺新郎·读史》这首词里面就讲：“铜铁炉中翻火焰，为问何时猜得？不过几千寒热。人世难逢开口笑，上疆场彼此弯弓月。流遍了，郊原血。”人类的历史都是在这种血与火的洗礼中前进的，老子在他那个时代，肯定也看到过这种情况。“勇于敢则杀”，也包括很多违背了国家法律法令的不法之徒，从直观地来看，也是属于勇敢，“勇于敢则杀”。“勇于不敢则活”，“勇于不敢”直观上看上去，我们把它叫做“懦弱”、“退缩”，但其实这样的“懦弱和退缩”还有另外的一类人，他们懂得保护自己的生命，以期谋得更大的成就与发展。其实，我们说懂得拒绝的人也是一种“勇于不敢”，有些该做的事情，勇敢去做；有些不该做的事情，勇于不敢，拒绝。老子接着说，“此两者，或利或害。”“此两者”指勇敢和勇于不敢。勇敢和勇于不敢这两种情况“或利或害”，就是说有时有利，有时有害，那到底何时有利，何时有害呢？谁能把握这个度呢？“天之所恶，孰知其故？”天呢，到底是喜欢还是厌恶？到底是怎么一回事？谁能够了解这里边的最根本的原因、缘故呢？“是以圣人犹难之”，就是再有智慧的人、有智慧的领导者，在这个方面也难以去理解清楚。所以你看这个认知啊，非常困难，到底是该杀还是该活，到底该怎么对待，这是一个非常难的选择。那老子是不是就放弃了对这个难题的解决呢？不是的，事实上，老子是认为，只有站在更高的视野才能解决这个困扰，也就是第四章说的“解其纷”。所以老子在下边就说，如果从天道的角度来认知这个事情是什么样呢？“天之道，不争而善胜”，不争斗，却能够获得胜利，这是符合天道的。“不言而善应”，要行不言之教，不是老去命令、政令，大家对他反而非常支持，非常响应。言教不如身教，“不召而自来”，大家自然而然就聚拢到你的麾下，这是符合天道的。“繟然而善谋”，“繟”就是坦然、从容。天道看不出来痕迹，从从容容地向那个方向发展，就像一个善于谋划的人一样，不露痕迹地谋划。所以后面就讲“天网恢恢，疏而不失”，天网虽然好像有很多疏漏，但是最后你会发现，这天道如此，天网恢恢，疏而不漏。我们中国人经常把这个讲做“人在做天在看”、“为人别做亏心事，古往今来放过谁。”到这里，逻辑就逐渐清晰了：天道不争，不强制，自然而然，所以为民，不能滥用所谓勇敢；为王，也不能滥用强制，这都是不符合天道的，不符合天道，则是必然要失败的，也就是讲“天网恢恢，疏而不失”。所有违逆天道的所谓“勇敢”最后都会受到惩罚，天网虽然好像有很多疏漏，但是最后你会发现，这天道如此，天网恢恢，疏而不漏。关于这一点，我们再引证下孔子这句话：“人之生也直，罔之生也幸而免”，就更清楚了。意思就是那些不正直的勇于敢者、对抗天道天理的人，也许会侥幸漏掉一时，但终究逃不脱天道天理的惩罚。孔子的真正意义在于，若靠侥幸活着，你是活不好的。而老子对于敢对抗天道天理的人、与天争胜的人，警告更为严厉：“天网恢恢，疏而不漏。”换句话说就是“人在做天在看”、“为人别做亏心事，古往今来放过谁。</t>
   </si>
   <si>
+    <t>德经 | 政策之道</t>
+  </si>
+  <si>
     <t>第七十四章（74）</t>
   </si>
   <si>
@@ -1274,30 +1300,39 @@
     <t>七十四章开头这句话，在讲什么呢？“民不畏死，奈何以死惧之？”假如这国家的人民都不怕死了，都感觉到生无可恋了，你还能有什么方法去管理他们呢？上一章不是说过吗，“狎其所居，厌其所生”，百姓感觉到压力太大，感觉到生不如死，那就会产生“民不畏死”的情况。这个时候，你拿死去吓唬他还有什么用呢？毛泽东在《别了，司徒雷登》中引用过这一句，并引申说，“中国人死都不怕，还怕困难吗？”接着老先生做了一个假设，“若使民常畏死”，假如这个国家的人民经常地、普遍性地害怕死，老百姓对生活抱有憧憬和希望，这个时候，如果有搞幺蛾子的人，铤而走险犯法的人，“而为奇者吾得执而杀之”，做领导的、做统治者的，把这些人逮过来杀掉了。“孰敢”，没有人会响应这些人，大家不都不吭声了，国家也就恢复了平和、安定。大家注意，这话里暗含着一种假设，事实是什么呢？老百姓生活没有希望，不畏惧死亡。这时候，你杀的人越多，反抗的人越多；镇压得越多，起来呼应的人更多。所以，老子说你管理靠镇压是不行的，这不是根本的方法。历史上还有比秦朝法令更严苛、更严酷的时代吗？满大街都是被砍断手脚的人，严刑重罚，稍有违犯，立马严惩。最终，大家不还是起来造反了吗？秦朝之前，老先生就已经提醒过，靠残酷的镇压是不管用的，这不是处理问题的根本方法。下面上升到了更高层面，“常有司杀者杀”，大家知道，我们讲“秋后问斩”。秋天是代表肃杀的，杀人的时候是在秋天，这个代表符合天道、天杀。《道德经》的这句话是说，人的生死是由天来司管的。再退一步讲，国家也是按照国家的法令、按照符合道的方式制定的法律，来约束人的。当然这句话就《道德经》的本身而言，是在讲天操管着人的生杀予夺大权，人没有这个权力去决定别人生死的，即便是有的话，也应该有专门的部门来管。“夫代司杀者杀”，代天来杀人，这叫什么？“代大匠斫”，我们知道木匠的锛凿斧锯别人是不能动的，太锋利了，只能他们自己使用。你不熟悉这一行，你不懂怎么使用，你代替他们，“希有不伤其手矣”，哪会有不伤到自己的？老先生拿这个来做类比：你应该不用这些东西，不善于用这些东西，你越俎代庖，那么你自己肯定也会受伤的。因此，只用杀戮、镇压的方式，是不符合天道的，对自己的统治、领导也有着重大的损伤。这段话其实对统治者提出的警告：靠镇压的政策、残杀的政策，也会影响威胁到自己的统治，不要相信武力能解决一切问题。三十五章讲“执大象，天下往。往而不害，安平太。”应该用符合“道”的方式来管理国家，以民为本，注重根基，这样才能够和谐相处，才能够“安”、“平”、“太”。</t>
   </si>
   <si>
+    <t>德经 | 分权之道</t>
+  </si>
+  <si>
     <t>第七十五章（75）</t>
   </si>
   <si>
     <t>民之饥，以其上食税之多，是以饥。民之难治，以其上之有为，是以难治。民之轻死，以其求生之厚，是以轻死。夫唯无以生为者，是贤于贵生。</t>
   </si>
   <si>
-    <t>人民之所以饥饿，是因为统治者收取挥霍的税负太多，所以人民饥饿。人民之所以难以治理，是因为统治者总是胡为、妄为，所以人民难以治理。人民之所以不怕死，是因为统治者所求奉养过多，所以人民不怕死。不把自己生命看得绝对重要的，不搜刮剥夺人民以奉养自己生命的，胜过那些过分重视自我生命的统治者。</t>
+    <t>人民之所以饥饿，是因为统治者收取挥霍的税负太多，所以人民饥饿。人民之所以难以治理，是因为统治者总是胡为、妄为，所以人民难以治理。人民之所以不怕死，是因为统治者所求奉养过多，所以人民不怕死。那些不把自己生命看得绝对重要的人，胜过那些过分重视自我生命的统治者。</t>
   </si>
   <si>
     <t>这一章的核心话题还是“民”，解释了三个问题。第一，百姓为什么饥寒交迫；第二，百姓为什么难以治理；第三百姓为什么不怕死。解释完三个内容，然后对领导者、统治者提出要求。“民之饥，以其上食税之多”，百姓为什么饥寒交迫？“上”，上面的领导者、统治者，“食税”，收的税太多了，而且收的税都被这些人挥霍。“民之难治，以其上之有为”，百姓为什么难以治理呢？原因不在他们这儿，是因为上边胡来、瞎折腾。在《道德经》里，“有为”这个词就是妄为，胡折腾，上边老瞎折腾，就把民心折腾乱了。“信不足焉，有不信焉”，折腾得多了，讲的话也不诚信了，也失去百姓的信任，说什么都没用了。“是以难治”，“是”，“这是”的意思。这话讲得就比较理性，你老说他们是刁民，老在他们身上找，其实这原因就在自己的“有为”。老子对坐在对面的那些领导者、统治者就讲，你得找到真正的原因，百姓为什么饥寒交迫？你们收税收得太多了，收的税都被挥霍了。百姓为什么难以治理？你们整天瞎折腾，胡来妄为，把民心搞乱了。“民之轻死，以其求生之厚”。“其”指谁？领导者、统治者。百姓为什么轻死，把死不当一回事？是因为你们这些统治者，把自己的生命看得那么重要，不惜用剥夺的方式积累财富，花天酒地，穷奢极欲，这财富都聚积在他们自己手里，老百姓难以生存。就像国民党时期，财富都积累在“四大家族”手中，很少的人占有了绝大部分的财富，底下的人都生活在水深火热之中。当你“求生之厚”的时候，底下的百姓就觉得没什么活路和希望了，也就不把死当一回事，“是以轻死”。那么应该怎么做呢？“夫唯无以生为者”，不要把自己的生命看作是绝对重要的。不要把财富、好吃的好用的，全都集中在自己这儿来，认为只有自己的生命才是生命，对别人的生命、生存视而不见，感到无足轻重。不把聚敛、穷奢极欲当作生命的重要的部分，这个就是“贤于贵生”。百姓为什么饥寒交迫？上食税之多；为什么难以治理？上面胡来妄为；为什么不怕死？求生之厚。这章三个并列句，像诗一样的语言，讲得又非常深刻、非常理性。把七十五章和七十四章结合起来理解，我们就能发现，老先生苦口婆心地劝坐在对面的那些领导者、统治者：你们要对自己国家的人民好一点，否则啊，他们日子过不好，你们的日子也不安稳，你们只靠这种高压的政策，这不是解决问题的根本的方法。我们完全可以说在这几章里看到了《道德经》的“真实面目”，很多话是针对那些统治者讲的，苦口婆心地劝他们，应该怎么样对待这个国家的人民，才能使国家长久地、持续地发展。</t>
   </si>
   <si>
+    <t>德经 | 定位之道</t>
+  </si>
+  <si>
     <t>第七十六章（76）</t>
   </si>
   <si>
     <t>人之生也柔弱，其死也坚强。万物草木之生也柔脆，其死也枯槁（gǎo）。故坚强者死之徒，柔弱者生之徒。是以兵强则不胜，木强则折（shé）。强大处下，柔弱处上。</t>
   </si>
   <si>
-    <t>人活着的时候身体柔软，死之后身体便会僵硬。万物草木活着的时候形质柔软，死后变得干枯。所以坚强的东西属于死的那一类（追求刚强是条死路），柔弱的东西属于生的那一类（保持柔弱是条生路）。因此兵力强大了就会灭亡，树木坚硬就会一折就断。总认为自己强大的、夸耀自己强大的，反而会处在下面；懂得柔弱、谦逊的，反而会居于上面。</t>
+    <t>人活着的时候身体柔软，死之后身体便会僵硬。万物草木活着的时候形质柔软，死后变得干枯。所以坚强的东西属于死的那一类（追求刚强是条死路），柔弱的东西属于生的那一类（保持柔弱是条生路）。因此兵力强大了就会灭亡，树木坚硬就会一折就断。总认为自己强大的、夸耀自己强大的 反而会处在下面；懂得柔弱、谦逊的 反而会居于上面。</t>
   </si>
   <si>
     <t>现在我们来说一下第七十六章，王弼本子的编辑是有着内在逻辑的。前两章，老先生劝统治者，不要用这种“强”的方式、镇压的方式来实施自己的统治，那么应该怎么做呢？要懂得以柔克刚、强大处下，这样才能形成一种和谐。有的人确实是没有认真地读这本书的原文，他们认为《道德经》是一个弱者斗争的哲学，这是不了解坐在老子对面的向他提问的那些人，他们并不是一般的平民，而是手握权力的领导者、统治者。要站在这个层面来理解第七十六章，知道他这些话是对是对那些认为自己自身或者自己国家很强大的统治者们讲的。老子劝他们用“柔弱”的方式来实施自己的统治，这个是非常有智慧的，这个非常能够体现老先生的慈悲仁爱之心。这一章强调两个字“柔弱”，所以一开始讲“人之生也柔弱”，最后强调“强大处下，柔弱处上”。“人之生也柔弱，其死也坚强。”人活着的时候是什么状态？柔韧性非常好。我们看跳舞的、练杂技的，就觉得这柔韧性好。柔弱柔软，这是生命昂扬、鲜活的状态。而人死的时候是什么样的一种情况呢？硬了、僵了，“其死也坚强”。老子首先拿人的生命的状态来说明柔弱具有的意义。如果这个问题大家觉得还没有理解到位，再换一个角度来理解。在苏州金鸡湖苏州新区里曾经出现过一尊老子的雕像，这尊雕像太丑陋了，老子张着嘴，吐着舌头，一颗门牙。很多人很不理解，心里想有大智慧的老子，怎么会是这样的形象，还有人打趣说，这个老子是来卖萌的……这个雕塑者姓田，他就站出来解释说，我这个雕塑叫“刚柔”，它的出处是说，当时孔子见老子的时候，老子没有给他多说什么，张开嘴巴让孔子看了看。孔子一看就明白了，老子当时已经都七十多岁了，牙早掉光了，但是舌头还在，讲的就是“柔弱更长久”的意思。雕塑者说“刚柔”倒没错，但是这段话不是出自正史，记载的也不是指孔子和老子之间的事，其实是当年老子毕业的时候，跟自己的老师讲的。您有什么送给我？老师也没说话，张开嘴巴给他看了看，老子就看明白了，老师年纪大了，牙掉光了，但舌头还在。牙齿是坚硬之物，到一定年龄就掉了，舌头没事，柔软更长久。所以，柔弱更有生命力、更长久，柔弱是生命的状态，而强硬、僵硬是死亡的状态。这是第一个，拿人来做比方。第二个以草木为例，“其生也柔脆，其死也枯槁。”我们以草为例，李世民在诗里说“疾风知劲草”。草，风往这边吹了，它这边倒，往那边吹了，往那边倒，风走了，它再站起来坚守脚下这片土地。什么时候草坚定了，不随风倒了，那草就死了、枯了。正因为草很柔弱，所以它能迎风起舞；正因为草很柔弱，所以“天涯何处无芳草”。下面得出结论，“坚强者死之徒”，“徒”就是那一类。认为自己坚强、强硬、强暴，其实这是属于走向死亡一类的。而“柔弱者生之徒”，柔软、柔韧，这是富有生命力的表现。沿着这个方向再往下推，就说到了人类社会，“兵强则不胜”，一个国家穷兵黩武，认为自己的军事力量强大，稍一不如意就动用军队发起战争，“国虽大，好战必亡。”“兵强则不胜”，不是说你这场战役打不胜，但穷兵黩武的最后结果一定是失败的。历史上多少强大的帝国，比如说秦朝，被称为“虎狼之师”，最后的结果怎么样？“兵强则不胜”“木强则折”，这个“强”就是僵硬。春天，万物复苏，一根细小的柳枝也很有韧性，很难去折断它。秋天，柳枝水分干枯，好像很强硬地挺在那里，可是它内在枯槁了，一折就断。小的时候，我在石厂里边劳动，砸石子做铺路之用。那时候我就见了一个非常奇怪的现象，石场里石匠用的榔头把儿，一种是很粗大的木棒，看着很稳定；一种是很细的木棒，看起来很危险。我去问那个石匠，怎么用这么细的斧柄？他说这个东西叫“水曲柳”，你别看它细，但它韧性非常好，你用多大劲儿也没事儿。所以每当读到这个地方，我就想起这个事情。“木强则折”，看似强大僵硬，其实没有了韧性，它就没有了生命力，一碰就断掉了。讲完这个了，再看这里边两层的推论。第一层推论：“坚强者死之徒，柔弱者生之徒”，然后推到人类社会，表达他对用这种强横的方式予以统治、用这种强横的方式予以领导的不认同，指出这个方式的致命的弱点。战争中也是如此，“兵强则不胜”，就像“木强则折”一样。讲完这个，推论到第二层：“强大处下”，老是炫耀自己强大，去任意地凌辱别的小的国家；自己有了高的位置，可以盛气颐指，不符合道，这是向死亡方向去发展。“强大处下，柔弱处上。”懂得以柔克刚，懂得以退为进，懂得谦逊谦让，这才是符合道的，才是真正有智慧的表现。第六十一章，“天下之牝，牝常以静胜牡”，讲以静制动、以柔克刚的道理。所以对人生来讲，强大、用强，这事儿大家都知道，也并不是说老子对这个东西一味排斥，因为人生有的时候强也是需要的，但是大家都把这个事情推到极端了，认为“强”是解决问题唯一的方式，所以，老先生在面对那些领导者、统治者的时候，苦口婆心，形象具体地讲述柔弱处下的道理。我们现在读这一章，也可以把智慧扩大到我们的为人处事，不要只认为用强才能解决问题，要懂得强弱两者的相辅相成，老去逞强，不是真正智慧的做法，这是只是智慧的一个方面，而“以柔克刚”才是一种真正高级的智慧。适当的时候，我们要懂得示弱，这是我们在和社会、和别人打交道的时候，非常重要的智慧，有重要的启迪。</t>
   </si>
   <si>
+    <t>德经 | 强弱之道</t>
+  </si>
+  <si>
     <t>第七十七章（77）</t>
   </si>
   <si>
@@ -1310,6 +1345,9 @@
     <t>第七十七章，这一章重要在什么地方呢？大家都知道“马太效应”，马太效应出自《圣经·马太福音》，直观的解释是穷者越穷，富者越富，越穷越倒霉，越富反而财富滚滚而来，这也是我们人类社会大家都认同的一个普遍的现象。怎么解决这个问题呢？怎么样解决这样的一种贫富的两极分化呢？《道德经》很早就给出了一个方案，所以我们把这一章叫什么呢？叫“张弓效应”。在这一章里边我们可以看到一句话，这句话和马太效应讲的意思是一样的，叫“损不足以奉有余”。“天之道，其犹张弓与？”老子在这一章里面就讲，说天道就像拉弓射箭一样，拉弓射箭要有的放矢。这个箭，你瞄得高了，往下压一下；低了，往起抬一下，“高者抑之，下者举之”。沿着这样的一个比喻，自然就得出这个结论，对于人类社会也是这样，“有余者损之，不足者补之”。财富多的人应该拿出更多帮助这些不足的人，收入高的人当然应该多交税。这就是“天道”，天道如此，天道均衡，“天之道，损有余而补不足”。可是人道，这个社会是怎么做的呢？“人之道则不然”，老子对他当时的情况看得很清楚，财富都掌握在少数人的手里，“损不足以奉有余”，越是不足的、穷的，反而被压榨得越厉害，富的反而越来越富。于是，老子面对那些统治者讲，一个好的领导者、统治者应该向“圣人”的方面去发展，做一个好王。大家注意古代那个“圣”的写法，王上边并列两个字，耳和口，听得进别人的意见，说话温暖。通达事理的王，称之为圣。老子就对他们讲，你们应该向这个方面努力，怎么做呢？“有余以奉天下”，让那些更富的人来为这个天下做贡献。“唯有道者”，就是了解道的人，按照道的方式去行事的人，才能做到这一点。说到这儿，我就得给大家说一下我们的文化背景。一句话大家都熟，叫“不患寡而患不均”，贫富不均，很容易产生问题。历史上那些农民起义，他们用的口号，你也能感觉到这一点，比如说王小波、李顺，“均贫富等贵贱”；比如说黄巢，“冲天平均大将军”……从社会心理能分析到这一点。所以老先生就讲，统治者、领导者，什么样的人才能够真正注意到、做到让贫穷的得以扶持，让富有的贡献更多呢？“唯有道者”，“是以圣人”。“是以圣人为而不恃，功成而不处，其不欲见贤。”一个好的领导者，“为而不恃”，他把这件事情做了，有作为了，却不把这个当作一种倚仗、凭借甚至勒索的手段。“功成而不处”，不居功自傲，“不欲见贤”，不想表现出自己的这种贤能贤明。这是有道者的表现，懂得让天下向共同富裕的方面发展，让那些先富起来的人懂得奉养天下，哪怕是把这些做成了，也不居功自傲，因为他们知道，这只是按照道的方式来做的。</t>
   </si>
   <si>
+    <t>德经 | 取舍之道</t>
+  </si>
+  <si>
     <t>第七十八章（78）</t>
   </si>
   <si>
@@ -1322,6 +1360,9 @@
     <t>第七十八章体现了这本书里的一个非常重要的理念，“善于处下”。这些内容我们之前都有过接触，甚至直接引用七十八章做过讲解，所以这一章我们并不需要花费太多的时间来解释，大家也能够明了。“天下莫柔弱于水，而攻坚强者莫之能胜”，天下没有什么东西比水更柔弱了，你拿什么容器装，它就是什么样，随方就圆。但天下也没有什么东西比水的力量更强大了，攻无不克，战无不胜。水就是以柔克刚、以弱胜强的最好的形象的代表。“以其无以易之”，因为没有什么东西能够替代水，天下最柔弱的东西，它力量又最为强大，最能够体现柔弱胜刚强的道理。“弱之胜强，柔之胜刚，天下莫不知，莫能行。”天下都知道，这东西表面上看似柔弱，但发挥作用的时候力量太强大了，但是真的要这样却非常不容易，为什么？人都有脾气，“柔弱胜刚强”得懂得忍耐、等待，忍耐是我们人最难练的一种功夫。水滴锲而不舍方能穿石，一条溪流不舍昼夜，慢慢积累，等待时机，才能发挥大用。“柔弱胜刚强”也是需要条件的，只是老子没有明说。“是以圣人云”，我再给大家强调一下，在老子心里，以前有很多好的统治者、有智慧的领导者，他称其为“圣人”，让大家向他们学习。我们在前面谈到过，他的很多话并不是原创的，是他引用的以前的圣人的，下边这话就表达得非常明确，所以这些圣人讲，“受国之垢”“受国不祥”。这两句话就是《道德经》里边从头至尾强调的，就是我们经常讲的善于处下。古往今来，夺得天下的表面看是一家一姓，实际上不都是一个团队吗？用我们现在的话讲是一个党派。什么样的团队，什么样的党派才能夺得天下，并且坐得了江山呢？之前，我们在第八章讲“处众人之所恶”时，也拿这个地方作为印证。吃苦在前，享受在后，有困难还得担着，有错误勇于改正，这不就是“受国之垢”“受国不祥”吗？所以真正想要夺得天下，坐稳江山，也就是所谓“处其上”，首先要懂得“处其下”，要“受国之垢”，要能忍受别人忍受不了的艰难困苦，要能承受别人承受不了的屈辱诟骂，这样才能成为江山社稷的主人。“受国不祥，是为天下王。”有灾难有困难，你别跑，要挺身而出，勇于担当，有错误要勇于承认，勇于改正。毛泽东把共产党的宗旨概括为五个字，叫“为人民服务”。两千多年前的“受国之垢”，“受国不祥”，“处众人之所恶”，两千多年后的“为人民服务”，这本质上的意思不是一样的吗？这就是《道德经》里面从头强调的，也是古往今来的大道。我们在讲第十四章的时候说过一句话，“执古之道以御今之有”。了解古往今来的大道，我们才能更好地做好今天的事情。读到这儿大家就会发现，这《道德经》里边蕴含着古往今来的大道，蕴含着一个人、一个团队、一个党派成功的最深的密码，值得大家认真地品味。总结上面这个表达的方式叫什么呢？叫“正言若反”，也就是第四十章讲的“反者，道之动”。看着是讲反话，大家都不愿意去做的事情：“受国之垢”，“受国之不祥”，“处众人之所恶”，可实际上，这才是能够让我们“处上”、取得成功的真正的智慧与奥妙。看似好像说的反话，其实深刻的道理就在这里边。</t>
   </si>
   <si>
+    <t>德经 | 正反之道</t>
+  </si>
+  <si>
     <t>8、9</t>
   </si>
   <si>
@@ -1337,18 +1378,24 @@
     <t>针对坐在对面的那些统治者、领导者，老子前面一直在讲，不要用高压的方式，要懂得用柔和的方式。如果一直用高压的方式，一直用“损不足以奉有余”的方式，这社会就积累了大的矛盾。老先生认为，有了这个矛盾之后，不管用什么方式解决，它都会遗留下很多的不满、埋怨、祸端。在这个基础上，我们才能够深入理解第七十九章的内容。这一章只有这么几句话，但道理非常丰富而深刻。“和大怨，必有余怨，安可以为善？”如果社会已经积累了大量的矛盾，即使用调和的方式，“和大怨”，可是，依旧会留下很多的这个埋怨、祸端。“安可以为善”？即使用和谐的方式，也不是一种善举，为什么呢？第六十四章讲“为之于未有，治之于未乱”，从一开始你就不应该让这社会积累了这么多的矛盾。我们之前举过晏子“救灾”的例子，其实针对我们目前的环境问题，也是一样。大家知道有一句话叫“反对先污染后治理”，你污染完了，你再治理，其难度之大，难以预料。“病来如山倒，病去如抽丝”，社会不也一样吗？积累了这么多复杂的矛盾，你老用调和的方式，你说现在已经柔和了、缓和了，但留下那么多的祸端，这当然不算是好的方法，不可以叫做善举。对应我们人际交往也是一样，我们不要本着“无所谓”的态度，想着跟别人、朋友之间有了裂痕，我们说以后自会解决的，事情往往没有我们想得那么简单。所以，平时做事就要小心，朋友之间要珍惜，家庭之间感情要珍惜，别真的等得了埋怨之后，再想办法去解决。这跟钉子钉在墙上一样，你拔出了钉子，那个眼还在。最好的“善”是什么？提前做出预防，“为之于未有，治之于未乱。”“是以圣人执左契，而不责于人。”有智慧的领导者、统治者，就像拿着契约的人。“左契”，契约，一撕两半，左边一个，右边一个，左边那个是借据。拿着这个契约借据而不责于人，不是天天去追着要，而是表达出圣人的一种宽容。老先生拿这个举例子，意思说，一个好的领导者，哪怕是你对大家都有恩德，对天下都有恩德，你别以为大家都欠你的，“不责于人”。所以“有德司契，无德司彻”，有德的人就像执左契而不责于人的人。“彻”，就是税官，收税的。这是代表着两种态度，一种是和缓的态度，另一种是苛刻的残酷的态度。所以平日里，应该像“有德司契”的样子，那就不会积累那么多的埋怨。反之如果像那个税官一样，苛捐杂税多，还步步紧逼，不肯放松，老子认为这是无德的表现，这样会留下大怨！下面两句话很容易引起误解，“天道无亲，常与善人。”在第五章曾经讲过，“天地不仁，以万物为刍狗”，天地是没有感情的，它并不因为你做了好事，就来奖赏你，也不因为你做了坏事，便来惩罚你。既然“天道无亲”，那为什么“常与善人”呢？又怎么把这个规律规则让那些善人能够理解，并按照它去做呢？这个事情我换一个角度让大家来理解，美国有一个报社的主编，他经常接到读者的来信，读者来信都反映一个什么问题呢？做好事不得好报。特别是其中有一个小孩就说，我弟弟什么都不干，我天天在家里干活那么勤奋，可是我妈妈就把好的东西都给我弟弟，就是喜欢他，这不是不公平吗？上帝在哪里？上帝怎么能够这么不公平？这个主编呢，一直不知道怎么解释这个问题。后来有一次，他参加了一个婚礼，新郎新娘互戴戒指，出现问题了，两人把戒指戴错手了，本来应该戴到左手，但都戴到了右手上。主持婚礼的牧师就用一种诙谐的方式说，右手已经够完美了，不用再修饰了，还是用戒指来装扮左手吧。这个主编就在那个时候领悟到一个道理：一个已经够好的人，你不用去奖励他，他已经够完美，最大的奖励是什么？就是他已经成为一个好人。天道对好人最大的奖赏是什么？放到西方的文化里边来讲，上帝对好人最大的奖赏是什么？就是让你成为一个好人，这已经就是最大的回报了。这里讲“天道无亲”，它是说天道是公平的，没有偏私的。让一个人成为一个好人，那么一个好人吃点亏，这是正常的，因为你作为一个好人，这已经就是最大“道”给你的回报了。天道是公平的，没有亲疏之分，但是，它把规律、规则赋予了那些做善事的人。做一个好人，我们免去了很多的祸端祸殃，成为一个好人——这就是对我们做好人的最大的回报，不需要其他的东西来“修饰”了。所以用“有德司契”的境界去管理、去治国，就不会有大怨；用“有德司契”的境界去为人、去处事，会让你成为一个“好人”，“福虽未至，祸已远离”。</t>
   </si>
   <si>
+    <t>德经 | 王霸之道</t>
+  </si>
+  <si>
     <t>第八十章（80）</t>
   </si>
   <si>
     <t>小国寡民，使有什伯之器而不用，使民重死而不远徙。虽有舟舆（yú），无所乘之；虽有甲兵，无所陈之；使人复结绳而用之。甘其食，美其服，安其居，乐其俗。邻国相望，鸡犬之声相闻，民至老死，不相往来。</t>
   </si>
   <si>
-    <t>（理想的国家是这样的：）国土小且百姓少，就算有十倍百倍于人力的工具器械也不使用，让人民都看重死亡而不远离故乡。即使有船有车，也没有人去乘坐；即使有盔甲兵器，也没有机会陈列；使人民回归到结绳记事的淳朴状态。人民觉得自己的食物是香甜的，觉得自己的衣服是很舒适的，安于自己的居所，乐于自己的风俗习惯。邻国可以相互望见，鸡鸣狗叫之声可以相互听见，而人们直到老死，也不相往来。</t>
+    <t>（理想的国家是这样的：）国土小且百姓少，就算有十倍百倍于人力的工具器械也不使用（意思是人如果使用工具，就有投机取巧之心），让人民都看重死亡而不远离故乡。即使有船有车，也没有人去乘坐；即使有盔甲兵器，也没有机会陈列；使人民回归到结绳记事的淳朴状态。人民觉得自己的食物是香甜的，觉得自己的衣服是很舒适的，安于自己的居所，乐于自己的风俗习惯。邻国可以相互望见，鸡鸣狗叫之声可以相互听见，而人们直到老死，也不相往来。</t>
   </si>
   <si>
     <t>第八十章历来被认为是老子思想中的一个非常重要的部分——老子的理想国。大家一听都知道，在哲学上，柏拉图有《理想国》，后来就出现了康帕内拉的《太阳城》、莫尔的《乌托邦》，就是对理想社会的设定。哲学家设定理想社会都有一个非常有趣的现象：要了解人类的未来啊，先看人类的开始。因为哲学里边讲否定之否定的规律，就讲事物到最后都回归到出发点，严格地讲叫“仿佛回到出发点的运动”，是在更高的层次上重复第一阶段的某些特征，所以我们看看人类的开始。人类开始的时候，大家是平等的，所以未来人类社会的也是平等的。你看三个阶段：平等——不平等——平等。沿着这样一种哲学思路，我们来理解老子这个小国寡民，也就知道，这也是他的一种空想，但是，这种空想代表了他理想的寄托。他理想的这个国家是什么样子？别天天老打仗，别弄那么多人，大家不要经常地过多地交往，过多交往就会产生的矛盾、冲突、隔阂、战争，他想让大家和平地和谐相处，所以要把这个国家变成一个“村”。“小国寡民”，让这个国家变小，人民变少，大家就像在一个乡村里边生活。在小国寡民的理念下，他就要限定，要这样做，即使有各种器皿也不用，为什么不用呢？因为在中国的历史上有一个说法，其实和西方后来的一些思想也遥相呼应。西方有一个哲学家叫卢梭，法国的启蒙思想家，当年给法国的自然科学院写过一篇论文，获了奖，叫《科学和技术的进步使人类道德堕落》，在中国历史上也有很多人认可这种看法。庄子文章里就讲了一件关于“抱瓮老人”的事：说一次孔子带着学生去游学，子贡就看见一个老头，有这个先进的工具不用，抱着瓦罐去井里打水。当时的先进的工具是什么呢？就是辘轳，现在大家都看不见了。自己跑到井里边抱着瓦罐去打水，子贡就觉得很奇怪：这老先生怎么这么笨，辘轳就在旁边，摇一摇不就上来了吗？你自己下去干嘛呢？老先生就郑重其事地跟他讲，我的老师讲过，人如果使用机器就会有投机取巧之心，为了保持我的朴素的道德，所以我不用这个机器，不会有投机取巧之心。大家仔细思量，我们使用的工具，确实对我们的思维的方式、性格也有很大的影响，所以《道德经》讲什伯之器，不用，用最简单的工具，保持简单的心灵，保持朴素的品德。当年曾国藩在做官的时候，经常给家里边写信，告诉他儿子，你每天得下地劳动；告诉他女儿，你得给我做鞋。其实，曾国藩在乎的不是地，不是鞋子，他是觉得这样的方式，会让子女形成他要的那种性格、品德。这个东西倒是真值得研究，人类使用的工具在不断进步，千奇百怪，人要想回归到朴素的道德，就很困难。“使民重死而不远徙”，人离开家乡之后成为流民，那么很多方面就无法保证。我们前面也讲过，这国家到处都是流民，它无法稳定，因为“无恒产者无恒心”，所以你离开了自己家乡的土地，成为一个流民，这就没有办法回归到一个小国寡民的所需要的品德和素质。下边一样，“虽有舟舆，无所乘之”，这也是工具，有这个船，有这个车，不要经常去坐。我们现在也有很多人领悟出来了，打趣说，汽车是毒药，自行车是泻药，走路是补药。现在，很多人也确实奇怪，开车节省出时间了，然后回家在跑步机上跑步，这个东西确实是挺难理解，有时间走走路，不也是一种锻炼吗？下边这句话重要了，是这段话里要表达的核心意思，“虽有甲兵，无所陈之”，有军队没地方放。我不打仗，我要军队干嘛？大家注意，咱们中国的“国”字，原来氏族的时候，它是没有边界、国界的。“国”字外面这个方框是代表着城墙，“国”字的繁体字，最常用的是哪个呢？就是里边的“或”。大家仔细琢磨“或”，你看它是什么？用武器，那个“戈”不就是武器吗？用武器来看守一定的人口。这国家一出现，国家一大了，它就需要军队，所以老子为什么要小国寡民呢？不要军队，大家干脆都别打仗。在他的理想国里是没有军队存在的位置的，反对战争，祈求和平。《淮南子》里也讲了这样一件事，大禹的父亲夏鲧治国的时候，修了一座很大的城池，弄了很多的军队，结果四海有反心，诸侯都准备起来背叛。大禹即位后怎么处理的呢？他把城拆了，把军队散了，结果四海归心。其实这故事表达的也是这个意思，《淮南子》主要解读道家思想，举的这个例子也是用来印证《道德经》里讲的这一理念。“使人复结绳而用之”，有的本子叫做“民”，都一样。百姓不再用文字了，人类最早不就结绳记事吗？据说当年文字出现的时候，天雨粟，鬼夜哭。当然我们这个文明延续到今天，受惠于文字太多了，但是《道德经》里说，文字有时候也让人变得复杂，有投机取巧之心。有的人说这老子是倒退，反对文明。其实大家要理解他的苦心，他主要是让人类回归到那种朴素的、平等的、和谐的、互相不冲突的理想国的状态。我们换一个角度给大家一个直观的印象，大家都知道陶渊明的《桃花源记》，那里的人都是什么样？都活得非常的和谐，“甘其食”，吃什么都觉得很香，不挑剔。“美其服”，不是说穿着漂亮的衣服，是穿什么衣服都觉得很好，都觉得很开心。“安其居，乐其俗”，安居乐业，觉得自己那个风俗大家很喜欢，很开心。“邻国相望”，因为现在搞得这国家都跟一个村子一样，国与国之间不打仗了，邻国相望，离得很近，“鸡犬之声相闻”。读《桃花源记》，很多的时候，你能感觉到这一章的影子，“狗吠深巷里，鸡鸣桑树颠”。老子也给我们勾画了一个美丽的，看似平凡但不可企及的生活。当然，“民至老死不相往来”，不是强调不相往来，而是强调没冲突、不打仗。这一章的核心是这句话：“虽有甲兵，无所陈之。”春秋无义战，那时候战争此起彼伏，没一场是正义的战争，尸横遍野，血流成河。在这个背景下，老子就想这解决办法是什么呢？国家小一点，各过各的日子，不打仗。哲学家讲的理想国，不管是柏拉图的《理想国》、康帕内拉的《太阳城》、莫尔的《乌托邦》，还是老子讲的这个小国寡民，还是陶渊明讲的《桃花源记》，都代表着对纷乱社会的不满，都希望人类回归和谐相处的、没有冲突的、没有战争的状态。如果我们理解中国历史上的非常沉痛的两句诗，我们也就明白“小国寡民”的良苦之用心，这两句诗叫“宁做太平犬，不做乱世人”，宁可做太平世界的一条狗，也不做乱世冲突、战争频仍时候的人，因为这时候人活得连狗都不如，没有尊严。所以我常讲，有些经常叫嚣战争的人，其实都是不懂战争。真正懂得战争的残忍，就知道这和平、平静，是多么可贵。大家上中学的时候学过一篇课文，叫《最可爱的人》，里边讲的一段话让人非常有同感。它说也许你正走在去上班的路上，也许你正背着书包走在上学的路上，你觉得这很平常，可是从朝鲜回来的人会告诉你，你是生活在幸福之中。经历过战争的人会告诉你，这种情况是生活在幸福之中。这对我们也有所启示，不能简单地说小国寡民是一个倒退，得看它的现实背景，得了解它的语境，我们才能真正地理解老子的用心，我们对这些历史上有智慧的人、有慈悲心肠的人，对他们才能有深深的敬佩。见到这样有智慧、有品德的人，我们身体不在鞠躬，心灵在鞠躬。读这样的书也是一样，我们应该有敬畏，在敬畏的基础上，认真阅读，认真品味，珍惜和平与幸福的生活。</t>
   </si>
   <si>
+    <t>德经 | 复古之道</t>
+  </si>
+  <si>
     <t>第八十一章（81）</t>
   </si>
   <si>
@@ -1359,6 +1406,773 @@
   </si>
   <si>
     <t>说起《道德经》的分章，大家一般认为最早是河上公以九九归一为神秘的数字指向，把它分成了八十一章。第八十一章可以看作是全书的总结，全书思想的总结和概括就是最后这两句话，“天之道，利而不害。”天道如此，人道应该效法天道，所以下一句“圣人之道，为而不争”，一个好的领导人、统治者是如此，对我们大家来讲也是如此。韩国有一个连任联合国秘书长的聪明人，叫潘基文。他在连任就职典礼上，开口讲的就是《道德经》的这两句话，只不过他引用的是这两句话中的八个字：“利而不害，为而不争。”我怎么做联合国秘书长？我对大家有利，不起坏心，为大家谋福利，“利而不害”。我把事情做了，不为自己争名夺利，“为而不争”。我们应该有一个非常深刻的体验：道家并不是消极的、被动的、什么事都不做。什么叫无为？“为而不争”是无为的一个重要的方面，这可以看作是全部《道德经》的核心的总结。我们回头去想，“上善若水”讲“善利万物而不争”；天道讲“为而不争”。这样我们就把整个的思想落地了，知道了《道德经》最后的核心落在什么地方。现在来看一下原文，“信言不美，美言不信”，真正诚信的话，不漂亮，只会讲漂亮话的，没诚信，过度漂亮的话里，往往隐含欺骗的内容，所以大家说，真理是朴素的，真理是赤裸裸的。“善者不辩，辩者不善”，真正善良的人，不老去争辩。庄子在他文章里边经常讲，老去靠争辩，争辩胜了，又能够体现什么？“善者不辩，辩者不善”，老去争辩，老为自己找借口，老觉得自己受了无尽的委屈，这个不是善良者的表现。“知者不博，博者不知”，一个有智慧的人，不是老是吹嘘自己渊博、博学、无所不知，老是吹嘘自己无所不知的人，其实是没有智慧的。下面就讲一个有智慧的领导者应该怎么去做事。“圣人不积”，一个有智慧的领导者，不是老想着去积累财富、有形的资产。“既以为人，己愈有”，什么叫做富？什么叫做有？我老去帮助别人，为别人做事，在给别人做事情，帮助别人的过程中，获得了无尽的快乐，这不是无形资产吗？这不是精神世界的充盈吗？“既以与人，己愈多”，给别人的越多，帮别人的越多，要财富发挥它的真正的作用，在“舍”的过程中反而自己得到更多。“既以为人，己愈有；既以与人，己愈多。”2014年习近平在斐济《斐济时报》发表署名文章，也用过这两句话。中国人喜欢双赢，帮助别人。我们的理念是什么？我们给别人做的事情越多，我们感觉到自己越富有；对别人帮得越多，感觉到自己获得的更多。所以我们经常讲，我们很多的快乐是在帮助别人成长，别人有困难的时候，我们帮扶的时候，感觉到自己的内心的充盈快乐。“为人”是什么？“与人”是什么？是善利。看似付出，自己反而获得更多，自己的精神世界也更为充盈。如果我们只一味地为自己积累财富，结果呢？我们经常讲一句话，叫穷得只剩下钱了，我们的物质世界越发达，财富越多，我们的精神家园就越花果飘零。“善利万物而不争”，这是全书的最后总结。不争什么？不争言语的漂亮，只为了它的实质；不为了争辩的胜利，只为它的真理；不吹嘘自己的知识的渊博，只让知识发挥它正确的作用；不积累那么多所谓的财富，而是让财富发挥它真正的作用，让我们的精神世界越来越充盈、越来越丰富。帮人越多，自己越富有；给人越多，自己获得越多。舍得、舍得，舍的同时，也是一种获得；帮人的过程，也是一种快乐。“既以为人，己愈有；既以与人，己愈多”，这两句话仔细思量，其即是天道。“天之道，利而不害”，天道如此，善利万物不起坏心。“圣人之道，为而不争”，把事情做了，不为自己争名夺利。“为而不争”和前面我们讲过的“善利万物而不争”、“生而不有，为而不恃，长而不宰”、“功成而弗居”、“衣养万物而不为主”，这些重要的语句遥相呼应。这样，我们就把思想穿成了一串珍珠，看清楚了这本书的真正的逻辑，也看清了这本书的“落脚点”。这些成为我们生活中的座右铭，指南针，对我们的思维方式、人生格局、精神境界都会有很大的启发和启迪。第八十一章的内容，我们解读完了。到这最后一章，我们看到这一章最后落在这句话上“圣人之道，为而不争”，可以清楚的看到这本经典的目的就是把士和王修养、培养成圣。这就是这本书的内在逻辑，也是老子的良苦用心。读这本经典要掌握以下几个关键性问题。一是《道德经》本质上是一本对话体，也就是对面坐着人问的问题。只不过老子在刻书时把对面坐的人是谁、问的什么问题都省略了，而只是把他当时给的答案概括、总结、提炼、升华形成的一本著作。当我们从书里找到士、王、圣这三类问问题的人时，也就很容易抓住问题的关键了。二是王弼本《道德经》哲学思维水平非常高。在第一章就提出有无相互统一思维方式的重要性，并指出“无”是全书的众妙之门，从而让我们清楚地知道了无为、无声、无色、无味、无色……在这本书中的重要性，也借此步入众妙之门。三是我们这种以经解经的方法前后参照，避免了八十一章本子的“碎片化”倾向，并且在通篇解读中发现了老子对他认为重要问题的强调方式：首先是用重复的方式强调。比如在第十章、第五十章都重复出现“生而不有，为而不恃，长而不宰”，并且在第二章、第三十四章也都出现类似的意思。其次是用首尾呼应的方式来强调，比如二十二章就是如此。其三是用正反两个方面的方式来强调一个观点的重要性，比如第六十七章就是如此。了解了上面这些导读的内容，我们再来听课、阅读，我们就会更深刻地了解这本书的深刻内容，这本“善建者不拔”的伟大经典指导下：“修之于身，其德乃真；修之于家，其德乃余；修之于乡，其德乃长；修之于国，其德乃丰；修之于天下，其德乃普。”当然即便是逐章解决了很多问题，讲的恐怕也是蜻蜓点水，就《道德经》而言，最重要的是大家自己的阅读和领悟。</t>
+  </si>
+  <si>
+    <t>德经 | 本源之道</t>
+  </si>
+  <si>
+    <r>
+      <t>学习道德经之前，先了解《道德经》的背景（其人，其书，其道）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1、其人：老子这个人，我们要讲两个内容：一个是老子的职业背景；另一个是这本书的写作背景。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（1）老子的职业：先他掌管天下的图书，别人看不到的很多的著作他都能读得到，知识渊博。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（2）写作的背景：尹喜在函谷关对老子说，如果不写“道”的思想，就不让其过关。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2、其书：经过考古验证发现，老子亲手撰写的版本为帛书版，为了便后人理解，前人进行了优化。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（1）版本的迭代：道德经被历史名人修改后很多版，后人多以魏晋王弼的经典版进行学习和传诵。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（2）书名的由来：因为“道”和“德”出现的频率最高，故汉朝时期又名《老子》。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（3）形象的体现：《道德经》落实到现实中包含的内容——目标、方向、规则、境界、边界、底线。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3、其道：老子所写的《道德经》的受众对象主要是针对三类人而写的。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（1）第一类人 - 士：基层的领导者和管理者（推十为一，把自己放在最后的位置）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（2）第二类人 - 王：主要的领导者（善用人者为之下，姿态谦卑尊重对方）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（3）第三类人 - 圣：品德修养高，通情达理的领导者（圣人之道为而不争，为大家谋福利）。</t>
+    </r>
+  </si>
+  <si>
+    <t>【真正的大道，说不出来】【道本无名 有无同源】（真正的大道，说不出来）本章是《道德经》的门户，核心是“有”和“无”，特别强调常被忽略的“无”。道可道，非常道；名可名，非常名：道是最高、最全面的存在，用语言和逻辑讲出来就变成有局限的道，所以要借形象来领悟（如 把道比喻成风）。无，名天地之始；有，名万物之母：天地起源时混沌无形，称为无；天地成形、万物出现，称为有。任何事物都有有和无两个方面，观察事物既要从“有”的角度看它的边界，也要从“无”的角度看它的妙处。
+此两者同出而异名，同谓之玄：能把有和无合起来理解，已是高级的思维水平，叫做玄；再进一步看到无形力量（精神、信仰、家风、作风等）的巨大作用，就是玄之又玄、众妙之门。译者·韩鹏杰以“风”为形象：风无形却力量无尽，正如人的精神世界。老子提醒人们不要只看到金钱、财富等有形的东西，更要看到精神、思想、理想信念这些无形的力量；只重有形，物质越发达，精神家园就越花果飘零。</t>
+  </si>
+  <si>
+    <t>4、6、11、14、21、25、32、40、42</t>
+  </si>
+  <si>
+    <t>【好坏都是比出来的，别瞎折腾】【相对相生 无为不言】本章讲世界运动的规律和认识世界的方法，是理解《道德经》的另一扇门。用哲学的语言概括：相比较而存在，相对立而发展。天下皆知美之为美，斯恶已；皆知善之为善，斯不善已：知道美就知道丑，知道善就知道不善，对立双方互相规定、互相依存。老子随后列出有无相生、难易相成、长短相较、高下相倾、音声相和、前后相随，指出这些对立面并非固定不变，而是在对立中运动、转化。
+因此圣人处无为之事，行不言之教：越是懂得有为，越要知道哪些该无为、该舍掉，从反面认识事情，才能达到更好的有为效果，千万不要把无为理解成消极。万物作焉而不辞，生而不有，为而不恃，功成而弗居：顺应万物自然生长而不干预，创造而不占有，做事而不依仗，有功而不居功，正因不居功，功德才不离去。后文许多重要内容都已在本章提前概括出来，读熟这一章，后面很多章节都能以经解经。</t>
+  </si>
+  <si>
+    <t>3、9、11、22、24、34、36、39、40、51、57、58、63、66、77</t>
+  </si>
+  <si>
+    <t>【别树榜样，百姓就不争了】【不尚贤 无为而治】本章与第二章紧密相连，讲看问题不能一点论，要两点论：好事发展到一定程度会向反面转化。不尚贤，使民不争：尚贤本是重视人才的好事，但一旦立了标准，就有人按标准投机取巧、自我包装，真正有才能的人不屑于此，反而被过滤掉，贤名被投机者占据，所以尚贤过了头反而害了人才选拔。不贵难得之货，使民不为盗；不见可欲，使民心不乱：不炒作珍贵物品、不显露引发欲望的东西，民心才不会乱。
+圣人之治，虚其心，实其腹，弱其志，强其骨：使民心虚静、生活温饱、欲望减弱、身体强健。常使民无知无欲，使夫智者不敢为也：少用智巧套路，投机者才不敢妄为。为无为，则无不治：治理者不妄为、不折腾，按规律和规则办事，天下自然治理得好。译者·韩鹏杰强调，老子的话对面坐着的是领导者，这些话是对治理者提出的警醒：任何事都有尺度，把握不好度，好事也会变成坏事。</t>
+  </si>
+  <si>
+    <t>2、17、19、32、37、49、57、65、72</t>
+  </si>
+  <si>
+    <t>【道是阴阳调和，藏锋芒混世俗】【道冲中和 和光同尘】本章强调道是万物的本源，理解的关键在“冲”字。冲是组合字，把两点放平就是“二中”，二指阴阳；冲的本义是两股水冲到一块，象征阴阳两种力量相互中和、相互作用、动态转化。道冲，而用之或不盈：阴阳中和而成道，作用无穷无尽。渊兮似万物之宗：道渊深博厚，像万物的宗主。挫其锐，解其纷，和其光，同其尘：道收敛锋芒、化解纷争，与光明融合、与尘垢同一，深远幽暗却无处不在。吾不知谁之子，象帝之先：道先于天帝而存在，是万事万物的本源。
+译者·韩鹏杰用第四十二章“道生一，一生二，二生三，三生万物；万物负阴而抱阳，冲气以为和”来印证：三即参，阴阳参与到一起而生万物，万事万物都同时具有阴阳两面，无论怎么转都像太极图一样保持和谐。了解道冲，就掌握了一种重要思维：任何事物都是两种相反力量在动态中达成的和谐，看问题、做决策都不能只偏执一方。</t>
+  </si>
+  <si>
+    <t>1、5、9、14、42、51、56、71</t>
+  </si>
+  <si>
+    <t>【天地不偏心，政令少折腾】【天地无私 守中虚静】本章讲天地对万物的平等和治理者的虚静。天地不仁，以万物为刍狗：不仁不是残忍，而是不偏爱、不干预；天地看待万物一视同仁，像草扎的祭狗，祭祀前被尊重，祭祀后被丢弃，无所爱惜。圣人不仁，以百姓为刍狗：好的领导者对百姓也应一律公平，制定规则法令，谁都不能例外；不要因为谁弱就特殊照顾，那反而是一种偏私，让被照顾者失去自立。道家讲的不仁是“大仁”，天地不偏私地让万物自己去奋斗、去努力。
+天地之间，其犹橐籥乎：天地像风箱，中间虚静，一拉动就能鼓出风来；政令也应如此，保持虚静、简要稳定，不能今天一变明天一变。多言数穷，不如守中：政令繁多、变动频繁会把自己逼入困境，不如恰到好处、大道至简。译者·韩鹏杰提醒，这些话都是讲给领导者听的：治理要公平无私，政令要少而稳定，靠规则而不是靠折腾。</t>
+  </si>
+  <si>
+    <t>4、7、23、57、77、79</t>
+  </si>
+  <si>
+    <t>【道像母体，永远生养不停】【谷神玄牝 生生不息】本章以谷与牝为喻，把道比作孕育万物的母体，根本精神是对母亲的尊重、对生命的敬畏。谷神不死，是谓玄牝：谷指空虚的山谷，神指精神、生机；牝指女性生殖器，代表母亲。谷神不死，即这种孕育生命的力量绵延不绝，称为玄牝。玄牝之门，是谓天地根：玄牝之门是天地万物的根源，道生万物与母亲生育生命是同一个道理。绵绵若存，用之不勤：它连绵不断地存在，取之不尽、用之不竭。
+译者·韩鹏杰强调，老子用神、玄这些最高字眼来称呼谷与牝，绝不允许亵渎；一个文化里若失去对母亲的尊重、对生命的敬畏，其他方面都会崩塌。读这一章不要陷入玄虚，要读出其中朴素而伟大的情感：尊重母亲、敬畏生命，是文化延续的根基。</t>
+  </si>
+  <si>
+    <t>1、20、21、25、42、51、52</t>
+  </si>
+  <si>
+    <t>【不自私，反而活得久】【无私长久 后身先存】本章与第八、九章共同讲进退、争让、强弱：人们习惯强调争、进、强，老子偏要讲被忽略的不争、退、弱，因为它们与争、进、强是阴阳的两个方面，具有同等力量。天长地久：天地之所以长久，是因为天地不自私，不以自己的生存为唯一目的，而是为万物提供阳光雨露土壤，任万物自由生长，因此赢得人们长久的敬畏。后其身而身先，外其身而身存：圣人把自身利益放在后面，反而被众人推举到前面；把自身安危置之度外，反而安然长存。非以其无私邪，故能成其私：正因无私，才更好地成就了自己的长久与被人敬仰，这是人人都有的潜意识私心。
+本章是典型的“天道人道”两段论：先讲天道，再讲人道，人道效法天道。译者·韩鹏杰用“公仪休不受鱼”的故事说明：懂得从长远看问题、不贪眼前不该得的利益，才能长久地满足自己的愿望；只盯着私利的人，最后连私利也保不住。</t>
+  </si>
+  <si>
+    <t>5、13、66、81</t>
+  </si>
+  <si>
+    <t>【做人要像水，利人不争】【上善若水 不争无尤】本章“上善若水”是《道德经》最著名的命题，也是中华民族精神的重要代表。上善若水，水善利万物而不争：最高的智慧与品德像水一样，滋润万物、成就他人而不争功，甘处众人不愿去的低处，所以最接近道。老子借水讲了善下、善渊、善仁、善信、善治、善能、善时等品质：居善地，甘居下位；心善渊，静水深流、宁静致远；与善仁，平等仁爱地给予；言善信，说话像潮信一样讲信用；政善治，政治清正公平如水；事善能，有多种本事又专一向前；动善时，该动则动、该静则静、该绕行则绕行。
+水的“不争”有丰富含义：有边界不争（湖有湖畔、河有河堤、海有海岸），有秩序不争（前后相随、循序渐进），有牺牲不争（成就万物而默默无闻）。夫唯不争，故无尤：不争就不会招来怨恨和过错。译者·韩鹏杰指出，老子不是趴在河边悟道，而是借水的形象传达从战争、政治、人生中领悟的智慧：善于成就别人，同时也成就自己，这正是双赢。</t>
+  </si>
+  <si>
+    <t>43、61、63、66、68、69、76、78、81</t>
+  </si>
+  <si>
+    <t>【见好就收，别贪】【功成身退 知止不殆】本章讲“不盈”：凡事勿求满，适可而止。持而盈之，不如其已：端着一盘盛满的水走路，战战兢兢还不断洒出，不如少装一点，走得更轻松。揣而锐之，不可长保：把锥子磨得极锋利，一碰就断；削铅笔削到只剩笔头，再尖也保不住。金玉满堂，莫之能守：家中满是财富珍宝，反而守不住。富贵而骄，自遗其咎：因富贵而骄傲自满，是自取灾难。功遂身退，天之道也：功成而不居功、懂得退让，才符合天道。
+译者·韩鹏杰用民间故事讲这个道理：弟弟只拿一点金子平安回家，哥哥贪心装满全身，被太阳晒化。第七章讲先后，第八章讲不争，第九章讲不盈，都提醒人知进退、懂谦让。中国文化的“中”就是恰到好处，不走到极端：物极必反、乐极生悲、泰极否来，好事到了极端容易向坏处转化，所以要战战兢兢、如履薄冰地把握分寸。</t>
+  </si>
+  <si>
+    <t>2、4、24、32、44、77、78</t>
+  </si>
+  <si>
+    <t>【身心合一，养了不占】【抱一守静 玄德不宰】本章与十一、十二章共讲“虚静”：心里放空才能宁静，宁静才能看清事物本质，抵抗外在诱惑。载营魄抱一，能无离乎：身体像车载着魂魄，灵魂与肉体能否合一不分离？不要做丢了灵魂的行尸走肉。专气致柔，能如婴儿乎：聚结精气、身心柔软，能否像婴儿一样纯粹？涤除玄览，能无疵乎：清除内心杂念，能否像明镜一样无瑕疵？爱民治国，能无为乎：治理能否顺其自然、不妄为？天门开阖，能为雌乎：面对外界纷扰，能否守住柔静？明白四达，能无知乎：通达事理之后，能否不用机巧套路？
+一连串反问都在讲修养路径：魂魄不离、身心合一、少欲守静、厚道不用智巧。最后点出玄德：生之畜之，生而不有，为而不恃，长而不宰——生养万物而不占有、不倚仗、不主宰，这是最高深的德。译者·韩鹏杰认为这一章是后面九章的总纲，虚静既是个人修养，也是治国的基础。</t>
+  </si>
+  <si>
+    <t>12、16、39、42、51、52、55、57、65、71、75</t>
+  </si>
+  <si>
+    <t>【空的地方才有用】【有以为利 无以为用】本章讲“无”的作用，用三个日常形象说明虚空的巨大价值。三十辐共一毂，当其无，有车之用：车轮有三十根辐条，车毂中间是空的，车轮才能转动，才有车的功用。埏埴以为器，当其无，有器之用：黏土烧成器皿，中间是空的，才能盛水装物。凿户牖以为室，当其无，有室之用：开凿门窗建成房屋，中间是空的，人才能居住。有之以为利，无之以为用：实体提供便利条件，虚空成就实际功用，有与无相互成全。
+译者·韩鹏杰指出，“利用”这个词就来自本章。第十章讲虚静，本章讲怎样虚静——心里放空，去掉杂念，才能听得进别人的意见、看得见别人的长处、学得到别人的优点，虚怀若谷、满招损谦受益。中国文化的悟道方式是“给一个形象，自己领悟”，本章就是最好的示范：通过车、器、室三个形象，让人领悟空与用的道理。</t>
+  </si>
+  <si>
+    <t>1、2、12、40、45、66</t>
+  </si>
+  <si>
+    <r>
+      <t>艳丽的色彩看多了会让人眼花缭乱；美妙的音乐听多了会伤害人的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>听力；过于丰盛的食物吃多了会让人味觉错乱；沉溺于驰马打猎，会让人心神狂乱；珍贵的金银财宝，会让人行为不轨。因此圣人只求吃饱肚子而不求感官享受，摒弃感官享受（过度的欲望）而选择简单朴素安定知足的生活方式。</t>
+    </r>
+  </si>
+  <si>
+    <t>【欲望太多，人就废了】【去欲存真 为腹不为目】本章讲外在诱惑对心灵的扰乱，以及如何以内心的虚静守住根本。五色令人目盲：颜色太多太杂，反而区分不出好坏，视觉被迷乱；五音令人耳聋：高音快节奏听多了，好音乐也分辨不出来；五味令人口爽：厚食重味吃多了，味觉被破坏（爽是错乱）；驰骋畋猎令人心发狂：声色犬马让人心静不下来；难得之货令人行妨：被炒作的珍奇之物让人行为失当。老子并不要求消灭这些享受，而是说要以内心的虚静合理把握，适可而止。
+是以圣人为腹不为目，故去彼取此：圣人重实质内容，不重外在浮华；取舍的标准是看什么最重要——健康、营养、真实比外表颜色更重要。译者·韩鹏杰把本章与第十章、十一章连起来读：虚静的心才能看清本质，处其厚不居其薄，掌握生命中真正重要的东西，返璞归真。</t>
+  </si>
+  <si>
+    <t>10、11、19、35、44、46、53</t>
+  </si>
+  <si>
+    <t>【荣辱都是浮云，命最金贵】【宠辱不惊 贵身托天下】本章讲宠辱与生命，核心是如何看待得失、珍视生命，什么样的人才可托付天下。宠辱若惊：得到宠幸和失去宠幸都会惊恐。为什么？宠为下：被宠的人在下面，宠我们的人在上面，所以得之若惊（怕失去），失之若惊（更恐惧），这叫宠辱若惊。能做到宠辱不惊、淡然处之，是难得的人生境界。贵大患若身：有身体就有祸患，身体代表利益，也带来疾病与麻烦；但身体是摆脱不掉的，所以更要珍视它。
+吾所以有大患者，为吾有身，及吾无身，吾有何患——不把身体和生命当回事的人（为了私欲、虚荣、争斗，随便豁出性命；为了名利，把自己身体不当回事），坐到重要位置上是很可怕的；声色犬马、厚食重味正是戕害生命。贵以身为天下，若可寄天下；爱以身为天下，若可托天下：真正把自身生命看得与天下一样贵重、肯为天下担当牺牲的人，才值得把天下托付给他。译者·韩鹏杰区分两种勇敢：无赖式的勇敢不把命当回事，有责任的勇敢珍视生命又肯担当，后者才值得托付。</t>
+  </si>
+  <si>
+    <t>7、44、50、72、74、75</t>
+  </si>
+  <si>
+    <t>【道看不见摸不着，但能管今天】【道无状象 执古御今】本章形容道大象无形却无处不在，并指出知古通今的方法。视之不见名曰夷，听之不闻名曰希，搏之不得名曰微：道太细微，看不见、听不到、摸不着，三个词都说明道不可用感官把握。此三者不可致诘，故混而为一：不能用语言追问道在哪里，它混然一体。其上不皦，其下不昧，绳绳不可名：道不明不暗、不上不下，绵延存在却无法命名。无状之状，无物之象，是谓惚恍：道没有具体形状和物象，似有若无。迎之不见其首，随之不见其后：寻不到它的首尾。
+执古之道，以御今之有：了解古往今来的大道，才能把握今天、做好今天的事；能知古始，是谓道纪：知道万物开始的道理，就是把握了道的纲领。译者·韩鹏杰用庄子的“道在瓦片、稗草、大小便中”来说明道无在无不在，越往下越有；用风的形象说明道无形却左右万物。学习本章要记住：道看不见摸不着，但真实存在、无处不在，了解它才能做好今天的事。</t>
+  </si>
+  <si>
+    <t>1、4、21、35、41</t>
+  </si>
+  <si>
+    <t>【高人深不可测，静下来才清】【微妙玄通 静之徐清】本章讲基层领导者“士”应有的修养。古之善为士者，微妙玄通，深不可识：善于做士的人，智慧微妙、通达深远，难以被了解，所以要强为之容（勉强形容）。豫兮若冬涉川：像冬天过河一样谨慎，一步一探；犹兮若畏四邻：像敬畏四邻一样不敢妄动；俨兮其若客：庄重像做客；涣兮若冰之将释：温和像冰雪消融；敦兮其若朴：敦厚像未经雕琢的木头；旷兮其若谷：胸怀开阔像山谷；混兮其若浊：包容混同像浊水。
+孰能浊以静之徐清？孰能安以久动之徐生：浊水静下来才能慢慢澄清，安定的状态动起来才能慢慢焕发生机，这是“静中求清、动中求生”的修养。保此道者不欲盈，夫唯不盈，故能蔽而新成：守道者不求满，留出空间，舍弃旧的东西才能革故鼎新。译者·韩鹏杰强调，书中的话多针对具体的人讲，本章针对带领十几人做事的小组长等“士”阶层，说明基层领导者也需要很高的素质：谨慎、敬畏、质朴、虚怀、不盈。</t>
+  </si>
+  <si>
+    <t>16、20、26、65</t>
+  </si>
+  <si>
+    <t>【心放空，看万物怎么转回来】【致虚守静 观复知常】本章承第十五章，进一步讲虚静观复、知常守根。致虚极，守静笃：把心放到极度虚空、极度宁静的状态，不是枯木死灰，而是心灵安稳、不受杂念干扰。万物并作，吾以观复：万物纷繁生长，观察它的根本规律就是一个“复”字，反复循环、复归本根。夫物芸芸，各复归其根：万物虽然纷纭，最终都要回归自己的根本。归根曰静，静曰复命，复命曰常：归根就是静，静就是复归本性，复归本性就是恒常之道。
+知常容，容乃公，公乃王，王乃天，天乃道，道乃久，没身不殆：懂得恒常之道就能包容，包容就公正，公正就周全，周全就合天，合天就合道，合道就长久，终身不会遇到危险。译者·韩鹏杰说，从草的枯荣到人的生死，都体现“复”的规律；观察规律是为了认识自己、掌控自己：知道哪些因素会带来负面状态，就主动避免；知道哪些条件带来积极状态，就主动创造，让好的状态恢复。</t>
+  </si>
+  <si>
+    <t>10、15、25、26、45、47、52、55</t>
+  </si>
+  <si>
+    <t>【最好的领导，百姓感觉不到他】【太上无为 百姓自然】本章讲领导者的层次与境界。太上，下知有之：最高明的领导者，百姓只隐隐知道有他这个人，因为他不过多干预、不越边界，该管的事管好，不该管的放手。其次，亲而誉之：次一等的领导者被百姓亲近、赞誉。其次，畏之：再次一等的，百姓畏惧他。其次，侮之：最差的，百姓轻侮他。信不足焉，有不信焉：领导者自身诚信不足，百姓自然不会信任他。悠兮其贵言：最高境界是少言、贵言，不唠里唠叨，把话讲得有分量。功成事遂，百姓皆谓我自然：事情办成了，百姓都觉得是我们自己自然而然做成的，而不是领导者的功劳和主宰。
+译者·韩鹏杰用“太上”的拆字讲：大上加一点才是太，点放下才成太，放到上面就成犬，寓意善于处下才能真正居上，太太、处长等词都蕴含此理。最好的教育和管理也是如此：不越俎代庖，让孩子、下属自己把事情做成，他们才有自信和成长，功成事遂皆谓我自然。</t>
+  </si>
+  <si>
+    <t>3、18、23、57、60、69、80</t>
+  </si>
+  <si>
+    <t>【世道坏了，才有人喊仁义】【大道废 仁义出】本章与第十九章原为一章，讲“越缺什么越提倡什么”的历史递降逻辑。大道废，有仁义：大道被废弃了，才需要提倡仁义；六亲不和，有孝慈：家庭不和睦了，才强调孝慈；国家昏乱，有忠臣：国家混乱了，才显出忠臣。智慧出，有大伪：智巧盛行，反而产生大伪诈。译者·韩鹏杰指出，这是老子的历史观：有道的时候不需要讲德，失道才讲德，失德才讲仁，失仁才讲义，失义才讲礼，一层一层往下掉。
+一个社会天天提倡道德，正说明道德已经滑坡；什么时候妇女节、教师节不再成为问题，才说明相关地位真正提高了。这不是否定仁义孝慈，而是提醒人们不要靠表面提倡来补救，要从根本上回到道。把第十八、十九章连起来读：与其用仁义、智巧等外在名目补救，不如回归素朴本心，做个好人、存点好心、行些好事。</t>
+  </si>
+  <si>
+    <t>17、19、38、65</t>
+  </si>
+  <si>
+    <t>【少玩心眼，回归朴实】【绝圣弃智 见素抱朴】本章主张绝弃外在名目，回归素朴本心。绝圣弃智，民利百倍：抛弃圣贤名号和智巧机心，百姓反而得到百倍利益；绝仁弃义，民复孝慈：不刻意提倡仁义，百姓反而自然做到孝慈；绝巧弃利，盗贼无有：清除技巧和利益诱惑，盗贼就不会产生。此三者以为文不足：仅仅在理论上讲这三条还不够，要落实为具体方向——见素抱朴，少私寡欲，绝学无忧：行为单纯、内心淳朴，减少私心、降低欲望，不为纷繁的学问和机巧所惑，就没有忧虑。
+译者·韩鹏杰说，道家认为人的本心就是真心，真心就是朴素之心，朴素之心就是少私寡欲；外在花花绿绿的学问看多了，反而把人搞乱。读经典要由博返约，最后陪我们一生的可能只是一两本书、一两句话，真传一句话，假传万卷书。绝学无忧不是不要学习，而是学真正的大道，不被浮华知识蒙蔽。</t>
+  </si>
+  <si>
+    <t>3、12、18、28、38、57、65、80</t>
+  </si>
+  <si>
+    <t>【别人都热闹，我独守本分】【独泊守母 大智若愚】本章是得道者的自画像。唯之与阿，相去几何？善之与恶，相去若何：恭敬的应答与呵斥相差多远？善与恶又相差多少？老子提醒，是非善恶的界限并非表面看起来那么分明，好事也可能带来坏结果。人之所畏，不可不畏：但众人共同敬畏的规则，也要敬守，不要为了标新立异而违背公认的规范。众人熙熙，如享太牢，如春登台：众人都热热闹闹，像参加盛宴、春日登台；我独泊兮，其未兆，如婴儿之未孩：得道者独自淡泊、无动于衷，像还不会笑的婴儿。
+众人皆有余，而我独若遗：众人都显得富足有余，得道者却像有所遗失。我愚人之心也哉，沌沌兮：一副愚人心肠，混沌淳朴。俗人昭昭，我独昏昏；俗人察察，我独闷闷：世人精明，得道者看似糊涂宽厚。澹兮其若海，飂兮若无止：他像大海一样淡泊深沉，像长风一样自由无羁。众人皆有以，而我独顽似鄙：世人都有用处，他看似冥顽无能。我独异于人，而贵食母：与众人不同，因为他以大道为归依。本章刻画了不随波逐流、独立守道的精神境界。</t>
+  </si>
+  <si>
+    <t>6、15、41、70</t>
+  </si>
+  <si>
+    <t>【大德跟着道走，恍惚里有真东西】【孔德从道 惚恍有精】本章讲大德与道的关系，证明道真实存在、可以验证。孔德之容，惟道是从：大德之人的样子，就是坚定地依道而行，“孔”是大，高僧大德即此意。道之为物，惟恍惟惚：道这个东西恍恍惚惚、没有固定形体；恍惚不是迷糊，而是心中忽然有光、有所领悟的顿悟状态。惚兮恍兮，其中有象；恍兮惚兮，其中有物：恍惚之中有境界、有内容。窈兮冥兮，其中有精：深远幽暗之中有精神；其精甚真，其中有信：这精神真实不虚，其中包含可信、可验证的规律。
+自古及今，其名不去，以阅众甫：从古至今，道的名字不曾消失，凭借它可以认识万物起始。吾何以知众甫之状哉？以此：我就是凭借道来认识圣人得道的状态。译者·韩鹏杰强调，道不仅是万物的本源和规律，也是人生的境界；离开了道，人就变成无源之水、无本之木。这一章让人对道建立确信：它看不见摸不着，但真实存在，是精神世界的根基。</t>
+  </si>
+  <si>
+    <t>1、6、14、42、51</t>
+  </si>
+  <si>
+    <t>【能弯才能直，不争才赢】【曲全枉直 不争而胜】本章开头即主旨：曲则全，枉则直——懂得委婉迂回，才有更圆满的结果，像水一样绕开障碍、曲折流淌，才能到达目标；洼则盈——低洼处先被水灌满，善于处下才能获得更多；敝则新——破旧才有更新，世界有生有灭才生生不息；少则得，多则惑——知道自己懂得少才会努力学习，贪多反而迷惑。是以圣人抱一为天下式：圣人持守“一”作为天下范式，“一”就是阴阳两者的统一，看问题不能偏颇，要把对立两面合起来理解，就像同是数字6，对面看是9，各有立场。
+不自见故明，不自是故彰，不自伐故有功，不自矜故长：不固执己见才看得清，不自以为是才声名彰显，不自我夸耀才保有功劳，不自高自大才长久。夫唯不争，故天下莫能与之争：因为不与别人争夺，天下没有人能争得过他。古之所谓曲则全者，岂虚言哉，诚全而归之：古人说的曲则全，确实能把圆满的结果带回来。本章教人以迂回、谦下、统一的思维处理问题。</t>
+  </si>
+  <si>
+    <t>2、24、28、39、45、66、78</t>
+  </si>
+  <si>
+    <t>【少说话，顺其自然】【希言自然 同道同德】本章讲少言自然、同气相求。希言自然：珍惜言语、少发号施令，顺其自然才是规律。飘风不终朝，骤雨不终日：狂风刮不过一个早晨，暴雨下不了一整天，天地发的“脾气”尚且不能长久，何况人呢？人不应长期处于急躁、暴躁、浮躁的情绪状态。从事于道者，同于道；德者，同于德；失者，同于失：追求道的人与道相合，修养德的人与德相合，放任过失的人与过失相合。
+同于道者，道亦乐得之；同于德者，德亦乐得之；同于失者，失亦乐得之：你喜欢什么、亲近什么，就会被什么吸引和成就，人身边聚集什么样的人，往往取决于你自己是什么样的人。信不足焉，有不信焉：自己诚信不足，别人自然不会信任你。译者·韩鹏杰指出，本章看似同语反复，其实在反复劝告：要让自己的境界不断提高，就要亲近有道有德的人和事，勇于发现并改正缺点，路是自己走出来的。</t>
+  </si>
+  <si>
+    <t>5、17、56、81</t>
+  </si>
+  <si>
+    <t>【踮脚站不稳，跨步走不远】【不企不跨 去余去赘】本章列举自见、自是、自伐、自矜四种毛病，提醒人们平稳谦逊。企者不立：踮起脚尖想站得高，反而站不稳；跨者不行：跨着大步想走得快，反而走不远，稳定才能致远。自见者不明：固执己见的人看不清，兼听则明、偏听则暗；自是者不彰：自以为是，德行和功绩反不能彰显；自伐者无功：自我夸耀、攻击别人，反而把功劳送掉；自矜者不长：自高自大、放不下虚荣，反而失去成长机会。
+其在道也，曰余食赘行：这些行为在道看来，就像吃饱了再吃、身上长赘瘤，多余无用；物或恶之，故有道者不处：人们厌恶它们，有道的人不做这些事。译者·韩鹏杰用项羽举例：力拔山兮气盖世，却因骄傲自大、听不进意见，落得自刎乌江的下场。孔子讲毋意、毋必、毋固、毋我，佛家讲无我相，与老子相通。做事要稳扎稳打，收敛自见、自是、自伐、自矜，才能不断进步。</t>
+  </si>
+  <si>
+    <t>2、9、22、30、33</t>
+  </si>
+  <si>
+    <t>【人跟地，地跟天，天跟道，道就这样】【道法自然 四大归宗】本章是《道德经》极重要的一章，把道确立为宇宙本源，并提出全书最高法则道法自然。有物混成，先天地生：有一个混然一体的东西，先于天地而存在；寂兮寥兮：它无声无形；独立不改，周行而不殆：独立存在、永不改变，循环运行、永不停止，可以为天下母：可以看作天地万物的母亲。吾不知其名，字之曰道，强为之名曰大：不知它叫什么名字，勉强称它为道，再勉强称它为大。大曰逝，逝曰远，远曰反：大则向前运行，运行则越走越远，远到极点又返回本根，这是道的运动轨迹——周而复始。
+道大，天大，地大，王亦大，域中有四大，而王居其一焉：道、天、地、人（王）都是大的，人只是四大之一，不能自大。人法地，地法天，天法道，道法自然：人效法地，地效法天，天效法道，道效法它本来的样子，自然就是本该如此。译者·韩鹏杰强调，道法自然是全书信仰和规则的源头，人要敬畏天道，与天地和谐相处。</t>
+  </si>
+  <si>
+    <t>1、6、16、40、42、45、51</t>
+  </si>
+  <si>
+    <t>【稳重是轻浮的根，安静是躁动的主】【重静为本 轻躁失根】本章讲重与轻、静与躁的关系。重为轻根：稳重是轻率的根本，要拿稳重控制住轻率，不让它表露、掌控自己；静为躁君：宁静是急躁的主宰，用安静、宁静、冷静控制浮躁、急躁、暴躁。是以圣人终日行不离辎重：有修养的人像行军不离粮草辎重一样，始终持守稳重这个根本。虽有荣观，燕处超然：面对华美堂皇的外在诱惑，依然安处超然，不为其所动。奈何万乘之主，而以身轻天下：为什么掌握大权的君主，却为了个人享乐而轻率地对待天下大事？
+轻则失根：轻率轻浮就失去根本，像飘蓬浮萍没有根基；躁则失君：浮躁急躁就失去对自己的掌控，冲动之下常常酿成大祸。译者·韩鹏杰用“路怒”举例：开车偶有小摩擦就粗口相向甚至拔刀，动手前问自己要不要动手、后果如何、有无别的办法，几秒钟的冷静可能改变结果。开头八字“重为轻根，静为躁君”与结尾“轻则失根，躁则失君”都是至理名言。</t>
+  </si>
+  <si>
+    <t>15、16、45、61</t>
+  </si>
+  <si>
+    <t>【会用人的人，没有废人】【善救无弃 袭明要妙】本章讲善行无迹、善救无弃。善行无辙迹：真正的善行不留下痕迹，做了好事为了留名、作秀，就走到反面；善言无瑕谪：会说话的人语言没有瑕疵，与其多言被挑毛病，不如大音希声、无言胜有声；善数不用筹策：真正会计算的人不用算盘筹码，很多事情越算计越被算计，厚道才是最高的聪明；善闭无关楗而不可开：真正会关闭的人不用门闩门锁，心门上锁就找不到锁在哪里；善结无绳约而不可解：真正会捆绑的人不用绳索，情丝情网看似无形却解不开。
+是以圣人常善救人，故无弃人；常善救物，故无弃物：圣人善于救人救物，天下没有可抛弃的人、没有可抛弃之物，你没发现用处不等于无用，无用方为大用。善人者，不善人之师；不善人者，善人之资：善人是恶人的老师，恶人是善人的借鉴，“师资”一词正源于此。不贵其师，不爱其资，虽智大迷：不尊重老师、不爱惜借鉴，再聪明也是大迷惑，这是道的枢要。做人要善行不留痕迹，看人看物发现其用处，并善于从正反两方面学习。</t>
+  </si>
+  <si>
+    <t>33、49、62</t>
+  </si>
+  <si>
+    <t>【知道啥是强，却甘愿守弱】【知雄守雌 复归于朴】本章是“抱一为天下式”的例证，讲刚柔、黑白、荣辱的辩证统一。知其雄，守其雌，为天下谿：知道自己强大，却不恃强，安守柔雌，甘做天下的溪谷，水都汇到低处来，反而源远流长，复归于婴儿：回归婴儿般纯真柔软。知其白，守其黑，为天下式：知道明亮，却安守暗黑，做天下范式，常德不忒，复归于无极：德行不出差错，回归无穷的境界。知其荣，守其辱，为天下谷：知道荣耀，却安守屈辱，甘做天下的虚谷，常德乃足，复归于朴：德行充足，回归素朴。
+朴散则为器，圣人用之则为官长，故大制不割：素朴分散为万物之器，圣人顺应本性管理，最好的制度不伤害本性。译者·韩鹏杰强调，守雌、守黑、守辱不是没有经历过强、白、荣就假装谦卑，而是先有实力和成就，再有资格谈守，比如书法先经历精巧，才能返璞归真。记住十八个字：知其雄守其雌，知其白守其黑，知其荣守其辱，就是这一章的核心智慧。</t>
+  </si>
+  <si>
+    <t>19、22、32、37、55</t>
+  </si>
+  <si>
+    <t>【天下不能强取，越折腾越坏】【天下神器 去甚去奢】本章讲天下不可强为、强取。将欲取天下而为之，吾见其不得已：想用强力、武力夺取天下并按个人意志治理，注定达不到目的。天下神器，不可为也，不可执也：天下是神圣之物，不可强行干预，不可强行把持；为者败之，执者失之：强行去做的必失败，死死抓住的必失去。是以圣人无为，故无败；无执，故无失：圣人顺其自然、不妄为，所以不会失败；不强行把持，所以不会失去。
+故物或行或随，或嘘或吹，或强或羸，或载或隳：万物本性各不相同，有前行有跟随，有轻嘘有急吹，有强壮有羸弱，有安稳有毁坏，不能用一个标准、一种方式强求。是以圣人去甚，去奢，去泰：圣人去掉极端的、奢侈的、过分的言行和欲望。译者·韩鹏杰指出，这一章要结合时代背景理解：春秋末期诸侯争霸、生灵涂炭，老子提出小国寡民设想，反对强为；读这一章要体会其中的沉痛感，任何事有生必有灭、有成必有败，强求和把持都违背天道。</t>
+  </si>
+  <si>
+    <t>30、37、48、60、64</t>
+  </si>
+  <si>
+    <t>【别靠打仗逞强，打完就遭报应】【不以兵强 果而勿矜】本章与三十一章表达中国人对战争的痛恨与对和平的热爱。以道佐人主者，不以兵强天下：用道辅佐君主的人，不靠武力逞强天下。其事好还：用兵之事很快有报应，你打人多重，反作用力就多重。师之所处，荆棘生焉：军队到过的地方，荆棘丛生、断壁残垣；大军之后，必有凶年：大战之后必有灾荒凶年。善有果而已，不敢以取强：不得已打仗，达到保卫目的就停手，不敢逞强。
+果而勿矜，果而勿伐，果而勿骄：胜利了不自大、不夸耀、不骄傲；果而不得已，果而勿强：胜利是出于不得已，胜了也不逞强。物壮则老，是谓不道，不道早已：事物强盛到极点就走向衰败，逞强求壮不合道，不合道就很快灭亡。译者·韩鹏杰说，这章最后三句话值得牢记：师之所处荆棘生焉，大军之后必有凶年，物壮则老。战争不可轻易发动，对待战争的态度就是对待同胞生命的态度；中华民族热爱和平，不惹事也不怕事。</t>
+  </si>
+  <si>
+    <t>24、29、31、46、67、68、69</t>
+  </si>
+  <si>
+    <t>【战争是丧事，赢了也该哭】【兵为不祥 胜以丧礼】本章继续讲对待战争的态度，主张以丧礼对待战争。夫兵者，不祥之器：兵器是不祥之物，人们都厌恶它，所以有道的人不使用它。君子居则贵左，用兵则贵右：平时以左为尊，作战时以右为尊，用兵属于凶事。兵者不祥之器，非君子之器，不得已而用之，恬淡为上：战争不是君子常用的东西，万不得已才用，还要淡然处之。胜而不美，而美之者，是乐杀人：打了胜仗不应赞美庆祝，赞美胜利就是以杀人为乐；以杀人为乐的人，不可能得志于天下。
+吉事尚左，凶事尚右：吉庆之事尚左，凶丧之事尚右；偏将军居左，上将军居右，就是用办理丧事的礼节来对待战争。杀人之众，以悲哀泣之，战胜以丧礼处之：战争杀人众多，要带着悲哀的心情参与，战胜了也要用丧礼的仪式对待。译者·韩鹏杰强调，这两章应该进小学课本，让和平的种子从小种下；战争胜利后第一件事不是放肆庆祝，而是祭奠双方的死者，因为他们都是生命。</t>
+  </si>
+  <si>
+    <t>30、46、67、68、69</t>
+  </si>
+  <si>
+    <t>【道朴实无名，懂得停才安全】【道常无名 知止不殆】本章讲道的特点和知止的智慧。道常无名，朴虽小，天下莫能臣：道恒常无名，它的重要属性是朴实厚道；朴像原木，看似微小，却没有任何东西能让它臣服。侯王若能守之，万物将自宾：领导者若能守住朴实厚道，万物自然宾服归附。天地相合，以降甘露，民莫之令而自均：天地阴阳相合降下甘露，没有人命令，雨露自然均匀，治理也应如此自然而然。
+始制有名，名亦既有，夫亦将知止，知止可以不殆：人类社会开始有制度、名分是合理的，但有了名分制度要懂得边界，不能制度崇拜、名分崇拜，做过了头就走向反面；知道适可而止，才能避免危险。譬道之在天下，犹川谷之于江海：道在天下，就像川谷流向江海，是自然归附的过程，不是强迫。译者·韩鹏杰强调，老子反复用重复和强调来突出重要思想，本章的核心就是朴与知止：做事朴实厚道，对制度名分保持克制，知道边界和限度，物极必反，知止不殆。</t>
+  </si>
+  <si>
+    <t>1、3、9、28、37、44</t>
+  </si>
+  <si>
+    <t>【了解别人是聪明，管住自己才是强】【自知者明 自胜者强】本章像一首哲理诗，讲认识自己、战胜自己。知人者智，自知者明：了解别人是智慧，了解自己才是高明，人贵有自知之明，眼睛能看远方却看不见自己的眉毛。胜人者有力，自胜者强：战胜别人只是有力，能战胜自己的欲望、弱点才是真正的强大，西方强国强调强加于人，只是胜人者有力。知足者富：知道满足才是真正的富有，贪得无厌永远觉得匮乏；强行者有志：坚持按道去做、知难而进的人才有志向。
+不失其所者久：不离开自己的归宿才能长久，“所”就是精神家园，物质再发达也不能让精神家园花果飘零。死而不亡者寿：身死而精神不亡，才是真正的长寿，那些思想家的光芒像群星，在黑暗时指引方向。译者·韩鹏杰说，这一章既写给领导者也写给普通人：自知、自胜、知足、强行、守所、精神不亡，六层递进，是中国文化中极高的人生境界。</t>
+  </si>
+  <si>
+    <t>24、27、44、46、47、52、54、71</t>
+  </si>
+  <si>
+    <t>【道到处都是，有功不占】【大道泛流 不居成大】本章讲道无处不在、成就万物而不主宰，因不自大而成其大。大道泛兮，其可左右：道如水、如风，无处不在，左右逢源。万物恃之而生而不辞：万物依赖道生长，道从不推辞；功成而不名有：成就万物却不居功留名。衣养万物而不为主：护养万物却不做主宰，不要求感恩戴德。常无欲，可名于小：道无欲谦下，可以说它渺小；万物归焉而不为主，可名为大：万物归附它却不自居为主，又可以说它伟大。以其终不自为大，故能成其大：正因为它始终不自以为大，才真正成就了伟大。
+译者·韩鹏杰强调，这一章讲量变质变、从小到大的道理：合抱之木生于毫末，九层之台起于累土，千里之行始于足下；天下难事必作于易，天下大事必作于细。做人做事不要自高自大、好高骛远，要虚怀若谷、脚踏实地，把容易的事当难事做，把小事做好，一步一步成就伟大。</t>
+  </si>
+  <si>
+    <t>2、51、77</t>
+  </si>
+  <si>
+    <t>【掌握大道，平淡却用不完】【执大象 道淡无味】本章讲守道则天下归往，平淡才是真。执大象，天下往：掌握大道（大象即道），天下人都会归附；往而不害，安平太：归附而不受伤害，安详、平稳、太平。乐与饵，过客止：音乐与美食能让人停下脚步，这些外在享受有吸引力，但也容易让人半途而废，不能沉溺其中。道之出口，淡乎其无味：道说出来淡而无味，不像美食音乐那样刺激；视之不足见，听之不足闻，用之不足既：看不见、听不到，却取之不尽、用之不竭。
+译者·韩鹏杰说，我们日常所用而不知，天天都在用道却不自知；饮食清淡有益健康，人格返璞归真才接近道，清水出芙蓉、天然去雕饰是艺术的高境界。年轻人都觉得自己会成为伟大人物，最后发现伟大来自平凡，把自己看得平凡，才能重归于朴、重归于真、重归于道。真正的力量不是热闹炫耀，而是平淡之中无穷无尽。</t>
+  </si>
+  <si>
+    <t>12、14、41</t>
+  </si>
+  <si>
+    <t>【想收拾谁，先让他膨胀】【欲歙固张 柔弱胜刚】本章把相反相成的思维讲得最直白，并提醒含藏的力量与边界。将欲歙之，必固张之：想收敛它，先让它张开；将欲弱之，必固强之：想削弱它，先让它强大（捧杀）；将欲废之，必固兴之：想废弃它，先让它兴盛，举得越高摔得越重；将欲夺之，必固与之：想夺取它，先给予它，钓鱼先下鱼饵。是谓微明：这种微妙而明确的智慧叫微明。柔弱胜刚强：柔弱可以战胜刚强。鱼不可脱于渊：鱼不能离开水，策略不能脱离客观条件；国之利器不可以示人：国家的利器不能轻易示人，时时亮剑威胁别人，别人就想折断你的剑。
+译者·韩鹏杰用捧杀典故解释：杀君马者道旁儿，过分夸奖、吹捧使人骄傲自满、退步失败，关羽过不了奉承关而败走麦城；两军对垒时老弱残兵挑衅、敌人弃辎重诱敌，都是将欲夺之必固与之。本章不是说用阴谋，而是讲事物转化的规律：看清对立面的运动，力量与边界都要含藏，不能张扬炫耀。</t>
+  </si>
+  <si>
+    <t>2、43、58、63、65、76、78</t>
+  </si>
+  <si>
+    <t>【不瞎折腾，天下自然安定】【道常无为 天下自定】本章是《道经》的收束，讲无为而无不为。道常无为而无不为：道恒常无为，不妄为、不干预，却成就万事万物。侯王若能守之，万物将自化：领导者若能守住道，万物自然化育成长。化而欲作，吾将镇之以无名之朴：万物生长中欲望萌动时，用无名的素朴去镇服安定。无名之朴，亦将无欲：素朴本身没有欲望。不欲以静，天下将自定：没有欲望就能安静，天下自然安定。
+译者·韩鹏杰把无为理解为：不违背规律、不妄为、不折腾，而不是消极不作为；治理的最高境界是让事物按自己的本性生长，让百姓自然发展生产、自然安定。从第一章到第三十七章是《道经》，讲道本身；后三十八章起是《德经》，讲道落实到人。把这两部分合起来读，“道在前而德在后”，做一切事才能顺理成章。</t>
+  </si>
+  <si>
+    <t>3、28、29、32、48、57、60、80</t>
+  </si>
+  <si>
+    <t>【真有德的，不觉得自己有德】【上德不德 去华取实】本章开启《德经》，讲真正的德是自然无心的。上德不德，是以有德：真正有德的人不把德行当回事，做了好事自然忘掉，反而真有德；下德不失德，是以无德：境界不高的人总怕德行失去，处处表现、宣扬，反而无德。上德无为而无以为：有德者自然作为，没有功利目的；下德为之而有以为：无德者做事带着目的。上仁为之而无以为：仁者做好事不为私欲；上义为之而有以为：讲义的人制定规则，多少带着私心；上礼为之而莫之应，则攘臂而扔之：讲礼的人若没人响应，就卷起袖子强推。
+失道而后德，失德而后仁，失仁而后义，失义而后礼：道、德、仁、义、礼逐层下降。夫礼者，忠信之薄而乱之首：礼是忠信稀薄、祸乱开始的标志。前识者，道之华而愚之始：自诩能预知未来的人，只是道的浮华外表，是愚昧的开始。是以大丈夫处其厚，不居其薄；处其实，不居其华：大丈夫要居厚实、弃浮华，去彼取此。译者·韩鹏杰说，上德不德也是相反相成思维：越在意形式越失去内容。</t>
+  </si>
+  <si>
+    <t>18、19、41、65</t>
+  </si>
+  <si>
+    <t>【得道才正常，高贵要以低贱为根】【得一为正 贵贱高卑】本章讲“得一”的力量和贵以贱为本。昔之得一者：天得一以清，地得一以宁，神得一以灵，谷得一以盈，万物得一以生，侯王得一以为天下正：天得道而清明，地得道而安宁，神得道而有灵，河谷得道而充盈，万物得道而生长，侯王得道而成为天下首领。“一”就是阴阳两者的统一，也就是道。其致之也：若失去道，天将裂、地将废、神将歇、谷将竭、万物将灭、侯王将蹶。故贵以贱为本，高以下为基：贵以贱为根本，高以下为基础。
+是以侯王自谓孤、寡、不穀：侯王自称孤、寡、不穀，正是以贱为本、以下为基。致数舆无舆：刻意追求众多荣誉反而失去荣誉。是故不欲琭琭如玉，珞珞如石：不要像华美的玉，要像坚硬的石头，石头能铺路济人，华美的玉看似高贵却少有用处。译者·韩鹏杰强调两个重点：一是“一”即道，是阴阳统一；二是“贵以贱为本，高以下为基”，位置越高越要善于处下，把根基打牢，做人要处实不居华。</t>
+  </si>
+  <si>
+    <t>2、10、22、42、56</t>
+  </si>
+  <si>
+    <t>【事物到了头就往回走，无中生有】【反者道动 有生于无】本章只有三句话，却是全书思维总纲。反者道之动：道向相反的方向运动，事物发展到极点就走向反面，又终而复返，回到更高层次的本根。所以看问题不能只站在自己的角度，要换位思考、正反合地看：正面看、反面看、合起来看，才能全面。弱者道之用：道的作用体现在柔弱一面，大家都逞强，柔弱反被强调，这是阴阳统一的思维方式。天下万物生于有，有生于无：万物产生于有，有产生于无；任何事物都有有和无两个方面，有让我们观察边界，无让我们观察妙处。
+译者·韩鹏杰强调，如果只看到有形东西的作用，忽略无形东西的作用，物质世界越发达，精神家园就越花果飘零；既要看到物质财富，更要看到精神、信仰、理论这些无形力量。前三章讲道，第四十章用三句话总结全书思维方式，后边各章都是它的展开和例证。</t>
+  </si>
+  <si>
+    <t>1、2、11、25、45、58、65</t>
+  </si>
+  <si>
+    <t>【最棒的人，成熟得晚】【大器晚成 大象无形】前边《德经》的部分我们讲了第三十八章，“上德不德，是以有德，下德不失德，是以无德。”讲了第三十九章，第三十九章第一个重要的概念是“一”。我再重申一遍，是阴阳两者的统一，也就是道。第三十九章里边的重点词，我们要不断地重申、重复，以求达到大家的记忆。“贵以贱为本，高以下为基。”第四十章我们极为看重。因为这一章开头五个字，是整个这一本书里思维的总纲：“反者，道之动”，下边是它的具体的体现，“弱者，道之用。天下万物生于有，生于无。”现在我们具体来讲第四十一章，这一章内容也非常丰富。首先我们在前边就强调过，《道德经》是对面有人问问题，老子给予的回答。现在对面有人问关于“士”的问题了。“士”这个阶层，把它理解为做官的阶层也可以，“士”这个概念，它的原意就是做事。延伸意指的是一个领导阶层。推十为一嘛，十个人里边推举出来一个领导大家，服务大家，管理大家。所以有人问老子，你看这些士，怎么来判断他们境界的高低呢？水平的高低呢？老子也是拿道来评价的。所以在这一章里边，一开始老子就讲“上士闻道，勤而行之”，境界高的、水平高的士这个阶层这些人，听到了道，比如说他的领导者讲的话，他觉得有道，有道理，“勤而行之”，就是执行力最强，坚定不移地按照它去做。有问题呢？自己勤勉、勤奋地把它解决，“勤而行之”，知行合一了嘛。知道了就按照道去做。中等境界的是什么呢？“中士闻道，若存若亡”，将信将疑。也想去按照道去做，但是一遇到事了就怀疑了。“若存若亡”，将信将疑，迟迟疑疑，犹犹豫豫，执行力不够。“下士闻道，大笑之”。境界最低的、最差的是干吗呢？嘲笑。人家说什么，制定什么样的制度规则，他都嘲笑，讲什么他都觉得不对，但是又提不出建设性意见，什么叫建设性意见？你觉得人家这个不好，你有没有更好的方案？觉得有问题，客观地指出来、提出来怎么改进，不是为了嘲笑而嘲笑，不是为了讽刺而讽刺。我觉得现在很多语言类的节目只是为了讽刺别人，讲话的时候只是为了打击别人，没有其他什么善良的目的。所以这就属于“大笑之”。别人给他讲道理，他还在那嘲笑，甚至羞辱人家。当然对这个事老子是想得开的。告诉坐在对面问他问题的人，怎么接待这些人，对待这些问题。别当回事，不笑不足以为道。这个世界现在已经没有哪件事是大家都赞成的了，所以有人嘲笑这是正常的。你要跟这些人计较，那就把自己的生命全都浪费了。说到这儿我就得插一句话，我觉得这个境界的差别，格局的差别，心胸的差别在什么地方呢？就在对待攻击者的身上。你看孟子也是我们文化里非常不得了的一个人，但是你看孟子的书里，会有一个什么感觉呢？年轻人，气势太盛。孟子对待当时的一些学术大咖，比如说墨子，比如说杨朱，当时杨墨是显学，名气很大。孟子怎么来评价他们呢？孟子就说墨子这个人讲“兼爱，是无父也”。兼爱嘛，你都平等，没有差别嘛，你置于你父亲于何地？没有把你父亲凸显出来，没有把对父亲的爱突出出来，无父也。杨朱不是讲，“拔一毛而利天下，吾不为也”。大家不要误解这句话，它的原意是你拿天下来换我的身体，让我损害自己的生命去换天下，我不干。它是强调自己的生命的重要。“拔一毛而利天下，吾不为也”。杨朱讲“为我”，所以孟子骂他是无君。你老为自己，你把君置于何地？“无父无君是禽兽也”——他骂杨朱和墨子两个人是禽兽。反过来看老子对待这些人的态度是——“不笑不足以为道”，淡然一笑，过了——很值得人佩服的一种态度。这就叫“明月清风”。对待别人的嘲讽，对待别人的攻击，有这样一个态度，也是很不得了的一种智慧与境界。这一段是本章里边的核心。因为我觉得他上中下的这种区分非常明了，很实用。“上士闻道，勤而行之”。坐而论道，不如起来行嘛。大家看道字的写法，首是头脑、思维、想。“走”之旁是行。所以这个道本身就是一个知行统一的概念。“上士闻道，勤而行之。中士闻道，若存若亡。”犹犹豫豫，不坚定，不能够坚定坚持的按照道去做。“下士闻道，大笑之。”我们千万不要做这种老是嘲笑别人，讽刺别人的，否则就会落于下乘，不笑不足以为道，太好了。明月清风一般地对待这种嘲讽辱骂的这种态度。下面这一段开头这句话非常有意思，叫“建言有之”，“建言”就是我们说的常言。常言说得好，这是我们经常用的，所以下面这句话大家注意，不是他本人的话。就是告诉大家了，明确下边讲的很多都是常言，在当时就是一句俗语。他讲的这些道理都是什么呢？都是前边我们讲的“反者，道之动”的例证。所以我在前面给大家说，第四十章是全书的总纲，可以举的例证会无限多，下边都是。“明道若昧”，光明的道路好像是昏暗不明的。为什么？有些给你指出的光明大道说得多么多么得好，指出光明大道简直就是美得不得了，你要小心了，前面有陷阱。真正的大道，反而像是昏暗不明的，就是把路上的艰险，遇到的阻碍，遇到的问题，都给你说清楚，让你看得清楚，这才是明道。给你说这条路没问题，太直了，平坦了，你沿着这条路走，肯定光明无限；沿着这条路走，肯定兴旺发达，一点阻碍都不会有，这个事绝对没问题。坏事了，这个时候你就得小心了。要知道“明道若昧”。再举个关于“朋友”的例子说明这个问题。朋友有三类，友直，友谅，友多闻。第一类的朋友直率，你有问题给你直接指出来。你走的道有问题的时候直接告诉你，跟你讲，怕你犯错误，怕你在这个地方出现问题。不是你的朋友呢？你走在道上遇到什么问题与他有什么关系啊，你问他这条道怎么样？他就告诉你，好好好，走走走，这条路没有任何问题。你给我提点建议，没什么建议，走就是了。你掉到坑里边他管你呀！所以我们说这“明道若昧”，暗昧，昏暗不明。“进道若退”。我们有的时候自己老觉得自己进步太小，人有时候都不免太着急，老觉得“一万年太久，只争朝夕”。只争朝夕，我每天都得进步，我都得看到自己的进步，一感觉到自己没有进步，就着急了。其实你别忘了，人呢，走在路上没有直线的，“进道若退”，有时候我们感觉是退步的时候，其实我们是在进步。比如说练书法，大家都有这个感觉，刚练这几天觉得进步很大，我以后每天按照这个速度会很快成为书法大家，过一段时间感觉怎么回事？怎么我这字越写越差了，还不如开始呢。好多事情开始都是这样。其实这就是我们前进中的一个必然的现象。懂得以退为进，懂得退就是进，有时候退不就是进嘛。“进道若退”，这不就是相反相成嘛。所以我在想，在老子那个时代，你说这些常言都在。这得说中国古代的这些人的哲学的思维水平竟然达到这样一个高度。所以有的时候我们做的事情感觉退步的时候不要着急，退是前进中的必须经历的。“大象无形。道隐无名，夫唯道善贷且成”。只有“道”才能善贷且成，资助万物，帮助万物成长，帮助万物成功。这一章给人很多的启发，很多的回味。每个人读，都会有不同的感受。随着年龄的增长，我们也会不断获得新的体会。</t>
+  </si>
+  <si>
+    <t>14、20、35、38、63、70</t>
+  </si>
+  <si>
+    <t>【道生万物，阴阳调和才和谐】【道生万物 冲气为和】《德经》部分我们今天讲四十二章。老规矩，把以前的这几章我们再顺一下。《德经》从第三十八章开始，第三十八章讲“上德不德，是以有德；下德不失德，是以无德。”第三十九章我们讲了两个重要的部分，一个就是这个“一”，因为第四十二章又出现了这个“一”，就是阴阳两者的相互平衡，形成的统一体。在第三十九章里边有两句话每一次我都要重申一下，以求让大家牢牢地记忆，“贵以贱为本，高以下为基”。第四十章有一个全部这本书思维的总纲，“反者，道之动”。下边举的这些都是“反者，道之动”的一些例证。比如说“弱者，道之用，天下万物生于有，生于无”。第四十一章的时候，我们是花了比较多的时间来说，为什么呢？因为这一章里边有非常多的“反者，道之动”的例证。比如说“大音希声，大象无形，大器晚成……”这些都是我们平时经常讲的成语。上次讲完了大家应该知道了它的出处。那么今天我们讲第四十二章，这一章并不难理解，但是非常的重要。因为这一章开头这段话，大家经常在很多地方看到，比如北京故宫是建筑的典范，故宫的太和、保和、中和三大殿都是三层台基，也就是建在三层高台之上，为什么选择“三”这个数字呢？再比如我所在的学校叫做西安交通大学，在交大的管理学院，我的一个朋友也在那做了一面墙的雕塑：太极，大家有机会到交大管理学院的时候就会看到，就在一楼。这两个地方的解释，用的都是这段话：“道生一，一生二，二生三，三生万物。”我们来解释这段话，原文大家都看到了：“道生一，一生二，二生三，三生万物。万物负阴而抱阳，冲气以为和。”这个“冲”字，读成中，一下就理解了。下面这段话其实大家也耳熟，起码意思在前边已经说过。“人之所恶，为孤寡不穀，而王公以为称。”大家讨厌的孤、寡、不榖，王公却用来称呼自己，这不是我们前面第三十九章的时候已经说过的这个意思嘛。“故物或损之而益，或益之而损。人之所教，我亦教之，强梁者不得其死，吾将以为教父。”这是第四十二章原文。我们一段一段来解释。先说第一段，“道生一”。“一”我们俗称叫太极。其实“一”就是道的具体的特点，强调道就是“一”，是说道的最重要的一个特点，就是它强调阴阳两者的统一，“一”里边蕴含着阴和阳两种力量，两个方面。“道生一，一生二”，这个“一”里边蕴含着“二”，也就是道里边蕴含着阴阳两种力量，两个方面，两种状态。中国人讲，事物都是相互对立而存在的，万事万物归结到最后，它也不会是一个单一的元素。你看咱们中国历史上的《易经》，落到最后就是两个符号，阴和阳。那已经到了事物的极致了，极点了。把阴和阳统一起来叫太极，但是这两个元素是最基本的。所以“一生二”，是说太极道里边蕴涵着阴阳两个方面，两种力量。“二生三”，很多人对这个“二生三”解释得太费劲。“三”是什么？很简单，就是繁体字那个“叁”，就是参。阴阳两者参与到一起，相互作用，形成了万事万物，多简单的事情。它们两者孤阴不生，孤阳不长，两者相互作用，形成万事万物，“三生万物”。所以我们用的那个《中庸》的名言叫“参天地，赞化育”。人能参与到天地之间的运动发展，天地人三才嘛。三才你看人不也参与其中嘛。这个赞可不是赞扬的意思，也是参与的意思。两者参与到一起，产生万事万物，这是从正面。然后再反过来推，既然是三生万物，那么万事万物里边都包含着这两种力量，两个方面，阴阳两个方面，所以叫“万物负阴而抱阳”。随便找，哪一个事物内部都有阴有阳，都包含着阴阳两种状态、两种力量。“万物负阴而抱阳，冲气以为和”。为什么要把这个“冲”念成“中”呢？大家看“冲”的写法，前边这两点其实就代表着阴和阳，那个中就是中和的意思，就是参的意思。阴阳两种力量，中国人把它叫做气，阴气、阳气嘛。通天下一气，形成和谐的、动态的、运动的世界，这就是冲气以为和。这一段讲了我们中国哲学中的宇宙生成模式，也讲了这个世界存在的状态，以及这个状态的原因。这种状态都是阴阳两者运动所形成的，动态的、和谐的状态。冲气以为和。再重复一遍。“道生一，一生二，二生三，三生万物。”所以万事万物都有阴阳两个方面，“万物负阴而抱阳，冲气以为和。”下边就开始讲。用这种思维方式你来理解世界，你就不能只站在一个方面了，明确地告诉你了。事物都是统一的，两个方面不可偏颇，不可偏废。所以对侯王讲，“人之所恶，唯孤寡不穀。”你说大家最讨厌的就是这些词，孤家、寡人、吃不上饭、饿死。可是你看这些王公大人，包括后来的皇帝，他们都拿这个来称呼自己。干嘛呢？“故物，或损之而益，或益之而损。”这个“物”大家不要解释成物质，就是我们中国人常讲的那个“东西”。中国人这个“东西”太奥妙了，什么都可以称之为东西，不管是物质的、精神的都可以称之为东西。所以老子就说你看说到万事万物存在的这些各类各样的东西，“或损之而益”，你以为它受损了，其实它得到了益处。有的时候我们受到一点挫折，我们觉得自己受了多大的这种屈辱一样，可是你知道人都是在不断地受的这种损中逐渐地成长起来的，你认为它是祸，其实它是福，“损之而益”。有的时候你认为自己是得到了，其实反而是一种损失。比如偷了东西的，得到了，其实把人格给损失掉了。有的人用不光彩的手段，不择手段得到的，其实他们损失的反而更大，“或益之而损”。所以老子讲的是相反相成的道理。我们中国人常用什么事情来说这个事？叫破财免灾，叫大难不死必有后福，叫祸福相依，叫塞翁失马焉知非福，你看这讲的都是“损之而益，益之而损”。刚才举的例子不就是这样吗？这侯王王公们不都在损自己吗？把自己叫做“孤寡不穀”。其实有这个提醒之后，反而避免了自己变成孤寡不穀。以前中国人也有这个习惯，给小孩起名起个贱名，好养活。当然现在这种习俗很少再看到了，它讲究的就是“损之而益，益之而损”。民间很多的道理大家也得认真对待，别以为我们上了学之后自己水平就高了，其实真正的高手在民间。很多老人讲的话，到最后你一生体会，反而你发现真的是有道理。“人之所教，我亦教之，强梁者不得其死”。老子也说这些东西，也都是别人教给我的，给我讲的。我再把这些写出来教给大家。这一句我们可得好好地来给大家说道说道。为什么呢？因为这涉及老子的思想的来源，老子的思想来源当然有很多方面，主要的两条，两条道路。一条道路自然就是《易经》。因为你看，《易经》它把这个叫易以道阴阳，老子也讲阴阳，而且这里边的损和益，这不就是《易经》里边的损卦和益卦嘛，损和益这也是《易经》里边经常强调的。另外一个，我觉得这一章里边非常奥妙，一个是讲这阴阳的事情，让我们知道他的思想里边《易经》是中国文化之源，众经之首，损之而益，益之而损。另外一个也表现出他的思想的来源，就是“强梁者不得其死”，这句话也不是老子自己的，它出自《金人铭》。传说黄帝写了六篇铭文，叫《黄帝六铭》。其中有一个是刻在周朝台阶右面立着的金人背后，金人就是青铜做的，这金人的背后有铭文。经过汉朝的刘向《说苑》的考证对比，发现《金人铭》里边的这句话：“强梁者不得其死”。“强梁”就是处处逞强。喜欢暴力的人，最后不会有好的结果。我们讲死得其所，叫得其死，得好死，不得好死，不得其死。强梁者不得其死。说到“强梁”这个词，我想读过《水浒传》的人一定记得，在《水浒传》里边用到“强梁”这个词的时候，是用在了矮脚虎王英的身上。矮脚虎王英，这个是梁山泊里边大家都瞧不上的那么一个人。原来是个车夫，后来抢劫，后来落草。所以用这个词来形容他，“强梁者”。“强梁者不得其死”，老子非常反对强暴，而强调和平、守弱，认为“强梁者不得其死”，“木强则折，兵强则灭”，这是他后边关于这个问题的一个延伸。“吾将以为教父”，这个“教父”就是说，这是别人教给我的，我也把它拿来作为座右铭，来指导我自己。总结一下，大家看这一章，第一段话是我们大家都耳熟能详的，“道生一，一生二，三生万物，万物负阴而抱阳，冲气以为和。”第二段是我们前边讲过的内容，在这个里边又重申了一遍，注意这些重申可不是排版排错了。因为《道德经》里边它讲的几条重要的原则，遇到机会的时候，它就会反复，用重复的方式来强调。“人之所恶，唯孤寡不穀，而王公以为称。”所以对于万事万物而言，对这个世界存在的东西而言，“或损之而益，或益之而损”。有的你觉得是损失了，结果反而是得到了。有的你认为自己得到了，反而是损失掉了。因此不可一概而论。遇到了乐事的时候，不要过于高兴，以免乐极生悲。遇到不好的事，祸事的时候，也不要丧气，因为这些可以成为我们的经验，塞翁失马，焉知非福！这是别人教给我的，我也把它来教给别人。然后下边这句话是老子也非常强调的，“强梁者不得其死”，还是要和平，还是要守弱，处处逞强，总和别人结梁子，最后不会有好的结果。国家也一样，“国虽大，好战必亡”。老子说我也要把这个当作座右铭，这就明显地透露出他思想的来源，一源于《易经》，阴阳之学，损益之论，谦卑之礼。二源于《金人铭》，尤其是《金人铭》里这句话对老子影响是非常大的，所以他把它叫做“教父”，座右铭。</t>
+  </si>
+  <si>
+    <t>1、4、6、10、21、25、39、51、55</t>
+  </si>
+  <si>
+    <t>【最软的，能穿透最硬的】【至柔克坚 无为之益】我们说“反者，道之动”是整个这本书思维的总纲，也就是说它是一种思维模式、思维方法。第四十章一开头就讲“反者，道之动，弱者，道之用。天下万物生于有，生于无。”这里边出现了两个在《道德经》里边非常重要的字，一个是“弱”，也可以称其为“柔”，另一个就是“无”。第四十三章是对这些内容进一步的引申和展开。第一句“天下之至柔，驰骋于天下之至坚，无有入无间”。最柔弱的东西，反而能够攻克最坚硬的东西。那些没有间隙的地方，无形的东西却能够进入，能攻克。就像风，没有什么地方它进不去的。这些就是“道”，道讲完了。老子开始讲“德”。“吾是以知无为之有益”。我从“至柔驰骋于至坚”，“无有入无间”中知道：人类也是一样，有些事情，无为比有为效果更好——“无为之有益”。可是话说回来，“不言之教，无为之益，天下希及之”按照无为的道理去做事，所获得的好处、益处，天下的人却很少能够知道，很少能够达到。这些话该怎样进一步理解呢？老子在第七十章讲过，“吾言甚易知，甚易行，天下莫能知，莫能行”。什么意思？其实，我讲的道理都是非常简单的、平常。但是大家为什么不知道呢？做不到呢？因为这里边就隔了一个东西——欲望。有些事情大家明知道是这么回事，但是很多东西被欲望牵引就变得难做了。就像我们说“不贪为宝”，但为什么还有那么多人上当？有些人上当了还不好意思说出来。因为自己心里清楚，自己是因为贪心才是上当受骗了嘛。没有这个贪心，很多事情理解起来就太容易，太简单了。但一个骗局，往往能骗很多很多人！再说回来，“天下之至柔，驰骋天下之至坚，无有入无间”。天下的“至柔”是什么？无形是风，有形是水。第七十八章就说，”天下莫柔弱于水，而攻坚强者莫之能胜”。这不是正是“天下之至柔，驰骋天下之至坚”吗？天下什么东西最坚硬，石头？水滴石穿；金属？水刀切可以割金属。有什么坚硬的东西是水它克服不了的呢？风更是弥漫天下，摧枯拉朽，无所不在，力量无尽。你说这个东西没有间隙，但是无形的东西，它反而能够穿透它。现在，科学发现有一些微小的东西，比如说中子、粒子、量子……他们是无形的，你看不见，但没间隙的地方，它们都能够进入。我们眼里没有间隙的地方，对于它们来讲，缝隙简直太大了。“无有入无间”，在强调无的东西的作用。道家的“无为”相当一部分内容在讲“无之为”——这些无形的东西、无用的东西的作为。所以，不要把“无”理解为“没有”，把“无为”理解为“不做事”。“吾不言之教”，第二章讲过“行不言之教”，为什么？身教重于言教，话太多了，老去教化，训导别人，反而会起负面的作用。老师也罢，家长也罢，国家的领导也罢，做一个好的榜样，上行下效。孔子也讲了一句话，叫“君子之德风，小人之德草”。这里小人不是道德上的低下，而是指人民、平民、一般人。榜样的“不言之教”就像风一样，一般人就像草一样。风向哪个方向吹，他们跟随着风而倒。无之为所带来的益处，天下却很少有人能够达到——“希及之”！在讲第三十七章的时候我们说，“道常无为而无不为”，道的规律、规则就是“无为”，而“无为”的效果却是“无不为”——覆盖面更广，效果更好。这不就是“无为之益”吗？一开始讲第一章的时候，我就给大家说过，道家讲的“無”和舞蹈的“舞”字形极为相近。因为对于原始人来讲，舞蹈起到的作用实在太大了。有形的几个姿势，产生出的力量却是巨大的。既然是“无”是“无之为”，那么“无用”，也就是“无用之用”。你认为没用的东西，其实不是它没用，只是你没有看见它的用处。书法有什么用，绘画有什么用？不能当吃，不能当穿，可是如果大家否定了这些，那不就进入了一种狭隘的功利主义的境地了吗？人生最没用的事是什么？睡觉。睡着了什么都做不成。小孩最讨厌睡觉了，可是大家都知道现在有多少人被失眠所折磨，为睡不着觉而痛苦。这些“没用”的事你做不成，那么有用的事你也做不来。最后一句，“无为之益，天下希及之”是老子的感慨。大家老看不到这一点，老觉得无为的事情没用。殊不知你不做这些无为的事，就不能真正的有为。不了解这些无用东西的作用，你也就不知道什么才算是真正的有用。从“反者，道之动”，一直到现在，都在讲述一个道理。</t>
+  </si>
+  <si>
+    <t>8、36、48、76、78</t>
+  </si>
+  <si>
+    <t>【名声和命，哪个更亲？】【名身孰亲 知足知止】前面我们说了第四十三章，最后说“不言之教，无为之益，天下希及之”。然后说这都是前面“反者，道之动”这种思维方式的进一步的延伸和具体的例证。这种方法我们大家已经习惯了，在哲学上叫做“二分法”，叫做“对立的统一”。第四十四章讲的也是这个。一开始先列出来三个对立的事物——名与身、身与货、得与亡，进行比较。“名与身孰亲？”“名”和“身”哪一个更重要？哪一个是对大家来讲是更亲的东西？“身与货孰多？”我们的生命和外在的物质相，财富哪一个更重要？“亲”也罢，“多”也罢，意思都在说哪一个更重要。我们常说“身外之物”，常说名和利生不带来，死不带去。你看，这一章就在解读这个问题了。第三个，“得与亡孰病？”这个好理解，参照我们前面讲的“或损之而益，或益之而损”，是得到的好还是失去的好？哪一个危害更大呢？“病”当然不是什么好词了，“得与亡孰病？”其实在问的时候这个答案已经有了。这就是一种反问的语气，表示强调。因为有的人在名和自己生命的选择之中选择了殉名；有的人，“人为财死，鸟为食亡”——因为财富的事，把自己的生命搭上去了。真的是得到就好，失去就不好吗？比如，我们读像《道德经》这样的书，我们会得到什么？也许什么都没得到，但是我们失去了焦虑，失去了急躁，失去了自高自大，这些东西失去了，那不就是一种得到吗？不是说得到就好，失去就不好。有的东西失去，反而是获得；有些东西得到，反而是真正地失去。三个反问句，答案其实都在里边。下面这几句话，讲得就更深刻了。“甚爱必大费，多藏必厚亡”，对一个东西太珍爱了，最后一定会付出大的代价。比如，有的人他有这种癖好，他喜欢古玩，别人送的别的东西他不要，你拿着古玩一贿赂他就收下来，最后就因为这个自己犯了事儿——“甚爱必大费”。有的人把减肥当作唯一的事业，尝试各种各样靠谱不靠谱的方法，把身体折腾得一塌糊涂，那不就得付出大的代价吗？很多事情都是这样的结果。“甚爱”，太过分了，不是说不好，但是过分了，这就走向了它的反面，物极必反嘛！“多藏必厚亡”，很多东西收敛、搜刮到了，自己把它藏起来，能藏得住吗？最后这个搜刮来的东西一定都成为自己的污点和罪证。多藏必厚亡，“厚”也是大的意思。下边这两句话大家都熟：“知足不辱”。我们知道满足有边界，这样才不会受屈辱。这事我知足，我不卑躬屈膝求别人，我觉得我这个已经很好了，这是我自己奋斗来的，额外的，不择手段得来的东西，我不需要，“知足不辱”。“知止不殆”。这个地方，我得给大家多说几句。老子这个人真的是不得了，他只用一个“走道”的形象，就说清楚了很多问题。我们走在道上，应该注意什么呢？有几个最重要的内容：方向、目标、规则、境界、边界、底线。我们要去什么地方？方向、目标。我们什么时候该停下来呢？只要是道就有边界，道外边往往就是深沟，就是深渊，就是歧路。我们了解边界底线，不贸然地前闯，有“底线思维”，“红线思维”，给我们的欲望划出边界，就是“知足”。知足才能不辱。“知止不殆”，“殆”就是危险失败。知道边界、底线不闯，我们才能没有危险，没有失败。当年杨虎城在陕西把他办公的行园就改名叫“止园”。出处就是这四个字，“知止不殆”。“知足不辱，知止不殆”的意义在哪儿呢？——“可以长久”。其实这些事情不用举太多的例证，为什么？因为例证太多了，不了解边界、底线，冒进、冒险，肯定会导致大的，糟糕的后果。这一章没有什么难以理解的，但是内容也非常深刻，尤其是前边这三个提问或者叫反问，都是我们应该深深思考，并做出回答的。拿我们的生命和名声去交换名利，到底划得来划不来？到底哪个更重要？哪个对我们更亲？身与货和这些财富进行比较的时候，到底哪个更重要？我们拿生命去换财富，回头再拿财富来换健康——有时候，甚至换不回来。“得与亡孰病？”不要认为得到就高兴，失去就不高兴，其实得失就是这样的相反相成。很多事情反而是损之而益，有的是益之而损。祸福相依，相互转化，物极必反。既然物极必反，下面这几句话就好理解了，“甚爱必大费，多藏必厚亡”，因此应该“知足不辱，知止不殆”——知足可以不辱，知止可以不殆。知足、知止，我们才能长久。不管是对于生命，还是对于事业而言，才能稳定致远，长久地发展。这是第四十四章的内容，内容不多，但是我们应该熟记，尤其是几个对偶的句子：“甚爱必大费，多藏必厚亡”；“知足不辱，知止不殆”。</t>
+  </si>
+  <si>
+    <t>9、12、13、32、33、46、59</t>
+  </si>
+  <si>
+    <t>【最完美的看着像有缺，清静才是正道】【大成若缺 清静为正】我们先来看一下原文，有几个词我们要注意先区分一下。比如说大辩若讷，这个讷呢，我们知道一个词叫做木讷，也就是说，说话不是那么样的流利，不是那么样的辩才无碍。但实际上在这章里，它所要表达的是谨慎，说话严谨、谨慎。为什么要给大家说“讷”这个字呢？大家知道，毛泽东两个女儿，一个叫李敏，一个叫李讷。可是包括中央电视台的广播员都把这个念成nà，其实这个讷，只有一个读音，应该读作nè（讷）。毛泽东两个女儿的名字出自《论语》，“讷于言而敏于行”。先把这个事情给大家说一下，然后我们从头一句一句来解释。“大成若缺，其用不弊。”这个是在讲，完满的东西都仿佛有缺陷。我们平常讲一句话叫完美诚不易。其实这个世界上没有真正完美的东西，任何事物都是有缺点的。了解到这一点，引申到道家的思想，那么这句话想要表达的真正的含义就是，一个越是有大成就的人，他越了解自己的缺点，越觉得自己有缺点，有缺憾。所以，他就不断学习，不断努力，这样的一种动力，它发挥的作用，那么是无穷无尽的。认识到自己有缺点，这样他才能够很好地避免自己的弊端，很好地使自己的缺点得以改正和进步。这个道理在《道德经》里边多处谈到，比如说第七十一章就在讲，“知不知，上；不知知，病”。你知道自己不知道，这个才是水平高的。你不知道自己不知道，这就出问题了，出弊端了。所以大成若缺，其用不弊。一个越是有大成就的人，越懂得应该不断学习，不断进步，不断努力，不断充电。反而是一些有一点小小成就的人，喜欢到处吹嘘，不把旁边人吹得感觉到活不下去，他都不松口。其实遇到这种人，我们根本不用去揭穿他，淡然一笑就可以了。一个越是喜欢自我吹嘘的人，其实越不会有什么大的成就。反之，大成若缺，其用不弊。其实这个道理不止局限于此，我们还可以把这个道理向更深处延展一下。比如说中国人从月圆月缺，领悟出一个道理，其实任何事物发展到到它的极点的时候，它就会向相反的方面转化。人生的最美的境界，花未全开月未圆。花全开了，就往凋零的方向走了，月圆了就往缺的方向走了。所以在临近全圆和全开那时候，才是最美的境界。其实大家注意，我们在生活中经常喜欢用一个词，来对人表示一种赞赏，叫如日中天。其实这个不是一个好的事情。你说人如日中天，不是马上就说他要走下坡路了吗？用道家的这种思想我们来理解。明白在我们生活中讲的很多事情，和这个道理的吻合。大成若缺，其用不弊。“大盈若冲，其用不穷。”“盈”就是满，“大盈”就是大满。“大盈若冲”，“冲”就是冲虚。我们经常讲，用这个冲虚来代表着谦逊谦虚，就像大家看《笑傲江湖》里边的武当的掌门，冲虚道长，大盈若冲。一个越是智慧高的人，智慧聪明的人，他越谦虚，越谦逊。在前面我们曾经说过，“满招损，谦受益”，这话出自《尚书》——中国第一部历史总集。在《尚书》里边有一篇讲到了君臣之间探讨治国的谋略，大禹手下的第二号人物叫伯益。就给他的领导讲了这样的一句话，“满招损，谦受益”，并且伯益还制作了一件警戒器，叫欹器。这个东西非常奥妙，水装满了就颠倒了，倾覆了。装得不满的时候，它稳稳当当。提醒告诫我们这个道理，“满招损，谦受益。”孔子的后半生这个警戒器也一直放在身旁，这么大的一个学问家，还经常提醒自己，“满招损，谦受益”的道理，何况我们。所以“大盈若冲”！一个越是知识充盈的人，知识多的人，越表现得外在的谦逊谦虚，感觉到自己的不足，不断学习，不断努力。“其用不穷”，这样他的知识才能够更好地发挥作用，它的作用无穷无尽，不会出现上边所说的那些弊端，其用不穷。这都是相反相成的道理，按照这个道理我们再解释下边的内容，就比较容易了。“大直若屈，大巧若拙。”一个越是正直的人，越是有正直的、高尚的境界的人，反而外在表现得都比较随和，对很多的事情不那么喜欢争锋，对很多的事情都能够宽容。若屈并不是真的屈枉，他只是懂得外圆而内方，用这种方式和外面的人相处、相衔接，“大直若屈”。关于“大巧若拙，”这个我们得多说几句，在第二十五章里我们讲过，“大曰逝，逝曰远，远曰反”，这是一个逐步发展的过程。就像中国的艺术品一样，一开始没有技巧，后来学到了很多技巧。真正达到一个更高的境界的时候，反而把这些技巧忘掉了，返璞归真。中国雕塑的最高的境界是什么呢？有机会大家到汉武帝的陵墓——茂陵看一看，就会有所体会。那儿被认为是中国雕塑的顶峰。可是大家进去一看却发现非常奇怪，汉代的雕塑几乎一件精巧的东西都没有，都是那样的笨拙、朴拙。特别是霍去病墓前的《马踏匈奴》，那简直笨拙到了极点。团块、圆雕。可是那是中国象征雕塑的顶峰，正因为它这个拙，反而体现出大气势、大气象、大境界，“大巧若拙。”中国诗歌的最高境界是什么呢？清水出芙蓉，天然去雕饰，自然而然，返璞归真。中国书法的最高境界是什么呢？大的书法家最后写得越来越笨拙，越来越稚拙，反而开拓出一片新的气象。我读过一本书法书，是凌云超先生的《中国五千年书法史》。凌云超先生讲到这样一件事，他说中国的书法到后来写得越来越精巧，越来越美，但是像小家碧玉。而中国早期的书法，比如说石鼓文、金文，如旷野风月，给人一种大开大合的气象，这当然是我们在欣赏过程中感觉到的。越是这种稚拙、朴拙、笨拙，反而给人带来更强烈的一种审美的气势和感觉，崇高的一种味道。所以“大巧若拙”。其实《道德经》里边主要讲的并不只是这些，主要说的是人格。一个人格发展到一种高点的时候，他就达到了一种自然而然，返璞归真，忘记了那些小的技巧，心眼、套路，回归到一种真正的高尚的人格的境界。“大巧若拙”，返璞归真，自然而然，明月清风。这是我们说“大巧若拙”。“大辩若讷”。“讷”字我们前面解释过了，这个意思也就非常清楚。真正辩才高的人，他出语反而非常谨慎，让人感觉到仿佛他语言不是那么样的流畅，辩才无碍。其实他不只是为了用语言和人争锋，用语言和人争辩，出语谨慎，这也是我们讲的道家思想里边的一个重要的方面，这样的人才是真正有大的这种辩才的人，“大辩若讷”。下边这几句话原文上就有争论了。我们按照原文先解释一下。“躁胜寒，静胜热”。这个“躁”，表面上意思是急躁，燥热，实际上在讲的是运动。运动可以战胜寒冷。“静胜热”是说冷静可以战胜昏热。因为比如说我们夏天的时候用冰镇，这个方式可以解暑，战胜暑热，但这个地方要讲的实际上是内心的这样的一种冷静，可以战胜我们头脑发热，“静胜热”。但有的人也认为，其实这句话应该是静胜躁，寒胜热。这样和原文连接起来就更顺了，我倒是同意这样的一种说法。因为比如说我们夏天的时候用冰镇，这个方式可以解暑，战胜暑热，所比喻的也是冷静下来时才能战胜头脑发热，而且句式更为对称。现在很多本子也这样做了这样的一种改动。我觉得这个说法更为成立。总之都是讲，内心冷静、宁静、安静，它可以战胜我们的急躁。如果我们能够保持内心的宁静、安静、冷静，这样就可以战胜我们的浮躁、急躁、暴躁、狂躁，宁静以致远，这个和原文意思比较吻合。寒胜热，也是这样一个意思的表现，就像我们刚才说的，一个人冷静下来，可以战胜头脑发热，万物静观犹自得，我们冷静下来才能看清事物的本来面貌，冷静下来才能找到解决问题的正确方法。所以这六个字，大家不妨把它理解为静胜躁，寒胜热。这样后边这句话就自然而然地引申出来了，“清静为天下正”。我们保持内心的清静，一个王者、统治者、领导者保持内心的清静，这样才能够引导天下走上正道。“我好静而民自正”，“清静为天下正”，让内心的清静、冷静、宁静，又具备这样的一种修养。这才能够引导天下走向正道。这个是天下最正的一种领导的方式方法，也是我们修养的由内圣而外王的一种正确的修养的方式方法。</t>
+  </si>
+  <si>
+    <t>11、16、22、25、26、40</t>
+  </si>
+  <si>
+    <t>【最大的祸，是不知足】【知足常足 有道归耕】“天下有道，却走马以粪；天下无道，戎马生于郊，祸莫大于不知足，咎莫大于欲得，故知足之足，常足矣。”这段话也是《道德经》里边非常精彩的一章。因为它体现了我们中国人对待战争的态度，对待和平的热爱。前面我们讲的第三十章的内容，不知道大家是否还有印象，“师之所处，荆棘生焉。”军队打过仗的地方，一片衰草枯杨，断壁残垣，“大军之后，必有凶年。”打过仗以后，灾荒瘟疫都来了。第三十一章，老子讲得更为沉痛，说中国人把战争当作丧礼一样来对待，“以悲哀泣之，以丧礼处之，胜而不美，胜而美者是乐于杀人。”我以前讲过，通过“四大名著”让国外了解我们的文化，效果恐怕不尽如人意，应该让他们看什么呢？让他们看《道德经》，这部能真正代表中国人思想理念、境界和智慧的经典，像我们讲过的三十章、三十一章和现在要讲的第四十六章，就是如此。“天下有道”，普天下清明有道，这个“天下”包括各个诸侯国了。“天下有道，却走马以粪”，“却”就是推却，“走马”就是跑马，也就是好马。这好马不用来打仗，离开战场，推却战争，干吗呢？回来耕田。当然，古人耕田是要上肥的，撒上粪肥，马耕着田，把地耕好，也就是我们经常讲的，卸甲归田，“卸马归田”，把马从战场上拉回来，干它的本务工作。“天下无道，戎马生于郊”，普天下无道的时候，混乱不堪不清明的时候，是什么情况呢？战马把小马驹生到了战场之上，“郊”就是郊野，此处指疆场，战马把小马驹生到了疆场之上。打仗公马不够用了，母马也上去了，最后出现这种情况——“戎马生于郊”，说得非常形象。我要重点强调一下，这四句是以马喻道，马之却为有道，戎马生于郊为无道，也就是以马的“却”与“生”，比拟天下之有道与无道：以“粪马”与“戎马”，象征国家之治与不治。比喻巧妙，寓意深远。纵观《道德经》的治国之道，当以无为自然以养民，以无欲之事而安民。好像马匹一样，虽是有用之物，用之于疆场可以卫国，用之于战阵可以御敌，用之于农事可以耕田。道行天下之时，国泰民安，上下祥和，无兵甲之患，天下太平安然，百姓安居乐业，故用走马耕田种地，积粪肥田。所以说：“天下有道，却走马以粪。天下无道，戎马生于郊。”太精辟了。“祸莫大于不知足，咎莫大于欲得。”这个大家清楚，老子生活在春秋，春秋无义战——没有什么正义的战争。大家都为了争夺财富、城池、人口，相互混战，战火频仍，烽火四起。面对这种情况，老子在当时总结出这两句话：“祸莫大于不知足，咎莫大于欲得。”惹祸最大的原因在哪呢？在于内心的贪念，贪心不足，得到了还想更多，只会做加法，不会做减法。“人心不足蛇吞象”，其实这句话，不单只对当时的现实概括，对我们现在也有这种启发的意义。生活中这种情况也比比皆是：有了还想更有，多了还想更多，衣架里边永远缺一件衣服，房子永远少一间，总是处在不知足的这种状态。“祸莫大于不知足，咎莫大于欲得”，“咎”罪过，过错，动辄得咎，过往不咎。这个“欲得”，就是别人的东西，自己也想要，把别人东西尽量弄到自己手上——这就成了一种罪过了。前面讲“不知足”是一种“祸”，祸患，而“欲得”就是一种罪过了，甚至可以是一种罪恶。别人的城，想要；别人的人民，想要，什么都想占有，用占有的态度对待这个世界，天下是我的。他说古代封建时代皇帝是什么样子呢？“离散天下人之儿女，屠毒天下人之肝脑，以博我一人之产业。”是说皇帝他觉得天下都是自己的，什么东西想拿就拿，想要就要，想占有就占有。这不就是“欲得”吗，这不就是一种大的过错、罪过吗？“咎莫大于欲得。”这个事情该怎么样来处理呢？该我们得的，我们应该得，不该我们的，“虽一毫而莫取也”。这段话大家也知道，东坡先生的《前赤壁赋》，“物各有主，苟非吾之所有，虽一毫而莫取。”划清边界，该得的得，不该得的不要老去强占，不要老是欲得。我们有了边界、底线、标准，那么就知道知足，知足的满足才是长久的满足。知足者富，所以如果永远处在不知足的状态，人也就永远不会有心灵的安宁。我们把这段话和第四十四章联系起来理解就更加明确了。第四十四章最后的三句话讲，“知足不辱，知止不殆，可以长久。”这一章说，“祸莫大于不知足，咎莫大于欲得。故知足之足，常足矣。”</t>
+  </si>
+  <si>
+    <t>12、30、31、33、44、53</t>
+  </si>
+  <si>
+    <t>【不用出门，就能懂天下】【不出知天下 不为而成】由于这两章的内容非常相吻合、相近，所以我们合到一起作为一章来讲解。四十七章讲的是一个什么事儿呢？是说人的感性认识，从哲学上说就是我们的感官接触客观世界，有时候接触得多了，它反而会造成一种迷乱和混乱，要通过人的智慧、理性认识，这样我们才能了解事物的规律，也就是这一章里边所说的“天道”。在这个基础上，我们一句句来解释。“不出户，知天下。”“户”就是门户，也就是大门。我不用走出家门，不用去外边到处跑，也能了解天下的大事。为什么？因为道家认为，天下大道归根到底，融于人的内心。内心里边有道，也就了解了天下的正道，了解了天下的大事。“不窥牖，见天道。”“窥”，从小孔里看；“牖”，就是窗户。我不用通过窗户去看，也知道天地之间日月星辰运行的规律。所以你看这个地方，“出户”是行走，出行，行万里路；“窥牖”是眼睛看，用感官接触客观世界，我不用这样。所以这个地方大家就感觉到，直观的一开始看，就觉得老子这个人有点轻视感性认识，人得通过实践嘛，人得通过感官接触客观世界，才能产生对客观世界的认识。是不是老子把这些东西全部都否认了呢？不是的。因为大家从书里已经看得非常的清楚，《道德经》举了很多生活中的例子，比如说“治大国若烹小鲜”，比如说“凿户牖以为室”，比如“说三十辐共一毂”，前面讲过的，这不都是生活中的例证吗？他对这个东西也很熟悉，怎么知道的呢？通过接触、了解。为什么在这一章里一开始他就讲这个事呢？要落到下面这八个字上。“其出弥远，其知弥少。”“弥”就是越来越，有的人走的地方越多，见得越多，不懂得甄别，不懂得筛选，不懂得提炼概括，“乱花渐欲迷人眼”，出得越远，反而了解到的真知越少，进步越少，为什么？不懂得反观自省，不懂得人心像一面镜子，如果你这个镜子是被灰尘蒙蔽的，你见得越多，其实反而获得的真知越少。这八个字在强调什么？我们要反观自省，要自我修行，自我修养，从哲学上说，从那些感性认识要上升到一种理性认识，达到对事物本质和规律的认识。所以你看，天下、天道代表着对事物全面的、本质的、规律性的认识，这个规律性的认识，需要我们安静地学习，在家里边读古往今来的著作，这不也是“不出户”嘛，也是“不窥牖”！我们了解这些间接的经验，从前人那里得到根本性的、全面的、通过理论阐释的这些知识，我们才能更了解事物的本质，更了解事物的规律。所以不要只把希望寄托在我们出去跑一跑，看一看，以为这样我们的知识就会越来越深刻，很多事情其实要通过理性的思维，这样我们才能进入到对事物本质和规律的认识，“其出弥远，其知弥少”。如果从中国的文化的角度来进一步理解的话，它还探讨一个什么问题、强调一个什么问题呢？就是人的品德。“大道之行，以心之知。”就是我们的心，我们的自我的内在的精神世界，这是道的重要的方面。所以很多人认为知识就是智慧，知识就是品德。不是的，很多人知识很多，不一定有智慧，知识多也不一定有境界、有品德。所以《道德经》强调的根本的“知”，从前面的比较中，相对于我们的感官而言，是人的理性的思维，理性认识、智慧，相对于外面的世界而言，它又是人的道德品德、人的品德。明朝的时候，关学的代表人物冯从吾先生讲过的一句话，我觉得冯从吾先生的这句话就非常能够解释这个道理，冯先生认为，古往今来的大学问都不出乎三句话：“做个好人，存点好心，行些好事。”做个好人，心正，身安，魂梦稳；行些好事，天知，地鉴，鬼神钦。所以一个人内心的品德、境界，通过自我的反省，自我的修养，达到了一个更高的水平，返璞归真，“归根曰静”，这些也是通过内在的自我修养来达到的。所以《道德经》认为人的理性认识，人这样的内心、这样的根本，它可以通过“不出户”、“不窥牖”，也可以自我修养，自我认知，不断地进步以达到。“是以圣人不行而知，不见而明，不为而成。”“是以圣人不行而知”，“是以”，“是”就是这样，“以”就是用，“是”可以解释为所以。“圣人”，好的统治者、领导者，在《道德经》称其为圣人。这些圣人，好的领导者、统治者要经常反躬自省，要经常内心关照，提高自己对大道和规律的认知水平。“不行而知”，不用到处跑，这一点也是可以得到的。“不见而明”，不用亲自去看，也能够明了道理，明了了这个道理，那就内心清净、无欲。“不为而成”，“不为”就是无为，就是按照大道的方式自然而然地去做，而不去妄为，这样一切都会顺理成章。这是我们第四十七章里边讲的内容，字虽然不多，但道理需要我们认真体会，“不出户，知天下；不窥牖，见天道。其出弥远，其知弥少。是以圣人不行而知，不见而明，不为而成。”当然对这一章的更进一步的理解需要我们和第四十八章，也就是我后面要讲的这一章相互参照，我们对这个理解才会更深刻、更准确。一开始就给大家说第四十七章、第四十八章我们要合起来，相互参照，为什么？这两章的内容讲的是非常吻合的，事实上也应该是一章的内容。第四十七章里边讲，“其出弥远，其知弥少”，第四十八章一开头就讲：“为学日益，为道日损。损之又损，以至于无为，无为而无不为。”这八个字一下子和上边的内容就衔接起来，为什么跑得越远反而知道的越少，这是站在道的角度来讲的。“为学”，在学知识，学到的知识内容越来越多。当然从学知识的角度来讲，这是非常有益的，不断地增多，可是我们获得很多的东西，见到了很多的东西，其实对我们了解根本性的规律和本质，了解大道并没有好处。站在一个更高的层次理解，就是说我们“为学”，讲究的是越多越好，见得多，看得多，见多识广。但是“为道”讲究的是什么呢？讲究的是内心的修行，讲究的是减少，用我们前面讲的话来讲，为学做的是加法，为道做的是减法，减少我们内心的欲念，减少我们的贪念，减少我们对很多问题的一种受了外界的影响而导致的内心的纷扰、困惑、迷乱，把这些东西损之又损，一点一点地把它减少，就像那镜子的灰尘一点点擦掉一样，“损之又损，以至于无为。”“无为”就是自然而为，把欲望减少，减少再减少，就达到了一种“无为”的境界，没那么多的贪念，没那么多的纷扰。我们用镜子来照这个天下，来照事物，万物进入到镜子里边，呈现出它本来的面貌。我们了解了事物的本质规律，了解了大道按照它来做，“无为而无不为”达到的是“无不为”的效果。所以在这儿借着这个机会，我再说一下道家自然无为的具体的含义：第一，不妄为；第十六章里边就讲，“不知常，妄作，凶。”你不了解事物的规律、规则，瞎折腾、胡折腾，那结果是非常糟糕的。我们“损之又损”，减少了这些遮挡着我们的认识，遮挡了我们的心窍的这些外在的事物、灰尘、迷乱，我们就照见了事物的本质和规律，我们就“不妄为”。第二，不多为；抓住关键，举重若轻，静观，看到事物的本质，找到解决问题的正确的方法，抓住关键，举重若轻。第三，有所不为；人要想有所为，必须有所不为，要想有所得，必须有所舍。我们舍弃了那些阻碍了我们正确行动、阻碍我们沿着大道行走的那些纷纷扰扰，这样能达到一个无不为的效果，也就是覆盖面广，效果更好，“无为而无不为”。下面这一段就讲，按照“无为”的方式来理解天下万事万物。“取天下常以无事，及其有事，不足以取天下。”“取天下”的规则是什么呢？“无事”。“无事”就是不多事，不干涉，不扰民，这样一切就自然而然顺理成章。所以第五十七章里边讲的这个事情就比较明确，“我无事而民自富，我无为而民自化”。“及其有事”，如果老是多事，老是妄为，不懂得事物的规律、规则，瞎折腾、胡折腾，这就是“及其有事”。则“不足以取天下”，那就不能够获得天下。得到的天下也得失去，因为它违背了大道。</t>
+  </si>
+  <si>
+    <t>16、33、52、71</t>
+  </si>
+  <si>
+    <t>【学知识做加法，修道做减法】【为道日损 无为无不为】由于四十七、四十八这两章的内容非常相吻合、相近，所以我们合到一起作为一章来讲解。四十七章讲的是一个什么事儿呢？是说人的感性认识，从哲学上说就是我们的感官接触客观世界，有时候接触得多了，它反而会造成一种迷乱和混乱，要通过人的智慧、理性认识，这样我们才能了解事物的规律，也就是这一章里边所说的“天道”。在这个基础上，我们一句句来解释。“不出户，知天下。”“户”就是门户，也就是大门。我不用走出家门，不用去外边到处跑，也能了解天下的大事。为什么？因为道家认为，天下大道归根到底，融于人的内心。内心里边有道，也就了解了天下的正道，了解了天下的大事。“不窥牖，见天道。”“窥”，从小孔里看；“牖”，就是窗户。我不用通过窗户去看，也知道天地之间日月星辰运行的规律。所以你看这个地方，“出户”是行走，出行，行万里路；“窥牖”是眼睛看，用感官接触客观世界，我不用这样。所以这个地方大家就感觉到，直观的一开始看，就觉得老子这个人有点轻视感性认识，人得通过实践嘛，人得通过感官接触客观世界，才能产生对客观世界的认识。是不是老子把这些东西全部都否认了呢？不是的。因为大家从书里已经看得非常的清楚，《道德经》举了很多生活中的例子，比如说“治大国若烹小鲜”，比如说“凿户牖以为室”，比如“说三十辐共一毂”，前面讲过的，这不都是生活中的例证吗？他对这个东西也很熟悉，怎么知道的呢？通过接触、了解。为什么在这一章里一开始他就讲这个事呢？要落到下面这八个字上。“其出弥远，其知弥少。”“弥”就是越来越，有的人走的地方越多，见得越多，不懂得甄别，不懂得筛选，不懂得提炼概括，“乱花渐欲迷人眼”，出得越远，反而了解到的真知越少，进步越少，为什么？不懂得反观自省，不懂得人心像一面镜子，如果你这个镜子是被灰尘蒙蔽的，你见得越多，其实反而获得的真知越少。这八个字在强调什么？我们要反观自省，要自我修行，自我修养，从哲学上说，从那些感性认识要上升到一种理性认识，达到对事物本质和规律的认识。所以你看，天下、天道代表着对事物全面的、本质的、规律性的认识，这个规律性的认识，需要我们安静地学习，在家里边读古往今来的著作，这不也是“不出户”嘛，也是“不窥牖”！我们了解这些间接的经验，从前人那里得到根本性的、全面的、通过理论阐释的这些知识，我们才能更了解事物的本质，更了解事物的规律。所以不要只把希望寄托在我们出去跑一跑，看一看，以为这样我们的知识就会越来越深刻，很多事情其实要通过理性的思维，这样我们才能进入到对事物本质和规律的认识，“其出弥远，其知弥少”。如果从中国的文化的角度来进一步理解的话，它还探讨一个什么问题、强调一个什么问题呢？就是人的品德。“大道之行，以心之知。”就是我们的心，我们的自我的内在的精神世界，这是道的重要的方面。所以很多人认为知识就是智慧，知识就是品德。不是的，很多人知识很多，不一定有智慧，知识多也不一定有境界、有品德。所以《道德经》强调的根本的“知”，从前面的比较中，相对于我们的感官而言，是人的理性的思维，理性认识、智慧，相对于外面的世界而言，它又是人的道德品德、人的品德。明朝的时候，关学的代表人物冯从吾先生讲过的一句话，我觉得冯从吾先生的这句话就非常能够解释这个道理，冯先生认为，古往今来的大学问都不出乎三句话：“做个好人，存点好心，行些好事。”做个好人，心正，身安，魂梦稳；行些好事，天知，地鉴，鬼神钦。所以一个人内心的品德、境界，通过自我的反省，自我的修养，达到了一个更高的水平，返璞归真，“归根曰静”，这些也是通过内在的自我修养来达到的。所以《道德经》认为人的理性认识，人这样的内心、这样的根本，它可以通过“不出户”、“不窥牖”，也可以自我修养，自我认知，不断地进步以达到。“是以圣人不行而知，不见而明，不为而成。”“是以圣人不行而知”，“是以”，“是”就是这样，“以”就是用，“是”可以解释为所以。“圣人”，好的统治者、领导者，在《道德经》称其为圣人。这些圣人，好的领导者、统治者要经常反躬自省，要经常内心关照，提高自己对大道和规律的认知水平。“不行而知”，不用到处跑，这一点也是可以得到的。“不见而明”，不用亲自去看，也能够明了道理，明了了这个道理，那就内心清净、无欲。“不为而成”，“不为”就是无为，就是按照大道的方式自然而然地去做，而不去妄为，这样一切都会顺理成章。这是我们第四十七章里边讲的内容，字虽然不多，但道理需要我们认真体会，“不出户，知天下；不窥牖，见天道。其出弥远，其知弥少。是以圣人不行而知，不见而明，不为而成。”当然对这一章的更进一步的理解需要我们和第四十八章，也就是我后面要讲的这一章相互参照，我们对这个理解才会更深刻、更准确。一开始就给大家说第四十七章、第四十八章我们要合起来，相互参照，为什么？这两章的内容讲的是非常吻合的，事实上也应该是一章的内容。第四十七章里边讲，“其出弥远，其知弥少”，第四十八章一开头就讲：“为学日益，为道日损。损之又损，以至于无为，无为而无不为。”这八个字一下子和上边的内容就衔接起来，为什么跑得越远反而知道的越少，这是站在道的角度来讲的。“为学”，在学知识，学到的知识内容越来越多。当然从学知识的角度来讲，这是非常有益的，不断地增多，可是我们获得很多的东西，见到了很多的东西，其实对我们了解根本性的规律和本质，了解大道并没有好处。站在一个更高的层次理解，就是说我们“为学”，讲究的是越多越好，见得多，看得多，见多识广。但是“为道”讲究的是什么呢？讲究的是内心的修行，讲究的是减少，用我们前面讲的话来讲，为学做的是加法，为道做的是减法，减少我们内心的欲念，减少我们的贪念，减少我们对很多问题的一种受了外界的影响而导致的内心的纷扰、困惑、迷乱，把这些东西损之又损，一点一点地把它减少，就像那镜子的灰尘一点点擦掉一样，“损之又损，以至于无为。”“无为”就是自然而为，把欲望减少，减少再减少，就达到了一种“无为”的境界，没那么多的贪念，没那么多的纷扰。我们用镜子来照这个天下，来照事物，万物进入到镜子里边，呈现出它本来的面貌。我们了解了事物的本质规律，了解了大道按照它来做，“无为而无不为”达到的是“无不为”的效果。所以在这儿借着这个机会，我再说一下道家自然无为的具体的含义：第一，不妄为；第十六章里边就讲，“不知常，妄作，凶。”你不了解事物的规律、规则，瞎折腾、胡折腾，那结果是非常糟糕的。我们“损之又损”，减少了这些遮挡着我们的认识，遮挡了我们的心窍的这些外在的事物、灰尘、迷乱，我们就照见了事物的本质和规律，我们就“不妄为”。第二，不多为；抓住关键，举重若轻，静观，看到事物的本质，找到解决问题的正确的方法，抓住关键，举重若轻。第三，有所不为；人要想有所为，必须有所不为，要想有所得，必须有所舍。我们舍弃了那些阻碍了我们正确行动、阻碍我们沿着大道行走的那些纷纷扰扰，这样能达到一个无不为的效果，也就是覆盖面广，效果更好，“无为而无不为”。下面这一段就讲，按照“无为”的方式来理解天下万事万物。“取天下常以无事，及其有事，不足以取天下。”“取天下”的规则是什么呢？“无事”。“无事”就是不多事，不干涉，不扰民，这样一切就自然而然顺理成章。所以第五十七章里边讲的这个事情就比较明确，“我无事而民自富，我无为而民自化”。“及其有事”，如果老是多事，老是妄为，不懂得事物的规律、规则，瞎折腾、胡折腾，这就是“及其有事”。则“不足以取天下”，那就不能够获得天下。得到的天下也得失去，因为它违背了大道。</t>
+  </si>
+  <si>
+    <t>29、37、43、57、59、64、65</t>
+  </si>
+  <si>
+    <t>【圣人没自己的想法，百姓想啥他想啥】【圣人无心 百姓心为心】第四十九章是《道德经》里边比较重要的一章，因为这里边有一句话大家都很熟悉，我们领导者讲话的时候也经常引用，就是以“百姓心为心”。从前面讲的内容，大家会知道这是一个通过换位思考，得出来这样的一种结论。这一章开头这句话我们先说一下。“圣人无常心，以百姓心为心。”是说一个好的领导者、统治者，不要老固执己见。“常心”就是固定的心思，自我的执着，不要老固执己见，不要老把自己的意志强加给别人，乃至强加给人民。应该怎么样呢？换位思考，将心比心，“以百姓心为心”，倾听民众的呼声，关注民众的利益，吸取民众的智慧，这都是“以百姓心为心”的表现。我们先体会一下这一章的宗旨在讲什么？其实这个道理就是讲了，换位思考，将心比心。百姓善良，我也对他善良；不善良，我也对他善良；信任我的，我信任他；不信任我的，我也信任他。干吗呢？这样我就能让人向善，让大家讲诚信。最后这一段就说一个好的领导者、统治者，让百姓都回归到他本来的这种生活，关注的是自己的生活中的事情。不要想那么多，不要心思混乱，不要烦乱，这样才能够形成一种良好的和谐的状态。这是老子的想法。我们一句一句来解释。“圣人无常心”，我再重申一遍，“圣”的繁体字，上面是个耳和口——聖，这两个字并列就代表着通达事理，下面是个王，也就是说一个好的领导者、领导人称其为“圣”。在这一章里体现得最为明显。“圣人无常心”，有的本子也叫“常无心”，意思都是一样的，就是不固执己见，没有自己僵化固定的思维，懂得换位思考。其实关于这个意思，我们通过前面讲过的第二十二章参照着理解，就比较容易了。我在前面多次说过，读《道德经》最好的方法就是不看注解，以经解经，相互参照，明白它要讲的真正的含义，谁的解读也不如他本人对这个东西的解释更符合他的本意。第二十二章里边就讲“不自是”“不自见”“不自矜”“不自伐”这“四不”。“不自是，故彰。不自伐，故有功。不自矜，故长。”这样我们才能不断成长，不断进步。一个好的领导人也是这样的，领导者、统治者，也应该“四不”，也就是“无常心”。你没有这样的智慧，老是固执己见，老是自我吹嘘，老是自我夸耀，老是觉得自己了不起，那你就没办法换位思考，将心比心了。所以“无常心”才能以百姓之心为心，倾听民众的呼声，吸取民众的智慧，关注民众的利益。沿着这个思路下面也好理解了。“善者，吾善之；不善者，吾亦善之，德善。”善良的人我用善良去对待他，不善良的人，我也用善良的方式去对待他，干嘛呀？教化、感化，这样我就得到了真正的善良。为什么呢？你这样做，起代表带头作用，大家也就人心向善了。大家注意这个“德”，王弼的解释非常明确，“德者，得也”，这样做就得到了这个天下、这个社会，这个国家就会人心向善。“信者，吾信之；不信者，吾亦信之，德信。”信我的人，我相信他，我跟他讲诚信；不相信我的人，我也相信他，跟他讲诚信。干嘛呀？这样天下人就会觉得诚信可贵，也就往诚信的方向去努力去发展了——“德信”。“圣人在天下歙歙”，“歙”就是合，就是收敛。你说圣人怎么样领导、管理这个天下呢？先要收敛自己的欲望，要想领导好别人，你先领导好自己，要想领导好自己，你先领导好自己的情绪，领导好自己的欲念，上梁不正则下梁歪嘛。“歙歙”，收敛自己的欲望，减少自己的欲念。“为天下浑其心”，让这个天下都怎么样呢？大家都没那么精明。不总是为了什么事都去争，“浑其心”，都那么样地浑厚、淳朴、厚道，关心自己的现实生活，而不是那么多纷乱的思维，那么多胡乱的想法，那么多的技巧、智谋、套路、心眼，用这种方式让大家和谐相处。“圣人皆孩之”，一个好的领导者把天下人都当作儿童，当作自己的孩子，一方面对他们非常关爱，另一方面也不要让百姓人心混乱，都像孩童一样纯净、淳朴。当然了，后边这一段大家也看得出来，这也是老子的一厢情愿。他希望统治者减少自己的欲望，天下人跟着也减少自己的欲望，关注自己的现实的生活，没有那么多的争斗、心眼、套路、技巧、欺骗、欺诈。这是老子生活的理想状态，也是他认为是和谐世界的前景，我们权当这也是他的一种理念和希望，毕竟这个社会的和谐也是我们的一种希望。只是他这种方法大家要辩证对待，大概用这种方法实现天下的太平，也只能是一种理想和理念，很难真正得以实现。但这一章里边大家要注意，开头这句话，我们要熟记，因为在我们国家的领导人的很多讲话里边都能看到这句话的出现，“以百姓心为心”，这是道家思想里边非常重要的一句话，让我们感觉到老子这个人在他冷静的、甚至有点冷酷的外表之下，内心涌动的热流，对于天下人的关注，对于天下人的关爱。这一章的原文我们解释完了，再强调一下这章的逻辑和重点，这章里边的关键在哪呢？这一章里边的关键是讲“圣人”和“百姓”，他们是国家不同层面的人，这一章讲究什么呢？讲究各安其位，各循其理。老子对这些做统治者的讲，你们要“以百姓之心为心”，善良的人呢你要好好地对待，不善良的人呢你也要好好对待，这样你才能得到这个国家人心向善的风气。信你的人你要讲诚信，不信你的人你也要讲诚信，这样才能得到天下诚信的风气。“圣人在天下”，圣人在上，领导天下。应该怎么样呢？怎么样叫循理循道呢？应该清静，无为，少折腾，少多事儿，这是上边的理，给他们讲的，你应该这样做，收敛自己的欲望，减少自己的奢靡、奢华，“清静为天下正”，这是对他们。对下边怎么讲呢？你这个在上边的人应该让下边遵循一个什么样的道理呢？“为天下浑其心”，让这个百姓浑厚，淳朴，宁静，没有那么多纷乱的想法，那么多技巧、心眼、套路、欺诈、欺骗，按照这个方向，百姓都关注自己现实的生活，把自己的日子过好，少管别的事儿，你让百姓能够做到这一点，上边的管上边的事，循上边之理，下边的循下边之理，这天下不就和谐了嘛。大家看出来了吧，“圣人皆孩之”，好的领导，一个国家的领导者，让这国家的百姓都像小孩一样，纯净、淳朴，没有那么多的欺瞒欺诈。上按上边的道理，下按下边的道理，这不就形成了一个和谐的状态了嘛。我们知道，真正的和谐是有差别的统一，大家都应该有表达自己的意见的机会，表达自己观点的机会，“各美其美，美人之美”，有差别的统一。但是老子这个地方讲的道理不是这样的，他讲的是“圣人无常心”，你要考虑到百姓，百姓在圣人的领导下应该怎么做呢？应该浑厚淳朴，没有那么多的智谋、欺诈、心眼，关注自己的现实生活，干好自己的事情，像儿童一样，纯净、干净、宁静，形成这个社会的和谐状态。所以我们只能说，老子这个想法呀追求一种和谐的目标，但是这个所用的方法在我们看来，这还是有很多地方值得检讨的，因为真的把百姓都变成小孩，还是不免有一点愚民政策的感觉。这一点大家还是要正确地理解。</t>
+  </si>
+  <si>
+    <t>3、27、54、57、62、79</t>
+  </si>
+  <si>
+    <t>【别作死，就没人能弄死你】【出生入死 善摄无死地】我们来讲第五十章，这一章表面上在讲养生之道，也就是文章所说的“摄生”，实际上表达的是更为深刻的道理。我们看书、看电视剧的时候，会发现有那么一些大师、大医生，一些位重权高的人向他们请教养生之道，“我怎么样能活得更加长寿？”这些医生、养生大师啊，大都是告诉他们要清心寡欲，不要奢靡奢华，不要胡吃海塞，其实这就是道家对于养生这事儿往更高的一个层次所要修养的内容，我们也可以把它概括为道家的生死观。道家认为养生跟生死密切关联。养生要顺应自然，要自然而然，要掌握规律、规则。你看我们读《庄子·养生主》里边的“庖丁解牛”，讲的不就是这个道理吗？目无全牛，游刃有余！这牛解得跟跳舞一样，跟音乐一样。所以文惠君最后就对这个庖丁讲：“吾闻庖丁之言，得养生焉。”养生要顺应自然规律，自然而然，自然而为。“生之徒十有三，死之徒十有三。”然后老子做分析，如果把天下的人分做十成，那么有十分之三的人是“生之徒”，也就是长寿的，还有十分之三的人是“死之徒”，是短命的。还有十分之三的人是怎么样的呢？“人之生，动之死地，亦十有三。”这些人本来可以长寿，最后由于自己的胡为、妄为、折腾，就把自己置于死地了。所以你看它的分类很有趣，十成的人中，三分之一的人应该是长寿的，三分之一的人本身体质各方面就是短寿的，还有三分之一的人本来可以长寿，但是妄动、胡为而置于死地。为什么会这样？《道德经》给了我们这样一句话：“以其生生之厚。”生，养生，或者可以解释得更明确，叫“求生”。太着急了，太迫切了，老想延长自己的性命，老害怕自己的营养不够，最后营养过剩了，反而把自己置于一个另外的相反的方向。当下一些有智慧的医生就提醒，我们现在不是营养不良，而是营养过剩，“生生之厚”。当然《道德经》讲的这句话只针对当时的统治者、位高权重的人而言，老是生活得这样奢靡奢华，“五色令人目盲，五音令人耳聋，五味令人口爽，驰骋畋猎，令人心发狂……”老是这样，还以为是让自己生命不亏，活得不亏。求生之厚，太急、太迫切，营养过剩，自己本来可以长寿，反而被置于成“死之徒”了，到短寿的那一拨去了。所以下面老子就讲了：“盖闻善摄生者”，听说这善于养生的人是什么样子呢？他们用了下边一段形容：“陆行不遇兕虎，入军不被甲兵。兕无所投其角，虎无所措其爪，兵无所容其刃。”习惯上我们以为“兕”是犀牛，或者有的叫母犀牛，其实这两种动物还不一样。这个“兕”是古代的一种瑞兽，比较凶猛，所以在古代的文字中，经常用这个“兕虎熊”比喻凶险之地。懂得养生的人，懂得正确对待自己生命的人，不去冒这个险。陆行的时候，尽量不碰这些凶猛的动物，如果你碰上它了，那你就没办法了，谁让你冒那个险呢？明知道野生动物园人家不让下车，你非得下车，遇到老虎了吧。有些地方人家告诉这个规则，这里边有危险，你偏不听，明知山有虎，偏向虎山行，明知山有狼，偏要做狼餐，这不就是“人之生，动之死地”吗？“入军不被甲兵”，上阵打仗的时候不为兵器所伤。为什么呢？“兕无所投其角”，你不遇到这个兕，那当然它那个凶猛的角就没有办法发挥它的作用了，没有办法针对你。一般我们画“兕”的时候都习惯把它画成独角兽。“兕”最有名的代表就是太上老君骑的那个板角青牛了，角非常锋利，尖锐，杀伤力强，你不遇到它，尽量别碰到，别把自己置于危险的境地，它的角当然就无所用了。“虎无所措其爪”，你不往虎山行，不遇到它，提前准备好避免这种凶险，老虎爪子再尖利，牙齿再锋利，它也无法对你发挥作用。“兵无所容其刃”，上阵不为甲兵所伤，尖锐的兵器，也没有办法发挥它的作用。“夫何故？”为什么会这样？“以其无死地”，不把自己置于死地，这样也就不会让自己的生命受到戕害。这是就是五十章。这一章体现了道家的养生之道：简单地说就是不要“作死”，自己不要找死，本来可以长寿的，自己作死把自己置于死地。很多人非得触犯法律的界限，甚至因此送掉了自己的生命，这不就是把自己置于死地嘛！所以我们说“NoZuoNoDie”，不作不死。从养生的角度来讲，你看道家讲的顺应自然，不单只是生活中的清心寡欲，而且还指不触犯边界底线，不触犯红线，知足不辱，知止不殆，不置身于死地，不让自己冒这种凶险，这也是道家养生之道里边的一个重要的内容，而且是更接近于哲学层面的、更有智慧的内容。那么这一段我们讲完了之后，我还要跟大家强调一下，道家的养生观，其实也是道家的生命观。道家对于生命的看法讲究的是自然而然，意思是什么呢？过于求生，过于厌恶死，这都不是一种自然而然的智慧，因为死亡本身就是生命的一部分，人自然而生，自然而死，真的到了生命结束的时候，那也应该开朗地、乐观地对待。这一点在道家的继承者那里，也就是道家的第二号人物庄子那里，讲得非常的明确——“之所以善吾生者，乃所以善吾死”。我们很好地对待自己的生命，不把自己的生命主动地置于死地，不求生之厚，真的面临死亡的时候，也应该把它好好地对待。自然而生，自然而亡，这是生命的自然而然的规律，谁也阻挡不了。第五十章，老子借养生之道讲了一个更重要的道理：有的人求生太急迫，太厌恶死亡，太害怕死亡，越是求生之厚，服了大量的药，用各种各样的营养的方式，推开死亡，想要避免，没想到越想避免的反而来得越快。所以，道家讲究自然而然的思想，这有着重要、杰出的意义。我们做个小小的梳理。第五十章，我们从开始讲的时候就给大家讲过，这一章可以分成两段，一段是讲有的人本来可以长寿，却进入了短命的行列，是因为“求生之厚”，太急迫、营养过剩导致的，另外一个是由于妄为、“作”，把自己置于死地的。怎样才能避免这两点呢？还是道家的这种思想，顺其自然，清心寡欲，清静为天下正。正确地对待生命和死亡，不把死亡当作是完全可以避免的事情，真的面临死亡的时候，也能够开朗地、乐观地对待。</t>
+  </si>
+  <si>
+    <t>13、55、74、75、76</t>
+  </si>
+  <si>
+    <t>【道生养万物，有功不占就是玄德】【道生德畜 玄德不宰】第五十一章逐句地来解释一下。“道生之”，“生”，创造，生养。道创造了万事万物。“德畜之”，德畜养了万事万物。“物形之”，万事万物有了具体的形状。“势成之”，周围的环境使它得以成长。正因为如此，所以“万物莫不尊道而贵德”，以道为尊，以德为贵。“道之尊，德之贵，夫莫之命而常自然。”尊道贵德，那自然会得到一个良好的结局和结果，这不是命，这就是自然而然的规律、规则。“故道生之，德畜之。”所以道生养万物，德蓄养万事万物。“长之、育之”，使它成长，使它不断地培育长大。“亭之、毒之”，这个“亭”呢，其实也好理解，我们常说亭亭玉立，这个“亭”就是成长的意思。这个“毒”就是成熟的意思，使万事万物成长，使其成熟。“养之、覆之”，“养”和“覆”都是保护的意思。养育万物，保护万物。“生而不有，为而不恃，长而不宰。”生养了万事万物，却不把它当作私有的产品，对万事万物有作为，却不把这个当作一种倚仗、凭借，甚至勒索的手段，对万事万物有这么大的功德，却不是以主宰者的身份出现。这个就是“玄德”，这就是最高深的、最深刻的智慧与品德。这是我们对这一段的直观的解释。其实，这一段的深意远不止于此。因为中国人讲哲学讲究“知行合一”，讲道的品性，其实也是为了人向道的品性去学习，按照道去做，这个也就是“德”。所以第五十一章里边讲道养育万物，德蓄养万物，也是人应该效法学习的。在这个层面上，我们深入地理解这一段话。“道生之，德畜之”，道创造了万事万物，但是它不把万事万物作为一种私有产品，并不是以一种主宰者的身份，以求其回报。由此我们可以看到，老子给我们提供了想要做成一件事的四个核心的要素和条件，也就是一种应有的程序和原则。第一个，要有道，因为道是创造万事万物的本源，所以我们要坚守大道，按大道的方式来创造。第二个，“德畜之”，“畜”就是积累的意思。在有道的基础上，我们要不断地、坚定地按照道去做，也就是“积德”。德就像水一样，我们就像一条船一样，我们积累的水越多，我们这条船在水上才能够航行得更自由。所以朱熹有一首诗说：“昨夜江边春水生，艨艟巨舰一毛轻。向来枉费推移力，此日中流自在行。”昨天江边涨水了，平常推也推不动的大船，现在根本不用推了，水多了，自然而然地就航行更加自由。他讲的是读书的积累达到一种自由的境界，其实人生又何尝不是如此呢？我们积累的德多了，按照道做事，更坚定、坚持、持久，那也就给我们人生提供了更广阔的空间与平台，不断地积德，我们的行为也就更加自由，我们的行为也就更加能够符合大道。庄子在《逍遥游》里面也讲了这样一句话，“且夫水之积也不厚，则其负大舟也无力”。水积累不多的时候，大船是浮不起来的，只要积累得多了，结果就是自然而然的事情，和朱熹所讲的道理不谋而合。第三个，“物形之”。人有道有德，是不是就可以把事情做成了呢？不够的，还需要一定的物质条件和手段，巧妇也难为无米之炊。有条件要上，没有条件我们创造条件，这样才能把事情向更成功的方向去发展。道、德、物三个条件总够了吧？不够的。要想把事情真正做成，还有一个很重要的条件，就是“势”，“势成之”。道家讲的无为，更强调的是顺势而为，掌握这个形势，了解大势，这样才能把事情做成。《淮南子》中举过这样的一个例子，大禹为什么能把水治成呢？顺水势而为。商汤周武为什么能夺得天下呢？顺民心而为。民心所向，就是历史发展的大势与潮流。所以大家在第二个层面把这四个字提炼出来，它是一个很好的成功学的例证，我觉得比现在讲的一些所谓的零零散散的成功学，不知道要深刻多少倍。道、德、物、势，“道生之，德畜之，物形之，势成之”。既然这四个要素，道和德是排在最前面的，“是以万物莫不尊道贵德”，所以万事万物没有不尊道而贵德的。人更是如此，有道有德，后边的事情才能继续发展，所以“道之尊，德之贵，夫莫之命而常自然”，这不是命，这就是一个永恒的自然而然的规律、规则。你按照道，按照德，尊道而贵德，会得到一个自然而然的良好的结局和结果，这是自然而然的事情。这不是命，这就是自然而然的规律和规则。所以大家注意，我们中国的这些经典，比如说《易经》，比如说《道德经》，都不是用来算卦占卜的，它就讲一个重要的内容：按照规律、规则来做，结果水到渠成、自然而然。下面这一段是对上面做的一个延伸。“道生之，德畜之”，道和德，生养万物，为万物提供条件，让它生长发展。“长之、育之”，培育万事万物使其生长、发展。“亭之、毒之”，使它成长、成熟。“养之、覆之”，不仅如此，还要养护万物，覆盖万物。道和德让万物长大，培育万物的成长，使它成熟又予以保护，功德可谓无量。孔子有一段名言：子曰：“予欲无言。”子贡曰：“子如不言，则小子何述焉？”子曰：“天何言哉？四时行焉，百物生焉，天何言哉？”这段话的直译是：孔子说：“我现在只想沉默。”子贡说：“如果你不说出心里想什么，那么我们这些学生还拿什么去记述呢？”孔子说：“自然说过些什么？不过放纵四季周而复始，任由百物蓬勃生长。自然你又何曾告诉别人什么啊？”很多人把这段话中的“天”翻译成神灵，这是不对的。其实这个“天”指的是大自然，也就是《道德经》里的天地，天地无语而泽被苍生万物，确又无语不居功自傲，不把自己当做万物主宰。这不也是《道德经》第五十一章的核心吗？培育万物的成长，使它成熟又予以保护，功德可谓无量。其实，在这样的智慧层面，孔子和老子的见解都是一样，“生而不有，为而不恃，长而不宰，是谓玄德”。关于这段重要的话，我们在第十章已经详细说过，不再重复。</t>
+  </si>
+  <si>
+    <t>2、4、6、10、21、25、34、42、62、65</t>
+  </si>
+  <si>
+    <t>【找到根本就懂万物，堵上欲望终身不累】【守母知子 塞兑闭门】一开始我们就说过，《道德经》里边有一个非常好的“正能量”，就是每当说到高大上的、特别伟大的事情，都喜欢用母亲的“母”字来作为代替和概括，或者说用“母”来做一个形象的比喻。如果我们的孩子读这样的文字，潜意识里就会有对母亲有一种敬畏与尊重。我们在第一章里边就说到，“无，名天地之始；有，名万物之母”。在这一章里边，又出现了母亲的这个“母”的概念。“天下有始，以为天下母。”就像动物、人类都是由母亲生养的一样，万事万物也都是由道创造的。老子用“母”来比喻大道，生动形象且让人充满对道的敬畏，意思就是说，天地一开始的时候，其实大道已经就在了。“既得其母，以知其子。”我们了解了大道，就是“既得其母”。知晓了大道，那我们就“以知其子”，也就了解了儿女。这个意思是什么呢？道是万事万物的普遍规律，它永恒存在，具体的事物都拥有具体的道，也就是具体的规律。你了解了大道，就可以以此来了解万事万物的具体规律。茶有茶道，花有花道，练武有武道，下棋有棋道……了解了普遍的道，也就更能够了解这些具体事物间的规律与规则。反过来也一样，“既知其子，复守其母。”我们从具体的事物之间，比如棋道、花道、茶道，从这具体的事物之间，我们了解了大道，感知了大道，那也就能更好地坚定地坚守大道。“没身不殆”，这样地做事情永远没有危险，没有失败，为什么？以道佑之，以道护之，这样我们做事情才能没有危险，没有失败。下面就说了解大道的方式方法。大道的了解，不是靠感性来体验到的，就像我们前边说的，“为学日增，为道日损。”“不出户，知天下；不窥牖，见天道。”所以如果是跟着感觉走的话，你是了解不了真正的大道的。因此“塞其兑，闭其门，终身不勤”，不要依赖感觉，不要把我们所见所知的就当作大道，重要的要用心，也就是哲学上讲的，用理性的思维，来了解认知大道。反过来讲，“开其兑，济其事，终身不救”，如果跟着感觉走，打开我们的感官的门户，感官这个东西，它是有很大的局限的。第十二章里面就讲，“五色令人目盲，五音令人耳聋，五味令人口爽”。你只靠这个是了解不了大道的。“见小曰明，守柔曰强。”什么叫“见小”啊？“小”就是具体的事物，具体的事物里面也蕴含着规律、规则。你能够从具体事物里了解具体的道、具体的规律，这也是一种明智。“守柔曰强”，道家是讲“柔弱胜刚强”的，道家是讲“知其雄，守其雌”的，“柔”就是雌柔，不管我们多么强大，我们也懂得坚守这个柔弱，因为柔弱更能长久。力量不够的时候，我们懂得用守柔的方式、韬晦的方式，来使自己的力量不断增大、不断增强，这样才能成为真正的强大。“用其光，复归其明”，用道的光芒，“复归其明”，来了解具体事物中的规律、规则，复归到事物光明的、明智的状态，我们才能走在光明的大道上。“无遗身殃”，不会给自己留下那么多的祸殃。“是为习常”，这个“习”，不同的本子有不同的写法。习，就是普遍、永恒的意思，就是普遍的永恒的规律、规则。也有的本子用的是沿袭的“袭”，也就是遮盖的意思。《道德经》里边用这个“袭”字的意思就是说，这是被大家认识不到的、被遮盖的规律规则，了解了这一点，我们也就对事物的了解更加深入。这两个意思都通，我们这里边用的是复习的“习”，学习的“习”，也就是经常的、普遍的、永恒的意思。“是为习常”，这就是一个经常的、普遍的、永恒的规律、规则。这一章核心的内容是说，道是一个普遍的规律，它存在于天地之间，所以叫“大道”。我们了解了大道，掌握了普遍的规律、规则，再来认识具体事物中的规律、规则，这是非常有帮助的，也是非常重要的。反过来也是一样，了解了具体事物中的规律、规则，也能够让我们更加坚信大道的存在，更加了解大道的伟大。这一章以母和子为喻，大和小对照，就讲述了这样的一个哲学的道理。这样的智慧能让我们用到大道的光芒，走在光明的大道上。</t>
+  </si>
+  <si>
+    <t>6、10、16、33、47、56</t>
+  </si>
+  <si>
+    <t>【大路平坦有人偏走邪路，还装阔】【大道甚夷 盗竽非道】讲到这里大家已经非常清楚了，老子衡量事情的最高原则就是大道。“使我介然有知”，“芥”就是小的、稍微的意思。假如让我稍微有知识、有智慧，“行于大道”，走在大道上。我最怕的是什么呢？“唯施是畏”，“施”，就是逶迤、曲折，在这里指的是邪路、歧路。走在大道上最可怕的是什么呢？就是害怕歧路太多，害怕走到邪路上去。“大道甚夷，而民好径。”其实大道是非常平坦的，但是一般人都喜欢走捷径，老想抄近道。“朝甚除”，朝政非常得混乱。“田甚芜”，田园都已经荒芜了。“仓甚虚”，仓廪实才好嘛，现在仓库里边都是空虚的。可是那些统治者在干吗呢？“服文采，带利剑。”穿着漂亮的、非常昂贵的衣服，带着珍珠宝石装饰的利剑。“厌饮食”，什么东西都吃腻了，对什么好吃的东西都已经感觉到厌烦了。“财货有余”，家里的财宝有那么多的富余。这叫什么？“是为盗夸。”《道德经》认为这个就叫“盗夸”，强盗，还夸耀自己的强盗行为。《道德经》在第七十七章里边就讲，“天之道，损有余而补不足”。现在这些人做的是什么呢？“损不足，以奉有余”。“非道也哉”，这完全不符合道的规律、规则，完全不是按照道的方式来做嘛。这一章表现了老子的平民的思想、公平的思想，指责在“朝甚除，田甚芜，仓甚虚”的情况下，那些人“服文彩，带利剑，厌饮食，财货有余”夸耀自己的强盗行为。这一章有一些字，我们还得具体地、细致地解释一下。“唯施是畏”，凭什么把这个“施”念成“迤”，解释成歧路呢？因为道弯弯曲曲的时候，歧路众多。在《列子•说符篇》里边讲的一件事——歧路亡羊。杨朱他们家的邻居羊丢了，很多人都出去找，杨朱就觉得很奇怪就问，就一只羊怎么这么多人去找啊？邻居就告诉他，歧路多，岔路太多了。找羊的人回来了，杨朱问找到了吗？邻居说没找到。又派更多的人去找，还没有找到。歧路中又有歧路，岔路中又有岔路，所以常常使人丧失了大道，迷失了大道，所以杨朱听了之后几天都不说话。古人有“歧路亡羊”，也有遇穷途而哭，走道遇到没有路了，痛哭而返，其实都是感觉到了人生道路上的一些很值得人害怕的事情。行于大道，最害怕的就是歧路、岔路，一旦走错路，方向一错，后边的一切麻烦就都来了。所以老子说“大道甚夷”，“夷”就是平坦的意思，大道其实极为平坦。“而民好径”，人却老喜欢去走这个捷径，走了捷径之后，最后发现回到正确的大道上是非常困难的。其实，很多的所谓捷径就是歧路，就是邪路，人要脚踏实地，这样才能够行走在正确的大道上。通过努力获得成功，而不要投机取巧，更不要把投机取巧里边得到的东西当作一种炫耀夸耀，这个叫什么？“盗夸，非道也哉。”</t>
+  </si>
+  <si>
+    <t>12、46、57、75</t>
+  </si>
+  <si>
+    <t>【修道从自身做起，一步步推及天下】【善建不拔 以身观身】第五十四章由三段构成。第一段：“善建者不拔，善抱者不脱，子孙以祭祀不辍。”这一段在讲按照大道来建设，没有人能够攻击倒它，把它拔除掉。大家想，人类建设的很多的东西，有成必有毁，都是会被拔除掉的，而大自然呢，比如说山川，这是大自然建筑的东西，有的或许可以被拔除掉，但这一章讲的不是这个意思。“善建者”指的是人精神方面的建设，大道方面的建设，这个伟大的思想是不会被攻击倒、被拔除掉的。比如我们现在学的《道德经》，历经两千多年，很多人都在攻击，在否定，在嘲笑，可是这无碍于它伟大的思想，现在学的人越来越多，大家越来越从里边得到一种智慧的启迪。另外像佛祖释迦牟尼，像孔子，历史上一些伟大人物的思想，他们的思想像什么？就像夜幕中的星光，给我们在黑暗中指引方向，有的甚至像光明普照的太阳。这些思想属于“善建者”，是没有办法把它攻击倒、拔除掉的。“善抱者”是什么意思呢？直观的理解就是善于把你抱住的人，你是脱离不开他的掌控的，其实这只是望文生义的理解。在《道德经》里边多次提到“抱”字，比如说第二十二章，“抱一为天下式”；比如说第四十二章，“万物负阴而抱阳，冲气以为和”。抱的是什么？“负阴抱阳”。所以这个“善抱者”就是掌握阴阳之不测，掌握阴阳相互作用、相互变化的规律规则，而“一阴一阳之谓道”，所谓“善抱者”，也就是了解大道的人。“不脱”，脱离不开大道的掌控，脱离了大道就走到了一个危险的境界。“子孙以祭祀不辍”，一代一代，千秋万代，按照“善建者”、“善抱者”这些伟大的思想来做，对他们表示一种尊重、敬仰，不断地学习。“修之于身，其德乃真。”按照这个伟大的思想来做事、来修身，这样所得到的德，才是真实的、纯净的。“修之于家，其德乃余。”按照大道来修家，一家人遵循大道，这样获得的家的品德才是丰盈有余的，积德之家必有余庆嘛。“修之于乡，其德乃长。”拿大道来传达给一个乡，按照这个方式形成一种良好的乡风。“长”就是领导的意思。你把这个方式在乡里边普及，让大家坚定地按照道的方式来做，你才能成为这个乡的好的领导者。我们知道，在宋朝的时候，陕西“蓝田四吕”首先制定了乡约，它对我们中国良好的乡风的培育起了非常大的作用，这不就是“修之于乡，其德乃长”的具体表现嘛。“修之于国，其德乃丰。”按照这样的一个方式来治理国家，让国家按照大道去做，所收获的德才是丰盛的、伟大的。同样的道理，“修之于天下，其德乃普。”天下是天下人的天下，不是一人之天下，所以大道之行，天下为公。按照善建、善抱的大道来做，修之于天下，这样大家得到的才是普遍的，如光明之普照。这是第二段，老子在讲按照“善建”、“善抱”的原则来做，所获得的伟大的结果。“以身观身”，“观”就是观察。我们按照修身的要求，大道修身的方式来观察这个人，他修身方面是不是善建、善抱，是不是没有脱离大道。“以家观家”，按照家庭的修养的要求来观察家庭的品德、家风。当然这个“观”的时候就自然有对比的意思，和其他的家里边进行对比，相互比较，看哪一个是更能按照“善建”、“善抱”的这种符合大道的原则方式来修身、来齐家。下边也是同样的道理，“以乡观乡”，乡自有乡的要求，和家是不一样的，范围扩展了，有很多家庭。但是如果这个大道一以贯穿，都是按照对“善建”的、“善抱”的原则祭祀不辍、尊敬，敬仰，以按照这样的一种规则来作为荣耀，都为良好的家风、乡风做出贡献，这不就是道一以贯之吗？同样的道理，“以国观国”，一个国家有这个国家的精神、思想、风貌，按照大道要求来做，在和其他国家比较中，取长补短。同样的道理，“以天下观天下”。大道一以贯之，一条主线，一切顺理成章，自然而然，无往而不胜。所以最后老子说，我怎么知道天下也会是这个样子？“以此”。大道所向无往而不胜，虽然人世间有那么多的枝枝蔓蔓，但是核心“善建”、“善抱”之大道，不要脱离开大道，坚定地、坚持地按照它去做，按照道去做就是“有德”。修身得到的是“真”，修家得到的是“余”，修乡得到的是“长”，修国得到的是“丰”，修天下得到的是“普”。所以，从修身开始，最后落到天下，不就是这样一个简单的道理吗？其实读这一章的时候，大家会有一个非常深刻的感受，中国先秦时代是中国的轴心时代，各个思想流派之间的思想，虽然有差别，但是也有相同的地方。所以我们看这和儒家的思想，修身、齐家、治国、平天下一样，都是从修身开始，最后才能够成为国家的好的领导者，才能把这种思想普及到天下。“天下难事必做于易，天下大事必做于细。”从自身做起，要求自己按照大道的这种修养、修为，按照“善建”、“善抱”的原则，坚持地、坚定地去做，我们才能真正地有德。</t>
+  </si>
+  <si>
+    <t>33、49、59、67</t>
+  </si>
+  <si>
+    <t>【德厚的人像婴儿，柔和又有生机】【含德若赤子 知和曰常】这章开头讲了一个非常有意思的概念，就是“赤子”，这是因为婴儿刚出生的时候浑身是红色的，但这个词更重要的作用是比喻心地的纯净、纯洁。“含德之厚，比于赤子。”按照道的标准来衡量，赤子心地纯净，无恃无为。这是含德浑厚的一种表现。其实，不只老子，孔子也对婴儿的状态充满了景仰，认为这是一种有道的含德之厚的表现。孟子也说，“大人者不失其赤子心”。老子更是把婴儿作为一个范本与榜样，第十章就说“专气致柔，能如婴儿乎？”人精神集中，气息平和，那不就是像婴儿的样子吗？下边这些都是从经验的角度来讲获得的感受。小孩的他精神状态很安稳，蜂子、毒虫、蛇也不蜇他，也不咬他，为什么呢？因为小孩没有危险，没有对这些动物造成威胁的举动。其实有时候蜂子落到我们脸上，也许只是为了得一滴汗液，没有汗液，它采的蜜也不能凝固，可是我们一打它，它当作危险的时候，就要用它的毒针来蜇我们。很多动物也是这样，人没有危险动作的时候，其实也不会攻击人，但人见到它就害怕，就有一种防范甚至攻击性的动作，这也是难免的。老子说你看，这婴儿啊，“毒虫不螫”，毒虫不蜇他。“猛兽不据”，虎啊、狼啊这些猛兽，也不把它叼走，不用爪子把他抓走。我们经常会听到这样的一些事，很多动物还喂养、抚育这些落在田野里边的荒野上的小孩，当然这也不是全部的情况，我估计老子也是拿这个做一个说明而已。“攫鸟不搏”，攫，攫取。有的时候，人手上拿着一个什么东西，比如说拿着肉，在一些荒远的地方，老鹰就飞下来把这肉抢走了，但是对小孩它却不这样做，除非是尸体。“骨弱筋柔而握固”，这小孩其实身体是最柔软的，但是你看他这小拳头却握得很紧固。这人生啊，深究起来是有点意思。小孩刚出生的时候，都是握着拳头，似乎想抓住点什么，但人最后离开这个世界的时候，却是放手了，知道什么也抓不住。“未知牝牡之合而全作”，“牝牡”本来指的是雄性和雌性的动物，但是这个地方指的是男女。小孩刚出生不知道什么男女的事情，但是你看他的小生殖器却非常坚挺。老子用这样的一个方式来做形容，说婴儿精气很纯、很多、很壮，“精之至也”，达到了一个最好的状态，老子是这样认为。下边这个描述确实挺有意思，叫“终日号而不嗄”，小孩终日啼哭，但是嗓子却不哑，那不是精气足的表现吗？我现在讲课，讲一段时间喉咙就哑了，我们现在为什么会这样？老子可能认为，这人长大了，欲望多了，精气耗费得多了，所以就不像小孩那样精气充足。这一段把婴儿作为一个得道者的良好状态的表现讲完了，下边老子该阐述自己的观点了。“知和曰常”，“常”就是规律、规则。了解了这个“和”，通过婴儿引出来的“和之至”，谁能够像婴儿一样，让我们气息平和，让我们的欲望平和，不那么欲壑难填，就了解大道的规律、规则。“知常曰明”，了解这个事物规律、规则的人，那才是明智。“益生曰祥”，让我们的生命有益，这个才是一个吉祥的表现。这是正面，那负面呢？“心使气曰强”，老是盛气凌人，体现的是这种强横、强暴，这个是道家所反对的。气息不平和，纵心任气、任性，这个是强暴、强蛮的表现。在前面第二十三章讲过，“飘风不终朝，骤雨不终日，孰为此者？天地。天地尚不能久，而况于人乎？”暴风骤雨它不会持久，天地的使强也不过只是持续一阵子，它告诉我们这个道理，强不能持久。“心使气曰强”，这不是一种好现象。“物壮则老”，事物发展到顶峰的时候，就开始走下坡路了，人到了壮年之后，就逐渐向衰老的方向发展了。“谓之不道”，这已经使气，老是以强壮来作为目标、作为处理问题的方式，这是不符合大道的。“不道早已”，既然不符合大道，那这个事情就不能持久，很快就会结束了。你看这婴儿的状态，其实应该能存活得更长久、寿命更长，为什么后来很多人变得短寿了呢？那就是让自己脱离了大道，没有像婴儿那样，“精之至”，“和之至”。所以人应该“知和，知常，益生”，而不应该使气，不应该“物壮”，如日中天的时候就走下坡路了。人生最美的境界是什么？花未全开月未圆。所以，按照大道的方式来处事、认知事物，这样我们才能够明，才能够益，否则的话就会“不道早已”。</t>
+  </si>
+  <si>
+    <t>10、16、28、42、50、58、76</t>
+  </si>
+  <si>
+    <t>【懂的人不多说，收敛锋芒混日子】【知者不言 和光同尘】这一章还是比较容易理解的。“知者不言，言者不知。”开头的第一句话就讲，有智慧的人是不多言的，所谓“行不言之教”，还有“悠兮其贵言”，都在讲这个道理，有智慧的人是不会多嘴多舌的，不会去乱说的。“知者不言，言者不知”，老是认为自己无所不知、以为自己有智慧的人，其实是不具备真正的智慧的。“塞其兑，闭其门。”我们前边解释过，“兑”指的就是耳、目、鼻、舌这些感官，所以它强调的是感性对事物的认识，是不可信的。“塞其兑，闭其门”，这样才能对事物本质的根本的内容有真正的理解。下面讲处理问题的方式方法，做人的思想与智慧，要“挫其锐，解其分，和其光，同其尘”，不要锋芒外露，这样才能长久。要解除那些纷纷扰扰，不要让纷纷扰扰在心里打成结——心有千千结。真正了解道的含义的人，按照道去做事的人，是很容易摆脱这些纷纷扰扰的。“和光同尘”，也就是讲同流而不合污，所谓外圆而内方，所谓与世推移。那么这个叫什么呢？就叫做“玄同”。“玄”本来是天的颜色，意味着深远，这样的同是深远的、深刻的，同流而不合污，当然里边就非常有玄妙了。下面的内容讲得也非常清楚，就是说道并不是为人谋利益的，得道的人他怎么样来和万事万物打交道呢？就像道一样，“不可得而亲，不可得而疏”，道并不是对谁更亲近，或者对谁更疏远。有亲就必有疏，有疏就必有亲，这个就不平等了，这就不“玄同”了。所以，按照道的、“玄同”的方式来做，没有亲疏之别，无差别。“不可得而利，不可得而害”，有利必有害，有害也必有利。所以你并不能凭借道而获利，也不能用这个道来危害别人，无差别，无利无害。“不可得而贵，不可得而贱”，道对谁也没有贵贱之分，还是依然玄同、平等，一旦有贵贱之别，便也就丧失了道的本质的属性。所以庄子讲，“以物观之，自贵而相贱。以俗观之，贵贱不在己。”从物的角度来看，都认为自己是珍贵的、宝贵的，其他的东西比不上自己的尊贵。用世俗的观点来看，贵和贱不在于自己，而在于别人的评价，在于外在的标准。而“以道观之，物无贵贱”，从道的角度来看，这万事万物并没有什么贵贱之分，所谓公正、平等、无差别、无贵贱之分。正是因为这样，所以它成为天下最尊贵的，“故为天下贵”。所以这章的内容啊，道表现为玄同，按照这样的深远的玄同的道理来理解事物，就是从道的角度来观察问题。道没有亲疏之别，没有利害之分，没有贵贱之差，所以用这样的一个角度来观察世界，这个才使它成为天下最令人敬重尊仰的，“故为天下贵”。</t>
+  </si>
+  <si>
+    <t>4、23、39、52、70、81</t>
+  </si>
+  <si>
+    <t>【治国靠正道，不折腾百姓就自然好】【以正治国 无为民化】第五十七章的这段话非常有智慧，因为这段话一开始就指出来了，事物之间的不同，有本质的区别，所以处理问题、解决问题的方式方法也不一样。“以正治国，以奇用兵”，治国讲究的是堂堂正道。道家讲的“正”当然就是清静无为，不多事，不扰民，这就是道家讲的正道，是治国的大道理。可是用兵讲究的是“以奇用兵”，“兵者诡道也”，兵不厌诈。所以不能把用兵的方式、战争的方式用到治国的上面来，这两者不同，解决的方式也不一样。“以无事取天下”，无事就是不多事、不扰民、不刁难，这样才能够得到天下，并且坐得了江山。道家“无事”是“无为”的一个重要的方面，不多事、不扰民、不刁难，而“有为”讲的是妄为，多事、扰民、刁难，我们在前边这一点已经非常明确了。“吾何以知其然哉”，我怎么知道是这个样子呢？所谓“以此”就是依据上边“以正治国，以奇用兵”它们之间的本质不一样，所以解决的方式方法也不同而得出的结论。下面，老子开始谈他对治理天下的重要的看法。违背了大道，违背了道家的以“清静无为”为根本来治理国家的方式，会出现什么问题呢？“天下多忌讳，而民弥贫”，治理天下、领导国家忌讳太多，这个也不能动，那个也不能动，这个人的职务比较高，法令涉及不到他，当然出现了忌讳，不敢动，这个地方一定会形成一个空场，形成一个腐败的群体。百姓当然越来越穷了，财富都集中在少数人的手上。“民多利器，国家滋昏”，“滋”就是越来越。如果民间利器众多，武器众多，民与民之间械斗、抗法，那国家当然越来越混乱。“人多伎巧，奇物滋起”，“伎巧”就是各种各样的奇技淫巧，越来越多，大家对这些越来越感兴趣，这个技巧能够给他们带来利益，那么各种各样的奇奇怪怪的东西，甚至包括那些妖孽的东西，就不断兴起。“法令滋彰，盗贼多有”，既然这样，要用法律来管，法条定得越来越多，越来越严苛，反而盗贼越来越多。在前面这一段讲完之后，《道德经》说“故圣人云”，很明显，这是引用以往的通达事理的王们的话，老子用自己心中有智慧的人的语言来作为结尾。“我无为而民自化”，道家讲的无为，第一，“不妄为”。第十六章里边说“不知常，妄作，凶”，不了解事物的规律、规则，瞎折腾、胡折腾，这个结果是非常糟糕的。第二是“不多为”。抓住关键，举重若轻，多言数穷，不如守中，适可而止，恰到好处。第三讲究的是“有所不为”。人要想有所为，必须有所不为。一个政府也罢，一个领导者也罢，所有的事情都抓在自己手上，那底下的人怎么得到锻炼呢？不把担子压给他，他怎么练出独当一面的能力呢？什么事都控制在自己手上，那众人怎么样自我化育自我成长呢？所以无为才能让国家的人民、才能让自己的属下自我化育自我成长。事情成了应该怎么样呢？第十七章“功成事遂，百姓皆谓‘我自然’”，事情做成了，百姓都说这是我们的努力把这事情做成的，这就叫“民自化”。“我好静而民自正”，前面我们讲过，道家讲的静，内心的清净，静下来才能找到解决事物的正确的方法。我清静，走正道，不那么浮躁、急躁、暴躁、狂躁，做一个好的表率，上梁而正，百姓当然也就正了，百姓当然也就好静而走正道了。“我无事而民自富”，不多事、不扰民、不刁难，那百姓自然就富起来了。“我无欲而民自朴”，“朴”就是原木，《道德经》里用原木喻指做事敦厚、朴实、厚道，没那么多欲望，不是老想抢夺别人、占有别人的。就像黄宗羲在《明夷待访录》里边讲的，古代的那些皇帝都是什么样的？“离散天下人之儿女，荼毒天下人之肝脑，以供一人之淫乐。”这是我的，普天之下都是我的。所以欲望无止境，你让百姓能够朴实厚道，这也不可能。所以不要欲壑难填，不要什么东西都看作是自己的，可以任意掠夺，这样百姓自然就朴实、厚道，民心淳朴。这里边的两句话，我们国家的领导者讲话的时候也经常引用：“我无为而民自化，我无事而民自富。”所以，第五十七章讲了两个重要的道理，第一个不能把打仗的这一套用到治国之上。治国讲究的是堂堂大道，讲究的是清静无为，所以以无事取天下。第二个就讲站在领导者的角度，站在统治者的角度，应该怎么做呢？无为、好静、无事、无欲，这样自然一切顺理成章，百姓就会自化、自正、自富、自朴，事成了也会“功遂身退，百姓皆谓我自然”。这是一个好的领导者、好的政府做事的道理之所在，反之越多事儿，越是用那种严苛的法令，导致的结果适得其反。忌讳多了，百姓就越来越穷，民间的利器多了，国家就越来越混乱，大家都倾向于奇技淫巧，把这个当作一种喜欢的甚至不停地去追求的目标，那这个国家就越来越怪，各种奇葩的事情都纷至沓来。越觉得法令不够，越制定得严格、细致，以为单靠着法令就可以解决所有问题，反而适得其反，盗贼多有。所以，这一章里边讲的，也是我们经常说的——这本书的总纲：“反者，道之动”。我们考虑问题，不要只考虑它一面，要相反相成，用一个更高的观察事物的角度来理解。</t>
+  </si>
+  <si>
+    <t>2、3、5、10、17、19、37、48、49、53、60、65、75、80</t>
+  </si>
+  <si>
+    <t>【祸里藏着福，福里埋着祸】【祸福相依 方而不割】第五十八章有两个我们非常熟悉的成语，一个叫“祸福相依”，一个叫“光而不耀”，也是这一章核心的内容。祸福相依，福和祸是相互转化的，两者也是相辅相成的，分不开的。“光而不耀”在讲什么呢？我们大家看到过月亮，月光是明亮的，在黑暗中给我们指引以方向；同时月光也是不张扬的、不炫耀的、不刺眼的。中国人喜欢拿月亮来比喻君子的形象，做君子得先有光，但是不管我们有什么，都不要老想着去张扬、炫耀，让别人感觉到刺眼。所以《道德经》很多章节，都向我们揭示了这样一个道理：有才华、有知识、有道德的人，不要老想着去张扬、炫耀。以这两个成语为切入点，我们会对这一章的内容有个直观的感觉。我们来逐字逐句地解释一下。“其政闷闷”，“闷”就是淳厚。就说政治比较淳厚宽容，那么这个国家的百姓也就是敦朴淳厚，不耍心眼。“其政察察，其民缺缺”，假如这个政治非常苛察，对一切都监控得到位，那老百姓就会感觉到有很多的缺陷与不足，就要耍心眼。所谓上有政策，下有对策，也就失去了原本的淳朴。“祸兮福之所倚，福兮祸之所伏。”福和祸是相辅相成的，在一定条件下是相互转化的。民间的很多说法，大家都能够体会到这意思的延伸和运用，比如，我们经常说“大难不死必有后福”、“好事多磨”……福和祸是相伴而行的，有时候我们认为是福的事情，它可以转化为祸，反过来也是一样，所以这就叫“祸福相依”。怎么样来理解这个事情呢？给大家举个例子，大家就清楚了。其实各民族的智慧到达高点的时候，往往是相互重合的，印度有一本佛经叫《大般涅槃经》，在这里面讲了这样一个故事。有一天早晨，一家主人一开门，门口站着一个衣着光鲜、非常漂亮的女子，主人就问你是谁，女子说我是“功德大天”，我到谁家谁家就一切兴旺。主人高兴地请进来，焚香供拜。刚一关门又有人敲门，开门一看，门口站着一个衣衫褴褛，非常丑陋的、黑瘦的女子，主人就没好气了，主人就问你是谁呀，那女子说我是“黑暗”，我到谁家，谁家就一切破败！主人当然不让她进来，拿着刀驱赶。结果这女孩说你太笨了，刚进去的是我姐姐，我们俩从出生这天起就没有分开过，你把我赶走了，她也留不下。主人不信，进去一问果然是这样。福跟祸是相伴而行的，所以它就提醒我们，遇到福事的时候就要小心谨慎，避免乐极生悲；遇到祸事的时候，也不要感觉到沮丧，因为我们对灾祸有所警惕，它可以避免后面更大的灾难。韩非子讲过“千里之堤，溃于蚁穴”，我们发现了这个蚂蚁窝，知道它是一个祸患，很早的把它堵上，那就避免了以后更大祸事的发生。这就是“祸福相依”的道理，在我们文化中影响是非常深刻的。讲完这一段后，《道德经》就说“孰知其极？”这个事物到达极点的时候，向它相反的方面转化，所谓两极相通，所谓物极必反，但是这个极在哪里呢？这个是需要我们认真去体会把握的。“其无正”，其实并没有确定的标准，所以并没有说我们到了一个什么程度，一定会向它相反的方面转化，这是要根据不同的时间、地点、条件，需要我们认真去领会把握的、体悟的一种智慧。“正复为奇，善复为妖。”“正”，你把它弄到极点它就偏了，“善”到达极点的时候，它就转化为它相反的方面。有些人老想寻找一个固定的标准，《道德经》就说：“人之迷，其日固久。”在这个方面的迷惑，时间已经由来已久。所以我们总是要寻找一个固定的标准，总是觉得做事情有一个固定的程序，固定的套路，这个就不圆融。下面就讲，“是以圣人方而不割”，“方”就是方正，“割”就是生硬。有原则但是不生硬，人要懂得去碰硬，但是不要去硬碰。方正而不生硬，这样才能圆融，我们把它叫做“外圆而内方”。“廉而不刿”，“廉”就是棱角，“刿”就是锐利。有棱角但是不要老用锐利之处去刺伤人。“直而不肆”，有人经常就说，我说这话你别在意，我这人很直。其实有的时候不是直而是自私，是放肆、过分。所以我们说直率，它是一种心态，但是你讲话的方式得懂得圆融，直率而不放肆。“光而不耀”，有光芒，但是不要老去张扬、炫耀，让别人感觉到刺眼。咱们中国人喜欢讲君子，什么样的人是君子呢？中国人除了用月亮来代表君子“光而不耀”的特点之外，另外，也喜欢用玉来代表君子的形象，所谓“谦谦君子，温润如玉”。“谦谦君子”出自《易经·谦卦》，原话叫“谦谦君子，用涉大川”，一个人保持这种内敛的、谦逊的风度，这样才能走好人生长远的坎坷的道路。另外一个是出自《诗经》的“温润如玉”，谁都知道闪着贼光的肯定不是什么好玉，真正的好玉都是光芒内敛，给人一种温润感。我认为“光而不耀”是中国文化里，对君子形象用得最好的一个比喻。我们有知识，不要老想着去张扬、炫耀，大家聚到一块的时候，一个人老去炫耀自己的知识，对别人的说法都嗤之以鼻，认为自己什么都懂，百事通，时间长了，大家就不喜欢跟这人打交道了。有道德，道德是约束我们内心的，不是老是向别人去张扬炫耀。《道德经》第三十八章开头这句话，大家都知道——“上德不德”，最有道德的人从来不去张扬、炫耀自己的道德。当然，至于炫官、炫富，这不仅不是一种君子的形象，还会给自己惹来无尽的祸殃。是否还记得第九章里“金玉满堂，莫之能守；富贵而骄，自遗其咎”，炫富炫贵，会给自己惹来无尽的祸殃。在第二章里“功成而弗居”，哪怕我们有功劳，不管是对家庭、对单位、对国家有功劳，也不要老想着去张扬、炫耀，越是不张扬、不炫耀，这个才能在人心里长久地存在。第九章里面也说“功遂身退，天之道”，这是符合自然的道理。第五十八章讲完之后，我再做一下梳理和强调。这一章有两点需要注意，一个是“祸福相依”的道理，一个是“光而不耀”的形象，怎么样能做到这一点？我们要明白“物极必反，两极相通”。了解这样的智慧与道理，我们做事情才能够圆融。所以一个有智慧的人，有智慧的领导者，为人处事应该方正而不生硬，要圆融，有棱角，但不要老去割伤人，要懂得委婉迂回地处理问题的方式。直率，但又不越界进入到了放肆、无所顾忌的程度，光芒内敛而不要老去张扬、炫耀，要给人留下一种谦谦君子、温润如玉的形象。这是我们和别人、和这个社会打交道的一个重要的思想与智慧。</t>
+  </si>
+  <si>
+    <t>2、36、40、55</t>
+  </si>
+  <si>
+    <t>【治国养生，节俭才是长久之道】【治人事天 啬为长生】这一章讲了两种生活的态度：一种是做“加法”，不断地叠加，不断地累积，有了还想更有，多了还想更多；另外一种是要懂得做减法，要节俭节制，有的时候我们的欲望减少一分，其实我们的幸福也就多一分。这两种人生态度也是相辅相成的，可是大家更注重的是第一种，所以一章就强调我们这种做减法的态度的重要性。其实这一章核心就讲四个字：节俭节制，讲节俭节制对一个国家、对社会的重要意义。“治人事天莫若啬。”一开始就讲“治人事天”，领导这个国家的人民要顺应天理。“莫若啬”，什么事情最顺应天理呢？节俭节制。我们现在用的这个词叫“吝啬”，这个词有点负面的含义，在《道德经》中这个“啬”，我们把它译成节俭节制，这样更符合于我们的接受习惯。“夫唯啬，是谓早服”，“夫唯”是个语气助词，“啬”是节俭节制。“是谓早服”，“早服”就是早得道。懂得节俭节制的道理，就是可以早得道的人。“早服谓之重积德”，“重”就是不断。懂得节俭节制就是在不断地积累自己的品德，积累自己的德行。因为我们说《道德经》道和德要分开理解，按照道去做，就是有德，不断地按照道去做，就是不断地积德。重积德就是不断地积德，所以你看“早服谓之重积德”，早得道，一直坚定地坚持按照这个去做，就是不断地积累自己的德性，积累自己的品德，积德。我们就像一条船，我们积的德就像水，水积累得越多，我们船才能自由地航行，不管你船多大，如果没有水，在那儿搁浅，它也发挥不了船的这种作用。“重积德则无不克”，“克”就是克服，按照这个“啬”的方式，也就是节俭节制的方式去做事情，那就没有什么困难克服不了的。因为在节俭节制里边磨练的就是人的思想品德，磨练的就是人的意志，磨练的就是人面对困难无所畏惧的态度。“无不克则莫知其极”，你说这个东西力量这么强大，没有什么东西它克服不了，所以它的力量“莫知其极”，你不知道它的力量有多么强大，对一个人是这样，对一个国家更是如此。“莫知其极，可以有国。”你看这话是给谁讲的？给统治者、领导者讲的。一个领导者领导团队，领导这个国家的人民培养出一种节俭节制之风，你这样才能让你的国家长久地存在，长久地发展。毛泽东主席在中华人民共和国成立的时候就指出，“贪污和浪费是极大的犯罪”，自己也以身作则。你领导团队，领导全国人民培养出一种节俭节制之风，这样面临什么样的困难的时候，大家都有信心去克服。“有国之母，可以长久。”“母”就是根本。节俭节制是立国，是国家长久发展的根本。我们现在叫“八项规定”“反四风”，领导国家的人民培养出节俭节制之风，国家才能长久持续地发展。有一件事儿大家都知道，电视经常打出一个公益广告，说现在每年中国人浪费的粮食就是世界上两亿人的口粮。你说世界上现在每天都有人在饿死，可我们中国人这么浪费，能符合天道，能符合天理吗？如果因为这种浪费有什么惩罚落到我们头上，那么我们也无话可讲。你从这一章里面就可以感觉到，一个人浪费，糟蹋的是自己的福分；一个国家浪费，糟蹋的是国家的福分，对国家的根本有所损伤。“是谓深根固柢，长生久视之道。”国家培养出节俭节制之风，才能长久发展，这样做叫什么？叫“深根固柢”。我们讲叫根深蒂固，你让这个根本、让根扎得深，扎得稳固，深根固柢。“长生久视之道”，于人来讲是如此，可以让我们的生命更为长久，因为一个人的节制节俭，不去放纵自己的欲望，这也是一种养生之道。得以长久地存在，长久地发展，得以长寿，对国家来讲也是如此。所以“长生久视”，长久地存在，大家能够长久地看到它。《道德经》强调“做减法”的这个方面，在世界哲学界，有着非常重要的影响。我们中国人有一个优良的文化传统，讲勤俭持家，讲勤俭治国，所以这个是我们文化中非常重要的方面，但是很少在哪一本著作里面把它强调到这样的一个高度。“治人事天莫若啬。夫唯啬，是谓早服。”这就是早得道，坚定地按照这个道去做，就叫积德。不断地积德，那就使我们能够根深蒂固，长久存在，长久发展。人如此，国家亦如此，道理是相同的。第五十九章，希望大家认真地品味体会老先生给我们讲的“根深蒂固”的道理。</t>
+  </si>
+  <si>
+    <t>44、48、54、64、67</t>
+  </si>
+  <si>
+    <t>【治大国就像煎小鱼，别乱翻】【治大国 若烹小鲜】这一章有一句话，大家都非常熟，叫“治大国若烹小鲜”，这句话也是这一章的核心。一九八七年，美国前总统里根在发表国情咨文的时候也引过这句话。二〇一三年，“金砖各国”开会，在一个联合的采访中，有一位巴西记者问过习近平这样的一个问题：你担任这么大的一个国家的这么重要的职位是一种什么心态？你用什么样的态度来对待自己的职位？习近平答记者问，先引的是《诗经》，来回答第一个问题：“战战兢兢，如临深渊，如履薄冰。”这话出自《诗经·小雅·小旻》。治理国家要小心谨慎，就像行走在结着薄冰的冰面上一样，就像站在悬崖边一样，要小心谨慎，因为稍不谨慎就会出大的问题、大的危险。然后引用这句话来回答第二个问题，我要以“治大国若烹小鲜”的态度来对待我的职位。“治大国若烹小鲜”是什么意思呢？大家如果上网去搜对这句话的解释，类型就有二十多种，每一种解释都不一样，有的甚至把它直接翻译为“治理一个大的国家就像烹一碟小菜那么简单”，这是完全没有理解这句话的真正的含义。“小鲜”就是小鱼儿，鱼肉很细很嫩，拿它的时候就得小心谨慎，尤其是在高温里烹炒它的时候，都要小心谨慎，要有耐心。火候不到的时候你老折腾，甚至锅铲飞舞，翻腾，鱼不就成了碎片了吗？汉朝的毛亨，喜欢《诗经》的人都知道，这个人写过《毛诗传》的，他就用两句话来解读这句话，其实最符合它的本意。第一句话叫“烹鱼烦则碎”，环节太多老折腾它，那鱼就成了碎片了。第二句话“治民烦则乱”，治理一个国家也是一样，讲究的是制度的稳定，不能今天一个制度，明天一个制度，朝令夕改；你不能今天一个运动，明天一个运动来回折腾，国家不就被折腾散架了嘛。“治大国若烹小鲜”和“战战兢兢，如履薄冰”的道理是相同的，讲究的是小心谨慎，有耐心，掌握火候。“以道莅天下，其鬼不神。”“莅”就是莅临。用道来领导天下，指引天下。大家注意，这个“神”字很多的理解有问题，其实并不是神鬼的神，不是说我们后来的人格神、神化了的神。这个“神”在《易传》里面的解释是非常明确的，“阴阳之不测之谓神”，也就是神秘莫测。用道来领导天下、指引天下，鬼也没有什么神秘莫测的力量，因为你走的是正道，你走的是堂堂大道，鬼也没有办法去伤害到你，所以“以道莅天下，其鬼不神”。《道德经》里用它的道，把大家所恐惧的鬼的位置给取代了，你堂堂大道，鬼也近不了你的身，“其鬼不神；非其鬼不神”，不是鬼不神秘莫测，是因为你走大道，它的神秘、莫测、玄妙、诡秘已经没有办法伤害到你。所以把下一句话作为上一句话“其鬼不神”的注解，就很容易理解了。“非其鬼不神”，不是说这鬼不神秘莫测了，神秘莫测是它的本性。“其神不伤人”，但是它的神秘莫测已经伤害不了这种走在大道上的人、得道的人。“非其神不伤人，圣人亦不伤人”，不单是指鬼的力量伤害不了人了，反过来说，圣人他智慧高，但圣人智慧高也得返璞归真。圣人不会因为自己的智慧高，心眼多套路深，就使用这种“技巧”，这个东西不是正道。所以，鬼的神秘莫测伤不了人，圣人的智慧在领导大家的时候也会“善利万物而不争”，对人民没有伤害，“夫两不相伤”，你看鬼的神秘莫测也伤不了人，圣人领导也伤不了人。“夫两不相伤，故德交归焉。”所以有德的事情，积德的事情，两者交汇到一起，两不相伤。因为你按照道来做事情的话，鬼伤不了你，圣人也是按照道来做的，彼此也不相伤。这样大家就走在正确的道上，按照道去做，不断地积德，所以叫“德交归焉”，交汇，归到一块。“治大国若烹小鲜。以道莅天下，其鬼不神。非其鬼不神，其神不伤人；非其神不伤人，圣人亦不伤人。”如果这样两不相伤的，那就是“德交归焉”，这样就形成了一个和谐的、有道的、有德的世界。</t>
+  </si>
+  <si>
+    <t>17、29、37、57</t>
+  </si>
+  <si>
+    <t>【大国要放低姿态，像大海在下游】【大国下流 静牝胜牡】《道德经》从头至尾有一个非常重要的智慧与理念：善于处下。在第八章里面就说，“处众人之所恶，故几于道”，水去的是又低又脏的地方，把那里的污浊洗净，在那个地方滋润万物，跟道最接近的。做人要做“上善若水”的人，才能称其为“大人”，这个“大”代表的是品德。国家要成为一个大的国家，该怎么样做呢？它的处事的态度是什么呢？第六十一章里边开头这句话说得简要、明确、深刻：“大国者下流。”所以，这一章的核心我们看一下，开头“大国者下流”；结尾“大者宜为下”。越是大的国家越懂得善于处下，和小的国家打交道的时候谦逊谦和，和谐相处，你就把小的国家争取了。人也如此，位置越高，越要善于处下，这样才能真正居上。这是这一章的开头、结尾，也是这一章的核心。我们在解读“大国者下流”之前，我们需要采用以经解经的方式，拿第六十六章开头这句话，用这个形象先来让大家直观地感知一下，这个直观的形象我们了解了，再来看这一章就容易了。第六十六章开头这句话：“江海所以能为百谷王者，以其善下之，故能为百谷王。”大江大海为什么能成其大呢？它地势低，善于处下，其他的水系就都汇到它这来了，用我们习惯的话讲，就叫“善于团结一切可以团结的力量”。不辞细流，所以成为大江大海。然后我们再来看第六十一章开头这个五个字就很容易理解了。“大国者下流。”所谓“下流”，就是善于处下、处在水的下游，最好是处在大海的入海口，涓涓细流慢慢地汇成大江大海。那么善于处下《道德经》拿什么来比喻它呢？这个地方是什么？是天下的水交汇的地方，所以叫“天下之交”。拿什么来比喻“天下之交”的呢？《道德经》把它叫“天下之牝”，“牝”代表母性、女性，本来这个“牝”是指母性的生殖部分。因为在《道德经》里边母性、女性代表着慈，代表着柔，代表着静，“牝常以静胜牡”，“牡”是雄性，“牝”是雌性。这世界上的事情便是如此，这雌性善于柔，善于静，所以她的力量更长久。拿这个道理来说明什么呢？以静为下，什么叫善于处下？就是以静为下。别那么急躁、暴躁、浮躁、狂躁，善于处下，这样才能具有更大的力量、更长久的力量。这段讲完了，下边又接着“大国者下流”的道理。上面那一段是在论述它力量产生的源泉。一个大国老去动武，喜欢好战，好战者必亡，看着很强大，其实这都不是长生久视之道。所以下面就讲，“故大国以下小国，则取小国。”不是以静为下吗？善于处下吗？一个大的国家在跟小的国家打交道的时候，态度谦逊谦和，善于处下，不是居高临下、盛气凌人、不可一世的处事的方式方法，把这个小的国家就争取了。你和它平等相待，它觉得你这个大国可以倚靠，它喜欢跟你交往，遇到事情的时候喜欢支持你，帮助你，为你出力。“小国以下大国，则取大国。”为什么小国会这样做呢？因为小的国家也得找倚靠。小的国家在和大的国家打交道的时候，也善于处下，也把自己的位置放低，那么它就成了大国的朋友，有事的时候，大国才能给予支持，用我们现在习惯的话叫“罩着你”。大国也罢小国也罢，都得善于处下，这样才能形成一种和谐的关系。下面这两句话是比较难以理解的。“故或下以取，或下而取。”什么叫“以取”呢？争取有两种方式，一种是从上边抓起来，还有一种方式是更为有智慧的从下面轻轻地托起来。别小看这两个虚字、连词，“以”和“而”，这表示不同的动作。“或下以取”，要抓住你掌控你，“执者失之”，越想抓住越想掌控，失去得越快。“或下而取”，其实我们在帮助别人的时候，也就获得了别人的这样一种真心的敬佩，遇到事情的时候才能够得到人家帮助。“大国不过欲兼畜人”，大国想要更强大，就得需要更强大地支持，大国就得团结更多的小的国家，形成一个相互支持、相互帮助的局面。我给大家举一个例子，大家对这个问题就理解更深刻一点。我们中国文化的图腾——龙，大家都熟悉，我们叫“龙的传人”。可是，龙在自然界里面是没有的，它是怎么形成的呢？原来这些氏族部落，我们也可以把它看作是一个一个小的国家，那个时候他们互相征战、合并。龙的主体的部分就是蛇图腾，源自中原地区一个力量非常强大的部落，后来这个部落把很多小的部落合并到自己大的部落里边，它们收归一个部落就加上一个部落的图腾，这样，逐渐形成了龙的样子：蛇的身，马的头，鬣的尾……这不就是“兼畜人”吗？其实落到国家的层面也是一样，形成了一个团结的阵营，当然最好是正义的，遇到事情力量不就强大了吗？“大国不过欲兼畜人，小国不过欲入事人。”小国不过也想加入这个里面，大家一起做事，遇到事情的时候，大国还可以帮助、支持，这不是挺好的事儿吗？各得其所，所以叫“夫两者各得其所欲”，都得到自己所想要的。话讲完了，下边这句话又来了，“大者宜为下”，越是大的国家，越是位置高的人，越要懂得善于处下。</t>
+  </si>
+  <si>
+    <t>8、26、66、68</t>
+  </si>
+  <si>
+    <t>【道是万物的靠山，坏人也能得救】【道为万物奥 不善亦保】这一章比较难理解，先说一下这一章的断句，有很多不一样的版本。现在大家基本上能够认可的是“美言可以市尊，美行可以加人”，有的本子是“美言可以市，尊行可以加人”，断句的差别就在这两句上。这一章讲什么呢？这一章是讲“道”的重要性，“善人之宝”，善人要不停地按照道去做，是善人的宝贝。但是，不善人也不会被道所抛弃，道可以来拯救他，所以叫“不善人之所保”。现在我们从头来解释。“道者万物之奥，善人之宝，不善人之所保。”这个道是万事万物的奥妙之所在，所以它是“善人之宝”，是善良人的珍贵的宝贝，也是“不善人之所保”，是不善人得以被拯救的保障，道可以拯救这些走错路的人，让他回到正道上来。“美言可以市尊”，美言，好的话。说好的话、正确的话，它可以得到人们的尊重。“美行可以加人”，好的品行，可以增加人的尊贵，团结更多的人。其实这个道理也比较容易理解，我们熟悉的三个人——魏徵、李世民和长孙皇后。魏徵是美言，他劝李世民，你要做一个好皇帝，有些事你不能做。李世民很愤怒，回来之后在家里边发火，说要把魏徵给杀掉。长孙皇后反而衣服穿得很整齐，给他道喜，说你遇到了一个好的臣子，我应该向你贺喜。李世民后来领悟到这一点，他说镜子可以正衣冠，魏徵就像一面镜子可以正我的品行。历史上，三个人留下的都是美言，都得到了人们的尊重，所以叫“美言可以市尊”。既然道是“善人之宝，不善人之所保”，那么“人之不善，何弃之有”。有的人走错路了，你为什么就觉得要把他抛弃掉？让他回到正道上来，用道去教化、去拯救。这是从正面来说它的作用。下面就讲的这个事就有针对性了。“故立天子，置三公。”国家的制度慢慢地有了天子，作为最高的领导者，还有三公——辅佐天子的最重要的职位。“虽有拱璧以先驷马”，古代敬献礼的时候，拱璧，捧着玉璧，捧璧的人在前边，乘着高头大马进献。珍贵吧？不如“道”珍贵！这里面有两个意思：一个就讲国家的制度，有天子，有三公，很重要，但这也只是形式。还有呢，用高头大马进献珍贵的玉璧，这也是很珍贵。但是“不如坐进此道”，这些都不如按照道来做，大道才是“万物之奥”，“万物之宝”。“古之所以贵此道者何？不曰以求得，有罪以免邪？故为天下贵。”意犹未尽，讲到这地方，《道德经》还觉得这个话就应该再强调一下，说古往今来，为什么都要把这个道看得这样珍贵呢？“古之所以贵此道者何？”不就是说你按照道去做，你才能得到自己真正想要得到的吗？“以求得”，你要的那个东西才能真正得到。这里的“以求得”并不是像我们烧香拜佛求得发财。“有罪以免邪”，因为前面讲过，“不善人之所保”，就算走错路了，但是我们重归正道，浪子回头金不换，原来的这个罪，也能得以补偿。这个并不像有的宗教里边说你犯了什么罪去忏悔一下，这个罪就免除了，它是让你按照大道来做，回到正道。我们来分分类，人不就是这两类：“善人”、“不善人”，对那些不善良的人，走错路的人，你为什么要抛弃他呢？“坐进此道”，回归此道就可以啊。弄了那么多的官职，天子、三公，有那么多珍贵的财宝，拱璧、驷马，还不如“坐进此道”。既然如此，“道”就是天下人最珍贵、最宝贵的，“故为天下贵”。</t>
+  </si>
+  <si>
+    <t>27、49、51、79</t>
+  </si>
+  <si>
+    <t>【难事从容易处开始，大事从小处做起】【图难于易 为大于细】第六十三章的内容，我们在前边已经有所接触。之前我们说，第二章就是《道德经》的“目录”，第二章列出来了后边讲的六个重要内容，有无相生、难易相成等等，这一章的核心就是“难”和“易”。这一章的核心意思就说，要想做大事，先从小事做起，想要以后攻坚克难，你得从容易的事情做起。还有一个重要的问题、重要的智慧：你要把容易的事情当作难的事情来做，要有充分的、认真的准备，提前思考它的步骤、程序、会遇到的问题，这样再出什么问题的时候，你就能从容应对。有这样的态度，天下也没什么难事。天下无难事，但天下都是难事，看你怎么对待。开头这九个字非常有趣：“为无为，事无事，味无味。”“为无为”——想要有为吗？你得先懂得无为的道理。为什么？因为有些事你越有为，越强求，什么事都管，反而最后结果非常不好。道家讲的无为，就是按照道的方式来作为，想要有为，先要懂得无为的道理，不要妄为，要抓住关键，举重若轻，有所舍才能有所得，所以为无为。其实也就是第三十七章里边讲的“道常无为而无不为”，道的规律、规则是什么？用无为的方式达到无不为的效果，更好的效果。我再强调一下，《道德经》里出现得最多的一个词是“天下”。《道德经》针对的是天下，千万不要把道家当作一种消极的被动的思想，它是“想为”，但是强调要通过正确的道路和手段，懂得无为的正确的道路和手段，才能达到真正的有效的为，也就是用无为的方式，达到无不为的这种效果。下边再落一层，“事无事”。大家都想做事，可是大家有没有注意到，有些人他是“找事”，他是捣乱，是阻碍、多事，天下本无事，庸人自扰之。所以我们做事的时候要懂得无事的道理，不要多事，不要找事，不要刁难。尤其是做领导者，没事找事，权力就是刁难，你这不就麻烦了吗？“事无事”，想做事，得懂得无事的道理，不要多事，不要扰民。再落一层，“味无味”。我们经常讲一个词叫“真水无香”，真正好的饮料，就像那白开水一样，没有味道。我们饮食讲究清淡，寡味，少油少盐。最高的味道，反而是没有味道，无味。当然，这三个词核心还是“为无为”，让大家能够更明白一点。老子展开来讲，“事无事”，不要多事，不要扰民，不要刁难，就像“味无味”的道理一样。按照这样的一个逻辑推下来，下面四个字大家就能明白了，“大小、多少”，千万不要把它念成“大小多少”，这个东西就没意义了。这是告诉大家要“大其小”、要“多其少”，要把小事看得很重要，细节决定成败，千万不要忽略这个细节。为什么要“大其小”呢？因为天下的大事，都是从小事做起，为什么要“多其少”呢？因为积少才能成多。想要多，你得从少的一点一点积累，积少成多。就像我们学习《道德经》，一章一章讲，一章一章学，不要着急，最后达到一个整体的理解。我们经常讲“聚沙成塔”、“集腋成裘”，这不都是“多其少”的道理吗？“报怨以德”，按照这种相反相成的道理，对别人的埋怨、恩怨，也应该站在一个“德”的角度，因为德是符合道，用道的东西里面去感化。第六十二章不是讲了吗？“人之不善，何弃之有？”人家有这个埋怨，怎么正确地对待呢？“报怨以德”。用这种智慧和层次，让大家一起能回归到正途，回归到正道。“图难于其易，为大于其细。天下难事必作于易，天下大事必作于细。”这几句话，在我们文化里边名气非常大，因为讲的是哲学上的量的积累达到质的变化的道理。“图难于其易”，“图”就是图谋、计划。你计划想要做难的事情，要从容易的事情做起。“为大于其细”，想要做大的事情，得从小的事情一步一步来。我们大家都知道要脚踏实地，循序渐进，有条不紊，一屋不扫，何以扫天下？“天下难事必作于易”，天下所有的难事，都要从容易的事情做起。就像小孩的培养，让他们在处理小的事情中就形成良好的习惯，把小的事情、容易的事当成培养良好习惯的重要途径，将来，小孩在遇到大事、难事都能从容应对。现在很多人都有一个致命的弱点，大概是人的通病，就是好高骛远，老觉得自己应该是做大事的人，对小的事情不屑一顾。《道德经》就告诉我们这个智慧：想要做难的事情，从容易的事情做起；想要做大的事情，从小的事情做起，“天下大事必作于细”。“是以圣人终不为大，故能成其大。”“是以”，“是”就是这样，“以”就是所以。所以有智慧的领导者就是这样：“终不为大”，不是老说大话，不是老给大家画饼充饥，而是脚踏实地，一步一步地做起，“故能成其大”。一步一步把这个事情完成了，一步一步地完成计划，最后实现一个大的蓝图，好的结果，水到渠成。所以一个有智慧的人，不是老用那些虚幻的东西来画饼充饥，老是给大家讲大话、空话。“终不为大，故能成其大”，最后反而成就了大事，这话讲得非常好。我建议大家学习《道德经》，有一种重要的学习方法，就是反复看。有的人看《道德经》，也许一年就看一章，反复地看，反复地体会，“少则得，多则惑”，“终不为大，故能成其大”。以管窥天，以锥扎地，我们视力更集中，这样把这个事情才能做得更踏实，扎得更透。我们每一次的进步，虽然看起来好像只是一点点，但是这一点点积累起来就不得了了，“终不为大，故能成其大”。“轻诺必寡信”，大家还记得我们在讲《道德经》第八章的时候，就讲过“言善信”，我们中国人喜欢拿潮水作为讲信用的代表和象征，所以，有一个词就叫“潮信”。你看那钱塘潮每到农历八月十八前后就来了，人也应该如此，说话要讲信用，要有诚信，能给别人做成的事我们再去允诺，没把握做成的事，不要轻易去答应，不管我们有多热情。如果我们答应人家的很多事最后都做不成，时间长了，人家一定认为我们是食言而肥，不讲信用。《道德经》讲话是比较宽缓的，但这句话用的就是强逻辑判断，“轻诺必寡信”，这不是对我们委婉的劝告，这简直就是对我们严厉的警告。所以要讲诚信，君子重一诺，一诺千金嘛，所以“轻诺必寡信”，要避免这种结果出现。“多易必多难”，你把这个事情看得很容易，做什么事情，最后一定出问题。世界上哪有容易的事情，吃个饭喝个水，这都需要功夫，需要本事，小事情我们都要认真对待。我们经常讲“小河沟里翻船”，把一个事情看得太容易了，太简单了，往往会在这个事情上出问题。面对很多难的事情，大家战战兢兢，小心谨慎，反而没事，反而就是在一些认为最容易的事情出问题。很多学生做题、考试也是一样，难题没事，在容易的题上，出了问题，回去捶胸顿足，懊悔无比。所以，我们平常要形成一种把容易的事情当作难的事情来做的习惯，你要懂得“多易必多难”，凡事太容易，后面一定会出现很多的困难，出现很多的问题。所以，下边这句话就讲：“是以圣人犹难之”，所以有智慧的人，把这容易的事情都看作很难。天下的事情都当作难的事情来做，反而结果没有什么难的事情，“故终无难矣”。这个道理非常有趣，其实就是相反相成的道理，这个叫“难易相成”。世界上有没有难事呢？有，也没有。你把这个难的事情当作难的事情，看作是无法克服的，它就是难的事情；你把容易的事情当作容易的事情，没有认真对待，最后也会变成难的事情。我们把容易的事情当作难的事情来做，最后那个难的事也就做成了；真正难的事情，我们认真准备，有充分的信心，最后这难的事情也就克服了。“故终无难矣！”世上无难事，这就是“难易相成”的智慧。很多事情，决定于我们的想法、态度，态度不同，难易之间就会相互转化。</t>
+  </si>
+  <si>
+    <t>2、8、36、41、64</t>
+  </si>
+  <si>
+    <t>【再远的路从脚下一步步走，快成了更要谨慎】【千里之行 始于足下】第六十三章、第六十四章讲的道理，就是大家熟悉的量变和质变的道理，量的积累达到质的变化。但是大家注意，这个量的积累，有向好的方面，也有向不好的方面。前面讲了“为大于其细”，要做大事，从小的事情做起，这样才能最后达到想要的结果，假如积累的是一个不好的量，最后就积重难返。第六十四章一开始就要把两个方面，都给大家做了说明，有的事情在它刚出现向坏的方面发展苗头的时候，我们在这个阶段就把它解决了。这一章里有两个非常重要的内容，一个是大家都熟悉的一段话：“合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。”第二个就告诉我们，做事情要“慎终如始，则无败事”。这两个重要内容，我们先有一个直观的认识，再来读就好理解了。我们一句一句来解释。“其安易持”，“安”就是稳定，局面稳定的时候，容易掌控，就像一个东西，它稳定的时候，你容易把它把握住；它活蹦乱跳的时候，你把握起来就困难了。“其未兆易谋”，“未兆”，没有征兆的时候，苗头还没有开始的时候，容易去谋划。“其脆易泮”，脆的时候一打就打散了。“其微易散”，很微小的时候，很容易把它解散。比如说一件事情，很小的时候，人数很少的时候，你把它处理起来很容易。众怒难犯，一大群人轰起来、闹起来的时候，这事情解决起来就困难。前面告诉大家这些现象，然后告诉大家处理的方法。什么方法呢？“为之于未有”——在事情没有出现的时候，没有开始的时候，要有预见性，就要有作为，凡事预则立，不预则废。“治之于未乱”，还没有出现这种乱象的时候，就把它治理了、解决了。这也是习近平讲话时经常引用的两句话。怎么来理解呢？先给大家说第一个例证。有一次晏子出巡，齐国发大水，把一座石桥给冲毁了，晏子就把自己的船让给了灾民，大家都赞誉晏子爱民如子。然而一位有智慧的高人就批评晏子，就说你做这个国家的宰相，齐国发大水能把一座桥梁冲毁，你都没有预见到，没有提前做出预防，你失职。所以应该是怎么样？“为之于未有”，你别等这个事情都已经成为这个样子，再去处理它，不管你处理的方式多么巧妙，多么有智慧，但是不如让这件事情没有发生。另外一个例证更能说明这个道理。有一次，扁鹊的国王问扁鹊：扁鹊你名气太大了，你是不是国家医术最高的？扁鹊说不是，别人我不知道，起码我大哥、我二哥都比我的医术高。所以这个国王就很奇怪，你大哥、你二哥是谁？他们医术那么高，怎么大家都不知道他们呀？扁鹊就说，我大哥怎么治病的呢？人家还没有病，他告诉人家怎么预防、怎么不得病。这不是“为之于未有”吗？提前就有作为了，预防得病。我二哥怎么治病的呢？人家刚有一点小病，他就把人治好了，不让他酿成大病，“治之于未乱”。所以我们经常讲，凡事预则立，不预则废，要有远见，要有预见，要未雨绸缪。这是讲负面，因为有些事情量的积累是向不好的方面发展的，所以要提前把这个问题给处理掉。下面讲的这个事，非常重要。我们做大事情都要从容易的事情、小的事情，一步一步积累才能达到这种质的变化，要脚踏实地，循序渐进。因为什么呢？“合抱之木，生于毫末”，合抱之木，它是一点一点长起来的。“九层之台，起于累土”，中国文化中，三六九都代表着高、多。那么高的高台也是一层一层土积累起来的。“千里之行，始于足下”，走这么远的路，要脚踏实地一步一步地做起。说到这里，我得加一句，有人老认为道家思想是消极的、被动的、无为的。“合抱之木，生于毫末；九层之台，起于累土；千里之行，始于足下。”这不就是自强不息吗？所以有些事我们不能人云亦云，我们得看原文，以原典作为证据。“为者败之，执者失之。”“为”就是强为、妄为。因为《道德经》讲的真正的为叫“无为”，就是按照道的方式来作为，不按照道的方式来作为就是强为、妄为。越是强为，最后的结果越糟糕，因为量的积累还不到，你老想强行地发生质变，这不是急躁冒进吗？“执者失之”，就像我们抓沙子一样，你握得越紧，流出来越多，越想用力地把它抓住，反而失去得越来越快。所以一个有智慧的领导者，“无为”，按照道的方式来作为，不妄为，不强为，不多为，有所不为，所以也不会有急躁冒进的失败。“无执故无失”，没有这样的强执，最后也不会失去。“民之从事”，平常人做事，或者说领着大家做事，在什么时候最容易把事情给做砸了呢？“常于几成而败之”，经常在快要接近成功的时候，把事情给做砸了。那应该怎么办？“慎终如始，则无败事。”什么叫慎终如始呢？我先给大家打一个比方，大家走在结着冰的冰面上的时候，刚一下到冰面上都是小心谨慎，战战兢兢。走一会儿，觉得自己走熟了，就放松警惕了，有的干脆最后开始跑了，有的甚至在冰面上炫耀，危险往往就在这个时候发生了。所以我们中国人经常讲一句话叫“行百里者半九十”，一百里的路，走到九十里路的时候，还要当才走了一半，越是剩下那一段的时候越紧要，民间讲“编筐编篓，全在收口”，即最后这个结尾。“慎终如始”，走到最后那几步，还像开始下到冰面上一样小心谨慎，一步都不放松，那就没什么败事，没什么事情做不成。“慎终如始，则无败事”，就是我们现在经常讲的不忘初心，善始善终，那就没有什么事情做不成的。“是以圣人欲不欲”，一个有智慧的人，特别是一个有智慧的领导者，想要的东西是什么呢？是别人都不关心的，都不想要的。因为“天下熙熙，皆为利来；天下攘攘，皆为利往”，大家关心的是获取利益的方式方法，而一个有智慧的人，有智慧的领导者，应该有这种无功利之心。“欲不欲”，别人都不想这样的，反而是你应该考虑的。大家都针对“有”的东西，这有智慧的人、好的领导者得针对这无形的东西：人的精神财富，人的精神世界，人的修养。既然“欲不欲”，你跟一般人的欲望不一样，他们认为那个东西是珍贵的、难得的，反而在你的眼里是不重要的，不把它看作是难得的。领导国家的时候也是如此，第三章讲的，“不贵难得之货，使民不为盗”，形成一种淳朴的风气。“学不学，复众人之所过。”《道德经》讲的道理，叫“绝学”，一般人不愿意学，学这个东西能带来什么样的好处、利益吗？人的境界高的时候，学的很多的东西不就是和一般人不一样的嘛。一般人不愿意学的东西，又花功夫，又不能带来什么实际的利益，可是“学”这些东西代表了真正的智慧与学问。学这些东西干吗呢？“复众人之所过”，这个“复”不是重复，我们下围棋的人都知道有个词叫“复盘”，通过不断的重复模拟来检视，哪个地方下得好，哪个地方下得不好。别人犯的过错像复盘一样历历在目，以此为鉴，别再犯大家都经常犯的错误。“以辅万物之自然，而不敢为。”“以辅万物之自然”，就是按照自然的规律去做，追求的是一种水到渠成、自然而然的结果。“辅自然”就是无为。“而不敢为”，就是不敢妄为。因为我们违背了道，违背了自然规律，哪怕是短时间取得成功，其实也会受到更大的一种惩罚。这章告诉我们，一是我们做事情要“为之于未有，治之于未乱”，懂得预防，懂得不好的事情在苗头出现的时候就把它解决掉；二是我们做事情要脚踏实地，循序渐进；三是我们要“慎终如始”，不忘初心，善始善终，因为我们做事情经常在快要成功的时候，结果功亏一篑，所以要懂得这样一个道理。</t>
+  </si>
+  <si>
+    <t>29、48、59、63</t>
+  </si>
+  <si>
+    <t>【别用小聪明治国，百姓淳朴才是福】【不以智治国 玄德大顺】这一章所涉及的，也是我们现在哲学里面经常讲的一个道理，叫“否定之否定”规律，讲事物的发展分为三个阶段，第一个阶段是肯定，第二个阶段是否定，第三个阶段是否定之否定。比如说麦粒长出麦苗，最后结出更多的麦粒，这就是一个否定之否定的阶段。第三个阶段常常重复第一个阶段的某些特征，却是在更高的程度上重复第一阶段的某些特征。这一章和第四十章讲的“反者，道之动”，所运用的哲学的智慧和道理是一样的，既然这样，把这个道理运用到治国上，应该如何呢？这就用到了一个我们大家熟悉的词，叫“返璞归真”，《道德经》认为治民最关键的是要使民风纯朴，不要那么多的技巧，不要那么多的套路。了解了这一点，我们再来看这一章，就明白了老先生的良苦用心。“古之善为道者”，以前的那些善于按照道来治理国家的人。“非以明民，将以愚之”，不是让百姓有那么多的心眼技巧。这个“愚”，不是愚民，而是敦厚、厚道，让人民的民风纯朴。“民之难治，以其智多。”百姓为什么难以治理？因为他心眼多、技巧多。“智”就是技巧、心眼、套路。“故以智治国，国之贼”，用技巧来治国，经常用骗术谎言，这是国家的灾难。“不以智治国，国之福”，不用这些技巧，让民风纯朴、敦厚，这个才是国家的福祉、国家的福分。“知此两者，亦稽式。”“稽式”就是法则。知道这两个的差别，这就是一个法则，治国的一个法则。“常知稽式”，“常”就是规律。按照规律，我们来了解这个法则。这叫什么？“是谓玄德”，“玄”就是深远的意思，这个就是深远的智慧与品德。下面这句话就是我一开头讲的，这个品德“深矣，远矣，与物反矣”，“与物反矣”不就是“反者，道之动”吗？我们都能看到事物的正向的发展，所以《道德经》经常提醒我们，“反者，道之动”，道是向它相反的方向运动，所以你理解问题也不能只看一面。“与物反矣”怎么解释呢？第二十五章，“大曰逝，逝曰远，远曰反”，最后又回到了它的根本。根本是什么？“归根曰静”。民心没那么多的躁动，变得清静宁静、敦厚朴实，这不就符合大道了嘛。“然后乃至大顺”，这样慢慢地就回归到了正确的道路，符合自然之道。所以，这一章讲的就一个问题：你用什么方式治国呢？要让民心变得纯朴、敦厚，返璞归真，没那么多的技巧，没那么多的套路，没那么多骗人的把戏，这样才是符合大道。</t>
+  </si>
+  <si>
+    <t>3、10、15、18、19、36、38、40、48、51、57</t>
+  </si>
+  <si>
+    <t>【江海能成老大，因为它待在最低处】【江海善下 不争而王】这一章所讲的这个道理是《道德经》从头至尾所强调的“善于处下”，只有善于处下，才能真正居上。我们在一开始说过，《道德经》的很多话是针对那些领导者、统治者讲的，所以老先生认为越是位置高的领导者、统治者，越要善于处下，为什么呢？首先从处下的结果上来看，“江海所以能为百谷王者，以其善下之，故能为百谷王。”这句话我在前面也多次引用过。大江大海之所以能成为大江大海，是因为善于处下，不辞细流，能团结一切可以团结的力量，故能为“百谷王”。老子先拿“百川归海”的形象讲了这个道理，让大家有一个感知。下面就开始讲具体的做法和内容。“是以欲上民，必以言下之。”所以你要想站在上面领导好下面这些人，在语言上要懂得谦逊、谦让。领导者，尤其国君、皇帝这一类的，讲话的时候不能够居高临下，盛气凌人，自尊自大，不可一世。第三十九章说过“贵以贱为本，高以下为基。是以侯王自称孤寡不穀”，所以在语言上要谦逊。“欲先民，必以身后之。”想要站在前面当好领导、当好领头的，要懂得把自己的利益放在后面，想要领导别人就得给别人利益。一个人既要领导别人，又想什么好处、利益、功名都抢在自己手上，这个人下场不是不言而喻的吗？范仲淹的《岳阳楼记》里说“先天下之忧而忧，后天下之乐而乐”，做官、做领导不得如此吗？钱钟书先生认为范仲淹这两句话就是出自《道德经》的。但是人家学得比较好，不也成了大家都熟悉的名句了吗？“是以圣人处上而民不重”，所以一个好的领导者，你在上面领导大家，大家没有感觉到沉重的压力。“处前而民不害”，你在前面领导大家，大家没有感觉到你对他的危害。因为你要想领导别人，得让别人得到利益。西汉史学家司马迁在《史记·循吏列传》说：“公仪休者，鲁博士也。以高弟为鲁相。奉法循理，无所变更，百官自正。使食禄者不得与下民争利，受大者不得取小。”这里的食禄者不与民争利，意思是做官的人不许和百姓争夺利益。“是以天下乐推而不厌”，所以天下的人民都往高举你，往前推你，不感觉到厌倦、厌烦。如果统治者穷奢极欲，危害百姓，草菅人命，下面的人就会感觉到“害”、感觉到“重”，这样的人百姓会“乐推”吗？当然不会。“以其不争，故天下莫能与之争。”一个领导者，能得到了大家的拥护、拥戴，正因为你不争，不与民争利，不与其他人争名，“利而不害，为而不争”，结果是“以其不争，故天下莫能与之争”。越是争的人，最后往往失败得越惨，因为你的位置已经规定了你应有的担当、使命和责任。陈毅元帅讲过“手莫伸，伸手必被捉”，形象而深刻，那么，反过来用这个道理讲，就得以更加明确了。“以其不争，故天下莫能与之争”，所谓“不争”，并不是消极被动，“不争”，当然要了解边界，不争边界之外的东西，这样的话才能“天下乐推而不厌”。</t>
+  </si>
+  <si>
+    <t>2、7、8、11、22、61、68、78、81</t>
+  </si>
+  <si>
+    <t>【我有三件宝：慈爱、节俭、不抢第一】【三宝：慈 俭 不敢为先】老子、孔子、释迦牟尼、柏拉图，这都是同时代人，在他们那个时代，书其实只有一种题材，就是对话体。《论语》是孔子弟子记的，记得非常清楚，坐在对面的是什么人，提了什么问题，老师怎么回答，所以大家读起来一目了然。佛经呢？很多的佛经也都是释迦牟尼对弟子问题的回答，大家看《金刚经》，是回答须菩提的，《心经》是回答舍利子的，都是针对他们的问题的回答。古希腊哲学家苏格拉底的学生叫柏拉图，写了一本《对话录》，就是记载当时苏格拉底跟学生之间的互动，对各种问题的解答。其实《道德经》的最早的形成也是这种形式，也是对面坐的人问的问题，老先生给予回答，也是对话体，所以我们读这本书，始终要感觉到这是在回答对方的问题，是有针对性的解释和回答，这样很多问题我们才能够得以正确地理解。那么这一章是在回答什么问题呢？对面坐的人，问老子关于道和德的事，老先生给他讲半天，他没听懂，于是提出要求：能不能把你的思想概括得简单点？你让我也能听得明白。大家自然会有疑问，我怎么知道是这样的？是不是我自己在杜撰？让我们回到原文，大家看一下这一章的开头就清楚了。“天下皆谓我道大，似不肖。”老子这个意思就是说，不仅是你，天下人都认为我把道讲得太大、太宽泛了，听不懂。你听不懂，我得给你打比方，类比虽然不能够说明问题，但是它可以让人理解问题。我说道就像风一样，大象无形，你们说不像；我说道就像水一样，大道汜兮，其可左右，你们还说不像……“夫唯大，故似不肖。”正因为把道讲得这么大，拿什么给他打比方，他都说不肖，所以老子就感慨，假如真的像的话，“久矣其细也夫”。意思是假如真的像，那早就归到小道了。比如，说道像一条大河，你拿这个比方，要像的话，就像支流了。道就像一条大道，你要说比方像的话，就像小道。其实意思就说，拿道打比方，要是真的像的话，就是把道说得太小、太细了。那怎么办？不跟你讲那么多了，把我的思想概括到简单得不能再简单。只剩下三个方面，“我有三宝，持而保之。”把我的思想概括到最后，简单得不能再简单了，就剩下三个方面拿出去，按照去做就行。那这“三宝”是什么呢？“一曰慈，二曰俭，三曰不敢为天下先。”大家解读这三组词的时候，不可以单独先解释几个字词，一定要把“三宝”里边的字词和后面的语句连接来解读：“一曰慈，慈故能勇；二曰俭，俭故能广；三曰不敢为天下先，故能成器长。”否则，会失之宽泛。“一曰慈，慈故能勇。”“慈”是指什么？指的是慈母的情怀。做领导、做家长，有了慈母的情怀，才能有真正的担当、勇敢。如果你单独解释这个“慈”就麻烦了，慈母有时候也唠里唠叨，有时也无原则地爱，不是经常说“慈母多败儿”吗？可是《道德经》为什么把“慈”放到第一位呢？这是针对坐在对面的提问者的。作为领导、作为诸侯王，你在这个位置，就要有慈母的情怀，才能有真正的担当、勇敢。如果没有慈母的情怀，一出事就会出卖国家和人民，一出事就把自己的部下当做替罪羊推到前边。“二曰俭，俭故能广。”我还是觉得这位老先生对咱们中国人了解得非常深刻，我们中国人致命的弱点是什么？好面子，好虚荣，好攀比。所以一旦是公开的场合，一旦是监督不力，往往就奢靡之风盛行，浪费之风盛行。没有节俭节制，而是有奢靡之风浪费之风，那就没办法“广”，“广”就是长久持续。家庭没有培养出节俭、节制之风，家庭就没有办法长久持续地发展，所以要勤俭持家。国家人民没有培养出节俭节制之风，而是奢靡浪费，这个国家也没有办法长久持续地发展。“三曰不敢为天下先，故能成器长。”先理解“成器长”，咱们中国很多的词是组合性的，所以大家理解的时候，也要把它组合的东西拆开，“成器长”拆成四个字“成器成长”。我们怎么样才能不断地成长，终成大器呢？“不敢为天下先”，现在咱们天天讲叫“敢为天下先”，这又来一个“不敢为天下先”，这两句话不就怼上了吗？其实这两句话根本不矛盾，讲的不是一回事儿。我们现在强调的“敢为天下先”，是敢闯敢创新，这是一种很好的品质，创新是一个民族的灵魂。《道德经》讲的“不敢为天下先”是什么意思呢？做领导，领着大家做事，要懂得把自己的利益放在后面，要懂得先人后己，不要私欲膨胀，不要什么事情只关注自己，这样才能够不断地进步，不断地成长，终成大器。各位是否还记得我在前面给大家说过，其实读这本书的时候，不用别人给你画出重点，你自己都能感觉到，因为老子在书里不断地强调自己的重点，一种强调的方法是重复，第二种强调的方法是头尾，第三种强调的方式就叫正反，也就是他正面讲完了，觉得是还言犹未尽，要从相反方面给大家再论证一下，你看这一章不就是这样吗？现在的人是什么样的，本来应该按照道的方式来做，要慈、俭、不敢为天下先，我们把这“不敢为天下先”也可以概括成两个字叫“谦让”，或者概括一个字叫“让”。我有三宝，慈、俭、让。可是老子对当时的人不满意，这些人都怎么做的？“舍慈且勇”，根本没有这种情怀，还到处炫耀自己的勇敢。我们现在不也经常看到这种情况？酒驾了，还拍个视频给警察发过去，我醉驾，警察你来抓我呀，炫耀自己无赖似的勇敢。“舍俭且广”，没有这种节俭、节制，还奢求长久持续地发展，不可能。“舍后且先”，遇到好处、利益，争先恐后，一点都不肯让，甚至不该自己的也抢，这样做的结果是什么呢？“死矣！”这样做的最终结果，就把自己弄到死路上去了。“夫慈，以战则胜，以守则固。天将救之，以慈卫之。”这些讲完了，又把他讲的第一个“慈”再说一遍。有这种慈母情怀的人，那么面临事情的时候就会“以战则胜”。他勇于担当，真正遇到困难的时候，领着这个大家当然攻无不克，战无不胜。“以守则固”，国家遇到侵犯的时候，领导者的这种情怀，力量无尽，守无不固。“天将救之，以慈卫之”，如果天真的有情感的话，他要拯救国家的人民，拯救团队团体，一定是“以慈卫之”，你一定有这种慈母的情怀才值得，因为它本身就拥有无穷无尽的力量。第六十七章，核心的就是“我有三宝，持而保之”，要坚定、坚持地按照去做。</t>
+  </si>
+  <si>
+    <t>30、31、54、59、68、69、73</t>
+  </si>
+  <si>
+    <t>【会打仗的不发怒，会用人的放低姿态】【不争之德 用人之力】这一章讲什么呢？我们中国人有一个习惯，喜欢拿战争的术语来打比方，比如说我们现在吃个饭，也可以说“打个冲锋”，来个“歼灭战”，平常我们也经常讲“占领制高点”。这一章既是在讲战争，又通过战争延伸开来，讲普遍性的制度。“善为士者不武”，“武”的意思就是耀武扬威。善于做基层领导者的人，或者说指挥打仗的士官，不耀武扬威。不要有了这样的一个位置，就耀武扬威，趾高气扬，盛气凌人，不可一世。“善为士者不武”，保持一种谦逊的、平和的、冷静的心态。“善战者不怒”，善于指挥作战的人，不是动不动就暴跳如雷。“不怒”，懂得制怒。任何一个人不管他位置多高，在急躁、浮躁、暴躁、狂躁的心理状态下都谈不上智慧。我们看一下“怒”的写法，上面是个“奴隶”的“奴”，下面是个“心”，当我们控制不了自己的情绪，心成了情绪的奴隶，没有办法保持清醒、冷静、理智的心理状态，才会发怒。所以真正善于作战的人，善于做事的人，要保持这种清醒、冷静、理智的心理状态。“善胜敌者不与”，“不与”，就是不和他发生正面的冲突。从字面的意义上来讲，善于制胜的人，懂得用委婉迂回的方式获得胜利。我们把这个“战争术语”延伸一下，其实在家里也一样，两个人情绪都到达高点、发生剧烈的冲突，这时候解决起来就比较困难。所以，越是到这个时候，越要懂得以退为进，懂得用委婉迂回的方式来解决问题、处理问题，这样才能很好地战胜对方，说服对方。“善用人者为之下”，我在前面多次说过，这是《道德经》从头至尾强调的一个最普遍的原则，善于处下者方能真正居上。一个领导者也是如此，朋友之间相处也是如此，保持自己这种谦逊处下的态度，这样才能够跟人和谐相处，才能“用人之力”。这个叫什么？“是谓不争之德”。“善为士者不武，善战者不怒，善胜敌者不与”，尤其是“善用人者为之下”，都是《道德经》里边从头至尾强调的“不争之德”。说到“不争之德”，我们的思路又回到第八章，“上善若水，水善利万物而不争”，后边讲了“不争”的七种品德：去大家不愿意去的地方——“居善地”；我们要保持内心的宁静，静水流深——“心善渊”；和别人相处，要懂得关爱，一视同仁——“与善仁”；讲话要讲诚信——“言善信”；公平、公正、清廉，所谓政清如水——“政善治”；做事情的时候要尽其所能，像水一样有多种多样的这种本领——“事善能”；善于把握时机，掌握机会——“动善时”。所以，这里的“不武”、“不怒”、“不与”、“为之下”，也是对这个“不争之德”的进一步说明。这个就叫“用人之力”，我们熟悉的一个词叫“借力打力”，熟悉的一句话叫“孤举者不起，众行者易趋”。一个人举重物举不起来，大家同心协力，形成这种趋势，这样才能把事情做成。既然如此，就要懂得用人之力，而不是孤军奋斗，这样做才能够很好地和别人和谐团结。再往高了说“是谓配天古之极”，“古”就是古往今来，所谓“配天”就是符合天道，这些是古往今来的大智慧。第六十八章没有什么难的地方。大家要明白一点，我们中国人习惯用战争的术语来讲生活中的事情，所以我们的理解不能停留在字面上。</t>
+  </si>
+  <si>
+    <t>8、30、31、61、66、67、69</t>
+  </si>
+  <si>
+    <t>【不主动挑事，被逼应战的一方赢】【不敢为主 哀兵必胜】第六十八章是用战争的术语来做比方，讲的道理当然比仅局限于战争更为广泛。第六十九章我们也当作如是观，他讲的是战争的事情，但是这个道理我们也可以做延伸、做扩展，成为我们生活中的、工作中的普遍的思想与智慧。我们知道《道德经》里边很多的内容并不是老子本人的话语，他也是一个“集大成者”。他经常在回答坐在对面的圣、王、士这些领导者的问题的时候，引用当时或者以前那些智者的语言。第一句话，“用兵者言”，懂得用兵的人怎么做谋划？怎么来认识问题呢？“吾不敢为主而为客”，我才不去老是发动战争去侵略别人，“国虽大，好战必亡。”“我不敢进寸而退尺”，打不过的时候，对手力量太强大的时候，就要懂得以退为进，这个叫什么呢？这个就叫“行无行，攘无臂，扔无敌，执无兵”，这十二个字怎么理解？我先换一个角度给大家来认知这个问题。抗日战争胜利之后，有很多日本人就对这场战争表示不是很服气，因为他们有的认为，是因为东条英机改变了战略，才导致这场战争在中国的战场上的失利；有的人认为，日本战败是因为美军的加入，所以他们也想专门研究战败的原因。有一位日本学者专程来到了中国，他也是通过一本经典来了解我们中国人在这方面的思想与智慧，这本经典就是毛泽东的《论持久战》。各位知道，一九三七年七月七日卢沟桥事变，抗日战争全面爆发，同年的八月二十二日到二十五日，就在陕北洛川召开了洛川会议。在这次会议上，毛泽东就已经开始讲持久战的思想，一九三八年的时候这本书就面世，这不是战后的马后炮，是战前的预测。他把整个战争的进程就概括为六个字，而历史就是沿着这六个字发展：退却，相持，反攻。一开始当然日本侵略者锋芒外露，我们没有办法直接跟他们对抗，因为日本是一个统一的国家，而当时我们的中国四分五裂，军阀混战，政令不统一。日本军队装备精良，又蓄谋已久，所以一开始没有可能把他们赶出去，他们肯定会占领我们很多地方。所以这个时候我们就要懂得退却，以退为进。但是日本的军队又不多，占领我们的地方多了，双方就进入了一种相持的阶段。因为武汉和鄂西会战之后，双方就进入相持阶段，咬牙坚持。我们中国是站在正义的一方，况且我们是一个统一的世界反法西斯战场的一部分，为整个世界反法西斯战场拖住了那么多的日本军队，自然要得到国际舆论的支持、国际力量的援助，最后获得胜利。那么日本为什么会陷在中国的战场上？因为原本按照日本人的想法，中国战场很快就能拿下来，以此为基地，北面是针对苏联，南面是针对南洋的那些国家，很多是英国的殖民地，所以它的主要的目标并不是在中国。可是没想到中国的战场，几乎拖住了它绝大部分的力量，为什么会这样？我们来看一下下面这几句话，“行无行，攘无臂，扔无敌，执无兵”。侵略者进入了另外一个国家，虽然这个国家的人民没有站成军队的样子，“行无行”，但是他们不都是你的敌人吗？“攘无臂”，打击你非得用拳头吗？有各种各样的方式，坚壁清野可不可以？游击战可不可以？全民皆兵，所以叫“扔无敌”。“执无兵”，虽然他们手中没有兵器，但他们用多种多样的方式和侵略者对抗，到处都是敌人。所以为什么说“国虽大，好战必亡”？因为你侵略者是不得人心的，进入到别的国家的军队会遭到别的国家人民的反抗，到处都是你的敌人，“扔无敌，执无兵”。所以对于战争而言，你不要认为一个小的国家就好侵略，“祸莫大于轻敌”，对双方皆是如此。战略上藐视敌人，战术上要重视敌人。“祸莫大于轻敌，轻敌几丧吾宝”，轻敌，就把最宝贵的东西也就是“道”丢掉。所以在战争中要冷静理智，要对对方予以重视，在战略上藐视敌人，但是在战术上要重视敌人，不要轻敌。下面这句话基于上面的这个意思就好理解，“故抗兵相加，哀者胜矣。”就是站在正义一方的抵抗的军队、防御的军队，对抗侵略者，处在相持的阶段，双方相持不下、在那较劲的时候，旁边只要有人帮一下，都会起大的作用。可是大家知道问题的决定性作用并不在旁人，没有形成相持的状态谁帮也没用。所以我们说这句话让我们领悟到一个重要的问题，中国人获得这场抗日战争的胜利，根本的原因在于我们中国人自身，而不在于外面力量的援助。斯大林曾经说过，拉开窗帘天是亮，你不拉开窗帘，天也是亮，反正中国人会获胜，应该帮一下。所以这决定的作用不在外部，而在于我们中国自身。讲得最妙的是最后一句话，最后谁获胜呢？“哀者胜矣”，“哀”可不是哀伤的意思。鲁迅先生写的《阿Q正传》中有一句话叫“哀其不幸，怒其不争”，“哀”就是同情。我们中国人从古汉语里面延续了一个习惯，讲话的时候这种使动用法，通俗地说就是被动型用法。比如我们说老头晒太阳，其实是老头被太阳晒。比如大家到陕西来吃的肉夹馍，那是肉夹馍吗？那是肉被馍夹住了。所以这种使动的用法，用这个来理解，这句话就很清楚了，“哀者胜矣”，谁是被同情、被支持的一方，最后获得胜利。“退却，相持，反攻”——惊人的一致。毛泽东从十几岁就开始读《道德经》，我觉得他从这本书里得到的最大的启发就是这种格局上的、战略上的。人站得高了才能看得远，对未来才能有一个正确的这种预测。所以我说第六十九章，大家不要只局限在战争的一个方面，它也可以把我们的智慧得以扩展和延伸，成为一个普遍性的思想与智慧，成为一个普遍性的原则。</t>
+  </si>
+  <si>
+    <t>8、17、30、31、67、68、73</t>
+  </si>
+  <si>
+    <t>【我的话很简单可没人懂，高人穿得破怀里有宝】【被褐怀玉 知我者希】从第七十章开始，老子强调的重点又发生了改变，他在强调什么呢？他说，我们看问题要“以道观物”，可是有道的人往往为人所误解。老子在书里经常用“吾”这个字，“吾”是人格化的我。“吾”作为一个有道者的代表，一个人格化的有道者的身份，并不一定是指老子本人。第七十章开始就讲人认知的重要性。“吾言甚易知，甚易行。”得道者讲的话，其实很容易被了解，很容易去实行。“天下莫能知，莫能行。”可是结果是什么？这天下的人都是没办法了解，或者说不去了解，也不去按照这个去做。这是一种沉重而深刻的感慨。我们常说道很玄妙，很难把握，而老子在这一章讲，按照道去行事并不难知，不难行，那为什么“莫能知，莫能行”呢？是因为大家根本不愿意去相信它，也不愿意按照它去做，是因为大家认识不到这个事情的重要的意义，认识不到“道”在我们生活中的重要的作用。老子这段话主要是针对领导者、统治者来讲的，老子在对他们讲了很多次之后，发现“万言不值一杯水，犹如东风射马耳”，那些话语仿佛随风而去，并没改变什么。所以，他有此感慨：“莫能知，莫能行”。“言有宗，事有君。”“宗”就是宗旨，说话你得有宗旨，得有核心。“君”是领导控制，做事情也得掌握这个事情的关键。言外之意就是讲，你看我讲的这些话，它是有核心宗旨的。他告诉大家做事怎么样掌握事物的关键，了解事物的本质，把事情做好。“夫唯无知，是以不我知。”可是正因为这些人无知、不了解、不想知道，所以他对我们得道的这些人也就不了解。“知我者希，则我者贵。”了解我的人太少了，懂我的人太少了。我们现在经常有这种感慨，有没有人懂我？其实我们真的了解一个人的精神世界，尤其是了解这些富有大智慧的人的精神世界，不是一件容易的事情。我们中国人经常说一个词叫“知道”，现在大家再说一下这个词，它的分量就不一样，并不是你听到了就叫“知道”，“知”还得去“行”。所以了解我的人太少了，按照我这个去做的人那就更为珍贵了。“是以圣人被褐怀玉”，“褐”，褐色，粗布衣服的颜色。所以得道的人，就像穿着粗布衣服可是身上却怀着珍宝的人一样。得道者讲了很多道理，可是很多人，因为“以貌取人”就是不信。所以，我们经常要透过现象来认识事物的本质，不要以貌取人，不要认为《道德经》里的语言不是那么华丽，就否定其思想与智慧。《道德经》的很多章节都在讲人贵有自知之明。第三十三章“知人者智”，我们真正能够去了解别人，这是一种非常有智慧的表现，可是比这个了解别人更重要的，是我们要了解自己，“自知者明”。人认识最少，却自认为认识最多的知识就是关于自己的知识。因为我们自我的认知，经常被一些假象所迷惑，被情绪所左右，所以“知人者智，自知者明”。其实，老子不仅是感叹“吾言甚易知，甚易行。天下莫能知，莫能行”，他对当时的领导者这种认知的不足及其原因，是有深刻认识的。一千多年后，王阳明提出“知是行之始，行是知之成”，也是这个话题的延伸。</t>
+  </si>
+  <si>
+    <t>20、41、56、71</t>
+  </si>
+  <si>
+    <t>【知道自己不懂才高明，不懂装懂是毛病】【知不知为上 病病不病】第七十章讲“夫唯无知，是以不我知”，由于我们的认识上出了偏差，出了问题，所以没有办法了解有高超智慧的人、得道的，很多的时候，我们也没有办法真正地去了解自己，那么问题出在什么地方呢？这一章在分析问题的原因。我经常开玩笑说，这一章是我见过的中国历史上最有智慧的一段绕口令，比那些相声演员用来练贯口的绕口令更富有思想与智慧。“知不知，上”，我们知道自己不知道，我们知道自己的认识有局限，我们知道自己有缺点需要弥补，这是最有智慧的。后来庄子在《秋水》篇里面把这个意思给大家演绎得非常清楚，而且富有哲理。秋天发大水的时候，河伯就以为自己这个地方就是天下最大的，“以天下之美为尽在己”。后来流到了大海，见到了北海若，发现自己太渺小了。北海若又说，其实我在天下所占的位置，也就是像一粒米那样……这就叫“知不知”，知道自己不知道，那才能够不断地进步。“不知知，病”，不知道，却把它当作知道，也就是不懂装懂，这就是一个思想上的大病。怎么样来让我们病得以痊愈？“夫唯病病，是以不病”，我们知道自己有很多的东西不知道，我们知道这是我们的缺点，我们向别人学习，取长补短，谦逊努力。知道自己“有病”，却不讳疾忌医，这反而是没有病。大家熟悉的是《论语》里边的一句话：“由，诲汝知之乎？知之为知之，不知为不知，是知也。”知道就是知道，不知道就是不知道，坦率承认，不要不懂装懂，这个达到的结果“是知也”。这不是一样的意思吗？“夫唯病病，是以不病。”所以对一个有智慧的人，特别是对于领导者、统治者来讲，周边的人都在说好话，阿谀奉承，这样就经常让自己飘飘然，如果这个时候还能保持清醒的头脑，那就是一个有智慧的好的领导者和统治者。他在这个认知上的表现是什么呢？“圣人不病”，一个有智慧的人在这个方面没有病，没有缺点。为什么说它没有缺点？“以其病病”，因为他知道自己的问题在什么地方，知道哪个地方是自己所不擅长的。就像刘邦一样，虽然不能说刘邦为一位圣人，但是他讲的这段话却可以给很多领导者、统治者以启发：“夫运筹策帷帐之中，决胜于千里之外，吾不如子房。镇国家，抚百姓，给馈饷，不绝粮道，吾不如萧何。连百万之军，战必胜，攻必取，吾不如韩信。此三者，皆人杰也，吾能用之，此吾所以取天下也。”刘邦知道自己的短处，借人之力得以弥补，因为有这种清醒的认识，反而成了一个长项。有人总认为自己什么都可以，哪个地方都是自己水平最高，比如说诸葛亮从来也不听别人的意见，打仗的时候都自己谋划，要不就弄个锦囊远程指挥，像这样的人，很难成为一个优秀的领导者。我们经常讲一个人浑身是铁，能打多少钉，要懂得用人之力，懂得借别人的智慧。现在不是有很多的智库、智囊吗？历史上很多杰出的人，比如像曾国藩，手下有多少谋士啊！很多的问题不是他一个人想出来的，得集众人之力，一个优秀的领导者得知道自己弱项、短板在哪儿。对我们个人来讲，一定要知道，其实我们的认知视野都是非常狭窄的，了解了这一点，我们也就不会把自己当作是一个完人，当作什么都知道，不懂装懂。人有什么不懂的，坦率承认没有什么可丢脸的，即便是圣贤，也有自己认知的局限，可是他们的做法和平常人的不同在哪儿呢？“圣人不病，以其病病，是以不病。”知道自己这方面有弱点、有问题，因此不断学习，不断进步，不断成长。这一章虽然很短，但是意蕴深长，道理深刻。这段绕口令大家既可以当作练表达能力、练嘴皮子的体操，也可以当作思想上的体操，一举而双得，何乐而不为？</t>
+  </si>
+  <si>
+    <t>4、10、33、47、70</t>
+  </si>
+  <si>
+    <t>【百姓不怕你了大祸就来，别逼人活不下去】【民不畏威 自爱不贵】七十二章到七十五章，这一部分都出现了一个核心的概念——“民”。在中国历史上有“民本”的思想，我们大家熟悉孟子讲的“民为贵，社稷次之，君为轻”，大家觉得讲得好。但是，在孟子之前，《道德经》已经从哲学的层面把民本思想发展到非常高的程度，而且讲得更为具体。这一章最后一句话讲得非常明白，这两条路摆在这儿了，你应该走哪条路？“故去彼取此。”有哪些路可以选择呢？走哪条路是符合道的呢？我们从头来看。“民不畏威，则大威至。”如果一个国家的人民不害怕统治者、领导者的威严，那么对统治者、领导者来讲，大的麻烦就来了。什么大的麻烦呢？“民无信不立”，领导者在民众中丧失了诚信，就没法统治领导他们了，这不是一种大威吗？所以“无狎其所居”，“狎”通“狭”，也是使动用法。领导者，不要让百姓住的地方越来越狭小，最后都流离失所。因为“无恒产者无恒心”，一个国家如果到处都是流民，它能稳定才怪。“无厌其所生”，“厌”通“压”。不要让他们感觉到生存受到了压迫，不要去压迫他们，不要让他们感觉到厌倦生活，因为哪里有压迫，哪里就有反抗。所以这个“厌”，大家可以把它理解为两个意思，一个就是压迫，一个就是导致的结果感觉到生不如死，厌倦自己的生活。“夫唯不厌，是以不厌。”你不去压迫他们，不让他们感觉到生活的局迫、窘迫、生不如死，他们才不会对你的统治行为、领导行为感觉到厌烦。第六十六章说“处上而民不重，处前而民不害”，处上又重，处前而害，他当然会感觉到这种受压迫的厌烦的感觉。那么，真正有智慧的领导者、统治者应该是什么样呢？“自知，不自见”，自己有自知之明，不是有一点功劳，有一点什么就去自我表现。“自爱，不自贵”，很珍爱自己的生命，珍爱自己名声，自爱自重，但是不自以为高贵。第三十九章最重要的两句话，第一句话就是“贵以贱为本”，不要认为自己身份高贵，没有这个国家的人民，也就是很多人眼中的贱民，哪来你高贵的身份？自爱是对的，因为一个人不爱惜自己的生命，也就不会珍惜别人的生命。第十三章讲过，什么样的人才能把天下寄托给他呢？“贵以身为天下”、“爱以身为天下”。所以好的领导者对自己的生命非常珍视，但是为了天下的使命，可以奉献自己的生命，这样的人我们才能把天下寄托给他。“故去彼取此”，取的是什么呢？取的是自知自爱；去的是什么？去的是自见、自贵。</t>
+  </si>
+  <si>
+    <t>3、13、74、75</t>
+  </si>
+  <si>
+    <t>【敢拼命的死，敢示弱的活，老天看着呢】【勇于不敢 天网恢恢】这一章首先谈的话题是“勇敢”。关于“勇敢”，《道德经》并不像我们一般认识那么简单，表达那么直白，它把“勇敢”分为“勇敢”和“勇于不敢”，这个说法的妙处我们后边再做解说。接着读这一章，大家会发现熟悉的语句“天网恢恢，疏而不漏”，其原文就出自第七十三章“天网恢恢，疏而不失”。我们中国人读失去的“失”啊，总觉得有点绕口，换了一个字，意思都是一模一样的。天网恢恢，疏而不漏，天道如此。庄子也讲过这样一段话，一个人做了亏心事之后，在客观世界上把有形的痕迹抹掉容易，可是抹不掉内心的痕迹。即便是不受客观世界的惩罚，也得受良知的惩罚。那么第七十三章的结尾，怎么得出“天网恢恢，失而不漏”的结论呢？是怎么过渡到“天网”、“天道”的呢？“勇于敢则杀”，毛泽东在《贺新郎·读史》这首词里面就讲：“铜铁炉中翻火焰，为问何时猜得？不过几千寒热。人世难逢开口笑，上疆场彼此弯弓月。流遍了，郊原血。”人类的历史都是在这种血与火的洗礼中前进的，老子在他那个时代，肯定也看到过这种情况。“勇于敢则杀”，也包括很多违背了国家法律法令的不法之徒，从直观地来看，也是属于勇敢，“勇于敢则杀”。“勇于不敢则活”，“勇于不敢”直观上看上去，我们把它叫做“懦弱”、“退缩”，但其实这样的“懦弱和退缩”还有另外的一类人，他们懂得保护自己的生命，以期谋得更大的成就与发展。其实，我们说懂得拒绝的人也是一种“勇于不敢”，有些该做的事情，勇敢去做；有些不该做的事情，勇于不敢，拒绝。老子接着说，“此两者，或利或害。”“此两者”指勇敢和勇于不敢。勇敢和勇于不敢这两种情况“或利或害”，就是说有时有利，有时有害，那到底何时有利，何时有害呢？谁能把握这个度呢？“天之所恶，孰知其故？”天呢，到底是喜欢还是厌恶？到底是怎么一回事？谁能够了解这里边的最根本的原因、缘故呢？“是以圣人犹难之”，就是再有智慧的人、有智慧的领导者，在这个方面也难以去理解清楚。所以你看这个认知啊，非常困难，到底是该杀还是该活，到底该怎么对待，这是一个非常难的选择。那老子是不是就放弃了对这个难题的解决呢？不是的，事实上，老子是认为，只有站在更高的视野才能解决这个困扰，也就是第四章说的“解其纷”。所以老子在下边就说，如果从天道的角度来认知这个事情是什么样呢？“天之道，不争而善胜”，不争斗，却能够获得胜利，这是符合天道的。“不言而善应”，要行不言之教，不是老去命令、政令，大家对他反而非常支持，非常响应。言教不如身教，“不召而自来”，大家自然而然就聚拢到你的麾下，这是符合天道的。“繟然而善谋”，“繟”就是坦然、从容。天道看不出来痕迹，从从容容地向那个方向发展，就像一个善于谋划的人一样，不露痕迹地谋划。所以后面就讲“天网恢恢，疏而不失”，天网虽然好像有很多疏漏，但是最后你会发现，这天道如此，天网恢恢，疏而不漏。我们中国人经常把这个讲做“人在做天在看”、“为人别做亏心事，古往今来放过谁。”到这里，逻辑就逐渐清晰了：天道不争，不强制，自然而然，所以为民，不能滥用所谓勇敢；为王，也不能滥用强制，这都是不符合天道的，不符合天道，则是必然要失败的，也就是讲“天网恢恢，疏而不失”。所有违逆天道的所谓“勇敢”最后都会受到惩罚，天网虽然好像有很多疏漏，但是最后你会发现，这天道如此，天网恢恢，疏而不漏。关于这一点，我们再引证下孔子这句话：“人之生也直，罔之生也幸而免”，就更清楚了。意思就是那些不正直的勇于敢者、对抗天道天理的人，也许会侥幸漏掉一时，但终究逃不脱天道天理的惩罚。孔子的真正意义在于，若靠侥幸活着，你是活不好的。而老子对于敢对抗天道天理的人、与天争胜的人，警告更为严厉：“天网恢恢，疏而不漏。”换句话说就是“人在做天在看”、“为人别做亏心事，古往今来放过谁。</t>
+  </si>
+  <si>
+    <t>67、69、76、79</t>
+  </si>
+  <si>
+    <t>【老百姓不怕死，你拿死刑吓唬谁？】【民不畏死 勿代司杀】七十四章开头这句话，在讲什么呢？“民不畏死，奈何以死惧之？”假如这国家的人民都不怕死了，都感觉到生无可恋了，你还能有什么方法去管理他们呢？上一章不是说过吗，“狎其所居，厌其所生”，百姓感觉到压力太大，感觉到生不如死，那就会产生“民不畏死”的情况。这个时候，你拿死去吓唬他还有什么用呢？毛泽东在《别了，司徒雷登》中引用过这一句，并引申说，“中国人死都不怕，还怕困难吗？”接着老先生做了一个假设，“若使民常畏死”，假如这个国家的人民经常地、普遍性地害怕死，老百姓对生活抱有憧憬和希望，这个时候，如果有搞幺蛾子的人，铤而走险犯法的人，“而为奇者吾得执而杀之”，做领导的、做统治者的，把这些人逮过来杀掉了。“孰敢”，没有人会响应这些人，大家不都不吭声了，国家也就恢复了平和、安定。大家注意，这话里暗含着一种假设，事实是什么呢？老百姓生活没有希望，不畏惧死亡。这时候，你杀的人越多，反抗的人越多；镇压得越多，起来呼应的人更多。所以，老子说你管理靠镇压是不行的，这不是根本的方法。历史上还有比秦朝法令更严苛、更严酷的时代吗？满大街都是被砍断手脚的人，严刑重罚，稍有违犯，立马严惩。最终，大家不还是起来造反了吗？秦朝之前，老先生就已经提醒过，靠残酷的镇压是不管用的，这不是处理问题的根本方法。下面上升到了更高层面，“常有司杀者杀”，大家知道，我们讲“秋后问斩”。秋天是代表肃杀的，杀人的时候是在秋天，这个代表符合天道、天杀。《道德经》的这句话是说，人的生死是由天来司管的。再退一步讲，国家也是按照国家的法令、按照符合道的方式制定的法律，来约束人的。当然这句话就《道德经》的本身而言，是在讲天操管着人的生杀予夺大权，人没有这个权力去决定别人生死的，即便是有的话，也应该有专门的部门来管。“夫代司杀者杀”，代天来杀人，这叫什么？“代大匠斫”，我们知道木匠的锛凿斧锯别人是不能动的，太锋利了，只能他们自己使用。你不熟悉这一行，你不懂怎么使用，你代替他们，“希有不伤其手矣”，哪会有不伤到自己的？老先生拿这个来做类比：你应该不用这些东西，不善于用这些东西，你越俎代庖，那么你自己肯定也会受伤的。因此，只用杀戮、镇压的方式，是不符合天道的，对自己的统治、领导也有着重大的损伤。这段话其实对统治者提出的警告：靠镇压的政策、残杀的政策，也会影响威胁到自己的统治，不要相信武力能解决一切问题。三十五章讲“执大象，天下往。往而不害，安平太。”应该用符合“道”的方式来管理国家，以民为本，注重根基，这样才能够和谐相处，才能够“安”、“平”、“太”。</t>
+  </si>
+  <si>
+    <t>13、50、72、75</t>
+  </si>
+  <si>
+    <t>【百姓饿肚子，是因为上面收税太多】【上多税民饥 厚生轻死】这一章的核心话题还是“民”，解释了三个问题。第一，百姓为什么饥寒交迫；第二，百姓为什么难以治理；第三百姓为什么不怕死。解释完三个内容，然后对领导者、统治者提出要求。“民之饥，以其上食税之多”，百姓为什么饥寒交迫？“上”，上面的领导者、统治者，“食税”，收的税太多了，而且收的税都被这些人挥霍。“民之难治，以其上之有为”，百姓为什么难以治理呢？原因不在他们这儿，是因为上边胡来、瞎折腾。在《道德经》里，“有为”这个词就是妄为，胡折腾，上边老瞎折腾，就把民心折腾乱了。“信不足焉，有不信焉”，折腾得多了，讲的话也不诚信了，也失去百姓的信任，说什么都没用了。“是以难治”，“是”，“这是”的意思。这话讲得就比较理性，你老说他们是刁民，老在他们身上找，其实这原因就在自己的“有为”。老子对坐在对面的那些领导者、统治者就讲，你得找到真正的原因，百姓为什么饥寒交迫？你们收税收得太多了，收的税都被挥霍了。百姓为什么难以治理？你们整天瞎折腾，胡来妄为，把民心搞乱了。“民之轻死，以其求生之厚”。“其”指谁？领导者、统治者。百姓为什么轻死，把死不当一回事？是因为你们这些统治者，把自己的生命看得那么重要，不惜用剥夺的方式积累财富，花天酒地，穷奢极欲，这财富都聚积在他们自己手里，老百姓难以生存。就像国民党时期，财富都积累在“四大家族”手中，很少的人占有了绝大部分的财富，底下的人都生活在水深火热之中。当你“求生之厚”的时候，底下的百姓就觉得没什么活路和希望了，也就不把死当一回事，“是以轻死”。那么应该怎么做呢？“夫唯无以生为者”，不要把自己的生命看作是绝对重要的。不要把财富、好吃的好用的，全都集中在自己这儿来，认为只有自己的生命才是生命，对别人的生命、生存视而不见，感到无足轻重。不把聚敛、穷奢极欲当作生命的重要的部分，这个就是“贤于贵生”。百姓为什么饥寒交迫？上食税之多；为什么难以治理？上面胡来妄为；为什么不怕死？求生之厚。这章三个并列句，像诗一样的语言，讲得又非常深刻、非常理性。把七十五章和七十四章结合起来理解，我们就能发现，老先生苦口婆心地劝坐在对面的那些领导者、统治者：你们要对自己国家的人民好一点，否则啊，他们日子过不好，你们的日子也不安稳，你们只靠这种高压的政策，这不是解决问题的根本的方法。我们完全可以说在这几章里看到了《道德经》的“真实面目”，很多话是针对那些统治者讲的，苦口婆心地劝他们，应该怎么样对待这个国家的人民，才能使国家长久地、持续地发展。</t>
+  </si>
+  <si>
+    <t>10、13、50、53、57、72、74</t>
+  </si>
+  <si>
+    <t>【活着的都软，死了才硬，逞强是死路】【柔弱生徒 坚强死徒】现在我们来说一下第七十六章，王弼本子的编辑是有着内在逻辑的。前两章，老先生劝统治者，不要用这种“强”的方式、镇压的方式来实施自己的统治，那么应该怎么做呢？要懂得以柔克刚、强大处下，这样才能形成一种和谐。有的人确实是没有认真地读这本书的原文，他们认为《道德经》是一个弱者斗争的哲学，这是不了解坐在老子对面的向他提问的那些人，他们并不是一般的平民，而是手握权力的领导者、统治者。要站在这个层面来理解第七十六章，知道他这些话是对是对那些认为自己自身或者自己国家很强大的统治者们讲的。老子劝他们用“柔弱”的方式来实施自己的统治，这个是非常有智慧的，这个非常能够体现老先生的慈悲仁爱之心。这一章强调两个字“柔弱”，所以一开始讲“人之生也柔弱”，最后强调“强大处下，柔弱处上”。“人之生也柔弱，其死也坚强。”人活着的时候是什么状态？柔韧性非常好。我们看跳舞的、练杂技的，就觉得这柔韧性好。柔弱柔软，这是生命昂扬、鲜活的状态。而人死的时候是什么样的一种情况呢？硬了、僵了，“其死也坚强”。老子首先拿人的生命的状态来说明柔弱具有的意义。如果这个问题大家觉得还没有理解到位，再换一个角度来理解。在苏州金鸡湖苏州新区里曾经出现过一尊老子的雕像，这尊雕像太丑陋了，老子张着嘴，吐着舌头，一颗门牙。很多人很不理解，心里想有大智慧的老子，怎么会是这样的形象，还有人打趣说，这个老子是来卖萌的……这个雕塑者姓田，他就站出来解释说，我这个雕塑叫“刚柔”，它的出处是说，当时孔子见老子的时候，老子没有给他多说什么，张开嘴巴让孔子看了看。孔子一看就明白了，老子当时已经都七十多岁了，牙早掉光了，但是舌头还在，讲的就是“柔弱更长久”的意思。雕塑者说“刚柔”倒没错，但是这段话不是出自正史，记载的也不是指孔子和老子之间的事，其实是当年老子毕业的时候，跟自己的老师讲的。您有什么送给我？老师也没说话，张开嘴巴给他看了看，老子就看明白了，老师年纪大了，牙掉光了，但舌头还在。牙齿是坚硬之物，到一定年龄就掉了，舌头没事，柔软更长久。所以，柔弱更有生命力、更长久，柔弱是生命的状态，而强硬、僵硬是死亡的状态。这是第一个，拿人来做比方。第二个以草木为例，“其生也柔脆，其死也枯槁。”我们以草为例，李世民在诗里说“疾风知劲草”。草，风往这边吹了，它这边倒，往那边吹了，往那边倒，风走了，它再站起来坚守脚下这片土地。什么时候草坚定了，不随风倒了，那草就死了、枯了。正因为草很柔弱，所以它能迎风起舞；正因为草很柔弱，所以“天涯何处无芳草”。下面得出结论，“坚强者死之徒”，“徒”就是那一类。认为自己坚强、强硬、强暴，其实这是属于走向死亡一类的。而“柔弱者生之徒”，柔软、柔韧，这是富有生命力的表现。沿着这个方向再往下推，就说到了人类社会，“兵强则不胜”，一个国家穷兵黩武，认为自己的军事力量强大，稍一不如意就动用军队发起战争，“国虽大，好战必亡。”“兵强则不胜”，不是说你这场战役打不胜，但穷兵黩武的最后结果一定是失败的。历史上多少强大的帝国，比如说秦朝，被称为“虎狼之师”，最后的结果怎么样？“兵强则不胜”“木强则折”，这个“强”就是僵硬。春天，万物复苏，一根细小的柳枝也很有韧性，很难去折断它。秋天，柳枝水分干枯，好像很强硬地挺在那里，可是它内在枯槁了，一折就断。小的时候，我在石厂里边劳动，砸石子做铺路之用。那时候我就见了一个非常奇怪的现象，石场里石匠用的榔头把儿，一种是很粗大的木棒，看着很稳定；一种是很细的木棒，看起来很危险。我去问那个石匠，怎么用这么细的斧柄？他说这个东西叫“水曲柳”，你别看它细，但它韧性非常好，你用多大劲儿也没事儿。所以每当读到这个地方，我就想起这个事情。“木强则折”，看似强大僵硬，其实没有了韧性，它就没有了生命力，一碰就断掉了。讲完这个了，再看这里边两层的推论。第一层推论：“坚强者死之徒，柔弱者生之徒”，然后推到人类社会，表达他对用这种强横的方式予以统治、用这种强横的方式予以领导的不认同，指出这个方式的致命的弱点。战争中也是如此，“兵强则不胜”，就像“木强则折”一样。讲完这个，推论到第二层：“强大处下”，老是炫耀自己强大，去任意地凌辱别的小的国家；自己有了高的位置，可以盛气颐指，不符合道，这是向死亡方向去发展。“强大处下，柔弱处上。”懂得以柔克刚，懂得以退为进，懂得谦逊谦让，这才是符合道的，才是真正有智慧的表现。第六十一章，“天下之牝，牝常以静胜牡”，讲以静制动、以柔克刚的道理。所以对人生来讲，强大、用强，这事儿大家都知道，也并不是说老子对这个东西一味排斥，因为人生有的时候强也是需要的，但是大家都把这个事情推到极端了，认为“强”是解决问题唯一的方式，所以，老先生在面对那些领导者、统治者的时候，苦口婆心，形象具体地讲述柔弱处下的道理。我们现在读这一章，也可以把智慧扩大到我们的为人处事，不要只认为用强才能解决问题，要懂得强弱两者的相辅相成，老去逞强，不是真正智慧的做法，这是只是智慧的一个方面，而“以柔克刚”才是一种真正高级的智慧。适当的时候，我们要懂得示弱，这是我们在和社会、和别人打交道的时候，非常重要的智慧，有重要的启迪。</t>
+  </si>
+  <si>
+    <t>8、36、43、50、55、73、78</t>
+  </si>
+  <si>
+    <t>【老天劫富济贫，人却嫌贫爱富】【天道损补 人道反是】第七十七章，这一章重要在什么地方呢？大家都知道“马太效应”，马太效应出自《圣经·马太福音》，直观的解释是穷者越穷，富者越富，越穷越倒霉，越富反而财富滚滚而来，这也是我们人类社会大家都认同的一个普遍的现象。怎么解决这个问题呢？怎么样解决这样的一种贫富的两极分化呢？《道德经》很早就给出了一个方案，所以我们把这一章叫什么呢？叫“张弓效应”。在这一章里边我们可以看到一句话，这句话和马太效应讲的意思是一样的，叫“损不足以奉有余”。“天之道，其犹张弓与？”老子在这一章里面就讲，说天道就像拉弓射箭一样，拉弓射箭要有的放矢。这个箭，你瞄得高了，往下压一下；低了，往起抬一下，“高者抑之，下者举之”。沿着这样的一个比喻，自然就得出这个结论，对于人类社会也是这样，“有余者损之，不足者补之”。财富多的人应该拿出更多帮助这些不足的人，收入高的人当然应该多交税。这就是“天道”，天道如此，天道均衡，“天之道，损有余而补不足”。可是人道，这个社会是怎么做的呢？“人之道则不然”，老子对他当时的情况看得很清楚，财富都掌握在少数人的手里，“损不足以奉有余”，越是不足的、穷的，反而被压榨得越厉害，富的反而越来越富。于是，老子面对那些统治者讲，一个好的领导者、统治者应该向“圣人”的方面去发展，做一个好王。大家注意古代那个“圣”的写法，王上边并列两个字，耳和口，听得进别人的意见，说话温暖。通达事理的王，称之为圣。老子就对他们讲，你们应该向这个方面努力，怎么做呢？“有余以奉天下”，让那些更富的人来为这个天下做贡献。“唯有道者”，就是了解道的人，按照道的方式去行事的人，才能做到这一点。说到这儿，我就得给大家说一下我们的文化背景。一句话大家都熟，叫“不患寡而患不均”，贫富不均，很容易产生问题。历史上那些农民起义，他们用的口号，你也能感觉到这一点，比如说王小波、李顺，“均贫富等贵贱”；比如说黄巢，“冲天平均大将军”……从社会心理能分析到这一点。所以老先生就讲，统治者、领导者，什么样的人才能够真正注意到、做到让贫穷的得以扶持，让富有的贡献更多呢？“唯有道者”，“是以圣人”。“是以圣人为而不恃，功成而不处，其不欲见贤。”一个好的领导者，“为而不恃”，他把这件事情做了，有作为了，却不把这个当作一种倚仗、凭借甚至勒索的手段。“功成而不处”，不居功自傲，“不欲见贤”，不想表现出自己的这种贤能贤明。这是有道者的表现，懂得让天下向共同富裕的方面发展，让那些先富起来的人懂得奉养天下，哪怕是把这些做成了，也不居功自傲，因为他们知道，这只是按照道的方式来做的。</t>
+  </si>
+  <si>
+    <t>2、5、9、34、79</t>
+  </si>
+  <si>
+    <t>【水最软但谁也打不过，能受委屈才能当王】【柔弱胜刚 受垢为王】第七十八章体现了这本书里的一个非常重要的理念，“善于处下”。这些内容我们之前都有过接触，甚至直接引用七十八章做过讲解，所以这一章我们并不需要花费太多的时间来解释，大家也能够明了。“天下莫柔弱于水，而攻坚强者莫之能胜”，天下没有什么东西比水更柔弱了，你拿什么容器装，它就是什么样，随方就圆。但天下也没有什么东西比水的力量更强大了，攻无不克，战无不胜。水就是以柔克刚、以弱胜强的最好的形象的代表。“以其无以易之”，因为没有什么东西能够替代水，天下最柔弱的东西，它力量又最为强大，最能够体现柔弱胜刚强的道理。“弱之胜强，柔之胜刚，天下莫不知，莫能行。”天下都知道，这东西表面上看似柔弱，但发挥作用的时候力量太强大了，但是真的要这样却非常不容易，为什么？人都有脾气，“柔弱胜刚强”得懂得忍耐、等待，忍耐是我们人最难练的一种功夫。水滴锲而不舍方能穿石，一条溪流不舍昼夜，慢慢积累，等待时机，才能发挥大用。“柔弱胜刚强”也是需要条件的，只是老子没有明说。“是以圣人云”，我再给大家强调一下，在老子心里，以前有很多好的统治者、有智慧的领导者，他称其为“圣人”，让大家向他们学习。我们在前面谈到过，他的很多话并不是原创的，是他引用的以前的圣人的，下边这话就表达得非常明确，所以这些圣人讲，“受国之垢”“受国不祥”。这两句话就是《道德经》里边从头至尾强调的，就是我们经常讲的善于处下。古往今来，夺得天下的表面看是一家一姓，实际上不都是一个团队吗？用我们现在的话讲是一个党派。什么样的团队，什么样的党派才能夺得天下，并且坐得了江山呢？之前，我们在第八章讲“处众人之所恶”时，也拿这个地方作为印证。吃苦在前，享受在后，有困难还得担着，有错误勇于改正，这不就是“受国之垢”“受国不祥”吗？所以真正想要夺得天下，坐稳江山，也就是所谓“处其上”，首先要懂得“处其下”，要“受国之垢”，要能忍受别人忍受不了的艰难困苦，要能承受别人承受不了的屈辱诟骂，这样才能成为江山社稷的主人。“受国不祥，是为天下王。”有灾难有困难，你别跑，要挺身而出，勇于担当，有错误要勇于承认，勇于改正。毛泽东把共产党的宗旨概括为五个字，叫“为人民服务”。两千多年前的“受国之垢”，“受国不祥”，“处众人之所恶”，两千多年后的“为人民服务”，这本质上的意思不是一样的吗？这就是《道德经》里面从头强调的，也是古往今来的大道。我们在讲第十四章的时候说过一句话，“执古之道以御今之有”。了解古往今来的大道，我们才能更好地做好今天的事情。读到这儿大家就会发现，这《道德经》里边蕴含着古往今来的大道，蕴含着一个人、一个团队、一个党派成功的最深的密码，值得大家认真地品味。总结上面这个表达的方式叫什么呢？叫“正言若反”，也就是第四十章讲的“反者，道之动”。看着是讲反话，大家都不愿意去做的事情：“受国之垢”，“受国之不祥”，“处众人之所恶”，可实际上，这才是能够让我们“处上”、取得成功的真正的智慧与奥妙。看似好像说的反话，其实深刻的道理就在这里边。</t>
+  </si>
+  <si>
+    <t>8、9、22、36、43、66、76</t>
+  </si>
+  <si>
+    <t>【大仇和解了也有遗留，不如宽容，天道帮好人】【和怨有余 天道亲善】针对坐在对面的那些统治者、领导者，老子前面一直在讲，不要用高压的方式，要懂得用柔和的方式。如果一直用高压的方式，一直用“损不足以奉有余”的方式，这社会就积累了大的矛盾。老先生认为，有了这个矛盾之后，不管用什么方式解决，它都会遗留下很多的不满、埋怨、祸端。在这个基础上，我们才能够深入理解第七十九章的内容。这一章只有这么几句话，但道理非常丰富而深刻。“和大怨，必有余怨，安可以为善？”如果社会已经积累了大量的矛盾，即使用调和的方式，“和大怨”，可是，依旧会留下很多的这个埋怨、祸端。“安可以为善”？即使用和谐的方式，也不是一种善举，为什么呢？第六十四章讲“为之于未有，治之于未乱”，从一开始你就不应该让这社会积累了这么多的矛盾。我们之前举过晏子“救灾”的例子，其实针对我们目前的环境问题，也是一样。大家知道有一句话叫“反对先污染后治理”，你污染完了，你再治理，其难度之大，难以预料。“病来如山倒，病去如抽丝”，社会不也一样吗？积累了这么多复杂的矛盾，你老用调和的方式，你说现在已经柔和了、缓和了，但留下那么多的祸端，这当然不算是好的方法，不可以叫做善举。对应我们人际交往也是一样，我们不要本着“无所谓”的态度，想着跟别人、朋友之间有了裂痕，我们说以后自会解决的，事情往往没有我们想得那么简单。所以，平时做事就要小心，朋友之间要珍惜，家庭之间感情要珍惜，别真的等得了埋怨之后，再想办法去解决。这跟钉子钉在墙上一样，你拔出了钉子，那个眼还在。最好的“善”是什么？提前做出预防，“为之于未有，治之于未乱。”“是以圣人执左契，而不责于人。”有智慧的领导者、统治者，就像拿着契约的人。“左契”，契约，一撕两半，左边一个，右边一个，左边那个是借据。拿着这个契约借据而不责于人，不是天天去追着要，而是表达出圣人的一种宽容。老先生拿这个举例子，意思说，一个好的领导者，哪怕是你对大家都有恩德，对天下都有恩德，你别以为大家都欠你的，“不责于人”。所以“有德司契，无德司彻”，有德的人就像执左契而不责于人的人。“彻”，就是税官，收税的。这是代表着两种态度，一种是和缓的态度，另一种是苛刻的残酷的态度。所以平日里，应该像“有德司契”的样子，那就不会积累那么多的埋怨。反之如果像那个税官一样，苛捐杂税多，还步步紧逼，不肯放松，老子认为这是无德的表现，这样会留下大怨！下面两句话很容易引起误解，“天道无亲，常与善人。”在第五章曾经讲过，“天地不仁，以万物为刍狗”，天地是没有感情的，它并不因为你做了好事，就来奖赏你，也不因为你做了坏事，便来惩罚你。既然“天道无亲”，那为什么“常与善人”呢？又怎么把这个规律规则让那些善人能够理解，并按照它去做呢？这个事情我换一个角度让大家来理解，美国有一个报社的主编，他经常接到读者的来信，读者来信都反映一个什么问题呢？做好事不得好报。特别是其中有一个小孩就说，我弟弟什么都不干，我天天在家里干活那么勤奋，可是我妈妈就把好的东西都给我弟弟，就是喜欢他，这不是不公平吗？上帝在哪里？上帝怎么能够这么不公平？这个主编呢，一直不知道怎么解释这个问题。后来有一次，他参加了一个婚礼，新郎新娘互戴戒指，出现问题了，两人把戒指戴错手了，本来应该戴到左手，但都戴到了右手上。主持婚礼的牧师就用一种诙谐的方式说，右手已经够完美了，不用再修饰了，还是用戒指来装扮左手吧。这个主编就在那个时候领悟到一个道理：一个已经够好的人，你不用去奖励他，他已经够完美，最大的奖励是什么？就是他已经成为一个好人。天道对好人最大的奖赏是什么？放到西方的文化里边来讲，上帝对好人最大的奖赏是什么？就是让你成为一个好人，这已经就是最大的回报了。这里讲“天道无亲”，它是说天道是公平的，没有偏私的。让一个人成为一个好人，那么一个好人吃点亏，这是正常的，因为你作为一个好人，这已经就是最大“道”给你的回报了。天道是公平的，没有亲疏之分，但是，它把规律、规则赋予了那些做善事的人。做一个好人，我们免去了很多的祸端祸殃，成为一个好人——这就是对我们做好人的最大的回报，不需要其他的东西来“修饰”了。所以用“有德司契”的境界去管理、去治国，就不会有大怨；用“有德司契”的境界去为人、去处事，会让你成为一个“好人”，“福虽未至，祸已远离”。</t>
+  </si>
+  <si>
+    <t>5、49、62、73、77</t>
+  </si>
+  <si>
+    <t>【国家小人少，日子安稳，邻国到老不往来】【小国寡民 安居乐业】第八十章历来被认为是老子思想中的一个非常重要的部分——老子的理想国。大家一听都知道，在哲学上，柏拉图有《理想国》，后来就出现了康帕内拉的《太阳城》、莫尔的《乌托邦》，就是对理想社会的设定。哲学家设定理想社会都有一个非常有趣的现象：要了解人类的未来啊，先看人类的开始。因为哲学里边讲否定之否定的规律，就讲事物到最后都回归到出发点，严格地讲叫“仿佛回到出发点的运动”，是在更高的层次上重复第一阶段的某些特征，所以我们看看人类的开始。人类开始的时候，大家是平等的，所以未来人类社会的也是平等的。你看三个阶段：平等——不平等——平等。沿着这样一种哲学思路，我们来理解老子这个小国寡民，也就知道，这也是他的一种空想，但是，这种空想代表了他理想的寄托。他理想的这个国家是什么样子？别天天老打仗，别弄那么多人，大家不要经常地过多地交往，过多交往就会产生的矛盾、冲突、隔阂、战争，他想让大家和平地和谐相处，所以要把这个国家变成一个“村”。“小国寡民”，让这个国家变小，人民变少，大家就像在一个乡村里边生活。在小国寡民的理念下，他就要限定，要这样做，即使有各种器皿也不用，为什么不用呢？因为在中国的历史上有一个说法，其实和西方后来的一些思想也遥相呼应。西方有一个哲学家叫卢梭，法国的启蒙思想家，当年给法国的自然科学院写过一篇论文，获了奖，叫《科学和技术的进步使人类道德堕落》，在中国历史上也有很多人认可这种看法。庄子文章里就讲了一件关于“抱瓮老人”的事：说一次孔子带着学生去游学，子贡就看见一个老头，有这个先进的工具不用，抱着瓦罐去井里打水。当时的先进的工具是什么呢？就是辘轳，现在大家都看不见了。自己跑到井里边抱着瓦罐去打水，子贡就觉得很奇怪：这老先生怎么这么笨，辘轳就在旁边，摇一摇不就上来了吗？你自己下去干嘛呢？老先生就郑重其事地跟他讲，我的老师讲过，人如果使用机器就会有投机取巧之心，为了保持我的朴素的道德，所以我不用这个机器，不会有投机取巧之心。大家仔细思量，我们使用的工具，确实对我们的思维的方式、性格也有很大的影响，所以《道德经》讲什伯之器，不用，用最简单的工具，保持简单的心灵，保持朴素的品德。当年曾国藩在做官的时候，经常给家里边写信，告诉他儿子，你每天得下地劳动；告诉他女儿，你得给我做鞋。其实，曾国藩在乎的不是地，不是鞋子，他是觉得这样的方式，会让子女形成他要的那种性格、品德。这个东西倒是真值得研究，人类使用的工具在不断进步，千奇百怪，人要想回归到朴素的道德，就很困难。“使民重死而不远徙”，人离开家乡之后成为流民，那么很多方面就无法保证。我们前面也讲过，这国家到处都是流民，它无法稳定，因为“无恒产者无恒心”，所以你离开了自己家乡的土地，成为一个流民，这就没有办法回归到一个小国寡民的所需要的品德和素质。下边一样，“虽有舟舆，无所乘之”，这也是工具，有这个船，有这个车，不要经常去坐。我们现在也有很多人领悟出来了，打趣说，汽车是毒药，自行车是泻药，走路是补药。现在，很多人也确实奇怪，开车节省出时间了，然后回家在跑步机上跑步，这个东西确实是挺难理解，有时间走走路，不也是一种锻炼吗？下边这句话重要了，是这段话里要表达的核心意思，“虽有甲兵，无所陈之”，有军队没地方放。我不打仗，我要军队干嘛？大家注意，咱们中国的“国”字，原来氏族的时候，它是没有边界、国界的。“国”字外面这个方框是代表着城墙，“国”字的繁体字，最常用的是哪个呢？就是里边的“或”。大家仔细琢磨“或”，你看它是什么？用武器，那个“戈”不就是武器吗？用武器来看守一定的人口。这国家一出现，国家一大了，它就需要军队，所以老子为什么要小国寡民呢？不要军队，大家干脆都别打仗。在他的理想国里是没有军队存在的位置的，反对战争，祈求和平。《淮南子》里也讲了这样一件事，大禹的父亲夏鲧治国的时候，修了一座很大的城池，弄了很多的军队，结果四海有反心，诸侯都准备起来背叛。大禹即位后怎么处理的呢？他把城拆了，把军队散了，结果四海归心。其实这故事表达的也是这个意思，《淮南子》主要解读道家思想，举的这个例子也是用来印证《道德经》里讲的这一理念。“使人复结绳而用之”，有的本子叫做“民”，都一样。百姓不再用文字了，人类最早不就结绳记事吗？据说当年文字出现的时候，天雨粟，鬼夜哭。当然我们这个文明延续到今天，受惠于文字太多了，但是《道德经》里说，文字有时候也让人变得复杂，有投机取巧之心。有的人说这老子是倒退，反对文明。其实大家要理解他的苦心，他主要是让人类回归到那种朴素的、平等的、和谐的、互相不冲突的理想国的状态。我们换一个角度给大家一个直观的印象，大家都知道陶渊明的《桃花源记》，那里的人都是什么样？都活得非常的和谐，“甘其食”，吃什么都觉得很香，不挑剔。“美其服”，不是说穿着漂亮的衣服，是穿什么衣服都觉得很好，都觉得很开心。“安其居，乐其俗”，安居乐业，觉得自己那个风俗大家很喜欢，很开心。“邻国相望”，因为现在搞得这国家都跟一个村子一样，国与国之间不打仗了，邻国相望，离得很近，“鸡犬之声相闻”。读《桃花源记》，很多的时候，你能感觉到这一章的影子，“狗吠深巷里，鸡鸣桑树颠”。老子也给我们勾画了一个美丽的，看似平凡但不可企及的生活。当然，“民至老死不相往来”，不是强调不相往来，而是强调没冲突、不打仗。这一章的核心是这句话：“虽有甲兵，无所陈之。”春秋无义战，那时候战争此起彼伏，没一场是正义的战争，尸横遍野，血流成河。在这个背景下，老子就想这解决办法是什么呢？国家小一点，各过各的日子，不打仗。哲学家讲的理想国，不管是柏拉图的《理想国》、康帕内拉的《太阳城》、莫尔的《乌托邦》，还是老子讲的这个小国寡民，还是陶渊明讲的《桃花源记》，都代表着对纷乱社会的不满，都希望人类回归和谐相处的、没有冲突的、没有战争的状态。如果我们理解中国历史上的非常沉痛的两句诗，我们也就明白“小国寡民”的良苦之用心，这两句诗叫“宁做太平犬，不做乱世人”，宁可做太平世界的一条狗，也不做乱世冲突、战争频仍时候的人，因为这时候人活得连狗都不如，没有尊严。所以我常讲，有些经常叫嚣战争的人，其实都是不懂战争。真正懂得战争的残忍，就知道这和平、平静，是多么可贵。大家上中学的时候学过一篇课文，叫《最可爱的人》，里边讲的一段话让人非常有同感。它说也许你正走在去上班的路上，也许你正背着书包走在上学的路上，你觉得这很平常，可是从朝鲜回来的人会告诉你，你是生活在幸福之中。经历过战争的人会告诉你，这种情况是生活在幸福之中。这对我们也有所启示，不能简单地说小国寡民是一个倒退，得看它的现实背景，得了解它的语境，我们才能真正地理解老子的用心，我们对这些历史上有智慧的人、有慈悲心肠的人，对他们才能有深深的敬佩。见到这样有智慧、有品德的人，我们身体不在鞠躬，心灵在鞠躬。读这样的书也是一样，我们应该有敬畏，在敬畏的基础上，认真阅读，认真品味，珍惜和平与幸福的生活。</t>
+  </si>
+  <si>
+    <t>17、19、37、57</t>
+  </si>
+  <si>
+    <t>【真话不好听，做好事不争夺】【信言不美 为而不争】说起《道德经》的分章，大家一般认为最早是河上公以九九归一为神秘的数字指向，把它分成了八十一章。第八十一章可以看作是全书的总结，全书思想的总结和概括就是最后这两句话，“天之道，利而不害。”天道如此，人道应该效法天道，所以下一句“圣人之道，为而不争”，一个好的领导人、统治者是如此，对我们大家来讲也是如此。韩国有一个连任联合国秘书长的聪明人，叫潘基文。他在连任就职典礼上，开口讲的就是《道德经》的这两句话，只不过他引用的是这两句话中的八个字：“利而不害，为而不争。”我怎么做联合国秘书长？我对大家有利，不起坏心，为大家谋福利，“利而不害”。我把事情做了，不为自己争名夺利，“为而不争”。我们应该有一个非常深刻的体验：道家并不是消极的、被动的、什么事都不做。什么叫无为？“为而不争”是无为的一个重要的方面，这可以看作是全部《道德经》的核心的总结。我们回头去想，“上善若水”讲“善利万物而不争”；天道讲“为而不争”。这样我们就把整个的思想落地了，知道了《道德经》最后的核心落在什么地方。现在来看一下原文，“信言不美，美言不信”，真正诚信的话，不漂亮，只会讲漂亮话的，没诚信，过度漂亮的话里，往往隐含欺骗的内容，所以大家说，真理是朴素的，真理是赤裸裸的。“善者不辩，辩者不善”，真正善良的人，不老去争辩。庄子在他文章里边经常讲，老去靠争辩，争辩胜了，又能够体现什么？“善者不辩，辩者不善”，老去争辩，老为自己找借口，老觉得自己受了无尽的委屈，这个不是善良者的表现。“知者不博，博者不知”，一个有智慧的人，不是老是吹嘘自己渊博、博学、无所不知，老是吹嘘自己无所不知的人，其实是没有智慧的。下面就讲一个有智慧的领导者应该怎么去做事。“圣人不积”，一个有智慧的领导者，不是老想着去积累财富、有形的资产。“既以为人，己愈有”，什么叫做富？什么叫做有？我老去帮助别人，为别人做事，在给别人做事情，帮助别人的过程中，获得了无尽的快乐，这不是无形资产吗？这不是精神世界的充盈吗？“既以与人，己愈多”，给别人的越多，帮别人的越多，要财富发挥它的真正的作用，在“舍”的过程中反而自己得到更多。“既以为人，己愈有；既以与人，己愈多。”2014年习近平在斐济《斐济时报》发表署名文章，也用过这两句话。中国人喜欢双赢，帮助别人。我们的理念是什么？我们给别人做的事情越多，我们感觉到自己越富有；对别人帮得越多，感觉到自己获得的更多。所以我们经常讲，我们很多的快乐是在帮助别人成长，别人有困难的时候，我们帮扶的时候，感觉到自己的内心的充盈快乐。“为人”是什么？“与人”是什么？是善利。看似付出，自己反而获得更多，自己的精神世界也更为充盈。如果我们只一味地为自己积累财富，结果呢？我们经常讲一句话，叫穷得只剩下钱了，我们的物质世界越发达，财富越多，我们的精神家园就越花果飘零。“善利万物而不争”，这是全书的最后总结。不争什么？不争言语的漂亮，只为了它的实质；不为了争辩的胜利，只为它的真理；不吹嘘自己的知识的渊博，只让知识发挥它正确的作用；不积累那么多所谓的财富，而是让财富发挥它真正的作用，让我们的精神世界越来越充盈、越来越丰富。帮人越多，自己越富有；给人越多，自己获得越多。舍得、舍得，舍的同时，也是一种获得；帮人的过程，也是一种快乐。“既以为人，己愈有；既以与人，己愈多”，这两句话仔细思量，其即是天道。“天之道，利而不害”，天道如此，善利万物不起坏心。“圣人之道，为而不争”，把事情做了，不为自己争名夺利。“为而不争”和前面我们讲过的“善利万物而不争”、“生而不有，为而不恃，长而不宰”、“功成而弗居”、“衣养万物而不为主”，这些重要的语句遥相呼应。这样，我们就把思想穿成了一串珍珠，看清楚了这本书的真正的逻辑，也看清了这本书的“落脚点”。这些成为我们生活中的座右铭，指南针，对我们的思维方式、人生格局、精神境界都会有很大的启发和启迪。第八十一章的内容，我们解读完了。到这最后一章，我们看到这一章最后落在这句话上“圣人之道，为而不争”，可以清楚的看到这本经典的目的就是把士和王修养、培养成圣。这就是这本书的内在逻辑，也是老子的良苦用心。读这本经典要掌握以下几个关键性问题。一是《道德经》本质上是一本对话体，也就是对面坐着人问的问题。只不过老子在刻书时把对面坐的人是谁、问的什么问题都省略了，而只是把他当时给的答案概括、总结、提炼、升华形成的一本著作。当我们从书里找到士、王、圣这三类问问题的人时，也就很容易抓住问题的关键了。二是王弼本《道德经》哲学思维水平非常高。在第一章就提出有无相互统一思维方式的重要性，并指出“无”是全书的众妙之门，从而让我们清楚地知道了无为、无声、无色、无味、无色……在这本书中的重要性，也借此步入众妙之门。三是我们这种以经解经的方法前后参照，避免了八十一章本子的“碎片化”倾向，并且在通篇解读中发现了老子对他认为重要问题的强调方式：首先是用重复的方式强调。比如在第十章、第五十章都重复出现“生而不有，为而不恃，长而不宰”，并且在第二章、第三十四章也都出现类似的意思。其次是用首尾呼应的方式来强调，比如二十二章就是如此。其三是用正反两个方面的方式来强调一个观点的重要性，比如第六十七章就是如此。了解了上面这些导读的内容，我们再来听课、阅读，我们就会更深刻地了解这本书的深刻内容，这本“善建者不拔”的伟大经典指导下：“修之于身，其德乃真；修之于家，其德乃余；修之于乡，其德乃长；修之于国，其德乃丰；修之于天下，其德乃普。”当然即便是逐章解决了很多问题，讲的恐怕也是蜻蜓点水，就《道德经》而言，最重要的是大家自己的阅读和领悟。</t>
+  </si>
+  <si>
+    <t>7、8、23、56、66</t>
   </si>
   <si>
     <t>经第一章（1-1）</t>
@@ -2065,12 +2879,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2197,7 +3026,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
@@ -2209,34 +3038,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
@@ -2321,7 +3150,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2344,6 +3173,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2822,8 +3660,8 @@
   <dimension ref="A1:G83"/>
   <sheetFormatPr defaultColWidth="23.75" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.36111111111111" style="8" customWidth="1"/>
-    <col min="2" max="2" width="15" style="8" customWidth="1"/>
+    <col min="1" max="1" width="6.36111111111111" style="11" customWidth="1"/>
+    <col min="2" max="2" width="15" style="11" customWidth="1"/>
     <col min="3" max="3" width="59.25" style="3" customWidth="1"/>
     <col min="4" max="4" width="60.6666666666667" style="3" customWidth="1"/>
     <col min="5" max="5" width="75.25" style="3" customWidth="1"/>
@@ -2834,1839 +3672,1841 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" s="3" customFormat="1" ht="374.4" spans="1:7">
-      <c r="A2" s="10">
+      <c r="A2" s="13">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="11"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" ht="172.8" spans="1:7">
-      <c r="A3" s="10">
+      <c r="A3" s="13">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="14" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" ht="172.8" spans="1:7">
-      <c r="A4" s="10">
+      <c r="A4" s="13">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="14" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" ht="172.8" spans="1:7">
-      <c r="A5" s="10">
+      <c r="A5" s="13">
         <v>3</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="14" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" ht="172.8" spans="1:7">
-      <c r="A6" s="10">
+      <c r="A6" s="13">
         <v>4</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="14" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" ht="158.4" spans="1:7">
-      <c r="A7" s="10">
+      <c r="A7" s="13">
         <v>5</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="14">
         <v>57</v>
       </c>
     </row>
     <row r="8" ht="144" spans="1:7">
-      <c r="A8" s="10">
+      <c r="A8" s="13">
         <v>6</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="14" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="9" ht="158.4" spans="1:7">
-      <c r="A9" s="10">
+      <c r="A9" s="13">
         <v>7</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="14" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="10" ht="187.2" spans="1:7">
-      <c r="A10" s="10">
+      <c r="A10" s="13">
         <v>8</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="14" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="11" ht="158.4" spans="1:7">
-      <c r="A11" s="10">
+      <c r="A11" s="13">
         <v>9</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="14" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="12" ht="172.8" spans="1:7">
-      <c r="A12" s="10">
+      <c r="A12" s="13">
         <v>10</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="14" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="13" ht="158.4" spans="1:7">
-      <c r="A13" s="10">
+      <c r="A13" s="13">
         <v>11</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="14" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="14" ht="158.4" spans="1:7">
-      <c r="A14" s="10">
+      <c r="A14" s="13">
         <v>12</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="14" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="15" ht="187.2" spans="1:7">
-      <c r="A15" s="10">
+      <c r="A15" s="13">
         <v>13</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="11"/>
+      <c r="G15" s="14"/>
     </row>
     <row r="16" ht="172.8" spans="1:7">
-      <c r="A16" s="10">
+      <c r="A16" s="13">
         <v>14</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="14" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="17" ht="172.8" spans="1:7">
-      <c r="A17" s="10">
+      <c r="A17" s="13">
         <v>15</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="14">
         <v>26</v>
       </c>
     </row>
     <row r="18" ht="172.8" spans="1:7">
-      <c r="A18" s="10">
+      <c r="A18" s="13">
         <v>16</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="G18" s="11"/>
+      <c r="G18" s="14"/>
     </row>
     <row r="19" ht="172.8" spans="1:7">
-      <c r="A19" s="10">
+      <c r="A19" s="13">
         <v>17</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="14">
         <v>69</v>
       </c>
     </row>
     <row r="20" ht="158.4" spans="1:7">
-      <c r="A20" s="10">
+      <c r="A20" s="13">
         <v>18</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="14" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="21" ht="158.4" spans="1:7">
-      <c r="A21" s="10">
+      <c r="A21" s="13">
         <v>19</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="14" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="22" ht="187.2" spans="1:7">
-      <c r="A22" s="10">
+      <c r="A22" s="13">
         <v>20</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="14">
         <v>6</v>
       </c>
     </row>
     <row r="23" ht="172.8" spans="1:7">
-      <c r="A23" s="10">
+      <c r="A23" s="13">
         <v>21</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="14" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="24" ht="187.2" spans="1:7">
-      <c r="A24" s="10">
+      <c r="A24" s="13">
         <v>22</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="14" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="25" ht="158.4" spans="1:7">
-      <c r="A25" s="10">
+      <c r="A25" s="13">
         <v>23</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="G25" s="11"/>
+      <c r="G25" s="14"/>
     </row>
     <row r="26" ht="172.8" spans="1:7">
-      <c r="A26" s="10">
+      <c r="A26" s="13">
         <v>24</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G26" s="14">
         <v>2</v>
       </c>
     </row>
     <row r="27" ht="172.8" spans="1:7">
-      <c r="A27" s="10">
+      <c r="A27" s="13">
         <v>25</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="G27" s="14" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="28" ht="172.8" spans="1:7">
-      <c r="A28" s="10">
+      <c r="A28" s="13">
         <v>26</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="14">
         <v>15</v>
       </c>
     </row>
     <row r="29" ht="187.2" spans="1:7">
-      <c r="A29" s="10">
+      <c r="A29" s="13">
         <v>27</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="G29" s="11"/>
+      <c r="G29" s="14"/>
     </row>
     <row r="30" ht="172.8" spans="1:7">
-      <c r="A30" s="10">
+      <c r="A30" s="13">
         <v>28</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="14">
         <v>22</v>
       </c>
     </row>
     <row r="31" ht="172.8" spans="1:7">
-      <c r="A31" s="10">
+      <c r="A31" s="13">
         <v>29</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="G31" s="11"/>
+      <c r="G31" s="14"/>
     </row>
     <row r="32" ht="172.8" spans="1:7">
-      <c r="A32" s="10">
+      <c r="A32" s="13">
         <v>30</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="11">
+      <c r="G32" s="14">
         <v>31</v>
       </c>
     </row>
     <row r="33" ht="172.8" spans="1:7">
-      <c r="A33" s="10">
+      <c r="A33" s="13">
         <v>31</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="G33" s="11">
+      <c r="G33" s="14">
         <v>30</v>
       </c>
     </row>
     <row r="34" ht="172.8" spans="1:7">
-      <c r="A34" s="10">
+      <c r="A34" s="13">
         <v>32</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="G34" s="11" t="s">
+      <c r="G34" s="14" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="35" ht="172.8" spans="1:7">
-      <c r="A35" s="10">
+      <c r="A35" s="13">
         <v>33</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E35" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="G35" s="11"/>
+      <c r="G35" s="14"/>
     </row>
     <row r="36" ht="172.8" spans="1:7">
-      <c r="A36" s="10">
+      <c r="A36" s="13">
         <v>34</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="G36" s="11">
+      <c r="G36" s="14">
         <v>2</v>
       </c>
     </row>
     <row r="37" ht="158.4" spans="1:7">
-      <c r="A37" s="10">
+      <c r="A37" s="13">
         <v>35</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E37" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="G37" s="11">
+      <c r="G37" s="14">
         <v>12</v>
       </c>
     </row>
     <row r="38" ht="172.8" spans="1:7">
-      <c r="A38" s="10">
+      <c r="A38" s="13">
         <v>36</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="E38" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="G38" s="11">
+      <c r="G38" s="14">
         <v>2</v>
       </c>
     </row>
     <row r="39" ht="158.4" spans="1:7">
-      <c r="A39" s="10">
+      <c r="A39" s="13">
         <v>37</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="E39" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F39" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G39" s="11"/>
+      <c r="G39" s="14"/>
     </row>
     <row r="40" ht="187.2" spans="1:7">
-      <c r="A40" s="10">
+      <c r="A40" s="13">
         <v>38</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D40" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E40" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="G40" s="11"/>
+      <c r="G40" s="14"/>
     </row>
     <row r="41" ht="172.8" spans="1:7">
-      <c r="A41" s="10">
+      <c r="A41" s="13">
         <v>39</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C41" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="G41" s="11">
+      <c r="G41" s="14">
         <v>2</v>
       </c>
     </row>
-    <row r="42" ht="158.4" spans="1:7">
-      <c r="A42" s="10">
+    <row r="42" ht="172.8" spans="1:7">
+      <c r="A42" s="13">
         <v>40</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C42" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="D42" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E42" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="G42" s="11" t="s">
+      <c r="G42" s="14" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="43" ht="409.5" spans="1:7">
-      <c r="A43" s="10">
+      <c r="A43" s="13">
         <v>41</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D43" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="E43" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="F43" s="11" t="s">
+      <c r="F43" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="G43" s="11"/>
+      <c r="G43" s="14"/>
     </row>
     <row r="44" ht="409.5" spans="1:7">
-      <c r="A44" s="10">
+      <c r="A44" s="13">
         <v>42</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="E44" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="F44" s="11" t="s">
+      <c r="F44" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="G44" s="11" t="s">
+      <c r="G44" s="14" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="45" ht="409.5" spans="1:7">
-      <c r="A45" s="10">
+      <c r="A45" s="13">
         <v>43</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="E45" s="12" t="s">
+      <c r="E45" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="F45" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="G45" s="11"/>
+      <c r="G45" s="14"/>
     </row>
     <row r="46" ht="409.5" spans="1:7">
-      <c r="A46" s="10">
+      <c r="A46" s="13">
         <v>44</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="E46" s="12" t="s">
+      <c r="E46" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="G46" s="11"/>
+      <c r="G46" s="14"/>
     </row>
     <row r="47" ht="409.5" spans="1:7">
-      <c r="A47" s="10">
+      <c r="A47" s="13">
         <v>45</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C47" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="E47" s="12" t="s">
+      <c r="E47" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="G47" s="11">
+      <c r="G47" s="14">
         <v>25</v>
       </c>
     </row>
     <row r="48" ht="409.5" spans="1:7">
-      <c r="A48" s="10">
+      <c r="A48" s="13">
         <v>46</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="C48" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="E48" s="12" t="s">
+      <c r="E48" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="G48" s="11"/>
+      <c r="G48" s="14"/>
     </row>
     <row r="49" ht="409.5" spans="1:7">
-      <c r="A49" s="10">
+      <c r="A49" s="13">
         <v>47</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="E49" s="12" t="s">
+      <c r="E49" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F49" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="G49" s="11"/>
+      <c r="G49" s="14"/>
     </row>
     <row r="50" ht="409.5" spans="1:7">
-      <c r="A50" s="10">
+      <c r="A50" s="13">
         <v>48</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="E50" s="12" t="s">
+      <c r="E50" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="F50" s="11" t="s">
+      <c r="F50" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="G50" s="11"/>
+      <c r="G50" s="14"/>
     </row>
     <row r="51" ht="409.5" spans="1:7">
-      <c r="A51" s="10">
+      <c r="A51" s="13">
         <v>49</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="E51" s="12" t="s">
+      <c r="E51" s="15" t="s">
         <v>274</v>
       </c>
-      <c r="F51" s="11" t="s">
+      <c r="F51" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="G51" s="11"/>
+      <c r="G51" s="14"/>
     </row>
     <row r="52" ht="409.5" spans="1:7">
-      <c r="A52" s="10">
+      <c r="A52" s="13">
         <v>50</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B52" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="E52" s="12" t="s">
+      <c r="E52" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="F52" s="11" t="s">
+      <c r="F52" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="G52" s="11"/>
+      <c r="G52" s="14"/>
     </row>
     <row r="53" ht="409.5" spans="1:7">
-      <c r="A53" s="10">
+      <c r="A53" s="13">
         <v>51</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="E53" s="12" t="s">
+      <c r="E53" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="F53" s="11" t="s">
+      <c r="F53" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="G53" s="11"/>
+      <c r="G53" s="14"/>
     </row>
     <row r="54" ht="409.5" spans="1:7">
-      <c r="A54" s="10">
+      <c r="A54" s="13">
         <v>52</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B54" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="E54" s="12" t="s">
+      <c r="E54" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="F54" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="G54" s="11">
+      <c r="G54" s="14">
         <v>6</v>
       </c>
     </row>
     <row r="55" ht="409.5" spans="1:7">
-      <c r="A55" s="10">
+      <c r="A55" s="13">
         <v>53</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="D55" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="E55" s="12" t="s">
+      <c r="E55" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="G55" s="11"/>
+      <c r="G55" s="14"/>
     </row>
     <row r="56" ht="409.5" spans="1:7">
-      <c r="A56" s="10">
+      <c r="A56" s="13">
         <v>54</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B56" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="D56" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="E56" s="12" t="s">
+      <c r="E56" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="F56" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="G56" s="11"/>
+      <c r="G56" s="14"/>
     </row>
     <row r="57" ht="409.5" spans="1:7">
-      <c r="A57" s="10">
+      <c r="A57" s="13">
         <v>55</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B57" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="E57" s="12" t="s">
+      <c r="E57" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="G57" s="11"/>
+      <c r="G57" s="14"/>
     </row>
     <row r="58" ht="403.2" spans="1:7">
-      <c r="A58" s="10">
+      <c r="A58" s="13">
         <v>56</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="B58" s="13" t="s">
         <v>306</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D58" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="E58" s="12" t="s">
+      <c r="E58" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="F58" s="11" t="s">
+      <c r="F58" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="G58" s="11"/>
+      <c r="G58" s="14"/>
     </row>
     <row r="59" ht="409.5" spans="1:7">
-      <c r="A59" s="10">
+      <c r="A59" s="13">
         <v>57</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="E59" s="12" t="s">
+      <c r="E59" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="F59" s="11" t="s">
+      <c r="F59" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="G59" s="11" t="s">
+      <c r="G59" s="14" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="60" ht="409.5" spans="1:7">
-      <c r="A60" s="10">
+      <c r="A60" s="13">
         <v>58</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="B60" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="D60" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="E60" s="12" t="s">
+      <c r="E60" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="F60" s="11" t="s">
+      <c r="F60" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="G60" s="11"/>
+      <c r="G60" s="14"/>
     </row>
     <row r="61" ht="409.5" spans="1:7">
-      <c r="A61" s="10">
+      <c r="A61" s="13">
         <v>59</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="15" t="s">
         <v>323</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="E61" s="12" t="s">
+      <c r="E61" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="F61" s="11" t="s">
+      <c r="F61" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="G61" s="11"/>
+      <c r="G61" s="14"/>
     </row>
     <row r="62" ht="409.5" spans="1:7">
-      <c r="A62" s="10">
+      <c r="A62" s="13">
         <v>60</v>
       </c>
-      <c r="B62" s="10" t="s">
+      <c r="B62" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="C62" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="D62" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="E62" s="12" t="s">
+      <c r="E62" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="F62" s="11" t="s">
+      <c r="F62" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="G62" s="11"/>
+      <c r="G62" s="14"/>
     </row>
     <row r="63" ht="409.5" spans="1:7">
-      <c r="A63" s="10">
+      <c r="A63" s="13">
         <v>61</v>
       </c>
-      <c r="B63" s="10" t="s">
+      <c r="B63" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="C63" s="12" t="s">
+      <c r="C63" s="15" t="s">
         <v>333</v>
       </c>
-      <c r="D63" s="12" t="s">
+      <c r="D63" s="15" t="s">
         <v>334</v>
       </c>
-      <c r="E63" s="12" t="s">
+      <c r="E63" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="F63" s="11" t="s">
+      <c r="F63" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="G63" s="11">
+      <c r="G63" s="14">
         <v>68</v>
       </c>
     </row>
     <row r="64" ht="409.5" spans="1:7">
-      <c r="A64" s="10">
+      <c r="A64" s="13">
         <v>62</v>
       </c>
-      <c r="B64" s="10" t="s">
+      <c r="B64" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="D64" s="12" t="s">
+      <c r="D64" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="E64" s="12" t="s">
+      <c r="E64" s="15" t="s">
         <v>340</v>
       </c>
-      <c r="F64" s="11" t="s">
+      <c r="F64" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="G64" s="11"/>
+      <c r="G64" s="14"/>
     </row>
     <row r="65" ht="409.5" spans="1:7">
-      <c r="A65" s="10">
+      <c r="A65" s="13">
         <v>63</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="D65" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="E65" s="12" t="s">
+      <c r="E65" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="F65" s="11" t="s">
+      <c r="F65" s="14" t="s">
         <v>346</v>
       </c>
-      <c r="G65" s="11" t="s">
+      <c r="G65" s="14" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="66" ht="409.5" spans="1:7">
-      <c r="A66" s="10">
+      <c r="A66" s="13">
         <v>64</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="B66" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C66" s="15" t="s">
         <v>349</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D66" s="15" t="s">
         <v>350</v>
       </c>
-      <c r="E66" s="12" t="s">
+      <c r="E66" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="F66" s="11" t="s">
+      <c r="F66" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="G66" s="11">
+      <c r="G66" s="14">
         <v>63</v>
       </c>
     </row>
     <row r="67" ht="374.4" spans="1:7">
-      <c r="A67" s="10">
+      <c r="A67" s="13">
         <v>65</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B67" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="15" t="s">
         <v>354</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D67" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="E67" s="12" t="s">
+      <c r="E67" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="F67" s="11" t="s">
+      <c r="F67" s="14" t="s">
         <v>357</v>
       </c>
-      <c r="G67" s="11"/>
+      <c r="G67" s="14">
+        <v>40</v>
+      </c>
     </row>
     <row r="68" ht="409.5" spans="1:7">
-      <c r="A68" s="10">
+      <c r="A68" s="13">
         <v>66</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B68" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="D68" s="15" t="s">
         <v>360</v>
       </c>
-      <c r="E68" s="12" t="s">
+      <c r="E68" s="15" t="s">
         <v>361</v>
       </c>
-      <c r="F68" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="G68" s="11" t="s">
+      <c r="F68" s="14" t="s">
         <v>362</v>
       </c>
+      <c r="G68" s="14" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="69" ht="409.5" spans="1:7">
-      <c r="A69" s="10">
+      <c r="A69" s="13">
         <v>67</v>
       </c>
-      <c r="B69" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C69" s="12" t="s">
+      <c r="B69" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="D69" s="12" t="s">
+      <c r="C69" s="15" t="s">
         <v>365</v>
       </c>
-      <c r="E69" s="12" t="s">
+      <c r="D69" s="15" t="s">
         <v>366</v>
       </c>
-      <c r="F69" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="G69" s="11"/>
+      <c r="E69" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="F69" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="G69" s="14"/>
     </row>
     <row r="70" ht="409.5" spans="1:7">
-      <c r="A70" s="10">
+      <c r="A70" s="13">
         <v>68</v>
       </c>
-      <c r="B70" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="C70" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="D70" s="12" t="s">
+      <c r="B70" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="E70" s="12" t="s">
+      <c r="C70" s="15" t="s">
         <v>370</v>
       </c>
-      <c r="F70" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="G70" s="11">
+      <c r="D70" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="E70" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="F70" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="G70" s="14">
         <v>61</v>
       </c>
     </row>
     <row r="71" ht="409.5" spans="1:7">
-      <c r="A71" s="10">
+      <c r="A71" s="13">
         <v>69</v>
       </c>
-      <c r="B71" s="10" t="s">
-        <v>371</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="D71" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="E71" s="12" t="s">
+      <c r="B71" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="F71" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="G71" s="11">
+      <c r="C71" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="E71" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="F71" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="G71" s="14">
         <v>17</v>
       </c>
     </row>
     <row r="72" ht="409.5" spans="1:7">
-      <c r="A72" s="10">
+      <c r="A72" s="13">
         <v>70</v>
       </c>
-      <c r="B72" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="C72" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="E72" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="F72" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="G72" s="11"/>
+      <c r="B72" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="E72" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="F72" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="G72" s="14"/>
     </row>
     <row r="73" ht="409.5" spans="1:7">
-      <c r="A73" s="10">
+      <c r="A73" s="13">
         <v>71</v>
       </c>
-      <c r="B73" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="C73" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="E73" s="12" t="s">
-        <v>382</v>
-      </c>
-      <c r="F73" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="G73" s="11" t="s">
+      <c r="B73" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="E73" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="F73" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="G73" s="14" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="74" ht="374.4" spans="1:7">
-      <c r="A74" s="10">
+      <c r="A74" s="13">
         <v>72</v>
       </c>
-      <c r="B74" s="10" t="s">
-        <v>383</v>
-      </c>
-      <c r="C74" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="E74" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="F74" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="G74" s="11"/>
+      <c r="B74" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="D74" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="E74" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="F74" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="G74" s="14"/>
     </row>
     <row r="75" ht="409.5" spans="1:7">
-      <c r="A75" s="10">
+      <c r="A75" s="13">
         <v>73</v>
       </c>
-      <c r="B75" s="10" t="s">
-        <v>387</v>
-      </c>
-      <c r="C75" s="12" t="s">
-        <v>388</v>
-      </c>
-      <c r="D75" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="E75" s="12" t="s">
-        <v>390</v>
-      </c>
-      <c r="F75" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="G75" s="11"/>
+      <c r="B75" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="E75" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="F75" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="G75" s="14"/>
     </row>
     <row r="76" ht="409.5" spans="1:7">
-      <c r="A76" s="10">
+      <c r="A76" s="13">
         <v>74</v>
       </c>
-      <c r="B76" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="C76" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="E76" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="F76" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="G76" s="11"/>
+      <c r="B76" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="D76" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="E76" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="F76" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="G76" s="14"/>
     </row>
     <row r="77" ht="403.2" spans="1:7">
-      <c r="A77" s="10">
+      <c r="A77" s="13">
         <v>75</v>
       </c>
-      <c r="B77" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="C77" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>397</v>
-      </c>
-      <c r="E77" s="12" t="s">
-        <v>398</v>
-      </c>
-      <c r="F77" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="G77" s="11">
+      <c r="B77" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="C77" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="E77" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="F77" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="G77" s="14">
         <v>10</v>
       </c>
     </row>
     <row r="78" ht="409.5" spans="1:7">
-      <c r="A78" s="10">
+      <c r="A78" s="13">
         <v>76</v>
       </c>
-      <c r="B78" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="C78" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="D78" s="12" t="s">
-        <v>401</v>
-      </c>
-      <c r="E78" s="12" t="s">
-        <v>402</v>
-      </c>
-      <c r="F78" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="G78" s="11"/>
+      <c r="B78" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="D78" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="E78" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="F78" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="G78" s="14"/>
     </row>
     <row r="79" ht="409.5" spans="1:7">
-      <c r="A79" s="10">
+      <c r="A79" s="13">
         <v>77</v>
       </c>
-      <c r="B79" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="C79" s="12" t="s">
-        <v>404</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>405</v>
-      </c>
-      <c r="E79" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="F79" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="G79" s="11"/>
+      <c r="B79" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="D79" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="E79" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="F79" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="G79" s="14"/>
     </row>
     <row r="80" ht="409.5" spans="1:7">
-      <c r="A80" s="10">
+      <c r="A80" s="13">
         <v>78</v>
       </c>
-      <c r="B80" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="C80" s="12" t="s">
-        <v>408</v>
-      </c>
-      <c r="D80" s="12" t="s">
-        <v>409</v>
-      </c>
-      <c r="E80" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="F80" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="G80" s="11" t="s">
-        <v>411</v>
+      <c r="B80" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="D80" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="E80" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="F80" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="G80" s="14" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="81" ht="409.5" spans="1:7">
-      <c r="A81" s="10">
+      <c r="A81" s="13">
         <v>79</v>
       </c>
-      <c r="B81" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="C81" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="D81" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="E81" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="F81" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="G81" s="11"/>
+      <c r="B81" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="D81" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="E81" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="F81" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="G81" s="14"/>
     </row>
     <row r="82" ht="409.5" spans="1:7">
-      <c r="A82" s="10">
+      <c r="A82" s="13">
         <v>80</v>
       </c>
-      <c r="B82" s="10" t="s">
-        <v>416</v>
-      </c>
-      <c r="C82" s="12" t="s">
-        <v>417</v>
-      </c>
-      <c r="D82" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="E82" s="12" t="s">
-        <v>419</v>
-      </c>
-      <c r="F82" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="G82" s="11"/>
+      <c r="B82" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="C82" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="D82" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="E82" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="F82" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="G82" s="14"/>
     </row>
     <row r="83" ht="409.5" spans="1:7">
-      <c r="A83" s="10">
+      <c r="A83" s="13">
         <v>81</v>
       </c>
-      <c r="B83" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="C83" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="E83" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="F83" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="G83" s="11">
+      <c r="B83" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="C83" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="D83" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="E83" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="F83" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="G83" s="14">
         <v>7</v>
       </c>
     </row>
@@ -4680,6 +5520,2288 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G200"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="3.88888888888889" style="8" customWidth="1"/>
+    <col min="2" max="2" width="18.6666666666667" style="8" customWidth="1"/>
+    <col min="3" max="3" width="55.5555555555556" style="8" customWidth="1"/>
+    <col min="4" max="5" width="46.4444444444444" style="8" customWidth="1"/>
+    <col min="6" max="6" width="19.6666666666667" style="8" customWidth="1"/>
+    <col min="7" max="7" width="31" style="8" customWidth="1"/>
+    <col min="8" max="16384" width="8.88888888888889" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" ht="388.8" spans="1:7">
+      <c r="A2" s="10">
+        <v>0</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="3" ht="302.4" spans="1:7">
+      <c r="A3" s="10">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4" ht="288" spans="1:7">
+      <c r="A4" s="10">
+        <v>2</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="5" ht="273.6" spans="1:7">
+      <c r="A5" s="10">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="6" ht="273.6" spans="1:7">
+      <c r="A6" s="10">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="7" ht="259.2" spans="1:7">
+      <c r="A7" s="10">
+        <v>5</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="8" ht="230.4" spans="1:7">
+      <c r="A8" s="10">
+        <v>6</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="9" ht="273.6" spans="1:7">
+      <c r="A9" s="10">
+        <v>7</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="10" ht="302.4" spans="1:7">
+      <c r="A10" s="10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="11" ht="259.2" spans="1:7">
+      <c r="A11" s="10">
+        <v>9</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="12" ht="273.6" spans="1:7">
+      <c r="A12" s="10">
+        <v>10</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="13" ht="259.2" spans="1:7">
+      <c r="A13" s="10">
+        <v>11</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="14" ht="244.8" spans="1:7">
+      <c r="A14" s="10">
+        <v>12</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="15" ht="302.4" spans="1:7">
+      <c r="A15" s="10">
+        <v>13</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="16" ht="288" spans="1:7">
+      <c r="A16" s="10">
+        <v>14</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="17" ht="288" spans="1:7">
+      <c r="A17" s="10">
+        <v>15</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="18" ht="273.6" spans="1:7">
+      <c r="A18" s="10">
+        <v>16</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="19" ht="288" spans="1:7">
+      <c r="A19" s="10">
+        <v>17</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="20" ht="259.2" spans="1:7">
+      <c r="A20" s="10">
+        <v>18</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="21" ht="259.2" spans="1:7">
+      <c r="A21" s="10">
+        <v>19</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="22" ht="316.8" spans="1:7">
+      <c r="A22" s="10">
+        <v>20</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="23" ht="288" spans="1:7">
+      <c r="A23" s="10">
+        <v>21</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="24" ht="288" spans="1:7">
+      <c r="A24" s="10">
+        <v>22</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="25" ht="273.6" spans="1:7">
+      <c r="A25" s="10">
+        <v>23</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="26" ht="259.2" spans="1:7">
+      <c r="A26" s="10">
+        <v>24</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="27" ht="288" spans="1:7">
+      <c r="A27" s="10">
+        <v>25</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="28" ht="288" spans="1:7">
+      <c r="A28" s="10">
+        <v>26</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="29" ht="302.4" spans="1:7">
+      <c r="A29" s="10">
+        <v>27</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="30" ht="288" spans="1:7">
+      <c r="A30" s="10">
+        <v>28</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="31" ht="288" spans="1:7">
+      <c r="A31" s="10">
+        <v>29</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="32" ht="273.6" spans="1:7">
+      <c r="A32" s="10">
+        <v>30</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="33" ht="288" spans="1:7">
+      <c r="A33" s="10">
+        <v>31</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="34" ht="288" spans="1:7">
+      <c r="A34" s="10">
+        <v>32</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="35" ht="273.6" spans="1:7">
+      <c r="A35" s="10">
+        <v>33</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>506</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="36" ht="259.2" spans="1:7">
+      <c r="A36" s="10">
+        <v>34</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="37" ht="259.2" spans="1:7">
+      <c r="A37" s="10">
+        <v>35</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="38" ht="273.6" spans="1:7">
+      <c r="A38" s="10">
+        <v>36</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="39" ht="244.8" spans="1:7">
+      <c r="A39" s="10">
+        <v>37</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>514</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="40" ht="288" spans="1:7">
+      <c r="A40" s="10">
+        <v>38</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="41" ht="302.4" spans="1:7">
+      <c r="A41" s="10">
+        <v>39</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="42" ht="259.2" spans="1:7">
+      <c r="A42" s="10">
+        <v>40</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="43" ht="409.5" spans="1:7">
+      <c r="A43" s="10">
+        <v>41</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="44" ht="409.5" spans="1:7">
+      <c r="A44" s="10">
+        <v>42</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>524</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="45" ht="409.5" spans="1:7">
+      <c r="A45" s="10">
+        <v>43</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="46" ht="409.5" spans="1:7">
+      <c r="A46" s="10">
+        <v>44</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="47" ht="409.5" spans="1:7">
+      <c r="A47" s="10">
+        <v>45</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="48" ht="409.5" spans="1:7">
+      <c r="A48" s="10">
+        <v>46</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="49" ht="409.5" spans="1:7">
+      <c r="A49" s="10">
+        <v>47</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>534</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="50" ht="409.5" spans="1:7">
+      <c r="A50" s="10">
+        <v>48</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="51" ht="409.5" spans="1:7">
+      <c r="A51" s="10">
+        <v>49</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="52" ht="409.5" spans="1:7">
+      <c r="A52" s="10">
+        <v>50</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="53" ht="409.5" spans="1:7">
+      <c r="A53" s="10">
+        <v>51</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>542</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="54" ht="409.5" spans="1:7">
+      <c r="A54" s="10">
+        <v>52</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>544</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="55" ht="409.5" spans="1:7">
+      <c r="A55" s="10">
+        <v>53</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>546</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="56" ht="409.5" spans="1:7">
+      <c r="A56" s="10">
+        <v>54</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="57" ht="409.5" spans="1:7">
+      <c r="A57" s="10">
+        <v>55</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>550</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="58" ht="409.5" spans="1:7">
+      <c r="A58" s="10">
+        <v>56</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="59" ht="409.5" spans="1:7">
+      <c r="A59" s="10">
+        <v>57</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>554</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="60" ht="409.5" spans="1:7">
+      <c r="A60" s="10">
+        <v>58</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="61" ht="409.5" spans="1:7">
+      <c r="A61" s="10">
+        <v>59</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="62" ht="409.5" spans="1:7">
+      <c r="A62" s="10">
+        <v>60</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="G62" s="10" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="63" ht="409.5" spans="1:7">
+      <c r="A63" s="10">
+        <v>61</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="64" ht="409.5" spans="1:7">
+      <c r="A64" s="10">
+        <v>62</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="G64" s="10" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="65" ht="409.5" spans="1:7">
+      <c r="A65" s="10">
+        <v>63</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>566</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="G65" s="10" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="66" ht="409.5" spans="1:7">
+      <c r="A66" s="10">
+        <v>64</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="G66" s="10" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="67" ht="409.5" spans="1:7">
+      <c r="A67" s="10">
+        <v>65</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="68" ht="409.5" spans="1:7">
+      <c r="A68" s="10">
+        <v>66</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="69" ht="409.5" spans="1:7">
+      <c r="A69" s="10">
+        <v>67</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>574</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="70" ht="409.5" spans="1:7">
+      <c r="A70" s="10">
+        <v>68</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>576</v>
+      </c>
+      <c r="F70" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="71" ht="409.5" spans="1:7">
+      <c r="A71" s="10">
+        <v>69</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="72" ht="409.5" spans="1:7">
+      <c r="A72" s="10">
+        <v>70</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>580</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="73" ht="409.5" spans="1:7">
+      <c r="A73" s="10">
+        <v>71</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="74" ht="409.5" spans="1:7">
+      <c r="A74" s="10">
+        <v>72</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="F74" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="G74" s="10" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="75" ht="409.5" spans="1:7">
+      <c r="A75" s="10">
+        <v>73</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>586</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="76" ht="409.5" spans="1:7">
+      <c r="A76" s="10">
+        <v>74</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="77" ht="409.5" spans="1:7">
+      <c r="A77" s="10">
+        <v>75</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="78" ht="409.5" spans="1:7">
+      <c r="A78" s="10">
+        <v>76</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>592</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="79" ht="409.5" spans="1:7">
+      <c r="A79" s="10">
+        <v>77</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="80" ht="409.5" spans="1:7">
+      <c r="A80" s="10">
+        <v>78</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="81" ht="409.5" spans="1:7">
+      <c r="A81" s="10">
+        <v>79</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="82" ht="409.5" spans="1:7">
+      <c r="A82" s="10">
+        <v>80</v>
+      </c>
+      <c r="B82" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>600</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="83" ht="409.5" spans="1:7">
+      <c r="A83" s="10">
+        <v>81</v>
+      </c>
+      <c r="B83" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>602</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="G84" s="10"/>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="G85" s="10"/>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="G86" s="10"/>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="G87" s="10"/>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="G88" s="10"/>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="G89" s="10"/>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="G90" s="10"/>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="G91" s="10"/>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="G92" s="10"/>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="G93" s="10"/>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="G94" s="10"/>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="G95" s="10"/>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="G96" s="10"/>
+    </row>
+    <row r="97" spans="7:7">
+      <c r="G97" s="10"/>
+    </row>
+    <row r="98" spans="7:7">
+      <c r="G98" s="10"/>
+    </row>
+    <row r="99" spans="7:7">
+      <c r="G99" s="10"/>
+    </row>
+    <row r="100" spans="7:7">
+      <c r="G100" s="10"/>
+    </row>
+    <row r="101" spans="7:7">
+      <c r="G101" s="10"/>
+    </row>
+    <row r="102" spans="7:7">
+      <c r="G102" s="10"/>
+    </row>
+    <row r="103" spans="7:7">
+      <c r="G103" s="10"/>
+    </row>
+    <row r="104" spans="7:7">
+      <c r="G104" s="10"/>
+    </row>
+    <row r="105" spans="7:7">
+      <c r="G105" s="10"/>
+    </row>
+    <row r="106" spans="7:7">
+      <c r="G106" s="10"/>
+    </row>
+    <row r="107" spans="7:7">
+      <c r="G107" s="10"/>
+    </row>
+    <row r="108" spans="7:7">
+      <c r="G108" s="10"/>
+    </row>
+    <row r="109" spans="7:7">
+      <c r="G109" s="10"/>
+    </row>
+    <row r="110" spans="7:7">
+      <c r="G110" s="10"/>
+    </row>
+    <row r="111" spans="7:7">
+      <c r="G111" s="10"/>
+    </row>
+    <row r="112" spans="7:7">
+      <c r="G112" s="10"/>
+    </row>
+    <row r="113" spans="7:7">
+      <c r="G113" s="10"/>
+    </row>
+    <row r="114" spans="7:7">
+      <c r="G114" s="10"/>
+    </row>
+    <row r="115" spans="7:7">
+      <c r="G115" s="10"/>
+    </row>
+    <row r="116" spans="7:7">
+      <c r="G116" s="10"/>
+    </row>
+    <row r="117" spans="7:7">
+      <c r="G117" s="10"/>
+    </row>
+    <row r="118" spans="7:7">
+      <c r="G118" s="10"/>
+    </row>
+    <row r="119" spans="7:7">
+      <c r="G119" s="10"/>
+    </row>
+    <row r="120" spans="7:7">
+      <c r="G120" s="10"/>
+    </row>
+    <row r="121" spans="7:7">
+      <c r="G121" s="10"/>
+    </row>
+    <row r="122" spans="7:7">
+      <c r="G122" s="10"/>
+    </row>
+    <row r="123" spans="7:7">
+      <c r="G123" s="10"/>
+    </row>
+    <row r="124" spans="7:7">
+      <c r="G124" s="10"/>
+    </row>
+    <row r="125" spans="7:7">
+      <c r="G125" s="10"/>
+    </row>
+    <row r="126" spans="7:7">
+      <c r="G126" s="10"/>
+    </row>
+    <row r="127" spans="7:7">
+      <c r="G127" s="10"/>
+    </row>
+    <row r="128" spans="7:7">
+      <c r="G128" s="10"/>
+    </row>
+    <row r="129" spans="7:7">
+      <c r="G129" s="10"/>
+    </row>
+    <row r="130" spans="7:7">
+      <c r="G130" s="10"/>
+    </row>
+    <row r="131" spans="7:7">
+      <c r="G131" s="10"/>
+    </row>
+    <row r="132" spans="7:7">
+      <c r="G132" s="10"/>
+    </row>
+    <row r="133" spans="7:7">
+      <c r="G133" s="10"/>
+    </row>
+    <row r="134" spans="7:7">
+      <c r="G134" s="10"/>
+    </row>
+    <row r="135" spans="7:7">
+      <c r="G135" s="10"/>
+    </row>
+    <row r="136" spans="7:7">
+      <c r="G136" s="10"/>
+    </row>
+    <row r="137" spans="7:7">
+      <c r="G137" s="10"/>
+    </row>
+    <row r="138" spans="7:7">
+      <c r="G138" s="10"/>
+    </row>
+    <row r="139" spans="7:7">
+      <c r="G139" s="10"/>
+    </row>
+    <row r="140" spans="7:7">
+      <c r="G140" s="10"/>
+    </row>
+    <row r="141" spans="7:7">
+      <c r="G141" s="10"/>
+    </row>
+    <row r="142" spans="7:7">
+      <c r="G142" s="10"/>
+    </row>
+    <row r="143" spans="7:7">
+      <c r="G143" s="10"/>
+    </row>
+    <row r="144" spans="7:7">
+      <c r="G144" s="10"/>
+    </row>
+    <row r="145" spans="7:7">
+      <c r="G145" s="10"/>
+    </row>
+    <row r="146" spans="7:7">
+      <c r="G146" s="10"/>
+    </row>
+    <row r="147" spans="7:7">
+      <c r="G147" s="10"/>
+    </row>
+    <row r="148" spans="7:7">
+      <c r="G148" s="10"/>
+    </row>
+    <row r="149" spans="7:7">
+      <c r="G149" s="10"/>
+    </row>
+    <row r="150" spans="7:7">
+      <c r="G150" s="10"/>
+    </row>
+    <row r="151" spans="7:7">
+      <c r="G151" s="10"/>
+    </row>
+    <row r="152" spans="7:7">
+      <c r="G152" s="10"/>
+    </row>
+    <row r="153" spans="7:7">
+      <c r="G153" s="10"/>
+    </row>
+    <row r="154" spans="7:7">
+      <c r="G154" s="10"/>
+    </row>
+    <row r="155" spans="7:7">
+      <c r="G155" s="10"/>
+    </row>
+    <row r="156" spans="7:7">
+      <c r="G156" s="10"/>
+    </row>
+    <row r="157" spans="7:7">
+      <c r="G157" s="10"/>
+    </row>
+    <row r="158" spans="7:7">
+      <c r="G158" s="10"/>
+    </row>
+    <row r="159" spans="7:7">
+      <c r="G159" s="10"/>
+    </row>
+    <row r="160" spans="7:7">
+      <c r="G160" s="10"/>
+    </row>
+    <row r="161" spans="7:7">
+      <c r="G161" s="10"/>
+    </row>
+    <row r="162" spans="7:7">
+      <c r="G162" s="10"/>
+    </row>
+    <row r="163" spans="7:7">
+      <c r="G163" s="10"/>
+    </row>
+    <row r="164" spans="7:7">
+      <c r="G164" s="10"/>
+    </row>
+    <row r="165" spans="7:7">
+      <c r="G165" s="10"/>
+    </row>
+    <row r="166" spans="7:7">
+      <c r="G166" s="10"/>
+    </row>
+    <row r="167" spans="7:7">
+      <c r="G167" s="10"/>
+    </row>
+    <row r="168" spans="7:7">
+      <c r="G168" s="10"/>
+    </row>
+    <row r="169" spans="7:7">
+      <c r="G169" s="10"/>
+    </row>
+    <row r="170" spans="7:7">
+      <c r="G170" s="10"/>
+    </row>
+    <row r="171" spans="7:7">
+      <c r="G171" s="10"/>
+    </row>
+    <row r="172" spans="7:7">
+      <c r="G172" s="10"/>
+    </row>
+    <row r="173" spans="7:7">
+      <c r="G173" s="10"/>
+    </row>
+    <row r="174" spans="7:7">
+      <c r="G174" s="10"/>
+    </row>
+    <row r="175" spans="7:7">
+      <c r="G175" s="10"/>
+    </row>
+    <row r="176" spans="7:7">
+      <c r="G176" s="10"/>
+    </row>
+    <row r="177" spans="7:7">
+      <c r="G177" s="10"/>
+    </row>
+    <row r="178" spans="7:7">
+      <c r="G178" s="10"/>
+    </row>
+    <row r="179" spans="7:7">
+      <c r="G179" s="10"/>
+    </row>
+    <row r="180" spans="7:7">
+      <c r="G180" s="10"/>
+    </row>
+    <row r="181" spans="7:7">
+      <c r="G181" s="10"/>
+    </row>
+    <row r="182" spans="7:7">
+      <c r="G182" s="10"/>
+    </row>
+    <row r="183" spans="7:7">
+      <c r="G183" s="10"/>
+    </row>
+    <row r="184" spans="7:7">
+      <c r="G184" s="10"/>
+    </row>
+    <row r="185" spans="7:7">
+      <c r="G185" s="10"/>
+    </row>
+    <row r="186" spans="7:7">
+      <c r="G186" s="10"/>
+    </row>
+    <row r="187" spans="7:7">
+      <c r="G187" s="10"/>
+    </row>
+    <row r="188" spans="7:7">
+      <c r="G188" s="10"/>
+    </row>
+    <row r="189" spans="7:7">
+      <c r="G189" s="10"/>
+    </row>
+    <row r="190" spans="7:7">
+      <c r="G190" s="10"/>
+    </row>
+    <row r="191" spans="7:7">
+      <c r="G191" s="10"/>
+    </row>
+    <row r="192" spans="7:7">
+      <c r="G192" s="10"/>
+    </row>
+    <row r="193" spans="7:7">
+      <c r="G193" s="10"/>
+    </row>
+    <row r="194" spans="7:7">
+      <c r="G194" s="10"/>
+    </row>
+    <row r="195" spans="7:7">
+      <c r="G195" s="10"/>
+    </row>
+    <row r="196" spans="7:7">
+      <c r="G196" s="10"/>
+    </row>
+    <row r="197" spans="7:7">
+      <c r="G197" s="10"/>
+    </row>
+    <row r="198" spans="7:7">
+      <c r="G198" s="10"/>
+    </row>
+    <row r="199" spans="7:7">
+      <c r="G199" s="10"/>
+    </row>
+    <row r="200" spans="7:7">
+      <c r="G200" s="10"/>
+    </row>
+  </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G83" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G28"/>
@@ -4722,19 +7844,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>424</v>
+        <v>604</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>425</v>
+        <v>605</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>426</v>
+        <v>606</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>427</v>
+        <v>607</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>428</v>
+        <v>608</v>
       </c>
       <c r="G2" s="3"/>
     </row>
@@ -4743,19 +7865,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>429</v>
+        <v>609</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>430</v>
+        <v>610</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>431</v>
+        <v>611</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>432</v>
+        <v>612</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>428</v>
+        <v>608</v>
       </c>
       <c r="G3" s="4"/>
     </row>
@@ -4764,19 +7886,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>433</v>
+        <v>613</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>434</v>
+        <v>614</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>435</v>
+        <v>615</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>436</v>
+        <v>616</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>428</v>
+        <v>608</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -4785,19 +7907,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>437</v>
+        <v>617</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>438</v>
+        <v>618</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>439</v>
+        <v>619</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>440</v>
+        <v>620</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>441</v>
+        <v>621</v>
       </c>
       <c r="G5" s="4"/>
     </row>
@@ -4806,19 +7928,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>442</v>
+        <v>622</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>443</v>
+        <v>623</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>444</v>
+        <v>624</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>445</v>
+        <v>625</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>446</v>
+        <v>626</v>
       </c>
       <c r="G6" s="4"/>
     </row>
@@ -4827,19 +7949,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>447</v>
+        <v>627</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>448</v>
+        <v>628</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>449</v>
+        <v>629</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>450</v>
+        <v>630</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>451</v>
+        <v>631</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -4848,19 +7970,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>452</v>
+        <v>632</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>453</v>
+        <v>633</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>454</v>
+        <v>634</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>455</v>
+        <v>635</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>451</v>
+        <v>631</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -4869,19 +7991,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>456</v>
+        <v>636</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>457</v>
+        <v>637</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>458</v>
+        <v>638</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>459</v>
+        <v>639</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>451</v>
+        <v>631</v>
       </c>
       <c r="G9" s="4"/>
     </row>
@@ -4890,19 +8012,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>460</v>
+        <v>640</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>461</v>
+        <v>641</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>462</v>
+        <v>642</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>463</v>
+        <v>643</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>451</v>
+        <v>631</v>
       </c>
       <c r="G10" s="4"/>
     </row>
@@ -4911,19 +8033,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>464</v>
+        <v>644</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>465</v>
+        <v>645</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>466</v>
+        <v>646</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>467</v>
+        <v>647</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>468</v>
+        <v>648</v>
       </c>
       <c r="G11" s="4"/>
     </row>
@@ -4932,19 +8054,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>469</v>
+        <v>649</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>470</v>
+        <v>650</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>471</v>
+        <v>651</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>472</v>
+        <v>652</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>473</v>
+        <v>653</v>
       </c>
       <c r="G12" s="4"/>
     </row>
@@ -4953,19 +8075,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>474</v>
+        <v>654</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>475</v>
+        <v>655</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>476</v>
+        <v>656</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>477</v>
+        <v>657</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>478</v>
+        <v>658</v>
       </c>
       <c r="G13" s="4"/>
     </row>
@@ -4974,19 +8096,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>479</v>
+        <v>659</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>480</v>
+        <v>660</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>481</v>
+        <v>661</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>482</v>
+        <v>662</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>483</v>
+        <v>663</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -4995,19 +8117,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>484</v>
+        <v>664</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>485</v>
+        <v>665</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>486</v>
+        <v>666</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>487</v>
+        <v>667</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>488</v>
+        <v>668</v>
       </c>
       <c r="G15" s="4"/>
     </row>
@@ -5016,19 +8138,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>489</v>
+        <v>669</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>490</v>
+        <v>670</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>491</v>
+        <v>671</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>492</v>
+        <v>672</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>488</v>
+        <v>668</v>
       </c>
       <c r="G16" s="4"/>
     </row>
@@ -5037,19 +8159,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>493</v>
+        <v>673</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>494</v>
+        <v>674</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>495</v>
+        <v>675</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>496</v>
+        <v>676</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>488</v>
+        <v>668</v>
       </c>
       <c r="G17" s="4"/>
     </row>
@@ -5058,19 +8180,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>497</v>
+        <v>677</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>498</v>
+        <v>678</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>499</v>
+        <v>679</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>500</v>
+        <v>680</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>488</v>
+        <v>668</v>
       </c>
       <c r="G18" s="4"/>
     </row>
@@ -5079,19 +8201,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>501</v>
+        <v>681</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>502</v>
+        <v>682</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>503</v>
+        <v>683</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>504</v>
+        <v>684</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>488</v>
+        <v>668</v>
       </c>
       <c r="G19" s="4"/>
     </row>
@@ -5100,19 +8222,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>505</v>
+        <v>685</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>506</v>
+        <v>686</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>507</v>
+        <v>687</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>508</v>
+        <v>688</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>488</v>
+        <v>668</v>
       </c>
       <c r="G20" s="4"/>
     </row>
@@ -5121,19 +8243,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>509</v>
+        <v>689</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>510</v>
+        <v>690</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>511</v>
+        <v>691</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>512</v>
+        <v>692</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>513</v>
+        <v>693</v>
       </c>
       <c r="G21" s="4"/>
     </row>
@@ -5142,19 +8264,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>514</v>
+        <v>694</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>515</v>
+        <v>695</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>516</v>
+        <v>696</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>517</v>
+        <v>697</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>513</v>
+        <v>693</v>
       </c>
       <c r="G22" s="4"/>
     </row>
@@ -5163,19 +8285,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>518</v>
+        <v>698</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>519</v>
+        <v>699</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>520</v>
+        <v>700</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>521</v>
+        <v>701</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>513</v>
+        <v>693</v>
       </c>
       <c r="G23" s="4"/>
     </row>
@@ -5184,19 +8306,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>522</v>
+        <v>702</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>523</v>
+        <v>703</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>524</v>
+        <v>704</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>525</v>
+        <v>705</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>513</v>
+        <v>693</v>
       </c>
       <c r="G24" s="4"/>
     </row>
@@ -5205,19 +8327,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>526</v>
+        <v>706</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>527</v>
+        <v>707</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>528</v>
+        <v>708</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>529</v>
+        <v>709</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>513</v>
+        <v>693</v>
       </c>
       <c r="G25" s="4"/>
     </row>
@@ -5226,19 +8348,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>530</v>
+        <v>710</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>531</v>
+        <v>711</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>532</v>
+        <v>712</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>533</v>
+        <v>713</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>513</v>
+        <v>693</v>
       </c>
       <c r="G26" s="4"/>
     </row>
@@ -5247,19 +8369,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>534</v>
+        <v>714</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>535</v>
+        <v>715</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>536</v>
+        <v>716</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>537</v>
+        <v>717</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>513</v>
+        <v>693</v>
       </c>
       <c r="G27" s="4"/>
     </row>
@@ -5268,19 +8390,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>538</v>
+        <v>718</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>539</v>
+        <v>719</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>540</v>
+        <v>720</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>541</v>
+        <v>721</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>513</v>
+        <v>693</v>
       </c>
       <c r="G28" s="4"/>
     </row>
